--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="Rdecfc4dd5c1f4f19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="R2bfefe90daa4426d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="R5570409a76ef4bc4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="R4ba1f3edd33e4c01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="5" r:id="Rcb80722295364643"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="6" r:id="Rbc40f460c0174eba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="7" r:id="Rc6464d372c8145b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="8" r:id="Re07f18634ea14a3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="Rc475514a4e0444a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="R67869e4c11f44cb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="R0258a7f038464a23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="R6fbc1c14114c495b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="5" r:id="R467b95edc45347f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="6" r:id="Rbc83140bd49f4e13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="7" r:id="Re3a05694e96a48cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="8" r:id="R753f1a2348444cab"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -397,7 +397,7 @@
         <x:v>08-14 09:00</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E3" s="10" t="n">
         <x:v>788</x:v>
@@ -415,7 +415,7 @@
         <x:v>1.11</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str">
-        <x:v>2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -461,7 +461,7 @@
         <x:v>06-29 17:30</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E5" s="10" t="n">
         <x:v>67</x:v>
@@ -479,7 +479,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="J5" s="10" t="str">
-        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -525,7 +525,7 @@
         <x:v>07-20 10:00</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E7" s="10" t="n">
         <x:v>66</x:v>
@@ -543,7 +543,7 @@
         <x:v>0.99</x:v>
       </x:c>
       <x:c r="J7" s="10" t="str">
-        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -589,7 +589,7 @@
         <x:v>08-21 17:00</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E9" s="10" t="n">
         <x:v>50</x:v>
@@ -603,7 +603,7 @@
       <x:c r="H9" s="11" t="str"/>
       <x:c r="I9" s="11" t="str"/>
       <x:c r="J9" s="10" t="str">
-        <x:v>2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -611,27 +611,27 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>婆婆要我上交工资卡，我反手只留两千</x:v>
+        <x:v>我将恩人一家捡回村</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>08-09 11:00</x:v>
+        <x:v>08-13 10:00</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E10" s="10" t="n">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F10" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="G10" s="10" t="str">
-        <x:v>家庭伦理 / 逆袭打脸</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="H10" s="11" t="str"/>
       <x:c r="I10" s="11" t="str"/>
       <x:c r="J10" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-29、2026-08-30、2026-08-31、2026-09-03、2026-09-06</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-03、2026-09-04、2026-09-05、2026-09-07、2026-09-08、2026-09-09、2026-09-11、2026-09-12、2026-09-13</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -639,27 +639,27 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>我将恩人一家捡回村</x:v>
+        <x:v>婆婆要我上交工资卡，我反手只留两千</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>08-13 10:00</x:v>
+        <x:v>08-09 11:00</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="E11" s="10" t="n">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F11" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G11" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>家庭伦理 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="H11" s="11" t="str"/>
       <x:c r="I11" s="11" t="str"/>
       <x:c r="J11" s="10" t="str">
-        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-03、2026-09-04、2026-09-05、2026-09-07、2026-09-08、2026-09-09、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-29、2026-08-30、2026-08-31、2026-09-03、2026-09-06</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -667,31 +667,27 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>收租老汉</x:v>
+        <x:v>我年终奖80w降到1w9，领导却慌了</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>08-10 06:00</x:v>
+        <x:v>08-24 08:00</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="E12" s="10" t="n">
-        <x:v>121</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F12" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G12" s="10" t="str">
-        <x:v>种田囤货</x:v>
-      </x:c>
-      <x:c r="H12" s="11" t="n">
-        <x:v>1045</x:v>
-      </x:c>
-      <x:c r="I12" s="11" t="str">
-        <x:v>1.04</x:v>
-      </x:c>
+        <x:v>都市职场</x:v>
+      </x:c>
+      <x:c r="H12" s="11" t="str"/>
+      <x:c r="I12" s="11" t="str"/>
       <x:c r="J12" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -699,27 +695,31 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>一瓶奶走过两个清晨</x:v>
+        <x:v>收租老汉</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>08-18 15:11</x:v>
+        <x:v>08-10 06:00</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E13" s="10" t="n">
-        <x:v>63</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F13" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G13" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="H13" s="11" t="str"/>
-      <x:c r="I13" s="11" t="str"/>
+        <x:v>种田囤货</x:v>
+      </x:c>
+      <x:c r="H13" s="11" t="n">
+        <x:v>1045</x:v>
+      </x:c>
+      <x:c r="I13" s="11" t="str">
+        <x:v>1.04</x:v>
+      </x:c>
       <x:c r="J13" s="10" t="str">
-        <x:v>2026-08-19、2026-08-23、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -727,27 +727,27 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>我年终奖80w降到1w9，领导却慌了</x:v>
+        <x:v>一瓶奶走过两个清晨</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>08-24 08:00</x:v>
+        <x:v>08-18 15:11</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="E14" s="10" t="n">
-        <x:v>77</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F14" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G14" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="H14" s="11" t="str"/>
       <x:c r="I14" s="11" t="str"/>
       <x:c r="J14" s="10" t="str">
-        <x:v>2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-10、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-08-19、2026-08-23、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-11、2026-09-12</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -819,19 +819,19 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>看透妻子之后</x:v>
+        <x:v>姜猎娶妻之知青良缘</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>08-24 18:02</x:v>
+        <x:v>08-17 09:38</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="E17" s="10" t="n">
-        <x:v>46</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F17" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G17" s="10" t="str">
         <x:v>婚姻情感</x:v>
@@ -839,7 +839,7 @@
       <x:c r="H17" s="11" t="str"/>
       <x:c r="I17" s="11" t="str"/>
       <x:c r="J17" s="10" t="str">
-        <x:v>2026-08-23、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-10、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-09、2026-09-11、2026-09-12、2026-09-13</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -847,27 +847,27 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>重生六七：赶山狩猎养全家</x:v>
+        <x:v>看透妻子之后</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>08-25 18:00</x:v>
+        <x:v>08-24 18:02</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="E18" s="10" t="n">
-        <x:v>108</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F18" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="G18" s="10" t="str">
-        <x:v>种田囤货</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="H18" s="11" t="str"/>
       <x:c r="I18" s="11" t="str"/>
       <x:c r="J18" s="10" t="str">
-        <x:v>2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-08-23、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-10、2026-09-11、2026-09-12</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -875,27 +875,27 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>38元炒鸡风波</x:v>
+        <x:v>重生六七：赶山狩猎养全家</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>06-03 09:01</x:v>
+        <x:v>08-25 18:00</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E19" s="10" t="n">
-        <x:v>53</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F19" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G19" s="10" t="str">
-        <x:v>美食治愈 / 现实反转</x:v>
+        <x:v>种田囤货</x:v>
       </x:c>
       <x:c r="H19" s="11" t="str"/>
       <x:c r="I19" s="11" t="str"/>
       <x:c r="J19" s="10" t="str">
-        <x:v>2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-09-03、2026-09-04、2026-09-05、2026-09-07、2026-09-09、2026-09-10、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -903,27 +903,27 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>姜猎娶妻之知青良缘</x:v>
+        <x:v>38元炒鸡风波</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>08-17 09:38</x:v>
+        <x:v>06-03 09:01</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E20" s="10" t="n">
-        <x:v>62</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F20" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="G20" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>美食治愈 / 现实反转</x:v>
       </x:c>
       <x:c r="H20" s="11" t="str"/>
       <x:c r="I20" s="11" t="str"/>
       <x:c r="J20" s="10" t="str">
-        <x:v>2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-09、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-09-03、2026-09-04、2026-09-05、2026-09-07、2026-09-09、2026-09-10、2026-09-11、2026-09-12</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -987,27 +987,27 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>贪念散尽卤香</x:v>
+        <x:v>福宝治愈全世界，家有萌娃岁岁安</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>08-24 08:26</x:v>
+        <x:v>08-21 10:00</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E23" s="10" t="n">
-        <x:v>41</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="F23" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G23" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>萌宝治愈</x:v>
       </x:c>
       <x:c r="H23" s="11" t="str"/>
       <x:c r="I23" s="11" t="str"/>
       <x:c r="J23" s="10" t="str">
-        <x:v>2026-08-23、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-09、2026-09-12</x:v>
+        <x:v>2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-03、2026-09-05、2026-09-06、2026-09-12、2026-09-13</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1015,27 +1015,27 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>重生之从迎娶大小姐开始逆袭</x:v>
+        <x:v>贪念散尽卤香</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>08-23 11:00</x:v>
+        <x:v>08-24 08:26</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E24" s="10" t="n">
-        <x:v>145</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F24" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G24" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="H24" s="11" t="str"/>
       <x:c r="I24" s="11" t="str"/>
       <x:c r="J24" s="10" t="str">
-        <x:v>2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-09、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-08-23、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-09、2026-09-12</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1043,27 +1043,27 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>一瓶水，让我看清亲生女儿</x:v>
+        <x:v>重生之从迎娶大小姐开始逆袭</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>08-23 10:00</x:v>
+        <x:v>08-23 11:00</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E25" s="10" t="n">
-        <x:v>69</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="F25" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G25" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="H25" s="11" t="str"/>
       <x:c r="I25" s="11" t="str"/>
       <x:c r="J25" s="10" t="str">
-        <x:v>2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09</x:v>
+        <x:v>2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-09、2026-09-11、2026-09-12</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1071,27 +1071,27 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>乱世我家顿顿吃肉</x:v>
+        <x:v>一瓶水，让我看清亲生女儿</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
-        <x:v>08-15 04:30</x:v>
+        <x:v>08-23 10:00</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E26" s="10" t="n">
-        <x:v>54</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F26" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="G26" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="H26" s="11" t="str"/>
       <x:c r="I26" s="11" t="str"/>
       <x:c r="J26" s="10" t="str">
-        <x:v>2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-09、2026-09-10、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1164,13 +1164,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B2" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
+        <x:v>泰城错嫁</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>09-11 09:00</x:v>
+        <x:v>09-12 21:10</x:v>
       </x:c>
       <x:c r="E2" s="11" t="str"/>
       <x:c r="F2" s="11" t="str"/>
@@ -1181,19 +1181,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I2" s="11" t="n">
-        <x:v>133</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J2" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K2" s="10" t="str">
-        <x:v>年代怀旧 / 家庭伦理</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L2" s="11" t="str">
-        <x:v>阳阳动画</x:v>
+        <x:v>夜草剧场</x:v>
       </x:c>
       <x:c r="M2" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
+        <x:v>二十世纪三十年代泰国，两姐妹姐妹同日嫁人，丑妹珠珠嫁帅气宋帕，美姐南佩却配憨汉啊光。迎亲途中大象突然发情，两对新人错上婚车、错入洞房。泼辣珠珠遇上憨厚啊光，闹洞房、斗婆婆，从互殴到相守；温柔南佩遇上冷脸宋帕，假装吵架赶走宾客，从陌生到动心。两对夫妻先后离婚，珠珠与啊光携手生子，南佩闯荡成舞台名角，与宋帕久别重逢。错的人成了对的人，两对冤家，各得圆满。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1201,13 +1201,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
-        <x:v>征地我秒签跑路，全村笑我半年</x:v>
+        <x:v>回到零四年进军彩铃界</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>09-10 11:30</x:v>
+        <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str"/>
       <x:c r="F3" s="11" t="str"/>
@@ -1217,34 +1217,28 @@
       <x:c r="H3" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I3" s="11" t="n">
-        <x:v>59</x:v>
-      </x:c>
+      <x:c r="I3" s="11" t="str"/>
       <x:c r="J3" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K3" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L3" s="11" t="str">
-        <x:v>小六动漫</x:v>
-      </x:c>
-      <x:c r="M3" s="10" t="str">
-        <x:v>赵家湾迎来高速征地，村民受村长赵德厚鼓动抱团拒签，妄想抬价拿到四百五十万补偿。林远察觉当地岩溶地质暗藏线路改线风险，不顾全村嘲讽，果断签下312万补偿款，带父母搬离老家。后续高速果真改线，全村一分补偿落空。曾经嘲笑林远的村民陷入债务困境，赵德厚登门求助，林远守住底线，一家人握紧安稳生活，告诫众人抉择要靠自己。</x:v>
-      </x:c>
+      <x:c r="L3" s="11" t="str"/>
+      <x:c r="M3" s="10" t="str"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
-        <x:v>退婚从抢我车位开始</x:v>
+        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>2026-09-12</x:v>
+        <x:v>09-11 09:00</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str"/>
       <x:c r="F4" s="11" t="str"/>
@@ -1254,28 +1248,34 @@
       <x:c r="H4" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I4" s="11" t="str"/>
+      <x:c r="I4" s="11" t="n">
+        <x:v>133</x:v>
+      </x:c>
       <x:c r="J4" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K4" s="10" t="str">
-        <x:v>都市职场 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="L4" s="11" t="str"/>
-      <x:c r="M4" s="10" t="str"/>
+        <x:v>年代怀旧 / 家庭伦理</x:v>
+      </x:c>
+      <x:c r="L4" s="11" t="str">
+        <x:v>阳阳动画</x:v>
+      </x:c>
+      <x:c r="M4" s="10" t="str">
+        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
-        <x:v>带着龙凤胎：和前夫共续前缘</x:v>
+        <x:v>退婚从抢我车位开始</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-09-12</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str"/>
       <x:c r="F5" s="11" t="str"/>
@@ -1290,7 +1290,7 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="K5" s="10" t="str">
-        <x:v>古装宫廷 / 婚姻情感 / 战神异能</x:v>
+        <x:v>都市职场 / 婚姻情感</x:v>
       </x:c>
       <x:c r="L5" s="11" t="str"/>
       <x:c r="M5" s="10" t="str"/>
@@ -1300,13 +1300,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>回到零四年进军彩铃界</x:v>
+        <x:v>今天开始做裴总</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>2026-09-11</x:v>
+        <x:v>09-12 19:48</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str"/>
       <x:c r="F6" s="11" t="str"/>
@@ -1316,28 +1316,34 @@
       <x:c r="H6" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I6" s="11" t="str"/>
+      <x:c r="I6" s="11" t="n">
+        <x:v>100</x:v>
+      </x:c>
       <x:c r="J6" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K6" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L6" s="11" t="str"/>
-      <x:c r="M6" s="10" t="str"/>
+      <x:c r="L6" s="11" t="str">
+        <x:v>严墨墨</x:v>
+      </x:c>
+      <x:c r="M6" s="10" t="str">
+        <x:v>裴野低调蛰伏三年，甘愿扮作普通员工，在公司默默沉淀，面对职场非议、旁人轻视从未辩解。年会之上，他惨遭当众开除，相伴多年的婚姻也走向终点，跌入人生低谷。褪去伪装，他不再刻意隐忍，解锁真实身份，告别敷衍度日的过往。一路轻松逆袭，打破所有人的偏见，凭自身实力惊艳全场，开启属于自己的全新人生。</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
-        <x:v>假老板娘遇上真董事长</x:v>
+        <x:v>误救高冷校花，她爷爷非要我做孙女婿</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-09-12</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str"/>
       <x:c r="F7" s="11" t="str"/>
@@ -1352,7 +1358,7 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="K7" s="10" t="str">
-        <x:v>都市职场 / 现实反转</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="L7" s="11" t="str"/>
       <x:c r="M7" s="10" t="str"/>
@@ -1362,13 +1368,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
-        <x:v>大坝边寻回的真千金</x:v>
+        <x:v>装傻下山</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>09-10 11:26</x:v>
+        <x:v>2026-09-12</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str"/>
       <x:c r="F8" s="11" t="str"/>
@@ -1378,34 +1384,28 @@
       <x:c r="H8" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I8" s="11" t="n">
-        <x:v>53</x:v>
-      </x:c>
+      <x:c r="I8" s="11" t="str"/>
       <x:c r="J8" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K8" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L8" s="11" t="str">
-        <x:v>喵琪琪追剧</x:v>
-      </x:c>
-      <x:c r="M8" s="10" t="str">
-        <x:v>大坝突发险情，农村女孩夏晚禾凭借熟悉的环境和过人的勇气，不顾危险救下被困的沈长洲。一次意外的救援，让两个陌生人的命运重新交织。随着调查深入，沈长洲发现这个善良坚韧的女孩，竟是自己失散二十年的亲生女儿。面对迟来的亲情和真假千金的风波，夏晚禾没有依靠身份改变人生，而是用智慧、担当和努力证明自己的价值。陆言川也在一次次并肩相处中，被她的真诚与坚强打动，陪她找回亲情，走向新的未来。</x:v>
-      </x:c>
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="L8" s="11" t="str"/>
+      <x:c r="M8" s="10" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
-        <x:v>我的眼睛变成了透视神瞳</x:v>
+        <x:v>七套房产，换来一纸调令</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>09-11 11:00</x:v>
+        <x:v>09-12 08:18</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str"/>
       <x:c r="F9" s="11" t="str"/>
@@ -1416,19 +1416,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I9" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J9" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K9" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L9" s="11" t="str">
-        <x:v>奇迹漫剧</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="M9" s="10" t="str">
-        <x:v>罗川本是四处奔波的废品回收从业者，日子过得窘迫潦倒。一次意外，他觉醒透视异能，双眼能够看穿物件内里，辨明真伪与隐藏价值。凭借这份神异能力，他在旧货市场、废品堆里频频捡漏，屡屡发现被人忽视的珍宝。从被旁人轻视的底层小人物，他一步步积累财富与阅历，在古玩鉴宝圈崭露头角，破除无数圈套骗局，逆袭成受人敬重的顶尖鉴宝高手，改写了自己的平凡人生。</x:v>
+        <x:v>公婆将七套房产全数赠予小叔子，长子陈峰看似顺从鼓掌，实则暗中申请援疆调令。面对父母偏心和弟媳挑衅，陈峰携妻林晚隐忍筹备。最终在家庭会议上，他出示双人调令宣告远赴新疆，打破原生家庭剥削链条。经历异地磨砺与除夕和解，一家人终在理解中重建亲情边界，实现各自独立与成长。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1436,13 +1436,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
-        <x:v>灵猴伴神葫</x:v>
+        <x:v>锦书迟</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>09-10 19:31</x:v>
+        <x:v>09-12 07:30</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str"/>
       <x:c r="F10" s="11" t="str"/>
@@ -1453,19 +1453,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I10" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J10" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K10" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L10" s="11" t="str">
-        <x:v>青禾故事</x:v>
+        <x:v>咩咩漫文</x:v>
       </x:c>
       <x:c r="M10" s="10" t="str">
-        <x:v>遭遇百日大旱，老汉心怀仁善，半瓢清水唤醒神树，得宝葫芦济世救人。面对贪婪财主的觊觎破坏，天上丰年母穗濒临枯萎。危难之时，村民同心，自愿献出百家粮回馈天地，贪念缠身的钱万贯也幡然醒悟，献出粮种弥补过错。母穗复苏，甘霖普降。众人懂得神物只能解一时之急，唯有脚踏实地耕耘劳作，守望相助，方能守住岁岁安稳的烟火日子。</x:v>
+        <x:v>三年前，沈昭昭嫁与永宁侯谢凛，新婚燕尔他便远赴边关。她苦等家书，却不知双向书信早被人暗中截留。她终于心冷离开侯府。三年后，她带着孩子在市井支摊卖画立足，他却循着蛛丝马迹寻来，真相层层揭开，原来他从未负她。</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1473,13 +1473,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C11" s="10" t="str">
-        <x:v>我拿下1.2亿订单公司只给3千块</x:v>
+        <x:v>当初闹着算清账目，我答应后他退休金见了底</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>09-11 06:30</x:v>
+        <x:v>09-12 08:00</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str"/>
       <x:c r="F11" s="11" t="str"/>
@@ -1490,19 +1490,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I11" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J11" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K11" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="L11" s="11" t="str">
-        <x:v>呆哥说漫</x:v>
+        <x:v>小狐狸剧场</x:v>
       </x:c>
       <x:c r="M11" s="10" t="str">
-        <x:v>连续五年蝉联销售冠军的陈志远，苦跟两年拿下1亿2订单，却只收到3280元提成。公司临时改制，将客户划给副总裁外甥周凯，夺走他的九十六万提成。陈志远离职后，客户因失去真正服务者纷纷暂停合作，公司却倒打一耙，指控他带客并索赔三千万元。董事会调查中，制度、合同、伪造邮件和聊天证据接连浮出水面，周建华的利益输送与甩锅阴谋曝光。陈志远洗清污名，追回提成，也让公司重建公平规则。</x:v>
+        <x:v>许宁嫁入孟家四年，包揽房贷、学费与婆婆医药费，却从未被看见。饭桌上，公公孟栋泽手握六千八退休金，当众提出分家。无人反对，许宁也坦然应允。所有人都以为她是被供养的闲人，直到分家后，她默默停掉所有开支。断水断电、房贷逾期、催缴单纷至沓来，这个家一夜停摆。当真相浮出水面，他们才惊觉，被轻视的儿媳才是唯一的支柱。</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1510,13 +1510,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
-        <x:v>当初闹着算清账目，我答应后他退休金见了底</x:v>
+        <x:v>深宫锁狐：陛下您的皇儿是妖</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>09-12 08:00</x:v>
+        <x:v>09-12 19:00</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str"/>
       <x:c r="F12" s="11" t="str"/>
@@ -1527,19 +1527,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I12" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J12" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K12" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="L12" s="11" t="str">
-        <x:v>小狐狸剧场</x:v>
+        <x:v>观月剧场</x:v>
       </x:c>
       <x:c r="M12" s="10" t="str">
-        <x:v>许宁嫁入孟家四年，包揽房贷、学费与婆婆医药费，却从未被看见。饭桌上，公公孟栋泽手握六千八退休金，当众提出分家。无人反对，许宁也坦然应允。所有人都以为她是被供养的闲人，直到分家后，她默默停掉所有开支。断水断电、房贷逾期、催缴单纷至沓来，这个家一夜停摆。当真相浮出水面，他们才惊觉，被轻视的儿媳才是唯一的支柱。</x:v>
+        <x:v>皇子一到夜里就变白狐，苏晚禾提心吊胆藏了五年。直到皇帝破门而入，头顶竟也冒出狐耳！她这才知儿子是天狐血脉。贤妃带兵逼宫要诛妖，她反手布局，当众撕开真相，掀翻后宫。可最后她发现自己也是月狐之后，全家都是狐狸！</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1547,13 +1547,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B13" s="11" t="n">
-        <x:v>31</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
-        <x:v>赶海人生：重回1983小渔村</x:v>
+        <x:v>我的眼睛变成了透视神瞳</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
-        <x:v>09-10 08:55</x:v>
+        <x:v>09-11 11:00</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str"/>
       <x:c r="F13" s="11" t="str"/>
@@ -1564,19 +1564,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I13" s="11" t="n">
-        <x:v>158</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="J13" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K13" s="10" t="str">
-        <x:v>年代怀旧 / 种田囤货</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="L13" s="11" t="str">
-        <x:v>梦落漫漫</x:v>
+        <x:v>奇迹漫剧</x:v>
       </x:c>
       <x:c r="M13" s="10" t="str">
-        <x:v>前世杨建国跳海离世，意外重生回到1983年东沟小渔村。这一年开海祭龙王，妻子即将遭遇毒蛇险境，家中穷困潦倒，伯父还妄图霸占自家渔船。曾经的街溜子幡然醒悟，凭借超前记忆踏海赶海，捕捞对虾、鲍鱼，对抗邻里刁难，守护妻儿老小，在汹涌海潮之中改写一家人贫苦命运。</x:v>
+        <x:v>罗川本是四处奔波的废品回收从业者，日子过得窘迫潦倒。一次意外，他觉醒透视异能，双眼能够看穿物件内里，辨明真伪与隐藏价值。凭借这份神异能力，他在旧货市场、废品堆里频频捡漏，屡屡发现被人忽视的珍宝。从被旁人轻视的底层小人物，他一步步积累财富与阅历，在古玩鉴宝圈崭露头角，破除无数圈套骗局，逆袭成受人敬重的顶尖鉴宝高手，改写了自己的平凡人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1584,13 +1584,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B14" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
-        <x:v>三分钱的取舍</x:v>
+        <x:v>恰逢其时的婚约</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>09-10 17:29</x:v>
+        <x:v>09-11 13:35</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str"/>
       <x:c r="F14" s="11" t="str"/>
@@ -1601,19 +1601,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I14" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J14" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K14" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L14" s="11" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>听闻木东</x:v>
       </x:c>
       <x:c r="M14" s="10" t="str">
-        <x:v>青石沟果农为省下代办三分钱，甩开中间商周成岳，直接对接收购商方洪生收桃。可脱离周成岳统筹调度后，摘桃、排单、装车乱象丛生，桃子积压损耗。周成岳转身接手偏远的十里湾桃园，凭口碑站稳脚跟。经历一季波折，青石沟众人幡然醒悟，重新读懂代办的价值。</x:v>
+        <x:v>从乡下被接回豪门的柳晨，对继承家业毫无兴趣，只想靠自己的本事踏实赚钱。一次家族联姻，让他与外表强势、内心孤独的顾晴岚成为“合同夫妻”。从互相试探到并肩面对误解与困境，柳晨始终守住底线、重情重义，用责任与真诚赢得尊重，也让顾晴岚重新相信感情。两个原本各有所求的人，在相互扶持中收获成长，也明白了财富有价，真心、担当与尊严无价。</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1621,13 +1621,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B15" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
-        <x:v>分家受辱,我竟是龙城龙主</x:v>
+        <x:v>重生山火前，我舍祖宅护全家</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
-        <x:v>2026-09-11</x:v>
+        <x:v>09-12 16:06</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str"/>
       <x:c r="F15" s="11" t="str"/>
@@ -1637,28 +1637,34 @@
       <x:c r="H15" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I15" s="11" t="str"/>
+      <x:c r="I15" s="11" t="n">
+        <x:v>89</x:v>
+      </x:c>
       <x:c r="J15" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K15" s="10" t="str">
-        <x:v>战神异能</x:v>
-      </x:c>
-      <x:c r="L15" s="11" t="str"/>
-      <x:c r="M15" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L15" s="11" t="str">
+        <x:v>千鹤动漫</x:v>
+      </x:c>
+      <x:c r="M15" s="10" t="str">
+        <x:v>顾长河带着前世山火中痛失全家的记忆重生归来，得知三日后西岭大火将再次席卷村庄，他不顾众人质疑，卖掉祖宅，带着妻子母亲和儿子搬上白石坡，储水备粮清出防火带，只为改写一家人的命运，当烈火真正逼近，所有人终于明白，他舍掉的只是房子，拼命守住的才是真正的家。</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C16" s="10" t="str">
-        <x:v>锦书迟</x:v>
+        <x:v>我拿下1.2亿订单公司只给3千块</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
-        <x:v>09-12 07:30</x:v>
+        <x:v>09-11 06:30</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str"/>
       <x:c r="F16" s="11" t="str"/>
@@ -1669,19 +1675,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I16" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J16" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K16" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="L16" s="11" t="str">
-        <x:v>咩咩漫文</x:v>
+        <x:v>呆哥说漫</x:v>
       </x:c>
       <x:c r="M16" s="10" t="str">
-        <x:v>三年前，沈昭昭嫁与永宁侯谢凛，新婚燕尔他便远赴边关。她苦等家书，却不知双向书信早被人暗中截留。她终于心冷离开侯府。三年后，她带着孩子在市井支摊卖画立足，他却循着蛛丝马迹寻来，真相层层揭开，原来他从未负她。</x:v>
+        <x:v>连续五年蝉联销售冠军的陈志远，苦跟两年拿下1亿2订单，却只收到3280元提成。公司临时改制，将客户划给副总裁外甥周凯，夺走他的九十六万提成。陈志远离职后，客户因失去真正服务者纷纷暂停合作，公司却倒打一耙，指控他带客并索赔三千万元。董事会调查中，制度、合同、伪造邮件和聊天证据接连浮出水面，周建华的利益输送与甩锅阴谋曝光。陈志远洗清污名，追回提成，也让公司重建公平规则。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1689,13 +1695,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>46</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C17" s="10" t="str">
-        <x:v>重生1985年，赶海我有系统</x:v>
+        <x:v>敢抢我的车位</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
-        <x:v>09-11 07:00</x:v>
+        <x:v>09-11 18:00</x:v>
       </x:c>
       <x:c r="E17" s="11" t="str"/>
       <x:c r="F17" s="11" t="str"/>
@@ -1706,19 +1712,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I17" s="11" t="n">
-        <x:v>132</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J17" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K17" s="10" t="str">
-        <x:v>种田囤货 / 战神异能</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="L17" s="11" t="str">
-        <x:v>依语动漫</x:v>
+        <x:v>石爷剧场</x:v>
       </x:c>
       <x:c r="M17" s="10" t="str">
-        <x:v>八十年代小渔村，林舟出钱出力帮家里盖起红砖新房，落成之日却遭到父母兄长算计，新房被夺走，自己只分得被搬空的破旧老屋。带着前世被家人压榨到老的遗憾，重活一世的林舟不再愚孝，请来村长当众分家切割亲缘。绝境之中，他意外激活渔业情报系统，可以接收大海给出的渔获线索。他借得工具赶海，捞获珍贵大石斑鱼赚取第一笔启动资金，又约上好友李二狗大雾天冒险出海，依靠系统指引追逐鱼群。</x:v>
+        <x:v>蒋依依低调返乡履行婚约，却在王氏集团门口因停车问题，与柳如烟和未婚夫王霸产生误会。随着双方接触加深，婚约背后的分歧也逐渐显现。面对王霸前后不同的态度，蒋依依选择坚持自己的原则，果断结束这段并不合适的关系。与此同时，一场意外车辆纠纷也进入正式处理程序。原本普通的一次停车风波，让几个人重新认识彼此，也让蒋依依更加坚定了自己的选择。</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1729,52 +1735,58 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C18" s="10" t="str">
-        <x:v>一张废票毁了她</x:v>
+        <x:v>穿越七零:月季花开</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>2026-09-11</x:v>
+        <x:v>09-11 22:25</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str"/>
       <x:c r="F18" s="11" t="str"/>
       <x:c r="G18" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H18" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I18" s="11" t="str"/>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I18" s="11" t="n">
+        <x:v>219</x:v>
+      </x:c>
       <x:c r="J18" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K18" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L18" s="11" t="str"/>
-      <x:c r="M18" s="10" t="str"/>
+        <x:v>年代怀旧</x:v>
+      </x:c>
+      <x:c r="L18" s="11" t="str">
+        <x:v>维维动画</x:v>
+      </x:c>
+      <x:c r="M18" s="10" t="str">
+        <x:v>女知青白月季意外穿进书中，原主本打算上山打掉腹中孩子。清醒过来的她选择接受命运，不再执念过往的情缘，决定和周野好好过日子。周野看似粗犷，实则重情重义，满心珍视白月季。二人携手扎根乡村，对抗邻里闲言碎语，努力耕耘生活。白月季凭借文笔投稿赚取稿费，周野踏实打拼养家，还迎来双胞胎。在柴米烟火里互相扶持，跨过重重风波，把平凡的农家日子过得滚烫又幸福。</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C19" s="10" t="str">
-        <x:v>人间归暖意</x:v>
+        <x:v>破麻袋里的亿万人生</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
-        <x:v>09-10 18:00</x:v>
+        <x:v>09-11 15:30</x:v>
       </x:c>
       <x:c r="E19" s="11" t="str"/>
       <x:c r="F19" s="11" t="str"/>
       <x:c r="G19" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H19" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J19" s="10" t="str">
         <x:v>其他</x:v>
@@ -1783,10 +1795,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L19" s="11" t="str">
-        <x:v>丛逸鑫漫剧</x:v>
+        <x:v>小博漫剧社</x:v>
       </x:c>
       <x:c r="M19" s="10" t="str">
-        <x:v>陆时衍提前回国，发现坐月子的妻子和刚出生的女儿受了委屈。七年求子来之不易，他决心守护好这个家。查清一桩陈年旧事后，他逐步纠正家中不当做法，理清公司事务，让该担责的人受到应有处理。真相水落石出，妻子得回公道，家也回归温暖平静。</x:v>
+        <x:v>失踪二十年的方小树因幼年被人贩子打伤，长期神志不清、沿街流浪。一次跳河救下海城富商顾振山的孙子，他得到七百万元谢礼，也意外回到方家。亲大哥方志强、二姐方玉梅只惦记他的钱，三姐方秀兰却始终护着他。受伤恢复记忆后，方小树选择继续装傻看清人心，并凭眼光投资远芯科技，从乞丐逆袭成身家过亿的股东。沈家千金沈清月因十八年前的救命之恩找到他，从报恩走向真爱。最终方小树认祖归宗、清算恶亲与幕后黑手</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1794,36 +1806,36 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C20" s="10" t="str">
-        <x:v>家有新章</x:v>
+        <x:v>我的师兄全是修仙界大佬</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>09-10 09:00</x:v>
+        <x:v>09-11 18:16</x:v>
       </x:c>
       <x:c r="E20" s="11" t="str"/>
       <x:c r="F20" s="11" t="str"/>
       <x:c r="G20" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H20" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I20" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="J20" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K20" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="L20" s="11" t="str">
-        <x:v>尔尔剧场</x:v>
+        <x:v>大公鸡剧场</x:v>
       </x:c>
       <x:c r="M20" s="10" t="str">
-        <x:v>新婚回门日，新媳妇秦麦穗因拒被大伯母郭凤英拿捏、不让丈夫无偿干活，彻底得罪大房一家。郭凤英处处刁难，断其公公杀猪活路麦穗逆势创业，靠卤味、腊肠做起小作坊，安稳养家。反观眼高手低的堂哥梁大勇，贪快钱误入骗局欠债，辛苦还债幡然醒悟。最终两家境遇悬殊，踏实肯干的秦家岁岁安稳、日子红火。</x:v>
+        <x:v>六岁的女主奉师父顾青崖之命下山历练，寻找五位失散数百年的师兄。她天生神力，把九品丹药当糖豆吃，背着重剑闯修仙界。本以为师兄们在外落魄难归，却发现大师兄是正道第一人九天仙尊，二师兄是统御九幽的幽冥帝君，余下三位也皆是绝世大佬。小奶娃一路闯荡，把隐世多年的师兄们挨个喊回了家。</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1831,73 +1843,67 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C21" s="10" t="str">
-        <x:v>穿越七零:月季花开</x:v>
+        <x:v>垃圾桶里捡到爹</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
-        <x:v>09-11 22:25</x:v>
+        <x:v>2026-09-12</x:v>
       </x:c>
       <x:c r="E21" s="11" t="str"/>
       <x:c r="F21" s="11" t="str"/>
       <x:c r="G21" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H21" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I21" s="11" t="n">
-        <x:v>219</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I21" s="11" t="str"/>
       <x:c r="J21" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K21" s="10" t="str">
-        <x:v>年代怀旧</x:v>
-      </x:c>
-      <x:c r="L21" s="11" t="str">
-        <x:v>维维动画</x:v>
-      </x:c>
-      <x:c r="M21" s="10" t="str">
-        <x:v>女知青白月季意外穿进书中，原主本打算上山打掉腹中孩子。清醒过来的她选择接受命运，不再执念过往的情缘，决定和周野好好过日子。周野看似粗犷，实则重情重义，满心珍视白月季。二人携手扎根乡村，对抗邻里闲言碎语，努力耕耘生活。白月季凭借文笔投稿赚取稿费，周野踏实打拼养家，还迎来双胞胎。在柴米烟火里互相扶持，跨过重重风波，把平凡的农家日子过得滚烫又幸福。</x:v>
-      </x:c>
+        <x:v>家庭伦理</x:v>
+      </x:c>
+      <x:c r="L21" s="11" t="str"/>
+      <x:c r="M21" s="10" t="str"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C22" s="10" t="str">
-        <x:v>七套房产，换来一纸调令</x:v>
+        <x:v>甜宝来了：空间萌宝两岁半带流放全家逆袭</x:v>
       </x:c>
       <x:c r="D22" s="11" t="str">
-        <x:v>09-12 08:18</x:v>
+        <x:v>09-11 18:26</x:v>
       </x:c>
       <x:c r="E22" s="11" t="str"/>
       <x:c r="F22" s="11" t="str"/>
       <x:c r="G22" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H22" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I22" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="J22" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K22" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>萌宝治愈 / 美食治愈 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="L22" s="11" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>喵喵看漫</x:v>
       </x:c>
       <x:c r="M22" s="10" t="str">
-        <x:v>公婆将七套房产全数赠予小叔子，长子陈峰看似顺从鼓掌，实则暗中申请援疆调令。面对父母偏心和弟媳挑衅，陈峰携妻林晚隐忍筹备。最终在家庭会议上，他出示双人调令宣告远赴新疆，打破原生家庭剥削链条。经历异地磨砺与除夕和解，一家人终在理解中重建亲情边界，实现各自独立与成长。</x:v>
+        <x:v>两岁的苦宝自幼在乡下钱家受尽苛待，到两岁时，失散的太守府叶家亲人终于寻来，将她接回身边，疼她的姥姥还将她改名为甜宝。本以为终于拥有温暖的家，但叶家却蒙冤获罪，举家流放荒疆。小小甜宝身怀奇妙能力，能和小鸟沟通，眼泪还可以疗伤。在荒凉的流放地，她用自己的方式守护姥姥、舅父与兄长，给这片土地带来粮种和希望，一家人彼此扶持，直面磨难，在荒芜之地重新闯出一片天。</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1905,36 +1911,36 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C23" s="10" t="str">
-        <x:v>我提前三天被丢进了末世</x:v>
+        <x:v>活宝老爹再赴青春，竟与女儿同上大学</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
-        <x:v>09-11 14:53</x:v>
+        <x:v>09-13 00:10</x:v>
       </x:c>
       <x:c r="E23" s="11" t="str"/>
       <x:c r="F23" s="11" t="str"/>
       <x:c r="G23" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H23" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I23" s="11" t="n">
-        <x:v>122</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J23" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K23" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="L23" s="11" t="str">
-        <x:v>白枭</x:v>
+        <x:v>长风剧场</x:v>
       </x:c>
       <x:c r="M23" s="10" t="str">
-        <x:v>暑假打工的范堃本该随全人类三天后传送至末日之地，却意外提前降临。他选中拥有“吞噬”能力的神级洞穴，可夺取其他庇护所的属性与资源。身处兽族聚居的区域，他伪装九尾天狐王族，一边猎杀腐尸提升修为、囤积灵晶，一边建立势力“天宫”招揽部属。在腐尸天灾与兽族的双重围堵中步步变强，迎战跨区域竞赛，在末世闯出属于人族的生存之路。</x:v>
+        <x:v>45岁的白烨意外激活成长系统。只要亲身体验年轻人的日常，就能重拾青春活力，还能收获丰厚奖励。为完成系统任务，他报名成人高考，顺利考入大学，竟和女儿成了同校同学。重返校园的白烨，一边认真完成任务感受青春，一边在校园里开启一段充满趣味的全新人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1942,24 +1948,24 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C24" s="10" t="str">
-        <x:v>重生后我守住全村</x:v>
+        <x:v>锚定诸天之天灾启世</x:v>
       </x:c>
       <x:c r="D24" s="11" t="str">
-        <x:v>09-10 08:08</x:v>
+        <x:v>09-12 15:39</x:v>
       </x:c>
       <x:c r="E24" s="11" t="str"/>
       <x:c r="F24" s="11" t="str"/>
       <x:c r="G24" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H24" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I24" s="11" t="n">
-        <x:v>129</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J24" s="10" t="str">
         <x:v>其他</x:v>
@@ -1968,10 +1974,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L24" s="11" t="str">
-        <x:v>金果漫剧</x:v>
+        <x:v>葡萄瓜瓜</x:v>
       </x:c>
       <x:c r="M24" s="10" t="str">
-        <x:v>70年代冬，赵满仓在父亲离世后重回鼠灾前八天。面对家中骤变，他选择先护住亲人，带着前世经验迁入碾坊，储粮备药，筑墙防鼠，设点防疫。灾情来临时，他联合李杏儿，刘石头和乡亲稳住村庄，并用账册与规矩澄清父亲名誉。风雪过后，黎家沟建起防鼠坊，猫舍和净粮地窖，众人也在互助中迎来新生。</x:v>
+        <x:v>外卖员叶锋意外遭遇意外，机缘巧合中断穿越，成为唯一留守故乡的穿越者，解锁专属系统，连通诸天万界的顶尖穿越者聊天群，群内一众万界至尊大佬，纷纷拜托他代为照看故乡的亲友，偶然展露的过人学识，让他被业内顶尖学者赏识，意外踏入顶级科研圈层，开启平凡生活里的传奇逆袭之路。</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1982,33 +1988,31 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="C25" s="10" t="str">
-        <x:v>甜宝来了：空间萌宝两岁半带流放全家逆袭</x:v>
+        <x:v>别咬，你太大只啦</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
-        <x:v>09-11 18:26</x:v>
+        <x:v>09-13 00:06</x:v>
       </x:c>
       <x:c r="E25" s="11" t="str"/>
       <x:c r="F25" s="11" t="str"/>
       <x:c r="G25" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H25" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I25" s="11" t="n">
-        <x:v>162</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="J25" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K25" s="10" t="str">
-        <x:v>萌宝治愈 / 美食治愈 / 逆袭打脸</x:v>
-      </x:c>
-      <x:c r="L25" s="11" t="str">
-        <x:v>喵喵看漫</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L25" s="11" t="str"/>
       <x:c r="M25" s="10" t="str">
-        <x:v>两岁的苦宝自幼在乡下钱家受尽苛待，到两岁时，失散的太守府叶家亲人终于寻来，将她接回身边，疼她的姥姥还将她改名为甜宝。本以为终于拥有温暖的家，但叶家却蒙冤获罪，举家流放荒疆。小小甜宝身怀奇妙能力，能和小鸟沟通，眼泪还可以疗伤。在荒凉的流放地，她用自己的方式守护姥姥、舅父与兄长，给这片土地带来粮种和希望，一家人彼此扶持，直面磨难，在荒芜之地重新闯出一片天。</x:v>
+        <x:v>邵糯原本是一个生活拮据的少女，转生成动物后反而很容易从吃饱、睡好、有人陪伴中获得幸福感。第一世，穿成萨摩耶邂逅强大的银灰狼凯尔，历经族群纷争、生老病死，在风雪之中走完一生。第二世，她变成一只布偶猫，误入山野遇见巨型亚欧猞猁凯尔，在危机四伏的松林磨合羁绊，对抗狼群，晚年被救助站收留。两世，不同物种，却始终拥有命中注定的双向羁绊，全程还有野外直播实时见证他们的故事。</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -2016,13 +2020,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B26" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C26" s="10" t="str">
-        <x:v>破麻袋里的亿万人生</x:v>
+        <x:v>废柴大师兄：师妹修炼我无敌</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
-        <x:v>09-11 15:30</x:v>
+        <x:v>09-11 11:20</x:v>
       </x:c>
       <x:c r="E26" s="11" t="str"/>
       <x:c r="F26" s="11" t="str"/>
@@ -2033,19 +2037,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I26" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="J26" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K26" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="L26" s="11" t="str">
-        <x:v>小博漫剧社</x:v>
+        <x:v>在下二蛋</x:v>
       </x:c>
       <x:c r="M26" s="10" t="str">
-        <x:v>失踪二十年的方小树因幼年被人贩子打伤，长期神志不清、沿街流浪。一次跳河救下海城富商顾振山的孙子，他得到七百万元谢礼，也意外回到方家。亲大哥方志强、二姐方玉梅只惦记他的钱，三姐方秀兰却始终护着他。受伤恢复记忆后，方小树选择继续装傻看清人心，并凭眼光投资远芯科技，从乞丐逆袭成身家过亿的股东。沈家千金沈清月因十八年前的救命之恩找到他，从报恩走向真爱。最终方小树认祖归宗、清算恶亲与幕后黑手</x:v>
+        <x:v>谁能想到终日摆烂的废柴大师兄，真实境界竟是大帝！叶玄迎来女帝转世的师妹柳如烟，顺势激活特殊系统，永久比师妹高出十个大境界，直接解锁大帝实力。他继续伪装成酒鬼混在宗门，下山途中轻松碾压前来夺舍的黑魔老怪。得知桃花镇百姓被恶虎山匪徒掳走，叶玄火速前往救人，以绝对实力击溃一众匪寇。匪首铁虎慌忙跪地求饶。可叶玄杀意已决，磅礴力量正在汇聚，铁虎能否活过这一劫？</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -2053,36 +2057,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B27" s="11" t="n">
-        <x:v>57</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C27" s="10" t="str">
-        <x:v>敢抢我的车位</x:v>
+        <x:v>今晚查寝，别开门</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
-        <x:v>09-11 18:00</x:v>
+        <x:v>09-12 23:35</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F27" s="11" t="str">
-        <x:v>↑40位</x:v>
+        <x:v>↑50位</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str"/>
       <x:c r="H27" s="11" t="str"/>
       <x:c r="I27" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J27" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K27" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L27" s="11" t="str">
-        <x:v>石爷剧场</x:v>
+        <x:v>辣妹漫剧</x:v>
       </x:c>
       <x:c r="M27" s="10" t="str">
-        <x:v>蒋依依低调返乡履行婚约，却在王氏集团门口因停车问题，与柳如烟和未婚夫王霸产生误会。随着双方接触加深，婚约背后的分歧也逐渐显现。面对王霸前后不同的态度，蒋依依选择坚持自己的原则，果断结束这段并不合适的关系。与此同时，一场意外车辆纠纷也进入正式处理程序。原本普通的一次停车风波，让几个人重新认识彼此，也让蒋依依更加坚定了自己的选择。</x:v>
+        <x:v>程妍重生回女生宿舍407遇害前二十分钟，笃定深夜“临时查寝”是致命陷阱，不顾室友质疑拼死堵门。四人合力对抗冒充宿管的歹徒，最终揪出泄露学生信息的内鬼。案件告破，四个女孩平安毕业，407一个都没少，再然后就发生了这些事。</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -2090,73 +2094,68 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B28" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C28" s="10" t="str">
-        <x:v>我拿下1.2亿订单公司只给3千块</x:v>
+        <x:v>垃圾桶里捡到爹</x:v>
       </x:c>
       <x:c r="D28" s="11" t="str">
-        <x:v>09-11 06:30</x:v>
+        <x:v>2026-09-12</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
-        <x:v>57</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F28" s="11" t="str">
-        <x:v>↑32位</x:v>
+        <x:v>↑27位</x:v>
       </x:c>
       <x:c r="G28" s="11" t="str"/>
       <x:c r="H28" s="11" t="str"/>
-      <x:c r="I28" s="11" t="n">
-        <x:v>53</x:v>
-      </x:c>
+      <x:c r="I28" s="11" t="str"/>
       <x:c r="J28" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K28" s="10" t="str">
-        <x:v>都市职场</x:v>
-      </x:c>
-      <x:c r="L28" s="11" t="str">
-        <x:v>呆哥说漫</x:v>
-      </x:c>
-      <x:c r="M28" s="10" t="str">
-        <x:v>连续五年蝉联销售冠军的陈志远，苦跟两年拿下1亿2订单，却只收到3280元提成。公司临时改制，将客户划给副总裁外甥周凯，夺走他的九十六万提成。陈志远离职后，客户因失去真正服务者纷纷暂停合作，公司却倒打一耙，指控他带客并索赔三千万元。董事会调查中，制度、合同、伪造邮件和聊天证据接连浮出水面，周建华的利益输送与甩锅阴谋曝光。陈志远洗清污名，追回提成，也让公司重建公平规则。</x:v>
-      </x:c>
+        <x:v>家庭伦理</x:v>
+      </x:c>
+      <x:c r="L28" s="11" t="str"/>
+      <x:c r="M28" s="10" t="str"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B29" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C29" s="10" t="str">
-        <x:v>甜宝来了：空间萌宝两岁半带流放全家逆袭</x:v>
+        <x:v>青牛引泉来</x:v>
       </x:c>
       <x:c r="D29" s="11" t="str">
-        <x:v>09-11 18:26</x:v>
+        <x:v>09-11 15:20</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F29" s="11" t="str">
-        <x:v>↑29位</x:v>
+        <x:v>↑18位</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str"/>
       <x:c r="H29" s="11" t="str"/>
       <x:c r="I29" s="11" t="n">
-        <x:v>162</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="J29" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K29" s="10" t="str">
-        <x:v>萌宝治愈 / 美食治愈 / 逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L29" s="11" t="str">
-        <x:v>喵喵看漫</x:v>
+        <x:v>车仔漫</x:v>
       </x:c>
       <x:c r="M29" s="10" t="str">
-        <x:v>两岁的苦宝自幼在乡下钱家受尽苛待，到两岁时，失散的太守府叶家亲人终于寻来，将她接回身边，疼她的姥姥还将她改名为甜宝。本以为终于拥有温暖的家，但叶家却蒙冤获罪，举家流放荒疆。小小甜宝身怀奇妙能力，能和小鸟沟通，眼泪还可以疗伤。在荒凉的流放地，她用自己的方式守护姥姥、舅父与兄长，给这片土地带来粮种和希望，一家人彼此扶持，直面磨难，在荒芜之地重新闯出一片天。</x:v>
+        <x:v>大旱之年，贫苦庄稼汉石满仓为宽慰盼他成家的母亲，扎了个稻草媳妇，谁料草人竟化作姑娘阿禾。原来阿禾是有灵性的青牛，十年前大旱濒死时被石满仓用豆秸和水救下，此番借稻草人身躯前来报恩。
+阿禾感知到村井即将枯竭，带领众人找到被封堵的牛眠岭古泉。靠卖自家井水牟利的马有财因利益受损，百般阻挠，甚至污染泉水、堵塞闸口。</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -2164,36 +2163,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B30" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C30" s="10" t="str">
-        <x:v>人间归暖意</x:v>
+        <x:v>恰逢其时的婚约</x:v>
       </x:c>
       <x:c r="D30" s="11" t="str">
-        <x:v>09-10 18:00</x:v>
+        <x:v>09-11 13:35</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F30" s="11" t="str">
-        <x:v>↑17位</x:v>
+        <x:v>↑18位</x:v>
       </x:c>
       <x:c r="G30" s="11" t="str"/>
       <x:c r="H30" s="11" t="str"/>
       <x:c r="I30" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J30" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K30" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L30" s="11" t="str">
-        <x:v>丛逸鑫漫剧</x:v>
+        <x:v>听闻木东</x:v>
       </x:c>
       <x:c r="M30" s="10" t="str">
-        <x:v>陆时衍提前回国，发现坐月子的妻子和刚出生的女儿受了委屈。七年求子来之不易，他决心守护好这个家。查清一桩陈年旧事后，他逐步纠正家中不当做法，理清公司事务，让该担责的人受到应有处理。真相水落石出，妻子得回公道，家也回归温暖平静。</x:v>
+        <x:v>从乡下被接回豪门的柳晨，对继承家业毫无兴趣，只想靠自己的本事踏实赚钱。一次家族联姻，让他与外表强势、内心孤独的顾晴岚成为“合同夫妻”。从互相试探到并肩面对误解与困境，柳晨始终守住底线、重情重义，用责任与真诚赢得尊重，也让顾晴岚重新相信感情。两个原本各有所求的人，在相互扶持中收获成长，也明白了财富有价，真心、担当与尊严无价。</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -2201,16 +2200,16 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B31" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C31" s="10" t="str">
-        <x:v>茅房里出来的七品官</x:v>
+        <x:v>深海之眼：我靠透视海底逆袭</x:v>
       </x:c>
       <x:c r="D31" s="11" t="str">
-        <x:v>09-11 18:08</x:v>
+        <x:v>09-12 08:30</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F31" s="11" t="str">
         <x:v>↑16位</x:v>
@@ -2218,19 +2217,19 @@
       <x:c r="G31" s="11" t="str"/>
       <x:c r="H31" s="11" t="str"/>
       <x:c r="I31" s="11" t="n">
-        <x:v>111</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="J31" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K31" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="L31" s="11" t="str">
-        <x:v>听风剧场</x:v>
+        <x:v>林八</x:v>
       </x:c>
       <x:c r="M31" s="10" t="str">
-        <x:v>大晟雁川县令沈砚川意外通过县衙茅房打通古今通道，可往返于古代与现代。面对属地蝗灾肆虐、官仓见底、流民涌入的绝境，他先到现代打工换粮救急，又组织雁川手艺人制作绣品、书法销往现代换取钱粮，陆续引入土豆良种、抽水机、微耕机，兴水利、拓荒地，与乡绅梁万山展开博弈。最终土豆丰收，州府赈灾粮抵达，雁川县成功渡过饥荒。</x:v>
+        <x:v>林凡的穷小子，在渔村替人打了三年工，老板克扣工钱，一船三万二的货，到他手里只剩两百块。他本来认命了。直到有一天，他意外发现自己能看透海底，鱼在哪里、暗礁在哪里、沉船在哪里，一清二楚。从此他开挂了。从破舢板换到小木船，从小木船换到八十米大铁船，几百斤的石斑鱼、两千斤的蓝鳍金枪鱼王，一条就卖一百万。就在人生翻盘时，一块海底捞起的铜牌，揭开了父亲十七年前失踪的真相。</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -2238,36 +2237,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B32" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C32" s="10" t="str">
-        <x:v>重生后我守住全村</x:v>
+        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
       </x:c>
       <x:c r="D32" s="11" t="str">
-        <x:v>09-10 08:08</x:v>
+        <x:v>09-13 08:00</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F32" s="11" t="str">
-        <x:v>↑14位</x:v>
+        <x:v>↑12位</x:v>
       </x:c>
       <x:c r="G32" s="11" t="str"/>
       <x:c r="H32" s="11" t="str"/>
       <x:c r="I32" s="11" t="n">
-        <x:v>129</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J32" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K32" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="L32" s="11" t="str">
-        <x:v>金果漫剧</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="M32" s="10" t="str">
-        <x:v>70年代冬，赵满仓在父亲离世后重回鼠灾前八天。面对家中骤变，他选择先护住亲人，带着前世经验迁入碾坊，储粮备药，筑墙防鼠，设点防疫。灾情来临时，他联合李杏儿，刘石头和乡亲稳住村庄，并用账册与规矩澄清父亲名誉。风雪过后，黎家沟建起防鼠坊，猫舍和净粮地窖，众人也在互助中迎来新生。</x:v>
+        <x:v>大晋七公主沈令仪，自幼被冷落于听竹宫，沉默藏锋，苟全性命。宫宴之上，太子带回的秦照雪笑盈盈提议将她送去北狄和亲。满殿以为皇帝会点头，他却掷出“废太子”三字。一夜之间，沈令仪被推到台前。北狄求和的急报恰在此时入京——与她方才所言分毫不差。可当她回望母亲遗下的那半卷秘策时，才发现这局棋，早在二十年前就已落子。</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -2275,90 +2274,78 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B33" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C33" s="10" t="str">
-        <x:v>灵猴伴神葫</x:v>
+        <x:v>反派拿捏！</x:v>
       </x:c>
       <x:c r="D33" s="11" t="str">
-        <x:v>09-10 19:31</x:v>
+        <x:v>2026-09-13</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F33" s="11" t="str">
-        <x:v>↑10位</x:v>
+        <x:v>↑12位</x:v>
       </x:c>
       <x:c r="G33" s="11" t="str"/>
       <x:c r="H33" s="11" t="str"/>
-      <x:c r="I33" s="11" t="n">
-        <x:v>56</x:v>
-      </x:c>
+      <x:c r="I33" s="11" t="str"/>
       <x:c r="J33" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K33" s="10" t="str">
-        <x:v>战神异能</x:v>
-      </x:c>
-      <x:c r="L33" s="11" t="str">
-        <x:v>青禾故事</x:v>
-      </x:c>
-      <x:c r="M33" s="10" t="str">
-        <x:v>遭遇百日大旱，老汉心怀仁善，半瓢清水唤醒神树，得宝葫芦济世救人。面对贪婪财主的觊觎破坏，天上丰年母穗濒临枯萎。危难之时，村民同心，自愿献出百家粮回馈天地，贪念缠身的钱万贯也幡然醒悟，献出粮种弥补过错。母穗复苏，甘霖普降。众人懂得神物只能解一时之急，唯有脚踏实地耕耘劳作，守望相助，方能守住岁岁安稳的烟火日子。</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L33" s="11" t="str"/>
+      <x:c r="M33" s="10" t="str"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B34" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C34" s="10" t="str">
-        <x:v>七套房产，换来一纸调令</x:v>
+        <x:v>退婚从抢我车位开始</x:v>
       </x:c>
       <x:c r="D34" s="11" t="str">
-        <x:v>09-12 08:18</x:v>
+        <x:v>2026-09-12</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F34" s="11" t="str">
         <x:v>↑9位</x:v>
       </x:c>
       <x:c r="G34" s="11" t="str"/>
       <x:c r="H34" s="11" t="str"/>
-      <x:c r="I34" s="11" t="n">
-        <x:v>60</x:v>
-      </x:c>
+      <x:c r="I34" s="11" t="str"/>
       <x:c r="J34" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K34" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L34" s="11" t="str">
-        <x:v>幻境大剧场</x:v>
-      </x:c>
-      <x:c r="M34" s="10" t="str">
-        <x:v>公婆将七套房产全数赠予小叔子，长子陈峰看似顺从鼓掌，实则暗中申请援疆调令。面对父母偏心和弟媳挑衅，陈峰携妻林晚隐忍筹备。最终在家庭会议上，他出示双人调令宣告远赴新疆，打破原生家庭剥削链条。经历异地磨砺与除夕和解，一家人终在理解中重建亲情边界，实现各自独立与成长。</x:v>
-      </x:c>
+        <x:v>都市职场 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="L34" s="11" t="str"/>
+      <x:c r="M34" s="10" t="str"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B35" s="11" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C35" s="10" t="str">
+        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
+      </x:c>
+      <x:c r="D35" s="11" t="str">
+        <x:v>09-11 09:00</x:v>
+      </x:c>
+      <x:c r="E35" s="11" t="n">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="C35" s="10" t="str">
-        <x:v>大坝边寻回的真千金</x:v>
-      </x:c>
-      <x:c r="D35" s="11" t="str">
-        <x:v>09-10 11:26</x:v>
-      </x:c>
-      <x:c r="E35" s="11" t="n">
-        <x:v>24</x:v>
       </x:c>
       <x:c r="F35" s="11" t="str">
         <x:v>↑4位</x:v>
@@ -2366,19 +2353,19 @@
       <x:c r="G35" s="11" t="str"/>
       <x:c r="H35" s="11" t="str"/>
       <x:c r="I35" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="J35" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K35" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧 / 家庭伦理</x:v>
       </x:c>
       <x:c r="L35" s="11" t="str">
-        <x:v>喵琪琪追剧</x:v>
+        <x:v>阳阳动画</x:v>
       </x:c>
       <x:c r="M35" s="10" t="str">
-        <x:v>大坝突发险情，农村女孩夏晚禾凭借熟悉的环境和过人的勇气，不顾危险救下被困的沈长洲。一次意外的救援，让两个陌生人的命运重新交织。随着调查深入，沈长洲发现这个善良坚韧的女孩，竟是自己失散二十年的亲生女儿。面对迟来的亲情和真假千金的风波，夏晚禾没有依靠身份改变人生，而是用智慧、担当和努力证明自己的价值。陆言川也在一次次并肩相处中，被她的真诚与坚强打动，陪她找回亲情，走向新的未来。</x:v>
+        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -2386,84 +2373,84 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B36" s="11" t="n">
-        <x:v>86</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C36" s="10" t="str">
-        <x:v>这一秒沉沦</x:v>
+        <x:v>装傻下山</x:v>
       </x:c>
       <x:c r="D36" s="11" t="str">
-        <x:v>09-12 05:00</x:v>
+        <x:v>2026-09-12</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F36" s="11" t="str">
         <x:v>↑4位</x:v>
       </x:c>
       <x:c r="G36" s="11" t="str"/>
       <x:c r="H36" s="11" t="str"/>
-      <x:c r="I36" s="11" t="n">
-        <x:v>56</x:v>
-      </x:c>
+      <x:c r="I36" s="11" t="str"/>
       <x:c r="J36" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K36" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L36" s="11" t="str">
-        <x:v>包包短剧</x:v>
-      </x:c>
-      <x:c r="M36" s="10" t="str">
-        <x:v>向往烟火陪伴的温玉棠，在相亲的机缘下认识了周砚。周砚独自照料着姐姐离世后留下的外甥，两个渴望安稳生活的人决定走到一起共同生活。朝夕相伴的日子里，周砚用心打理家事、细心陪伴孩子，二人彼此体谅扶持，在平淡日常中慢慢滋生出真挚的情愫。二人携手举行婚礼，彼此珍惜，经营出温暖和睦的三口之家。</x:v>
-      </x:c>
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="L36" s="11" t="str"/>
+      <x:c r="M36" s="10" t="str"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B37" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C37" s="10" t="str">
-        <x:v>带着龙凤胎：和前夫共续前缘</x:v>
+        <x:v>清醒飒姐，携崽归来</x:v>
       </x:c>
       <x:c r="D37" s="11" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>09-11 10:00</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F37" s="11" t="str">
-        <x:v>↑3位</x:v>
+        <x:v>↑4位</x:v>
       </x:c>
       <x:c r="G37" s="11" t="str"/>
       <x:c r="H37" s="11" t="str"/>
-      <x:c r="I37" s="11" t="str"/>
+      <x:c r="I37" s="11" t="n">
+        <x:v>73</x:v>
+      </x:c>
       <x:c r="J37" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K37" s="10" t="str">
-        <x:v>古装宫廷 / 婚姻情感 / 战神异能</x:v>
-      </x:c>
-      <x:c r="L37" s="11" t="str"/>
-      <x:c r="M37" s="10" t="str"/>
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="L37" s="11" t="str">
+        <x:v>小布丁漫剧</x:v>
+      </x:c>
+      <x:c r="M37" s="10" t="str">
+        <x:v>苏念五年前与顾衍舟一夜纠葛，独自生下儿子小野。母亲重病之际，她将儿子托付给顾衍舟并甩出亲子鉴定，轰动顾、沈两家。沈家沈亦清先后拿出五百万、两千万逼她离开，苏念拒绝妥协，凭借律师拿到对方商业把柄对等博弈。她拒绝依附豪门，凭过硬医学能力入职三甲医院成为访问学者。顾衍舟被她的坚韧打动，放下家世偏见，两人签订共同抚养协议，逐渐相爱。沈家败落后小野归宗改姓。苏念事业家庭双圆满，活成不被金钱和家世定义的模样。</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B38" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C38" s="10" t="str">
-        <x:v>回到零四年进军彩铃界</x:v>
+        <x:v>误救高冷校花，她爷爷非要我做孙女婿</x:v>
       </x:c>
       <x:c r="D38" s="11" t="str">
-        <x:v>2026-09-11</x:v>
+        <x:v>2026-09-12</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F38" s="11" t="str">
         <x:v>↑3位</x:v>
@@ -2475,7 +2462,7 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="K38" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="L38" s="11" t="str"/>
       <x:c r="M38" s="10" t="str"/>
@@ -2485,67 +2472,73 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B39" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C39" s="10" t="str">
-        <x:v>假老板娘遇上真董事长</x:v>
+        <x:v>破麻袋里的亿万人生</x:v>
       </x:c>
       <x:c r="D39" s="11" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>09-11 15:30</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F39" s="11" t="str">
         <x:v>↑3位</x:v>
       </x:c>
       <x:c r="G39" s="11" t="str"/>
       <x:c r="H39" s="11" t="str"/>
-      <x:c r="I39" s="11" t="str"/>
+      <x:c r="I39" s="11" t="n">
+        <x:v>65</x:v>
+      </x:c>
       <x:c r="J39" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K39" s="10" t="str">
-        <x:v>都市职场 / 现实反转</x:v>
-      </x:c>
-      <x:c r="L39" s="11" t="str"/>
-      <x:c r="M39" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L39" s="11" t="str">
+        <x:v>小博漫剧社</x:v>
+      </x:c>
+      <x:c r="M39" s="10" t="str">
+        <x:v>失踪二十年的方小树因幼年被人贩子打伤，长期神志不清、沿街流浪。一次跳河救下海城富商顾振山的孙子，他得到七百万元谢礼，也意外回到方家。亲大哥方志强、二姐方玉梅只惦记他的钱，三姐方秀兰却始终护着他。受伤恢复记忆后，方小树选择继续装傻看清人心，并凭眼光投资远芯科技，从乞丐逆袭成身家过亿的股东。沈家千金沈清月因十八年前的救命之恩找到他，从报恩走向真爱。最终方小树认祖归宗、清算恶亲与幕后黑手</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B40" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C40" s="10" t="str">
-        <x:v>人心不论斤两</x:v>
+        <x:v>我赚上千万跟爸妈说50W，隔天就被找上门</x:v>
       </x:c>
       <x:c r="D40" s="11" t="str">
-        <x:v>09-10 09:18</x:v>
+        <x:v>09-13 08:00</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F40" s="11" t="str">
-        <x:v>↑3位</x:v>
+        <x:v>↑2位</x:v>
       </x:c>
       <x:c r="G40" s="11" t="str"/>
       <x:c r="H40" s="11" t="str"/>
       <x:c r="I40" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J40" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K40" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L40" s="11" t="str">
-        <x:v>在下长生</x:v>
+        <x:v>至尊爽剧社</x:v>
       </x:c>
       <x:c r="M40" s="10" t="str">
-        <x:v>朱逸群被母亲安排装穷相亲，遇到修旧货的许清禾。她不在意他月薪五千、没房没车，反而帮他修老房、换电线、装扶手，还叮嘱他“能修就别扔”。朱逸群在相处中真心喜欢上她，却又因隐瞒身份被她发现而分开。他没有用钱挽回，而是每天下班去她店里免费干活、搬货修电路，靠行动重新赢回信任。</x:v>
+        <x:v>三十二岁那年，贺川用六年孤注一掷的钻研，换来了七千六百万的回报。可财富还没捂热，先尝到的却是亲人无度的索取。他谎称只赚五十万，叮嘱保密，却挡不住消息走漏。隔天登门的亲戚不止要借钱买房，更联手外人盗用他的身份资料，试图冒名签约、伪造担保债务。贺川报警取证，警方介入追回大部分资金，涉案者包括部分机构人员均承担了法律责任，这笔帐，能否算清？</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -2553,16 +2546,16 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B41" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C41" s="10" t="str">
-        <x:v>征地我秒签跑路，全村笑我半年</x:v>
+        <x:v>当初闹着算清账目，我答应后他退休金见了底</x:v>
       </x:c>
       <x:c r="D41" s="11" t="str">
-        <x:v>09-10 11:30</x:v>
+        <x:v>09-12 08:00</x:v>
       </x:c>
       <x:c r="E41" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F41" s="11" t="str">
         <x:v>↑2位</x:v>
@@ -2570,19 +2563,19 @@
       <x:c r="G41" s="11" t="str"/>
       <x:c r="H41" s="11" t="str"/>
       <x:c r="I41" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J41" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K41" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="L41" s="11" t="str">
-        <x:v>小六动漫</x:v>
+        <x:v>小狐狸剧场</x:v>
       </x:c>
       <x:c r="M41" s="10" t="str">
-        <x:v>赵家湾迎来高速征地，村民受村长赵德厚鼓动抱团拒签，妄想抬价拿到四百五十万补偿。林远察觉当地岩溶地质暗藏线路改线风险，不顾全村嘲讽，果断签下312万补偿款，带父母搬离老家。后续高速果真改线，全村一分补偿落空。曾经嘲笑林远的村民陷入债务困境，赵德厚登门求助，林远守住底线，一家人握紧安稳生活，告诫众人抉择要靠自己。</x:v>
+        <x:v>许宁嫁入孟家四年，包揽房贷、学费与婆婆医药费，却从未被看见。饭桌上，公公孟栋泽手握六千八退休金，当众提出分家。无人反对，许宁也坦然应允。所有人都以为她是被供养的闲人，直到分家后，她默默停掉所有开支。断水断电、房贷逾期、催缴单纷至沓来，这个家一夜停摆。当真相浮出水面，他们才惊觉，被轻视的儿媳才是唯一的支柱。</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -2590,19 +2583,19 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B42" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C42" s="10" t="str">
-        <x:v>分家受辱,我竟是龙城龙主</x:v>
+        <x:v>回到零四年进军彩铃界</x:v>
       </x:c>
       <x:c r="D42" s="11" t="str">
         <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="E42" s="11" t="n">
-        <x:v>35</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F42" s="11" t="str">
-        <x:v>↑2位</x:v>
+        <x:v>↑1位</x:v>
       </x:c>
       <x:c r="G42" s="11" t="str"/>
       <x:c r="H42" s="11" t="str"/>
@@ -2611,7 +2604,7 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="K42" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L42" s="11" t="str"/>
       <x:c r="M42" s="10" t="str"/>
@@ -2621,16 +2614,16 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B43" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C43" s="10" t="str">
-        <x:v>我的眼睛变成了透视神瞳</x:v>
+        <x:v>活宝老爹再赴青春，竟与女儿同上大学</x:v>
       </x:c>
       <x:c r="D43" s="11" t="str">
-        <x:v>09-11 11:00</x:v>
+        <x:v>09-13 00:10</x:v>
       </x:c>
       <x:c r="E43" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F43" s="11" t="str">
         <x:v>↑1位</x:v>
@@ -2638,19 +2631,19 @@
       <x:c r="G43" s="11" t="str"/>
       <x:c r="H43" s="11" t="str"/>
       <x:c r="I43" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J43" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K43" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="L43" s="11" t="str">
-        <x:v>奇迹漫剧</x:v>
+        <x:v>长风剧场</x:v>
       </x:c>
       <x:c r="M43" s="10" t="str">
-        <x:v>罗川本是四处奔波的废品回收从业者，日子过得窘迫潦倒。一次意外，他觉醒透视异能，双眼能够看穿物件内里，辨明真伪与隐藏价值。凭借这份神异能力，他在旧货市场、废品堆里频频捡漏，屡屡发现被人忽视的珍宝。从被旁人轻视的底层小人物，他一步步积累财富与阅历，在古玩鉴宝圈崭露头角，破除无数圈套骗局，逆袭成受人敬重的顶尖鉴宝高手，改写了自己的平凡人生。</x:v>
+        <x:v>45岁的白烨意外激活成长系统。只要亲身体验年轻人的日常，就能重拾青春活力，还能收获丰厚奖励。为完成系统任务，他报名成人高考，顺利考入大学，竟和女儿成了同校同学。重返校园的白烨，一边认真完成任务感受青春，一边在校园里开启一段充满趣味的全新人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -2658,16 +2651,16 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B44" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C44" s="10" t="str">
-        <x:v>锦书迟</x:v>
+        <x:v>我的师兄全是修仙界大佬</x:v>
       </x:c>
       <x:c r="D44" s="11" t="str">
-        <x:v>09-12 07:30</x:v>
+        <x:v>09-11 18:16</x:v>
       </x:c>
       <x:c r="E44" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F44" s="11" t="str">
         <x:v>↑1位</x:v>
@@ -2675,91 +2668,19 @@
       <x:c r="G44" s="11" t="str"/>
       <x:c r="H44" s="11" t="str"/>
       <x:c r="I44" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="J44" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K44" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="L44" s="11" t="str">
-        <x:v>咩咩漫文</x:v>
+        <x:v>大公鸡剧场</x:v>
       </x:c>
       <x:c r="M44" s="10" t="str">
-        <x:v>三年前，沈昭昭嫁与永宁侯谢凛，新婚燕尔他便远赴边关。她苦等家书，却不知双向书信早被人暗中截留。她终于心冷离开侯府。三年后，她带着孩子在市井支摊卖画立足，他却循着蛛丝马迹寻来，真相层层揭开，原来他从未负她。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45">
-      <x:c r="A45" s="11" t="str">
-        <x:v>新剧上升</x:v>
-      </x:c>
-      <x:c r="B45" s="11" t="n">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C45" s="10" t="str">
-        <x:v>家有新章</x:v>
-      </x:c>
-      <x:c r="D45" s="11" t="str">
-        <x:v>09-10 09:00</x:v>
-      </x:c>
-      <x:c r="E45" s="11" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F45" s="11" t="str">
-        <x:v>↑1位</x:v>
-      </x:c>
-      <x:c r="G45" s="11" t="str"/>
-      <x:c r="H45" s="11" t="str"/>
-      <x:c r="I45" s="11" t="n">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="J45" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="K45" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L45" s="11" t="str">
-        <x:v>尔尔剧场</x:v>
-      </x:c>
-      <x:c r="M45" s="10" t="str">
-        <x:v>新婚回门日，新媳妇秦麦穗因拒被大伯母郭凤英拿捏、不让丈夫无偿干活，彻底得罪大房一家。郭凤英处处刁难，断其公公杀猪活路麦穗逆势创业，靠卤味、腊肠做起小作坊，安稳养家。反观眼高手低的堂哥梁大勇，贪快钱误入骗局欠债，辛苦还债幡然醒悟。最终两家境遇悬殊，踏实肯干的秦家岁岁安稳、日子红火。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="11" t="str">
-        <x:v>新剧上升</x:v>
-      </x:c>
-      <x:c r="B46" s="11" t="n">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C46" s="10" t="str">
-        <x:v>我送弟弟上青云</x:v>
-      </x:c>
-      <x:c r="D46" s="11" t="str">
-        <x:v>09-12 09:52</x:v>
-      </x:c>
-      <x:c r="E46" s="11" t="str"/>
-      <x:c r="F46" s="11" t="str">
-        <x:v>新上榜</x:v>
-      </x:c>
-      <x:c r="G46" s="11" t="str"/>
-      <x:c r="H46" s="11" t="str"/>
-      <x:c r="I46" s="11" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="J46" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="K46" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L46" s="11" t="str">
-        <x:v>落云</x:v>
-      </x:c>
-      <x:c r="M46" s="10" t="str">
-        <x:v>宋远回乡发现弟弟宋临被父亲剥夺上学权利，只能干农活。他毅然带走弟弟，用微薄工资供他读书。宋临考上名校建筑系，毕业后成为身价过亿的设计师。他用第一桶金给哥哥买房，报答当年恩情。面对迟来求和的父亲，宋临完成了心灵的真正和解。这是一个关于“长兄如父、手足情深”的故事，诠释了扶助与感恩的力量。</x:v>
+        <x:v>六岁的女主奉师父顾青崖之命下山历练，寻找五位失散数百年的师兄。她天生神力，把九品丹药当糖豆吃，背着重剑闯修仙界。本以为师兄们在外落魄难归，却发现大师兄是正道第一人九天仙尊，二师兄是统御九幽的幽冥帝君，余下三位也皆是绝世大佬。小奶娃一路闯荡，把隐世多年的师兄们挨个喊回了家。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2805,180 +2726,155 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
-        <x:v>退婚从抢我车位开始</x:v>
+        <x:v>我赚上千万跟爸妈说50W，隔天就被找上门</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>当日新上榜</x:v>
-      </x:c>
-      <x:c r="D2" s="11" t="str"/>
-      <x:c r="E2" s="11" t="str"/>
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D2" s="11" t="str">
+        <x:v>09-13 08:00</x:v>
+      </x:c>
+      <x:c r="E2" s="11" t="n">
+        <x:v>78</x:v>
+      </x:c>
       <x:c r="F2" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="G2" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G2" s="10" t="str">
+        <x:v>至尊爽剧社</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>当初闹着算清账目，我答应后他退休金见了底</x:v>
+        <x:v>活宝老爹再赴青春，竟与女儿同上大学</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>09-12 08:00</x:v>
+        <x:v>09-13 00:10</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F3" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G3" s="10" t="str">
-        <x:v>小狐狸剧场</x:v>
+        <x:v>长风剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>七套房产，换来一纸调令</x:v>
+        <x:v>我绝顶杀手旷世神医，下山即无敌</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>今日发布</x:v>
+        <x:v>当日新上榜</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>09-12 08:18</x:v>
+        <x:v>07-06 13:51</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F4" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="G4" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>每日欢乐漫剧</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>锦书迟</x:v>
+        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>09-12 07:30</x:v>
+        <x:v>09-13 08:00</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F5" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G5" s="10" t="str">
-        <x:v>咩咩漫文</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>我送弟弟上青云</x:v>
+        <x:v>反派拿捏！</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>今日发布</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="str">
-        <x:v>09-12 09:52</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="n">
-        <x:v>55</x:v>
-      </x:c>
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str"/>
+      <x:c r="E6" s="11" t="str"/>
       <x:c r="F6" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G6" s="10" t="str">
-        <x:v>落云</x:v>
-      </x:c>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="G6" s="10" t="str"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>谁让这个悍匪修仙的！第三季</x:v>
+        <x:v>别咬，你太大只啦</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>09-12 00:07</x:v>
+        <x:v>09-13 00:06</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="F7" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="str">
-        <x:v>千帧动画</x:v>
-      </x:c>
+      <x:c r="G7" s="10" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>小师叔下山，喊大佬回家吃饭</x:v>
+        <x:v>玄门大佬萧安乐</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>今日发布</x:v>
+        <x:v>当日新上榜</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>09-12 07:30</x:v>
+        <x:v>08-19 19:18</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
-        <x:v>89</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="F8" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G8" s="10" t="str">
-        <x:v>杰瑞剧场</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="11" t="n">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="B9" s="10" t="str">
-        <x:v>这一秒沉沦</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="str">
-        <x:v>今日发布</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="str">
-        <x:v>09-12 05:00</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="F9" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G9" s="10" t="str">
-        <x:v>包包短剧</x:v>
+        <x:v>AIGC 楠楠</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3048,13 +2944,13 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
-        <x:v>破库房的秘密</x:v>
+        <x:v>一墙之隔，皆是人心</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>2026-09-05</x:v>
+        <x:v>09-06 15:48</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
         <x:v>7</x:v>
@@ -3066,20 +2962,26 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G2" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H2" s="11" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H2" s="11" t="n">
+        <x:v>85</x:v>
+      </x:c>
       <x:c r="I2" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J2" s="11" t="str"/>
       <x:c r="K2" s="11" t="str"/>
-      <x:c r="L2" s="10" t="str"/>
-      <x:c r="M2" s="10" t="str"/>
+      <x:c r="L2" s="10" t="str">
+        <x:v>在下长生</x:v>
+      </x:c>
+      <x:c r="M2" s="10" t="str">
+        <x:v>妻子临产被车堵住出口，叶瑾抱着羊水破裂的她跑了三公里才到医院，母子平安。面对无理的车主，他没有以暴制暴，而是选择依法行事——在自家院内合法砌墙、种下高价值树苗，全程录像留证。车主回来后暴力砸墙、碾压树苗，最终被依法追究责任。</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
         <x:v>退婚后我在七零赚钱养家致富</x:v>
@@ -3088,7 +2990,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
         <x:v>7</x:v>
@@ -3114,16 +3016,16 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>一墙之隔，皆是人心</x:v>
+        <x:v>破库房的秘密</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>09-06 15:48</x:v>
+        <x:v>2026-09-05</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
         <x:v>7</x:v>
@@ -3132,35 +3034,29 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G4" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="11" t="n">
-        <x:v>85</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H4" s="11" t="str"/>
       <x:c r="I4" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J4" s="11" t="str"/>
       <x:c r="K4" s="11" t="str"/>
-      <x:c r="L4" s="10" t="str">
-        <x:v>在下长生</x:v>
-      </x:c>
-      <x:c r="M4" s="10" t="str">
-        <x:v>妻子临产被车堵住出口，叶瑾抱着羊水破裂的她跑了三公里才到医院，母子平安。面对无理的车主，他没有以暴制暴，而是选择依法行事——在自家院内合法砌墙、种下高价值树苗，全程录像留证。车主回来后暴力砸墙、碾压树苗，最终被依法追究责任。</x:v>
-      </x:c>
+      <x:c r="L4" s="10" t="str"/>
+      <x:c r="M4" s="10" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>一针绣出自己的路</x:v>
+        <x:v>惊絮无声：傻女的绝杀</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>09-04 19:51</x:v>
+        <x:v>09-06 10:00</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
         <x:v>7</x:v>
@@ -3169,10 +3065,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G5" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H5" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I5" s="10" t="str">
         <x:v>其他</x:v>
@@ -3180,24 +3076,24 @@
       <x:c r="J5" s="11" t="str"/>
       <x:c r="K5" s="11" t="str"/>
       <x:c r="L5" s="10" t="str">
-        <x:v>墨尘漫剧</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="M5" s="10" t="str">
-        <x:v>苏绾青她从裁缝店半张旧桌重新开始，凭一针一线修补旧物、绣出人心，也把被看轻的手艺做成自己的路。故事温暖励志，展现普通女性靠勤奋、诚信和坚持赢得尊重、改变生活的力量。所有的事情都可以迎刃而解，代表了生活中的光</x:v>
+        <x:v>沈家人人都是天才，唯独小女儿沈惊絮是公认的傻子。没人知道，她不仅装傻多年，还带着前世金牌律师的记忆重生而来。本想闭嘴躺平一生，谁料内鬼勾结资本做空沈氏，一纸合同就要让全家净身出户、背上百亿债务。父亲落笔前，她终于按住协议“这字不能签！”绝地反杀的沈惊絮，一步步挫败了对沈家的围剿，也让全家人重新认识了自己。沈家也迎来了新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>我的奇葩舍友</x:v>
+        <x:v>一针绣出自己的路</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>09-06 09:55</x:v>
+        <x:v>09-04 19:51</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
         <x:v>7</x:v>
@@ -3206,10 +3102,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G6" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H6" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
         <x:v>其他</x:v>
@@ -3217,21 +3113,21 @@
       <x:c r="J6" s="11" t="str"/>
       <x:c r="K6" s="11" t="str"/>
       <x:c r="L6" s="10" t="str">
-        <x:v>金鱼漫剪</x:v>
+        <x:v>墨尘漫剧</x:v>
       </x:c>
       <x:c r="M6" s="10" t="str">
-        <x:v>林嘉宝从小由母亲周美兰一手带大，事无巨细都由妈妈安排。上大学后，他不会套被套，不会洗衣服，遇事第一反应是打电话问妈妈。母亲为他定下各种宿舍规矩，与室友矛盾不断。直到家中突遭变故，父亲破产，豪宅被封，母亲失联。嘉宝一夜之间失去所有依靠，被迫独自面对生活，一步步学会洗衣、打工、交电费，逐渐成为独立的大学生。</x:v>
+        <x:v>苏绾青她从裁缝店半张旧桌重新开始，凭一针一线修补旧物、绣出人心，也把被看轻的手艺做成自己的路。故事温暖励志，展现普通女性靠勤奋、诚信和坚持赢得尊重、改变生活的力量。所有的事情都可以迎刃而解，代表了生活中的光</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>惊絮无声：傻女的绝杀</x:v>
+        <x:v>凤阙承安</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>09-06 10:00</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
         <x:v>6</x:v>
@@ -3243,32 +3139,26 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G7" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="11" t="n">
-        <x:v>60</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H7" s="11" t="str"/>
       <x:c r="I7" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J7" s="11" t="str"/>
       <x:c r="K7" s="11" t="str"/>
-      <x:c r="L7" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
-      </x:c>
-      <x:c r="M7" s="10" t="str">
-        <x:v>沈家人人都是天才，唯独小女儿沈惊絮是公认的傻子。没人知道，她不仅装傻多年，还带着前世金牌律师的记忆重生而来。本想闭嘴躺平一生，谁料内鬼勾结资本做空沈氏，一纸合同就要让全家净身出户、背上百亿债务。父亲落笔前，她终于按住协议“这字不能签！”绝地反杀的沈惊絮，一步步挫败了对沈家的围剿，也让全家人重新认识了自己。沈家也迎来了新生。</x:v>
-      </x:c>
+      <x:c r="L7" s="10" t="str"/>
+      <x:c r="M7" s="10" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="n">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>野茶开出花</x:v>
+        <x:v>我的奇葩舍友</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>09-05 18:16</x:v>
+        <x:v>09-06 09:55</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
         <x:v>7</x:v>
@@ -3280,10 +3170,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G8" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H8" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
         <x:v>其他</x:v>
@@ -3291,24 +3181,24 @@
       <x:c r="J8" s="11" t="str"/>
       <x:c r="K8" s="11" t="str"/>
       <x:c r="L8" s="10" t="str">
-        <x:v>多米漫剧场</x:v>
+        <x:v>金鱼漫剪</x:v>
       </x:c>
       <x:c r="M8" s="10" t="str">
-        <x:v>苏晚星十九岁，一百八十斤，被母亲断卡后送进深山。石阶四十分钟，土屋、木板床、没信号的手机，迎接她的是守山四十年的石奶奶。采茶磨出水泡，跑山喘不上气，半夜偷吃生黄豆被当场抓住。阿杏叫她晚星姐，集市阿婆说她壮实，她第一次觉得胖没那么刺耳。体重从一百八到一百二，手上磨出了茧。她拍短视频卖茶，建山风茶舍。再次上山，她站在山顶说山神爷爷，我回来了。山风知道她来过，也知道她变成了谁。</x:v>
+        <x:v>林嘉宝从小由母亲周美兰一手带大，事无巨细都由妈妈安排。上大学后，他不会套被套，不会洗衣服，遇事第一反应是打电话问妈妈。母亲为他定下各种宿舍规矩，与室友矛盾不断。直到家中突遭变故，父亲破产，豪宅被封，母亲失联。嘉宝一夜之间失去所有依靠，被迫独自面对生活，一步步学会洗衣、打工、交电费，逐渐成为独立的大学生。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>那块玉，带我们回家</x:v>
+        <x:v>蒙蒙半故</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>09-05 07:18</x:v>
+        <x:v>09-05 20:27</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
         <x:v>7</x:v>
@@ -3317,10 +3207,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G9" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H9" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str">
         <x:v>其他</x:v>
@@ -3328,21 +3218,21 @@
       <x:c r="J9" s="11" t="str"/>
       <x:c r="K9" s="11" t="str"/>
       <x:c r="L9" s="10" t="str">
-        <x:v>五指毛桃</x:v>
+        <x:v>小斐漫剧</x:v>
       </x:c>
       <x:c r="M9" s="10" t="str">
-        <x:v>六岁孩童为救母拾荒半年，孝心感动天地，更牵出一段失散六年的亲情。缘分以信物为引，助离散一家重逢。当暗处之手伸向团圆，真相与信任如光破晓，令恶念无处遁形。正义为善良护航，温暖在守望中生长。孩子用稚嫩肩膀撑起希望，父母以爱重筑家园，善意在风雨中传递，终迎阖家安康的晴空。</x:v>
+        <x:v>拥有漫长寿命的男人隐姓埋名，以外卖员身份在都市生活。百岁老人临终的遗愿，让他卷入豪门家族的纷争。他结识家族女总裁，接连应对家族内斗、敌对势力与神秘长生组织的重重算计。二人携手揭开千年前的尘封秘辛，对抗妄图窃取长生力量的反派，在危机之中彼此羁绊，还要面对即将开启的上古昆仑之门带来的巨大未知考验。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>黑蛋孵出山海神兽后我无敌了</x:v>
+        <x:v>苏小姐高调离婚，前夫哭惨了</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>09-06 18:00</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
         <x:v>6</x:v>
@@ -3354,32 +3244,26 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G10" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H10" s="11" t="n">
-        <x:v>154</x:v>
-      </x:c>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H10" s="11" t="str"/>
       <x:c r="I10" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J10" s="11" t="str"/>
       <x:c r="K10" s="11" t="str"/>
-      <x:c r="L10" s="10" t="str">
-        <x:v>抱月剧场</x:v>
-      </x:c>
-      <x:c r="M10" s="10" t="str">
-        <x:v>寒门少年李初七攒了三年银子，仍买不起最低等的兽蛋。一次意外，他在后山捡到一枚黑蛋，孵出的煤球又小又馋，偏偏爱啃铜钱。可每吞下一缕兽息，它便能复现对手的能力。县学测灵那日，测灵石骤然亮起黑光，群兽伏地。所有人都以为他只是走了好运，只有陆远山想起古籍中的禁忌——黑光现，万兽伏。煤球究竟是什么？</x:v>
-      </x:c>
+      <x:c r="L10" s="10" t="str"/>
+      <x:c r="M10" s="10" t="str"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
+        <x:v>黑蛋孵出山海神兽后我无敌了</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>2026-09-05</x:v>
+        <x:v>09-06 18:00</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
         <x:v>7</x:v>
@@ -3391,29 +3275,35 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G11" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="11" t="str"/>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H11" s="11" t="n">
+        <x:v>154</x:v>
+      </x:c>
       <x:c r="I11" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J11" s="11" t="str"/>
       <x:c r="K11" s="11" t="str"/>
-      <x:c r="L11" s="10" t="str"/>
-      <x:c r="M11" s="10" t="str"/>
+      <x:c r="L11" s="10" t="str">
+        <x:v>抱月剧场</x:v>
+      </x:c>
+      <x:c r="M11" s="10" t="str">
+        <x:v>寒门少年李初七攒了三年银子，仍买不起最低等的兽蛋。一次意外，他在后山捡到一枚黑蛋，孵出的煤球又小又馋，偏偏爱啃铜钱。可每吞下一缕兽息，它便能复现对手的能力。县学测灵那日，测灵石骤然亮起黑光，群兽伏地。所有人都以为他只是走了好运，只有陆远山想起古籍中的禁忌——黑光现，万兽伏。煤球究竟是什么？</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="n">
-        <x:v>43</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>蒙蒙半故</x:v>
+        <x:v>野茶开出花</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>09-05 20:27</x:v>
+        <x:v>09-05 18:16</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
         <x:v>7</x:v>
@@ -3422,10 +3312,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G12" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H12" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str">
         <x:v>其他</x:v>
@@ -3433,21 +3323,21 @@
       <x:c r="J12" s="11" t="str"/>
       <x:c r="K12" s="11" t="str"/>
       <x:c r="L12" s="10" t="str">
-        <x:v>小斐漫剧</x:v>
+        <x:v>多米漫剧场</x:v>
       </x:c>
       <x:c r="M12" s="10" t="str">
-        <x:v>拥有漫长寿命的男人隐姓埋名，以外卖员身份在都市生活。百岁老人临终的遗愿，让他卷入豪门家族的纷争。他结识家族女总裁，接连应对家族内斗、敌对势力与神秘长生组织的重重算计。二人携手揭开千年前的尘封秘辛，对抗妄图窃取长生力量的反派，在危机之中彼此羁绊，还要面对即将开启的上古昆仑之门带来的巨大未知考验。</x:v>
+        <x:v>苏晚星十九岁，一百八十斤，被母亲断卡后送进深山。石阶四十分钟，土屋、木板床、没信号的手机，迎接她的是守山四十年的石奶奶。采茶磨出水泡，跑山喘不上气，半夜偷吃生黄豆被当场抓住。阿杏叫她晚星姐，集市阿婆说她壮实，她第一次觉得胖没那么刺耳。体重从一百八到一百二，手上磨出了茧。她拍短视频卖茶，建山风茶舍。再次上山，她站在山顶说山神爷爷，我回来了。山风知道她来过，也知道她变成了谁。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="n">
-        <x:v>49</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>让你代写情书，你落笔惊哭大儒第四季</x:v>
+        <x:v>重生扬子鳄：从网购开始吞噬进化</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>2026-09-06</x:v>
+        <x:v>09-07 00:04</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
         <x:v>6</x:v>
@@ -3459,29 +3349,35 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G13" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H13" s="11" t="str"/>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H13" s="11" t="n">
+        <x:v>134</x:v>
+      </x:c>
       <x:c r="I13" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J13" s="11" t="str"/>
       <x:c r="K13" s="11" t="str"/>
-      <x:c r="L13" s="10" t="str"/>
-      <x:c r="M13" s="10" t="str"/>
+      <x:c r="L13" s="10" t="str">
+        <x:v>最漫剧场</x:v>
+      </x:c>
+      <x:c r="M13" s="10" t="str">
+        <x:v>陆沉加班猝死，重生为一只扬子鳄，却意外激活吞噬进化系统。他从小小鳄鱼起步，吞噬万物，不断觉醒龙族血脉。从护佑一方村民到对抗敌人九阶妖兽，他一步步蜕变成长。面对灵气复苏后崛起的强敌，陆沉立誓守护故土，踏上通往真龙的逆天进化之路。吞噬进化，龙威初显！既是妖兽，更是守护神！本漫剧改编自番茄小说《重生扬子鳄，从网购开始吞噬进化》作者《风依臣》</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>大将军扛楼养活百万大军第二季</x:v>
+        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>09-06 14:06</x:v>
+        <x:v>2026-09-05</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
         <x:v>7</x:v>
@@ -3490,35 +3386,29 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G14" s="11" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H14" s="11" t="n">
-        <x:v>203</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="str"/>
       <x:c r="I14" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J14" s="11" t="str"/>
       <x:c r="K14" s="11" t="str"/>
-      <x:c r="L14" s="10" t="str">
-        <x:v>林晨动画</x:v>
-      </x:c>
-      <x:c r="M14" s="10" t="str">
-        <x:v>沙州武威大将军萧镇北坚守沙州三年，弹尽粮绝，却意外通过茅房穿越到了二十一世纪这个资源充足的年代。为了让城中百姓吃好喝好，萧镇北开启了自己的打工生涯。扛楼？我干！一口气上五楼，不费劲！健身模特？给钱就干。什么，做教练？我也行！不久后，古代出现了各种现代武器。</x:v>
-      </x:c>
+      <x:c r="L14" s="10" t="str"/>
+      <x:c r="M14" s="10" t="str"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>大力末世降临，小尸尸我呀吸吸吸</x:v>
+        <x:v>不负恩情不负卿</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
-        <x:v>09-05 06:39</x:v>
+        <x:v>2026-09-05</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
         <x:v>7</x:v>
@@ -3527,35 +3417,29 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G15" s="11" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H15" s="11" t="n">
-        <x:v>120</x:v>
-      </x:c>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H15" s="11" t="str"/>
       <x:c r="I15" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J15" s="11" t="str"/>
       <x:c r="K15" s="11" t="str"/>
-      <x:c r="L15" s="10" t="str">
-        <x:v>漫剧传送门</x:v>
-      </x:c>
-      <x:c r="M15" s="10" t="str">
-        <x:v>末世降临前三分钟，互联网实习生许多多收到末日预警，凭借超强求生本能疯狂囤货，固守自家堡垒苟命求生。可末世浩劫之下，她依旧不幸感染病毒，意外蜕变为保留完整人类意识的特殊丧尸，同时解锁无限扩容的多面魔方空间。半月后，3A特殊作战小队前来清剿，带队队长竟是她年少暗恋的同桌秦洛。知晓她的特殊异能与理智后，秦洛将她收留，她自此成为小队最强辅助与移动军需库。</x:v>
-      </x:c>
+      <x:c r="L15" s="10" t="str"/>
+      <x:c r="M15" s="10" t="str"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>一碗热饭暖人性</x:v>
+        <x:v>那块玉，带我们回家</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>09-03 00:06</x:v>
+        <x:v>09-05 07:18</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
         <x:v>7</x:v>
@@ -3564,37 +3448,35 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G16" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H16" s="11" t="n">
-        <x:v>49</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="J16" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K16" s="11" t="str">
-        <x:v>0.00</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="J16" s="11" t="str"/>
+      <x:c r="K16" s="11" t="str"/>
       <x:c r="L16" s="10" t="str">
-        <x:v>第九幕</x:v>
-      </x:c>
-      <x:c r="M16" s="10" t="str"/>
+        <x:v>五指毛桃</x:v>
+      </x:c>
+      <x:c r="M16" s="10" t="str">
+        <x:v>六岁孩童为救母拾荒半年，孝心感动天地，更牵出一段失散六年的亲情。缘分以信物为引，助离散一家重逢。当暗处之手伸向团圆，真相与信任如光破晓，令恶念无处遁形。正义为善良护航，温暖在守望中生长。孩子用稚嫩肩膀撑起希望，父母以爱重筑家园，善意在风雨中传递，终迎阖家安康的晴空。</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="n">
-        <x:v>94</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>白鹿照归途</x:v>
+        <x:v>重回急诊当天，我不再犹豫</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>09-03 14:40</x:v>
+        <x:v>09-07 08:00</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
         <x:v>7</x:v>
@@ -3603,34 +3485,32 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G17" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H17" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I17" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="J17" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="K17" s="11" t="str">
-        <x:v>0.60</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="J17" s="11" t="str"/>
+      <x:c r="K17" s="11" t="str"/>
       <x:c r="L17" s="10" t="str">
-        <x:v>漫漫天星</x:v>
-      </x:c>
-      <x:c r="M17" s="10" t="str"/>
+        <x:v>番荔枝剧场</x:v>
+      </x:c>
+      <x:c r="M17" s="10" t="str">
+        <x:v>沈峥重生回海城医院急诊大厅，那四个从非洲归来的学生正走进大门。周宇扬手臂上的异样红疹让他心头一紧。这一次，他果断按下警报按钮。辅导员李健急得拍窗，家长投诉不断。监控画面里，陈浩背包中的动物残骨悄然露出。有些秘密，比病毒藏得更深。</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="n">
-        <x:v>99</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>重生八零，从捡蘑菇开始安家</x:v>
+        <x:v>让你代写情书，你落笔惊哭大儒第四季</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>09-05 17:58</x:v>
+        <x:v>2026-09-06</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
         <x:v>7</x:v>
@@ -3642,63 +3522,63 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G18" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="11" t="n">
-        <x:v>97</x:v>
-      </x:c>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H18" s="11" t="str"/>
       <x:c r="I18" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J18" s="11" t="str"/>
       <x:c r="K18" s="11" t="str"/>
-      <x:c r="L18" s="10" t="str">
-        <x:v>七星动画</x:v>
-      </x:c>
-      <x:c r="M18" s="10" t="str">
-        <x:v>徐林带着前世的遗憾重回八十年代，过去的他浑浑噩噩，错过了爱人，落得孤苦收场。重生之后，他彻底洗心革面，迎娶心性温婉、知书达理的祝薇薇。他抓住时代机遇，收购蘑菇野味做起生意，用心呵护妻子。既要应对邻里间的猜忌算计、各村村民的矛盾纠纷，又要带领乡亲寻找谋生出路，在一地鸡毛的乡村烟火里，拼尽全力守护家庭，改写属于自己与身边人的命运。</x:v>
-      </x:c>
+      <x:c r="L18" s="10" t="str"/>
+      <x:c r="M18" s="10" t="str"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>不负恩情不负卿</x:v>
+        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>2026-09-05</x:v>
+        <x:v>09-08 17:58</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G19" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H19" s="11" t="str"/>
+      <x:c r="H19" s="11" t="n">
+        <x:v>111</x:v>
+      </x:c>
       <x:c r="I19" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J19" s="11" t="str"/>
       <x:c r="K19" s="11" t="str"/>
-      <x:c r="L19" s="10" t="str"/>
-      <x:c r="M19" s="10" t="str"/>
+      <x:c r="L19" s="10" t="str">
+        <x:v>禾苗动画</x:v>
+      </x:c>
+      <x:c r="M19" s="10" t="str">
+        <x:v>末世异能者沐小暖意外穿书，成为七个反派继子的恶毒后娘。原主辛劳养娃却遭流言中伤，最终含恨而终。沐小暖决心扭转命运，恩威并施管教孩子，凭末世身手进山打猎采药、种地赶集改善家计，更以百年老参为礼，为长子求得名儒霍政谚收为关门弟子。她护佑家人躲过恶人算计与亲戚夺产，建起新宅。七个孩子从怨恨抗拒到真心信赖，争着喊她娘，一家人携手改写命运，收获温暖亲情。</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>凤阙承安</x:v>
+        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>09-08 11:00</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
         <x:v>5</x:v>
@@ -3710,26 +3590,32 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G20" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H20" s="11" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H20" s="11" t="n">
+        <x:v>91</x:v>
+      </x:c>
       <x:c r="I20" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J20" s="11" t="str"/>
       <x:c r="K20" s="11" t="str"/>
-      <x:c r="L20" s="10" t="str"/>
-      <x:c r="M20" s="10" t="str"/>
+      <x:c r="L20" s="10" t="str">
+        <x:v>白桃剧场</x:v>
+      </x:c>
+      <x:c r="M20" s="10" t="str">
+        <x:v>阿梨一觉睡了三百年，养大的五只小兽尽数离去。她带着五只旧饭碗、十二枚铜钱与一把锈柴刀下山寻兽。昔日的小家伙已成威震四方的妖祖，历经重重相遇与揭秘，阿梨知晓三百年封印的真相，携手五只妖祖，一同对抗祸世灭灵兽神。</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>苏小姐高调离婚，前夫哭惨了</x:v>
+        <x:v>抢个新娘来当后娘第一季</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>09-08 15:10</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
         <x:v>5</x:v>
@@ -3741,26 +3627,32 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G21" s="11" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H21" s="11" t="str"/>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H21" s="11" t="n">
+        <x:v>177</x:v>
+      </x:c>
       <x:c r="I21" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J21" s="11" t="str"/>
       <x:c r="K21" s="11" t="str"/>
-      <x:c r="L21" s="10" t="str"/>
-      <x:c r="M21" s="10" t="str"/>
+      <x:c r="L21" s="10" t="str">
+        <x:v>麻辣公主</x:v>
+      </x:c>
+      <x:c r="M21" s="10" t="str">
+        <x:v>带着十里红妆出嫁那日，我才得知新郎早已另娶，这门亲事不过是盯上了我李家的家产。换作旁人或许忍气吞声，我偏不。我当众拒入侯府，主动上书朝廷，愿以嫁妆资援南方水患，只求解除婚约、护我父母周全。这份胆识赢得安王敬重，他以正妃之礼娶我入门。我立誓此生不做妾、不与人共侍一夫，终得一份彼此尊重的姻缘。</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>这一炉羊，我不敢卖便宜</x:v>
+        <x:v>重启人生，拒绝校花？</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>09-07 16:11</x:v>
+        <x:v>09-08 08:30</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
         <x:v>5</x:v>
@@ -3772,10 +3664,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G22" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H22" s="11" t="n">
-        <x:v>57</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str">
         <x:v>其他</x:v>
@@ -3783,36 +3675,36 @@
       <x:c r="J22" s="11" t="str"/>
       <x:c r="K22" s="11" t="str"/>
       <x:c r="L22" s="10" t="str">
-        <x:v>林帧漫剧</x:v>
+        <x:v>肆漫简</x:v>
       </x:c>
       <x:c r="M22" s="10" t="str">
-        <x:v>流动烤羊师傅杜成山坚守一千六百元全包定价，拒绝跟风同行罗彪九百九十九元的低价内卷。园区为逐利压价客户盲从低价。绝境之下，杜成山夫妻转战郊外露营地，凭足斤足两的真材实料，绝不糊弄的匠心服务慢慢翻盘。而低价抢单的罗彪为保本偷换劣质货源，最终因食品安全问题翻车崩盘。这场价格与品质的博弈，揭开市井生意真相，廉价不是捷径，踏实用料、坚守底线，才是长久谋生的根本。</x:v>
+        <x:v>白陌重生回到2004年高考夜，果断避开前世陷害自己的宾馆陷阱，救下被下药的校花江洛菡，彻底扭转人生走向。他不再执着于过往的情感执念，跳出卑微追爱的困局，转而关心恩师健康、规划学业与创业方向，结识志同道合的伙伴。凭借重生阅历清醒选择前路，把握青春重启人生，用行动改写原本遗憾的命运，活出全新成长轨迹。</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
+        <x:v>穿书后我带萌宝上门认爹</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>09-08 17:58</x:v>
+        <x:v>09-07 19:18</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G23" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H23" s="11" t="n">
-        <x:v>111</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
         <x:v>其他</x:v>
@@ -3820,21 +3712,21 @@
       <x:c r="J23" s="11" t="str"/>
       <x:c r="K23" s="11" t="str"/>
       <x:c r="L23" s="10" t="str">
-        <x:v>禾苗动画</x:v>
+        <x:v>虾仁不自在</x:v>
       </x:c>
       <x:c r="M23" s="10" t="str">
-        <x:v>末世异能者沐小暖意外穿书，成为七个反派继子的恶毒后娘。原主辛劳养娃却遭流言中伤，最终含恨而终。沐小暖决心扭转命运，恩威并施管教孩子，凭末世身手进山打猎采药、种地赶集改善家计，更以百年老参为礼，为长子求得名儒霍政谚收为关门弟子。她护佑家人躲过恶人算计与亲戚夺产，建起新宅。七个孩子从怨恨抗拒到真心信赖，争着喊她娘，一家人携手改写命运，收获温暖亲情。</x:v>
+        <x:v>许知棠重生穿进书中，当即带着五岁儿子许小舟登门，将孩子送到亲生父亲——傅氏集团总裁傅临川面前，只想抽身退出剧情。幼儿园里儿子遭同学诬陷、老师偏心，她强势护崽，硬刚蛮横家长与失职老师。亲子鉴定尘埃落定，萌娃黏妈不黏爹，反倒让清冷总裁渐渐上心。</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
+        <x:v>重生三天前，我用水泥封死地下室</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>09-08 11:00</x:v>
+        <x:v>09-09 09:28</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
         <x:v>4</x:v>
@@ -3849,7 +3741,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H24" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I24" s="10" t="str">
         <x:v>其他</x:v>
@@ -3857,21 +3749,21 @@
       <x:c r="J24" s="11" t="str"/>
       <x:c r="K24" s="11" t="str"/>
       <x:c r="L24" s="10" t="str">
-        <x:v>白桃剧场</x:v>
+        <x:v>忘忧剧场</x:v>
       </x:c>
       <x:c r="M24" s="10" t="str">
-        <x:v>阿梨一觉睡了三百年，养大的五只小兽尽数离去。她带着五只旧饭碗、十二枚铜钱与一把锈柴刀下山寻兽。昔日的小家伙已成威震四方的妖祖，历经重重相遇与揭秘，阿梨知晓三百年封印的真相，携手五只妖祖，一同对抗祸世灭灵兽神。</x:v>
+        <x:v>阮清重生回被保姆王妈一家害死的三天前，前世她因心善引狼入室，保姆全家蜗居别墅地下室偷窃投毒，最终惨遭勒死。重生后她假装不知，趁王妈外出时用水泥将地下室彻底封死。警方破墙后，五具尸体令真相大白，王妈因盗窃、投毒被判十五年。阮清与父母团聚，恶人终得恶报，她重获新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>迷局终有破晓时</x:v>
+        <x:v>不靠谱爸妈很靠谱</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>09-08 21:18</x:v>
+        <x:v>09-09 11:08</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
         <x:v>4</x:v>
@@ -3883,10 +3775,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G25" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H25" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str">
         <x:v>其他</x:v>
@@ -3894,21 +3786,21 @@
       <x:c r="J25" s="11" t="str"/>
       <x:c r="K25" s="11" t="str"/>
       <x:c r="L25" s="10" t="str">
-        <x:v>时雨生</x:v>
+        <x:v>灵妹儿</x:v>
       </x:c>
       <x:c r="M25" s="10" t="str">
-        <x:v>男主陆承安的好友到访家中，发现家中潜藏重大疑点，留下关键线索后意外离世。陆承安凭借遗留信物逐步排查，察觉妻子沈知微隐瞒秘密，私下开展不合规研究。他主动对接警方，巧妙布局收集完整证据，配合警方成功解救被困人员，促使沈知微承担相应法律后果。风波过后，陆承安带着孩子走出过往阴霾，开启崭新平静的生活。</x:v>
+        <x:v>外表张扬的年轻夫妻在冬夜救下女婴林小小，用十七年的辛勤劳动和无条件陪伴，为她撑起温暖的家。曾经成绩落后的林小小，在父母的鼓励下重新学习，一步步成长为优秀学生。面对亲生家庭带来的资源与人生选择，她也开始重新理解血缘、养育与责任。当外界的误解影响到父母的生活，林小小决定勇敢站出来，用事实守护家人，也用努力证明真正的爱，是尊重、陪伴和彼此成就。</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>抢个新娘来当后娘第一季</x:v>
+        <x:v>美颜系统开挂，大佬全跪下</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
-        <x:v>09-08 15:10</x:v>
+        <x:v>09-09 00:10</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
         <x:v>4</x:v>
@@ -3920,10 +3812,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G26" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H26" s="11" t="n">
-        <x:v>177</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="I26" s="10" t="str">
         <x:v>其他</x:v>
@@ -3931,21 +3823,21 @@
       <x:c r="J26" s="11" t="str"/>
       <x:c r="K26" s="11" t="str"/>
       <x:c r="L26" s="10" t="str">
-        <x:v>麻辣公主</x:v>
+        <x:v>御儿</x:v>
       </x:c>
       <x:c r="M26" s="10" t="str">
-        <x:v>带着十里红妆出嫁那日，我才得知新郎早已另娶，这门亲事不过是盯上了我李家的家产。换作旁人或许忍气吞声，我偏不。我当众拒入侯府，主动上书朝廷，愿以嫁妆资援南方水患，只求解除婚约、护我父母周全。这份胆识赢得安王敬重，他以正妃之礼娶我入门。我立誓此生不做妾、不与人共侍一夫，终得一份彼此尊重的姻缘。</x:v>
+        <x:v>曾因外形饱受非议的米珂华丽转身，蜕变得耀眼又夺目。从前对她嗤之以鼻的蒋少开始频频在意，素来冷眼毒舌的陆总不知不觉深陷其中，连一向克己的商界大佬也为她打破原则。米珂凭智商与手腕周旋于众人之间，上演一场势均力敌的情感博弈。没有俗套的救赎，只有双向的拉扯。看一众高高在上的精英暗自较劲、步步沉沦，心甘情愿为她卸下防备。</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>穿书后我带萌宝上门认爹</x:v>
+        <x:v>全家施压：我反手签了过户合同</x:v>
       </x:c>
       <x:c r="C27" s="11" t="str">
-        <x:v>09-07 19:18</x:v>
+        <x:v>09-08 16:58</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
         <x:v>5</x:v>
@@ -3957,10 +3849,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G27" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H27" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I27" s="10" t="str">
         <x:v>其他</x:v>
@@ -3968,21 +3860,21 @@
       <x:c r="J27" s="11" t="str"/>
       <x:c r="K27" s="11" t="str"/>
       <x:c r="L27" s="10" t="str">
-        <x:v>虾仁不自在</x:v>
+        <x:v>灵川剧场</x:v>
       </x:c>
       <x:c r="M27" s="10" t="str">
-        <x:v>许知棠重生穿进书中，当即带着五岁儿子许小舟登门，将孩子送到亲生父亲——傅氏集团总裁傅临川面前，只想抽身退出剧情。幼儿园里儿子遭同学诬陷、老师偏心，她强势护崽，硬刚蛮横家长与失职老师。亲子鉴定尘埃落定，萌娃黏妈不黏爹，反倒让清冷总裁渐渐上心。</x:v>
+        <x:v>儿子儿媳多次提议我搬回乡下养老，将城里的宽敞住房腾出来给女方父母长期居住。我笑着点头应下，转头便将这套三室朝南的江景房产挂牌出售，最终成交二百八十万元。我随即购置了一套一室一厅的小户型，更换门锁后独自入住。他们上门索要钥匙，我没有开门。名下房产我自有主张，谁也别想插手安排。</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>重启人生，拒绝校花？</x:v>
+        <x:v>离家十年，回来女儿被换了</x:v>
       </x:c>
       <x:c r="C28" s="11" t="str">
-        <x:v>09-08 08:30</x:v>
+        <x:v>09-09 00:04</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
         <x:v>4</x:v>
@@ -3994,10 +3886,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G28" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H28" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="I28" s="10" t="str">
         <x:v>其他</x:v>
@@ -4005,81 +3897,116 @@
       <x:c r="J28" s="11" t="str"/>
       <x:c r="K28" s="11" t="str"/>
       <x:c r="L28" s="10" t="str">
-        <x:v>肆漫简</x:v>
+        <x:v>魔方影视（上剧版</x:v>
       </x:c>
       <x:c r="M28" s="10" t="str">
-        <x:v>白陌重生回到2004年高考夜，果断避开前世陷害自己的宾馆陷阱，救下被下药的校花江洛菡，彻底扭转人生走向。他不再执着于过往的情感执念，跳出卑微追爱的困局，转而关心恩师健康、规划学业与创业方向，结识志同道合的伙伴。凭借重生阅历清醒选择前路，把握青春重启人生，用行动改写原本遗憾的命运，活出全新成长轨迹。</x:v>
+        <x:v>程砚宁完成长期绝密任务归来，满心想要弥补亲情，却发现家中早已物是人非。身边亲近之人被私欲蒙蔽，制造重重骗局，试图侵占她的事业与财富。面对接连而来的算计与危机，她凭借过人的魄力与智慧步步拆解阴谋，联合正义力量搜集证据，厘清全部是非纠葛。在守护自身事业的同时，她放下过往伤痛，投身公益，完成自我和解，迎来属于自己的全新人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="11" t="n">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>来不及说的爱与痛</x:v>
+        <x:v>清禾自立</x:v>
       </x:c>
       <x:c r="C29" s="11" t="str">
-        <x:v>2026-09-04</x:v>
+        <x:v>09-08 18:22</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G29" s="11" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H29" s="11" t="str"/>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H29" s="11" t="n">
+        <x:v>69</x:v>
+      </x:c>
       <x:c r="I29" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J29" s="11" t="str"/>
       <x:c r="K29" s="11" t="str"/>
-      <x:c r="L29" s="10" t="str"/>
-      <x:c r="M29" s="10" t="str"/>
+      <x:c r="L29" s="10" t="str">
+        <x:v>晚风漫剧</x:v>
+      </x:c>
+      <x:c r="M29" s="10" t="str">
+        <x:v>1978年，母亲离世仅仅二十七天，陆清禾平静的家骤然崩塌。继母母女觊觎母亲遗物与房间，父亲陆振邦一味偏袒外人，甚至要逼她停学顾家。无依无靠的十五岁少女没有哭闹逃离，她攥紧母亲留下的缝纫机与设计底稿，靠着一针一针做布头花、帆布包艰难谋生。面对家庭压榨，她拿起证据求助工会、文教局，守住学籍与尊严，用双手挣属于自己的读书机会与未来。</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>一纸离书赴南港</x:v>
+        <x:v>末世来临，我靠囤货种田丰衣足食</x:v>
       </x:c>
       <x:c r="C30" s="11" t="str">
-        <x:v>09-03 07:00</x:v>
+        <x:v>09-09 15:30</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F30" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G30" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H30" s="11" t="n">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="I30" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="J30" s="11" t="str"/>
+      <x:c r="K30" s="11" t="str"/>
+      <x:c r="L30" s="10" t="str">
+        <x:v>渲渲动画</x:v>
+      </x:c>
+      <x:c r="M30" s="10" t="str">
+        <x:v>吴真真带着末世惨死的记忆重生，抢下秘宝空间，囤积海量物资，提前规避天灾人祸。她意外发现家人同样重生，一家人携手为末日做足准备。灾变如期而至，病毒、台风、极寒轮番降临。她机缘结识实力强悍的谢穆辰，二人从互相试探到并肩而立。面对凶悍恶徒与重重危机，吴真真依靠空间与智慧守护至亲，谢穆辰以自身力量与之守望相助，在满目疮痍的末世里，拼尽全力守住生存希望，奔赴属于他们的新生。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="11" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B31" s="10" t="str">
+        <x:v>我的植物人老公不对劲</x:v>
+      </x:c>
+      <x:c r="C31" s="11" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+      <x:c r="D31" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E31" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F30" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G30" s="11" t="n">
+      <x:c r="F31" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H30" s="11" t="n">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="I30" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="J30" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K30" s="11" t="str">
-        <x:v>0.00</x:v>
-      </x:c>
-      <x:c r="L30" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
-      </x:c>
-      <x:c r="M30" s="10" t="str"/>
+      <x:c r="G31" s="11" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H31" s="11" t="str"/>
+      <x:c r="I31" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="J31" s="11" t="str"/>
+      <x:c r="K31" s="11" t="str"/>
+      <x:c r="L31" s="10" t="str"/>
+      <x:c r="M31" s="10" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4143,30 +4070,34 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
-        <x:v>山王传奇</x:v>
+        <x:v>商场收回档口我成了全城的供应商</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>08-15 10:00</x:v>
+        <x:v>08-19 20:22</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="G2" s="10" t="n">
-        <x:v>95</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H2" s="11" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="I2" s="11" t="str"/>
-      <x:c r="J2" s="11" t="str"/>
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="I2" s="11" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="J2" s="11" t="str">
+        <x:v>1.08</x:v>
+      </x:c>
       <x:c r="K2" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜7次、累计13次，起量能力已被验证；95集长剧集；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜7次、累计12次，起量能力已被验证；经典3D制作；52集长剧集；题材契合爆款主线（都市职场）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -4174,34 +4105,30 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>商场收回档口我成了全城的供应商</x:v>
+        <x:v>天降横财，我带姐姐翻身</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>08-19 20:22</x:v>
+        <x:v>08-21 08:00</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="G3" s="10" t="n">
-        <x:v>52</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H3" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="I3" s="11" t="n">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="J3" s="11" t="str">
-        <x:v>1.08</x:v>
-      </x:c>
+      <x:c r="I3" s="11" t="str"/>
+      <x:c r="J3" s="11" t="str"/>
       <x:c r="K3" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜7次、累计12次，起量能力已被验证；经典3D制作；52集长剧集；题材契合爆款主线（都市职场）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜7次、累计8次，起量能力已被验证；经典3D制作；82集长剧集；题材契合爆款主线（家庭伦理 / 逆袭打脸）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -4209,34 +4136,30 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>1977山猎重生，我以余生偿前错</x:v>
+        <x:v>婆婆要我上交工资卡，我反手只留两千</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>08-10 20:00</x:v>
+        <x:v>08-09 11:00</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>2026-09-06</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>375</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H4" s="11" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="I4" s="11" t="n">
-        <x:v>10183</x:v>
-      </x:c>
-      <x:c r="J4" s="11" t="str">
-        <x:v>1.07</x:v>
-      </x:c>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="I4" s="11" t="str"/>
+      <x:c r="J4" s="11" t="str"/>
       <x:c r="K4" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜6次、累计26次，起量能力已被验证；经典3D制作；375集长剧集；题材契合爆款主线（年代怀旧 / 种田囤货）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜6次、累计21次，起量能力已被验证；66集长剧集；题材契合爆款主线（家庭伦理 / 逆袭打脸）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -4244,22 +4167,22 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>婆婆要我上交工资卡，我反手只留两千</x:v>
+        <x:v>山王传奇</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>08-09 11:00</x:v>
+        <x:v>08-15 10:00</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
-        <x:v>2026-09-06</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>66</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H5" s="11" t="str">
         <x:v>未标注</x:v>
@@ -4267,7 +4190,7 @@
       <x:c r="I5" s="11" t="str"/>
       <x:c r="J5" s="11" t="str"/>
       <x:c r="K5" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜6次、累计21次，起量能力已被验证；66集长剧集；题材契合爆款主线（家庭伦理 / 逆袭打脸）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜6次、累计13次，起量能力已被验证；95集长剧集；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -4275,34 +4198,30 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>沉渊三年：老槐树下的传家宝</x:v>
+        <x:v>塘埂上的人心</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>08-10 15:00</x:v>
+        <x:v>08-21 16:00</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>2026-08-25</x:v>
+        <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
         <x:v>53</x:v>
       </x:c>
       <x:c r="H6" s="11" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="I6" s="11" t="n">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="str">
-        <x:v>0.99</x:v>
-      </x:c>
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I6" s="11" t="str"/>
+      <x:c r="J6" s="11" t="str"/>
       <x:c r="K6" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜6次、累计14次，起量能力已被验证；经典3D制作；53集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜6次、累计9次，起量能力已被验证；仿真人制作；53集长剧集；题材契合爆款主线（现实反转）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -4310,10 +4229,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>垫付高铁票被拉黑，我不忍了</x:v>
+        <x:v>大伯孩子升学，却让我花钱办升学宴</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>08-19 08:00</x:v>
+        <x:v>08-22 10:00</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
         <x:v>6</x:v>
@@ -4322,10 +4241,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H7" s="11" t="str">
         <x:v>经典3D</x:v>
@@ -4333,7 +4252,7 @@
       <x:c r="I7" s="11" t="str"/>
       <x:c r="J7" s="11" t="str"/>
       <x:c r="K7" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜6次、累计9次，起量能力已被验证；经典3D制作；59集长剧集；题材契合爆款主线（都市职场 / 逆袭打脸）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜6次、累计9次，起量能力已被验证；经典3D制作；60集长剧集；题材契合爆款主线（萌宝治愈）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -4341,30 +4260,30 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>暴雪见人心</x:v>
+        <x:v>河里捞个小锦鲤，四岁萌宝旺全家</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>08-16 08:21</x:v>
+        <x:v>08-22 00:13</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F8" s="11" t="str">
-        <x:v>2026-08-25</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>68</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H8" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I8" s="11" t="str"/>
       <x:c r="J8" s="11" t="str"/>
       <x:c r="K8" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜6次、累计9次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜6次、累计8次，起量能力已被验证；81集长剧集；题材契合爆款主线（萌宝治愈 / 战神异能）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -4372,30 +4291,34 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>天降横财，我带姐姐翻身</x:v>
+        <x:v>1977山猎重生，我以余生偿前错</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>08-21 08:00</x:v>
+        <x:v>08-10 20:00</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F9" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>82</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="H9" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="I9" s="11" t="str"/>
-      <x:c r="J9" s="11" t="str"/>
+      <x:c r="I9" s="11" t="n">
+        <x:v>10183</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="str">
+        <x:v>1.07</x:v>
+      </x:c>
       <x:c r="K9" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜6次、累计8次，起量能力已被验证；经典3D制作；82集长剧集；题材契合爆款主线（家庭伦理 / 逆袭打脸）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计26次，起量能力已被验证；经典3D制作；375集长剧集；题材契合爆款主线（年代怀旧 / 种田囤货）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -4403,22 +4326,22 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>保姆心声让顾家人看清儿子真面目</x:v>
+        <x:v>八零小旺媳之冷面队长懵了</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>08-19 18:00</x:v>
+        <x:v>07-22 09:08</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="11" t="str">
-        <x:v>2026-08-25</x:v>
+        <x:v>2026-09-08</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>82</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H10" s="11" t="str">
         <x:v>经典3D</x:v>
@@ -4426,7 +4349,7 @@
       <x:c r="I10" s="11" t="str"/>
       <x:c r="J10" s="11" t="str"/>
       <x:c r="K10" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜6次、累计6次，起量能力已被验证；经典3D制作；82集长剧集；题材契合爆款主线（家庭伦理 / 美食治愈 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计14次，起量能力已被验证；经典3D制作；105集长剧集；题材契合爆款主线（年代怀旧 / 美食治愈）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -4434,34 +4357,34 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>包子里的真心</x:v>
+        <x:v>沉渊三年：老槐树下的传家宝</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>08-07 17:29</x:v>
+        <x:v>08-10 15:00</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="11" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>41</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H11" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I11" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="J11" s="11" t="str">
-        <x:v>0.91</x:v>
+        <x:v>0.99</x:v>
       </x:c>
       <x:c r="K11" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜5次、累计15次，起量能力已被验证；经典3D制作；题材契合爆款主线（婚姻情感 / 美食治愈）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计14次，起量能力已被验证；经典3D制作；53集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -4469,22 +4392,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>八零小旺媳之冷面队长懵了</x:v>
+        <x:v>岁岁和亲：换山河无恙</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>07-22 09:08</x:v>
+        <x:v>08-23 13:00</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F12" s="11" t="str">
-        <x:v>2026-09-08</x:v>
+        <x:v>2026-09-06</x:v>
       </x:c>
       <x:c r="G12" s="10" t="n">
-        <x:v>105</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H12" s="11" t="str">
         <x:v>经典3D</x:v>
@@ -4492,7 +4415,7 @@
       <x:c r="I12" s="11" t="str"/>
       <x:c r="J12" s="11" t="str"/>
       <x:c r="K12" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜5次、累计14次，起量能力已被验证；经典3D制作；105集长剧集；题材契合爆款主线（年代怀旧 / 美食治愈）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计12次，起量能力已被验证；经典3D制作；126集长剧集；题材契合爆款主线（古装宫廷）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -4500,22 +4423,22 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>福宝治愈全世界，家有萌娃岁岁安</x:v>
+        <x:v>大将军扛楼养活百万大军</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>08-21 10:00</x:v>
+        <x:v>08-22 08:02</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F13" s="11" t="str">
-        <x:v>2026-09-06</x:v>
+        <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G13" s="10" t="n">
-        <x:v>169</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H13" s="11" t="str">
         <x:v>未标注</x:v>
@@ -4523,7 +4446,7 @@
       <x:c r="I13" s="11" t="str"/>
       <x:c r="J13" s="11" t="str"/>
       <x:c r="K13" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜5次、累计14次，起量能力已被验证；169集长剧集；题材契合爆款主线（萌宝治愈）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计10次，起量能力已被验证；133集长剧集；题材契合爆款主线（古装宫廷）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -4531,10 +4454,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>塘埂上的人心</x:v>
+        <x:v>垫付高铁票被拉黑，我不忍了</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>08-21 16:00</x:v>
+        <x:v>08-19 08:00</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
         <x:v>5</x:v>
@@ -4543,18 +4466,18 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="F14" s="11" t="str">
-        <x:v>2026-08-30</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="G14" s="10" t="n">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H14" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I14" s="11" t="str"/>
       <x:c r="J14" s="11" t="str"/>
       <x:c r="K14" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜5次、累计9次，起量能力已被验证；仿真人制作；53集长剧集；题材契合爆款主线（现实反转）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计9次，起量能力已被验证；经典3D制作；59集长剧集；题材契合爆款主线（都市职场 / 逆袭打脸）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -4562,10 +4485,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>大伯孩子升学，却让我花钱办升学宴</x:v>
+        <x:v>暴雪见人心</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
-        <x:v>08-22 10:00</x:v>
+        <x:v>08-16 08:21</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
         <x:v>5</x:v>
@@ -4574,10 +4497,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="F15" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="G15" s="10" t="n">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H15" s="11" t="str">
         <x:v>经典3D</x:v>
@@ -4585,7 +4508,7 @@
       <x:c r="I15" s="11" t="str"/>
       <x:c r="J15" s="11" t="str"/>
       <x:c r="K15" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜5次、累计9次，起量能力已被验证；经典3D制作；60集长剧集；题材契合爆款主线（萌宝治愈）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计9次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -4593,30 +4516,30 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>河里捞个小锦鲤，四岁萌宝旺全家</x:v>
+        <x:v>洗手间引发的整顿</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>08-22 00:13</x:v>
+        <x:v>08-23 17:30</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F16" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="G16" s="10" t="n">
-        <x:v>81</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H16" s="11" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I16" s="11" t="str"/>
       <x:c r="J16" s="11" t="str"/>
       <x:c r="K16" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜5次、累计8次，起量能力已被验证；81集长剧集；题材契合爆款主线（萌宝治愈 / 战神异能）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计9次，起量能力已被验证；经典3D制作；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -4624,30 +4547,30 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>棠花灼</x:v>
+        <x:v>这一次，禾禾有家了</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>08-19 08:00</x:v>
+        <x:v>08-22 13:54</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F17" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="G17" s="10" t="n">
-        <x:v>55</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H17" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I17" s="11" t="str"/>
       <x:c r="J17" s="11" t="str"/>
       <x:c r="K17" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜5次、累计7次，起量能力已被验证；经典3D制作；55集长剧集；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计8次，起量能力已被验证；仿真人制作；66集长剧集；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -4655,22 +4578,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>东北阿姨：捡了个南方小土豆</x:v>
+        <x:v>棠花灼</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>08-19 07:40</x:v>
+        <x:v>08-19 08:00</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F18" s="11" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-08-27</x:v>
       </x:c>
       <x:c r="G18" s="10" t="n">
-        <x:v>68</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H18" s="11" t="str">
         <x:v>经典3D</x:v>
@@ -4678,7 +4601,7 @@
       <x:c r="I18" s="11" t="str"/>
       <x:c r="J18" s="11" t="str"/>
       <x:c r="K18" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜5次、累计6次，起量能力已被验证；经典3D制作；68集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计7次，起量能力已被验证；经典3D制作；55集长剧集；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -4686,10 +4609,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>同事蹭了我三个月顺风车，把我当免费司机</x:v>
+        <x:v>保姆心声让顾家人看清儿子真面目</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>08-19 06:00</x:v>
+        <x:v>08-19 18:00</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
         <x:v>5</x:v>
@@ -4698,18 +4621,18 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="F19" s="11" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="G19" s="10" t="n">
-        <x:v>49</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H19" s="11" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I19" s="11" t="str"/>
       <x:c r="J19" s="11" t="str"/>
       <x:c r="K19" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜5次、累计6次，起量能力已被验证；题材契合爆款主线（都市职场）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计6次，起量能力已被验证；经典3D制作；82集长剧集；题材契合爆款主线（家庭伦理 / 美食治愈 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -4717,10 +4640,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>奶奶跳完舞，后悔哭了</x:v>
+        <x:v>您好！我的代驾新郎</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>08-19 13:10</x:v>
+        <x:v>08-21 00:15</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
         <x:v>5</x:v>
@@ -4732,15 +4655,15 @@
         <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="G20" s="10" t="n">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H20" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I20" s="11" t="str"/>
       <x:c r="J20" s="11" t="str"/>
       <x:c r="K20" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜5次、累计6次，起量能力已被验证；经典3D制作；51集长剧集；题材契合爆款主线（家庭伦理）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计6次，起量能力已被验证；仿真人制作；55集长剧集；题材契合爆款主线（都市职场 / 婚姻情感）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -4872,34 +4795,34 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>先帝将我赐婚将军，他当众降我为妾</x:v>
+        <x:v>包子里的真心</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>08-11 08:00</x:v>
+        <x:v>08-07 17:29</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F25" s="11" t="str">
         <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="G25" s="10" t="n">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H25" s="11" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I25" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J25" s="11" t="str">
-        <x:v>0.14</x:v>
+        <x:v>0.91</x:v>
       </x:c>
       <x:c r="K25" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计13次，起量能力已被验证；题材契合爆款主线（古装宫廷 / 婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计15次，起量能力已被验证；经典3D制作；题材契合爆款主线（婚姻情感 / 美食治愈）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -4907,30 +4830,30 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>姐们谁管你真假千金，我天生锦鲤好命</x:v>
+        <x:v>庶女抢我女儿婚事，重生后我亲手替她披嫁衣</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
-        <x:v>08-18 11:00</x:v>
+        <x:v>08-25 08:00</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F26" s="11" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>2026-09-09</x:v>
       </x:c>
       <x:c r="G26" s="10" t="n">
-        <x:v>137</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H26" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I26" s="11" t="str"/>
       <x:c r="J26" s="11" t="str"/>
       <x:c r="K26" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计12次，起量能力已被验证；仿真人制作；137集长剧集；题材契合爆款主线（战神异能）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计15次，起量能力已被验证；经典3D制作；96集长剧集；题材契合爆款主线（家庭伦理 / 婚姻情感）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -4938,30 +4861,30 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>岁岁和亲：换山河无恙</x:v>
+        <x:v>装穷人设撑不住，我和大小姐双双摊牌了</x:v>
       </x:c>
       <x:c r="C27" s="11" t="str">
-        <x:v>08-23 13:00</x:v>
+        <x:v>08-16 08:00</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F27" s="11" t="str">
-        <x:v>2026-09-06</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="G27" s="10" t="n">
-        <x:v>126</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H27" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I27" s="11" t="str"/>
       <x:c r="J27" s="11" t="str"/>
       <x:c r="K27" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计12次，起量能力已被验证；经典3D制作；126集长剧集；题材契合爆款主线（古装宫廷）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计11次，起量能力已被验证；66集长剧集；题材契合爆款主线（都市职场 / 逆袭打脸 / 现实反转）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -4969,10 +4892,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>大将军扛楼养活百万大军</x:v>
+        <x:v>一碗面养出个状元</x:v>
       </x:c>
       <x:c r="C28" s="11" t="str">
-        <x:v>08-22 08:02</x:v>
+        <x:v>07-25 17:30</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
         <x:v>4</x:v>
@@ -4981,10 +4904,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F28" s="11" t="str">
-        <x:v>2026-09-04</x:v>
+        <x:v>2026-09-05</x:v>
       </x:c>
       <x:c r="G28" s="10" t="n">
-        <x:v>133</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H28" s="11" t="str">
         <x:v>未标注</x:v>
@@ -4992,7 +4915,7 @@
       <x:c r="I28" s="11" t="str"/>
       <x:c r="J28" s="11" t="str"/>
       <x:c r="K28" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计10次，起量能力已被验证；133集长剧集；题材契合爆款主线（古装宫廷）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计10次，起量能力已被验证；60集长剧集；题材契合爆款主线（古装宫廷 / 美食治愈）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -5000,22 +4923,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>洗手间引发的整顿</x:v>
+        <x:v>退婚毁我百年侯府，重活一世我不忍了</x:v>
       </x:c>
       <x:c r="C29" s="11" t="str">
-        <x:v>08-23 17:30</x:v>
+        <x:v>08-23 08:00</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F29" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-09</x:v>
       </x:c>
       <x:c r="G29" s="10" t="n">
-        <x:v>40</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H29" s="11" t="str">
         <x:v>经典3D</x:v>
@@ -5023,7 +4946,7 @@
       <x:c r="I29" s="11" t="str"/>
       <x:c r="J29" s="11" t="str"/>
       <x:c r="K29" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计9次，起量能力已被验证；经典3D制作；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计10次，起量能力已被验证；经典3D制作；60集长剧集；题材契合爆款主线（古装宫廷 / 婚姻情感 / 逆袭打脸）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -5031,30 +4954,30 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>我在大隋拔山抗鼎第一季</x:v>
+        <x:v>小奶团报道：我在相府做团宠第一季</x:v>
       </x:c>
       <x:c r="C30" s="11" t="str">
-        <x:v>08-21 22:40</x:v>
+        <x:v>08-21 18:15</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F30" s="11" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="G30" s="10" t="n">
-        <x:v>89</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="H30" s="11" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I30" s="11" t="str"/>
       <x:c r="J30" s="11" t="str"/>
       <x:c r="K30" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计8次，起量能力已被验证；89集长剧集；题材契合爆款主线（古装宫廷）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计9次，起量能力已被验证；经典3D制作；146集长剧集；题材契合爆款主线（萌宝治愈 / 婚姻情感）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -5062,22 +4985,22 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>这一次，禾禾有家了</x:v>
+        <x:v>重生之李阳闯八零</x:v>
       </x:c>
       <x:c r="C31" s="11" t="str">
-        <x:v>08-22 13:54</x:v>
+        <x:v>08-22 10:00</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F31" s="11" t="str">
-        <x:v>2026-08-30</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="G31" s="10" t="n">
-        <x:v>66</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H31" s="11" t="str">
         <x:v>仿真人</x:v>
@@ -5085,7 +5008,7 @@
       <x:c r="I31" s="11" t="str"/>
       <x:c r="J31" s="11" t="str"/>
       <x:c r="K31" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计8次，起量能力已被验证；仿真人制作；66集长剧集；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计9次，起量能力已被验证；仿真人制作；172集长剧集；题材契合爆款主线（年代怀旧）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -5093,30 +5016,30 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="10" t="str">
-        <x:v>医风秩序线</x:v>
+        <x:v>古今小货郎</x:v>
       </x:c>
       <x:c r="C32" s="11" t="str">
-        <x:v>08-17 11:00</x:v>
+        <x:v>08-24 10:00</x:v>
       </x:c>
       <x:c r="D32" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F32" s="11" t="str">
-        <x:v>2026-09-08</x:v>
+        <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G32" s="10" t="n">
-        <x:v>89</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H32" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I32" s="11" t="str"/>
       <x:c r="J32" s="11" t="str"/>
       <x:c r="K32" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计7次，起量能力已被验证；仿真人制作；89集长剧集；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计8次，起量能力已被验证；经典3D制作；55集长剧集；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -5124,30 +5047,30 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="10" t="str">
-        <x:v>各生归途</x:v>
+        <x:v>我在大隋拔山抗鼎第一季</x:v>
       </x:c>
       <x:c r="C33" s="11" t="str">
-        <x:v>08-17 17:50</x:v>
+        <x:v>08-21 22:40</x:v>
       </x:c>
       <x:c r="D33" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F33" s="11" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="G33" s="10" t="n">
-        <x:v>82</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H33" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I33" s="11" t="str"/>
       <x:c r="J33" s="11" t="str"/>
       <x:c r="K33" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计6次，起量能力已被验证；仿真人制作；82集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计8次，起量能力已被验证；89集长剧集；题材契合爆款主线（古装宫廷）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -5155,10 +5078,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="10" t="str">
-        <x:v>您好！我的代驾新郎</x:v>
+        <x:v>一壶热水算清十年兄弟情</x:v>
       </x:c>
       <x:c r="C34" s="11" t="str">
-        <x:v>08-21 00:15</x:v>
+        <x:v>08-24 16:00</x:v>
       </x:c>
       <x:c r="D34" s="11" t="n">
         <x:v>4</x:v>
@@ -5167,18 +5090,18 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="F34" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="G34" s="10" t="n">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H34" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I34" s="11" t="str"/>
       <x:c r="J34" s="11" t="str"/>
       <x:c r="K34" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计6次，起量能力已被验证；仿真人制作；55集长剧集；题材契合爆款主线（都市职场 / 婚姻情感）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计6次，起量能力已被验证；56集长剧集；题材契合爆款主线（家庭伦理 / 婚姻情感）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -5186,22 +5109,22 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="10" t="str">
-        <x:v>入府为婢：我在侯府攒身家</x:v>
+        <x:v>东北阿姨：捡了个南方小土豆</x:v>
       </x:c>
       <x:c r="C35" s="11" t="str">
-        <x:v>08-03 10:30</x:v>
+        <x:v>08-19 07:40</x:v>
       </x:c>
       <x:c r="D35" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F35" s="11" t="str">
-        <x:v>2026-08-25</x:v>
+        <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="G35" s="10" t="n">
-        <x:v>78</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H35" s="11" t="str">
         <x:v>经典3D</x:v>
@@ -5209,7 +5132,7 @@
       <x:c r="I35" s="11" t="str"/>
       <x:c r="J35" s="11" t="str"/>
       <x:c r="K35" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；78集长剧集；题材契合爆款主线（古装宫廷）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计6次，起量能力已被验证；经典3D制作；68集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -5217,30 +5140,30 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="10" t="str">
-        <x:v>厨神附体我把沙县开成了黑店</x:v>
+        <x:v>同事蹭了我三个月顺风车，把我当免费司机</x:v>
       </x:c>
       <x:c r="C36" s="11" t="str">
-        <x:v>08-22 11:00</x:v>
+        <x:v>08-19 06:00</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F36" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="G36" s="10" t="n">
-        <x:v>87</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H36" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I36" s="11" t="str"/>
       <x:c r="J36" s="11" t="str"/>
       <x:c r="K36" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；87集长剧集；题材契合爆款主线（都市职场 / 美食治愈 / 战神异能）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计6次，起量能力已被验证；题材契合爆款主线（都市职场）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -5248,22 +5171,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="10" t="str">
-        <x:v>寒途微光</x:v>
+        <x:v>奶奶跳完舞，后悔哭了</x:v>
       </x:c>
       <x:c r="C37" s="11" t="str">
-        <x:v>07-25 10:00</x:v>
+        <x:v>08-19 13:10</x:v>
       </x:c>
       <x:c r="D37" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F37" s="11" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="G37" s="10" t="n">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H37" s="11" t="str">
         <x:v>经典3D</x:v>
@@ -5271,7 +5194,7 @@
       <x:c r="I37" s="11" t="str"/>
       <x:c r="J37" s="11" t="str"/>
       <x:c r="K37" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计6次，起量能力已被验证；经典3D制作；51集长剧集；题材契合爆款主线（家庭伦理）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -5279,29 +5202,277 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="10" t="str">
-        <x:v>闪婚老公不一般</x:v>
+        <x:v>带着超人手下闯都市</x:v>
       </x:c>
       <x:c r="C38" s="11" t="str">
-        <x:v>08-19 09:00</x:v>
+        <x:v>08-25 06:16</x:v>
       </x:c>
       <x:c r="D38" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F38" s="11" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="G38" s="10" t="n">
-        <x:v>80</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H38" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I38" s="11" t="str"/>
       <x:c r="J38" s="11" t="str"/>
       <x:c r="K38" s="10" t="str">
+        <x:v>8-16~8-22两周期内上榜4次、累计6次，起量能力已被验证；经典3D制作；97集长剧集；题材契合爆款主线（战神异能）；回落时间短、热度余温仍在</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="11" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B39" s="10" t="str">
+        <x:v>从今天起，我的车只拉自己的菜</x:v>
+      </x:c>
+      <x:c r="C39" s="11" t="str">
+        <x:v>08-23 14:20</x:v>
+      </x:c>
+      <x:c r="D39" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E39" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F39" s="11" t="str">
+        <x:v>2026-08-28</x:v>
+      </x:c>
+      <x:c r="G39" s="10" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H39" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="I39" s="11" t="str"/>
+      <x:c r="J39" s="11" t="str"/>
+      <x:c r="K39" s="10" t="str">
+        <x:v>8-16~8-22两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；71集长剧集；题材契合爆款主线（美食治愈）；回落时间短、热度余温仍在</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="11" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B40" s="10" t="str">
+        <x:v>厨神附体我把沙县开成了黑店</x:v>
+      </x:c>
+      <x:c r="C40" s="11" t="str">
+        <x:v>08-22 11:00</x:v>
+      </x:c>
+      <x:c r="D40" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E40" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F40" s="11" t="str">
+        <x:v>2026-08-29</x:v>
+      </x:c>
+      <x:c r="G40" s="10" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="H40" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="I40" s="11" t="str"/>
+      <x:c r="J40" s="11" t="str"/>
+      <x:c r="K40" s="10" t="str">
+        <x:v>8-16~8-22两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；87集长剧集；题材契合爆款主线（都市职场 / 美食治愈 / 战神异能）；回落时间短、热度余温仍在</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="11" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B41" s="10" t="str">
+        <x:v>天下第一婿，重振百年门庭</x:v>
+      </x:c>
+      <x:c r="C41" s="11" t="str">
+        <x:v>08-23 11:00</x:v>
+      </x:c>
+      <x:c r="D41" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E41" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F41" s="11" t="str">
+        <x:v>2026-08-28</x:v>
+      </x:c>
+      <x:c r="G41" s="10" t="n">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="H41" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I41" s="11" t="str"/>
+      <x:c r="J41" s="11" t="str"/>
+      <x:c r="K41" s="10" t="str">
+        <x:v>8-16~8-22两周期内上榜4次、累计5次，起量能力已被验证；仿真人制作；115集长剧集；题材契合爆款主线（古装宫廷）；回落时间短、热度余温仍在</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="11" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B42" s="10" t="str">
+        <x:v>寻亲23年，找回来的女儿身价百亿</x:v>
+      </x:c>
+      <x:c r="C42" s="11" t="str">
+        <x:v>08-22 07:48</x:v>
+      </x:c>
+      <x:c r="D42" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E42" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F42" s="11" t="str">
+        <x:v>2026-08-28</x:v>
+      </x:c>
+      <x:c r="G42" s="10" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="H42" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="I42" s="11" t="str"/>
+      <x:c r="J42" s="11" t="str"/>
+      <x:c r="K42" s="10" t="str">
+        <x:v>8-16~8-22两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；140集长剧集；题材契合爆款主线（家庭伦理 / 现实反转）；回落时间短、热度余温仍在</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="11" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B43" s="10" t="str">
+        <x:v>我的破单车，你赔不起</x:v>
+      </x:c>
+      <x:c r="C43" s="11" t="str">
+        <x:v>08-24 10:00</x:v>
+      </x:c>
+      <x:c r="D43" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E43" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F43" s="11" t="str">
+        <x:v>2026-08-28</x:v>
+      </x:c>
+      <x:c r="G43" s="10" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H43" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="I43" s="11" t="str"/>
+      <x:c r="J43" s="11" t="str"/>
+      <x:c r="K43" s="10" t="str">
+        <x:v>8-16~8-22两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；题材契合爆款主线（都市职场）；回落时间短、热度余温仍在</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="11" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B44" s="10" t="str">
+        <x:v>纹身儿媳替我撑腰</x:v>
+      </x:c>
+      <x:c r="C44" s="11" t="str">
+        <x:v>08-22 06:00</x:v>
+      </x:c>
+      <x:c r="D44" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E44" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F44" s="11" t="str">
+        <x:v>2026-08-28</x:v>
+      </x:c>
+      <x:c r="G44" s="10" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H44" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I44" s="11" t="str"/>
+      <x:c r="J44" s="11" t="str"/>
+      <x:c r="K44" s="10" t="str">
+        <x:v>8-16~8-22两周期内上榜4次、累计5次，起量能力已被验证；仿真人制作；63集长剧集；题材契合爆款主线（家庭伦理）；回落时间短、热度余温仍在</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="11" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B45" s="10" t="str">
+        <x:v>重生后婆婆终于有边界感了</x:v>
+      </x:c>
+      <x:c r="C45" s="11" t="str">
+        <x:v>08-24 16:24</x:v>
+      </x:c>
+      <x:c r="D45" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E45" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F45" s="11" t="str">
+        <x:v>2026-08-28</x:v>
+      </x:c>
+      <x:c r="G45" s="10" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H45" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="I45" s="11" t="str"/>
+      <x:c r="J45" s="11" t="str"/>
+      <x:c r="K45" s="10" t="str">
+        <x:v>8-16~8-22两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；54集长剧集；题材契合爆款主线（家庭伦理）；回落时间短、热度余温仍在</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="11" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B46" s="10" t="str">
+        <x:v>闪婚老公不一般</x:v>
+      </x:c>
+      <x:c r="C46" s="11" t="str">
+        <x:v>08-19 09:00</x:v>
+      </x:c>
+      <x:c r="D46" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E46" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F46" s="11" t="str">
+        <x:v>2026-09-07</x:v>
+      </x:c>
+      <x:c r="G46" s="10" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H46" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I46" s="11" t="str"/>
+      <x:c r="J46" s="11" t="str"/>
+      <x:c r="K46" s="10" t="str">
         <x:v>8-16~8-22两周期内上榜4次、累计5次，起量能力已被验证；仿真人制作；80集长剧集；题材契合爆款主线（家庭伦理 / 婚姻情感）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
@@ -5998,8 +6169,12 @@
       <x:c r="G20" s="10" t="str">
         <x:v>心动漫剧场</x:v>
       </x:c>
-      <x:c r="H20" s="11" t="str"/>
-      <x:c r="I20" s="10" t="str"/>
+      <x:c r="H20" s="11" t="str">
+        <x:v>已上榜</x:v>
+      </x:c>
+      <x:c r="I20" s="10" t="str">
+        <x:v>2026-09-13</x:v>
+      </x:c>
       <x:c r="J20" s="10" t="str">
         <x:v>大晋七公主沈令仪，自幼被冷落于听竹宫，沉默藏锋，苟全性命。宫宴之上，太子带回的秦照雪笑盈盈提议将她送去北狄和亲。满殿以为皇帝会点头，他却掷出“废太子”三字。一夜之间，沈令仪被推到台前。北狄求和的急报恰在此时入京——与她方才所言分毫不差。可当她回望母亲遗下的那半卷秘策时，才发现这局棋，早在二十年前就已落子。</x:v>
       </x:c>
@@ -6578,7 +6753,7 @@
         <x:v>已上榜</x:v>
       </x:c>
       <x:c r="I37" s="10" t="str">
-        <x:v>2026-09-12</x:v>
+        <x:v>2026-09-12、2026-09-13</x:v>
       </x:c>
       <x:c r="J37" s="10" t="str">
         <x:v>顾佑璃前世因阻拦哥哥救妹遭全家怨恨。重生后她选择放手，导致哥哥重伤失声、事业尽毁，家族陷入混乱。面对家人的道德绑架与诉讼勒索，顾佑璃不再妥协，公开火灾真相并切断经济供养。最终她摆脱原生家庭束缚，在养母支持下开启全新人生，实现自我救赎。</x:v>
@@ -9546,7 +9721,7 @@
         <x:v>已上榜</x:v>
       </x:c>
       <x:c r="I124" s="10" t="str">
-        <x:v>2026-09-09、2026-09-10、2026-09-11</x:v>
+        <x:v>2026-09-09、2026-09-10、2026-09-11、2026-09-12</x:v>
       </x:c>
       <x:c r="J124" s="10" t="str">
         <x:v>韩清夏被至亲推向绝境，失去家园，没能守住重要伙伴。再次睁眼，她回到了灾变来临前，并意外激活超级领主系统。她果断卖房筹资、囤积物资，将废弃防空洞升级为坚固基地，与战犬夏天并肩成长。危机爆发后，她凭借清醒判断、强大异能和充足准备救下幸存者，组建盛夏联盟。面对旧日亲人的算计、各方势力的试探与接连不断的考验，韩清夏不再退让。这一世，她要守住伙伴、掌握命运，在废墟之上建起属于自己的家园。</x:v>
@@ -10026,7 +10201,7 @@
         <x:v>已上榜</x:v>
       </x:c>
       <x:c r="I138" s="10" t="str">
-        <x:v>2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
       </x:c>
       <x:c r="J138" s="10" t="str">
         <x:v>沈峥重生回海城医院急诊大厅，那四个从非洲归来的学生正走进大门。周宇扬手臂上的异样红疹让他心头一紧。这一次，他果断按下警报按钮。辅导员李健急得拍窗，家长投诉不断。监控画面里，陈浩背包中的动物残骨悄然露出。有些秘密，比病毒藏得更深。</x:v>
@@ -10716,7 +10891,7 @@
         <x:v>已上榜</x:v>
       </x:c>
       <x:c r="I158" s="10" t="str">
-        <x:v>2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
       </x:c>
       <x:c r="J158" s="10" t="str">
         <x:v>沈家人人都是天才，唯独小女儿沈惊絮是公认的傻子。没人知道，她不仅装傻多年，还带着前世金牌律师的记忆重生而来。本想闭嘴躺平一生，谁料内鬼勾结资本做空沈氏，一纸合同就要让全家净身出户、背上百亿债务。父亲落笔前，她终于按住协议“这字不能签！”绝地反杀的沈惊絮，一步步挫败了对沈家的围剿，也让全家人重新认识了自己。沈家也迎来了新生。</x:v>
@@ -15737,8 +15912,12 @@
       <x:c r="G20" s="10" t="str">
         <x:v>心动漫剧场</x:v>
       </x:c>
-      <x:c r="H20" s="11" t="str"/>
-      <x:c r="I20" s="10" t="str"/>
+      <x:c r="H20" s="11" t="str">
+        <x:v>已上榜</x:v>
+      </x:c>
+      <x:c r="I20" s="10" t="str">
+        <x:v>2026-09-13</x:v>
+      </x:c>
       <x:c r="J20" s="10" t="str">
         <x:v>大晋七公主沈令仪，自幼被冷落于听竹宫，沉默藏锋，苟全性命。宫宴之上，太子带回的秦照雪笑盈盈提议将她送去北狄和亲。满殿以为皇帝会点头，他却掷出“废太子”三字。一夜之间，沈令仪被推到台前。北狄求和的急报恰在此时入京——与她方才所言分毫不差。可当她回望母亲遗下的那半卷秘策时，才发现这局棋，早在二十年前就已落子。</x:v>
       </x:c>
@@ -16009,8 +16188,12 @@
       <x:c r="G28" s="10" t="str">
         <x:v>至尊爽剧社</x:v>
       </x:c>
-      <x:c r="H28" s="11" t="str"/>
-      <x:c r="I28" s="10" t="str"/>
+      <x:c r="H28" s="11" t="str">
+        <x:v>已上榜</x:v>
+      </x:c>
+      <x:c r="I28" s="10" t="str">
+        <x:v>2026-09-13</x:v>
+      </x:c>
       <x:c r="J28" s="10" t="str">
         <x:v>三十二岁那年，贺川用六年孤注一掷的钻研，换来了七千六百万的回报。可财富还没捂热，先尝到的却是亲人无度的索取。他谎称只赚五十万，叮嘱保密，却挡不住消息走漏。隔天登门的亲戚不止要借钱买房，更联手外人盗用他的身份资料，试图冒名签约、伪造担保债务。贺川报警取证，警方介入追回大部分资金，涉案者包括部分机构人员均承担了法律责任，这笔帐，能否算清？</x:v>
       </x:c>
@@ -16317,7 +16500,7 @@
         <x:v>已上榜</x:v>
       </x:c>
       <x:c r="I37" s="10" t="str">
-        <x:v>2026-09-12</x:v>
+        <x:v>2026-09-12、2026-09-13</x:v>
       </x:c>
       <x:c r="J37" s="10" t="str">
         <x:v>顾佑璃前世因阻拦哥哥救妹遭全家怨恨。重生后她选择放手，导致哥哥重伤失声、事业尽毁，家族陷入混乱。面对家人的道德绑架与诉讼勒索，顾佑璃不再妥协，公开火灾真相并切断经济供养。最终她摆脱原生家庭束缚，在养母支持下开启全新人生，实现自我救赎。</x:v>
@@ -16589,8 +16772,12 @@
       <x:c r="G45" s="10" t="str">
         <x:v>星漫世界</x:v>
       </x:c>
-      <x:c r="H45" s="11" t="str"/>
-      <x:c r="I45" s="10" t="str"/>
+      <x:c r="H45" s="11" t="str">
+        <x:v>已上榜</x:v>
+      </x:c>
+      <x:c r="I45" s="10" t="str">
+        <x:v>2026-09-12</x:v>
+      </x:c>
       <x:c r="J45" s="10" t="str">
         <x:v>澜江市，刚结束七年恋情的江晓棠如愿上岸，决然转身离去。没曾想，前男友贺铭以转业安置身份，空降进入同一应急管理局。旧爱狭路相逢，尴尬拉扯还未落幕，滨南快速路突发危化品连环车祸。报到首日的贺铭无视现场命令，冲破警戒线冲入火场，拼尽全力营救被困女童。就在撤离瞬间轿车爆炸，火光席卷全场，他纵身将怀中女孩与赶来的女医生向澜舒一并护在身下。</x:v>
       </x:c>
@@ -17179,7 +17366,7 @@
         <x:v>已上榜</x:v>
       </x:c>
       <x:c r="I62" s="10" t="str">
-        <x:v>2026-09-12</x:v>
+        <x:v>2026-09-12、2026-09-13</x:v>
       </x:c>
       <x:c r="J62" s="10" t="str">
         <x:v>沈泽凯衣锦还乡想要报恩，却得知当年为供他读书卖掉家中唯一土地的小舅早已病故。悲痛之际，他在海边捡到金色珍珠，意外重返少年，觉醒小世界沙盘，可洞悉整片海域动向。重活一世，小舅依旧为他倾尽所有。前世已是县城首富的沈泽凯，打算利用暑假借助沙盘帮小舅赚钱娶妻。赶海寻宝、乘风破浪，他屡次邂逅深海智慧生灵，逐步揭开海王宝藏的秘密。这一世，他守护至亲，驰骋碧海，活出别样人生。</x:v>
@@ -17933,7 +18120,7 @@
         <x:v>已上榜</x:v>
       </x:c>
       <x:c r="I84" s="10" t="str">
-        <x:v>2026-09-11、2026-09-12</x:v>
+        <x:v>2026-09-11、2026-09-12、2026-09-13</x:v>
       </x:c>
       <x:c r="J84" s="10" t="str">
         <x:v>青石沟果农为省下代办三分钱，甩开中间商周成岳，直接对接收购商方洪生收桃。可脱离周成岳统筹调度后，摘桃、排单、装车乱象丛生，桃子积压损耗。周成岳转身接手偏远的十里湾桃园，凭口碑站稳脚跟。经历一季波折，青石沟众人幡然醒悟，重新读懂代办的价值。</x:v>
@@ -17971,7 +18158,7 @@
         <x:v>已上榜</x:v>
       </x:c>
       <x:c r="I85" s="10" t="str">
-        <x:v>2026-09-10、2026-09-11</x:v>
+        <x:v>2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
       </x:c>
       <x:c r="J85" s="10" t="str">
         <x:v>七岁那年，许荞意外被留在县城，幸得饭馆老板宋春桃照顾，从此与宋小满成为一家人。一路成长中，她在妈妈的守护下读书、追梦，也渐渐学会独立与担当。多年后，面对家庭与事业的新考验，许荞决定站到妈妈身前，守住这个温暖的家。爱从不只由血缘定义，真正的家人，是彼此守护、相互托举、共同成长。</x:v>
@@ -19175,7 +19362,7 @@
         <x:v>已上榜</x:v>
       </x:c>
       <x:c r="I120" s="10" t="str">
-        <x:v>2026-09-09、2026-09-10、2026-09-11</x:v>
+        <x:v>2026-09-09、2026-09-10、2026-09-11、2026-09-12</x:v>
       </x:c>
       <x:c r="J120" s="10" t="str">
         <x:v>韩清夏被至亲推向绝境，失去家园，没能守住重要伙伴。再次睁眼，她回到了灾变来临前，并意外激活超级领主系统。她果断卖房筹资、囤积物资，将废弃防空洞升级为坚固基地，与战犬夏天并肩成长。危机爆发后，她凭借清醒判断、强大异能和充足准备救下幸存者，组建盛夏联盟。面对旧日亲人的算计、各方势力的试探与接连不断的考验，韩清夏不再退让。这一世，她要守住伙伴、掌握命运，在废墟之上建起属于自己的家园。</x:v>
@@ -19791,7 +19978,7 @@
         <x:v>已上榜</x:v>
       </x:c>
       <x:c r="I138" s="10" t="str">
-        <x:v>2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
       </x:c>
       <x:c r="J138" s="10" t="str">
         <x:v>沈峥重生回海城医院急诊大厅，那四个从非洲归来的学生正走进大门。周宇扬手臂上的异样红疹让他心头一紧。这一次，他果断按下警报按钮。辅导员李健急得拍窗，家长投诉不断。监控画面里，陈浩背包中的动物残骨悄然露出。有些秘密，比病毒藏得更深。</x:v>
@@ -20481,7 +20668,7 @@
         <x:v>已上榜</x:v>
       </x:c>
       <x:c r="I158" s="10" t="str">
-        <x:v>2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
       </x:c>
       <x:c r="J158" s="10" t="str">
         <x:v>沈家人人都是天才，唯独小女儿沈惊絮是公认的傻子。没人知道，她不仅装傻多年，还带着前世金牌律师的记忆重生而来。本想闭嘴躺平一生，谁料内鬼勾结资本做空沈氏，一纸合同就要让全家净身出户、背上百亿债务。父亲落笔前，她终于按住协议“这字不能签！”绝地反杀的沈惊絮，一步步挫败了对沈家的围剿，也让全家人重新认识了自己。沈家也迎来了新生。</x:v>
@@ -24852,10 +25039,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>768</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>49.0%</x:v>
+        <x:v>50.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -24866,7 +25053,7 @@
         <x:v>465</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>29.7%</x:v>
+        <x:v>28.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -24874,10 +25061,10 @@
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>334</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>21.3%</x:v>
+        <x:v>21.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
@@ -24901,10 +25088,10 @@
         <x:v>30-49集</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>11.1%</x:v>
+        <x:v>11%</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -24912,10 +25099,10 @@
         <x:v>50-79集</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>618</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>42.5%</x:v>
+        <x:v>42.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -24923,7 +25110,7 @@
         <x:v>80-99集</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>184</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
         <x:v>12.6%</x:v>
@@ -24934,10 +25121,10 @@
         <x:v>100集以上</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>490</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>33.7%</x:v>
+        <x:v>34.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
@@ -24961,7 +25148,7 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>685</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
         <x:v>43.7%</x:v>
@@ -24972,10 +25159,10 @@
         <x:v>婚姻/情感</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>282</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>18.0%</x:v>
+        <x:v>17.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -24983,7 +25170,7 @@
         <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>148</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
         <x:v>9.4%</x:v>
@@ -24994,10 +25181,10 @@
         <x:v>年代怀旧/种田囤货</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>136</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>8.7%</x:v>
+        <x:v>8.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -25005,7 +25192,7 @@
         <x:v>家庭伦理/萌宝</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>134</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
         <x:v>8.6%</x:v>
@@ -25016,10 +25203,10 @@
         <x:v>战神/异能/爽文</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>134</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>8.6%</x:v>
+        <x:v>8.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -25027,10 +25214,10 @@
         <x:v>现实反转/人性</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>6.5%</x:v>
+        <x:v>6.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -25038,7 +25225,7 @@
         <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
         <x:v>5.7%</x:v>
@@ -25049,10 +25236,10 @@
         <x:v>逆袭/打脸</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>4.6%</x:v>
+        <x:v>4.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -25063,7 +25250,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>4.4%</x:v>
+        <x:v>4.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="22" customHeight="1">
@@ -25095,7 +25282,7 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="10" t="str">
-        <x:v>上榜27次</x:v>
+        <x:v>上榜28次</x:v>
       </x:c>
       <x:c r="B30" s="11" t="n">
         <x:v>1</x:v>
@@ -25109,7 +25296,7 @@
         <x:v>上榜26次</x:v>
       </x:c>
       <x:c r="B31" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C31" s="11" t="str">
         <x:v>0.1%</x:v>
@@ -25120,7 +25307,7 @@
         <x:v>上榜25次</x:v>
       </x:c>
       <x:c r="B32" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C32" s="11" t="str">
         <x:v>0.1%</x:v>
@@ -25128,10 +25315,10 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="10" t="str">
-        <x:v>上榜23次</x:v>
+        <x:v>上榜24次</x:v>
       </x:c>
       <x:c r="B33" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C33" s="11" t="str">
         <x:v>0.1%</x:v>
@@ -25139,10 +25326,10 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="10" t="str">
-        <x:v>上榜22次</x:v>
+        <x:v>上榜23次</x:v>
       </x:c>
       <x:c r="B34" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C34" s="11" t="str">
         <x:v>0.1%</x:v>
@@ -25150,18 +25337,18 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="10" t="str">
-        <x:v>上榜21次</x:v>
+        <x:v>上榜22次</x:v>
       </x:c>
       <x:c r="B35" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C35" s="11" t="str">
-        <x:v>0.2%</x:v>
+        <x:v>0.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="10" t="str">
-        <x:v>上榜20次</x:v>
+        <x:v>上榜21次</x:v>
       </x:c>
       <x:c r="B36" s="11" t="n">
         <x:v>3</x:v>
@@ -25172,10 +25359,10 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="10" t="str">
-        <x:v>上榜19次</x:v>
+        <x:v>上榜20次</x:v>
       </x:c>
       <x:c r="B37" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C37" s="11" t="str">
         <x:v>0.1%</x:v>
@@ -25183,10 +25370,10 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="10" t="str">
-        <x:v>上榜18次</x:v>
+        <x:v>上榜19次</x:v>
       </x:c>
       <x:c r="B38" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C38" s="11" t="str">
         <x:v>0.1%</x:v>
@@ -25194,284 +25381,284 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="10" t="str">
-        <x:v>上榜17次</x:v>
+        <x:v>上榜18次</x:v>
       </x:c>
       <x:c r="B39" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C39" s="11" t="str">
-        <x:v>0.1%</x:v>
+        <x:v>0.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="10" t="str">
-        <x:v>上榜16次</x:v>
+        <x:v>上榜17次</x:v>
       </x:c>
       <x:c r="B40" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C40" s="11" t="str">
-        <x:v>0.3%</x:v>
+        <x:v>0.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="10" t="str">
-        <x:v>上榜15次</x:v>
+        <x:v>上榜16次</x:v>
       </x:c>
       <x:c r="B41" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C41" s="11" t="str">
-        <x:v>0.4%</x:v>
+        <x:v>0.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="10" t="str">
-        <x:v>上榜14次</x:v>
+        <x:v>上榜15次</x:v>
       </x:c>
       <x:c r="B42" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C42" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="10" t="str">
-        <x:v>上榜13次</x:v>
+        <x:v>上榜14次</x:v>
       </x:c>
       <x:c r="B43" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C43" s="11" t="str">
-        <x:v>0.7%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="10" t="str">
-        <x:v>上榜12次</x:v>
+        <x:v>上榜13次</x:v>
       </x:c>
       <x:c r="B44" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C44" s="11" t="str">
-        <x:v>0.7%</x:v>
+        <x:v>0.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="10" t="str">
-        <x:v>上榜11次</x:v>
+        <x:v>上榜12次</x:v>
       </x:c>
       <x:c r="B45" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C45" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>0.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="10" t="str">
-        <x:v>上榜10次</x:v>
+        <x:v>上榜11次</x:v>
       </x:c>
       <x:c r="B46" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C46" s="11" t="str">
-        <x:v>1.2%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="10" t="str">
-        <x:v>上榜9次</x:v>
+        <x:v>上榜10次</x:v>
       </x:c>
       <x:c r="B47" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C47" s="11" t="str">
-        <x:v>1.7%</x:v>
+        <x:v>1.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="10" t="str">
-        <x:v>上榜8次</x:v>
+        <x:v>上榜9次</x:v>
       </x:c>
       <x:c r="B48" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C48" s="11" t="str">
-        <x:v>2.6%</x:v>
+        <x:v>1.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="10" t="str">
-        <x:v>上榜7次</x:v>
+        <x:v>上榜8次</x:v>
       </x:c>
       <x:c r="B49" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C49" s="11" t="str">
-        <x:v>2.6%</x:v>
+        <x:v>2.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="10" t="str">
-        <x:v>上榜6次</x:v>
+        <x:v>上榜7次</x:v>
       </x:c>
       <x:c r="B50" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C50" s="11" t="str">
-        <x:v>3.4%</x:v>
+        <x:v>2.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="10" t="str">
-        <x:v>上榜5次</x:v>
+        <x:v>上榜6次</x:v>
       </x:c>
       <x:c r="B51" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C51" s="11" t="str">
-        <x:v>4.5%</x:v>
+        <x:v>3.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="10" t="str">
-        <x:v>上榜4次</x:v>
+        <x:v>上榜5次</x:v>
       </x:c>
       <x:c r="B52" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C52" s="11" t="str">
-        <x:v>5.1%</x:v>
+        <x:v>4.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="10" t="str">
-        <x:v>上榜3次</x:v>
+        <x:v>上榜4次</x:v>
       </x:c>
       <x:c r="B53" s="11" t="n">
-        <x:v>167</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C53" s="11" t="str">
-        <x:v>10.7%</x:v>
+        <x:v>5.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="10" t="str">
-        <x:v>上榜2次</x:v>
+        <x:v>上榜3次</x:v>
       </x:c>
       <x:c r="B54" s="11" t="n">
-        <x:v>306</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C54" s="11" t="str">
-        <x:v>19.5%</x:v>
+        <x:v>10.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="10" t="str">
+        <x:v>上榜2次</x:v>
+      </x:c>
+      <x:c r="B55" s="11" t="n">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="C55" s="11" t="str">
+        <x:v>19.9%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="10" t="str">
         <x:v>上榜1次</x:v>
       </x:c>
-      <x:c r="B55" s="11" t="n">
-        <x:v>695</x:v>
-      </x:c>
-      <x:c r="C55" s="11" t="str">
-        <x:v>44.4%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" ht="22" customHeight="1">
-      <x:c r="A57" s="14" t="str">
+      <x:c r="B56" s="11" t="n">
+        <x:v>703</x:v>
+      </x:c>
+      <x:c r="C56" s="11" t="str">
+        <x:v>43.7%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="22" customHeight="1">
+      <x:c r="A58" s="14" t="str">
         <x:v>版权类型分布</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="24" customHeight="1">
-      <x:c r="A58" s="5" t="str">
+    <x:row r="59" ht="24" customHeight="1">
+      <x:c r="A59" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B58" t="str">
+      <x:c r="B59" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C58" t="str">
+      <x:c r="C59" t="str">
         <x:v>占比</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59">
-      <x:c r="A59" s="10" t="str">
-        <x:v>CP自营</x:v>
-      </x:c>
-      <x:c r="B59" s="11" t="n">
-        <x:v>1116</x:v>
-      </x:c>
-      <x:c r="C59" s="11" t="str">
-        <x:v>71.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>CP自营</x:v>
       </x:c>
       <x:c r="B60" s="11" t="n">
-        <x:v>440</x:v>
+        <x:v>1121</x:v>
       </x:c>
       <x:c r="C60" s="11" t="str">
-        <x:v>28.1%</x:v>
+        <x:v>69.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="10" t="str">
-        <x:v>CP托管</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="B61" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="C61" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>29.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="10" t="str">
+        <x:v>CP托管</x:v>
+      </x:c>
+      <x:c r="B62" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C62" s="11" t="str">
+        <x:v>0.6%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="10" t="str">
         <x:v>番茄原创</x:v>
       </x:c>
-      <x:c r="B62" s="11" t="n">
+      <x:c r="B63" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C62" s="11" t="str">
+      <x:c r="C63" s="11" t="str">
         <x:v>0.1%</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" ht="22" customHeight="1">
-      <x:c r="A64" s="14" t="str">
+    <x:row r="65" ht="22" customHeight="1">
+      <x:c r="A65" s="14" t="str">
         <x:v>发布抖音号TOP15·上榜次数</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" ht="24" customHeight="1">
-      <x:c r="A65" s="5" t="str">
+    <x:row r="66" ht="24" customHeight="1">
+      <x:c r="A66" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B65" t="str">
+      <x:c r="B66" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C65" t="str">
+      <x:c r="C66" t="str">
         <x:v>占比</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66">
-      <x:c r="A66" s="10" t="str">
-        <x:v>番荔枝剧场</x:v>
-      </x:c>
-      <x:c r="B66" s="11" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C66" s="11" t="str">
-        <x:v>1.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
+        <x:v>番荔枝剧场</x:v>
       </x:c>
       <x:c r="B67" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C67" s="11" t="str">
         <x:v>1.1%</x:v>
@@ -25479,43 +25666,43 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="B68" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C68" s="11" t="str">
-        <x:v>1%</x:v>
+        <x:v>1.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="10" t="str">
-        <x:v>渲渲动画</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="B69" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C69" s="11" t="str">
-        <x:v>0.8%</x:v>
+        <x:v>1%</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="10" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>渲渲动画</x:v>
       </x:c>
       <x:c r="B70" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C70" s="11" t="str">
-        <x:v>0.7%</x:v>
+        <x:v>0.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="10" t="str">
-        <x:v>东山啊</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="B71" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C71" s="11" t="str">
         <x:v>0.7%</x:v>
@@ -25526,7 +25713,7 @@
         <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="B72" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C72" s="11" t="str">
         <x:v>0.7%</x:v>
@@ -25534,10 +25721,10 @@
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="10" t="str">
-        <x:v>左手良画</x:v>
+        <x:v>东山啊</x:v>
       </x:c>
       <x:c r="B73" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C73" s="11" t="str">
         <x:v>0.6%</x:v>
@@ -25545,10 +25732,10 @@
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="10" t="str">
-        <x:v>阅友动漫</x:v>
+        <x:v>左手良画</x:v>
       </x:c>
       <x:c r="B74" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C74" s="11" t="str">
         <x:v>0.6%</x:v>
@@ -25556,10 +25743,10 @@
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>阅友动漫</x:v>
       </x:c>
       <x:c r="B75" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C75" s="11" t="str">
         <x:v>0.6%</x:v>
@@ -25567,10 +25754,10 @@
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="10" t="str">
-        <x:v>茉冉漫影</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="B76" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C76" s="11" t="str">
         <x:v>0.5%</x:v>
@@ -25578,7 +25765,7 @@
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="10" t="str">
-        <x:v>每日沙雕速递</x:v>
+        <x:v>茉冉漫影</x:v>
       </x:c>
       <x:c r="B77" s="11" t="n">
         <x:v>26</x:v>
@@ -25592,7 +25779,7 @@
         <x:v>在下轻北</x:v>
       </x:c>
       <x:c r="B78" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C78" s="11" t="str">
         <x:v>0.5%</x:v>
@@ -25600,10 +25787,10 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="10" t="str">
-        <x:v>一张不够花</x:v>
+        <x:v>每日沙雕速递</x:v>
       </x:c>
       <x:c r="B79" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C79" s="11" t="str">
         <x:v>0.5%</x:v>
@@ -25614,59 +25801,59 @@
         <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="B80" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C80" s="11" t="str">
         <x:v>0.5%</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" ht="22" customHeight="1">
-      <x:c r="A82" s="14" t="str">
+    <x:row r="81">
+      <x:c r="A81" s="10" t="str">
+        <x:v>壹琚-娜娜看剧</x:v>
+      </x:c>
+      <x:c r="B81" s="11" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C81" s="11" t="str">
+        <x:v>0.5%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="22" customHeight="1">
+      <x:c r="A83" s="14" t="str">
         <x:v>发布抖音号TOP15·上榜剧数</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" ht="24" customHeight="1">
-      <x:c r="A83" s="5" t="str">
+    <x:row r="84" ht="24" customHeight="1">
+      <x:c r="A84" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B83" t="str">
+      <x:c r="B84" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C83" t="str">
+      <x:c r="C84" t="str">
         <x:v>占比</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84">
-      <x:c r="A84" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
-      </x:c>
-      <x:c r="B84" s="11" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C84" s="11" t="str">
-        <x:v>1.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="B85" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C85" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>1.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="B86" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C86" s="11" t="str">
-        <x:v>0.4%</x:v>
+        <x:v>0.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -25674,18 +25861,18 @@
         <x:v>星漫世界</x:v>
       </x:c>
       <x:c r="B87" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C87" s="11" t="str">
-        <x:v>0.4%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="10" t="str">
-        <x:v>渲渲动画</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="B88" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C88" s="11" t="str">
         <x:v>0.4%</x:v>
@@ -25693,10 +25880,10 @@
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="B89" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C89" s="11" t="str">
         <x:v>0.4%</x:v>
@@ -25704,7 +25891,7 @@
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="10" t="str">
-        <x:v>番荔枝剧场</x:v>
+        <x:v>渲渲动画</x:v>
       </x:c>
       <x:c r="B90" s="11" t="n">
         <x:v>6</x:v>
@@ -25715,7 +25902,7 @@
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="10" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="B91" s="11" t="n">
         <x:v>6</x:v>
@@ -25726,7 +25913,7 @@
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>番荔枝剧场</x:v>
       </x:c>
       <x:c r="B92" s="11" t="n">
         <x:v>6</x:v>
@@ -25737,18 +25924,18 @@
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="10" t="str">
-        <x:v>阅友动漫</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="B93" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C93" s="11" t="str">
-        <x:v>0.3%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="10" t="str">
-        <x:v>云影漫剧</x:v>
+        <x:v>阅友动漫</x:v>
       </x:c>
       <x:c r="B94" s="11" t="n">
         <x:v>5</x:v>
@@ -25759,7 +25946,7 @@
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="10" t="str">
-        <x:v>小小动画</x:v>
+        <x:v>云影漫剧</x:v>
       </x:c>
       <x:c r="B95" s="11" t="n">
         <x:v>5</x:v>
@@ -25770,7 +25957,7 @@
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="10" t="str">
-        <x:v>云间漫剧-玉川</x:v>
+        <x:v>小小动画</x:v>
       </x:c>
       <x:c r="B96" s="11" t="n">
         <x:v>5</x:v>
@@ -25781,7 +25968,7 @@
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="10" t="str">
-        <x:v>潮汐互娱-爽剧社</x:v>
+        <x:v>云间漫剧-玉川</x:v>
       </x:c>
       <x:c r="B97" s="11" t="n">
         <x:v>5</x:v>
@@ -25792,7 +25979,7 @@
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="10" t="str">
-        <x:v>暖星追剧</x:v>
+        <x:v>星屿漫剧场</x:v>
       </x:c>
       <x:c r="B98" s="11" t="n">
         <x:v>5</x:v>
@@ -25801,91 +25988,91 @@
         <x:v>0.3%</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" ht="22" customHeight="1">
-      <x:c r="A100" s="14" t="str">
+    <x:row r="99">
+      <x:c r="A99" s="10" t="str">
+        <x:v>至尊爽剧社</x:v>
+      </x:c>
+      <x:c r="B99" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C99" s="11" t="str">
+        <x:v>0.3%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="22" customHeight="1">
+      <x:c r="A101" s="14" t="str">
         <x:v>付费榜主题分布</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" ht="24" customHeight="1">
-      <x:c r="A101" s="5" t="str">
+    <x:row r="102" ht="24" customHeight="1">
+      <x:c r="A102" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B101" t="str">
+      <x:c r="B102" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C101" t="str">
+      <x:c r="C102" t="str">
         <x:v>占比</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102">
-      <x:c r="A102" s="10" t="str">
-        <x:v>婚姻/情感</x:v>
-      </x:c>
-      <x:c r="B102" s="11" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C102" s="11" t="str">
-        <x:v>19.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="10" t="str">
-        <x:v>家庭伦理/萌宝</x:v>
+        <x:v>婚姻/情感</x:v>
       </x:c>
       <x:c r="B103" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C103" s="11" t="str">
-        <x:v>15.0%</x:v>
+        <x:v>19.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>家庭伦理/萌宝</x:v>
       </x:c>
       <x:c r="B104" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C104" s="11" t="str">
-        <x:v>10.0%</x:v>
+        <x:v>15.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="B105" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C105" s="11" t="str">
-        <x:v>9.0%</x:v>
+        <x:v>10.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="10" t="str">
-        <x:v>年代怀旧/种田</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="B106" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C106" s="11" t="str">
-        <x:v>7.0%</x:v>
+        <x:v>9.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="10" t="str">
-        <x:v>现实反转/人性</x:v>
+        <x:v>年代怀旧/种田</x:v>
       </x:c>
       <x:c r="B107" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C107" s="11" t="str">
-        <x:v>6.0%</x:v>
+        <x:v>7.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="10" t="str">
-        <x:v>战神/异能</x:v>
+        <x:v>现实反转/人性</x:v>
       </x:c>
       <x:c r="B108" s="11" t="n">
         <x:v>6</x:v>
@@ -25896,12 +26083,23 @@
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="10" t="str">
+        <x:v>战神/异能</x:v>
+      </x:c>
+      <x:c r="B109" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C109" s="11" t="str">
+        <x:v>6.0%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="10" t="str">
         <x:v>美食治愈</x:v>
       </x:c>
-      <x:c r="B109" s="11" t="n">
+      <x:c r="B110" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C109" s="11" t="str">
+      <x:c r="C110" s="11" t="str">
         <x:v>5.0%</x:v>
       </x:c>
     </x:row>
@@ -25911,10 +26109,10 @@
     <x:mergeCell ref="A7:C7"/>
     <x:mergeCell ref="A14:C14"/>
     <x:mergeCell ref="A27:C27"/>
-    <x:mergeCell ref="A57:C57"/>
-    <x:mergeCell ref="A64:C64"/>
-    <x:mergeCell ref="A82:C82"/>
-    <x:mergeCell ref="A100:C100"/>
+    <x:mergeCell ref="A58:C58"/>
+    <x:mergeCell ref="A65:C65"/>
+    <x:mergeCell ref="A83:C83"/>
+    <x:mergeCell ref="A101:C101"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="Rab71c50e9fbb4c4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="R1a724b153083473b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="R4de89fbccbf34c9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="R37a646a5a3654904"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="5" r:id="R5ba0d384abc24635"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="6" r:id="Rbd8f50047db9459c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="7" r:id="Rf26ee4e56dd3469b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="8" r:id="R352a36f9063047de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="Ref4c6b2facca4e00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="R5db8c344e5d5474c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="R995d3dcd640641ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="Rb07105345451487e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="5" r:id="R243d532f16a249b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="6" r:id="R48be0494a8144f47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="7" r:id="Rf37a162f40464899"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="8" r:id="Rc3fd070dbff34a6f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -819,27 +819,27 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>姜猎娶妻之知青良缘</x:v>
+        <x:v>重生六七：赶山狩猎养全家</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>08-17 09:38</x:v>
+        <x:v>08-25 18:00</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E17" s="10" t="n">
-        <x:v>62</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F17" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G17" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>种田囤货</x:v>
       </x:c>
       <x:c r="H17" s="11" t="str"/>
       <x:c r="I17" s="11" t="str"/>
       <x:c r="J17" s="10" t="str">
-        <x:v>2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-09、2026-09-11、2026-09-12、2026-09-13</x:v>
+        <x:v>2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -847,19 +847,19 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>看透妻子之后</x:v>
+        <x:v>姜猎娶妻之知青良缘</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>08-24 18:02</x:v>
+        <x:v>08-17 09:38</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="E18" s="10" t="n">
-        <x:v>46</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F18" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G18" s="10" t="str">
         <x:v>婚姻情感</x:v>
@@ -867,7 +867,7 @@
       <x:c r="H18" s="11" t="str"/>
       <x:c r="I18" s="11" t="str"/>
       <x:c r="J18" s="10" t="str">
-        <x:v>2026-08-23、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-10、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-09、2026-09-11、2026-09-12、2026-09-13</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -875,27 +875,27 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>重生六七：赶山狩猎养全家</x:v>
+        <x:v>看透妻子之后</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>08-25 18:00</x:v>
+        <x:v>08-24 18:02</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="E19" s="10" t="n">
-        <x:v>108</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F19" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="G19" s="10" t="str">
-        <x:v>种田囤货</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="H19" s="11" t="str"/>
       <x:c r="I19" s="11" t="str"/>
       <x:c r="J19" s="10" t="str">
-        <x:v>2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-08-23、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-10、2026-09-11、2026-09-12</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -937,7 +937,7 @@
         <x:v>08-02 14:08</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E21" s="10" t="n">
         <x:v>122</x:v>
@@ -951,7 +951,7 @@
       <x:c r="H21" s="11" t="str"/>
       <x:c r="I21" s="11" t="str"/>
       <x:c r="J21" s="10" t="str">
-        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -959,27 +959,27 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>山下是绝路，山上是生门</x:v>
+        <x:v>乱世我家顿顿吃肉</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>08-27 07:03</x:v>
+        <x:v>08-15 04:30</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E22" s="10" t="n">
-        <x:v>99</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F22" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G22" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="H22" s="11" t="str"/>
       <x:c r="I22" s="11" t="str"/>
       <x:c r="J22" s="10" t="str">
-        <x:v>2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -987,27 +987,27 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>福宝治愈全世界，家有萌娃岁岁安</x:v>
+        <x:v>山下是绝路，山上是生门</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>08-21 10:00</x:v>
+        <x:v>08-27 07:03</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E23" s="10" t="n">
-        <x:v>169</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F23" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G23" s="10" t="str">
-        <x:v>萌宝治愈</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="H23" s="11" t="str"/>
       <x:c r="I23" s="11" t="str"/>
       <x:c r="J23" s="10" t="str">
-        <x:v>2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-03、2026-09-05、2026-09-06、2026-09-12、2026-09-13</x:v>
+        <x:v>2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1015,27 +1015,27 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>贪念散尽卤香</x:v>
+        <x:v>福宝治愈全世界，家有萌娃岁岁安</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>08-24 08:26</x:v>
+        <x:v>08-21 10:00</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E24" s="10" t="n">
-        <x:v>41</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="F24" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G24" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>萌宝治愈</x:v>
       </x:c>
       <x:c r="H24" s="11" t="str"/>
       <x:c r="I24" s="11" t="str"/>
       <x:c r="J24" s="10" t="str">
-        <x:v>2026-08-23、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-09、2026-09-12</x:v>
+        <x:v>2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-03、2026-09-05、2026-09-06、2026-09-12、2026-09-13</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1043,27 +1043,27 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>重生之从迎娶大小姐开始逆袭</x:v>
+        <x:v>贪念散尽卤香</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>08-23 11:00</x:v>
+        <x:v>08-24 08:26</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E25" s="10" t="n">
-        <x:v>145</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F25" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G25" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="H25" s="11" t="str"/>
       <x:c r="I25" s="11" t="str"/>
       <x:c r="J25" s="10" t="str">
-        <x:v>2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-09、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-08-23、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-09、2026-09-12</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1071,27 +1071,27 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>一瓶水，让我看清亲生女儿</x:v>
+        <x:v>重生之从迎娶大小姐开始逆袭</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
-        <x:v>08-23 10:00</x:v>
+        <x:v>08-23 11:00</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E26" s="10" t="n">
-        <x:v>69</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="F26" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G26" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="H26" s="11" t="str"/>
       <x:c r="I26" s="11" t="str"/>
       <x:c r="J26" s="10" t="str">
-        <x:v>2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09</x:v>
+        <x:v>2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-09、2026-09-11、2026-09-12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1167,10 +1167,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
-        <x:v>泰城错嫁</x:v>
+        <x:v>今晚查寝，别开门</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>09-12 21:10</x:v>
+        <x:v>09-12 23:35</x:v>
       </x:c>
       <x:c r="E2" s="11" t="str"/>
       <x:c r="F2" s="11" t="str"/>
@@ -1181,19 +1181,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I2" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J2" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K2" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L2" s="11" t="str">
-        <x:v>夜草剧场</x:v>
+        <x:v>辣妹漫剧</x:v>
       </x:c>
       <x:c r="M2" s="10" t="str">
-        <x:v>二十世纪三十年代泰国，两姐妹姐妹同日嫁人，丑妹珠珠嫁帅气宋帕，美姐南佩却配憨汉啊光。迎亲途中大象突然发情，两对新人错上婚车、错入洞房。泼辣珠珠遇上憨厚啊光，闹洞房、斗婆婆，从互殴到相守；温柔南佩遇上冷脸宋帕，假装吵架赶走宾客，从陌生到动心。两对夫妻先后离婚，珠珠与啊光携手生子，南佩闯荡成舞台名角，与宋帕久别重逢。错的人成了对的人，两对冤家，各得圆满。</x:v>
+        <x:v>程妍重生回女生宿舍407遇害前二十分钟，笃定深夜“临时查寝”是致命陷阱，不顾室友质疑拼死堵门。四人合力对抗冒充宿管的歹徒，最终揪出泄露学生信息的内鬼。案件告破，四个女孩平安毕业，407一个都没少，再然后就发生了这些事。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1201,13 +1201,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
-        <x:v>回到零四年进军彩铃界</x:v>
+        <x:v>锦书迟</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>2026-09-11</x:v>
+        <x:v>09-12 07:30</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str"/>
       <x:c r="F3" s="11" t="str"/>
@@ -1217,28 +1217,34 @@
       <x:c r="H3" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I3" s="11" t="str"/>
+      <x:c r="I3" s="11" t="n">
+        <x:v>58</x:v>
+      </x:c>
       <x:c r="J3" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K3" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L3" s="11" t="str"/>
-      <x:c r="M3" s="10" t="str"/>
+      <x:c r="L3" s="11" t="str">
+        <x:v>咩咩漫文</x:v>
+      </x:c>
+      <x:c r="M3" s="10" t="str">
+        <x:v>三年前，沈昭昭嫁与永宁侯谢凛，新婚燕尔他便远赴边关。她苦等家书，却不知双向书信早被人暗中截留。她终于心冷离开侯府。三年后，她带着孩子在市井支摊卖画立足，他却循着蛛丝马迹寻来，真相层层揭开，原来他从未负她。</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
-        <x:v>今天开始做裴总</x:v>
+        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>09-12 19:48</x:v>
+        <x:v>09-11 09:00</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str"/>
       <x:c r="F4" s="11" t="str"/>
@@ -1249,19 +1255,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I4" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="J4" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K4" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧 / 家庭伦理</x:v>
       </x:c>
       <x:c r="L4" s="11" t="str">
-        <x:v>严墨墨</x:v>
+        <x:v>阳阳动画</x:v>
       </x:c>
       <x:c r="M4" s="10" t="str">
-        <x:v>裴野低调蛰伏三年，甘愿扮作普通员工，在公司默默沉淀，面对职场非议、旁人轻视从未辩解。年会之上，他惨遭当众开除，相伴多年的婚姻也走向终点，跌入人生低谷。褪去伪装，他不再刻意隐忍，解锁真实身份，告别敷衍度日的过往。一路轻松逆袭，打破所有人的偏见，凭自身实力惊艳全场，开启属于自己的全新人生。</x:v>
+        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1269,13 +1275,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
+        <x:v>七套房产，换来一纸调令</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>09-11 09:00</x:v>
+        <x:v>09-12 08:18</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str"/>
       <x:c r="F5" s="11" t="str"/>
@@ -1286,19 +1292,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I5" s="11" t="n">
-        <x:v>133</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J5" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K5" s="10" t="str">
-        <x:v>年代怀旧 / 家庭伦理</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L5" s="11" t="str">
-        <x:v>阳阳动画</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="M5" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
+        <x:v>公婆将七套房产全数赠予小叔子，长子陈峰看似顺从鼓掌，实则暗中申请援疆调令。面对父母偏心和弟媳挑衅，陈峰携妻林晚隐忍筹备。最终在家庭会议上，他出示双人调令宣告远赴新疆，打破原生家庭剥削链条。经历异地磨砺与除夕和解，一家人终在理解中重建亲情边界，实现各自独立与成长。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1306,13 +1312,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>退婚从抢我车位开始</x:v>
+        <x:v>泰城错嫁</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>2026-09-12</x:v>
+        <x:v>09-12 21:10</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str"/>
       <x:c r="F6" s="11" t="str"/>
@@ -1322,28 +1328,34 @@
       <x:c r="H6" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I6" s="11" t="str"/>
+      <x:c r="I6" s="11" t="n">
+        <x:v>50</x:v>
+      </x:c>
       <x:c r="J6" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K6" s="10" t="str">
-        <x:v>都市职场 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="L6" s="11" t="str"/>
-      <x:c r="M6" s="10" t="str"/>
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="L6" s="11" t="str">
+        <x:v>夜草剧场</x:v>
+      </x:c>
+      <x:c r="M6" s="10" t="str">
+        <x:v>二十世纪三十年代泰国，两姐妹姐妹同日嫁人，丑妹珠珠嫁帅气宋帕，美姐南佩却配憨汉啊光。迎亲途中大象突然发情，两对新人错上婚车、错入洞房。泼辣珠珠遇上憨厚啊光，闹洞房、斗婆婆，从互殴到相守；温柔南佩遇上冷脸宋帕，假装吵架赶走宾客，从陌生到动心。两对夫妻先后离婚，珠珠与啊光携手生子，南佩闯荡成舞台名角，与宋帕久别重逢。错的人成了对的人，两对冤家，各得圆满。</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
-        <x:v>误救高冷校花，她爷爷非要我做孙女婿</x:v>
+        <x:v>我赚上千万跟爸妈说50W，隔天就被找上门</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>2026-09-12</x:v>
+        <x:v>09-13 08:00</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str"/>
       <x:c r="F7" s="11" t="str"/>
@@ -1353,25 +1365,31 @@
       <x:c r="H7" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="str"/>
+      <x:c r="I7" s="11" t="n">
+        <x:v>78</x:v>
+      </x:c>
       <x:c r="J7" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K7" s="10" t="str">
-        <x:v>家庭伦理</x:v>
-      </x:c>
-      <x:c r="L7" s="11" t="str"/>
-      <x:c r="M7" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L7" s="11" t="str">
+        <x:v>至尊爽剧社</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="str">
+        <x:v>三十二岁那年，贺川用六年孤注一掷的钻研，换来了七千六百万的回报。可财富还没捂热，先尝到的却是亲人无度的索取。他谎称只赚五十万，叮嘱保密，却挡不住消息走漏。隔天登门的亲戚不止要借钱买房，更联手外人盗用他的身份资料，试图冒名签约、伪造担保债务。贺川报警取证，警方介入追回大部分资金，涉案者包括部分机构人员均承担了法律责任，这笔帐，能否算清？</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
-        <x:v>装傻下山</x:v>
+        <x:v>退婚从抢我车位开始</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
         <x:v>2026-09-12</x:v>
@@ -1389,7 +1407,7 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="K8" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>都市职场 / 婚姻情感</x:v>
       </x:c>
       <x:c r="L8" s="11" t="str"/>
       <x:c r="M8" s="10" t="str"/>
@@ -1399,13 +1417,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
-        <x:v>七套房产，换来一纸调令</x:v>
+        <x:v>今天开始做裴总</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>09-12 08:18</x:v>
+        <x:v>09-12 19:48</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str"/>
       <x:c r="F9" s="11" t="str"/>
@@ -1416,7 +1434,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I9" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J9" s="10" t="str">
         <x:v>其他</x:v>
@@ -1425,10 +1443,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L9" s="11" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>严墨墨</x:v>
       </x:c>
       <x:c r="M9" s="10" t="str">
-        <x:v>公婆将七套房产全数赠予小叔子，长子陈峰看似顺从鼓掌，实则暗中申请援疆调令。面对父母偏心和弟媳挑衅，陈峰携妻林晚隐忍筹备。最终在家庭会议上，他出示双人调令宣告远赴新疆，打破原生家庭剥削链条。经历异地磨砺与除夕和解，一家人终在理解中重建亲情边界，实现各自独立与成长。</x:v>
+        <x:v>裴野低调蛰伏三年，甘愿扮作普通员工，在公司默默沉淀，面对职场非议、旁人轻视从未辩解。年会之上，他惨遭当众开除，相伴多年的婚姻也走向终点，跌入人生低谷。褪去伪装，他不再刻意隐忍，解锁真实身份，告别敷衍度日的过往。一路轻松逆袭，打破所有人的偏见，凭自身实力惊艳全场，开启属于自己的全新人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1436,13 +1454,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
-        <x:v>我拿下1.2亿订单公司只给3千块</x:v>
+        <x:v>回到零四年进军彩铃界</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>09-11 06:30</x:v>
+        <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str"/>
       <x:c r="F10" s="11" t="str"/>
@@ -1452,34 +1470,28 @@
       <x:c r="H10" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I10" s="11" t="n">
-        <x:v>53</x:v>
-      </x:c>
+      <x:c r="I10" s="11" t="str"/>
       <x:c r="J10" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K10" s="10" t="str">
-        <x:v>都市职场</x:v>
-      </x:c>
-      <x:c r="L10" s="11" t="str">
-        <x:v>呆哥说漫</x:v>
-      </x:c>
-      <x:c r="M10" s="10" t="str">
-        <x:v>连续五年蝉联销售冠军的陈志远，苦跟两年拿下1亿2订单，却只收到3280元提成。公司临时改制，将客户划给副总裁外甥周凯，夺走他的九十六万提成。陈志远离职后，客户因失去真正服务者纷纷暂停合作，公司却倒打一耙，指控他带客并索赔三千万元。董事会调查中，制度、合同、伪造邮件和聊天证据接连浮出水面，周建华的利益输送与甩锅阴谋曝光。陈志远洗清污名，追回提成，也让公司重建公平规则。</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L10" s="11" t="str"/>
+      <x:c r="M10" s="10" t="str"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C11" s="10" t="str">
-        <x:v>穿越七零:月季花开</x:v>
+        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>09-11 22:25</x:v>
+        <x:v>09-13 08:00</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str"/>
       <x:c r="F11" s="11" t="str"/>
@@ -1490,19 +1502,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I11" s="11" t="n">
-        <x:v>219</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J11" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K11" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="L11" s="11" t="str">
-        <x:v>维维动画</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="M11" s="10" t="str">
-        <x:v>女知青白月季意外穿进书中，原主本打算上山打掉腹中孩子。清醒过来的她选择接受命运，不再执念过往的情缘，决定和周野好好过日子。周野看似粗犷，实则重情重义，满心珍视白月季。二人携手扎根乡村，对抗邻里闲言碎语，努力耕耘生活。白月季凭借文笔投稿赚取稿费，周野踏实打拼养家，还迎来双胞胎。在柴米烟火里互相扶持，跨过重重风波，把平凡的农家日子过得滚烫又幸福。</x:v>
+        <x:v>大晋七公主沈令仪，自幼被冷落于听竹宫，沉默藏锋，苟全性命。宫宴之上，太子带回的秦照雪笑盈盈提议将她送去北狄和亲。满殿以为皇帝会点头，他却掷出“废太子”三字。一夜之间，沈令仪被推到台前。北狄求和的急报恰在此时入京——与她方才所言分毫不差。可当她回望母亲遗下的那半卷秘策时，才发现这局棋，早在二十年前就已落子。</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1510,13 +1522,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
-        <x:v>锦书迟</x:v>
+        <x:v>深海之眼：我靠透视海底逆袭</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>09-12 07:30</x:v>
+        <x:v>09-12 08:30</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str"/>
       <x:c r="F12" s="11" t="str"/>
@@ -1527,19 +1539,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I12" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="J12" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K12" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="L12" s="11" t="str">
-        <x:v>咩咩漫文</x:v>
+        <x:v>林八</x:v>
       </x:c>
       <x:c r="M12" s="10" t="str">
-        <x:v>三年前，沈昭昭嫁与永宁侯谢凛，新婚燕尔他便远赴边关。她苦等家书，却不知双向书信早被人暗中截留。她终于心冷离开侯府。三年后，她带着孩子在市井支摊卖画立足，他却循着蛛丝马迹寻来，真相层层揭开，原来他从未负她。</x:v>
+        <x:v>林凡的穷小子，在渔村替人打了三年工，老板克扣工钱，一船三万二的货，到他手里只剩两百块。他本来认命了。直到有一天，他意外发现自己能看透海底，鱼在哪里、暗礁在哪里、沉船在哪里，一清二楚。从此他开挂了。从破舢板换到小木船，从小木船换到八十米大铁船，几百斤的石斑鱼、两千斤的蓝鳍金枪鱼王，一条就卖一百万。就在人生翻盘时，一块海底捞起的铜牌，揭开了父亲十七年前失踪的真相。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1547,13 +1559,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B13" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
-        <x:v>当初闹着算清账目，我答应后他退休金见了底</x:v>
+        <x:v>穿越七零:月季花开</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
-        <x:v>09-12 08:00</x:v>
+        <x:v>09-11 22:25</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str"/>
       <x:c r="F13" s="11" t="str"/>
@@ -1564,19 +1576,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I13" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="J13" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K13" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="L13" s="11" t="str">
-        <x:v>小狐狸剧场</x:v>
+        <x:v>维维动画</x:v>
       </x:c>
       <x:c r="M13" s="10" t="str">
-        <x:v>许宁嫁入孟家四年，包揽房贷、学费与婆婆医药费，却从未被看见。饭桌上，公公孟栋泽手握六千八退休金，当众提出分家。无人反对，许宁也坦然应允。所有人都以为她是被供养的闲人，直到分家后，她默默停掉所有开支。断水断电、房贷逾期、催缴单纷至沓来，这个家一夜停摆。当真相浮出水面，他们才惊觉，被轻视的儿媳才是唯一的支柱。</x:v>
+        <x:v>女知青白月季意外穿进书中，原主本打算上山打掉腹中孩子。清醒过来的她选择接受命运，不再执念过往的情缘，决定和周野好好过日子。周野看似粗犷，实则重情重义，满心珍视白月季。二人携手扎根乡村，对抗邻里闲言碎语，努力耕耘生活。白月季凭借文笔投稿赚取稿费，周野踏实打拼养家，还迎来双胞胎。在柴米烟火里互相扶持，跨过重重风波，把平凡的农家日子过得滚烫又幸福。</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1584,13 +1596,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B14" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
-        <x:v>恰逢其时的婚约</x:v>
+        <x:v>重生山火前，我舍祖宅护全家</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>09-11 13:35</x:v>
+        <x:v>09-12 16:06</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str"/>
       <x:c r="F14" s="11" t="str"/>
@@ -1601,19 +1613,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I14" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J14" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K14" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L14" s="11" t="str">
-        <x:v>听闻木东</x:v>
+        <x:v>千鹤动漫</x:v>
       </x:c>
       <x:c r="M14" s="10" t="str">
-        <x:v>从乡下被接回豪门的柳晨，对继承家业毫无兴趣，只想靠自己的本事踏实赚钱。一次家族联姻，让他与外表强势、内心孤独的顾晴岚成为“合同夫妻”。从互相试探到并肩面对误解与困境，柳晨始终守住底线、重情重义，用责任与真诚赢得尊重，也让顾晴岚重新相信感情。两个原本各有所求的人，在相互扶持中收获成长，也明白了财富有价，真心、担当与尊严无价。</x:v>
+        <x:v>顾长河带着前世山火中痛失全家的记忆重生归来，得知三日后西岭大火将再次席卷村庄，他不顾众人质疑，卖掉祖宅，带着妻子母亲和儿子搬上白石坡，储水备粮清出防火带，只为改写一家人的命运，当烈火真正逼近，所有人终于明白，他舍掉的只是房子，拼命守住的才是真正的家。</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1621,13 +1633,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B15" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
-        <x:v>重生山火前，我舍祖宅护全家</x:v>
+        <x:v>装傻下山</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
-        <x:v>09-12 16:06</x:v>
+        <x:v>2026-09-12</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str"/>
       <x:c r="F15" s="11" t="str"/>
@@ -1637,34 +1649,28 @@
       <x:c r="H15" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I15" s="11" t="n">
-        <x:v>89</x:v>
-      </x:c>
+      <x:c r="I15" s="11" t="str"/>
       <x:c r="J15" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K15" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L15" s="11" t="str">
-        <x:v>千鹤动漫</x:v>
-      </x:c>
-      <x:c r="M15" s="10" t="str">
-        <x:v>顾长河带着前世山火中痛失全家的记忆重生归来，得知三日后西岭大火将再次席卷村庄，他不顾众人质疑，卖掉祖宅，带着妻子母亲和儿子搬上白石坡，储水备粮清出防火带，只为改写一家人的命运，当烈火真正逼近，所有人终于明白，他舍掉的只是房子，拼命守住的才是真正的家。</x:v>
-      </x:c>
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="L15" s="11" t="str"/>
+      <x:c r="M15" s="10" t="str"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C16" s="10" t="str">
-        <x:v>深宫锁狐：陛下您的皇儿是妖</x:v>
+        <x:v>误救高冷校花，她爷爷非要我做孙女婿</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
-        <x:v>09-12 19:00</x:v>
+        <x:v>2026-09-12</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str"/>
       <x:c r="F16" s="11" t="str"/>
@@ -1674,34 +1680,28 @@
       <x:c r="H16" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I16" s="11" t="n">
-        <x:v>100</x:v>
-      </x:c>
+      <x:c r="I16" s="11" t="str"/>
       <x:c r="J16" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K16" s="10" t="str">
-        <x:v>古装宫廷</x:v>
-      </x:c>
-      <x:c r="L16" s="11" t="str">
-        <x:v>观月剧场</x:v>
-      </x:c>
-      <x:c r="M16" s="10" t="str">
-        <x:v>皇子一到夜里就变白狐，苏晚禾提心吊胆藏了五年。直到皇帝破门而入，头顶竟也冒出狐耳！她这才知儿子是天狐血脉。贤妃带兵逼宫要诛妖，她反手布局，当众撕开真相，掀翻后宫。可最后她发现自己也是月狐之后，全家都是狐狸！</x:v>
-      </x:c>
+        <x:v>家庭伦理</x:v>
+      </x:c>
+      <x:c r="L16" s="11" t="str"/>
+      <x:c r="M16" s="10" t="str"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C17" s="10" t="str">
-        <x:v>我的眼睛变成了透视神瞳</x:v>
+        <x:v>反派拿捏！</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
-        <x:v>09-11 11:00</x:v>
+        <x:v>2026-09-13</x:v>
       </x:c>
       <x:c r="E17" s="11" t="str"/>
       <x:c r="F17" s="11" t="str"/>
@@ -1711,34 +1711,28 @@
       <x:c r="H17" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I17" s="11" t="n">
-        <x:v>90</x:v>
-      </x:c>
+      <x:c r="I17" s="11" t="str"/>
       <x:c r="J17" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K17" s="10" t="str">
-        <x:v>战神异能</x:v>
-      </x:c>
-      <x:c r="L17" s="11" t="str">
-        <x:v>奇迹漫剧</x:v>
-      </x:c>
-      <x:c r="M17" s="10" t="str">
-        <x:v>罗川本是四处奔波的废品回收从业者，日子过得窘迫潦倒。一次意外，他觉醒透视异能，双眼能够看穿物件内里，辨明真伪与隐藏价值。凭借这份神异能力，他在旧货市场、废品堆里频频捡漏，屡屡发现被人忽视的珍宝。从被旁人轻视的底层小人物，他一步步积累财富与阅历，在古玩鉴宝圈崭露头角，破除无数圈套骗局，逆袭成受人敬重的顶尖鉴宝高手，改写了自己的平凡人生。</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L17" s="11" t="str"/>
+      <x:c r="M17" s="10" t="str"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C18" s="10" t="str">
-        <x:v>敢抢我的车位</x:v>
+        <x:v>活宝老爹再赴青春，竟与女儿同上大学</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>09-11 18:00</x:v>
+        <x:v>09-13 00:08</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str"/>
       <x:c r="F18" s="11" t="str"/>
@@ -1749,19 +1743,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I18" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J18" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K18" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="L18" s="11" t="str">
-        <x:v>石爷剧场</x:v>
+        <x:v>长风剧场</x:v>
       </x:c>
       <x:c r="M18" s="10" t="str">
-        <x:v>蒋依依低调返乡履行婚约，却在王氏集团门口因停车问题，与柳如烟和未婚夫王霸产生误会。随着双方接触加深，婚约背后的分歧也逐渐显现。面对王霸前后不同的态度，蒋依依选择坚持自己的原则，果断结束这段并不合适的关系。与此同时，一场意外车辆纠纷也进入正式处理程序。原本普通的一次停车风波，让几个人重新认识彼此，也让蒋依依更加坚定了自己的选择。</x:v>
+        <x:v>45岁的白烨意外激活成长系统。只要亲身体验年轻人的日常，就能重拾青春活力，还能收获丰厚奖励。为完成系统任务，他报名成人高考，顺利考入大学，竟和女儿成了同校同学。重返校园的白烨，一边认真完成任务感受青春，一边在校园里开启一段充满趣味的全新人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1769,7 +1763,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C19" s="10" t="str">
         <x:v>锚定诸天之天灾启世</x:v>
@@ -1780,10 +1774,10 @@
       <x:c r="E19" s="11" t="str"/>
       <x:c r="F19" s="11" t="str"/>
       <x:c r="G19" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H19" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I19" s="11" t="n">
         <x:v>120</x:v>
@@ -1806,36 +1800,37 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C20" s="10" t="str">
-        <x:v>活宝老爹再赴青春，竟与女儿同上大学</x:v>
+        <x:v>青牛引泉来</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>09-13 00:08</x:v>
+        <x:v>09-11 15:20</x:v>
       </x:c>
       <x:c r="E20" s="11" t="str"/>
       <x:c r="F20" s="11" t="str"/>
       <x:c r="G20" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H20" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I20" s="11" t="n">
-        <x:v>140</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="J20" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K20" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L20" s="11" t="str">
-        <x:v>长风剧场</x:v>
+        <x:v>车仔漫</x:v>
       </x:c>
       <x:c r="M20" s="10" t="str">
-        <x:v>45岁的白烨意外激活成长系统。只要亲身体验年轻人的日常，就能重拾青春活力，还能收获丰厚奖励。为完成系统任务，他报名成人高考，顺利考入大学，竟和女儿成了同校同学。重返校园的白烨，一边认真完成任务感受青春，一边在校园里开启一段充满趣味的全新人生。</x:v>
+        <x:v>大旱之年，贫苦庄稼汉石满仓为宽慰盼他成家的母亲，扎了个稻草媳妇，谁料草人竟化作姑娘阿禾。原来阿禾是有灵性的青牛，十年前大旱濒死时被石满仓用豆秸和水救下，此番借稻草人身躯前来报恩。
+阿禾感知到村井即将枯竭，带领众人找到被封堵的牛眠岭古泉。靠卖自家井水牟利的马有财因利益受损，百般阻挠，甚至污染泉水、堵塞闸口。</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1843,34 +1838,36 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>87</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C21" s="10" t="str">
-        <x:v>别咬，你太大只啦</x:v>
+        <x:v>我的眼睛变成了透视神瞳</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
-        <x:v>09-13 00:06</x:v>
+        <x:v>09-11 11:00</x:v>
       </x:c>
       <x:c r="E21" s="11" t="str"/>
       <x:c r="F21" s="11" t="str"/>
       <x:c r="G21" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H21" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I21" s="11" t="n">
-        <x:v>180</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="J21" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K21" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L21" s="11" t="str"/>
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="L21" s="11" t="str">
+        <x:v>奇迹漫剧</x:v>
+      </x:c>
       <x:c r="M21" s="10" t="str">
-        <x:v>邵糯原本是一个生活拮据的少女，转生成动物后反而很容易从吃饱、睡好、有人陪伴中获得幸福感。第一世，穿成萨摩耶邂逅强大的银灰狼凯尔，历经族群纷争、生老病死，在风雪之中走完一生。第二世，她变成一只布偶猫，误入山野遇见巨型亚欧猞猁凯尔，在危机四伏的松林磨合羁绊，对抗狼群，晚年被救助站收留。两世，不同物种，却始终拥有命中注定的双向羁绊，全程还有野外直播实时见证他们的故事。</x:v>
+        <x:v>罗川本是四处奔波的废品回收从业者，日子过得窘迫潦倒。一次意外，他觉醒透视异能，双眼能够看穿物件内里，辨明真伪与隐藏价值。凭借这份神异能力，他在旧货市场、废品堆里频频捡漏，屡屡发现被人忽视的珍宝。从被旁人轻视的底层小人物，他一步步积累财富与阅历，在古玩鉴宝圈崭露头角，破除无数圈套骗局，逆袭成受人敬重的顶尖鉴宝高手，改写了自己的平凡人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1878,36 +1875,36 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>99</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C22" s="10" t="str">
-        <x:v>废柴大师兄：师妹修炼我无敌</x:v>
+        <x:v>深宫锁狐：陛下您的皇儿是妖</x:v>
       </x:c>
       <x:c r="D22" s="11" t="str">
-        <x:v>09-11 11:20</x:v>
+        <x:v>09-12 19:00</x:v>
       </x:c>
       <x:c r="E22" s="11" t="str"/>
       <x:c r="F22" s="11" t="str"/>
       <x:c r="G22" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H22" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I22" s="11" t="n">
-        <x:v>158</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J22" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K22" s="10" t="str">
-        <x:v>逆袭打脸 / 战神异能</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="L22" s="11" t="str">
-        <x:v>在下二蛋</x:v>
+        <x:v>观月剧场</x:v>
       </x:c>
       <x:c r="M22" s="10" t="str">
-        <x:v>谁能想到终日摆烂的废柴大师兄，真实境界竟是大帝！叶玄迎来女帝转世的师妹柳如烟，顺势激活特殊系统，永久比师妹高出十个大境界，直接解锁大帝实力。他继续伪装成酒鬼混在宗门，下山途中轻松碾压前来夺舍的黑魔老怪。得知桃花镇百姓被恶虎山匪徒掳走，叶玄火速前往救人，以绝对实力击溃一众匪寇。匪首铁虎慌忙跪地求饶。可叶玄杀意已决，磅礴力量正在汇聚，铁虎能否活过这一劫？</x:v>
+        <x:v>皇子一到夜里就变白狐，苏晚禾提心吊胆藏了五年。直到皇帝破门而入，头顶竟也冒出狐耳！她这才知儿子是天狐血脉。贤妃带兵逼宫要诛妖，她反手布局，当众撕开真相，掀翻后宫。可最后她发现自己也是月狐之后，全家都是狐狸！</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1915,13 +1912,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C23" s="10" t="str">
-        <x:v>破麻袋里的亿万人生</x:v>
+        <x:v>我的师兄全是修仙界大佬</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
-        <x:v>09-11 15:30</x:v>
+        <x:v>09-11 18:16</x:v>
       </x:c>
       <x:c r="E23" s="11" t="str"/>
       <x:c r="F23" s="11" t="str"/>
@@ -1929,22 +1926,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H23" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I23" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="J23" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K23" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="L23" s="11" t="str">
-        <x:v>小博漫剧社</x:v>
+        <x:v>大公鸡剧场</x:v>
       </x:c>
       <x:c r="M23" s="10" t="str">
-        <x:v>失踪二十年的方小树因幼年被人贩子打伤，长期神志不清、沿街流浪。一次跳河救下海城富商顾振山的孙子，他得到七百万元谢礼，也意外回到方家。亲大哥方志强、二姐方玉梅只惦记他的钱，三姐方秀兰却始终护着他。受伤恢复记忆后，方小树选择继续装傻看清人心，并凭眼光投资远芯科技，从乞丐逆袭成身家过亿的股东。沈家千金沈清月因十八年前的救命之恩找到他，从报恩走向真爱。最终方小树认祖归宗、清算恶亲与幕后黑手</x:v>
+        <x:v>六岁的女主奉师父顾青崖之命下山历练，寻找五位失散数百年的师兄。她天生神力，把九品丹药当糖豆吃，背着重剑闯修仙界。本以为师兄们在外落魄难归，却发现大师兄是正道第一人九天仙尊，二师兄是统御九幽的幽冥帝君，余下三位也皆是绝世大佬。小奶娃一路闯荡，把隐世多年的师兄们挨个喊回了家。</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1952,13 +1949,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C24" s="10" t="str">
-        <x:v>我的师兄全是修仙界大佬</x:v>
+        <x:v>当初闹着算清账目，我答应后他退休金见了底</x:v>
       </x:c>
       <x:c r="D24" s="11" t="str">
-        <x:v>09-11 18:16</x:v>
+        <x:v>09-12 08:00</x:v>
       </x:c>
       <x:c r="E24" s="11" t="str"/>
       <x:c r="F24" s="11" t="str"/>
@@ -1966,22 +1963,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H24" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I24" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J24" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K24" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="L24" s="11" t="str">
-        <x:v>大公鸡剧场</x:v>
+        <x:v>小狐狸剧场</x:v>
       </x:c>
       <x:c r="M24" s="10" t="str">
-        <x:v>六岁的女主奉师父顾青崖之命下山历练，寻找五位失散数百年的师兄。她天生神力，把九品丹药当糖豆吃，背着重剑闯修仙界。本以为师兄们在外落魄难归，却发现大师兄是正道第一人九天仙尊，二师兄是统御九幽的幽冥帝君，余下三位也皆是绝世大佬。小奶娃一路闯荡，把隐世多年的师兄们挨个喊回了家。</x:v>
+        <x:v>许宁嫁入孟家四年，包揽房贷、学费与婆婆医药费，却从未被看见。饭桌上，公公孟栋泽手握六千八退休金，当众提出分家。无人反对，许宁也坦然应允。所有人都以为她是被供养的闲人，直到分家后，她默默停掉所有开支。断水断电、房贷逾期、催缴单纷至沓来，这个家一夜停摆。当真相浮出水面，他们才惊觉，被轻视的儿媳才是唯一的支柱。</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1989,13 +1986,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C25" s="10" t="str">
-        <x:v>今晚查寝，别开门</x:v>
+        <x:v>一张废票毁了她</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
-        <x:v>09-12 23:35</x:v>
+        <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="E25" s="11" t="str"/>
       <x:c r="F25" s="11" t="str"/>
@@ -2005,34 +2002,28 @@
       <x:c r="H25" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I25" s="11" t="n">
-        <x:v>40</x:v>
-      </x:c>
+      <x:c r="I25" s="11" t="str"/>
       <x:c r="J25" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K25" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L25" s="11" t="str">
-        <x:v>辣妹漫剧</x:v>
-      </x:c>
-      <x:c r="M25" s="10" t="str">
-        <x:v>程妍重生回女生宿舍407遇害前二十分钟，笃定深夜“临时查寝”是致命陷阱，不顾室友质疑拼死堵门。四人合力对抗冒充宿管的歹徒，最终揪出泄露学生信息的内鬼。案件告破，四个女孩平安毕业，407一个都没少，再然后就发生了这些事。</x:v>
-      </x:c>
+      <x:c r="L25" s="11" t="str"/>
+      <x:c r="M25" s="10" t="str"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B26" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C26" s="10" t="str">
-        <x:v>我赚上千万跟爸妈说50W，隔天就被找上门</x:v>
+        <x:v>甜宝来了：空间萌宝两岁半带流放全家逆袭</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
-        <x:v>09-13 08:00</x:v>
+        <x:v>09-11 18:26</x:v>
       </x:c>
       <x:c r="E26" s="11" t="str"/>
       <x:c r="F26" s="11" t="str"/>
@@ -2040,22 +2031,22 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H26" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I26" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="J26" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K26" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>萌宝治愈 / 美食治愈 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="L26" s="11" t="str">
-        <x:v>至尊爽剧社</x:v>
+        <x:v>喵喵看漫</x:v>
       </x:c>
       <x:c r="M26" s="10" t="str">
-        <x:v>三十二岁那年，贺川用六年孤注一掷的钻研，换来了七千六百万的回报。可财富还没捂热，先尝到的却是亲人无度的索取。他谎称只赚五十万，叮嘱保密，却挡不住消息走漏。隔天登门的亲戚不止要借钱买房，更联手外人盗用他的身份资料，试图冒名签约、伪造担保债务。贺川报警取证，警方介入追回大部分资金，涉案者包括部分机构人员均承担了法律责任，这笔帐，能否算清？</x:v>
+        <x:v>两岁的苦宝自幼在乡下钱家受尽苛待，到两岁时，失散的太守府叶家亲人终于寻来，将她接回身边，疼她的姥姥还将她改名为甜宝。本以为终于拥有温暖的家，但叶家却蒙冤获罪，举家流放荒疆。小小甜宝身怀奇妙能力，能和小鸟沟通，眼泪还可以疗伤。在荒凉的流放地，她用自己的方式守护姥姥、舅父与兄长，给这片土地带来粮种和希望，一家人彼此扶持，直面磨难，在荒芜之地重新闯出一片天。</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -2063,67 +2054,73 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B27" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C27" s="10" t="str">
-        <x:v>一张废票毁了她</x:v>
+        <x:v>河箱送福来</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
-        <x:v>2026-09-11</x:v>
+        <x:v>09-13 11:00</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F27" s="11" t="str">
-        <x:v>↑62位</x:v>
+        <x:v>↑31位</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str"/>
       <x:c r="H27" s="11" t="str"/>
-      <x:c r="I27" s="11" t="str"/>
+      <x:c r="I27" s="11" t="n">
+        <x:v>64</x:v>
+      </x:c>
       <x:c r="J27" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K27" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L27" s="11" t="str"/>
-      <x:c r="M27" s="10" t="str"/>
+      <x:c r="L27" s="11" t="str">
+        <x:v>灵心讲故事</x:v>
+      </x:c>
+      <x:c r="M27" s="10" t="str">
+        <x:v>张家老两口从河中救回一只木箱，收养了箱中受伤的福生。福生长大后修桥开田，引水惠及乡亲，成家立业。二老相继离世后，山洪威胁村庄，福生为救乡亲舍命撑住巨石，最终重伤落水，下落不明。秀娥守着小院苦等多年，直到熟悉的声音再次响起。</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B28" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C28" s="10" t="str">
-        <x:v>我拿下1.2亿订单公司只给3千块</x:v>
+        <x:v>重生山火前，我舍祖宅护全家</x:v>
       </x:c>
       <x:c r="D28" s="11" t="str">
-        <x:v>09-11 06:30</x:v>
+        <x:v>09-12 16:06</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F28" s="11" t="str">
-        <x:v>↑39位</x:v>
+        <x:v>↑20位</x:v>
       </x:c>
       <x:c r="G28" s="11" t="str"/>
       <x:c r="H28" s="11" t="str"/>
       <x:c r="I28" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J28" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K28" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L28" s="11" t="str">
-        <x:v>呆哥说漫</x:v>
+        <x:v>千鹤动漫</x:v>
       </x:c>
       <x:c r="M28" s="10" t="str">
-        <x:v>连续五年蝉联销售冠军的陈志远，苦跟两年拿下1亿2订单，却只收到3280元提成。公司临时改制，将客户划给副总裁外甥周凯，夺走他的九十六万提成。陈志远离职后，客户因失去真正服务者纷纷暂停合作，公司却倒打一耙，指控他带客并索赔三千万元。董事会调查中，制度、合同、伪造邮件和聊天证据接连浮出水面，周建华的利益输送与甩锅阴谋曝光。陈志远洗清污名，追回提成，也让公司重建公平规则。</x:v>
+        <x:v>顾长河带着前世山火中痛失全家的记忆重生归来，得知三日后西岭大火将再次席卷村庄，他不顾众人质疑，卖掉祖宅，带着妻子母亲和儿子搬上白石坡，储水备粮清出防火带，只为改写一家人的命运，当烈火真正逼近，所有人终于明白，他舍掉的只是房子，拼命守住的才是真正的家。</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -2131,36 +2128,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B29" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C29" s="10" t="str">
-        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
+        <x:v>锚定诸天之天灾启世</x:v>
       </x:c>
       <x:c r="D29" s="11" t="str">
-        <x:v>09-13 08:00</x:v>
+        <x:v>09-12 15:37</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F29" s="11" t="str">
-        <x:v>↑10位</x:v>
+        <x:v>↑18位</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str"/>
       <x:c r="H29" s="11" t="str"/>
       <x:c r="I29" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J29" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K29" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L29" s="11" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>葡萄瓜瓜</x:v>
       </x:c>
       <x:c r="M29" s="10" t="str">
-        <x:v>大晋七公主沈令仪，自幼被冷落于听竹宫，沉默藏锋，苟全性命。宫宴之上，太子带回的秦照雪笑盈盈提议将她送去北狄和亲。满殿以为皇帝会点头，他却掷出“废太子”三字。一夜之间，沈令仪被推到台前。北狄求和的急报恰在此时入京——与她方才所言分毫不差。可当她回望母亲遗下的那半卷秘策时，才发现这局棋，早在二十年前就已落子。</x:v>
+        <x:v>外卖员叶锋意外遭遇意外，机缘巧合中断穿越，成为唯一留守故乡的穿越者，解锁专属系统，连通诸天万界的顶尖穿越者聊天群，群内一众万界至尊大佬，纷纷拜托他代为照看故乡的亲友，偶然展露的过人学识，让他被业内顶尖学者赏识，意外踏入顶级科研圈层，开启平凡生活里的传奇逆袭之路。</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -2168,36 +2165,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B30" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C30" s="10" t="str">
-        <x:v>深海之眼：我靠透视海底逆袭</x:v>
+        <x:v>甜宝来了：空间萌宝两岁半带流放全家逆袭</x:v>
       </x:c>
       <x:c r="D30" s="11" t="str">
-        <x:v>09-12 08:30</x:v>
+        <x:v>09-11 18:26</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>35</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F30" s="11" t="str">
-        <x:v>↑9位</x:v>
+        <x:v>↑5位</x:v>
       </x:c>
       <x:c r="G30" s="11" t="str"/>
       <x:c r="H30" s="11" t="str"/>
       <x:c r="I30" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="J30" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K30" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>萌宝治愈 / 美食治愈 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="L30" s="11" t="str">
-        <x:v>林八</x:v>
+        <x:v>喵喵看漫</x:v>
       </x:c>
       <x:c r="M30" s="10" t="str">
-        <x:v>林凡的穷小子，在渔村替人打了三年工，老板克扣工钱，一船三万二的货，到他手里只剩两百块。他本来认命了。直到有一天，他意外发现自己能看透海底，鱼在哪里、暗礁在哪里、沉船在哪里，一清二楚。从此他开挂了。从破舢板换到小木船，从小木船换到八十米大铁船，几百斤的石斑鱼、两千斤的蓝鳍金枪鱼王，一条就卖一百万。就在人生翻盘时，一块海底捞起的铜牌，揭开了父亲十七年前失踪的真相。</x:v>
+        <x:v>两岁的苦宝自幼在乡下钱家受尽苛待，到两岁时，失散的太守府叶家亲人终于寻来，将她接回身边，疼她的姥姥还将她改名为甜宝。本以为终于拥有温暖的家，但叶家却蒙冤获罪，举家流放荒疆。小小甜宝身怀奇妙能力，能和小鸟沟通，眼泪还可以疗伤。在荒凉的流放地，她用自己的方式守护姥姥、舅父与兄长，给这片土地带来粮种和希望，一家人彼此扶持，直面磨难，在荒芜之地重新闯出一片天。</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -2205,92 +2202,92 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B31" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C31" s="10" t="str">
-        <x:v>垃圾桶里捡到爹</x:v>
+        <x:v>七套房产，换来一纸调令</x:v>
       </x:c>
       <x:c r="D31" s="11" t="str">
-        <x:v>2026-09-12</x:v>
+        <x:v>09-12 08:18</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F31" s="11" t="str">
-        <x:v>↑8位</x:v>
+        <x:v>↑4位</x:v>
       </x:c>
       <x:c r="G31" s="11" t="str"/>
       <x:c r="H31" s="11" t="str"/>
-      <x:c r="I31" s="11" t="str"/>
+      <x:c r="I31" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
       <x:c r="J31" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K31" s="10" t="str">
-        <x:v>家庭伦理</x:v>
-      </x:c>
-      <x:c r="L31" s="11" t="str"/>
-      <x:c r="M31" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L31" s="11" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="M31" s="10" t="str">
+        <x:v>公婆将七套房产全数赠予小叔子，长子陈峰看似顺从鼓掌，实则暗中申请援疆调令。面对父母偏心和弟媳挑衅，陈峰携妻林晚隐忍筹备。最终在家庭会议上，他出示双人调令宣告远赴新疆，打破原生家庭剥削链条。经历异地磨砺与除夕和解，一家人终在理解中重建亲情边界，实现各自独立与成长。</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B32" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C32" s="10" t="str">
-        <x:v>今晚查寝，别开门</x:v>
+        <x:v>小妹初长成</x:v>
       </x:c>
       <x:c r="D32" s="11" t="str">
-        <x:v>09-12 23:35</x:v>
+        <x:v>2026-09-13</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F32" s="11" t="str">
-        <x:v>↑7位</x:v>
+        <x:v>↑4位</x:v>
       </x:c>
       <x:c r="G32" s="11" t="str"/>
       <x:c r="H32" s="11" t="str"/>
-      <x:c r="I32" s="11" t="n">
-        <x:v>40</x:v>
-      </x:c>
+      <x:c r="I32" s="11" t="str"/>
       <x:c r="J32" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K32" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L32" s="11" t="str">
-        <x:v>辣妹漫剧</x:v>
-      </x:c>
-      <x:c r="M32" s="10" t="str">
-        <x:v>程妍重生回女生宿舍407遇害前二十分钟，笃定深夜“临时查寝”是致命陷阱，不顾室友质疑拼死堵门。四人合力对抗冒充宿管的歹徒，最终揪出泄露学生信息的内鬼。案件告破，四个女孩平安毕业，407一个都没少，再然后就发生了这些事。</x:v>
-      </x:c>
+      <x:c r="L32" s="11" t="str"/>
+      <x:c r="M32" s="10" t="str"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B33" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C33" s="10" t="str">
-        <x:v>我的手艺价值千万</x:v>
+        <x:v>今天开始做裴总</x:v>
       </x:c>
       <x:c r="D33" s="11" t="str">
-        <x:v>09-11 18:30</x:v>
+        <x:v>09-12 19:48</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F33" s="11" t="str">
-        <x:v>↑7位</x:v>
+        <x:v>↑4位</x:v>
       </x:c>
       <x:c r="G33" s="11" t="str"/>
       <x:c r="H33" s="11" t="str"/>
       <x:c r="I33" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J33" s="10" t="str">
         <x:v>其他</x:v>
@@ -2299,10 +2296,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L33" s="11" t="str">
-        <x:v>幻山漫剧</x:v>
+        <x:v>严墨墨</x:v>
       </x:c>
       <x:c r="M33" s="10" t="str">
-        <x:v>大席师傅周长河在堂哥周富贵的酒楼干了二十年，凭一手好厨艺撑起招牌，却从未拿到承诺的分红，还因吃一口饭被当众羞辱。心寒之下，他带着伙计转身离开，与濒临倒闭的老赵家宴合作，从六十八桌喜宴重新起步。面对周富贵的使坏打压，周长河靠真材实料、诚信和本事一次次翻盘，最终让破店红火起来，也让轻视他的人尝到苦果。</x:v>
+        <x:v>裴野低调蛰伏三年，甘愿扮作普通员工，在公司默默沉淀，面对职场非议、旁人轻视从未辩解。年会之上，他惨遭当众开除，相伴多年的婚姻也走向终点，跌入人生低谷。褪去伪装，他不再刻意隐忍，解锁真实身份，告别敷衍度日的过往。一路轻松逆袭，打破所有人的偏见，凭自身实力惊艳全场，开启属于自己的全新人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -2310,111 +2307,98 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B34" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C34" s="10" t="str">
-        <x:v>破麻袋里的亿万人生</x:v>
+        <x:v>一张废票毁了她</x:v>
       </x:c>
       <x:c r="D34" s="11" t="str">
-        <x:v>09-11 15:30</x:v>
+        <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
-        <x:v>87</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F34" s="11" t="str">
-        <x:v>↑7位</x:v>
+        <x:v>↑3位</x:v>
       </x:c>
       <x:c r="G34" s="11" t="str"/>
       <x:c r="H34" s="11" t="str"/>
-      <x:c r="I34" s="11" t="n">
-        <x:v>65</x:v>
-      </x:c>
+      <x:c r="I34" s="11" t="str"/>
       <x:c r="J34" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K34" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L34" s="11" t="str">
-        <x:v>小博漫剧社</x:v>
-      </x:c>
-      <x:c r="M34" s="10" t="str">
-        <x:v>失踪二十年的方小树因幼年被人贩子打伤，长期神志不清、沿街流浪。一次跳河救下海城富商顾振山的孙子，他得到七百万元谢礼，也意外回到方家。亲大哥方志强、二姐方玉梅只惦记他的钱，三姐方秀兰却始终护着他。受伤恢复记忆后，方小树选择继续装傻看清人心，并凭眼光投资远芯科技，从乞丐逆袭成身家过亿的股东。沈家千金沈清月因十八年前的救命之恩找到他，从报恩走向真爱。最终方小树认祖归宗、清算恶亲与幕后黑手</x:v>
-      </x:c>
+      <x:c r="L34" s="11" t="str"/>
+      <x:c r="M34" s="10" t="str"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B35" s="11" t="n">
-        <x:v>92</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C35" s="10" t="str">
-        <x:v>甜宝来了：空间萌宝两岁半带流放全家逆袭</x:v>
+        <x:v>退婚从抢我车位开始</x:v>
       </x:c>
       <x:c r="D35" s="11" t="str">
-        <x:v>09-11 18:26</x:v>
+        <x:v>2026-09-12</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
-        <x:v>99</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F35" s="11" t="str">
-        <x:v>↑7位</x:v>
+        <x:v>↑3位</x:v>
       </x:c>
       <x:c r="G35" s="11" t="str"/>
       <x:c r="H35" s="11" t="str"/>
-      <x:c r="I35" s="11" t="n">
-        <x:v>162</x:v>
-      </x:c>
+      <x:c r="I35" s="11" t="str"/>
       <x:c r="J35" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K35" s="10" t="str">
-        <x:v>萌宝治愈 / 美食治愈 / 逆袭打脸</x:v>
-      </x:c>
-      <x:c r="L35" s="11" t="str">
-        <x:v>喵喵看漫</x:v>
-      </x:c>
-      <x:c r="M35" s="10" t="str">
-        <x:v>两岁的苦宝自幼在乡下钱家受尽苛待，到两岁时，失散的太守府叶家亲人终于寻来，将她接回身边，疼她的姥姥还将她改名为甜宝。本以为终于拥有温暖的家，但叶家却蒙冤获罪，举家流放荒疆。小小甜宝身怀奇妙能力，能和小鸟沟通，眼泪还可以疗伤。在荒凉的流放地，她用自己的方式守护姥姥、舅父与兄长，给这片土地带来粮种和希望，一家人彼此扶持，直面磨难，在荒芜之地重新闯出一片天。</x:v>
-      </x:c>
+        <x:v>都市职场 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="L35" s="11" t="str"/>
+      <x:c r="M35" s="10" t="str"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B36" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C36" s="10" t="str">
-        <x:v>青牛引泉来</x:v>
+        <x:v>活宝老爹再赴青春，竟与女儿同上大学</x:v>
       </x:c>
       <x:c r="D36" s="11" t="str">
-        <x:v>09-11 15:20</x:v>
+        <x:v>09-13 00:08</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F36" s="11" t="str">
-        <x:v>↑6位</x:v>
+        <x:v>↑3位</x:v>
       </x:c>
       <x:c r="G36" s="11" t="str"/>
       <x:c r="H36" s="11" t="str"/>
       <x:c r="I36" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J36" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K36" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="L36" s="11" t="str">
-        <x:v>车仔漫</x:v>
+        <x:v>长风剧场</x:v>
       </x:c>
       <x:c r="M36" s="10" t="str">
-        <x:v>大旱之年，贫苦庄稼汉石满仓为宽慰盼他成家的母亲，扎了个稻草媳妇，谁料草人竟化作姑娘阿禾。原来阿禾是有灵性的青牛，十年前大旱濒死时被石满仓用豆秸和水救下，此番借稻草人身躯前来报恩。
-阿禾感知到村井即将枯竭，带领众人找到被封堵的牛眠岭古泉。靠卖自家井水牟利的马有财因利益受损，百般阻挠，甚至污染泉水、堵塞闸口。</x:v>
+        <x:v>45岁的白烨意外激活成长系统。只要亲身体验年轻人的日常，就能重拾青春活力，还能收获丰厚奖励。为完成系统任务，他报名成人高考，顺利考入大学，竟和女儿成了同校同学。重返校园的白烨，一边认真完成任务感受青春，一边在校园里开启一段充满趣味的全新人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -2422,36 +2406,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B37" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C37" s="10" t="str">
-        <x:v>我赚上千万跟爸妈说50W，隔天就被找上门</x:v>
+        <x:v>听水小锦鲤</x:v>
       </x:c>
       <x:c r="D37" s="11" t="str">
-        <x:v>09-13 08:00</x:v>
+        <x:v>09-12 21:13</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F37" s="11" t="str">
-        <x:v>↑5位</x:v>
+        <x:v>↑2位</x:v>
       </x:c>
       <x:c r="G37" s="11" t="str"/>
       <x:c r="H37" s="11" t="str"/>
       <x:c r="I37" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="J37" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K37" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="L37" s="11" t="str">
-        <x:v>至尊爽剧社</x:v>
+        <x:v>末日废土</x:v>
       </x:c>
       <x:c r="M37" s="10" t="str">
-        <x:v>三十二岁那年，贺川用六年孤注一掷的钻研，换来了七千六百万的回报。可财富还没捂热，先尝到的却是亲人无度的索取。他谎称只赚五十万，叮嘱保密，却挡不住消息走漏。隔天登门的亲戚不止要借钱买房，更联手外人盗用他的身份资料，试图冒名签约、伪造担保债务。贺川报警取证，警方介入追回大部分资金，涉案者包括部分机构人员均承担了法律责任，这笔帐，能否算清？</x:v>
+        <x:v>渔民周青从河中救下孤女汐汐，汐汐能感知水与水中生灵。周青捕鱼遭奸商王老板恶意封锁销路，依靠汐汐指引找到地下暗河运鱼脱困。他巧包被毒水污染的废弃水洼，利用地下活泉发展渔业，屡次化解对手的恶意算计。后来又克服缺冰、设备停电等重重难关，办起罐头厂，带领全村勤劳致富，正式收养汐汐，收获了阖家幸福与乡亲的美好生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -2459,36 +2443,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B38" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C38" s="10" t="str">
-        <x:v>七套房产，换来一纸调令</x:v>
+        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
       </x:c>
       <x:c r="D38" s="11" t="str">
-        <x:v>09-12 08:18</x:v>
+        <x:v>09-11 09:00</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
-        <x:v>37</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F38" s="11" t="str">
-        <x:v>↑5位</x:v>
+        <x:v>↑2位</x:v>
       </x:c>
       <x:c r="G38" s="11" t="str"/>
       <x:c r="H38" s="11" t="str"/>
       <x:c r="I38" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="J38" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K38" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧 / 家庭伦理</x:v>
       </x:c>
       <x:c r="L38" s="11" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>阳阳动画</x:v>
       </x:c>
       <x:c r="M38" s="10" t="str">
-        <x:v>公婆将七套房产全数赠予小叔子，长子陈峰看似顺从鼓掌，实则暗中申请援疆调令。面对父母偏心和弟媳挑衅，陈峰携妻林晚隐忍筹备。最终在家庭会议上，他出示双人调令宣告远赴新疆，打破原生家庭剥削链条。经历异地磨砺与除夕和解，一家人终在理解中重建亲情边界，实现各自独立与成长。</x:v>
+        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -2496,44 +2480,38 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B39" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C39" s="10" t="str">
-        <x:v>穿越七零:月季花开</x:v>
+        <x:v>回到零四年进军彩铃界</x:v>
       </x:c>
       <x:c r="D39" s="11" t="str">
-        <x:v>09-11 22:25</x:v>
+        <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
-        <x:v>46</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F39" s="11" t="str">
-        <x:v>↑5位</x:v>
+        <x:v>↑1位</x:v>
       </x:c>
       <x:c r="G39" s="11" t="str"/>
       <x:c r="H39" s="11" t="str"/>
-      <x:c r="I39" s="11" t="n">
-        <x:v>219</x:v>
-      </x:c>
+      <x:c r="I39" s="11" t="str"/>
       <x:c r="J39" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K39" s="10" t="str">
-        <x:v>年代怀旧</x:v>
-      </x:c>
-      <x:c r="L39" s="11" t="str">
-        <x:v>维维动画</x:v>
-      </x:c>
-      <x:c r="M39" s="10" t="str">
-        <x:v>女知青白月季意外穿进书中，原主本打算上山打掉腹中孩子。清醒过来的她选择接受命运，不再执念过往的情缘，决定和周野好好过日子。周野看似粗犷，实则重情重义，满心珍视白月季。二人携手扎根乡村，对抗邻里闲言碎语，努力耕耘生活。白月季凭借文笔投稿赚取稿费，周野踏实打拼养家，还迎来双胞胎。在柴米烟火里互相扶持，跨过重重风波，把平凡的农家日子过得滚烫又幸福。</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L39" s="11" t="str"/>
+      <x:c r="M39" s="10" t="str"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B40" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C40" s="10" t="str">
         <x:v>装傻下山</x:v>
@@ -2542,10 +2520,10 @@
         <x:v>2026-09-12</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F40" s="11" t="str">
-        <x:v>↑4位</x:v>
+        <x:v>↑1位</x:v>
       </x:c>
       <x:c r="G40" s="11" t="str"/>
       <x:c r="H40" s="11" t="str"/>
@@ -2564,36 +2542,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B41" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C41" s="10" t="str">
-        <x:v>今天开始做裴总</x:v>
+        <x:v>我的眼睛变成了透视神瞳</x:v>
       </x:c>
       <x:c r="D41" s="11" t="str">
-        <x:v>09-12 19:48</x:v>
+        <x:v>09-11 11:00</x:v>
       </x:c>
       <x:c r="E41" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F41" s="11" t="str">
-        <x:v>↑2位</x:v>
+        <x:v>↑1位</x:v>
       </x:c>
       <x:c r="G41" s="11" t="str"/>
       <x:c r="H41" s="11" t="str"/>
       <x:c r="I41" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="J41" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K41" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="L41" s="11" t="str">
-        <x:v>严墨墨</x:v>
+        <x:v>奇迹漫剧</x:v>
       </x:c>
       <x:c r="M41" s="10" t="str">
-        <x:v>裴野低调蛰伏三年，甘愿扮作普通员工，在公司默默沉淀，面对职场非议、旁人轻视从未辩解。年会之上，他惨遭当众开除，相伴多年的婚姻也走向终点，跌入人生低谷。褪去伪装，他不再刻意隐忍，解锁真实身份，告别敷衍度日的过往。一路轻松逆袭，打破所有人的偏见，凭自身实力惊艳全场，开启属于自己的全新人生。</x:v>
+        <x:v>罗川本是四处奔波的废品回收从业者，日子过得窘迫潦倒。一次意外，他觉醒透视异能，双眼能够看穿物件内里，辨明真伪与隐藏价值。凭借这份神异能力，他在旧货市场、废品堆里频频捡漏，屡屡发现被人忽视的珍宝。从被旁人轻视的底层小人物，他一步步积累财富与阅历，在古玩鉴宝圈崭露头角，破除无数圈套骗局，逆袭成受人敬重的顶尖鉴宝高手，改写了自己的平凡人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -2601,67 +2579,69 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B42" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C42" s="10" t="str">
-        <x:v>误救高冷校花，她爷爷非要我做孙女婿</x:v>
+        <x:v>远山架子班</x:v>
       </x:c>
       <x:c r="D42" s="11" t="str">
-        <x:v>2026-09-12</x:v>
-      </x:c>
-      <x:c r="E42" s="11" t="n">
-        <x:v>22</x:v>
-      </x:c>
+        <x:v>09-13 07:30</x:v>
+      </x:c>
+      <x:c r="E42" s="11" t="str"/>
       <x:c r="F42" s="11" t="str">
-        <x:v>↑2位</x:v>
+        <x:v>新上榜</x:v>
       </x:c>
       <x:c r="G42" s="11" t="str"/>
       <x:c r="H42" s="11" t="str"/>
-      <x:c r="I42" s="11" t="str"/>
+      <x:c r="I42" s="11" t="n">
+        <x:v>62</x:v>
+      </x:c>
       <x:c r="J42" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K42" s="10" t="str">
-        <x:v>家庭伦理</x:v>
-      </x:c>
-      <x:c r="L42" s="11" t="str"/>
-      <x:c r="M42" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L42" s="11" t="str">
+        <x:v>空空书漫</x:v>
+      </x:c>
+      <x:c r="M42" s="10" t="str">
+        <x:v>工地上，彭大勇拿着别家四十一天的招工纸，问贺远山凭什么只给三十。贺远山不争辩，只把账摊开，安全装备饭钱他管，工钱三天一结，从没拖欠。有人奔着高薪离开，可那边层层扣下来，到手反不如从前，还屡屡涉险。工友受伤住院，贺远山二话不说垫钱救人，又帮着把旧账一笔笔算清。他始终守着一条理，钱要挣，命不能换。规矩立得住，人心自然拢得回，班越带越稳，账越算越明。</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B43" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C43" s="10" t="str">
-        <x:v>我的师兄全是修仙界大佬</x:v>
+        <x:v>冰粉乌龙</x:v>
       </x:c>
       <x:c r="D43" s="11" t="str">
-        <x:v>09-11 18:16</x:v>
-      </x:c>
-      <x:c r="E43" s="11" t="n">
-        <x:v>83</x:v>
-      </x:c>
+        <x:v>09-13 07:05</x:v>
+      </x:c>
+      <x:c r="E43" s="11" t="str"/>
       <x:c r="F43" s="11" t="str">
-        <x:v>↑2位</x:v>
+        <x:v>新上榜</x:v>
       </x:c>
       <x:c r="G43" s="11" t="str"/>
       <x:c r="H43" s="11" t="str"/>
       <x:c r="I43" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="J43" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K43" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="L43" s="11" t="str">
-        <x:v>大公鸡剧场</x:v>
+        <x:v>星漫动漫剧场</x:v>
       </x:c>
       <x:c r="M43" s="10" t="str">
-        <x:v>六岁的女主奉师父顾青崖之命下山历练，寻找五位失散数百年的师兄。她天生神力，把九品丹药当糖豆吃，背着重剑闯修仙界。本以为师兄们在外落魄难归，却发现大师兄是正道第一人九天仙尊，二师兄是统御九幽的幽冥帝君，余下三位也皆是绝世大佬。小奶娃一路闯荡，把隐世多年的师兄们挨个喊回了家。</x:v>
+        <x:v>林北经营祖传冰粉店，因网络用语误会引来黑道人物何彪。双方消除隔阂后，林北又被迫为逃犯岑德海制作冰粉以拖延时间。最终警方赶到抓获罪犯，林北凭借机智与手艺协助破案，洗清嫌疑并获颁警民联络点荣誉，守护了家族手艺与社区安宁。</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -2669,36 +2649,34 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B44" s="11" t="n">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C44" s="10" t="str">
-        <x:v>清醒飒姐，携崽归来</x:v>
+        <x:v>竞争的枷锁</x:v>
       </x:c>
       <x:c r="D44" s="11" t="str">
-        <x:v>09-11 10:00</x:v>
-      </x:c>
-      <x:c r="E44" s="11" t="n">
-        <x:v>86</x:v>
-      </x:c>
+        <x:v>09-12 16:30</x:v>
+      </x:c>
+      <x:c r="E44" s="11" t="str"/>
       <x:c r="F44" s="11" t="str">
-        <x:v>↑2位</x:v>
+        <x:v>新上榜</x:v>
       </x:c>
       <x:c r="G44" s="11" t="str"/>
       <x:c r="H44" s="11" t="str"/>
       <x:c r="I44" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J44" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K44" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L44" s="11" t="str">
-        <x:v>小布丁漫剧</x:v>
+        <x:v>懒洋洋不懒</x:v>
       </x:c>
       <x:c r="M44" s="10" t="str">
-        <x:v>苏念五年前与顾衍舟一夜纠葛，独自生下儿子小野。母亲重病之际，她将儿子托付给顾衍舟并甩出亲子鉴定，轰动顾、沈两家。沈家沈亦清先后拿出五百万、两千万逼她离开，苏念拒绝妥协，凭借律师拿到对方商业把柄对等博弈。她拒绝依附豪门，凭过硬医学能力入职三甲医院成为访问学者。顾衍舟被她的坚韧打动，放下家世偏见，两人签订共同抚养协议，逐渐相爱。沈家败落后小野归宗改姓。苏念事业家庭双圆满，活成不被金钱和家世定义的模样。</x:v>
+        <x:v>双胞胎周朗和周昊从小就在家中竞争模式下长大，各类生活资源都要靠比拼争取，二人一直把对方视作对手。考入同一所大学后，争抢食堂岗位的契机下，他们才发现父母编织的谎言，两人都过得拮据艰难。过往多年的误会被解开，隔阂逐渐消散。兄弟俩放下彼此间的敌意，携手依靠打工谋求生活，摆脱旧有家庭模式的桎梏。往后不必再分出高下，并肩前行，认真经营属于自己的平凡生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -2706,13 +2684,13 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B45" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C45" s="10" t="str">
-        <x:v>器灵助我鉴万宝</x:v>
+        <x:v>方寸工位，亿万筹码</x:v>
       </x:c>
       <x:c r="D45" s="11" t="str">
-        <x:v>09-12 20:05</x:v>
+        <x:v>2026-09-13</x:v>
       </x:c>
       <x:c r="E45" s="11" t="str"/>
       <x:c r="F45" s="11" t="str">
@@ -2720,56 +2698,15 @@
       </x:c>
       <x:c r="G45" s="11" t="str"/>
       <x:c r="H45" s="11" t="str"/>
-      <x:c r="I45" s="11" t="n">
-        <x:v>80</x:v>
-      </x:c>
+      <x:c r="I45" s="11" t="str"/>
       <x:c r="J45" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K45" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L45" s="11" t="str">
-        <x:v>忆长安</x:v>
-      </x:c>
-      <x:c r="M45" s="10" t="str">
-        <x:v>古玩店打工青年陆沉川意外被碎瓷划伤，激活祖传龙纹佩，从此可以听见古董器灵的声音。他识破老板的假货圈套后，开启鉴宝之路。在拍卖会、鬼市、赌石大会上，陆沉川凭借特殊能力屡屡识破赝品，还对抗盗卖国宝的反派势力。他开设沉龙阁，坚守本心守护古物珍宝，直面神秘组织归墟会的威胁，踏上守护国宝的冒险。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="11" t="str">
-        <x:v>新剧上升</x:v>
-      </x:c>
-      <x:c r="B46" s="11" t="n">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C46" s="10" t="str">
-        <x:v>听水小锦鲤</x:v>
-      </x:c>
-      <x:c r="D46" s="11" t="str">
-        <x:v>09-12 21:13</x:v>
-      </x:c>
-      <x:c r="E46" s="11" t="str"/>
-      <x:c r="F46" s="11" t="str">
-        <x:v>新上榜</x:v>
-      </x:c>
-      <x:c r="G46" s="11" t="str"/>
-      <x:c r="H46" s="11" t="str"/>
-      <x:c r="I46" s="11" t="n">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="J46" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="K46" s="10" t="str">
-        <x:v>战神异能</x:v>
-      </x:c>
-      <x:c r="L46" s="11" t="str">
-        <x:v>末日废土</x:v>
-      </x:c>
-      <x:c r="M46" s="10" t="str">
-        <x:v>渔民周青从河中救下孤女汐汐，汐汐能感知水与水中生灵。周青捕鱼遭奸商王老板恶意封锁销路，依靠汐汐指引找到地下暗河运鱼脱困。他巧包被毒水污染的废弃水洼，利用地下活泉发展渔业，屡次化解对手的恶意算计。后来又克服缺冰、设备停电等重重难关，办起罐头厂，带领全村勤劳致富，正式收养汐汐，收获了阖家幸福与乡亲的美好生活。</x:v>
-      </x:c>
+      <x:c r="L45" s="11" t="str"/>
+      <x:c r="M45" s="10" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2814,33 +2751,27 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
-        <x:v>我赚上千万跟爸妈说50W，隔天就被找上门</x:v>
+        <x:v>小妹初长成</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>今日发布</x:v>
-      </x:c>
-      <x:c r="D2" s="11" t="str">
-        <x:v>09-13 08:00</x:v>
-      </x:c>
-      <x:c r="E2" s="11" t="n">
-        <x:v>78</x:v>
-      </x:c>
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D2" s="11" t="str"/>
+      <x:c r="E2" s="11" t="str"/>
       <x:c r="F2" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G2" s="10" t="str">
-        <x:v>至尊爽剧社</x:v>
-      </x:c>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="G2" s="10" t="str"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
+        <x:v>我赚上千万跟爸妈说50W，隔天就被找上门</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
         <x:v>今日发布</x:v>
@@ -2849,98 +2780,163 @@
         <x:v>09-13 08:00</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F3" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G3" s="10" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>至尊爽剧社</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>活宝老爹再赴青春，竟与女儿同上大学</x:v>
+        <x:v>远山架子班</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>09-13 00:08</x:v>
+        <x:v>09-13 07:30</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
-        <x:v>140</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F4" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G4" s="10" t="str">
-        <x:v>长风剧场</x:v>
+        <x:v>空空书漫</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>反派拿捏！</x:v>
+        <x:v>河箱送福来</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>当日新上榜</x:v>
-      </x:c>
-      <x:c r="D5" s="11" t="str"/>
-      <x:c r="E5" s="11" t="str"/>
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>09-13 11:00</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="n">
+        <x:v>64</x:v>
+      </x:c>
       <x:c r="F5" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G5" s="10" t="str">
+        <x:v>灵心讲故事</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>87</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>别咬，你太大只啦</x:v>
+        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>09-13 00:06</x:v>
+        <x:v>09-13 08:00</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
-        <x:v>180</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F6" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="G6" s="10" t="str"/>
+      <x:c r="G6" s="10" t="str">
+        <x:v>心动漫剧场</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>玄门大佬萧安乐</x:v>
+        <x:v>反派拿捏！</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
         <x:v>当日新上榜</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="str">
-        <x:v>08-19 19:18</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="n">
-        <x:v>137</x:v>
-      </x:c>
+      <x:c r="D7" s="11" t="str"/>
+      <x:c r="E7" s="11" t="str"/>
       <x:c r="F7" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="str">
-        <x:v>AIGC 楠楠</x:v>
-      </x:c>
+      <x:c r="G7" s="10" t="str"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="11" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B8" s="10" t="str">
+        <x:v>活宝老爹再赴青春，竟与女儿同上大学</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="str">
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="str">
+        <x:v>09-13 00:08</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F8" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G8" s="10" t="str">
+        <x:v>长风剧场</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="11" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B9" s="10" t="str">
+        <x:v>冰粉乌龙</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="str">
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="str">
+        <x:v>09-13 07:05</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F9" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G9" s="10" t="str">
+        <x:v>星漫动漫剧场</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="11" t="n">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B10" s="10" t="str">
+        <x:v>方寸工位，亿万筹码</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="str">
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D10" s="11" t="str"/>
+      <x:c r="E10" s="11" t="str"/>
+      <x:c r="F10" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="G10" s="10" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3009,16 +3005,16 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
-        <x:v>退婚后我在七零赚钱养家致富</x:v>
+        <x:v>破库房的秘密</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>2026-09-04</x:v>
+        <x:v>2026-09-05</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
         <x:v>7</x:v>
@@ -3027,33 +3023,29 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G2" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H2" s="11" t="str"/>
       <x:c r="I2" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="J2" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K2" s="11" t="str">
-        <x:v>0.00</x:v>
-      </x:c>
+      <x:c r="J2" s="11" t="str"/>
+      <x:c r="K2" s="11" t="str"/>
       <x:c r="L2" s="10" t="str"/>
       <x:c r="M2" s="10" t="str"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>一墙之隔，皆是人心</x:v>
+        <x:v>退婚后我在七零赚钱养家致富</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>09-06 15:48</x:v>
+        <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
         <x:v>7</x:v>
@@ -3064,33 +3056,31 @@
       <x:c r="G3" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H3" s="11" t="n">
-        <x:v>85</x:v>
-      </x:c>
+      <x:c r="H3" s="11" t="str"/>
       <x:c r="I3" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J3" s="11" t="str"/>
-      <x:c r="K3" s="11" t="str"/>
-      <x:c r="L3" s="10" t="str">
-        <x:v>在下长生</x:v>
-      </x:c>
-      <x:c r="M3" s="10" t="str">
-        <x:v>妻子临产被车堵住出口，叶瑾抱着羊水破裂的她跑了三公里才到医院，母子平安。面对无理的车主，他没有以暴制暴，而是选择依法行事——在自家院内合法砌墙、种下高价值树苗，全程录像留证。车主回来后暴力砸墙、碾压树苗，最终被依法追究责任。</x:v>
-      </x:c>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="J3" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K3" s="11" t="str">
+        <x:v>0.00</x:v>
+      </x:c>
+      <x:c r="L3" s="10" t="str"/>
+      <x:c r="M3" s="10" t="str"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>破库房的秘密</x:v>
+        <x:v>一墙之隔，皆是人心</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>2026-09-05</x:v>
+        <x:v>09-06 15:48</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
         <x:v>7</x:v>
@@ -3099,20 +3089,26 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G4" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H4" s="11" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H4" s="11" t="n">
+        <x:v>85</x:v>
+      </x:c>
       <x:c r="I4" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J4" s="11" t="str"/>
       <x:c r="K4" s="11" t="str"/>
-      <x:c r="L4" s="10" t="str"/>
-      <x:c r="M4" s="10" t="str"/>
+      <x:c r="L4" s="10" t="str">
+        <x:v>在下长生</x:v>
+      </x:c>
+      <x:c r="M4" s="10" t="str">
+        <x:v>妻子临产被车堵住出口，叶瑾抱着羊水破裂的她跑了三公里才到医院，母子平安。面对无理的车主，他没有以暴制暴，而是选择依法行事——在自家院内合法砌墙、种下高价值树苗，全程录像留证。车主回来后暴力砸墙、碾压树苗，最终被依法追究责任。</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
         <x:v>惊絮无声：傻女的绝杀</x:v>
@@ -3149,16 +3145,16 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>凤阙承安</x:v>
+        <x:v>我的奇葩舍友</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>09-06 09:55</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
         <x:v>7</x:v>
@@ -3167,29 +3163,35 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G6" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H6" s="11" t="str"/>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H6" s="11" t="n">
+        <x:v>59</x:v>
+      </x:c>
       <x:c r="I6" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J6" s="11" t="str"/>
       <x:c r="K6" s="11" t="str"/>
-      <x:c r="L6" s="10" t="str"/>
-      <x:c r="M6" s="10" t="str"/>
+      <x:c r="L6" s="10" t="str">
+        <x:v>金鱼漫剪</x:v>
+      </x:c>
+      <x:c r="M6" s="10" t="str">
+        <x:v>林嘉宝从小由母亲周美兰一手带大，事无巨细都由妈妈安排。上大学后，他不会套被套，不会洗衣服，遇事第一反应是打电话问妈妈。母亲为他定下各种宿舍规矩，与室友矛盾不断。直到家中突遭变故，父亲破产，豪宅被封，母亲失联。嘉宝一夜之间失去所有依靠，被迫独自面对生活，一步步学会洗衣、打工、交电费，逐渐成为独立的大学生。</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>一针绣出自己的路</x:v>
+        <x:v>那块玉，带我们回家</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>09-04 19:51</x:v>
+        <x:v>09-05 07:18</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
         <x:v>7</x:v>
@@ -3198,10 +3200,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G7" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H7" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="I7" s="10" t="str">
         <x:v>其他</x:v>
@@ -3209,24 +3211,24 @@
       <x:c r="J7" s="11" t="str"/>
       <x:c r="K7" s="11" t="str"/>
       <x:c r="L7" s="10" t="str">
-        <x:v>墨尘漫剧</x:v>
+        <x:v>五指毛桃</x:v>
       </x:c>
       <x:c r="M7" s="10" t="str">
-        <x:v>苏绾青她从裁缝店半张旧桌重新开始，凭一针一线修补旧物、绣出人心，也把被看轻的手艺做成自己的路。故事温暖励志，展现普通女性靠勤奋、诚信和坚持赢得尊重、改变生活的力量。所有的事情都可以迎刃而解，代表了生活中的光</x:v>
+        <x:v>六岁孩童为救母拾荒半年，孝心感动天地，更牵出一段失散六年的亲情。缘分以信物为引，助离散一家重逢。当暗处之手伸向团圆，真相与信任如光破晓，令恶念无处遁形。正义为善良护航，温暖在守望中生长。孩子用稚嫩肩膀撑起希望，父母以爱重筑家园，善意在风雨中传递，终迎阖家安康的晴空。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>我的奇葩舍友</x:v>
+        <x:v>一针绣出自己的路</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>09-06 09:55</x:v>
+        <x:v>09-04 19:51</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
         <x:v>7</x:v>
@@ -3235,10 +3237,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G8" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H8" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
         <x:v>其他</x:v>
@@ -3246,24 +3248,24 @@
       <x:c r="J8" s="11" t="str"/>
       <x:c r="K8" s="11" t="str"/>
       <x:c r="L8" s="10" t="str">
-        <x:v>金鱼漫剪</x:v>
+        <x:v>墨尘漫剧</x:v>
       </x:c>
       <x:c r="M8" s="10" t="str">
-        <x:v>林嘉宝从小由母亲周美兰一手带大，事无巨细都由妈妈安排。上大学后，他不会套被套，不会洗衣服，遇事第一反应是打电话问妈妈。母亲为他定下各种宿舍规矩，与室友矛盾不断。直到家中突遭变故，父亲破产，豪宅被封，母亲失联。嘉宝一夜之间失去所有依靠，被迫独自面对生活，一步步学会洗衣、打工、交电费，逐渐成为独立的大学生。</x:v>
+        <x:v>苏绾青她从裁缝店半张旧桌重新开始，凭一针一线修补旧物、绣出人心，也把被看轻的手艺做成自己的路。故事温暖励志，展现普通女性靠勤奋、诚信和坚持赢得尊重、改变生活的力量。所有的事情都可以迎刃而解，代表了生活中的光</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>那块玉，带我们回家</x:v>
+        <x:v>凤阙承安</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>09-05 07:18</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
         <x:v>7</x:v>
@@ -3272,35 +3274,29 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G9" s="11" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="H9" s="11" t="n">
-        <x:v>69</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H9" s="11" t="str"/>
       <x:c r="I9" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J9" s="11" t="str"/>
       <x:c r="K9" s="11" t="str"/>
-      <x:c r="L9" s="10" t="str">
-        <x:v>五指毛桃</x:v>
-      </x:c>
-      <x:c r="M9" s="10" t="str">
-        <x:v>六岁孩童为救母拾荒半年，孝心感动天地，更牵出一段失散六年的亲情。缘分以信物为引，助离散一家重逢。当暗处之手伸向团圆，真相与信任如光破晓，令恶念无处遁形。正义为善良护航，温暖在守望中生长。孩子用稚嫩肩膀撑起希望，父母以爱重筑家园，善意在风雨中传递，终迎阖家安康的晴空。</x:v>
-      </x:c>
+      <x:c r="L9" s="10" t="str"/>
+      <x:c r="M9" s="10" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>蒙蒙半故</x:v>
+        <x:v>重生扬子鳄：从网购开始吞噬进化</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>09-05 20:27</x:v>
+        <x:v>09-07 00:04</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
         <x:v>7</x:v>
@@ -3309,10 +3305,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G10" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H10" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="I10" s="10" t="str">
         <x:v>其他</x:v>
@@ -3320,21 +3316,21 @@
       <x:c r="J10" s="11" t="str"/>
       <x:c r="K10" s="11" t="str"/>
       <x:c r="L10" s="10" t="str">
-        <x:v>小斐漫剧</x:v>
+        <x:v>最漫剧场</x:v>
       </x:c>
       <x:c r="M10" s="10" t="str">
-        <x:v>拥有漫长寿命的男人隐姓埋名，以外卖员身份在都市生活。百岁老人临终的遗愿，让他卷入豪门家族的纷争。他结识家族女总裁，接连应对家族内斗、敌对势力与神秘长生组织的重重算计。二人携手揭开千年前的尘封秘辛，对抗妄图窃取长生力量的反派，在危机之中彼此羁绊，还要面对即将开启的上古昆仑之门带来的巨大未知考验。</x:v>
+        <x:v>陆沉加班猝死，重生为一只扬子鳄，却意外激活吞噬进化系统。他从小小鳄鱼起步，吞噬万物，不断觉醒龙族血脉。从护佑一方村民到对抗敌人九阶妖兽，他一步步蜕变成长。面对灵气复苏后崛起的强敌，陆沉立誓守护故土，踏上通往真龙的逆天进化之路。吞噬进化，龙威初显！既是妖兽，更是守护神！本漫剧改编自番茄小说《重生扬子鳄，从网购开始吞噬进化》作者《风依臣》</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="n">
-        <x:v>44</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>不负恩情不负卿</x:v>
+        <x:v>野茶开出花</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>2026-09-05</x:v>
+        <x:v>09-05 18:16</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
         <x:v>8</x:v>
@@ -3346,26 +3342,32 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G11" s="11" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H11" s="11" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H11" s="11" t="n">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="I11" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J11" s="11" t="str"/>
       <x:c r="K11" s="11" t="str"/>
-      <x:c r="L11" s="10" t="str"/>
-      <x:c r="M11" s="10" t="str"/>
+      <x:c r="L11" s="10" t="str">
+        <x:v>多米漫剧场</x:v>
+      </x:c>
+      <x:c r="M11" s="10" t="str">
+        <x:v>苏晚星十九岁，一百八十斤，被母亲断卡后送进深山。石阶四十分钟，土屋、木板床、没信号的手机，迎接她的是守山四十年的石奶奶。采茶磨出水泡，跑山喘不上气，半夜偷吃生黄豆被当场抓住。阿杏叫她晚星姐，集市阿婆说她壮实，她第一次觉得胖没那么刺耳。体重从一百八到一百二，手上磨出了茧。她拍短视频卖茶，建山风茶舍。再次上山，她站在山顶说山神爷爷，我回来了。山风知道她来过，也知道她变成了谁。</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>野茶开出花</x:v>
+        <x:v>蒙蒙半故</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>09-05 18:16</x:v>
+        <x:v>09-05 20:27</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
         <x:v>8</x:v>
@@ -3377,10 +3379,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G12" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H12" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str">
         <x:v>其他</x:v>
@@ -3388,24 +3390,24 @@
       <x:c r="J12" s="11" t="str"/>
       <x:c r="K12" s="11" t="str"/>
       <x:c r="L12" s="10" t="str">
-        <x:v>多米漫剧场</x:v>
+        <x:v>小斐漫剧</x:v>
       </x:c>
       <x:c r="M12" s="10" t="str">
-        <x:v>苏晚星十九岁，一百八十斤，被母亲断卡后送进深山。石阶四十分钟，土屋、木板床、没信号的手机，迎接她的是守山四十年的石奶奶。采茶磨出水泡，跑山喘不上气，半夜偷吃生黄豆被当场抓住。阿杏叫她晚星姐，集市阿婆说她壮实，她第一次觉得胖没那么刺耳。体重从一百八到一百二，手上磨出了茧。她拍短视频卖茶，建山风茶舍。再次上山，她站在山顶说山神爷爷，我回来了。山风知道她来过，也知道她变成了谁。</x:v>
+        <x:v>拥有漫长寿命的男人隐姓埋名，以外卖员身份在都市生活。百岁老人临终的遗愿，让他卷入豪门家族的纷争。他结识家族女总裁，接连应对家族内斗、敌对势力与神秘长生组织的重重算计。二人携手揭开千年前的尘封秘辛，对抗妄图窃取长生力量的反派，在危机之中彼此羁绊，还要面对即将开启的上古昆仑之门带来的巨大未知考验。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>重生扬子鳄：从网购开始吞噬进化</x:v>
+        <x:v>不负恩情不负卿</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>09-07 00:04</x:v>
+        <x:v>2026-09-05</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
         <x:v>7</x:v>
@@ -3414,32 +3416,26 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G13" s="11" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H13" s="11" t="n">
-        <x:v>134</x:v>
-      </x:c>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H13" s="11" t="str"/>
       <x:c r="I13" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J13" s="11" t="str"/>
       <x:c r="K13" s="11" t="str"/>
-      <x:c r="L13" s="10" t="str">
-        <x:v>最漫剧场</x:v>
-      </x:c>
-      <x:c r="M13" s="10" t="str">
-        <x:v>陆沉加班猝死，重生为一只扬子鳄，却意外激活吞噬进化系统。他从小小鳄鱼起步，吞噬万物，不断觉醒龙族血脉。从护佑一方村民到对抗敌人九阶妖兽，他一步步蜕变成长。面对灵气复苏后崛起的强敌，陆沉立誓守护故土，踏上通往真龙的逆天进化之路。吞噬进化，龙威初显！既是妖兽，更是守护神！本漫剧改编自番茄小说《重生扬子鳄，从网购开始吞噬进化》作者《风依臣》</x:v>
-      </x:c>
+      <x:c r="L13" s="10" t="str"/>
+      <x:c r="M13" s="10" t="str"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>黑蛋孵出山海神兽后我无敌了</x:v>
+        <x:v>让你代写情书，你落笔惊哭大儒第四季</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>09-06 18:00</x:v>
+        <x:v>2026-09-06</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
         <x:v>7</x:v>
@@ -3453,24 +3449,18 @@
       <x:c r="G14" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H14" s="11" t="n">
-        <x:v>154</x:v>
-      </x:c>
+      <x:c r="H14" s="11" t="str"/>
       <x:c r="I14" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J14" s="11" t="str"/>
       <x:c r="K14" s="11" t="str"/>
-      <x:c r="L14" s="10" t="str">
-        <x:v>抱月剧场</x:v>
-      </x:c>
-      <x:c r="M14" s="10" t="str">
-        <x:v>寒门少年李初七攒了三年银子，仍买不起最低等的兽蛋。一次意外，他在后山捡到一枚黑蛋，孵出的煤球又小又馋，偏偏爱啃铜钱。可每吞下一缕兽息，它便能复现对手的能力。县学测灵那日，测灵石骤然亮起黑光，群兽伏地。所有人都以为他只是走了好运，只有陆远山想起古籍中的禁忌——黑光现，万兽伏。煤球究竟是什么？</x:v>
-      </x:c>
+      <x:c r="L14" s="10" t="str"/>
+      <x:c r="M14" s="10" t="str"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="n">
-        <x:v>76</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
         <x:v>苏小姐高调离婚，前夫哭惨了</x:v>
@@ -3501,16 +3491,16 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>一碗热饭暖人性</x:v>
+        <x:v>黑蛋孵出山海神兽后我无敌了</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>09-03 00:06</x:v>
+        <x:v>09-06 18:00</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
         <x:v>7</x:v>
@@ -3519,37 +3509,35 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G16" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H16" s="11" t="n">
-        <x:v>49</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="J16" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K16" s="11" t="str">
-        <x:v>0.00</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="J16" s="11" t="str"/>
+      <x:c r="K16" s="11" t="str"/>
       <x:c r="L16" s="10" t="str">
-        <x:v>第九幕</x:v>
-      </x:c>
-      <x:c r="M16" s="10" t="str"/>
+        <x:v>抱月剧场</x:v>
+      </x:c>
+      <x:c r="M16" s="10" t="str">
+        <x:v>寒门少年李初七攒了三年银子，仍买不起最低等的兽蛋。一次意外，他在后山捡到一枚黑蛋，孵出的煤球又小又馋，偏偏爱啃铜钱。可每吞下一缕兽息，它便能复现对手的能力。县学测灵那日，测灵石骤然亮起黑光，群兽伏地。所有人都以为他只是走了好运，只有陆远山想起古籍中的禁忌——黑光现，万兽伏。煤球究竟是什么？</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="n">
         <x:v>83</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>让你代写情书，你落笔惊哭大儒第四季</x:v>
+        <x:v>重生八零，从捡蘑菇开始安家</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>2026-09-06</x:v>
+        <x:v>09-05 17:58</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
         <x:v>7</x:v>
@@ -3558,29 +3546,35 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G17" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H17" s="11" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H17" s="11" t="n">
+        <x:v>97</x:v>
+      </x:c>
       <x:c r="I17" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J17" s="11" t="str"/>
       <x:c r="K17" s="11" t="str"/>
-      <x:c r="L17" s="10" t="str"/>
-      <x:c r="M17" s="10" t="str"/>
+      <x:c r="L17" s="10" t="str">
+        <x:v>七星动画</x:v>
+      </x:c>
+      <x:c r="M17" s="10" t="str">
+        <x:v>徐林带着前世的遗憾重回八十年代，过去的他浑浑噩噩，错过了爱人，落得孤苦收场。重生之后，他彻底洗心革面，迎娶心性温婉、知书达理的祝薇薇。他抓住时代机遇，收购蘑菇野味做起生意，用心呵护妻子。既要应对邻里间的猜忌算计、各村村民的矛盾纠纷，又要带领乡亲寻找谋生出路，在一地鸡毛的乡村烟火里，拼尽全力守护家庭，改写属于自己与身边人的命运。</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
+        <x:v>白鹿照归途</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>2026-09-05</x:v>
+        <x:v>09-03 14:40</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
         <x:v>7</x:v>
@@ -3589,41 +3583,49 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G18" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="11" t="str"/>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H18" s="11" t="n">
+        <x:v>79</x:v>
+      </x:c>
       <x:c r="I18" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="J18" s="11" t="str"/>
-      <x:c r="K18" s="11" t="str"/>
-      <x:c r="L18" s="10" t="str"/>
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="J18" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K18" s="11" t="str">
+        <x:v>0.60</x:v>
+      </x:c>
+      <x:c r="L18" s="10" t="str">
+        <x:v>漫漫天星</x:v>
+      </x:c>
       <x:c r="M18" s="10" t="str"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>重生八零，从捡蘑菇开始安家</x:v>
+        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>09-05 17:58</x:v>
+        <x:v>09-08 17:58</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G19" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H19" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str">
         <x:v>其他</x:v>
@@ -3631,21 +3633,21 @@
       <x:c r="J19" s="11" t="str"/>
       <x:c r="K19" s="11" t="str"/>
       <x:c r="L19" s="10" t="str">
-        <x:v>七星动画</x:v>
+        <x:v>禾苗动画</x:v>
       </x:c>
       <x:c r="M19" s="10" t="str">
-        <x:v>徐林带着前世的遗憾重回八十年代，过去的他浑浑噩噩，错过了爱人，落得孤苦收场。重生之后，他彻底洗心革面，迎娶心性温婉、知书达理的祝薇薇。他抓住时代机遇，收购蘑菇野味做起生意，用心呵护妻子。既要应对邻里间的猜忌算计、各村村民的矛盾纠纷，又要带领乡亲寻找谋生出路，在一地鸡毛的乡村烟火里，拼尽全力守护家庭，改写属于自己与身边人的命运。</x:v>
+        <x:v>末世异能者沐小暖意外穿书，成为七个反派继子的恶毒后娘。原主辛劳养娃却遭流言中伤，最终含恨而终。沐小暖决心扭转命运，恩威并施管教孩子，凭末世身手进山打猎采药、种地赶集改善家计，更以百年老参为礼，为长子求得名儒霍政谚收为关门弟子。她护佑家人躲过恶人算计与亲戚夺产，建起新宅。七个孩子从怨恨抗拒到真心信赖，争着喊她娘，一家人携手改写命运，收获温暖亲情。</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
+        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>09-08 17:58</x:v>
+        <x:v>09-08 11:00</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
         <x:v>5</x:v>
@@ -3660,7 +3662,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H20" s="11" t="n">
-        <x:v>111</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="I20" s="10" t="str">
         <x:v>其他</x:v>
@@ -3668,21 +3670,21 @@
       <x:c r="J20" s="11" t="str"/>
       <x:c r="K20" s="11" t="str"/>
       <x:c r="L20" s="10" t="str">
-        <x:v>禾苗动画</x:v>
+        <x:v>白桃剧场</x:v>
       </x:c>
       <x:c r="M20" s="10" t="str">
-        <x:v>末世异能者沐小暖意外穿书，成为七个反派继子的恶毒后娘。原主辛劳养娃却遭流言中伤，最终含恨而终。沐小暖决心扭转命运，恩威并施管教孩子，凭末世身手进山打猎采药、种地赶集改善家计，更以百年老参为礼，为长子求得名儒霍政谚收为关门弟子。她护佑家人躲过恶人算计与亲戚夺产，建起新宅。七个孩子从怨恨抗拒到真心信赖，争着喊她娘，一家人携手改写命运，收获温暖亲情。</x:v>
+        <x:v>阿梨一觉睡了三百年，养大的五只小兽尽数离去。她带着五只旧饭碗、十二枚铜钱与一把锈柴刀下山寻兽。昔日的小家伙已成威震四方的妖祖，历经重重相遇与揭秘，阿梨知晓三百年封印的真相，携手五只妖祖，一同对抗祸世灭灵兽神。</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
+        <x:v>抢个新娘来当后娘第一季</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>09-08 11:00</x:v>
+        <x:v>09-08 15:10</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
         <x:v>5</x:v>
@@ -3694,10 +3696,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G21" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H21" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="I21" s="10" t="str">
         <x:v>其他</x:v>
@@ -3705,24 +3707,24 @@
       <x:c r="J21" s="11" t="str"/>
       <x:c r="K21" s="11" t="str"/>
       <x:c r="L21" s="10" t="str">
-        <x:v>白桃剧场</x:v>
+        <x:v>麻辣公主</x:v>
       </x:c>
       <x:c r="M21" s="10" t="str">
-        <x:v>阿梨一觉睡了三百年，养大的五只小兽尽数离去。她带着五只旧饭碗、十二枚铜钱与一把锈柴刀下山寻兽。昔日的小家伙已成威震四方的妖祖，历经重重相遇与揭秘，阿梨知晓三百年封印的真相，携手五只妖祖，一同对抗祸世灭灵兽神。</x:v>
+        <x:v>带着十里红妆出嫁那日，我才得知新郎早已另娶，这门亲事不过是盯上了我李家的家产。换作旁人或许忍气吞声，我偏不。我当众拒入侯府，主动上书朝廷，愿以嫁妆资援南方水患，只求解除婚约、护我父母周全。这份胆识赢得安王敬重，他以正妃之礼娶我入门。我立誓此生不做妾、不与人共侍一夫，终得一份彼此尊重的姻缘。</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>抢个新娘来当后娘第一季</x:v>
+        <x:v>穿书后我带萌宝上门认爹</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>09-08 15:10</x:v>
+        <x:v>09-07 19:18</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
         <x:v>6</x:v>
@@ -3731,10 +3733,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G22" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H22" s="11" t="n">
-        <x:v>177</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str">
         <x:v>其他</x:v>
@@ -3742,36 +3744,36 @@
       <x:c r="J22" s="11" t="str"/>
       <x:c r="K22" s="11" t="str"/>
       <x:c r="L22" s="10" t="str">
-        <x:v>麻辣公主</x:v>
+        <x:v>虾仁不自在</x:v>
       </x:c>
       <x:c r="M22" s="10" t="str">
-        <x:v>带着十里红妆出嫁那日，我才得知新郎早已另娶，这门亲事不过是盯上了我李家的家产。换作旁人或许忍气吞声，我偏不。我当众拒入侯府，主动上书朝廷，愿以嫁妆资援南方水患，只求解除婚约、护我父母周全。这份胆识赢得安王敬重，他以正妃之礼娶我入门。我立誓此生不做妾、不与人共侍一夫，终得一份彼此尊重的姻缘。</x:v>
+        <x:v>许知棠重生穿进书中，当即带着五岁儿子许小舟登门，将孩子送到亲生父亲——傅氏集团总裁傅临川面前，只想抽身退出剧情。幼儿园里儿子遭同学诬陷、老师偏心，她强势护崽，硬刚蛮横家长与失职老师。亲子鉴定尘埃落定，萌娃黏妈不黏爹，反倒让清冷总裁渐渐上心。</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="n">
-        <x:v>37</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>重启人生，拒绝校花？</x:v>
+        <x:v>重生三天前，我用水泥封死地下室</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>09-08 08:30</x:v>
+        <x:v>09-09 09:28</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E23" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E23" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="F23" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G23" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H23" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
         <x:v>其他</x:v>
@@ -3779,36 +3781,36 @@
       <x:c r="J23" s="11" t="str"/>
       <x:c r="K23" s="11" t="str"/>
       <x:c r="L23" s="10" t="str">
-        <x:v>肆漫简</x:v>
+        <x:v>忘忧剧场</x:v>
       </x:c>
       <x:c r="M23" s="10" t="str">
-        <x:v>白陌重生回到2004年高考夜，果断避开前世陷害自己的宾馆陷阱，救下被下药的校花江洛菡，彻底扭转人生走向。他不再执着于过往的情感执念，跳出卑微追爱的困局，转而关心恩师健康、规划学业与创业方向，结识志同道合的伙伴。凭借重生阅历清醒选择前路，把握青春重启人生，用行动改写原本遗憾的命运，活出全新成长轨迹。</x:v>
+        <x:v>阮清重生回被保姆王妈一家害死的三天前，前世她因心善引狼入室，保姆全家蜗居别墅地下室偷窃投毒，最终惨遭勒死。重生后她假装不知，趁王妈外出时用水泥将地下室彻底封死。警方破墙后，五具尸体令真相大白，王妈因盗窃、投毒被判十五年。阮清与父母团聚，恶人终得恶报，她重获新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>穿书后我带萌宝上门认爹</x:v>
+        <x:v>不靠谱爸妈很靠谱</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>09-07 19:18</x:v>
+        <x:v>09-09 11:08</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G24" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H24" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I24" s="10" t="str">
         <x:v>其他</x:v>
@@ -3816,24 +3818,24 @@
       <x:c r="J24" s="11" t="str"/>
       <x:c r="K24" s="11" t="str"/>
       <x:c r="L24" s="10" t="str">
-        <x:v>虾仁不自在</x:v>
+        <x:v>灵妹儿</x:v>
       </x:c>
       <x:c r="M24" s="10" t="str">
-        <x:v>许知棠重生穿进书中，当即带着五岁儿子许小舟登门，将孩子送到亲生父亲——傅氏集团总裁傅临川面前，只想抽身退出剧情。幼儿园里儿子遭同学诬陷、老师偏心，她强势护崽，硬刚蛮横家长与失职老师。亲子鉴定尘埃落定，萌娃黏妈不黏爹，反倒让清冷总裁渐渐上心。</x:v>
+        <x:v>外表张扬的年轻夫妻在冬夜救下女婴林小小，用十七年的辛勤劳动和无条件陪伴，为她撑起温暖的家。曾经成绩落后的林小小，在父母的鼓励下重新学习，一步步成长为优秀学生。面对亲生家庭带来的资源与人生选择，她也开始重新理解血缘、养育与责任。当外界的误解影响到父母的生活，林小小决定勇敢站出来，用事实守护家人，也用努力证明真正的爱，是尊重、陪伴和彼此成就。</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>重生三天前，我用水泥封死地下室</x:v>
+        <x:v>全家施压：我反手签了过户合同</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>09-09 09:28</x:v>
+        <x:v>09-08 16:58</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
         <x:v>5</x:v>
@@ -3842,10 +3844,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G25" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H25" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str">
         <x:v>其他</x:v>
@@ -3853,21 +3855,21 @@
       <x:c r="J25" s="11" t="str"/>
       <x:c r="K25" s="11" t="str"/>
       <x:c r="L25" s="10" t="str">
-        <x:v>忘忧剧场</x:v>
+        <x:v>灵川剧场</x:v>
       </x:c>
       <x:c r="M25" s="10" t="str">
-        <x:v>阮清重生回被保姆王妈一家害死的三天前，前世她因心善引狼入室，保姆全家蜗居别墅地下室偷窃投毒，最终惨遭勒死。重生后她假装不知，趁王妈外出时用水泥将地下室彻底封死。警方破墙后，五具尸体令真相大白，王妈因盗窃、投毒被判十五年。阮清与父母团聚，恶人终得恶报，她重获新生。</x:v>
+        <x:v>儿子儿媳多次提议我搬回乡下养老，将城里的宽敞住房腾出来给女方父母长期居住。我笑着点头应下，转头便将这套三室朝南的江景房产挂牌出售，最终成交二百八十万元。我随即购置了一套一室一厅的小户型，更换门锁后独自入住。他们上门索要钥匙，我没有开门。名下房产我自有主张，谁也别想插手安排。</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>不靠谱爸妈很靠谱</x:v>
+        <x:v>离家十年，回来女儿被换了</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
-        <x:v>09-09 11:08</x:v>
+        <x:v>09-09 00:04</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
         <x:v>4</x:v>
@@ -3879,10 +3881,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G26" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H26" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="I26" s="10" t="str">
         <x:v>其他</x:v>
@@ -3890,24 +3892,24 @@
       <x:c r="J26" s="11" t="str"/>
       <x:c r="K26" s="11" t="str"/>
       <x:c r="L26" s="10" t="str">
-        <x:v>灵妹儿</x:v>
+        <x:v>魔方影视（上剧版</x:v>
       </x:c>
       <x:c r="M26" s="10" t="str">
-        <x:v>外表张扬的年轻夫妻在冬夜救下女婴林小小，用十七年的辛勤劳动和无条件陪伴，为她撑起温暖的家。曾经成绩落后的林小小，在父母的鼓励下重新学习，一步步成长为优秀学生。面对亲生家庭带来的资源与人生选择，她也开始重新理解血缘、养育与责任。当外界的误解影响到父母的生活，林小小决定勇敢站出来，用事实守护家人，也用努力证明真正的爱，是尊重、陪伴和彼此成就。</x:v>
+        <x:v>程砚宁完成长期绝密任务归来，满心想要弥补亲情，却发现家中早已物是人非。身边亲近之人被私欲蒙蔽，制造重重骗局，试图侵占她的事业与财富。面对接连而来的算计与危机，她凭借过人的魄力与智慧步步拆解阴谋，联合正义力量搜集证据，厘清全部是非纠葛。在守护自身事业的同时，她放下过往伤痛，投身公益，完成自我和解，迎来属于自己的全新人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>全家施压：我反手签了过户合同</x:v>
+        <x:v>美颜系统开挂，大佬全跪下</x:v>
       </x:c>
       <x:c r="C27" s="11" t="str">
-        <x:v>09-08 16:58</x:v>
+        <x:v>09-09 00:10</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
         <x:v>5</x:v>
@@ -3916,10 +3918,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G27" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H27" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="I27" s="10" t="str">
         <x:v>其他</x:v>
@@ -3927,21 +3929,21 @@
       <x:c r="J27" s="11" t="str"/>
       <x:c r="K27" s="11" t="str"/>
       <x:c r="L27" s="10" t="str">
-        <x:v>灵川剧场</x:v>
+        <x:v>御儿</x:v>
       </x:c>
       <x:c r="M27" s="10" t="str">
-        <x:v>儿子儿媳多次提议我搬回乡下养老，将城里的宽敞住房腾出来给女方父母长期居住。我笑着点头应下，转头便将这套三室朝南的江景房产挂牌出售，最终成交二百八十万元。我随即购置了一套一室一厅的小户型，更换门锁后独自入住。他们上门索要钥匙，我没有开门。名下房产我自有主张，谁也别想插手安排。</x:v>
+        <x:v>曾因外形饱受非议的米珂华丽转身，蜕变得耀眼又夺目。从前对她嗤之以鼻的蒋少开始频频在意，素来冷眼毒舌的陆总不知不觉深陷其中，连一向克己的商界大佬也为她打破原则。米珂凭智商与手腕周旋于众人之间，上演一场势均力敌的情感博弈。没有俗套的救赎，只有双向的拉扯。看一众高高在上的精英暗自较劲、步步沉沦，心甘情愿为她卸下防备。</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>美颜系统开挂，大佬全跪下</x:v>
+        <x:v>末世来临，我靠囤货种田丰衣足食</x:v>
       </x:c>
       <x:c r="C28" s="11" t="str">
-        <x:v>09-09 00:10</x:v>
+        <x:v>09-09 15:30</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
         <x:v>4</x:v>
@@ -3953,10 +3955,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G28" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H28" s="11" t="n">
-        <x:v>172</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="I28" s="10" t="str">
         <x:v>其他</x:v>
@@ -3964,24 +3966,24 @@
       <x:c r="J28" s="11" t="str"/>
       <x:c r="K28" s="11" t="str"/>
       <x:c r="L28" s="10" t="str">
-        <x:v>御儿</x:v>
+        <x:v>渲渲动画</x:v>
       </x:c>
       <x:c r="M28" s="10" t="str">
-        <x:v>曾因外形饱受非议的米珂华丽转身，蜕变得耀眼又夺目。从前对她嗤之以鼻的蒋少开始频频在意，素来冷眼毒舌的陆总不知不觉深陷其中，连一向克己的商界大佬也为她打破原则。米珂凭智商与手腕周旋于众人之间，上演一场势均力敌的情感博弈。没有俗套的救赎，只有双向的拉扯。看一众高高在上的精英暗自较劲、步步沉沦，心甘情愿为她卸下防备。</x:v>
+        <x:v>吴真真带着末世惨死的记忆重生，抢下秘宝空间，囤积海量物资，提前规避天灾人祸。她意外发现家人同样重生，一家人携手为末日做足准备。灾变如期而至，病毒、台风、极寒轮番降临。她机缘结识实力强悍的谢穆辰，二人从互相试探到并肩而立。面对凶悍恶徒与重重危机，吴真真依靠空间与智慧守护至亲，谢穆辰以自身力量与之守望相助，在满目疮痍的末世里，拼尽全力守住生存希望，奔赴属于他们的新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>离家十年，回来女儿被换了</x:v>
+        <x:v>清禾自立</x:v>
       </x:c>
       <x:c r="C29" s="11" t="str">
-        <x:v>09-09 00:04</x:v>
+        <x:v>09-08 18:22</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
         <x:v>5</x:v>
@@ -3990,10 +3992,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G29" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H29" s="11" t="n">
-        <x:v>155</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="I29" s="10" t="str">
         <x:v>其他</x:v>
@@ -4001,61 +4003,55 @@
       <x:c r="J29" s="11" t="str"/>
       <x:c r="K29" s="11" t="str"/>
       <x:c r="L29" s="10" t="str">
-        <x:v>魔方影视（上剧版</x:v>
+        <x:v>晚风漫剧</x:v>
       </x:c>
       <x:c r="M29" s="10" t="str">
-        <x:v>程砚宁完成长期绝密任务归来，满心想要弥补亲情，却发现家中早已物是人非。身边亲近之人被私欲蒙蔽，制造重重骗局，试图侵占她的事业与财富。面对接连而来的算计与危机，她凭借过人的魄力与智慧步步拆解阴谋，联合正义力量搜集证据，厘清全部是非纠葛。在守护自身事业的同时，她放下过往伤痛，投身公益，完成自我和解，迎来属于自己的全新人生。</x:v>
+        <x:v>1978年，母亲离世仅仅二十七天，陆清禾平静的家骤然崩塌。继母母女觊觎母亲遗物与房间，父亲陆振邦一味偏袒外人，甚至要逼她停学顾家。无依无靠的十五岁少女没有哭闹逃离，她攥紧母亲留下的缝纫机与设计底稿，靠着一针一针做布头花、帆布包艰难谋生。面对家庭压榨，她拿起证据求助工会、文教局，守住学籍与尊严，用双手挣属于自己的读书机会与未来。</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>末世来临，我靠囤货种田丰衣足食</x:v>
+        <x:v>反派亲妈：反派漂亮亲妈十斤反骨</x:v>
       </x:c>
       <x:c r="C30" s="11" t="str">
-        <x:v>09-09 15:30</x:v>
+        <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G30" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H30" s="11" t="n">
-        <x:v>344</x:v>
-      </x:c>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H30" s="11" t="str"/>
       <x:c r="I30" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J30" s="11" t="str"/>
       <x:c r="K30" s="11" t="str"/>
-      <x:c r="L30" s="10" t="str">
-        <x:v>渲渲动画</x:v>
-      </x:c>
-      <x:c r="M30" s="10" t="str">
-        <x:v>吴真真带着末世惨死的记忆重生，抢下秘宝空间，囤积海量物资，提前规避天灾人祸。她意外发现家人同样重生，一家人携手为末日做足准备。灾变如期而至，病毒、台风、极寒轮番降临。她机缘结识实力强悍的谢穆辰，二人从互相试探到并肩而立。面对凶悍恶徒与重重危机，吴真真依靠空间与智慧守护至亲，谢穆辰以自身力量与之守望相助，在满目疮痍的末世里，拼尽全力守住生存希望，奔赴属于他们的新生。</x:v>
-      </x:c>
+      <x:c r="L30" s="10" t="str"/>
+      <x:c r="M30" s="10" t="str"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="11" t="n">
-        <x:v>82</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>我的植物人老公不对劲</x:v>
+        <x:v>一纸离书赴南港</x:v>
       </x:c>
       <x:c r="C31" s="11" t="str">
-        <x:v>2026-09-06</x:v>
+        <x:v>09-03 07:00</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
         <x:v>6</x:v>
@@ -4064,15 +4060,23 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G31" s="11" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H31" s="11" t="str"/>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H31" s="11" t="n">
+        <x:v>85</x:v>
+      </x:c>
       <x:c r="I31" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="J31" s="11" t="str"/>
-      <x:c r="K31" s="11" t="str"/>
-      <x:c r="L31" s="10" t="str"/>
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="J31" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K31" s="11" t="str">
+        <x:v>0.00</x:v>
+      </x:c>
+      <x:c r="L31" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
       <x:c r="M31" s="10" t="str"/>
     </x:row>
   </x:sheetData>
@@ -16697,7 +16701,7 @@
         <x:v>洛宇重生回夺命急诊那天，面对谎报马尔堡病毒的学生网红团，他不再心软，果断启动应急预案并封锁区域。尽管遭遇直播施压与校方干预，洛宇坚持专业处置，揭露隐瞒接触史真相。最终他凭借详实数据驳回医院不合理托管方案，坚守医疗底线，守护公共卫生安全。</x:v>
       </x:c>
       <x:c r="K11" s="10" t="str">
-        <x:v>发布账号「星漫动漫剧场」稳定产出（上榜22次/出过3部），账号基础分；题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×1；82集，主力长度；剧名钩子×1</x:v>
+        <x:v>发布账号「星漫动漫剧场」稳定产出（上榜23次/出过4部），账号基础分；题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×1；82集，主力长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="L11" s="11" t="n">
         <x:v>11</x:v>
@@ -16833,7 +16837,7 @@
         <x:v>婚礼接亲当日，新郎方源撞破前任王腾私闯新娘房，新娘白凝冰还挺身维护对方，婚礼当场宣告取消。原本的婚约彻底破裂后，方源着手清算彩礼与婚礼损失，不料王腾身负巨额网贷，企图借婚礼捞钱，还剪辑现场视频在网上颠倒黑白。在证据的博弈与舆论风波中，方源冷静搜集全部线索，面对女方家庭的和稀泥、对方的恶意构陷，他依靠法律维护自身权益，层层拨开资金代持、作伪证等重重阴谋，斩断过往纠葛，走向全新的人生。</x:v>
       </x:c>
       <x:c r="K15" s="10" t="str">
-        <x:v>发布账号「星漫动漫剧场」稳定产出（上榜22次/出过3部），账号基础分；题材契合爆款主线×2（剧名/分类/简介三路识别）；84集，主力长度</x:v>
+        <x:v>发布账号「星漫动漫剧场」稳定产出（上榜23次/出过4部），账号基础分；题材契合爆款主线×2（剧名/分类/简介三路识别）；84集，主力长度</x:v>
       </x:c>
       <x:c r="L15" s="11" t="n">
         <x:v>9</x:v>
@@ -17014,13 +17018,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B21" s="11" t="str">
-        <x:v>09-15 10:00</x:v>
+        <x:v>09-15 07:10</x:v>
       </x:c>
       <x:c r="C21" s="10" t="str">
-        <x:v>高考落榜，从听彩票心声开始逆袭</x:v>
+        <x:v>婴语满级，宫斗逆袭</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E21" s="11" t="str">
         <x:v>其他</x:v>
@@ -17029,18 +17033,18 @@
         <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G21" s="10" t="str">
-        <x:v>糖糖动漫剧场</x:v>
+        <x:v>星漫剧院</x:v>
       </x:c>
       <x:c r="H21" s="11" t="str"/>
       <x:c r="I21" s="10" t="str"/>
       <x:c r="J21" s="10" t="str">
-        <x:v>高考落榜的陈阳意外觉醒聆听万物心声的特殊能力。面对世俗偏见与亲友的冷眼，他没有沉沦，坚守本心脚踏实地，凭借能力识破骗局、守护家人。抓住机遇创业致富，反哺故土，助力乡村建设，伸张社会正义，用实干证明人生不止高考一条出路，诠释新时代青年的责任与担当。</x:v>
+        <x:v>皇后言氏早产，婴儿遭侍女翠鸾调包。女官绿玉意外听见真公主心声，识破阴谋。面对滴血认亲的伪造证据与皇帝猜忌，绿玉在言家支持下揭露水中明矾诡计，证实公主身份。随后皇帝萧衍野心暴露，勾结叛军逼宫。绿玉凭借心声指引，助皇后与言将军里应外合，最终铲除逆贼，助公主登基，开启女子为官新盛世。</x:v>
       </x:c>
       <x:c r="K21" s="10" t="str">
-        <x:v>发布账号「糖糖动漫剧场」稳定产出（上榜4次/出过4部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；70集，主力长度；剧名钩子×1</x:v>
+        <x:v>发布账号「星漫剧院」稳定产出（上榜10次/出过4部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；77集，主力长度；剧名钩子×1；女频受众</x:v>
       </x:c>
       <x:c r="L21" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -17051,30 +17055,30 @@
         <x:v>09-15 10:00</x:v>
       </x:c>
       <x:c r="C22" s="10" t="str">
-        <x:v>另一场奔赴</x:v>
+        <x:v>高考落榜，从听彩票心声开始逆袭</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E22" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F22" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G22" s="10" t="str">
-        <x:v>诗婳-小林看剧</x:v>
+        <x:v>糖糖动漫剧场</x:v>
       </x:c>
       <x:c r="H22" s="11" t="str"/>
       <x:c r="I22" s="10" t="str"/>
       <x:c r="J22" s="10" t="str">
-        <x:v>大婚当日，温氧遭未婚夫秦阮当众轻慢——对方嫌接亲麻烦，竟指派外卖骑手周延代为到场。心冷的温氧顺势让周延顶替新郎完成婚礼，二人更冲动领证闪婚。随后温氧重返家族企业夺权，才发现周延实为隐姓埋名的周家二公子，送外卖是为调查家族旧案。两人从协议夫妻联手对抗幕后鹿家势力，揭开内奸阴谋、寻回至亲，最终假戏真做，收获圆满爱情与事业。</x:v>
+        <x:v>高考落榜的陈阳意外觉醒聆听万物心声的特殊能力。面对世俗偏见与亲友的冷眼，他没有沉沦，坚守本心脚踏实地，凭借能力识破骗局、守护家人。抓住机遇创业致富，反哺故土，助力乡村建设，伸张社会正义，用实干证明人生不止高考一条出路，诠释新时代青年的责任与担当。</x:v>
       </x:c>
       <x:c r="K22" s="10" t="str">
-        <x:v>发布账号「诗婳-小林看剧」稳定产出（上榜5次/出过4部），账号基础分；题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×1；83集，主力长度；通用受众</x:v>
+        <x:v>发布账号「糖糖动漫剧场」稳定产出（上榜4次/出过4部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；70集，主力长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="L22" s="11" t="n">
-        <x:v>10.5</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -17085,30 +17089,30 @@
         <x:v>09-15 10:00</x:v>
       </x:c>
       <x:c r="C23" s="10" t="str">
-        <x:v>八年错爱终梦醒</x:v>
+        <x:v>另一场奔赴</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E23" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F23" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G23" s="10" t="str">
-        <x:v>心动短剧场</x:v>
+        <x:v>诗婳-小林看剧</x:v>
       </x:c>
       <x:c r="H23" s="11" t="str"/>
       <x:c r="I23" s="10" t="str"/>
       <x:c r="J23" s="10" t="str">
-        <x:v>曾是个将八年青春错付的重度恋爱脑，为了攒钱结婚甚至舍不得吃超过15元的盒饭。在看清未婚夫与亲生父母的背叛后，展现出极强的决断力。她不内耗不纠缠，果断抽身，将全部精力投入事业，最终凭借极强的专业能力登顶北城科技集团副总裁，完成了从泥沼仰望者到云端掌局者的华丽蜕变。</x:v>
+        <x:v>大婚当日，温氧遭未婚夫秦阮当众轻慢——对方嫌接亲麻烦，竟指派外卖骑手周延代为到场。心冷的温氧顺势让周延顶替新郎完成婚礼，二人更冲动领证闪婚。随后温氧重返家族企业夺权，才发现周延实为隐姓埋名的周家二公子，送外卖是为调查家族旧案。两人从协议夫妻联手对抗幕后鹿家势力，揭开内奸阴谋、寻回至亲，最终假戏真做，收获圆满爱情与事业。</x:v>
       </x:c>
       <x:c r="K23" s="10" t="str">
-        <x:v>发布账号「心动短剧场」稳定产出（上榜17次/出过3部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；50集，次优长度；女频受众</x:v>
+        <x:v>发布账号「诗婳-小林看剧」稳定产出（上榜5次/出过4部），账号基础分；题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×1；83集，主力长度；通用受众</x:v>
       </x:c>
       <x:c r="L23" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>10.5</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -17116,30 +17120,30 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B24" s="11" t="str">
-        <x:v>09-15 07:00</x:v>
+        <x:v>09-15 10:00</x:v>
       </x:c>
       <x:c r="C24" s="10" t="str">
-        <x:v>刚重生就被退婚乌鸦带我赶海逆袭</x:v>
+        <x:v>八年错爱终梦醒</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E24" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F24" s="10" t="str">
-        <x:v>种田囤货 / 婚姻情感 / 逆袭打脸</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G24" s="10" t="str">
-        <x:v>章鱼漫剧</x:v>
+        <x:v>心动短剧场</x:v>
       </x:c>
       <x:c r="H24" s="11" t="str"/>
       <x:c r="I24" s="10" t="str"/>
       <x:c r="J24" s="10" t="str">
-        <x:v>一个穷渔夫重生回到二十年前，退婚现场被未来岳母当面羞辱，一只乌鸦突然开口说话“你家灶台的红糖被她顺走了。”——就这一句话，命运的齿轮开始逆转。他赌命闯进荒废礁石区，挖出整枝红珊瑚，乌鸦却撂下一句“值不少，先别急着卖。三天后，你会用得上。”穷得叮当响的退婚废物，兜里揣着全村人眼红的宝贝，却不知道这支珊瑚会在三天后的饭桌上掀起什么风波。三十年河东，三十年河西——这一世，且看他如何走到人生巅峰！</x:v>
+        <x:v>曾是个将八年青春错付的重度恋爱脑，为了攒钱结婚甚至舍不得吃超过15元的盒饭。在看清未婚夫与亲生父母的背叛后，展现出极强的决断力。她不内耗不纠缠，果断抽身，将全部精力投入事业，最终凭借极强的专业能力登顶北城科技集团副总裁，完成了从泥沼仰望者到云端掌局者的华丽蜕变。</x:v>
       </x:c>
       <x:c r="K24" s="10" t="str">
-        <x:v>发布账号「章鱼漫剧」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；70集，主力长度；剧名钩子×2</x:v>
+        <x:v>发布账号「心动短剧场」稳定产出（上榜17次/出过3部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；50集，次优长度；女频受众</x:v>
       </x:c>
       <x:c r="L24" s="11" t="n">
         <x:v>10</x:v>
@@ -17150,30 +17154,30 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B25" s="11" t="str">
-        <x:v>09-15 10:00</x:v>
+        <x:v>09-15 07:00</x:v>
       </x:c>
       <x:c r="C25" s="10" t="str">
-        <x:v>坐地起价，旺铺成空铺</x:v>
+        <x:v>刚重生就被退婚乌鸦带我赶海逆袭</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E25" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F25" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>种田囤货 / 婚姻情感 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="G25" s="10" t="str">
-        <x:v>屿风漫剧</x:v>
+        <x:v>章鱼漫剧</x:v>
       </x:c>
       <x:c r="H25" s="11" t="str"/>
       <x:c r="I25" s="10" t="str"/>
       <x:c r="J25" s="10" t="str">
-        <x:v>陈峰与妻子林念慈在老城区正街经营陈记卤味，凭借好手艺和用料攒下大批老顾客。房东周德发眼红生意，撕毁合同，将房租从八万暴涨至十八万，还找假租客施压。陈峰不愿被拿捏，在城北老街租下六万一年的铺子重新开始。周德发索性自己开起卤味店，用低价和半成品吸引客流，却因品质差、缺斤短两迅速流失客人，最终关门欠债。陈峰坚守当天卤当天卖，靠品质和口碑让新店越来越红火。</x:v>
+        <x:v>一个穷渔夫重生回到二十年前，退婚现场被未来岳母当面羞辱，一只乌鸦突然开口说话“你家灶台的红糖被她顺走了。”——就这一句话，命运的齿轮开始逆转。他赌命闯进荒废礁石区，挖出整枝红珊瑚，乌鸦却撂下一句“值不少，先别急着卖。三天后，你会用得上。”穷得叮当响的退婚废物，兜里揣着全村人眼红的宝贝，却不知道这支珊瑚会在三天后的饭桌上掀起什么风波。三十年河东，三十年河西——这一世，且看他如何走到人生巅峰！</x:v>
       </x:c>
       <x:c r="K25" s="10" t="str">
-        <x:v>发布账号「屿风漫剧」稳定产出（上榜13次/出过4部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；60集，主力长度</x:v>
+        <x:v>发布账号「章鱼漫剧」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；70集，主力长度；剧名钩子×2</x:v>
       </x:c>
       <x:c r="L25" s="11" t="n">
         <x:v>10</x:v>
@@ -17184,13 +17188,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B26" s="11" t="str">
-        <x:v>09-15 00:06</x:v>
+        <x:v>09-15 10:00</x:v>
       </x:c>
       <x:c r="C26" s="10" t="str">
-        <x:v>火车上捡来的小土豆成了咱家宝</x:v>
+        <x:v>坐地起价，旺铺成空铺</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>122</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E26" s="11" t="str">
         <x:v>其他</x:v>
@@ -17199,18 +17203,18 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G26" s="10" t="str">
-        <x:v>潮汐心动放映厅</x:v>
+        <x:v>屿风漫剧</x:v>
       </x:c>
       <x:c r="H26" s="11" t="str"/>
       <x:c r="I26" s="10" t="str"/>
       <x:c r="J26" s="10" t="str">
-        <x:v>南方女孩庄棉棉家里奶奶离世后她万念俱灰，坐绿皮火车去往哈尔滨想了结自己。火车上被热心东北阿姨高雪华救下，带回东北家中。她遇见高雪华当兵回家的儿子姜瑜，在姜家滚烫的烟火与家人的善待中，庄棉棉慢慢走出过往伤痛。二人互生情愫，顺利订婚领证。姜瑜因任务短暂离家，庄棉棉在公婆陪伴下怀孕生女安安。姜瑜平安归来，转岗留在家乡，一家人补办婚礼，岁岁平安相守。</x:v>
+        <x:v>陈峰与妻子林念慈在老城区正街经营陈记卤味，凭借好手艺和用料攒下大批老顾客。房东周德发眼红生意，撕毁合同，将房租从八万暴涨至十八万，还找假租客施压。陈峰不愿被拿捏，在城北老街租下六万一年的铺子重新开始。周德发索性自己开起卤味店，用低价和半成品吸引客流，却因品质差、缺斤短两迅速流失客人，最终关门欠债。陈峰坚守当天卤当天卖，靠品质和口碑让新店越来越红火。</x:v>
       </x:c>
       <x:c r="K26" s="10" t="str">
-        <x:v>发布账号「潮汐心动放映厅」稳定产出（上榜12次/出过2部），账号基础分；题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×1；122集，次优长度；通用受众</x:v>
+        <x:v>发布账号「屿风漫剧」稳定产出（上榜13次/出过4部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；60集，主力长度</x:v>
       </x:c>
       <x:c r="L26" s="11" t="n">
-        <x:v>9.5</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -17218,33 +17222,33 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B27" s="11" t="str">
-        <x:v>09-15 10:20</x:v>
+        <x:v>09-15 00:06</x:v>
       </x:c>
       <x:c r="C27" s="10" t="str">
-        <x:v>同事送我梳妆镜，我反手给花甲老奶奶</x:v>
+        <x:v>火车上捡来的小土豆成了咱家宝</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E27" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F27" s="10" t="str">
-        <x:v>家庭伦理 / 都市职场 / 逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G27" s="10" t="str">
-        <x:v>旺旺动画</x:v>
+        <x:v>潮汐心动放映厅</x:v>
       </x:c>
       <x:c r="H27" s="11" t="str"/>
       <x:c r="I27" s="10" t="str"/>
       <x:c r="J27" s="10" t="str">
-        <x:v>主播苏晚重生归来，躲开了林薇薇送来的诡异古镜圈套。林薇薇依靠神秘道具屡次陷害苏晚，用尽手段想要毁掉苏晚的事业与名声。苏晚联合阿宁、陈婆婆收集线索，一步步查清对方的秘密据点。众人闯入废弃工厂，却落入对方布下的圈套，苏晚被困镜阵之内。阿宁逃出险境，拆开师父留下的锦囊拨通神秘号码，可电话接通之后，等待众人的又会是什么未知危机。</x:v>
+        <x:v>南方女孩庄棉棉家里奶奶离世后她万念俱灰，坐绿皮火车去往哈尔滨想了结自己。火车上被热心东北阿姨高雪华救下，带回东北家中。她遇见高雪华当兵回家的儿子姜瑜，在姜家滚烫的烟火与家人的善待中，庄棉棉慢慢走出过往伤痛。二人互生情愫，顺利订婚领证。姜瑜因任务短暂离家，庄棉棉在公婆陪伴下怀孕生女安安。姜瑜平安归来，转岗留在家乡，一家人补办婚礼，岁岁平安相守。</x:v>
       </x:c>
       <x:c r="K27" s="10" t="str">
-        <x:v>发布账号「旺旺动画」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；66集，主力长度；剧名钩子×1</x:v>
+        <x:v>发布账号「潮汐心动放映厅」稳定产出（上榜12次/出过2部），账号基础分；题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×1；122集，次优长度；通用受众</x:v>
       </x:c>
       <x:c r="L27" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>9.5</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -17252,30 +17256,30 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B28" s="11" t="str">
-        <x:v>09-15 11:00</x:v>
+        <x:v>09-15 10:20</x:v>
       </x:c>
       <x:c r="C28" s="10" t="str">
-        <x:v>后视镜那枚拼豆，惊醒了我</x:v>
+        <x:v>同事送我梳妆镜，我反手给花甲老奶奶</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E28" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F28" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理 / 都市职场 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="G28" s="10" t="str">
-        <x:v>盐系少女社</x:v>
+        <x:v>旺旺动画</x:v>
       </x:c>
       <x:c r="H28" s="11" t="str"/>
       <x:c r="I28" s="10" t="str"/>
       <x:c r="J28" s="10" t="str">
-        <x:v>相恋七年的姜栀子，凌晨去机场接出差归来的男友沈闻舟，却发现车内自己送的平安符，被换成实习生林暖手工做的拼豆挂件。面对男友的谎言与恼羞成怒的指责，姜栀子清醒识破背叛，抢先将试图把自己丢在郊外的沈闻舟赶下车。回到家中，林暖找上门，姜栀子直接将二人赶出属于自己的房子。经过一系列的矛盾之后，姜栀子彻底斩断过往，专注事业奔赴属于自己的人生。</x:v>
+        <x:v>主播苏晚重生归来，躲开了林薇薇送来的诡异古镜圈套。林薇薇依靠神秘道具屡次陷害苏晚，用尽手段想要毁掉苏晚的事业与名声。苏晚联合阿宁、陈婆婆收集线索，一步步查清对方的秘密据点。众人闯入废弃工厂，却落入对方布下的圈套，苏晚被困镜阵之内。阿宁逃出险境，拆开师父留下的锦囊拨通神秘号码，可电话接通之后，等待众人的又会是什么未知危机。</x:v>
       </x:c>
       <x:c r="K28" s="10" t="str">
-        <x:v>发布账号「盐系少女社」稳定产出（上榜12次/出过3部），账号基础分；题材契合爆款主线×1（剧名/分类/简介三路识别）；简介爽点词×1；52集，次优长度；女频受众</x:v>
+        <x:v>发布账号「旺旺动画」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；66集，主力长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="L28" s="11" t="n">
         <x:v>9</x:v>
@@ -17286,13 +17290,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B29" s="11" t="str">
-        <x:v>09-15 10:00</x:v>
+        <x:v>09-15 11:00</x:v>
       </x:c>
       <x:c r="C29" s="10" t="str">
-        <x:v>我用烂泥换成金</x:v>
+        <x:v>后视镜那枚拼豆，惊醒了我</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E29" s="11" t="str">
         <x:v>其他</x:v>
@@ -17301,15 +17305,15 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G29" s="10" t="str">
-        <x:v>秋浔动漫</x:v>
+        <x:v>盐系少女社</x:v>
       </x:c>
       <x:c r="H29" s="11" t="str"/>
       <x:c r="I29" s="10" t="str"/>
       <x:c r="J29" s="10" t="str">
-        <x:v>现代风控操盘手沈南星穿越到大楚，沦为人人嘲讽的沈家假千金，遭未婚夫顾长渊退婚夺田。她不悲反怒，以百亩良田置换三百亩废弃烂泥塘，挖出泥炭垄断燃料市场，打造桑基鱼塘生态闭环。她凭超前认知步步为营，智斗乡绅权贵，借天灾逆袭破局，从人人鄙夷的烂泥滩起家，终建起横跨江南的商业帝国，受封镇国商王。</x:v>
+        <x:v>相恋七年的姜栀子，凌晨去机场接出差归来的男友沈闻舟，却发现车内自己送的平安符，被换成实习生林暖手工做的拼豆挂件。面对男友的谎言与恼羞成怒的指责，姜栀子清醒识破背叛，抢先将试图把自己丢在郊外的沈闻舟赶下车。回到家中，林暖找上门，姜栀子直接将二人赶出属于自己的房子。经过一系列的矛盾之后，姜栀子彻底斩断过往，专注事业奔赴属于自己的人生。</x:v>
       </x:c>
       <x:c r="K29" s="10" t="str">
-        <x:v>发布账号「秋浔动漫」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；78集，主力长度；女频受众</x:v>
+        <x:v>发布账号「盐系少女社」稳定产出（上榜12次/出过3部），账号基础分；题材契合爆款主线×1（剧名/分类/简介三路识别）；简介爽点词×1；52集，次优长度；女频受众</x:v>
       </x:c>
       <x:c r="L29" s="11" t="n">
         <x:v>9</x:v>
@@ -17320,13 +17324,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B30" s="11" t="str">
-        <x:v>09-15 12:01</x:v>
+        <x:v>09-15 10:00</x:v>
       </x:c>
       <x:c r="C30" s="10" t="str">
-        <x:v>贪财道长俏千金</x:v>
+        <x:v>我用烂泥换成金</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E30" s="11" t="str">
         <x:v>其他</x:v>
@@ -17335,18 +17339,18 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G30" s="10" t="str">
-        <x:v>二里清风</x:v>
+        <x:v>秋浔动漫</x:v>
       </x:c>
       <x:c r="H30" s="11" t="str"/>
       <x:c r="I30" s="10" t="str"/>
       <x:c r="J30" s="10" t="str">
-        <x:v>林夏误吞灵山道观的灵萝卜，与外冷内热的守观道士顾青锋结缘。顾青锋持早年定下的婚书下山，意外救下林夏的奶奶，就此住进林家。相处中，二人携手化解林家药园危机，林夏也从娇俏千金逐渐成长。顾青锋体内寒煞发作，林夏催动自身药气催生灵萝相救，揭开二人童年渊源。最终两人心意相通，婚约成真，一同守护药园与彼此。</x:v>
+        <x:v>现代风控操盘手沈南星穿越到大楚，沦为人人嘲讽的沈家假千金，遭未婚夫顾长渊退婚夺田。她不悲反怒，以百亩良田置换三百亩废弃烂泥塘，挖出泥炭垄断燃料市场，打造桑基鱼塘生态闭环。她凭超前认知步步为营，智斗乡绅权贵，借天灾逆袭破局，从人人鄙夷的烂泥滩起家，终建起横跨江南的商业帝国，受封镇国商王。</x:v>
       </x:c>
       <x:c r="K30" s="10" t="str">
-        <x:v>发布账号「二里清风」稳定产出（上榜10次/出过4部），账号基础分；题材契合爆款主线×1（剧名/分类/简介三路识别）；77集，主力长度；通用受众</x:v>
+        <x:v>发布账号「秋浔动漫」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；78集，主力长度；女频受众</x:v>
       </x:c>
       <x:c r="L30" s="11" t="n">
-        <x:v>8.5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -17354,13 +17358,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B31" s="11" t="str">
-        <x:v>09-15 09:00</x:v>
+        <x:v>09-15 12:01</x:v>
       </x:c>
       <x:c r="C31" s="10" t="str">
-        <x:v>寸草还报三春晖</x:v>
+        <x:v>贪财道长俏千金</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E31" s="11" t="str">
         <x:v>其他</x:v>
@@ -17369,18 +17373,18 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G31" s="10" t="str">
-        <x:v>泰北剧场</x:v>
+        <x:v>二里清风</x:v>
       </x:c>
       <x:c r="H31" s="11" t="str"/>
       <x:c r="I31" s="10" t="str"/>
       <x:c r="J31" s="10" t="str">
-        <x:v>十二岁风雪夜，李雪花被重男轻女的生父母以一百元送人，大伯拼命救回并悉心收养。她勤学考入名校，成为风投大佬，让养父母过上优渥生活。而溺爱儿子败尽家财的生父母眼红至极，屡次用血缘勒索。李雪花以法律和资本强势反击，绝不退让。最终她为养父母养老，创立女子教育基金，逆袭传奇印证养育之恩大过天。</x:v>
+        <x:v>林夏误吞灵山道观的灵萝卜，与外冷内热的守观道士顾青锋结缘。顾青锋持早年定下的婚书下山，意外救下林夏的奶奶，就此住进林家。相处中，二人携手化解林家药园危机，林夏也从娇俏千金逐渐成长。顾青锋体内寒煞发作，林夏催动自身药气催生灵萝相救，揭开二人童年渊源。最终两人心意相通，婚约成真，一同守护药园与彼此。</x:v>
       </x:c>
       <x:c r="K31" s="10" t="str">
-        <x:v>发布账号「泰北剧场」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；65集，主力长度；女频受众</x:v>
+        <x:v>发布账号「二里清风」稳定产出（上榜10次/出过4部），账号基础分；题材契合爆款主线×1（剧名/分类/简介三路识别）；77集，主力长度；通用受众</x:v>
       </x:c>
       <x:c r="L31" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>8.5</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -18223,8 +18227,12 @@
       <x:c r="G56" s="10" t="str">
         <x:v>星漫动漫剧场</x:v>
       </x:c>
-      <x:c r="H56" s="11" t="str"/>
-      <x:c r="I56" s="10" t="str"/>
+      <x:c r="H56" s="11" t="str">
+        <x:v>已上榜</x:v>
+      </x:c>
+      <x:c r="I56" s="10" t="str">
+        <x:v>2026-09-13</x:v>
+      </x:c>
       <x:c r="J56" s="10" t="str">
         <x:v>林北经营祖传冰粉店，因网络用语误会引来黑道人物何彪。双方消除隔阂后，林北又被迫为逃犯岑德海制作冰粉以拖延时间。最终警方赶到抓获罪犯，林北凭借机智与手艺协助破案，洗清嫌疑并获颁警民联络点荣誉，守护了家族手艺与社区安宁。</x:v>
       </x:c>
@@ -19117,8 +19125,12 @@
       <x:c r="G82" s="10" t="str">
         <x:v>星空漫漫</x:v>
       </x:c>
-      <x:c r="H82" s="11" t="str"/>
-      <x:c r="I82" s="10" t="str"/>
+      <x:c r="H82" s="11" t="str">
+        <x:v>已上榜</x:v>
+      </x:c>
+      <x:c r="I82" s="10" t="str">
+        <x:v>2026-09-13</x:v>
+      </x:c>
       <x:c r="J82" s="10" t="str">
         <x:v>秋庙会前夜，禾糖铺的老糖师突然撂挑子，年轻掌柜清禾被迫独自接下五十多家订单和一整夜的大锅。一次废糖、一场庙会，也让她真正站到了灶台前。面对同行压价、恶意挑刺、大单失误与人情旧账，她没有靠争吵赢生意，而是把分量写清、把账目记明、把规矩立稳。守住的不只是祖传糖艺，更是一家老铺重新长出来的信誉与传承。</x:v>
       </x:c>
@@ -27142,10 +27154,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>809</x:v>
+        <x:v>819</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>50.2%</x:v>
+        <x:v>50.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -27156,7 +27168,7 @@
         <x:v>465</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>28.8%</x:v>
+        <x:v>28.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -27167,7 +27179,7 @@
         <x:v>338</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>21.0%</x:v>
+        <x:v>20.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
@@ -27191,7 +27203,7 @@
         <x:v>30-49集</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
         <x:v>11%</x:v>
@@ -27202,10 +27214,10 @@
         <x:v>50-79集</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>629</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>42.2%</x:v>
+        <x:v>42.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -27216,7 +27228,7 @@
         <x:v>189</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>12.7%</x:v>
+        <x:v>12.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -27224,10 +27236,10 @@
         <x:v>100集以上</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>508</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>34.1%</x:v>
+        <x:v>34%</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
@@ -27251,10 +27263,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>706</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>43.8%</x:v>
+        <x:v>44.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -27265,7 +27277,7 @@
         <x:v>287</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>17.8%</x:v>
+        <x:v>17.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -27276,7 +27288,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>9.4%</x:v>
+        <x:v>9.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -27295,7 +27307,7 @@
         <x:v>家庭伦理/萌宝</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
         <x:v>8.6%</x:v>
@@ -27306,7 +27318,7 @@
         <x:v>战神/异能/爽文</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
         <x:v>8.6%</x:v>
@@ -27317,7 +27329,7 @@
         <x:v>现实反转/人性</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
         <x:v>6.4%</x:v>
@@ -27328,7 +27340,7 @@
         <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
         <x:v>5.7%</x:v>
@@ -27473,21 +27485,21 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="10" t="str">
-        <x:v>上榜18次</x:v>
+        <x:v>上榜19次</x:v>
       </x:c>
       <x:c r="B38" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C38" s="11" t="str">
-        <x:v>0.2%</x:v>
+        <x:v>0.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="10" t="str">
-        <x:v>上榜17次</x:v>
+        <x:v>上榜18次</x:v>
       </x:c>
       <x:c r="B39" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C39" s="11" t="str">
         <x:v>0.1%</x:v>
@@ -27495,32 +27507,32 @@
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="10" t="str">
-        <x:v>上榜16次</x:v>
+        <x:v>上榜17次</x:v>
       </x:c>
       <x:c r="B40" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C40" s="11" t="str">
-        <x:v>0.3%</x:v>
+        <x:v>0.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="10" t="str">
-        <x:v>上榜15次</x:v>
+        <x:v>上榜16次</x:v>
       </x:c>
       <x:c r="B41" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C41" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="10" t="str">
-        <x:v>上榜14次</x:v>
+        <x:v>上榜15次</x:v>
       </x:c>
       <x:c r="B42" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C42" s="11" t="str">
         <x:v>0.4%</x:v>
@@ -27528,240 +27540,240 @@
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="10" t="str">
-        <x:v>上榜13次</x:v>
+        <x:v>上榜14次</x:v>
       </x:c>
       <x:c r="B43" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C43" s="11" t="str">
-        <x:v>0.8%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="10" t="str">
-        <x:v>上榜12次</x:v>
+        <x:v>上榜13次</x:v>
       </x:c>
       <x:c r="B44" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C44" s="11" t="str">
-        <x:v>0.9%</x:v>
+        <x:v>0.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="10" t="str">
-        <x:v>上榜11次</x:v>
+        <x:v>上榜12次</x:v>
       </x:c>
       <x:c r="B45" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C45" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="10" t="str">
-        <x:v>上榜10次</x:v>
+        <x:v>上榜11次</x:v>
       </x:c>
       <x:c r="B46" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C46" s="11" t="str">
-        <x:v>1.1%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="10" t="str">
-        <x:v>上榜9次</x:v>
+        <x:v>上榜10次</x:v>
       </x:c>
       <x:c r="B47" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C47" s="11" t="str">
-        <x:v>1.9%</x:v>
+        <x:v>1.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="10" t="str">
-        <x:v>上榜8次</x:v>
+        <x:v>上榜9次</x:v>
       </x:c>
       <x:c r="B48" s="11" t="n">
-        <x:v>46</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C48" s="11" t="str">
-        <x:v>2.9%</x:v>
+        <x:v>1.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="10" t="str">
-        <x:v>上榜7次</x:v>
+        <x:v>上榜8次</x:v>
       </x:c>
       <x:c r="B49" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C49" s="11" t="str">
-        <x:v>2.2%</x:v>
+        <x:v>2.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="10" t="str">
-        <x:v>上榜6次</x:v>
+        <x:v>上榜7次</x:v>
       </x:c>
       <x:c r="B50" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C50" s="11" t="str">
-        <x:v>3.3%</x:v>
+        <x:v>2.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="10" t="str">
-        <x:v>上榜5次</x:v>
+        <x:v>上榜6次</x:v>
       </x:c>
       <x:c r="B51" s="11" t="n">
-        <x:v>77</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C51" s="11" t="str">
-        <x:v>4.8%</x:v>
+        <x:v>3.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="10" t="str">
-        <x:v>上榜4次</x:v>
+        <x:v>上榜5次</x:v>
       </x:c>
       <x:c r="B52" s="11" t="n">
-        <x:v>87</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C52" s="11" t="str">
-        <x:v>5.4%</x:v>
+        <x:v>4.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="10" t="str">
-        <x:v>上榜3次</x:v>
+        <x:v>上榜4次</x:v>
       </x:c>
       <x:c r="B53" s="11" t="n">
-        <x:v>166</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C53" s="11" t="str">
-        <x:v>10.3%</x:v>
+        <x:v>5.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="10" t="str">
-        <x:v>上榜2次</x:v>
+        <x:v>上榜3次</x:v>
       </x:c>
       <x:c r="B54" s="11" t="n">
-        <x:v>318</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C54" s="11" t="str">
-        <x:v>19.7%</x:v>
+        <x:v>10.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="10" t="str">
+        <x:v>上榜2次</x:v>
+      </x:c>
+      <x:c r="B55" s="11" t="n">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="C55" s="11" t="str">
+        <x:v>19.6%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="10" t="str">
         <x:v>上榜1次</x:v>
       </x:c>
-      <x:c r="B55" s="11" t="n">
-        <x:v>708</x:v>
-      </x:c>
-      <x:c r="C55" s="11" t="str">
-        <x:v>43.9%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" ht="22" customHeight="1">
-      <x:c r="A57" s="14" t="str">
+      <x:c r="B56" s="11" t="n">
+        <x:v>716</x:v>
+      </x:c>
+      <x:c r="C56" s="11" t="str">
+        <x:v>44.1%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="22" customHeight="1">
+      <x:c r="A58" s="14" t="str">
         <x:v>版权类型分布</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="24" customHeight="1">
-      <x:c r="A58" s="5" t="str">
+    <x:row r="59" ht="24" customHeight="1">
+      <x:c r="A59" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B58" t="str">
+      <x:c r="B59" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C58" t="str">
+      <x:c r="C59" t="str">
         <x:v>占比</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59">
-      <x:c r="A59" s="10" t="str">
-        <x:v>CP自营</x:v>
-      </x:c>
-      <x:c r="B59" s="11" t="n">
-        <x:v>1121</x:v>
-      </x:c>
-      <x:c r="C59" s="11" t="str">
-        <x:v>69.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>CP自营</x:v>
       </x:c>
       <x:c r="B60" s="11" t="n">
-        <x:v>480</x:v>
+        <x:v>1121</x:v>
       </x:c>
       <x:c r="C60" s="11" t="str">
-        <x:v>29.8%</x:v>
+        <x:v>69.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="10" t="str">
-        <x:v>CP托管</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="B61" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="C61" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>30.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="10" t="str">
+        <x:v>CP托管</x:v>
+      </x:c>
+      <x:c r="B62" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C62" s="11" t="str">
+        <x:v>0.6%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="10" t="str">
         <x:v>番茄原创</x:v>
       </x:c>
-      <x:c r="B62" s="11" t="n">
+      <x:c r="B63" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C62" s="11" t="str">
+      <x:c r="C63" s="11" t="str">
         <x:v>0.1%</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" ht="22" customHeight="1">
-      <x:c r="A64" s="14" t="str">
+    <x:row r="65" ht="22" customHeight="1">
+      <x:c r="A65" s="14" t="str">
         <x:v>发布抖音号TOP15·上榜次数</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" ht="24" customHeight="1">
-      <x:c r="A65" s="5" t="str">
+    <x:row r="66" ht="24" customHeight="1">
+      <x:c r="A66" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B65" t="str">
+      <x:c r="B66" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C65" t="str">
+      <x:c r="C66" t="str">
         <x:v>占比</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66">
-      <x:c r="A66" s="10" t="str">
-        <x:v>番荔枝剧场</x:v>
-      </x:c>
-      <x:c r="B66" s="11" t="n">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C66" s="11" t="str">
-        <x:v>1.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
+        <x:v>番荔枝剧场</x:v>
       </x:c>
       <x:c r="B67" s="11" t="n">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C67" s="11" t="str">
         <x:v>1.1%</x:v>
@@ -27769,43 +27781,43 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="B68" s="11" t="n">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C68" s="11" t="str">
-        <x:v>1%</x:v>
+        <x:v>1.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="10" t="str">
-        <x:v>渲渲动画</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="B69" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C69" s="11" t="str">
-        <x:v>0.8%</x:v>
+        <x:v>1%</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="10" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>渲渲动画</x:v>
       </x:c>
       <x:c r="B70" s="11" t="n">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C70" s="11" t="str">
-        <x:v>0.7%</x:v>
+        <x:v>0.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="B71" s="11" t="n">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C71" s="11" t="str">
         <x:v>0.7%</x:v>
@@ -27813,21 +27825,21 @@
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="10" t="str">
-        <x:v>东山啊</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="B72" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C72" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>0.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="10" t="str">
-        <x:v>左手良画</x:v>
+        <x:v>东山啊</x:v>
       </x:c>
       <x:c r="B73" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C73" s="11" t="str">
         <x:v>0.6%</x:v>
@@ -27835,7 +27847,7 @@
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="10" t="str">
-        <x:v>阅友动漫</x:v>
+        <x:v>左手良画</x:v>
       </x:c>
       <x:c r="B74" s="11" t="n">
         <x:v>30</x:v>
@@ -27846,21 +27858,21 @@
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>阅友动漫</x:v>
       </x:c>
       <x:c r="B75" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C75" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="10" t="str">
-        <x:v>茉冉漫影</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="B76" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C76" s="11" t="str">
         <x:v>0.5%</x:v>
@@ -27868,7 +27880,7 @@
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="10" t="str">
-        <x:v>在下轻北</x:v>
+        <x:v>茉冉漫影</x:v>
       </x:c>
       <x:c r="B77" s="11" t="n">
         <x:v>26</x:v>
@@ -27879,7 +27891,7 @@
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="10" t="str">
-        <x:v>每日沙雕速递</x:v>
+        <x:v>在下轻北</x:v>
       </x:c>
       <x:c r="B78" s="11" t="n">
         <x:v>26</x:v>
@@ -27890,7 +27902,7 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>每日沙雕速递</x:v>
       </x:c>
       <x:c r="B79" s="11" t="n">
         <x:v>26</x:v>
@@ -27901,78 +27913,78 @@
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="10" t="str">
-        <x:v>壹琚-娜娜看剧</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="B80" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C80" s="11" t="str">
         <x:v>0.5%</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" ht="22" customHeight="1">
-      <x:c r="A82" s="14" t="str">
+    <x:row r="81">
+      <x:c r="A81" s="10" t="str">
+        <x:v>壹琚-娜娜看剧</x:v>
+      </x:c>
+      <x:c r="B81" s="11" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C81" s="11" t="str">
+        <x:v>0.5%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="22" customHeight="1">
+      <x:c r="A83" s="14" t="str">
         <x:v>发布抖音号TOP15·上榜剧数</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" ht="24" customHeight="1">
-      <x:c r="A83" s="5" t="str">
+    <x:row r="84" ht="24" customHeight="1">
+      <x:c r="A84" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B83" t="str">
+      <x:c r="B84" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C83" t="str">
+      <x:c r="C84" t="str">
         <x:v>占比</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84">
-      <x:c r="A84" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
-      </x:c>
-      <x:c r="B84" s="11" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C84" s="11" t="str">
-        <x:v>1.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="B85" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C85" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>1%</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="10" t="str">
-        <x:v>星漫世界</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="B86" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C86" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="10" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>星漫世界</x:v>
       </x:c>
       <x:c r="B87" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C87" s="11" t="str">
-        <x:v>0.4%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="B88" s="11" t="n">
         <x:v>7</x:v>
@@ -27983,10 +27995,10 @@
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="10" t="str">
-        <x:v>渲渲动画</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="B89" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C89" s="11" t="str">
         <x:v>0.4%</x:v>
@@ -27994,7 +28006,7 @@
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>渲渲动画</x:v>
       </x:c>
       <x:c r="B90" s="11" t="n">
         <x:v>6</x:v>
@@ -28005,7 +28017,7 @@
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="10" t="str">
-        <x:v>番荔枝剧场</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="B91" s="11" t="n">
         <x:v>6</x:v>
@@ -28016,7 +28028,7 @@
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>番荔枝剧场</x:v>
       </x:c>
       <x:c r="B92" s="11" t="n">
         <x:v>6</x:v>
@@ -28027,18 +28039,18 @@
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="10" t="str">
-        <x:v>阅友动漫</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="B93" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C93" s="11" t="str">
-        <x:v>0.3%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="10" t="str">
-        <x:v>忆梦剧场</x:v>
+        <x:v>阅友动漫</x:v>
       </x:c>
       <x:c r="B94" s="11" t="n">
         <x:v>5</x:v>
@@ -28049,7 +28061,7 @@
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="10" t="str">
-        <x:v>云影漫剧</x:v>
+        <x:v>忆梦剧场</x:v>
       </x:c>
       <x:c r="B95" s="11" t="n">
         <x:v>5</x:v>
@@ -28060,7 +28072,7 @@
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="10" t="str">
-        <x:v>小小动画</x:v>
+        <x:v>云影漫剧</x:v>
       </x:c>
       <x:c r="B96" s="11" t="n">
         <x:v>5</x:v>
@@ -28071,7 +28083,7 @@
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="10" t="str">
-        <x:v>云间漫剧-玉川</x:v>
+        <x:v>小小动画</x:v>
       </x:c>
       <x:c r="B97" s="11" t="n">
         <x:v>5</x:v>
@@ -28082,7 +28094,7 @@
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="10" t="str">
-        <x:v>星屿漫剧场</x:v>
+        <x:v>云间漫剧-玉川</x:v>
       </x:c>
       <x:c r="B98" s="11" t="n">
         <x:v>5</x:v>
@@ -28091,91 +28103,91 @@
         <x:v>0.3%</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" ht="22" customHeight="1">
-      <x:c r="A100" s="14" t="str">
+    <x:row r="99">
+      <x:c r="A99" s="10" t="str">
+        <x:v>星屿漫剧场</x:v>
+      </x:c>
+      <x:c r="B99" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C99" s="11" t="str">
+        <x:v>0.3%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="22" customHeight="1">
+      <x:c r="A101" s="14" t="str">
         <x:v>付费榜主题分布</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" ht="24" customHeight="1">
-      <x:c r="A101" s="5" t="str">
+    <x:row r="102" ht="24" customHeight="1">
+      <x:c r="A102" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B101" t="str">
+      <x:c r="B102" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C101" t="str">
+      <x:c r="C102" t="str">
         <x:v>占比</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102">
-      <x:c r="A102" s="10" t="str">
-        <x:v>婚姻/情感</x:v>
-      </x:c>
-      <x:c r="B102" s="11" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C102" s="11" t="str">
-        <x:v>19.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="10" t="str">
-        <x:v>家庭伦理/萌宝</x:v>
+        <x:v>婚姻/情感</x:v>
       </x:c>
       <x:c r="B103" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C103" s="11" t="str">
-        <x:v>15.0%</x:v>
+        <x:v>19.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>家庭伦理/萌宝</x:v>
       </x:c>
       <x:c r="B104" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C104" s="11" t="str">
-        <x:v>10.0%</x:v>
+        <x:v>15.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="B105" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C105" s="11" t="str">
-        <x:v>9.0%</x:v>
+        <x:v>10.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="10" t="str">
-        <x:v>年代怀旧/种田</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="B106" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C106" s="11" t="str">
-        <x:v>7.0%</x:v>
+        <x:v>9.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="10" t="str">
-        <x:v>现实反转/人性</x:v>
+        <x:v>年代怀旧/种田</x:v>
       </x:c>
       <x:c r="B107" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C107" s="11" t="str">
-        <x:v>6.0%</x:v>
+        <x:v>7.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="10" t="str">
-        <x:v>战神/异能</x:v>
+        <x:v>现实反转/人性</x:v>
       </x:c>
       <x:c r="B108" s="11" t="n">
         <x:v>6</x:v>
@@ -28186,12 +28198,23 @@
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="10" t="str">
+        <x:v>战神/异能</x:v>
+      </x:c>
+      <x:c r="B109" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C109" s="11" t="str">
+        <x:v>6.0%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="10" t="str">
         <x:v>美食治愈</x:v>
       </x:c>
-      <x:c r="B109" s="11" t="n">
+      <x:c r="B110" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C109" s="11" t="str">
+      <x:c r="C110" s="11" t="str">
         <x:v>5.0%</x:v>
       </x:c>
     </x:row>
@@ -28201,10 +28224,10 @@
     <x:mergeCell ref="A7:C7"/>
     <x:mergeCell ref="A14:C14"/>
     <x:mergeCell ref="A27:C27"/>
-    <x:mergeCell ref="A57:C57"/>
-    <x:mergeCell ref="A64:C64"/>
-    <x:mergeCell ref="A82:C82"/>
-    <x:mergeCell ref="A100:C100"/>
+    <x:mergeCell ref="A58:C58"/>
+    <x:mergeCell ref="A65:C65"/>
+    <x:mergeCell ref="A83:C83"/>
+    <x:mergeCell ref="A101:C101"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="Rec68a9f1e91b412c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="R1cb24aafc5624fa1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="Rda6db5a745294111"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="R032d404452054743"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="5" r:id="R98dced4b0e2a4fc9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="6" r:id="R6dc59f61730043f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="7" r:id="R5407742a8ceb4123"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="8" r:id="R08eda3232d384f96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R5e74f8a0ec5545b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="R814c0b5574814569"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="R12a2287e54684969"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="R2a70006ac6804d26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="5" r:id="R84cdb04b1f204d95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="6" r:id="R45b2de8eef734ad7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="7" r:id="R383d6d47951b4cd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="8" r:id="R1bfad869fdfa47f0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -461,7 +461,7 @@
         <x:v>06-29 17:30</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E5" s="10" t="n">
         <x:v>67</x:v>
@@ -479,7 +479,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="J5" s="10" t="str">
-        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -639,31 +639,27 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>收租老汉</x:v>
+        <x:v>我年终奖80w降到1w9，领导却慌了</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>08-10 06:00</x:v>
+        <x:v>08-24 08:00</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E11" s="10" t="n">
-        <x:v>121</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F11" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G11" s="10" t="str">
-        <x:v>种田囤货</x:v>
-      </x:c>
-      <x:c r="H11" s="11" t="n">
-        <x:v>1045</x:v>
-      </x:c>
-      <x:c r="I11" s="11" t="str">
-        <x:v>1.04</x:v>
-      </x:c>
+        <x:v>都市职场</x:v>
+      </x:c>
+      <x:c r="H11" s="11" t="str"/>
+      <x:c r="I11" s="11" t="str"/>
       <x:c r="J11" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
+        <x:v>2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -671,27 +667,31 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>婆婆要我上交工资卡，我反手只留两千</x:v>
+        <x:v>收租老汉</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>08-09 11:00</x:v>
+        <x:v>08-10 06:00</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E12" s="10" t="n">
-        <x:v>66</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F12" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G12" s="10" t="str">
-        <x:v>家庭伦理 / 逆袭打脸</x:v>
-      </x:c>
-      <x:c r="H12" s="11" t="str"/>
-      <x:c r="I12" s="11" t="str"/>
+        <x:v>种田囤货</x:v>
+      </x:c>
+      <x:c r="H12" s="11" t="n">
+        <x:v>1045</x:v>
+      </x:c>
+      <x:c r="I12" s="11" t="str">
+        <x:v>1.04</x:v>
+      </x:c>
       <x:c r="J12" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-29、2026-08-30、2026-08-31、2026-09-03、2026-09-06</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -699,27 +699,27 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>我年终奖80w降到1w9，领导却慌了</x:v>
+        <x:v>婆婆要我上交工资卡，我反手只留两千</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>08-24 08:00</x:v>
+        <x:v>08-09 11:00</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="E13" s="10" t="n">
-        <x:v>77</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F13" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G13" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>家庭伦理 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="H13" s="11" t="str"/>
       <x:c r="I13" s="11" t="str"/>
       <x:c r="J13" s="10" t="str">
-        <x:v>2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-29、2026-08-30、2026-08-31、2026-09-03、2026-09-06</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1204,10 +1204,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
-        <x:v>装傻下山</x:v>
+        <x:v>七套房产，换来一纸调令</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>2026-09-12</x:v>
+        <x:v>09-12 08:18</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str"/>
       <x:c r="F3" s="11" t="str"/>
@@ -1217,15 +1217,21 @@
       <x:c r="H3" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I3" s="11" t="str"/>
+      <x:c r="I3" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
       <x:c r="J3" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K3" s="10" t="str">
-        <x:v>现实反转</x:v>
-      </x:c>
-      <x:c r="L3" s="11" t="str"/>
-      <x:c r="M3" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L3" s="11" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="M3" s="10" t="str">
+        <x:v>公婆将七套房产全数赠予小叔子，长子陈峰看似顺从鼓掌，实则暗中申请援疆调令。面对父母偏心和弟媳挑衅，陈峰携妻林晚隐忍筹备。最终在家庭会议上，他出示双人调令宣告远赴新疆，打破原生家庭剥削链条。经历异地磨砺与除夕和解，一家人终在理解中重建亲情边界，实现各自独立与成长。</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
@@ -1269,13 +1275,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
-        <x:v>七套房产，换来一纸调令</x:v>
+        <x:v>锦书迟</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>09-12 08:18</x:v>
+        <x:v>09-12 07:30</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str"/>
       <x:c r="F5" s="11" t="str"/>
@@ -1286,7 +1292,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I5" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J5" s="10" t="str">
         <x:v>其他</x:v>
@@ -1295,10 +1301,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L5" s="11" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>咩咩漫文</x:v>
       </x:c>
       <x:c r="M5" s="10" t="str">
-        <x:v>公婆将七套房产全数赠予小叔子，长子陈峰看似顺从鼓掌，实则暗中申请援疆调令。面对父母偏心和弟媳挑衅，陈峰携妻林晚隐忍筹备。最终在家庭会议上，他出示双人调令宣告远赴新疆，打破原生家庭剥削链条。经历异地磨砺与除夕和解，一家人终在理解中重建亲情边界，实现各自独立与成长。</x:v>
+        <x:v>三年前，沈昭昭嫁与永宁侯谢凛，新婚燕尔他便远赴边关。她苦等家书，却不知双向书信早被人暗中截留。她终于心冷离开侯府。三年后，她带着孩子在市井支摊卖画立足，他却循着蛛丝马迹寻来，真相层层揭开，原来他从未负她。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1306,7 +1312,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
         <x:v>泰城错嫁</x:v>
@@ -1343,13 +1349,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
-        <x:v>锦书迟</x:v>
+        <x:v>反派拿捏！</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>09-12 07:30</x:v>
+        <x:v>2026-09-13</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str"/>
       <x:c r="F7" s="11" t="str"/>
@@ -1359,21 +1365,15 @@
       <x:c r="H7" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="n">
-        <x:v>58</x:v>
-      </x:c>
+      <x:c r="I7" s="11" t="str"/>
       <x:c r="J7" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K7" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="str">
-        <x:v>咩咩漫文</x:v>
-      </x:c>
-      <x:c r="M7" s="10" t="str">
-        <x:v>三年前，沈昭昭嫁与永宁侯谢凛，新婚燕尔他便远赴边关。她苦等家书，却不知双向书信早被人暗中截留。她终于心冷离开侯府。三年后，她带着孩子在市井支摊卖画立足，他却循着蛛丝马迹寻来，真相层层揭开，原来他从未负她。</x:v>
-      </x:c>
+      <x:c r="L7" s="11" t="str"/>
+      <x:c r="M7" s="10" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
@@ -1383,10 +1383,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
-        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
+        <x:v>装傻下山</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>09-13 08:00</x:v>
+        <x:v>2026-09-12</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str"/>
       <x:c r="F8" s="11" t="str"/>
@@ -1396,34 +1396,28 @@
       <x:c r="H8" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I8" s="11" t="n">
-        <x:v>64</x:v>
-      </x:c>
+      <x:c r="I8" s="11" t="str"/>
       <x:c r="J8" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K8" s="10" t="str">
-        <x:v>古装宫廷</x:v>
-      </x:c>
-      <x:c r="L8" s="11" t="str">
-        <x:v>心动漫剧场</x:v>
-      </x:c>
-      <x:c r="M8" s="10" t="str">
-        <x:v>大晋七公主沈令仪，自幼被冷落于听竹宫，沉默藏锋，苟全性命。宫宴之上，太子带回的秦照雪笑盈盈提议将她送去北狄和亲。满殿以为皇帝会点头，他却掷出“废太子”三字。一夜之间，沈令仪被推到台前。北狄求和的急报恰在此时入京——与她方才所言分毫不差。可当她回望母亲遗下的那半卷秘策时，才发现这局棋，早在二十年前就已落子。</x:v>
-      </x:c>
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="L8" s="11" t="str"/>
+      <x:c r="M8" s="10" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
-        <x:v>今天开始做裴总</x:v>
+        <x:v>今晚查寝，别开门</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>09-12 19:48</x:v>
+        <x:v>09-12 23:35</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str"/>
       <x:c r="F9" s="11" t="str"/>
@@ -1434,7 +1428,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I9" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J9" s="10" t="str">
         <x:v>其他</x:v>
@@ -1443,10 +1437,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L9" s="11" t="str">
-        <x:v>严墨墨</x:v>
+        <x:v>辣妹漫剧</x:v>
       </x:c>
       <x:c r="M9" s="10" t="str">
-        <x:v>裴野低调蛰伏三年，甘愿扮作普通员工，在公司默默沉淀，面对职场非议、旁人轻视从未辩解。年会之上，他惨遭当众开除，相伴多年的婚姻也走向终点，跌入人生低谷。褪去伪装，他不再刻意隐忍，解锁真实身份，告别敷衍度日的过往。一路轻松逆袭，打破所有人的偏见，凭自身实力惊艳全场，开启属于自己的全新人生。</x:v>
+        <x:v>程妍重生回女生宿舍407遇害前二十分钟，笃定深夜“临时查寝”是致命陷阱，不顾室友质疑拼死堵门。四人合力对抗冒充宿管的歹徒，最终揪出泄露学生信息的内鬼。案件告破，四个女孩平安毕业，407一个都没少，再然后就发生了这些事。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1454,13 +1448,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
-        <x:v>反派拿捏！</x:v>
+        <x:v>这桌团圆饭，我不做了</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>2026-09-13</x:v>
+        <x:v>09-13 17:02</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str"/>
       <x:c r="F10" s="11" t="str"/>
@@ -1470,28 +1464,34 @@
       <x:c r="H10" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I10" s="11" t="str"/>
+      <x:c r="I10" s="11" t="n">
+        <x:v>50</x:v>
+      </x:c>
       <x:c r="J10" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K10" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L10" s="11" t="str"/>
-      <x:c r="M10" s="10" t="str"/>
+        <x:v>美食治愈</x:v>
+      </x:c>
+      <x:c r="L10" s="11" t="str">
+        <x:v>锦鲤漫</x:v>
+      </x:c>
+      <x:c r="M10" s="10" t="str">
+        <x:v>除夕前夕，乔宁发现丈夫擅自退掉她陪父母吃年夜饭的包间，还将三十一人的团圆饭默认交给她操持。她不再争吵，也不再兜底，而是选择回家陪伴父母。随着陆家亲自接手年夜饭，众人才逐渐明白，一顿“简单”的团圆饭背后，藏着多少被忽视的付出与责任。</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C11" s="10" t="str">
-        <x:v>这桌团圆饭，我不做了</x:v>
+        <x:v>今天开始做裴总</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>09-13 17:02</x:v>
+        <x:v>09-12 19:48</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str"/>
       <x:c r="F11" s="11" t="str"/>
@@ -1502,19 +1502,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I11" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J11" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K11" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L11" s="11" t="str">
-        <x:v>锦鲤漫</x:v>
+        <x:v>严墨墨</x:v>
       </x:c>
       <x:c r="M11" s="10" t="str">
-        <x:v>除夕前夕，乔宁发现丈夫擅自退掉她陪父母吃年夜饭的包间，还将三十一人的团圆饭默认交给她操持。她不再争吵，也不再兜底，而是选择回家陪伴父母。随着陆家亲自接手年夜饭，众人才逐渐明白，一顿“简单”的团圆饭背后，藏着多少被忽视的付出与责任。</x:v>
+        <x:v>裴野低调蛰伏三年，甘愿扮作普通员工，在公司默默沉淀，面对职场非议、旁人轻视从未辩解。年会之上，他惨遭当众开除，相伴多年的婚姻也走向终点，跌入人生低谷。褪去伪装，他不再刻意隐忍，解锁真实身份，告别敷衍度日的过往。一路轻松逆袭，打破所有人的偏见，凭自身实力惊艳全场，开启属于自己的全新人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1522,7 +1522,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
         <x:v>小妹初长成</x:v>
@@ -1553,13 +1553,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B13" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
-        <x:v>返乡种田，我看透了人性</x:v>
+        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
-        <x:v>09-13 00:10</x:v>
+        <x:v>09-13 08:00</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str"/>
       <x:c r="F13" s="11" t="str"/>
@@ -1570,19 +1570,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I13" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J13" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K13" s="10" t="str">
-        <x:v>种田囤货</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="L13" s="11" t="str">
-        <x:v>一初动漫剧场</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="M13" s="10" t="str">
-        <x:v>卖掉公司股份实现财富自由后，江枫隐藏巨额身家，辞职回到农村老家，准备享受田园生活。没想到一条朋友圈，让女友提出分手，同学冷眼嘲讽。返乡后，他的种种操作又遭到村民质疑。可谁也没想到，江枫不仅迎娶了家境富裕的校花，还带领亲友发家致富。那些曾经嘲笑、疏远他的人，最终只能后悔。</x:v>
+        <x:v>大晋七公主沈令仪，自幼被冷落于听竹宫，沉默藏锋，苟全性命。宫宴之上，太子带回的秦照雪笑盈盈提议将她送去北狄和亲。满殿以为皇帝会点头，他却掷出“废太子”三字。一夜之间，沈令仪被推到台前。北狄求和的急报恰在此时入京——与她方才所言分毫不差。可当她回望母亲遗下的那半卷秘策时，才发现这局棋，早在二十年前就已落子。</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1590,13 +1590,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B14" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
-        <x:v>今晚查寝，别开门</x:v>
+        <x:v>返乡种田，我看透了人性</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>09-12 23:35</x:v>
+        <x:v>09-13 00:10</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str"/>
       <x:c r="F14" s="11" t="str"/>
@@ -1607,19 +1607,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I14" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="J14" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K14" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>种田囤货</x:v>
       </x:c>
       <x:c r="L14" s="11" t="str">
-        <x:v>辣妹漫剧</x:v>
+        <x:v>一初动漫剧场</x:v>
       </x:c>
       <x:c r="M14" s="10" t="str">
-        <x:v>程妍重生回女生宿舍407遇害前二十分钟，笃定深夜“临时查寝”是致命陷阱，不顾室友质疑拼死堵门。四人合力对抗冒充宿管的歹徒，最终揪出泄露学生信息的内鬼。案件告破，四个女孩平安毕业，407一个都没少，再然后就发生了这些事。</x:v>
+        <x:v>卖掉公司股份实现财富自由后，江枫隐藏巨额身家，辞职回到农村老家，准备享受田园生活。没想到一条朋友圈，让女友提出分手，同学冷眼嘲讽。返乡后，他的种种操作又遭到村民质疑。可谁也没想到，江枫不仅迎娶了家境富裕的校花，还带领亲友发家致富。那些曾经嘲笑、疏远他的人，最终只能后悔。</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1627,7 +1627,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B15" s="11" t="n">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
         <x:v>员工跑路我扩店</x:v>
@@ -1667,10 +1667,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C16" s="10" t="str">
-        <x:v>活宝老爹再赴青春，竟与女儿同上大学</x:v>
+        <x:v>枕上独宠第一季</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
-        <x:v>09-13 00:08</x:v>
+        <x:v>09-13 11:05</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str"/>
       <x:c r="F16" s="11" t="str"/>
@@ -1681,19 +1681,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I16" s="11" t="n">
-        <x:v>140</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="J16" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K16" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L16" s="11" t="str">
-        <x:v>长风剧场</x:v>
+        <x:v>语跃文化</x:v>
       </x:c>
       <x:c r="M16" s="10" t="str">
-        <x:v>45岁的白烨意外激活成长系统。只要亲身体验年轻人的日常，就能重拾青春活力，还能收获丰厚奖励。为完成系统任务，他报名成人高考，顺利考入大学，竟和女儿成了同校同学。重返校园的白烨，一边认真完成任务感受青春，一边在校园里开启一段充满趣味的全新人生。</x:v>
+        <x:v>四年前我不告而别，远走他国，以为他在家族逼婚与我之间选择了前者。四年后我以记者身份回国，第一场采访对象正是已成集团总裁的前男友。我问他订婚传闻，他冷言相对，却一直留着我送的旧物。直到闺蜜点破真相，当年他被家中软禁，错过我的电话，此后数年拼命往上走，只为有能力护住想护的人。误会尽释，这一次我不会再逃。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1701,13 +1701,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C17" s="10" t="str">
-        <x:v>我赚上千万跟爸妈说50W，隔天就被找上门</x:v>
+        <x:v>河箱送福来</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
-        <x:v>09-13 08:00</x:v>
+        <x:v>09-13 11:00</x:v>
       </x:c>
       <x:c r="E17" s="11" t="str"/>
       <x:c r="F17" s="11" t="str"/>
@@ -1718,7 +1718,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I17" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J17" s="10" t="str">
         <x:v>其他</x:v>
@@ -1727,10 +1727,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L17" s="11" t="str">
-        <x:v>至尊爽剧社</x:v>
+        <x:v>灵心讲故事</x:v>
       </x:c>
       <x:c r="M17" s="10" t="str">
-        <x:v>三十二岁那年，贺川用六年孤注一掷的钻研，换来了七千六百万的回报。可财富还没捂热，先尝到的却是亲人无度的索取。他谎称只赚五十万，叮嘱保密，却挡不住消息走漏。隔天登门的亲戚不止要借钱买房，更联手外人盗用他的身份资料，试图冒名签约、伪造担保债务。贺川报警取证，警方介入追回大部分资金，涉案者包括部分机构人员均承担了法律责任，这笔帐，能否算清？</x:v>
+        <x:v>张家老两口从河中救回一只木箱，收养了箱中受伤的福生。福生长大后修桥开田，引水惠及乡亲，成家立业。二老相继离世后，山洪威胁村庄，福生为救乡亲舍命撑住巨石，最终重伤落水，下落不明。秀娥守着小院苦等多年，直到熟悉的声音再次响起。</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1738,13 +1738,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>49</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C18" s="10" t="str">
-        <x:v>河箱送福来</x:v>
+        <x:v>活宝老爹再赴青春，竟与女儿同上大学</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>09-13 11:00</x:v>
+        <x:v>09-13 00:08</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str"/>
       <x:c r="F18" s="11" t="str"/>
@@ -1755,19 +1755,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I18" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J18" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K18" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="L18" s="11" t="str">
-        <x:v>灵心讲故事</x:v>
+        <x:v>长风剧场</x:v>
       </x:c>
       <x:c r="M18" s="10" t="str">
-        <x:v>张家老两口从河中救回一只木箱，收养了箱中受伤的福生。福生长大后修桥开田，引水惠及乡亲，成家立业。二老相继离世后，山洪威胁村庄，福生为救乡亲舍命撑住巨石，最终重伤落水，下落不明。秀娥守着小院苦等多年，直到熟悉的声音再次响起。</x:v>
+        <x:v>45岁的白烨意外激活成长系统。只要亲身体验年轻人的日常，就能重拾青春活力，还能收获丰厚奖励。为完成系统任务，他报名成人高考，顺利考入大学，竟和女儿成了同校同学。重返校园的白烨，一边认真完成任务感受青春，一边在校园里开启一段充满趣味的全新人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1775,13 +1775,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C19" s="10" t="str">
-        <x:v>退婚从抢我车位开始</x:v>
+        <x:v>我赚上千万跟爸妈说50W，隔天就被找上门</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
-        <x:v>2026-09-12</x:v>
+        <x:v>09-13 08:00</x:v>
       </x:c>
       <x:c r="E19" s="11" t="str"/>
       <x:c r="F19" s="11" t="str"/>
@@ -1791,22 +1791,28 @@
       <x:c r="H19" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I19" s="11" t="str"/>
+      <x:c r="I19" s="11" t="n">
+        <x:v>78</x:v>
+      </x:c>
       <x:c r="J19" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K19" s="10" t="str">
-        <x:v>都市职场 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="L19" s="11" t="str"/>
-      <x:c r="M19" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L19" s="11" t="str">
+        <x:v>至尊爽剧社</x:v>
+      </x:c>
+      <x:c r="M19" s="10" t="str">
+        <x:v>三十二岁那年，贺川用六年孤注一掷的钻研，换来了七千六百万的回报。可财富还没捂热，先尝到的却是亲人无度的索取。他谎称只赚五十万，叮嘱保密，却挡不住消息走漏。隔天登门的亲戚不止要借钱买房，更联手外人盗用他的身份资料，试图冒名签约、伪造担保债务。贺川报警取证，警方介入追回大部分资金，涉案者包括部分机构人员均承担了法律责任，这笔帐，能否算清？</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C20" s="10" t="str">
         <x:v>远山架子班</x:v>
@@ -1843,13 +1849,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C21" s="10" t="str">
-        <x:v>别咬，你太大只啦</x:v>
+        <x:v>退婚从抢我车位开始</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
-        <x:v>09-13 00:06</x:v>
+        <x:v>2026-09-12</x:v>
       </x:c>
       <x:c r="E21" s="11" t="str"/>
       <x:c r="F21" s="11" t="str"/>
@@ -1859,32 +1865,28 @@
       <x:c r="H21" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I21" s="11" t="n">
-        <x:v>180</x:v>
-      </x:c>
+      <x:c r="I21" s="11" t="str"/>
       <x:c r="J21" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K21" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>都市职场 / 婚姻情感</x:v>
       </x:c>
       <x:c r="L21" s="11" t="str"/>
-      <x:c r="M21" s="10" t="str">
-        <x:v>邵糯原本是一个生活拮据的少女，转生成动物后反而很容易从吃饱、睡好、有人陪伴中获得幸福感。第一世，穿成萨摩耶邂逅强大的银灰狼凯尔，历经族群纷争、生老病死，在风雪之中走完一生。第二世，她变成一只布偶猫，误入山野遇见巨型亚欧猞猁凯尔，在危机四伏的松林磨合羁绊，对抗狼群，晚年被救助站收留。两世，不同物种，却始终拥有命中注定的双向羁绊，全程还有野外直播实时见证他们的故事。</x:v>
-      </x:c>
+      <x:c r="M21" s="10" t="str"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>87</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C22" s="10" t="str">
-        <x:v>427元扳倒老油条</x:v>
+        <x:v>别咬，你太大只啦</x:v>
       </x:c>
       <x:c r="D22" s="11" t="str">
-        <x:v>09-13 16:00</x:v>
+        <x:v>09-13 00:06</x:v>
       </x:c>
       <x:c r="E22" s="11" t="str"/>
       <x:c r="F22" s="11" t="str"/>
@@ -1895,7 +1897,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I22" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="J22" s="10" t="str">
         <x:v>其他</x:v>
@@ -1903,11 +1905,9 @@
       <x:c r="K22" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L22" s="11" t="str">
-        <x:v>安然然</x:v>
-      </x:c>
+      <x:c r="L22" s="11" t="str"/>
       <x:c r="M22" s="10" t="str">
-        <x:v>职场新人许宁向老员工马丽芬讨要427元代垫外卖款，反遭易绑架马丽芬交出饭钱后怀恨在心，利用行政特权私吞福利，并在组织团餐时疏同事差价许宁按兵不动收集证据，最终将马丽芬长期贪占两万余元的行径在老板曝光的照片中马丽芬被直接开除，许宁成功维护了职场底线。</x:v>
+        <x:v>邵糯原本是一个生活拮据的少女，转生成动物后反而很容易从吃饱、睡好、有人陪伴中获得幸福感。第一世，穿成萨摩耶邂逅强大的银灰狼凯尔，历经族群纷争、生老病死，在风雪之中走完一生。第二世，她变成一只布偶猫，误入山野遇见巨型亚欧猞猁凯尔，在危机四伏的松林磨合羁绊，对抗狼群，晚年被救助站收留。两世，不同物种，却始终拥有命中注定的双向羁绊，全程还有野外直播实时见证他们的故事。</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1915,36 +1915,36 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C23" s="10" t="str">
-        <x:v>枕上独宠第一季</x:v>
+        <x:v>427元扳倒老油条</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
-        <x:v>09-13 11:05</x:v>
+        <x:v>09-13 16:00</x:v>
       </x:c>
       <x:c r="E23" s="11" t="str"/>
       <x:c r="F23" s="11" t="str"/>
       <x:c r="G23" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H23" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I23" s="11" t="n">
-        <x:v>185</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J23" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K23" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L23" s="11" t="str">
-        <x:v>语跃文化</x:v>
+        <x:v>安然然</x:v>
       </x:c>
       <x:c r="M23" s="10" t="str">
-        <x:v>四年前我不告而别，远走他国，以为他在家族逼婚与我之间选择了前者。四年后我以记者身份回国，第一场采访对象正是已成集团总裁的前男友。我问他订婚传闻，他冷言相对，却一直留着我送的旧物。直到闺蜜点破真相，当年他被家中软禁，错过我的电话，此后数年拼命往上走，只为有能力护住想护的人。误会尽释，这一次我不会再逃。</x:v>
+        <x:v>职场新人许宁向老员工马丽芬讨要427元代垫外卖款，反遭易绑架马丽芬交出饭钱后怀恨在心，利用行政特权私吞福利，并在组织团餐时疏同事差价许宁按兵不动收集证据，最终将马丽芬长期贪占两万余元的行径在老板曝光的照片中马丽芬被直接开除，许宁成功维护了职场底线。</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1952,13 +1952,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C24" s="10" t="str">
-        <x:v>重生山火前，我舍祖宅护全家</x:v>
+        <x:v>归来仍是掌心明珠</x:v>
       </x:c>
       <x:c r="D24" s="11" t="str">
-        <x:v>09-12 16:06</x:v>
+        <x:v>09-13 17:17</x:v>
       </x:c>
       <x:c r="E24" s="11" t="str"/>
       <x:c r="F24" s="11" t="str"/>
@@ -1966,22 +1966,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H24" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I24" s="11" t="n">
-        <x:v>89</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J24" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K24" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="L24" s="11" t="str">
-        <x:v>千鹤动漫</x:v>
+        <x:v>艾特弘</x:v>
       </x:c>
       <x:c r="M24" s="10" t="str">
-        <x:v>顾长河带着前世山火中痛失全家的记忆重生归来，得知三日后西岭大火将再次席卷村庄，他不顾众人质疑，卖掉祖宅，带着妻子母亲和儿子搬上白石坡，储水备粮清出防火带，只为改写一家人的命运，当烈火真正逼近，所有人终于明白，他舍掉的只是房子，拼命守住的才是真正的家。</x:v>
+        <x:v>沈念安在江南养父的悉心关爱下长大。得知自己是京城顾家的真千金后，面对身份的转变与波折，她不卑不亢，坚决拒绝毫无意义的家庭内耗。在养父的支持与亲哥顾时行默默的守护下，沈念安并未迷失自我，而是选择凭借扎实的法语专业在职场大放异彩，证明了个人价值。她以独立清醒、阳光向上的人生态度，不仅收获了两份温暖的亲情，更活出了属于自己的精彩人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1989,36 +1989,36 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>94</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C25" s="10" t="str">
-        <x:v>归来仍是掌心明珠</x:v>
+        <x:v>重生山火前，我舍祖宅护全家</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
-        <x:v>09-13 17:17</x:v>
+        <x:v>09-12 16:06</x:v>
       </x:c>
       <x:c r="E25" s="11" t="str"/>
       <x:c r="F25" s="11" t="str"/>
       <x:c r="G25" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H25" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I25" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J25" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K25" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L25" s="11" t="str">
-        <x:v>艾特弘</x:v>
+        <x:v>千鹤动漫</x:v>
       </x:c>
       <x:c r="M25" s="10" t="str">
-        <x:v>沈念安在江南养父的悉心关爱下长大。得知自己是京城顾家的真千金后，面对身份的转变与波折，她不卑不亢，坚决拒绝毫无意义的家庭内耗。在养父的支持与亲哥顾时行默默的守护下，沈念安并未迷失自我，而是选择凭借扎实的法语专业在职场大放异彩，证明了个人价值。她以独立清醒、阳光向上的人生态度，不仅收获了两份温暖的亲情，更活出了属于自己的精彩人生。</x:v>
+        <x:v>顾长河带着前世山火中痛失全家的记忆重生归来，得知三日后西岭大火将再次席卷村庄，他不顾众人质疑，卖掉祖宅，带着妻子母亲和儿子搬上白石坡，储水备粮清出防火带，只为改写一家人的命运，当烈火真正逼近，所有人终于明白，他舍掉的只是房子，拼命守住的才是真正的家。</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -2026,7 +2026,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B26" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C26" s="10" t="str">
         <x:v>垃圾桶里捡到爹</x:v>
@@ -2040,7 +2040,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H26" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I26" s="11" t="str"/>
       <x:c r="J26" s="10" t="str">
@@ -2057,36 +2057,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B27" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C27" s="10" t="str">
-        <x:v>枕上独宠第一季</x:v>
+        <x:v>竞争的枷锁</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
-        <x:v>09-13 11:05</x:v>
+        <x:v>09-12 16:30</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F27" s="11" t="str">
-        <x:v>↑47位</x:v>
+        <x:v>↑56位</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str"/>
       <x:c r="H27" s="11" t="str"/>
       <x:c r="I27" s="11" t="n">
-        <x:v>185</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J27" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K27" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L27" s="11" t="str">
-        <x:v>语跃文化</x:v>
+        <x:v>懒洋洋不懒</x:v>
       </x:c>
       <x:c r="M27" s="10" t="str">
-        <x:v>四年前我不告而别，远走他国，以为他在家族逼婚与我之间选择了前者。四年后我以记者身份回国，第一场采访对象正是已成集团总裁的前男友。我问他订婚传闻，他冷言相对，却一直留着我送的旧物。直到闺蜜点破真相，当年他被家中软禁，错过我的电话，此后数年拼命往上走，只为有能力护住想护的人。误会尽释，这一次我不会再逃。</x:v>
+        <x:v>双胞胎周朗和周昊从小就在家中竞争模式下长大，各类生活资源都要靠比拼争取，二人一直把对方视作对手。考入同一所大学后，争抢食堂岗位的契机下，他们才发现父母编织的谎言，两人都过得拮据艰难。过往多年的误会被解开，隔阂逐渐消散。兄弟俩放下彼此间的敌意，携手依靠打工谋求生活，摆脱旧有家庭模式的桎梏。往后不必再分出高下，并肩前行，认真经营属于自己的平凡生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -2094,61 +2094,55 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B28" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C28" s="10" t="str">
-        <x:v>我赚上千万跟爸妈说50W，隔天就被找上门</x:v>
+        <x:v>离婚那天我多了个痞帅老爹</x:v>
       </x:c>
       <x:c r="D28" s="11" t="str">
-        <x:v>09-13 08:00</x:v>
+        <x:v>2026-09-13</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F28" s="11" t="str">
-        <x:v>↑27位</x:v>
+        <x:v>↑40位</x:v>
       </x:c>
       <x:c r="G28" s="11" t="str"/>
       <x:c r="H28" s="11" t="str"/>
-      <x:c r="I28" s="11" t="n">
-        <x:v>78</x:v>
-      </x:c>
+      <x:c r="I28" s="11" t="str"/>
       <x:c r="J28" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K28" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L28" s="11" t="str">
-        <x:v>至尊爽剧社</x:v>
-      </x:c>
-      <x:c r="M28" s="10" t="str">
-        <x:v>三十二岁那年，贺川用六年孤注一掷的钻研，换来了七千六百万的回报。可财富还没捂热，先尝到的却是亲人无度的索取。他谎称只赚五十万，叮嘱保密，却挡不住消息走漏。隔天登门的亲戚不止要借钱买房，更联手外人盗用他的身份资料，试图冒名签约、伪造担保债务。贺川报警取证，警方介入追回大部分资金，涉案者包括部分机构人员均承担了法律责任，这笔帐，能否算清？</x:v>
-      </x:c>
+        <x:v>家庭伦理 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="L28" s="11" t="str"/>
+      <x:c r="M28" s="10" t="str"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B29" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C29" s="10" t="str">
-        <x:v>别咬，你太大只啦</x:v>
+        <x:v>427元扳倒老油条</x:v>
       </x:c>
       <x:c r="D29" s="11" t="str">
-        <x:v>09-13 00:06</x:v>
+        <x:v>09-13 16:00</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F29" s="11" t="str">
-        <x:v>↑24位</x:v>
+        <x:v>↑26位</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str"/>
       <x:c r="H29" s="11" t="str"/>
       <x:c r="I29" s="11" t="n">
-        <x:v>180</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J29" s="10" t="str">
         <x:v>其他</x:v>
@@ -2156,9 +2150,11 @@
       <x:c r="K29" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L29" s="11" t="str"/>
+      <x:c r="L29" s="11" t="str">
+        <x:v>安然然</x:v>
+      </x:c>
       <x:c r="M29" s="10" t="str">
-        <x:v>邵糯原本是一个生活拮据的少女，转生成动物后反而很容易从吃饱、睡好、有人陪伴中获得幸福感。第一世，穿成萨摩耶邂逅强大的银灰狼凯尔，历经族群纷争、生老病死，在风雪之中走完一生。第二世，她变成一只布偶猫，误入山野遇见巨型亚欧猞猁凯尔，在危机四伏的松林磨合羁绊，对抗狼群，晚年被救助站收留。两世，不同物种，却始终拥有命中注定的双向羁绊，全程还有野外直播实时见证他们的故事。</x:v>
+        <x:v>职场新人许宁向老员工马丽芬讨要427元代垫外卖款，反遭易绑架马丽芬交出饭钱后怀恨在心，利用行政特权私吞福利，并在组织团餐时疏同事差价许宁按兵不动收集证据，最终将马丽芬长期贪占两万余元的行径在老板曝光的照片中马丽芬被直接开除，许宁成功维护了职场底线。</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -2166,55 +2162,59 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B30" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C30" s="10" t="str">
-        <x:v>反派拿捏！</x:v>
+        <x:v>别咬，你太大只啦</x:v>
       </x:c>
       <x:c r="D30" s="11" t="str">
-        <x:v>2026-09-13</x:v>
+        <x:v>09-13 00:06</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F30" s="11" t="str">
-        <x:v>↑13位</x:v>
+        <x:v>↑22位</x:v>
       </x:c>
       <x:c r="G30" s="11" t="str"/>
       <x:c r="H30" s="11" t="str"/>
-      <x:c r="I30" s="11" t="str"/>
+      <x:c r="I30" s="11" t="n">
+        <x:v>180</x:v>
+      </x:c>
       <x:c r="J30" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K30" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L30" s="11" t="str"/>
-      <x:c r="M30" s="10" t="str"/>
+      <x:c r="M30" s="10" t="str">
+        <x:v>邵糯原本是一个生活拮据的少女，转生成动物后反而很容易从吃饱、睡好、有人陪伴中获得幸福感。第一世，穿成萨摩耶邂逅强大的银灰狼凯尔，历经族群纷争、生老病死，在风雪之中走完一生。第二世，她变成一只布偶猫，误入山野遇见巨型亚欧猞猁凯尔，在危机四伏的松林磨合羁绊，对抗狼群，晚年被救助站收留。两世，不同物种，却始终拥有命中注定的双向羁绊，全程还有野外直播实时见证他们的故事。</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B31" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C31" s="10" t="str">
-        <x:v>今晚查寝，别开门</x:v>
+        <x:v>重生山火前，我舍祖宅护全家</x:v>
       </x:c>
       <x:c r="D31" s="11" t="str">
-        <x:v>09-12 23:35</x:v>
+        <x:v>09-12 16:06</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F31" s="11" t="str">
-        <x:v>↑10位</x:v>
+        <x:v>↑20位</x:v>
       </x:c>
       <x:c r="G31" s="11" t="str"/>
       <x:c r="H31" s="11" t="str"/>
       <x:c r="I31" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J31" s="10" t="str">
         <x:v>其他</x:v>
@@ -2223,10 +2223,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L31" s="11" t="str">
-        <x:v>辣妹漫剧</x:v>
+        <x:v>千鹤动漫</x:v>
       </x:c>
       <x:c r="M31" s="10" t="str">
-        <x:v>程妍重生回女生宿舍407遇害前二十分钟，笃定深夜“临时查寝”是致命陷阱，不顾室友质疑拼死堵门。四人合力对抗冒充宿管的歹徒，最终揪出泄露学生信息的内鬼。案件告破，四个女孩平安毕业，407一个都没少，再然后就发生了这些事。</x:v>
+        <x:v>顾长河带着前世山火中痛失全家的记忆重生归来，得知三日后西岭大火将再次席卷村庄，他不顾众人质疑，卖掉祖宅，带着妻子母亲和儿子搬上白石坡，储水备粮清出防火带，只为改写一家人的命运，当烈火真正逼近，所有人终于明白，他舍掉的只是房子，拼命守住的才是真正的家。</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -2234,73 +2234,67 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B32" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C32" s="10" t="str">
-        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
+        <x:v>垃圾桶里捡到爹</x:v>
       </x:c>
       <x:c r="D32" s="11" t="str">
-        <x:v>09-13 08:00</x:v>
+        <x:v>2026-09-12</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F32" s="11" t="str">
-        <x:v>↑8位</x:v>
+        <x:v>↑16位</x:v>
       </x:c>
       <x:c r="G32" s="11" t="str"/>
       <x:c r="H32" s="11" t="str"/>
-      <x:c r="I32" s="11" t="n">
-        <x:v>64</x:v>
-      </x:c>
+      <x:c r="I32" s="11" t="str"/>
       <x:c r="J32" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K32" s="10" t="str">
-        <x:v>古装宫廷</x:v>
-      </x:c>
-      <x:c r="L32" s="11" t="str">
-        <x:v>心动漫剧场</x:v>
-      </x:c>
-      <x:c r="M32" s="10" t="str">
-        <x:v>大晋七公主沈令仪，自幼被冷落于听竹宫，沉默藏锋，苟全性命。宫宴之上，太子带回的秦照雪笑盈盈提议将她送去北狄和亲。满殿以为皇帝会点头，他却掷出“废太子”三字。一夜之间，沈令仪被推到台前。北狄求和的急报恰在此时入京——与她方才所言分毫不差。可当她回望母亲遗下的那半卷秘策时，才发现这局棋，早在二十年前就已落子。</x:v>
-      </x:c>
+        <x:v>家庭伦理</x:v>
+      </x:c>
+      <x:c r="L32" s="11" t="str"/>
+      <x:c r="M32" s="10" t="str"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B33" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C33" s="10" t="str">
-        <x:v>返乡种田，我看透了人性</x:v>
+        <x:v>野草归家</x:v>
       </x:c>
       <x:c r="D33" s="11" t="str">
-        <x:v>09-13 00:10</x:v>
+        <x:v>09-14 08:00</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:v>34</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F33" s="11" t="str">
-        <x:v>↑7位</x:v>
+        <x:v>↑16位</x:v>
       </x:c>
       <x:c r="G33" s="11" t="str"/>
       <x:c r="H33" s="11" t="str"/>
       <x:c r="I33" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J33" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K33" s="10" t="str">
-        <x:v>种田囤货</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L33" s="11" t="str">
-        <x:v>一初动漫剧场</x:v>
+        <x:v>小狐狸剧场</x:v>
       </x:c>
       <x:c r="M33" s="10" t="str">
-        <x:v>卖掉公司股份实现财富自由后，江枫隐藏巨额身家，辞职回到农村老家，准备享受田园生活。没想到一条朋友圈，让女友提出分手，同学冷眼嘲讽。返乡后，他的种种操作又遭到村民质疑。可谁也没想到，江枫不仅迎娶了家境富裕的校花，还带领亲友发家致富。那些曾经嘲笑、疏远他的人，最终只能后悔。</x:v>
+        <x:v>大雪夜，五岁的赵小草因为夹了一块肉，被养母赶出家门。她蜷在垃圾桶里取暖，捡到一张寻人启事——照片上的女孩和自己一般大，胎记的位置分毫不差。一个被苦寻，一个被弃如敝履。她攥着仅有的两块钱，拨通了那个号码。电话那头，是找了女儿四年的父亲。当裴靖川从垃圾桶里抱起奄奄一息的她时，谁也不知道，这一抱，抱回了一个被偷走四年的真相。</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -2308,36 +2302,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B34" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C34" s="10" t="str">
-        <x:v>活宝老爹再赴青春，竟与女儿同上大学</x:v>
+        <x:v>远山架子班</x:v>
       </x:c>
       <x:c r="D34" s="11" t="str">
-        <x:v>09-13 00:08</x:v>
+        <x:v>09-13 07:30</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
-        <x:v>37</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F34" s="11" t="str">
-        <x:v>↑7位</x:v>
+        <x:v>↑15位</x:v>
       </x:c>
       <x:c r="G34" s="11" t="str"/>
       <x:c r="H34" s="11" t="str"/>
       <x:c r="I34" s="11" t="n">
-        <x:v>140</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J34" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K34" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L34" s="11" t="str">
-        <x:v>长风剧场</x:v>
+        <x:v>空空书漫</x:v>
       </x:c>
       <x:c r="M34" s="10" t="str">
-        <x:v>45岁的白烨意外激活成长系统。只要亲身体验年轻人的日常，就能重拾青春活力，还能收获丰厚奖励。为完成系统任务，他报名成人高考，顺利考入大学，竟和女儿成了同校同学。重返校园的白烨，一边认真完成任务感受青春，一边在校园里开启一段充满趣味的全新人生。</x:v>
+        <x:v>工地上，彭大勇拿着别家四十一天的招工纸，问贺远山凭什么只给三十。贺远山不争辩，只把账摊开，安全装备饭钱他管，工钱三天一结，从没拖欠。有人奔着高薪离开，可那边层层扣下来，到手反不如从前，还屡屡涉险。工友受伤住院，贺远山二话不说垫钱救人，又帮着把旧账一笔笔算清。他始终守着一条理，钱要挣，命不能换。规矩立得住，人心自然拢得回，班越带越稳，账越算越明。</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -2345,55 +2339,61 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B35" s="11" t="n">
-        <x:v>86</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C35" s="10" t="str">
-        <x:v>满月当天，我选择离婚</x:v>
+        <x:v>河箱送福来</x:v>
       </x:c>
       <x:c r="D35" s="11" t="str">
-        <x:v>2026-09-14</x:v>
+        <x:v>09-13 11:00</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F35" s="11" t="str">
-        <x:v>↑5位</x:v>
+        <x:v>↑14位</x:v>
       </x:c>
       <x:c r="G35" s="11" t="str"/>
       <x:c r="H35" s="11" t="str"/>
-      <x:c r="I35" s="11" t="str"/>
+      <x:c r="I35" s="11" t="n">
+        <x:v>64</x:v>
+      </x:c>
       <x:c r="J35" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K35" s="10" t="str">
-        <x:v>婚姻情感</x:v>
-      </x:c>
-      <x:c r="L35" s="11" t="str"/>
-      <x:c r="M35" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L35" s="11" t="str">
+        <x:v>灵心讲故事</x:v>
+      </x:c>
+      <x:c r="M35" s="10" t="str">
+        <x:v>张家老两口从河中救回一只木箱，收养了箱中受伤的福生。福生长大后修桥开田，引水惠及乡亲，成家立业。二老相继离世后，山洪威胁村庄，福生为救乡亲舍命撑住巨石，最终重伤落水，下落不明。秀娥守着小院苦等多年，直到熟悉的声音再次响起。</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B36" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C36" s="10" t="str">
-        <x:v>七套房产，换来一纸调令</x:v>
+        <x:v>股东名单没我名字，我果断抛售71%股权</x:v>
       </x:c>
       <x:c r="D36" s="11" t="str">
-        <x:v>09-12 08:18</x:v>
+        <x:v>09-14 08:00</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F36" s="11" t="str">
-        <x:v>↑4位</x:v>
+        <x:v>↑12位</x:v>
       </x:c>
       <x:c r="G36" s="11" t="str"/>
       <x:c r="H36" s="11" t="str"/>
       <x:c r="I36" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J36" s="10" t="str">
         <x:v>其他</x:v>
@@ -2402,10 +2402,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L36" s="11" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>番荔枝剧场</x:v>
       </x:c>
       <x:c r="M36" s="10" t="str">
-        <x:v>公婆将七套房产全数赠予小叔子，长子陈峰看似顺从鼓掌，实则暗中申请援疆调令。面对父母偏心和弟媳挑衅，陈峰携妻林晚隐忍筹备。最终在家庭会议上，他出示双人调令宣告远赴新疆，打破原生家庭剥削链条。经历异地磨砺与除夕和解，一家人终在理解中重建亲情边界，实现各自独立与成长。</x:v>
+        <x:v>徐陈用八年写下瀚海星辰的每一行核心代码，把公司从两千万做到二十亿。母亲病重，他将一切托付给合伙人和妻子。三个月后归来，股东名册上十二个名字，没有一个是他的。陈凯持股三十五，妻子江瑶十五，连她还在读书的弟弟都占了五。他站在会议室门口，手里的文件袋很轻，里面装着北斗科技的全部专利，和一个谁也想不到的决定。</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -2413,24 +2413,24 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B37" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C37" s="10" t="str">
-        <x:v>我在他心上</x:v>
+        <x:v>今晚查寝，别开门</x:v>
       </x:c>
       <x:c r="D37" s="11" t="str">
-        <x:v>09-12 19:30</x:v>
+        <x:v>09-12 23:35</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F37" s="11" t="str">
-        <x:v>↑3位</x:v>
+        <x:v>↑11位</x:v>
       </x:c>
       <x:c r="G37" s="11" t="str"/>
       <x:c r="H37" s="11" t="str"/>
       <x:c r="I37" s="11" t="n">
-        <x:v>166</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J37" s="10" t="str">
         <x:v>其他</x:v>
@@ -2439,10 +2439,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L37" s="11" t="str">
-        <x:v>雨沐漫画</x:v>
+        <x:v>辣妹漫剧</x:v>
       </x:c>
       <x:c r="M37" s="10" t="str">
-        <x:v>一场意外失忆后，我忘记了一切，包括那个让我又爱又痛、有名无实的总裁老婆。生性内敛却深情满满的沈大总裁慌了。从来眼里只能看见小儿子的方家人也慌了。方休微笑脸别跪，没用。再后来以为自己是小可怜的方休发现自己生活中的每一个细节，都有着被老婆往死里宠着的痕迹。</x:v>
+        <x:v>程妍重生回女生宿舍407遇害前二十分钟，笃定深夜“临时查寝”是致命陷阱，不顾室友质疑拼死堵门。四人合力对抗冒充宿管的歹徒，最终揪出泄露学生信息的内鬼。案件告破，四个女孩平安毕业，407一个都没少，再然后就发生了这些事。</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -2450,56 +2450,50 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B38" s="11" t="n">
-        <x:v>29</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C38" s="10" t="str">
-        <x:v>员工跑路我扩店</x:v>
+        <x:v>反派拿捏！</x:v>
       </x:c>
       <x:c r="D38" s="11" t="str">
-        <x:v>09-13 08:58</x:v>
+        <x:v>2026-09-13</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
-        <x:v>31</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F38" s="11" t="str">
-        <x:v>↑2位</x:v>
+        <x:v>↑8位</x:v>
       </x:c>
       <x:c r="G38" s="11" t="str"/>
       <x:c r="H38" s="11" t="str"/>
-      <x:c r="I38" s="11" t="n">
-        <x:v>70</x:v>
-      </x:c>
+      <x:c r="I38" s="11" t="str"/>
       <x:c r="J38" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K38" s="10" t="str">
-        <x:v>都市职场</x:v>
-      </x:c>
-      <x:c r="L38" s="11" t="str">
-        <x:v>大梨看剧</x:v>
-      </x:c>
-      <x:c r="M38" s="10" t="str">
-        <x:v>林辰经营天力健身馆，年终为员工每人发放五万元奖金。几位教练希望获得更多发展空间，与林辰理念产生分歧，决定在隔壁开设新馆，一场实力较量就此展开。林辰选择升级场地、引进专业团队，并提拔刘阿姨担任店长。正月初七，千名会员到场，用选择见证真诚服务的价值。</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L38" s="11" t="str"/>
+      <x:c r="M38" s="10" t="str"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B39" s="11" t="n">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C39" s="10" t="str">
-        <x:v>离婚那天我多了个痞帅老爹</x:v>
+        <x:v>退婚从抢我车位开始</x:v>
       </x:c>
       <x:c r="D39" s="11" t="str">
-        <x:v>2026-09-13</x:v>
+        <x:v>2026-09-12</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
-        <x:v>99</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F39" s="11" t="str">
-        <x:v>↑1位</x:v>
+        <x:v>↑7位</x:v>
       </x:c>
       <x:c r="G39" s="11" t="str"/>
       <x:c r="H39" s="11" t="str"/>
@@ -2508,7 +2502,7 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="K39" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感</x:v>
+        <x:v>都市职场 / 婚姻情感</x:v>
       </x:c>
       <x:c r="L39" s="11" t="str"/>
       <x:c r="M39" s="10" t="str"/>
@@ -2518,34 +2512,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B40" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C40" s="10" t="str">
-        <x:v>股东名单没我名字，我果断抛售71%股权</x:v>
+        <x:v>归来仍是掌心明珠</x:v>
       </x:c>
       <x:c r="D40" s="11" t="str">
-        <x:v>09-14 08:00</x:v>
-      </x:c>
-      <x:c r="E40" s="11" t="str"/>
+        <x:v>09-13 17:17</x:v>
+      </x:c>
+      <x:c r="E40" s="11" t="n">
+        <x:v>94</x:v>
+      </x:c>
       <x:c r="F40" s="11" t="str">
-        <x:v>新上榜</x:v>
+        <x:v>↑7位</x:v>
       </x:c>
       <x:c r="G40" s="11" t="str"/>
       <x:c r="H40" s="11" t="str"/>
       <x:c r="I40" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J40" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K40" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="L40" s="11" t="str">
-        <x:v>番荔枝剧场</x:v>
+        <x:v>艾特弘</x:v>
       </x:c>
       <x:c r="M40" s="10" t="str">
-        <x:v>徐陈用八年写下瀚海星辰的每一行核心代码，把公司从两千万做到二十亿。母亲病重，他将一切托付给合伙人和妻子。三个月后归来，股东名册上十二个名字，没有一个是他的。陈凯持股三十五，妻子江瑶十五，连她还在读书的弟弟都占了五。他站在会议室门口，手里的文件袋很轻，里面装着北斗科技的全部专利，和一个谁也想不到的决定。</x:v>
+        <x:v>沈念安在江南养父的悉心关爱下长大。得知自己是京城顾家的真千金后，面对身份的转变与波折，她不卑不亢，坚决拒绝毫无意义的家庭内耗。在养父的支持与亲哥顾时行默默的守护下，沈念安并未迷失自我，而是选择凭借扎实的法语专业在职场大放异彩，证明了个人价值。她以独立清醒、阳光向上的人生态度，不仅收获了两份温暖的亲情，更活出了属于自己的精彩人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -2553,34 +2549,215 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B41" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C41" s="10" t="str">
-        <x:v>野草归家</x:v>
+        <x:v>小妹初长成</x:v>
       </x:c>
       <x:c r="D41" s="11" t="str">
-        <x:v>09-14 08:00</x:v>
-      </x:c>
-      <x:c r="E41" s="11" t="str"/>
+        <x:v>2026-09-13</x:v>
+      </x:c>
+      <x:c r="E41" s="11" t="n">
+        <x:v>26</x:v>
+      </x:c>
       <x:c r="F41" s="11" t="str">
-        <x:v>新上榜</x:v>
+        <x:v>↑4位</x:v>
       </x:c>
       <x:c r="G41" s="11" t="str"/>
       <x:c r="H41" s="11" t="str"/>
-      <x:c r="I41" s="11" t="n">
-        <x:v>65</x:v>
-      </x:c>
+      <x:c r="I41" s="11" t="str"/>
       <x:c r="J41" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K41" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L41" s="11" t="str">
-        <x:v>小狐狸剧场</x:v>
-      </x:c>
-      <x:c r="M41" s="10" t="str">
-        <x:v>大雪夜，五岁的赵小草因为夹了一块肉，被养母赶出家门。她蜷在垃圾桶里取暖，捡到一张寻人启事——照片上的女孩和自己一般大，胎记的位置分毫不差。一个被苦寻，一个被弃如敝履。她攥着仅有的两块钱，拨通了那个号码。电话那头，是找了女儿四年的父亲。当裴靖川从垃圾桶里抱起奄奄一息的她时，谁也不知道，这一抱，抱回了一个被偷走四年的真相。</x:v>
+      <x:c r="L41" s="11" t="str"/>
+      <x:c r="M41" s="10" t="str"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B42" s="11" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C42" s="10" t="str">
+        <x:v>这桌团圆饭，我不做了</x:v>
+      </x:c>
+      <x:c r="D42" s="11" t="str">
+        <x:v>09-13 17:02</x:v>
+      </x:c>
+      <x:c r="E42" s="11" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F42" s="11" t="str">
+        <x:v>↑3位</x:v>
+      </x:c>
+      <x:c r="G42" s="11" t="str"/>
+      <x:c r="H42" s="11" t="str"/>
+      <x:c r="I42" s="11" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J42" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K42" s="10" t="str">
+        <x:v>美食治愈</x:v>
+      </x:c>
+      <x:c r="L42" s="11" t="str">
+        <x:v>锦鲤漫</x:v>
+      </x:c>
+      <x:c r="M42" s="10" t="str">
+        <x:v>除夕前夕，乔宁发现丈夫擅自退掉她陪父母吃年夜饭的包间，还将三十一人的团圆饭默认交给她操持。她不再争吵，也不再兜底，而是选择回家陪伴父母。随着陆家亲自接手年夜饭，众人才逐渐明白，一顿“简单”的团圆饭背后，藏着多少被忽视的付出与责任。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B43" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C43" s="10" t="str">
+        <x:v>七套房产，换来一纸调令</x:v>
+      </x:c>
+      <x:c r="D43" s="11" t="str">
+        <x:v>09-12 08:18</x:v>
+      </x:c>
+      <x:c r="E43" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F43" s="11" t="str">
+        <x:v>↑2位</x:v>
+      </x:c>
+      <x:c r="G43" s="11" t="str"/>
+      <x:c r="H43" s="11" t="str"/>
+      <x:c r="I43" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="J43" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K43" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L43" s="11" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="M43" s="10" t="str">
+        <x:v>公婆将七套房产全数赠予小叔子，长子陈峰看似顺从鼓掌，实则暗中申请援疆调令。面对父母偏心和弟媳挑衅，陈峰携妻林晚隐忍筹备。最终在家庭会议上，他出示双人调令宣告远赴新疆，打破原生家庭剥削链条。经历异地磨砺与除夕和解，一家人终在理解中重建亲情边界，实现各自独立与成长。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B44" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C44" s="10" t="str">
+        <x:v>锦书迟</x:v>
+      </x:c>
+      <x:c r="D44" s="11" t="str">
+        <x:v>09-12 07:30</x:v>
+      </x:c>
+      <x:c r="E44" s="11" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F44" s="11" t="str">
+        <x:v>↑2位</x:v>
+      </x:c>
+      <x:c r="G44" s="11" t="str"/>
+      <x:c r="H44" s="11" t="str"/>
+      <x:c r="I44" s="11" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J44" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K44" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L44" s="11" t="str">
+        <x:v>咩咩漫文</x:v>
+      </x:c>
+      <x:c r="M44" s="10" t="str">
+        <x:v>三年前，沈昭昭嫁与永宁侯谢凛，新婚燕尔他便远赴边关。她苦等家书，却不知双向书信早被人暗中截留。她终于心冷离开侯府。三年后，她带着孩子在市井支摊卖画立足，他却循着蛛丝马迹寻来，真相层层揭开，原来他从未负她。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B45" s="11" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C45" s="10" t="str">
+        <x:v>员工跑路我扩店</x:v>
+      </x:c>
+      <x:c r="D45" s="11" t="str">
+        <x:v>09-13 08:58</x:v>
+      </x:c>
+      <x:c r="E45" s="11" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F45" s="11" t="str">
+        <x:v>↑2位</x:v>
+      </x:c>
+      <x:c r="G45" s="11" t="str"/>
+      <x:c r="H45" s="11" t="str"/>
+      <x:c r="I45" s="11" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="J45" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K45" s="10" t="str">
+        <x:v>都市职场</x:v>
+      </x:c>
+      <x:c r="L45" s="11" t="str">
+        <x:v>大梨看剧</x:v>
+      </x:c>
+      <x:c r="M45" s="10" t="str">
+        <x:v>林辰经营天力健身馆，年终为员工每人发放五万元奖金。几位教练希望获得更多发展空间，与林辰理念产生分歧，决定在隔壁开设新馆，一场实力较量就此展开。林辰选择升级场地、引进专业团队，并提拔刘阿姨担任店长。正月初七，千名会员到场，用选择见证真诚服务的价值。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B46" s="11" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C46" s="10" t="str">
+        <x:v>枕上独宠第一季</x:v>
+      </x:c>
+      <x:c r="D46" s="11" t="str">
+        <x:v>09-13 11:05</x:v>
+      </x:c>
+      <x:c r="E46" s="11" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F46" s="11" t="str">
+        <x:v>↑2位</x:v>
+      </x:c>
+      <x:c r="G46" s="11" t="str"/>
+      <x:c r="H46" s="11" t="str"/>
+      <x:c r="I46" s="11" t="n">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="J46" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K46" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="L46" s="11" t="str">
+        <x:v>语跃文化</x:v>
+      </x:c>
+      <x:c r="M46" s="10" t="str">
+        <x:v>四年前我不告而别，远走他国，以为他在家族逼婚与我之间选择了前者。四年后我以记者身份回国，第一场采访对象正是已成集团总裁的前男友。我问他订婚传闻，他冷言相对，却一直留着我送的旧物。直到闺蜜点破真相，当年他被家中软禁，错过我的电话，此后数年拼命往上走，只为有能力护住想护的人。误会尽释，这一次我不会再逃。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2626,56 +2803,56 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
-        <x:v>穷途千万</x:v>
+        <x:v>重生归来，我才是真正的千金</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
         <x:v>当日新上榜</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>07-29 09:00</x:v>
+        <x:v>09-02 11:27</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
-        <x:v>117</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F2" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="G2" s="10" t="str">
-        <x:v>不惑剧场</x:v>
+        <x:v>宝晨传媒</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>重生归来，我才是真正的千金</x:v>
+        <x:v>股东名单没我名字，我果断抛售71%股权</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>当日新上榜</x:v>
+        <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>09-02 11:27</x:v>
+        <x:v>09-14 08:00</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
-        <x:v>129</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F3" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G3" s="10" t="str">
-        <x:v>宝晨传媒</x:v>
+        <x:v>番荔枝剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>股东名单没我名字，我果断抛售71%股权</x:v>
+        <x:v>野草归家</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
         <x:v>今日发布</x:v>
@@ -2684,123 +2861,31 @@
         <x:v>09-14 08:00</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F4" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G4" s="10" t="str">
-        <x:v>番荔枝剧场</x:v>
+        <x:v>小狐狸剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>68</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>以规护仁心</x:v>
+        <x:v>同事把我当冤种，别怪我翻脸</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
         <x:v>当日新上榜</x:v>
       </x:c>
-      <x:c r="D5" s="11" t="str">
-        <x:v>07-30 11:00</x:v>
-      </x:c>
-      <x:c r="E5" s="11" t="n">
-        <x:v>87</x:v>
-      </x:c>
+      <x:c r="D5" s="11" t="str"/>
+      <x:c r="E5" s="11" t="str"/>
       <x:c r="F5" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="str">
-        <x:v>盐系少女社</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="11" t="n">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="B6" s="10" t="str">
-        <x:v>47岁应聘保安，董事长却要亲自见他</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="str">
-        <x:v>当日新上榜</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="str">
-        <x:v>08-14 12:59</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="n">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F6" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="G6" s="10" t="str">
-        <x:v>鑫鑫漫剧</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="11" t="n">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B7" s="10" t="str">
-        <x:v>野草归家</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="str">
-        <x:v>今日发布</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="str">
-        <x:v>09-14 08:00</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="n">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F7" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G7" s="10" t="str">
-        <x:v>小狐狸剧场</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="11" t="n">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="B8" s="10" t="str">
-        <x:v>满月当天，我选择离婚</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="str">
-        <x:v>当日新上榜</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="str"/>
-      <x:c r="E8" s="11" t="str"/>
-      <x:c r="F8" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="G8" s="10" t="str"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="11" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="B9" s="10" t="str">
-        <x:v>清风照星河</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="str">
-        <x:v>当日新上榜</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="str">
-        <x:v>08-11 20:04</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F9" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="G9" s="10" t="str">
-        <x:v>三针剧场</x:v>
-      </x:c>
+      <x:c r="G5" s="10" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2869,16 +2954,16 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
-        <x:v>退婚后我在七零赚钱养家致富</x:v>
+        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>2026-09-04</x:v>
+        <x:v>09-08 17:58</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
         <x:v>7</x:v>
@@ -2889,28 +2974,30 @@
       <x:c r="G2" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H2" s="11" t="str"/>
+      <x:c r="H2" s="11" t="n">
+        <x:v>111</x:v>
+      </x:c>
       <x:c r="I2" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="J2" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K2" s="11" t="str">
-        <x:v>0.00</x:v>
-      </x:c>
-      <x:c r="L2" s="10" t="str"/>
-      <x:c r="M2" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="J2" s="11" t="str"/>
+      <x:c r="K2" s="11" t="str"/>
+      <x:c r="L2" s="10" t="str">
+        <x:v>禾苗动画</x:v>
+      </x:c>
+      <x:c r="M2" s="10" t="str">
+        <x:v>末世异能者沐小暖意外穿书，成为七个反派继子的恶毒后娘。原主辛劳养娃却遭流言中伤，最终含恨而终。沐小暖决心扭转命运，恩威并施管教孩子，凭末世身手进山打猎采药、种地赶集改善家计，更以百年老参为礼，为长子求得名儒霍政谚收为关门弟子。她护佑家人躲过恶人算计与亲戚夺产，建起新宅。七个孩子从怨恨抗拒到真心信赖，争着喊她娘，一家人携手改写命运，收获温暖亲情。</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>惊絮无声：傻女的绝杀</x:v>
+        <x:v>一墙之隔，皆是人心</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>09-06 10:00</x:v>
+        <x:v>09-06 15:48</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
         <x:v>8</x:v>
@@ -2925,7 +3012,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H3" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
         <x:v>其他</x:v>
@@ -2933,24 +3020,24 @@
       <x:c r="J3" s="11" t="str"/>
       <x:c r="K3" s="11" t="str"/>
       <x:c r="L3" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>在下长生</x:v>
       </x:c>
       <x:c r="M3" s="10" t="str">
-        <x:v>沈家人人都是天才，唯独小女儿沈惊絮是公认的傻子。没人知道，她不仅装傻多年，还带着前世金牌律师的记忆重生而来。本想闭嘴躺平一生，谁料内鬼勾结资本做空沈氏，一纸合同就要让全家净身出户、背上百亿债务。父亲落笔前，她终于按住协议“这字不能签！”绝地反杀的沈惊絮，一步步挫败了对沈家的围剿，也让全家人重新认识了自己。沈家也迎来了新生。</x:v>
+        <x:v>妻子临产被车堵住出口，叶瑾抱着羊水破裂的她跑了三公里才到医院，母子平安。面对无理的车主，他没有以暴制暴，而是选择依法行事——在自家院内合法砌墙、种下高价值树苗，全程录像留证。车主回来后暴力砸墙、碾压树苗，最终被依法追究责任。</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
+        <x:v>退婚后我在七零赚钱养家致富</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>09-08 17:58</x:v>
+        <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
         <x:v>7</x:v>
@@ -2961,30 +3048,28 @@
       <x:c r="G4" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H4" s="11" t="n">
-        <x:v>111</x:v>
-      </x:c>
+      <x:c r="H4" s="11" t="str"/>
       <x:c r="I4" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J4" s="11" t="str"/>
-      <x:c r="K4" s="11" t="str"/>
-      <x:c r="L4" s="10" t="str">
-        <x:v>禾苗动画</x:v>
-      </x:c>
-      <x:c r="M4" s="10" t="str">
-        <x:v>末世异能者沐小暖意外穿书，成为七个反派继子的恶毒后娘。原主辛劳养娃却遭流言中伤，最终含恨而终。沐小暖决心扭转命运，恩威并施管教孩子，凭末世身手进山打猎采药、种地赶集改善家计，更以百年老参为礼，为长子求得名儒霍政谚收为关门弟子。她护佑家人躲过恶人算计与亲戚夺产，建起新宅。七个孩子从怨恨抗拒到真心信赖，争着喊她娘，一家人携手改写命运，收获温暖亲情。</x:v>
-      </x:c>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="J4" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K4" s="11" t="str">
+        <x:v>0.00</x:v>
+      </x:c>
+      <x:c r="L4" s="10" t="str"/>
+      <x:c r="M4" s="10" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>一墙之隔，皆是人心</x:v>
+        <x:v>惊絮无声：傻女的绝杀</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>09-06 15:48</x:v>
+        <x:v>09-06 10:00</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
         <x:v>8</x:v>
@@ -2999,7 +3084,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H5" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I5" s="10" t="str">
         <x:v>其他</x:v>
@@ -3007,24 +3092,24 @@
       <x:c r="J5" s="11" t="str"/>
       <x:c r="K5" s="11" t="str"/>
       <x:c r="L5" s="10" t="str">
-        <x:v>在下长生</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="M5" s="10" t="str">
-        <x:v>妻子临产被车堵住出口，叶瑾抱着羊水破裂的她跑了三公里才到医院，母子平安。面对无理的车主，他没有以暴制暴，而是选择依法行事——在自家院内合法砌墙、种下高价值树苗，全程录像留证。车主回来后暴力砸墙、碾压树苗，最终被依法追究责任。</x:v>
+        <x:v>沈家人人都是天才，唯独小女儿沈惊絮是公认的傻子。没人知道，她不仅装傻多年，还带着前世金牌律师的记忆重生而来。本想闭嘴躺平一生，谁料内鬼勾结资本做空沈氏，一纸合同就要让全家净身出户、背上百亿债务。父亲落笔前，她终于按住协议“这字不能签！”绝地反杀的沈惊絮，一步步挫败了对沈家的围剿，也让全家人重新认识了自己。沈家也迎来了新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>破库房的秘密</x:v>
+        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>2026-09-05</x:v>
+        <x:v>09-08 11:00</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
         <x:v>7</x:v>
@@ -3033,29 +3118,35 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G6" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H6" s="11" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H6" s="11" t="n">
+        <x:v>91</x:v>
+      </x:c>
       <x:c r="I6" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J6" s="11" t="str"/>
       <x:c r="K6" s="11" t="str"/>
-      <x:c r="L6" s="10" t="str"/>
-      <x:c r="M6" s="10" t="str"/>
+      <x:c r="L6" s="10" t="str">
+        <x:v>白桃剧场</x:v>
+      </x:c>
+      <x:c r="M6" s="10" t="str">
+        <x:v>阿梨一觉睡了三百年，养大的五只小兽尽数离去。她带着五只旧饭碗、十二枚铜钱与一把锈柴刀下山寻兽。昔日的小家伙已成威震四方的妖祖，历经重重相遇与揭秘，阿梨知晓三百年封印的真相，携手五只妖祖，一同对抗祸世灭灵兽神。</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>谢谢爸妈的穷养现在我富了</x:v>
+        <x:v>破库房的秘密</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>09-08 17:00</x:v>
+        <x:v>2026-09-05</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
         <x:v>7</x:v>
@@ -3064,35 +3155,29 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G7" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H7" s="11" t="n">
-        <x:v>120</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H7" s="11" t="str"/>
       <x:c r="I7" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J7" s="11" t="str"/>
       <x:c r="K7" s="11" t="str"/>
-      <x:c r="L7" s="10" t="str">
-        <x:v>风云剧场</x:v>
-      </x:c>
-      <x:c r="M7" s="10" t="str">
-        <x:v>秦明从小被父母区别对待，十八年后才知一切只是父母对两个儿子的不同教育安排。重生回到高三，他拒绝向既定命运低头，从校园起步，抓住时代机遇暗中积蓄力量。父母继续对弟弟偏爱，秦明也继续低调生活——整整十八年。直到除夕夜，他回到那个破旧的家，把所有真相摆在父母面前，把自己失去的人生，亲手要了回来。</x:v>
-      </x:c>
+      <x:c r="L7" s="10" t="str"/>
+      <x:c r="M7" s="10" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
+        <x:v>凤阙承安</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>09-08 11:00</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
         <x:v>7</x:v>
@@ -3101,35 +3186,29 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G8" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="11" t="n">
-        <x:v>91</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H8" s="11" t="str"/>
       <x:c r="I8" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J8" s="11" t="str"/>
       <x:c r="K8" s="11" t="str"/>
-      <x:c r="L8" s="10" t="str">
-        <x:v>白桃剧场</x:v>
-      </x:c>
-      <x:c r="M8" s="10" t="str">
-        <x:v>阿梨一觉睡了三百年，养大的五只小兽尽数离去。她带着五只旧饭碗、十二枚铜钱与一把锈柴刀下山寻兽。昔日的小家伙已成威震四方的妖祖，历经重重相遇与揭秘，阿梨知晓三百年封印的真相，携手五只妖祖，一同对抗祸世灭灵兽神。</x:v>
-      </x:c>
+      <x:c r="L8" s="10" t="str"/>
+      <x:c r="M8" s="10" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>蒙蒙半故</x:v>
+        <x:v>抢个新娘来当后娘第一季</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>09-05 20:27</x:v>
+        <x:v>09-08 15:10</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
         <x:v>7</x:v>
@@ -3138,10 +3217,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G9" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H9" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str">
         <x:v>其他</x:v>
@@ -3149,24 +3228,24 @@
       <x:c r="J9" s="11" t="str"/>
       <x:c r="K9" s="11" t="str"/>
       <x:c r="L9" s="10" t="str">
-        <x:v>小斐漫剧</x:v>
+        <x:v>麻辣公主</x:v>
       </x:c>
       <x:c r="M9" s="10" t="str">
-        <x:v>拥有漫长寿命的男人隐姓埋名，以外卖员身份在都市生活。百岁老人临终的遗愿，让他卷入豪门家族的纷争。他结识家族女总裁，接连应对家族内斗、敌对势力与神秘长生组织的重重算计。二人携手揭开千年前的尘封秘辛，对抗妄图窃取长生力量的反派，在危机之中彼此羁绊，还要面对即将开启的上古昆仑之门带来的巨大未知考验。</x:v>
+        <x:v>带着十里红妆出嫁那日，我才得知新郎早已另娶，这门亲事不过是盯上了我李家的家产。换作旁人或许忍气吞声，我偏不。我当众拒入侯府，主动上书朝廷，愿以嫁妆资援南方水患，只求解除婚约、护我父母周全。这份胆识赢得安王敬重，他以正妃之礼娶我入门。我立誓此生不做妾、不与人共侍一夫，终得一份彼此尊重的姻缘。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>凤阙承安</x:v>
+        <x:v>一针绣出自己的路</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>09-04 19:51</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
         <x:v>7</x:v>
@@ -3177,27 +3256,33 @@
       <x:c r="G10" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H10" s="11" t="str"/>
+      <x:c r="H10" s="11" t="n">
+        <x:v>62</x:v>
+      </x:c>
       <x:c r="I10" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J10" s="11" t="str"/>
       <x:c r="K10" s="11" t="str"/>
-      <x:c r="L10" s="10" t="str"/>
-      <x:c r="M10" s="10" t="str"/>
+      <x:c r="L10" s="10" t="str">
+        <x:v>墨尘漫剧</x:v>
+      </x:c>
+      <x:c r="M10" s="10" t="str">
+        <x:v>苏绾青她从裁缝店半张旧桌重新开始，凭一针一线修补旧物、绣出人心，也把被看轻的手艺做成自己的路。故事温暖励志，展现普通女性靠勤奋、诚信和坚持赢得尊重、改变生活的力量。所有的事情都可以迎刃而解，代表了生活中的光</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="n">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>抢个新娘来当后娘第一季</x:v>
+        <x:v>不负恩情不负卿</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>09-08 15:10</x:v>
+        <x:v>2026-09-05</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
         <x:v>7</x:v>
@@ -3206,35 +3291,29 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G11" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H11" s="11" t="n">
-        <x:v>177</x:v>
-      </x:c>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H11" s="11" t="str"/>
       <x:c r="I11" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J11" s="11" t="str"/>
       <x:c r="K11" s="11" t="str"/>
-      <x:c r="L11" s="10" t="str">
-        <x:v>麻辣公主</x:v>
-      </x:c>
-      <x:c r="M11" s="10" t="str">
-        <x:v>带着十里红妆出嫁那日，我才得知新郎早已另娶，这门亲事不过是盯上了我李家的家产。换作旁人或许忍气吞声，我偏不。我当众拒入侯府，主动上书朝廷，愿以嫁妆资援南方水患，只求解除婚约、护我父母周全。这份胆识赢得安王敬重，他以正妃之礼娶我入门。我立誓此生不做妾、不与人共侍一夫，终得一份彼此尊重的姻缘。</x:v>
-      </x:c>
+      <x:c r="L11" s="10" t="str"/>
+      <x:c r="M11" s="10" t="str"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>一针绣出自己的路</x:v>
+        <x:v>谢谢爸妈的穷养现在我富了</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>09-04 19:51</x:v>
+        <x:v>09-08 17:00</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
         <x:v>7</x:v>
@@ -3243,10 +3322,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G12" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H12" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str">
         <x:v>其他</x:v>
@@ -3254,24 +3333,24 @@
       <x:c r="J12" s="11" t="str"/>
       <x:c r="K12" s="11" t="str"/>
       <x:c r="L12" s="10" t="str">
-        <x:v>墨尘漫剧</x:v>
+        <x:v>风云剧场</x:v>
       </x:c>
       <x:c r="M12" s="10" t="str">
-        <x:v>苏绾青她从裁缝店半张旧桌重新开始，凭一针一线修补旧物、绣出人心，也把被看轻的手艺做成自己的路。故事温暖励志，展现普通女性靠勤奋、诚信和坚持赢得尊重、改变生活的力量。所有的事情都可以迎刃而解，代表了生活中的光</x:v>
+        <x:v>秦明从小被父母区别对待，十八年后才知一切只是父母对两个儿子的不同教育安排。重生回到高三，他拒绝向既定命运低头，从校园起步，抓住时代机遇暗中积蓄力量。父母继续对弟弟偏爱，秦明也继续低调生活——整整十八年。直到除夕夜，他回到那个破旧的家，把所有真相摆在父母面前，把自己失去的人生，亲手要了回来。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>我的奇葩舍友</x:v>
+        <x:v>蒙蒙半故</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>09-06 09:55</x:v>
+        <x:v>09-05 20:27</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
         <x:v>7</x:v>
@@ -3280,10 +3359,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G13" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H13" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="I13" s="10" t="str">
         <x:v>其他</x:v>
@@ -3291,24 +3370,24 @@
       <x:c r="J13" s="11" t="str"/>
       <x:c r="K13" s="11" t="str"/>
       <x:c r="L13" s="10" t="str">
-        <x:v>金鱼漫剪</x:v>
+        <x:v>小斐漫剧</x:v>
       </x:c>
       <x:c r="M13" s="10" t="str">
-        <x:v>林嘉宝从小由母亲周美兰一手带大，事无巨细都由妈妈安排。上大学后，他不会套被套，不会洗衣服，遇事第一反应是打电话问妈妈。母亲为他定下各种宿舍规矩，与室友矛盾不断。直到家中突遭变故，父亲破产，豪宅被封，母亲失联。嘉宝一夜之间失去所有依靠，被迫独自面对生活，一步步学会洗衣、打工、交电费，逐渐成为独立的大学生。</x:v>
+        <x:v>拥有漫长寿命的男人隐姓埋名，以外卖员身份在都市生活。百岁老人临终的遗愿，让他卷入豪门家族的纷争。他结识家族女总裁，接连应对家族内斗、敌对势力与神秘长生组织的重重算计。二人携手揭开千年前的尘封秘辛，对抗妄图窃取长生力量的反派，在危机之中彼此羁绊，还要面对即将开启的上古昆仑之门带来的巨大未知考验。</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>那块玉，带我们回家</x:v>
+        <x:v>我的奇葩舍友</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>09-05 07:18</x:v>
+        <x:v>09-06 09:55</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
         <x:v>7</x:v>
@@ -3317,10 +3396,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G14" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H14" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I14" s="10" t="str">
         <x:v>其他</x:v>
@@ -3328,21 +3407,21 @@
       <x:c r="J14" s="11" t="str"/>
       <x:c r="K14" s="11" t="str"/>
       <x:c r="L14" s="10" t="str">
-        <x:v>五指毛桃</x:v>
+        <x:v>金鱼漫剪</x:v>
       </x:c>
       <x:c r="M14" s="10" t="str">
-        <x:v>六岁孩童为救母拾荒半年，孝心感动天地，更牵出一段失散六年的亲情。缘分以信物为引，助离散一家重逢。当暗处之手伸向团圆，真相与信任如光破晓，令恶念无处遁形。正义为善良护航，温暖在守望中生长。孩子用稚嫩肩膀撑起希望，父母以爱重筑家园，善意在风雨中传递，终迎阖家安康的晴空。</x:v>
+        <x:v>林嘉宝从小由母亲周美兰一手带大，事无巨细都由妈妈安排。上大学后，他不会套被套，不会洗衣服，遇事第一反应是打电话问妈妈。母亲为他定下各种宿舍规矩，与室友矛盾不断。直到家中突遭变故，父亲破产，豪宅被封，母亲失联。嘉宝一夜之间失去所有依靠，被迫独自面对生活，一步步学会洗衣、打工、交电费，逐渐成为独立的大学生。</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>不负恩情不负卿</x:v>
+        <x:v>野茶开出花</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
-        <x:v>2026-09-05</x:v>
+        <x:v>09-05 18:16</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
         <x:v>9</x:v>
@@ -3354,26 +3433,32 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G15" s="11" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H15" s="11" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H15" s="11" t="n">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="I15" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J15" s="11" t="str"/>
       <x:c r="K15" s="11" t="str"/>
-      <x:c r="L15" s="10" t="str"/>
-      <x:c r="M15" s="10" t="str"/>
+      <x:c r="L15" s="10" t="str">
+        <x:v>多米漫剧场</x:v>
+      </x:c>
+      <x:c r="M15" s="10" t="str">
+        <x:v>苏晚星十九岁，一百八十斤，被母亲断卡后送进深山。石阶四十分钟，土屋、木板床、没信号的手机，迎接她的是守山四十年的石奶奶。采茶磨出水泡，跑山喘不上气，半夜偷吃生黄豆被当场抓住。阿杏叫她晚星姐，集市阿婆说她壮实，她第一次觉得胖没那么刺耳。体重从一百八到一百二，手上磨出了茧。她拍短视频卖茶，建山风茶舍。再次上山，她站在山顶说山神爷爷，我回来了。山风知道她来过，也知道她变成了谁。</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="n">
-        <x:v>99</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>野茶开出花</x:v>
+        <x:v>那块玉，带我们回家</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>09-05 18:16</x:v>
+        <x:v>09-05 07:18</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
         <x:v>9</x:v>
@@ -3385,10 +3470,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G16" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H16" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str">
         <x:v>其他</x:v>
@@ -3396,36 +3481,36 @@
       <x:c r="J16" s="11" t="str"/>
       <x:c r="K16" s="11" t="str"/>
       <x:c r="L16" s="10" t="str">
-        <x:v>多米漫剧场</x:v>
+        <x:v>五指毛桃</x:v>
       </x:c>
       <x:c r="M16" s="10" t="str">
-        <x:v>苏晚星十九岁，一百八十斤，被母亲断卡后送进深山。石阶四十分钟，土屋、木板床、没信号的手机，迎接她的是守山四十年的石奶奶。采茶磨出水泡，跑山喘不上气，半夜偷吃生黄豆被当场抓住。阿杏叫她晚星姐，集市阿婆说她壮实，她第一次觉得胖没那么刺耳。体重从一百八到一百二，手上磨出了茧。她拍短视频卖茶，建山风茶舍。再次上山，她站在山顶说山神爷爷，我回来了。山风知道她来过，也知道她变成了谁。</x:v>
+        <x:v>六岁孩童为救母拾荒半年，孝心感动天地，更牵出一段失散六年的亲情。缘分以信物为引，助离散一家重逢。当暗处之手伸向团圆，真相与信任如光破晓，令恶念无处遁形。正义为善良护航，温暖在守望中生长。孩子用稚嫩肩膀撑起希望，父母以爱重筑家园，善意在风雨中传递，终迎阖家安康的晴空。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B17" s="10" t="str">
+        <x:v>穿书后我带萌宝上门认爹</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="str">
+        <x:v>09-07 19:18</x:v>
+      </x:c>
+      <x:c r="D17" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B17" s="10" t="str">
-        <x:v>离家十年，回来女儿被换了</x:v>
-      </x:c>
-      <x:c r="C17" s="11" t="str">
-        <x:v>09-09 00:04</x:v>
-      </x:c>
-      <x:c r="D17" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="E17" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F17" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G17" s="11" t="n">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="H17" s="11" t="n">
-        <x:v>155</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="I17" s="10" t="str">
         <x:v>其他</x:v>
@@ -3433,36 +3518,36 @@
       <x:c r="J17" s="11" t="str"/>
       <x:c r="K17" s="11" t="str"/>
       <x:c r="L17" s="10" t="str">
-        <x:v>魔方影视（上剧版</x:v>
+        <x:v>虾仁不自在</x:v>
       </x:c>
       <x:c r="M17" s="10" t="str">
-        <x:v>程砚宁完成长期绝密任务归来，满心想要弥补亲情，却发现家中早已物是人非。身边亲近之人被私欲蒙蔽，制造重重骗局，试图侵占她的事业与财富。面对接连而来的算计与危机，她凭借过人的魄力与智慧步步拆解阴谋，联合正义力量搜集证据，厘清全部是非纠葛。在守护自身事业的同时，她放下过往伤痛，投身公益，完成自我和解，迎来属于自己的全新人生。</x:v>
+        <x:v>许知棠重生穿进书中，当即带着五岁儿子许小舟登门，将孩子送到亲生父亲——傅氏集团总裁傅临川面前，只想抽身退出剧情。幼儿园里儿子遭同学诬陷、老师偏心，她强势护崽，硬刚蛮横家长与失职老师。亲子鉴定尘埃落定，萌娃黏妈不黏爹，反倒让清冷总裁渐渐上心。</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>重生三天前，我用水泥封死地下室</x:v>
+        <x:v>重启人生，拒绝校花？</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>09-09 09:28</x:v>
+        <x:v>09-08 08:30</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G18" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H18" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="I18" s="10" t="str">
         <x:v>其他</x:v>
@@ -3470,36 +3555,36 @@
       <x:c r="J18" s="11" t="str"/>
       <x:c r="K18" s="11" t="str"/>
       <x:c r="L18" s="10" t="str">
-        <x:v>忘忧剧场</x:v>
+        <x:v>肆漫简</x:v>
       </x:c>
       <x:c r="M18" s="10" t="str">
-        <x:v>阮清重生回被保姆王妈一家害死的三天前，前世她因心善引狼入室，保姆全家蜗居别墅地下室偷窃投毒，最终惨遭勒死。重生后她假装不知，趁王妈外出时用水泥将地下室彻底封死。警方破墙后，五具尸体令真相大白，王妈因盗窃、投毒被判十五年。阮清与父母团聚，恶人终得恶报，她重获新生。</x:v>
+        <x:v>白陌重生回到2004年高考夜，果断避开前世陷害自己的宾馆陷阱，救下被下药的校花江洛菡，彻底扭转人生走向。他不再执着于过往的情感执念，跳出卑微追爱的困局，转而关心恩师健康、规划学业与创业方向，结识志同道合的伙伴。凭借重生阅历清醒选择前路，把握青春重启人生，用行动改写原本遗憾的命运，活出全新成长轨迹。</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>全家施压：我反手签了过户合同</x:v>
+        <x:v>黑蛋孵出山海神兽后我无敌了</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>09-08 16:58</x:v>
+        <x:v>09-06 18:00</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E19" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F19" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G19" s="11" t="n">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="H19" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str">
         <x:v>其他</x:v>
@@ -3507,58 +3592,52 @@
       <x:c r="J19" s="11" t="str"/>
       <x:c r="K19" s="11" t="str"/>
       <x:c r="L19" s="10" t="str">
-        <x:v>灵川剧场</x:v>
+        <x:v>抱月剧场</x:v>
       </x:c>
       <x:c r="M19" s="10" t="str">
-        <x:v>儿子儿媳多次提议我搬回乡下养老，将城里的宽敞住房腾出来给女方父母长期居住。我笑着点头应下，转头便将这套三室朝南的江景房产挂牌出售，最终成交二百八十万元。我随即购置了一套一室一厅的小户型，更换门锁后独自入住。他们上门索要钥匙，我没有开门。名下房产我自有主张，谁也别想插手安排。</x:v>
+        <x:v>寒门少年李初七攒了三年银子，仍买不起最低等的兽蛋。一次意外，他在后山捡到一枚黑蛋，孵出的煤球又小又馋，偏偏爱啃铜钱。可每吞下一缕兽息，它便能复现对手的能力。县学测灵那日，测灵石骤然亮起黑光，群兽伏地。所有人都以为他只是走了好运，只有陆远山想起古籍中的禁忌——黑光现，万兽伏。煤球究竟是什么？</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>美颜系统开挂，大佬全跪下</x:v>
+        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>09-09 00:10</x:v>
+        <x:v>2026-09-05</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G20" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H20" s="11" t="n">
-        <x:v>172</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H20" s="11" t="str"/>
       <x:c r="I20" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J20" s="11" t="str"/>
       <x:c r="K20" s="11" t="str"/>
-      <x:c r="L20" s="10" t="str">
-        <x:v>御儿</x:v>
-      </x:c>
-      <x:c r="M20" s="10" t="str">
-        <x:v>曾因外形饱受非议的米珂华丽转身，蜕变得耀眼又夺目。从前对她嗤之以鼻的蒋少开始频频在意，素来冷眼毒舌的陆总不知不觉深陷其中，连一向克己的商界大佬也为她打破原则。米珂凭智商与手腕周旋于众人之间，上演一场势均力敌的情感博弈。没有俗套的救赎，只有双向的拉扯。看一众高高在上的精英暗自较劲、步步沉沦，心甘情愿为她卸下防备。</x:v>
-      </x:c>
+      <x:c r="L20" s="10" t="str"/>
+      <x:c r="M20" s="10" t="str"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>不靠谱爸妈很靠谱</x:v>
+        <x:v>离家十年，回来女儿被换了</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>09-09 11:08</x:v>
+        <x:v>09-09 00:04</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
         <x:v>5</x:v>
@@ -3570,10 +3649,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G21" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H21" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="I21" s="10" t="str">
         <x:v>其他</x:v>
@@ -3581,21 +3660,21 @@
       <x:c r="J21" s="11" t="str"/>
       <x:c r="K21" s="11" t="str"/>
       <x:c r="L21" s="10" t="str">
-        <x:v>灵妹儿</x:v>
+        <x:v>魔方影视（上剧版</x:v>
       </x:c>
       <x:c r="M21" s="10" t="str">
-        <x:v>外表张扬的年轻夫妻在冬夜救下女婴林小小，用十七年的辛勤劳动和无条件陪伴，为她撑起温暖的家。曾经成绩落后的林小小，在父母的鼓励下重新学习，一步步成长为优秀学生。面对亲生家庭带来的资源与人生选择，她也开始重新理解血缘、养育与责任。当外界的误解影响到父母的生活，林小小决定勇敢站出来，用事实守护家人，也用努力证明真正的爱，是尊重、陪伴和彼此成就。</x:v>
+        <x:v>程砚宁完成长期绝密任务归来，满心想要弥补亲情，却发现家中早已物是人非。身边亲近之人被私欲蒙蔽，制造重重骗局，试图侵占她的事业与财富。面对接连而来的算计与危机，她凭借过人的魄力与智慧步步拆解阴谋，联合正义力量搜集证据，厘清全部是非纠葛。在守护自身事业的同时，她放下过往伤痛，投身公益，完成自我和解，迎来属于自己的全新人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>末世来临，我靠囤货种田丰衣足食</x:v>
+        <x:v>重生三天前，我用水泥封死地下室</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>09-09 15:30</x:v>
+        <x:v>09-09 09:28</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
         <x:v>5</x:v>
@@ -3607,10 +3686,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G22" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H22" s="11" t="n">
-        <x:v>344</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str">
         <x:v>其他</x:v>
@@ -3618,36 +3697,36 @@
       <x:c r="J22" s="11" t="str"/>
       <x:c r="K22" s="11" t="str"/>
       <x:c r="L22" s="10" t="str">
-        <x:v>渲渲动画</x:v>
+        <x:v>忘忧剧场</x:v>
       </x:c>
       <x:c r="M22" s="10" t="str">
-        <x:v>吴真真带着末世惨死的记忆重生，抢下秘宝空间，囤积海量物资，提前规避天灾人祸。她意外发现家人同样重生，一家人携手为末日做足准备。灾变如期而至，病毒、台风、极寒轮番降临。她机缘结识实力强悍的谢穆辰，二人从互相试探到并肩而立。面对凶悍恶徒与重重危机，吴真真依靠空间与智慧守护至亲，谢穆辰以自身力量与之守望相助，在满目疮痍的末世里，拼尽全力守住生存希望，奔赴属于他们的新生。</x:v>
+        <x:v>阮清重生回被保姆王妈一家害死的三天前，前世她因心善引狼入室，保姆全家蜗居别墅地下室偷窃投毒，最终惨遭勒死。重生后她假装不知，趁王妈外出时用水泥将地下室彻底封死。警方破墙后，五具尸体令真相大白，王妈因盗窃、投毒被判十五年。阮清与父母团聚，恶人终得恶报，她重获新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>征地我秒签跑路，全村笑我半年</x:v>
+        <x:v>全家施压：我反手签了过户合同</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>09-10 11:30</x:v>
+        <x:v>09-08 16:58</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G23" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H23" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
         <x:v>其他</x:v>
@@ -3655,71 +3734,73 @@
       <x:c r="J23" s="11" t="str"/>
       <x:c r="K23" s="11" t="str"/>
       <x:c r="L23" s="10" t="str">
-        <x:v>小六动漫</x:v>
+        <x:v>灵川剧场</x:v>
       </x:c>
       <x:c r="M23" s="10" t="str">
-        <x:v>赵家湾迎来高速征地，村民受村长赵德厚鼓动抱团拒签，妄想抬价拿到四百五十万补偿。林远察觉当地岩溶地质暗藏线路改线风险，不顾全村嘲讽，果断签下312万补偿款，带父母搬离老家。后续高速果真改线，全村一分补偿落空。曾经嘲笑林远的村民陷入债务困境，赵德厚登门求助，林远守住底线，一家人握紧安稳生活，告诫众人抉择要靠自己。</x:v>
+        <x:v>儿子儿媳多次提议我搬回乡下养老，将城里的宽敞住房腾出来给女方父母长期居住。我笑着点头应下，转头便将这套三室朝南的江景房产挂牌出售，最终成交二百八十万元。我随即购置了一套一室一厅的小户型，更换门锁后独自入住。他们上门索要钥匙，我没有开门。名下房产我自有主张，谁也别想插手安排。</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>大四毕业季，别人忙着答辩我忙着吐！</x:v>
+        <x:v>不靠谱爸妈很靠谱</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>2026-09-04</x:v>
+        <x:v>09-09 11:08</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G24" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H24" s="11" t="str"/>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H24" s="11" t="n">
+        <x:v>73</x:v>
+      </x:c>
       <x:c r="I24" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="J24" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K24" s="11" t="str">
-        <x:v>0.00</x:v>
-      </x:c>
-      <x:c r="L24" s="10" t="str"/>
-      <x:c r="M24" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="J24" s="11" t="str"/>
+      <x:c r="K24" s="11" t="str"/>
+      <x:c r="L24" s="10" t="str">
+        <x:v>灵妹儿</x:v>
+      </x:c>
+      <x:c r="M24" s="10" t="str">
+        <x:v>外表张扬的年轻夫妻在冬夜救下女婴林小小，用十七年的辛勤劳动和无条件陪伴，为她撑起温暖的家。曾经成绩落后的林小小，在父母的鼓励下重新学习，一步步成长为优秀学生。面对亲生家庭带来的资源与人生选择，她也开始重新理解血缘、养育与责任。当外界的误解影响到父母的生活，林小小决定勇敢站出来，用事实守护家人，也用努力证明真正的爱，是尊重、陪伴和彼此成就。</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>重生后我守住全村</x:v>
+        <x:v>美颜系统开挂，大佬全跪下</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>09-10 08:08</x:v>
+        <x:v>09-09 00:10</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G25" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H25" s="11" t="n">
-        <x:v>129</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str">
         <x:v>其他</x:v>
@@ -3727,10 +3808,10 @@
       <x:c r="J25" s="11" t="str"/>
       <x:c r="K25" s="11" t="str"/>
       <x:c r="L25" s="10" t="str">
-        <x:v>金果漫剧</x:v>
+        <x:v>御儿</x:v>
       </x:c>
       <x:c r="M25" s="10" t="str">
-        <x:v>70年代冬，赵满仓在父亲离世后重回鼠灾前八天。面对家中骤变，他选择先护住亲人，带着前世经验迁入碾坊，储粮备药，筑墙防鼠，设点防疫。灾情来临时，他联合李杏儿，刘石头和乡亲稳住村庄，并用账册与规矩澄清父亲名誉。风雪过后，黎家沟建起防鼠坊，猫舍和净粮地窖，众人也在互助中迎来新生。</x:v>
+        <x:v>曾因外形饱受非议的米珂华丽转身，蜕变得耀眼又夺目。从前对她嗤之以鼻的蒋少开始频频在意，素来冷眼毒舌的陆总不知不觉深陷其中，连一向克己的商界大佬也为她打破原则。米珂凭智商与手腕周旋于众人之间，上演一场势均力敌的情感博弈。没有俗套的救赎，只有双向的拉扯。看一众高高在上的精英暗自较劲、步步沉沦，心甘情愿为她卸下防备。</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -3738,44 +3819,50 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>假老板娘遇上真董事长</x:v>
+        <x:v>末世来临，我靠囤货种田丰衣足食</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>09-09 15:30</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E26" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F26" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G26" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E26" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F26" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G26" s="11" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H26" s="11" t="str"/>
+      <x:c r="H26" s="11" t="n">
+        <x:v>344</x:v>
+      </x:c>
       <x:c r="I26" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J26" s="11" t="str"/>
       <x:c r="K26" s="11" t="str"/>
-      <x:c r="L26" s="10" t="str"/>
-      <x:c r="M26" s="10" t="str"/>
+      <x:c r="L26" s="10" t="str">
+        <x:v>渲渲动画</x:v>
+      </x:c>
+      <x:c r="M26" s="10" t="str">
+        <x:v>吴真真带着末世惨死的记忆重生，抢下秘宝空间，囤积海量物资，提前规避天灾人祸。她意外发现家人同样重生，一家人携手为末日做足准备。灾变如期而至，病毒、台风、极寒轮番降临。她机缘结识实力强悍的谢穆辰，二人从互相试探到并肩而立。面对凶悍恶徒与重重危机，吴真真依靠空间与智慧守护至亲，谢穆辰以自身力量与之守望相助，在满目疮痍的末世里，拼尽全力守住生存希望，奔赴属于他们的新生。</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>迟来深情皆是刃</x:v>
+        <x:v>征地我秒签跑路，全村笑我半年</x:v>
       </x:c>
       <x:c r="C27" s="11" t="str">
-        <x:v>09-09 10:00</x:v>
+        <x:v>09-10 11:30</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
         <x:v>5</x:v>
@@ -3784,10 +3871,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G27" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H27" s="11" t="n">
-        <x:v>184</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I27" s="10" t="str">
         <x:v>其他</x:v>
@@ -3795,24 +3882,24 @@
       <x:c r="J27" s="11" t="str"/>
       <x:c r="K27" s="11" t="str"/>
       <x:c r="L27" s="10" t="str">
-        <x:v>展瓦-佩云看剧</x:v>
+        <x:v>小六动漫</x:v>
       </x:c>
       <x:c r="M27" s="10" t="str">
-        <x:v>天才芯片科研人姜莱，隐去光芒，在婚姻里默默付出四年，却遭遇丈夫沈荀的背叛与冷待。看清现实的她挣脱窒息的婚姻，撕下普通家庭主妇的伪装，重拾科研理想。面对丈夫、情敌的百般算计，她冷静反击。在自研芯重大项目竞标舞台上，姜莱展露真实实力，完成华丽逆袭，实现自我价值。过往伤痛化作成长力量，她告别糟糕的旧生活，向着事业与崭新的人生大步奔赴，迎来属于自己的光明未来。</x:v>
+        <x:v>赵家湾迎来高速征地，村民受村长赵德厚鼓动抱团拒签，妄想抬价拿到四百五十万补偿。林远察觉当地岩溶地质暗藏线路改线风险，不顾全村嘲讽，果断签下312万补偿款，带父母搬离老家。后续高速果真改线，全村一分补偿落空。曾经嘲笑林远的村民陷入债务困境，赵德厚登门求助，林远守住底线，一家人握紧安稳生活，告诫众人抉择要靠自己。</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="11" t="n">
-        <x:v>77</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>除夕夜，我被直升机接回前夫家</x:v>
+        <x:v>大四毕业季，别人忙着答辩我忙着吐！</x:v>
       </x:c>
       <x:c r="C28" s="11" t="str">
-        <x:v>09-10 08:00</x:v>
+        <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
         <x:v>5</x:v>
@@ -3821,32 +3908,30 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G28" s="11" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H28" s="11" t="n">
-        <x:v>78</x:v>
-      </x:c>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H28" s="11" t="str"/>
       <x:c r="I28" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J28" s="11" t="str"/>
-      <x:c r="K28" s="11" t="str"/>
-      <x:c r="L28" s="10" t="str">
-        <x:v>小狐狸剧场</x:v>
-      </x:c>
-      <x:c r="M28" s="10" t="str">
-        <x:v>除夕夜，一架直升机将顾晚棠从苏州小院接回豪门。十九年前，她背负罪名被傅家扫地出门，与幼子傅知衍骨肉分离。如今化名林棠的她，已是高端苏绣“棠记”的主理人，归来只为讨一个公道。宴会上，面对伪善的沈若薇与家族胁迫，她亮出证据步步为营。真相浮出水面，儿子终知愧疚。然而傅老夫人觊觎棠记，设局破坏。顾晚棠能否守住心血，彻底挣脱过往枷锁？</x:v>
-      </x:c>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="J28" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K28" s="11" t="str">
+        <x:v>0.00</x:v>
+      </x:c>
+      <x:c r="L28" s="10" t="str"/>
+      <x:c r="M28" s="10" t="str"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>赶海人生：重回1983小渔村</x:v>
+        <x:v>重生后我守住全村</x:v>
       </x:c>
       <x:c r="C29" s="11" t="str">
-        <x:v>09-10 08:55</x:v>
+        <x:v>09-10 08:08</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
         <x:v>4</x:v>
@@ -3858,10 +3943,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G29" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H29" s="11" t="n">
-        <x:v>158</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="I29" s="10" t="str">
         <x:v>其他</x:v>
@@ -3869,73 +3954,67 @@
       <x:c r="J29" s="11" t="str"/>
       <x:c r="K29" s="11" t="str"/>
       <x:c r="L29" s="10" t="str">
-        <x:v>梦落漫漫</x:v>
+        <x:v>金果漫剧</x:v>
       </x:c>
       <x:c r="M29" s="10" t="str">
-        <x:v>前世杨建国跳海离世，意外重生回到1983年东沟小渔村。这一年开海祭龙王，妻子即将遭遇毒蛇险境，家中穷困潦倒，伯父还妄图霸占自家渔船。曾经的街溜子幡然醒悟，凭借超前记忆踏海赶海，捕捞对虾、鲍鱼，对抗邻里刁难，守护妻儿老小，在汹涌海潮之中改写一家人贫苦命运。</x:v>
+        <x:v>70年代冬，赵满仓在父亲离世后重回鼠灾前八天。面对家中骤变，他选择先护住亲人，带着前世经验迁入碾坊，储粮备药，筑墙防鼠，设点防疫。灾情来临时，他联合李杏儿，刘石头和乡亲稳住村庄，并用账册与规矩澄清父亲名誉。风雪过后，黎家沟建起防鼠坊，猫舍和净粮地窖，众人也在互助中迎来新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="11" t="n">
-        <x:v>37</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>张兰芬重生记</x:v>
+        <x:v>假老板娘遇上真董事长</x:v>
       </x:c>
       <x:c r="C30" s="11" t="str">
-        <x:v>09-05 17:00</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G30" s="11" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H30" s="11" t="n">
-        <x:v>176</x:v>
-      </x:c>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H30" s="11" t="str"/>
       <x:c r="I30" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J30" s="11" t="str"/>
       <x:c r="K30" s="11" t="str"/>
-      <x:c r="L30" s="10" t="str">
-        <x:v>璀璨Ai剧场</x:v>
-      </x:c>
-      <x:c r="M30" s="10" t="str">
-        <x:v>张兰芬操劳半生，是旁人羡慕的当家主母。她为李家养育四子两女，持家有道、将家中大小事务打理得井井有条。半生付出尽数落空，张兰芬郁结于心，最终含恨病逝医院。一朝重生，她回到所有遗憾尚未发生之时，彻底看透人心，决意放下执念，好好为自己活一次。</x:v>
-      </x:c>
+      <x:c r="L30" s="10" t="str"/>
+      <x:c r="M30" s="10" t="str"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>人间烟火遇见你</x:v>
+        <x:v>赶海人生：重回1983小渔村</x:v>
       </x:c>
       <x:c r="C31" s="11" t="str">
-        <x:v>09-05 21:40</x:v>
+        <x:v>09-10 08:55</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G31" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H31" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="I31" s="10" t="str">
         <x:v>其他</x:v>
@@ -3943,10 +4022,10 @@
       <x:c r="J31" s="11" t="str"/>
       <x:c r="K31" s="11" t="str"/>
       <x:c r="L31" s="10" t="str">
-        <x:v>大刀剧场</x:v>
+        <x:v>梦落漫漫</x:v>
       </x:c>
       <x:c r="M31" s="10" t="str">
-        <x:v>经历丧夫的林晚晴，故意坐着轮椅去相亲，以此试探相亲对象的人品。接连遭遇刻薄势利的追求者，直到遇见摆摊厨师周庭远。他不因轮椅与过往经历轻视她，危难时刻挺身护她，待人真诚憨厚。走访周家，面对邻里闲言碎语与家人顾虑，周庭远母子始终坚定维护林晚晴。褪去伪装，两人双向靠近，冲破世俗偏见，收获烟火气满满的真挚爱情。</x:v>
+        <x:v>前世杨建国跳海离世，意外重生回到1983年东沟小渔村。这一年开海祭龙王，妻子即将遭遇毒蛇险境，家中穷困潦倒，伯父还妄图霸占自家渔船。曾经的街溜子幡然醒悟，凭借超前记忆踏海赶海，捕捞对虾、鲍鱼，对抗邻里刁难，守护妻儿老小，在汹涌海潮之中改写一家人贫苦命运。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -27032,7 +27111,7 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>857</x:v>
+        <x:v>859</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
         <x:v>51.3%</x:v>
@@ -27057,7 +27136,7 @@
         <x:v>342</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>20.5%</x:v>
+        <x:v>20.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
@@ -27081,10 +27160,10 @@
         <x:v>30-49集</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>11%</x:v>
+        <x:v>11.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -27117,7 +27196,7 @@
         <x:v>522</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>33.9%</x:v>
+        <x:v>33.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
@@ -27144,7 +27223,7 @@
         <x:v>730</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>43.7%</x:v>
+        <x:v>43.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -27196,10 +27275,10 @@
         <x:v>战神/异能/爽文</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>8.4%</x:v>
+        <x:v>8.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -27240,10 +27319,10 @@
         <x:v>都市职场</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>4.2%</x:v>
+        <x:v>4.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="22" customHeight="1">
@@ -27289,7 +27368,7 @@
         <x:v>上榜27次</x:v>
       </x:c>
       <x:c r="B31" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C31" s="11" t="str">
         <x:v>0.1%</x:v>
@@ -27300,7 +27379,7 @@
         <x:v>上榜26次</x:v>
       </x:c>
       <x:c r="B32" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C32" s="11" t="str">
         <x:v>0.1%</x:v>
@@ -27333,10 +27412,10 @@
         <x:v>上榜22次</x:v>
       </x:c>
       <x:c r="B35" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C35" s="11" t="str">
-        <x:v>0.1%</x:v>
+        <x:v>0.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -27344,7 +27423,7 @@
         <x:v>上榜21次</x:v>
       </x:c>
       <x:c r="B36" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C36" s="11" t="str">
         <x:v>0.1%</x:v>
@@ -27421,7 +27500,7 @@
         <x:v>上榜14次</x:v>
       </x:c>
       <x:c r="B43" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C43" s="11" t="str">
         <x:v>0.7%</x:v>
@@ -27443,10 +27522,10 @@
         <x:v>上榜12次</x:v>
       </x:c>
       <x:c r="B45" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C45" s="11" t="str">
-        <x:v>1.0%</x:v>
+        <x:v>0.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -27465,7 +27544,7 @@
         <x:v>上榜10次</x:v>
       </x:c>
       <x:c r="B47" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C47" s="11" t="str">
         <x:v>1.3%</x:v>
@@ -27476,10 +27555,10 @@
         <x:v>上榜9次</x:v>
       </x:c>
       <x:c r="B48" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C48" s="11" t="str">
-        <x:v>1.8%</x:v>
+        <x:v>1.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -27487,10 +27566,10 @@
         <x:v>上榜8次</x:v>
       </x:c>
       <x:c r="B49" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C49" s="11" t="str">
-        <x:v>2.7%</x:v>
+        <x:v>2.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -27509,10 +27588,10 @@
         <x:v>上榜6次</x:v>
       </x:c>
       <x:c r="B51" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C51" s="11" t="str">
-        <x:v>3.2%</x:v>
+        <x:v>3.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -27520,7 +27599,7 @@
         <x:v>上榜5次</x:v>
       </x:c>
       <x:c r="B52" s="11" t="n">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C52" s="11" t="str">
         <x:v>4.5%</x:v>
@@ -27542,10 +27621,10 @@
         <x:v>上榜3次</x:v>
       </x:c>
       <x:c r="B54" s="11" t="n">
-        <x:v>184</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C54" s="11" t="str">
-        <x:v>11.0%</x:v>
+        <x:v>11.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -27553,10 +27632,10 @@
         <x:v>上榜2次</x:v>
       </x:c>
       <x:c r="B55" s="11" t="n">
-        <x:v>326</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="C55" s="11" t="str">
-        <x:v>19.5%</x:v>
+        <x:v>19.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -27564,7 +27643,7 @@
         <x:v>上榜1次</x:v>
       </x:c>
       <x:c r="B56" s="11" t="n">
-        <x:v>728</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="C56" s="11" t="str">
         <x:v>43.5%</x:v>
@@ -27594,7 +27673,7 @@
         <x:v>1135</x:v>
       </x:c>
       <x:c r="C60" s="11" t="str">
-        <x:v>67.9%</x:v>
+        <x:v>67.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -27602,7 +27681,7 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B61" s="11" t="n">
-        <x:v>526</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="C61" s="11" t="str">
         <x:v>31.5%</x:v>
@@ -27648,10 +27727,10 @@
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
+        <x:v>番荔枝剧场</x:v>
       </x:c>
       <x:c r="B67" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C67" s="11" t="str">
         <x:v>1.1%</x:v>
@@ -27659,7 +27738,7 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="10" t="str">
-        <x:v>番荔枝剧场</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="B68" s="11" t="n">
         <x:v>59</x:v>
@@ -27758,7 +27837,7 @@
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>在下轻北</x:v>
       </x:c>
       <x:c r="B77" s="11" t="n">
         <x:v>27</x:v>
@@ -27769,10 +27848,10 @@
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="10" t="str">
-        <x:v>在下轻北</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="B78" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C78" s="11" t="str">
         <x:v>0.5%</x:v>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R70611ef274164003"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="R503fc5b290d84dce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="R908b90529b79497c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="Rc9cf17d3573d4f5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top剧重点跟踪" sheetId="5" r:id="Rf842e827b8fd4a9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="6" r:id="R1d72bfaea2ca4d1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="7" r:id="Rac314ca5c2a24b5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="8" r:id="Rb3436fc8d4e14961"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="9" r:id="Rd253fe1bde5f4b59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R1855fb0984df4879"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="R98ea4b9401794981"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="R10d32ae6ee5b46ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="Rf8b2c838605346a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP20剧重点跟踪" sheetId="5" r:id="R20ae3fde751c4700"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="6" r:id="R426efd3d9b2d434e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="7" r:id="R83453d8a29434911"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="8" r:id="Rd30ba2c0e43d4710"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="9" r:id="R0a1f9334f60841fb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1165,7 +1165,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B2" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
         <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
@@ -1202,7 +1202,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
         <x:v>小妹初长成</x:v>
@@ -1233,13 +1233,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
-        <x:v>乡宴见人心</x:v>
+        <x:v>婚礼当天我不嫁了</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>09-13 17:12</x:v>
+        <x:v>09-14 09:00</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str"/>
       <x:c r="F4" s="11" t="str"/>
@@ -1250,19 +1250,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I4" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="J4" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K4" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L4" s="11" t="str">
-        <x:v>黑白动漫</x:v>
+        <x:v>大梨看剧</x:v>
       </x:c>
       <x:c r="M4" s="10" t="str">
-        <x:v>高满仓在赵家大院办了八年流水席，十里八村都认他的手艺。眼看生意越来越旺，院主赵金贵突然把租金翻倍，还要按桌抽钱。高满仓干脆带着人和家伙搬进镇外的废米厂，从头再来。赵金贵以为守着大院就守住了客人，靠低价抢生意，却越省越狠。一边是稳稳当当把席办好，一边是亲手砸掉自己的口碑，这场较量最后看的是院子，还是人心。</x:v>
+        <x:v>婚礼当天，沈清面对不同婚俗，勇敢表达自我，果断选择结束婚约。哥哥和好友支持，她用法律与智慧处理彩礼、名誉及后续事宜，守护尊严与安全。成长历程中，她开启独立新生活，搬入温暖新家，与家人朋友相伴成长。故事传递出，婚姻应建立在尊重、平等和真诚之上，表达选择，才能拥抱更好的未来。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1270,13 +1270,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>34</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
-        <x:v>427元扳倒老油条</x:v>
+        <x:v>长工失牛，焉知非福</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>09-13 16:00</x:v>
+        <x:v>2026-09-13</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str"/>
       <x:c r="F5" s="11" t="str"/>
@@ -1286,34 +1286,28 @@
       <x:c r="H5" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I5" s="11" t="n">
-        <x:v>55</x:v>
-      </x:c>
+      <x:c r="I5" s="11" t="str"/>
       <x:c r="J5" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K5" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L5" s="11" t="str">
-        <x:v>安然然</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="str">
-        <x:v>职场新人许宁向老员工马丽芬讨要427元代垫外卖款，反遭易绑架马丽芬交出饭钱后怀恨在心，利用行政特权私吞福利，并在组织团餐时疏同事差价许宁按兵不动收集证据，最终将马丽芬长期贪占两万余元的行径在老板曝光的照片中马丽芬被直接开除，许宁成功维护了职场底线。</x:v>
-      </x:c>
+      <x:c r="L5" s="11" t="str"/>
+      <x:c r="M5" s="10" t="str"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>婚礼当天我不嫁了</x:v>
+        <x:v>427元扳倒老油条</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>09-14 09:00</x:v>
+        <x:v>09-13 16:00</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str"/>
       <x:c r="F6" s="11" t="str"/>
@@ -1324,19 +1318,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I6" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J6" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K6" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L6" s="11" t="str">
-        <x:v>大梨看剧</x:v>
+        <x:v>安然然</x:v>
       </x:c>
       <x:c r="M6" s="10" t="str">
-        <x:v>婚礼当天，沈清面对不同婚俗，勇敢表达自我，果断选择结束婚约。哥哥和好友支持，她用法律与智慧处理彩礼、名誉及后续事宜，守护尊严与安全。成长历程中，她开启独立新生活，搬入温暖新家，与家人朋友相伴成长。故事传递出，婚姻应建立在尊重、平等和真诚之上，表达选择，才能拥抱更好的未来。</x:v>
+        <x:v>职场新人许宁向老员工马丽芬讨要427元代垫外卖款，反遭易绑架马丽芬交出饭钱后怀恨在心，利用行政特权私吞福利，并在组织团餐时疏同事差价许宁按兵不动收集证据，最终将马丽芬长期贪占两万余元的行径在老板曝光的照片中马丽芬被直接开除，许宁成功维护了职场底线。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1344,7 +1338,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>37</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
         <x:v>重生80，救下神雕后我带村民走出大山</x:v>
@@ -1381,7 +1375,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
         <x:v>河箱送福来</x:v>
@@ -1418,13 +1412,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>76</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
-        <x:v>员工跑路我扩店</x:v>
+        <x:v>乡宴见人心</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>09-13 08:58</x:v>
+        <x:v>09-13 17:12</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str"/>
       <x:c r="F9" s="11" t="str"/>
@@ -1435,19 +1429,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I9" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J9" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K9" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="L9" s="11" t="str">
-        <x:v>大梨看剧</x:v>
+        <x:v>黑白动漫</x:v>
       </x:c>
       <x:c r="M9" s="10" t="str">
-        <x:v>林辰经营天力健身馆，年终为员工每人发放五万元奖金。几位教练希望获得更多发展空间，与林辰理念产生分歧，决定在隔壁开设新馆，一场实力较量就此展开。林辰选择升级场地、引进专业团队，并提拔刘阿姨担任店长。正月初七，千名会员到场，用选择见证真诚服务的价值。</x:v>
+        <x:v>高满仓在赵家大院办了八年流水席，十里八村都认他的手艺。眼看生意越来越旺，院主赵金贵突然把租金翻倍，还要按桌抽钱。高满仓干脆带着人和家伙搬进镇外的废米厂，从头再来。赵金贵以为守着大院就守住了客人，靠低价抢生意，却越省越狠。一边是稳稳当当把席办好，一边是亲手砸掉自己的口碑，这场较量最后看的是院子，还是人心。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1455,13 +1449,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
-        <x:v>我赚上千万跟爸妈说50W，隔天就被找上门</x:v>
+        <x:v>员工跑路我扩店</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>09-13 08:00</x:v>
+        <x:v>09-13 08:58</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str"/>
       <x:c r="F10" s="11" t="str"/>
@@ -1472,19 +1466,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I10" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J10" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K10" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="L10" s="11" t="str">
-        <x:v>至尊爽剧社</x:v>
+        <x:v>大梨看剧</x:v>
       </x:c>
       <x:c r="M10" s="10" t="str">
-        <x:v>三十二岁那年，贺川用六年孤注一掷的钻研，换来了七千六百万的回报。可财富还没捂热，先尝到的却是亲人无度的索取。他谎称只赚五十万，叮嘱保密，却挡不住消息走漏。隔天登门的亲戚不止要借钱买房，更联手外人盗用他的身份资料，试图冒名签约、伪造担保债务。贺川报警取证，警方介入追回大部分资金，涉案者包括部分机构人员均承担了法律责任，这笔帐，能否算清？</x:v>
+        <x:v>林辰经营天力健身馆，年终为员工每人发放五万元奖金。几位教练希望获得更多发展空间，与林辰理念产生分歧，决定在隔壁开设新馆，一场实力较量就此展开。林辰选择升级场地、引进专业团队，并提拔刘阿姨担任店长。正月初七，千名会员到场，用选择见证真诚服务的价值。</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1492,13 +1486,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C11" s="10" t="str">
-        <x:v>长工失牛，焉知非福</x:v>
+        <x:v>我赚上千万跟爸妈说50W，隔天就被找上门</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>2026-09-13</x:v>
+        <x:v>09-13 08:00</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str"/>
       <x:c r="F11" s="11" t="str"/>
@@ -1508,28 +1502,34 @@
       <x:c r="H11" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I11" s="11" t="str"/>
+      <x:c r="I11" s="11" t="n">
+        <x:v>78</x:v>
+      </x:c>
       <x:c r="J11" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K11" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L11" s="11" t="str"/>
-      <x:c r="M11" s="10" t="str"/>
+      <x:c r="L11" s="11" t="str">
+        <x:v>至尊爽剧社</x:v>
+      </x:c>
+      <x:c r="M11" s="10" t="str">
+        <x:v>三十二岁那年，贺川用六年孤注一掷的钻研，换来了七千六百万的回报。可财富还没捂热，先尝到的却是亲人无度的索取。他谎称只赚五十万，叮嘱保密，却挡不住消息走漏。隔天登门的亲戚不止要借钱买房，更联手外人盗用他的身份资料，试图冒名签约、伪造担保债务。贺川报警取证，警方介入追回大部分资金，涉案者包括部分机构人员均承担了法律责任，这笔帐，能否算清？</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
-        <x:v>离婚那天我多了个痞帅老爹</x:v>
+        <x:v>风雪边界</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>2026-09-13</x:v>
+        <x:v>09-14 03:01</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str"/>
       <x:c r="F12" s="11" t="str"/>
@@ -1537,30 +1537,36 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H12" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="I12" s="11" t="str"/>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I12" s="11" t="n">
+        <x:v>53</x:v>
+      </x:c>
       <x:c r="J12" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K12" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="L12" s="11" t="str"/>
-      <x:c r="M12" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L12" s="11" t="str">
+        <x:v>腿毛漫漫</x:v>
+      </x:c>
+      <x:c r="M12" s="10" t="str">
+        <x:v>高原补给站老板岑夏坚持完整安全套餐，却遭企业负责人质疑价格，团队转投低价营地。暴雪突至，危机逼近，岑夏仍坚守原则，以专业判断协助应急处置，也让众人重新理解安全的价值。真正昂贵的不是房费，而是忽视风险的代价。敬畏自然、尊重专业，安全永远值得认真对待。</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B13" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
-        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
+        <x:v>离婚那天我多了个痞帅老爹</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
-        <x:v>09-13 08:00</x:v>
+        <x:v>2026-09-13</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str"/>
       <x:c r="F13" s="11" t="str"/>
@@ -1568,36 +1574,30 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H13" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="I13" s="11" t="n">
-        <x:v>64</x:v>
-      </x:c>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I13" s="11" t="str"/>
       <x:c r="J13" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K13" s="10" t="str">
-        <x:v>古装宫廷</x:v>
-      </x:c>
-      <x:c r="L13" s="11" t="str">
-        <x:v>心动漫剧场</x:v>
-      </x:c>
-      <x:c r="M13" s="10" t="str">
-        <x:v>大晋七公主沈令仪，自幼被冷落于听竹宫，沉默藏锋，苟全性命。宫宴之上，太子带回的秦照雪笑盈盈提议将她送去北狄和亲。满殿以为皇帝会点头，他却掷出“废太子”三字。一夜之间，沈令仪被推到台前。北狄求和的急报恰在此时入京——与她方才所言分毫不差。可当她回望母亲遗下的那半卷秘策时，才发现这局棋，早在二十年前就已落子。</x:v>
-      </x:c>
+        <x:v>家庭伦理 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="L13" s="11" t="str"/>
+      <x:c r="M13" s="10" t="str"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B14" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
-        <x:v>风雪边界</x:v>
+        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>09-14 03:01</x:v>
+        <x:v>09-13 08:00</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str"/>
       <x:c r="F14" s="11" t="str"/>
@@ -1605,22 +1605,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H14" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I14" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J14" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K14" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="L14" s="11" t="str">
-        <x:v>腿毛漫漫</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="M14" s="10" t="str">
-        <x:v>高原补给站老板岑夏坚持完整安全套餐，却遭企业负责人质疑价格，团队转投低价营地。暴雪突至，危机逼近，岑夏仍坚守原则，以专业判断协助应急处置，也让众人重新理解安全的价值。真正昂贵的不是房费，而是忽视风险的代价。敬畏自然、尊重专业，安全永远值得认真对待。</x:v>
+        <x:v>大晋七公主沈令仪，自幼被冷落于听竹宫，沉默藏锋，苟全性命。宫宴之上，太子带回的秦照雪笑盈盈提议将她送去北狄和亲。满殿以为皇帝会点头，他却掷出“废太子”三字。一夜之间，沈令仪被推到台前。北狄求和的急报恰在此时入京——与她方才所言分毫不差。可当她回望母亲遗下的那半卷秘策时，才发现这局棋，早在二十年前就已落子。</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1628,7 +1628,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B15" s="11" t="n">
-        <x:v>43</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
         <x:v>四个崽崽瞒不住了</x:v>
@@ -1642,7 +1642,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H15" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I15" s="11" t="n">
         <x:v>124</x:v>
@@ -1665,814 +1665,166 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C16" s="10" t="str">
-        <x:v>那朵胸花，被丢进垃圾桶</x:v>
+        <x:v>结婚八年，我娶的原来是仇人的女儿</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
-        <x:v>09-14 21:00</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str"/>
       <x:c r="F16" s="11" t="str"/>
       <x:c r="G16" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H16" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I16" s="11" t="n">
-        <x:v>65</x:v>
-      </x:c>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I16" s="11" t="str"/>
       <x:c r="J16" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K16" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L16" s="11" t="str">
-        <x:v>临渊剧场</x:v>
-      </x:c>
-      <x:c r="M16" s="10" t="str">
-        <x:v>接亲当天，新郎踹开新娘房门。新娘护着前任，前任用胸花挑衅，婚礼当场取消。她求他，他放完整视频反击。前任欠债跑路，债主堵门，新娘崩溃。他换锁卖房，一笔账一笔账清。可账单会说话，旧爱跑不了，这条线，该断了。</x:v>
-      </x:c>
+        <x:v>家庭伦理 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="L16" s="11" t="str"/>
+      <x:c r="M16" s="10" t="str"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="str">
-        <x:v>持续在榜</x:v>
+        <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C17" s="10" t="str">
-        <x:v>晚风吹散旧姻尘第一季</x:v>
+        <x:v>长工失牛，焉知非福</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
-        <x:v>09-13 18:00</x:v>
-      </x:c>
-      <x:c r="E17" s="11" t="str"/>
-      <x:c r="F17" s="11" t="str"/>
-      <x:c r="G17" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H17" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I17" s="11" t="n">
-        <x:v>145</x:v>
-      </x:c>
+        <x:v>2026-09-13</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="str">
+        <x:v>↑46位</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="str"/>
+      <x:c r="H17" s="11" t="str"/>
+      <x:c r="I17" s="11" t="str"/>
       <x:c r="J17" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K17" s="10" t="str">
-        <x:v>年代怀旧 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="L17" s="11" t="str">
-        <x:v>小沫漫剧</x:v>
-      </x:c>
-      <x:c r="M17" s="10" t="str">
-        <x:v>庄言前世卑微讨好，却被亲手养大的儿子拔掉氧气管。重生回订婚当夜，面对为白月光顾前缺席宴会的夏晚，他当众退婚、脱离庄家，转身登上恋爱综艺，只为自己活一次。谁料影后初恋姜宁高调追回，夏晚的小姨陆烟也步步逼近、直球示爱。夏晚看着他彻底转身，终于乱了心。前任后悔、初恋回头、小姨强势夺爱，庄言最终会把真心交给谁</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L17" s="11" t="str"/>
+      <x:c r="M17" s="10" t="str"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="str">
-        <x:v>持续在榜</x:v>
+        <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C18" s="10" t="str">
-        <x:v>同事把我当冤种，别怪我翻脸</x:v>
+        <x:v>结婚八年，我娶的原来是仇人的女儿</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>2026-09-14</x:v>
-      </x:c>
-      <x:c r="E18" s="11" t="str"/>
-      <x:c r="F18" s="11" t="str"/>
-      <x:c r="G18" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H18" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F18" s="11" t="str">
+        <x:v>↑14位</x:v>
+      </x:c>
+      <x:c r="G18" s="11" t="str"/>
+      <x:c r="H18" s="11" t="str"/>
       <x:c r="I18" s="11" t="str"/>
       <x:c r="J18" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="K18" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>家庭伦理 / 婚姻情感</x:v>
       </x:c>
       <x:c r="L18" s="11" t="str"/>
       <x:c r="M18" s="10" t="str"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="str">
-        <x:v>持续在榜</x:v>
+        <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C19" s="10" t="str">
-        <x:v>反派拿捏！</x:v>
+        <x:v>风雪边界</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
-        <x:v>2026-09-13</x:v>
-      </x:c>
-      <x:c r="E19" s="11" t="str"/>
-      <x:c r="F19" s="11" t="str"/>
-      <x:c r="G19" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H19" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I19" s="11" t="str"/>
+        <x:v>09-14 03:01</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="str">
+        <x:v>↑13位</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="str"/>
+      <x:c r="H19" s="11" t="str"/>
+      <x:c r="I19" s="11" t="n">
+        <x:v>53</x:v>
+      </x:c>
       <x:c r="J19" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K19" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L19" s="11" t="str"/>
-      <x:c r="M19" s="10" t="str"/>
+      <x:c r="L19" s="11" t="str">
+        <x:v>腿毛漫漫</x:v>
+      </x:c>
+      <x:c r="M19" s="10" t="str">
+        <x:v>高原补给站老板岑夏坚持完整安全套餐，却遭企业负责人质疑价格，团队转投低价营地。暴雪突至，危机逼近，岑夏仍坚守原则，以专业判断协助应急处置，也让众人重新理解安全的价值。真正昂贵的不是房费，而是忽视风险的代价。敬畏自然、尊重专业，安全永远值得认真对待。</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="str">
-        <x:v>持续在榜</x:v>
+        <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C20" s="10" t="str">
-        <x:v>远山架子班</x:v>
+        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>09-13 07:30</x:v>
-      </x:c>
-      <x:c r="E20" s="11" t="str"/>
-      <x:c r="F20" s="11" t="str"/>
-      <x:c r="G20" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H20" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>09-13 08:00</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="str">
+        <x:v>↑1位</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="str"/>
+      <x:c r="H20" s="11" t="str"/>
       <x:c r="I20" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J20" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K20" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="L20" s="11" t="str">
-        <x:v>空空书漫</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="M20" s="10" t="str">
-        <x:v>工地上，彭大勇拿着别家四十一天的招工纸，问贺远山凭什么只给三十。贺远山不争辩，只把账摊开，安全装备饭钱他管，工钱三天一结，从没拖欠。有人奔着高薪离开，可那边层层扣下来，到手反不如从前，还屡屡涉险。工友受伤住院，贺远山二话不说垫钱救人，又帮着把旧账一笔笔算清。他始终守着一条理，钱要挣，命不能换。规矩立得住，人心自然拢得回，班越带越稳，账越算越明。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="11" t="str">
-        <x:v>持续在榜</x:v>
-      </x:c>
-      <x:c r="B21" s="11" t="n">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C21" s="10" t="str">
-        <x:v>7路公交车的终点</x:v>
-      </x:c>
-      <x:c r="D21" s="11" t="str">
-        <x:v>09-14 10:00</x:v>
-      </x:c>
-      <x:c r="E21" s="11" t="str"/>
-      <x:c r="F21" s="11" t="str"/>
-      <x:c r="G21" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H21" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I21" s="11" t="n">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="J21" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="K21" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L21" s="11" t="str">
-        <x:v>鹿姐短剧</x:v>
-      </x:c>
-      <x:c r="M21" s="10" t="str">
-        <x:v>何云身为顾氏集团实际控股人，隐姓埋名开了二十年公交。亲家肖大海一家在公交上闹事伤人，其女肖琴琴当众殴打何云，还剪辑视频网暴她。何云收集完整录像与肖琴琴挪用公款的证据，于订婚宴当众揭穿一切。肖家人被警方带走，何云出任公交公司总经理，与儿子和好。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="11" t="str">
-        <x:v>持续在榜</x:v>
-      </x:c>
-      <x:c r="B22" s="11" t="n">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C22" s="10" t="str">
-        <x:v>她说分手后我取消了所有共享支付</x:v>
-      </x:c>
-      <x:c r="D22" s="11" t="str">
-        <x:v>09-14 17:58</x:v>
-      </x:c>
-      <x:c r="E22" s="11" t="str"/>
-      <x:c r="F22" s="11" t="str"/>
-      <x:c r="G22" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H22" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I22" s="11" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="J22" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="K22" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L22" s="11" t="str">
-        <x:v>量量剧场</x:v>
-      </x:c>
-      <x:c r="M22" s="10" t="str">
-        <x:v>江临川与许嘉宁相恋三年，默默承担她与家人的共享支付、亲属卡和琐碎开销。许嘉宁一句“分手吧”，他不再挽留，当场解绑支付、收回钥匙，拒绝继续做无偿后盾。周慧兰、许嘉航接连施压，陆远泽介入，旧情与利益纠缠。江临川守着小维修店，靠手艺重建边界；许嘉宁在失去依靠后被迫独立，换工作、理旧账、与原生家庭划清界限。两人从怨怼走向平静，最终各自成长。江临川也遇见了愿意“账清楚”的林晚禾，新生活从一个人付得起开始。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="11" t="str">
-        <x:v>持续在榜</x:v>
-      </x:c>
-      <x:c r="B23" s="11" t="n">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C23" s="10" t="str">
-        <x:v>八零大院：灶台藏尽温柔</x:v>
-      </x:c>
-      <x:c r="D23" s="11" t="str">
-        <x:v>09-13 10:00</x:v>
-      </x:c>
-      <x:c r="E23" s="11" t="str"/>
-      <x:c r="F23" s="11" t="str"/>
-      <x:c r="G23" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H23" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I23" s="11" t="n">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="J23" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="K23" s="10" t="str">
-        <x:v>年代怀旧 / 种田囤货</x:v>
-      </x:c>
-      <x:c r="L23" s="11" t="str">
-        <x:v>枭枭动画</x:v>
-      </x:c>
-      <x:c r="M23" s="10" t="str">
-        <x:v>现代私宴主厨祝宁意外穿越至八十年代，为反抗包办婚姻毅然出走，凭借一身精湛厨艺在军区大院门口摆摊谋生。她做的饭菜香气独特，意外治愈了因战场创伤患上心理性厌食症的军区首长贺枭。进入军区食堂后，祝宁靠着过硬的厨艺和坦荡正直的性格渐渐站稳脚跟。面对旁人的刁难与恶意构陷，她始终坚守原则、沉着应对，最终不仅凭借专业能力获得全军区的认可，获评军区膳食顾问，也与贺枭解开重重误会，在烟火日常中收获了真挚的感情。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="11" t="str">
-        <x:v>持续在榜</x:v>
-      </x:c>
-      <x:c r="B24" s="11" t="n">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C24" s="10" t="str">
-        <x:v>晚棠知归，七年终见你</x:v>
-      </x:c>
-      <x:c r="D24" s="11" t="str">
-        <x:v>09-14 11:26</x:v>
-      </x:c>
-      <x:c r="E24" s="11" t="str"/>
-      <x:c r="F24" s="11" t="str"/>
-      <x:c r="G24" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H24" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I24" s="11" t="n">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="J24" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="K24" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L24" s="11" t="str">
-        <x:v>喵琪琪追剧</x:v>
-      </x:c>
-      <x:c r="M24" s="10" t="str">
-        <x:v>七年前，夏晚棠为救深爱的陆知珩，付出了一切，却被误会成背叛，独自带着女儿生活。多年后，两人再次相遇，陆知珩才发现当年的真相，也终于明白她承受了怎样的苦难。面对迟来的爱与亏欠，夏晚棠没有停留在过去，而是重新找回自己，用专业和坚强开启新的人生。最终，两人在女儿的陪伴下解开心结，携手迎来属于他们的幸福。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="11" t="str">
-        <x:v>新剧上升</x:v>
-      </x:c>
-      <x:c r="B25" s="11" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C25" s="10" t="str">
-        <x:v>427元扳倒老油条</x:v>
-      </x:c>
-      <x:c r="D25" s="11" t="str">
-        <x:v>09-13 16:00</x:v>
-      </x:c>
-      <x:c r="E25" s="11" t="n">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="F25" s="11" t="str">
-        <x:v>↑60位</x:v>
-      </x:c>
-      <x:c r="G25" s="11" t="str"/>
-      <x:c r="H25" s="11" t="str"/>
-      <x:c r="I25" s="11" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="J25" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="K25" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L25" s="11" t="str">
-        <x:v>安然然</x:v>
-      </x:c>
-      <x:c r="M25" s="10" t="str">
-        <x:v>职场新人许宁向老员工马丽芬讨要427元代垫外卖款，反遭易绑架马丽芬交出饭钱后怀恨在心，利用行政特权私吞福利，并在组织团餐时疏同事差价许宁按兵不动收集证据，最终将马丽芬长期贪占两万余元的行径在老板曝光的照片中马丽芬被直接开除，许宁成功维护了职场底线。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="11" t="str">
-        <x:v>新剧上升</x:v>
-      </x:c>
-      <x:c r="B26" s="11" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C26" s="10" t="str">
-        <x:v>乡宴见人心</x:v>
-      </x:c>
-      <x:c r="D26" s="11" t="str">
-        <x:v>09-13 17:12</x:v>
-      </x:c>
-      <x:c r="E26" s="11" t="n">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F26" s="11" t="str">
-        <x:v>↑52位</x:v>
-      </x:c>
-      <x:c r="G26" s="11" t="str"/>
-      <x:c r="H26" s="11" t="str"/>
-      <x:c r="I26" s="11" t="n">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="J26" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="K26" s="10" t="str">
-        <x:v>现实反转</x:v>
-      </x:c>
-      <x:c r="L26" s="11" t="str">
-        <x:v>黑白动漫</x:v>
-      </x:c>
-      <x:c r="M26" s="10" t="str">
-        <x:v>高满仓在赵家大院办了八年流水席，十里八村都认他的手艺。眼看生意越来越旺，院主赵金贵突然把租金翻倍，还要按桌抽钱。高满仓干脆带着人和家伙搬进镇外的废米厂，从头再来。赵金贵以为守着大院就守住了客人，靠低价抢生意，却越省越狠。一边是稳稳当当把席办好，一边是亲手砸掉自己的口碑，这场较量最后看的是院子，还是人心。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="11" t="str">
-        <x:v>新剧上升</x:v>
-      </x:c>
-      <x:c r="B27" s="11" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C27" s="10" t="str">
-        <x:v>河箱送福来</x:v>
-      </x:c>
-      <x:c r="D27" s="11" t="str">
-        <x:v>09-13 11:00</x:v>
-      </x:c>
-      <x:c r="E27" s="11" t="n">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="F27" s="11" t="str">
-        <x:v>↑30位</x:v>
-      </x:c>
-      <x:c r="G27" s="11" t="str"/>
-      <x:c r="H27" s="11" t="str"/>
-      <x:c r="I27" s="11" t="n">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="J27" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="K27" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L27" s="11" t="str">
-        <x:v>灵心讲故事</x:v>
-      </x:c>
-      <x:c r="M27" s="10" t="str">
-        <x:v>张家老两口从河中救回一只木箱，收养了箱中受伤的福生。福生长大后修桥开田，引水惠及乡亲，成家立业。二老相继离世后，山洪威胁村庄，福生为救乡亲舍命撑住巨石，最终重伤落水，下落不明。秀娥守着小院苦等多年，直到熟悉的声音再次响起。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="11" t="str">
-        <x:v>新剧上升</x:v>
-      </x:c>
-      <x:c r="B28" s="11" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C28" s="10" t="str">
-        <x:v>重生80，救下神雕后我带村民走出大山</x:v>
-      </x:c>
-      <x:c r="D28" s="11" t="str">
-        <x:v>09-13 09:00</x:v>
-      </x:c>
-      <x:c r="E28" s="11" t="n">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F28" s="11" t="str">
-        <x:v>↑28位</x:v>
-      </x:c>
-      <x:c r="G28" s="11" t="str"/>
-      <x:c r="H28" s="11" t="str"/>
-      <x:c r="I28" s="11" t="n">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="J28" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="K28" s="10" t="str">
-        <x:v>战神异能</x:v>
-      </x:c>
-      <x:c r="L28" s="11" t="str">
-        <x:v>拾光漫漫</x:v>
-      </x:c>
-      <x:c r="M28" s="10" t="str">
-        <x:v>林大山遭人为意外，意外重生回到1980年。前世他错信爱人落得凄惨下场，重生后果断当众退婚。机缘巧合救下受伤的灵智神雕金羽，还遇见落难善良的白秋月。他携手知恩图报的神雕，依托卧龙山的资源，发掘名贵药材，抓住时代发展机遇。面对同行刁难，林大山坚守本心，凭借智慧与实干，包下荒山兴办药材加工坊。他善待家人，带领乡里百姓勤劳致富，在八十年代的时代浪潮里，靠着双手改写命运，收获美满爱情与事业。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="11" t="str">
-        <x:v>新剧上升</x:v>
-      </x:c>
-      <x:c r="B29" s="11" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C29" s="10" t="str">
-        <x:v>婚礼当天我不嫁了</x:v>
-      </x:c>
-      <x:c r="D29" s="11" t="str">
-        <x:v>09-14 09:00</x:v>
-      </x:c>
-      <x:c r="E29" s="11" t="n">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F29" s="11" t="str">
-        <x:v>↑10位</x:v>
-      </x:c>
-      <x:c r="G29" s="11" t="str"/>
-      <x:c r="H29" s="11" t="str"/>
-      <x:c r="I29" s="11" t="n">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="J29" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="K29" s="10" t="str">
-        <x:v>婚姻情感</x:v>
-      </x:c>
-      <x:c r="L29" s="11" t="str">
-        <x:v>大梨看剧</x:v>
-      </x:c>
-      <x:c r="M29" s="10" t="str">
-        <x:v>婚礼当天，沈清面对不同婚俗，勇敢表达自我，果断选择结束婚约。哥哥和好友支持，她用法律与智慧处理彩礼、名誉及后续事宜，守护尊严与安全。成长历程中，她开启独立新生活，搬入温暖新家，与家人朋友相伴成长。故事传递出，婚姻应建立在尊重、平等和真诚之上，表达选择，才能拥抱更好的未来。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="11" t="str">
-        <x:v>新剧上升</x:v>
-      </x:c>
-      <x:c r="B30" s="11" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C30" s="10" t="str">
-        <x:v>小妹初长成</x:v>
-      </x:c>
-      <x:c r="D30" s="11" t="str">
-        <x:v>2026-09-13</x:v>
-      </x:c>
-      <x:c r="E30" s="11" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F30" s="11" t="str">
-        <x:v>↑8位</x:v>
-      </x:c>
-      <x:c r="G30" s="11" t="str"/>
-      <x:c r="H30" s="11" t="str"/>
-      <x:c r="I30" s="11" t="str"/>
-      <x:c r="J30" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="K30" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L30" s="11" t="str"/>
-      <x:c r="M30" s="10" t="str"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="11" t="str">
-        <x:v>新剧上升</x:v>
-      </x:c>
-      <x:c r="B31" s="11" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C31" s="10" t="str">
-        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
-      </x:c>
-      <x:c r="D31" s="11" t="str">
-        <x:v>09-13 09:58</x:v>
-      </x:c>
-      <x:c r="E31" s="11" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F31" s="11" t="str">
-        <x:v>↑7位</x:v>
-      </x:c>
-      <x:c r="G31" s="11" t="str"/>
-      <x:c r="H31" s="11" t="str"/>
-      <x:c r="I31" s="11" t="n">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="J31" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="K31" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L31" s="11" t="str">
-        <x:v>创想剧场</x:v>
-      </x:c>
-      <x:c r="M31" s="10" t="str">
-        <x:v>游戏公会会长林小勇筹备婚礼，却在婚宴上遭遇未婚妻临时加价逼婚。危急时刻，几位相交多年的游戏老友现身力挺他，林小勇果断取消婚礼。之后他搬进好友赠送的别墅，与陈董的两个女儿渐渐熟识。同学聚会上，众人见识到林小勇不一般的际遇。平静日子没过多久，当年游戏里的宿敌将出席游戏八周年嘉年华，一众老友决定赴约，一场新旧对决即将开启。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="11" t="str">
-        <x:v>新剧上升</x:v>
-      </x:c>
-      <x:c r="B32" s="11" t="n">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C32" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
-      </x:c>
-      <x:c r="D32" s="11" t="str">
-        <x:v>09-15 00:08</x:v>
-      </x:c>
-      <x:c r="E32" s="11" t="n">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F32" s="11" t="str">
-        <x:v>↑6位</x:v>
-      </x:c>
-      <x:c r="G32" s="11" t="str"/>
-      <x:c r="H32" s="11" t="str"/>
-      <x:c r="I32" s="11" t="n">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="J32" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="K32" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L32" s="11" t="str">
-        <x:v>桃子动漫剧场</x:v>
-      </x:c>
-      <x:c r="M32" s="10" t="str">
-        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="11" t="str">
-        <x:v>新剧上升</x:v>
-      </x:c>
-      <x:c r="B33" s="11" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C33" s="10" t="str">
-        <x:v>那朵胸花，被丢进垃圾桶</x:v>
-      </x:c>
-      <x:c r="D33" s="11" t="str">
-        <x:v>09-14 21:00</x:v>
-      </x:c>
-      <x:c r="E33" s="11" t="n">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F33" s="11" t="str">
-        <x:v>↑6位</x:v>
-      </x:c>
-      <x:c r="G33" s="11" t="str"/>
-      <x:c r="H33" s="11" t="str"/>
-      <x:c r="I33" s="11" t="n">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="J33" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="K33" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L33" s="11" t="str">
-        <x:v>临渊剧场</x:v>
-      </x:c>
-      <x:c r="M33" s="10" t="str">
-        <x:v>接亲当天，新郎踹开新娘房门。新娘护着前任，前任用胸花挑衅，婚礼当场取消。她求他，他放完整视频反击。前任欠债跑路，债主堵门，新娘崩溃。他换锁卖房，一笔账一笔账清。可账单会说话，旧爱跑不了，这条线，该断了。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="11" t="str">
-        <x:v>新剧上升</x:v>
-      </x:c>
-      <x:c r="B34" s="11" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C34" s="10" t="str">
-        <x:v>离婚那天我多了个痞帅老爹</x:v>
-      </x:c>
-      <x:c r="D34" s="11" t="str">
-        <x:v>2026-09-13</x:v>
-      </x:c>
-      <x:c r="E34" s="11" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F34" s="11" t="str">
-        <x:v>↑1位</x:v>
-      </x:c>
-      <x:c r="G34" s="11" t="str"/>
-      <x:c r="H34" s="11" t="str"/>
-      <x:c r="I34" s="11" t="str"/>
-      <x:c r="J34" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="K34" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="L34" s="11" t="str"/>
-      <x:c r="M34" s="10" t="str"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="11" t="str">
-        <x:v>新剧上升</x:v>
-      </x:c>
-      <x:c r="B35" s="11" t="n">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C35" s="10" t="str">
-        <x:v>晚棠知归，七年终见你</x:v>
-      </x:c>
-      <x:c r="D35" s="11" t="str">
-        <x:v>09-14 11:26</x:v>
-      </x:c>
-      <x:c r="E35" s="11" t="n">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="F35" s="11" t="str">
-        <x:v>↑1位</x:v>
-      </x:c>
-      <x:c r="G35" s="11" t="str"/>
-      <x:c r="H35" s="11" t="str"/>
-      <x:c r="I35" s="11" t="n">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="J35" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="K35" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L35" s="11" t="str">
-        <x:v>喵琪琪追剧</x:v>
-      </x:c>
-      <x:c r="M35" s="10" t="str">
-        <x:v>七年前，夏晚棠为救深爱的陆知珩，付出了一切，却被误会成背叛，独自带着女儿生活。多年后，两人再次相遇，陆知珩才发现当年的真相，也终于明白她承受了怎样的苦难。面对迟来的爱与亏欠，夏晚棠没有停留在过去，而是重新找回自己，用专业和坚强开启新的人生。最终，两人在女儿的陪伴下解开心结，携手迎来属于他们的幸福。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="11" t="str">
-        <x:v>新剧上升</x:v>
-      </x:c>
-      <x:c r="B36" s="11" t="n">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C36" s="10" t="str">
-        <x:v>重生嫡女：太子妃她手撕孽缘</x:v>
-      </x:c>
-      <x:c r="D36" s="11" t="str">
-        <x:v>09-13 11:00</x:v>
-      </x:c>
-      <x:c r="E36" s="11" t="str"/>
-      <x:c r="F36" s="11" t="str">
-        <x:v>新上榜</x:v>
-      </x:c>
-      <x:c r="G36" s="11" t="str"/>
-      <x:c r="H36" s="11" t="str"/>
-      <x:c r="I36" s="11" t="n">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="J36" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="K36" s="10" t="str">
-        <x:v>古装宫廷 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="L36" s="11" t="str">
-        <x:v>展瓦-小付说剧</x:v>
-      </x:c>
-      <x:c r="M36" s="10" t="str">
-        <x:v>嫡女顾明筝前世遭庶妹顾明玉与未婚夫谢哲安联手算计，错嫁后受尽折磨含恨而死。一朝重生回到大婚当日，她将计就计当众揭穿二人私情，顺势改入东宫成为太子妃。她悉心调理病弱太子的身体，夫妻相得，后顺利诞下皇太孙，地位愈发稳固。反观顾明玉嫁入平南侯府后宅斗失算，下毒害人反遭反噬，痛失子嗣被逐出府；谢哲安身中绝嗣之毒，世子之位岌岌可危，侯府彻底败落。最终太子病逝，顾明筝携幼子坚定立身，彻底改写前世悲剧命运。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" s="11" t="str">
-        <x:v>新剧上升</x:v>
-      </x:c>
-      <x:c r="B37" s="11" t="n">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C37" s="10" t="str">
-        <x:v>婆媳联手破残局</x:v>
-      </x:c>
-      <x:c r="D37" s="11" t="str">
-        <x:v>2026-09-15</x:v>
-      </x:c>
-      <x:c r="E37" s="11" t="str"/>
-      <x:c r="F37" s="11" t="str">
-        <x:v>新上榜</x:v>
-      </x:c>
-      <x:c r="G37" s="11" t="str"/>
-      <x:c r="H37" s="11" t="str"/>
-      <x:c r="I37" s="11" t="str"/>
-      <x:c r="J37" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="K37" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L37" s="11" t="str"/>
-      <x:c r="M37" s="10" t="str"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="A38" s="11" t="str">
-        <x:v>新剧上升</x:v>
-      </x:c>
-      <x:c r="B38" s="11" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C38" s="10" t="str">
-        <x:v>枕上独宠第一季</x:v>
-      </x:c>
-      <x:c r="D38" s="11" t="str">
-        <x:v>09-13 11:05</x:v>
-      </x:c>
-      <x:c r="E38" s="11" t="str"/>
-      <x:c r="F38" s="11" t="str">
-        <x:v>新上榜</x:v>
-      </x:c>
-      <x:c r="G38" s="11" t="str"/>
-      <x:c r="H38" s="11" t="str"/>
-      <x:c r="I38" s="11" t="n">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="J38" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="K38" s="10" t="str">
-        <x:v>婚姻情感</x:v>
-      </x:c>
-      <x:c r="L38" s="11" t="str">
-        <x:v>语跃文化</x:v>
-      </x:c>
-      <x:c r="M38" s="10" t="str">
-        <x:v>四年前我不告而别，远走他国，以为他在家族逼婚与我之间选择了前者。四年后我以记者身份回国，第一场采访对象正是已成集团总裁的前男友。我问他订婚传闻，他冷言相对，却一直留着我送的旧物。直到闺蜜点破真相，当年他被家中软禁，错过我的电话，此后数年拼命往上走，只为有能力护住想护的人。误会尽释，这一次我不会再逃。</x:v>
+        <x:v>大晋七公主沈令仪，自幼被冷落于听竹宫，沉默藏锋，苟全性命。宫宴之上，太子带回的秦照雪笑盈盈提议将她送去北狄和亲。满殿以为皇帝会点头，他却掷出“废太子”三字。一夜之间，沈令仪被推到台前。北狄求和的急报恰在此时入京——与她方才所言分毫不差。可当她回望母亲遗下的那半卷秘策时，才发现这局棋，早在二十年前就已落子。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2518,7 +1870,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>35</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
         <x:v>结婚八年，我娶的原来是仇人的女儿</x:v>
@@ -2535,66 +1887,227 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
+        <x:v>别欺负我奶奶</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>今日发布</x:v>
+        <x:v>当日新上榜</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>09-15 00:08</x:v>
+        <x:v>09-02 18:27</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F3" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G3" s="10" t="str">
-        <x:v>桃子动漫剧场</x:v>
+        <x:v>小焓追剧</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>我的面包车，你砸不起</x:v>
+        <x:v>和叔叔合伙五年，却用五百块打发我</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
         <x:v>当日新上榜</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>08-16 09:30</x:v>
+        <x:v>08-07 08:00</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F4" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="G4" s="10" t="str">
-        <x:v>剧鲸漫剧</x:v>
+        <x:v>阅友动漫</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>婆媳联手破残局</x:v>
+        <x:v>四个崽崽瞒不住了</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>09-15 00:08</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="n">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="F5" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G5" s="10" t="str">
+        <x:v>桃子动漫剧场</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="11" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B6" s="10" t="str">
+        <x:v>我的面包车，你砸不起</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
         <x:v>当日新上榜</x:v>
       </x:c>
-      <x:c r="D5" s="11" t="str"/>
-      <x:c r="E5" s="11" t="str"/>
-      <x:c r="F5" s="10" t="str">
+      <x:c r="D6" s="11" t="str">
+        <x:v>08-16 09:30</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F6" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="G5" s="10" t="str"/>
+      <x:c r="G6" s="10" t="str">
+        <x:v>剧鲸漫剧</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="11" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B7" s="10" t="str">
+        <x:v>偷脸</x:v>
+      </x:c>
+      <x:c r="C7" s="11" t="str">
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="str"/>
+      <x:c r="E7" s="11" t="str"/>
+      <x:c r="F7" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="str"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="11" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B8" s="10" t="str">
+        <x:v>重生之我为苍生执灯人！</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="str">
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="str">
+        <x:v>08-28 11:58</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F8" s="10" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="G8" s="10" t="str">
+        <x:v>微风追剧</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="11" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B9" s="10" t="str">
+        <x:v>一叶守义满山春</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="str">
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="str">
+        <x:v>08-14 10:10</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F9" s="10" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="G9" s="10" t="str">
+        <x:v>挽风文化传媒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="11" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B10" s="10" t="str">
+        <x:v>苏辻晏的故事</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="str">
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D10" s="11" t="str">
+        <x:v>07-18 21:00</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="n">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="F10" s="10" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="G10" s="10" t="str">
+        <x:v>老登动画</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="11" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B11" s="10" t="str">
+        <x:v>最后一次迁就，是放手</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="str">
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="str">
+        <x:v>08-27 18:00</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F11" s="10" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="G11" s="10" t="str">
+        <x:v>非洲小白脸</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="11" t="n">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B12" s="10" t="str">
+        <x:v>我靠预判走向人生巅峰</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="str">
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D12" s="11" t="str">
+        <x:v>06-27 15:00</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="n">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F12" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="G12" s="10" t="str">
+        <x:v>数智影视-小六看剧</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2663,13 +2176,13 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
-        <x:v>重生三天前，我用水泥封死地下室</x:v>
+        <x:v>离家十年，回来女儿被换了</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>09-09 09:28</x:v>
+        <x:v>09-09 00:04</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
         <x:v>6</x:v>
@@ -2684,7 +2197,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H2" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="I2" s="10" t="str">
         <x:v>其他</x:v>
@@ -2692,24 +2205,24 @@
       <x:c r="J2" s="11" t="str"/>
       <x:c r="K2" s="11" t="str"/>
       <x:c r="L2" s="10" t="str">
-        <x:v>忘忧剧场</x:v>
+        <x:v>魔方影视（上剧版</x:v>
       </x:c>
       <x:c r="M2" s="10" t="str">
-        <x:v>阮清重生回被保姆王妈一家害死的三天前，前世她因心善引狼入室，保姆全家蜗居别墅地下室偷窃投毒，最终惨遭勒死。重生后她假装不知，趁王妈外出时用水泥将地下室彻底封死。警方破墙后，五具尸体令真相大白，王妈因盗窃、投毒被判十五年。阮清与父母团聚，恶人终得恶报，她重获新生。</x:v>
+        <x:v>程砚宁完成长期绝密任务归来，满心想要弥补亲情，却发现家中早已物是人非。身边亲近之人被私欲蒙蔽，制造重重骗局，试图侵占她的事业与财富。面对接连而来的算计与危机，她凭借过人的魄力与智慧步步拆解阴谋，联合正义力量搜集证据，厘清全部是非纠葛。在守护自身事业的同时，她放下过往伤痛，投身公益，完成自我和解，迎来属于自己的全新人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>离家十年，回来女儿被换了</x:v>
+        <x:v>惊絮无声：傻女的绝杀</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>09-09 00:04</x:v>
+        <x:v>09-06 10:00</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
         <x:v>7</x:v>
@@ -2718,10 +2231,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G3" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H3" s="11" t="n">
-        <x:v>155</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
         <x:v>其他</x:v>
@@ -2729,24 +2242,24 @@
       <x:c r="J3" s="11" t="str"/>
       <x:c r="K3" s="11" t="str"/>
       <x:c r="L3" s="10" t="str">
-        <x:v>魔方影视（上剧版</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="M3" s="10" t="str">
-        <x:v>程砚宁完成长期绝密任务归来，满心想要弥补亲情，却发现家中早已物是人非。身边亲近之人被私欲蒙蔽，制造重重骗局，试图侵占她的事业与财富。面对接连而来的算计与危机，她凭借过人的魄力与智慧步步拆解阴谋，联合正义力量搜集证据，厘清全部是非纠葛。在守护自身事业的同时，她放下过往伤痛，投身公益，完成自我和解，迎来属于自己的全新人生。</x:v>
+        <x:v>沈家人人都是天才，唯独小女儿沈惊絮是公认的傻子。没人知道，她不仅装傻多年，还带着前世金牌律师的记忆重生而来。本想闭嘴躺平一生，谁料内鬼勾结资本做空沈氏，一纸合同就要让全家净身出户、背上百亿债务。父亲落笔前，她终于按住协议“这字不能签！”绝地反杀的沈惊絮，一步步挫败了对沈家的围剿，也让全家人重新认识了自己。沈家也迎来了新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>惊絮无声：傻女的绝杀</x:v>
+        <x:v>重生三天前，我用水泥封死地下室</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>09-06 10:00</x:v>
+        <x:v>09-09 09:28</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
         <x:v>7</x:v>
@@ -2755,10 +2268,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G4" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H4" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I4" s="10" t="str">
         <x:v>其他</x:v>
@@ -2766,10 +2279,10 @@
       <x:c r="J4" s="11" t="str"/>
       <x:c r="K4" s="11" t="str"/>
       <x:c r="L4" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>忘忧剧场</x:v>
       </x:c>
       <x:c r="M4" s="10" t="str">
-        <x:v>沈家人人都是天才，唯独小女儿沈惊絮是公认的傻子。没人知道，她不仅装傻多年，还带着前世金牌律师的记忆重生而来。本想闭嘴躺平一生，谁料内鬼勾结资本做空沈氏，一纸合同就要让全家净身出户、背上百亿债务。父亲落笔前，她终于按住协议“这字不能签！”绝地反杀的沈惊絮，一步步挫败了对沈家的围剿，也让全家人重新认识了自己。沈家也迎来了新生。</x:v>
+        <x:v>阮清重生回被保姆王妈一家害死的三天前，前世她因心善引狼入室，保姆全家蜗居别墅地下室偷窃投毒，最终惨遭勒死。重生后她假装不知，趁王妈外出时用水泥将地下室彻底封死。警方破墙后，五具尸体令真相大白，王妈因盗窃、投毒被判十五年。阮清与父母团聚，恶人终得恶报，她重获新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2777,13 +2290,13 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
+        <x:v>破库房的秘密</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>09-08 17:58</x:v>
+        <x:v>2026-09-05</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
         <x:v>7</x:v>
@@ -2792,35 +2305,29 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G5" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="11" t="n">
-        <x:v>111</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H5" s="11" t="str"/>
       <x:c r="I5" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J5" s="11" t="str"/>
       <x:c r="K5" s="11" t="str"/>
-      <x:c r="L5" s="10" t="str">
-        <x:v>禾苗动画</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="str">
-        <x:v>末世异能者沐小暖意外穿书，成为七个反派继子的恶毒后娘。原主辛劳养娃却遭流言中伤，最终含恨而终。沐小暖决心扭转命运，恩威并施管教孩子，凭末世身手进山打猎采药、种地赶集改善家计，更以百年老参为礼，为长子求得名儒霍政谚收为关门弟子。她护佑家人躲过恶人算计与亲戚夺产，建起新宅。七个孩子从怨恨抗拒到真心信赖，争着喊她娘，一家人携手改写命运，收获温暖亲情。</x:v>
-      </x:c>
+      <x:c r="L5" s="10" t="str"/>
+      <x:c r="M5" s="10" t="str"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>穿书后我带萌宝上门认爹</x:v>
+        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>09-07 19:18</x:v>
+        <x:v>09-08 17:58</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
         <x:v>7</x:v>
@@ -2829,10 +2336,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G6" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
         <x:v>其他</x:v>
@@ -2840,15 +2347,15 @@
       <x:c r="J6" s="11" t="str"/>
       <x:c r="K6" s="11" t="str"/>
       <x:c r="L6" s="10" t="str">
-        <x:v>虾仁不自在</x:v>
+        <x:v>禾苗动画</x:v>
       </x:c>
       <x:c r="M6" s="10" t="str">
-        <x:v>许知棠重生穿进书中，当即带着五岁儿子许小舟登门，将孩子送到亲生父亲——傅氏集团总裁傅临川面前，只想抽身退出剧情。幼儿园里儿子遭同学诬陷、老师偏心，她强势护崽，硬刚蛮横家长与失职老师。亲子鉴定尘埃落定，萌娃黏妈不黏爹，反倒让清冷总裁渐渐上心。</x:v>
+        <x:v>末世异能者沐小暖意外穿书，成为七个反派继子的恶毒后娘。原主辛劳养娃却遭流言中伤，最终含恨而终。沐小暖决心扭转命运，恩威并施管教孩子，凭末世身手进山打猎采药、种地赶集改善家计，更以百年老参为礼，为长子求得名儒霍政谚收为关门弟子。她护佑家人躲过恶人算计与亲戚夺产，建起新宅。七个孩子从怨恨抗拒到真心信赖，争着喊她娘，一家人携手改写命运，收获温暖亲情。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
         <x:v>一墙之隔，皆是人心</x:v>
@@ -2885,16 +2392,16 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
+        <x:v>抢个新娘来当后娘第一季</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>2026-09-05</x:v>
+        <x:v>09-08 15:10</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
         <x:v>7</x:v>
@@ -2903,29 +2410,35 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G8" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="11" t="str"/>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H8" s="11" t="n">
+        <x:v>177</x:v>
+      </x:c>
       <x:c r="I8" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J8" s="11" t="str"/>
       <x:c r="K8" s="11" t="str"/>
-      <x:c r="L8" s="10" t="str"/>
-      <x:c r="M8" s="10" t="str"/>
+      <x:c r="L8" s="10" t="str">
+        <x:v>麻辣公主</x:v>
+      </x:c>
+      <x:c r="M8" s="10" t="str">
+        <x:v>带着十里红妆出嫁那日，我才得知新郎早已另娶，这门亲事不过是盯上了我李家的家产。换作旁人或许忍气吞声，我偏不。我当众拒入侯府，主动上书朝廷，愿以嫁妆资援南方水患，只求解除婚约、护我父母周全。这份胆识赢得安王敬重，他以正妃之礼娶我入门。我立誓此生不做妾、不与人共侍一夫，终得一份彼此尊重的姻缘。</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>破库房的秘密</x:v>
+        <x:v>穿书后我带萌宝上门认爹</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>2026-09-05</x:v>
+        <x:v>09-07 19:18</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
         <x:v>7</x:v>
@@ -2934,29 +2447,35 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G9" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H9" s="11" t="str"/>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H9" s="11" t="n">
+        <x:v>95</x:v>
+      </x:c>
       <x:c r="I9" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J9" s="11" t="str"/>
       <x:c r="K9" s="11" t="str"/>
-      <x:c r="L9" s="10" t="str"/>
-      <x:c r="M9" s="10" t="str"/>
+      <x:c r="L9" s="10" t="str">
+        <x:v>虾仁不自在</x:v>
+      </x:c>
+      <x:c r="M9" s="10" t="str">
+        <x:v>许知棠重生穿进书中，当即带着五岁儿子许小舟登门，将孩子送到亲生父亲——傅氏集团总裁傅临川面前，只想抽身退出剧情。幼儿园里儿子遭同学诬陷、老师偏心，她强势护崽，硬刚蛮横家长与失职老师。亲子鉴定尘埃落定，萌娃黏妈不黏爹，反倒让清冷总裁渐渐上心。</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>不靠谱爸妈很靠谱</x:v>
+        <x:v>凤阙承安</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>09-09 11:08</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
         <x:v>7</x:v>
@@ -2967,33 +2486,27 @@
       <x:c r="G10" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H10" s="11" t="n">
-        <x:v>73</x:v>
-      </x:c>
+      <x:c r="H10" s="11" t="str"/>
       <x:c r="I10" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J10" s="11" t="str"/>
       <x:c r="K10" s="11" t="str"/>
-      <x:c r="L10" s="10" t="str">
-        <x:v>灵妹儿</x:v>
-      </x:c>
-      <x:c r="M10" s="10" t="str">
-        <x:v>外表张扬的年轻夫妻在冬夜救下女婴林小小，用十七年的辛勤劳动和无条件陪伴，为她撑起温暖的家。曾经成绩落后的林小小，在父母的鼓励下重新学习，一步步成长为优秀学生。面对亲生家庭带来的资源与人生选择，她也开始重新理解血缘、养育与责任。当外界的误解影响到父母的生活，林小小决定勇敢站出来，用事实守护家人，也用努力证明真正的爱，是尊重、陪伴和彼此成就。</x:v>
-      </x:c>
+      <x:c r="L10" s="10" t="str"/>
+      <x:c r="M10" s="10" t="str"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>凤阙承安</x:v>
+        <x:v>全家施压：我反手签了过户合同</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>09-08 16:58</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
         <x:v>7</x:v>
@@ -3002,29 +2515,35 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G11" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H11" s="11" t="str"/>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H11" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
       <x:c r="I11" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J11" s="11" t="str"/>
       <x:c r="K11" s="11" t="str"/>
-      <x:c r="L11" s="10" t="str"/>
-      <x:c r="M11" s="10" t="str"/>
+      <x:c r="L11" s="10" t="str">
+        <x:v>灵川剧场</x:v>
+      </x:c>
+      <x:c r="M11" s="10" t="str">
+        <x:v>儿子儿媳多次提议我搬回乡下养老，将城里的宽敞住房腾出来给女方父母长期居住。我笑着点头应下，转头便将这套三室朝南的江景房产挂牌出售，最终成交二百八十万元。我随即购置了一套一室一厅的小户型，更换门锁后独自入住。他们上门索要钥匙，我没有开门。名下房产我自有主张，谁也别想插手安排。</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>抢个新娘来当后娘第一季</x:v>
+        <x:v>不靠谱爸妈很靠谱</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>09-08 15:10</x:v>
+        <x:v>09-09 11:08</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
         <x:v>7</x:v>
@@ -3033,10 +2552,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G12" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H12" s="11" t="n">
-        <x:v>177</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str">
         <x:v>其他</x:v>
@@ -3044,24 +2563,24 @@
       <x:c r="J12" s="11" t="str"/>
       <x:c r="K12" s="11" t="str"/>
       <x:c r="L12" s="10" t="str">
-        <x:v>麻辣公主</x:v>
+        <x:v>灵妹儿</x:v>
       </x:c>
       <x:c r="M12" s="10" t="str">
-        <x:v>带着十里红妆出嫁那日，我才得知新郎早已另娶，这门亲事不过是盯上了我李家的家产。换作旁人或许忍气吞声，我偏不。我当众拒入侯府，主动上书朝廷，愿以嫁妆资援南方水患，只求解除婚约、护我父母周全。这份胆识赢得安王敬重，他以正妃之礼娶我入门。我立誓此生不做妾、不与人共侍一夫，终得一份彼此尊重的姻缘。</x:v>
+        <x:v>外表张扬的年轻夫妻在冬夜救下女婴林小小，用十七年的辛勤劳动和无条件陪伴，为她撑起温暖的家。曾经成绩落后的林小小，在父母的鼓励下重新学习，一步步成长为优秀学生。面对亲生家庭带来的资源与人生选择，她也开始重新理解血缘、养育与责任。当外界的误解影响到父母的生活，林小小决定勇敢站出来，用事实守护家人，也用努力证明真正的爱，是尊重、陪伴和彼此成就。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>重启人生，拒绝校花？</x:v>
+        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>09-08 08:30</x:v>
+        <x:v>2026-09-05</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
         <x:v>7</x:v>
@@ -3070,35 +2589,29 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G13" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H13" s="11" t="n">
-        <x:v>108</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H13" s="11" t="str"/>
       <x:c r="I13" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J13" s="11" t="str"/>
       <x:c r="K13" s="11" t="str"/>
-      <x:c r="L13" s="10" t="str">
-        <x:v>肆漫简</x:v>
-      </x:c>
-      <x:c r="M13" s="10" t="str">
-        <x:v>白陌重生回到2004年高考夜，果断避开前世陷害自己的宾馆陷阱，救下被下药的校花江洛菡，彻底扭转人生走向。他不再执着于过往的情感执念，跳出卑微追爱的困局，转而关心恩师健康、规划学业与创业方向，结识志同道合的伙伴。凭借重生阅历清醒选择前路，把握青春重启人生，用行动改写原本遗憾的命运，活出全新成长轨迹。</x:v>
-      </x:c>
+      <x:c r="L13" s="10" t="str"/>
+      <x:c r="M13" s="10" t="str"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>苏小姐高调离婚，前夫哭惨了</x:v>
+        <x:v>重启人生，拒绝校花？</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>09-08 08:30</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
         <x:v>7</x:v>
@@ -3107,29 +2620,35 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G14" s="11" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H14" s="11" t="str"/>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="n">
+        <x:v>108</x:v>
+      </x:c>
       <x:c r="I14" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J14" s="11" t="str"/>
       <x:c r="K14" s="11" t="str"/>
-      <x:c r="L14" s="10" t="str"/>
-      <x:c r="M14" s="10" t="str"/>
+      <x:c r="L14" s="10" t="str">
+        <x:v>肆漫简</x:v>
+      </x:c>
+      <x:c r="M14" s="10" t="str">
+        <x:v>白陌重生回到2004年高考夜，果断避开前世陷害自己的宾馆陷阱，救下被下药的校花江洛菡，彻底扭转人生走向。他不再执着于过往的情感执念，跳出卑微追爱的困局，转而关心恩师健康、规划学业与创业方向，结识志同道合的伙伴。凭借重生阅历清醒选择前路，把握青春重启人生，用行动改写原本遗憾的命运，活出全新成长轨迹。</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="n">
-        <x:v>57</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>美颜系统开挂，大佬全跪下</x:v>
+        <x:v>苏小姐高调离婚，前夫哭惨了</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
-        <x:v>09-09 00:10</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
         <x:v>7</x:v>
@@ -3138,35 +2657,29 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G15" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H15" s="11" t="n">
-        <x:v>172</x:v>
-      </x:c>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H15" s="11" t="str"/>
       <x:c r="I15" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J15" s="11" t="str"/>
       <x:c r="K15" s="11" t="str"/>
-      <x:c r="L15" s="10" t="str">
-        <x:v>御儿</x:v>
-      </x:c>
-      <x:c r="M15" s="10" t="str">
-        <x:v>曾因外形饱受非议的米珂华丽转身，蜕变得耀眼又夺目。从前对她嗤之以鼻的蒋少开始频频在意，素来冷眼毒舌的陆总不知不觉深陷其中，连一向克己的商界大佬也为她打破原则。米珂凭智商与手腕周旋于众人之间，上演一场势均力敌的情感博弈。没有俗套的救赎，只有双向的拉扯。看一众高高在上的精英暗自较劲、步步沉沦，心甘情愿为她卸下防备。</x:v>
-      </x:c>
+      <x:c r="L15" s="10" t="str"/>
+      <x:c r="M15" s="10" t="str"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>全家施压：我反手签了过户合同</x:v>
+        <x:v>美颜系统开挂，大佬全跪下</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>09-08 16:58</x:v>
+        <x:v>09-09 00:10</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
         <x:v>7</x:v>
@@ -3175,10 +2688,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G16" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H16" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str">
         <x:v>其他</x:v>
@@ -3186,15 +2699,15 @@
       <x:c r="J16" s="11" t="str"/>
       <x:c r="K16" s="11" t="str"/>
       <x:c r="L16" s="10" t="str">
-        <x:v>灵川剧场</x:v>
+        <x:v>御儿</x:v>
       </x:c>
       <x:c r="M16" s="10" t="str">
-        <x:v>儿子儿媳多次提议我搬回乡下养老，将城里的宽敞住房腾出来给女方父母长期居住。我笑着点头应下，转头便将这套三室朝南的江景房产挂牌出售，最终成交二百八十万元。我随即购置了一套一室一厅的小户型，更换门锁后独自入住。他们上门索要钥匙，我没有开门。名下房产我自有主张，谁也别想插手安排。</x:v>
+        <x:v>曾因外形饱受非议的米珂华丽转身，蜕变得耀眼又夺目。从前对她嗤之以鼻的蒋少开始频频在意，素来冷眼毒舌的陆总不知不觉深陷其中，连一向克己的商界大佬也为她打破原则。米珂凭智商与手腕周旋于众人之间，上演一场势均力敌的情感博弈。没有俗套的救赎，只有双向的拉扯。看一众高高在上的精英暗自较劲、步步沉沦，心甘情愿为她卸下防备。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
         <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
@@ -3231,7 +2744,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
         <x:v>蒙蒙半故</x:v>
@@ -3268,28 +2781,28 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="n">
-        <x:v>89</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>末世来临，我靠囤货种田丰衣足食</x:v>
+        <x:v>征地我秒签跑路，全村笑我半年</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>09-09 15:30</x:v>
+        <x:v>09-10 11:30</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E19" s="11" t="n">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="F19" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G19" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H19" s="11" t="n">
-        <x:v>344</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str">
         <x:v>其他</x:v>
@@ -3297,58 +2810,52 @@
       <x:c r="J19" s="11" t="str"/>
       <x:c r="K19" s="11" t="str"/>
       <x:c r="L19" s="10" t="str">
-        <x:v>渲渲动画</x:v>
+        <x:v>小六动漫</x:v>
       </x:c>
       <x:c r="M19" s="10" t="str">
-        <x:v>吴真真带着末世惨死的记忆重生，抢下秘宝空间，囤积海量物资，提前规避天灾人祸。她意外发现家人同样重生，一家人携手为末日做足准备。灾变如期而至，病毒、台风、极寒轮番降临。她机缘结识实力强悍的谢穆辰，二人从互相试探到并肩而立。面对凶悍恶徒与重重危机，吴真真依靠空间与智慧守护至亲，谢穆辰以自身力量与之守望相助，在满目疮痍的末世里，拼尽全力守住生存希望，奔赴属于他们的新生。</x:v>
+        <x:v>赵家湾迎来高速征地，村民受村长赵德厚鼓动抱团拒签，妄想抬价拿到四百五十万补偿。林远察觉当地岩溶地质暗藏线路改线风险，不顾全村嘲讽，果断签下312万补偿款，带父母搬离老家。后续高速果真改线，全村一分补偿落空。曾经嘲笑林远的村民陷入债务困境，赵德厚登门求助，林远守住底线，一家人握紧安稳生活，告诫众人抉择要靠自己。</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="n">
-        <x:v>92</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>天灾末世，她囤满物资后所向披靡！</x:v>
+        <x:v>假老板娘遇上真董事长</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>09-08 15:00</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G20" s="11" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H20" s="11" t="n">
-        <x:v>536</x:v>
-      </x:c>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H20" s="11" t="str"/>
       <x:c r="I20" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J20" s="11" t="str"/>
       <x:c r="K20" s="11" t="str"/>
-      <x:c r="L20" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
-      </x:c>
-      <x:c r="M20" s="10" t="str">
-        <x:v>韩清夏被至亲推向绝境，失去家园，没能守住重要伙伴。再次睁眼，她回到了灾变来临前，并意外激活超级领主系统。她果断卖房筹资、囤积物资，将废弃防空洞升级为坚固基地，与战犬夏天并肩成长。危机爆发后，她凭借清醒判断、强大异能和充足准备救下幸存者，组建盛夏联盟。面对旧日亲人的算计、各方势力的试探与接连不断的考验，韩清夏不再退让。这一世，她要守住伙伴、掌握命运，在废墟之上建起属于自己的家园。</x:v>
-      </x:c>
+      <x:c r="L20" s="10" t="str"/>
+      <x:c r="M20" s="10" t="str"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>征地我秒签跑路，全村笑我半年</x:v>
+        <x:v>大坝边寻回的真千金</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>09-10 11:30</x:v>
+        <x:v>09-10 11:26</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
         <x:v>5</x:v>
@@ -3360,10 +2867,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G21" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H21" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I21" s="10" t="str">
         <x:v>其他</x:v>
@@ -3371,15 +2878,15 @@
       <x:c r="J21" s="11" t="str"/>
       <x:c r="K21" s="11" t="str"/>
       <x:c r="L21" s="10" t="str">
-        <x:v>小六动漫</x:v>
+        <x:v>喵琪琪追剧</x:v>
       </x:c>
       <x:c r="M21" s="10" t="str">
-        <x:v>赵家湾迎来高速征地，村民受村长赵德厚鼓动抱团拒签，妄想抬价拿到四百五十万补偿。林远察觉当地岩溶地质暗藏线路改线风险，不顾全村嘲讽，果断签下312万补偿款，带父母搬离老家。后续高速果真改线，全村一分补偿落空。曾经嘲笑林远的村民陷入债务困境，赵德厚登门求助，林远守住底线，一家人握紧安稳生活，告诫众人抉择要靠自己。</x:v>
+        <x:v>大坝突发险情，农村女孩夏晚禾凭借熟悉的环境和过人的勇气，不顾危险救下被困的沈长洲。一次意外的救援，让两个陌生人的命运重新交织。随着调查深入，沈长洲发现这个善良坚韧的女孩，竟是自己失散二十年的亲生女儿。面对迟来的亲情和真假千金的风波，夏晚禾没有依靠身份改变人生，而是用智慧、担当和努力证明自己的价值。陆言川也在一次次并肩相处中，被她的真诚与坚强打动，陪她找回亲情，走向新的未来。</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="n">
-        <x:v>44</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
         <x:v>重生后我守住全村</x:v>
@@ -3416,28 +2923,28 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="n">
-        <x:v>49</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>除夕夜，我被直升机接回前夫家</x:v>
+        <x:v>三分钱的取舍</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>09-10 08:00</x:v>
+        <x:v>09-10 17:29</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G23" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H23" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
         <x:v>其他</x:v>
@@ -3445,67 +2952,73 @@
       <x:c r="J23" s="11" t="str"/>
       <x:c r="K23" s="11" t="str"/>
       <x:c r="L23" s="10" t="str">
-        <x:v>小狐狸剧场</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="M23" s="10" t="str">
-        <x:v>除夕夜，一架直升机将顾晚棠从苏州小院接回豪门。十九年前，她背负罪名被傅家扫地出门，与幼子傅知衍骨肉分离。如今化名林棠的她，已是高端苏绣“棠记”的主理人，归来只为讨一个公道。宴会上，面对伪善的沈若薇与家族胁迫，她亮出证据步步为营。真相浮出水面，儿子终知愧疚。然而傅老夫人觊觎棠记，设局破坏。顾晚棠能否守住心血，彻底挣脱过往枷锁？</x:v>
+        <x:v>青石沟果农为省下代办三分钱，甩开中间商周成岳，直接对接收购商方洪生收桃。可脱离周成岳统筹调度后，摘桃、排单、装车乱象丛生，桃子积压损耗。周成岳转身接手偏远的十里湾桃园，凭口碑站稳脚跟。经历一季波折，青石沟众人幡然醒悟，重新读懂代办的价值。</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>假老板娘遇上真董事长</x:v>
+        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>09-11 09:00</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E24" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E24" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="F24" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G24" s="11" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H24" s="11" t="str"/>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H24" s="11" t="n">
+        <x:v>133</x:v>
+      </x:c>
       <x:c r="I24" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J24" s="11" t="str"/>
       <x:c r="K24" s="11" t="str"/>
-      <x:c r="L24" s="10" t="str"/>
-      <x:c r="M24" s="10" t="str"/>
+      <x:c r="L24" s="10" t="str">
+        <x:v>阳阳动画</x:v>
+      </x:c>
+      <x:c r="M24" s="10" t="str">
+        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="n">
-        <x:v>87</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>大坝边寻回的真千金</x:v>
+        <x:v>穿越60我有空间不愁吃喝</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>09-10 11:26</x:v>
+        <x:v>09-07 00:04</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E25" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E25" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="F25" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G25" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H25" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str">
         <x:v>其他</x:v>
@@ -3513,36 +3026,36 @@
       <x:c r="J25" s="11" t="str"/>
       <x:c r="K25" s="11" t="str"/>
       <x:c r="L25" s="10" t="str">
-        <x:v>喵琪琪追剧</x:v>
+        <x:v>夜珠AI剧场</x:v>
       </x:c>
       <x:c r="M25" s="10" t="str">
-        <x:v>大坝突发险情，农村女孩夏晚禾凭借熟悉的环境和过人的勇气，不顾危险救下被困的沈长洲。一次意外的救援，让两个陌生人的命运重新交织。随着调查深入，沈长洲发现这个善良坚韧的女孩，竟是自己失散二十年的亲生女儿。面对迟来的亲情和真假千金的风波，夏晚禾没有依靠身份改变人生，而是用智慧、担当和努力证明自己的价值。陆言川也在一次次并肩相处中，被她的真诚与坚强打动，陪她找回亲情，走向新的未来。</x:v>
+        <x:v>现代青年刘大壮意外穿越到60年代，成了同名同姓的16岁穷小子。原主因相亲被拒、家徒四壁，下河摸鱼时溺亡。大壮醒来后发现脑中多了一座九层宝塔空间——内有灵药田与灵泉潭水，作物两小时成熟、产量翻五倍。饥荒年代，别人啃树皮喝稀粥，他靠空间种出满仓土豆粮食，黑市换粮票钞票，让饿肚子的父母姐姐们吃上饱饭。从人人嘲笑的穷小子，到带着全家逆袭翻盘，且看他手握宝塔空间，在艰苦年代闯出一条吃喝不愁的逆袭</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>赶海人生：重回1983小渔村</x:v>
+        <x:v>重生一世，我不再痴恋竹马</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
-        <x:v>09-10 08:55</x:v>
+        <x:v>09-10 10:00</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G26" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H26" s="11" t="n">
-        <x:v>158</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="I26" s="10" t="str">
         <x:v>其他</x:v>
@@ -3550,36 +3063,36 @@
       <x:c r="J26" s="11" t="str"/>
       <x:c r="K26" s="11" t="str"/>
       <x:c r="L26" s="10" t="str">
-        <x:v>梦落漫漫</x:v>
+        <x:v>锦书映年华</x:v>
       </x:c>
       <x:c r="M26" s="10" t="str">
-        <x:v>前世杨建国跳海离世，意外重生回到1983年东沟小渔村。这一年开海祭龙王，妻子即将遭遇毒蛇险境，家中穷困潦倒，伯父还妄图霸占自家渔船。曾经的街溜子幡然醒悟，凭借超前记忆踏海赶海，捕捞对虾、鲍鱼，对抗邻里刁难，守护妻儿老小，在汹涌海潮之中改写一家人贫苦命运。</x:v>
+        <x:v>承平公主前世错恋齐远安，受尽磋磨含恨落幕。一朝重生，恰逢圣旨赐婚，齐远安却当众恳请解除婚约，求取太后义孙女傅明珠。她坦然放手，主动成全二人，看着他们得偿所愿。宁国侯夫人动用旧物强求赐婚，她巧妙改换婚事，选择边关归来、品性刚正的齐远舟。婚后她聪慧通透，看清傅明珠与齐远安的本性，冷眼旁观二人矛盾丛生。历经风波，她与齐远舟彼此扶持，挣脱过往伤痛，收获属于自己安稳坦荡的人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>三分钱的取舍</x:v>
+        <x:v>张兰芬重生记</x:v>
       </x:c>
       <x:c r="C27" s="11" t="str">
-        <x:v>09-10 17:29</x:v>
+        <x:v>09-05 17:00</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G27" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H27" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="I27" s="10" t="str">
         <x:v>其他</x:v>
@@ -3587,73 +3100,67 @@
       <x:c r="J27" s="11" t="str"/>
       <x:c r="K27" s="11" t="str"/>
       <x:c r="L27" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>璀璨Ai剧场</x:v>
       </x:c>
       <x:c r="M27" s="10" t="str">
-        <x:v>青石沟果农为省下代办三分钱，甩开中间商周成岳，直接对接收购商方洪生收桃。可脱离周成岳统筹调度后，摘桃、排单、装车乱象丛生，桃子积压损耗。周成岳转身接手偏远的十里湾桃园，凭口碑站稳脚跟。经历一季波折，青石沟众人幡然醒悟，重新读懂代办的价值。</x:v>
+        <x:v>张兰芬操劳半生，是旁人羡慕的当家主母。她为李家养育四子两女，持家有道、将家中大小事务打理得井井有条。半生付出尽数落空，张兰芬郁结于心，最终含恨病逝医院。一朝重生，她回到所有遗憾尚未发生之时，彻底看透人心，决意放下执念，好好为自己活一次。</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
+        <x:v>穿成恋爱脑女配，我把将军府带偏了呀</x:v>
       </x:c>
       <x:c r="C28" s="11" t="str">
-        <x:v>09-11 09:00</x:v>
+        <x:v>2026-09-06</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F28" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G28" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H28" s="11" t="n">
-        <x:v>133</x:v>
-      </x:c>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H28" s="11" t="str"/>
       <x:c r="I28" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J28" s="11" t="str"/>
       <x:c r="K28" s="11" t="str"/>
-      <x:c r="L28" s="10" t="str">
-        <x:v>阳阳动画</x:v>
-      </x:c>
-      <x:c r="M28" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
-      </x:c>
+      <x:c r="L28" s="10" t="str"/>
+      <x:c r="M28" s="10" t="str"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>穿越60我有空间不愁吃喝</x:v>
+        <x:v>迷局终有破晓时</x:v>
       </x:c>
       <x:c r="C29" s="11" t="str">
-        <x:v>09-07 00:04</x:v>
+        <x:v>09-08 21:18</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G29" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H29" s="11" t="n">
-        <x:v>1000</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I29" s="10" t="str">
         <x:v>其他</x:v>
@@ -3661,79 +3168,11 @@
       <x:c r="J29" s="11" t="str"/>
       <x:c r="K29" s="11" t="str"/>
       <x:c r="L29" s="10" t="str">
-        <x:v>夜珠AI剧场</x:v>
+        <x:v>时雨生</x:v>
       </x:c>
       <x:c r="M29" s="10" t="str">
-        <x:v>现代青年刘大壮意外穿越到60年代，成了同名同姓的16岁穷小子。原主因相亲被拒、家徒四壁，下河摸鱼时溺亡。大壮醒来后发现脑中多了一座九层宝塔空间——内有灵药田与灵泉潭水，作物两小时成熟、产量翻五倍。饥荒年代，别人啃树皮喝稀粥，他靠空间种出满仓土豆粮食，黑市换粮票钞票，让饿肚子的父母姐姐们吃上饱饭。从人人嘲笑的穷小子，到带着全家逆袭翻盘，且看他手握宝塔空间，在艰苦年代闯出一条吃喝不愁的逆袭</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="11" t="n">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B30" s="10" t="str">
-        <x:v>重生一世，我不再痴恋竹马</x:v>
-      </x:c>
-      <x:c r="C30" s="11" t="str">
-        <x:v>09-10 10:00</x:v>
-      </x:c>
-      <x:c r="D30" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E30" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F30" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G30" s="11" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H30" s="11" t="n">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="I30" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J30" s="11" t="str"/>
-      <x:c r="K30" s="11" t="str"/>
-      <x:c r="L30" s="10" t="str">
-        <x:v>锦书映年华</x:v>
-      </x:c>
-      <x:c r="M30" s="10" t="str">
-        <x:v>承平公主前世错恋齐远安，受尽磋磨含恨落幕。一朝重生，恰逢圣旨赐婚，齐远安却当众恳请解除婚约，求取太后义孙女傅明珠。她坦然放手，主动成全二人，看着他们得偿所愿。宁国侯夫人动用旧物强求赐婚，她巧妙改换婚事，选择边关归来、品性刚正的齐远舟。婚后她聪慧通透，看清傅明珠与齐远安的本性，冷眼旁观二人矛盾丛生。历经风波，她与齐远舟彼此扶持，挣脱过往伤痛，收获属于自己安稳坦荡的人生。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="11" t="n">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B31" s="10" t="str">
-        <x:v>穿成恋爱脑女配，我把将军府带偏了呀</x:v>
-      </x:c>
-      <x:c r="C31" s="11" t="str">
-        <x:v>2026-09-06</x:v>
-      </x:c>
-      <x:c r="D31" s="11" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E31" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F31" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G31" s="11" t="n">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H31" s="11" t="str"/>
-      <x:c r="I31" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="J31" s="11" t="str"/>
-      <x:c r="K31" s="11" t="str"/>
-      <x:c r="L31" s="10" t="str"/>
-      <x:c r="M31" s="10" t="str"/>
+        <x:v>男主陆承安的好友到访家中，发现家中潜藏重大疑点，留下关键线索后意外离世。陆承安凭借遗留信物逐步排查，察觉妻子沈知微隐瞒秘密，私下开展不合规研究。他主动对接警方，巧妙布局收集完整证据，配合警方成功解救被困人员，促使沈知微承担相应法律后果。风波过后，陆承安带着孩子走出过往阴霾，开启崭新平静的生活。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3761,7 +3200,7 @@
         <x:v>剧名</x:v>
       </x:c>
       <x:c r="C1" t="str">
-        <x:v>进入TOP10次数</x:v>
+        <x:v>进入TOP20次数</x:v>
       </x:c>
       <x:c r="D1" t="str">
         <x:v>平均排名</x:v>
@@ -3787,16 +3226,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
-        <x:v>1.4</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F2" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-15 02-44</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3819,7 +3258,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-15 02-44</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -3830,19 +3269,19 @@
         <x:v>七套房产，换来一纸调令</x:v>
       </x:c>
       <x:c r="C4" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>6.4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F4" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-15 02-44</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3850,22 +3289,22 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
+        <x:v>重生三天前，我用水泥封死地下室</x:v>
       </x:c>
       <x:c r="C5" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>5.8</x:v>
+        <x:v>10.4</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F5" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>2026-09-14 21-12</x:v>
+        <x:v>2026-09-15 02-44</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -3873,22 +3312,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
+        <x:v>今晚查寝，别开门</x:v>
       </x:c>
       <x:c r="C6" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>5.8</x:v>
+        <x:v>6.9</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F6" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-15 02-44</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3896,19 +3335,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>今晚查寝，别开门</x:v>
+        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
       </x:c>
       <x:c r="C7" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>7.5</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F7" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
         <x:v>2026-09-15 01-59</x:v>
@@ -3919,22 +3358,22 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>重生三天前，我用水泥封死地下室</x:v>
+        <x:v>破库房的秘密</x:v>
       </x:c>
       <x:c r="C8" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>5.8</x:v>
+        <x:v>11.8</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-15 02-44</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3942,22 +3381,22 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>退婚后我在七零赚钱养家致富</x:v>
+        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
       </x:c>
       <x:c r="C9" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>7.5</x:v>
+        <x:v>7.3</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>2026-09-14 12-34</x:v>
+        <x:v>2026-09-15 02-44</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -3965,22 +3404,22 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>破库房的秘密</x:v>
+        <x:v>退婚后我在七零赚钱养家致富</x:v>
       </x:c>
       <x:c r="C10" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>7.3</x:v>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F10" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>2026-09-14 20-18</x:v>
+        <x:v>2026-09-14 22-12</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -3988,22 +3427,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>今天开始做裴总</x:v>
+        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
       </x:c>
       <x:c r="C11" s="11" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="D11" s="11" t="n">
-        <x:v>5.3</x:v>
-      </x:c>
       <x:c r="E11" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-14 20-18</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -4011,22 +3450,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
+        <x:v>锦书迟</x:v>
       </x:c>
       <x:c r="C12" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>7.1</x:v>
+        <x:v>13.4</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G12" s="11" t="str">
-        <x:v>2026-09-14 07-11</x:v>
+        <x:v>2026-09-15 02-44</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -4034,22 +3473,22 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>惊絮无声：傻女的绝杀</x:v>
+        <x:v>泰城错嫁</x:v>
       </x:c>
       <x:c r="C13" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>8.2</x:v>
+        <x:v>12.9</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G13" s="11" t="str">
-        <x:v>2026-09-15 01-12</x:v>
+        <x:v>2026-09-14 22-12</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -4057,22 +3496,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>泰城错嫁</x:v>
+        <x:v>今天开始做裴总</x:v>
       </x:c>
       <x:c r="C14" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>10.8</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G14" s="11" t="str">
-        <x:v>2026-09-14 21-12</x:v>
+        <x:v>2026-09-15 02-44</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -4080,22 +3519,22 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>锦书迟</x:v>
+        <x:v>一墙之隔，皆是人心</x:v>
       </x:c>
       <x:c r="C15" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>9.3</x:v>
+        <x:v>13.3</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F15" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G15" s="11" t="str">
-        <x:v>2026-09-14 22-12</x:v>
+        <x:v>2026-09-15 01-59</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -4103,22 +3542,22 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>一墙之隔，皆是人心</x:v>
+        <x:v>惊絮无声：傻女的绝杀</x:v>
       </x:c>
       <x:c r="C16" s="11" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D16" s="11" t="n">
+        <x:v>11.5</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="n">
         <x:v>5</x:v>
-      </x:c>
-      <x:c r="D16" s="11" t="n">
-        <x:v>7.8</x:v>
-      </x:c>
-      <x:c r="E16" s="11" t="n">
-        <x:v>7</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="G16" s="11" t="str">
-        <x:v>2026-09-14 03-11</x:v>
+        <x:v>2026-09-15 02-44</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -4126,22 +3565,22 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>装傻下山</x:v>
+        <x:v>反派拿捏！</x:v>
       </x:c>
       <x:c r="C17" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>4.2</x:v>
+        <x:v>14.6</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F17" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G17" s="11" t="str">
-        <x:v>2026-09-14 02-11</x:v>
+        <x:v>2026-09-14 20-13</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -4149,22 +3588,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>重生后我守住全村</x:v>
+        <x:v>离家十年，回来女儿被换了</x:v>
       </x:c>
       <x:c r="C18" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>5.8</x:v>
+        <x:v>11.2</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G18" s="11" t="str">
-        <x:v>2026-09-14 20-18</x:v>
+        <x:v>2026-09-15 02-44</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -4172,22 +3611,22 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>离家十年，回来女儿被换了</x:v>
+        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
       </x:c>
       <x:c r="C19" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>15.9</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G19" s="11" t="str">
-        <x:v>2026-09-15 01-12</x:v>
+        <x:v>2026-09-14 06-11</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -4195,19 +3634,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>人人都说她娇气，出事她护我到底</x:v>
+        <x:v>小妹初长成</x:v>
       </x:c>
       <x:c r="C20" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>5.3</x:v>
+        <x:v>12.7</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G20" s="11" t="str">
         <x:v>2026-09-14 12-34</x:v>
@@ -4218,22 +3657,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>我家后山藏真龙</x:v>
+        <x:v>退婚从抢我车位开始</x:v>
       </x:c>
       <x:c r="C21" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>5.7</x:v>
+        <x:v>14.1</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G21" s="11" t="str">
-        <x:v>2026-09-14 09-24</x:v>
+        <x:v>2026-09-14 20-18</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -4241,22 +3680,22 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>小妹初长成</x:v>
+        <x:v>回到零四年进军彩铃界</x:v>
       </x:c>
       <x:c r="C22" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>6.7</x:v>
+        <x:v>16.4</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G22" s="11" t="str">
-        <x:v>2026-09-14 10-32</x:v>
+        <x:v>2026-09-14 12-34</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -4264,22 +3703,22 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>三分钱的取舍</x:v>
+        <x:v>河箱送福来</x:v>
       </x:c>
       <x:c r="C23" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E23" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E23" s="11" t="n">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="F23" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G23" s="11" t="str">
-        <x:v>2026-09-15 01-12</x:v>
+        <x:v>2026-09-14 20-18</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -4287,22 +3726,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
+        <x:v>三分钱的取舍</x:v>
       </x:c>
       <x:c r="C24" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>12.1</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G24" s="11" t="str">
-        <x:v>2026-09-14 22-12</x:v>
+        <x:v>2026-09-15 02-44</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -4310,22 +3749,22 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>零元年终奖</x:v>
+        <x:v>婚礼当天我不嫁了</x:v>
       </x:c>
       <x:c r="C25" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>4.5</x:v>
+        <x:v>14.8</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G25" s="11" t="str">
-        <x:v>2026-09-13 22-11</x:v>
+        <x:v>2026-09-14 22-12</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -4333,22 +3772,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>不负恩情不负卿</x:v>
+        <x:v>装傻下山</x:v>
       </x:c>
       <x:c r="C26" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8.2</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G26" s="11" t="str">
-        <x:v>2026-09-14 09-24</x:v>
+        <x:v>2026-09-14 04-11</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -4356,22 +3795,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>我SSS级狂龙，出世即无敌</x:v>
+        <x:v>穿越60我有空间不愁吃喝</x:v>
       </x:c>
       <x:c r="C27" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>5.5</x:v>
+        <x:v>15.7</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-14 20-18</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -4379,22 +3818,22 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>一碗人间赴景深</x:v>
+        <x:v>重生后我守住全村</x:v>
       </x:c>
       <x:c r="C28" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8.6</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F28" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G28" s="11" t="str">
-        <x:v>2026-09-14 09-24</x:v>
+        <x:v>2026-09-14 20-18</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -4402,22 +3841,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>那块玉，带我们回家</x:v>
+        <x:v>一张废票毁了她</x:v>
       </x:c>
       <x:c r="C29" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>14.5</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str">
-        <x:v>2026-09-14 09-24</x:v>
+        <x:v>2026-09-14 10-32</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -4425,22 +3864,22 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>一针绣出自己的路</x:v>
+        <x:v>全家施压：我反手签了过户合同</x:v>
       </x:c>
       <x:c r="C30" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>7.5</x:v>
+        <x:v>17.2</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G30" s="11" t="str">
-        <x:v>2026-09-13 20-11</x:v>
+        <x:v>2026-09-14 12-34</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -4448,22 +3887,22 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>谢谢爸妈的穷养现在我富了</x:v>
+        <x:v>这桌团圆饭，我不做了</x:v>
       </x:c>
       <x:c r="C31" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>16.5</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G31" s="11" t="str">
-        <x:v>2026-09-14 01-11</x:v>
+        <x:v>2026-09-14 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -4471,22 +3910,22 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="10" t="str">
-        <x:v>那半块玉佩</x:v>
+        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
       </x:c>
       <x:c r="C32" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D32" s="11" t="n">
-        <x:v>7.5</x:v>
+        <x:v>8.7</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G32" s="11" t="str">
-        <x:v>2026-09-14 09-24</x:v>
+        <x:v>2026-09-15 01-59</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -4494,22 +3933,22 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="10" t="str">
-        <x:v>婚礼当天我不嫁了</x:v>
+        <x:v>人人都说她娇气，出事她护我到底</x:v>
       </x:c>
       <x:c r="C33" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D33" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>5.3</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F33" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="G33" s="11" t="str">
-        <x:v>2026-09-14 20-18</x:v>
+        <x:v>2026-09-14 12-34</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -4517,22 +3956,22 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="10" t="str">
-        <x:v>河箱送福来</x:v>
+        <x:v>我家后山藏真龙</x:v>
       </x:c>
       <x:c r="C34" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D34" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>5.7</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F34" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G34" s="11" t="str">
-        <x:v>2026-09-14 20-18</x:v>
+        <x:v>2026-09-14 09-24</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -4540,22 +3979,22 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="10" t="str">
-        <x:v>闪婚老公有点野</x:v>
+        <x:v>不负恩情不负卿</x:v>
       </x:c>
       <x:c r="C35" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D35" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>9.7</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F35" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G35" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-14 10-32</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -4563,22 +4002,22 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="10" t="str">
-        <x:v>离婚那天我多了个痞帅老爹</x:v>
+        <x:v>一针绣出自己的路</x:v>
       </x:c>
       <x:c r="C36" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
-        <x:v>9.5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G36" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-13 21-11</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -4586,22 +4025,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="10" t="str">
-        <x:v>白鹿照归途</x:v>
+        <x:v>谢谢爸妈的穷养现在我富了</x:v>
       </x:c>
       <x:c r="C37" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D37" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>10.7</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G37" s="11" t="str">
-        <x:v>2026-09-14 08-11</x:v>
+        <x:v>2026-09-14 02-11</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -4609,13 +4048,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="10" t="str">
-        <x:v>三天后穿越古代，我贷款搬空商城！</x:v>
+        <x:v>那块玉，带我们回家</x:v>
       </x:c>
       <x:c r="C38" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D38" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>11.3</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
         <x:v>6</x:v>
@@ -4624,7 +4063,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G38" s="11" t="str">
-        <x:v>2026-09-14 20-13</x:v>
+        <x:v>2026-09-14 09-24</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -4632,22 +4071,22 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="10" t="str">
-        <x:v>退婚从抢我车位开始</x:v>
+        <x:v>闪婚老公有点野</x:v>
       </x:c>
       <x:c r="C39" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D39" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>11.3</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G39" s="11" t="str">
-        <x:v>2026-09-13 18-11</x:v>
+        <x:v>2026-09-15 01-59</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -4655,22 +4094,22 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="10" t="str">
-        <x:v>全家施压：我反手签了过户合同</x:v>
+        <x:v>离婚那天我多了个痞帅老爹</x:v>
       </x:c>
       <x:c r="C40" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D40" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>12.7</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G40" s="11" t="str">
-        <x:v>2026-09-13 14-11</x:v>
+        <x:v>2026-09-15 02-44</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -4678,22 +4117,22 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="10" t="str">
-        <x:v>一张废票毁了她</x:v>
+        <x:v>不靠谱爸妈很靠谱</x:v>
       </x:c>
       <x:c r="C41" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D41" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E41" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F41" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G41" s="11" t="str">
-        <x:v>2026-09-14 05-11</x:v>
+        <x:v>2026-09-14 21-12</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -4701,22 +4140,22 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B42" s="10" t="str">
-        <x:v>拂衣震九州</x:v>
+        <x:v>427元扳倒老油条</x:v>
       </x:c>
       <x:c r="C42" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D42" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>15.7</x:v>
       </x:c>
       <x:c r="E42" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F42" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G42" s="11" t="str">
-        <x:v>2026-09-15 01-12</x:v>
+        <x:v>2026-09-14 20-18</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -4724,22 +4163,22 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" s="10" t="str">
-        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
+        <x:v>穿书后我带萌宝上门认爹</x:v>
       </x:c>
       <x:c r="C43" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D43" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>16.3</x:v>
       </x:c>
       <x:c r="E43" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F43" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G43" s="11" t="str">
-        <x:v>2026-09-13 18-11</x:v>
+        <x:v>2026-09-15 01-59</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -4747,22 +4186,22 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="10" t="str">
-        <x:v>反派拿捏！</x:v>
+        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
       </x:c>
       <x:c r="C44" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D44" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>17.7</x:v>
       </x:c>
       <x:c r="E44" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F44" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G44" s="11" t="str">
-        <x:v>2026-09-14 06-11</x:v>
+        <x:v>2026-09-15 02-44</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -4770,22 +4209,160 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="10" t="str">
-        <x:v>青城山下来个姑奶奶</x:v>
+        <x:v>零元年终奖</x:v>
       </x:c>
       <x:c r="C45" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D45" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="E45" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F45" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G45" s="11" t="str">
-        <x:v>2026-09-14 11-12</x:v>
+        <x:v>2026-09-13 22-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="11" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B46" s="10" t="str">
+        <x:v>我SSS级狂龙，出世即无敌</x:v>
+      </x:c>
+      <x:c r="C46" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D46" s="11" t="n">
+        <x:v>5.5</x:v>
+      </x:c>
+      <x:c r="E46" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F46" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G46" s="11" t="str">
+        <x:v>2026-09-15 01-59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="11" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B47" s="10" t="str">
+        <x:v>一碗人间赴景深</x:v>
+      </x:c>
+      <x:c r="C47" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D47" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E47" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F47" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G47" s="11" t="str">
+        <x:v>2026-09-14 09-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="11" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B48" s="10" t="str">
+        <x:v>白鹿照归途</x:v>
+      </x:c>
+      <x:c r="C48" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D48" s="11" t="n">
+        <x:v>12.5</x:v>
+      </x:c>
+      <x:c r="E48" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F48" s="11" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G48" s="11" t="str">
+        <x:v>2026-09-14 09-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="11" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B49" s="10" t="str">
+        <x:v>三天后穿越古代，我贷款搬空商城！</x:v>
+      </x:c>
+      <x:c r="C49" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D49" s="11" t="n">
+        <x:v>8.5</x:v>
+      </x:c>
+      <x:c r="E49" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F49" s="11" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G49" s="11" t="str">
+        <x:v>2026-09-14 21-12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="11" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B50" s="10" t="str">
+        <x:v>假老板娘遇上真董事长</x:v>
+      </x:c>
+      <x:c r="C50" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D50" s="11" t="n">
+        <x:v>12.5</x:v>
+      </x:c>
+      <x:c r="E50" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F50" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G50" s="11" t="str">
+        <x:v>2026-09-15 02-44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="11" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B51" s="10" t="str">
+        <x:v>那半块玉佩</x:v>
+      </x:c>
+      <x:c r="C51" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D51" s="11" t="n">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="E51" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F51" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G51" s="11" t="str">
+        <x:v>2026-09-14 09-24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -29789,7 +29366,7 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>898</x:v>
+        <x:v>899</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
         <x:v>52.2%</x:v>
@@ -29803,7 +29380,7 @@
         <x:v>476</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>27.7%</x:v>
+        <x:v>27.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -29811,10 +29388,10 @@
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>345</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>20.1%</x:v>
+        <x:v>20.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
@@ -29849,7 +29426,7 @@
         <x:v>50-79集</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>676</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
         <x:v>42.8%</x:v>
@@ -29860,10 +29437,10 @@
         <x:v>80-99集</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>12.5%</x:v>
+        <x:v>12.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -29871,10 +29448,10 @@
         <x:v>100集以上</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>529</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>33.5%</x:v>
+        <x:v>33.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
@@ -29898,10 +29475,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>754</x:v>
+        <x:v>758</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>43.9%</x:v>
+        <x:v>44.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -29912,7 +29489,7 @@
         <x:v>309</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>18.0%</x:v>
+        <x:v>17.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -30244,7 +29821,7 @@
         <x:v>上榜9次</x:v>
       </x:c>
       <x:c r="B49" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C49" s="11" t="str">
         <x:v>1.9%</x:v>
@@ -30255,10 +29832,10 @@
         <x:v>上榜8次</x:v>
       </x:c>
       <x:c r="B50" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C50" s="11" t="str">
-        <x:v>2.8%</x:v>
+        <x:v>2.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -30266,10 +29843,10 @@
         <x:v>上榜7次</x:v>
       </x:c>
       <x:c r="B51" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C51" s="11" t="str">
-        <x:v>2.2%</x:v>
+        <x:v>2.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -30288,7 +29865,7 @@
         <x:v>上榜5次</x:v>
       </x:c>
       <x:c r="B53" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C53" s="11" t="str">
         <x:v>4.1%</x:v>
@@ -30310,10 +29887,10 @@
         <x:v>上榜3次</x:v>
       </x:c>
       <x:c r="B55" s="11" t="n">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C55" s="11" t="str">
-        <x:v>11.3%</x:v>
+        <x:v>11.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -30321,10 +29898,10 @@
         <x:v>上榜2次</x:v>
       </x:c>
       <x:c r="B56" s="11" t="n">
-        <x:v>320</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="C56" s="11" t="str">
-        <x:v>18.6%</x:v>
+        <x:v>18.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -30332,10 +29909,10 @@
         <x:v>上榜1次</x:v>
       </x:c>
       <x:c r="B57" s="11" t="n">
-        <x:v>743</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="C57" s="11" t="str">
-        <x:v>43.2%</x:v>
+        <x:v>43.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="22" customHeight="1">
@@ -30359,10 +29936,10 @@
         <x:v>CP自营</x:v>
       </x:c>
       <x:c r="B61" s="11" t="n">
-        <x:v>1145</x:v>
+        <x:v>1149</x:v>
       </x:c>
       <x:c r="C61" s="11" t="str">
-        <x:v>66.6%</x:v>
+        <x:v>66.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -30373,7 +29950,7 @@
         <x:v>563</x:v>
       </x:c>
       <x:c r="C62" s="11" t="str">
-        <x:v>32.8%</x:v>
+        <x:v>32.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -30751,7 +30328,7 @@
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="10" t="str">
-        <x:v>云影漫剧</x:v>
+        <x:v>云间漫剧-玉川</x:v>
       </x:c>
       <x:c r="B100" s="11" t="n">
         <x:v>5</x:v>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R1855fb0984df4879"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="R98ea4b9401794981"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="R10d32ae6ee5b46ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="Rf8b2c838605346a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP20剧重点跟踪" sheetId="5" r:id="R20ae3fde751c4700"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="6" r:id="R426efd3d9b2d434e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="7" r:id="R83453d8a29434911"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="8" r:id="Rd30ba2c0e43d4710"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="9" r:id="R0a1f9334f60841fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R3665e6e048274da3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="Rf8c5e0703cf1402e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="R401745f0829d4a7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="Rf84bac82e8844f97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP20剧重点跟踪" sheetId="5" r:id="Re7355b82b1474f87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="6" r:id="R487b5ef519654edd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="7" r:id="Re0e8f0c803764f61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="8" r:id="R1f2227aa6dd64d09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="9" r:id="Rd26185b476e04050"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -424,31 +424,31 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>县令哭穷五年，李世民进城懵了</x:v>
+        <x:v>1977山猎重生，我以余生偿前错</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>06-29 17:30</x:v>
+        <x:v>08-10 20:00</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E4" s="10" t="n">
-        <x:v>67</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="F4" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G4" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧 / 种田囤货</x:v>
       </x:c>
       <x:c r="H4" s="11" t="n">
-        <x:v>86</x:v>
+        <x:v>10183</x:v>
       </x:c>
       <x:c r="I4" s="11" t="str">
-        <x:v>0.78</x:v>
+        <x:v>1.07</x:v>
       </x:c>
       <x:c r="J4" s="10" t="str">
-        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15</x:v>
+        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-13、2026-09-15</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -456,31 +456,31 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>1977山猎重生，我以余生偿前错</x:v>
+        <x:v>县令哭穷五年，李世民进城懵了</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>08-10 20:00</x:v>
+        <x:v>06-29 17:30</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E5" s="10" t="n">
-        <x:v>375</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F5" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="G5" s="10" t="str">
-        <x:v>年代怀旧 / 种田囤货</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="H5" s="11" t="n">
-        <x:v>10183</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="I5" s="11" t="str">
-        <x:v>1.07</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="J5" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-13</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1165,13 +1165,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B2" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
-        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
+        <x:v>离婚那天我多了个痞帅老爹</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>09-13 09:58</x:v>
+        <x:v>2026-09-13</x:v>
       </x:c>
       <x:c r="E2" s="11" t="str"/>
       <x:c r="F2" s="11" t="str"/>
@@ -1181,34 +1181,28 @@
       <x:c r="H2" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I2" s="11" t="n">
-        <x:v>66</x:v>
-      </x:c>
+      <x:c r="I2" s="11" t="str"/>
       <x:c r="J2" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K2" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L2" s="11" t="str">
-        <x:v>创想剧场</x:v>
-      </x:c>
-      <x:c r="M2" s="10" t="str">
-        <x:v>游戏公会会长林小勇筹备婚礼，却在婚宴上遭遇未婚妻临时加价逼婚。危急时刻，几位相交多年的游戏老友现身力挺他，林小勇果断取消婚礼。之后他搬进好友赠送的别墅，与陈董的两个女儿渐渐熟识。同学聚会上，众人见识到林小勇不一般的际遇。平静日子没过多久，当年游戏里的宿敌将出席游戏八周年嘉年华，一众老友决定赴约，一场新旧对决即将开启。</x:v>
-      </x:c>
+        <x:v>家庭伦理 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="L2" s="11" t="str"/>
+      <x:c r="M2" s="10" t="str"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
-        <x:v>小妹初长成</x:v>
+        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>2026-09-13</x:v>
+        <x:v>09-13 09:58</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str"/>
       <x:c r="F3" s="11" t="str"/>
@@ -1218,28 +1212,34 @@
       <x:c r="H3" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I3" s="11" t="str"/>
+      <x:c r="I3" s="11" t="n">
+        <x:v>66</x:v>
+      </x:c>
       <x:c r="J3" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K3" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L3" s="11" t="str"/>
-      <x:c r="M3" s="10" t="str"/>
+      <x:c r="L3" s="11" t="str">
+        <x:v>创想剧场</x:v>
+      </x:c>
+      <x:c r="M3" s="10" t="str">
+        <x:v>游戏公会会长林小勇筹备婚礼，却在婚宴上遭遇未婚妻临时加价逼婚。危急时刻，几位相交多年的游戏老友现身力挺他，林小勇果断取消婚礼。之后他搬进好友赠送的别墅，与陈董的两个女儿渐渐熟识。同学聚会上，众人见识到林小勇不一般的际遇。平静日子没过多久，当年游戏里的宿敌将出席游戏八周年嘉年华，一众老友决定赴约，一场新旧对决即将开启。</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
-        <x:v>婚礼当天我不嫁了</x:v>
+        <x:v>员工跑路我扩店</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>09-14 09:00</x:v>
+        <x:v>09-13 08:58</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str"/>
       <x:c r="F4" s="11" t="str"/>
@@ -1250,19 +1250,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I4" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J4" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K4" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="L4" s="11" t="str">
         <x:v>大梨看剧</x:v>
       </x:c>
       <x:c r="M4" s="10" t="str">
-        <x:v>婚礼当天，沈清面对不同婚俗，勇敢表达自我，果断选择结束婚约。哥哥和好友支持，她用法律与智慧处理彩礼、名誉及后续事宜，守护尊严与安全。成长历程中，她开启独立新生活，搬入温暖新家，与家人朋友相伴成长。故事传递出，婚姻应建立在尊重、平等和真诚之上，表达选择，才能拥抱更好的未来。</x:v>
+        <x:v>林辰经营天力健身馆，年终为员工每人发放五万元奖金。几位教练希望获得更多发展空间，与林辰理念产生分歧，决定在隔壁开设新馆，一场实力较量就此展开。林辰选择升级场地、引进专业团队，并提拔刘阿姨担任店长。正月初七，千名会员到场，用选择见证真诚服务的价值。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1270,13 +1270,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>49</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
-        <x:v>长工失牛，焉知非福</x:v>
+        <x:v>风雪边界</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>2026-09-13</x:v>
+        <x:v>09-14 03:01</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str"/>
       <x:c r="F5" s="11" t="str"/>
@@ -1286,28 +1286,34 @@
       <x:c r="H5" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I5" s="11" t="str"/>
+      <x:c r="I5" s="11" t="n">
+        <x:v>53</x:v>
+      </x:c>
       <x:c r="J5" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K5" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L5" s="11" t="str"/>
-      <x:c r="M5" s="10" t="str"/>
+      <x:c r="L5" s="11" t="str">
+        <x:v>腿毛漫漫</x:v>
+      </x:c>
+      <x:c r="M5" s="10" t="str">
+        <x:v>高原补给站老板岑夏坚持完整安全套餐，却遭企业负责人质疑价格，团队转投低价营地。暴雪突至，危机逼近，岑夏仍坚守原则，以专业判断协助应急处置，也让众人重新理解安全的价值。真正昂贵的不是房费，而是忽视风险的代价。敬畏自然、尊重专业，安全永远值得认真对待。</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>427元扳倒老油条</x:v>
+        <x:v>小妹初长成</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>09-13 16:00</x:v>
+        <x:v>2026-09-13</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str"/>
       <x:c r="F6" s="11" t="str"/>
@@ -1317,34 +1323,28 @@
       <x:c r="H6" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I6" s="11" t="n">
-        <x:v>55</x:v>
-      </x:c>
+      <x:c r="I6" s="11" t="str"/>
       <x:c r="J6" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K6" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L6" s="11" t="str">
-        <x:v>安然然</x:v>
-      </x:c>
-      <x:c r="M6" s="10" t="str">
-        <x:v>职场新人许宁向老员工马丽芬讨要427元代垫外卖款，反遭易绑架马丽芬交出饭钱后怀恨在心，利用行政特权私吞福利，并在组织团餐时疏同事差价许宁按兵不动收集证据，最终将马丽芬长期贪占两万余元的行径在老板曝光的照片中马丽芬被直接开除，许宁成功维护了职场底线。</x:v>
-      </x:c>
+      <x:c r="L6" s="11" t="str"/>
+      <x:c r="M6" s="10" t="str"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
-        <x:v>重生80，救下神雕后我带村民走出大山</x:v>
+        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>09-13 09:00</x:v>
+        <x:v>09-13 08:00</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str"/>
       <x:c r="F7" s="11" t="str"/>
@@ -1355,19 +1355,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I7" s="11" t="n">
-        <x:v>187</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J7" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K7" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="L7" s="11" t="str">
-        <x:v>拾光漫漫</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="M7" s="10" t="str">
-        <x:v>林大山遭人为意外，意外重生回到1980年。前世他错信爱人落得凄惨下场，重生后果断当众退婚。机缘巧合救下受伤的灵智神雕金羽，还遇见落难善良的白秋月。他携手知恩图报的神雕，依托卧龙山的资源，发掘名贵药材，抓住时代发展机遇。面对同行刁难，林大山坚守本心，凭借智慧与实干，包下荒山兴办药材加工坊。他善待家人，带领乡里百姓勤劳致富，在八十年代的时代浪潮里，靠着双手改写命运，收获美满爱情与事业。</x:v>
+        <x:v>大晋七公主沈令仪，自幼被冷落于听竹宫，沉默藏锋，苟全性命。宫宴之上，太子带回的秦照雪笑盈盈提议将她送去北狄和亲。满殿以为皇帝会点头，他却掷出“废太子”三字。一夜之间，沈令仪被推到台前。北狄求和的急报恰在此时入京——与她方才所言分毫不差。可当她回望母亲遗下的那半卷秘策时，才发现这局棋，早在二十年前就已落子。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1375,13 +1375,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
-        <x:v>河箱送福来</x:v>
+        <x:v>四个崽崽瞒不住了</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>09-13 11:00</x:v>
+        <x:v>09-15 00:08</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str"/>
       <x:c r="F8" s="11" t="str"/>
@@ -1392,7 +1392,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="J8" s="10" t="str">
         <x:v>其他</x:v>
@@ -1401,10 +1401,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L8" s="11" t="str">
-        <x:v>灵心讲故事</x:v>
+        <x:v>桃子动漫剧场</x:v>
       </x:c>
       <x:c r="M8" s="10" t="str">
-        <x:v>张家老两口从河中救回一只木箱，收养了箱中受伤的福生。福生长大后修桥开田，引水惠及乡亲，成家立业。二老相继离世后，山洪威胁村庄，福生为救乡亲舍命撑住巨石，最终重伤落水，下落不明。秀娥守着小院苦等多年，直到熟悉的声音再次响起。</x:v>
+        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1412,13 +1412,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
-        <x:v>乡宴见人心</x:v>
+        <x:v>我赚上千万跟爸妈说50W，隔天就被找上门</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>09-13 17:12</x:v>
+        <x:v>09-13 08:00</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str"/>
       <x:c r="F9" s="11" t="str"/>
@@ -1429,19 +1429,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I9" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J9" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K9" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L9" s="11" t="str">
-        <x:v>黑白动漫</x:v>
+        <x:v>至尊爽剧社</x:v>
       </x:c>
       <x:c r="M9" s="10" t="str">
-        <x:v>高满仓在赵家大院办了八年流水席，十里八村都认他的手艺。眼看生意越来越旺，院主赵金贵突然把租金翻倍，还要按桌抽钱。高满仓干脆带着人和家伙搬进镇外的废米厂，从头再来。赵金贵以为守着大院就守住了客人，靠低价抢生意，却越省越狠。一边是稳稳当当把席办好，一边是亲手砸掉自己的口碑，这场较量最后看的是院子，还是人心。</x:v>
+        <x:v>三十二岁那年，贺川用六年孤注一掷的钻研，换来了七千六百万的回报。可财富还没捂热，先尝到的却是亲人无度的索取。他谎称只赚五十万，叮嘱保密，却挡不住消息走漏。隔天登门的亲戚不止要借钱买房，更联手外人盗用他的身份资料，试图冒名签约、伪造担保债务。贺川报警取证，警方介入追回大部分资金，涉案者包括部分机构人员均承担了法律责任，这笔帐，能否算清？</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1449,13 +1449,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
-        <x:v>员工跑路我扩店</x:v>
+        <x:v>重生80，救下神雕后我带村民走出大山</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>09-13 08:58</x:v>
+        <x:v>09-13 09:00</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str"/>
       <x:c r="F10" s="11" t="str"/>
@@ -1466,19 +1466,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I10" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="J10" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K10" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="L10" s="11" t="str">
-        <x:v>大梨看剧</x:v>
+        <x:v>拾光漫漫</x:v>
       </x:c>
       <x:c r="M10" s="10" t="str">
-        <x:v>林辰经营天力健身馆，年终为员工每人发放五万元奖金。几位教练希望获得更多发展空间，与林辰理念产生分歧，决定在隔壁开设新馆，一场实力较量就此展开。林辰选择升级场地、引进专业团队，并提拔刘阿姨担任店长。正月初七，千名会员到场，用选择见证真诚服务的价值。</x:v>
+        <x:v>林大山遭人为意外，意外重生回到1980年。前世他错信爱人落得凄惨下场，重生后果断当众退婚。机缘巧合救下受伤的灵智神雕金羽，还遇见落难善良的白秋月。他携手知恩图报的神雕，依托卧龙山的资源，发掘名贵药材，抓住时代发展机遇。面对同行刁难，林大山坚守本心，凭借智慧与实干，包下荒山兴办药材加工坊。他善待家人，带领乡里百姓勤劳致富，在八十年代的时代浪潮里，靠着双手改写命运，收获美满爱情与事业。</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1486,13 +1486,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C11" s="10" t="str">
-        <x:v>我赚上千万跟爸妈说50W，隔天就被找上门</x:v>
+        <x:v>河箱送福来</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>09-13 08:00</x:v>
+        <x:v>09-13 11:00</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str"/>
       <x:c r="F11" s="11" t="str"/>
@@ -1503,7 +1503,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I11" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J11" s="10" t="str">
         <x:v>其他</x:v>
@@ -1512,10 +1512,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L11" s="11" t="str">
-        <x:v>至尊爽剧社</x:v>
+        <x:v>灵心讲故事</x:v>
       </x:c>
       <x:c r="M11" s="10" t="str">
-        <x:v>三十二岁那年，贺川用六年孤注一掷的钻研，换来了七千六百万的回报。可财富还没捂热，先尝到的却是亲人无度的索取。他谎称只赚五十万，叮嘱保密，却挡不住消息走漏。隔天登门的亲戚不止要借钱买房，更联手外人盗用他的身份资料，试图冒名签约、伪造担保债务。贺川报警取证，警方介入追回大部分资金，涉案者包括部分机构人员均承担了法律责任，这笔帐，能否算清？</x:v>
+        <x:v>张家老两口从河中救回一只木箱，收养了箱中受伤的福生。福生长大后修桥开田，引水惠及乡亲，成家立业。二老相继离世后，山洪威胁村庄，福生为救乡亲舍命撑住巨石，最终重伤落水，下落不明。秀娥守着小院苦等多年，直到熟悉的声音再次响起。</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1523,36 +1523,36 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
-        <x:v>风雪边界</x:v>
+        <x:v>乡宴见人心</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>09-14 03:01</x:v>
+        <x:v>09-13 17:12</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str"/>
       <x:c r="F12" s="11" t="str"/>
       <x:c r="G12" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H12" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I12" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J12" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K12" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="L12" s="11" t="str">
-        <x:v>腿毛漫漫</x:v>
+        <x:v>黑白动漫</x:v>
       </x:c>
       <x:c r="M12" s="10" t="str">
-        <x:v>高原补给站老板岑夏坚持完整安全套餐，却遭企业负责人质疑价格，团队转投低价营地。暴雪突至，危机逼近，岑夏仍坚守原则，以专业判断协助应急处置，也让众人重新理解安全的价值。真正昂贵的不是房费，而是忽视风险的代价。敬畏自然、尊重专业，安全永远值得认真对待。</x:v>
+        <x:v>高满仓在赵家大院办了八年流水席，十里八村都认他的手艺。眼看生意越来越旺，院主赵金贵突然把租金翻倍，还要按桌抽钱。高满仓干脆带着人和家伙搬进镇外的废米厂，从头再来。赵金贵以为守着大院就守住了客人，靠低价抢生意，却越省越狠。一边是稳稳当当把席办好，一边是亲手砸掉自己的口碑，这场较量最后看的是院子，还是人心。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1560,67 +1560,73 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B13" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
-        <x:v>离婚那天我多了个痞帅老爹</x:v>
+        <x:v>427元扳倒老油条</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
-        <x:v>2026-09-13</x:v>
+        <x:v>09-13 16:00</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str"/>
       <x:c r="F13" s="11" t="str"/>
       <x:c r="G13" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H13" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I13" s="11" t="str"/>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I13" s="11" t="n">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="J13" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K13" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="L13" s="11" t="str"/>
-      <x:c r="M13" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L13" s="11" t="str">
+        <x:v>安然然</x:v>
+      </x:c>
+      <x:c r="M13" s="10" t="str">
+        <x:v>职场新人许宁向老员工马丽芬讨要427元代垫外卖款，反遭易绑架马丽芬交出饭钱后怀恨在心，利用行政特权私吞福利，并在组织团餐时疏同事差价许宁按兵不动收集证据，最终将马丽芬长期贪占两万余元的行径在老板曝光的照片中马丽芬被直接开除，许宁成功维护了职场底线。</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B14" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
-        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
+        <x:v>婚礼当天我不嫁了</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>09-13 08:00</x:v>
+        <x:v>09-14 09:00</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str"/>
       <x:c r="F14" s="11" t="str"/>
       <x:c r="G14" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H14" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I14" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="J14" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K14" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L14" s="11" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>大梨看剧</x:v>
       </x:c>
       <x:c r="M14" s="10" t="str">
-        <x:v>大晋七公主沈令仪，自幼被冷落于听竹宫，沉默藏锋，苟全性命。宫宴之上，太子带回的秦照雪笑盈盈提议将她送去北狄和亲。满殿以为皇帝会点头，他却掷出“废太子”三字。一夜之间，沈令仪被推到台前。北狄求和的急报恰在此时入京——与她方才所言分毫不差。可当她回望母亲遗下的那半卷秘策时，才发现这局棋，早在二十年前就已落子。</x:v>
+        <x:v>婚礼当天，沈清面对不同婚俗，勇敢表达自我，果断选择结束婚约。哥哥和好友支持，她用法律与智慧处理彩礼、名誉及后续事宜，守护尊严与安全。成长历程中，她开启独立新生活，搬入温暖新家，与家人朋友相伴成长。故事传递出，婚姻应建立在尊重、平等和真诚之上，表达选择，才能拥抱更好的未来。</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1628,50 +1634,44 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B15" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
+        <x:v>结婚八年，我娶的原来是仇人的女儿</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
-        <x:v>09-15 00:08</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str"/>
       <x:c r="F15" s="11" t="str"/>
       <x:c r="G15" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H15" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I15" s="11" t="n">
-        <x:v>124</x:v>
-      </x:c>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I15" s="11" t="str"/>
       <x:c r="J15" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K15" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L15" s="11" t="str">
-        <x:v>桃子动漫剧场</x:v>
-      </x:c>
-      <x:c r="M15" s="10" t="str">
-        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
-      </x:c>
+        <x:v>家庭伦理 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="L15" s="11" t="str"/>
+      <x:c r="M15" s="10" t="str"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C16" s="10" t="str">
-        <x:v>结婚八年，我娶的原来是仇人的女儿</x:v>
+        <x:v>重生极品婆婆，带全家发家致富！</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>09-14 20:29</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str"/>
       <x:c r="F16" s="11" t="str"/>
@@ -1679,39 +1679,45 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H16" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="I16" s="11" t="str"/>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I16" s="11" t="n">
+        <x:v>126</x:v>
+      </x:c>
       <x:c r="J16" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K16" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="L16" s="11" t="str"/>
-      <x:c r="M16" s="10" t="str"/>
+        <x:v>家庭伦理 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="L16" s="11" t="str">
+        <x:v>懒少爱我</x:v>
+      </x:c>
+      <x:c r="M16" s="10" t="str">
+        <x:v>寡妇傅兰秀前世一生吝啬守财，刻薄对待儿女儿媳，到头来钱财被贼人掠夺，落得个凄惨离世的下场。一朝重生，她回到悲剧尚未发生之时。痛定思痛，她彻底改掉抠门的性子，学着善待家里的晚辈。可日子并不太平，爱占便宜的亲戚总上门搅扰，家中两个儿媳也矛盾不断，家务是非接连找上门。傅兰秀靠着清醒的头脑，一边化解各类家庭纷争，一边寻找营生门路，努力扭转命运，拼尽全力守护一家人的安稳生活。</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>49</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C17" s="10" t="str">
-        <x:v>长工失牛，焉知非福</x:v>
+        <x:v>偷脸</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
-        <x:v>2026-09-13</x:v>
-      </x:c>
-      <x:c r="E17" s="11" t="n">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="F17" s="11" t="str">
-        <x:v>↑46位</x:v>
-      </x:c>
-      <x:c r="G17" s="11" t="str"/>
-      <x:c r="H17" s="11" t="str"/>
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="str"/>
+      <x:c r="F17" s="11" t="str"/>
+      <x:c r="G17" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H17" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="I17" s="11" t="str"/>
       <x:c r="J17" s="10" t="str">
         <x:v>未标注</x:v>
@@ -1727,67 +1733,73 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C18" s="10" t="str">
-        <x:v>结婚八年，我娶的原来是仇人的女儿</x:v>
+        <x:v>员工跑路我扩店</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>09-13 08:58</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
-        <x:v>35</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F18" s="11" t="str">
-        <x:v>↑14位</x:v>
+        <x:v>↑56位</x:v>
       </x:c>
       <x:c r="G18" s="11" t="str"/>
       <x:c r="H18" s="11" t="str"/>
-      <x:c r="I18" s="11" t="str"/>
+      <x:c r="I18" s="11" t="n">
+        <x:v>70</x:v>
+      </x:c>
       <x:c r="J18" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K18" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="L18" s="11" t="str"/>
-      <x:c r="M18" s="10" t="str"/>
+        <x:v>都市职场</x:v>
+      </x:c>
+      <x:c r="L18" s="11" t="str">
+        <x:v>大梨看剧</x:v>
+      </x:c>
+      <x:c r="M18" s="10" t="str">
+        <x:v>林辰经营天力健身馆，年终为员工每人发放五万元奖金。几位教练希望获得更多发展空间，与林辰理念产生分歧，决定在隔壁开设新馆，一场实力较量就此展开。林辰选择升级场地、引进专业团队，并提拔刘阿姨担任店长。正月初七，千名会员到场，用选择见证真诚服务的价值。</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C19" s="10" t="str">
-        <x:v>风雪边界</x:v>
+        <x:v>活宝老爹再赴青春，竟与女儿同上大学</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
-        <x:v>09-14 03:01</x:v>
+        <x:v>09-13 00:08</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F19" s="11" t="str">
-        <x:v>↑13位</x:v>
+        <x:v>↑54位</x:v>
       </x:c>
       <x:c r="G19" s="11" t="str"/>
       <x:c r="H19" s="11" t="str"/>
       <x:c r="I19" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J19" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K19" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="L19" s="11" t="str">
-        <x:v>腿毛漫漫</x:v>
+        <x:v>长风剧场</x:v>
       </x:c>
       <x:c r="M19" s="10" t="str">
-        <x:v>高原补给站老板岑夏坚持完整安全套餐，却遭企业负责人质疑价格，团队转投低价营地。暴雪突至，危机逼近，岑夏仍坚守原则，以专业判断协助应急处置，也让众人重新理解安全的价值。真正昂贵的不是房费，而是忽视风险的代价。敬畏自然、尊重专业，安全永远值得认真对待。</x:v>
+        <x:v>45岁的白烨意外激活成长系统。只要亲身体验年轻人的日常，就能重拾青春活力，还能收获丰厚奖励。为完成系统任务，他报名成人高考，顺利考入大学，竟和女儿成了同校同学。重返校园的白烨，一边认真完成任务感受青春，一边在校园里开启一段充满趣味的全新人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1795,36 +1807,298 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C20" s="10" t="str">
-        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
+        <x:v>我赚上千万跟爸妈说50W，隔天就被找上门</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
         <x:v>09-13 08:00</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F20" s="11" t="str">
-        <x:v>↑1位</x:v>
+        <x:v>↑33位</x:v>
       </x:c>
       <x:c r="G20" s="11" t="str"/>
       <x:c r="H20" s="11" t="str"/>
       <x:c r="I20" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J20" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K20" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L20" s="11" t="str">
+        <x:v>至尊爽剧社</x:v>
+      </x:c>
+      <x:c r="M20" s="10" t="str">
+        <x:v>三十二岁那年，贺川用六年孤注一掷的钻研，换来了七千六百万的回报。可财富还没捂热，先尝到的却是亲人无度的索取。他谎称只赚五十万，叮嘱保密，却挡不住消息走漏。隔天登门的亲戚不止要借钱买房，更联手外人盗用他的身份资料，试图冒名签约、伪造担保债务。贺川报警取证，警方介入追回大部分资金，涉案者包括部分机构人员均承担了法律责任，这笔帐，能否算清？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B21" s="11" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C21" s="10" t="str">
+        <x:v>丈母娘住下我搬走</x:v>
+      </x:c>
+      <x:c r="D21" s="11" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="E21" s="11" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F21" s="11" t="str">
+        <x:v>↑19位</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="str"/>
+      <x:c r="H21" s="11" t="str"/>
+      <x:c r="I21" s="11" t="str"/>
+      <x:c r="J21" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="K21" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L21" s="11" t="str"/>
+      <x:c r="M21" s="10" t="str"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B22" s="11" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C22" s="10" t="str">
+        <x:v>重生极品婆婆，带全家发家致富！</x:v>
+      </x:c>
+      <x:c r="D22" s="11" t="str">
+        <x:v>09-14 20:29</x:v>
+      </x:c>
+      <x:c r="E22" s="11" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F22" s="11" t="str">
+        <x:v>↑14位</x:v>
+      </x:c>
+      <x:c r="G22" s="11" t="str"/>
+      <x:c r="H22" s="11" t="str"/>
+      <x:c r="I22" s="11" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="J22" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K22" s="10" t="str">
+        <x:v>家庭伦理 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="L22" s="11" t="str">
+        <x:v>懒少爱我</x:v>
+      </x:c>
+      <x:c r="M22" s="10" t="str">
+        <x:v>寡妇傅兰秀前世一生吝啬守财，刻薄对待儿女儿媳，到头来钱财被贼人掠夺，落得个凄惨离世的下场。一朝重生，她回到悲剧尚未发生之时。痛定思痛，她彻底改掉抠门的性子，学着善待家里的晚辈。可日子并不太平，爱占便宜的亲戚总上门搅扰，家中两个儿媳也矛盾不断，家务是非接连找上门。傅兰秀靠着清醒的头脑，一边化解各类家庭纷争，一边寻找营生门路，努力扭转命运，拼尽全力守护一家人的安稳生活。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B23" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C23" s="10" t="str">
+        <x:v>离婚那天我多了个痞帅老爹</x:v>
+      </x:c>
+      <x:c r="D23" s="11" t="str">
+        <x:v>2026-09-13</x:v>
+      </x:c>
+      <x:c r="E23" s="11" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F23" s="11" t="str">
+        <x:v>↑12位</x:v>
+      </x:c>
+      <x:c r="G23" s="11" t="str"/>
+      <x:c r="H23" s="11" t="str"/>
+      <x:c r="I23" s="11" t="str"/>
+      <x:c r="J23" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="K23" s="10" t="str">
+        <x:v>家庭伦理 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="L23" s="11" t="str"/>
+      <x:c r="M23" s="10" t="str"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B24" s="11" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C24" s="10" t="str">
+        <x:v>四个崽崽瞒不住了</x:v>
+      </x:c>
+      <x:c r="D24" s="11" t="str">
+        <x:v>09-15 00:08</x:v>
+      </x:c>
+      <x:c r="E24" s="11" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F24" s="11" t="str">
+        <x:v>↑12位</x:v>
+      </x:c>
+      <x:c r="G24" s="11" t="str"/>
+      <x:c r="H24" s="11" t="str"/>
+      <x:c r="I24" s="11" t="n">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="J24" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K24" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L24" s="11" t="str">
+        <x:v>桃子动漫剧场</x:v>
+      </x:c>
+      <x:c r="M24" s="10" t="str">
+        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B25" s="11" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C25" s="10" t="str">
+        <x:v>小妹初长成</x:v>
+      </x:c>
+      <x:c r="D25" s="11" t="str">
+        <x:v>2026-09-13</x:v>
+      </x:c>
+      <x:c r="E25" s="11" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F25" s="11" t="str">
+        <x:v>↑5位</x:v>
+      </x:c>
+      <x:c r="G25" s="11" t="str"/>
+      <x:c r="H25" s="11" t="str"/>
+      <x:c r="I25" s="11" t="str"/>
+      <x:c r="J25" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="K25" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L25" s="11" t="str"/>
+      <x:c r="M25" s="10" t="str"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B26" s="11" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C26" s="10" t="str">
+        <x:v>婚不容欺</x:v>
+      </x:c>
+      <x:c r="D26" s="11" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="E26" s="11" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F26" s="11" t="str">
+        <x:v>↑3位</x:v>
+      </x:c>
+      <x:c r="G26" s="11" t="str"/>
+      <x:c r="H26" s="11" t="str"/>
+      <x:c r="I26" s="11" t="str"/>
+      <x:c r="J26" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="K26" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="L26" s="11" t="str"/>
+      <x:c r="M26" s="10" t="str"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B27" s="11" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C27" s="10" t="str">
+        <x:v>辣媳进门，我给公婆撑腰</x:v>
+      </x:c>
+      <x:c r="D27" s="11" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="E27" s="11" t="str"/>
+      <x:c r="F27" s="11" t="str">
+        <x:v>新上榜</x:v>
+      </x:c>
+      <x:c r="G27" s="11" t="str"/>
+      <x:c r="H27" s="11" t="str"/>
+      <x:c r="I27" s="11" t="str"/>
+      <x:c r="J27" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="K27" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L27" s="11" t="str"/>
+      <x:c r="M27" s="10" t="str"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B28" s="11" t="n">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C28" s="10" t="str">
+        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
+      </x:c>
+      <x:c r="D28" s="11" t="str">
+        <x:v>09-15 08:00</x:v>
+      </x:c>
+      <x:c r="E28" s="11" t="str"/>
+      <x:c r="F28" s="11" t="str">
+        <x:v>新上榜</x:v>
+      </x:c>
+      <x:c r="G28" s="11" t="str"/>
+      <x:c r="H28" s="11" t="str"/>
+      <x:c r="I28" s="11" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="J28" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K28" s="10" t="str">
         <x:v>古装宫廷</x:v>
       </x:c>
-      <x:c r="L20" s="11" t="str">
+      <x:c r="L28" s="11" t="str">
         <x:v>心动漫剧场</x:v>
       </x:c>
-      <x:c r="M20" s="10" t="str">
-        <x:v>大晋七公主沈令仪，自幼被冷落于听竹宫，沉默藏锋，苟全性命。宫宴之上，太子带回的秦照雪笑盈盈提议将她送去北狄和亲。满殿以为皇帝会点头，他却掷出“废太子”三字。一夜之间，沈令仪被推到台前。北狄求和的急报恰在此时入京——与她方才所言分毫不差。可当她回望母亲遗下的那半卷秘策时，才发现这局棋，早在二十年前就已落子。</x:v>
+      <x:c r="M28" s="10" t="str">
+        <x:v>沈清韵嫁入靖王府三年，王爷冷落，侧妃得宠。王爷当众许诺，谁先诞下儿子，便请封世子。苏氏先怀孕，沈清韵却发现自己怀的是龙凤胎，她隐瞒消息，买通太医推迟产期，忍痛让苏氏先产子。王爷果然请封庶长子为世子，折子递入宗人府。受理之后，沈清韵才发动，生下龙凤胎。太后与皇上视为祥瑞，下旨赐嫡子承恩为靖王世子、嫡女承华为安乐郡主。王爷措手不及，苏氏地位一落千丈。而沈清韵知道，这只是第一步。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1870,10 +2144,10 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
-        <x:v>结婚八年，我娶的原来是仇人的女儿</x:v>
+        <x:v>辣媳进门，我给公婆撑腰</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
         <x:v>当日新上榜</x:v>
@@ -1887,227 +2161,186 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>别欺负我奶奶</x:v>
+        <x:v>被算计的新娘华丽转身</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
         <x:v>当日新上榜</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>09-02 18:27</x:v>
+        <x:v>07-28 00:29</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
-        <x:v>44</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F3" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="G3" s="10" t="str">
-        <x:v>小焓追剧</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>46</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>和叔叔合伙五年，却用五百块打发我</x:v>
+        <x:v>四个崽崽瞒不住了</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>当日新上榜</x:v>
+        <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>08-07 08:00</x:v>
+        <x:v>09-15 00:08</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F4" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G4" s="10" t="str">
-        <x:v>阅友动漫</x:v>
+        <x:v>桃子动漫剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
+        <x:v>结婚八年，我娶的原来是仇人的女儿</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>今日发布</x:v>
-      </x:c>
-      <x:c r="D5" s="11" t="str">
-        <x:v>09-15 00:08</x:v>
-      </x:c>
-      <x:c r="E5" s="11" t="n">
-        <x:v>124</x:v>
-      </x:c>
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str"/>
+      <x:c r="E5" s="11" t="str"/>
       <x:c r="F5" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="str">
-        <x:v>桃子动漫剧场</x:v>
-      </x:c>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="G5" s="10" t="str"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>我的面包车，你砸不起</x:v>
+        <x:v>丈母娘住下我搬走</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
         <x:v>当日新上榜</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="str">
-        <x:v>08-16 09:30</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="n">
-        <x:v>51</x:v>
-      </x:c>
+      <x:c r="D6" s="11" t="str"/>
+      <x:c r="E6" s="11" t="str"/>
       <x:c r="F6" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="G6" s="10" t="str">
-        <x:v>剧鲸漫剧</x:v>
-      </x:c>
+      <x:c r="G6" s="10" t="str"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>偷脸</x:v>
+        <x:v>一叶守义满山春</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
         <x:v>当日新上榜</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="str"/>
-      <x:c r="E7" s="11" t="str"/>
+      <x:c r="D7" s="11" t="str">
+        <x:v>08-14 10:10</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="n">
+        <x:v>86</x:v>
+      </x:c>
       <x:c r="F7" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="G7" s="10" t="str"/>
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="str">
+        <x:v>挽风文化传媒</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>重生之我为苍生执灯人！</x:v>
+        <x:v>别欺负我奶奶</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>当日新上榜</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>08-28 11:58</x:v>
+        <x:v>09-02 18:27</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F8" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G8" s="10" t="str">
-        <x:v>微风追剧</x:v>
+        <x:v>小焓追剧</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="n">
-        <x:v>84</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>一叶守义满山春</x:v>
+        <x:v>婚不容欺</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
         <x:v>当日新上榜</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="str">
-        <x:v>08-14 10:10</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="n">
-        <x:v>86</x:v>
-      </x:c>
+      <x:c r="D9" s="11" t="str"/>
+      <x:c r="E9" s="11" t="str"/>
       <x:c r="F9" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="G9" s="10" t="str">
-        <x:v>挽风文化传媒</x:v>
-      </x:c>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="G9" s="10" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="n">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>苏辻晏的故事</x:v>
+        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>当日新上榜</x:v>
+        <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>07-18 21:00</x:v>
+        <x:v>09-15 08:00</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
-        <x:v>117</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F10" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G10" s="10" t="str">
-        <x:v>老登动画</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="n">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>最后一次迁就，是放手</x:v>
+        <x:v>偷脸</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
         <x:v>当日新上榜</x:v>
       </x:c>
-      <x:c r="D11" s="11" t="str">
-        <x:v>08-27 18:00</x:v>
-      </x:c>
-      <x:c r="E11" s="11" t="n">
-        <x:v>67</x:v>
-      </x:c>
+      <x:c r="D11" s="11" t="str"/>
+      <x:c r="E11" s="11" t="str"/>
       <x:c r="F11" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="G11" s="10" t="str">
-        <x:v>非洲小白脸</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="11" t="n">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="B12" s="10" t="str">
-        <x:v>我靠预判走向人生巅峰</x:v>
-      </x:c>
-      <x:c r="C12" s="11" t="str">
-        <x:v>当日新上榜</x:v>
-      </x:c>
-      <x:c r="D12" s="11" t="str">
-        <x:v>06-27 15:00</x:v>
-      </x:c>
-      <x:c r="E12" s="11" t="n">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="F12" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="G12" s="10" t="str">
-        <x:v>数智影视-小六看剧</x:v>
-      </x:c>
+      <x:c r="G11" s="10" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2176,7 +2409,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
         <x:v>离家十年，回来女儿被换了</x:v>
@@ -2213,16 +2446,16 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>惊絮无声：傻女的绝杀</x:v>
+        <x:v>破库房的秘密</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>09-06 10:00</x:v>
+        <x:v>2026-09-05</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
         <x:v>7</x:v>
@@ -2233,33 +2466,27 @@
       <x:c r="G3" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H3" s="11" t="n">
-        <x:v>60</x:v>
-      </x:c>
+      <x:c r="H3" s="11" t="str"/>
       <x:c r="I3" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J3" s="11" t="str"/>
       <x:c r="K3" s="11" t="str"/>
-      <x:c r="L3" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
-      </x:c>
-      <x:c r="M3" s="10" t="str">
-        <x:v>沈家人人都是天才，唯独小女儿沈惊絮是公认的傻子。没人知道，她不仅装傻多年，还带着前世金牌律师的记忆重生而来。本想闭嘴躺平一生，谁料内鬼勾结资本做空沈氏，一纸合同就要让全家净身出户、背上百亿债务。父亲落笔前，她终于按住协议“这字不能签！”绝地反杀的沈惊絮，一步步挫败了对沈家的围剿，也让全家人重新认识了自己。沈家也迎来了新生。</x:v>
-      </x:c>
+      <x:c r="L3" s="10" t="str"/>
+      <x:c r="M3" s="10" t="str"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>重生三天前，我用水泥封死地下室</x:v>
+        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>09-09 09:28</x:v>
+        <x:v>09-08 17:58</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
         <x:v>7</x:v>
@@ -2271,7 +2498,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H4" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="I4" s="10" t="str">
         <x:v>其他</x:v>
@@ -2279,24 +2506,24 @@
       <x:c r="J4" s="11" t="str"/>
       <x:c r="K4" s="11" t="str"/>
       <x:c r="L4" s="10" t="str">
-        <x:v>忘忧剧场</x:v>
+        <x:v>禾苗动画</x:v>
       </x:c>
       <x:c r="M4" s="10" t="str">
-        <x:v>阮清重生回被保姆王妈一家害死的三天前，前世她因心善引狼入室，保姆全家蜗居别墅地下室偷窃投毒，最终惨遭勒死。重生后她假装不知，趁王妈外出时用水泥将地下室彻底封死。警方破墙后，五具尸体令真相大白，王妈因盗窃、投毒被判十五年。阮清与父母团聚，恶人终得恶报，她重获新生。</x:v>
+        <x:v>末世异能者沐小暖意外穿书，成为七个反派继子的恶毒后娘。原主辛劳养娃却遭流言中伤，最终含恨而终。沐小暖决心扭转命运，恩威并施管教孩子，凭末世身手进山打猎采药、种地赶集改善家计，更以百年老参为礼，为长子求得名儒霍政谚收为关门弟子。她护佑家人躲过恶人算计与亲戚夺产，建起新宅。七个孩子从怨恨抗拒到真心信赖，争着喊她娘，一家人携手改写命运，收获温暖亲情。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>破库房的秘密</x:v>
+        <x:v>惊絮无声：傻女的绝杀</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>2026-09-05</x:v>
+        <x:v>09-06 10:00</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
         <x:v>7</x:v>
@@ -2307,27 +2534,33 @@
       <x:c r="G5" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H5" s="11" t="str"/>
+      <x:c r="H5" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
       <x:c r="I5" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J5" s="11" t="str"/>
       <x:c r="K5" s="11" t="str"/>
-      <x:c r="L5" s="10" t="str"/>
-      <x:c r="M5" s="10" t="str"/>
+      <x:c r="L5" s="10" t="str">
+        <x:v>闪闪动漫社</x:v>
+      </x:c>
+      <x:c r="M5" s="10" t="str">
+        <x:v>沈家人人都是天才，唯独小女儿沈惊絮是公认的傻子。没人知道，她不仅装傻多年，还带着前世金牌律师的记忆重生而来。本想闭嘴躺平一生，谁料内鬼勾结资本做空沈氏，一纸合同就要让全家净身出户、背上百亿债务。父亲落笔前，她终于按住协议“这字不能签！”绝地反杀的沈惊絮，一步步挫败了对沈家的围剿，也让全家人重新认识了自己。沈家也迎来了新生。</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
+        <x:v>重生三天前，我用水泥封死地下室</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>09-08 17:58</x:v>
+        <x:v>09-09 09:28</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
         <x:v>7</x:v>
@@ -2339,7 +2572,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="11" t="n">
-        <x:v>111</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
         <x:v>其他</x:v>
@@ -2347,15 +2580,15 @@
       <x:c r="J6" s="11" t="str"/>
       <x:c r="K6" s="11" t="str"/>
       <x:c r="L6" s="10" t="str">
-        <x:v>禾苗动画</x:v>
+        <x:v>忘忧剧场</x:v>
       </x:c>
       <x:c r="M6" s="10" t="str">
-        <x:v>末世异能者沐小暖意外穿书，成为七个反派继子的恶毒后娘。原主辛劳养娃却遭流言中伤，最终含恨而终。沐小暖决心扭转命运，恩威并施管教孩子，凭末世身手进山打猎采药、种地赶集改善家计，更以百年老参为礼，为长子求得名儒霍政谚收为关门弟子。她护佑家人躲过恶人算计与亲戚夺产，建起新宅。七个孩子从怨恨抗拒到真心信赖，争着喊她娘，一家人携手改写命运，收获温暖亲情。</x:v>
+        <x:v>阮清重生回被保姆王妈一家害死的三天前，前世她因心善引狼入室，保姆全家蜗居别墅地下室偷窃投毒，最终惨遭勒死。重生后她假装不知，趁王妈外出时用水泥将地下室彻底封死。警方破墙后，五具尸体令真相大白，王妈因盗窃、投毒被判十五年。阮清与父母团聚，恶人终得恶报，她重获新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
         <x:v>一墙之隔，皆是人心</x:v>
@@ -2392,16 +2625,16 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>抢个新娘来当后娘第一季</x:v>
+        <x:v>穿书后我带萌宝上门认爹</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>09-08 15:10</x:v>
+        <x:v>09-07 19:18</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
         <x:v>7</x:v>
@@ -2410,10 +2643,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G8" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H8" s="11" t="n">
-        <x:v>177</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
         <x:v>其他</x:v>
@@ -2421,10 +2654,10 @@
       <x:c r="J8" s="11" t="str"/>
       <x:c r="K8" s="11" t="str"/>
       <x:c r="L8" s="10" t="str">
-        <x:v>麻辣公主</x:v>
+        <x:v>虾仁不自在</x:v>
       </x:c>
       <x:c r="M8" s="10" t="str">
-        <x:v>带着十里红妆出嫁那日，我才得知新郎早已另娶，这门亲事不过是盯上了我李家的家产。换作旁人或许忍气吞声，我偏不。我当众拒入侯府，主动上书朝廷，愿以嫁妆资援南方水患，只求解除婚约、护我父母周全。这份胆识赢得安王敬重，他以正妃之礼娶我入门。我立誓此生不做妾、不与人共侍一夫，终得一份彼此尊重的姻缘。</x:v>
+        <x:v>许知棠重生穿进书中，当即带着五岁儿子许小舟登门，将孩子送到亲生父亲——傅氏集团总裁傅临川面前，只想抽身退出剧情。幼儿园里儿子遭同学诬陷、老师偏心，她强势护崽，硬刚蛮横家长与失职老师。亲子鉴定尘埃落定，萌娃黏妈不黏爹，反倒让清冷总裁渐渐上心。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -2432,13 +2665,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>穿书后我带萌宝上门认爹</x:v>
+        <x:v>不靠谱爸妈很靠谱</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>09-07 19:18</x:v>
+        <x:v>09-09 11:08</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
         <x:v>7</x:v>
@@ -2447,10 +2680,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G9" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H9" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str">
         <x:v>其他</x:v>
@@ -2458,24 +2691,24 @@
       <x:c r="J9" s="11" t="str"/>
       <x:c r="K9" s="11" t="str"/>
       <x:c r="L9" s="10" t="str">
-        <x:v>虾仁不自在</x:v>
+        <x:v>灵妹儿</x:v>
       </x:c>
       <x:c r="M9" s="10" t="str">
-        <x:v>许知棠重生穿进书中，当即带着五岁儿子许小舟登门，将孩子送到亲生父亲——傅氏集团总裁傅临川面前，只想抽身退出剧情。幼儿园里儿子遭同学诬陷、老师偏心，她强势护崽，硬刚蛮横家长与失职老师。亲子鉴定尘埃落定，萌娃黏妈不黏爹，反倒让清冷总裁渐渐上心。</x:v>
+        <x:v>外表张扬的年轻夫妻在冬夜救下女婴林小小，用十七年的辛勤劳动和无条件陪伴，为她撑起温暖的家。曾经成绩落后的林小小，在父母的鼓励下重新学习，一步步成长为优秀学生。面对亲生家庭带来的资源与人生选择，她也开始重新理解血缘、养育与责任。当外界的误解影响到父母的生活，林小小决定勇敢站出来，用事实守护家人，也用努力证明真正的爱，是尊重、陪伴和彼此成就。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>凤阙承安</x:v>
+        <x:v>抢个新娘来当后娘第一季</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>09-08 15:10</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
         <x:v>7</x:v>
@@ -2484,29 +2717,35 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G10" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H10" s="11" t="str"/>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H10" s="11" t="n">
+        <x:v>177</x:v>
+      </x:c>
       <x:c r="I10" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J10" s="11" t="str"/>
       <x:c r="K10" s="11" t="str"/>
-      <x:c r="L10" s="10" t="str"/>
-      <x:c r="M10" s="10" t="str"/>
+      <x:c r="L10" s="10" t="str">
+        <x:v>麻辣公主</x:v>
+      </x:c>
+      <x:c r="M10" s="10" t="str">
+        <x:v>带着十里红妆出嫁那日，我才得知新郎早已另娶，这门亲事不过是盯上了我李家的家产。换作旁人或许忍气吞声，我偏不。我当众拒入侯府，主动上书朝廷，愿以嫁妆资援南方水患，只求解除婚约、护我父母周全。这份胆识赢得安王敬重，他以正妃之礼娶我入门。我立誓此生不做妾、不与人共侍一夫，终得一份彼此尊重的姻缘。</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>全家施压：我反手签了过户合同</x:v>
+        <x:v>凤阙承安</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>09-08 16:58</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
         <x:v>7</x:v>
@@ -2515,35 +2754,29 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G11" s="11" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H11" s="11" t="n">
-        <x:v>60</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H11" s="11" t="str"/>
       <x:c r="I11" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J11" s="11" t="str"/>
       <x:c r="K11" s="11" t="str"/>
-      <x:c r="L11" s="10" t="str">
-        <x:v>灵川剧场</x:v>
-      </x:c>
-      <x:c r="M11" s="10" t="str">
-        <x:v>儿子儿媳多次提议我搬回乡下养老，将城里的宽敞住房腾出来给女方父母长期居住。我笑着点头应下，转头便将这套三室朝南的江景房产挂牌出售，最终成交二百八十万元。我随即购置了一套一室一厅的小户型，更换门锁后独自入住。他们上门索要钥匙，我没有开门。名下房产我自有主张，谁也别想插手安排。</x:v>
-      </x:c>
+      <x:c r="L11" s="10" t="str"/>
+      <x:c r="M11" s="10" t="str"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="n">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>不靠谱爸妈很靠谱</x:v>
+        <x:v>重启人生，拒绝校花？</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>09-09 11:08</x:v>
+        <x:v>09-08 08:30</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
         <x:v>7</x:v>
@@ -2555,7 +2788,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H12" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str">
         <x:v>其他</x:v>
@@ -2563,15 +2796,15 @@
       <x:c r="J12" s="11" t="str"/>
       <x:c r="K12" s="11" t="str"/>
       <x:c r="L12" s="10" t="str">
-        <x:v>灵妹儿</x:v>
+        <x:v>肆漫简</x:v>
       </x:c>
       <x:c r="M12" s="10" t="str">
-        <x:v>外表张扬的年轻夫妻在冬夜救下女婴林小小，用十七年的辛勤劳动和无条件陪伴，为她撑起温暖的家。曾经成绩落后的林小小，在父母的鼓励下重新学习，一步步成长为优秀学生。面对亲生家庭带来的资源与人生选择，她也开始重新理解血缘、养育与责任。当外界的误解影响到父母的生活，林小小决定勇敢站出来，用事实守护家人，也用努力证明真正的爱，是尊重、陪伴和彼此成就。</x:v>
+        <x:v>白陌重生回到2004年高考夜，果断避开前世陷害自己的宾馆陷阱，救下被下药的校花江洛菡，彻底扭转人生走向。他不再执着于过往的情感执念，跳出卑微追爱的困局，转而关心恩师健康、规划学业与创业方向，结识志同道合的伙伴。凭借重生阅历清醒选择前路，把握青春重启人生，用行动改写原本遗憾的命运，活出全新成长轨迹。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
         <x:v>重回千禧年，赶海捡出万贯家财</x:v>
@@ -2602,13 +2835,13 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>重启人生，拒绝校花？</x:v>
+        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>09-08 08:30</x:v>
+        <x:v>09-08 11:00</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
         <x:v>7</x:v>
@@ -2620,10 +2853,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G14" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H14" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="I14" s="10" t="str">
         <x:v>其他</x:v>
@@ -2631,24 +2864,24 @@
       <x:c r="J14" s="11" t="str"/>
       <x:c r="K14" s="11" t="str"/>
       <x:c r="L14" s="10" t="str">
-        <x:v>肆漫简</x:v>
+        <x:v>白桃剧场</x:v>
       </x:c>
       <x:c r="M14" s="10" t="str">
-        <x:v>白陌重生回到2004年高考夜，果断避开前世陷害自己的宾馆陷阱，救下被下药的校花江洛菡，彻底扭转人生走向。他不再执着于过往的情感执念，跳出卑微追爱的困局，转而关心恩师健康、规划学业与创业方向，结识志同道合的伙伴。凭借重生阅历清醒选择前路，把握青春重启人生，用行动改写原本遗憾的命运，活出全新成长轨迹。</x:v>
+        <x:v>阿梨一觉睡了三百年，养大的五只小兽尽数离去。她带着五只旧饭碗、十二枚铜钱与一把锈柴刀下山寻兽。昔日的小家伙已成威震四方的妖祖，历经重重相遇与揭秘，阿梨知晓三百年封印的真相，携手五只妖祖，一同对抗祸世灭灵兽神。</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>苏小姐高调离婚，前夫哭惨了</x:v>
+        <x:v>美颜系统开挂，大佬全跪下</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>09-09 00:10</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
         <x:v>7</x:v>
@@ -2657,41 +2890,47 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G15" s="11" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H15" s="11" t="str"/>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H15" s="11" t="n">
+        <x:v>172</x:v>
+      </x:c>
       <x:c r="I15" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J15" s="11" t="str"/>
       <x:c r="K15" s="11" t="str"/>
-      <x:c r="L15" s="10" t="str"/>
-      <x:c r="M15" s="10" t="str"/>
+      <x:c r="L15" s="10" t="str">
+        <x:v>御儿</x:v>
+      </x:c>
+      <x:c r="M15" s="10" t="str">
+        <x:v>曾因外形饱受非议的米珂华丽转身，蜕变得耀眼又夺目。从前对她嗤之以鼻的蒋少开始频频在意，素来冷眼毒舌的陆总不知不觉深陷其中，连一向克己的商界大佬也为她打破原则。米珂凭智商与手腕周旋于众人之间，上演一场势均力敌的情感博弈。没有俗套的救赎，只有双向的拉扯。看一众高高在上的精英暗自较劲、步步沉沦，心甘情愿为她卸下防备。</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="n">
-        <x:v>82</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>美颜系统开挂，大佬全跪下</x:v>
+        <x:v>征地我秒签跑路，全村笑我半年</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>09-09 00:10</x:v>
+        <x:v>09-10 11:30</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E16" s="11" t="n">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="F16" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G16" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H16" s="11" t="n">
-        <x:v>172</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str">
         <x:v>其他</x:v>
@@ -2699,36 +2938,36 @@
       <x:c r="J16" s="11" t="str"/>
       <x:c r="K16" s="11" t="str"/>
       <x:c r="L16" s="10" t="str">
-        <x:v>御儿</x:v>
+        <x:v>小六动漫</x:v>
       </x:c>
       <x:c r="M16" s="10" t="str">
-        <x:v>曾因外形饱受非议的米珂华丽转身，蜕变得耀眼又夺目。从前对她嗤之以鼻的蒋少开始频频在意，素来冷眼毒舌的陆总不知不觉深陷其中，连一向克己的商界大佬也为她打破原则。米珂凭智商与手腕周旋于众人之间，上演一场势均力敌的情感博弈。没有俗套的救赎，只有双向的拉扯。看一众高高在上的精英暗自较劲、步步沉沦，心甘情愿为她卸下防备。</x:v>
+        <x:v>赵家湾迎来高速征地，村民受村长赵德厚鼓动抱团拒签，妄想抬价拿到四百五十万补偿。林远察觉当地岩溶地质暗藏线路改线风险，不顾全村嘲讽，果断签下312万补偿款，带父母搬离老家。后续高速果真改线，全村一分补偿落空。曾经嘲笑林远的村民陷入债务困境，赵德厚登门求助，林远守住底线，一家人握紧安稳生活，告诫众人抉择要靠自己。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="n">
-        <x:v>86</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
+        <x:v>大坝边寻回的真千金</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>09-08 11:00</x:v>
+        <x:v>09-10 11:26</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F17" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G17" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H17" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I17" s="10" t="str">
         <x:v>其他</x:v>
@@ -2736,61 +2975,55 @@
       <x:c r="J17" s="11" t="str"/>
       <x:c r="K17" s="11" t="str"/>
       <x:c r="L17" s="10" t="str">
-        <x:v>白桃剧场</x:v>
+        <x:v>喵琪琪追剧</x:v>
       </x:c>
       <x:c r="M17" s="10" t="str">
-        <x:v>阿梨一觉睡了三百年，养大的五只小兽尽数离去。她带着五只旧饭碗、十二枚铜钱与一把锈柴刀下山寻兽。昔日的小家伙已成威震四方的妖祖，历经重重相遇与揭秘，阿梨知晓三百年封印的真相，携手五只妖祖，一同对抗祸世灭灵兽神。</x:v>
+        <x:v>大坝突发险情，农村女孩夏晚禾凭借熟悉的环境和过人的勇气，不顾危险救下被困的沈长洲。一次意外的救援，让两个陌生人的命运重新交织。随着调查深入，沈长洲发现这个善良坚韧的女孩，竟是自己失散二十年的亲生女儿。面对迟来的亲情和真假千金的风波，夏晚禾没有依靠身份改变人生，而是用智慧、担当和努力证明自己的价值。陆言川也在一次次并肩相处中，被她的真诚与坚强打动，陪她找回亲情，走向新的未来。</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>蒙蒙半故</x:v>
+        <x:v>假老板娘遇上真董事长</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>09-05 20:27</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G18" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H18" s="11" t="n">
-        <x:v>75</x:v>
-      </x:c>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H18" s="11" t="str"/>
       <x:c r="I18" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J18" s="11" t="str"/>
       <x:c r="K18" s="11" t="str"/>
-      <x:c r="L18" s="10" t="str">
-        <x:v>小斐漫剧</x:v>
-      </x:c>
-      <x:c r="M18" s="10" t="str">
-        <x:v>拥有漫长寿命的男人隐姓埋名，以外卖员身份在都市生活。百岁老人临终的遗愿，让他卷入豪门家族的纷争。他结识家族女总裁，接连应对家族内斗、敌对势力与神秘长生组织的重重算计。二人携手揭开千年前的尘封秘辛，对抗妄图窃取长生力量的反派，在危机之中彼此羁绊，还要面对即将开启的上古昆仑之门带来的巨大未知考验。</x:v>
-      </x:c>
+      <x:c r="L18" s="10" t="str"/>
+      <x:c r="M18" s="10" t="str"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>征地我秒签跑路，全村笑我半年</x:v>
+        <x:v>迟来深情皆是刃</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>09-10 11:30</x:v>
+        <x:v>09-09 10:00</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
         <x:v>6</x:v>
@@ -2799,10 +3032,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G19" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H19" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str">
         <x:v>其他</x:v>
@@ -2810,21 +3043,21 @@
       <x:c r="J19" s="11" t="str"/>
       <x:c r="K19" s="11" t="str"/>
       <x:c r="L19" s="10" t="str">
-        <x:v>小六动漫</x:v>
+        <x:v>展瓦-佩云看剧</x:v>
       </x:c>
       <x:c r="M19" s="10" t="str">
-        <x:v>赵家湾迎来高速征地，村民受村长赵德厚鼓动抱团拒签，妄想抬价拿到四百五十万补偿。林远察觉当地岩溶地质暗藏线路改线风险，不顾全村嘲讽，果断签下312万补偿款，带父母搬离老家。后续高速果真改线，全村一分补偿落空。曾经嘲笑林远的村民陷入债务困境，赵德厚登门求助，林远守住底线，一家人握紧安稳生活，告诫众人抉择要靠自己。</x:v>
+        <x:v>天才芯片科研人姜莱，隐去光芒，在婚姻里默默付出四年，却遭遇丈夫沈荀的背叛与冷待。看清现实的她挣脱窒息的婚姻，撕下普通家庭主妇的伪装，重拾科研理想。面对丈夫、情敌的百般算计，她冷静反击。在自研芯重大项目竞标舞台上，姜莱展露真实实力，完成华丽逆袭，实现自我价值。过往伤痛化作成长力量，她告别糟糕的旧生活，向着事业与崭新的人生大步奔赴，迎来属于自己的光明未来。</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>假老板娘遇上真董事长</x:v>
+        <x:v>重生后我守住全村</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>09-10 08:08</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
         <x:v>5</x:v>
@@ -2836,41 +3069,47 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G20" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H20" s="11" t="str"/>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H20" s="11" t="n">
+        <x:v>129</x:v>
+      </x:c>
       <x:c r="I20" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J20" s="11" t="str"/>
       <x:c r="K20" s="11" t="str"/>
-      <x:c r="L20" s="10" t="str"/>
-      <x:c r="M20" s="10" t="str"/>
+      <x:c r="L20" s="10" t="str">
+        <x:v>金果漫剧</x:v>
+      </x:c>
+      <x:c r="M20" s="10" t="str">
+        <x:v>70年代冬，赵满仓在父亲离世后重回鼠灾前八天。面对家中骤变，他选择先护住亲人，带着前世经验迁入碾坊，储粮备药，筑墙防鼠，设点防疫。灾情来临时，他联合李杏儿，刘石头和乡亲稳住村庄，并用账册与规矩澄清父亲名誉。风雪过后，黎家沟建起防鼠坊，猫舍和净粮地窖，众人也在互助中迎来新生。</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>大坝边寻回的真千金</x:v>
+        <x:v>三分钱的取舍</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>09-10 11:26</x:v>
+        <x:v>09-10 17:29</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G21" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H21" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I21" s="10" t="str">
         <x:v>其他</x:v>
@@ -2878,36 +3117,36 @@
       <x:c r="J21" s="11" t="str"/>
       <x:c r="K21" s="11" t="str"/>
       <x:c r="L21" s="10" t="str">
-        <x:v>喵琪琪追剧</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="M21" s="10" t="str">
-        <x:v>大坝突发险情，农村女孩夏晚禾凭借熟悉的环境和过人的勇气，不顾危险救下被困的沈长洲。一次意外的救援，让两个陌生人的命运重新交织。随着调查深入，沈长洲发现这个善良坚韧的女孩，竟是自己失散二十年的亲生女儿。面对迟来的亲情和真假千金的风波，夏晚禾没有依靠身份改变人生，而是用智慧、担当和努力证明自己的价值。陆言川也在一次次并肩相处中，被她的真诚与坚强打动，陪她找回亲情，走向新的未来。</x:v>
+        <x:v>青石沟果农为省下代办三分钱，甩开中间商周成岳，直接对接收购商方洪生收桃。可脱离周成岳统筹调度后，摘桃、排单、装车乱象丛生，桃子积压损耗。周成岳转身接手偏远的十里湾桃园，凭口碑站稳脚跟。经历一季波折，青石沟众人幡然醒悟，重新读懂代办的价值。</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>重生后我守住全村</x:v>
+        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>09-10 08:08</x:v>
+        <x:v>09-11 09:00</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E22" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E22" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="F22" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G22" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H22" s="11" t="n">
-        <x:v>129</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str">
         <x:v>其他</x:v>
@@ -2915,21 +3154,21 @@
       <x:c r="J22" s="11" t="str"/>
       <x:c r="K22" s="11" t="str"/>
       <x:c r="L22" s="10" t="str">
-        <x:v>金果漫剧</x:v>
+        <x:v>阳阳动画</x:v>
       </x:c>
       <x:c r="M22" s="10" t="str">
-        <x:v>70年代冬，赵满仓在父亲离世后重回鼠灾前八天。面对家中骤变，他选择先护住亲人，带着前世经验迁入碾坊，储粮备药，筑墙防鼠，设点防疫。灾情来临时，他联合李杏儿，刘石头和乡亲稳住村庄，并用账册与规矩澄清父亲名誉。风雪过后，黎家沟建起防鼠坊，猫舍和净粮地窖，众人也在互助中迎来新生。</x:v>
+        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>三分钱的取舍</x:v>
+        <x:v>重生一世，我不再痴恋竹马</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>09-10 17:29</x:v>
+        <x:v>09-10 10:00</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
         <x:v>5</x:v>
@@ -2941,10 +3180,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G23" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H23" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
         <x:v>其他</x:v>
@@ -2952,24 +3191,24 @@
       <x:c r="J23" s="11" t="str"/>
       <x:c r="K23" s="11" t="str"/>
       <x:c r="L23" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>锦书映年华</x:v>
       </x:c>
       <x:c r="M23" s="10" t="str">
-        <x:v>青石沟果农为省下代办三分钱，甩开中间商周成岳，直接对接收购商方洪生收桃。可脱离周成岳统筹调度后，摘桃、排单、装车乱象丛生，桃子积压损耗。周成岳转身接手偏远的十里湾桃园，凭口碑站稳脚跟。经历一季波折，青石沟众人幡然醒悟，重新读懂代办的价值。</x:v>
+        <x:v>承平公主前世错恋齐远安，受尽磋磨含恨落幕。一朝重生，恰逢圣旨赐婚，齐远安却当众恳请解除婚约，求取太后义孙女傅明珠。她坦然放手，主动成全二人，看着他们得偿所愿。宁国侯夫人动用旧物强求赐婚，她巧妙改换婚事，选择边关归来、品性刚正的齐远舟。婚后她聪慧通透，看清傅明珠与齐远安的本性，冷眼旁观二人矛盾丛生。历经风波，她与齐远舟彼此扶持，挣脱过往伤痛，收获属于自己安稳坦荡的人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="n">
-        <x:v>31</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
+        <x:v>穿越60我有空间不愁吃喝</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>09-11 09:00</x:v>
+        <x:v>09-07 00:04</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
         <x:v>5</x:v>
@@ -2978,10 +3217,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G24" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H24" s="11" t="n">
-        <x:v>133</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="I24" s="10" t="str">
         <x:v>其他</x:v>
@@ -2989,36 +3228,36 @@
       <x:c r="J24" s="11" t="str"/>
       <x:c r="K24" s="11" t="str"/>
       <x:c r="L24" s="10" t="str">
-        <x:v>阳阳动画</x:v>
+        <x:v>夜珠AI剧场</x:v>
       </x:c>
       <x:c r="M24" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
+        <x:v>现代青年刘大壮意外穿越到60年代，成了同名同姓的16岁穷小子。原主因相亲被拒、家徒四壁，下河摸鱼时溺亡。大壮醒来后发现脑中多了一座九层宝塔空间——内有灵药田与灵泉潭水，作物两小时成熟、产量翻五倍。饥荒年代，别人啃树皮喝稀粥，他靠空间种出满仓土豆粮食，黑市换粮票钞票，让饿肚子的父母姐姐们吃上饱饭。从人人嘲笑的穷小子，到带着全家逆袭翻盘，且看他手握宝塔空间，在艰苦年代闯出一条吃喝不愁的逆袭</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>穿越60我有空间不愁吃喝</x:v>
+        <x:v>张兰芬重生记</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>09-07 00:04</x:v>
+        <x:v>09-05 17:00</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G25" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H25" s="11" t="n">
-        <x:v>1000</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str">
         <x:v>其他</x:v>
@@ -3026,153 +3265,73 @@
       <x:c r="J25" s="11" t="str"/>
       <x:c r="K25" s="11" t="str"/>
       <x:c r="L25" s="10" t="str">
-        <x:v>夜珠AI剧场</x:v>
+        <x:v>璀璨Ai剧场</x:v>
       </x:c>
       <x:c r="M25" s="10" t="str">
-        <x:v>现代青年刘大壮意外穿越到60年代，成了同名同姓的16岁穷小子。原主因相亲被拒、家徒四壁，下河摸鱼时溺亡。大壮醒来后发现脑中多了一座九层宝塔空间——内有灵药田与灵泉潭水，作物两小时成熟、产量翻五倍。饥荒年代，别人啃树皮喝稀粥，他靠空间种出满仓土豆粮食，黑市换粮票钞票，让饿肚子的父母姐姐们吃上饱饭。从人人嘲笑的穷小子，到带着全家逆袭翻盘，且看他手握宝塔空间，在艰苦年代闯出一条吃喝不愁的逆袭</x:v>
+        <x:v>张兰芬操劳半生，是旁人羡慕的当家主母。她为李家养育四子两女，持家有道、将家中大小事务打理得井井有条。半生付出尽数落空，张兰芬郁结于心，最终含恨病逝医院。一朝重生，她回到所有遗憾尚未发生之时，彻底看透人心，决意放下执念，好好为自己活一次。</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>重生一世，我不再痴恋竹马</x:v>
+        <x:v>穿成恋爱脑女配，我把将军府带偏了呀</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
-        <x:v>09-10 10:00</x:v>
+        <x:v>2026-09-06</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G26" s="11" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H26" s="11" t="n">
-        <x:v>65</x:v>
-      </x:c>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H26" s="11" t="str"/>
       <x:c r="I26" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J26" s="11" t="str"/>
       <x:c r="K26" s="11" t="str"/>
-      <x:c r="L26" s="10" t="str">
-        <x:v>锦书映年华</x:v>
-      </x:c>
-      <x:c r="M26" s="10" t="str">
-        <x:v>承平公主前世错恋齐远安，受尽磋磨含恨落幕。一朝重生，恰逢圣旨赐婚，齐远安却当众恳请解除婚约，求取太后义孙女傅明珠。她坦然放手，主动成全二人，看着他们得偿所愿。宁国侯夫人动用旧物强求赐婚，她巧妙改换婚事，选择边关归来、品性刚正的齐远舟。婚后她聪慧通透，看清傅明珠与齐远安的本性，冷眼旁观二人矛盾丛生。历经风波，她与齐远舟彼此扶持，挣脱过往伤痛，收获属于自己安稳坦荡的人生。</x:v>
-      </x:c>
+      <x:c r="L26" s="10" t="str"/>
+      <x:c r="M26" s="10" t="str"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>张兰芬重生记</x:v>
+        <x:v>带着龙凤胎：和前夫共续前缘</x:v>
       </x:c>
       <x:c r="C27" s="11" t="str">
-        <x:v>09-05 17:00</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G27" s="11" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H27" s="11" t="n">
-        <x:v>176</x:v>
-      </x:c>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H27" s="11" t="str"/>
       <x:c r="I27" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J27" s="11" t="str"/>
       <x:c r="K27" s="11" t="str"/>
-      <x:c r="L27" s="10" t="str">
-        <x:v>璀璨Ai剧场</x:v>
-      </x:c>
-      <x:c r="M27" s="10" t="str">
-        <x:v>张兰芬操劳半生，是旁人羡慕的当家主母。她为李家养育四子两女，持家有道、将家中大小事务打理得井井有条。半生付出尽数落空，张兰芬郁结于心，最终含恨病逝医院。一朝重生，她回到所有遗憾尚未发生之时，彻底看透人心，决意放下执念，好好为自己活一次。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="11" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B28" s="10" t="str">
-        <x:v>穿成恋爱脑女配，我把将军府带偏了呀</x:v>
-      </x:c>
-      <x:c r="C28" s="11" t="str">
-        <x:v>2026-09-06</x:v>
-      </x:c>
-      <x:c r="D28" s="11" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E28" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F28" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G28" s="11" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H28" s="11" t="str"/>
-      <x:c r="I28" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="J28" s="11" t="str"/>
-      <x:c r="K28" s="11" t="str"/>
-      <x:c r="L28" s="10" t="str"/>
-      <x:c r="M28" s="10" t="str"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="11" t="n">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="B29" s="10" t="str">
-        <x:v>迷局终有破晓时</x:v>
-      </x:c>
-      <x:c r="C29" s="11" t="str">
-        <x:v>09-08 21:18</x:v>
-      </x:c>
-      <x:c r="D29" s="11" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E29" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F29" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G29" s="11" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H29" s="11" t="n">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="I29" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J29" s="11" t="str"/>
-      <x:c r="K29" s="11" t="str"/>
-      <x:c r="L29" s="10" t="str">
-        <x:v>时雨生</x:v>
-      </x:c>
-      <x:c r="M29" s="10" t="str">
-        <x:v>男主陆承安的好友到访家中，发现家中潜藏重大疑点，留下关键线索后意外离世。陆承安凭借遗留信物逐步排查，察觉妻子沈知微隐瞒秘密，私下开展不合规研究。他主动对接警方，巧妙布局收集完整证据，配合警方成功解救被困人员，促使沈知微承担相应法律后果。风波过后，陆承安带着孩子走出过往阴霾，开启崭新平静的生活。</x:v>
-      </x:c>
+      <x:c r="L27" s="10" t="str"/>
+      <x:c r="M27" s="10" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3232,10 +3391,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F2" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>2026-09-15 02-44</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3249,16 +3408,16 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
-        <x:v>2.4</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F3" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>2026-09-15 02-44</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -3278,10 +3437,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F4" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>2026-09-15 02-44</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3295,16 +3454,16 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>10.4</x:v>
+        <x:v>10.7</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F5" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>2026-09-15 02-44</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -3318,16 +3477,16 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>6.9</x:v>
+        <x:v>6.6</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F6" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>2026-09-15 02-44</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3341,16 +3500,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>7.5</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F7" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -3358,22 +3517,22 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>破库房的秘密</x:v>
+        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
       </x:c>
       <x:c r="C8" s="11" t="n">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>11.8</x:v>
+        <x:v>7.4</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>2026-09-15 02-44</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3381,22 +3540,22 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
+        <x:v>破库房的秘密</x:v>
       </x:c>
       <x:c r="C9" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>7.3</x:v>
+        <x:v>12.1</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>2026-09-15 02-44</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -3407,7 +3566,7 @@
         <x:v>退婚后我在七零赚钱养家致富</x:v>
       </x:c>
       <x:c r="C10" s="11" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
         <x:v>10.2</x:v>
@@ -3433,16 +3592,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>11.6</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
-        <x:v>2026-09-14 20-18</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -3453,7 +3612,7 @@
         <x:v>锦书迟</x:v>
       </x:c>
       <x:c r="C12" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
         <x:v>13.4</x:v>
@@ -3473,22 +3632,22 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>泰城错嫁</x:v>
+        <x:v>今天开始做裴总</x:v>
       </x:c>
       <x:c r="C13" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>12.9</x:v>
+        <x:v>11.1</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G13" s="11" t="str">
-        <x:v>2026-09-14 22-12</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -3496,22 +3655,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>今天开始做裴总</x:v>
+        <x:v>泰城错嫁</x:v>
       </x:c>
       <x:c r="C14" s="11" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>10.8</x:v>
+        <x:v>12.6</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G14" s="11" t="str">
-        <x:v>2026-09-15 02-44</x:v>
+        <x:v>2026-09-14 22-12</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -3548,16 +3707,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>11.5</x:v>
+        <x:v>11.9</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G16" s="11" t="str">
-        <x:v>2026-09-15 02-44</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -3594,16 +3753,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>11.2</x:v>
+        <x:v>10.1</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G18" s="11" t="str">
-        <x:v>2026-09-15 02-44</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -3611,22 +3770,22 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
+        <x:v>小妹初长成</x:v>
       </x:c>
       <x:c r="C19" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>15.9</x:v>
+        <x:v>12.7</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G19" s="11" t="str">
-        <x:v>2026-09-14 06-11</x:v>
+        <x:v>2026-09-14 12-34</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -3634,22 +3793,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>小妹初长成</x:v>
+        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
       </x:c>
       <x:c r="C20" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>12.7</x:v>
+        <x:v>15.7</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G20" s="11" t="str">
-        <x:v>2026-09-14 12-34</x:v>
+        <x:v>2026-09-14 06-11</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -3660,10 +3819,10 @@
         <x:v>退婚从抢我车位开始</x:v>
       </x:c>
       <x:c r="C21" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>14.1</x:v>
+        <x:v>14.3</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
         <x:v>7</x:v>
@@ -3680,22 +3839,22 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>回到零四年进军彩铃界</x:v>
+        <x:v>三分钱的取舍</x:v>
       </x:c>
       <x:c r="C22" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>16.4</x:v>
+        <x:v>11.3</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G22" s="11" t="str">
-        <x:v>2026-09-14 12-34</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -3703,22 +3862,22 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>河箱送福来</x:v>
+        <x:v>回到零四年进军彩铃界</x:v>
       </x:c>
       <x:c r="C23" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>16.4</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G23" s="11" t="str">
-        <x:v>2026-09-14 20-18</x:v>
+        <x:v>2026-09-14 12-34</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -3726,13 +3885,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>三分钱的取舍</x:v>
+        <x:v>婚礼当天我不嫁了</x:v>
       </x:c>
       <x:c r="C24" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>12.1</x:v>
+        <x:v>14.8</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
         <x:v>7</x:v>
@@ -3741,7 +3900,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="G24" s="11" t="str">
-        <x:v>2026-09-15 02-44</x:v>
+        <x:v>2026-09-14 22-12</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -3749,22 +3908,22 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>婚礼当天我不嫁了</x:v>
+        <x:v>河箱送福来</x:v>
       </x:c>
       <x:c r="C25" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>14.8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G25" s="11" t="str">
-        <x:v>2026-09-14 22-12</x:v>
+        <x:v>2026-09-14 20-18</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -3841,22 +4000,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>一张废票毁了她</x:v>
+        <x:v>离婚那天我多了个痞帅老爹</x:v>
       </x:c>
       <x:c r="C29" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>14.5</x:v>
+        <x:v>11.2</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str">
-        <x:v>2026-09-14 10-32</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -3864,22 +4023,22 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>全家施压：我反手签了过户合同</x:v>
+        <x:v>一张废票毁了她</x:v>
       </x:c>
       <x:c r="C30" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>17.2</x:v>
+        <x:v>14.5</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G30" s="11" t="str">
-        <x:v>2026-09-14 12-34</x:v>
+        <x:v>2026-09-14 10-32</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -4071,22 +4230,22 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="10" t="str">
-        <x:v>闪婚老公有点野</x:v>
+        <x:v>拂衣震九州</x:v>
       </x:c>
       <x:c r="C39" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D39" s="11" t="n">
-        <x:v>11.3</x:v>
+        <x:v>10.3</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G39" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -4094,22 +4253,22 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="10" t="str">
-        <x:v>离婚那天我多了个痞帅老爹</x:v>
+        <x:v>闪婚老公有点野</x:v>
       </x:c>
       <x:c r="C40" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D40" s="11" t="n">
-        <x:v>12.7</x:v>
+        <x:v>11.3</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G40" s="11" t="str">
-        <x:v>2026-09-15 02-44</x:v>
+        <x:v>2026-09-15 01-59</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -4117,22 +4276,22 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="10" t="str">
-        <x:v>不靠谱爸妈很靠谱</x:v>
+        <x:v>青牛引泉来</x:v>
       </x:c>
       <x:c r="C41" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D41" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>15.3</x:v>
       </x:c>
       <x:c r="E41" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F41" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G41" s="11" t="str">
-        <x:v>2026-09-14 21-12</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -4140,22 +4299,22 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B42" s="10" t="str">
-        <x:v>427元扳倒老油条</x:v>
+        <x:v>大坝边寻回的真千金</x:v>
       </x:c>
       <x:c r="C42" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D42" s="11" t="n">
-        <x:v>15.7</x:v>
+        <x:v>12.7</x:v>
       </x:c>
       <x:c r="E42" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F42" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G42" s="11" t="str">
-        <x:v>2026-09-14 20-18</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -4163,22 +4322,22 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" s="10" t="str">
-        <x:v>穿书后我带萌宝上门认爹</x:v>
+        <x:v>山下是绝路，山上是生门</x:v>
       </x:c>
       <x:c r="C43" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D43" s="11" t="n">
-        <x:v>16.3</x:v>
+        <x:v>14.3</x:v>
       </x:c>
       <x:c r="E43" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F43" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G43" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -4186,22 +4345,22 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="10" t="str">
-        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
+        <x:v>不靠谱爸妈很靠谱</x:v>
       </x:c>
       <x:c r="C44" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D44" s="11" t="n">
-        <x:v>17.7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E44" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F44" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G44" s="11" t="str">
-        <x:v>2026-09-15 02-44</x:v>
+        <x:v>2026-09-14 21-12</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -4209,22 +4368,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="10" t="str">
-        <x:v>零元年终奖</x:v>
+        <x:v>427元扳倒老油条</x:v>
       </x:c>
       <x:c r="C45" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D45" s="11" t="n">
-        <x:v>4.5</x:v>
+        <x:v>15.7</x:v>
       </x:c>
       <x:c r="E45" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F45" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G45" s="11" t="str">
-        <x:v>2026-09-13 22-11</x:v>
+        <x:v>2026-09-14 20-18</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -4232,19 +4391,19 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B46" s="10" t="str">
-        <x:v>我SSS级狂龙，出世即无敌</x:v>
+        <x:v>穿书后我带萌宝上门认爹</x:v>
       </x:c>
       <x:c r="C46" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D46" s="11" t="n">
-        <x:v>5.5</x:v>
+        <x:v>16.3</x:v>
       </x:c>
       <x:c r="E46" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F46" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G46" s="11" t="str">
         <x:v>2026-09-15 01-59</x:v>
@@ -4255,22 +4414,22 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B47" s="10" t="str">
-        <x:v>一碗人间赴景深</x:v>
+        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
       </x:c>
       <x:c r="C47" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D47" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>17.7</x:v>
       </x:c>
       <x:c r="E47" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F47" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G47" s="11" t="str">
-        <x:v>2026-09-14 09-24</x:v>
+        <x:v>2026-09-15 02-44</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -4278,22 +4437,22 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B48" s="10" t="str">
-        <x:v>白鹿照归途</x:v>
+        <x:v>全家施压：我反手签了过户合同</x:v>
       </x:c>
       <x:c r="C48" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D48" s="11" t="n">
-        <x:v>12.5</x:v>
+        <x:v>19.3</x:v>
       </x:c>
       <x:c r="E48" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F48" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G48" s="11" t="str">
-        <x:v>2026-09-14 09-24</x:v>
+        <x:v>2026-09-14 12-34</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -4301,22 +4460,22 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B49" s="10" t="str">
-        <x:v>三天后穿越古代，我贷款搬空商城！</x:v>
+        <x:v>零元年终奖</x:v>
       </x:c>
       <x:c r="C49" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D49" s="11" t="n">
-        <x:v>8.5</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="E49" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F49" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G49" s="11" t="str">
-        <x:v>2026-09-14 21-12</x:v>
+        <x:v>2026-09-13 22-11</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -4324,22 +4483,22 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B50" s="10" t="str">
-        <x:v>假老板娘遇上真董事长</x:v>
+        <x:v>我SSS级狂龙，出世即无敌</x:v>
       </x:c>
       <x:c r="C50" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D50" s="11" t="n">
-        <x:v>12.5</x:v>
+        <x:v>5.5</x:v>
       </x:c>
       <x:c r="E50" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F50" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G50" s="11" t="str">
-        <x:v>2026-09-15 02-44</x:v>
+        <x:v>2026-09-15 01-59</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -4347,19 +4506,19 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B51" s="10" t="str">
-        <x:v>那半块玉佩</x:v>
+        <x:v>一碗人间赴景深</x:v>
       </x:c>
       <x:c r="C51" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D51" s="11" t="n">
-        <x:v>7.5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E51" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F51" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G51" s="11" t="str">
         <x:v>2026-09-14 09-24</x:v>
@@ -5786,10 +5945,10 @@
         <x:v>姬昭身为姬府嫡长女，前世错嫁淮南王世子崔涟，被庶妹姬柔窃取书信与诗作，背负欺瞒之名，冷院惨死。一朝重生，她回到提亲当日，当众拒婚，转而以一只蛐蛐为契，相中世人眼中顽劣的霍家幼子霍睢。可就在她以为命运终于转向时，姬柔却抱着那叠书信，缓缓走向了火盆。</x:v>
       </x:c>
       <x:c r="K2" s="10" t="str">
-        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×1；67集，主力长度；发布账号「芙浚动漫短剧」按上榜剧数入榜</x:v>
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×1；67集，主力长度；发布账号「芙浚动漫短剧」双口径都产爆款</x:v>
       </x:c>
       <x:c r="L2" s="11" t="n">
-        <x:v>8.5</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -7342,8 +7501,12 @@
       <x:c r="G48" s="10" t="str">
         <x:v>心动漫剧场</x:v>
       </x:c>
-      <x:c r="H48" s="11" t="str"/>
-      <x:c r="I48" s="10" t="str"/>
+      <x:c r="H48" s="11" t="str">
+        <x:v>已上榜</x:v>
+      </x:c>
+      <x:c r="I48" s="10" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
       <x:c r="J48" s="10" t="str">
         <x:v>沈清韵嫁入靖王府三年，王爷冷落，侧妃得宠。王爷当众许诺，谁先诞下儿子，便请封世子。苏氏先怀孕，沈清韵却发现自己怀的是龙凤胎，她隐瞒消息，买通太医推迟产期，忍痛让苏氏先产子。王爷果然请封庶长子为世子，折子递入宗人府。受理之后，沈清韵才发动，生下龙凤胎。太后与皇上视为祥瑞，下旨赐嫡子承恩为靖王世子、嫡女承华为安乐郡主。王爷措手不及，苏氏地位一落千丈。而沈清韵知道，这只是第一步。</x:v>
       </x:c>
@@ -9732,8 +9895,12 @@
       <x:c r="G118" s="10" t="str">
         <x:v>芙浚动漫短剧</x:v>
       </x:c>
-      <x:c r="H118" s="11" t="str"/>
-      <x:c r="I118" s="10" t="str"/>
+      <x:c r="H118" s="11" t="str">
+        <x:v>已上榜</x:v>
+      </x:c>
+      <x:c r="I118" s="10" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
       <x:c r="J118" s="10" t="str">
         <x:v>全职主妇温宁与沈嘉树结婚八年，表面美满，唯一古怪的是丈夫每晚对着鱼缸静坐两小时。闺蜜程露发现鱼缸暗藏玄机后仓皇逃离，当夜坠江身亡，手中紧握一只橡皮泥小鱼。温宁循着红光，在鱼缸底座暗格中发现监控屏幕——沈嘉树日夜盯着的，是病床上插管的植物人女子林晚。而所有人以为她八年前早已出国。温宁低下头，看见鱼缸里游动的影子，像极了那张病历照片上的脸。</x:v>
       </x:c>
@@ -17575,10 +17742,10 @@
         <x:v>姬昭身为姬府嫡长女，前世错嫁淮南王世子崔涟，被庶妹姬柔窃取书信与诗作，背负欺瞒之名，冷院惨死。一朝重生，她回到提亲当日，当众拒婚，转而以一只蛐蛐为契，相中世人眼中顽劣的霍家幼子霍睢。可就在她以为命运终于转向时，姬柔却抱着那叠书信，缓缓走向了火盆。</x:v>
       </x:c>
       <x:c r="K2" s="10" t="str">
-        <x:v>发布账号「芙浚动漫短剧」进入单口径TOP12，账号高分；题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×1；67集，主力长度；女频受众</x:v>
+        <x:v>发布账号「芙浚动漫短剧」双口径TOP12精品号，账号满分；题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×1；67集，主力长度；女频受众</x:v>
       </x:c>
       <x:c r="L2" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -19133,8 +19300,12 @@
       <x:c r="G48" s="10" t="str">
         <x:v>心动漫剧场</x:v>
       </x:c>
-      <x:c r="H48" s="11" t="str"/>
-      <x:c r="I48" s="10" t="str"/>
+      <x:c r="H48" s="11" t="str">
+        <x:v>已上榜</x:v>
+      </x:c>
+      <x:c r="I48" s="10" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
       <x:c r="J48" s="10" t="str">
         <x:v>沈清韵嫁入靖王府三年，王爷冷落，侧妃得宠。王爷当众许诺，谁先诞下儿子，便请封世子。苏氏先怀孕，沈清韵却发现自己怀的是龙凤胎，她隐瞒消息，买通太医推迟产期，忍痛让苏氏先产子。王爷果然请封庶长子为世子，折子递入宗人府。受理之后，沈清韵才发动，生下龙凤胎。太后与皇上视为祥瑞，下旨赐嫡子承恩为靖王世子、嫡女承华为安乐郡主。王爷措手不及，苏氏地位一落千丈。而沈清韵知道，这只是第一步。</x:v>
       </x:c>
@@ -21545,8 +21716,12 @@
       <x:c r="G118" s="10" t="str">
         <x:v>芙浚动漫短剧</x:v>
       </x:c>
-      <x:c r="H118" s="11" t="str"/>
-      <x:c r="I118" s="10" t="str"/>
+      <x:c r="H118" s="11" t="str">
+        <x:v>已上榜</x:v>
+      </x:c>
+      <x:c r="I118" s="10" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
       <x:c r="J118" s="10" t="str">
         <x:v>全职主妇温宁与沈嘉树结婚八年，表面美满，唯一古怪的是丈夫每晚对着鱼缸静坐两小时。闺蜜程露发现鱼缸暗藏玄机后仓皇逃离，当夜坠江身亡，手中紧握一只橡皮泥小鱼。温宁循着红光，在鱼缸底座暗格中发现监控屏幕——沈嘉树日夜盯着的，是病床上插管的植物人女子林晚。而所有人以为她八年前早已出国。温宁低下头，看见鱼缸里游动的影子，像极了那张病历照片上的脸。</x:v>
       </x:c>
@@ -29366,7 +29541,7 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>899</x:v>
+        <x:v>902</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
         <x:v>52.2%</x:v>
@@ -29388,7 +29563,7 @@
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>348</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
         <x:v>20.2%</x:v>
@@ -29418,7 +29593,7 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>11.2%</x:v>
+        <x:v>11.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -29426,10 +29601,10 @@
         <x:v>50-79集</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>678</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>42.8%</x:v>
+        <x:v>42.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -29440,7 +29615,7 @@
         <x:v>199</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>12.6%</x:v>
+        <x:v>12.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -29475,10 +29650,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>758</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>44.0%</x:v>
+        <x:v>43.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -29486,10 +29661,10 @@
         <x:v>婚姻/情感</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>309</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>17.9%</x:v>
+        <x:v>18.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -29497,7 +29672,7 @@
         <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
         <x:v>9.2%</x:v>
@@ -29505,10 +29680,10 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="10" t="str">
-        <x:v>年代怀旧/种田囤货</x:v>
+        <x:v>家庭伦理/萌宝</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
         <x:v>8.6%</x:v>
@@ -29516,7 +29691,7 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="10" t="str">
-        <x:v>家庭伦理/萌宝</x:v>
+        <x:v>年代怀旧/种田囤货</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
         <x:v>148</x:v>
@@ -29566,7 +29741,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>4.8%</x:v>
+        <x:v>4.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -29623,7 +29798,7 @@
         <x:v>上榜28次</x:v>
       </x:c>
       <x:c r="B31" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C31" s="11" t="str">
         <x:v>0.1%</x:v>
@@ -29634,7 +29809,7 @@
         <x:v>上榜27次</x:v>
       </x:c>
       <x:c r="B32" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C32" s="11" t="str">
         <x:v>0.1%</x:v>
@@ -29799,7 +29974,7 @@
         <x:v>上榜11次</x:v>
       </x:c>
       <x:c r="B47" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C47" s="11" t="str">
         <x:v>0.6%</x:v>
@@ -29810,7 +29985,7 @@
         <x:v>上榜10次</x:v>
       </x:c>
       <x:c r="B48" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C48" s="11" t="str">
         <x:v>1.2%</x:v>
@@ -29832,10 +30007,10 @@
         <x:v>上榜8次</x:v>
       </x:c>
       <x:c r="B50" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C50" s="11" t="str">
-        <x:v>2.7%</x:v>
+        <x:v>2.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -29843,10 +30018,10 @@
         <x:v>上榜7次</x:v>
       </x:c>
       <x:c r="B51" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C51" s="11" t="str">
-        <x:v>2.3%</x:v>
+        <x:v>2.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -29865,7 +30040,7 @@
         <x:v>上榜5次</x:v>
       </x:c>
       <x:c r="B53" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C53" s="11" t="str">
         <x:v>4.1%</x:v>
@@ -29876,7 +30051,7 @@
         <x:v>上榜4次</x:v>
       </x:c>
       <x:c r="B54" s="11" t="n">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C54" s="11" t="str">
         <x:v>6.3%</x:v>
@@ -29887,7 +30062,7 @@
         <x:v>上榜3次</x:v>
       </x:c>
       <x:c r="B55" s="11" t="n">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C55" s="11" t="str">
         <x:v>11.4%</x:v>
@@ -29898,10 +30073,10 @@
         <x:v>上榜2次</x:v>
       </x:c>
       <x:c r="B56" s="11" t="n">
-        <x:v>319</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="C56" s="11" t="str">
-        <x:v>18.5%</x:v>
+        <x:v>18.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -29909,10 +30084,10 @@
         <x:v>上榜1次</x:v>
       </x:c>
       <x:c r="B57" s="11" t="n">
-        <x:v>747</x:v>
+        <x:v>751</x:v>
       </x:c>
       <x:c r="C57" s="11" t="str">
-        <x:v>43.4%</x:v>
+        <x:v>43.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="22" customHeight="1">
@@ -29936,10 +30111,10 @@
         <x:v>CP自营</x:v>
       </x:c>
       <x:c r="B61" s="11" t="n">
-        <x:v>1149</x:v>
+        <x:v>1150</x:v>
       </x:c>
       <x:c r="C61" s="11" t="str">
-        <x:v>66.7%</x:v>
+        <x:v>66.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -29947,10 +30122,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B62" s="11" t="n">
-        <x:v>563</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="C62" s="11" t="str">
-        <x:v>32.7%</x:v>
+        <x:v>32.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -30040,10 +30215,10 @@
         <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="B72" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C72" s="11" t="str">
-        <x:v>0.7%</x:v>
+        <x:v>0.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -30051,7 +30226,7 @@
         <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="B73" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C73" s="11" t="str">
         <x:v>0.7%</x:v>
@@ -30092,7 +30267,7 @@
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="10" t="str">
-        <x:v>在下轻北</x:v>
+        <x:v>茉冉漫影</x:v>
       </x:c>
       <x:c r="B77" s="11" t="n">
         <x:v>28</x:v>
@@ -30103,7 +30278,7 @@
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>在下轻北</x:v>
       </x:c>
       <x:c r="B78" s="11" t="n">
         <x:v>28</x:v>
@@ -30114,10 +30289,10 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="10" t="str">
-        <x:v>茉冉漫影</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="B79" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C79" s="11" t="str">
         <x:v>0.5%</x:v>
@@ -30125,10 +30300,10 @@
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="10" t="str">
-        <x:v>壹琚-娜娜看剧</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="B80" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C80" s="11" t="str">
         <x:v>0.5%</x:v>
@@ -30136,7 +30311,7 @@
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="10" t="str">
-        <x:v>一张不够花</x:v>
+        <x:v>壹琚-娜娜看剧</x:v>
       </x:c>
       <x:c r="B81" s="11" t="n">
         <x:v>27</x:v>
@@ -30147,7 +30322,7 @@
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>一张不够花</x:v>
       </x:c>
       <x:c r="B82" s="11" t="n">
         <x:v>27</x:v>
@@ -30177,7 +30352,7 @@
         <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="B86" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C86" s="11" t="str">
         <x:v>1%</x:v>
@@ -30196,7 +30371,7 @@
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="10" t="str">
-        <x:v>星漫世界</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="B88" s="11" t="n">
         <x:v>8</x:v>
@@ -30207,29 +30382,29 @@
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="10" t="str">
-        <x:v>番荔枝剧场</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="B89" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C89" s="11" t="str">
-        <x:v>0.4%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="10" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>星漫世界</x:v>
       </x:c>
       <x:c r="B90" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C90" s="11" t="str">
-        <x:v>0.4%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>番荔枝剧场</x:v>
       </x:c>
       <x:c r="B91" s="11" t="n">
         <x:v>7</x:v>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R3665e6e048274da3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="Rf8c5e0703cf1402e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="R401745f0829d4a7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="Rf84bac82e8844f97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP20剧重点跟踪" sheetId="5" r:id="Re7355b82b1474f87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="6" r:id="R487b5ef519654edd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="7" r:id="Re0e8f0c803764f61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="8" r:id="R1f2227aa6dd64d09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="9" r:id="Rd26185b476e04050"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R31a7881fd822407e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="R1b954d774af74684"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="R9682989e572c4c4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="R474e2d5aff104f49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP20剧重点跟踪" sheetId="5" r:id="R5dce38b07a1c4538"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="6" r:id="Re3ca73120d334fc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="7" r:id="R02839863c12c46b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="8" r:id="R3a5074f3c097446d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="9" r:id="R9af3adb7e9904d71"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1016,27 +1016,27 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>一瓶水，让我看清亲生女儿</x:v>
+        <x:v>铺子空了，房东慌了</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>08-23 10:00</x:v>
+        <x:v>08-29 16:49</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E24" s="10" t="n">
-        <x:v>69</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F24" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G24" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="H24" s="11" t="str"/>
       <x:c r="I24" s="11" t="str"/>
       <x:c r="J24" s="10" t="str">
-        <x:v>2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-15</x:v>
+        <x:v>2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1044,27 +1044,27 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>乱世我家顿顿吃肉</x:v>
+        <x:v>一瓶水，让我看清亲生女儿</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>08-15 04:30</x:v>
+        <x:v>08-23 10:00</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E25" s="10" t="n">
-        <x:v>54</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F25" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="G25" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="H25" s="11" t="str"/>
       <x:c r="I25" s="11" t="str"/>
       <x:c r="J25" s="10" t="str">
-        <x:v>2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
+        <x:v>2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-15</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1072,27 +1072,27 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>福宝治愈全世界，家有萌娃岁岁安</x:v>
+        <x:v>乱世我家顿顿吃肉</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
-        <x:v>08-21 10:00</x:v>
+        <x:v>08-15 04:30</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E26" s="10" t="n">
-        <x:v>169</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F26" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G26" s="10" t="str">
-        <x:v>萌宝治愈</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="H26" s="11" t="str"/>
       <x:c r="I26" s="11" t="str"/>
       <x:c r="J26" s="10" t="str">
-        <x:v>2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-03、2026-09-05、2026-09-06、2026-09-12、2026-09-13</x:v>
+        <x:v>2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1165,13 +1165,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B2" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
-        <x:v>离婚那天我多了个痞帅老爹</x:v>
+        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>2026-09-13</x:v>
+        <x:v>09-13 09:58</x:v>
       </x:c>
       <x:c r="E2" s="11" t="str"/>
       <x:c r="F2" s="11" t="str"/>
@@ -1181,28 +1181,34 @@
       <x:c r="H2" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I2" s="11" t="str"/>
+      <x:c r="I2" s="11" t="n">
+        <x:v>66</x:v>
+      </x:c>
       <x:c r="J2" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K2" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="L2" s="11" t="str"/>
-      <x:c r="M2" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L2" s="11" t="str">
+        <x:v>创想剧场</x:v>
+      </x:c>
+      <x:c r="M2" s="10" t="str">
+        <x:v>游戏公会会长林小勇筹备婚礼，却在婚宴上遭遇未婚妻临时加价逼婚。危急时刻，几位相交多年的游戏老友现身力挺他，林小勇果断取消婚礼。之后他搬进好友赠送的别墅，与陈董的两个女儿渐渐熟识。同学聚会上，众人见识到林小勇不一般的际遇。平静日子没过多久，当年游戏里的宿敌将出席游戏八周年嘉年华，一众老友决定赴约，一场新旧对决即将开启。</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
-        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
+        <x:v>四个崽崽瞒不住了</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>09-13 09:58</x:v>
+        <x:v>09-15 00:08</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str"/>
       <x:c r="F3" s="11" t="str"/>
@@ -1213,7 +1219,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I3" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str">
         <x:v>其他</x:v>
@@ -1222,10 +1228,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L3" s="11" t="str">
-        <x:v>创想剧场</x:v>
+        <x:v>桃子动漫剧场</x:v>
       </x:c>
       <x:c r="M3" s="10" t="str">
-        <x:v>游戏公会会长林小勇筹备婚礼，却在婚宴上遭遇未婚妻临时加价逼婚。危急时刻，几位相交多年的游戏老友现身力挺他，林小勇果断取消婚礼。之后他搬进好友赠送的别墅，与陈董的两个女儿渐渐熟识。同学聚会上，众人见识到林小勇不一般的际遇。平静日子没过多久，当年游戏里的宿敌将出席游戏八周年嘉年华，一众老友决定赴约，一场新旧对决即将开启。</x:v>
+        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1233,13 +1239,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
-        <x:v>员工跑路我扩店</x:v>
+        <x:v>小妹初长成</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>09-13 08:58</x:v>
+        <x:v>2026-09-13</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str"/>
       <x:c r="F4" s="11" t="str"/>
@@ -1249,34 +1255,28 @@
       <x:c r="H4" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I4" s="11" t="n">
-        <x:v>70</x:v>
-      </x:c>
+      <x:c r="I4" s="11" t="str"/>
       <x:c r="J4" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K4" s="10" t="str">
-        <x:v>都市职场</x:v>
-      </x:c>
-      <x:c r="L4" s="11" t="str">
-        <x:v>大梨看剧</x:v>
-      </x:c>
-      <x:c r="M4" s="10" t="str">
-        <x:v>林辰经营天力健身馆，年终为员工每人发放五万元奖金。几位教练希望获得更多发展空间，与林辰理念产生分歧，决定在隔壁开设新馆，一场实力较量就此展开。林辰选择升级场地、引进专业团队，并提拔刘阿姨担任店长。正月初七，千名会员到场，用选择见证真诚服务的价值。</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L4" s="11" t="str"/>
+      <x:c r="M4" s="10" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
-        <x:v>风雪边界</x:v>
+        <x:v>重生80，救下神雕后我带村民走出大山</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>09-14 03:01</x:v>
+        <x:v>09-13 09:00</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str"/>
       <x:c r="F5" s="11" t="str"/>
@@ -1287,19 +1287,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I5" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="J5" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K5" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="L5" s="11" t="str">
-        <x:v>腿毛漫漫</x:v>
+        <x:v>拾光漫漫</x:v>
       </x:c>
       <x:c r="M5" s="10" t="str">
-        <x:v>高原补给站老板岑夏坚持完整安全套餐，却遭企业负责人质疑价格，团队转投低价营地。暴雪突至，危机逼近，岑夏仍坚守原则，以专业判断协助应急处置，也让众人重新理解安全的价值。真正昂贵的不是房费，而是忽视风险的代价。敬畏自然、尊重专业，安全永远值得认真对待。</x:v>
+        <x:v>林大山遭人为意外，意外重生回到1980年。前世他错信爱人落得凄惨下场，重生后果断当众退婚。机缘巧合救下受伤的灵智神雕金羽，还遇见落难善良的白秋月。他携手知恩图报的神雕，依托卧龙山的资源，发掘名贵药材，抓住时代发展机遇。面对同行刁难，林大山坚守本心，凭借智慧与实干，包下荒山兴办药材加工坊。他善待家人，带领乡里百姓勤劳致富，在八十年代的时代浪潮里，靠着双手改写命运，收获美满爱情与事业。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1307,10 +1307,10 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>小妹初长成</x:v>
+        <x:v>离婚那天我多了个痞帅老爹</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
         <x:v>2026-09-13</x:v>
@@ -1328,7 +1328,7 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="K6" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理 / 婚姻情感</x:v>
       </x:c>
       <x:c r="L6" s="11" t="str"/>
       <x:c r="M6" s="10" t="str"/>
@@ -1338,13 +1338,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
-        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
+        <x:v>乡宴见人心</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>09-13 08:00</x:v>
+        <x:v>09-13 17:12</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str"/>
       <x:c r="F7" s="11" t="str"/>
@@ -1355,19 +1355,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I7" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J7" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K7" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="L7" s="11" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>黑白动漫</x:v>
       </x:c>
       <x:c r="M7" s="10" t="str">
-        <x:v>大晋七公主沈令仪，自幼被冷落于听竹宫，沉默藏锋，苟全性命。宫宴之上，太子带回的秦照雪笑盈盈提议将她送去北狄和亲。满殿以为皇帝会点头，他却掷出“废太子”三字。一夜之间，沈令仪被推到台前。北狄求和的急报恰在此时入京——与她方才所言分毫不差。可当她回望母亲遗下的那半卷秘策时，才发现这局棋，早在二十年前就已落子。</x:v>
+        <x:v>高满仓在赵家大院办了八年流水席，十里八村都认他的手艺。眼看生意越来越旺，院主赵金贵突然把租金翻倍，还要按桌抽钱。高满仓干脆带着人和家伙搬进镇外的废米厂，从头再来。赵金贵以为守着大院就守住了客人，靠低价抢生意，却越省越狠。一边是稳稳当当把席办好，一边是亲手砸掉自己的口碑，这场较量最后看的是院子，还是人心。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1375,13 +1375,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
+        <x:v>河箱送福来</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>09-15 00:08</x:v>
+        <x:v>09-13 11:00</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str"/>
       <x:c r="F8" s="11" t="str"/>
@@ -1392,7 +1392,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J8" s="10" t="str">
         <x:v>其他</x:v>
@@ -1401,10 +1401,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L8" s="11" t="str">
-        <x:v>桃子动漫剧场</x:v>
+        <x:v>灵心讲故事</x:v>
       </x:c>
       <x:c r="M8" s="10" t="str">
-        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
+        <x:v>张家老两口从河中救回一只木箱，收养了箱中受伤的福生。福生长大后修桥开田，引水惠及乡亲，成家立业。二老相继离世后，山洪威胁村庄，福生为救乡亲舍命撑住巨石，最终重伤落水，下落不明。秀娥守着小院苦等多年，直到熟悉的声音再次响起。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1412,10 +1412,10 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
-        <x:v>我赚上千万跟爸妈说50W，隔天就被找上门</x:v>
+        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
         <x:v>09-13 08:00</x:v>
@@ -1429,19 +1429,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I9" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J9" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K9" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="L9" s="11" t="str">
-        <x:v>至尊爽剧社</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="M9" s="10" t="str">
-        <x:v>三十二岁那年，贺川用六年孤注一掷的钻研，换来了七千六百万的回报。可财富还没捂热，先尝到的却是亲人无度的索取。他谎称只赚五十万，叮嘱保密，却挡不住消息走漏。隔天登门的亲戚不止要借钱买房，更联手外人盗用他的身份资料，试图冒名签约、伪造担保债务。贺川报警取证，警方介入追回大部分资金，涉案者包括部分机构人员均承担了法律责任，这笔帐，能否算清？</x:v>
+        <x:v>大晋七公主沈令仪，自幼被冷落于听竹宫，沉默藏锋，苟全性命。宫宴之上，太子带回的秦照雪笑盈盈提议将她送去北狄和亲。满殿以为皇帝会点头，他却掷出“废太子”三字。一夜之间，沈令仪被推到台前。北狄求和的急报恰在此时入京——与她方才所言分毫不差。可当她回望母亲遗下的那半卷秘策时，才发现这局棋，早在二十年前就已落子。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1449,13 +1449,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
-        <x:v>重生80，救下神雕后我带村民走出大山</x:v>
+        <x:v>员工跑路我扩店</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>09-13 09:00</x:v>
+        <x:v>09-13 08:58</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str"/>
       <x:c r="F10" s="11" t="str"/>
@@ -1466,19 +1466,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I10" s="11" t="n">
-        <x:v>187</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J10" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K10" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="L10" s="11" t="str">
-        <x:v>拾光漫漫</x:v>
+        <x:v>大梨看剧</x:v>
       </x:c>
       <x:c r="M10" s="10" t="str">
-        <x:v>林大山遭人为意外，意外重生回到1980年。前世他错信爱人落得凄惨下场，重生后果断当众退婚。机缘巧合救下受伤的灵智神雕金羽，还遇见落难善良的白秋月。他携手知恩图报的神雕，依托卧龙山的资源，发掘名贵药材，抓住时代发展机遇。面对同行刁难，林大山坚守本心，凭借智慧与实干，包下荒山兴办药材加工坊。他善待家人，带领乡里百姓勤劳致富，在八十年代的时代浪潮里，靠着双手改写命运，收获美满爱情与事业。</x:v>
+        <x:v>林辰经营天力健身馆，年终为员工每人发放五万元奖金。几位教练希望获得更多发展空间，与林辰理念产生分歧，决定在隔壁开设新馆，一场实力较量就此展开。林辰选择升级场地、引进专业团队，并提拔刘阿姨担任店长。正月初七，千名会员到场，用选择见证真诚服务的价值。</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1486,13 +1486,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C11" s="10" t="str">
-        <x:v>河箱送福来</x:v>
+        <x:v>风雪边界</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>09-13 11:00</x:v>
+        <x:v>09-14 03:01</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str"/>
       <x:c r="F11" s="11" t="str"/>
@@ -1503,7 +1503,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I11" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J11" s="10" t="str">
         <x:v>其他</x:v>
@@ -1512,10 +1512,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L11" s="11" t="str">
-        <x:v>灵心讲故事</x:v>
+        <x:v>腿毛漫漫</x:v>
       </x:c>
       <x:c r="M11" s="10" t="str">
-        <x:v>张家老两口从河中救回一只木箱，收养了箱中受伤的福生。福生长大后修桥开田，引水惠及乡亲，成家立业。二老相继离世后，山洪威胁村庄，福生为救乡亲舍命撑住巨石，最终重伤落水，下落不明。秀娥守着小院苦等多年，直到熟悉的声音再次响起。</x:v>
+        <x:v>高原补给站老板岑夏坚持完整安全套餐，却遭企业负责人质疑价格，团队转投低价营地。暴雪突至，危机逼近，岑夏仍坚守原则，以专业判断协助应急处置，也让众人重新理解安全的价值。真正昂贵的不是房费，而是忽视风险的代价。敬畏自然、尊重专业，安全永远值得认真对待。</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1523,13 +1523,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
-        <x:v>乡宴见人心</x:v>
+        <x:v>427元扳倒老油条</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>09-13 17:12</x:v>
+        <x:v>09-13 16:00</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str"/>
       <x:c r="F12" s="11" t="str"/>
@@ -1540,19 +1540,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I12" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J12" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K12" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L12" s="11" t="str">
-        <x:v>黑白动漫</x:v>
+        <x:v>安然然</x:v>
       </x:c>
       <x:c r="M12" s="10" t="str">
-        <x:v>高满仓在赵家大院办了八年流水席，十里八村都认他的手艺。眼看生意越来越旺，院主赵金贵突然把租金翻倍，还要按桌抽钱。高满仓干脆带着人和家伙搬进镇外的废米厂，从头再来。赵金贵以为守着大院就守住了客人，靠低价抢生意，却越省越狠。一边是稳稳当当把席办好，一边是亲手砸掉自己的口碑，这场较量最后看的是院子，还是人心。</x:v>
+        <x:v>职场新人许宁向老员工马丽芬讨要427元代垫外卖款，反遭易绑架马丽芬交出饭钱后怀恨在心，利用行政特权私吞福利，并在组织团餐时疏同事差价许宁按兵不动收集证据，最终将马丽芬长期贪占两万余元的行径在老板曝光的照片中马丽芬被直接开除，许宁成功维护了职场底线。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1560,36 +1560,36 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B13" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
-        <x:v>427元扳倒老油条</x:v>
+        <x:v>重生极品婆婆，带全家发家致富！</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
-        <x:v>09-13 16:00</x:v>
+        <x:v>09-14 20:29</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str"/>
       <x:c r="F13" s="11" t="str"/>
       <x:c r="G13" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H13" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I13" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="J13" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K13" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="L13" s="11" t="str">
-        <x:v>安然然</x:v>
+        <x:v>懒少爱我</x:v>
       </x:c>
       <x:c r="M13" s="10" t="str">
-        <x:v>职场新人许宁向老员工马丽芬讨要427元代垫外卖款，反遭易绑架马丽芬交出饭钱后怀恨在心，利用行政特权私吞福利，并在组织团餐时疏同事差价许宁按兵不动收集证据，最终将马丽芬长期贪占两万余元的行径在老板曝光的照片中马丽芬被直接开除，许宁成功维护了职场底线。</x:v>
+        <x:v>寡妇傅兰秀前世一生吝啬守财，刻薄对待儿女儿媳，到头来钱财被贼人掠夺，落得个凄惨离世的下场。一朝重生，她回到悲剧尚未发生之时。痛定思痛，她彻底改掉抠门的性子，学着善待家里的晚辈。可日子并不太平，爱占便宜的亲戚总上门搅扰，家中两个儿媳也矛盾不断，家务是非接连找上门。傅兰秀靠着清醒的头脑，一边化解各类家庭纷争，一边寻找营生门路，努力扭转命运，拼尽全力守护一家人的安稳生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1597,36 +1597,36 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B14" s="11" t="n">
-        <x:v>99</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
-        <x:v>婚礼当天我不嫁了</x:v>
+        <x:v>活宝老爹再赴青春，竟与女儿同上大学</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>09-14 09:00</x:v>
+        <x:v>09-13 00:08</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str"/>
       <x:c r="F14" s="11" t="str"/>
       <x:c r="G14" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H14" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I14" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J14" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K14" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="L14" s="11" t="str">
-        <x:v>大梨看剧</x:v>
+        <x:v>长风剧场</x:v>
       </x:c>
       <x:c r="M14" s="10" t="str">
-        <x:v>婚礼当天，沈清面对不同婚俗，勇敢表达自我，果断选择结束婚约。哥哥和好友支持，她用法律与智慧处理彩礼、名誉及后续事宜，守护尊严与安全。成长历程中，她开启独立新生活，搬入温暖新家，与家人朋友相伴成长。故事传递出，婚姻应建立在尊重、平等和真诚之上，表达选择，才能拥抱更好的未来。</x:v>
+        <x:v>45岁的白烨意外激活成长系统。只要亲身体验年轻人的日常，就能重拾青春活力，还能收获丰厚奖励。为完成系统任务，他报名成人高考，顺利考入大学，竟和女儿成了同校同学。重返校园的白烨，一边认真完成任务感受青春，一边在校园里开启一段充满趣味的全新人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1634,28 +1634,28 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B15" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
-        <x:v>结婚八年，我娶的原来是仇人的女儿</x:v>
+        <x:v>反派拿捏！</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>2026-09-13</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str"/>
       <x:c r="F15" s="11" t="str"/>
       <x:c r="G15" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H15" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="11" t="str"/>
       <x:c r="J15" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="K15" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L15" s="11" t="str"/>
       <x:c r="M15" s="10" t="str"/>
@@ -1665,13 +1665,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C16" s="10" t="str">
-        <x:v>重生极品婆婆，带全家发家致富！</x:v>
+        <x:v>那朵胸花，被丢进垃圾桶</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
-        <x:v>09-14 20:29</x:v>
+        <x:v>09-14 21:00</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str"/>
       <x:c r="F16" s="11" t="str"/>
@@ -1679,22 +1679,22 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H16" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="11" t="n">
-        <x:v>126</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J16" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K16" s="10" t="str">
-        <x:v>家庭伦理 / 逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L16" s="11" t="str">
-        <x:v>懒少爱我</x:v>
+        <x:v>临渊剧场</x:v>
       </x:c>
       <x:c r="M16" s="10" t="str">
-        <x:v>寡妇傅兰秀前世一生吝啬守财，刻薄对待儿女儿媳，到头来钱财被贼人掠夺，落得个凄惨离世的下场。一朝重生，她回到悲剧尚未发生之时。痛定思痛，她彻底改掉抠门的性子，学着善待家里的晚辈。可日子并不太平，爱占便宜的亲戚总上门搅扰，家中两个儿媳也矛盾不断，家务是非接连找上门。傅兰秀靠着清醒的头脑，一边化解各类家庭纷争，一边寻找营生门路，努力扭转命运，拼尽全力守护一家人的安稳生活。</x:v>
+        <x:v>接亲当天，新郎踹开新娘房门。新娘护着前任，前任用胸花挑衅，婚礼当场取消。她求他，他放完整视频反击。前任欠债跑路，债主堵门，新娘崩溃。他换锁卖房，一笔账一笔账清。可账单会说话，旧爱跑不了，这条线，该断了。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1702,13 +1702,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C17" s="10" t="str">
-        <x:v>偷脸</x:v>
+        <x:v>重生嫡女：太子妃她手撕孽缘</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>09-13 11:00</x:v>
       </x:c>
       <x:c r="E17" s="11" t="str"/>
       <x:c r="F17" s="11" t="str"/>
@@ -1716,53 +1716,59 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H17" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I17" s="11" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I17" s="11" t="n">
+        <x:v>57</x:v>
+      </x:c>
       <x:c r="J17" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K17" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L17" s="11" t="str"/>
-      <x:c r="M17" s="10" t="str"/>
+        <x:v>古装宫廷 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="L17" s="11" t="str">
+        <x:v>展瓦-小付说剧</x:v>
+      </x:c>
+      <x:c r="M17" s="10" t="str">
+        <x:v>嫡女顾明筝前世遭庶妹顾明玉与未婚夫谢哲安联手算计，错嫁后受尽折磨含恨而死。一朝重生回到大婚当日，她将计就计当众揭穿二人私情，顺势改入东宫成为太子妃。她悉心调理病弱太子的身体，夫妻相得，后顺利诞下皇太孙，地位愈发稳固。反观顾明玉嫁入平南侯府后宅斗失算，下毒害人反遭反噬，痛失子嗣被逐出府；谢哲安身中绝嗣之毒，世子之位岌岌可危，侯府彻底败落。最终太子病逝，顾明筝携幼子坚定立身，彻底改写前世悲剧命运。</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C18" s="10" t="str">
-        <x:v>员工跑路我扩店</x:v>
+        <x:v>远山架子班</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>09-13 08:58</x:v>
-      </x:c>
-      <x:c r="E18" s="11" t="n">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="F18" s="11" t="str">
-        <x:v>↑56位</x:v>
-      </x:c>
-      <x:c r="G18" s="11" t="str"/>
-      <x:c r="H18" s="11" t="str"/>
+        <x:v>09-13 07:30</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="str"/>
+      <x:c r="F18" s="11" t="str"/>
+      <x:c r="G18" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H18" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="I18" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J18" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K18" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L18" s="11" t="str">
-        <x:v>大梨看剧</x:v>
+        <x:v>空空书漫</x:v>
       </x:c>
       <x:c r="M18" s="10" t="str">
-        <x:v>林辰经营天力健身馆，年终为员工每人发放五万元奖金。几位教练希望获得更多发展空间，与林辰理念产生分歧，决定在隔壁开设新馆，一场实力较量就此展开。林辰选择升级场地、引进专业团队，并提拔刘阿姨担任店长。正月初七，千名会员到场，用选择见证真诚服务的价值。</x:v>
+        <x:v>工地上，彭大勇拿着别家四十一天的招工纸，问贺远山凭什么只给三十。贺远山不争辩，只把账摊开，安全装备饭钱他管，工钱三天一结，从没拖欠。有人奔着高薪离开，可那边层层扣下来，到手反不如从前，还屡屡涉险。工友受伤住院，贺远山二话不说垫钱救人，又帮着把旧账一笔笔算清。他始终守着一条理，钱要挣，命不能换。规矩立得住，人心自然拢得回，班越带越稳，账越算越明。</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1770,36 +1776,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>35</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C19" s="10" t="str">
-        <x:v>活宝老爹再赴青春，竟与女儿同上大学</x:v>
+        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
-        <x:v>09-13 00:08</x:v>
+        <x:v>09-15 08:00</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
-        <x:v>89</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F19" s="11" t="str">
-        <x:v>↑54位</x:v>
+        <x:v>↑90位</x:v>
       </x:c>
       <x:c r="G19" s="11" t="str"/>
       <x:c r="H19" s="11" t="str"/>
       <x:c r="I19" s="11" t="n">
-        <x:v>140</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J19" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K19" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="L19" s="11" t="str">
-        <x:v>长风剧场</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="M19" s="10" t="str">
-        <x:v>45岁的白烨意外激活成长系统。只要亲身体验年轻人的日常，就能重拾青春活力，还能收获丰厚奖励。为完成系统任务，他报名成人高考，顺利考入大学，竟和女儿成了同校同学。重返校园的白烨，一边认真完成任务感受青春，一边在校园里开启一段充满趣味的全新人生。</x:v>
+        <x:v>沈清韵嫁入靖王府三年，王爷冷落，侧妃得宠。王爷当众许诺，谁先诞下儿子，便请封世子。苏氏先怀孕，沈清韵却发现自己怀的是龙凤胎，她隐瞒消息，买通太医推迟产期，忍痛让苏氏先产子。王爷果然请封庶长子为世子，折子递入宗人府。受理之后，沈清韵才发动，生下龙凤胎。太后与皇上视为祥瑞，下旨赐嫡子承恩为靖王世子、嫡女承华为安乐郡主。王爷措手不及，苏氏地位一落千丈。而沈清韵知道，这只是第一步。</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1807,36 +1813,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C20" s="10" t="str">
-        <x:v>我赚上千万跟爸妈说50W，隔天就被找上门</x:v>
+        <x:v>重生80，救下神雕后我带村民走出大山</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>09-13 08:00</x:v>
+        <x:v>09-13 09:00</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F20" s="11" t="str">
-        <x:v>↑33位</x:v>
+        <x:v>↑36位</x:v>
       </x:c>
       <x:c r="G20" s="11" t="str"/>
       <x:c r="H20" s="11" t="str"/>
       <x:c r="I20" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="J20" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K20" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="L20" s="11" t="str">
-        <x:v>至尊爽剧社</x:v>
+        <x:v>拾光漫漫</x:v>
       </x:c>
       <x:c r="M20" s="10" t="str">
-        <x:v>三十二岁那年，贺川用六年孤注一掷的钻研，换来了七千六百万的回报。可财富还没捂热，先尝到的却是亲人无度的索取。他谎称只赚五十万，叮嘱保密，却挡不住消息走漏。隔天登门的亲戚不止要借钱买房，更联手外人盗用他的身份资料，试图冒名签约、伪造担保债务。贺川报警取证，警方介入追回大部分资金，涉案者包括部分机构人员均承担了法律责任，这笔帐，能否算清？</x:v>
+        <x:v>林大山遭人为意外，意外重生回到1980年。前世他错信爱人落得凄惨下场，重生后果断当众退婚。机缘巧合救下受伤的灵智神雕金羽，还遇见落难善良的白秋月。他携手知恩图报的神雕，依托卧龙山的资源，发掘名贵药材，抓住时代发展机遇。面对同行刁难，林大山坚守本心，凭借智慧与实干，包下荒山兴办药材加工坊。他善待家人，带领乡里百姓勤劳致富，在八十年代的时代浪潮里，靠着双手改写命运，收获美满爱情与事业。</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1844,123 +1850,129 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C21" s="10" t="str">
-        <x:v>丈母娘住下我搬走</x:v>
+        <x:v>乡宴见人心</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>09-13 17:12</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F21" s="11" t="str">
-        <x:v>↑19位</x:v>
+        <x:v>↑27位</x:v>
       </x:c>
       <x:c r="G21" s="11" t="str"/>
       <x:c r="H21" s="11" t="str"/>
-      <x:c r="I21" s="11" t="str"/>
+      <x:c r="I21" s="11" t="n">
+        <x:v>72</x:v>
+      </x:c>
       <x:c r="J21" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K21" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L21" s="11" t="str"/>
-      <x:c r="M21" s="10" t="str"/>
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="L21" s="11" t="str">
+        <x:v>黑白动漫</x:v>
+      </x:c>
+      <x:c r="M21" s="10" t="str">
+        <x:v>高满仓在赵家大院办了八年流水席，十里八村都认他的手艺。眼看生意越来越旺，院主赵金贵突然把租金翻倍，还要按桌抽钱。高满仓干脆带着人和家伙搬进镇外的废米厂，从头再来。赵金贵以为守着大院就守住了客人，靠低价抢生意，却越省越狠。一边是稳稳当当把席办好，一边是亲手砸掉自己的口碑，这场较量最后看的是院子，还是人心。</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C22" s="10" t="str">
-        <x:v>重生极品婆婆，带全家发家致富！</x:v>
+        <x:v>辣媳进门，我给公婆撑腰</x:v>
       </x:c>
       <x:c r="D22" s="11" t="str">
-        <x:v>09-14 20:29</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F22" s="11" t="str">
-        <x:v>↑14位</x:v>
+        <x:v>↑26位</x:v>
       </x:c>
       <x:c r="G22" s="11" t="str"/>
       <x:c r="H22" s="11" t="str"/>
-      <x:c r="I22" s="11" t="n">
-        <x:v>126</x:v>
-      </x:c>
+      <x:c r="I22" s="11" t="str"/>
       <x:c r="J22" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K22" s="10" t="str">
-        <x:v>家庭伦理 / 逆袭打脸</x:v>
-      </x:c>
-      <x:c r="L22" s="11" t="str">
-        <x:v>懒少爱我</x:v>
-      </x:c>
-      <x:c r="M22" s="10" t="str">
-        <x:v>寡妇傅兰秀前世一生吝啬守财，刻薄对待儿女儿媳，到头来钱财被贼人掠夺，落得个凄惨离世的下场。一朝重生，她回到悲剧尚未发生之时。痛定思痛，她彻底改掉抠门的性子，学着善待家里的晚辈。可日子并不太平，爱占便宜的亲戚总上门搅扰，家中两个儿媳也矛盾不断，家务是非接连找上门。傅兰秀靠着清醒的头脑，一边化解各类家庭纷争，一边寻找营生门路，努力扭转命运，拼尽全力守护一家人的安稳生活。</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L22" s="11" t="str"/>
+      <x:c r="M22" s="10" t="str"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C23" s="10" t="str">
-        <x:v>离婚那天我多了个痞帅老爹</x:v>
+        <x:v>四个崽崽瞒不住了</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
-        <x:v>2026-09-13</x:v>
+        <x:v>09-15 00:08</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F23" s="11" t="str">
-        <x:v>↑12位</x:v>
+        <x:v>↑25位</x:v>
       </x:c>
       <x:c r="G23" s="11" t="str"/>
       <x:c r="H23" s="11" t="str"/>
-      <x:c r="I23" s="11" t="str"/>
+      <x:c r="I23" s="11" t="n">
+        <x:v>124</x:v>
+      </x:c>
       <x:c r="J23" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K23" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="L23" s="11" t="str"/>
-      <x:c r="M23" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L23" s="11" t="str">
+        <x:v>桃子动漫剧场</x:v>
+      </x:c>
+      <x:c r="M23" s="10" t="str">
+        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C24" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
+        <x:v>427元扳倒老油条</x:v>
       </x:c>
       <x:c r="D24" s="11" t="str">
-        <x:v>09-15 00:08</x:v>
+        <x:v>09-13 16:00</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F24" s="11" t="str">
-        <x:v>↑12位</x:v>
+        <x:v>↑18位</x:v>
       </x:c>
       <x:c r="G24" s="11" t="str"/>
       <x:c r="H24" s="11" t="str"/>
       <x:c r="I24" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J24" s="10" t="str">
         <x:v>其他</x:v>
@@ -1969,10 +1981,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L24" s="11" t="str">
-        <x:v>桃子动漫剧场</x:v>
+        <x:v>安然然</x:v>
       </x:c>
       <x:c r="M24" s="10" t="str">
-        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
+        <x:v>职场新人许宁向老员工马丽芬讨要427元代垫外卖款，反遭易绑架马丽芬交出饭钱后怀恨在心，利用行政特权私吞福利，并在组织团餐时疏同事差价许宁按兵不动收集证据，最终将马丽芬长期贪占两万余元的行径在老板曝光的照片中马丽芬被直接开除，许宁成功维护了职场底线。</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1980,50 +1992,56 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C25" s="10" t="str">
-        <x:v>小妹初长成</x:v>
+        <x:v>河箱送福来</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
-        <x:v>2026-09-13</x:v>
+        <x:v>09-13 11:00</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F25" s="11" t="str">
-        <x:v>↑5位</x:v>
+        <x:v>↑13位</x:v>
       </x:c>
       <x:c r="G25" s="11" t="str"/>
       <x:c r="H25" s="11" t="str"/>
-      <x:c r="I25" s="11" t="str"/>
+      <x:c r="I25" s="11" t="n">
+        <x:v>64</x:v>
+      </x:c>
       <x:c r="J25" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K25" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L25" s="11" t="str"/>
-      <x:c r="M25" s="10" t="str"/>
+      <x:c r="L25" s="11" t="str">
+        <x:v>灵心讲故事</x:v>
+      </x:c>
+      <x:c r="M25" s="10" t="str">
+        <x:v>张家老两口从河中救回一只木箱，收养了箱中受伤的福生。福生长大后修桥开田，引水惠及乡亲，成家立业。二老相继离世后，山洪威胁村庄，福生为救乡亲舍命撑住巨石，最终重伤落水，下落不明。秀娥守着小院苦等多年，直到熟悉的声音再次响起。</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B26" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C26" s="10" t="str">
-        <x:v>婚不容欺</x:v>
+        <x:v>反派拿捏！</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>2026-09-13</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F26" s="11" t="str">
-        <x:v>↑3位</x:v>
+        <x:v>↑13位</x:v>
       </x:c>
       <x:c r="G26" s="11" t="str"/>
       <x:c r="H26" s="11" t="str"/>
@@ -2032,7 +2050,7 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="K26" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L26" s="11" t="str"/>
       <x:c r="M26" s="10" t="str"/>
@@ -2042,17 +2060,19 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B27" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C27" s="10" t="str">
-        <x:v>辣媳进门，我给公婆撑腰</x:v>
+        <x:v>小妹初长成</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
-        <x:v>2026-09-15</x:v>
-      </x:c>
-      <x:c r="E27" s="11" t="str"/>
+        <x:v>2026-09-13</x:v>
+      </x:c>
+      <x:c r="E27" s="11" t="n">
+        <x:v>27</x:v>
+      </x:c>
       <x:c r="F27" s="11" t="str">
-        <x:v>新上榜</x:v>
+        <x:v>↑3位</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str"/>
       <x:c r="H27" s="11" t="str"/>
@@ -2071,34 +2091,199 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B28" s="11" t="n">
-        <x:v>93</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C28" s="10" t="str">
-        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
+        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
       </x:c>
       <x:c r="D28" s="11" t="str">
-        <x:v>09-15 08:00</x:v>
-      </x:c>
-      <x:c r="E28" s="11" t="str"/>
+        <x:v>09-13 09:58</x:v>
+      </x:c>
+      <x:c r="E28" s="11" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="F28" s="11" t="str">
-        <x:v>新上榜</x:v>
+        <x:v>↑2位</x:v>
       </x:c>
       <x:c r="G28" s="11" t="str"/>
       <x:c r="H28" s="11" t="str"/>
       <x:c r="I28" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J28" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K28" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L28" s="11" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>创想剧场</x:v>
       </x:c>
       <x:c r="M28" s="10" t="str">
-        <x:v>沈清韵嫁入靖王府三年，王爷冷落，侧妃得宠。王爷当众许诺，谁先诞下儿子，便请封世子。苏氏先怀孕，沈清韵却发现自己怀的是龙凤胎，她隐瞒消息，买通太医推迟产期，忍痛让苏氏先产子。王爷果然请封庶长子为世子，折子递入宗人府。受理之后，沈清韵才发动，生下龙凤胎。太后与皇上视为祥瑞，下旨赐嫡子承恩为靖王世子、嫡女承华为安乐郡主。王爷措手不及，苏氏地位一落千丈。而沈清韵知道，这只是第一步。</x:v>
+        <x:v>游戏公会会长林小勇筹备婚礼，却在婚宴上遭遇未婚妻临时加价逼婚。危急时刻，几位相交多年的游戏老友现身力挺他，林小勇果断取消婚礼。之后他搬进好友赠送的别墅，与陈董的两个女儿渐渐熟识。同学聚会上，众人见识到林小勇不一般的际遇。平静日子没过多久，当年游戏里的宿敌将出席游戏八周年嘉年华，一众老友决定赴约，一场新旧对决即将开启。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B29" s="11" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C29" s="10" t="str">
+        <x:v>我在工地卖盒饭带火一座城</x:v>
+      </x:c>
+      <x:c r="D29" s="11" t="str">
+        <x:v>09-14 14:52</x:v>
+      </x:c>
+      <x:c r="E29" s="11" t="str"/>
+      <x:c r="F29" s="11" t="str">
+        <x:v>新上榜</x:v>
+      </x:c>
+      <x:c r="G29" s="11" t="str"/>
+      <x:c r="H29" s="11" t="str"/>
+      <x:c r="I29" s="11" t="n">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="J29" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K29" s="10" t="str">
+        <x:v>美食治愈</x:v>
+      </x:c>
+      <x:c r="L29" s="11" t="str">
+        <x:v>左手良画</x:v>
+      </x:c>
+      <x:c r="M29" s="10" t="str">
+        <x:v>小伙白叶遭遇老板跑路，半年工资付诸东流，意外被铁炒勺砸中觉醒超级餐饮系统。大雪封路堵车途中完成首份任务，靠着系统加持的厨艺，路边卖盒饭赚到第一桶金。回乡钻研秘制酱肉，赶集摆摊火爆出圈，还临危接手大型寿宴惊艳众人。过完新年，他怀揣梦想奔赴外地，准备开启属于自己的餐饮创业之路。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B30" s="11" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C30" s="10" t="str">
+        <x:v>一枚硬币换来的人生</x:v>
+      </x:c>
+      <x:c r="D30" s="11" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="E30" s="11" t="str"/>
+      <x:c r="F30" s="11" t="str">
+        <x:v>新上榜</x:v>
+      </x:c>
+      <x:c r="G30" s="11" t="str"/>
+      <x:c r="H30" s="11" t="str"/>
+      <x:c r="I30" s="11" t="str"/>
+      <x:c r="J30" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="K30" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L30" s="11" t="str"/>
+      <x:c r="M30" s="10" t="str"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B31" s="11" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C31" s="10" t="str">
+        <x:v>从老娘车上滚下去</x:v>
+      </x:c>
+      <x:c r="D31" s="11" t="str">
+        <x:v>2026-09-14</x:v>
+      </x:c>
+      <x:c r="E31" s="11" t="str"/>
+      <x:c r="F31" s="11" t="str">
+        <x:v>新上榜</x:v>
+      </x:c>
+      <x:c r="G31" s="11" t="str"/>
+      <x:c r="H31" s="11" t="str"/>
+      <x:c r="I31" s="11" t="str"/>
+      <x:c r="J31" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="K31" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L31" s="11" t="str"/>
+      <x:c r="M31" s="10" t="str"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B32" s="11" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C32" s="10" t="str">
+        <x:v>假装破产试真心，我看清大学舍友的真面目</x:v>
+      </x:c>
+      <x:c r="D32" s="11" t="str">
+        <x:v>09-15 08:00</x:v>
+      </x:c>
+      <x:c r="E32" s="11" t="str"/>
+      <x:c r="F32" s="11" t="str">
+        <x:v>新上榜</x:v>
+      </x:c>
+      <x:c r="G32" s="11" t="str"/>
+      <x:c r="H32" s="11" t="str"/>
+      <x:c r="I32" s="11" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="J32" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K32" s="10" t="str">
+        <x:v>婚姻情感 / 美食治愈 / 现实反转</x:v>
+      </x:c>
+      <x:c r="L32" s="11" t="str">
+        <x:v>芙浚动漫短剧</x:v>
+      </x:c>
+      <x:c r="M32" s="10" t="str">
+        <x:v>洛宁对外谎称家中破产那天，宿舍里的空气忽然变了味道。曾经收下她慷慨馈赠的陆清颜瞬间冷脸，惦记着还没到手的贵重礼物，处处刁难；贫困生齐黎一边继续收下她的物资，只象征性付点小钱，一边冷眼旁观，甚至给她介绍风月兼职。洛宁没有争辩，只是默默打开电脑，把每一句话、每一个眼神，都记进了那份越来越厚的PPT里。校庆那天，她准备了一份谁也想不到的“礼物”。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B33" s="11" t="n">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C33" s="10" t="str">
+        <x:v>废材逆袭，我能截胡主角机缘</x:v>
+      </x:c>
+      <x:c r="D33" s="11" t="str">
+        <x:v>09-13 10:28</x:v>
+      </x:c>
+      <x:c r="E33" s="11" t="str"/>
+      <x:c r="F33" s="11" t="str">
+        <x:v>新上榜</x:v>
+      </x:c>
+      <x:c r="G33" s="11" t="str"/>
+      <x:c r="H33" s="11" t="str"/>
+      <x:c r="I33" s="11" t="n">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J33" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K33" s="10" t="str">
+        <x:v>婚姻情感 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="L33" s="11" t="str">
+        <x:v>寻光短剧剧场</x:v>
+      </x:c>
+      <x:c r="M33" s="10" t="str">
+        <x:v>秦云遭未婚妻徐凝烟退婚，觉醒“气运真视”金手指，能预见机缘与灾劫。他接连截胡多位天命主角的机缘，获真龙道体、上古九秘，得古道圣人毕生传承，进入紫州圣地登顶圣子，闯魔宫夺八荒魔戟，入佛门揭佛渊秘辛，收先天魔胎囡囡为徒，最终于对战中悟透大道突破成圣，开启纵横天下的全新征程。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2144,7 +2329,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
         <x:v>辣媳进门，我给公婆撑腰</x:v>
@@ -2161,30 +2346,30 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
-        <x:v>37</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>被算计的新娘华丽转身</x:v>
+        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>当日新上榜</x:v>
+        <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>07-28 00:29</x:v>
+        <x:v>09-15 08:00</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F3" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G3" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
         <x:v>四个崽崽瞒不住了</x:v>
@@ -2207,27 +2392,33 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>结婚八年，我娶的原来是仇人的女儿</x:v>
+        <x:v>被算计的新娘华丽转身</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
         <x:v>当日新上榜</x:v>
       </x:c>
-      <x:c r="D5" s="11" t="str"/>
-      <x:c r="E5" s="11" t="str"/>
+      <x:c r="D5" s="11" t="str">
+        <x:v>07-28 00:29</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="n">
+        <x:v>72</x:v>
+      </x:c>
       <x:c r="F5" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="str"/>
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="G5" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>丈母娘住下我搬走</x:v>
+        <x:v>一枚硬币换来的人生</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
         <x:v>当日新上榜</x:v>
@@ -2241,106 +2432,26 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>一叶守义满山春</x:v>
+        <x:v>假装破产试真心，我看清大学舍友的真面目</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>当日新上榜</x:v>
+        <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>08-14 10:10</x:v>
+        <x:v>09-15 08:00</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
-        <x:v>86</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F7" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G7" s="10" t="str">
-        <x:v>挽风文化传媒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="11" t="n">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B8" s="10" t="str">
-        <x:v>别欺负我奶奶</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="str">
-        <x:v>当日新上榜</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="str">
-        <x:v>09-02 18:27</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="n">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F8" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="G8" s="10" t="str">
-        <x:v>小焓追剧</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="11" t="n">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="B9" s="10" t="str">
-        <x:v>婚不容欺</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="str">
-        <x:v>当日新上榜</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="str"/>
-      <x:c r="E9" s="11" t="str"/>
-      <x:c r="F9" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="G9" s="10" t="str"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="11" t="n">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="B10" s="10" t="str">
-        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
-      </x:c>
-      <x:c r="C10" s="11" t="str">
-        <x:v>今日发布</x:v>
-      </x:c>
-      <x:c r="D10" s="11" t="str">
-        <x:v>09-15 08:00</x:v>
-      </x:c>
-      <x:c r="E10" s="11" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F10" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G10" s="10" t="str">
-        <x:v>心动漫剧场</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="11" t="n">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="B11" s="10" t="str">
-        <x:v>偷脸</x:v>
-      </x:c>
-      <x:c r="C11" s="11" t="str">
-        <x:v>当日新上榜</x:v>
-      </x:c>
-      <x:c r="D11" s="11" t="str"/>
-      <x:c r="E11" s="11" t="str"/>
-      <x:c r="F11" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="G11" s="10" t="str"/>
+        <x:v>芙浚动漫短剧</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2409,16 +2520,16 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
-        <x:v>离家十年，回来女儿被换了</x:v>
+        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>09-09 00:04</x:v>
+        <x:v>09-08 17:58</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
         <x:v>7</x:v>
@@ -2430,7 +2541,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H2" s="11" t="n">
-        <x:v>155</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="I2" s="10" t="str">
         <x:v>其他</x:v>
@@ -2438,24 +2549,24 @@
       <x:c r="J2" s="11" t="str"/>
       <x:c r="K2" s="11" t="str"/>
       <x:c r="L2" s="10" t="str">
-        <x:v>魔方影视（上剧版</x:v>
+        <x:v>禾苗动画</x:v>
       </x:c>
       <x:c r="M2" s="10" t="str">
-        <x:v>程砚宁完成长期绝密任务归来，满心想要弥补亲情，却发现家中早已物是人非。身边亲近之人被私欲蒙蔽，制造重重骗局，试图侵占她的事业与财富。面对接连而来的算计与危机，她凭借过人的魄力与智慧步步拆解阴谋，联合正义力量搜集证据，厘清全部是非纠葛。在守护自身事业的同时，她放下过往伤痛，投身公益，完成自我和解，迎来属于自己的全新人生。</x:v>
+        <x:v>末世异能者沐小暖意外穿书，成为七个反派继子的恶毒后娘。原主辛劳养娃却遭流言中伤，最终含恨而终。沐小暖决心扭转命运，恩威并施管教孩子，凭末世身手进山打猎采药、种地赶集改善家计，更以百年老参为礼，为长子求得名儒霍政谚收为关门弟子。她护佑家人躲过恶人算计与亲戚夺产，建起新宅。七个孩子从怨恨抗拒到真心信赖，争着喊她娘，一家人携手改写命运，收获温暖亲情。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>破库房的秘密</x:v>
+        <x:v>重生三天前，我用水泥封死地下室</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>2026-09-05</x:v>
+        <x:v>09-09 09:28</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
         <x:v>7</x:v>
@@ -2464,29 +2575,35 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G3" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H3" s="11" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H3" s="11" t="n">
+        <x:v>45</x:v>
+      </x:c>
       <x:c r="I3" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J3" s="11" t="str"/>
       <x:c r="K3" s="11" t="str"/>
-      <x:c r="L3" s="10" t="str"/>
-      <x:c r="M3" s="10" t="str"/>
+      <x:c r="L3" s="10" t="str">
+        <x:v>忘忧剧场</x:v>
+      </x:c>
+      <x:c r="M3" s="10" t="str">
+        <x:v>阮清重生回被保姆王妈一家害死的三天前，前世她因心善引狼入室，保姆全家蜗居别墅地下室偷窃投毒，最终惨遭勒死。重生后她假装不知，趁王妈外出时用水泥将地下室彻底封死。警方破墙后，五具尸体令真相大白，王妈因盗窃、投毒被判十五年。阮清与父母团聚，恶人终得恶报，她重获新生。</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
+        <x:v>一墙之隔，皆是人心</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>09-08 17:58</x:v>
+        <x:v>09-06 15:48</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
         <x:v>7</x:v>
@@ -2498,7 +2615,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H4" s="11" t="n">
-        <x:v>111</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="I4" s="10" t="str">
         <x:v>其他</x:v>
@@ -2506,24 +2623,24 @@
       <x:c r="J4" s="11" t="str"/>
       <x:c r="K4" s="11" t="str"/>
       <x:c r="L4" s="10" t="str">
-        <x:v>禾苗动画</x:v>
+        <x:v>在下长生</x:v>
       </x:c>
       <x:c r="M4" s="10" t="str">
-        <x:v>末世异能者沐小暖意外穿书，成为七个反派继子的恶毒后娘。原主辛劳养娃却遭流言中伤，最终含恨而终。沐小暖决心扭转命运，恩威并施管教孩子，凭末世身手进山打猎采药、种地赶集改善家计，更以百年老参为礼，为长子求得名儒霍政谚收为关门弟子。她护佑家人躲过恶人算计与亲戚夺产，建起新宅。七个孩子从怨恨抗拒到真心信赖，争着喊她娘，一家人携手改写命运，收获温暖亲情。</x:v>
+        <x:v>妻子临产被车堵住出口，叶瑾抱着羊水破裂的她跑了三公里才到医院，母子平安。面对无理的车主，他没有以暴制暴，而是选择依法行事——在自家院内合法砌墙、种下高价值树苗，全程录像留证。车主回来后暴力砸墙、碾压树苗，最终被依法追究责任。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>惊絮无声：傻女的绝杀</x:v>
+        <x:v>离家十年，回来女儿被换了</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>09-06 10:00</x:v>
+        <x:v>09-09 00:04</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
         <x:v>7</x:v>
@@ -2532,10 +2649,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G5" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H5" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="I5" s="10" t="str">
         <x:v>其他</x:v>
@@ -2543,24 +2660,24 @@
       <x:c r="J5" s="11" t="str"/>
       <x:c r="K5" s="11" t="str"/>
       <x:c r="L5" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>魔方影视（上剧版</x:v>
       </x:c>
       <x:c r="M5" s="10" t="str">
-        <x:v>沈家人人都是天才，唯独小女儿沈惊絮是公认的傻子。没人知道，她不仅装傻多年，还带着前世金牌律师的记忆重生而来。本想闭嘴躺平一生，谁料内鬼勾结资本做空沈氏，一纸合同就要让全家净身出户、背上百亿债务。父亲落笔前，她终于按住协议“这字不能签！”绝地反杀的沈惊絮，一步步挫败了对沈家的围剿，也让全家人重新认识了自己。沈家也迎来了新生。</x:v>
+        <x:v>程砚宁完成长期绝密任务归来，满心想要弥补亲情，却发现家中早已物是人非。身边亲近之人被私欲蒙蔽，制造重重骗局，试图侵占她的事业与财富。面对接连而来的算计与危机，她凭借过人的魄力与智慧步步拆解阴谋，联合正义力量搜集证据，厘清全部是非纠葛。在守护自身事业的同时，她放下过往伤痛，投身公益，完成自我和解，迎来属于自己的全新人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>重生三天前，我用水泥封死地下室</x:v>
+        <x:v>穿书后我带萌宝上门认爹</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>09-09 09:28</x:v>
+        <x:v>09-07 19:18</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
         <x:v>7</x:v>
@@ -2569,10 +2686,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G6" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H6" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
         <x:v>其他</x:v>
@@ -2580,21 +2697,21 @@
       <x:c r="J6" s="11" t="str"/>
       <x:c r="K6" s="11" t="str"/>
       <x:c r="L6" s="10" t="str">
-        <x:v>忘忧剧场</x:v>
+        <x:v>虾仁不自在</x:v>
       </x:c>
       <x:c r="M6" s="10" t="str">
-        <x:v>阮清重生回被保姆王妈一家害死的三天前，前世她因心善引狼入室，保姆全家蜗居别墅地下室偷窃投毒，最终惨遭勒死。重生后她假装不知，趁王妈外出时用水泥将地下室彻底封死。警方破墙后，五具尸体令真相大白，王妈因盗窃、投毒被判十五年。阮清与父母团聚，恶人终得恶报，她重获新生。</x:v>
+        <x:v>许知棠重生穿进书中，当即带着五岁儿子许小舟登门，将孩子送到亲生父亲——傅氏集团总裁傅临川面前，只想抽身退出剧情。幼儿园里儿子遭同学诬陷、老师偏心，她强势护崽，硬刚蛮横家长与失职老师。亲子鉴定尘埃落定，萌娃黏妈不黏爹，反倒让清冷总裁渐渐上心。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>一墙之隔，皆是人心</x:v>
+        <x:v>惊絮无声：傻女的绝杀</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>09-06 15:48</x:v>
+        <x:v>09-06 10:00</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
         <x:v>9</x:v>
@@ -2606,10 +2723,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G7" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H7" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I7" s="10" t="str">
         <x:v>其他</x:v>
@@ -2617,24 +2734,24 @@
       <x:c r="J7" s="11" t="str"/>
       <x:c r="K7" s="11" t="str"/>
       <x:c r="L7" s="10" t="str">
-        <x:v>在下长生</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="M7" s="10" t="str">
-        <x:v>妻子临产被车堵住出口，叶瑾抱着羊水破裂的她跑了三公里才到医院，母子平安。面对无理的车主，他没有以暴制暴，而是选择依法行事——在自家院内合法砌墙、种下高价值树苗，全程录像留证。车主回来后暴力砸墙、碾压树苗，最终被依法追究责任。</x:v>
+        <x:v>沈家人人都是天才，唯独小女儿沈惊絮是公认的傻子。没人知道，她不仅装傻多年，还带着前世金牌律师的记忆重生而来。本想闭嘴躺平一生，谁料内鬼勾结资本做空沈氏，一纸合同就要让全家净身出户、背上百亿债务。父亲落笔前，她终于按住协议“这字不能签！”绝地反杀的沈惊絮，一步步挫败了对沈家的围剿，也让全家人重新认识了自己。沈家也迎来了新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>穿书后我带萌宝上门认爹</x:v>
+        <x:v>不靠谱爸妈很靠谱</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>09-07 19:18</x:v>
+        <x:v>09-09 11:08</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
         <x:v>7</x:v>
@@ -2643,10 +2760,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G8" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H8" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
         <x:v>其他</x:v>
@@ -2654,24 +2771,24 @@
       <x:c r="J8" s="11" t="str"/>
       <x:c r="K8" s="11" t="str"/>
       <x:c r="L8" s="10" t="str">
-        <x:v>虾仁不自在</x:v>
+        <x:v>灵妹儿</x:v>
       </x:c>
       <x:c r="M8" s="10" t="str">
-        <x:v>许知棠重生穿进书中，当即带着五岁儿子许小舟登门，将孩子送到亲生父亲——傅氏集团总裁傅临川面前，只想抽身退出剧情。幼儿园里儿子遭同学诬陷、老师偏心，她强势护崽，硬刚蛮横家长与失职老师。亲子鉴定尘埃落定，萌娃黏妈不黏爹，反倒让清冷总裁渐渐上心。</x:v>
+        <x:v>外表张扬的年轻夫妻在冬夜救下女婴林小小，用十七年的辛勤劳动和无条件陪伴，为她撑起温暖的家。曾经成绩落后的林小小，在父母的鼓励下重新学习，一步步成长为优秀学生。面对亲生家庭带来的资源与人生选择，她也开始重新理解血缘、养育与责任。当外界的误解影响到父母的生活，林小小决定勇敢站出来，用事实守护家人，也用努力证明真正的爱，是尊重、陪伴和彼此成就。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="n">
-        <x:v>34</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>不靠谱爸妈很靠谱</x:v>
+        <x:v>破库房的秘密</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>09-09 11:08</x:v>
+        <x:v>2026-09-05</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
         <x:v>7</x:v>
@@ -2682,24 +2799,18 @@
       <x:c r="G9" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H9" s="11" t="n">
-        <x:v>73</x:v>
-      </x:c>
+      <x:c r="H9" s="11" t="str"/>
       <x:c r="I9" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J9" s="11" t="str"/>
       <x:c r="K9" s="11" t="str"/>
-      <x:c r="L9" s="10" t="str">
-        <x:v>灵妹儿</x:v>
-      </x:c>
-      <x:c r="M9" s="10" t="str">
-        <x:v>外表张扬的年轻夫妻在冬夜救下女婴林小小，用十七年的辛勤劳动和无条件陪伴，为她撑起温暖的家。曾经成绩落后的林小小，在父母的鼓励下重新学习，一步步成长为优秀学生。面对亲生家庭带来的资源与人生选择，她也开始重新理解血缘、养育与责任。当外界的误解影响到父母的生活，林小小决定勇敢站出来，用事实守护家人，也用努力证明真正的爱，是尊重、陪伴和彼此成就。</x:v>
-      </x:c>
+      <x:c r="L9" s="10" t="str"/>
+      <x:c r="M9" s="10" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="n">
-        <x:v>43</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
         <x:v>抢个新娘来当后娘第一季</x:v>
@@ -2736,7 +2847,7 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="n">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
         <x:v>凤阙承安</x:v>
@@ -2767,7 +2878,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
         <x:v>重启人生，拒绝校花？</x:v>
@@ -2804,16 +2915,16 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
+        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>2026-09-05</x:v>
+        <x:v>09-08 11:00</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
         <x:v>7</x:v>
@@ -2824,27 +2935,33 @@
       <x:c r="G13" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H13" s="11" t="str"/>
+      <x:c r="H13" s="11" t="n">
+        <x:v>91</x:v>
+      </x:c>
       <x:c r="I13" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J13" s="11" t="str"/>
       <x:c r="K13" s="11" t="str"/>
-      <x:c r="L13" s="10" t="str"/>
-      <x:c r="M13" s="10" t="str"/>
+      <x:c r="L13" s="10" t="str">
+        <x:v>白桃剧场</x:v>
+      </x:c>
+      <x:c r="M13" s="10" t="str">
+        <x:v>阿梨一觉睡了三百年，养大的五只小兽尽数离去。她带着五只旧饭碗、十二枚铜钱与一把锈柴刀下山寻兽。昔日的小家伙已成威震四方的妖祖，历经重重相遇与揭秘，阿梨知晓三百年封印的真相，携手五只妖祖，一同对抗祸世灭灵兽神。</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
+        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>09-08 11:00</x:v>
+        <x:v>2026-09-05</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
         <x:v>7</x:v>
@@ -2855,24 +2972,18 @@
       <x:c r="G14" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H14" s="11" t="n">
-        <x:v>91</x:v>
-      </x:c>
+      <x:c r="H14" s="11" t="str"/>
       <x:c r="I14" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J14" s="11" t="str"/>
       <x:c r="K14" s="11" t="str"/>
-      <x:c r="L14" s="10" t="str">
-        <x:v>白桃剧场</x:v>
-      </x:c>
-      <x:c r="M14" s="10" t="str">
-        <x:v>阿梨一觉睡了三百年，养大的五只小兽尽数离去。她带着五只旧饭碗、十二枚铜钱与一把锈柴刀下山寻兽。昔日的小家伙已成威震四方的妖祖，历经重重相遇与揭秘，阿梨知晓三百年封印的真相，携手五只妖祖，一同对抗祸世灭灵兽神。</x:v>
-      </x:c>
+      <x:c r="L14" s="10" t="str"/>
+      <x:c r="M14" s="10" t="str"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="n">
-        <x:v>84</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
         <x:v>美颜系统开挂，大佬全跪下</x:v>
@@ -2909,28 +3020,28 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>征地我秒签跑路，全村笑我半年</x:v>
+        <x:v>天灾末世，她囤满物资后所向披靡！</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>09-10 11:30</x:v>
+        <x:v>09-08 15:00</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G16" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H16" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str">
         <x:v>其他</x:v>
@@ -2938,36 +3049,36 @@
       <x:c r="J16" s="11" t="str"/>
       <x:c r="K16" s="11" t="str"/>
       <x:c r="L16" s="10" t="str">
-        <x:v>小六动漫</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="M16" s="10" t="str">
-        <x:v>赵家湾迎来高速征地，村民受村长赵德厚鼓动抱团拒签，妄想抬价拿到四百五十万补偿。林远察觉当地岩溶地质暗藏线路改线风险，不顾全村嘲讽，果断签下312万补偿款，带父母搬离老家。后续高速果真改线，全村一分补偿落空。曾经嘲笑林远的村民陷入债务困境，赵德厚登门求助，林远守住底线，一家人握紧安稳生活，告诫众人抉择要靠自己。</x:v>
+        <x:v>韩清夏被至亲推向绝境，失去家园，没能守住重要伙伴。再次睁眼，她回到了灾变来临前，并意外激活超级领主系统。她果断卖房筹资、囤积物资，将废弃防空洞升级为坚固基地，与战犬夏天并肩成长。危机爆发后，她凭借清醒判断、强大异能和充足准备救下幸存者，组建盛夏联盟。面对旧日亲人的算计、各方势力的试探与接连不断的考验，韩清夏不再退让。这一世，她要守住伙伴、掌握命运，在废墟之上建起属于自己的家园。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>大坝边寻回的真千金</x:v>
+        <x:v>蒙蒙半故</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>09-10 11:26</x:v>
+        <x:v>09-05 20:27</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E17" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F17" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G17" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="H17" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="I17" s="10" t="str">
         <x:v>其他</x:v>
@@ -2975,67 +3086,73 @@
       <x:c r="J17" s="11" t="str"/>
       <x:c r="K17" s="11" t="str"/>
       <x:c r="L17" s="10" t="str">
-        <x:v>喵琪琪追剧</x:v>
+        <x:v>小斐漫剧</x:v>
       </x:c>
       <x:c r="M17" s="10" t="str">
-        <x:v>大坝突发险情，农村女孩夏晚禾凭借熟悉的环境和过人的勇气，不顾危险救下被困的沈长洲。一次意外的救援，让两个陌生人的命运重新交织。随着调查深入，沈长洲发现这个善良坚韧的女孩，竟是自己失散二十年的亲生女儿。面对迟来的亲情和真假千金的风波，夏晚禾没有依靠身份改变人生，而是用智慧、担当和努力证明自己的价值。陆言川也在一次次并肩相处中，被她的真诚与坚强打动，陪她找回亲情，走向新的未来。</x:v>
+        <x:v>拥有漫长寿命的男人隐姓埋名，以外卖员身份在都市生活。百岁老人临终的遗愿，让他卷入豪门家族的纷争。他结识家族女总裁，接连应对家族内斗、敌对势力与神秘长生组织的重重算计。二人携手揭开千年前的尘封秘辛，对抗妄图窃取长生力量的反派，在危机之中彼此羁绊，还要面对即将开启的上古昆仑之门带来的巨大未知考验。</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>假老板娘遇上真董事长</x:v>
+        <x:v>那块玉，带我们回家</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>09-05 07:18</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G18" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H18" s="11" t="str"/>
+      <x:c r="H18" s="11" t="n">
+        <x:v>69</x:v>
+      </x:c>
       <x:c r="I18" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J18" s="11" t="str"/>
       <x:c r="K18" s="11" t="str"/>
-      <x:c r="L18" s="10" t="str"/>
-      <x:c r="M18" s="10" t="str"/>
+      <x:c r="L18" s="10" t="str">
+        <x:v>五指毛桃</x:v>
+      </x:c>
+      <x:c r="M18" s="10" t="str">
+        <x:v>六岁孩童为救母拾荒半年，孝心感动天地，更牵出一段失散六年的亲情。缘分以信物为引，助离散一家重逢。当暗处之手伸向团圆，真相与信任如光破晓，令恶念无处遁形。正义为善良护航，温暖在守望中生长。孩子用稚嫩肩膀撑起希望，父母以爱重筑家园，善意在风雨中传递，终迎阖家安康的晴空。</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>迟来深情皆是刃</x:v>
+        <x:v>谢谢爸妈的穷养现在我富了</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>09-09 10:00</x:v>
+        <x:v>09-08 17:00</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E19" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F19" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G19" s="11" t="n">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="H19" s="11" t="n">
-        <x:v>184</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str">
         <x:v>其他</x:v>
@@ -3043,36 +3160,36 @@
       <x:c r="J19" s="11" t="str"/>
       <x:c r="K19" s="11" t="str"/>
       <x:c r="L19" s="10" t="str">
-        <x:v>展瓦-佩云看剧</x:v>
+        <x:v>风云剧场</x:v>
       </x:c>
       <x:c r="M19" s="10" t="str">
-        <x:v>天才芯片科研人姜莱，隐去光芒，在婚姻里默默付出四年，却遭遇丈夫沈荀的背叛与冷待。看清现实的她挣脱窒息的婚姻，撕下普通家庭主妇的伪装，重拾科研理想。面对丈夫、情敌的百般算计，她冷静反击。在自研芯重大项目竞标舞台上，姜莱展露真实实力，完成华丽逆袭，实现自我价值。过往伤痛化作成长力量，她告别糟糕的旧生活，向着事业与崭新的人生大步奔赴，迎来属于自己的光明未来。</x:v>
+        <x:v>秦明从小被父母区别对待，十八年后才知一切只是父母对两个儿子的不同教育安排。重生回到高三，他拒绝向既定命运低头，从校园起步，抓住时代机遇暗中积蓄力量。父母继续对弟弟偏爱，秦明也继续低调生活——整整十八年。直到除夕夜，他回到那个破旧的家，把所有真相摆在父母面前，把自己失去的人生，亲手要了回来。</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>重生后我守住全村</x:v>
+        <x:v>全家施压：我反手签了过户合同</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>09-10 08:08</x:v>
+        <x:v>09-08 16:58</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G20" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H20" s="11" t="n">
-        <x:v>129</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I20" s="10" t="str">
         <x:v>其他</x:v>
@@ -3080,36 +3197,36 @@
       <x:c r="J20" s="11" t="str"/>
       <x:c r="K20" s="11" t="str"/>
       <x:c r="L20" s="10" t="str">
-        <x:v>金果漫剧</x:v>
+        <x:v>灵川剧场</x:v>
       </x:c>
       <x:c r="M20" s="10" t="str">
-        <x:v>70年代冬，赵满仓在父亲离世后重回鼠灾前八天。面对家中骤变，他选择先护住亲人，带着前世经验迁入碾坊，储粮备药，筑墙防鼠，设点防疫。灾情来临时，他联合李杏儿，刘石头和乡亲稳住村庄，并用账册与规矩澄清父亲名誉。风雪过后，黎家沟建起防鼠坊，猫舍和净粮地窖，众人也在互助中迎来新生。</x:v>
+        <x:v>儿子儿媳多次提议我搬回乡下养老，将城里的宽敞住房腾出来给女方父母长期居住。我笑着点头应下，转头便将这套三室朝南的江景房产挂牌出售，最终成交二百八十万元。我随即购置了一套一室一厅的小户型，更换门锁后独自入住。他们上门索要钥匙，我没有开门。名下房产我自有主张，谁也别想插手安排。</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>三分钱的取舍</x:v>
+        <x:v>征地我秒签跑路，全村笑我半年</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>09-10 17:29</x:v>
+        <x:v>09-10 11:30</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G21" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H21" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I21" s="10" t="str">
         <x:v>其他</x:v>
@@ -3117,36 +3234,36 @@
       <x:c r="J21" s="11" t="str"/>
       <x:c r="K21" s="11" t="str"/>
       <x:c r="L21" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>小六动漫</x:v>
       </x:c>
       <x:c r="M21" s="10" t="str">
-        <x:v>青石沟果农为省下代办三分钱，甩开中间商周成岳，直接对接收购商方洪生收桃。可脱离周成岳统筹调度后，摘桃、排单、装车乱象丛生，桃子积压损耗。周成岳转身接手偏远的十里湾桃园，凭口碑站稳脚跟。经历一季波折，青石沟众人幡然醒悟，重新读懂代办的价值。</x:v>
+        <x:v>赵家湾迎来高速征地，村民受村长赵德厚鼓动抱团拒签，妄想抬价拿到四百五十万补偿。林远察觉当地岩溶地质暗藏线路改线风险，不顾全村嘲讽，果断签下312万补偿款，带父母搬离老家。后续高速果真改线，全村一分补偿落空。曾经嘲笑林远的村民陷入债务困境，赵德厚登门求助，林远守住底线，一家人握紧安稳生活，告诫众人抉择要靠自己。</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
+        <x:v>大坝边寻回的真千金</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>09-11 09:00</x:v>
+        <x:v>09-10 11:26</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G22" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="H22" s="11" t="n">
-        <x:v>133</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str">
         <x:v>其他</x:v>
@@ -3154,36 +3271,36 @@
       <x:c r="J22" s="11" t="str"/>
       <x:c r="K22" s="11" t="str"/>
       <x:c r="L22" s="10" t="str">
-        <x:v>阳阳动画</x:v>
+        <x:v>喵琪琪追剧</x:v>
       </x:c>
       <x:c r="M22" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
+        <x:v>大坝突发险情，农村女孩夏晚禾凭借熟悉的环境和过人的勇气，不顾危险救下被困的沈长洲。一次意外的救援，让两个陌生人的命运重新交织。随着调查深入，沈长洲发现这个善良坚韧的女孩，竟是自己失散二十年的亲生女儿。面对迟来的亲情和真假千金的风波，夏晚禾没有依靠身份改变人生，而是用智慧、担当和努力证明自己的价值。陆言川也在一次次并肩相处中，被她的真诚与坚强打动，陪她找回亲情，走向新的未来。</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="n">
-        <x:v>29</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>重生一世，我不再痴恋竹马</x:v>
+        <x:v>重生后我守住全村</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>09-10 10:00</x:v>
+        <x:v>09-10 08:08</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G23" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H23" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
         <x:v>其他</x:v>
@@ -3191,73 +3308,67 @@
       <x:c r="J23" s="11" t="str"/>
       <x:c r="K23" s="11" t="str"/>
       <x:c r="L23" s="10" t="str">
-        <x:v>锦书映年华</x:v>
+        <x:v>金果漫剧</x:v>
       </x:c>
       <x:c r="M23" s="10" t="str">
-        <x:v>承平公主前世错恋齐远安，受尽磋磨含恨落幕。一朝重生，恰逢圣旨赐婚，齐远安却当众恳请解除婚约，求取太后义孙女傅明珠。她坦然放手，主动成全二人，看着他们得偿所愿。宁国侯夫人动用旧物强求赐婚，她巧妙改换婚事，选择边关归来、品性刚正的齐远舟。婚后她聪慧通透，看清傅明珠与齐远安的本性，冷眼旁观二人矛盾丛生。历经风波，她与齐远舟彼此扶持，挣脱过往伤痛，收获属于自己安稳坦荡的人生。</x:v>
+        <x:v>70年代冬，赵满仓在父亲离世后重回鼠灾前八天。面对家中骤变，他选择先护住亲人，带着前世经验迁入碾坊，储粮备药，筑墙防鼠，设点防疫。灾情来临时，他联合李杏儿，刘石头和乡亲稳住村庄，并用账册与规矩澄清父亲名誉。风雪过后，黎家沟建起防鼠坊，猫舍和净粮地窖，众人也在互助中迎来新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>穿越60我有空间不愁吃喝</x:v>
+        <x:v>假老板娘遇上真董事长</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>09-07 00:04</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G24" s="11" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H24" s="11" t="n">
-        <x:v>1000</x:v>
-      </x:c>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H24" s="11" t="str"/>
       <x:c r="I24" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J24" s="11" t="str"/>
       <x:c r="K24" s="11" t="str"/>
-      <x:c r="L24" s="10" t="str">
-        <x:v>夜珠AI剧场</x:v>
-      </x:c>
-      <x:c r="M24" s="10" t="str">
-        <x:v>现代青年刘大壮意外穿越到60年代，成了同名同姓的16岁穷小子。原主因相亲被拒、家徒四壁，下河摸鱼时溺亡。大壮醒来后发现脑中多了一座九层宝塔空间——内有灵药田与灵泉潭水，作物两小时成熟、产量翻五倍。饥荒年代，别人啃树皮喝稀粥，他靠空间种出满仓土豆粮食，黑市换粮票钞票，让饿肚子的父母姐姐们吃上饱饭。从人人嘲笑的穷小子，到带着全家逆袭翻盘，且看他手握宝塔空间，在艰苦年代闯出一条吃喝不愁的逆袭</x:v>
-      </x:c>
+      <x:c r="L24" s="10" t="str"/>
+      <x:c r="M24" s="10" t="str"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>张兰芬重生记</x:v>
+        <x:v>迟来深情皆是刃</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>09-05 17:00</x:v>
+        <x:v>09-09 10:00</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G25" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H25" s="11" t="n">
-        <x:v>176</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str">
         <x:v>其他</x:v>
@@ -3265,52 +3376,58 @@
       <x:c r="J25" s="11" t="str"/>
       <x:c r="K25" s="11" t="str"/>
       <x:c r="L25" s="10" t="str">
-        <x:v>璀璨Ai剧场</x:v>
+        <x:v>展瓦-佩云看剧</x:v>
       </x:c>
       <x:c r="M25" s="10" t="str">
-        <x:v>张兰芬操劳半生，是旁人羡慕的当家主母。她为李家养育四子两女，持家有道、将家中大小事务打理得井井有条。半生付出尽数落空，张兰芬郁结于心，最终含恨病逝医院。一朝重生，她回到所有遗憾尚未发生之时，彻底看透人心，决意放下执念，好好为自己活一次。</x:v>
+        <x:v>天才芯片科研人姜莱，隐去光芒，在婚姻里默默付出四年，却遭遇丈夫沈荀的背叛与冷待。看清现实的她挣脱窒息的婚姻，撕下普通家庭主妇的伪装，重拾科研理想。面对丈夫、情敌的百般算计，她冷静反击。在自研芯重大项目竞标舞台上，姜莱展露真实实力，完成华丽逆袭，实现自我价值。过往伤痛化作成长力量，她告别糟糕的旧生活，向着事业与崭新的人生大步奔赴，迎来属于自己的光明未来。</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="n">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>穿成恋爱脑女配，我把将军府带偏了呀</x:v>
+        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
-        <x:v>2026-09-06</x:v>
+        <x:v>09-11 09:00</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G26" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G26" s="11" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H26" s="11" t="str"/>
+      <x:c r="H26" s="11" t="n">
+        <x:v>133</x:v>
+      </x:c>
       <x:c r="I26" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J26" s="11" t="str"/>
       <x:c r="K26" s="11" t="str"/>
-      <x:c r="L26" s="10" t="str"/>
-      <x:c r="M26" s="10" t="str"/>
+      <x:c r="L26" s="10" t="str">
+        <x:v>阳阳动画</x:v>
+      </x:c>
+      <x:c r="M26" s="10" t="str">
+        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>带着龙凤胎：和前夫共续前缘</x:v>
+        <x:v>三分钱的取舍</x:v>
       </x:c>
       <x:c r="C27" s="11" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>09-10 17:29</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
         <x:v>5</x:v>
@@ -3319,19 +3436,161 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G27" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H27" s="11" t="str"/>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H27" s="11" t="n">
+        <x:v>58</x:v>
+      </x:c>
       <x:c r="I27" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J27" s="11" t="str"/>
       <x:c r="K27" s="11" t="str"/>
-      <x:c r="L27" s="10" t="str"/>
-      <x:c r="M27" s="10" t="str"/>
+      <x:c r="L27" s="10" t="str">
+        <x:v>马克动漫</x:v>
+      </x:c>
+      <x:c r="M27" s="10" t="str">
+        <x:v>青石沟果农为省下代办三分钱，甩开中间商周成岳，直接对接收购商方洪生收桃。可脱离周成岳统筹调度后，摘桃、排单、装车乱象丛生，桃子积压损耗。周成岳转身接手偏远的十里湾桃园，凭口碑站稳脚跟。经历一季波折，青石沟众人幡然醒悟，重新读懂代办的价值。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="11" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B28" s="10" t="str">
+        <x:v>一张废票毁了她</x:v>
+      </x:c>
+      <x:c r="C28" s="11" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="D28" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E28" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F28" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G28" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H28" s="11" t="str"/>
+      <x:c r="I28" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="J28" s="11" t="str"/>
+      <x:c r="K28" s="11" t="str"/>
+      <x:c r="L28" s="10" t="str"/>
+      <x:c r="M28" s="10" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="11" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B29" s="10" t="str">
+        <x:v>穿越60我有空间不愁吃喝</x:v>
+      </x:c>
+      <x:c r="C29" s="11" t="str">
+        <x:v>09-07 00:04</x:v>
+      </x:c>
+      <x:c r="D29" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E29" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F29" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G29" s="11" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H29" s="11" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="I29" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="J29" s="11" t="str"/>
+      <x:c r="K29" s="11" t="str"/>
+      <x:c r="L29" s="10" t="str">
+        <x:v>夜珠AI剧场</x:v>
+      </x:c>
+      <x:c r="M29" s="10" t="str">
+        <x:v>现代青年刘大壮意外穿越到60年代，成了同名同姓的16岁穷小子。原主因相亲被拒、家徒四壁，下河摸鱼时溺亡。大壮醒来后发现脑中多了一座九层宝塔空间——内有灵药田与灵泉潭水，作物两小时成熟、产量翻五倍。饥荒年代，别人啃树皮喝稀粥，他靠空间种出满仓土豆粮食，黑市换粮票钞票，让饿肚子的父母姐姐们吃上饱饭。从人人嘲笑的穷小子，到带着全家逆袭翻盘，且看他手握宝塔空间，在艰苦年代闯出一条吃喝不愁的逆袭</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="11" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B30" s="10" t="str">
+        <x:v>重生一世，我不再痴恋竹马</x:v>
+      </x:c>
+      <x:c r="C30" s="11" t="str">
+        <x:v>09-10 10:00</x:v>
+      </x:c>
+      <x:c r="D30" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E30" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F30" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G30" s="11" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H30" s="11" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="I30" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="J30" s="11" t="str"/>
+      <x:c r="K30" s="11" t="str"/>
+      <x:c r="L30" s="10" t="str">
+        <x:v>锦书映年华</x:v>
+      </x:c>
+      <x:c r="M30" s="10" t="str">
+        <x:v>承平公主前世错恋齐远安，受尽磋磨含恨落幕。一朝重生，恰逢圣旨赐婚，齐远安却当众恳请解除婚约，求取太后义孙女傅明珠。她坦然放手，主动成全二人，看着他们得偿所愿。宁国侯夫人动用旧物强求赐婚，她巧妙改换婚事，选择边关归来、品性刚正的齐远舟。婚后她聪慧通透，看清傅明珠与齐远安的本性，冷眼旁观二人矛盾丛生。历经风波，她与齐远舟彼此扶持，挣脱过往伤痛，收获属于自己安稳坦荡的人生。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="11" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B31" s="10" t="str">
+        <x:v>回到零四年进军彩铃界</x:v>
+      </x:c>
+      <x:c r="C31" s="11" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="D31" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E31" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F31" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G31" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="H31" s="11" t="str"/>
+      <x:c r="I31" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="J31" s="11" t="str"/>
+      <x:c r="K31" s="11" t="str"/>
+      <x:c r="L31" s="10" t="str"/>
+      <x:c r="M31" s="10" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3385,16 +3644,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
-        <x:v>1.5</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F2" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-15 05-08</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3417,7 +3676,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-15 05-08</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -3425,22 +3684,22 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>七套房产，换来一纸调令</x:v>
+        <x:v>重生三天前，我用水泥封死地下室</x:v>
       </x:c>
       <x:c r="C4" s="11" t="n">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>10.6</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F4" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-15 05-08</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3448,22 +3707,22 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>重生三天前，我用水泥封死地下室</x:v>
+        <x:v>七套房产，换来一纸调令</x:v>
       </x:c>
       <x:c r="C5" s="11" t="n">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>10.7</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F5" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-15 05-08</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -3477,16 +3736,16 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>6.6</x:v>
+        <x:v>6.4</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F6" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-15 05-08</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3500,16 +3759,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>7.8</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F7" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-15 05-08</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -3523,16 +3782,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>7.4</x:v>
+        <x:v>7.1</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-15 05-08</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3543,10 +3802,10 @@
         <x:v>破库房的秘密</x:v>
       </x:c>
       <x:c r="C9" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>12.1</x:v>
+        <x:v>12.4</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
         <x:v>4</x:v>
@@ -3563,22 +3822,22 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>退婚后我在七零赚钱养家致富</x:v>
+        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
       </x:c>
       <x:c r="C10" s="11" t="n">
         <x:v>23</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>10.2</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F10" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>2026-09-14 22-12</x:v>
+        <x:v>2026-09-15 05-08</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -3586,22 +3845,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
+        <x:v>退婚后我在七零赚钱养家致富</x:v>
       </x:c>
       <x:c r="C11" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>11.6</x:v>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-14 22-12</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -3612,7 +3871,7 @@
         <x:v>锦书迟</x:v>
       </x:c>
       <x:c r="C12" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
         <x:v>13.4</x:v>
@@ -3632,22 +3891,22 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>今天开始做裴总</x:v>
+        <x:v>泰城错嫁</x:v>
       </x:c>
       <x:c r="C13" s="11" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>11.1</x:v>
+        <x:v>12.5</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G13" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-15 05-08</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -3655,22 +3914,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>泰城错嫁</x:v>
+        <x:v>一墙之隔，皆是人心</x:v>
       </x:c>
       <x:c r="C14" s="11" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>12.6</x:v>
+        <x:v>13.2</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G14" s="11" t="str">
-        <x:v>2026-09-14 22-12</x:v>
+        <x:v>2026-09-15 05-08</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -3678,22 +3937,22 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>一墙之隔，皆是人心</x:v>
+        <x:v>今天开始做裴总</x:v>
       </x:c>
       <x:c r="C15" s="11" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>13.3</x:v>
+        <x:v>11.2</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F15" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G15" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -3707,16 +3966,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>11.9</x:v>
+        <x:v>12.5</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G16" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-15 05-08</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -3753,16 +4012,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>10.1</x:v>
+        <x:v>9.6</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G18" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-15 05-08</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -3793,22 +4052,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
+        <x:v>三分钱的取舍</x:v>
       </x:c>
       <x:c r="C20" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>15.7</x:v>
+        <x:v>12.1</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="G20" s="11" t="str">
-        <x:v>2026-09-14 06-11</x:v>
+        <x:v>2026-09-15 05-08</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -3816,22 +4075,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>退婚从抢我车位开始</x:v>
+        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
       </x:c>
       <x:c r="C21" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>14.3</x:v>
+        <x:v>15.7</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G21" s="11" t="str">
-        <x:v>2026-09-14 20-18</x:v>
+        <x:v>2026-09-14 06-11</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -3839,22 +4098,22 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>三分钱的取舍</x:v>
+        <x:v>退婚从抢我车位开始</x:v>
       </x:c>
       <x:c r="C22" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>11.3</x:v>
+        <x:v>14.3</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G22" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-14 20-18</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -3862,22 +4121,22 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>回到零四年进军彩铃界</x:v>
+        <x:v>婚礼当天我不嫁了</x:v>
       </x:c>
       <x:c r="C23" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>16.4</x:v>
+        <x:v>14.8</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G23" s="11" t="str">
-        <x:v>2026-09-14 12-34</x:v>
+        <x:v>2026-09-14 22-12</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -3885,22 +4144,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>婚礼当天我不嫁了</x:v>
+        <x:v>回到零四年进军彩铃界</x:v>
       </x:c>
       <x:c r="C24" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>14.8</x:v>
+        <x:v>16.6</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G24" s="11" t="str">
-        <x:v>2026-09-14 22-12</x:v>
+        <x:v>2026-09-14 12-34</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -3911,10 +4170,10 @@
         <x:v>河箱送福来</x:v>
       </x:c>
       <x:c r="C25" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>14.9</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
         <x:v>8</x:v>
@@ -4000,22 +4259,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>离婚那天我多了个痞帅老爹</x:v>
+        <x:v>青牛引泉来</x:v>
       </x:c>
       <x:c r="C29" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>11.2</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-15 05-08</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -4023,22 +4282,22 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>一张废票毁了她</x:v>
+        <x:v>离婚那天我多了个痞帅老爹</x:v>
       </x:c>
       <x:c r="C30" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>14.5</x:v>
+        <x:v>11.2</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G30" s="11" t="str">
-        <x:v>2026-09-14 10-32</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -4046,22 +4305,22 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>这桌团圆饭，我不做了</x:v>
+        <x:v>一张废票毁了她</x:v>
       </x:c>
       <x:c r="C31" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
-        <x:v>16.5</x:v>
+        <x:v>14.5</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G31" s="11" t="str">
-        <x:v>2026-09-14 03-11</x:v>
+        <x:v>2026-09-14 10-32</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -4069,22 +4328,22 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="10" t="str">
-        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
+        <x:v>不靠谱爸妈很靠谱</x:v>
       </x:c>
       <x:c r="C32" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D32" s="11" t="n">
-        <x:v>8.7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G32" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-15 05-08</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -4092,22 +4351,22 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="10" t="str">
-        <x:v>人人都说她娇气，出事她护我到底</x:v>
+        <x:v>穿书后我带萌宝上门认爹</x:v>
       </x:c>
       <x:c r="C33" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D33" s="11" t="n">
-        <x:v>5.3</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F33" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G33" s="11" t="str">
-        <x:v>2026-09-14 12-34</x:v>
+        <x:v>2026-09-15 05-08</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -4115,22 +4374,22 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="10" t="str">
-        <x:v>我家后山藏真龙</x:v>
+        <x:v>这桌团圆饭，我不做了</x:v>
       </x:c>
       <x:c r="C34" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D34" s="11" t="n">
-        <x:v>5.7</x:v>
+        <x:v>16.5</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F34" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G34" s="11" t="str">
-        <x:v>2026-09-14 09-24</x:v>
+        <x:v>2026-09-14 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -4138,22 +4397,22 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="10" t="str">
-        <x:v>不负恩情不负卿</x:v>
+        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
       </x:c>
       <x:c r="C35" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D35" s="11" t="n">
-        <x:v>9.7</x:v>
+        <x:v>8.7</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F35" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G35" s="11" t="str">
-        <x:v>2026-09-14 10-32</x:v>
+        <x:v>2026-09-15 01-59</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -4161,22 +4420,22 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="10" t="str">
-        <x:v>一针绣出自己的路</x:v>
+        <x:v>人人都说她娇气，出事她护我到底</x:v>
       </x:c>
       <x:c r="C36" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>5.3</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G36" s="11" t="str">
-        <x:v>2026-09-13 21-11</x:v>
+        <x:v>2026-09-14 12-34</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -4184,22 +4443,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="10" t="str">
-        <x:v>谢谢爸妈的穷养现在我富了</x:v>
+        <x:v>我家后山藏真龙</x:v>
       </x:c>
       <x:c r="C37" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D37" s="11" t="n">
-        <x:v>10.7</x:v>
+        <x:v>5.7</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G37" s="11" t="str">
-        <x:v>2026-09-14 02-11</x:v>
+        <x:v>2026-09-14 09-24</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -4207,22 +4466,22 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="10" t="str">
-        <x:v>那块玉，带我们回家</x:v>
+        <x:v>不负恩情不负卿</x:v>
       </x:c>
       <x:c r="C38" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D38" s="11" t="n">
-        <x:v>11.3</x:v>
+        <x:v>9.7</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F38" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G38" s="11" t="str">
-        <x:v>2026-09-14 09-24</x:v>
+        <x:v>2026-09-14 10-32</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -4230,22 +4489,22 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="10" t="str">
-        <x:v>拂衣震九州</x:v>
+        <x:v>一针绣出自己的路</x:v>
       </x:c>
       <x:c r="C39" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D39" s="11" t="n">
-        <x:v>10.3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G39" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-13 21-11</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -4253,22 +4512,22 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="10" t="str">
-        <x:v>闪婚老公有点野</x:v>
+        <x:v>谢谢爸妈的穷养现在我富了</x:v>
       </x:c>
       <x:c r="C40" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D40" s="11" t="n">
-        <x:v>11.3</x:v>
+        <x:v>10.7</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G40" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-14 02-11</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -4276,22 +4535,22 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="10" t="str">
-        <x:v>青牛引泉来</x:v>
+        <x:v>那块玉，带我们回家</x:v>
       </x:c>
       <x:c r="C41" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D41" s="11" t="n">
-        <x:v>15.3</x:v>
+        <x:v>11.3</x:v>
       </x:c>
       <x:c r="E41" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F41" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G41" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-14 09-24</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -4299,19 +4558,19 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B42" s="10" t="str">
-        <x:v>大坝边寻回的真千金</x:v>
+        <x:v>拂衣震九州</x:v>
       </x:c>
       <x:c r="C42" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D42" s="11" t="n">
-        <x:v>12.7</x:v>
+        <x:v>10.3</x:v>
       </x:c>
       <x:c r="E42" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F42" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G42" s="11" t="str">
         <x:v>2026-09-15 03-38</x:v>
@@ -4322,22 +4581,22 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" s="10" t="str">
-        <x:v>山下是绝路，山上是生门</x:v>
+        <x:v>闪婚老公有点野</x:v>
       </x:c>
       <x:c r="C43" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D43" s="11" t="n">
-        <x:v>14.3</x:v>
+        <x:v>11.3</x:v>
       </x:c>
       <x:c r="E43" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F43" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G43" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-15 01-59</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -4345,22 +4604,22 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="10" t="str">
-        <x:v>不靠谱爸妈很靠谱</x:v>
+        <x:v>大坝边寻回的真千金</x:v>
       </x:c>
       <x:c r="C44" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D44" s="11" t="n">
+        <x:v>12.7</x:v>
+      </x:c>
+      <x:c r="E44" s="11" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F44" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E44" s="11" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F44" s="11" t="n">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="G44" s="11" t="str">
-        <x:v>2026-09-14 21-12</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -4368,22 +4627,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="10" t="str">
-        <x:v>427元扳倒老油条</x:v>
+        <x:v>山下是绝路，山上是生门</x:v>
       </x:c>
       <x:c r="C45" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D45" s="11" t="n">
-        <x:v>15.7</x:v>
+        <x:v>14.3</x:v>
       </x:c>
       <x:c r="E45" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F45" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G45" s="11" t="str">
-        <x:v>2026-09-14 20-18</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -4391,22 +4650,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B46" s="10" t="str">
-        <x:v>穿书后我带萌宝上门认爹</x:v>
+        <x:v>427元扳倒老油条</x:v>
       </x:c>
       <x:c r="C46" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D46" s="11" t="n">
-        <x:v>16.3</x:v>
+        <x:v>15.7</x:v>
       </x:c>
       <x:c r="E46" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="F46" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G46" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-14 20-18</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -4437,22 +4696,22 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B48" s="10" t="str">
-        <x:v>全家施压：我反手签了过户合同</x:v>
+        <x:v>零元年终奖</x:v>
       </x:c>
       <x:c r="C48" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D48" s="11" t="n">
-        <x:v>19.3</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="E48" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F48" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G48" s="11" t="str">
-        <x:v>2026-09-14 12-34</x:v>
+        <x:v>2026-09-13 22-11</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -4460,22 +4719,22 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B49" s="10" t="str">
-        <x:v>零元年终奖</x:v>
+        <x:v>我SSS级狂龙，出世即无敌</x:v>
       </x:c>
       <x:c r="C49" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D49" s="11" t="n">
-        <x:v>4.5</x:v>
+        <x:v>5.5</x:v>
       </x:c>
       <x:c r="E49" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F49" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G49" s="11" t="str">
-        <x:v>2026-09-13 22-11</x:v>
+        <x:v>2026-09-15 01-59</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -4483,13 +4742,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B50" s="10" t="str">
-        <x:v>我SSS级狂龙，出世即无敌</x:v>
+        <x:v>一碗人间赴景深</x:v>
       </x:c>
       <x:c r="C50" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D50" s="11" t="n">
-        <x:v>5.5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E50" s="11" t="n">
         <x:v>5</x:v>
@@ -4498,7 +4757,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G50" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-14 09-24</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -4506,19 +4765,19 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B51" s="10" t="str">
-        <x:v>一碗人间赴景深</x:v>
+        <x:v>白鹿照归途</x:v>
       </x:c>
       <x:c r="C51" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D51" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>12.5</x:v>
       </x:c>
       <x:c r="E51" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F51" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G51" s="11" t="str">
         <x:v>2026-09-14 09-24</x:v>
@@ -29541,10 +29800,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>902</x:v>
+        <x:v>904</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>52.2%</x:v>
+        <x:v>52.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -29555,7 +29814,7 @@
         <x:v>476</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>27.6%</x:v>
+        <x:v>27.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -29590,10 +29849,10 @@
         <x:v>30-49集</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>11.1%</x:v>
+        <x:v>11.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -29650,10 +29909,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>759</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>43.9%</x:v>
+        <x:v>44.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -29661,7 +29920,7 @@
         <x:v>婚姻/情感</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>310</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
         <x:v>18.0%</x:v>
@@ -29716,7 +29975,7 @@
         <x:v>现实反转/人性</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
         <x:v>6.3%</x:v>
@@ -29727,7 +29986,7 @@
         <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
         <x:v>5.7%</x:v>
@@ -29908,7 +30167,7 @@
         <x:v>上榜17次</x:v>
       </x:c>
       <x:c r="B41" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C41" s="11" t="str">
         <x:v>0.1%</x:v>
@@ -29919,7 +30178,7 @@
         <x:v>上榜16次</x:v>
       </x:c>
       <x:c r="B42" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C42" s="11" t="str">
         <x:v>0.3%</x:v>
@@ -29963,10 +30222,10 @@
         <x:v>上榜12次</x:v>
       </x:c>
       <x:c r="B46" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C46" s="11" t="str">
-        <x:v>0.9%</x:v>
+        <x:v>1.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -29974,7 +30233,7 @@
         <x:v>上榜11次</x:v>
       </x:c>
       <x:c r="B47" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C47" s="11" t="str">
         <x:v>0.6%</x:v>
@@ -29985,7 +30244,7 @@
         <x:v>上榜10次</x:v>
       </x:c>
       <x:c r="B48" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C48" s="11" t="str">
         <x:v>1.2%</x:v>
@@ -29996,7 +30255,7 @@
         <x:v>上榜9次</x:v>
       </x:c>
       <x:c r="B49" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C49" s="11" t="str">
         <x:v>1.9%</x:v>
@@ -30007,7 +30266,7 @@
         <x:v>上榜8次</x:v>
       </x:c>
       <x:c r="B50" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C50" s="11" t="str">
         <x:v>2.8%</x:v>
@@ -30018,10 +30277,10 @@
         <x:v>上榜7次</x:v>
       </x:c>
       <x:c r="B51" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C51" s="11" t="str">
-        <x:v>2.2%</x:v>
+        <x:v>2.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -30040,10 +30299,10 @@
         <x:v>上榜5次</x:v>
       </x:c>
       <x:c r="B53" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C53" s="11" t="str">
-        <x:v>4.1%</x:v>
+        <x:v>4.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -30054,7 +30313,7 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="C54" s="11" t="str">
-        <x:v>6.3%</x:v>
+        <x:v>6.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -30062,10 +30321,10 @@
         <x:v>上榜3次</x:v>
       </x:c>
       <x:c r="B55" s="11" t="n">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C55" s="11" t="str">
-        <x:v>11.4%</x:v>
+        <x:v>11.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -30087,7 +30346,7 @@
         <x:v>751</x:v>
       </x:c>
       <x:c r="C57" s="11" t="str">
-        <x:v>43.5%</x:v>
+        <x:v>43.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="22" customHeight="1">
@@ -30114,7 +30373,7 @@
         <x:v>1150</x:v>
       </x:c>
       <x:c r="C61" s="11" t="str">
-        <x:v>66.6%</x:v>
+        <x:v>66.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -30122,10 +30381,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B62" s="11" t="n">
-        <x:v>566</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="C62" s="11" t="str">
-        <x:v>32.8%</x:v>
+        <x:v>32.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -30248,7 +30507,7 @@
         <x:v>左手良画</x:v>
       </x:c>
       <x:c r="B75" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C75" s="11" t="str">
         <x:v>0.6%</x:v>
@@ -30267,10 +30526,10 @@
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="10" t="str">
-        <x:v>茉冉漫影</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="B77" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C77" s="11" t="str">
         <x:v>0.5%</x:v>
@@ -30278,7 +30537,7 @@
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="10" t="str">
-        <x:v>在下轻北</x:v>
+        <x:v>茉冉漫影</x:v>
       </x:c>
       <x:c r="B78" s="11" t="n">
         <x:v>28</x:v>
@@ -30289,7 +30548,7 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>在下轻北</x:v>
       </x:c>
       <x:c r="B79" s="11" t="n">
         <x:v>28</x:v>
@@ -30371,10 +30630,10 @@
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="10" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="B88" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C88" s="11" t="str">
         <x:v>0.5%</x:v>
@@ -30382,7 +30641,7 @@
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="B89" s="11" t="n">
         <x:v>8</x:v>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R31a7881fd822407e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="R1b954d774af74684"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="R9682989e572c4c4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="R474e2d5aff104f49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP20剧重点跟踪" sheetId="5" r:id="R5dce38b07a1c4538"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="6" r:id="Re3ca73120d334fc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="7" r:id="R02839863c12c46b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="8" r:id="R3a5074f3c097446d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="9" r:id="R9af3adb7e9904d71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R4bddc8602fc442df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="Re60a828efa544e15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="R4627770ba2624e26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="Raff4803ec86e4d59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP20剧重点跟踪" sheetId="5" r:id="R178e4f7395424abd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="6" r:id="R920ed71b4f94449a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="7" r:id="R4f42b613390e4086"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="8" r:id="R7b69fd7308fb41da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="9" r:id="Rcf663e34986c4187"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -366,7 +366,7 @@
         <x:v>08-11 16:40</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E2" s="10" t="n">
         <x:v>82</x:v>
@@ -384,7 +384,7 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="J2" s="10" t="str">
-        <x:v>2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14</x:v>
+        <x:v>2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -494,7 +494,7 @@
         <x:v>08-10 16:30</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E6" s="10" t="n">
         <x:v>151</x:v>
@@ -512,7 +512,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="J6" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -558,7 +558,7 @@
         <x:v>08-08 17:00</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E8" s="10" t="n">
         <x:v>66</x:v>
@@ -576,7 +576,7 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="J8" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-30、2026-08-31、2026-09-02、2026-09-03、2026-09-09、2026-09-12、2026-09-13、2026-09-14</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-30、2026-08-31、2026-09-02、2026-09-03、2026-09-09、2026-09-12、2026-09-13、2026-09-14、2026-09-15</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1016,27 +1016,27 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>铺子空了，房东慌了</x:v>
+        <x:v>精通婴语满朝权贵求我带娃</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>08-29 16:49</x:v>
+        <x:v>08-03 11:51</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E24" s="10" t="n">
-        <x:v>55</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F24" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="G24" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>萌宝治愈</x:v>
       </x:c>
       <x:c r="H24" s="11" t="str"/>
       <x:c r="I24" s="11" t="str"/>
       <x:c r="J24" s="10" t="str">
-        <x:v>2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15</x:v>
+        <x:v>2026-08-20、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1044,27 +1044,27 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>一瓶水，让我看清亲生女儿</x:v>
+        <x:v>铺子空了，房东慌了</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>08-23 10:00</x:v>
+        <x:v>08-29 16:49</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E25" s="10" t="n">
-        <x:v>69</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F25" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G25" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="H25" s="11" t="str"/>
       <x:c r="I25" s="11" t="str"/>
       <x:c r="J25" s="10" t="str">
-        <x:v>2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-15</x:v>
+        <x:v>2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1072,27 +1072,27 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>乱世我家顿顿吃肉</x:v>
+        <x:v>一瓶水，让我看清亲生女儿</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
-        <x:v>08-15 04:30</x:v>
+        <x:v>08-23 10:00</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E26" s="10" t="n">
-        <x:v>54</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F26" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="G26" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="H26" s="11" t="str"/>
       <x:c r="I26" s="11" t="str"/>
       <x:c r="J26" s="10" t="str">
-        <x:v>2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
+        <x:v>2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-15</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1165,13 +1165,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B2" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
-        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
+        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>09-13 09:58</x:v>
+        <x:v>09-15 08:00</x:v>
       </x:c>
       <x:c r="E2" s="11" t="str"/>
       <x:c r="F2" s="11" t="str"/>
@@ -1182,19 +1182,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I2" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J2" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K2" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="L2" s="11" t="str">
-        <x:v>创想剧场</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="M2" s="10" t="str">
-        <x:v>游戏公会会长林小勇筹备婚礼，却在婚宴上遭遇未婚妻临时加价逼婚。危急时刻，几位相交多年的游戏老友现身力挺他，林小勇果断取消婚礼。之后他搬进好友赠送的别墅，与陈董的两个女儿渐渐熟识。同学聚会上，众人见识到林小勇不一般的际遇。平静日子没过多久，当年游戏里的宿敌将出席游戏八周年嘉年华，一众老友决定赴约，一场新旧对决即将开启。</x:v>
+        <x:v>沈清韵嫁入靖王府三年，王爷冷落，侧妃得宠。王爷当众许诺，谁先诞下儿子，便请封世子。苏氏先怀孕，沈清韵却发现自己怀的是龙凤胎，她隐瞒消息，买通太医推迟产期，忍痛让苏氏先产子。王爷果然请封庶长子为世子，折子递入宗人府。受理之后，沈清韵才发动，生下龙凤胎。太后与皇上视为祥瑞，下旨赐嫡子承恩为靖王世子、嫡女承华为安乐郡主。王爷措手不及，苏氏地位一落千丈。而沈清韵知道，这只是第一步。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1202,13 +1202,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
+        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>09-15 00:08</x:v>
+        <x:v>09-13 08:00</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str"/>
       <x:c r="F3" s="11" t="str"/>
@@ -1219,19 +1219,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I3" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K3" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="L3" s="11" t="str">
-        <x:v>桃子动漫剧场</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="M3" s="10" t="str">
-        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
+        <x:v>大晋七公主沈令仪，自幼被冷落于听竹宫，沉默藏锋，苟全性命。宫宴之上，太子带回的秦照雪笑盈盈提议将她送去北狄和亲。满殿以为皇帝会点头，他却掷出“废太子”三字。一夜之间，沈令仪被推到台前。北狄求和的急报恰在此时入京——与她方才所言分毫不差。可当她回望母亲遗下的那半卷秘策时，才发现这局棋，早在二十年前就已落子。</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1239,13 +1239,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>24</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
-        <x:v>小妹初长成</x:v>
+        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>2026-09-13</x:v>
+        <x:v>09-13 09:58</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str"/>
       <x:c r="F4" s="11" t="str"/>
@@ -1255,22 +1255,28 @@
       <x:c r="H4" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I4" s="11" t="str"/>
+      <x:c r="I4" s="11" t="n">
+        <x:v>66</x:v>
+      </x:c>
       <x:c r="J4" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K4" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L4" s="11" t="str"/>
-      <x:c r="M4" s="10" t="str"/>
+      <x:c r="L4" s="11" t="str">
+        <x:v>创想剧场</x:v>
+      </x:c>
+      <x:c r="M4" s="10" t="str">
+        <x:v>游戏公会会长林小勇筹备婚礼，却在婚宴上遭遇未婚妻临时加价逼婚。危急时刻，几位相交多年的游戏老友现身力挺他，林小勇果断取消婚礼。之后他搬进好友赠送的别墅，与陈董的两个女儿渐渐熟识。同学聚会上，众人见识到林小勇不一般的际遇。平静日子没过多久，当年游戏里的宿敌将出席游戏八周年嘉年华，一众老友决定赴约，一场新旧对决即将开启。</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
         <x:v>重生80，救下神雕后我带村民走出大山</x:v>
@@ -1307,13 +1313,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>离婚那天我多了个痞帅老爹</x:v>
+        <x:v>四个崽崽瞒不住了</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>2026-09-13</x:v>
+        <x:v>09-15 00:08</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str"/>
       <x:c r="F6" s="11" t="str"/>
@@ -1323,28 +1329,34 @@
       <x:c r="H6" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I6" s="11" t="str"/>
+      <x:c r="I6" s="11" t="n">
+        <x:v>124</x:v>
+      </x:c>
       <x:c r="J6" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K6" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="L6" s="11" t="str"/>
-      <x:c r="M6" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L6" s="11" t="str">
+        <x:v>桃子动漫剧场</x:v>
+      </x:c>
+      <x:c r="M6" s="10" t="str">
+        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
-        <x:v>乡宴见人心</x:v>
+        <x:v>小妹初长成</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>09-13 17:12</x:v>
+        <x:v>2026-09-13</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str"/>
       <x:c r="F7" s="11" t="str"/>
@@ -1354,34 +1366,28 @@
       <x:c r="H7" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="n">
-        <x:v>72</x:v>
-      </x:c>
+      <x:c r="I7" s="11" t="str"/>
       <x:c r="J7" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K7" s="10" t="str">
-        <x:v>现实反转</x:v>
-      </x:c>
-      <x:c r="L7" s="11" t="str">
-        <x:v>黑白动漫</x:v>
-      </x:c>
-      <x:c r="M7" s="10" t="str">
-        <x:v>高满仓在赵家大院办了八年流水席，十里八村都认他的手艺。眼看生意越来越旺，院主赵金贵突然把租金翻倍，还要按桌抽钱。高满仓干脆带着人和家伙搬进镇外的废米厂，从头再来。赵金贵以为守着大院就守住了客人，靠低价抢生意，却越省越狠。一边是稳稳当当把席办好，一边是亲手砸掉自己的口碑，这场较量最后看的是院子，还是人心。</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L7" s="11" t="str"/>
+      <x:c r="M7" s="10" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
-        <x:v>河箱送福来</x:v>
+        <x:v>乡宴见人心</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>09-13 11:00</x:v>
+        <x:v>09-13 17:12</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str"/>
       <x:c r="F8" s="11" t="str"/>
@@ -1392,19 +1398,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J8" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K8" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="L8" s="11" t="str">
-        <x:v>灵心讲故事</x:v>
+        <x:v>黑白动漫</x:v>
       </x:c>
       <x:c r="M8" s="10" t="str">
-        <x:v>张家老两口从河中救回一只木箱，收养了箱中受伤的福生。福生长大后修桥开田，引水惠及乡亲，成家立业。二老相继离世后，山洪威胁村庄，福生为救乡亲舍命撑住巨石，最终重伤落水，下落不明。秀娥守着小院苦等多年，直到熟悉的声音再次响起。</x:v>
+        <x:v>高满仓在赵家大院办了八年流水席，十里八村都认他的手艺。眼看生意越来越旺，院主赵金贵突然把租金翻倍，还要按桌抽钱。高满仓干脆带着人和家伙搬进镇外的废米厂，从头再来。赵金贵以为守着大院就守住了客人，靠低价抢生意，却越省越狠。一边是稳稳当当把席办好，一边是亲手砸掉自己的口碑，这场较量最后看的是院子，还是人心。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1412,13 +1418,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
-        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
+        <x:v>反派拿捏！</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>09-13 08:00</x:v>
+        <x:v>2026-09-13</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str"/>
       <x:c r="F9" s="11" t="str"/>
@@ -1428,34 +1434,28 @@
       <x:c r="H9" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I9" s="11" t="n">
-        <x:v>64</x:v>
-      </x:c>
+      <x:c r="I9" s="11" t="str"/>
       <x:c r="J9" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K9" s="10" t="str">
-        <x:v>古装宫廷</x:v>
-      </x:c>
-      <x:c r="L9" s="11" t="str">
-        <x:v>心动漫剧场</x:v>
-      </x:c>
-      <x:c r="M9" s="10" t="str">
-        <x:v>大晋七公主沈令仪，自幼被冷落于听竹宫，沉默藏锋，苟全性命。宫宴之上，太子带回的秦照雪笑盈盈提议将她送去北狄和亲。满殿以为皇帝会点头，他却掷出“废太子”三字。一夜之间，沈令仪被推到台前。北狄求和的急报恰在此时入京——与她方才所言分毫不差。可当她回望母亲遗下的那半卷秘策时，才发现这局棋，早在二十年前就已落子。</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L9" s="11" t="str"/>
+      <x:c r="M9" s="10" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
-        <x:v>员工跑路我扩店</x:v>
+        <x:v>离婚那天我多了个痞帅老爹</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>09-13 08:58</x:v>
+        <x:v>2026-09-13</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str"/>
       <x:c r="F10" s="11" t="str"/>
@@ -1465,34 +1465,28 @@
       <x:c r="H10" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I10" s="11" t="n">
-        <x:v>70</x:v>
-      </x:c>
+      <x:c r="I10" s="11" t="str"/>
       <x:c r="J10" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K10" s="10" t="str">
-        <x:v>都市职场</x:v>
-      </x:c>
-      <x:c r="L10" s="11" t="str">
-        <x:v>大梨看剧</x:v>
-      </x:c>
-      <x:c r="M10" s="10" t="str">
-        <x:v>林辰经营天力健身馆，年终为员工每人发放五万元奖金。几位教练希望获得更多发展空间，与林辰理念产生分歧，决定在隔壁开设新馆，一场实力较量就此展开。林辰选择升级场地、引进专业团队，并提拔刘阿姨担任店长。正月初七，千名会员到场，用选择见证真诚服务的价值。</x:v>
-      </x:c>
+        <x:v>家庭伦理 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="L10" s="11" t="str"/>
+      <x:c r="M10" s="10" t="str"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C11" s="10" t="str">
-        <x:v>风雪边界</x:v>
+        <x:v>河箱送福来</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>09-14 03:01</x:v>
+        <x:v>09-13 11:00</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str"/>
       <x:c r="F11" s="11" t="str"/>
@@ -1503,7 +1497,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I11" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J11" s="10" t="str">
         <x:v>其他</x:v>
@@ -1512,10 +1506,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L11" s="11" t="str">
-        <x:v>腿毛漫漫</x:v>
+        <x:v>灵心讲故事</x:v>
       </x:c>
       <x:c r="M11" s="10" t="str">
-        <x:v>高原补给站老板岑夏坚持完整安全套餐，却遭企业负责人质疑价格，团队转投低价营地。暴雪突至，危机逼近，岑夏仍坚守原则，以专业判断协助应急处置，也让众人重新理解安全的价值。真正昂贵的不是房费，而是忽视风险的代价。敬畏自然、尊重专业，安全永远值得认真对待。</x:v>
+        <x:v>张家老两口从河中救回一只木箱，收养了箱中受伤的福生。福生长大后修桥开田，引水惠及乡亲，成家立业。二老相继离世后，山洪威胁村庄，福生为救乡亲舍命撑住巨石，最终重伤落水，下落不明。秀娥守着小院苦等多年，直到熟悉的声音再次响起。</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1523,13 +1517,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
-        <x:v>427元扳倒老油条</x:v>
+        <x:v>重生极品婆婆，带全家发家致富！</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>09-13 16:00</x:v>
+        <x:v>09-14 20:29</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str"/>
       <x:c r="F12" s="11" t="str"/>
@@ -1540,19 +1534,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I12" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="J12" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K12" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="L12" s="11" t="str">
-        <x:v>安然然</x:v>
+        <x:v>懒少爱我</x:v>
       </x:c>
       <x:c r="M12" s="10" t="str">
-        <x:v>职场新人许宁向老员工马丽芬讨要427元代垫外卖款，反遭易绑架马丽芬交出饭钱后怀恨在心，利用行政特权私吞福利，并在组织团餐时疏同事差价许宁按兵不动收集证据，最终将马丽芬长期贪占两万余元的行径在老板曝光的照片中马丽芬被直接开除，许宁成功维护了职场底线。</x:v>
+        <x:v>寡妇傅兰秀前世一生吝啬守财，刻薄对待儿女儿媳，到头来钱财被贼人掠夺，落得个凄惨离世的下场。一朝重生，她回到悲剧尚未发生之时。痛定思痛，她彻底改掉抠门的性子，学着善待家里的晚辈。可日子并不太平，爱占便宜的亲戚总上门搅扰，家中两个儿媳也矛盾不断，家务是非接连找上门。傅兰秀靠着清醒的头脑，一边化解各类家庭纷争，一边寻找营生门路，努力扭转命运，拼尽全力守护一家人的安稳生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1560,36 +1554,36 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B13" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
-        <x:v>重生极品婆婆，带全家发家致富！</x:v>
+        <x:v>那朵胸花，被丢进垃圾桶</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
-        <x:v>09-14 20:29</x:v>
+        <x:v>09-14 21:00</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str"/>
       <x:c r="F13" s="11" t="str"/>
       <x:c r="G13" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H13" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I13" s="11" t="n">
-        <x:v>126</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J13" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K13" s="10" t="str">
-        <x:v>家庭伦理 / 逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L13" s="11" t="str">
-        <x:v>懒少爱我</x:v>
+        <x:v>临渊剧场</x:v>
       </x:c>
       <x:c r="M13" s="10" t="str">
-        <x:v>寡妇傅兰秀前世一生吝啬守财，刻薄对待儿女儿媳，到头来钱财被贼人掠夺，落得个凄惨离世的下场。一朝重生，她回到悲剧尚未发生之时。痛定思痛，她彻底改掉抠门的性子，学着善待家里的晚辈。可日子并不太平，爱占便宜的亲戚总上门搅扰，家中两个儿媳也矛盾不断，家务是非接连找上门。傅兰秀靠着清醒的头脑，一边化解各类家庭纷争，一边寻找营生门路，努力扭转命运，拼尽全力守护一家人的安稳生活。</x:v>
+        <x:v>接亲当天，新郎踹开新娘房门。新娘护着前任，前任用胸花挑衅，婚礼当场取消。她求他，他放完整视频反击。前任欠债跑路，债主堵门，新娘崩溃。他换锁卖房，一笔账一笔账清。可账单会说话，旧爱跑不了，这条线，该断了。</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1597,36 +1591,36 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B14" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
-        <x:v>活宝老爹再赴青春，竟与女儿同上大学</x:v>
+        <x:v>427元扳倒老油条</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>09-13 00:08</x:v>
+        <x:v>09-13 16:00</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str"/>
       <x:c r="F14" s="11" t="str"/>
       <x:c r="G14" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H14" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I14" s="11" t="n">
-        <x:v>140</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J14" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K14" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L14" s="11" t="str">
-        <x:v>长风剧场</x:v>
+        <x:v>安然然</x:v>
       </x:c>
       <x:c r="M14" s="10" t="str">
-        <x:v>45岁的白烨意外激活成长系统。只要亲身体验年轻人的日常，就能重拾青春活力，还能收获丰厚奖励。为完成系统任务，他报名成人高考，顺利考入大学，竟和女儿成了同校同学。重返校园的白烨，一边认真完成任务感受青春，一边在校园里开启一段充满趣味的全新人生。</x:v>
+        <x:v>职场新人许宁向老员工马丽芬讨要427元代垫外卖款，反遭易绑架马丽芬交出饭钱后怀恨在心，利用行政特权私吞福利，并在组织团餐时疏同事差价许宁按兵不动收集证据，最终将马丽芬长期贪占两万余元的行径在老板曝光的照片中马丽芬被直接开除，许宁成功维护了职场底线。</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1634,28 +1628,28 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B15" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
-        <x:v>反派拿捏！</x:v>
+        <x:v>结婚八年，我娶的原来是仇人的女儿</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
-        <x:v>2026-09-13</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str"/>
       <x:c r="F15" s="11" t="str"/>
       <x:c r="G15" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H15" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I15" s="11" t="str"/>
       <x:c r="J15" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="K15" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理 / 婚姻情感</x:v>
       </x:c>
       <x:c r="L15" s="11" t="str"/>
       <x:c r="M15" s="10" t="str"/>
@@ -1665,24 +1659,24 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C16" s="10" t="str">
-        <x:v>那朵胸花，被丢进垃圾桶</x:v>
+        <x:v>风雪边界</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
-        <x:v>09-14 21:00</x:v>
+        <x:v>09-14 03:01</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str"/>
       <x:c r="F16" s="11" t="str"/>
       <x:c r="G16" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H16" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I16" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J16" s="10" t="str">
         <x:v>其他</x:v>
@@ -1691,10 +1685,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L16" s="11" t="str">
-        <x:v>临渊剧场</x:v>
+        <x:v>腿毛漫漫</x:v>
       </x:c>
       <x:c r="M16" s="10" t="str">
-        <x:v>接亲当天，新郎踹开新娘房门。新娘护着前任，前任用胸花挑衅，婚礼当场取消。她求他，他放完整视频反击。前任欠债跑路，债主堵门，新娘崩溃。他换锁卖房，一笔账一笔账清。可账单会说话，旧爱跑不了，这条线，该断了。</x:v>
+        <x:v>高原补给站老板岑夏坚持完整安全套餐，却遭企业负责人质疑价格，团队转投低价营地。暴雪突至，危机逼近，岑夏仍坚守原则，以专业判断协助应急处置，也让众人重新理解安全的价值。真正昂贵的不是房费，而是忽视风险的代价。敬畏自然、尊重专业，安全永远值得认真对待。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1702,36 +1696,36 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C17" s="10" t="str">
-        <x:v>重生嫡女：太子妃她手撕孽缘</x:v>
+        <x:v>晚棠知归，七年终见你</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
-        <x:v>09-13 11:00</x:v>
+        <x:v>09-14 11:26</x:v>
       </x:c>
       <x:c r="E17" s="11" t="str"/>
       <x:c r="F17" s="11" t="str"/>
       <x:c r="G17" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H17" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I17" s="11" t="n">
-        <x:v>57</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J17" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K17" s="10" t="str">
-        <x:v>古装宫廷 / 婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L17" s="11" t="str">
-        <x:v>展瓦-小付说剧</x:v>
+        <x:v>喵琪琪追剧</x:v>
       </x:c>
       <x:c r="M17" s="10" t="str">
-        <x:v>嫡女顾明筝前世遭庶妹顾明玉与未婚夫谢哲安联手算计，错嫁后受尽折磨含恨而死。一朝重生回到大婚当日，她将计就计当众揭穿二人私情，顺势改入东宫成为太子妃。她悉心调理病弱太子的身体，夫妻相得，后顺利诞下皇太孙，地位愈发稳固。反观顾明玉嫁入平南侯府后宅斗失算，下毒害人反遭反噬，痛失子嗣被逐出府；谢哲安身中绝嗣之毒，世子之位岌岌可危，侯府彻底败落。最终太子病逝，顾明筝携幼子坚定立身，彻底改写前世悲剧命运。</x:v>
+        <x:v>七年前，夏晚棠为救深爱的陆知珩，付出了一切，却被误会成背叛，独自带着女儿生活。多年后，两人再次相遇，陆知珩才发现当年的真相，也终于明白她承受了怎样的苦难。面对迟来的爱与亏欠，夏晚棠没有停留在过去，而是重新找回自己，用专业和坚强开启新的人生。最终，两人在女儿的陪伴下解开心结，携手迎来属于他们的幸福。</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1739,155 +1733,153 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>86</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C18" s="10" t="str">
-        <x:v>远山架子班</x:v>
+        <x:v>高考刚结束父母就不装了</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>09-13 07:30</x:v>
+        <x:v>09-15 07:00</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str"/>
       <x:c r="F18" s="11" t="str"/>
       <x:c r="G18" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H18" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I18" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="J18" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K18" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="L18" s="11" t="str">
-        <x:v>空空书漫</x:v>
+        <x:v>千慕剧场</x:v>
       </x:c>
       <x:c r="M18" s="10" t="str">
-        <x:v>工地上，彭大勇拿着别家四十一天的招工纸，问贺远山凭什么只给三十。贺远山不争辩，只把账摊开，安全装备饭钱他管，工钱三天一结，从没拖欠。有人奔着高薪离开，可那边层层扣下来，到手反不如从前，还屡屡涉险。工友受伤住院，贺远山二话不说垫钱救人，又帮着把旧账一笔笔算清。他始终守着一条理，钱要挣，命不能换。规矩立得住，人心自然拢得回，班越带越稳，账越算越明。</x:v>
+        <x:v>高考结束那天，林寻在考场外被亲生父母认回原来十八年的普通生活，是父母为磨砺他而设的一场成长课。重回豪门，他没有迷失，反而在桥上遇见了那个让他心动的姑娘，南大冰山学姐苏清诗。从青涩的初次相遇，到演唱会上的合唱，再到大学校园里的朝夕相处，两个真诚的人慢慢靠近。曾经的求而不得终将释怀，双向奔赴的喜欢才最珍贵。褪去普通学生的身份，林寻只想以真心换真心。十八岁的夏天，最好的相遇，最甜的恋爱，才刚刚开始。</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C19" s="10" t="str">
-        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
+        <x:v>星际机修师</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
-        <x:v>09-15 08:00</x:v>
-      </x:c>
-      <x:c r="E19" s="11" t="n">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="F19" s="11" t="str">
-        <x:v>↑90位</x:v>
-      </x:c>
-      <x:c r="G19" s="11" t="str"/>
-      <x:c r="H19" s="11" t="str"/>
+        <x:v>09-14 00:06</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="str"/>
+      <x:c r="F19" s="11" t="str"/>
+      <x:c r="G19" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H19" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="I19" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="J19" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K19" s="10" t="str">
-        <x:v>古装宫廷</x:v>
-      </x:c>
-      <x:c r="L19" s="11" t="str">
-        <x:v>心动漫剧场</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L19" s="11" t="str"/>
       <x:c r="M19" s="10" t="str">
-        <x:v>沈清韵嫁入靖王府三年，王爷冷落，侧妃得宠。王爷当众许诺，谁先诞下儿子，便请封世子。苏氏先怀孕，沈清韵却发现自己怀的是龙凤胎，她隐瞒消息，买通太医推迟产期，忍痛让苏氏先产子。王爷果然请封庶长子为世子，折子递入宗人府。受理之后，沈清韵才发动，生下龙凤胎。太后与皇上视为祥瑞，下旨赐嫡子承恩为靖王世子、嫡女承华为安乐郡主。王爷措手不及，苏氏地位一落千丈。而沈清韵知道，这只是第一步。</x:v>
+        <x:v>3033年星际机甲时代，18岁的苏白没有机甲天赋，却是初级机修师。父母留下百万星币与破旧仓库后远行，他激活星际战甲系统，改造仓库开设星际维修店。修复报废机甲“红月”并解锁天赋技后，苏白获得SSS级天赋万物相融与星鲸吐纳法。各路天才机甲师慕名而来，他打造专属机甲“混沌”，卷入各种阴谋纷争。不断击败对手，并将维修店扩张为星际要塞级基地。</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C20" s="10" t="str">
-        <x:v>重生80，救下神雕后我带村民走出大山</x:v>
+        <x:v>远山架子班</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>09-13 09:00</x:v>
-      </x:c>
-      <x:c r="E20" s="11" t="n">
+        <x:v>09-13 07:30</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="str"/>
+      <x:c r="F20" s="11" t="str"/>
+      <x:c r="G20" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H20" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I20" s="11" t="n">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="F20" s="11" t="str">
-        <x:v>↑36位</x:v>
-      </x:c>
-      <x:c r="G20" s="11" t="str"/>
-      <x:c r="H20" s="11" t="str"/>
-      <x:c r="I20" s="11" t="n">
-        <x:v>187</x:v>
-      </x:c>
       <x:c r="J20" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K20" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L20" s="11" t="str">
-        <x:v>拾光漫漫</x:v>
+        <x:v>空空书漫</x:v>
       </x:c>
       <x:c r="M20" s="10" t="str">
-        <x:v>林大山遭人为意外，意外重生回到1980年。前世他错信爱人落得凄惨下场，重生后果断当众退婚。机缘巧合救下受伤的灵智神雕金羽，还遇见落难善良的白秋月。他携手知恩图报的神雕，依托卧龙山的资源，发掘名贵药材，抓住时代发展机遇。面对同行刁难，林大山坚守本心，凭借智慧与实干，包下荒山兴办药材加工坊。他善待家人，带领乡里百姓勤劳致富，在八十年代的时代浪潮里，靠着双手改写命运，收获美满爱情与事业。</x:v>
+        <x:v>工地上，彭大勇拿着别家四十一天的招工纸，问贺远山凭什么只给三十。贺远山不争辩，只把账摊开，安全装备饭钱他管，工钱三天一结，从没拖欠。有人奔着高薪离开，可那边层层扣下来，到手反不如从前，还屡屡涉险。工友受伤住院，贺远山二话不说垫钱救人，又帮着把旧账一笔笔算清。他始终守着一条理，钱要挣，命不能换。规矩立得住，人心自然拢得回，班越带越稳，账越算越明。</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C21" s="10" t="str">
-        <x:v>乡宴见人心</x:v>
+        <x:v>我赚上千万跟爸妈说50W，隔天就被找上门</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
-        <x:v>09-13 17:12</x:v>
-      </x:c>
-      <x:c r="E21" s="11" t="n">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="F21" s="11" t="str">
-        <x:v>↑27位</x:v>
-      </x:c>
-      <x:c r="G21" s="11" t="str"/>
-      <x:c r="H21" s="11" t="str"/>
+        <x:v>09-13 08:00</x:v>
+      </x:c>
+      <x:c r="E21" s="11" t="str"/>
+      <x:c r="F21" s="11" t="str"/>
+      <x:c r="G21" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H21" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="I21" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J21" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K21" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L21" s="11" t="str">
-        <x:v>黑白动漫</x:v>
+        <x:v>至尊爽剧社</x:v>
       </x:c>
       <x:c r="M21" s="10" t="str">
-        <x:v>高满仓在赵家大院办了八年流水席，十里八村都认他的手艺。眼看生意越来越旺，院主赵金贵突然把租金翻倍，还要按桌抽钱。高满仓干脆带着人和家伙搬进镇外的废米厂，从头再来。赵金贵以为守着大院就守住了客人，靠低价抢生意，却越省越狠。一边是稳稳当当把席办好，一边是亲手砸掉自己的口碑，这场较量最后看的是院子，还是人心。</x:v>
+        <x:v>三十二岁那年，贺川用六年孤注一掷的钻研，换来了七千六百万的回报。可财富还没捂热，先尝到的却是亲人无度的索取。他谎称只赚五十万，叮嘱保密，却挡不住消息走漏。隔天登门的亲戚不止要借钱买房，更联手外人盗用他的身份资料，试图冒名签约、伪造担保债务。贺川报警取证，警方介入追回大部分资金，涉案者包括部分机构人员均承担了法律责任，这笔帐，能否算清？</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C22" s="10" t="str">
         <x:v>辣媳进门，我给公婆撑腰</x:v>
@@ -1895,14 +1887,14 @@
       <x:c r="D22" s="11" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
-      <x:c r="E22" s="11" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F22" s="11" t="str">
-        <x:v>↑26位</x:v>
-      </x:c>
-      <x:c r="G22" s="11" t="str"/>
-      <x:c r="H22" s="11" t="str"/>
+      <x:c r="E22" s="11" t="str"/>
+      <x:c r="F22" s="11" t="str"/>
+      <x:c r="G22" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H22" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="I22" s="11" t="str"/>
       <x:c r="J22" s="10" t="str">
         <x:v>未标注</x:v>
@@ -1915,212 +1907,218 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C23" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
+        <x:v>一盒印泥引发的全局封锁</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
-        <x:v>09-15 00:08</x:v>
-      </x:c>
-      <x:c r="E23" s="11" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F23" s="11" t="str">
-        <x:v>↑25位</x:v>
-      </x:c>
-      <x:c r="G23" s="11" t="str"/>
-      <x:c r="H23" s="11" t="str"/>
-      <x:c r="I23" s="11" t="n">
-        <x:v>124</x:v>
-      </x:c>
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="E23" s="11" t="str"/>
+      <x:c r="F23" s="11" t="str"/>
+      <x:c r="G23" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H23" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I23" s="11" t="str"/>
       <x:c r="J23" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K23" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L23" s="11" t="str">
-        <x:v>桃子动漫剧场</x:v>
-      </x:c>
-      <x:c r="M23" s="10" t="str">
-        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
-      </x:c>
+      <x:c r="L23" s="11" t="str"/>
+      <x:c r="M23" s="10" t="str"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C24" s="10" t="str">
-        <x:v>427元扳倒老油条</x:v>
+        <x:v>年终奖900万变900块，我辞职后他怒了</x:v>
       </x:c>
       <x:c r="D24" s="11" t="str">
-        <x:v>09-13 16:00</x:v>
-      </x:c>
-      <x:c r="E24" s="11" t="n">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F24" s="11" t="str">
-        <x:v>↑18位</x:v>
-      </x:c>
-      <x:c r="G24" s="11" t="str"/>
-      <x:c r="H24" s="11" t="str"/>
+        <x:v>09-15 12:00</x:v>
+      </x:c>
+      <x:c r="E24" s="11" t="str"/>
+      <x:c r="F24" s="11" t="str"/>
+      <x:c r="G24" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H24" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="I24" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J24" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K24" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧 / 都市职场</x:v>
       </x:c>
       <x:c r="L24" s="11" t="str">
-        <x:v>安然然</x:v>
+        <x:v>至尊爽剧社</x:v>
       </x:c>
       <x:c r="M24" s="10" t="str">
-        <x:v>职场新人许宁向老员工马丽芬讨要427元代垫外卖款，反遭易绑架马丽芬交出饭钱后怀恨在心，利用行政特权私吞福利，并在组织团餐时疏同事差价许宁按兵不动收集证据，最终将马丽芬长期贪占两万余元的行径在老板曝光的照片中马丽芬被直接开除，许宁成功维护了职场底线。</x:v>
+        <x:v>林砚入职十一天，发现小数点篡改产生的巨额付款漏洞，查出三年近两千四百万异常支出，帮公司追回一千八百万，关键线索却断掉。他遭财务总监刘敏华记恨，绩效被克扣、报销被卡压。林砚没有冲动对峙，悄悄收集证据。年会上董事长特批九百万年终奖，他提前备份证据、备好辞呈。到手仅九百块。他拿着辞职信找到董事长，当众亮出证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C25" s="10" t="str">
-        <x:v>河箱送福来</x:v>
+        <x:v>枕上独宠第一季</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
-        <x:v>09-13 11:00</x:v>
-      </x:c>
-      <x:c r="E25" s="11" t="n">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F25" s="11" t="str">
-        <x:v>↑13位</x:v>
-      </x:c>
-      <x:c r="G25" s="11" t="str"/>
-      <x:c r="H25" s="11" t="str"/>
+        <x:v>09-13 11:05</x:v>
+      </x:c>
+      <x:c r="E25" s="11" t="str"/>
+      <x:c r="F25" s="11" t="str"/>
+      <x:c r="G25" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H25" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="I25" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="J25" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K25" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L25" s="11" t="str">
-        <x:v>灵心讲故事</x:v>
+        <x:v>语跃文化</x:v>
       </x:c>
       <x:c r="M25" s="10" t="str">
-        <x:v>张家老两口从河中救回一只木箱，收养了箱中受伤的福生。福生长大后修桥开田，引水惠及乡亲，成家立业。二老相继离世后，山洪威胁村庄，福生为救乡亲舍命撑住巨石，最终重伤落水，下落不明。秀娥守着小院苦等多年，直到熟悉的声音再次响起。</x:v>
+        <x:v>四年前我不告而别，远走他国，以为他在家族逼婚与我之间选择了前者。四年后我以记者身份回国，第一场采访对象正是已成集团总裁的前男友。我问他订婚传闻，他冷言相对，却一直留着我送的旧物。直到闺蜜点破真相，当年他被家中软禁，错过我的电话，此后数年拼命往上走，只为有能力护住想护的人。误会尽释，这一次我不会再逃。</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B26" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C26" s="10" t="str">
-        <x:v>反派拿捏！</x:v>
+        <x:v>这桌团圆饭，我不做了</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
-        <x:v>2026-09-13</x:v>
-      </x:c>
-      <x:c r="E26" s="11" t="n">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="F26" s="11" t="str">
-        <x:v>↑13位</x:v>
-      </x:c>
-      <x:c r="G26" s="11" t="str"/>
-      <x:c r="H26" s="11" t="str"/>
-      <x:c r="I26" s="11" t="str"/>
+        <x:v>09-13 17:02</x:v>
+      </x:c>
+      <x:c r="E26" s="11" t="str"/>
+      <x:c r="F26" s="11" t="str"/>
+      <x:c r="G26" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H26" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I26" s="11" t="n">
+        <x:v>50</x:v>
+      </x:c>
       <x:c r="J26" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K26" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L26" s="11" t="str"/>
-      <x:c r="M26" s="10" t="str"/>
+        <x:v>美食治愈</x:v>
+      </x:c>
+      <x:c r="L26" s="11" t="str">
+        <x:v>锦鲤漫</x:v>
+      </x:c>
+      <x:c r="M26" s="10" t="str">
+        <x:v>除夕前夕，乔宁发现丈夫擅自退掉她陪父母吃年夜饭的包间，还将三十一人的团圆饭默认交给她操持。她不再争吵，也不再兜底，而是选择回家陪伴父母。随着陆家亲自接手年夜饭，众人才逐渐明白，一顿“简单”的团圆饭背后，藏着多少被忽视的付出与责任。</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B27" s="11" t="n">
-        <x:v>24</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C27" s="10" t="str">
-        <x:v>小妹初长成</x:v>
+        <x:v>427元扳倒老油条</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
-        <x:v>2026-09-13</x:v>
+        <x:v>09-13 16:00</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F27" s="11" t="str">
-        <x:v>↑3位</x:v>
+        <x:v>↑10位</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str"/>
       <x:c r="H27" s="11" t="str"/>
-      <x:c r="I27" s="11" t="str"/>
+      <x:c r="I27" s="11" t="n">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="J27" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K27" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L27" s="11" t="str"/>
-      <x:c r="M27" s="10" t="str"/>
+      <x:c r="L27" s="11" t="str">
+        <x:v>安然然</x:v>
+      </x:c>
+      <x:c r="M27" s="10" t="str">
+        <x:v>职场新人许宁向老员工马丽芬讨要427元代垫外卖款，反遭易绑架马丽芬交出饭钱后怀恨在心，利用行政特权私吞福利，并在组织团餐时疏同事差价许宁按兵不动收集证据，最终将马丽芬长期贪占两万余元的行径在老板曝光的照片中马丽芬被直接开除，许宁成功维护了职场底线。</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B28" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C28" s="10" t="str">
-        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
+        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
       </x:c>
       <x:c r="D28" s="11" t="str">
-        <x:v>09-13 09:58</x:v>
+        <x:v>09-15 08:30</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F28" s="11" t="str">
-        <x:v>↑2位</x:v>
+        <x:v>↑6位</x:v>
       </x:c>
       <x:c r="G28" s="11" t="str"/>
       <x:c r="H28" s="11" t="str"/>
       <x:c r="I28" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J28" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K28" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L28" s="11" t="str">
-        <x:v>创想剧场</x:v>
+        <x:v>琥珀漫剧</x:v>
       </x:c>
       <x:c r="M28" s="10" t="str">
-        <x:v>游戏公会会长林小勇筹备婚礼，却在婚宴上遭遇未婚妻临时加价逼婚。危急时刻，几位相交多年的游戏老友现身力挺他，林小勇果断取消婚礼。之后他搬进好友赠送的别墅，与陈董的两个女儿渐渐熟识。同学聚会上，众人见识到林小勇不一般的际遇。平静日子没过多久，当年游戏里的宿敌将出席游戏八周年嘉年华，一众老友决定赴约，一场新旧对决即将开启。</x:v>
+        <x:v>海鲜市场老手陈放，因一个两块钱的冰袋被十二年合伙人当众算旧账，心寒清账，净身出户。他没有抱怨，也没有以牙还牙，而是加入冷清档口“梅姐水产”，从零开始。他坚持明码标价、沥水称重、死活分卖、批次可查，宁可少接单，也不混货、不凑数、不赚亏心钱。面对低价抢客、恶意破坏、临时缺货等风波，他与叶梅靠诚信、规矩和彼此信任，一步步赢得客户与连锁企业的认可。</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -2128,34 +2126,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B29" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C29" s="10" t="str">
-        <x:v>我在工地卖盒饭带火一座城</x:v>
+        <x:v>晚棠知归，七年终见你</x:v>
       </x:c>
       <x:c r="D29" s="11" t="str">
-        <x:v>09-14 14:52</x:v>
-      </x:c>
-      <x:c r="E29" s="11" t="str"/>
+        <x:v>09-14 11:26</x:v>
+      </x:c>
+      <x:c r="E29" s="11" t="n">
+        <x:v>33</x:v>
+      </x:c>
       <x:c r="F29" s="11" t="str">
-        <x:v>新上榜</x:v>
+        <x:v>↑5位</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str"/>
       <x:c r="H29" s="11" t="str"/>
       <x:c r="I29" s="11" t="n">
-        <x:v>144</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J29" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K29" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L29" s="11" t="str">
-        <x:v>左手良画</x:v>
+        <x:v>喵琪琪追剧</x:v>
       </x:c>
       <x:c r="M29" s="10" t="str">
-        <x:v>小伙白叶遭遇老板跑路，半年工资付诸东流，意外被铁炒勺砸中觉醒超级餐饮系统。大雪封路堵车途中完成首份任务，靠着系统加持的厨艺，路边卖盒饭赚到第一桶金。回乡钻研秘制酱肉，赶集摆摊火爆出圈，还临危接手大型寿宴惊艳众人。过完新年，他怀揣梦想奔赴外地，准备开启属于自己的餐饮创业之路。</x:v>
+        <x:v>七年前，夏晚棠为救深爱的陆知珩，付出了一切，却被误会成背叛，独自带着女儿生活。多年后，两人再次相遇，陆知珩才发现当年的真相，也终于明白她承受了怎样的苦难。面对迟来的爱与亏欠，夏晚棠没有停留在过去，而是重新找回自己，用专业和坚强开启新的人生。最终，两人在女儿的陪伴下解开心结，携手迎来属于他们的幸福。</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -2163,17 +2163,19 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B30" s="11" t="n">
-        <x:v>92</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C30" s="10" t="str">
-        <x:v>一枚硬币换来的人生</x:v>
+        <x:v>反派拿捏！</x:v>
       </x:c>
       <x:c r="D30" s="11" t="str">
-        <x:v>2026-09-15</x:v>
-      </x:c>
-      <x:c r="E30" s="11" t="str"/>
+        <x:v>2026-09-13</x:v>
+      </x:c>
+      <x:c r="E30" s="11" t="n">
+        <x:v>47</x:v>
+      </x:c>
       <x:c r="F30" s="11" t="str">
-        <x:v>新上榜</x:v>
+        <x:v>↑5位</x:v>
       </x:c>
       <x:c r="G30" s="11" t="str"/>
       <x:c r="H30" s="11" t="str"/>
@@ -2192,98 +2194,170 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B31" s="11" t="n">
-        <x:v>94</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C31" s="10" t="str">
-        <x:v>从老娘车上滚下去</x:v>
+        <x:v>星际机修师</x:v>
       </x:c>
       <x:c r="D31" s="11" t="str">
-        <x:v>2026-09-14</x:v>
-      </x:c>
-      <x:c r="E31" s="11" t="str"/>
+        <x:v>09-14 00:06</x:v>
+      </x:c>
+      <x:c r="E31" s="11" t="n">
+        <x:v>75</x:v>
+      </x:c>
       <x:c r="F31" s="11" t="str">
-        <x:v>新上榜</x:v>
+        <x:v>↑5位</x:v>
       </x:c>
       <x:c r="G31" s="11" t="str"/>
       <x:c r="H31" s="11" t="str"/>
-      <x:c r="I31" s="11" t="str"/>
+      <x:c r="I31" s="11" t="n">
+        <x:v>301</x:v>
+      </x:c>
       <x:c r="J31" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K31" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L31" s="11" t="str"/>
-      <x:c r="M31" s="10" t="str"/>
+      <x:c r="M31" s="10" t="str">
+        <x:v>3033年星际机甲时代，18岁的苏白没有机甲天赋，却是初级机修师。父母留下百万星币与破旧仓库后远行，他激活星际战甲系统，改造仓库开设星际维修店。修复报废机甲“红月”并解锁天赋技后，苏白获得SSS级天赋万物相融与星鲸吐纳法。各路天才机甲师慕名而来，他打造专属机甲“混沌”，卷入各种阴谋纷争。不断击败对手，并将维修店扩张为星际要塞级基地。</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B32" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C32" s="10" t="str">
-        <x:v>假装破产试真心，我看清大学舍友的真面目</x:v>
+        <x:v>离婚那天我多了个痞帅老爹</x:v>
       </x:c>
       <x:c r="D32" s="11" t="str">
-        <x:v>09-15 08:00</x:v>
-      </x:c>
-      <x:c r="E32" s="11" t="str"/>
+        <x:v>2026-09-13</x:v>
+      </x:c>
+      <x:c r="E32" s="11" t="n">
+        <x:v>51</x:v>
+      </x:c>
       <x:c r="F32" s="11" t="str">
-        <x:v>新上榜</x:v>
+        <x:v>↑4位</x:v>
       </x:c>
       <x:c r="G32" s="11" t="str"/>
       <x:c r="H32" s="11" t="str"/>
-      <x:c r="I32" s="11" t="n">
-        <x:v>45</x:v>
-      </x:c>
+      <x:c r="I32" s="11" t="str"/>
       <x:c r="J32" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K32" s="10" t="str">
-        <x:v>婚姻情感 / 美食治愈 / 现实反转</x:v>
-      </x:c>
-      <x:c r="L32" s="11" t="str">
-        <x:v>芙浚动漫短剧</x:v>
-      </x:c>
-      <x:c r="M32" s="10" t="str">
-        <x:v>洛宁对外谎称家中破产那天，宿舍里的空气忽然变了味道。曾经收下她慷慨馈赠的陆清颜瞬间冷脸，惦记着还没到手的贵重礼物，处处刁难；贫困生齐黎一边继续收下她的物资，只象征性付点小钱，一边冷眼旁观，甚至给她介绍风月兼职。洛宁没有争辩，只是默默打开电脑，把每一句话、每一个眼神，都记进了那份越来越厚的PPT里。校庆那天，她准备了一份谁也想不到的“礼物”。</x:v>
-      </x:c>
+        <x:v>家庭伦理 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="L32" s="11" t="str"/>
+      <x:c r="M32" s="10" t="str"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B33" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C33" s="10" t="str">
-        <x:v>废材逆袭，我能截胡主角机缘</x:v>
+        <x:v>小妹初长成</x:v>
       </x:c>
       <x:c r="D33" s="11" t="str">
-        <x:v>09-13 10:28</x:v>
-      </x:c>
-      <x:c r="E33" s="11" t="str"/>
+        <x:v>2026-09-13</x:v>
+      </x:c>
+      <x:c r="E33" s="11" t="n">
+        <x:v>25</x:v>
+      </x:c>
       <x:c r="F33" s="11" t="str">
-        <x:v>新上榜</x:v>
+        <x:v>↑3位</x:v>
       </x:c>
       <x:c r="G33" s="11" t="str"/>
       <x:c r="H33" s="11" t="str"/>
-      <x:c r="I33" s="11" t="n">
-        <x:v>141</x:v>
-      </x:c>
+      <x:c r="I33" s="11" t="str"/>
       <x:c r="J33" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K33" s="10" t="str">
-        <x:v>婚姻情感 / 逆袭打脸</x:v>
-      </x:c>
-      <x:c r="L33" s="11" t="str">
-        <x:v>寻光短剧剧场</x:v>
-      </x:c>
-      <x:c r="M33" s="10" t="str">
-        <x:v>秦云遭未婚妻徐凝烟退婚，觉醒“气运真视”金手指，能预见机缘与灾劫。他接连截胡多位天命主角的机缘，获真龙道体、上古九秘，得古道圣人毕生传承，进入紫州圣地登顶圣子，闯魔宫夺八荒魔戟，入佛门揭佛渊秘辛，收先天魔胎囡囡为徒，最终于对战中悟透大道突破成圣，开启纵横天下的全新征程。</x:v>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L33" s="11" t="str"/>
+      <x:c r="M33" s="10" t="str"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B34" s="11" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C34" s="10" t="str">
+        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
+      </x:c>
+      <x:c r="D34" s="11" t="str">
+        <x:v>09-13 09:58</x:v>
+      </x:c>
+      <x:c r="E34" s="11" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F34" s="11" t="str">
+        <x:v>↑2位</x:v>
+      </x:c>
+      <x:c r="G34" s="11" t="str"/>
+      <x:c r="H34" s="11" t="str"/>
+      <x:c r="I34" s="11" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="J34" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K34" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L34" s="11" t="str">
+        <x:v>创想剧场</x:v>
+      </x:c>
+      <x:c r="M34" s="10" t="str">
+        <x:v>游戏公会会长林小勇筹备婚礼，却在婚宴上遭遇未婚妻临时加价逼婚。危急时刻，几位相交多年的游戏老友现身力挺他，林小勇果断取消婚礼。之后他搬进好友赠送的别墅，与陈董的两个女儿渐渐熟识。同学聚会上，众人见识到林小勇不一般的际遇。平静日子没过多久，当年游戏里的宿敌将出席游戏八周年嘉年华，一众老友决定赴约，一场新旧对决即将开启。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B35" s="11" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C35" s="10" t="str">
+        <x:v>四个崽崽瞒不住了</x:v>
+      </x:c>
+      <x:c r="D35" s="11" t="str">
+        <x:v>09-15 00:08</x:v>
+      </x:c>
+      <x:c r="E35" s="11" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F35" s="11" t="str">
+        <x:v>↑1位</x:v>
+      </x:c>
+      <x:c r="G35" s="11" t="str"/>
+      <x:c r="H35" s="11" t="str"/>
+      <x:c r="I35" s="11" t="n">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="J35" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K35" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L35" s="11" t="str">
+        <x:v>桃子动漫剧场</x:v>
+      </x:c>
+      <x:c r="M35" s="10" t="str">
+        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2329,129 +2403,232 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
-        <x:v>辣媳进门，我给公婆撑腰</x:v>
+        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>当日新上榜</x:v>
-      </x:c>
-      <x:c r="D2" s="11" t="str"/>
-      <x:c r="E2" s="11" t="str"/>
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D2" s="11" t="str">
+        <x:v>09-15 08:00</x:v>
+      </x:c>
+      <x:c r="E2" s="11" t="n">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="F2" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="G2" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G2" s="10" t="str">
+        <x:v>心动漫剧场</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
+        <x:v>四个崽崽瞒不住了</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>09-15 08:00</x:v>
+        <x:v>09-15 00:08</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F3" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G3" s="10" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>桃子动漫剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
+        <x:v>一盒印泥引发的全局封锁</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>今日发布</x:v>
-      </x:c>
-      <x:c r="D4" s="11" t="str">
-        <x:v>09-15 00:08</x:v>
-      </x:c>
-      <x:c r="E4" s="11" t="n">
-        <x:v>124</x:v>
-      </x:c>
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D4" s="11" t="str"/>
+      <x:c r="E4" s="11" t="str"/>
       <x:c r="F4" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G4" s="10" t="str">
-        <x:v>桃子动漫剧场</x:v>
-      </x:c>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="G4" s="10" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>被算计的新娘华丽转身</x:v>
+        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>当日新上榜</x:v>
+        <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>07-28 00:29</x:v>
+        <x:v>09-15 08:30</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F5" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G5" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>琥珀漫剧</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>92</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>一枚硬币换来的人生</x:v>
+        <x:v>高考刚结束父母就不装了</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>当日新上榜</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="str"/>
-      <x:c r="E6" s="11" t="str"/>
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>09-15 07:00</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="n">
+        <x:v>173</x:v>
+      </x:c>
       <x:c r="F6" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="G6" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G6" s="10" t="str">
+        <x:v>千慕剧场</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>假装破产试真心，我看清大学舍友的真面目</x:v>
+        <x:v>年终奖900万变900块，我辞职后他怒了</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>09-15 08:00</x:v>
+        <x:v>09-15 12:00</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F7" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G7" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
-      </x:c>
+        <x:v>至尊爽剧社</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="11" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B8" s="10" t="str">
+        <x:v>被身高掩盖的谎言</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="str">
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="str">
+        <x:v>09-15 08:18</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F8" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G8" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="11" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B9" s="10" t="str">
+        <x:v>一宴断经年，旧账归于风</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="str">
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="str">
+        <x:v>09-15 06:13</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F9" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G9" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="11" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B10" s="10" t="str">
+        <x:v>结婚八年，我娶的原来是仇人的女儿</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="str">
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D10" s="11" t="str"/>
+      <x:c r="E10" s="11" t="str"/>
+      <x:c r="F10" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="G10" s="10" t="str"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="11" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B11" s="10" t="str">
+        <x:v>入局不为爱</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="str">
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="str"/>
+      <x:c r="E11" s="11" t="str"/>
+      <x:c r="F11" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="G11" s="10" t="str"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="11" t="n">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B12" s="10" t="str">
+        <x:v>辣媳进门，我给公婆撑腰</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="str">
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D12" s="11" t="str"/>
+      <x:c r="E12" s="11" t="str"/>
+      <x:c r="F12" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="G12" s="10" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2520,7 +2697,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
         <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
@@ -2557,7 +2734,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
         <x:v>重生三天前，我用水泥封死地下室</x:v>
@@ -2597,13 +2774,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>一墙之隔，皆是人心</x:v>
+        <x:v>不靠谱爸妈很靠谱</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>09-06 15:48</x:v>
+        <x:v>09-09 11:08</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
         <x:v>7</x:v>
@@ -2612,10 +2789,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G4" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H4" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I4" s="10" t="str">
         <x:v>其他</x:v>
@@ -2623,24 +2800,24 @@
       <x:c r="J4" s="11" t="str"/>
       <x:c r="K4" s="11" t="str"/>
       <x:c r="L4" s="10" t="str">
-        <x:v>在下长生</x:v>
+        <x:v>灵妹儿</x:v>
       </x:c>
       <x:c r="M4" s="10" t="str">
-        <x:v>妻子临产被车堵住出口，叶瑾抱着羊水破裂的她跑了三公里才到医院，母子平安。面对无理的车主，他没有以暴制暴，而是选择依法行事——在自家院内合法砌墙、种下高价值树苗，全程录像留证。车主回来后暴力砸墙、碾压树苗，最终被依法追究责任。</x:v>
+        <x:v>外表张扬的年轻夫妻在冬夜救下女婴林小小，用十七年的辛勤劳动和无条件陪伴，为她撑起温暖的家。曾经成绩落后的林小小，在父母的鼓励下重新学习，一步步成长为优秀学生。面对亲生家庭带来的资源与人生选择，她也开始重新理解血缘、养育与责任。当外界的误解影响到父母的生活，林小小决定勇敢站出来，用事实守护家人，也用努力证明真正的爱，是尊重、陪伴和彼此成就。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>离家十年，回来女儿被换了</x:v>
+        <x:v>一墙之隔，皆是人心</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>09-09 00:04</x:v>
+        <x:v>09-06 15:48</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
         <x:v>7</x:v>
@@ -2652,7 +2829,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H5" s="11" t="n">
-        <x:v>155</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="I5" s="10" t="str">
         <x:v>其他</x:v>
@@ -2660,15 +2837,15 @@
       <x:c r="J5" s="11" t="str"/>
       <x:c r="K5" s="11" t="str"/>
       <x:c r="L5" s="10" t="str">
-        <x:v>魔方影视（上剧版</x:v>
+        <x:v>在下长生</x:v>
       </x:c>
       <x:c r="M5" s="10" t="str">
-        <x:v>程砚宁完成长期绝密任务归来，满心想要弥补亲情，却发现家中早已物是人非。身边亲近之人被私欲蒙蔽，制造重重骗局，试图侵占她的事业与财富。面对接连而来的算计与危机，她凭借过人的魄力与智慧步步拆解阴谋，联合正义力量搜集证据，厘清全部是非纠葛。在守护自身事业的同时，她放下过往伤痛，投身公益，完成自我和解，迎来属于自己的全新人生。</x:v>
+        <x:v>妻子临产被车堵住出口，叶瑾抱着羊水破裂的她跑了三公里才到医院，母子平安。面对无理的车主，他没有以暴制暴，而是选择依法行事——在自家院内合法砌墙、种下高价值树苗，全程录像留证。车主回来后暴力砸墙、碾压树苗，最终被依法追究责任。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
         <x:v>穿书后我带萌宝上门认爹</x:v>
@@ -2705,16 +2882,16 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>惊絮无声：傻女的绝杀</x:v>
+        <x:v>离家十年，回来女儿被换了</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>09-06 10:00</x:v>
+        <x:v>09-09 00:04</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
         <x:v>7</x:v>
@@ -2723,10 +2900,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G7" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H7" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="I7" s="10" t="str">
         <x:v>其他</x:v>
@@ -2734,24 +2911,24 @@
       <x:c r="J7" s="11" t="str"/>
       <x:c r="K7" s="11" t="str"/>
       <x:c r="L7" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>魔方影视（上剧版</x:v>
       </x:c>
       <x:c r="M7" s="10" t="str">
-        <x:v>沈家人人都是天才，唯独小女儿沈惊絮是公认的傻子。没人知道，她不仅装傻多年，还带着前世金牌律师的记忆重生而来。本想闭嘴躺平一生，谁料内鬼勾结资本做空沈氏，一纸合同就要让全家净身出户、背上百亿债务。父亲落笔前，她终于按住协议“这字不能签！”绝地反杀的沈惊絮，一步步挫败了对沈家的围剿，也让全家人重新认识了自己。沈家也迎来了新生。</x:v>
+        <x:v>程砚宁完成长期绝密任务归来，满心想要弥补亲情，却发现家中早已物是人非。身边亲近之人被私欲蒙蔽，制造重重骗局，试图侵占她的事业与财富。面对接连而来的算计与危机，她凭借过人的魄力与智慧步步拆解阴谋，联合正义力量搜集证据，厘清全部是非纠葛。在守护自身事业的同时，她放下过往伤痛，投身公益，完成自我和解，迎来属于自己的全新人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>不靠谱爸妈很靠谱</x:v>
+        <x:v>破库房的秘密</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>09-09 11:08</x:v>
+        <x:v>2026-09-05</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
         <x:v>7</x:v>
@@ -2762,33 +2939,27 @@
       <x:c r="G8" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H8" s="11" t="n">
-        <x:v>73</x:v>
-      </x:c>
+      <x:c r="H8" s="11" t="str"/>
       <x:c r="I8" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J8" s="11" t="str"/>
       <x:c r="K8" s="11" t="str"/>
-      <x:c r="L8" s="10" t="str">
-        <x:v>灵妹儿</x:v>
-      </x:c>
-      <x:c r="M8" s="10" t="str">
-        <x:v>外表张扬的年轻夫妻在冬夜救下女婴林小小，用十七年的辛勤劳动和无条件陪伴，为她撑起温暖的家。曾经成绩落后的林小小，在父母的鼓励下重新学习，一步步成长为优秀学生。面对亲生家庭带来的资源与人生选择，她也开始重新理解血缘、养育与责任。当外界的误解影响到父母的生活，林小小决定勇敢站出来，用事实守护家人，也用努力证明真正的爱，是尊重、陪伴和彼此成就。</x:v>
-      </x:c>
+      <x:c r="L8" s="10" t="str"/>
+      <x:c r="M8" s="10" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>破库房的秘密</x:v>
+        <x:v>抢个新娘来当后娘第一季</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>2026-09-05</x:v>
+        <x:v>09-08 15:10</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
         <x:v>7</x:v>
@@ -2797,29 +2968,35 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G9" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H9" s="11" t="str"/>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H9" s="11" t="n">
+        <x:v>177</x:v>
+      </x:c>
       <x:c r="I9" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J9" s="11" t="str"/>
       <x:c r="K9" s="11" t="str"/>
-      <x:c r="L9" s="10" t="str"/>
-      <x:c r="M9" s="10" t="str"/>
+      <x:c r="L9" s="10" t="str">
+        <x:v>麻辣公主</x:v>
+      </x:c>
+      <x:c r="M9" s="10" t="str">
+        <x:v>带着十里红妆出嫁那日，我才得知新郎早已另娶，这门亲事不过是盯上了我李家的家产。换作旁人或许忍气吞声，我偏不。我当众拒入侯府，主动上书朝廷，愿以嫁妆资援南方水患，只求解除婚约、护我父母周全。这份胆识赢得安王敬重，他以正妃之礼娶我入门。我立誓此生不做妾、不与人共侍一夫，终得一份彼此尊重的姻缘。</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>抢个新娘来当后娘第一季</x:v>
+        <x:v>惊絮无声：傻女的绝杀</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>09-08 15:10</x:v>
+        <x:v>09-06 10:00</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
         <x:v>7</x:v>
@@ -2828,10 +3005,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G10" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H10" s="11" t="n">
-        <x:v>177</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I10" s="10" t="str">
         <x:v>其他</x:v>
@@ -2839,24 +3016,24 @@
       <x:c r="J10" s="11" t="str"/>
       <x:c r="K10" s="11" t="str"/>
       <x:c r="L10" s="10" t="str">
-        <x:v>麻辣公主</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="M10" s="10" t="str">
-        <x:v>带着十里红妆出嫁那日，我才得知新郎早已另娶，这门亲事不过是盯上了我李家的家产。换作旁人或许忍气吞声，我偏不。我当众拒入侯府，主动上书朝廷，愿以嫁妆资援南方水患，只求解除婚约、护我父母周全。这份胆识赢得安王敬重，他以正妃之礼娶我入门。我立誓此生不做妾、不与人共侍一夫，终得一份彼此尊重的姻缘。</x:v>
+        <x:v>沈家人人都是天才，唯独小女儿沈惊絮是公认的傻子。没人知道，她不仅装傻多年，还带着前世金牌律师的记忆重生而来。本想闭嘴躺平一生，谁料内鬼勾结资本做空沈氏，一纸合同就要让全家净身出户、背上百亿债务。父亲落笔前，她终于按住协议“这字不能签！”绝地反杀的沈惊絮，一步步挫败了对沈家的围剿，也让全家人重新认识了自己。沈家也迎来了新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="n">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>凤阙承安</x:v>
+        <x:v>美颜系统开挂，大佬全跪下</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>09-09 00:10</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
         <x:v>7</x:v>
@@ -2867,27 +3044,33 @@
       <x:c r="G11" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H11" s="11" t="str"/>
+      <x:c r="H11" s="11" t="n">
+        <x:v>172</x:v>
+      </x:c>
       <x:c r="I11" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J11" s="11" t="str"/>
       <x:c r="K11" s="11" t="str"/>
-      <x:c r="L11" s="10" t="str"/>
-      <x:c r="M11" s="10" t="str"/>
+      <x:c r="L11" s="10" t="str">
+        <x:v>御儿</x:v>
+      </x:c>
+      <x:c r="M11" s="10" t="str">
+        <x:v>曾因外形饱受非议的米珂华丽转身，蜕变得耀眼又夺目。从前对她嗤之以鼻的蒋少开始频频在意，素来冷眼毒舌的陆总不知不觉深陷其中，连一向克己的商界大佬也为她打破原则。米珂凭智商与手腕周旋于众人之间，上演一场势均力敌的情感博弈。没有俗套的救赎，只有双向的拉扯。看一众高高在上的精英暗自较劲、步步沉沦，心甘情愿为她卸下防备。</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>重启人生，拒绝校花？</x:v>
+        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>09-08 08:30</x:v>
+        <x:v>2026-09-05</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
         <x:v>7</x:v>
@@ -2896,26 +3079,20 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G12" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H12" s="11" t="n">
-        <x:v>108</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H12" s="11" t="str"/>
       <x:c r="I12" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J12" s="11" t="str"/>
       <x:c r="K12" s="11" t="str"/>
-      <x:c r="L12" s="10" t="str">
-        <x:v>肆漫简</x:v>
-      </x:c>
-      <x:c r="M12" s="10" t="str">
-        <x:v>白陌重生回到2004年高考夜，果断避开前世陷害自己的宾馆陷阱，救下被下药的校花江洛菡，彻底扭转人生走向。他不再执着于过往的情感执念，跳出卑微追爱的困局，转而关心恩师健康、规划学业与创业方向，结识志同道合的伙伴。凭借重生阅历清醒选择前路，把握青春重启人生，用行动改写原本遗憾的命运，活出全新成长轨迹。</x:v>
-      </x:c>
+      <x:c r="L12" s="10" t="str"/>
+      <x:c r="M12" s="10" t="str"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
         <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
@@ -2952,16 +3129,16 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
+        <x:v>重启人生，拒绝校花？</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>2026-09-05</x:v>
+        <x:v>09-08 08:30</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
         <x:v>7</x:v>
@@ -2970,29 +3147,35 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G14" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="11" t="str"/>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="n">
+        <x:v>108</x:v>
+      </x:c>
       <x:c r="I14" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J14" s="11" t="str"/>
       <x:c r="K14" s="11" t="str"/>
-      <x:c r="L14" s="10" t="str"/>
-      <x:c r="M14" s="10" t="str"/>
+      <x:c r="L14" s="10" t="str">
+        <x:v>肆漫简</x:v>
+      </x:c>
+      <x:c r="M14" s="10" t="str">
+        <x:v>白陌重生回到2004年高考夜，果断避开前世陷害自己的宾馆陷阱，救下被下药的校花江洛菡，彻底扭转人生走向。他不再执着于过往的情感执念，跳出卑微追爱的困局，转而关心恩师健康、规划学业与创业方向，结识志同道合的伙伴。凭借重生阅历清醒选择前路，把握青春重启人生，用行动改写原本遗憾的命运，活出全新成长轨迹。</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>美颜系统开挂，大佬全跪下</x:v>
+        <x:v>凤阙承安</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
-        <x:v>09-09 00:10</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
         <x:v>7</x:v>
@@ -3003,24 +3186,18 @@
       <x:c r="G15" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H15" s="11" t="n">
-        <x:v>172</x:v>
-      </x:c>
+      <x:c r="H15" s="11" t="str"/>
       <x:c r="I15" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J15" s="11" t="str"/>
       <x:c r="K15" s="11" t="str"/>
-      <x:c r="L15" s="10" t="str">
-        <x:v>御儿</x:v>
-      </x:c>
-      <x:c r="M15" s="10" t="str">
-        <x:v>曾因外形饱受非议的米珂华丽转身，蜕变得耀眼又夺目。从前对她嗤之以鼻的蒋少开始频频在意，素来冷眼毒舌的陆总不知不觉深陷其中，连一向克己的商界大佬也为她打破原则。米珂凭智商与手腕周旋于众人之间，上演一场势均力敌的情感博弈。没有俗套的救赎，只有双向的拉扯。看一众高高在上的精英暗自较劲、步步沉沦，心甘情愿为她卸下防备。</x:v>
-      </x:c>
+      <x:c r="L15" s="10" t="str"/>
+      <x:c r="M15" s="10" t="str"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="n">
-        <x:v>82</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
         <x:v>天灾末世，她囤满物资后所向披靡！</x:v>
@@ -3057,7 +3234,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
         <x:v>蒙蒙半故</x:v>
@@ -3094,16 +3271,16 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>那块玉，带我们回家</x:v>
+        <x:v>全家施压：我反手签了过户合同</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>09-05 07:18</x:v>
+        <x:v>09-08 16:58</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
         <x:v>7</x:v>
@@ -3112,10 +3289,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G18" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H18" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I18" s="10" t="str">
         <x:v>其他</x:v>
@@ -3123,24 +3300,24 @@
       <x:c r="J18" s="11" t="str"/>
       <x:c r="K18" s="11" t="str"/>
       <x:c r="L18" s="10" t="str">
-        <x:v>五指毛桃</x:v>
+        <x:v>灵川剧场</x:v>
       </x:c>
       <x:c r="M18" s="10" t="str">
-        <x:v>六岁孩童为救母拾荒半年，孝心感动天地，更牵出一段失散六年的亲情。缘分以信物为引，助离散一家重逢。当暗处之手伸向团圆，真相与信任如光破晓，令恶念无处遁形。正义为善良护航，温暖在守望中生长。孩子用稚嫩肩膀撑起希望，父母以爱重筑家园，善意在风雨中传递，终迎阖家安康的晴空。</x:v>
+        <x:v>儿子儿媳多次提议我搬回乡下养老，将城里的宽敞住房腾出来给女方父母长期居住。我笑着点头应下，转头便将这套三室朝南的江景房产挂牌出售，最终成交二百八十万元。我随即购置了一套一室一厅的小户型，更换门锁后独自入住。他们上门索要钥匙，我没有开门。名下房产我自有主张，谁也别想插手安排。</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="n">
-        <x:v>89</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>谢谢爸妈的穷养现在我富了</x:v>
+        <x:v>我的奇葩舍友</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>09-08 17:00</x:v>
+        <x:v>09-06 09:55</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
         <x:v>7</x:v>
@@ -3149,10 +3326,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G19" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H19" s="11" t="n">
-        <x:v>120</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str">
         <x:v>其他</x:v>
@@ -3160,24 +3337,24 @@
       <x:c r="J19" s="11" t="str"/>
       <x:c r="K19" s="11" t="str"/>
       <x:c r="L19" s="10" t="str">
-        <x:v>风云剧场</x:v>
+        <x:v>金鱼漫剪</x:v>
       </x:c>
       <x:c r="M19" s="10" t="str">
-        <x:v>秦明从小被父母区别对待，十八年后才知一切只是父母对两个儿子的不同教育安排。重生回到高三，他拒绝向既定命运低头，从校园起步，抓住时代机遇暗中积蓄力量。父母继续对弟弟偏爱，秦明也继续低调生活——整整十八年。直到除夕夜，他回到那个破旧的家，把所有真相摆在父母面前，把自己失去的人生，亲手要了回来。</x:v>
+        <x:v>林嘉宝从小由母亲周美兰一手带大，事无巨细都由妈妈安排。上大学后，他不会套被套，不会洗衣服，遇事第一反应是打电话问妈妈。母亲为他定下各种宿舍规矩，与室友矛盾不断。直到家中突遭变故，父亲破产，豪宅被封，母亲失联。嘉宝一夜之间失去所有依靠，被迫独自面对生活，一步步学会洗衣、打工、交电费，逐渐成为独立的大学生。</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>全家施压：我反手签了过户合同</x:v>
+        <x:v>那块玉，带我们回家</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>09-08 16:58</x:v>
+        <x:v>09-05 07:18</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
         <x:v>7</x:v>
@@ -3186,10 +3363,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G20" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H20" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="I20" s="10" t="str">
         <x:v>其他</x:v>
@@ -3197,15 +3374,15 @@
       <x:c r="J20" s="11" t="str"/>
       <x:c r="K20" s="11" t="str"/>
       <x:c r="L20" s="10" t="str">
-        <x:v>灵川剧场</x:v>
+        <x:v>五指毛桃</x:v>
       </x:c>
       <x:c r="M20" s="10" t="str">
-        <x:v>儿子儿媳多次提议我搬回乡下养老，将城里的宽敞住房腾出来给女方父母长期居住。我笑着点头应下，转头便将这套三室朝南的江景房产挂牌出售，最终成交二百八十万元。我随即购置了一套一室一厅的小户型，更换门锁后独自入住。他们上门索要钥匙，我没有开门。名下房产我自有主张，谁也别想插手安排。</x:v>
+        <x:v>六岁孩童为救母拾荒半年，孝心感动天地，更牵出一段失散六年的亲情。缘分以信物为引，助离散一家重逢。当暗处之手伸向团圆，真相与信任如光破晓，令恶念无处遁形。正义为善良护航，温暖在守望中生长。孩子用稚嫩肩膀撑起希望，父母以爱重筑家园，善意在风雨中传递，终迎阖家安康的晴空。</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
         <x:v>征地我秒签跑路，全村笑我半年</x:v>
@@ -3242,13 +3419,13 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>大坝边寻回的真千金</x:v>
+        <x:v>重生后我守住全村</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>09-10 11:26</x:v>
+        <x:v>09-10 08:08</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
         <x:v>5</x:v>
@@ -3260,10 +3437,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G22" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H22" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str">
         <x:v>其他</x:v>
@@ -3271,21 +3448,21 @@
       <x:c r="J22" s="11" t="str"/>
       <x:c r="K22" s="11" t="str"/>
       <x:c r="L22" s="10" t="str">
-        <x:v>喵琪琪追剧</x:v>
+        <x:v>金果漫剧</x:v>
       </x:c>
       <x:c r="M22" s="10" t="str">
-        <x:v>大坝突发险情，农村女孩夏晚禾凭借熟悉的环境和过人的勇气，不顾危险救下被困的沈长洲。一次意外的救援，让两个陌生人的命运重新交织。随着调查深入，沈长洲发现这个善良坚韧的女孩，竟是自己失散二十年的亲生女儿。面对迟来的亲情和真假千金的风波，夏晚禾没有依靠身份改变人生，而是用智慧、担当和努力证明自己的价值。陆言川也在一次次并肩相处中，被她的真诚与坚强打动，陪她找回亲情，走向新的未来。</x:v>
+        <x:v>70年代冬，赵满仓在父亲离世后重回鼠灾前八天。面对家中骤变，他选择先护住亲人，带着前世经验迁入碾坊，储粮备药，筑墙防鼠，设点防疫。灾情来临时，他联合李杏儿，刘石头和乡亲稳住村庄，并用账册与规矩澄清父亲名誉。风雪过后，黎家沟建起防鼠坊，猫舍和净粮地窖，众人也在互助中迎来新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>重生后我守住全村</x:v>
+        <x:v>大坝边寻回的真千金</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>09-10 08:08</x:v>
+        <x:v>09-10 11:26</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
         <x:v>5</x:v>
@@ -3297,10 +3474,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G23" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H23" s="11" t="n">
-        <x:v>129</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
         <x:v>其他</x:v>
@@ -3308,15 +3485,15 @@
       <x:c r="J23" s="11" t="str"/>
       <x:c r="K23" s="11" t="str"/>
       <x:c r="L23" s="10" t="str">
-        <x:v>金果漫剧</x:v>
+        <x:v>喵琪琪追剧</x:v>
       </x:c>
       <x:c r="M23" s="10" t="str">
-        <x:v>70年代冬，赵满仓在父亲离世后重回鼠灾前八天。面对家中骤变，他选择先护住亲人，带着前世经验迁入碾坊，储粮备药，筑墙防鼠，设点防疫。灾情来临时，他联合李杏儿，刘石头和乡亲稳住村庄，并用账册与规矩澄清父亲名誉。风雪过后，黎家沟建起防鼠坊，猫舍和净粮地窖，众人也在互助中迎来新生。</x:v>
+        <x:v>大坝突发险情，农村女孩夏晚禾凭借熟悉的环境和过人的勇气，不顾危险救下被困的沈长洲。一次意外的救援，让两个陌生人的命运重新交织。随着调查深入，沈长洲发现这个善良坚韧的女孩，竟是自己失散二十年的亲生女儿。面对迟来的亲情和真假千金的风波，夏晚禾没有依靠身份改变人生，而是用智慧、担当和努力证明自己的价值。陆言川也在一次次并肩相处中，被她的真诚与坚强打动，陪她找回亲情，走向新的未来。</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
         <x:v>假老板娘遇上真董事长</x:v>
@@ -3347,16 +3524,16 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="n">
-        <x:v>87</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>迟来深情皆是刃</x:v>
+        <x:v>赶海人生：重回1983小渔村</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>09-09 10:00</x:v>
+        <x:v>09-10 08:55</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
         <x:v>6</x:v>
@@ -3365,10 +3542,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G25" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H25" s="11" t="n">
-        <x:v>184</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str">
         <x:v>其他</x:v>
@@ -3376,24 +3553,24 @@
       <x:c r="J25" s="11" t="str"/>
       <x:c r="K25" s="11" t="str"/>
       <x:c r="L25" s="10" t="str">
-        <x:v>展瓦-佩云看剧</x:v>
+        <x:v>梦落漫漫</x:v>
       </x:c>
       <x:c r="M25" s="10" t="str">
-        <x:v>天才芯片科研人姜莱，隐去光芒，在婚姻里默默付出四年，却遭遇丈夫沈荀的背叛与冷待。看清现实的她挣脱窒息的婚姻，撕下普通家庭主妇的伪装，重拾科研理想。面对丈夫、情敌的百般算计，她冷静反击。在自研芯重大项目竞标舞台上，姜莱展露真实实力，完成华丽逆袭，实现自我价值。过往伤痛化作成长力量，她告别糟糕的旧生活，向着事业与崭新的人生大步奔赴，迎来属于自己的光明未来。</x:v>
+        <x:v>前世杨建国跳海离世，意外重生回到1983年东沟小渔村。这一年开海祭龙王，妻子即将遭遇毒蛇险境，家中穷困潦倒，伯父还妄图霸占自家渔船。曾经的街溜子幡然醒悟，凭借超前记忆踏海赶海，捕捞对虾、鲍鱼，对抗邻里刁难，守护妻儿老小，在汹涌海潮之中改写一家人贫苦命运。</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
+        <x:v>三分钱的取舍</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
-        <x:v>09-11 09:00</x:v>
+        <x:v>09-10 17:29</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
         <x:v>5</x:v>
@@ -3402,10 +3579,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G26" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H26" s="11" t="n">
-        <x:v>133</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I26" s="10" t="str">
         <x:v>其他</x:v>
@@ -3413,24 +3590,24 @@
       <x:c r="J26" s="11" t="str"/>
       <x:c r="K26" s="11" t="str"/>
       <x:c r="L26" s="10" t="str">
-        <x:v>阳阳动画</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="M26" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
+        <x:v>青石沟果农为省下代办三分钱，甩开中间商周成岳，直接对接收购商方洪生收桃。可脱离周成岳统筹调度后，摘桃、排单、装车乱象丛生，桃子积压损耗。周成岳转身接手偏远的十里湾桃园，凭口碑站稳脚跟。经历一季波折，青石沟众人幡然醒悟，重新读懂代办的价值。</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>三分钱的取舍</x:v>
+        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
       </x:c>
       <x:c r="C27" s="11" t="str">
-        <x:v>09-10 17:29</x:v>
+        <x:v>09-11 09:00</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
         <x:v>5</x:v>
@@ -3439,10 +3616,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G27" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H27" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="I27" s="10" t="str">
         <x:v>其他</x:v>
@@ -3450,24 +3627,24 @@
       <x:c r="J27" s="11" t="str"/>
       <x:c r="K27" s="11" t="str"/>
       <x:c r="L27" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>阳阳动画</x:v>
       </x:c>
       <x:c r="M27" s="10" t="str">
-        <x:v>青石沟果农为省下代办三分钱，甩开中间商周成岳，直接对接收购商方洪生收桃。可脱离周成岳统筹调度后，摘桃、排单、装车乱象丛生，桃子积压损耗。周成岳转身接手偏远的十里湾桃园，凭口碑站稳脚跟。经历一季波折，青石沟众人幡然醒悟，重新读懂代办的价值。</x:v>
+        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>一张废票毁了她</x:v>
+        <x:v>穿越60我有空间不愁吃喝</x:v>
       </x:c>
       <x:c r="C28" s="11" t="str">
-        <x:v>2026-09-11</x:v>
+        <x:v>09-07 00:04</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
         <x:v>5</x:v>
@@ -3476,29 +3653,35 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G28" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H28" s="11" t="str"/>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H28" s="11" t="n">
+        <x:v>1000</x:v>
+      </x:c>
       <x:c r="I28" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J28" s="11" t="str"/>
       <x:c r="K28" s="11" t="str"/>
-      <x:c r="L28" s="10" t="str"/>
-      <x:c r="M28" s="10" t="str"/>
+      <x:c r="L28" s="10" t="str">
+        <x:v>夜珠AI剧场</x:v>
+      </x:c>
+      <x:c r="M28" s="10" t="str">
+        <x:v>现代青年刘大壮意外穿越到60年代，成了同名同姓的16岁穷小子。原主因相亲被拒、家徒四壁，下河摸鱼时溺亡。大壮醒来后发现脑中多了一座九层宝塔空间——内有灵药田与灵泉潭水，作物两小时成熟、产量翻五倍。饥荒年代，别人啃树皮喝稀粥，他靠空间种出满仓土豆粮食，黑市换粮票钞票，让饿肚子的父母姐姐们吃上饱饭。从人人嘲笑的穷小子，到带着全家逆袭翻盘，且看他手握宝塔空间，在艰苦年代闯出一条吃喝不愁的逆袭</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>穿越60我有空间不愁吃喝</x:v>
+        <x:v>回到零四年进军彩铃界</x:v>
       </x:c>
       <x:c r="C29" s="11" t="str">
-        <x:v>09-07 00:04</x:v>
+        <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
         <x:v>5</x:v>
@@ -3507,35 +3690,29 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G29" s="11" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H29" s="11" t="n">
-        <x:v>1000</x:v>
-      </x:c>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="H29" s="11" t="str"/>
       <x:c r="I29" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J29" s="11" t="str"/>
       <x:c r="K29" s="11" t="str"/>
-      <x:c r="L29" s="10" t="str">
-        <x:v>夜珠AI剧场</x:v>
-      </x:c>
-      <x:c r="M29" s="10" t="str">
-        <x:v>现代青年刘大壮意外穿越到60年代，成了同名同姓的16岁穷小子。原主因相亲被拒、家徒四壁，下河摸鱼时溺亡。大壮醒来后发现脑中多了一座九层宝塔空间——内有灵药田与灵泉潭水，作物两小时成熟、产量翻五倍。饥荒年代，别人啃树皮喝稀粥，他靠空间种出满仓土豆粮食，黑市换粮票钞票，让饿肚子的父母姐姐们吃上饱饭。从人人嘲笑的穷小子，到带着全家逆袭翻盘，且看他手握宝塔空间，在艰苦年代闯出一条吃喝不愁的逆袭</x:v>
-      </x:c>
+      <x:c r="L29" s="10" t="str"/>
+      <x:c r="M29" s="10" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>重生一世，我不再痴恋竹马</x:v>
+        <x:v>一张废票毁了她</x:v>
       </x:c>
       <x:c r="C30" s="11" t="str">
-        <x:v>09-10 10:00</x:v>
+        <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
         <x:v>5</x:v>
@@ -3544,53 +3721,53 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G30" s="11" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H30" s="11" t="n">
-        <x:v>65</x:v>
-      </x:c>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H30" s="11" t="str"/>
       <x:c r="I30" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J30" s="11" t="str"/>
       <x:c r="K30" s="11" t="str"/>
-      <x:c r="L30" s="10" t="str">
-        <x:v>锦书映年华</x:v>
-      </x:c>
-      <x:c r="M30" s="10" t="str">
-        <x:v>承平公主前世错恋齐远安，受尽磋磨含恨落幕。一朝重生，恰逢圣旨赐婚，齐远安却当众恳请解除婚约，求取太后义孙女傅明珠。她坦然放手，主动成全二人，看着他们得偿所愿。宁国侯夫人动用旧物强求赐婚，她巧妙改换婚事，选择边关归来、品性刚正的齐远舟。婚后她聪慧通透，看清傅明珠与齐远安的本性，冷眼旁观二人矛盾丛生。历经风波，她与齐远舟彼此扶持，挣脱过往伤痛，收获属于自己安稳坦荡的人生。</x:v>
-      </x:c>
+      <x:c r="L30" s="10" t="str"/>
+      <x:c r="M30" s="10" t="str"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>回到零四年进军彩铃界</x:v>
+        <x:v>张兰芬重生记</x:v>
       </x:c>
       <x:c r="C31" s="11" t="str">
-        <x:v>2026-09-11</x:v>
+        <x:v>09-05 17:00</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G31" s="11" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H31" s="11" t="str"/>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H31" s="11" t="n">
+        <x:v>176</x:v>
+      </x:c>
       <x:c r="I31" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J31" s="11" t="str"/>
       <x:c r="K31" s="11" t="str"/>
-      <x:c r="L31" s="10" t="str"/>
-      <x:c r="M31" s="10" t="str"/>
+      <x:c r="L31" s="10" t="str">
+        <x:v>璀璨Ai剧场</x:v>
+      </x:c>
+      <x:c r="M31" s="10" t="str">
+        <x:v>张兰芬操劳半生，是旁人羡慕的当家主母。她为李家养育四子两女，持家有道、将家中大小事务打理得井井有条。半生付出尽数落空，张兰芬郁结于心，最终含恨病逝医院。一朝重生，她回到所有遗憾尚未发生之时，彻底看透人心，决意放下执念，好好为自己活一次。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3644,16 +3821,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
-        <x:v>1.6</x:v>
+        <x:v>1.7</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F2" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>2026-09-15 05-08</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3661,22 +3838,22 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>征地我秒签跑路，全村笑我半年</x:v>
+        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
       </x:c>
       <x:c r="C3" s="11" t="n">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
-        <x:v>2.3</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F3" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>2026-09-15 05-08</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -3684,22 +3861,22 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>重生三天前，我用水泥封死地下室</x:v>
+        <x:v>征地我秒签跑路，全村笑我半年</x:v>
       </x:c>
       <x:c r="C4" s="11" t="n">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>10.6</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F4" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F4" s="11" t="n">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>2026-09-15 05-08</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3713,16 +3890,16 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>7.2</x:v>
+        <x:v>7.3</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F5" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>2026-09-15 05-08</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -3730,22 +3907,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>今晚查寝，别开门</x:v>
+        <x:v>重生三天前，我用水泥封死地下室</x:v>
       </x:c>
       <x:c r="C6" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>6.4</x:v>
+        <x:v>11.7</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F6" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>2026-09-15 05-08</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3753,22 +3930,22 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
+        <x:v>今晚查寝，别开门</x:v>
       </x:c>
       <x:c r="C7" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>5.6</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F7" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>2026-09-15 05-08</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -3776,22 +3953,22 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
+        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
       </x:c>
       <x:c r="C8" s="11" t="n">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>7.1</x:v>
+        <x:v>8.7</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>2026-09-15 05-08</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3799,22 +3976,22 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>破库房的秘密</x:v>
+        <x:v>泰城错嫁</x:v>
       </x:c>
       <x:c r="C9" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>12.4</x:v>
+        <x:v>12.2</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -3822,22 +3999,22 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
+        <x:v>退婚后我在七零赚钱养家致富</x:v>
       </x:c>
       <x:c r="C10" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>11.7</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F10" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>2026-09-15 05-08</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -3845,22 +4022,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>退婚后我在七零赚钱养家致富</x:v>
+        <x:v>破库房的秘密</x:v>
       </x:c>
       <x:c r="C11" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>10.2</x:v>
+        <x:v>13.8</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
-        <x:v>2026-09-14 22-12</x:v>
+        <x:v>2026-09-15 09-11</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -3868,22 +4045,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>锦书迟</x:v>
+        <x:v>一墙之隔，皆是人心</x:v>
       </x:c>
       <x:c r="C12" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>13.4</x:v>
+        <x:v>13.9</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G12" s="11" t="str">
-        <x:v>2026-09-15 02-44</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -3891,22 +4068,22 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>泰城错嫁</x:v>
+        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
       </x:c>
       <x:c r="C13" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>12.5</x:v>
+        <x:v>11.6</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="G13" s="11" t="str">
-        <x:v>2026-09-15 05-08</x:v>
+        <x:v>2026-09-15 06-08</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -3914,22 +4091,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>一墙之隔，皆是人心</x:v>
+        <x:v>惊絮无声：傻女的绝杀</x:v>
       </x:c>
       <x:c r="C14" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>13.2</x:v>
+        <x:v>12.4</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G14" s="11" t="str">
-        <x:v>2026-09-15 05-08</x:v>
+        <x:v>2026-09-15 06-08</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -3937,22 +4114,22 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>今天开始做裴总</x:v>
+        <x:v>离家十年，回来女儿被换了</x:v>
       </x:c>
       <x:c r="C15" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>11.2</x:v>
+        <x:v>10.3</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F15" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G15" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -3960,22 +4137,22 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>惊絮无声：傻女的绝杀</x:v>
+        <x:v>三分钱的取舍</x:v>
       </x:c>
       <x:c r="C16" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>12.5</x:v>
+        <x:v>13.5</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G16" s="11" t="str">
-        <x:v>2026-09-15 05-08</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -3983,22 +4160,22 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>反派拿捏！</x:v>
+        <x:v>锦书迟</x:v>
       </x:c>
       <x:c r="C17" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>14.6</x:v>
+        <x:v>12.9</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F17" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G17" s="11" t="str">
-        <x:v>2026-09-14 20-13</x:v>
+        <x:v>2026-09-15 02-44</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -4006,22 +4183,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>离家十年，回来女儿被换了</x:v>
+        <x:v>今天开始做裴总</x:v>
       </x:c>
       <x:c r="C18" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>9.6</x:v>
+        <x:v>12.9</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="G18" s="11" t="str">
-        <x:v>2026-09-15 05-08</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -4052,22 +4229,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>三分钱的取舍</x:v>
+        <x:v>青牛引泉来</x:v>
       </x:c>
       <x:c r="C20" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>12.1</x:v>
+        <x:v>9.6</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G20" s="11" t="str">
-        <x:v>2026-09-15 05-08</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -4075,22 +4252,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
+        <x:v>反派拿捏！</x:v>
       </x:c>
       <x:c r="C21" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>15.7</x:v>
+        <x:v>14.7</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G21" s="11" t="str">
-        <x:v>2026-09-14 06-11</x:v>
+        <x:v>2026-09-14 20-13</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -4098,22 +4275,22 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>退婚从抢我车位开始</x:v>
+        <x:v>穿书后我带萌宝上门认爹</x:v>
       </x:c>
       <x:c r="C22" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>14.3</x:v>
+        <x:v>15.7</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G22" s="11" t="str">
-        <x:v>2026-09-14 20-18</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -4144,22 +4321,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>回到零四年进军彩铃界</x:v>
+        <x:v>不靠谱爸妈很靠谱</x:v>
       </x:c>
       <x:c r="C24" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>16.6</x:v>
+        <x:v>15.5</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G24" s="11" t="str">
-        <x:v>2026-09-14 12-34</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -4167,22 +4344,22 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>河箱送福来</x:v>
+        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
       </x:c>
       <x:c r="C25" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>14.9</x:v>
+        <x:v>3.4</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G25" s="11" t="str">
-        <x:v>2026-09-14 20-18</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -4190,22 +4367,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>装傻下山</x:v>
+        <x:v>回到零四年进军彩铃界</x:v>
       </x:c>
       <x:c r="C26" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>8.2</x:v>
+        <x:v>16.6</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G26" s="11" t="str">
-        <x:v>2026-09-14 04-11</x:v>
+        <x:v>2026-09-14 12-34</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -4213,22 +4390,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>穿越60我有空间不愁吃喝</x:v>
+        <x:v>装傻下山</x:v>
       </x:c>
       <x:c r="C27" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>15.7</x:v>
+        <x:v>8.2</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str">
-        <x:v>2026-09-14 20-18</x:v>
+        <x:v>2026-09-14 04-11</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -4236,22 +4413,22 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>重生后我守住全村</x:v>
+        <x:v>搬进江景房，老公每晚对着鱼缸坐两小时</x:v>
       </x:c>
       <x:c r="C28" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
-        <x:v>8.6</x:v>
+        <x:v>6.5</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="F28" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G28" s="11" t="str">
-        <x:v>2026-09-14 20-18</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -4259,22 +4436,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>青牛引泉来</x:v>
+        <x:v>四个崽崽瞒不住了</x:v>
       </x:c>
       <x:c r="C29" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>15.5</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str">
-        <x:v>2026-09-15 05-08</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -4282,22 +4459,22 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>离婚那天我多了个痞帅老爹</x:v>
+        <x:v>穿越60我有空间不愁吃喝</x:v>
       </x:c>
       <x:c r="C30" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>11.2</x:v>
+        <x:v>15.7</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G30" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-14 20-18</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -4305,22 +4482,22 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>一张废票毁了她</x:v>
+        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
       </x:c>
       <x:c r="C31" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
-        <x:v>14.5</x:v>
+        <x:v>12.2</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G31" s="11" t="str">
-        <x:v>2026-09-14 10-32</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -4328,22 +4505,22 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="10" t="str">
-        <x:v>不靠谱爸妈很靠谱</x:v>
+        <x:v>闪婚老公有点野</x:v>
       </x:c>
       <x:c r="C32" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D32" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>14.6</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G32" s="11" t="str">
-        <x:v>2026-09-15 05-08</x:v>
+        <x:v>2026-09-15 06-54</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -4351,22 +4528,22 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="10" t="str">
-        <x:v>穿书后我带萌宝上门认爹</x:v>
+        <x:v>一张废票毁了她</x:v>
       </x:c>
       <x:c r="C33" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D33" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F33" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G33" s="11" t="str">
-        <x:v>2026-09-15 05-08</x:v>
+        <x:v>2026-09-15 05-52</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -4374,22 +4551,22 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="10" t="str">
-        <x:v>这桌团圆饭，我不做了</x:v>
+        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
       </x:c>
       <x:c r="C34" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D34" s="11" t="n">
-        <x:v>16.5</x:v>
+        <x:v>17.2</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F34" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G34" s="11" t="str">
-        <x:v>2026-09-14 03-11</x:v>
+        <x:v>2026-09-14 06-11</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -4397,22 +4574,22 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="10" t="str">
-        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
+        <x:v>重生后我守住全村</x:v>
       </x:c>
       <x:c r="C35" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D35" s="11" t="n">
-        <x:v>8.7</x:v>
+        <x:v>5.8</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F35" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G35" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-14 20-18</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -4420,22 +4597,22 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="10" t="str">
-        <x:v>人人都说她娇气，出事她护我到底</x:v>
+        <x:v>离婚那天我多了个痞帅老爹</x:v>
       </x:c>
       <x:c r="C36" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
-        <x:v>5.3</x:v>
+        <x:v>11.2</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="G36" s="11" t="str">
-        <x:v>2026-09-14 12-34</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -4443,22 +4620,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="10" t="str">
-        <x:v>我家后山藏真龙</x:v>
+        <x:v>这桌团圆饭，我不做了</x:v>
       </x:c>
       <x:c r="C37" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D37" s="11" t="n">
-        <x:v>5.7</x:v>
+        <x:v>16.5</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G37" s="11" t="str">
-        <x:v>2026-09-14 09-24</x:v>
+        <x:v>2026-09-14 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -4466,22 +4643,22 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="10" t="str">
-        <x:v>不负恩情不负卿</x:v>
+        <x:v>重生80，救下神雕后我带村民走出大山</x:v>
       </x:c>
       <x:c r="C38" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D38" s="11" t="n">
-        <x:v>9.7</x:v>
+        <x:v>18.2</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F38" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G38" s="11" t="str">
-        <x:v>2026-09-14 10-32</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -4489,22 +4666,22 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="10" t="str">
-        <x:v>一针绣出自己的路</x:v>
+        <x:v>辣媳进门，我给公婆撑腰</x:v>
       </x:c>
       <x:c r="C39" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D39" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G39" s="11" t="str">
-        <x:v>2026-09-13 21-11</x:v>
+        <x:v>2026-09-15 06-08</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -4512,22 +4689,22 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="10" t="str">
-        <x:v>谢谢爸妈的穷养现在我富了</x:v>
+        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
       </x:c>
       <x:c r="C40" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D40" s="11" t="n">
-        <x:v>10.7</x:v>
+        <x:v>8.7</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G40" s="11" t="str">
-        <x:v>2026-09-14 02-11</x:v>
+        <x:v>2026-09-15 01-59</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -4535,22 +4712,22 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="10" t="str">
-        <x:v>那块玉，带我们回家</x:v>
+        <x:v>人人都说她娇气，出事她护我到底</x:v>
       </x:c>
       <x:c r="C41" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D41" s="11" t="n">
-        <x:v>11.3</x:v>
+        <x:v>5.3</x:v>
       </x:c>
       <x:c r="E41" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F41" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G41" s="11" t="str">
-        <x:v>2026-09-14 09-24</x:v>
+        <x:v>2026-09-14 12-34</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -4558,22 +4735,22 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B42" s="10" t="str">
-        <x:v>拂衣震九州</x:v>
+        <x:v>我家后山藏真龙</x:v>
       </x:c>
       <x:c r="C42" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D42" s="11" t="n">
-        <x:v>10.3</x:v>
+        <x:v>5.7</x:v>
       </x:c>
       <x:c r="E42" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F42" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G42" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-14 09-24</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -4581,22 +4758,22 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" s="10" t="str">
-        <x:v>闪婚老公有点野</x:v>
+        <x:v>不负恩情不负卿</x:v>
       </x:c>
       <x:c r="C43" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D43" s="11" t="n">
-        <x:v>11.3</x:v>
+        <x:v>9.7</x:v>
       </x:c>
       <x:c r="E43" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F43" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G43" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-14 10-32</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -4604,22 +4781,22 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="10" t="str">
-        <x:v>大坝边寻回的真千金</x:v>
+        <x:v>谢谢爸妈的穷养现在我富了</x:v>
       </x:c>
       <x:c r="C44" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D44" s="11" t="n">
-        <x:v>12.7</x:v>
+        <x:v>10.7</x:v>
       </x:c>
       <x:c r="E44" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F44" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="G44" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-14 02-11</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -4627,22 +4804,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="10" t="str">
-        <x:v>山下是绝路，山上是生门</x:v>
+        <x:v>那块玉，带我们回家</x:v>
       </x:c>
       <x:c r="C45" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D45" s="11" t="n">
-        <x:v>14.3</x:v>
+        <x:v>11.3</x:v>
       </x:c>
       <x:c r="E45" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F45" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G45" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-14 09-24</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -4650,22 +4827,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B46" s="10" t="str">
-        <x:v>427元扳倒老油条</x:v>
+        <x:v>拂衣震九州</x:v>
       </x:c>
       <x:c r="C46" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D46" s="11" t="n">
-        <x:v>15.7</x:v>
+        <x:v>10.3</x:v>
       </x:c>
       <x:c r="E46" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F46" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G46" s="11" t="str">
-        <x:v>2026-09-14 20-18</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -4673,22 +4850,22 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B47" s="10" t="str">
-        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
+        <x:v>大坝边寻回的真千金</x:v>
       </x:c>
       <x:c r="C47" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D47" s="11" t="n">
-        <x:v>17.7</x:v>
+        <x:v>12.7</x:v>
       </x:c>
       <x:c r="E47" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F47" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G47" s="11" t="str">
-        <x:v>2026-09-15 02-44</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -4696,22 +4873,22 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B48" s="10" t="str">
-        <x:v>零元年终奖</x:v>
+        <x:v>山下是绝路，山上是生门</x:v>
       </x:c>
       <x:c r="C48" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D48" s="11" t="n">
-        <x:v>4.5</x:v>
+        <x:v>14.3</x:v>
       </x:c>
       <x:c r="E48" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F48" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G48" s="11" t="str">
-        <x:v>2026-09-13 22-11</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -4719,22 +4896,22 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B49" s="10" t="str">
-        <x:v>我SSS级狂龙，出世即无敌</x:v>
+        <x:v>退婚从抢我车位开始</x:v>
       </x:c>
       <x:c r="C49" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D49" s="11" t="n">
-        <x:v>5.5</x:v>
+        <x:v>15.3</x:v>
       </x:c>
       <x:c r="E49" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F49" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G49" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-14 20-18</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -4742,13 +4919,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B50" s="10" t="str">
-        <x:v>一碗人间赴景深</x:v>
+        <x:v>我SSS级狂龙，出世即无敌</x:v>
       </x:c>
       <x:c r="C50" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D50" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>5.5</x:v>
       </x:c>
       <x:c r="E50" s="11" t="n">
         <x:v>5</x:v>
@@ -4757,7 +4934,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G50" s="11" t="str">
-        <x:v>2026-09-14 09-24</x:v>
+        <x:v>2026-09-15 01-59</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -4765,19 +4942,19 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B51" s="10" t="str">
-        <x:v>白鹿照归途</x:v>
+        <x:v>一碗人间赴景深</x:v>
       </x:c>
       <x:c r="C51" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D51" s="11" t="n">
-        <x:v>12.5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E51" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F51" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G51" s="11" t="str">
         <x:v>2026-09-14 09-24</x:v>
@@ -7726,8 +7903,12 @@
       <x:c r="G47" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H47" s="11" t="str"/>
-      <x:c r="I47" s="10" t="str"/>
+      <x:c r="H47" s="11" t="str">
+        <x:v>已上榜</x:v>
+      </x:c>
+      <x:c r="I47" s="10" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
       <x:c r="J47" s="10" t="str">
         <x:v>女孩林知晚回到命运转折的关键节点。她凭借智慧与勇气，敏锐察觉家中隐患，冷静引导家人、寻求帮助，用爱守护姐姐与全家。在共同努力下危机化解、正义伸张，一家人愈发珍视彼此，并且帮助到了更多有同样遭遇的人，最后迎来温暖安宁的幸福生活。</x:v>
       </x:c>
@@ -7832,8 +8013,12 @@
       <x:c r="G50" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H50" s="11" t="str"/>
-      <x:c r="I50" s="10" t="str"/>
+      <x:c r="H50" s="11" t="str">
+        <x:v>已上榜</x:v>
+      </x:c>
+      <x:c r="I50" s="10" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
       <x:c r="J50" s="10" t="str">
         <x:v>宋知遥为侄女宋雨欣付出十三年，却在毕业宴上遭其当众羞辱并拒绝感恩。宋知遥看清嫂嫂一家的贪婪嘴脸，果断停卡断供，收回承诺的房产。面对侄女的道德绑架与法律纠纷，她坚守底线，通过法律途径维权，最终切断所有不良羁绊，守护亲生女儿，重启清净生活。</x:v>
       </x:c>
@@ -9442,7 +9627,7 @@
         <x:v>已上榜</x:v>
       </x:c>
       <x:c r="I97" s="10" t="str">
-        <x:v>2026-09-12、2026-09-13</x:v>
+        <x:v>2026-09-12、2026-09-13、2026-09-15</x:v>
       </x:c>
       <x:c r="J97" s="10" t="str">
         <x:v>顾佑璃前世因阻拦哥哥救妹遭全家怨恨。重生后她选择放手，导致哥哥重伤失声、事业尽毁，家族陷入混乱。面对家人的道德绑架与诉讼勒索，顾佑璃不再妥协，公开火灾真相并切断经济供养。最终她摆脱原生家庭束缚，在养母支持下开启全新人生，实现自我救赎。</x:v>
@@ -19525,8 +19710,12 @@
       <x:c r="G47" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H47" s="11" t="str"/>
-      <x:c r="I47" s="10" t="str"/>
+      <x:c r="H47" s="11" t="str">
+        <x:v>已上榜</x:v>
+      </x:c>
+      <x:c r="I47" s="10" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
       <x:c r="J47" s="10" t="str">
         <x:v>女孩林知晚回到命运转折的关键节点。她凭借智慧与勇气，敏锐察觉家中隐患，冷静引导家人、寻求帮助，用爱守护姐姐与全家。在共同努力下危机化解、正义伸张，一家人愈发珍视彼此，并且帮助到了更多有同样遭遇的人，最后迎来温暖安宁的幸福生活。</x:v>
       </x:c>
@@ -19597,8 +19786,12 @@
       <x:c r="G49" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H49" s="11" t="str"/>
-      <x:c r="I49" s="10" t="str"/>
+      <x:c r="H49" s="11" t="str">
+        <x:v>已上榜</x:v>
+      </x:c>
+      <x:c r="I49" s="10" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
       <x:c r="J49" s="10" t="str">
         <x:v>宋知遥为侄女宋雨欣付出十三年，却在毕业宴上遭其当众羞辱并拒绝感恩。宋知遥看清嫂嫂一家的贪婪嘴脸，果断停卡断供，收回承诺的房产。面对侄女的道德绑架与法律纠纷，她坚守底线，通过法律途径维权，最终切断所有不良羁绊，守护亲生女儿，重启清净生活。</x:v>
       </x:c>
@@ -21253,7 +21446,7 @@
         <x:v>已上榜</x:v>
       </x:c>
       <x:c r="I97" s="10" t="str">
-        <x:v>2026-09-12、2026-09-13</x:v>
+        <x:v>2026-09-12、2026-09-13、2026-09-15</x:v>
       </x:c>
       <x:c r="J97" s="10" t="str">
         <x:v>顾佑璃前世因阻拦哥哥救妹遭全家怨恨。重生后她选择放手，导致哥哥重伤失声、事业尽毁，家族陷入混乱。面对家人的道德绑架与诉讼勒索，顾佑璃不再妥协，公开火灾真相并切断经济供养。最终她摆脱原生家庭束缚，在养母支持下开启全新人生，实现自我救赎。</x:v>
@@ -29800,10 +29993,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>904</x:v>
+        <x:v>916</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>52.3%</x:v>
+        <x:v>52.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -29814,7 +30007,7 @@
         <x:v>476</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>27.5%</x:v>
+        <x:v>27.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -29825,7 +30018,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>20.2%</x:v>
+        <x:v>20.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
@@ -29849,7 +30042,7 @@
         <x:v>30-49集</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
         <x:v>11.2%</x:v>
@@ -29860,10 +30053,10 @@
         <x:v>50-79集</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>681</x:v>
+        <x:v>684</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>42.9%</x:v>
+        <x:v>42.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -29882,10 +30075,10 @@
         <x:v>100集以上</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>530</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>33.4%</x:v>
+        <x:v>33.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
@@ -29909,10 +30102,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>760</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>44.0%</x:v>
+        <x:v>43.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -29920,7 +30113,7 @@
         <x:v>婚姻/情感</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>311</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
         <x:v>18.0%</x:v>
@@ -29931,7 +30124,7 @@
         <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
         <x:v>9.2%</x:v>
@@ -29939,7 +30132,7 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="10" t="str">
-        <x:v>家庭伦理/萌宝</x:v>
+        <x:v>年代怀旧/种田囤货</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
         <x:v>149</x:v>
@@ -29950,10 +30143,10 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="10" t="str">
-        <x:v>年代怀旧/种田囤货</x:v>
+        <x:v>家庭伦理/萌宝</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
         <x:v>8.6%</x:v>
@@ -29964,7 +30157,7 @@
         <x:v>战神/异能/爽文</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
         <x:v>8.4%</x:v>
@@ -29975,10 +30168,10 @@
         <x:v>现实反转/人性</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>6.3%</x:v>
+        <x:v>6.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -29997,10 +30190,10 @@
         <x:v>逆袭/打脸</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>4.7%</x:v>
+        <x:v>4.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -30008,7 +30201,7 @@
         <x:v>都市职场</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
         <x:v>4.2%</x:v>
@@ -30032,7 +30225,7 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="10" t="str">
-        <x:v>上榜31次</x:v>
+        <x:v>上榜32次</x:v>
       </x:c>
       <x:c r="B29" s="11" t="n">
         <x:v>1</x:v>
@@ -30057,18 +30250,18 @@
         <x:v>上榜28次</x:v>
       </x:c>
       <x:c r="B31" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C31" s="11" t="str">
-        <x:v>0.1%</x:v>
+        <x:v>0.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="10" t="str">
-        <x:v>上榜27次</x:v>
+        <x:v>上榜26次</x:v>
       </x:c>
       <x:c r="B32" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C32" s="11" t="str">
         <x:v>0.1%</x:v>
@@ -30076,7 +30269,7 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="10" t="str">
-        <x:v>上榜26次</x:v>
+        <x:v>上榜25次</x:v>
       </x:c>
       <x:c r="B33" s="11" t="n">
         <x:v>1</x:v>
@@ -30087,10 +30280,10 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="10" t="str">
-        <x:v>上榜25次</x:v>
+        <x:v>上榜23次</x:v>
       </x:c>
       <x:c r="B34" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C34" s="11" t="str">
         <x:v>0.1%</x:v>
@@ -30098,10 +30291,10 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="10" t="str">
-        <x:v>上榜23次</x:v>
+        <x:v>上榜22次</x:v>
       </x:c>
       <x:c r="B35" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C35" s="11" t="str">
         <x:v>0.1%</x:v>
@@ -30109,7 +30302,7 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="10" t="str">
-        <x:v>上榜22次</x:v>
+        <x:v>上榜21次</x:v>
       </x:c>
       <x:c r="B36" s="11" t="n">
         <x:v>2</x:v>
@@ -30120,7 +30313,7 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="10" t="str">
-        <x:v>上榜21次</x:v>
+        <x:v>上榜20次</x:v>
       </x:c>
       <x:c r="B37" s="11" t="n">
         <x:v>2</x:v>
@@ -30131,7 +30324,7 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="10" t="str">
-        <x:v>上榜20次</x:v>
+        <x:v>上榜19次</x:v>
       </x:c>
       <x:c r="B38" s="11" t="n">
         <x:v>2</x:v>
@@ -30142,21 +30335,21 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="10" t="str">
-        <x:v>上榜19次</x:v>
+        <x:v>上榜18次</x:v>
       </x:c>
       <x:c r="B39" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C39" s="11" t="str">
-        <x:v>0.1%</x:v>
+        <x:v>0.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="10" t="str">
-        <x:v>上榜18次</x:v>
+        <x:v>上榜17次</x:v>
       </x:c>
       <x:c r="B40" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C40" s="11" t="str">
         <x:v>0.2%</x:v>
@@ -30164,273 +30357,273 @@
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="10" t="str">
-        <x:v>上榜17次</x:v>
+        <x:v>上榜16次</x:v>
       </x:c>
       <x:c r="B41" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C41" s="11" t="str">
-        <x:v>0.1%</x:v>
+        <x:v>0.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="10" t="str">
-        <x:v>上榜16次</x:v>
+        <x:v>上榜15次</x:v>
       </x:c>
       <x:c r="B42" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C42" s="11" t="str">
-        <x:v>0.3%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="10" t="str">
-        <x:v>上榜15次</x:v>
+        <x:v>上榜14次</x:v>
       </x:c>
       <x:c r="B43" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C43" s="11" t="str">
-        <x:v>0.4%</x:v>
+        <x:v>0.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="10" t="str">
-        <x:v>上榜14次</x:v>
+        <x:v>上榜13次</x:v>
       </x:c>
       <x:c r="B44" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C44" s="11" t="str">
-        <x:v>0.8%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="10" t="str">
-        <x:v>上榜13次</x:v>
+        <x:v>上榜12次</x:v>
       </x:c>
       <x:c r="B45" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C45" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>1.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="10" t="str">
-        <x:v>上榜12次</x:v>
+        <x:v>上榜11次</x:v>
       </x:c>
       <x:c r="B46" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C46" s="11" t="str">
-        <x:v>1.0%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="10" t="str">
-        <x:v>上榜11次</x:v>
+        <x:v>上榜10次</x:v>
       </x:c>
       <x:c r="B47" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C47" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>1.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="10" t="str">
-        <x:v>上榜10次</x:v>
+        <x:v>上榜9次</x:v>
       </x:c>
       <x:c r="B48" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C48" s="11" t="str">
-        <x:v>1.2%</x:v>
+        <x:v>1.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="10" t="str">
-        <x:v>上榜9次</x:v>
+        <x:v>上榜8次</x:v>
       </x:c>
       <x:c r="B49" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C49" s="11" t="str">
-        <x:v>1.9%</x:v>
+        <x:v>2.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="10" t="str">
-        <x:v>上榜8次</x:v>
+        <x:v>上榜7次</x:v>
       </x:c>
       <x:c r="B50" s="11" t="n">
-        <x:v>49</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C50" s="11" t="str">
-        <x:v>2.8%</x:v>
+        <x:v>2.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="10" t="str">
-        <x:v>上榜7次</x:v>
+        <x:v>上榜6次</x:v>
       </x:c>
       <x:c r="B51" s="11" t="n">
-        <x:v>37</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C51" s="11" t="str">
-        <x:v>2.1%</x:v>
+        <x:v>3.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="10" t="str">
-        <x:v>上榜6次</x:v>
+        <x:v>上榜5次</x:v>
       </x:c>
       <x:c r="B52" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C52" s="11" t="str">
-        <x:v>3.4%</x:v>
+        <x:v>4.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="10" t="str">
-        <x:v>上榜5次</x:v>
+        <x:v>上榜4次</x:v>
       </x:c>
       <x:c r="B53" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C53" s="11" t="str">
-        <x:v>4.2%</x:v>
+        <x:v>6.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="10" t="str">
-        <x:v>上榜4次</x:v>
+        <x:v>上榜3次</x:v>
       </x:c>
       <x:c r="B54" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C54" s="11" t="str">
-        <x:v>6.2%</x:v>
+        <x:v>11.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="10" t="str">
-        <x:v>上榜3次</x:v>
+        <x:v>上榜2次</x:v>
       </x:c>
       <x:c r="B55" s="11" t="n">
-        <x:v>198</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="C55" s="11" t="str">
-        <x:v>11.5%</x:v>
+        <x:v>18.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="10" t="str">
-        <x:v>上榜2次</x:v>
+        <x:v>上榜1次</x:v>
       </x:c>
       <x:c r="B56" s="11" t="n">
-        <x:v>318</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="C56" s="11" t="str">
-        <x:v>18.4%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57">
-      <x:c r="A57" s="10" t="str">
-        <x:v>上榜1次</x:v>
-      </x:c>
-      <x:c r="B57" s="11" t="n">
-        <x:v>751</x:v>
-      </x:c>
-      <x:c r="C57" s="11" t="str">
-        <x:v>43.4%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" ht="22" customHeight="1">
-      <x:c r="A59" s="14" t="str">
+        <x:v>43.8%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="22" customHeight="1">
+      <x:c r="A58" s="14" t="str">
         <x:v>版权类型分布</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" ht="24" customHeight="1">
-      <x:c r="A60" s="5" t="str">
+    <x:row r="59" ht="24" customHeight="1">
+      <x:c r="A59" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B60" t="str">
+      <x:c r="B59" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C60" t="str">
+      <x:c r="C59" t="str">
         <x:v>占比</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="10" t="str">
+        <x:v>CP自营</x:v>
+      </x:c>
+      <x:c r="B60" s="11" t="n">
+        <x:v>1151</x:v>
+      </x:c>
+      <x:c r="C60" s="11" t="str">
+        <x:v>66.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="10" t="str">
-        <x:v>CP自营</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="B61" s="11" t="n">
-        <x:v>1150</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="C61" s="11" t="str">
-        <x:v>66.5%</x:v>
+        <x:v>33.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>CP托管</x:v>
       </x:c>
       <x:c r="B62" s="11" t="n">
-        <x:v>568</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C62" s="11" t="str">
-        <x:v>32.9%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="10" t="str">
-        <x:v>CP托管</x:v>
+        <x:v>番茄原创</x:v>
       </x:c>
       <x:c r="B63" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C63" s="11" t="str">
-        <x:v>0.5%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64">
-      <x:c r="A64" s="10" t="str">
-        <x:v>番茄原创</x:v>
-      </x:c>
-      <x:c r="B64" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C64" s="11" t="str">
         <x:v>0.1%</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" ht="22" customHeight="1">
-      <x:c r="A66" s="14" t="str">
+    <x:row r="65" ht="22" customHeight="1">
+      <x:c r="A65" s="14" t="str">
         <x:v>发布抖音号TOP15·上榜次数</x:v>
       </x:c>
     </x:row>
-    <x:row r="67" ht="24" customHeight="1">
-      <x:c r="A67" s="5" t="str">
+    <x:row r="66" ht="24" customHeight="1">
+      <x:c r="A66" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B67" t="str">
+      <x:c r="B66" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C67" t="str">
+      <x:c r="C66" t="str">
         <x:v>占比</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="10" t="str">
+        <x:v>孤灵剧场</x:v>
+      </x:c>
+      <x:c r="B67" s="11" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C67" s="11" t="str">
+        <x:v>1.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
+        <x:v>番荔枝剧场</x:v>
       </x:c>
       <x:c r="B68" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C68" s="11" t="str">
         <x:v>1.1%</x:v>
@@ -30438,29 +30631,29 @@
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="10" t="str">
-        <x:v>番荔枝剧场</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="B69" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C69" s="11" t="str">
-        <x:v>1.1%</x:v>
+        <x:v>0.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>渲渲动画</x:v>
       </x:c>
       <x:c r="B70" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C70" s="11" t="str">
-        <x:v>0.9%</x:v>
+        <x:v>0.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="10" t="str">
-        <x:v>渲渲动画</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="B71" s="11" t="n">
         <x:v>43</x:v>
@@ -30477,26 +30670,26 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="C72" s="11" t="str">
-        <x:v>0.8%</x:v>
+        <x:v>0.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>阅友动漫</x:v>
       </x:c>
       <x:c r="B73" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C73" s="11" t="str">
-        <x:v>0.7%</x:v>
+        <x:v>0.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="10" t="str">
-        <x:v>阅友动漫</x:v>
+        <x:v>左手良画</x:v>
       </x:c>
       <x:c r="B74" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C74" s="11" t="str">
         <x:v>0.6%</x:v>
@@ -30504,10 +30697,10 @@
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="10" t="str">
-        <x:v>左手良画</x:v>
+        <x:v>东山啊</x:v>
       </x:c>
       <x:c r="B75" s="11" t="n">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C75" s="11" t="str">
         <x:v>0.6%</x:v>
@@ -30515,21 +30708,21 @@
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="10" t="str">
-        <x:v>东山啊</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="B76" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C76" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>茉冉漫影</x:v>
       </x:c>
       <x:c r="B77" s="11" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C77" s="11" t="str">
         <x:v>0.5%</x:v>
@@ -30537,7 +30730,7 @@
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="10" t="str">
-        <x:v>茉冉漫影</x:v>
+        <x:v>在下轻北</x:v>
       </x:c>
       <x:c r="B78" s="11" t="n">
         <x:v>28</x:v>
@@ -30548,7 +30741,7 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="10" t="str">
-        <x:v>在下轻北</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="B79" s="11" t="n">
         <x:v>28</x:v>
@@ -30559,10 +30752,10 @@
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>壹琚-娜娜看剧</x:v>
       </x:c>
       <x:c r="B80" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C80" s="11" t="str">
         <x:v>0.5%</x:v>
@@ -30570,7 +30763,7 @@
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="10" t="str">
-        <x:v>壹琚-娜娜看剧</x:v>
+        <x:v>一张不够花</x:v>
       </x:c>
       <x:c r="B81" s="11" t="n">
         <x:v>27</x:v>
@@ -30579,47 +30772,47 @@
         <x:v>0.5%</x:v>
       </x:c>
     </x:row>
-    <x:row r="82">
-      <x:c r="A82" s="10" t="str">
-        <x:v>一张不够花</x:v>
-      </x:c>
-      <x:c r="B82" s="11" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C82" s="11" t="str">
-        <x:v>0.5%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" ht="22" customHeight="1">
-      <x:c r="A84" s="14" t="str">
+    <x:row r="83" ht="22" customHeight="1">
+      <x:c r="A83" s="14" t="str">
         <x:v>发布抖音号TOP15·上榜剧数</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" ht="24" customHeight="1">
-      <x:c r="A85" s="5" t="str">
+    <x:row r="84" ht="24" customHeight="1">
+      <x:c r="A84" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B85" t="str">
+      <x:c r="B84" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C85" t="str">
+      <x:c r="C84" t="str">
         <x:v>占比</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="B85" s="11" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C85" s="11" t="str">
+        <x:v>1.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="B86" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C86" s="11" t="str">
-        <x:v>1%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="B87" s="11" t="n">
         <x:v>9</x:v>
@@ -30630,10 +30823,10 @@
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="B88" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C88" s="11" t="str">
         <x:v>0.5%</x:v>
@@ -30641,7 +30834,7 @@
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="10" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>星漫世界</x:v>
       </x:c>
       <x:c r="B89" s="11" t="n">
         <x:v>8</x:v>
@@ -30652,29 +30845,29 @@
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="10" t="str">
-        <x:v>星漫世界</x:v>
+        <x:v>番荔枝剧场</x:v>
       </x:c>
       <x:c r="B90" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C90" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="10" t="str">
-        <x:v>番荔枝剧场</x:v>
+        <x:v>渲渲动画</x:v>
       </x:c>
       <x:c r="B91" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C91" s="11" t="str">
-        <x:v>0.4%</x:v>
+        <x:v>0.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="10" t="str">
-        <x:v>渲渲动画</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="B92" s="11" t="n">
         <x:v>6</x:v>
@@ -30685,7 +30878,7 @@
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>阅友动漫</x:v>
       </x:c>
       <x:c r="B93" s="11" t="n">
         <x:v>6</x:v>
@@ -30696,7 +30889,7 @@
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="10" t="str">
-        <x:v>阅友动漫</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="B94" s="11" t="n">
         <x:v>6</x:v>
@@ -30707,7 +30900,7 @@
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>至尊爽剧社</x:v>
       </x:c>
       <x:c r="B95" s="11" t="n">
         <x:v>6</x:v>
@@ -30760,91 +30953,91 @@
         <x:v>0.3%</x:v>
       </x:c>
     </x:row>
-    <x:row r="100">
-      <x:c r="A100" s="10" t="str">
-        <x:v>云间漫剧-玉川</x:v>
-      </x:c>
-      <x:c r="B100" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C100" s="11" t="str">
-        <x:v>0.3%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" ht="22" customHeight="1">
-      <x:c r="A102" s="14" t="str">
+    <x:row r="101" ht="22" customHeight="1">
+      <x:c r="A101" s="14" t="str">
         <x:v>付费榜主题分布</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" ht="24" customHeight="1">
-      <x:c r="A103" s="5" t="str">
+    <x:row r="102" ht="24" customHeight="1">
+      <x:c r="A102" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B103" t="str">
+      <x:c r="B102" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C103" t="str">
+      <x:c r="C102" t="str">
         <x:v>占比</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="10" t="str">
+        <x:v>婚姻/情感</x:v>
+      </x:c>
+      <x:c r="B103" s="11" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C103" s="11" t="str">
+        <x:v>19.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="10" t="str">
-        <x:v>婚姻/情感</x:v>
+        <x:v>家庭伦理/萌宝</x:v>
       </x:c>
       <x:c r="B104" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C104" s="11" t="str">
-        <x:v>19.0%</x:v>
+        <x:v>15.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="10" t="str">
-        <x:v>家庭伦理/萌宝</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="B105" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C105" s="11" t="str">
-        <x:v>15.0%</x:v>
+        <x:v>10.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="B106" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C106" s="11" t="str">
-        <x:v>10.0%</x:v>
+        <x:v>9.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>年代怀旧/种田</x:v>
       </x:c>
       <x:c r="B107" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C107" s="11" t="str">
-        <x:v>9.0%</x:v>
+        <x:v>7.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="10" t="str">
-        <x:v>年代怀旧/种田</x:v>
+        <x:v>现实反转/人性</x:v>
       </x:c>
       <x:c r="B108" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C108" s="11" t="str">
-        <x:v>7.0%</x:v>
+        <x:v>6.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="10" t="str">
-        <x:v>现实反转/人性</x:v>
+        <x:v>战神/异能</x:v>
       </x:c>
       <x:c r="B109" s="11" t="n">
         <x:v>6</x:v>
@@ -30855,23 +31048,12 @@
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="10" t="str">
-        <x:v>战神/异能</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="B110" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C110" s="11" t="str">
-        <x:v>6.0%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="111">
-      <x:c r="A111" s="10" t="str">
-        <x:v>美食治愈</x:v>
-      </x:c>
-      <x:c r="B111" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C111" s="11" t="str">
         <x:v>5.0%</x:v>
       </x:c>
     </x:row>
@@ -30881,10 +31063,10 @@
     <x:mergeCell ref="A7:C7"/>
     <x:mergeCell ref="A14:C14"/>
     <x:mergeCell ref="A27:C27"/>
-    <x:mergeCell ref="A59:C59"/>
-    <x:mergeCell ref="A66:C66"/>
-    <x:mergeCell ref="A84:C84"/>
-    <x:mergeCell ref="A102:C102"/>
+    <x:mergeCell ref="A58:C58"/>
+    <x:mergeCell ref="A65:C65"/>
+    <x:mergeCell ref="A83:C83"/>
+    <x:mergeCell ref="A101:C101"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R4bddc8602fc442df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="Re60a828efa544e15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="R4627770ba2624e26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="Raff4803ec86e4d59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP20剧重点跟踪" sheetId="5" r:id="R178e4f7395424abd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="6" r:id="R920ed71b4f94449a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="7" r:id="R4f42b613390e4086"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="8" r:id="R7b69fd7308fb41da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="9" r:id="Rcf663e34986c4187"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R43c0a638e8dc47c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="Re133275321e64075"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="Rbd5c0da5a1ff4519"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="Ra6d9e901b0ee4ede"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP20剧重点跟踪" sheetId="5" r:id="Refbd34bdf7914924"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="6" r:id="R0f197b7c460b40e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="7" r:id="Rd65b961dc504425e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="8" r:id="R8b4f7061e23f4bda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="9" r:id="R79a58076f2b44156"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1165,13 +1165,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B2" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
-        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
+        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>09-15 08:00</x:v>
+        <x:v>09-13 08:00</x:v>
       </x:c>
       <x:c r="E2" s="11" t="str"/>
       <x:c r="F2" s="11" t="str"/>
@@ -1182,7 +1182,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I2" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J2" s="10" t="str">
         <x:v>其他</x:v>
@@ -1194,7 +1194,7 @@
         <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="M2" s="10" t="str">
-        <x:v>沈清韵嫁入靖王府三年，王爷冷落，侧妃得宠。王爷当众许诺，谁先诞下儿子，便请封世子。苏氏先怀孕，沈清韵却发现自己怀的是龙凤胎，她隐瞒消息，买通太医推迟产期，忍痛让苏氏先产子。王爷果然请封庶长子为世子，折子递入宗人府。受理之后，沈清韵才发动，生下龙凤胎。太后与皇上视为祥瑞，下旨赐嫡子承恩为靖王世子、嫡女承华为安乐郡主。王爷措手不及，苏氏地位一落千丈。而沈清韵知道，这只是第一步。</x:v>
+        <x:v>大晋七公主沈令仪，自幼被冷落于听竹宫，沉默藏锋，苟全性命。宫宴之上，太子带回的秦照雪笑盈盈提议将她送去北狄和亲。满殿以为皇帝会点头，他却掷出“废太子”三字。一夜之间，沈令仪被推到台前。北狄求和的急报恰在此时入京——与她方才所言分毫不差。可当她回望母亲遗下的那半卷秘策时，才发现这局棋，早在二十年前就已落子。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1202,13 +1202,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
-        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
+        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>09-13 08:00</x:v>
+        <x:v>09-15 08:00</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str"/>
       <x:c r="F3" s="11" t="str"/>
@@ -1219,7 +1219,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I3" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str">
         <x:v>其他</x:v>
@@ -1231,7 +1231,7 @@
         <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="M3" s="10" t="str">
-        <x:v>大晋七公主沈令仪，自幼被冷落于听竹宫，沉默藏锋，苟全性命。宫宴之上，太子带回的秦照雪笑盈盈提议将她送去北狄和亲。满殿以为皇帝会点头，他却掷出“废太子”三字。一夜之间，沈令仪被推到台前。北狄求和的急报恰在此时入京——与她方才所言分毫不差。可当她回望母亲遗下的那半卷秘策时，才发现这局棋，早在二十年前就已落子。</x:v>
+        <x:v>沈清韵嫁入靖王府三年，王爷冷落，侧妃得宠。王爷当众许诺，谁先诞下儿子，便请封世子。苏氏先怀孕，沈清韵却发现自己怀的是龙凤胎，她隐瞒消息，买通太医推迟产期，忍痛让苏氏先产子。王爷果然请封庶长子为世子，折子递入宗人府。受理之后，沈清韵才发动，生下龙凤胎。太后与皇上视为祥瑞，下旨赐嫡子承恩为靖王世子、嫡女承华为安乐郡主。王爷措手不及，苏氏地位一落千丈。而沈清韵知道，这只是第一步。</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1239,13 +1239,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
-        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
+        <x:v>重生80，救下神雕后我带村民走出大山</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>09-13 09:58</x:v>
+        <x:v>09-13 09:00</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str"/>
       <x:c r="F4" s="11" t="str"/>
@@ -1256,19 +1256,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I4" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="J4" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K4" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="L4" s="11" t="str">
-        <x:v>创想剧场</x:v>
+        <x:v>拾光漫漫</x:v>
       </x:c>
       <x:c r="M4" s="10" t="str">
-        <x:v>游戏公会会长林小勇筹备婚礼，却在婚宴上遭遇未婚妻临时加价逼婚。危急时刻，几位相交多年的游戏老友现身力挺他，林小勇果断取消婚礼。之后他搬进好友赠送的别墅，与陈董的两个女儿渐渐熟识。同学聚会上，众人见识到林小勇不一般的际遇。平静日子没过多久，当年游戏里的宿敌将出席游戏八周年嘉年华，一众老友决定赴约，一场新旧对决即将开启。</x:v>
+        <x:v>林大山遭人为意外，意外重生回到1980年。前世他错信爱人落得凄惨下场，重生后果断当众退婚。机缘巧合救下受伤的灵智神雕金羽，还遇见落难善良的白秋月。他携手知恩图报的神雕，依托卧龙山的资源，发掘名贵药材，抓住时代发展机遇。面对同行刁难，林大山坚守本心，凭借智慧与实干，包下荒山兴办药材加工坊。他善待家人，带领乡里百姓勤劳致富，在八十年代的时代浪潮里，靠着双手改写命运，收获美满爱情与事业。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1276,13 +1276,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
-        <x:v>重生80，救下神雕后我带村民走出大山</x:v>
+        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>09-13 09:00</x:v>
+        <x:v>09-13 09:58</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str"/>
       <x:c r="F5" s="11" t="str"/>
@@ -1293,19 +1293,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I5" s="11" t="n">
-        <x:v>187</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J5" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K5" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L5" s="11" t="str">
-        <x:v>拾光漫漫</x:v>
+        <x:v>创想剧场</x:v>
       </x:c>
       <x:c r="M5" s="10" t="str">
-        <x:v>林大山遭人为意外，意外重生回到1980年。前世他错信爱人落得凄惨下场，重生后果断当众退婚。机缘巧合救下受伤的灵智神雕金羽，还遇见落难善良的白秋月。他携手知恩图报的神雕，依托卧龙山的资源，发掘名贵药材，抓住时代发展机遇。面对同行刁难，林大山坚守本心，凭借智慧与实干，包下荒山兴办药材加工坊。他善待家人，带领乡里百姓勤劳致富，在八十年代的时代浪潮里，靠着双手改写命运，收获美满爱情与事业。</x:v>
+        <x:v>游戏公会会长林小勇筹备婚礼，却在婚宴上遭遇未婚妻临时加价逼婚。危急时刻，几位相交多年的游戏老友现身力挺他，林小勇果断取消婚礼。之后他搬进好友赠送的别墅，与陈董的两个女儿渐渐熟识。同学聚会上，众人见识到林小勇不一般的际遇。平静日子没过多久，当年游戏里的宿敌将出席游戏八周年嘉年华，一众老友决定赴约，一场新旧对决即将开启。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1313,13 +1313,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
+        <x:v>乡宴见人心</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>09-15 00:08</x:v>
+        <x:v>09-13 17:12</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str"/>
       <x:c r="F6" s="11" t="str"/>
@@ -1330,19 +1330,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I6" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J6" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K6" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="L6" s="11" t="str">
-        <x:v>桃子动漫剧场</x:v>
+        <x:v>黑白动漫</x:v>
       </x:c>
       <x:c r="M6" s="10" t="str">
-        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
+        <x:v>高满仓在赵家大院办了八年流水席，十里八村都认他的手艺。眼看生意越来越旺，院主赵金贵突然把租金翻倍，还要按桌抽钱。高满仓干脆带着人和家伙搬进镇外的废米厂，从头再来。赵金贵以为守着大院就守住了客人，靠低价抢生意，却越省越狠。一边是稳稳当当把席办好，一边是亲手砸掉自己的口碑，这场较量最后看的是院子，还是人心。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1350,13 +1350,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
-        <x:v>小妹初长成</x:v>
+        <x:v>四个崽崽瞒不住了</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>2026-09-13</x:v>
+        <x:v>09-15 00:08</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str"/>
       <x:c r="F7" s="11" t="str"/>
@@ -1366,28 +1366,34 @@
       <x:c r="H7" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="str"/>
+      <x:c r="I7" s="11" t="n">
+        <x:v>124</x:v>
+      </x:c>
       <x:c r="J7" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K7" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="str"/>
-      <x:c r="M7" s="10" t="str"/>
+      <x:c r="L7" s="11" t="str">
+        <x:v>桃子动漫剧场</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="str">
+        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
-        <x:v>乡宴见人心</x:v>
+        <x:v>晚棠知归，七年终见你</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>09-13 17:12</x:v>
+        <x:v>09-14 11:26</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str"/>
       <x:c r="F8" s="11" t="str"/>
@@ -1398,19 +1404,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J8" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K8" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L8" s="11" t="str">
-        <x:v>黑白动漫</x:v>
+        <x:v>喵琪琪追剧</x:v>
       </x:c>
       <x:c r="M8" s="10" t="str">
-        <x:v>高满仓在赵家大院办了八年流水席，十里八村都认他的手艺。眼看生意越来越旺，院主赵金贵突然把租金翻倍，还要按桌抽钱。高满仓干脆带着人和家伙搬进镇外的废米厂，从头再来。赵金贵以为守着大院就守住了客人，靠低价抢生意，却越省越狠。一边是稳稳当当把席办好，一边是亲手砸掉自己的口碑，这场较量最后看的是院子，还是人心。</x:v>
+        <x:v>七年前，夏晚棠为救深爱的陆知珩，付出了一切，却被误会成背叛，独自带着女儿生活。多年后，两人再次相遇，陆知珩才发现当年的真相，也终于明白她承受了怎样的苦难。面对迟来的爱与亏欠，夏晚棠没有停留在过去，而是重新找回自己，用专业和坚强开启新的人生。最终，两人在女儿的陪伴下解开心结，携手迎来属于他们的幸福。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1418,10 +1424,10 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
-        <x:v>反派拿捏！</x:v>
+        <x:v>小妹初长成</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
         <x:v>2026-09-13</x:v>
@@ -1449,13 +1455,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
-        <x:v>离婚那天我多了个痞帅老爹</x:v>
+        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>2026-09-13</x:v>
+        <x:v>09-15 08:30</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str"/>
       <x:c r="F10" s="11" t="str"/>
@@ -1465,28 +1471,34 @@
       <x:c r="H10" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I10" s="11" t="str"/>
+      <x:c r="I10" s="11" t="n">
+        <x:v>70</x:v>
+      </x:c>
       <x:c r="J10" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K10" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="L10" s="11" t="str"/>
-      <x:c r="M10" s="10" t="str"/>
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="L10" s="11" t="str">
+        <x:v>琥珀漫剧</x:v>
+      </x:c>
+      <x:c r="M10" s="10" t="str">
+        <x:v>海鲜市场老手陈放，因一个两块钱的冰袋被十二年合伙人当众算旧账，心寒清账，净身出户。他没有抱怨，也没有以牙还牙，而是加入冷清档口“梅姐水产”，从零开始。他坚持明码标价、沥水称重、死活分卖、批次可查，宁可少接单，也不混货、不凑数、不赚亏心钱。面对低价抢客、恶意破坏、临时缺货等风波，他与叶梅靠诚信、规矩和彼此信任，一步步赢得客户与连锁企业的认可。</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C11" s="10" t="str">
-        <x:v>河箱送福来</x:v>
+        <x:v>反派拿捏！</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>09-13 11:00</x:v>
+        <x:v>2026-09-13</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str"/>
       <x:c r="F11" s="11" t="str"/>
@@ -1496,34 +1508,28 @@
       <x:c r="H11" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I11" s="11" t="n">
-        <x:v>64</x:v>
-      </x:c>
+      <x:c r="I11" s="11" t="str"/>
       <x:c r="J11" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K11" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L11" s="11" t="str">
-        <x:v>灵心讲故事</x:v>
-      </x:c>
-      <x:c r="M11" s="10" t="str">
-        <x:v>张家老两口从河中救回一只木箱，收养了箱中受伤的福生。福生长大后修桥开田，引水惠及乡亲，成家立业。二老相继离世后，山洪威胁村庄，福生为救乡亲舍命撑住巨石，最终重伤落水，下落不明。秀娥守着小院苦等多年，直到熟悉的声音再次响起。</x:v>
-      </x:c>
+      <x:c r="L11" s="11" t="str"/>
+      <x:c r="M11" s="10" t="str"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
-        <x:v>重生极品婆婆，带全家发家致富！</x:v>
+        <x:v>高考刚结束父母就不装了</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>09-14 20:29</x:v>
+        <x:v>09-15 07:00</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str"/>
       <x:c r="F12" s="11" t="str"/>
@@ -1534,19 +1540,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I12" s="11" t="n">
-        <x:v>126</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="J12" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K12" s="10" t="str">
-        <x:v>家庭伦理 / 逆袭打脸</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="L12" s="11" t="str">
-        <x:v>懒少爱我</x:v>
+        <x:v>千慕剧场</x:v>
       </x:c>
       <x:c r="M12" s="10" t="str">
-        <x:v>寡妇傅兰秀前世一生吝啬守财，刻薄对待儿女儿媳，到头来钱财被贼人掠夺，落得个凄惨离世的下场。一朝重生，她回到悲剧尚未发生之时。痛定思痛，她彻底改掉抠门的性子，学着善待家里的晚辈。可日子并不太平，爱占便宜的亲戚总上门搅扰，家中两个儿媳也矛盾不断，家务是非接连找上门。傅兰秀靠着清醒的头脑，一边化解各类家庭纷争，一边寻找营生门路，努力扭转命运，拼尽全力守护一家人的安稳生活。</x:v>
+        <x:v>高考结束那天，林寻在考场外被亲生父母认回原来十八年的普通生活，是父母为磨砺他而设的一场成长课。重回豪门，他没有迷失，反而在桥上遇见了那个让他心动的姑娘，南大冰山学姐苏清诗。从青涩的初次相遇，到演唱会上的合唱，再到大学校园里的朝夕相处，两个真诚的人慢慢靠近。曾经的求而不得终将释怀，双向奔赴的喜欢才最珍贵。褪去普通学生的身份，林寻只想以真心换真心。十八岁的夏天，最好的相遇，最甜的恋爱，才刚刚开始。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1554,13 +1560,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B13" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
-        <x:v>那朵胸花，被丢进垃圾桶</x:v>
+        <x:v>一盒印泥引发的全局封锁</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
-        <x:v>09-14 21:00</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str"/>
       <x:c r="F13" s="11" t="str"/>
@@ -1570,34 +1576,28 @@
       <x:c r="H13" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I13" s="11" t="n">
-        <x:v>65</x:v>
-      </x:c>
+      <x:c r="I13" s="11" t="str"/>
       <x:c r="J13" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K13" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L13" s="11" t="str">
-        <x:v>临渊剧场</x:v>
-      </x:c>
-      <x:c r="M13" s="10" t="str">
-        <x:v>接亲当天，新郎踹开新娘房门。新娘护着前任，前任用胸花挑衅，婚礼当场取消。她求他，他放完整视频反击。前任欠债跑路，债主堵门，新娘崩溃。他换锁卖房，一笔账一笔账清。可账单会说话，旧爱跑不了，这条线，该断了。</x:v>
-      </x:c>
+      <x:c r="L13" s="11" t="str"/>
+      <x:c r="M13" s="10" t="str"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B14" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
-        <x:v>427元扳倒老油条</x:v>
+        <x:v>离婚那天我多了个痞帅老爹</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>09-13 16:00</x:v>
+        <x:v>2026-09-13</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str"/>
       <x:c r="F14" s="11" t="str"/>
@@ -1607,34 +1607,28 @@
       <x:c r="H14" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I14" s="11" t="n">
-        <x:v>55</x:v>
-      </x:c>
+      <x:c r="I14" s="11" t="str"/>
       <x:c r="J14" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K14" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L14" s="11" t="str">
-        <x:v>安然然</x:v>
-      </x:c>
-      <x:c r="M14" s="10" t="str">
-        <x:v>职场新人许宁向老员工马丽芬讨要427元代垫外卖款，反遭易绑架马丽芬交出饭钱后怀恨在心，利用行政特权私吞福利，并在组织团餐时疏同事差价许宁按兵不动收集证据，最终将马丽芬长期贪占两万余元的行径在老板曝光的照片中马丽芬被直接开除，许宁成功维护了职场底线。</x:v>
-      </x:c>
+        <x:v>家庭伦理 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="L14" s="11" t="str"/>
+      <x:c r="M14" s="10" t="str"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B15" s="11" t="n">
-        <x:v>82</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
-        <x:v>结婚八年，我娶的原来是仇人的女儿</x:v>
+        <x:v>河箱送福来</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>09-13 11:00</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str"/>
       <x:c r="F15" s="11" t="str"/>
@@ -1644,22 +1638,28 @@
       <x:c r="H15" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I15" s="11" t="str"/>
+      <x:c r="I15" s="11" t="n">
+        <x:v>64</x:v>
+      </x:c>
       <x:c r="J15" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K15" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="L15" s="11" t="str"/>
-      <x:c r="M15" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L15" s="11" t="str">
+        <x:v>灵心讲故事</x:v>
+      </x:c>
+      <x:c r="M15" s="10" t="str">
+        <x:v>张家老两口从河中救回一只木箱，收养了箱中受伤的福生。福生长大后修桥开田，引水惠及乡亲，成家立业。二老相继离世后，山洪威胁村庄，福生为救乡亲舍命撑住巨石，最终重伤落水，下落不明。秀娥守着小院苦等多年，直到熟悉的声音再次响起。</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C16" s="10" t="str">
         <x:v>风雪边界</x:v>
@@ -1696,73 +1696,67 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C17" s="10" t="str">
-        <x:v>晚棠知归，七年终见你</x:v>
+        <x:v>结婚八年，我娶的原来是仇人的女儿</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
-        <x:v>09-14 11:26</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="E17" s="11" t="str"/>
       <x:c r="F17" s="11" t="str"/>
       <x:c r="G17" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H17" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="I17" s="11" t="n">
-        <x:v>71</x:v>
-      </x:c>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I17" s="11" t="str"/>
       <x:c r="J17" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K17" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L17" s="11" t="str">
-        <x:v>喵琪琪追剧</x:v>
-      </x:c>
-      <x:c r="M17" s="10" t="str">
-        <x:v>七年前，夏晚棠为救深爱的陆知珩，付出了一切，却被误会成背叛，独自带着女儿生活。多年后，两人再次相遇，陆知珩才发现当年的真相，也终于明白她承受了怎样的苦难。面对迟来的爱与亏欠，夏晚棠没有停留在过去，而是重新找回自己，用专业和坚强开启新的人生。最终，两人在女儿的陪伴下解开心结，携手迎来属于他们的幸福。</x:v>
-      </x:c>
+        <x:v>家庭伦理 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="L17" s="11" t="str"/>
+      <x:c r="M17" s="10" t="str"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>37</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C18" s="10" t="str">
-        <x:v>高考刚结束父母就不装了</x:v>
+        <x:v>重生极品婆婆，带全家发家致富！</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>09-15 07:00</x:v>
+        <x:v>09-14 20:29</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str"/>
       <x:c r="F18" s="11" t="str"/>
       <x:c r="G18" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H18" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I18" s="11" t="n">
-        <x:v>173</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="J18" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K18" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>家庭伦理 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="L18" s="11" t="str">
-        <x:v>千慕剧场</x:v>
+        <x:v>懒少爱我</x:v>
       </x:c>
       <x:c r="M18" s="10" t="str">
-        <x:v>高考结束那天，林寻在考场外被亲生父母认回原来十八年的普通生活，是父母为磨砺他而设的一场成长课。重回豪门，他没有迷失，反而在桥上遇见了那个让他心动的姑娘，南大冰山学姐苏清诗。从青涩的初次相遇，到演唱会上的合唱，再到大学校园里的朝夕相处，两个真诚的人慢慢靠近。曾经的求而不得终将释怀，双向奔赴的喜欢才最珍贵。褪去普通学生的身份，林寻只想以真心换真心。十八岁的夏天，最好的相遇，最甜的恋爱，才刚刚开始。</x:v>
+        <x:v>寡妇傅兰秀前世一生吝啬守财，刻薄对待儿女儿媳，到头来钱财被贼人掠夺，落得个凄惨离世的下场。一朝重生，她回到悲剧尚未发生之时。痛定思痛，她彻底改掉抠门的性子，学着善待家里的晚辈。可日子并不太平，爱占便宜的亲戚总上门搅扰，家中两个儿媳也矛盾不断，家务是非接连找上门。傅兰秀靠着清醒的头脑，一边化解各类家庭纷争，一边寻找营生门路，努力扭转命运，拼尽全力守护一家人的安稳生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1770,24 +1764,24 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C19" s="10" t="str">
-        <x:v>星际机修师</x:v>
+        <x:v>远山架子班</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
-        <x:v>09-14 00:06</x:v>
+        <x:v>09-13 07:30</x:v>
       </x:c>
       <x:c r="E19" s="11" t="str"/>
       <x:c r="F19" s="11" t="str"/>
       <x:c r="G19" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H19" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I19" s="11" t="n">
-        <x:v>301</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J19" s="10" t="str">
         <x:v>其他</x:v>
@@ -1795,9 +1789,11 @@
       <x:c r="K19" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L19" s="11" t="str"/>
+      <x:c r="L19" s="11" t="str">
+        <x:v>空空书漫</x:v>
+      </x:c>
       <x:c r="M19" s="10" t="str">
-        <x:v>3033年星际机甲时代，18岁的苏白没有机甲天赋，却是初级机修师。父母留下百万星币与破旧仓库后远行，他激活星际战甲系统，改造仓库开设星际维修店。修复报废机甲“红月”并解锁天赋技后，苏白获得SSS级天赋万物相融与星鲸吐纳法。各路天才机甲师慕名而来，他打造专属机甲“混沌”，卷入各种阴谋纷争。不断击败对手，并将维修店扩张为星际要塞级基地。</x:v>
+        <x:v>工地上，彭大勇拿着别家四十一天的招工纸，问贺远山凭什么只给三十。贺远山不争辩，只把账摊开，安全装备饭钱他管，工钱三天一结，从没拖欠。有人奔着高薪离开，可那边层层扣下来，到手反不如从前，还屡屡涉险。工友受伤住院，贺远山二话不说垫钱救人，又帮着把旧账一笔笔算清。他始终守着一条理，钱要挣，命不能换。规矩立得住，人心自然拢得回，班越带越稳，账越算越明。</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1805,13 +1801,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>84</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C20" s="10" t="str">
-        <x:v>远山架子班</x:v>
+        <x:v>一宴断经年，旧账归于风</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>09-13 07:30</x:v>
+        <x:v>09-15 06:13</x:v>
       </x:c>
       <x:c r="E20" s="11" t="str"/>
       <x:c r="F20" s="11" t="str"/>
@@ -1819,22 +1815,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H20" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I20" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J20" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K20" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧 / 现实反转</x:v>
       </x:c>
       <x:c r="L20" s="11" t="str">
-        <x:v>空空书漫</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="M20" s="10" t="str">
-        <x:v>工地上，彭大勇拿着别家四十一天的招工纸，问贺远山凭什么只给三十。贺远山不争辩，只把账摊开，安全装备饭钱他管，工钱三天一结，从没拖欠。有人奔着高薪离开，可那边层层扣下来，到手反不如从前，还屡屡涉险。工友受伤住院，贺远山二话不说垫钱救人，又帮着把旧账一笔笔算清。他始终守着一条理，钱要挣，命不能换。规矩立得住，人心自然拢得回，班越带越稳，账越算越明。</x:v>
+        <x:v>宋知遥为侄女宋雨欣付出十三年，却在毕业宴上遭其当众羞辱并拒绝感恩。宋知遥看清嫂嫂一家的贪婪嘴脸，果断停卡断供，收回承诺的房产。面对侄女的道德绑架与法律纠纷，她坚守底线，通过法律途径维权，最终切断所有不良羁绊，守护亲生女儿，重启清净生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1842,36 +1838,36 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C21" s="10" t="str">
-        <x:v>我赚上千万跟爸妈说50W，隔天就被找上门</x:v>
+        <x:v>八零大院：灶台藏尽温柔</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
-        <x:v>09-13 08:00</x:v>
+        <x:v>09-13 10:00</x:v>
       </x:c>
       <x:c r="E21" s="11" t="str"/>
       <x:c r="F21" s="11" t="str"/>
       <x:c r="G21" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H21" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I21" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="J21" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K21" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧 / 种田囤货</x:v>
       </x:c>
       <x:c r="L21" s="11" t="str">
-        <x:v>至尊爽剧社</x:v>
+        <x:v>枭枭动画</x:v>
       </x:c>
       <x:c r="M21" s="10" t="str">
-        <x:v>三十二岁那年，贺川用六年孤注一掷的钻研，换来了七千六百万的回报。可财富还没捂热，先尝到的却是亲人无度的索取。他谎称只赚五十万，叮嘱保密，却挡不住消息走漏。隔天登门的亲戚不止要借钱买房，更联手外人盗用他的身份资料，试图冒名签约、伪造担保债务。贺川报警取证，警方介入追回大部分资金，涉案者包括部分机构人员均承担了法律责任，这笔帐，能否算清？</x:v>
+        <x:v>现代私宴主厨祝宁意外穿越至八十年代，为反抗包办婚姻毅然出走，凭借一身精湛厨艺在军区大院门口摆摊谋生。她做的饭菜香气独特，意外治愈了因战场创伤患上心理性厌食症的军区首长贺枭。进入军区食堂后，祝宁靠着过硬的厨艺和坦荡正直的性格渐渐站稳脚跟。面对旁人的刁难与恶意构陷，她始终坚守原则、沉着应对，最终不仅凭借专业能力获得全军区的认可，获评军区膳食顾问，也与贺枭解开重重误会，在烟火日常中收获了真挚的感情。</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1879,41 +1875,47 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C22" s="10" t="str">
-        <x:v>辣媳进门，我给公婆撑腰</x:v>
+        <x:v>我在工地卖盒饭带火一座城</x:v>
       </x:c>
       <x:c r="D22" s="11" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>09-14 14:52</x:v>
       </x:c>
       <x:c r="E22" s="11" t="str"/>
       <x:c r="F22" s="11" t="str"/>
       <x:c r="G22" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H22" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I22" s="11" t="str"/>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I22" s="11" t="n">
+        <x:v>144</x:v>
+      </x:c>
       <x:c r="J22" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K22" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L22" s="11" t="str"/>
-      <x:c r="M22" s="10" t="str"/>
+        <x:v>美食治愈</x:v>
+      </x:c>
+      <x:c r="L22" s="11" t="str">
+        <x:v>左手良画</x:v>
+      </x:c>
+      <x:c r="M22" s="10" t="str">
+        <x:v>小伙白叶遭遇老板跑路，半年工资付诸东流，意外被铁炒勺砸中觉醒超级餐饮系统。大雪封路堵车途中完成首份任务，靠着系统加持的厨艺，路边卖盒饭赚到第一桶金。回乡钻研秘制酱肉，赶集摆摊火爆出圈，还临危接手大型寿宴惊艳众人。过完新年，他怀揣梦想奔赴外地，准备开启属于自己的餐饮创业之路。</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C23" s="10" t="str">
-        <x:v>一盒印泥引发的全局封锁</x:v>
+        <x:v>辣媳进门，我给公婆撑腰</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
         <x:v>2026-09-15</x:v>
@@ -1921,10 +1923,10 @@
       <x:c r="E23" s="11" t="str"/>
       <x:c r="F23" s="11" t="str"/>
       <x:c r="G23" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H23" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="11" t="str"/>
       <x:c r="J23" s="10" t="str">
@@ -1938,187 +1940,157 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="str">
-        <x:v>持续在榜</x:v>
+        <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C24" s="10" t="str">
-        <x:v>年终奖900万变900块，我辞职后他怒了</x:v>
+        <x:v>反派拿捏！</x:v>
       </x:c>
       <x:c r="D24" s="11" t="str">
-        <x:v>09-15 12:00</x:v>
-      </x:c>
-      <x:c r="E24" s="11" t="str"/>
-      <x:c r="F24" s="11" t="str"/>
-      <x:c r="G24" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H24" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="I24" s="11" t="n">
-        <x:v>48</x:v>
-      </x:c>
+        <x:v>2026-09-13</x:v>
+      </x:c>
+      <x:c r="E24" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F24" s="11" t="str">
+        <x:v>↑2位</x:v>
+      </x:c>
+      <x:c r="G24" s="11" t="str"/>
+      <x:c r="H24" s="11" t="str"/>
+      <x:c r="I24" s="11" t="str"/>
       <x:c r="J24" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K24" s="10" t="str">
-        <x:v>年代怀旧 / 都市职场</x:v>
-      </x:c>
-      <x:c r="L24" s="11" t="str">
-        <x:v>至尊爽剧社</x:v>
-      </x:c>
-      <x:c r="M24" s="10" t="str">
-        <x:v>林砚入职十一天，发现小数点篡改产生的巨额付款漏洞，查出三年近两千四百万异常支出，帮公司追回一千八百万，关键线索却断掉。他遭财务总监刘敏华记恨，绩效被克扣、报销被卡压。林砚没有冲动对峙，悄悄收集证据。年会上董事长特批九百万年终奖，他提前备份证据、备好辞呈。到手仅九百块。他拿着辞职信找到董事长，当众亮出证据。</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L24" s="11" t="str"/>
+      <x:c r="M24" s="10" t="str"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="str">
-        <x:v>持续在榜</x:v>
+        <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C25" s="10" t="str">
-        <x:v>枕上独宠第一季</x:v>
+        <x:v>辣媳进门，我给公婆撑腰</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
-        <x:v>09-13 11:05</x:v>
-      </x:c>
-      <x:c r="E25" s="11" t="str"/>
-      <x:c r="F25" s="11" t="str"/>
-      <x:c r="G25" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H25" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="I25" s="11" t="n">
-        <x:v>185</x:v>
-      </x:c>
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="E25" s="11" t="n">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F25" s="11" t="str">
+        <x:v>↑2位</x:v>
+      </x:c>
+      <x:c r="G25" s="11" t="str"/>
+      <x:c r="H25" s="11" t="str"/>
+      <x:c r="I25" s="11" t="str"/>
       <x:c r="J25" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K25" s="10" t="str">
-        <x:v>婚姻情感</x:v>
-      </x:c>
-      <x:c r="L25" s="11" t="str">
-        <x:v>语跃文化</x:v>
-      </x:c>
-      <x:c r="M25" s="10" t="str">
-        <x:v>四年前我不告而别，远走他国，以为他在家族逼婚与我之间选择了前者。四年后我以记者身份回国，第一场采访对象正是已成集团总裁的前男友。我问他订婚传闻，他冷言相对，却一直留着我送的旧物。直到闺蜜点破真相，当年他被家中软禁，错过我的电话，此后数年拼命往上走，只为有能力护住想护的人。误会尽释，这一次我不会再逃。</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L25" s="11" t="str"/>
+      <x:c r="M25" s="10" t="str"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="str">
-        <x:v>持续在榜</x:v>
+        <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B26" s="11" t="n">
-        <x:v>98</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C26" s="10" t="str">
-        <x:v>这桌团圆饭，我不做了</x:v>
+        <x:v>沈总，夫人不忍了</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
-        <x:v>09-13 17:02</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="E26" s="11" t="str"/>
-      <x:c r="F26" s="11" t="str"/>
-      <x:c r="G26" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H26" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I26" s="11" t="n">
-        <x:v>50</x:v>
-      </x:c>
+      <x:c r="F26" s="11" t="str">
+        <x:v>新上榜</x:v>
+      </x:c>
+      <x:c r="G26" s="11" t="str"/>
+      <x:c r="H26" s="11" t="str"/>
+      <x:c r="I26" s="11" t="str"/>
       <x:c r="J26" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K26" s="10" t="str">
-        <x:v>美食治愈</x:v>
-      </x:c>
-      <x:c r="L26" s="11" t="str">
-        <x:v>锦鲤漫</x:v>
-      </x:c>
-      <x:c r="M26" s="10" t="str">
-        <x:v>除夕前夕，乔宁发现丈夫擅自退掉她陪父母吃年夜饭的包间，还将三十一人的团圆饭默认交给她操持。她不再争吵，也不再兜底，而是选择回家陪伴父母。随着陆家亲自接手年夜饭，众人才逐渐明白，一顿“简单”的团圆饭背后，藏着多少被忽视的付出与责任。</x:v>
-      </x:c>
+        <x:v>婚姻情感 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="L26" s="11" t="str"/>
+      <x:c r="M26" s="10" t="str"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B27" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C27" s="10" t="str">
-        <x:v>427元扳倒老油条</x:v>
+        <x:v>小福宝赶海</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
-        <x:v>09-13 16:00</x:v>
-      </x:c>
-      <x:c r="E27" s="11" t="n">
-        <x:v>88</x:v>
-      </x:c>
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="E27" s="11" t="str"/>
       <x:c r="F27" s="11" t="str">
-        <x:v>↑10位</x:v>
+        <x:v>新上榜</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str"/>
       <x:c r="H27" s="11" t="str"/>
-      <x:c r="I27" s="11" t="n">
-        <x:v>55</x:v>
-      </x:c>
+      <x:c r="I27" s="11" t="str"/>
       <x:c r="J27" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K27" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L27" s="11" t="str">
-        <x:v>安然然</x:v>
-      </x:c>
-      <x:c r="M27" s="10" t="str">
-        <x:v>职场新人许宁向老员工马丽芬讨要427元代垫外卖款，反遭易绑架马丽芬交出饭钱后怀恨在心，利用行政特权私吞福利，并在组织团餐时疏同事差价许宁按兵不动收集证据，最终将马丽芬长期贪占两万余元的行径在老板曝光的照片中马丽芬被直接开除，许宁成功维护了职场底线。</x:v>
-      </x:c>
+        <x:v>种田囤货 / 萌宝治愈</x:v>
+      </x:c>
+      <x:c r="L27" s="11" t="str"/>
+      <x:c r="M27" s="10" t="str"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B28" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C28" s="10" t="str">
-        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
+        <x:v>锅炉没爆炸，名声却先炸了</x:v>
       </x:c>
       <x:c r="D28" s="11" t="str">
-        <x:v>09-15 08:30</x:v>
-      </x:c>
-      <x:c r="E28" s="11" t="n">
-        <x:v>39</x:v>
-      </x:c>
+        <x:v>09-14 17:00</x:v>
+      </x:c>
+      <x:c r="E28" s="11" t="str"/>
       <x:c r="F28" s="11" t="str">
-        <x:v>↑6位</x:v>
+        <x:v>新上榜</x:v>
       </x:c>
       <x:c r="G28" s="11" t="str"/>
       <x:c r="H28" s="11" t="str"/>
       <x:c r="I28" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J28" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K28" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L28" s="11" t="str">
-        <x:v>琥珀漫剧</x:v>
+        <x:v>柔光映剧场</x:v>
       </x:c>
       <x:c r="M28" s="10" t="str">
-        <x:v>海鲜市场老手陈放，因一个两块钱的冰袋被十二年合伙人当众算旧账，心寒清账，净身出户。他没有抱怨，也没有以牙还牙，而是加入冷清档口“梅姐水产”，从零开始。他坚持明码标价、沥水称重、死活分卖、批次可查，宁可少接单，也不混货、不凑数、不赚亏心钱。面对低价抢客、恶意破坏、临时缺货等风波，他与叶梅靠诚信、规矩和彼此信任，一步步赢得客户与连锁企业的认可。</x:v>
+        <x:v>重生回宿舍，孙有田又喊锅炉要炸，拽我跑。上辈子我信了，名声被毁，嫁他挨打丧子。这回我一脚踹翻他，扯嗓喊抓流氓！他掏出我的信反咬，未婚夫也来退婚。我不哭，当场拆穿字迹与痣局，揪出幕后名额交易。高考恢复，我拼命读书，把陷害我的人全送进锅炉房。录取那天，我烧掉旧信。那棵树，开花了。</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -2126,24 +2098,22 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B29" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C29" s="10" t="str">
-        <x:v>晚棠知归，七年终见你</x:v>
+        <x:v>7路公交车的终点</x:v>
       </x:c>
       <x:c r="D29" s="11" t="str">
-        <x:v>09-14 11:26</x:v>
-      </x:c>
-      <x:c r="E29" s="11" t="n">
-        <x:v>33</x:v>
-      </x:c>
+        <x:v>09-14 10:00</x:v>
+      </x:c>
+      <x:c r="E29" s="11" t="str"/>
       <x:c r="F29" s="11" t="str">
-        <x:v>↑5位</x:v>
+        <x:v>新上榜</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str"/>
       <x:c r="H29" s="11" t="str"/>
       <x:c r="I29" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="J29" s="10" t="str">
         <x:v>其他</x:v>
@@ -2152,212 +2122,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L29" s="11" t="str">
-        <x:v>喵琪琪追剧</x:v>
+        <x:v>鹿姐短剧</x:v>
       </x:c>
       <x:c r="M29" s="10" t="str">
-        <x:v>七年前，夏晚棠为救深爱的陆知珩，付出了一切，却被误会成背叛，独自带着女儿生活。多年后，两人再次相遇，陆知珩才发现当年的真相，也终于明白她承受了怎样的苦难。面对迟来的爱与亏欠，夏晚棠没有停留在过去，而是重新找回自己，用专业和坚强开启新的人生。最终，两人在女儿的陪伴下解开心结，携手迎来属于他们的幸福。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="11" t="str">
-        <x:v>新剧上升</x:v>
-      </x:c>
-      <x:c r="B30" s="11" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C30" s="10" t="str">
-        <x:v>反派拿捏！</x:v>
-      </x:c>
-      <x:c r="D30" s="11" t="str">
-        <x:v>2026-09-13</x:v>
-      </x:c>
-      <x:c r="E30" s="11" t="n">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F30" s="11" t="str">
-        <x:v>↑5位</x:v>
-      </x:c>
-      <x:c r="G30" s="11" t="str"/>
-      <x:c r="H30" s="11" t="str"/>
-      <x:c r="I30" s="11" t="str"/>
-      <x:c r="J30" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="K30" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L30" s="11" t="str"/>
-      <x:c r="M30" s="10" t="str"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="11" t="str">
-        <x:v>新剧上升</x:v>
-      </x:c>
-      <x:c r="B31" s="11" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C31" s="10" t="str">
-        <x:v>星际机修师</x:v>
-      </x:c>
-      <x:c r="D31" s="11" t="str">
-        <x:v>09-14 00:06</x:v>
-      </x:c>
-      <x:c r="E31" s="11" t="n">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F31" s="11" t="str">
-        <x:v>↑5位</x:v>
-      </x:c>
-      <x:c r="G31" s="11" t="str"/>
-      <x:c r="H31" s="11" t="str"/>
-      <x:c r="I31" s="11" t="n">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="J31" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="K31" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L31" s="11" t="str"/>
-      <x:c r="M31" s="10" t="str">
-        <x:v>3033年星际机甲时代，18岁的苏白没有机甲天赋，却是初级机修师。父母留下百万星币与破旧仓库后远行，他激活星际战甲系统，改造仓库开设星际维修店。修复报废机甲“红月”并解锁天赋技后，苏白获得SSS级天赋万物相融与星鲸吐纳法。各路天才机甲师慕名而来，他打造专属机甲“混沌”，卷入各种阴谋纷争。不断击败对手，并将维修店扩张为星际要塞级基地。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="11" t="str">
-        <x:v>新剧上升</x:v>
-      </x:c>
-      <x:c r="B32" s="11" t="n">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C32" s="10" t="str">
-        <x:v>离婚那天我多了个痞帅老爹</x:v>
-      </x:c>
-      <x:c r="D32" s="11" t="str">
-        <x:v>2026-09-13</x:v>
-      </x:c>
-      <x:c r="E32" s="11" t="n">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F32" s="11" t="str">
-        <x:v>↑4位</x:v>
-      </x:c>
-      <x:c r="G32" s="11" t="str"/>
-      <x:c r="H32" s="11" t="str"/>
-      <x:c r="I32" s="11" t="str"/>
-      <x:c r="J32" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="K32" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="L32" s="11" t="str"/>
-      <x:c r="M32" s="10" t="str"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="11" t="str">
-        <x:v>新剧上升</x:v>
-      </x:c>
-      <x:c r="B33" s="11" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C33" s="10" t="str">
-        <x:v>小妹初长成</x:v>
-      </x:c>
-      <x:c r="D33" s="11" t="str">
-        <x:v>2026-09-13</x:v>
-      </x:c>
-      <x:c r="E33" s="11" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F33" s="11" t="str">
-        <x:v>↑3位</x:v>
-      </x:c>
-      <x:c r="G33" s="11" t="str"/>
-      <x:c r="H33" s="11" t="str"/>
-      <x:c r="I33" s="11" t="str"/>
-      <x:c r="J33" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="K33" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L33" s="11" t="str"/>
-      <x:c r="M33" s="10" t="str"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="11" t="str">
-        <x:v>新剧上升</x:v>
-      </x:c>
-      <x:c r="B34" s="11" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C34" s="10" t="str">
-        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
-      </x:c>
-      <x:c r="D34" s="11" t="str">
-        <x:v>09-13 09:58</x:v>
-      </x:c>
-      <x:c r="E34" s="11" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F34" s="11" t="str">
-        <x:v>↑2位</x:v>
-      </x:c>
-      <x:c r="G34" s="11" t="str"/>
-      <x:c r="H34" s="11" t="str"/>
-      <x:c r="I34" s="11" t="n">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="J34" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="K34" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L34" s="11" t="str">
-        <x:v>创想剧场</x:v>
-      </x:c>
-      <x:c r="M34" s="10" t="str">
-        <x:v>游戏公会会长林小勇筹备婚礼，却在婚宴上遭遇未婚妻临时加价逼婚。危急时刻，几位相交多年的游戏老友现身力挺他，林小勇果断取消婚礼。之后他搬进好友赠送的别墅，与陈董的两个女儿渐渐熟识。同学聚会上，众人见识到林小勇不一般的际遇。平静日子没过多久，当年游戏里的宿敌将出席游戏八周年嘉年华，一众老友决定赴约，一场新旧对决即将开启。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="11" t="str">
-        <x:v>新剧上升</x:v>
-      </x:c>
-      <x:c r="B35" s="11" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C35" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
-      </x:c>
-      <x:c r="D35" s="11" t="str">
-        <x:v>09-15 00:08</x:v>
-      </x:c>
-      <x:c r="E35" s="11" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F35" s="11" t="str">
-        <x:v>↑1位</x:v>
-      </x:c>
-      <x:c r="G35" s="11" t="str"/>
-      <x:c r="H35" s="11" t="str"/>
-      <x:c r="I35" s="11" t="n">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="J35" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="K35" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L35" s="11" t="str">
-        <x:v>桃子动漫剧场</x:v>
-      </x:c>
-      <x:c r="M35" s="10" t="str">
-        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
+        <x:v>何云身为顾氏集团实际控股人，隐姓埋名开了二十年公交。亲家肖大海一家在公交上闹事伤人，其女肖琴琴当众殴打何云，还剪辑视频网暴她。何云收集完整录像与肖琴琴挪用公款的证据，于订婚宴当众揭穿一切。肖家人被警方带走，何云出任公交公司总经理，与儿子和好。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2403,7 +2171,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
         <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
@@ -2426,33 +2194,33 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
+        <x:v>300块报销单，作没了一家千万公司</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>今日发布</x:v>
+        <x:v>当日新上榜</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>09-15 00:08</x:v>
+        <x:v>07-31 12:00</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F3" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G3" s="10" t="str">
-        <x:v>桃子动漫剧场</x:v>
+        <x:v>今朝动画</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>一盒印泥引发的全局封锁</x:v>
+        <x:v>沈总，夫人不忍了</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
         <x:v>当日新上榜</x:v>
@@ -2466,125 +2234,119 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
+        <x:v>四个崽崽瞒不住了</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>09-15 08:30</x:v>
+        <x:v>09-15 00:08</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F5" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G5" s="10" t="str">
-        <x:v>琥珀漫剧</x:v>
+        <x:v>桃子动漫剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>37</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>高考刚结束父母就不装了</x:v>
+        <x:v>七年，抵不过她男闺蜜一张机票</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>今日发布</x:v>
+        <x:v>当日新上榜</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>09-15 07:00</x:v>
+        <x:v>09-03 10:00</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
-        <x:v>173</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F6" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="G6" s="10" t="str">
-        <x:v>千慕剧场</x:v>
+        <x:v>九天追剧</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>年终奖900万变900块，我辞职后他怒了</x:v>
+        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>09-15 12:00</x:v>
+        <x:v>09-15 08:30</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F7" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G7" s="10" t="str">
-        <x:v>至尊爽剧社</x:v>
+        <x:v>琥珀漫剧</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="n">
-        <x:v>76</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>被身高掩盖的谎言</x:v>
+        <x:v>小福宝赶海</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>今日发布</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="str">
-        <x:v>09-15 08:18</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="n">
-        <x:v>60</x:v>
-      </x:c>
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="str"/>
+      <x:c r="E8" s="11" t="str"/>
       <x:c r="F8" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G8" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
-      </x:c>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="G8" s="10" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>一宴断经年，旧账归于风</x:v>
+        <x:v>高考刚结束父母就不装了</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>09-15 06:13</x:v>
+        <x:v>09-15 07:00</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="F9" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G9" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>千慕剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="n">
-        <x:v>82</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>结婚八年，我娶的原来是仇人的女儿</x:v>
+        <x:v>一盒印泥引发的全局封锁</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
         <x:v>当日新上榜</x:v>
@@ -2598,37 +2360,175 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>入局不为爱</x:v>
+        <x:v>宴后逢安</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
         <x:v>当日新上榜</x:v>
       </x:c>
-      <x:c r="D11" s="11" t="str"/>
-      <x:c r="E11" s="11" t="str"/>
+      <x:c r="D11" s="11" t="str">
+        <x:v>08-17 23:32</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="n">
+        <x:v>63</x:v>
+      </x:c>
       <x:c r="F11" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="G11" s="10" t="str"/>
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="G11" s="10" t="str">
+        <x:v>琢曜-小杨看剧</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>辣媳进门，我给公婆撑腰</x:v>
+        <x:v>系统穿古今，满满囤货到手软</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
         <x:v>当日新上榜</x:v>
       </x:c>
-      <x:c r="D12" s="11" t="str"/>
-      <x:c r="E12" s="11" t="str"/>
+      <x:c r="D12" s="11" t="str">
+        <x:v>08-19 18:18</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="n">
+        <x:v>125</x:v>
+      </x:c>
       <x:c r="F12" s="10" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="G12" s="10" t="str">
+        <x:v>二两清沙</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="11" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B13" s="10" t="str">
+        <x:v>自有归途</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="str">
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D13" s="11" t="str">
+        <x:v>07-06 22:30</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="F13" s="10" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="G13" s="10" t="str">
+        <x:v>维维动画</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="11" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B14" s="10" t="str">
+        <x:v>结婚八年，我娶的原来是仇人的女儿</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="str">
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="str"/>
+      <x:c r="E14" s="11" t="str"/>
+      <x:c r="F14" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="G12" s="10" t="str"/>
+      <x:c r="G14" s="10" t="str"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="11" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B15" s="10" t="str">
+        <x:v>刺耳的邻里情</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="str">
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D15" s="11" t="str">
+        <x:v>09-15 11:00</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F15" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G15" s="10" t="str">
+        <x:v>酒写一首诗</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="11" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B16" s="10" t="str">
+        <x:v>收发室打杂的竟是网络安全大佬</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="str">
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D16" s="11" t="str">
+        <x:v>07-24 10:00</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F16" s="10" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="G16" s="10" t="str">
+        <x:v>连连看剧场</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="11" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B17" s="10" t="str">
+        <x:v>辣媳进门，我给公婆撑腰</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="str">
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D17" s="11" t="str"/>
+      <x:c r="E17" s="11" t="str"/>
+      <x:c r="F17" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="G17" s="10" t="str"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="11" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B18" s="10" t="str">
+        <x:v>一宴断经年，旧账归于风</x:v>
+      </x:c>
+      <x:c r="C18" s="11" t="str">
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D18" s="11" t="str">
+        <x:v>09-15 06:13</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F18" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G18" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2697,7 +2597,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
         <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
@@ -2734,16 +2634,16 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B3" s="10" t="str">
+        <x:v>黑蛋孵出山海神兽后我无敌了</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="str">
+        <x:v>09-06 18:00</x:v>
+      </x:c>
+      <x:c r="D3" s="11" t="n">
         <x:v>9</x:v>
-      </x:c>
-      <x:c r="B3" s="10" t="str">
-        <x:v>重生三天前，我用水泥封死地下室</x:v>
-      </x:c>
-      <x:c r="C3" s="11" t="str">
-        <x:v>09-09 09:28</x:v>
-      </x:c>
-      <x:c r="D3" s="11" t="n">
-        <x:v>6</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
         <x:v>7</x:v>
@@ -2752,10 +2652,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G3" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H3" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
         <x:v>其他</x:v>
@@ -2763,24 +2663,24 @@
       <x:c r="J3" s="11" t="str"/>
       <x:c r="K3" s="11" t="str"/>
       <x:c r="L3" s="10" t="str">
-        <x:v>忘忧剧场</x:v>
+        <x:v>抱月剧场</x:v>
       </x:c>
       <x:c r="M3" s="10" t="str">
-        <x:v>阮清重生回被保姆王妈一家害死的三天前，前世她因心善引狼入室，保姆全家蜗居别墅地下室偷窃投毒，最终惨遭勒死。重生后她假装不知，趁王妈外出时用水泥将地下室彻底封死。警方破墙后，五具尸体令真相大白，王妈因盗窃、投毒被判十五年。阮清与父母团聚，恶人终得恶报，她重获新生。</x:v>
+        <x:v>寒门少年李初七攒了三年银子，仍买不起最低等的兽蛋。一次意外，他在后山捡到一枚黑蛋，孵出的煤球又小又馋，偏偏爱啃铜钱。可每吞下一缕兽息，它便能复现对手的能力。县学测灵那日，测灵石骤然亮起黑光，群兽伏地。所有人都以为他只是走了好运，只有陆远山想起古籍中的禁忌——黑光现，万兽伏。煤球究竟是什么？</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>不靠谱爸妈很靠谱</x:v>
+        <x:v>破库房的秘密</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>09-09 11:08</x:v>
+        <x:v>2026-09-05</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
         <x:v>7</x:v>
@@ -2791,33 +2691,27 @@
       <x:c r="G4" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H4" s="11" t="n">
-        <x:v>73</x:v>
-      </x:c>
+      <x:c r="H4" s="11" t="str"/>
       <x:c r="I4" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J4" s="11" t="str"/>
       <x:c r="K4" s="11" t="str"/>
-      <x:c r="L4" s="10" t="str">
-        <x:v>灵妹儿</x:v>
-      </x:c>
-      <x:c r="M4" s="10" t="str">
-        <x:v>外表张扬的年轻夫妻在冬夜救下女婴林小小，用十七年的辛勤劳动和无条件陪伴，为她撑起温暖的家。曾经成绩落后的林小小，在父母的鼓励下重新学习，一步步成长为优秀学生。面对亲生家庭带来的资源与人生选择，她也开始重新理解血缘、养育与责任。当外界的误解影响到父母的生活，林小小决定勇敢站出来，用事实守护家人，也用努力证明真正的爱，是尊重、陪伴和彼此成就。</x:v>
-      </x:c>
+      <x:c r="L4" s="10" t="str"/>
+      <x:c r="M4" s="10" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>一墙之隔，皆是人心</x:v>
+        <x:v>重生三天前，我用水泥封死地下室</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>09-06 15:48</x:v>
+        <x:v>09-09 09:28</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
         <x:v>7</x:v>
@@ -2829,7 +2723,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H5" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I5" s="10" t="str">
         <x:v>其他</x:v>
@@ -2837,24 +2731,24 @@
       <x:c r="J5" s="11" t="str"/>
       <x:c r="K5" s="11" t="str"/>
       <x:c r="L5" s="10" t="str">
-        <x:v>在下长生</x:v>
+        <x:v>忘忧剧场</x:v>
       </x:c>
       <x:c r="M5" s="10" t="str">
-        <x:v>妻子临产被车堵住出口，叶瑾抱着羊水破裂的她跑了三公里才到医院，母子平安。面对无理的车主，他没有以暴制暴，而是选择依法行事——在自家院内合法砌墙、种下高价值树苗，全程录像留证。车主回来后暴力砸墙、碾压树苗，最终被依法追究责任。</x:v>
+        <x:v>阮清重生回被保姆王妈一家害死的三天前，前世她因心善引狼入室，保姆全家蜗居别墅地下室偷窃投毒，最终惨遭勒死。重生后她假装不知，趁王妈外出时用水泥将地下室彻底封死。警方破墙后，五具尸体令真相大白，王妈因盗窃、投毒被判十五年。阮清与父母团聚，恶人终得恶报，她重获新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>穿书后我带萌宝上门认爹</x:v>
+        <x:v>不靠谱爸妈很靠谱</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>09-07 19:18</x:v>
+        <x:v>09-09 11:08</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
         <x:v>7</x:v>
@@ -2863,10 +2757,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G6" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H6" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
         <x:v>其他</x:v>
@@ -2874,24 +2768,24 @@
       <x:c r="J6" s="11" t="str"/>
       <x:c r="K6" s="11" t="str"/>
       <x:c r="L6" s="10" t="str">
-        <x:v>虾仁不自在</x:v>
+        <x:v>灵妹儿</x:v>
       </x:c>
       <x:c r="M6" s="10" t="str">
-        <x:v>许知棠重生穿进书中，当即带着五岁儿子许小舟登门，将孩子送到亲生父亲——傅氏集团总裁傅临川面前，只想抽身退出剧情。幼儿园里儿子遭同学诬陷、老师偏心，她强势护崽，硬刚蛮横家长与失职老师。亲子鉴定尘埃落定，萌娃黏妈不黏爹，反倒让清冷总裁渐渐上心。</x:v>
+        <x:v>外表张扬的年轻夫妻在冬夜救下女婴林小小，用十七年的辛勤劳动和无条件陪伴，为她撑起温暖的家。曾经成绩落后的林小小，在父母的鼓励下重新学习，一步步成长为优秀学生。面对亲生家庭带来的资源与人生选择，她也开始重新理解血缘、养育与责任。当外界的误解影响到父母的生活，林小小决定勇敢站出来，用事实守护家人，也用努力证明真正的爱，是尊重、陪伴和彼此成就。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>离家十年，回来女儿被换了</x:v>
+        <x:v>穿书后我带萌宝上门认爹</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>09-09 00:04</x:v>
+        <x:v>09-07 19:18</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
         <x:v>7</x:v>
@@ -2900,10 +2794,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G7" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H7" s="11" t="n">
-        <x:v>155</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="I7" s="10" t="str">
         <x:v>其他</x:v>
@@ -2911,24 +2805,24 @@
       <x:c r="J7" s="11" t="str"/>
       <x:c r="K7" s="11" t="str"/>
       <x:c r="L7" s="10" t="str">
-        <x:v>魔方影视（上剧版</x:v>
+        <x:v>虾仁不自在</x:v>
       </x:c>
       <x:c r="M7" s="10" t="str">
-        <x:v>程砚宁完成长期绝密任务归来，满心想要弥补亲情，却发现家中早已物是人非。身边亲近之人被私欲蒙蔽，制造重重骗局，试图侵占她的事业与财富。面对接连而来的算计与危机，她凭借过人的魄力与智慧步步拆解阴谋，联合正义力量搜集证据，厘清全部是非纠葛。在守护自身事业的同时，她放下过往伤痛，投身公益，完成自我和解，迎来属于自己的全新人生。</x:v>
+        <x:v>许知棠重生穿进书中，当即带着五岁儿子许小舟登门，将孩子送到亲生父亲——傅氏集团总裁傅临川面前，只想抽身退出剧情。幼儿园里儿子遭同学诬陷、老师偏心，她强势护崽，硬刚蛮横家长与失职老师。亲子鉴定尘埃落定，萌娃黏妈不黏爹，反倒让清冷总裁渐渐上心。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>破库房的秘密</x:v>
+        <x:v>一墙之隔，皆是人心</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>2026-09-05</x:v>
+        <x:v>09-06 15:48</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
         <x:v>7</x:v>
@@ -2937,29 +2831,35 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G8" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H8" s="11" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H8" s="11" t="n">
+        <x:v>85</x:v>
+      </x:c>
       <x:c r="I8" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J8" s="11" t="str"/>
       <x:c r="K8" s="11" t="str"/>
-      <x:c r="L8" s="10" t="str"/>
-      <x:c r="M8" s="10" t="str"/>
+      <x:c r="L8" s="10" t="str">
+        <x:v>在下长生</x:v>
+      </x:c>
+      <x:c r="M8" s="10" t="str">
+        <x:v>妻子临产被车堵住出口，叶瑾抱着羊水破裂的她跑了三公里才到医院，母子平安。面对无理的车主，他没有以暴制暴，而是选择依法行事——在自家院内合法砌墙、种下高价值树苗，全程录像留证。车主回来后暴力砸墙、碾压树苗，最终被依法追究责任。</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>抢个新娘来当后娘第一季</x:v>
+        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>09-08 15:10</x:v>
+        <x:v>2026-09-05</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
         <x:v>7</x:v>
@@ -2968,26 +2868,20 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G9" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H9" s="11" t="n">
-        <x:v>177</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H9" s="11" t="str"/>
       <x:c r="I9" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J9" s="11" t="str"/>
       <x:c r="K9" s="11" t="str"/>
-      <x:c r="L9" s="10" t="str">
-        <x:v>麻辣公主</x:v>
-      </x:c>
-      <x:c r="M9" s="10" t="str">
-        <x:v>带着十里红妆出嫁那日，我才得知新郎早已另娶，这门亲事不过是盯上了我李家的家产。换作旁人或许忍气吞声，我偏不。我当众拒入侯府，主动上书朝廷，愿以嫁妆资援南方水患，只求解除婚约、护我父母周全。这份胆识赢得安王敬重，他以正妃之礼娶我入门。我立誓此生不做妾、不与人共侍一夫，终得一份彼此尊重的姻缘。</x:v>
-      </x:c>
+      <x:c r="L9" s="10" t="str"/>
+      <x:c r="M9" s="10" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="n">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
         <x:v>惊絮无声：傻女的绝杀</x:v>
@@ -3024,13 +2918,13 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>美颜系统开挂，大佬全跪下</x:v>
+        <x:v>离家十年，回来女儿被换了</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>09-09 00:10</x:v>
+        <x:v>09-09 00:04</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
         <x:v>6</x:v>
@@ -3042,10 +2936,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G11" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H11" s="11" t="n">
-        <x:v>172</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="I11" s="10" t="str">
         <x:v>其他</x:v>
@@ -3053,24 +2947,24 @@
       <x:c r="J11" s="11" t="str"/>
       <x:c r="K11" s="11" t="str"/>
       <x:c r="L11" s="10" t="str">
-        <x:v>御儿</x:v>
+        <x:v>魔方影视（上剧版</x:v>
       </x:c>
       <x:c r="M11" s="10" t="str">
-        <x:v>曾因外形饱受非议的米珂华丽转身，蜕变得耀眼又夺目。从前对她嗤之以鼻的蒋少开始频频在意，素来冷眼毒舌的陆总不知不觉深陷其中，连一向克己的商界大佬也为她打破原则。米珂凭智商与手腕周旋于众人之间，上演一场势均力敌的情感博弈。没有俗套的救赎，只有双向的拉扯。看一众高高在上的精英暗自较劲、步步沉沦，心甘情愿为她卸下防备。</x:v>
+        <x:v>程砚宁完成长期绝密任务归来，满心想要弥补亲情，却发现家中早已物是人非。身边亲近之人被私欲蒙蔽，制造重重骗局，试图侵占她的事业与财富。面对接连而来的算计与危机，她凭借过人的魄力与智慧步步拆解阴谋，联合正义力量搜集证据，厘清全部是非纠葛。在守护自身事业的同时，她放下过往伤痛，投身公益，完成自我和解，迎来属于自己的全新人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="n">
-        <x:v>44</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
+        <x:v>抢个新娘来当后娘第一季</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>2026-09-05</x:v>
+        <x:v>09-08 15:10</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
         <x:v>7</x:v>
@@ -3079,26 +2973,32 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G12" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="11" t="str"/>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H12" s="11" t="n">
+        <x:v>177</x:v>
+      </x:c>
       <x:c r="I12" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J12" s="11" t="str"/>
       <x:c r="K12" s="11" t="str"/>
-      <x:c r="L12" s="10" t="str"/>
-      <x:c r="M12" s="10" t="str"/>
+      <x:c r="L12" s="10" t="str">
+        <x:v>麻辣公主</x:v>
+      </x:c>
+      <x:c r="M12" s="10" t="str">
+        <x:v>带着十里红妆出嫁那日，我才得知新郎早已另娶，这门亲事不过是盯上了我李家的家产。换作旁人或许忍气吞声，我偏不。我当众拒入侯府，主动上书朝廷，愿以嫁妆资援南方水患，只求解除婚约、护我父母周全。这份胆识赢得安王敬重，他以正妃之礼娶我入门。我立誓此生不做妾、不与人共侍一夫，终得一份彼此尊重的姻缘。</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
+        <x:v>天灾末世，她囤满物资后所向披靡！</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>09-08 11:00</x:v>
+        <x:v>09-08 15:00</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
         <x:v>7</x:v>
@@ -3110,10 +3010,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G13" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H13" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="I13" s="10" t="str">
         <x:v>其他</x:v>
@@ -3121,21 +3021,21 @@
       <x:c r="J13" s="11" t="str"/>
       <x:c r="K13" s="11" t="str"/>
       <x:c r="L13" s="10" t="str">
-        <x:v>白桃剧场</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="M13" s="10" t="str">
-        <x:v>阿梨一觉睡了三百年，养大的五只小兽尽数离去。她带着五只旧饭碗、十二枚铜钱与一把锈柴刀下山寻兽。昔日的小家伙已成威震四方的妖祖，历经重重相遇与揭秘，阿梨知晓三百年封印的真相，携手五只妖祖，一同对抗祸世灭灵兽神。</x:v>
+        <x:v>韩清夏被至亲推向绝境，失去家园，没能守住重要伙伴。再次睁眼，她回到了灾变来临前，并意外激活超级领主系统。她果断卖房筹资、囤积物资，将废弃防空洞升级为坚固基地，与战犬夏天并肩成长。危机爆发后，她凭借清醒判断、强大异能和充足准备救下幸存者，组建盛夏联盟。面对旧日亲人的算计、各方势力的试探与接连不断的考验，韩清夏不再退让。这一世，她要守住伙伴、掌握命运，在废墟之上建起属于自己的家园。</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>重启人生，拒绝校花？</x:v>
+        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>09-08 08:30</x:v>
+        <x:v>09-08 11:00</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
         <x:v>7</x:v>
@@ -3147,10 +3047,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G14" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H14" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="I14" s="10" t="str">
         <x:v>其他</x:v>
@@ -3158,24 +3058,24 @@
       <x:c r="J14" s="11" t="str"/>
       <x:c r="K14" s="11" t="str"/>
       <x:c r="L14" s="10" t="str">
-        <x:v>肆漫简</x:v>
+        <x:v>白桃剧场</x:v>
       </x:c>
       <x:c r="M14" s="10" t="str">
-        <x:v>白陌重生回到2004年高考夜，果断避开前世陷害自己的宾馆陷阱，救下被下药的校花江洛菡，彻底扭转人生走向。他不再执着于过往的情感执念，跳出卑微追爱的困局，转而关心恩师健康、规划学业与创业方向，结识志同道合的伙伴。凭借重生阅历清醒选择前路，把握青春重启人生，用行动改写原本遗憾的命运，活出全新成长轨迹。</x:v>
+        <x:v>阿梨一觉睡了三百年，养大的五只小兽尽数离去。她带着五只旧饭碗、十二枚铜钱与一把锈柴刀下山寻兽。昔日的小家伙已成威震四方的妖祖，历经重重相遇与揭秘，阿梨知晓三百年封印的真相，携手五只妖祖，一同对抗祸世灭灵兽神。</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>凤阙承安</x:v>
+        <x:v>美颜系统开挂，大佬全跪下</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>09-09 00:10</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
         <x:v>7</x:v>
@@ -3186,24 +3086,30 @@
       <x:c r="G15" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H15" s="11" t="str"/>
+      <x:c r="H15" s="11" t="n">
+        <x:v>172</x:v>
+      </x:c>
       <x:c r="I15" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J15" s="11" t="str"/>
       <x:c r="K15" s="11" t="str"/>
-      <x:c r="L15" s="10" t="str"/>
-      <x:c r="M15" s="10" t="str"/>
+      <x:c r="L15" s="10" t="str">
+        <x:v>御儿</x:v>
+      </x:c>
+      <x:c r="M15" s="10" t="str">
+        <x:v>曾因外形饱受非议的米珂华丽转身，蜕变得耀眼又夺目。从前对她嗤之以鼻的蒋少开始频频在意，素来冷眼毒舌的陆总不知不觉深陷其中，连一向克己的商界大佬也为她打破原则。米珂凭智商与手腕周旋于众人之间，上演一场势均力敌的情感博弈。没有俗套的救赎，只有双向的拉扯。看一众高高在上的精英暗自较劲、步步沉沦，心甘情愿为她卸下防备。</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>天灾末世，她囤满物资后所向披靡！</x:v>
+        <x:v>全家施压：我反手签了过户合同</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>09-08 15:00</x:v>
+        <x:v>09-08 16:58</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
         <x:v>7</x:v>
@@ -3218,7 +3124,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="H16" s="11" t="n">
-        <x:v>536</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str">
         <x:v>其他</x:v>
@@ -3226,36 +3132,36 @@
       <x:c r="J16" s="11" t="str"/>
       <x:c r="K16" s="11" t="str"/>
       <x:c r="L16" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
+        <x:v>灵川剧场</x:v>
       </x:c>
       <x:c r="M16" s="10" t="str">
-        <x:v>韩清夏被至亲推向绝境，失去家园，没能守住重要伙伴。再次睁眼，她回到了灾变来临前，并意外激活超级领主系统。她果断卖房筹资、囤积物资，将废弃防空洞升级为坚固基地，与战犬夏天并肩成长。危机爆发后，她凭借清醒判断、强大异能和充足准备救下幸存者，组建盛夏联盟。面对旧日亲人的算计、各方势力的试探与接连不断的考验，韩清夏不再退让。这一世，她要守住伙伴、掌握命运，在废墟之上建起属于自己的家园。</x:v>
+        <x:v>儿子儿媳多次提议我搬回乡下养老，将城里的宽敞住房腾出来给女方父母长期居住。我笑着点头应下，转头便将这套三室朝南的江景房产挂牌出售，最终成交二百八十万元。我随即购置了一套一室一厅的小户型，更换门锁后独自入住。他们上门索要钥匙，我没有开门。名下房产我自有主张，谁也别想插手安排。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>蒙蒙半故</x:v>
+        <x:v>征地我秒签跑路，全村笑我半年</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>09-05 20:27</x:v>
+        <x:v>09-10 11:30</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F17" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G17" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H17" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I17" s="10" t="str">
         <x:v>其他</x:v>
@@ -3263,36 +3169,36 @@
       <x:c r="J17" s="11" t="str"/>
       <x:c r="K17" s="11" t="str"/>
       <x:c r="L17" s="10" t="str">
-        <x:v>小斐漫剧</x:v>
+        <x:v>小六动漫</x:v>
       </x:c>
       <x:c r="M17" s="10" t="str">
-        <x:v>拥有漫长寿命的男人隐姓埋名，以外卖员身份在都市生活。百岁老人临终的遗愿，让他卷入豪门家族的纷争。他结识家族女总裁，接连应对家族内斗、敌对势力与神秘长生组织的重重算计。二人携手揭开千年前的尘封秘辛，对抗妄图窃取长生力量的反派，在危机之中彼此羁绊，还要面对即将开启的上古昆仑之门带来的巨大未知考验。</x:v>
+        <x:v>赵家湾迎来高速征地，村民受村长赵德厚鼓动抱团拒签，妄想抬价拿到四百五十万补偿。林远察觉当地岩溶地质暗藏线路改线风险，不顾全村嘲讽，果断签下312万补偿款，带父母搬离老家。后续高速果真改线，全村一分补偿落空。曾经嘲笑林远的村民陷入债务困境，赵德厚登门求助，林远守住底线，一家人握紧安稳生活，告诫众人抉择要靠自己。</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>全家施压：我反手签了过户合同</x:v>
+        <x:v>重生后我守住全村</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>09-08 16:58</x:v>
+        <x:v>09-10 08:08</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G18" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H18" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="I18" s="10" t="str">
         <x:v>其他</x:v>
@@ -3300,73 +3206,67 @@
       <x:c r="J18" s="11" t="str"/>
       <x:c r="K18" s="11" t="str"/>
       <x:c r="L18" s="10" t="str">
-        <x:v>灵川剧场</x:v>
+        <x:v>金果漫剧</x:v>
       </x:c>
       <x:c r="M18" s="10" t="str">
-        <x:v>儿子儿媳多次提议我搬回乡下养老，将城里的宽敞住房腾出来给女方父母长期居住。我笑着点头应下，转头便将这套三室朝南的江景房产挂牌出售，最终成交二百八十万元。我随即购置了一套一室一厅的小户型，更换门锁后独自入住。他们上门索要钥匙，我没有开门。名下房产我自有主张，谁也别想插手安排。</x:v>
+        <x:v>70年代冬，赵满仓在父亲离世后重回鼠灾前八天。面对家中骤变，他选择先护住亲人，带着前世经验迁入碾坊，储粮备药，筑墙防鼠，设点防疫。灾情来临时，他联合李杏儿，刘石头和乡亲稳住村庄，并用账册与规矩澄清父亲名誉。风雪过后，黎家沟建起防鼠坊，猫舍和净粮地窖，众人也在互助中迎来新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="n">
-        <x:v>77</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>我的奇葩舍友</x:v>
+        <x:v>假老板娘遇上真董事长</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>09-06 09:55</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G19" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H19" s="11" t="n">
-        <x:v>59</x:v>
-      </x:c>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H19" s="11" t="str"/>
       <x:c r="I19" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J19" s="11" t="str"/>
       <x:c r="K19" s="11" t="str"/>
-      <x:c r="L19" s="10" t="str">
-        <x:v>金鱼漫剪</x:v>
-      </x:c>
-      <x:c r="M19" s="10" t="str">
-        <x:v>林嘉宝从小由母亲周美兰一手带大，事无巨细都由妈妈安排。上大学后，他不会套被套，不会洗衣服，遇事第一反应是打电话问妈妈。母亲为他定下各种宿舍规矩，与室友矛盾不断。直到家中突遭变故，父亲破产，豪宅被封，母亲失联。嘉宝一夜之间失去所有依靠，被迫独自面对生活，一步步学会洗衣、打工、交电费，逐渐成为独立的大学生。</x:v>
-      </x:c>
+      <x:c r="L19" s="10" t="str"/>
+      <x:c r="M19" s="10" t="str"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>那块玉，带我们回家</x:v>
+        <x:v>大坝边寻回的真千金</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>09-05 07:18</x:v>
+        <x:v>09-10 11:26</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G20" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H20" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I20" s="10" t="str">
         <x:v>其他</x:v>
@@ -3374,36 +3274,36 @@
       <x:c r="J20" s="11" t="str"/>
       <x:c r="K20" s="11" t="str"/>
       <x:c r="L20" s="10" t="str">
-        <x:v>五指毛桃</x:v>
+        <x:v>喵琪琪追剧</x:v>
       </x:c>
       <x:c r="M20" s="10" t="str">
-        <x:v>六岁孩童为救母拾荒半年，孝心感动天地，更牵出一段失散六年的亲情。缘分以信物为引，助离散一家重逢。当暗处之手伸向团圆，真相与信任如光破晓，令恶念无处遁形。正义为善良护航，温暖在守望中生长。孩子用稚嫩肩膀撑起希望，父母以爱重筑家园，善意在风雨中传递，终迎阖家安康的晴空。</x:v>
+        <x:v>大坝突发险情，农村女孩夏晚禾凭借熟悉的环境和过人的勇气，不顾危险救下被困的沈长洲。一次意外的救援，让两个陌生人的命运重新交织。随着调查深入，沈长洲发现这个善良坚韧的女孩，竟是自己失散二十年的亲生女儿。面对迟来的亲情和真假千金的风波，夏晚禾没有依靠身份改变人生，而是用智慧、担当和努力证明自己的价值。陆言川也在一次次并肩相处中，被她的真诚与坚强打动，陪她找回亲情，走向新的未来。</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>征地我秒签跑路，全村笑我半年</x:v>
+        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>09-10 11:30</x:v>
+        <x:v>09-11 09:00</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E21" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E21" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="F21" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G21" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H21" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="I21" s="10" t="str">
         <x:v>其他</x:v>
@@ -3411,36 +3311,36 @@
       <x:c r="J21" s="11" t="str"/>
       <x:c r="K21" s="11" t="str"/>
       <x:c r="L21" s="10" t="str">
-        <x:v>小六动漫</x:v>
+        <x:v>阳阳动画</x:v>
       </x:c>
       <x:c r="M21" s="10" t="str">
-        <x:v>赵家湾迎来高速征地，村民受村长赵德厚鼓动抱团拒签，妄想抬价拿到四百五十万补偿。林远察觉当地岩溶地质暗藏线路改线风险，不顾全村嘲讽，果断签下312万补偿款，带父母搬离老家。后续高速果真改线，全村一分补偿落空。曾经嘲笑林远的村民陷入债务困境，赵德厚登门求助，林远守住底线，一家人握紧安稳生活，告诫众人抉择要靠自己。</x:v>
+        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>重生后我守住全村</x:v>
+        <x:v>穿越60我有空间不愁吃喝</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>09-10 08:08</x:v>
+        <x:v>09-07 00:04</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E22" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E22" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="F22" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G22" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H22" s="11" t="n">
-        <x:v>129</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str">
         <x:v>其他</x:v>
@@ -3448,36 +3348,36 @@
       <x:c r="J22" s="11" t="str"/>
       <x:c r="K22" s="11" t="str"/>
       <x:c r="L22" s="10" t="str">
-        <x:v>金果漫剧</x:v>
+        <x:v>夜珠AI剧场</x:v>
       </x:c>
       <x:c r="M22" s="10" t="str">
-        <x:v>70年代冬，赵满仓在父亲离世后重回鼠灾前八天。面对家中骤变，他选择先护住亲人，带着前世经验迁入碾坊，储粮备药，筑墙防鼠，设点防疫。灾情来临时，他联合李杏儿，刘石头和乡亲稳住村庄，并用账册与规矩澄清父亲名誉。风雪过后，黎家沟建起防鼠坊，猫舍和净粮地窖，众人也在互助中迎来新生。</x:v>
+        <x:v>现代青年刘大壮意外穿越到60年代，成了同名同姓的16岁穷小子。原主因相亲被拒、家徒四壁，下河摸鱼时溺亡。大壮醒来后发现脑中多了一座九层宝塔空间——内有灵药田与灵泉潭水，作物两小时成熟、产量翻五倍。饥荒年代，别人啃树皮喝稀粥，他靠空间种出满仓土豆粮食，黑市换粮票钞票，让饿肚子的父母姐姐们吃上饱饭。从人人嘲笑的穷小子，到带着全家逆袭翻盘，且看他手握宝塔空间，在艰苦年代闯出一条吃喝不愁的逆袭</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>大坝边寻回的真千金</x:v>
+        <x:v>三分钱的取舍</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>09-10 11:26</x:v>
+        <x:v>09-10 17:29</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G23" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H23" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
         <x:v>其他</x:v>
@@ -3485,33 +3385,33 @@
       <x:c r="J23" s="11" t="str"/>
       <x:c r="K23" s="11" t="str"/>
       <x:c r="L23" s="10" t="str">
-        <x:v>喵琪琪追剧</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="M23" s="10" t="str">
-        <x:v>大坝突发险情，农村女孩夏晚禾凭借熟悉的环境和过人的勇气，不顾危险救下被困的沈长洲。一次意外的救援，让两个陌生人的命运重新交织。随着调查深入，沈长洲发现这个善良坚韧的女孩，竟是自己失散二十年的亲生女儿。面对迟来的亲情和真假千金的风波，夏晚禾没有依靠身份改变人生，而是用智慧、担当和努力证明自己的价值。陆言川也在一次次并肩相处中，被她的真诚与坚强打动，陪她找回亲情，走向新的未来。</x:v>
+        <x:v>青石沟果农为省下代办三分钱，甩开中间商周成岳，直接对接收购商方洪生收桃。可脱离周成岳统筹调度后，摘桃、排单、装车乱象丛生，桃子积压损耗。周成岳转身接手偏远的十里湾桃园，凭口碑站稳脚跟。经历一季波折，青石沟众人幡然醒悟，重新读懂代办的价值。</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>假老板娘遇上真董事长</x:v>
+        <x:v>回到零四年进军彩铃界</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E24" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E24" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="F24" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G24" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H24" s="11" t="str"/>
       <x:c r="I24" s="10" t="str">
@@ -3524,28 +3424,28 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>赶海人生：重回1983小渔村</x:v>
+        <x:v>大力末世降临，小尸尸我呀吸吸吸</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>09-10 08:55</x:v>
+        <x:v>09-05 06:39</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G25" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H25" s="11" t="n">
-        <x:v>158</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str">
         <x:v>其他</x:v>
@@ -3553,220 +3453,10 @@
       <x:c r="J25" s="11" t="str"/>
       <x:c r="K25" s="11" t="str"/>
       <x:c r="L25" s="10" t="str">
-        <x:v>梦落漫漫</x:v>
+        <x:v>漫剧传送门</x:v>
       </x:c>
       <x:c r="M25" s="10" t="str">
-        <x:v>前世杨建国跳海离世，意外重生回到1983年东沟小渔村。这一年开海祭龙王，妻子即将遭遇毒蛇险境，家中穷困潦倒，伯父还妄图霸占自家渔船。曾经的街溜子幡然醒悟，凭借超前记忆踏海赶海，捕捞对虾、鲍鱼，对抗邻里刁难，守护妻儿老小，在汹涌海潮之中改写一家人贫苦命运。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="11" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B26" s="10" t="str">
-        <x:v>三分钱的取舍</x:v>
-      </x:c>
-      <x:c r="C26" s="11" t="str">
-        <x:v>09-10 17:29</x:v>
-      </x:c>
-      <x:c r="D26" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E26" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F26" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G26" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H26" s="11" t="n">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="I26" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J26" s="11" t="str"/>
-      <x:c r="K26" s="11" t="str"/>
-      <x:c r="L26" s="10" t="str">
-        <x:v>马克动漫</x:v>
-      </x:c>
-      <x:c r="M26" s="10" t="str">
-        <x:v>青石沟果农为省下代办三分钱，甩开中间商周成岳，直接对接收购商方洪生收桃。可脱离周成岳统筹调度后，摘桃、排单、装车乱象丛生，桃子积压损耗。周成岳转身接手偏远的十里湾桃园，凭口碑站稳脚跟。经历一季波折，青石沟众人幡然醒悟，重新读懂代办的价值。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="11" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B27" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
-      </x:c>
-      <x:c r="C27" s="11" t="str">
-        <x:v>09-11 09:00</x:v>
-      </x:c>
-      <x:c r="D27" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E27" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F27" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G27" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H27" s="11" t="n">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="I27" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J27" s="11" t="str"/>
-      <x:c r="K27" s="11" t="str"/>
-      <x:c r="L27" s="10" t="str">
-        <x:v>阳阳动画</x:v>
-      </x:c>
-      <x:c r="M27" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="11" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B28" s="10" t="str">
-        <x:v>穿越60我有空间不愁吃喝</x:v>
-      </x:c>
-      <x:c r="C28" s="11" t="str">
-        <x:v>09-07 00:04</x:v>
-      </x:c>
-      <x:c r="D28" s="11" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E28" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F28" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G28" s="11" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H28" s="11" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-      <x:c r="I28" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J28" s="11" t="str"/>
-      <x:c r="K28" s="11" t="str"/>
-      <x:c r="L28" s="10" t="str">
-        <x:v>夜珠AI剧场</x:v>
-      </x:c>
-      <x:c r="M28" s="10" t="str">
-        <x:v>现代青年刘大壮意外穿越到60年代，成了同名同姓的16岁穷小子。原主因相亲被拒、家徒四壁，下河摸鱼时溺亡。大壮醒来后发现脑中多了一座九层宝塔空间——内有灵药田与灵泉潭水，作物两小时成熟、产量翻五倍。饥荒年代，别人啃树皮喝稀粥，他靠空间种出满仓土豆粮食，黑市换粮票钞票，让饿肚子的父母姐姐们吃上饱饭。从人人嘲笑的穷小子，到带着全家逆袭翻盘，且看他手握宝塔空间，在艰苦年代闯出一条吃喝不愁的逆袭</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="11" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B29" s="10" t="str">
-        <x:v>回到零四年进军彩铃界</x:v>
-      </x:c>
-      <x:c r="C29" s="11" t="str">
-        <x:v>2026-09-11</x:v>
-      </x:c>
-      <x:c r="D29" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E29" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F29" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G29" s="11" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H29" s="11" t="str"/>
-      <x:c r="I29" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="J29" s="11" t="str"/>
-      <x:c r="K29" s="11" t="str"/>
-      <x:c r="L29" s="10" t="str"/>
-      <x:c r="M29" s="10" t="str"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="11" t="n">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="B30" s="10" t="str">
-        <x:v>一张废票毁了她</x:v>
-      </x:c>
-      <x:c r="C30" s="11" t="str">
-        <x:v>2026-09-11</x:v>
-      </x:c>
-      <x:c r="D30" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E30" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F30" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G30" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H30" s="11" t="str"/>
-      <x:c r="I30" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="J30" s="11" t="str"/>
-      <x:c r="K30" s="11" t="str"/>
-      <x:c r="L30" s="10" t="str"/>
-      <x:c r="M30" s="10" t="str"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="11" t="n">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="B31" s="10" t="str">
-        <x:v>张兰芬重生记</x:v>
-      </x:c>
-      <x:c r="C31" s="11" t="str">
-        <x:v>09-05 17:00</x:v>
-      </x:c>
-      <x:c r="D31" s="11" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E31" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F31" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G31" s="11" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H31" s="11" t="n">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="I31" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J31" s="11" t="str"/>
-      <x:c r="K31" s="11" t="str"/>
-      <x:c r="L31" s="10" t="str">
-        <x:v>璀璨Ai剧场</x:v>
-      </x:c>
-      <x:c r="M31" s="10" t="str">
-        <x:v>张兰芬操劳半生，是旁人羡慕的当家主母。她为李家养育四子两女，持家有道、将家中大小事务打理得井井有条。半生付出尽数落空，张兰芬郁结于心，最终含恨病逝医院。一朝重生，她回到所有遗憾尚未发生之时，彻底看透人心，决意放下执念，好好为自己活一次。</x:v>
+        <x:v>末世降临前三分钟，互联网实习生许多多收到末日预警，凭借超强求生本能疯狂囤货，固守自家堡垒苟命求生。可末世浩劫之下，她依旧不幸感染病毒，意外蜕变为保留完整人类意识的特殊丧尸，同时解锁无限扩容的多面魔方空间。半月后，3A特殊作战小队前来清剿，带队队长竟是她年少暗恋的同桌秦洛。知晓她的特殊异能与理智后，秦洛将她收留，她自此成为小队最强辅助与移动军需库。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3821,16 +3511,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
-        <x:v>1.7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F2" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>2026-09-15 09-53</x:v>
+        <x:v>2026-09-15 12-43</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3838,22 +3528,22 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
+        <x:v>征地我秒签跑路，全村笑我半年</x:v>
       </x:c>
       <x:c r="C3" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
-        <x:v>7.2</x:v>
+        <x:v>2.6</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F3" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>2026-09-15 09-53</x:v>
+        <x:v>2026-09-15 12-43</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -3861,22 +3551,22 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>征地我秒签跑路，全村笑我半年</x:v>
+        <x:v>今晚查寝，别开门</x:v>
       </x:c>
       <x:c r="C4" s="11" t="n">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>2.3</x:v>
+        <x:v>5.7</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F4" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>2026-09-15 09-53</x:v>
+        <x:v>2026-09-15 12-43</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3890,16 +3580,16 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>7.3</x:v>
+        <x:v>7.7</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F5" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>2026-09-15 09-53</x:v>
+        <x:v>2026-09-15 12-43</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -3907,22 +3597,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>重生三天前，我用水泥封死地下室</x:v>
+        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
       </x:c>
       <x:c r="C6" s="11" t="n">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>11.7</x:v>
+        <x:v>7.9</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F6" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>2026-09-15 09-53</x:v>
+        <x:v>2026-09-15 11-11</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3930,22 +3620,22 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>今晚查寝，别开门</x:v>
+        <x:v>重生三天前，我用水泥封死地下室</x:v>
       </x:c>
       <x:c r="C7" s="11" t="n">
         <x:v>27</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>5.6</x:v>
+        <x:v>11.6</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F7" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>2026-09-15 09-53</x:v>
+        <x:v>2026-09-15 10-11</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -3959,16 +3649,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>8.7</x:v>
+        <x:v>8.3</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>2026-09-15 09-53</x:v>
+        <x:v>2026-09-15 12-43</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3976,22 +3666,22 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>泰城错嫁</x:v>
+        <x:v>破库房的秘密</x:v>
       </x:c>
       <x:c r="C9" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>12.2</x:v>
+        <x:v>14.3</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>2026-09-15 09-53</x:v>
+        <x:v>2026-09-15 12-43</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -4002,19 +3692,19 @@
         <x:v>退婚后我在七零赚钱养家致富</x:v>
       </x:c>
       <x:c r="C10" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>11.7</x:v>
+        <x:v>12.6</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F10" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>2026-09-15 09-53</x:v>
+        <x:v>2026-09-15 10-11</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -4022,22 +3712,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>破库房的秘密</x:v>
+        <x:v>一墙之隔，皆是人心</x:v>
       </x:c>
       <x:c r="C11" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>13.8</x:v>
+        <x:v>13.4</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
-        <x:v>2026-09-15 09-11</x:v>
+        <x:v>2026-09-15 10-11</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -4045,19 +3735,19 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>一墙之隔，皆是人心</x:v>
+        <x:v>泰城错嫁</x:v>
       </x:c>
       <x:c r="C12" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>13.9</x:v>
+        <x:v>12.1</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G12" s="11" t="str">
         <x:v>2026-09-15 09-53</x:v>
@@ -4068,19 +3758,19 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
+        <x:v>惊絮无声：傻女的绝杀</x:v>
       </x:c>
       <x:c r="C13" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>11.6</x:v>
+        <x:v>12.3</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G13" s="11" t="str">
         <x:v>2026-09-15 06-08</x:v>
@@ -4091,19 +3781,19 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>惊絮无声：傻女的绝杀</x:v>
+        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
       </x:c>
       <x:c r="C14" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>12.4</x:v>
+        <x:v>11.7</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G14" s="11" t="str">
         <x:v>2026-09-15 06-08</x:v>
@@ -4114,19 +3804,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>离家十年，回来女儿被换了</x:v>
+        <x:v>三分钱的取舍</x:v>
       </x:c>
       <x:c r="C15" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>10.3</x:v>
+        <x:v>13.5</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F15" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G15" s="11" t="str">
         <x:v>2026-09-15 09-53</x:v>
@@ -4137,22 +3827,22 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>三分钱的取舍</x:v>
+        <x:v>青牛引泉来</x:v>
       </x:c>
       <x:c r="C16" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>13.5</x:v>
+        <x:v>11.1</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G16" s="11" t="str">
-        <x:v>2026-09-15 09-53</x:v>
+        <x:v>2026-09-15 12-43</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -4160,22 +3850,22 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>锦书迟</x:v>
+        <x:v>离家十年，回来女儿被换了</x:v>
       </x:c>
       <x:c r="C17" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>12.9</x:v>
+        <x:v>9.8</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F17" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G17" s="11" t="str">
-        <x:v>2026-09-15 02-44</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -4183,22 +3873,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>今天开始做裴总</x:v>
+        <x:v>锦书迟</x:v>
       </x:c>
       <x:c r="C18" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>12.9</x:v>
+        <x:v>13.6</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G18" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-15 02-44</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -4206,22 +3896,22 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>小妹初长成</x:v>
+        <x:v>穿书后我带萌宝上门认爹</x:v>
       </x:c>
       <x:c r="C19" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>12.7</x:v>
+        <x:v>15.8</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G19" s="11" t="str">
-        <x:v>2026-09-14 12-34</x:v>
+        <x:v>2026-09-15 11-11</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -4229,22 +3919,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>青牛引泉来</x:v>
+        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
       </x:c>
       <x:c r="C20" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>9.6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G20" s="11" t="str">
-        <x:v>2026-09-15 09-53</x:v>
+        <x:v>2026-09-15 12-43</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -4252,22 +3942,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>反派拿捏！</x:v>
+        <x:v>今天开始做裴总</x:v>
       </x:c>
       <x:c r="C21" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>14.7</x:v>
+        <x:v>14.2</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G21" s="11" t="str">
-        <x:v>2026-09-14 20-13</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -4275,22 +3965,22 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>穿书后我带萌宝上门认爹</x:v>
+        <x:v>反派拿捏！</x:v>
       </x:c>
       <x:c r="C22" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>15.7</x:v>
+        <x:v>14.7</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G22" s="11" t="str">
-        <x:v>2026-09-15 09-53</x:v>
+        <x:v>2026-09-14 20-13</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -4298,22 +3988,22 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>婚礼当天我不嫁了</x:v>
+        <x:v>不靠谱爸妈很靠谱</x:v>
       </x:c>
       <x:c r="C23" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>14.8</x:v>
+        <x:v>15.3</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G23" s="11" t="str">
-        <x:v>2026-09-14 22-12</x:v>
+        <x:v>2026-09-15 11-11</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -4321,22 +4011,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>不靠谱爸妈很靠谱</x:v>
+        <x:v>搬进江景房，老公每晚对着鱼缸坐两小时</x:v>
       </x:c>
       <x:c r="C24" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>15.5</x:v>
+        <x:v>7.9</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G24" s="11" t="str">
-        <x:v>2026-09-15 09-53</x:v>
+        <x:v>2026-09-15 12-43</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -4344,22 +4034,22 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
+        <x:v>小妹初长成</x:v>
       </x:c>
       <x:c r="C25" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>3.4</x:v>
+        <x:v>14.4</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G25" s="11" t="str">
-        <x:v>2026-09-15 09-53</x:v>
+        <x:v>2026-09-14 12-34</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -4367,22 +4057,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>回到零四年进军彩铃界</x:v>
+        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
       </x:c>
       <x:c r="C26" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>16.6</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G26" s="11" t="str">
-        <x:v>2026-09-14 12-34</x:v>
+        <x:v>2026-09-15 12-43</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -4390,22 +4080,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>装傻下山</x:v>
+        <x:v>婚礼当天我不嫁了</x:v>
       </x:c>
       <x:c r="C27" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>8.2</x:v>
+        <x:v>14.8</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str">
-        <x:v>2026-09-14 04-11</x:v>
+        <x:v>2026-09-14 22-12</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -4413,22 +4103,22 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>搬进江景房，老公每晚对着鱼缸坐两小时</x:v>
+        <x:v>四个崽崽瞒不住了</x:v>
       </x:c>
       <x:c r="C28" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
-        <x:v>6.5</x:v>
+        <x:v>16.1</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F28" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G28" s="11" t="str">
-        <x:v>2026-09-15 09-53</x:v>
+        <x:v>2026-09-15 10-11</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -4436,22 +4126,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
+        <x:v>回到零四年进军彩铃界</x:v>
       </x:c>
       <x:c r="C29" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>15.5</x:v>
+        <x:v>16.6</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str">
-        <x:v>2026-09-15 09-53</x:v>
+        <x:v>2026-09-14 12-34</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -4459,22 +4149,22 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>穿越60我有空间不愁吃喝</x:v>
+        <x:v>重生80，救下神雕后我带村民走出大山</x:v>
       </x:c>
       <x:c r="C30" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>15.7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G30" s="11" t="str">
-        <x:v>2026-09-14 20-18</x:v>
+        <x:v>2026-09-15 12-43</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -4482,22 +4172,22 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
+        <x:v>穿越60我有空间不愁吃喝</x:v>
       </x:c>
       <x:c r="C31" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
-        <x:v>12.2</x:v>
+        <x:v>15.7</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G31" s="11" t="str">
-        <x:v>2026-09-15 09-53</x:v>
+        <x:v>2026-09-14 20-18</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -4551,22 +4241,22 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="10" t="str">
-        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
+        <x:v>15年青春苦守，未婚夫装穷归来</x:v>
       </x:c>
       <x:c r="C34" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D34" s="11" t="n">
-        <x:v>17.2</x:v>
+        <x:v>5.2</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F34" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G34" s="11" t="str">
-        <x:v>2026-09-14 06-11</x:v>
+        <x:v>2026-09-15 12-43</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -4574,22 +4264,22 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="10" t="str">
-        <x:v>重生后我守住全村</x:v>
+        <x:v>新厂旧账</x:v>
       </x:c>
       <x:c r="C35" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D35" s="11" t="n">
-        <x:v>5.8</x:v>
+        <x:v>5.2</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F35" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="G35" s="11" t="str">
-        <x:v>2026-09-14 20-18</x:v>
+        <x:v>2026-09-15 12-43</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -4597,22 +4287,22 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="10" t="str">
-        <x:v>离婚那天我多了个痞帅老爹</x:v>
+        <x:v>重生后我守住全村</x:v>
       </x:c>
       <x:c r="C36" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
-        <x:v>11.2</x:v>
+        <x:v>5.8</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G36" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-14 20-18</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -4620,22 +4310,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="10" t="str">
-        <x:v>这桌团圆饭，我不做了</x:v>
+        <x:v>离婚那天我多了个痞帅老爹</x:v>
       </x:c>
       <x:c r="C37" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D37" s="11" t="n">
-        <x:v>16.5</x:v>
+        <x:v>11.2</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G37" s="11" t="str">
-        <x:v>2026-09-14 03-11</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -4643,22 +4333,22 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="10" t="str">
-        <x:v>重生80，救下神雕后我带村民走出大山</x:v>
+        <x:v>辣媳进门，我给公婆撑腰</x:v>
       </x:c>
       <x:c r="C38" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D38" s="11" t="n">
-        <x:v>18.2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F38" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G38" s="11" t="str">
-        <x:v>2026-09-15 09-53</x:v>
+        <x:v>2026-09-15 06-08</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -4666,22 +4356,22 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="10" t="str">
-        <x:v>辣媳进门，我给公婆撑腰</x:v>
+        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
       </x:c>
       <x:c r="C39" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D39" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8.7</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G39" s="11" t="str">
-        <x:v>2026-09-15 06-08</x:v>
+        <x:v>2026-09-15 01-59</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -4689,22 +4379,22 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="10" t="str">
-        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
+        <x:v>装傻下山</x:v>
       </x:c>
       <x:c r="C40" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D40" s="11" t="n">
-        <x:v>8.7</x:v>
+        <x:v>11.7</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G40" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-14 04-11</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -4781,22 +4471,22 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="10" t="str">
-        <x:v>谢谢爸妈的穷养现在我富了</x:v>
+        <x:v>那块玉，带我们回家</x:v>
       </x:c>
       <x:c r="C44" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D44" s="11" t="n">
-        <x:v>10.7</x:v>
+        <x:v>11.3</x:v>
       </x:c>
       <x:c r="E44" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="F44" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G44" s="11" t="str">
-        <x:v>2026-09-14 02-11</x:v>
+        <x:v>2026-09-14 09-24</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -4804,22 +4494,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="10" t="str">
-        <x:v>那块玉，带我们回家</x:v>
+        <x:v>拂衣震九州</x:v>
       </x:c>
       <x:c r="C45" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D45" s="11" t="n">
-        <x:v>11.3</x:v>
+        <x:v>10.3</x:v>
       </x:c>
       <x:c r="E45" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F45" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G45" s="11" t="str">
-        <x:v>2026-09-14 09-24</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -4827,19 +4517,19 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B46" s="10" t="str">
-        <x:v>拂衣震九州</x:v>
+        <x:v>大坝边寻回的真千金</x:v>
       </x:c>
       <x:c r="C46" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D46" s="11" t="n">
-        <x:v>10.3</x:v>
+        <x:v>12.7</x:v>
       </x:c>
       <x:c r="E46" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F46" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G46" s="11" t="str">
         <x:v>2026-09-15 03-38</x:v>
@@ -4850,19 +4540,19 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B47" s="10" t="str">
-        <x:v>大坝边寻回的真千金</x:v>
+        <x:v>山下是绝路，山上是生门</x:v>
       </x:c>
       <x:c r="C47" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D47" s="11" t="n">
-        <x:v>12.7</x:v>
+        <x:v>14.3</x:v>
       </x:c>
       <x:c r="E47" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F47" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G47" s="11" t="str">
         <x:v>2026-09-15 03-38</x:v>
@@ -4873,22 +4563,22 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B48" s="10" t="str">
-        <x:v>山下是绝路，山上是生门</x:v>
+        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
       </x:c>
       <x:c r="C48" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D48" s="11" t="n">
-        <x:v>14.3</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E48" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F48" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G48" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-14 06-11</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -4896,22 +4586,22 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B49" s="10" t="str">
-        <x:v>退婚从抢我车位开始</x:v>
+        <x:v>八零悍妇：女汉子逆袭记</x:v>
       </x:c>
       <x:c r="C49" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D49" s="11" t="n">
-        <x:v>15.3</x:v>
+        <x:v>5.5</x:v>
       </x:c>
       <x:c r="E49" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F49" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G49" s="11" t="str">
-        <x:v>2026-09-14 20-18</x:v>
+        <x:v>2026-09-15 12-43</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -9933,8 +9623,12 @@
       <x:c r="G106" s="10" t="str">
         <x:v>不周山漫剧</x:v>
       </x:c>
-      <x:c r="H106" s="11" t="str"/>
-      <x:c r="I106" s="10" t="str"/>
+      <x:c r="H106" s="11" t="str">
+        <x:v>已上榜</x:v>
+      </x:c>
+      <x:c r="I106" s="10" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
       <x:c r="J106" s="10" t="str">
         <x:v>末世异能者唐知夏穿成农女，被迫嫁给厌食失语、命不久矣的哑巴王爷林霄。为避开原著死局，她用木系异能辅以种田美食，治愈王爷顽疾，却意外收获先婚后爱的真情。期间智斗绿茶堂妹、暴打普信表哥，更与穿书反派白如玉展开正妻争夺战，联手夫君反击构陷、揭露阴谋。种田养夫日常甜宠，美食治病开局高能，反套路打脸爽感拉满——我带异能穿古，专治各种不服！</x:v>
       </x:c>
@@ -18370,27 +18064,27 @@
         <x:v>09-18 09:00</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
-        <x:v>弑天逆龙决</x:v>
+        <x:v>大伯的豪华婚房</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F8" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G8" s="10" t="str">
-        <x:v>未境剧场</x:v>
+        <x:v>琢曜-小杨看剧</x:v>
       </x:c>
       <x:c r="H8" s="11" t="str"/>
       <x:c r="I8" s="10" t="str"/>
       <x:c r="J8" s="10" t="str">
-        <x:v>太古时期，弑天龙帝被九大天帝围攻，又遭最器重的弟子暗算，陨落。三万多年后，借体重生，踏上复仇之路！修天功弑天逆龙决，诸多秘术，炼器、炼药、阵纹等无一不精！踩天才、压妖孽，势如破竹，无人能挡，誓要斩灭九大最强天帝，清理门户！</x:v>
+        <x:v>大伯为撑面子，扬言要给堂妹建全村最豪华婚房，还要重修村广场。他盯上我的装修贵宾账户，想暗中挂我的账买单。我提前设置付款密码，让他当众付款接连失败。吹下百万工程款的大伯骑虎难下，疯狂签下一堆增项，完工后才发现必须自己承担巨额账单。撒泼耍赖、冒签我的名字，还拿亲情道德绑架我。我手握全部证据，按合同拆除未付款装修，堂妹婚事告吹，大伯自食恶果，最后还被我一纸断亲书彻底划清界限。</x:v>
       </x:c>
       <x:c r="K8" s="10" t="str">
-        <x:v>发布账号「未境剧场」无榜单战绩，账号0分；题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；85集，主力长度</x:v>
+        <x:v>发布账号「琢曜-小杨看剧」稳定产出（上榜4次/出过4部），账号基础分；题材契合爆款主线×1（剧名/分类/简介三路识别）；52集，次优长度</x:v>
       </x:c>
       <x:c r="L8" s="11" t="n">
         <x:v>7</x:v>
@@ -18401,30 +18095,30 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>09-18 05:00</x:v>
+        <x:v>09-18 09:00</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
-        <x:v>重生抱紧武安王</x:v>
+        <x:v>弑天逆龙决</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>110</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F9" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="G9" s="10" t="str">
-        <x:v>豆包动画</x:v>
+        <x:v>未境剧场</x:v>
       </x:c>
       <x:c r="H9" s="11" t="str"/>
       <x:c r="I9" s="10" t="str"/>
       <x:c r="J9" s="10" t="str">
-        <x:v>沈穗岁亲眼目睹丈夫武安王为救自己自刎离世，带着无尽遗憾走完余生。一朝重生，这一次她幡然醒悟，果断手撕阴谋诡计的歹人丫鬟，主动退掉与薛云谦的婚约，远离虚伪薛云谦与心机表姐宁浅，她吸取前世教训，守护疼爱自己的父亲，凭借两世阅历看透朝堂风波。她记挂身中奇毒的裴肃，默默相助，想方设法助他。摒弃恋爱脑，她自立通透，不再执着情爱，兼顾亲情与道义，努力改写所有人的悲剧命运，勇敢奔赴属于自己的良缘与光明未来。</x:v>
+        <x:v>太古时期，弑天龙帝被九大天帝围攻，又遭最器重的弟子暗算，陨落。三万多年后，借体重生，踏上复仇之路！修天功弑天逆龙决，诸多秘术，炼器、炼药、阵纹等无一不精！踩天才、压妖孽，势如破竹，无人能挡，誓要斩灭九大最强天帝，清理门户！</x:v>
       </x:c>
       <x:c r="K9" s="10" t="str">
-        <x:v>发布账号「豆包动画」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；110集，次优长度；剧名钩子×1</x:v>
+        <x:v>发布账号「未境剧场」无榜单战绩，账号0分；题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；85集，主力长度</x:v>
       </x:c>
       <x:c r="L9" s="11" t="n">
         <x:v>7</x:v>
@@ -18435,13 +18129,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="11" t="str">
-        <x:v>09-18 10:00</x:v>
+        <x:v>09-18 05:00</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
-        <x:v>欢迎降落人间</x:v>
+        <x:v>重生抱紧武安王</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str">
         <x:v>其他</x:v>
@@ -18450,18 +18144,18 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G10" s="10" t="str">
-        <x:v>泰北剧场</x:v>
+        <x:v>豆包动画</x:v>
       </x:c>
       <x:c r="H10" s="11" t="str"/>
       <x:c r="I10" s="10" t="str"/>
       <x:c r="J10" s="10" t="str">
-        <x:v>心理医生林语笙闪婚特勤机长萧寒，婚后丈夫执行高危任务常年失联，她日夜忧心却独自支撑，霸气反击极品前任和同事的挑衅。萧寒带伤转岗后，她创立“云端的心跳”项目，用专业治愈飞行员高空创伤。在一次航班危机中，她稳定乘客情绪，协助丈夫指挥盲降成功，因过度紧张险些流产。幸得母女平安，家庭圆满。</x:v>
+        <x:v>沈穗岁亲眼目睹丈夫武安王为救自己自刎离世，带着无尽遗憾走完余生。一朝重生，这一次她幡然醒悟，果断手撕阴谋诡计的歹人丫鬟，主动退掉与薛云谦的婚约，远离虚伪薛云谦与心机表姐宁浅，她吸取前世教训，守护疼爱自己的父亲，凭借两世阅历看透朝堂风波。她记挂身中奇毒的裴肃，默默相助，想方设法助他。摒弃恋爱脑，她自立通透，不再执着情爱，兼顾亲情与道义，努力改写所有人的悲剧命运，勇敢奔赴属于自己的良缘与光明未来。</x:v>
       </x:c>
       <x:c r="K10" s="10" t="str">
-        <x:v>发布账号「泰北剧场」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；64集，主力长度；通用受众</x:v>
+        <x:v>发布账号「豆包动画」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；110集，次优长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="L10" s="11" t="n">
-        <x:v>6.5</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -18472,27 +18166,27 @@
         <x:v>09-18 10:00</x:v>
       </x:c>
       <x:c r="C11" s="10" t="str">
-        <x:v>福宝驾到</x:v>
+        <x:v>欢迎降落人间</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F11" s="10" t="str">
-        <x:v>萌宝治愈</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G11" s="10" t="str">
-        <x:v>笙笙不息剧场</x:v>
+        <x:v>泰北剧场</x:v>
       </x:c>
       <x:c r="H11" s="11" t="str"/>
       <x:c r="I11" s="10" t="str"/>
       <x:c r="J11" s="10" t="str">
-        <x:v>福宝出生那天，天降金龙，金元宝破土而出。原本倒霉的王文阳和妻子林婉，在福宝的好运加持下，从欠债的倒霉蛋逆袭成厨王，将福宝饭店开成了镇上最火的饭店。萌娃招财，母鸡镇宅，坏人遭殃，好人发财，福宝带领一家人把日子过得红红火火。</x:v>
+        <x:v>心理医生林语笙闪婚特勤机长萧寒，婚后丈夫执行高危任务常年失联，她日夜忧心却独自支撑，霸气反击极品前任和同事的挑衅。萧寒带伤转岗后，她创立“云端的心跳”项目，用专业治愈飞行员高空创伤。在一次航班危机中，她稳定乘客情绪，协助丈夫指挥盲降成功，因过度紧张险些流产。幸得母女平安，家庭圆满。</x:v>
       </x:c>
       <x:c r="K11" s="10" t="str">
-        <x:v>发布账号「笙笙不息剧场」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；通用受众</x:v>
+        <x:v>发布账号「泰北剧场」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；64集，主力长度；通用受众</x:v>
       </x:c>
       <x:c r="L11" s="11" t="n">
         <x:v>6.5</x:v>
@@ -18506,30 +18200,30 @@
         <x:v>09-18 10:00</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
-        <x:v>一笼包子暖一生</x:v>
+        <x:v>福宝驾到</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F12" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>萌宝治愈</x:v>
       </x:c>
       <x:c r="G12" s="10" t="str">
-        <x:v>鹿姐短剧</x:v>
+        <x:v>笙笙不息剧场</x:v>
       </x:c>
       <x:c r="H12" s="11" t="str"/>
       <x:c r="I12" s="10" t="str"/>
       <x:c r="J12" s="10" t="str">
-        <x:v>张默自幼家贫，被经营早餐铺的陈家夫妇好心收留。他刻苦读书、知恩图报，以优异成绩考上大学。多年后事业有成归来，帮助遇到困难的养兄重振早餐铺，还开设爱心窗口传递善意。一家人从隔阂到和解，用一餐一饭温暖彼此，演绎了平凡生活中的真情与成长。</x:v>
+        <x:v>福宝出生那天，天降金龙，金元宝破土而出。原本倒霉的王文阳和妻子林婉，在福宝的好运加持下，从欠债的倒霉蛋逆袭成厨王，将福宝饭店开成了镇上最火的饭店。萌娃招财，母鸡镇宅，坏人遭殃，好人发财，福宝带领一家人把日子过得红红火火。</x:v>
       </x:c>
       <x:c r="K12" s="10" t="str">
-        <x:v>发布账号「鹿姐短剧」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；85集，主力长度</x:v>
+        <x:v>发布账号「笙笙不息剧场」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；通用受众</x:v>
       </x:c>
       <x:c r="L12" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>6.5</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -18537,30 +18231,30 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="11" t="str">
-        <x:v>09-18 08:00</x:v>
+        <x:v>09-18 10:00</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
-        <x:v>七零：靠厨艺征服所有人</x:v>
+        <x:v>一笼包子暖一生</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F13" s="10" t="str">
-        <x:v>年代怀旧 / 美食治愈</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="G13" s="10" t="str">
-        <x:v>清染剧场</x:v>
+        <x:v>鹿姐短剧</x:v>
       </x:c>
       <x:c r="H13" s="11" t="str"/>
       <x:c r="I13" s="10" t="str"/>
       <x:c r="J13" s="10" t="str">
-        <x:v>北方农村姑娘乔麦穗身手强悍，却因体态丰腴愁婚嫁。她在后山救下受伤知青傅卫东，二人成婚。傅卫东意外昏迷，乔麦穗独自进城寻夫，途中勇擒扒手。小姑傅小玲持离婚协议逼她签字，当场被公安拆穿。傅母嫌弃她出身，杨小曼伺机想取代她。乔麦穗凭一手厨艺在医院食堂立足，接连挫败二人陷害。她怀双胞胎遭质疑，拿出孕检单自证清白。夫妻联手设局，揭露杨小曼制造车祸、策划绑架的罪行。乔麦穗凭实力收获事业与圆满家庭</x:v>
+        <x:v>张默自幼家贫，被经营早餐铺的陈家夫妇好心收留。他刻苦读书、知恩图报，以优异成绩考上大学。多年后事业有成归来，帮助遇到困难的养兄重振早餐铺，还开设爱心窗口传递善意。一家人从隔阂到和解，用一餐一饭温暖彼此，演绎了平凡生活中的真情与成长。</x:v>
       </x:c>
       <x:c r="K13" s="10" t="str">
-        <x:v>发布账号「清染剧场」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；61集，主力长度；女频受众</x:v>
+        <x:v>发布账号「鹿姐短剧」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；85集，主力长度</x:v>
       </x:c>
       <x:c r="L13" s="11" t="n">
         <x:v>6</x:v>
@@ -18571,30 +18265,30 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="11" t="str">
-        <x:v>09-18 08:30</x:v>
+        <x:v>09-18 08:00</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
-        <x:v>九洲影帝</x:v>
+        <x:v>七零：靠厨艺征服所有人</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F14" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>年代怀旧 / 美食治愈</x:v>
       </x:c>
       <x:c r="G14" s="10" t="str">
-        <x:v>白狼动画</x:v>
+        <x:v>清染剧场</x:v>
       </x:c>
       <x:c r="H14" s="11" t="str"/>
       <x:c r="I14" s="10" t="str"/>
       <x:c r="J14" s="10" t="str">
-        <x:v>十八年前，陆家伪造九色神光异象，为少主陆尘立下大帝转世人设，蒙蔽九州。十八年后，骗局即将败露，父亲陆寒却功成身退飞升仙界，将烂摊子尽数甩给陆尘。面对全九州的审视与试探，陆尘被迫以凡人之躯，靠演技、系统金手指与一张碎嘴，在一次次绝境中强行演戏、绝地求生，一步步将假帝演成真帝。</x:v>
+        <x:v>北方农村姑娘乔麦穗身手强悍，却因体态丰腴愁婚嫁。她在后山救下受伤知青傅卫东，二人成婚。傅卫东意外昏迷，乔麦穗独自进城寻夫，途中勇擒扒手。小姑傅小玲持离婚协议逼她签字，当场被公安拆穿。傅母嫌弃她出身，杨小曼伺机想取代她。乔麦穗凭一手厨艺在医院食堂立足，接连挫败二人陷害。她怀双胞胎遭质疑，拿出孕检单自证清白。夫妻联手设局，揭露杨小曼制造车祸、策划绑架的罪行。乔麦穗凭实力收获事业与圆满家庭</x:v>
       </x:c>
       <x:c r="K14" s="10" t="str">
-        <x:v>发布账号「白狼动画」无榜单战绩，账号0分；题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×2；75集，主力长度</x:v>
+        <x:v>发布账号「清染剧场」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；61集，主力长度；女频受众</x:v>
       </x:c>
       <x:c r="L14" s="11" t="n">
         <x:v>6</x:v>
@@ -18605,30 +18299,30 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="11" t="str">
-        <x:v>09-18 08:00</x:v>
+        <x:v>09-18 08:30</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
-        <x:v>公路求生：我能无限升级资源</x:v>
+        <x:v>九洲影帝</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>112</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F15" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G15" s="10" t="str">
-        <x:v>飞卢漫剧场</x:v>
+        <x:v>白狼动画</x:v>
       </x:c>
       <x:c r="H15" s="11" t="str"/>
       <x:c r="I15" s="10" t="str"/>
       <x:c r="J15" s="10" t="str">
-        <x:v>末世公路世界，陈博遭恋人与仇人联手背叛，险些死于异兽之口，濒死觉醒无限升级系统，万物皆可升级强化！他改造武器战车，收服寻宝战宠哈士奇，在危机四伏的戈壁求生复仇，结识夏安、周沫等伙伴。为对抗搞人体实验的邪恶组织黑玫区，他建立红叶盟，打造空中堡垒，横扫异兽与敌人。随着真相揭开，末世竟是高维文明深渊议会的筛选实验，人类只是实验品。陈博集结全球幸存者，迎战域外强敌，摧毁污染根源，净化星球，终结末日。</x:v>
+        <x:v>十八年前，陆家伪造九色神光异象，为少主陆尘立下大帝转世人设，蒙蔽九州。十八年后，骗局即将败露，父亲陆寒却功成身退飞升仙界，将烂摊子尽数甩给陆尘。面对全九州的审视与试探，陆尘被迫以凡人之躯，靠演技、系统金手指与一张碎嘴，在一次次绝境中强行演戏、绝地求生，一步步将假帝演成真帝。</x:v>
       </x:c>
       <x:c r="K15" s="10" t="str">
-        <x:v>发布账号「飞卢漫剧场」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；112集，次优长度</x:v>
+        <x:v>发布账号「白狼动画」无榜单战绩，账号0分；题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×2；75集，主力长度</x:v>
       </x:c>
       <x:c r="L15" s="11" t="n">
         <x:v>6</x:v>
@@ -18642,10 +18336,10 @@
         <x:v>09-18 08:00</x:v>
       </x:c>
       <x:c r="C16" s="10" t="str">
-        <x:v>别动我的车</x:v>
+        <x:v>公路求生：我能无限升级资源</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str">
         <x:v>其他</x:v>
@@ -18654,15 +18348,15 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G16" s="10" t="str">
-        <x:v>山海皆可平</x:v>
+        <x:v>飞卢漫剧场</x:v>
       </x:c>
       <x:c r="H16" s="11" t="str"/>
       <x:c r="I16" s="10" t="str"/>
       <x:c r="J16" s="10" t="str">
-        <x:v>李舒仪升职后通勤距离增加，想要取回自己的陪嫁车，却遭到公公霸占，丈夫还劝她骑电瓶车上班。公婆为留住车子，跑到她公司撒泼闹事，搅黄她来之不易的升职机会。李舒仪彻底清醒，决心结束婚姻。婆家不仅不愿归还车辆，还私自转走她五百万陪嫁，占用她的学区房。她步步维权，收回房产、追回钱款，与江述年顺利离婚，凭借自身实力重新争取到总监岗位，掌控自己的人生。</x:v>
+        <x:v>末世公路世界，陈博遭恋人与仇人联手背叛，险些死于异兽之口，濒死觉醒无限升级系统，万物皆可升级强化！他改造武器战车，收服寻宝战宠哈士奇，在危机四伏的戈壁求生复仇，结识夏安、周沫等伙伴。为对抗搞人体实验的邪恶组织黑玫区，他建立红叶盟，打造空中堡垒，横扫异兽与敌人。随着真相揭开，末世竟是高维文明深渊议会的筛选实验，人类只是实验品。陈博集结全球幸存者，迎战域外强敌，摧毁污染根源，净化星球，终结末日。</x:v>
       </x:c>
       <x:c r="K16" s="10" t="str">
-        <x:v>发布账号「山海皆可平」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；63集，主力长度；女频受众</x:v>
+        <x:v>发布账号「飞卢漫剧场」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；112集，次优长度</x:v>
       </x:c>
       <x:c r="L16" s="11" t="n">
         <x:v>6</x:v>
@@ -22100,8 +21794,12 @@
       <x:c r="G116" s="10" t="str">
         <x:v>不周山漫剧</x:v>
       </x:c>
-      <x:c r="H116" s="11" t="str"/>
-      <x:c r="I116" s="10" t="str"/>
+      <x:c r="H116" s="11" t="str">
+        <x:v>已上榜</x:v>
+      </x:c>
+      <x:c r="I116" s="10" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
       <x:c r="J116" s="10" t="str">
         <x:v>末世异能者唐知夏穿成农女，被迫嫁给厌食失语、命不久矣的哑巴王爷林霄。为避开原著死局，她用木系异能辅以种田美食，治愈王爷顽疾，却意外收获先婚后爱的真情。期间智斗绿茶堂妹、暴打普信表哥，更与穿书反派白如玉展开正妻争夺战，联手夫君反击构陷、揭露阴谋。种田养夫日常甜宠，美食治病开局高能，反套路打脸爽感拉满——我带异能穿古，专治各种不服！</x:v>
       </x:c>
@@ -29993,10 +29691,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>916</x:v>
+        <x:v>925</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>52.6%</x:v>
+        <x:v>52.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -30004,7 +29702,7 @@
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>476</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
         <x:v>27.3%</x:v>
@@ -30015,7 +29713,7 @@
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>349</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
         <x:v>20.0%</x:v>
@@ -30042,7 +29740,7 @@
         <x:v>30-49集</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>179</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
         <x:v>11.2%</x:v>
@@ -30053,7 +29751,7 @@
         <x:v>50-79集</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>684</x:v>
+        <x:v>690</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
         <x:v>42.8%</x:v>
@@ -30064,7 +29762,7 @@
         <x:v>80-99集</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>199</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
         <x:v>12.5%</x:v>
@@ -30075,10 +29773,10 @@
         <x:v>100集以上</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>535</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>33.5%</x:v>
+        <x:v>33.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
@@ -30102,10 +29800,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>764</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>43.9%</x:v>
+        <x:v>44.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -30113,10 +29811,10 @@
         <x:v>婚姻/情感</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>313</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>18.0%</x:v>
+        <x:v>17.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -30127,7 +29825,7 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>9.2%</x:v>
+        <x:v>9.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -30135,10 +29833,10 @@
         <x:v>年代怀旧/种田囤货</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>149</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>8.6%</x:v>
+        <x:v>8.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -30146,7 +29844,7 @@
         <x:v>家庭伦理/萌宝</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>149</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
         <x:v>8.6%</x:v>
@@ -30157,7 +29855,7 @@
         <x:v>战神/异能/爽文</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
         <x:v>8.4%</x:v>
@@ -30171,7 +29869,7 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>6.4%</x:v>
+        <x:v>6.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -30182,7 +29880,7 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>5.7%</x:v>
+        <x:v>5.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -30190,7 +29888,7 @@
         <x:v>逆袭/打脸</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
         <x:v>4.8%</x:v>
@@ -30201,7 +29899,7 @@
         <x:v>都市职场</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
         <x:v>4.2%</x:v>
@@ -30371,10 +30069,10 @@
         <x:v>上榜15次</x:v>
       </x:c>
       <x:c r="B42" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C42" s="11" t="str">
-        <x:v>0.4%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -30404,10 +30102,10 @@
         <x:v>上榜12次</x:v>
       </x:c>
       <x:c r="B45" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C45" s="11" t="str">
-        <x:v>1.0%</x:v>
+        <x:v>0.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -30415,10 +30113,10 @@
         <x:v>上榜11次</x:v>
       </x:c>
       <x:c r="B46" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C46" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -30426,7 +30124,7 @@
         <x:v>上榜10次</x:v>
       </x:c>
       <x:c r="B47" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C47" s="11" t="str">
         <x:v>1.3%</x:v>
@@ -30437,10 +30135,10 @@
         <x:v>上榜9次</x:v>
       </x:c>
       <x:c r="B48" s="11" t="n">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C48" s="11" t="str">
-        <x:v>1.8%</x:v>
+        <x:v>1.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -30448,10 +30146,10 @@
         <x:v>上榜8次</x:v>
       </x:c>
       <x:c r="B49" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C49" s="11" t="str">
-        <x:v>2.9%</x:v>
+        <x:v>3.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -30459,10 +30157,10 @@
         <x:v>上榜7次</x:v>
       </x:c>
       <x:c r="B50" s="11" t="n">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C50" s="11" t="str">
-        <x:v>2.0%</x:v>
+        <x:v>1.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -30492,7 +30190,7 @@
         <x:v>上榜4次</x:v>
       </x:c>
       <x:c r="B53" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C53" s="11" t="str">
         <x:v>6.2%</x:v>
@@ -30503,10 +30201,10 @@
         <x:v>上榜3次</x:v>
       </x:c>
       <x:c r="B54" s="11" t="n">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C54" s="11" t="str">
-        <x:v>11.7%</x:v>
+        <x:v>11.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -30514,10 +30212,10 @@
         <x:v>上榜2次</x:v>
       </x:c>
       <x:c r="B55" s="11" t="n">
-        <x:v>313</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="C55" s="11" t="str">
-        <x:v>18.0%</x:v>
+        <x:v>17.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -30525,10 +30223,10 @@
         <x:v>上榜1次</x:v>
       </x:c>
       <x:c r="B56" s="11" t="n">
-        <x:v>763</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="C56" s="11" t="str">
-        <x:v>43.8%</x:v>
+        <x:v>44.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="22" customHeight="1">
@@ -30552,10 +30250,10 @@
         <x:v>CP自营</x:v>
       </x:c>
       <x:c r="B60" s="11" t="n">
-        <x:v>1151</x:v>
+        <x:v>1158</x:v>
       </x:c>
       <x:c r="C60" s="11" t="str">
-        <x:v>66.1%</x:v>
+        <x:v>65.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -30563,10 +30261,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B61" s="11" t="n">
-        <x:v>579</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="C61" s="11" t="str">
-        <x:v>33.3%</x:v>
+        <x:v>33.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="62">

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R43c0a638e8dc47c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="Re133275321e64075"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="Rbd5c0da5a1ff4519"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="Ra6d9e901b0ee4ede"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP20剧重点跟踪" sheetId="5" r:id="Refbd34bdf7914924"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="6" r:id="R0f197b7c460b40e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="7" r:id="Rd65b961dc504425e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="8" r:id="R8b4f7061e23f4bda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="9" r:id="R79a58076f2b44156"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R77737c76d8a443ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="R97266d09b3114e78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="R48aeffa407054a08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="R5208464874374af6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP20剧重点跟踪" sheetId="5" r:id="R37dadf2238244fe7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="6" r:id="R4c26578026964f0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="7" r:id="Rf037b75baa9f46f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="8" r:id="R4c3af34a90234192"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="9" r:id="R6c21878f6a724297"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -820,27 +820,27 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>看透妻子之后</x:v>
+        <x:v>冷宫开席：陛下又来蹭饭了</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>08-24 18:02</x:v>
+        <x:v>08-02 14:08</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="E17" s="10" t="n">
-        <x:v>46</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="F17" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="G17" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷 / 美食治愈</x:v>
       </x:c>
       <x:c r="H17" s="11" t="str"/>
       <x:c r="I17" s="11" t="str"/>
       <x:c r="J17" s="10" t="str">
-        <x:v>2026-08-23、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -848,27 +848,27 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>重生六七：赶山狩猎养全家</x:v>
+        <x:v>看透妻子之后</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>08-25 18:00</x:v>
+        <x:v>08-24 18:02</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="E18" s="10" t="n">
-        <x:v>108</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F18" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="G18" s="10" t="str">
-        <x:v>种田囤货</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="H18" s="11" t="str"/>
       <x:c r="I18" s="11" t="str"/>
       <x:c r="J18" s="10" t="str">
-        <x:v>2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
+        <x:v>2026-08-23、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -876,27 +876,27 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>冷宫开席：陛下又来蹭饭了</x:v>
+        <x:v>重生六七：赶山狩猎养全家</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>08-02 14:08</x:v>
+        <x:v>08-25 18:00</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E19" s="10" t="n">
-        <x:v>122</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F19" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="G19" s="10" t="str">
-        <x:v>古装宫廷 / 美食治愈</x:v>
+        <x:v>种田囤货</x:v>
       </x:c>
       <x:c r="H19" s="11" t="str"/>
       <x:c r="I19" s="11" t="str"/>
       <x:c r="J19" s="10" t="str">
-        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14</x:v>
+        <x:v>2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1165,7 +1165,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B2" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
         <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
@@ -1239,13 +1239,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
-        <x:v>重生80，救下神雕后我带村民走出大山</x:v>
+        <x:v>我在工地卖盒饭带火一座城</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>09-13 09:00</x:v>
+        <x:v>09-14 14:52</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str"/>
       <x:c r="F4" s="11" t="str"/>
@@ -1256,19 +1256,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I4" s="11" t="n">
-        <x:v>187</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="J4" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K4" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="L4" s="11" t="str">
-        <x:v>拾光漫漫</x:v>
+        <x:v>左手良画</x:v>
       </x:c>
       <x:c r="M4" s="10" t="str">
-        <x:v>林大山遭人为意外，意外重生回到1980年。前世他错信爱人落得凄惨下场，重生后果断当众退婚。机缘巧合救下受伤的灵智神雕金羽，还遇见落难善良的白秋月。他携手知恩图报的神雕，依托卧龙山的资源，发掘名贵药材，抓住时代发展机遇。面对同行刁难，林大山坚守本心，凭借智慧与实干，包下荒山兴办药材加工坊。他善待家人，带领乡里百姓勤劳致富，在八十年代的时代浪潮里，靠着双手改写命运，收获美满爱情与事业。</x:v>
+        <x:v>小伙白叶遭遇老板跑路，半年工资付诸东流，意外被铁炒勺砸中觉醒超级餐饮系统。大雪封路堵车途中完成首份任务，靠着系统加持的厨艺，路边卖盒饭赚到第一桶金。回乡钻研秘制酱肉，赶集摆摊火爆出圈，还临危接手大型寿宴惊艳众人。过完新年，他怀揣梦想奔赴外地，准备开启属于自己的餐饮创业之路。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1276,13 +1276,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
-        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
+        <x:v>重生80，救下神雕后我带村民走出大山</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>09-13 09:58</x:v>
+        <x:v>09-13 09:00</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str"/>
       <x:c r="F5" s="11" t="str"/>
@@ -1293,19 +1293,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I5" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="J5" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K5" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="L5" s="11" t="str">
-        <x:v>创想剧场</x:v>
+        <x:v>拾光漫漫</x:v>
       </x:c>
       <x:c r="M5" s="10" t="str">
-        <x:v>游戏公会会长林小勇筹备婚礼，却在婚宴上遭遇未婚妻临时加价逼婚。危急时刻，几位相交多年的游戏老友现身力挺他，林小勇果断取消婚礼。之后他搬进好友赠送的别墅，与陈董的两个女儿渐渐熟识。同学聚会上，众人见识到林小勇不一般的际遇。平静日子没过多久，当年游戏里的宿敌将出席游戏八周年嘉年华，一众老友决定赴约，一场新旧对决即将开启。</x:v>
+        <x:v>林大山遭人为意外，意外重生回到1980年。前世他错信爱人落得凄惨下场，重生后果断当众退婚。机缘巧合救下受伤的灵智神雕金羽，还遇见落难善良的白秋月。他携手知恩图报的神雕，依托卧龙山的资源，发掘名贵药材，抓住时代发展机遇。面对同行刁难，林大山坚守本心，凭借智慧与实干，包下荒山兴办药材加工坊。他善待家人，带领乡里百姓勤劳致富，在八十年代的时代浪潮里，靠着双手改写命运，收获美满爱情与事业。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1313,13 +1313,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>乡宴见人心</x:v>
+        <x:v>一盒印泥引发的全局封锁</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>09-13 17:12</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str"/>
       <x:c r="F6" s="11" t="str"/>
@@ -1329,34 +1329,28 @@
       <x:c r="H6" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I6" s="11" t="n">
-        <x:v>72</x:v>
-      </x:c>
+      <x:c r="I6" s="11" t="str"/>
       <x:c r="J6" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K6" s="10" t="str">
-        <x:v>现实反转</x:v>
-      </x:c>
-      <x:c r="L6" s="11" t="str">
-        <x:v>黑白动漫</x:v>
-      </x:c>
-      <x:c r="M6" s="10" t="str">
-        <x:v>高满仓在赵家大院办了八年流水席，十里八村都认他的手艺。眼看生意越来越旺，院主赵金贵突然把租金翻倍，还要按桌抽钱。高满仓干脆带着人和家伙搬进镇外的废米厂，从头再来。赵金贵以为守着大院就守住了客人，靠低价抢生意，却越省越狠。一边是稳稳当当把席办好，一边是亲手砸掉自己的口碑，这场较量最后看的是院子，还是人心。</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L6" s="11" t="str"/>
+      <x:c r="M6" s="10" t="str"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>35</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
+        <x:v>晚棠知归，七年终见你</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>09-15 00:08</x:v>
+        <x:v>09-14 11:26</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str"/>
       <x:c r="F7" s="11" t="str"/>
@@ -1367,7 +1361,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I7" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J7" s="10" t="str">
         <x:v>其他</x:v>
@@ -1376,10 +1370,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L7" s="11" t="str">
-        <x:v>桃子动漫剧场</x:v>
+        <x:v>喵琪琪追剧</x:v>
       </x:c>
       <x:c r="M7" s="10" t="str">
-        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
+        <x:v>七年前，夏晚棠为救深爱的陆知珩，付出了一切，却被误会成背叛，独自带着女儿生活。多年后，两人再次相遇，陆知珩才发现当年的真相，也终于明白她承受了怎样的苦难。面对迟来的爱与亏欠，夏晚棠没有停留在过去，而是重新找回自己，用专业和坚强开启新的人生。最终，两人在女儿的陪伴下解开心结，携手迎来属于他们的幸福。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1387,13 +1381,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
-        <x:v>晚棠知归，七年终见你</x:v>
+        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>09-14 11:26</x:v>
+        <x:v>09-13 09:58</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str"/>
       <x:c r="F8" s="11" t="str"/>
@@ -1404,7 +1398,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J8" s="10" t="str">
         <x:v>其他</x:v>
@@ -1413,10 +1407,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L8" s="11" t="str">
-        <x:v>喵琪琪追剧</x:v>
+        <x:v>创想剧场</x:v>
       </x:c>
       <x:c r="M8" s="10" t="str">
-        <x:v>七年前，夏晚棠为救深爱的陆知珩，付出了一切，却被误会成背叛，独自带着女儿生活。多年后，两人再次相遇，陆知珩才发现当年的真相，也终于明白她承受了怎样的苦难。面对迟来的爱与亏欠，夏晚棠没有停留在过去，而是重新找回自己，用专业和坚强开启新的人生。最终，两人在女儿的陪伴下解开心结，携手迎来属于他们的幸福。</x:v>
+        <x:v>游戏公会会长林小勇筹备婚礼，却在婚宴上遭遇未婚妻临时加价逼婚。危急时刻，几位相交多年的游戏老友现身力挺他，林小勇果断取消婚礼。之后他搬进好友赠送的别墅，与陈董的两个女儿渐渐熟识。同学聚会上，众人见识到林小勇不一般的际遇。平静日子没过多久，当年游戏里的宿敌将出席游戏八周年嘉年华，一众老友决定赴约，一场新旧对决即将开启。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1424,13 +1418,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
-        <x:v>小妹初长成</x:v>
+        <x:v>乡宴见人心</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>2026-09-13</x:v>
+        <x:v>09-13 17:12</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str"/>
       <x:c r="F9" s="11" t="str"/>
@@ -1440,22 +1434,28 @@
       <x:c r="H9" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I9" s="11" t="str"/>
+      <x:c r="I9" s="11" t="n">
+        <x:v>72</x:v>
+      </x:c>
       <x:c r="J9" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K9" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L9" s="11" t="str"/>
-      <x:c r="M9" s="10" t="str"/>
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="L9" s="11" t="str">
+        <x:v>黑白动漫</x:v>
+      </x:c>
+      <x:c r="M9" s="10" t="str">
+        <x:v>高满仓在赵家大院办了八年流水席，十里八村都认他的手艺。眼看生意越来越旺，院主赵金贵突然把租金翻倍，还要按桌抽钱。高满仓干脆带着人和家伙搬进镇外的废米厂，从头再来。赵金贵以为守着大院就守住了客人，靠低价抢生意，却越省越狠。一边是稳稳当当把席办好，一边是亲手砸掉自己的口碑，这场较量最后看的是院子，还是人心。</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
         <x:v>一块冰袋，冻凉十二年合伙情</x:v>
@@ -1492,10 +1492,10 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C11" s="10" t="str">
-        <x:v>反派拿捏！</x:v>
+        <x:v>小妹初长成</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
         <x:v>2026-09-13</x:v>
@@ -1523,13 +1523,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
-        <x:v>高考刚结束父母就不装了</x:v>
+        <x:v>风雪边界</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>09-15 07:00</x:v>
+        <x:v>09-14 03:01</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str"/>
       <x:c r="F12" s="11" t="str"/>
@@ -1540,19 +1540,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I12" s="11" t="n">
-        <x:v>173</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J12" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K12" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L12" s="11" t="str">
-        <x:v>千慕剧场</x:v>
+        <x:v>腿毛漫漫</x:v>
       </x:c>
       <x:c r="M12" s="10" t="str">
-        <x:v>高考结束那天，林寻在考场外被亲生父母认回原来十八年的普通生活，是父母为磨砺他而设的一场成长课。重回豪门，他没有迷失，反而在桥上遇见了那个让他心动的姑娘，南大冰山学姐苏清诗。从青涩的初次相遇，到演唱会上的合唱，再到大学校园里的朝夕相处，两个真诚的人慢慢靠近。曾经的求而不得终将释怀，双向奔赴的喜欢才最珍贵。褪去普通学生的身份，林寻只想以真心换真心。十八岁的夏天，最好的相遇，最甜的恋爱，才刚刚开始。</x:v>
+        <x:v>高原补给站老板岑夏坚持完整安全套餐，却遭企业负责人质疑价格，团队转投低价营地。暴雪突至，危机逼近，岑夏仍坚守原则，以专业判断协助应急处置，也让众人重新理解安全的价值。真正昂贵的不是房费，而是忽视风险的代价。敬畏自然、尊重专业，安全永远值得认真对待。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1560,13 +1560,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B13" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
-        <x:v>一盒印泥引发的全局封锁</x:v>
+        <x:v>四个崽崽瞒不住了</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>09-15 00:08</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str"/>
       <x:c r="F13" s="11" t="str"/>
@@ -1576,28 +1576,34 @@
       <x:c r="H13" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I13" s="11" t="str"/>
+      <x:c r="I13" s="11" t="n">
+        <x:v>124</x:v>
+      </x:c>
       <x:c r="J13" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K13" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L13" s="11" t="str"/>
-      <x:c r="M13" s="10" t="str"/>
+      <x:c r="L13" s="11" t="str">
+        <x:v>桃子动漫剧场</x:v>
+      </x:c>
+      <x:c r="M13" s="10" t="str">
+        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B14" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
-        <x:v>离婚那天我多了个痞帅老爹</x:v>
+        <x:v>重生极品婆婆，带全家发家致富！</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>2026-09-13</x:v>
+        <x:v>09-14 20:29</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str"/>
       <x:c r="F14" s="11" t="str"/>
@@ -1607,28 +1613,34 @@
       <x:c r="H14" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I14" s="11" t="str"/>
+      <x:c r="I14" s="11" t="n">
+        <x:v>126</x:v>
+      </x:c>
       <x:c r="J14" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K14" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="L14" s="11" t="str"/>
-      <x:c r="M14" s="10" t="str"/>
+        <x:v>家庭伦理 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="L14" s="11" t="str">
+        <x:v>懒少爱我</x:v>
+      </x:c>
+      <x:c r="M14" s="10" t="str">
+        <x:v>寡妇傅兰秀前世一生吝啬守财，刻薄对待儿女儿媳，到头来钱财被贼人掠夺，落得个凄惨离世的下场。一朝重生，她回到悲剧尚未发生之时。痛定思痛，她彻底改掉抠门的性子，学着善待家里的晚辈。可日子并不太平，爱占便宜的亲戚总上门搅扰，家中两个儿媳也矛盾不断，家务是非接连找上门。傅兰秀靠着清醒的头脑，一边化解各类家庭纷争，一边寻找营生门路，努力扭转命运，拼尽全力守护一家人的安稳生活。</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B15" s="11" t="n">
-        <x:v>68</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
-        <x:v>河箱送福来</x:v>
+        <x:v>高考刚结束父母就不装了</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
-        <x:v>09-13 11:00</x:v>
+        <x:v>09-15 07:00</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str"/>
       <x:c r="F15" s="11" t="str"/>
@@ -1639,19 +1651,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I15" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="J15" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K15" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="L15" s="11" t="str">
-        <x:v>灵心讲故事</x:v>
+        <x:v>千慕剧场</x:v>
       </x:c>
       <x:c r="M15" s="10" t="str">
-        <x:v>张家老两口从河中救回一只木箱，收养了箱中受伤的福生。福生长大后修桥开田，引水惠及乡亲，成家立业。二老相继离世后，山洪威胁村庄，福生为救乡亲舍命撑住巨石，最终重伤落水，下落不明。秀娥守着小院苦等多年，直到熟悉的声音再次响起。</x:v>
+        <x:v>高考结束那天，林寻在考场外被亲生父母认回原来十八年的普通生活，是父母为磨砺他而设的一场成长课。重回豪门，他没有迷失，反而在桥上遇见了那个让他心动的姑娘，南大冰山学姐苏清诗。从青涩的初次相遇，到演唱会上的合唱，再到大学校园里的朝夕相处，两个真诚的人慢慢靠近。曾经的求而不得终将释怀，双向奔赴的喜欢才最珍贵。褪去普通学生的身份，林寻只想以真心换真心。十八岁的夏天，最好的相遇，最甜的恋爱，才刚刚开始。</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1659,13 +1671,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>86</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C16" s="10" t="str">
-        <x:v>风雪边界</x:v>
+        <x:v>反派拿捏！</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
-        <x:v>09-14 03:01</x:v>
+        <x:v>2026-09-13</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str"/>
       <x:c r="F16" s="11" t="str"/>
@@ -1675,28 +1687,22 @@
       <x:c r="H16" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I16" s="11" t="n">
-        <x:v>53</x:v>
-      </x:c>
+      <x:c r="I16" s="11" t="str"/>
       <x:c r="J16" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K16" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L16" s="11" t="str">
-        <x:v>腿毛漫漫</x:v>
-      </x:c>
-      <x:c r="M16" s="10" t="str">
-        <x:v>高原补给站老板岑夏坚持完整安全套餐，却遭企业负责人质疑价格，团队转投低价营地。暴雪突至，危机逼近，岑夏仍坚守原则，以专业判断协助应急处置，也让众人重新理解安全的价值。真正昂贵的不是房费，而是忽视风险的代价。敬畏自然、尊重专业，安全永远值得认真对待。</x:v>
-      </x:c>
+      <x:c r="L16" s="11" t="str"/>
+      <x:c r="M16" s="10" t="str"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>87</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C17" s="10" t="str">
         <x:v>结婚八年，我娶的原来是仇人的女儿</x:v>
@@ -1727,13 +1733,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C18" s="10" t="str">
-        <x:v>重生极品婆婆，带全家发家致富！</x:v>
+        <x:v>八零大院：灶台藏尽温柔</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>09-14 20:29</x:v>
+        <x:v>09-13 10:00</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str"/>
       <x:c r="F18" s="11" t="str"/>
@@ -1744,19 +1750,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I18" s="11" t="n">
-        <x:v>126</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="J18" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K18" s="10" t="str">
-        <x:v>家庭伦理 / 逆袭打脸</x:v>
+        <x:v>年代怀旧 / 种田囤货</x:v>
       </x:c>
       <x:c r="L18" s="11" t="str">
-        <x:v>懒少爱我</x:v>
+        <x:v>枭枭动画</x:v>
       </x:c>
       <x:c r="M18" s="10" t="str">
-        <x:v>寡妇傅兰秀前世一生吝啬守财，刻薄对待儿女儿媳，到头来钱财被贼人掠夺，落得个凄惨离世的下场。一朝重生，她回到悲剧尚未发生之时。痛定思痛，她彻底改掉抠门的性子，学着善待家里的晚辈。可日子并不太平，爱占便宜的亲戚总上门搅扰，家中两个儿媳也矛盾不断，家务是非接连找上门。傅兰秀靠着清醒的头脑，一边化解各类家庭纷争，一边寻找营生门路，努力扭转命运，拼尽全力守护一家人的安稳生活。</x:v>
+        <x:v>现代私宴主厨祝宁意外穿越至八十年代，为反抗包办婚姻毅然出走，凭借一身精湛厨艺在军区大院门口摆摊谋生。她做的饭菜香气独特，意外治愈了因战场创伤患上心理性厌食症的军区首长贺枭。进入军区食堂后，祝宁靠着过硬的厨艺和坦荡正直的性格渐渐站稳脚跟。面对旁人的刁难与恶意构陷，她始终坚守原则、沉着应对，最终不仅凭借专业能力获得全军区的认可，获评军区膳食顾问，也与贺枭解开重重误会，在烟火日常中收获了真挚的感情。</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1764,7 +1770,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C19" s="10" t="str">
         <x:v>远山架子班</x:v>
@@ -1801,36 +1807,36 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C20" s="10" t="str">
-        <x:v>一宴断经年，旧账归于风</x:v>
+        <x:v>河箱送福来</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>09-15 06:13</x:v>
+        <x:v>09-13 11:00</x:v>
       </x:c>
       <x:c r="E20" s="11" t="str"/>
       <x:c r="F20" s="11" t="str"/>
       <x:c r="G20" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H20" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I20" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J20" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K20" s="10" t="str">
-        <x:v>年代怀旧 / 现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L20" s="11" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>灵心讲故事</x:v>
       </x:c>
       <x:c r="M20" s="10" t="str">
-        <x:v>宋知遥为侄女宋雨欣付出十三年，却在毕业宴上遭其当众羞辱并拒绝感恩。宋知遥看清嫂嫂一家的贪婪嘴脸，果断停卡断供，收回承诺的房产。面对侄女的道德绑架与法律纠纷，她坚守底线，通过法律途径维权，最终切断所有不良羁绊，守护亲生女儿，重启清净生活。</x:v>
+        <x:v>张家老两口从河中救回一只木箱，收养了箱中受伤的福生。福生长大后修桥开田，引水惠及乡亲，成家立业。二老相继离世后，山洪威胁村庄，福生为救乡亲舍命撑住巨石，最终重伤落水，下落不明。秀娥守着小院苦等多年，直到熟悉的声音再次响起。</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1838,73 +1844,67 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C21" s="10" t="str">
-        <x:v>八零大院：灶台藏尽温柔</x:v>
+        <x:v>离婚那天我多了个痞帅老爹</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
-        <x:v>09-13 10:00</x:v>
+        <x:v>2026-09-13</x:v>
       </x:c>
       <x:c r="E21" s="11" t="str"/>
       <x:c r="F21" s="11" t="str"/>
       <x:c r="G21" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H21" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="I21" s="11" t="n">
-        <x:v>67</x:v>
-      </x:c>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I21" s="11" t="str"/>
       <x:c r="J21" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K21" s="10" t="str">
-        <x:v>年代怀旧 / 种田囤货</x:v>
-      </x:c>
-      <x:c r="L21" s="11" t="str">
-        <x:v>枭枭动画</x:v>
-      </x:c>
-      <x:c r="M21" s="10" t="str">
-        <x:v>现代私宴主厨祝宁意外穿越至八十年代，为反抗包办婚姻毅然出走，凭借一身精湛厨艺在军区大院门口摆摊谋生。她做的饭菜香气独特，意外治愈了因战场创伤患上心理性厌食症的军区首长贺枭。进入军区食堂后，祝宁靠着过硬的厨艺和坦荡正直的性格渐渐站稳脚跟。面对旁人的刁难与恶意构陷，她始终坚守原则、沉着应对，最终不仅凭借专业能力获得全军区的认可，获评军区膳食顾问，也与贺枭解开重重误会，在烟火日常中收获了真挚的感情。</x:v>
-      </x:c>
+        <x:v>家庭伦理 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="L21" s="11" t="str"/>
+      <x:c r="M21" s="10" t="str"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C22" s="10" t="str">
-        <x:v>我在工地卖盒饭带火一座城</x:v>
+        <x:v>刺耳的邻里情</x:v>
       </x:c>
       <x:c r="D22" s="11" t="str">
-        <x:v>09-14 14:52</x:v>
+        <x:v>09-15 11:00</x:v>
       </x:c>
       <x:c r="E22" s="11" t="str"/>
       <x:c r="F22" s="11" t="str"/>
       <x:c r="G22" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H22" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I22" s="11" t="n">
-        <x:v>144</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J22" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K22" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L22" s="11" t="str">
-        <x:v>左手良画</x:v>
+        <x:v>酒写一首诗</x:v>
       </x:c>
       <x:c r="M22" s="10" t="str">
-        <x:v>小伙白叶遭遇老板跑路，半年工资付诸东流，意外被铁炒勺砸中觉醒超级餐饮系统。大雪封路堵车途中完成首份任务，靠着系统加持的厨艺，路边卖盒饭赚到第一桶金。回乡钻研秘制酱肉，赶集摆摊火爆出圈，还临危接手大型寿宴惊艳众人。过完新年，他怀揣梦想奔赴外地，准备开启属于自己的餐饮创业之路。</x:v>
+        <x:v>邻居大强夫妇痴迷比赛，深夜制造噪音打扰四邻，甚至潜入邻院破坏，终因违规致使墙倒器毁、面临赔偿。青年陈默没有以怨报怨，只凭合农机与科学常识理性应对。大强夫妇在赔偿检讨中受教，重新学会遵守规则、尊重邻里；陈默则凭宽容智慧用赔款修筑村广场，走出一条和谐讲理的乡村新路。</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1912,185 +1912,215 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C23" s="10" t="str">
-        <x:v>辣媳进门，我给公婆撑腰</x:v>
+        <x:v>锅炉没爆炸，名声却先炸了</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>09-14 17:00</x:v>
       </x:c>
       <x:c r="E23" s="11" t="str"/>
       <x:c r="F23" s="11" t="str"/>
       <x:c r="G23" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H23" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I23" s="11" t="str"/>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I23" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
       <x:c r="J23" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K23" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L23" s="11" t="str"/>
-      <x:c r="M23" s="10" t="str"/>
+      <x:c r="L23" s="11" t="str">
+        <x:v>柔光映剧场</x:v>
+      </x:c>
+      <x:c r="M23" s="10" t="str">
+        <x:v>重生回宿舍，孙有田又喊锅炉要炸，拽我跑。上辈子我信了，名声被毁，嫁他挨打丧子。这回我一脚踹翻他，扯嗓喊抓流氓！他掏出我的信反咬，未婚夫也来退婚。我不哭，当场拆穿字迹与痣局，揪出幕后名额交易。高考恢复，我拼命读书，把陷害我的人全送进锅炉房。录取那天，我烧掉旧信。那棵树，开花了。</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C24" s="10" t="str">
-        <x:v>反派拿捏！</x:v>
+        <x:v>沈总，夫人不忍了</x:v>
       </x:c>
       <x:c r="D24" s="11" t="str">
-        <x:v>2026-09-13</x:v>
-      </x:c>
-      <x:c r="E24" s="11" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F24" s="11" t="str">
-        <x:v>↑2位</x:v>
-      </x:c>
-      <x:c r="G24" s="11" t="str"/>
-      <x:c r="H24" s="11" t="str"/>
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="E24" s="11" t="str"/>
+      <x:c r="F24" s="11" t="str"/>
+      <x:c r="G24" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H24" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="I24" s="11" t="str"/>
       <x:c r="J24" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="K24" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="L24" s="11" t="str"/>
       <x:c r="M24" s="10" t="str"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C25" s="10" t="str">
-        <x:v>辣媳进门，我给公婆撑腰</x:v>
+        <x:v>一顶假发的真价</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
-        <x:v>2026-09-15</x:v>
-      </x:c>
-      <x:c r="E25" s="11" t="n">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F25" s="11" t="str">
-        <x:v>↑2位</x:v>
-      </x:c>
-      <x:c r="G25" s="11" t="str"/>
-      <x:c r="H25" s="11" t="str"/>
-      <x:c r="I25" s="11" t="str"/>
+        <x:v>09-14 18:10</x:v>
+      </x:c>
+      <x:c r="E25" s="11" t="str"/>
+      <x:c r="F25" s="11" t="str"/>
+      <x:c r="G25" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H25" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I25" s="11" t="n">
+        <x:v>53</x:v>
+      </x:c>
       <x:c r="J25" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K25" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L25" s="11" t="str"/>
-      <x:c r="M25" s="10" t="str"/>
+      <x:c r="L25" s="11" t="str">
+        <x:v>土堆剧场</x:v>
+      </x:c>
+      <x:c r="M25" s="10" t="str">
+        <x:v>商业街新开假发店以“全真发299起”低价爆火，隔壁老店乔蔓坚守品质定价六百有余，一度被网暴“行业暴利”。为撑住低价，店主孟玲偷换硬网底、掺化纤发丝，终引发头皮过敏、假发打结的售后风波。真相渐显后，顾客开始在意假发内里的材质与做工，乔蔓凭扎实手艺与坦诚经营口碑逆袭，订单排至下月，始终守着“标什么就做什么”的底线。</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B26" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C26" s="10" t="str">
-        <x:v>沈总，夫人不忍了</x:v>
+        <x:v>打工六年回家满院蜈蚣</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>09-14 22:39</x:v>
       </x:c>
       <x:c r="E26" s="11" t="str"/>
-      <x:c r="F26" s="11" t="str">
-        <x:v>新上榜</x:v>
-      </x:c>
-      <x:c r="G26" s="11" t="str"/>
-      <x:c r="H26" s="11" t="str"/>
-      <x:c r="I26" s="11" t="str"/>
+      <x:c r="F26" s="11" t="str"/>
+      <x:c r="G26" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H26" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I26" s="11" t="n">
+        <x:v>35</x:v>
+      </x:c>
       <x:c r="J26" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K26" s="10" t="str">
-        <x:v>婚姻情感 / 逆袭打脸</x:v>
-      </x:c>
-      <x:c r="L26" s="11" t="str"/>
-      <x:c r="M26" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L26" s="11" t="str">
+        <x:v>于一动画</x:v>
+      </x:c>
+      <x:c r="M26" s="10" t="str">
+        <x:v>打工六年的岑北河因老家拆迁返乡，意外发现当年遗忘的三百只蜈蚣已繁育成珍稀金头种群。他凭借合法养殖凭证与专业认知，化解邻里刁难与拆迁风波，联手药企建成标准化养殖示范基地，以一场意外的“虫缘”开启乡村创业新征程。</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B27" s="11" t="n">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C27" s="10" t="str">
-        <x:v>小福宝赶海</x:v>
+        <x:v>重生极品婆婆，带全家发家致富！</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
-        <x:v>2026-09-15</x:v>
-      </x:c>
-      <x:c r="E27" s="11" t="str"/>
+        <x:v>09-14 20:29</x:v>
+      </x:c>
+      <x:c r="E27" s="11" t="n">
+        <x:v>72</x:v>
+      </x:c>
       <x:c r="F27" s="11" t="str">
-        <x:v>新上榜</x:v>
+        <x:v>↑32位</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str"/>
       <x:c r="H27" s="11" t="str"/>
-      <x:c r="I27" s="11" t="str"/>
+      <x:c r="I27" s="11" t="n">
+        <x:v>126</x:v>
+      </x:c>
       <x:c r="J27" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K27" s="10" t="str">
-        <x:v>种田囤货 / 萌宝治愈</x:v>
-      </x:c>
-      <x:c r="L27" s="11" t="str"/>
-      <x:c r="M27" s="10" t="str"/>
+        <x:v>家庭伦理 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="L27" s="11" t="str">
+        <x:v>懒少爱我</x:v>
+      </x:c>
+      <x:c r="M27" s="10" t="str">
+        <x:v>寡妇傅兰秀前世一生吝啬守财，刻薄对待儿女儿媳，到头来钱财被贼人掠夺，落得个凄惨离世的下场。一朝重生，她回到悲剧尚未发生之时。痛定思痛，她彻底改掉抠门的性子，学着善待家里的晚辈。可日子并不太平，爱占便宜的亲戚总上门搅扰，家中两个儿媳也矛盾不断，家务是非接连找上门。傅兰秀靠着清醒的头脑，一边化解各类家庭纷争，一边寻找营生门路，努力扭转命运，拼尽全力守护一家人的安稳生活。</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B28" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C28" s="10" t="str">
-        <x:v>锅炉没爆炸，名声却先炸了</x:v>
+        <x:v>刺耳的邻里情</x:v>
       </x:c>
       <x:c r="D28" s="11" t="str">
-        <x:v>09-14 17:00</x:v>
-      </x:c>
-      <x:c r="E28" s="11" t="str"/>
+        <x:v>09-15 11:00</x:v>
+      </x:c>
+      <x:c r="E28" s="11" t="n">
+        <x:v>79</x:v>
+      </x:c>
       <x:c r="F28" s="11" t="str">
-        <x:v>新上榜</x:v>
+        <x:v>↑27位</x:v>
       </x:c>
       <x:c r="G28" s="11" t="str"/>
       <x:c r="H28" s="11" t="str"/>
       <x:c r="I28" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J28" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K28" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L28" s="11" t="str">
-        <x:v>柔光映剧场</x:v>
+        <x:v>酒写一首诗</x:v>
       </x:c>
       <x:c r="M28" s="10" t="str">
-        <x:v>重生回宿舍，孙有田又喊锅炉要炸，拽我跑。上辈子我信了，名声被毁，嫁他挨打丧子。这回我一脚踹翻他，扯嗓喊抓流氓！他掏出我的信反咬，未婚夫也来退婚。我不哭，当场拆穿字迹与痣局，揪出幕后名额交易。高考恢复，我拼命读书，把陷害我的人全送进锅炉房。录取那天，我烧掉旧信。那棵树，开花了。</x:v>
+        <x:v>邻居大强夫妇痴迷比赛，深夜制造噪音打扰四邻，甚至潜入邻院破坏，终因违规致使墙倒器毁、面临赔偿。青年陈默没有以怨报怨，只凭合农机与科学常识理性应对。大强夫妇在赔偿检讨中受教，重新学会遵守规则、尊重邻里；陈默则凭宽容智慧用赔款修筑村广场，走出一条和谐讲理的乡村新路。</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -2098,34 +2128,641 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B29" s="11" t="n">
-        <x:v>99</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C29" s="10" t="str">
-        <x:v>7路公交车的终点</x:v>
+        <x:v>反派拿捏！</x:v>
       </x:c>
       <x:c r="D29" s="11" t="str">
-        <x:v>09-14 10:00</x:v>
-      </x:c>
-      <x:c r="E29" s="11" t="str"/>
+        <x:v>2026-09-13</x:v>
+      </x:c>
+      <x:c r="E29" s="11" t="n">
+        <x:v>75</x:v>
+      </x:c>
       <x:c r="F29" s="11" t="str">
-        <x:v>新上榜</x:v>
+        <x:v>↑21位</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str"/>
       <x:c r="H29" s="11" t="str"/>
-      <x:c r="I29" s="11" t="n">
-        <x:v>85</x:v>
-      </x:c>
+      <x:c r="I29" s="11" t="str"/>
       <x:c r="J29" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K29" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L29" s="11" t="str">
-        <x:v>鹿姐短剧</x:v>
-      </x:c>
-      <x:c r="M29" s="10" t="str">
-        <x:v>何云身为顾氏集团实际控股人，隐姓埋名开了二十年公交。亲家肖大海一家在公交上闹事伤人，其女肖琴琴当众殴打何云，还剪辑视频网暴她。何云收集完整录像与肖琴琴挪用公款的证据，于订婚宴当众揭穿一切。肖家人被警方带走，何云出任公交公司总经理，与儿子和好。</x:v>
+      <x:c r="L29" s="11" t="str"/>
+      <x:c r="M29" s="10" t="str"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B30" s="11" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C30" s="10" t="str">
+        <x:v>荔月饕临</x:v>
+      </x:c>
+      <x:c r="D30" s="11" t="str">
+        <x:v>09-15 08:33</x:v>
+      </x:c>
+      <x:c r="E30" s="11" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="F30" s="11" t="str">
+        <x:v>↑19位</x:v>
+      </x:c>
+      <x:c r="G30" s="11" t="str"/>
+      <x:c r="H30" s="11" t="str"/>
+      <x:c r="I30" s="11" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J30" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K30" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L30" s="11" t="str">
+        <x:v>荔月动漫</x:v>
+      </x:c>
+      <x:c r="M30" s="10" t="str">
+        <x:v>沈知微身为大胤太子妃，受尽太子裴景珩与侧妃苏婉柔百般折辱，被废位、灌红花，甚至囚入地牢。世人皆当她是任人拿捏的软弱孤女，殊不知她乃是上古饕餮，当年受开国太祖相求，立下十年契约镇守大胤国运，唯一条件便是一日八餐。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B31" s="11" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C31" s="10" t="str">
+        <x:v>风雪边界</x:v>
+      </x:c>
+      <x:c r="D31" s="11" t="str">
+        <x:v>09-14 03:01</x:v>
+      </x:c>
+      <x:c r="E31" s="11" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F31" s="11" t="str">
+        <x:v>↑18位</x:v>
+      </x:c>
+      <x:c r="G31" s="11" t="str"/>
+      <x:c r="H31" s="11" t="str"/>
+      <x:c r="I31" s="11" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J31" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K31" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L31" s="11" t="str">
+        <x:v>腿毛漫漫</x:v>
+      </x:c>
+      <x:c r="M31" s="10" t="str">
+        <x:v>高原补给站老板岑夏坚持完整安全套餐，却遭企业负责人质疑价格，团队转投低价营地。暴雪突至，危机逼近，岑夏仍坚守原则，以专业判断协助应急处置，也让众人重新理解安全的价值。真正昂贵的不是房费，而是忽视风险的代价。敬畏自然、尊重专业，安全永远值得认真对待。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B32" s="11" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C32" s="10" t="str">
+        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
+      </x:c>
+      <x:c r="D32" s="11" t="str">
+        <x:v>09-15 08:30</x:v>
+      </x:c>
+      <x:c r="E32" s="11" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F32" s="11" t="str">
+        <x:v>↑17位</x:v>
+      </x:c>
+      <x:c r="G32" s="11" t="str"/>
+      <x:c r="H32" s="11" t="str"/>
+      <x:c r="I32" s="11" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="J32" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K32" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="L32" s="11" t="str">
+        <x:v>琥珀漫剧</x:v>
+      </x:c>
+      <x:c r="M32" s="10" t="str">
+        <x:v>海鲜市场老手陈放，因一个两块钱的冰袋被十二年合伙人当众算旧账，心寒清账，净身出户。他没有抱怨，也没有以牙还牙，而是加入冷清档口“梅姐水产”，从零开始。他坚持明码标价、沥水称重、死活分卖、批次可查，宁可少接单，也不混货、不凑数、不赚亏心钱。面对低价抢客、恶意破坏、临时缺货等风波，他与叶梅靠诚信、规矩和彼此信任，一步步赢得客户与连锁企业的认可。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B33" s="11" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C33" s="10" t="str">
+        <x:v>一盒印泥引发的全局封锁</x:v>
+      </x:c>
+      <x:c r="D33" s="11" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="E33" s="11" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F33" s="11" t="str">
+        <x:v>↑11位</x:v>
+      </x:c>
+      <x:c r="G33" s="11" t="str"/>
+      <x:c r="H33" s="11" t="str"/>
+      <x:c r="I33" s="11" t="str"/>
+      <x:c r="J33" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="K33" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L33" s="11" t="str"/>
+      <x:c r="M33" s="10" t="str"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B34" s="11" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C34" s="10" t="str">
+        <x:v>锅炉没爆炸，名声却先炸了</x:v>
+      </x:c>
+      <x:c r="D34" s="11" t="str">
+        <x:v>09-14 17:00</x:v>
+      </x:c>
+      <x:c r="E34" s="11" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F34" s="11" t="str">
+        <x:v>↑11位</x:v>
+      </x:c>
+      <x:c r="G34" s="11" t="str"/>
+      <x:c r="H34" s="11" t="str"/>
+      <x:c r="I34" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="J34" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K34" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L34" s="11" t="str">
+        <x:v>柔光映剧场</x:v>
+      </x:c>
+      <x:c r="M34" s="10" t="str">
+        <x:v>重生回宿舍，孙有田又喊锅炉要炸，拽我跑。上辈子我信了，名声被毁，嫁他挨打丧子。这回我一脚踹翻他，扯嗓喊抓流氓！他掏出我的信反咬，未婚夫也来退婚。我不哭，当场拆穿字迹与痣局，揪出幕后名额交易。高考恢复，我拼命读书，把陷害我的人全送进锅炉房。录取那天，我烧掉旧信。那棵树，开花了。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B35" s="11" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C35" s="10" t="str">
+        <x:v>八零大院：灶台藏尽温柔</x:v>
+      </x:c>
+      <x:c r="D35" s="11" t="str">
+        <x:v>09-13 10:00</x:v>
+      </x:c>
+      <x:c r="E35" s="11" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="F35" s="11" t="str">
+        <x:v>↑10位</x:v>
+      </x:c>
+      <x:c r="G35" s="11" t="str"/>
+      <x:c r="H35" s="11" t="str"/>
+      <x:c r="I35" s="11" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="J35" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K35" s="10" t="str">
+        <x:v>年代怀旧 / 种田囤货</x:v>
+      </x:c>
+      <x:c r="L35" s="11" t="str">
+        <x:v>枭枭动画</x:v>
+      </x:c>
+      <x:c r="M35" s="10" t="str">
+        <x:v>现代私宴主厨祝宁意外穿越至八十年代，为反抗包办婚姻毅然出走，凭借一身精湛厨艺在军区大院门口摆摊谋生。她做的饭菜香气独特，意外治愈了因战场创伤患上心理性厌食症的军区首长贺枭。进入军区食堂后，祝宁靠着过硬的厨艺和坦荡正直的性格渐渐站稳脚跟。面对旁人的刁难与恶意构陷，她始终坚守原则、沉着应对，最终不仅凭借专业能力获得全军区的认可，获评军区膳食顾问，也与贺枭解开重重误会，在烟火日常中收获了真挚的感情。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B36" s="11" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C36" s="10" t="str">
+        <x:v>被身高掩盖的谎言</x:v>
+      </x:c>
+      <x:c r="D36" s="11" t="str">
+        <x:v>09-15 08:18</x:v>
+      </x:c>
+      <x:c r="E36" s="11" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F36" s="11" t="str">
+        <x:v>↑10位</x:v>
+      </x:c>
+      <x:c r="G36" s="11" t="str"/>
+      <x:c r="H36" s="11" t="str"/>
+      <x:c r="I36" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="J36" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K36" s="10" t="str">
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="L36" s="11" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="M36" s="10" t="str">
+        <x:v>女孩林知晚回到命运转折的关键节点。她凭借智慧与勇气，敏锐察觉家中隐患，冷静引导家人、寻求帮助，用爱守护姐姐与全家。在共同努力下危机化解、正义伸张，一家人愈发珍视彼此，并且帮助到了更多有同样遭遇的人，最后迎来温暖安宁的幸福生活。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B37" s="11" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C37" s="10" t="str">
+        <x:v>结婚八年，我娶的原来是仇人的女儿</x:v>
+      </x:c>
+      <x:c r="D37" s="11" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="E37" s="11" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F37" s="11" t="str">
+        <x:v>↑9位</x:v>
+      </x:c>
+      <x:c r="G37" s="11" t="str"/>
+      <x:c r="H37" s="11" t="str"/>
+      <x:c r="I37" s="11" t="str"/>
+      <x:c r="J37" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="K37" s="10" t="str">
+        <x:v>家庭伦理 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="L37" s="11" t="str"/>
+      <x:c r="M37" s="10" t="str"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B38" s="11" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C38" s="10" t="str">
+        <x:v>我在工地卖盒饭带火一座城</x:v>
+      </x:c>
+      <x:c r="D38" s="11" t="str">
+        <x:v>09-14 14:52</x:v>
+      </x:c>
+      <x:c r="E38" s="11" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F38" s="11" t="str">
+        <x:v>↑8位</x:v>
+      </x:c>
+      <x:c r="G38" s="11" t="str"/>
+      <x:c r="H38" s="11" t="str"/>
+      <x:c r="I38" s="11" t="n">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="J38" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K38" s="10" t="str">
+        <x:v>美食治愈</x:v>
+      </x:c>
+      <x:c r="L38" s="11" t="str">
+        <x:v>左手良画</x:v>
+      </x:c>
+      <x:c r="M38" s="10" t="str">
+        <x:v>小伙白叶遭遇老板跑路，半年工资付诸东流，意外被铁炒勺砸中觉醒超级餐饮系统。大雪封路堵车途中完成首份任务，靠着系统加持的厨艺，路边卖盒饭赚到第一桶金。回乡钻研秘制酱肉，赶集摆摊火爆出圈，还临危接手大型寿宴惊艳众人。过完新年，他怀揣梦想奔赴外地，准备开启属于自己的餐饮创业之路。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B39" s="11" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C39" s="10" t="str">
+        <x:v>晚棠知归，七年终见你</x:v>
+      </x:c>
+      <x:c r="D39" s="11" t="str">
+        <x:v>09-14 11:26</x:v>
+      </x:c>
+      <x:c r="E39" s="11" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F39" s="11" t="str">
+        <x:v>↑6位</x:v>
+      </x:c>
+      <x:c r="G39" s="11" t="str"/>
+      <x:c r="H39" s="11" t="str"/>
+      <x:c r="I39" s="11" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="J39" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K39" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L39" s="11" t="str">
+        <x:v>喵琪琪追剧</x:v>
+      </x:c>
+      <x:c r="M39" s="10" t="str">
+        <x:v>七年前，夏晚棠为救深爱的陆知珩，付出了一切，却被误会成背叛，独自带着女儿生活。多年后，两人再次相遇，陆知珩才发现当年的真相，也终于明白她承受了怎样的苦难。面对迟来的爱与亏欠，夏晚棠没有停留在过去，而是重新找回自己，用专业和坚强开启新的人生。最终，两人在女儿的陪伴下解开心结，携手迎来属于他们的幸福。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B40" s="11" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C40" s="10" t="str">
+        <x:v>小妹初长成</x:v>
+      </x:c>
+      <x:c r="D40" s="11" t="str">
+        <x:v>2026-09-13</x:v>
+      </x:c>
+      <x:c r="E40" s="11" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F40" s="11" t="str">
+        <x:v>↑6位</x:v>
+      </x:c>
+      <x:c r="G40" s="11" t="str"/>
+      <x:c r="H40" s="11" t="str"/>
+      <x:c r="I40" s="11" t="str"/>
+      <x:c r="J40" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="K40" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L40" s="11" t="str"/>
+      <x:c r="M40" s="10" t="str"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B41" s="11" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C41" s="10" t="str">
+        <x:v>高考刚结束父母就不装了</x:v>
+      </x:c>
+      <x:c r="D41" s="11" t="str">
+        <x:v>09-15 07:00</x:v>
+      </x:c>
+      <x:c r="E41" s="11" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F41" s="11" t="str">
+        <x:v>↑5位</x:v>
+      </x:c>
+      <x:c r="G41" s="11" t="str"/>
+      <x:c r="H41" s="11" t="str"/>
+      <x:c r="I41" s="11" t="n">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="J41" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K41" s="10" t="str">
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="L41" s="11" t="str">
+        <x:v>千慕剧场</x:v>
+      </x:c>
+      <x:c r="M41" s="10" t="str">
+        <x:v>高考结束那天，林寻在考场外被亲生父母认回原来十八年的普通生活，是父母为磨砺他而设的一场成长课。重回豪门，他没有迷失，反而在桥上遇见了那个让他心动的姑娘，南大冰山学姐苏清诗。从青涩的初次相遇，到演唱会上的合唱，再到大学校园里的朝夕相处，两个真诚的人慢慢靠近。曾经的求而不得终将释怀，双向奔赴的喜欢才最珍贵。褪去普通学生的身份，林寻只想以真心换真心。十八岁的夏天，最好的相遇，最甜的恋爱，才刚刚开始。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B42" s="11" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C42" s="10" t="str">
+        <x:v>重生80，救下神雕后我带村民走出大山</x:v>
+      </x:c>
+      <x:c r="D42" s="11" t="str">
+        <x:v>09-13 09:00</x:v>
+      </x:c>
+      <x:c r="E42" s="11" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F42" s="11" t="str">
+        <x:v>↑3位</x:v>
+      </x:c>
+      <x:c r="G42" s="11" t="str"/>
+      <x:c r="H42" s="11" t="str"/>
+      <x:c r="I42" s="11" t="n">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="J42" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K42" s="10" t="str">
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="L42" s="11" t="str">
+        <x:v>拾光漫漫</x:v>
+      </x:c>
+      <x:c r="M42" s="10" t="str">
+        <x:v>林大山遭人为意外，意外重生回到1980年。前世他错信爱人落得凄惨下场，重生后果断当众退婚。机缘巧合救下受伤的灵智神雕金羽，还遇见落难善良的白秋月。他携手知恩图报的神雕，依托卧龙山的资源，发掘名贵药材，抓住时代发展机遇。面对同行刁难，林大山坚守本心，凭借智慧与实干，包下荒山兴办药材加工坊。他善待家人，带领乡里百姓勤劳致富，在八十年代的时代浪潮里，靠着双手改写命运，收获美满爱情与事业。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B43" s="11" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C43" s="10" t="str">
+        <x:v>一顶假发的真价</x:v>
+      </x:c>
+      <x:c r="D43" s="11" t="str">
+        <x:v>09-14 18:10</x:v>
+      </x:c>
+      <x:c r="E43" s="11" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="F43" s="11" t="str">
+        <x:v>↑3位</x:v>
+      </x:c>
+      <x:c r="G43" s="11" t="str"/>
+      <x:c r="H43" s="11" t="str"/>
+      <x:c r="I43" s="11" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J43" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K43" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L43" s="11" t="str">
+        <x:v>土堆剧场</x:v>
+      </x:c>
+      <x:c r="M43" s="10" t="str">
+        <x:v>商业街新开假发店以“全真发299起”低价爆火，隔壁老店乔蔓坚守品质定价六百有余，一度被网暴“行业暴利”。为撑住低价，店主孟玲偷换硬网底、掺化纤发丝，终引发头皮过敏、假发打结的售后风波。真相渐显后，顾客开始在意假发内里的材质与做工，乔蔓凭扎实手艺与坦诚经营口碑逆袭，订单排至下月，始终守着“标什么就做什么”的底线。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B44" s="11" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C44" s="10" t="str">
+        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
+      </x:c>
+      <x:c r="D44" s="11" t="str">
+        <x:v>09-13 09:58</x:v>
+      </x:c>
+      <x:c r="E44" s="11" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F44" s="11" t="str">
+        <x:v>↑2位</x:v>
+      </x:c>
+      <x:c r="G44" s="11" t="str"/>
+      <x:c r="H44" s="11" t="str"/>
+      <x:c r="I44" s="11" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="J44" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K44" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L44" s="11" t="str">
+        <x:v>创想剧场</x:v>
+      </x:c>
+      <x:c r="M44" s="10" t="str">
+        <x:v>游戏公会会长林小勇筹备婚礼，却在婚宴上遭遇未婚妻临时加价逼婚。危急时刻，几位相交多年的游戏老友现身力挺他，林小勇果断取消婚礼。之后他搬进好友赠送的别墅，与陈董的两个女儿渐渐熟识。同学聚会上，众人见识到林小勇不一般的际遇。平静日子没过多久，当年游戏里的宿敌将出席游戏八周年嘉年华，一众老友决定赴约，一场新旧对决即将开启。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B45" s="11" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C45" s="10" t="str">
+        <x:v>四个崽崽瞒不住了</x:v>
+      </x:c>
+      <x:c r="D45" s="11" t="str">
+        <x:v>09-15 00:08</x:v>
+      </x:c>
+      <x:c r="E45" s="11" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F45" s="11" t="str">
+        <x:v>↑2位</x:v>
+      </x:c>
+      <x:c r="G45" s="11" t="str"/>
+      <x:c r="H45" s="11" t="str"/>
+      <x:c r="I45" s="11" t="n">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="J45" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K45" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L45" s="11" t="str">
+        <x:v>桃子动漫剧场</x:v>
+      </x:c>
+      <x:c r="M45" s="10" t="str">
+        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B46" s="11" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C46" s="10" t="str">
+        <x:v>我的系统不对劲，行善积德反着来</x:v>
+      </x:c>
+      <x:c r="D46" s="11" t="str">
+        <x:v>09-15 10:00</x:v>
+      </x:c>
+      <x:c r="E46" s="11" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F46" s="11" t="str">
+        <x:v>↑2位</x:v>
+      </x:c>
+      <x:c r="G46" s="11" t="str"/>
+      <x:c r="H46" s="11" t="str"/>
+      <x:c r="I46" s="11" t="n">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="J46" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K46" s="10" t="str">
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="L46" s="11" t="str">
+        <x:v>掌读微剧</x:v>
+      </x:c>
+      <x:c r="M46" s="10" t="str">
+        <x:v>贵为玄天宗第一天骄，苏云峰惨遭师尊沈傲雪背叛，被夺去至尊骨后含恨而亡！再度睁眼，他意外获得另类的行善积德系统。在系统的帮助下，昔日温顺弟子彻底觉醒，不再任人宰割，苏云峰的命运轨迹被彻底改写，走出一条截然不同的修行路！</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2197,130 +2834,136 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>300块报销单，作没了一家千万公司</x:v>
+        <x:v>一盒印泥引发的全局封锁</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
         <x:v>当日新上榜</x:v>
       </x:c>
-      <x:c r="D3" s="11" t="str">
-        <x:v>07-31 12:00</x:v>
-      </x:c>
-      <x:c r="E3" s="11" t="n">
-        <x:v>48</x:v>
-      </x:c>
+      <x:c r="D3" s="11" t="str"/>
+      <x:c r="E3" s="11" t="str"/>
       <x:c r="F3" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="G3" s="10" t="str">
-        <x:v>今朝动画</x:v>
-      </x:c>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="G3" s="10" t="str"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>沈总，夫人不忍了</x:v>
+        <x:v>七年，抵不过她男闺蜜一张机票</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
         <x:v>当日新上榜</x:v>
       </x:c>
-      <x:c r="D4" s="11" t="str"/>
-      <x:c r="E4" s="11" t="str"/>
+      <x:c r="D4" s="11" t="str">
+        <x:v>09-03 10:00</x:v>
+      </x:c>
+      <x:c r="E4" s="11" t="n">
+        <x:v>81</x:v>
+      </x:c>
       <x:c r="F4" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="G4" s="10" t="str"/>
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="G4" s="10" t="str">
+        <x:v>九天追剧</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
+        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>09-15 00:08</x:v>
+        <x:v>09-15 08:30</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F5" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G5" s="10" t="str">
-        <x:v>桃子动漫剧场</x:v>
+        <x:v>琥珀漫剧</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>46</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>七年，抵不过她男闺蜜一张机票</x:v>
+        <x:v>四个崽崽瞒不住了</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>当日新上榜</x:v>
+        <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>09-03 10:00</x:v>
+        <x:v>09-15 00:08</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F6" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G6" s="10" t="str">
-        <x:v>九天追剧</x:v>
+        <x:v>桃子动漫剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
+        <x:v>因为大黄遇见你</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>今日发布</x:v>
+        <x:v>当日新上榜</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>09-15 08:30</x:v>
+        <x:v>08-22 06:06</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F7" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G7" s="10" t="str">
-        <x:v>琥珀漫剧</x:v>
+        <x:v>晨兴剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="n">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>小福宝赶海</x:v>
+        <x:v>攻略失败后我不装了</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>当日新上榜</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="str"/>
-      <x:c r="E8" s="11" t="str"/>
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="str">
+        <x:v>09-15 15:00</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="n">
+        <x:v>69</x:v>
+      </x:c>
       <x:c r="F8" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="G8" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G8" s="10" t="str">
+        <x:v>喵喵说漫</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
         <x:v>高考刚结束父母就不装了</x:v>
@@ -2343,96 +2986,96 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>一盒印泥引发的全局封锁</x:v>
+        <x:v>刺耳的邻里情</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>当日新上榜</x:v>
-      </x:c>
-      <x:c r="D10" s="11" t="str"/>
-      <x:c r="E10" s="11" t="str"/>
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D10" s="11" t="str">
+        <x:v>09-15 11:00</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="n">
+        <x:v>59</x:v>
+      </x:c>
       <x:c r="F10" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="G10" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G10" s="10" t="str">
+        <x:v>酒写一首诗</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>宴后逢安</x:v>
+        <x:v>旧布尺量人心</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
         <x:v>当日新上榜</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>08-17 23:32</x:v>
+        <x:v>07-22 06:00</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F11" s="10" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="G11" s="10" t="str">
-        <x:v>琢曜-小杨看剧</x:v>
+        <x:v>冬日雪</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>系统穿古今，满满囤货到手软</x:v>
+        <x:v>结婚八年，我娶的原来是仇人的女儿</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
         <x:v>当日新上榜</x:v>
       </x:c>
-      <x:c r="D12" s="11" t="str">
-        <x:v>08-19 18:18</x:v>
-      </x:c>
-      <x:c r="E12" s="11" t="n">
-        <x:v>125</x:v>
-      </x:c>
+      <x:c r="D12" s="11" t="str"/>
+      <x:c r="E12" s="11" t="str"/>
       <x:c r="F12" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="G12" s="10" t="str">
-        <x:v>二两清沙</x:v>
-      </x:c>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="G12" s="10" t="str"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>自有归途</x:v>
+        <x:v>被身高掩盖的谎言</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>当日新上榜</x:v>
+        <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
-        <x:v>07-06 22:30</x:v>
+        <x:v>09-15 08:18</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F13" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G13" s="10" t="str">
-        <x:v>维维动画</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="n">
-        <x:v>87</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>结婚八年，我娶的原来是仇人的女儿</x:v>
+        <x:v>沈总，夫人不忍了</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
         <x:v>当日新上榜</x:v>
@@ -2446,89 +3089,112 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>刺耳的邻里情</x:v>
+        <x:v>荔月饕临</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
-        <x:v>09-15 11:00</x:v>
+        <x:v>09-15 08:33</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F15" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G15" s="10" t="str">
-        <x:v>酒写一首诗</x:v>
+        <x:v>荔月动漫</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="n">
-        <x:v>92</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>收发室打杂的竟是网络安全大佬</x:v>
+        <x:v>一念惊魂：儿媳的救赎</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
         <x:v>当日新上榜</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
-        <x:v>07-24 10:00</x:v>
+        <x:v>08-27 06:16</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F16" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G16" s="10" t="str">
-        <x:v>连连看剧场</x:v>
+        <x:v>维娅短剧</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>辣媳进门，我给公婆撑腰</x:v>
+        <x:v>我的系统不对劲，行善积德反着来</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>当日新上榜</x:v>
-      </x:c>
-      <x:c r="D17" s="11" t="str"/>
-      <x:c r="E17" s="11" t="str"/>
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D17" s="11" t="str">
+        <x:v>09-15 10:00</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="n">
+        <x:v>122</x:v>
+      </x:c>
       <x:c r="F17" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="G17" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G17" s="10" t="str">
+        <x:v>掌读微剧</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>一宴断经年，旧账归于风</x:v>
+        <x:v>后视镜那枚拼豆，惊醒了我</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>09-15 06:13</x:v>
+        <x:v>09-15 11:00</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F18" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G18" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
-      </x:c>
+        <x:v>盐系少女社</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="11" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B19" s="10" t="str">
+        <x:v>他踢不走我</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="str">
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D19" s="11" t="str"/>
+      <x:c r="E19" s="11" t="str"/>
+      <x:c r="F19" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="G19" s="10" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2597,16 +3263,16 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
-        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
+        <x:v>破库房的秘密</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>09-08 17:58</x:v>
+        <x:v>2026-09-05</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
         <x:v>7</x:v>
@@ -2615,35 +3281,29 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G2" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="11" t="n">
-        <x:v>111</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H2" s="11" t="str"/>
       <x:c r="I2" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J2" s="11" t="str"/>
       <x:c r="K2" s="11" t="str"/>
-      <x:c r="L2" s="10" t="str">
-        <x:v>禾苗动画</x:v>
-      </x:c>
-      <x:c r="M2" s="10" t="str">
-        <x:v>末世异能者沐小暖意外穿书，成为七个反派继子的恶毒后娘。原主辛劳养娃却遭流言中伤，最终含恨而终。沐小暖决心扭转命运，恩威并施管教孩子，凭末世身手进山打猎采药、种地赶集改善家计，更以百年老参为礼，为长子求得名儒霍政谚收为关门弟子。她护佑家人躲过恶人算计与亲戚夺产，建起新宅。七个孩子从怨恨抗拒到真心信赖，争着喊她娘，一家人携手改写命运，收获温暖亲情。</x:v>
-      </x:c>
+      <x:c r="L2" s="10" t="str"/>
+      <x:c r="M2" s="10" t="str"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>黑蛋孵出山海神兽后我无敌了</x:v>
+        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>09-06 18:00</x:v>
+        <x:v>09-08 17:58</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
         <x:v>7</x:v>
@@ -2652,10 +3312,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G3" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H3" s="11" t="n">
-        <x:v>154</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
         <x:v>其他</x:v>
@@ -2663,24 +3323,24 @@
       <x:c r="J3" s="11" t="str"/>
       <x:c r="K3" s="11" t="str"/>
       <x:c r="L3" s="10" t="str">
-        <x:v>抱月剧场</x:v>
+        <x:v>禾苗动画</x:v>
       </x:c>
       <x:c r="M3" s="10" t="str">
-        <x:v>寒门少年李初七攒了三年银子，仍买不起最低等的兽蛋。一次意外，他在后山捡到一枚黑蛋，孵出的煤球又小又馋，偏偏爱啃铜钱。可每吞下一缕兽息，它便能复现对手的能力。县学测灵那日，测灵石骤然亮起黑光，群兽伏地。所有人都以为他只是走了好运，只有陆远山想起古籍中的禁忌——黑光现，万兽伏。煤球究竟是什么？</x:v>
+        <x:v>末世异能者沐小暖意外穿书，成为七个反派继子的恶毒后娘。原主辛劳养娃却遭流言中伤，最终含恨而终。沐小暖决心扭转命运，恩威并施管教孩子，凭末世身手进山打猎采药、种地赶集改善家计，更以百年老参为礼，为长子求得名儒霍政谚收为关门弟子。她护佑家人躲过恶人算计与亲戚夺产，建起新宅。七个孩子从怨恨抗拒到真心信赖，争着喊她娘，一家人携手改写命运，收获温暖亲情。</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>破库房的秘密</x:v>
+        <x:v>重生三天前，我用水泥封死地下室</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>2026-09-05</x:v>
+        <x:v>09-09 09:28</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
         <x:v>7</x:v>
@@ -2689,26 +3349,32 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G4" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H4" s="11" t="str"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H4" s="11" t="n">
+        <x:v>45</x:v>
+      </x:c>
       <x:c r="I4" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J4" s="11" t="str"/>
       <x:c r="K4" s="11" t="str"/>
-      <x:c r="L4" s="10" t="str"/>
-      <x:c r="M4" s="10" t="str"/>
+      <x:c r="L4" s="10" t="str">
+        <x:v>忘忧剧场</x:v>
+      </x:c>
+      <x:c r="M4" s="10" t="str">
+        <x:v>阮清重生回被保姆王妈一家害死的三天前，前世她因心善引狼入室，保姆全家蜗居别墅地下室偷窃投毒，最终惨遭勒死。重生后她假装不知，趁王妈外出时用水泥将地下室彻底封死。警方破墙后，五具尸体令真相大白，王妈因盗窃、投毒被判十五年。阮清与父母团聚，恶人终得恶报，她重获新生。</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>重生三天前，我用水泥封死地下室</x:v>
+        <x:v>离家十年，回来女儿被换了</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>09-09 09:28</x:v>
+        <x:v>09-09 00:04</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
         <x:v>6</x:v>
@@ -2723,7 +3389,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H5" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="I5" s="10" t="str">
         <x:v>其他</x:v>
@@ -2731,24 +3397,24 @@
       <x:c r="J5" s="11" t="str"/>
       <x:c r="K5" s="11" t="str"/>
       <x:c r="L5" s="10" t="str">
-        <x:v>忘忧剧场</x:v>
+        <x:v>魔方影视（上剧版</x:v>
       </x:c>
       <x:c r="M5" s="10" t="str">
-        <x:v>阮清重生回被保姆王妈一家害死的三天前，前世她因心善引狼入室，保姆全家蜗居别墅地下室偷窃投毒，最终惨遭勒死。重生后她假装不知，趁王妈外出时用水泥将地下室彻底封死。警方破墙后，五具尸体令真相大白，王妈因盗窃、投毒被判十五年。阮清与父母团聚，恶人终得恶报，她重获新生。</x:v>
+        <x:v>程砚宁完成长期绝密任务归来，满心想要弥补亲情，却发现家中早已物是人非。身边亲近之人被私欲蒙蔽，制造重重骗局，试图侵占她的事业与财富。面对接连而来的算计与危机，她凭借过人的魄力与智慧步步拆解阴谋，联合正义力量搜集证据，厘清全部是非纠葛。在守护自身事业的同时，她放下过往伤痛，投身公益，完成自我和解，迎来属于自己的全新人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>不靠谱爸妈很靠谱</x:v>
+        <x:v>惊絮无声：傻女的绝杀</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>09-09 11:08</x:v>
+        <x:v>09-06 10:00</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
         <x:v>7</x:v>
@@ -2760,7 +3426,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H6" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
         <x:v>其他</x:v>
@@ -2768,15 +3434,15 @@
       <x:c r="J6" s="11" t="str"/>
       <x:c r="K6" s="11" t="str"/>
       <x:c r="L6" s="10" t="str">
-        <x:v>灵妹儿</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="M6" s="10" t="str">
-        <x:v>外表张扬的年轻夫妻在冬夜救下女婴林小小，用十七年的辛勤劳动和无条件陪伴，为她撑起温暖的家。曾经成绩落后的林小小，在父母的鼓励下重新学习，一步步成长为优秀学生。面对亲生家庭带来的资源与人生选择，她也开始重新理解血缘、养育与责任。当外界的误解影响到父母的生活，林小小决定勇敢站出来，用事实守护家人，也用努力证明真正的爱，是尊重、陪伴和彼此成就。</x:v>
+        <x:v>沈家人人都是天才，唯独小女儿沈惊絮是公认的傻子。没人知道，她不仅装傻多年，还带着前世金牌律师的记忆重生而来。本想闭嘴躺平一生，谁料内鬼勾结资本做空沈氏，一纸合同就要让全家净身出户、背上百亿债务。父亲落笔前，她终于按住协议“这字不能签！”绝地反杀的沈惊絮，一步步挫败了对沈家的围剿，也让全家人重新认识了自己。沈家也迎来了新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
         <x:v>穿书后我带萌宝上门认爹</x:v>
@@ -2813,16 +3479,16 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="n">
-        <x:v>29</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>一墙之隔，皆是人心</x:v>
+        <x:v>不靠谱爸妈很靠谱</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>09-06 15:48</x:v>
+        <x:v>09-09 11:08</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
         <x:v>7</x:v>
@@ -2831,10 +3497,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G8" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H8" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
         <x:v>其他</x:v>
@@ -2842,24 +3508,24 @@
       <x:c r="J8" s="11" t="str"/>
       <x:c r="K8" s="11" t="str"/>
       <x:c r="L8" s="10" t="str">
-        <x:v>在下长生</x:v>
+        <x:v>灵妹儿</x:v>
       </x:c>
       <x:c r="M8" s="10" t="str">
-        <x:v>妻子临产被车堵住出口，叶瑾抱着羊水破裂的她跑了三公里才到医院，母子平安。面对无理的车主，他没有以暴制暴，而是选择依法行事——在自家院内合法砌墙、种下高价值树苗，全程录像留证。车主回来后暴力砸墙、碾压树苗，最终被依法追究责任。</x:v>
+        <x:v>外表张扬的年轻夫妻在冬夜救下女婴林小小，用十七年的辛勤劳动和无条件陪伴，为她撑起温暖的家。曾经成绩落后的林小小，在父母的鼓励下重新学习，一步步成长为优秀学生。面对亲生家庭带来的资源与人生选择，她也开始重新理解血缘、养育与责任。当外界的误解影响到父母的生活，林小小决定勇敢站出来，用事实守护家人，也用努力证明真正的爱，是尊重、陪伴和彼此成就。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="n">
-        <x:v>34</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
+        <x:v>一墙之隔，皆是人心</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>2026-09-05</x:v>
+        <x:v>09-06 15:48</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
         <x:v>7</x:v>
@@ -2870,27 +3536,33 @@
       <x:c r="G9" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H9" s="11" t="str"/>
+      <x:c r="H9" s="11" t="n">
+        <x:v>85</x:v>
+      </x:c>
       <x:c r="I9" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J9" s="11" t="str"/>
       <x:c r="K9" s="11" t="str"/>
-      <x:c r="L9" s="10" t="str"/>
-      <x:c r="M9" s="10" t="str"/>
+      <x:c r="L9" s="10" t="str">
+        <x:v>在下长生</x:v>
+      </x:c>
+      <x:c r="M9" s="10" t="str">
+        <x:v>妻子临产被车堵住出口，叶瑾抱着羊水破裂的她跑了三公里才到医院，母子平安。面对无理的车主，他没有以暴制暴，而是选择依法行事——在自家院内合法砌墙、种下高价值树苗，全程录像留证。车主回来后暴力砸墙、碾压树苗，最终被依法追究责任。</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>惊絮无声：傻女的绝杀</x:v>
+        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>09-06 10:00</x:v>
+        <x:v>09-08 11:00</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
         <x:v>7</x:v>
@@ -2899,10 +3571,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G10" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H10" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="I10" s="10" t="str">
         <x:v>其他</x:v>
@@ -2910,24 +3582,24 @@
       <x:c r="J10" s="11" t="str"/>
       <x:c r="K10" s="11" t="str"/>
       <x:c r="L10" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>白桃剧场</x:v>
       </x:c>
       <x:c r="M10" s="10" t="str">
-        <x:v>沈家人人都是天才，唯独小女儿沈惊絮是公认的傻子。没人知道，她不仅装傻多年，还带着前世金牌律师的记忆重生而来。本想闭嘴躺平一生，谁料内鬼勾结资本做空沈氏，一纸合同就要让全家净身出户、背上百亿债务。父亲落笔前，她终于按住协议“这字不能签！”绝地反杀的沈惊絮，一步步挫败了对沈家的围剿，也让全家人重新认识了自己。沈家也迎来了新生。</x:v>
+        <x:v>阿梨一觉睡了三百年，养大的五只小兽尽数离去。她带着五只旧饭碗、十二枚铜钱与一把锈柴刀下山寻兽。昔日的小家伙已成威震四方的妖祖，历经重重相遇与揭秘，阿梨知晓三百年封印的真相，携手五只妖祖，一同对抗祸世灭灵兽神。</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="n">
-        <x:v>43</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>离家十年，回来女儿被换了</x:v>
+        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>09-09 00:04</x:v>
+        <x:v>2026-09-05</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
         <x:v>7</x:v>
@@ -2938,30 +3610,24 @@
       <x:c r="G11" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H11" s="11" t="n">
-        <x:v>155</x:v>
-      </x:c>
+      <x:c r="H11" s="11" t="str"/>
       <x:c r="I11" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J11" s="11" t="str"/>
       <x:c r="K11" s="11" t="str"/>
-      <x:c r="L11" s="10" t="str">
-        <x:v>魔方影视（上剧版</x:v>
-      </x:c>
-      <x:c r="M11" s="10" t="str">
-        <x:v>程砚宁完成长期绝密任务归来，满心想要弥补亲情，却发现家中早已物是人非。身边亲近之人被私欲蒙蔽，制造重重骗局，试图侵占她的事业与财富。面对接连而来的算计与危机，她凭借过人的魄力与智慧步步拆解阴谋，联合正义力量搜集证据，厘清全部是非纠葛。在守护自身事业的同时，她放下过往伤痛，投身公益，完成自我和解，迎来属于自己的全新人生。</x:v>
-      </x:c>
+      <x:c r="L11" s="10" t="str"/>
+      <x:c r="M11" s="10" t="str"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>抢个新娘来当后娘第一季</x:v>
+        <x:v>天灾末世，她囤满物资后所向披靡！</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>09-08 15:10</x:v>
+        <x:v>09-08 15:00</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
         <x:v>7</x:v>
@@ -2973,10 +3639,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G12" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H12" s="11" t="n">
-        <x:v>177</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str">
         <x:v>其他</x:v>
@@ -2984,24 +3650,24 @@
       <x:c r="J12" s="11" t="str"/>
       <x:c r="K12" s="11" t="str"/>
       <x:c r="L12" s="10" t="str">
-        <x:v>麻辣公主</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="M12" s="10" t="str">
-        <x:v>带着十里红妆出嫁那日，我才得知新郎早已另娶，这门亲事不过是盯上了我李家的家产。换作旁人或许忍气吞声，我偏不。我当众拒入侯府，主动上书朝廷，愿以嫁妆资援南方水患，只求解除婚约、护我父母周全。这份胆识赢得安王敬重，他以正妃之礼娶我入门。我立誓此生不做妾、不与人共侍一夫，终得一份彼此尊重的姻缘。</x:v>
+        <x:v>韩清夏被至亲推向绝境，失去家园，没能守住重要伙伴。再次睁眼，她回到了灾变来临前，并意外激活超级领主系统。她果断卖房筹资、囤积物资，将废弃防空洞升级为坚固基地，与战犬夏天并肩成长。危机爆发后，她凭借清醒判断、强大异能和充足准备救下幸存者，组建盛夏联盟。面对旧日亲人的算计、各方势力的试探与接连不断的考验，韩清夏不再退让。这一世，她要守住伙伴、掌握命运，在废墟之上建起属于自己的家园。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>天灾末世，她囤满物资后所向披靡！</x:v>
+        <x:v>黑蛋孵出山海神兽后我无敌了</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>09-08 15:00</x:v>
+        <x:v>09-06 18:00</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
         <x:v>7</x:v>
@@ -3010,10 +3676,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G13" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H13" s="11" t="n">
-        <x:v>536</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="I13" s="10" t="str">
         <x:v>其他</x:v>
@@ -3021,21 +3687,21 @@
       <x:c r="J13" s="11" t="str"/>
       <x:c r="K13" s="11" t="str"/>
       <x:c r="L13" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
+        <x:v>抱月剧场</x:v>
       </x:c>
       <x:c r="M13" s="10" t="str">
-        <x:v>韩清夏被至亲推向绝境，失去家园，没能守住重要伙伴。再次睁眼，她回到了灾变来临前，并意外激活超级领主系统。她果断卖房筹资、囤积物资，将废弃防空洞升级为坚固基地，与战犬夏天并肩成长。危机爆发后，她凭借清醒判断、强大异能和充足准备救下幸存者，组建盛夏联盟。面对旧日亲人的算计、各方势力的试探与接连不断的考验，韩清夏不再退让。这一世，她要守住伙伴、掌握命运，在废墟之上建起属于自己的家园。</x:v>
+        <x:v>寒门少年李初七攒了三年银子，仍买不起最低等的兽蛋。一次意外，他在后山捡到一枚黑蛋，孵出的煤球又小又馋，偏偏爱啃铜钱。可每吞下一缕兽息，它便能复现对手的能力。县学测灵那日，测灵石骤然亮起黑光，群兽伏地。所有人都以为他只是走了好运，只有陆远山想起古籍中的禁忌——黑光现，万兽伏。煤球究竟是什么？</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
+        <x:v>抢个新娘来当后娘第一季</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>09-08 11:00</x:v>
+        <x:v>09-08 15:10</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
         <x:v>7</x:v>
@@ -3047,10 +3713,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G14" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H14" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="I14" s="10" t="str">
         <x:v>其他</x:v>
@@ -3058,24 +3724,24 @@
       <x:c r="J14" s="11" t="str"/>
       <x:c r="K14" s="11" t="str"/>
       <x:c r="L14" s="10" t="str">
-        <x:v>白桃剧场</x:v>
+        <x:v>麻辣公主</x:v>
       </x:c>
       <x:c r="M14" s="10" t="str">
-        <x:v>阿梨一觉睡了三百年，养大的五只小兽尽数离去。她带着五只旧饭碗、十二枚铜钱与一把锈柴刀下山寻兽。昔日的小家伙已成威震四方的妖祖，历经重重相遇与揭秘，阿梨知晓三百年封印的真相，携手五只妖祖，一同对抗祸世灭灵兽神。</x:v>
+        <x:v>带着十里红妆出嫁那日，我才得知新郎早已另娶，这门亲事不过是盯上了我李家的家产。换作旁人或许忍气吞声，我偏不。我当众拒入侯府，主动上书朝廷，愿以嫁妆资援南方水患，只求解除婚约、护我父母周全。这份胆识赢得安王敬重，他以正妃之礼娶我入门。我立誓此生不做妾、不与人共侍一夫，终得一份彼此尊重的姻缘。</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="n">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>美颜系统开挂，大佬全跪下</x:v>
+        <x:v>全家施压：我反手签了过户合同</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
-        <x:v>09-09 00:10</x:v>
+        <x:v>09-08 16:58</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
         <x:v>7</x:v>
@@ -3084,10 +3750,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G15" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H15" s="11" t="n">
-        <x:v>172</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I15" s="10" t="str">
         <x:v>其他</x:v>
@@ -3095,24 +3761,24 @@
       <x:c r="J15" s="11" t="str"/>
       <x:c r="K15" s="11" t="str"/>
       <x:c r="L15" s="10" t="str">
-        <x:v>御儿</x:v>
+        <x:v>灵川剧场</x:v>
       </x:c>
       <x:c r="M15" s="10" t="str">
-        <x:v>曾因外形饱受非议的米珂华丽转身，蜕变得耀眼又夺目。从前对她嗤之以鼻的蒋少开始频频在意，素来冷眼毒舌的陆总不知不觉深陷其中，连一向克己的商界大佬也为她打破原则。米珂凭智商与手腕周旋于众人之间，上演一场势均力敌的情感博弈。没有俗套的救赎，只有双向的拉扯。看一众高高在上的精英暗自较劲、步步沉沦，心甘情愿为她卸下防备。</x:v>
+        <x:v>儿子儿媳多次提议我搬回乡下养老，将城里的宽敞住房腾出来给女方父母长期居住。我笑着点头应下，转头便将这套三室朝南的江景房产挂牌出售，最终成交二百八十万元。我随即购置了一套一室一厅的小户型，更换门锁后独自入住。他们上门索要钥匙，我没有开门。名下房产我自有主张，谁也别想插手安排。</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="n">
-        <x:v>89</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>全家施压：我反手签了过户合同</x:v>
+        <x:v>末世来临，我靠囤货种田丰衣足食</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>09-08 16:58</x:v>
+        <x:v>09-09 15:30</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
         <x:v>7</x:v>
@@ -3121,10 +3787,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G16" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H16" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str">
         <x:v>其他</x:v>
@@ -3132,36 +3798,36 @@
       <x:c r="J16" s="11" t="str"/>
       <x:c r="K16" s="11" t="str"/>
       <x:c r="L16" s="10" t="str">
-        <x:v>灵川剧场</x:v>
+        <x:v>渲渲动画</x:v>
       </x:c>
       <x:c r="M16" s="10" t="str">
-        <x:v>儿子儿媳多次提议我搬回乡下养老，将城里的宽敞住房腾出来给女方父母长期居住。我笑着点头应下，转头便将这套三室朝南的江景房产挂牌出售，最终成交二百八十万元。我随即购置了一套一室一厅的小户型，更换门锁后独自入住。他们上门索要钥匙，我没有开门。名下房产我自有主张，谁也别想插手安排。</x:v>
+        <x:v>吴真真带着末世惨死的记忆重生，抢下秘宝空间，囤积海量物资，提前规避天灾人祸。她意外发现家人同样重生，一家人携手为末日做足准备。灾变如期而至，病毒、台风、极寒轮番降临。她机缘结识实力强悍的谢穆辰，二人从互相试探到并肩而立。面对凶悍恶徒与重重危机，吴真真依靠空间与智慧守护至亲，谢穆辰以自身力量与之守望相助，在满目疮痍的末世里，拼尽全力守住生存希望，奔赴属于他们的新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B17" s="10" t="str">
+        <x:v>蒙蒙半故</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="str">
+        <x:v>09-05 20:27</x:v>
+      </x:c>
+      <x:c r="D17" s="11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B17" s="10" t="str">
-        <x:v>征地我秒签跑路，全村笑我半年</x:v>
-      </x:c>
-      <x:c r="C17" s="11" t="str">
-        <x:v>09-10 11:30</x:v>
-      </x:c>
-      <x:c r="D17" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E17" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F17" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G17" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="H17" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="I17" s="10" t="str">
         <x:v>其他</x:v>
@@ -3169,21 +3835,21 @@
       <x:c r="J17" s="11" t="str"/>
       <x:c r="K17" s="11" t="str"/>
       <x:c r="L17" s="10" t="str">
-        <x:v>小六动漫</x:v>
+        <x:v>小斐漫剧</x:v>
       </x:c>
       <x:c r="M17" s="10" t="str">
-        <x:v>赵家湾迎来高速征地，村民受村长赵德厚鼓动抱团拒签，妄想抬价拿到四百五十万补偿。林远察觉当地岩溶地质暗藏线路改线风险，不顾全村嘲讽，果断签下312万补偿款，带父母搬离老家。后续高速果真改线，全村一分补偿落空。曾经嘲笑林远的村民陷入债务困境，赵德厚登门求助，林远守住底线，一家人握紧安稳生活，告诫众人抉择要靠自己。</x:v>
+        <x:v>拥有漫长寿命的男人隐姓埋名，以外卖员身份在都市生活。百岁老人临终的遗愿，让他卷入豪门家族的纷争。他结识家族女总裁，接连应对家族内斗、敌对势力与神秘长生组织的重重算计。二人携手揭开千年前的尘封秘辛，对抗妄图窃取长生力量的反派，在危机之中彼此羁绊，还要面对即将开启的上古昆仑之门带来的巨大未知考验。</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>重生后我守住全村</x:v>
+        <x:v>征地我秒签跑路，全村笑我半年</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>09-10 08:08</x:v>
+        <x:v>09-10 11:30</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
         <x:v>5</x:v>
@@ -3195,10 +3861,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G18" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H18" s="11" t="n">
-        <x:v>129</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I18" s="10" t="str">
         <x:v>其他</x:v>
@@ -3206,21 +3872,21 @@
       <x:c r="J18" s="11" t="str"/>
       <x:c r="K18" s="11" t="str"/>
       <x:c r="L18" s="10" t="str">
-        <x:v>金果漫剧</x:v>
+        <x:v>小六动漫</x:v>
       </x:c>
       <x:c r="M18" s="10" t="str">
-        <x:v>70年代冬，赵满仓在父亲离世后重回鼠灾前八天。面对家中骤变，他选择先护住亲人，带着前世经验迁入碾坊，储粮备药，筑墙防鼠，设点防疫。灾情来临时，他联合李杏儿，刘石头和乡亲稳住村庄，并用账册与规矩澄清父亲名誉。风雪过后，黎家沟建起防鼠坊，猫舍和净粮地窖，众人也在互助中迎来新生。</x:v>
+        <x:v>赵家湾迎来高速征地，村民受村长赵德厚鼓动抱团拒签，妄想抬价拿到四百五十万补偿。林远察觉当地岩溶地质暗藏线路改线风险，不顾全村嘲讽，果断签下312万补偿款，带父母搬离老家。后续高速果真改线，全村一分补偿落空。曾经嘲笑林远的村民陷入债务困境，赵德厚登门求助，林远守住底线，一家人握紧安稳生活，告诫众人抉择要靠自己。</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>假老板娘遇上真董事长</x:v>
+        <x:v>重生后我守住全村</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>09-10 08:08</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
         <x:v>5</x:v>
@@ -3232,26 +3898,32 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G19" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H19" s="11" t="str"/>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H19" s="11" t="n">
+        <x:v>129</x:v>
+      </x:c>
       <x:c r="I19" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J19" s="11" t="str"/>
       <x:c r="K19" s="11" t="str"/>
-      <x:c r="L19" s="10" t="str"/>
-      <x:c r="M19" s="10" t="str"/>
+      <x:c r="L19" s="10" t="str">
+        <x:v>金果漫剧</x:v>
+      </x:c>
+      <x:c r="M19" s="10" t="str">
+        <x:v>70年代冬，赵满仓在父亲离世后重回鼠灾前八天。面对家中骤变，他选择先护住亲人，带着前世经验迁入碾坊，储粮备药，筑墙防鼠，设点防疫。灾情来临时，他联合李杏儿，刘石头和乡亲稳住村庄，并用账册与规矩澄清父亲名誉。风雪过后，黎家沟建起防鼠坊，猫舍和净粮地窖，众人也在互助中迎来新生。</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>大坝边寻回的真千金</x:v>
+        <x:v>假老板娘遇上真董事长</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>09-10 11:26</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
         <x:v>5</x:v>
@@ -3263,47 +3935,41 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G20" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H20" s="11" t="n">
-        <x:v>53</x:v>
-      </x:c>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H20" s="11" t="str"/>
       <x:c r="I20" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J20" s="11" t="str"/>
       <x:c r="K20" s="11" t="str"/>
-      <x:c r="L20" s="10" t="str">
-        <x:v>喵琪琪追剧</x:v>
-      </x:c>
-      <x:c r="M20" s="10" t="str">
-        <x:v>大坝突发险情，农村女孩夏晚禾凭借熟悉的环境和过人的勇气，不顾危险救下被困的沈长洲。一次意外的救援，让两个陌生人的命运重新交织。随着调查深入，沈长洲发现这个善良坚韧的女孩，竟是自己失散二十年的亲生女儿。面对迟来的亲情和真假千金的风波，夏晚禾没有依靠身份改变人生，而是用智慧、担当和努力证明自己的价值。陆言川也在一次次并肩相处中，被她的真诚与坚强打动，陪她找回亲情，走向新的未来。</x:v>
-      </x:c>
+      <x:c r="L20" s="10" t="str"/>
+      <x:c r="M20" s="10" t="str"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
+        <x:v>大坝边寻回的真千金</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>09-11 09:00</x:v>
+        <x:v>09-10 11:26</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G21" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="H21" s="11" t="n">
-        <x:v>133</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I21" s="10" t="str">
         <x:v>其他</x:v>
@@ -3311,24 +3977,24 @@
       <x:c r="J21" s="11" t="str"/>
       <x:c r="K21" s="11" t="str"/>
       <x:c r="L21" s="10" t="str">
-        <x:v>阳阳动画</x:v>
+        <x:v>喵琪琪追剧</x:v>
       </x:c>
       <x:c r="M21" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
+        <x:v>大坝突发险情，农村女孩夏晚禾凭借熟悉的环境和过人的勇气，不顾危险救下被困的沈长洲。一次意外的救援，让两个陌生人的命运重新交织。随着调查深入，沈长洲发现这个善良坚韧的女孩，竟是自己失散二十年的亲生女儿。面对迟来的亲情和真假千金的风波，夏晚禾没有依靠身份改变人生，而是用智慧、担当和努力证明自己的价值。陆言川也在一次次并肩相处中，被她的真诚与坚强打动，陪她找回亲情，走向新的未来。</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>穿越60我有空间不愁吃喝</x:v>
+        <x:v>三分钱的取舍</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>09-07 00:04</x:v>
+        <x:v>09-10 17:29</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
         <x:v>5</x:v>
@@ -3337,10 +4003,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G22" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H22" s="11" t="n">
-        <x:v>1000</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str">
         <x:v>其他</x:v>
@@ -3348,24 +4014,24 @@
       <x:c r="J22" s="11" t="str"/>
       <x:c r="K22" s="11" t="str"/>
       <x:c r="L22" s="10" t="str">
-        <x:v>夜珠AI剧场</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="M22" s="10" t="str">
-        <x:v>现代青年刘大壮意外穿越到60年代，成了同名同姓的16岁穷小子。原主因相亲被拒、家徒四壁，下河摸鱼时溺亡。大壮醒来后发现脑中多了一座九层宝塔空间——内有灵药田与灵泉潭水，作物两小时成熟、产量翻五倍。饥荒年代，别人啃树皮喝稀粥，他靠空间种出满仓土豆粮食，黑市换粮票钞票，让饿肚子的父母姐姐们吃上饱饭。从人人嘲笑的穷小子，到带着全家逆袭翻盘，且看他手握宝塔空间，在艰苦年代闯出一条吃喝不愁的逆袭</x:v>
+        <x:v>青石沟果农为省下代办三分钱，甩开中间商周成岳，直接对接收购商方洪生收桃。可脱离周成岳统筹调度后，摘桃、排单、装车乱象丛生，桃子积压损耗。周成岳转身接手偏远的十里湾桃园，凭口碑站稳脚跟。经历一季波折，青石沟众人幡然醒悟，重新读懂代办的价值。</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="n">
-        <x:v>49</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>三分钱的取舍</x:v>
+        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>09-10 17:29</x:v>
+        <x:v>09-11 09:00</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
         <x:v>5</x:v>
@@ -3374,10 +4040,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G23" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H23" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
         <x:v>其他</x:v>
@@ -3385,15 +4051,15 @@
       <x:c r="J23" s="11" t="str"/>
       <x:c r="K23" s="11" t="str"/>
       <x:c r="L23" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>阳阳动画</x:v>
       </x:c>
       <x:c r="M23" s="10" t="str">
-        <x:v>青石沟果农为省下代办三分钱，甩开中间商周成岳，直接对接收购商方洪生收桃。可脱离周成岳统筹调度后，摘桃、排单、装车乱象丛生，桃子积压损耗。周成岳转身接手偏远的十里湾桃园，凭口碑站稳脚跟。经历一季波折，青石沟众人幡然醒悟，重新读懂代办的价值。</x:v>
+        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
         <x:v>回到零四年进军彩铃界</x:v>
@@ -3424,28 +4090,28 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="n">
-        <x:v>24</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>大力末世降临，小尸尸我呀吸吸吸</x:v>
+        <x:v>穿越60我有空间不愁吃喝</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>09-05 06:39</x:v>
+        <x:v>09-07 00:04</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G25" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H25" s="11" t="n">
-        <x:v>120</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str">
         <x:v>其他</x:v>
@@ -3453,10 +4119,121 @@
       <x:c r="J25" s="11" t="str"/>
       <x:c r="K25" s="11" t="str"/>
       <x:c r="L25" s="10" t="str">
+        <x:v>夜珠AI剧场</x:v>
+      </x:c>
+      <x:c r="M25" s="10" t="str">
+        <x:v>现代青年刘大壮意外穿越到60年代，成了同名同姓的16岁穷小子。原主因相亲被拒、家徒四壁，下河摸鱼时溺亡。大壮醒来后发现脑中多了一座九层宝塔空间——内有灵药田与灵泉潭水，作物两小时成熟、产量翻五倍。饥荒年代，别人啃树皮喝稀粥，他靠空间种出满仓土豆粮食，黑市换粮票钞票，让饿肚子的父母姐姐们吃上饱饭。从人人嘲笑的穷小子，到带着全家逆袭翻盘，且看他手握宝塔空间，在艰苦年代闯出一条吃喝不愁的逆袭</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="11" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B26" s="10" t="str">
+        <x:v>大力末世降临，小尸尸我呀吸吸吸</x:v>
+      </x:c>
+      <x:c r="C26" s="11" t="str">
+        <x:v>09-05 06:39</x:v>
+      </x:c>
+      <x:c r="D26" s="11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E26" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F26" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G26" s="11" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H26" s="11" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="I26" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="J26" s="11" t="str"/>
+      <x:c r="K26" s="11" t="str"/>
+      <x:c r="L26" s="10" t="str">
         <x:v>漫剧传送门</x:v>
       </x:c>
-      <x:c r="M25" s="10" t="str">
+      <x:c r="M26" s="10" t="str">
         <x:v>末世降临前三分钟，互联网实习生许多多收到末日预警，凭借超强求生本能疯狂囤货，固守自家堡垒苟命求生。可末世浩劫之下，她依旧不幸感染病毒，意外蜕变为保留完整人类意识的特殊丧尸，同时解锁无限扩容的多面魔方空间。半月后，3A特殊作战小队前来清剿，带队队长竟是她年少暗恋的同桌秦洛。知晓她的特殊异能与理智后，秦洛将她收留，她自此成为小队最强辅助与移动军需库。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="11" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B27" s="10" t="str">
+        <x:v>一碗剩饭，看清二十五年工友情</x:v>
+      </x:c>
+      <x:c r="C27" s="11" t="str">
+        <x:v>09-09 16:30</x:v>
+      </x:c>
+      <x:c r="D27" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E27" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F27" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G27" s="11" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H27" s="11" t="n">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="I27" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="J27" s="11" t="str"/>
+      <x:c r="K27" s="11" t="str"/>
+      <x:c r="L27" s="10" t="str">
+        <x:v>花花剧场</x:v>
+      </x:c>
+      <x:c r="M27" s="10" t="str">
+        <x:v>工地老工友孟庆福深夜胃疾发作，求热一份食堂将要倒掉的剩饭，却遭相熟二十五年的食堂老板周大海拒绝，宁可倒进泔水桶也不通融。钢筋班班长陈守山目睹后不再做班组挂账，四十多名工人不再光顾。周大海为抢市场降价挤压对手，打压新入局者罗建军。罗建军从零摸索完善供餐制度，周大海恶性竞争选用低价货源，最终在食品安全检查中失去工地经营资格。二十五年工友情再也回不到当初，但彼此可以体面相见。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="11" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B28" s="10" t="str">
+        <x:v>我月薪八千，但公司是我的</x:v>
+      </x:c>
+      <x:c r="C28" s="11" t="str">
+        <x:v>09-09 20:47</x:v>
+      </x:c>
+      <x:c r="D28" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E28" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F28" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G28" s="11" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H28" s="11" t="n">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="I28" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="J28" s="11" t="str"/>
+      <x:c r="K28" s="11" t="str"/>
+      <x:c r="L28" s="10" t="str">
+        <x:v>阿宝剧场</x:v>
+      </x:c>
+      <x:c r="M28" s="10" t="str">
+        <x:v>北辰科技创始人陆景川为人低调，相亲时只坦言月薪八千，当即被相亲对象乔思雨嫌弃离场，还被对方在朋友圈造谣成“蹭咖啡捞男”。后续乔思雨应聘北辰科技、出席投资饭局，接连撞见陆景川，场面屡屡社死。陆景川却在常去的咖啡厅，因店员沈安然的仗义执言，窥见了比金钱更动人的真心。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3511,16 +4288,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>2.2</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F2" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>2026-09-15 12-43</x:v>
+        <x:v>2026-09-15 15-11</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3528,22 +4305,22 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>征地我秒签跑路，全村笑我半年</x:v>
+        <x:v>今晚查寝，别开门</x:v>
       </x:c>
       <x:c r="C3" s="11" t="n">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
-        <x:v>2.6</x:v>
+        <x:v>5.2</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F3" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>2026-09-15 12-43</x:v>
+        <x:v>2026-09-15 15-11</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -3551,22 +4328,22 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>今晚查寝，别开门</x:v>
+        <x:v>征地我秒签跑路，全村笑我半年</x:v>
       </x:c>
       <x:c r="C4" s="11" t="n">
         <x:v>29</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>5.7</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F4" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>2026-09-15 12-43</x:v>
+        <x:v>2026-09-15 15-11</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3580,16 +4357,16 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>7.7</x:v>
+        <x:v>8.7</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F5" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>2026-09-15 12-43</x:v>
+        <x:v>2026-09-15 15-11</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -3600,19 +4377,19 @@
         <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
       </x:c>
       <x:c r="C6" s="11" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>7.9</x:v>
+        <x:v>9.1</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F6" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>2026-09-15 11-11</x:v>
+        <x:v>2026-09-15 15-11</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3626,16 +4403,16 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>11.6</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F7" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>2026-09-15 10-11</x:v>
+        <x:v>2026-09-15 15-11</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -3649,16 +4426,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>8.3</x:v>
+        <x:v>9.1</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>2026-09-15 12-43</x:v>
+        <x:v>2026-09-15 15-11</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3672,16 +4449,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>14.3</x:v>
+        <x:v>13.5</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>2026-09-15 12-43</x:v>
+        <x:v>2026-09-15 15-11</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -3689,22 +4466,22 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>退婚后我在七零赚钱养家致富</x:v>
+        <x:v>青牛引泉来</x:v>
       </x:c>
       <x:c r="C10" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>12.6</x:v>
+        <x:v>10.9</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F10" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>2026-09-15 10-11</x:v>
+        <x:v>2026-09-15 15-11</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -3712,22 +4489,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>一墙之隔，皆是人心</x:v>
+        <x:v>三分钱的取舍</x:v>
       </x:c>
       <x:c r="C11" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>13.4</x:v>
+        <x:v>13.5</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
-        <x:v>2026-09-15 10-11</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -3735,22 +4512,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>泰城错嫁</x:v>
+        <x:v>退婚后我在七零赚钱养家致富</x:v>
       </x:c>
       <x:c r="C12" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>12.1</x:v>
+        <x:v>13.5</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G12" s="11" t="str">
-        <x:v>2026-09-15 09-53</x:v>
+        <x:v>2026-09-15 10-11</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -3758,22 +4535,22 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>惊絮无声：傻女的绝杀</x:v>
+        <x:v>一墙之隔，皆是人心</x:v>
       </x:c>
       <x:c r="C13" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>12.3</x:v>
+        <x:v>13.9</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G13" s="11" t="str">
-        <x:v>2026-09-15 06-08</x:v>
+        <x:v>2026-09-15 10-11</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -3781,22 +4558,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
+        <x:v>泰城错嫁</x:v>
       </x:c>
       <x:c r="C14" s="11" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="n">
+        <x:v>12.8</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D14" s="11" t="n">
-        <x:v>11.7</x:v>
-      </x:c>
-      <x:c r="E14" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F14" s="11" t="n">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="G14" s="11" t="str">
-        <x:v>2026-09-15 06-08</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -3804,22 +4581,22 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>三分钱的取舍</x:v>
+        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
       </x:c>
       <x:c r="C15" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>13.5</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F15" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G15" s="11" t="str">
-        <x:v>2026-09-15 09-53</x:v>
+        <x:v>2026-09-15 15-11</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -3827,22 +4604,22 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>青牛引泉来</x:v>
+        <x:v>惊絮无声：傻女的绝杀</x:v>
       </x:c>
       <x:c r="C16" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>11.1</x:v>
+        <x:v>12.9</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G16" s="11" t="str">
-        <x:v>2026-09-15 12-43</x:v>
+        <x:v>2026-09-15 06-08</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -3850,22 +4627,22 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>离家十年，回来女儿被换了</x:v>
+        <x:v>搬进江景房，老公每晚对着鱼缸坐两小时</x:v>
       </x:c>
       <x:c r="C17" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>9.8</x:v>
+        <x:v>7.4</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F17" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G17" s="11" t="str">
-        <x:v>2026-09-15 09-53</x:v>
+        <x:v>2026-09-15 15-11</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -3873,22 +4650,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>锦书迟</x:v>
+        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
       </x:c>
       <x:c r="C18" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>13.6</x:v>
+        <x:v>13.1</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G18" s="11" t="str">
-        <x:v>2026-09-15 02-44</x:v>
+        <x:v>2026-09-15 06-08</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -3919,22 +4696,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
+        <x:v>离家十年，回来女儿被换了</x:v>
       </x:c>
       <x:c r="C20" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>9.5</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G20" s="11" t="str">
-        <x:v>2026-09-15 12-43</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -3942,22 +4719,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>今天开始做裴总</x:v>
+        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
       </x:c>
       <x:c r="C21" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>14.2</x:v>
+        <x:v>6.7</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G21" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-15 15-11</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -3965,22 +4742,22 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>反派拿捏！</x:v>
+        <x:v>不靠谱爸妈很靠谱</x:v>
       </x:c>
       <x:c r="C22" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>14.7</x:v>
+        <x:v>15.3</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G22" s="11" t="str">
-        <x:v>2026-09-14 20-13</x:v>
+        <x:v>2026-09-15 11-11</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -3988,22 +4765,22 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>不靠谱爸妈很靠谱</x:v>
+        <x:v>重生80，救下神雕后我带村民走出大山</x:v>
       </x:c>
       <x:c r="C23" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>15.3</x:v>
+        <x:v>17.5</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G23" s="11" t="str">
-        <x:v>2026-09-15 11-11</x:v>
+        <x:v>2026-09-15 15-11</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -4011,22 +4788,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>搬进江景房，老公每晚对着鱼缸坐两小时</x:v>
+        <x:v>锦书迟</x:v>
       </x:c>
       <x:c r="C24" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>7.9</x:v>
+        <x:v>14.9</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G24" s="11" t="str">
-        <x:v>2026-09-15 12-43</x:v>
+        <x:v>2026-09-15 02-44</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -4034,22 +4811,22 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>小妹初长成</x:v>
+        <x:v>婚礼当天我不嫁了</x:v>
       </x:c>
       <x:c r="C25" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>14.4</x:v>
+        <x:v>14.8</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G25" s="11" t="str">
-        <x:v>2026-09-14 12-34</x:v>
+        <x:v>2026-09-14 22-12</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -4057,22 +4834,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
+        <x:v>小妹初长成</x:v>
       </x:c>
       <x:c r="C26" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>8.5</x:v>
+        <x:v>13.8</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G26" s="11" t="str">
-        <x:v>2026-09-15 12-43</x:v>
+        <x:v>2026-09-14 12-34</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -4080,22 +4857,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>婚礼当天我不嫁了</x:v>
+        <x:v>15年青春苦守，未婚夫装穷归来</x:v>
       </x:c>
       <x:c r="C27" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>14.8</x:v>
+        <x:v>3.4</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str">
-        <x:v>2026-09-14 22-12</x:v>
+        <x:v>2026-09-15 15-11</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -4103,22 +4880,22 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
+        <x:v>新厂旧账</x:v>
       </x:c>
       <x:c r="C28" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
-        <x:v>16.1</x:v>
+        <x:v>7.1</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F28" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G28" s="11" t="str">
-        <x:v>2026-09-15 10-11</x:v>
+        <x:v>2026-09-15 15-11</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -4126,22 +4903,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>回到零四年进军彩铃界</x:v>
+        <x:v>今天开始做裴总</x:v>
       </x:c>
       <x:c r="C29" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>16.6</x:v>
+        <x:v>12.4</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str">
-        <x:v>2026-09-14 12-34</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -4149,22 +4926,22 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>重生80，救下神雕后我带村民走出大山</x:v>
+        <x:v>反派拿捏！</x:v>
       </x:c>
       <x:c r="C30" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>14.7</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G30" s="11" t="str">
-        <x:v>2026-09-15 12-43</x:v>
+        <x:v>2026-09-14 20-13</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -4172,22 +4949,22 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>穿越60我有空间不愁吃喝</x:v>
+        <x:v>四个崽崽瞒不住了</x:v>
       </x:c>
       <x:c r="C31" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
-        <x:v>15.7</x:v>
+        <x:v>16.1</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G31" s="11" t="str">
-        <x:v>2026-09-14 20-18</x:v>
+        <x:v>2026-09-15 10-11</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -4195,22 +4972,22 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="10" t="str">
-        <x:v>闪婚老公有点野</x:v>
+        <x:v>回到零四年进军彩铃界</x:v>
       </x:c>
       <x:c r="C32" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D32" s="11" t="n">
-        <x:v>14.6</x:v>
+        <x:v>16.6</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G32" s="11" t="str">
-        <x:v>2026-09-15 06-54</x:v>
+        <x:v>2026-09-14 12-34</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -4218,22 +4995,22 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="10" t="str">
-        <x:v>一张废票毁了她</x:v>
+        <x:v>穿越60我有空间不愁吃喝</x:v>
       </x:c>
       <x:c r="C33" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D33" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>15.7</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F33" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G33" s="11" t="str">
-        <x:v>2026-09-15 05-52</x:v>
+        <x:v>2026-09-14 20-18</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -4241,22 +5018,22 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="10" t="str">
-        <x:v>15年青春苦守，未婚夫装穷归来</x:v>
+        <x:v>重回82：我成山君契约万兽打猎宠妻</x:v>
       </x:c>
       <x:c r="C34" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D34" s="11" t="n">
-        <x:v>5.2</x:v>
+        <x:v>8.6</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F34" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G34" s="11" t="str">
-        <x:v>2026-09-15 12-43</x:v>
+        <x:v>2026-09-15 15-11</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -4264,22 +5041,22 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="10" t="str">
-        <x:v>新厂旧账</x:v>
+        <x:v>八零悍妇：女汉子逆袭记</x:v>
       </x:c>
       <x:c r="C35" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D35" s="11" t="n">
+        <x:v>10.8</x:v>
+      </x:c>
+      <x:c r="E35" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D35" s="11" t="n">
-        <x:v>5.2</x:v>
-      </x:c>
-      <x:c r="E35" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="F35" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G35" s="11" t="str">
-        <x:v>2026-09-15 12-43</x:v>
+        <x:v>2026-09-15 15-11</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -4287,22 +5064,22 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="10" t="str">
-        <x:v>重生后我守住全村</x:v>
+        <x:v>闪婚老公有点野</x:v>
       </x:c>
       <x:c r="C36" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
-        <x:v>5.8</x:v>
+        <x:v>14.6</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G36" s="11" t="str">
-        <x:v>2026-09-14 20-18</x:v>
+        <x:v>2026-09-15 06-54</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -4310,22 +5087,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="10" t="str">
-        <x:v>离婚那天我多了个痞帅老爹</x:v>
+        <x:v>重生后我守住全村</x:v>
       </x:c>
       <x:c r="C37" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D37" s="11" t="n">
-        <x:v>11.2</x:v>
+        <x:v>5.8</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G37" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-14 20-18</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -4333,22 +5110,22 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="10" t="str">
-        <x:v>辣媳进门，我给公婆撑腰</x:v>
+        <x:v>离婚那天我多了个痞帅老爹</x:v>
       </x:c>
       <x:c r="C38" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D38" s="11" t="n">
+        <x:v>11.2</x:v>
+      </x:c>
+      <x:c r="E38" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E38" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="F38" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G38" s="11" t="str">
-        <x:v>2026-09-15 06-08</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -4356,22 +5133,22 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="10" t="str">
-        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
+        <x:v>一张废票毁了她</x:v>
       </x:c>
       <x:c r="C39" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D39" s="11" t="n">
-        <x:v>8.7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G39" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-15 05-52</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -4379,22 +5156,22 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="10" t="str">
-        <x:v>装傻下山</x:v>
+        <x:v>辣媳进门，我给公婆撑腰</x:v>
       </x:c>
       <x:c r="C40" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D40" s="11" t="n">
-        <x:v>11.7</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G40" s="11" t="str">
-        <x:v>2026-09-14 04-11</x:v>
+        <x:v>2026-09-15 06-08</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -4402,22 +5179,22 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="10" t="str">
-        <x:v>人人都说她娇气，出事她护我到底</x:v>
+        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
       </x:c>
       <x:c r="C41" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D41" s="11" t="n">
-        <x:v>5.3</x:v>
+        <x:v>8.7</x:v>
       </x:c>
       <x:c r="E41" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F41" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G41" s="11" t="str">
-        <x:v>2026-09-14 12-34</x:v>
+        <x:v>2026-09-15 01-59</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -4425,22 +5202,22 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B42" s="10" t="str">
-        <x:v>我家后山藏真龙</x:v>
+        <x:v>人人都说她娇气，出事她护我到底</x:v>
       </x:c>
       <x:c r="C42" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D42" s="11" t="n">
-        <x:v>5.7</x:v>
+        <x:v>5.3</x:v>
       </x:c>
       <x:c r="E42" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="F42" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G42" s="11" t="str">
-        <x:v>2026-09-14 09-24</x:v>
+        <x:v>2026-09-14 12-34</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -4448,22 +5225,22 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" s="10" t="str">
-        <x:v>不负恩情不负卿</x:v>
+        <x:v>我家后山藏真龙</x:v>
       </x:c>
       <x:c r="C43" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D43" s="11" t="n">
-        <x:v>9.7</x:v>
+        <x:v>5.7</x:v>
       </x:c>
       <x:c r="E43" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="F43" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G43" s="11" t="str">
-        <x:v>2026-09-14 10-32</x:v>
+        <x:v>2026-09-14 09-24</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -4471,22 +5248,22 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="10" t="str">
-        <x:v>那块玉，带我们回家</x:v>
+        <x:v>不负恩情不负卿</x:v>
       </x:c>
       <x:c r="C44" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D44" s="11" t="n">
-        <x:v>11.3</x:v>
+        <x:v>9.7</x:v>
       </x:c>
       <x:c r="E44" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F44" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G44" s="11" t="str">
-        <x:v>2026-09-14 09-24</x:v>
+        <x:v>2026-09-14 10-32</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -4494,22 +5271,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="10" t="str">
-        <x:v>拂衣震九州</x:v>
+        <x:v>那块玉，带我们回家</x:v>
       </x:c>
       <x:c r="C45" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D45" s="11" t="n">
-        <x:v>10.3</x:v>
+        <x:v>11.3</x:v>
       </x:c>
       <x:c r="E45" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F45" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G45" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-14 09-24</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -4517,19 +5294,19 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B46" s="10" t="str">
-        <x:v>大坝边寻回的真千金</x:v>
+        <x:v>拂衣震九州</x:v>
       </x:c>
       <x:c r="C46" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D46" s="11" t="n">
-        <x:v>12.7</x:v>
+        <x:v>10.3</x:v>
       </x:c>
       <x:c r="E46" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F46" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G46" s="11" t="str">
         <x:v>2026-09-15 03-38</x:v>
@@ -4540,19 +5317,19 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B47" s="10" t="str">
-        <x:v>山下是绝路，山上是生门</x:v>
+        <x:v>大坝边寻回的真千金</x:v>
       </x:c>
       <x:c r="C47" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D47" s="11" t="n">
-        <x:v>14.3</x:v>
+        <x:v>12.7</x:v>
       </x:c>
       <x:c r="E47" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F47" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G47" s="11" t="str">
         <x:v>2026-09-15 03-38</x:v>
@@ -4563,22 +5340,22 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B48" s="10" t="str">
-        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
+        <x:v>山下是绝路，山上是生门</x:v>
       </x:c>
       <x:c r="C48" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D48" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>14.3</x:v>
       </x:c>
       <x:c r="E48" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F48" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G48" s="11" t="str">
-        <x:v>2026-09-14 06-11</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -4586,7 +5363,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B49" s="10" t="str">
-        <x:v>八零悍妇：女汉子逆袭记</x:v>
+        <x:v>我SSS级狂龙，出世即无敌</x:v>
       </x:c>
       <x:c r="C49" s="11" t="n">
         <x:v>2</x:v>
@@ -4595,13 +5372,13 @@
         <x:v>5.5</x:v>
       </x:c>
       <x:c r="E49" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F49" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G49" s="11" t="str">
-        <x:v>2026-09-15 12-43</x:v>
+        <x:v>2026-09-15 01-59</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -4609,13 +5386,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B50" s="10" t="str">
-        <x:v>我SSS级狂龙，出世即无敌</x:v>
+        <x:v>一碗人间赴景深</x:v>
       </x:c>
       <x:c r="C50" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D50" s="11" t="n">
-        <x:v>5.5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E50" s="11" t="n">
         <x:v>5</x:v>
@@ -4624,7 +5401,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G50" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-14 09-24</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -4632,19 +5409,19 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B51" s="10" t="str">
-        <x:v>一碗人间赴景深</x:v>
+        <x:v>白鹿照归途</x:v>
       </x:c>
       <x:c r="C51" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D51" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>12.5</x:v>
       </x:c>
       <x:c r="E51" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F51" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G51" s="11" t="str">
         <x:v>2026-09-14 09-24</x:v>
@@ -6252,30 +7029,30 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>09-18 07:30</x:v>
+        <x:v>09-18 10:00</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
-        <x:v>制度面前，没有例外</x:v>
+        <x:v>欢迎降落人间</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F8" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G8" s="10" t="str">
-        <x:v>星漫动漫剧场</x:v>
+        <x:v>泰北剧场</x:v>
       </x:c>
       <x:c r="H8" s="11" t="str"/>
       <x:c r="I8" s="10" t="str"/>
       <x:c r="J8" s="10" t="str">
-        <x:v>网络安全工程师陈东明因抵御黑客攻击累倒，醒来却遭副总监孙振邦以旷工为由处罚。陈东明未作争辩，而是依据员工手册对孙振邦的管理行为进行合规审查。他通过调取日志与单据，揭露对方虚报加班及违规操作导致安全漏洞的事实，最终借助审计力量使真相大白，维护了职场公平与正义。</x:v>
+        <x:v>心理医生林语笙闪婚特勤机长萧寒，婚后丈夫执行高危任务常年失联，她日夜忧心却独自支撑，霸气反击极品前任和同事的挑衅。萧寒带伤转岗后，她创立“云端的心跳”项目，用专业治愈飞行员高空创伤。在一次航班危机中，她稳定乘客情绪，协助丈夫指挥盲降成功，因过度紧张险些流产。幸得母女平安，家庭圆满。</x:v>
       </x:c>
       <x:c r="K8" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；54集，次优长度；发布账号「星漫动漫剧场」按上榜剧数入榜</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；64集，主力长度；发布账号「泰北剧场」</x:v>
       </x:c>
       <x:c r="L8" s="11" t="n">
         <x:v>6.5</x:v>
@@ -6289,27 +7066,27 @@
         <x:v>09-18 10:00</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
-        <x:v>欢迎降落人间</x:v>
+        <x:v>福宝驾到</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F9" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>萌宝治愈</x:v>
       </x:c>
       <x:c r="G9" s="10" t="str">
-        <x:v>泰北剧场</x:v>
+        <x:v>笙笙不息剧场</x:v>
       </x:c>
       <x:c r="H9" s="11" t="str"/>
       <x:c r="I9" s="10" t="str"/>
       <x:c r="J9" s="10" t="str">
-        <x:v>心理医生林语笙闪婚特勤机长萧寒，婚后丈夫执行高危任务常年失联，她日夜忧心却独自支撑，霸气反击极品前任和同事的挑衅。萧寒带伤转岗后，她创立“云端的心跳”项目，用专业治愈飞行员高空创伤。在一次航班危机中，她稳定乘客情绪，协助丈夫指挥盲降成功，因过度紧张险些流产。幸得母女平安，家庭圆满。</x:v>
+        <x:v>福宝出生那天，天降金龙，金元宝破土而出。原本倒霉的王文阳和妻子林婉，在福宝的好运加持下，从欠债的倒霉蛋逆袭成厨王，将福宝饭店开成了镇上最火的饭店。萌娃招财，母鸡镇宅，坏人遭殃，好人发财，福宝带领一家人把日子过得红红火火。</x:v>
       </x:c>
       <x:c r="K9" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；64集，主力长度；发布账号「泰北剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「笙笙不息剧场」</x:v>
       </x:c>
       <x:c r="L9" s="11" t="n">
         <x:v>6.5</x:v>
@@ -6323,30 +7100,30 @@
         <x:v>09-18 10:00</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
-        <x:v>福宝驾到</x:v>
+        <x:v>一笼包子暖一生</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F10" s="10" t="str">
-        <x:v>萌宝治愈</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="G10" s="10" t="str">
-        <x:v>笙笙不息剧场</x:v>
+        <x:v>鹿姐短剧</x:v>
       </x:c>
       <x:c r="H10" s="11" t="str"/>
       <x:c r="I10" s="10" t="str"/>
       <x:c r="J10" s="10" t="str">
-        <x:v>福宝出生那天，天降金龙，金元宝破土而出。原本倒霉的王文阳和妻子林婉，在福宝的好运加持下，从欠债的倒霉蛋逆袭成厨王，将福宝饭店开成了镇上最火的饭店。萌娃招财，母鸡镇宅，坏人遭殃，好人发财，福宝带领一家人把日子过得红红火火。</x:v>
+        <x:v>张默自幼家贫，被经营早餐铺的陈家夫妇好心收留。他刻苦读书、知恩图报，以优异成绩考上大学。多年后事业有成归来，帮助遇到困难的养兄重振早餐铺，还开设爱心窗口传递善意。一家人从隔阂到和解，用一餐一饭温暖彼此，演绎了平凡生活中的真情与成长。</x:v>
       </x:c>
       <x:c r="K10" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「笙笙不息剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；85集，主力长度；发布账号「鹿姐短剧」</x:v>
       </x:c>
       <x:c r="L10" s="11" t="n">
-        <x:v>6.5</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -6354,30 +7131,30 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="11" t="str">
-        <x:v>09-18 10:00</x:v>
+        <x:v>09-18 08:00</x:v>
       </x:c>
       <x:c r="C11" s="10" t="str">
-        <x:v>一笼包子暖一生</x:v>
+        <x:v>七零：靠厨艺征服所有人</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F11" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>年代怀旧 / 美食治愈</x:v>
       </x:c>
       <x:c r="G11" s="10" t="str">
-        <x:v>鹿姐短剧</x:v>
+        <x:v>清染剧场</x:v>
       </x:c>
       <x:c r="H11" s="11" t="str"/>
       <x:c r="I11" s="10" t="str"/>
       <x:c r="J11" s="10" t="str">
-        <x:v>张默自幼家贫，被经营早餐铺的陈家夫妇好心收留。他刻苦读书、知恩图报，以优异成绩考上大学。多年后事业有成归来，帮助遇到困难的养兄重振早餐铺，还开设爱心窗口传递善意。一家人从隔阂到和解，用一餐一饭温暖彼此，演绎了平凡生活中的真情与成长。</x:v>
+        <x:v>北方农村姑娘乔麦穗身手强悍，却因体态丰腴愁婚嫁。她在后山救下受伤知青傅卫东，二人成婚。傅卫东意外昏迷，乔麦穗独自进城寻夫，途中勇擒扒手。小姑傅小玲持离婚协议逼她签字，当场被公安拆穿。傅母嫌弃她出身，杨小曼伺机想取代她。乔麦穗凭一手厨艺在医院食堂立足，接连挫败二人陷害。她怀双胞胎遭质疑，拿出孕检单自证清白。夫妻联手设局，揭露杨小曼制造车祸、策划绑架的罪行。乔麦穗凭实力收获事业与圆满家庭</x:v>
       </x:c>
       <x:c r="K11" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；85集，主力长度；发布账号「鹿姐短剧」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；61集，主力长度；发布账号「清染剧场」；女频受众</x:v>
       </x:c>
       <x:c r="L11" s="11" t="n">
         <x:v>6</x:v>
@@ -6388,30 +7165,30 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="11" t="str">
-        <x:v>09-18 08:00</x:v>
+        <x:v>09-18 08:30</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
-        <x:v>七零：靠厨艺征服所有人</x:v>
+        <x:v>九洲影帝</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F12" s="10" t="str">
-        <x:v>年代怀旧 / 美食治愈</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G12" s="10" t="str">
-        <x:v>清染剧场</x:v>
+        <x:v>白狼动画</x:v>
       </x:c>
       <x:c r="H12" s="11" t="str"/>
       <x:c r="I12" s="10" t="str"/>
       <x:c r="J12" s="10" t="str">
-        <x:v>北方农村姑娘乔麦穗身手强悍，却因体态丰腴愁婚嫁。她在后山救下受伤知青傅卫东，二人成婚。傅卫东意外昏迷，乔麦穗独自进城寻夫，途中勇擒扒手。小姑傅小玲持离婚协议逼她签字，当场被公安拆穿。傅母嫌弃她出身，杨小曼伺机想取代她。乔麦穗凭一手厨艺在医院食堂立足，接连挫败二人陷害。她怀双胞胎遭质疑，拿出孕检单自证清白。夫妻联手设局，揭露杨小曼制造车祸、策划绑架的罪行。乔麦穗凭实力收获事业与圆满家庭</x:v>
+        <x:v>十八年前，陆家伪造九色神光异象，为少主陆尘立下大帝转世人设，蒙蔽九州。十八年后，骗局即将败露，父亲陆寒却功成身退飞升仙界，将烂摊子尽数甩给陆尘。面对全九州的审视与试探，陆尘被迫以凡人之躯，靠演技、系统金手指与一张碎嘴，在一次次绝境中强行演戏、绝地求生，一步步将假帝演成真帝。</x:v>
       </x:c>
       <x:c r="K12" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；61集，主力长度；发布账号「清染剧场」；女频受众</x:v>
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×2；75集，主力长度；发布账号「白狼动画」</x:v>
       </x:c>
       <x:c r="L12" s="11" t="n">
         <x:v>6</x:v>
@@ -6422,30 +7199,30 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="11" t="str">
-        <x:v>09-18 08:30</x:v>
+        <x:v>09-18 08:00</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
-        <x:v>九洲影帝</x:v>
+        <x:v>公路求生：我能无限升级资源</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F13" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G13" s="10" t="str">
-        <x:v>白狼动画</x:v>
+        <x:v>飞卢漫剧场</x:v>
       </x:c>
       <x:c r="H13" s="11" t="str"/>
       <x:c r="I13" s="10" t="str"/>
       <x:c r="J13" s="10" t="str">
-        <x:v>十八年前，陆家伪造九色神光异象，为少主陆尘立下大帝转世人设，蒙蔽九州。十八年后，骗局即将败露，父亲陆寒却功成身退飞升仙界，将烂摊子尽数甩给陆尘。面对全九州的审视与试探，陆尘被迫以凡人之躯，靠演技、系统金手指与一张碎嘴，在一次次绝境中强行演戏、绝地求生，一步步将假帝演成真帝。</x:v>
+        <x:v>末世公路世界，陈博遭恋人与仇人联手背叛，险些死于异兽之口，濒死觉醒无限升级系统，万物皆可升级强化！他改造武器战车，收服寻宝战宠哈士奇，在危机四伏的戈壁求生复仇，结识夏安、周沫等伙伴。为对抗搞人体实验的邪恶组织黑玫区，他建立红叶盟，打造空中堡垒，横扫异兽与敌人。随着真相揭开，末世竟是高维文明深渊议会的筛选实验，人类只是实验品。陈博集结全球幸存者，迎战域外强敌，摧毁污染根源，净化星球，终结末日。</x:v>
       </x:c>
       <x:c r="K13" s="10" t="str">
-        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×2；75集，主力长度；发布账号「白狼动画」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；112集，次优长度；发布账号「飞卢漫剧场」</x:v>
       </x:c>
       <x:c r="L13" s="11" t="n">
         <x:v>6</x:v>
@@ -6459,10 +7236,10 @@
         <x:v>09-18 08:00</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
-        <x:v>公路求生：我能无限升级资源</x:v>
+        <x:v>别动我的车</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>112</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str">
         <x:v>其他</x:v>
@@ -6471,15 +7248,15 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G14" s="10" t="str">
-        <x:v>飞卢漫剧场</x:v>
+        <x:v>山海皆可平</x:v>
       </x:c>
       <x:c r="H14" s="11" t="str"/>
       <x:c r="I14" s="10" t="str"/>
       <x:c r="J14" s="10" t="str">
-        <x:v>末世公路世界，陈博遭恋人与仇人联手背叛，险些死于异兽之口，濒死觉醒无限升级系统，万物皆可升级强化！他改造武器战车，收服寻宝战宠哈士奇，在危机四伏的戈壁求生复仇，结识夏安、周沫等伙伴。为对抗搞人体实验的邪恶组织黑玫区，他建立红叶盟，打造空中堡垒，横扫异兽与敌人。随着真相揭开，末世竟是高维文明深渊议会的筛选实验，人类只是实验品。陈博集结全球幸存者，迎战域外强敌，摧毁污染根源，净化星球，终结末日。</x:v>
+        <x:v>李舒仪升职后通勤距离增加，想要取回自己的陪嫁车，却遭到公公霸占，丈夫还劝她骑电瓶车上班。公婆为留住车子，跑到她公司撒泼闹事，搅黄她来之不易的升职机会。李舒仪彻底清醒，决心结束婚姻。婆家不仅不愿归还车辆，还私自转走她五百万陪嫁，占用她的学区房。她步步维权，收回房产、追回钱款，与江述年顺利离婚，凭借自身实力重新争取到总监岗位，掌控自己的人生。</x:v>
       </x:c>
       <x:c r="K14" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；112集，次优长度；发布账号「飞卢漫剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；63集，主力长度；发布账号「山海皆可平」；女频受众</x:v>
       </x:c>
       <x:c r="L14" s="11" t="n">
         <x:v>6</x:v>
@@ -6490,30 +7267,30 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="11" t="str">
-        <x:v>09-18 08:00</x:v>
+        <x:v>09-18 10:00</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
-        <x:v>别动我的车</x:v>
+        <x:v>十八年的枕边谎言</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F15" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="G15" s="10" t="str">
-        <x:v>山海皆可平</x:v>
+        <x:v>南风听你说</x:v>
       </x:c>
       <x:c r="H15" s="11" t="str"/>
       <x:c r="I15" s="10" t="str"/>
       <x:c r="J15" s="10" t="str">
-        <x:v>李舒仪升职后通勤距离增加，想要取回自己的陪嫁车，却遭到公公霸占，丈夫还劝她骑电瓶车上班。公婆为留住车子，跑到她公司撒泼闹事，搅黄她来之不易的升职机会。李舒仪彻底清醒，决心结束婚姻。婆家不仅不愿归还车辆，还私自转走她五百万陪嫁，占用她的学区房。她步步维权，收回房产、追回钱款，与江述年顺利离婚，凭借自身实力重新争取到总监岗位，掌控自己的人生。</x:v>
+        <x:v>开学日，贺安然陪同女儿肖雨入学，却被丈夫肖晨与他的青梅许悠联手，以游戏惩罚为由扔在三十公里外的烈日路边，身无分文。心死的她彻底觉醒，当即返程火速出售婚前房产，委托律师提起离婚。梳理共同财产时，肖晨隐瞒十八年、暗中供养私生子的真相随之曝光。最终肖晨身败名裂、众叛亲离，许悠卷走其仅剩积蓄抽身离去，骄纵的女儿也幡然悔悟。贺安然彻底摆脱消耗型婚姻，重拾事业与自我，终遇良人开启全新人生。</x:v>
       </x:c>
       <x:c r="K15" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；63集，主力长度；发布账号「山海皆可平」；女频受众</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；57集，次优长度；发布账号「南风听你说」；剧名钩子×1</x:v>
       </x:c>
       <x:c r="L15" s="11" t="n">
         <x:v>6</x:v>
@@ -6524,30 +7301,30 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="11" t="str">
-        <x:v>09-18 10:00</x:v>
+        <x:v>09-18 00:06</x:v>
       </x:c>
       <x:c r="C16" s="10" t="str">
-        <x:v>十八年的枕边谎言</x:v>
+        <x:v>摆摊被讹十万，我的千金身份藏不住了</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F16" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="G16" s="10" t="str">
-        <x:v>南风听你说</x:v>
+        <x:v>郁郁剧场</x:v>
       </x:c>
       <x:c r="H16" s="11" t="str"/>
       <x:c r="I16" s="10" t="str"/>
       <x:c r="J16" s="10" t="str">
-        <x:v>开学日，贺安然陪同女儿肖雨入学，却被丈夫肖晨与他的青梅许悠联手，以游戏惩罚为由扔在三十公里外的烈日路边，身无分文。心死的她彻底觉醒，当即返程火速出售婚前房产，委托律师提起离婚。梳理共同财产时，肖晨隐瞒十八年、暗中供养私生子的真相随之曝光。最终肖晨身败名裂、众叛亲离，许悠卷走其仅剩积蓄抽身离去，骄纵的女儿也幡然悔悟。贺安然彻底摆脱消耗型婚姻，重拾事业与自我，终遇良人开启全新人生。</x:v>
+        <x:v>天鸿集团千金姜晚晴隐瞒身份，在自家工地门口摆摊卖饺子做社会实践，因物美价廉抢了包工头妻子王秀梅的生意。王秀梅掀摊泼水烫伤姜晚晴，还联合当项目经理的弟弟王志强讹诈十万赔偿，威胁作证工人。姜晚晴联系集团秘书，亮出真实身份。董事长姜鸿远赶到，结合暗访记者的取证，彻查工地贪腐乱象。王家姐弟互相揭发内讧，相关人员被带走调查，工地不公问题得到整治。</x:v>
       </x:c>
       <x:c r="K16" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；57集，次优长度；发布账号「南风听你说」；剧名钩子×1</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；58集，次优长度；发布账号「郁郁剧场」；剧名钩子×1</x:v>
       </x:c>
       <x:c r="L16" s="11" t="n">
         <x:v>6</x:v>
@@ -17914,10 +18691,10 @@
         <x:v>网络安全工程师陈东明因抵御黑客攻击累倒，醒来却遭副总监孙振邦以旷工为由处罚。陈东明未作争辩，而是依据员工手册对孙振邦的管理行为进行合规审查。他通过调取日志与单据，揭露对方虚报加班及违规操作导致安全漏洞的事实，最终借助审计力量使真相大白，维护了职场公平与正义。</x:v>
       </x:c>
       <x:c r="K3" s="10" t="str">
-        <x:v>发布账号「星漫动漫剧场」进入单口径TOP12，账号高分；题材契合爆款主线×3（剧名/分类/简介三路识别）；54集，次优长度</x:v>
+        <x:v>发布账号「星漫动漫剧场」稳定产出（上榜25次/出过5部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；54集，次优长度</x:v>
       </x:c>
       <x:c r="L3" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -18503,30 +19280,30 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B21" s="11" t="str">
-        <x:v>09-17 06:10</x:v>
+        <x:v>09-17 11:00</x:v>
       </x:c>
       <x:c r="C21" s="10" t="str">
-        <x:v>回乡赶海：海底宝贝一眼看清</x:v>
+        <x:v>重生九零，我成了窝囊二房掌权人</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>152</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E21" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F21" s="10" t="str">
-        <x:v>种田囤货</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G21" s="10" t="str">
-        <x:v>星漫动漫剧场</x:v>
+        <x:v>诗婳-小林看剧</x:v>
       </x:c>
       <x:c r="H21" s="11" t="str"/>
       <x:c r="I21" s="10" t="str"/>
       <x:c r="J21" s="10" t="str">
-        <x:v>叶廷遭上司陷害离职，回乡激活海洋系统。凭借海神之眼，他在碎石滩捕获珍稀海产，狠狠打脸嘲讽他的村民与亲戚。随后他发掘明代沉船获国家表彰，取得岛屿自治权。面对暗网高额悬赏，叶廷聘请特种兵教官，誓要守护宝藏并反击跨国势力。</x:v>
+        <x:v>90年代，重生回到新婚第二天的女主苏晚，为保护曾被奶奶张淑芬和大房磋磨致死的公婆、丈夫与小姑，凭借前世记忆与经商能力，反抗偏心长辈的压榨，阻止换亲、夺回小姑录取通知书，带领二房创办卤味厂分家单过，最终发家致富，让二房挺直腰杆，带动全村共同致富。</x:v>
       </x:c>
       <x:c r="K21" s="10" t="str">
-        <x:v>发布账号「星漫动漫剧场」进入单口径TOP12，账号高分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；152集，长度需关注</x:v>
+        <x:v>发布账号「诗婳-小林看剧」稳定产出（上榜8次/出过5部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；66集，主力长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="L21" s="11" t="n">
         <x:v>13</x:v>
@@ -18537,13 +19314,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B22" s="11" t="str">
-        <x:v>09-17 11:00</x:v>
+        <x:v>09-17 14:00</x:v>
       </x:c>
       <x:c r="C22" s="10" t="str">
-        <x:v>重生九零，我成了窝囊二房掌权人</x:v>
+        <x:v>宫韵渡人间</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E22" s="11" t="str">
         <x:v>其他</x:v>
@@ -18552,18 +19329,18 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G22" s="10" t="str">
-        <x:v>诗婳-小林看剧</x:v>
+        <x:v>风花叙漫事</x:v>
       </x:c>
       <x:c r="H22" s="11" t="str"/>
       <x:c r="I22" s="10" t="str"/>
       <x:c r="J22" s="10" t="str">
-        <x:v>90年代，重生回到新婚第二天的女主苏晚，为保护曾被奶奶张淑芬和大房磋磨致死的公婆、丈夫与小姑，凭借前世记忆与经商能力，反抗偏心长辈的压榨，阻止换亲、夺回小姑录取通知书，带领二房创办卤味厂分家单过，最终发家致富，让二房挺直腰杆，带动全村共同致富。</x:v>
+        <x:v>宫廷首席教引嬷嬷穿越成现代保姆，刚被儿媳赶出家门，便凭一身鉴宝茶艺惊艳豪门，被林家重金特聘。面对堂叔对独孙的捧杀纵容，她以皇家教养之道点醒孩子奋起用功，更在寿宴上揭穿阴谋、反将一军。护住继承人，签下终身契约，于今世重放光芒。</x:v>
       </x:c>
       <x:c r="K22" s="10" t="str">
-        <x:v>发布账号「诗婳-小林看剧」稳定产出（上榜8次/出过5部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；66集，主力长度；剧名钩子×1</x:v>
+        <x:v>发布账号「风花叙漫事」稳定产出（上榜12次/出过4部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；54集，次优长度；女频受众</x:v>
       </x:c>
       <x:c r="L22" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -18571,13 +19348,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B23" s="11" t="str">
-        <x:v>09-17 14:00</x:v>
+        <x:v>09-17 07:18</x:v>
       </x:c>
       <x:c r="C23" s="10" t="str">
-        <x:v>宫韵渡人间</x:v>
+        <x:v>辰辰的升职奇遇</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E23" s="11" t="str">
         <x:v>其他</x:v>
@@ -18586,15 +19363,15 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G23" s="10" t="str">
-        <x:v>风花叙漫事</x:v>
+        <x:v>星漫世界</x:v>
       </x:c>
       <x:c r="H23" s="11" t="str"/>
       <x:c r="I23" s="10" t="str"/>
       <x:c r="J23" s="10" t="str">
-        <x:v>宫廷首席教引嬷嬷穿越成现代保姆，刚被儿媳赶出家门，便凭一身鉴宝茶艺惊艳豪门，被林家重金特聘。面对堂叔对独孙的捧杀纵容，她以皇家教养之道点醒孩子奋起用功，更在寿宴上揭穿阴谋、反将一军。护住继承人，签下终身契约，于今世重放光芒。</x:v>
+        <x:v>待业程序员江辰因救助走失女童，报警时措辞不当引发警方误会，被当作嫌疑人带走。虽经监控澄清清白，却因网络误解陷入舆论风波。为保护尽职警官，他主动承担责难，并凭借专业逻辑协助破案，最终化解危机，赢得尊重与职业机遇。</x:v>
       </x:c>
       <x:c r="K23" s="10" t="str">
-        <x:v>发布账号「风花叙漫事」稳定产出（上榜12次/出过4部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；54集，次优长度；女频受众</x:v>
+        <x:v>发布账号「星漫世界」进入单口径TOP12，账号高分；题材契合爆款主线×2（剧名/分类/简介三路识别）；96集，主力长度</x:v>
       </x:c>
       <x:c r="L23" s="11" t="n">
         <x:v>12</x:v>
@@ -18605,33 +19382,33 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B24" s="11" t="str">
-        <x:v>09-17 07:18</x:v>
+        <x:v>09-17 10:00</x:v>
       </x:c>
       <x:c r="C24" s="10" t="str">
-        <x:v>辰辰的升职奇遇</x:v>
+        <x:v>全能系统：我和校花的三个月考察期</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E24" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F24" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="G24" s="10" t="str">
-        <x:v>星漫世界</x:v>
+        <x:v>糖糖动漫剧场</x:v>
       </x:c>
       <x:c r="H24" s="11" t="str"/>
       <x:c r="I24" s="10" t="str"/>
       <x:c r="J24" s="10" t="str">
-        <x:v>待业程序员江辰因救助走失女童，报警时措辞不当引发警方误会，被当作嫌疑人带走。虽经监控澄清清白，却因网络误解陷入舆论风波。为保护尽职警官，他主动承担责难，并凭借专业逻辑协助破案，最终化解危机，赢得尊重与职业机遇。</x:v>
+        <x:v>大四学生陈阳意外激活全能系统，机缘之下与叶清雅开启相处。他恪守责任底线，善用系统赋能的投资、技艺能力踏实创业，打造金融与实业版图。面对情敌刁难、豪门审视，始终坚守本心，凭借自身才干赢得认可，携手爱人并肩打拼，实现事业爱情双丰收，诠释当代青年自立向上的奋斗风貌。</x:v>
       </x:c>
       <x:c r="K24" s="10" t="str">
-        <x:v>发布账号「星漫世界」进入单口径TOP12，账号高分；题材契合爆款主线×2（剧名/分类/简介三路识别）；96集，主力长度</x:v>
+        <x:v>发布账号「糖糖动漫剧场」稳定产出（上榜6次/出过5部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；79集，主力长度</x:v>
       </x:c>
       <x:c r="L24" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -18639,30 +19416,30 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B25" s="11" t="str">
-        <x:v>09-17 10:00</x:v>
+        <x:v>09-17 08:00</x:v>
       </x:c>
       <x:c r="C25" s="10" t="str">
-        <x:v>全能系统：我和校花的三个月考察期</x:v>
+        <x:v>夫人她求权不求爱</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E25" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F25" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G25" s="10" t="str">
-        <x:v>糖糖动漫剧场</x:v>
+        <x:v>小狐狸剧场</x:v>
       </x:c>
       <x:c r="H25" s="11" t="str"/>
       <x:c r="I25" s="10" t="str"/>
       <x:c r="J25" s="10" t="str">
-        <x:v>大四学生陈阳意外激活全能系统，机缘之下与叶清雅开启相处。他恪守责任底线，善用系统赋能的投资、技艺能力踏实创业，打造金融与实业版图。面对情敌刁难、豪门审视，始终坚守本心，凭借自身才干赢得认可，携手爱人并肩打拼，实现事业爱情双丰收，诠释当代青年自立向上的奋斗风貌。</x:v>
+        <x:v>阮朝歌与裴寂夜自幼相互扶持。婚后她扶他坐上裴氏掌权人之位，代行总裁权力，守住裴胤的继承权。后来，裴寂夜的心渐渐远了。阮朝歌表面纵容，实则早在那场手术里留下无法逆转的伏笔。宋玲儿回国后，表面替她不平，暗中却靠近裴寂夜，伤害她。宋玲儿有孕，裴家动摇。阮朝歌明知那不是裴寂夜的血脉，交权离婚，远走海外。</x:v>
       </x:c>
       <x:c r="K25" s="10" t="str">
-        <x:v>发布账号「糖糖动漫剧场」稳定产出（上榜6次/出过5部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；79集，主力长度</x:v>
+        <x:v>发布账号「小狐狸剧场」稳定产出（上榜11次/出过5部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；60集，主力长度；女频受众</x:v>
       </x:c>
       <x:c r="L25" s="11" t="n">
         <x:v>11</x:v>
@@ -18673,30 +19450,30 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B26" s="11" t="str">
-        <x:v>09-17 08:00</x:v>
+        <x:v>09-17 06:00</x:v>
       </x:c>
       <x:c r="C26" s="10" t="str">
-        <x:v>夫人她求权不求爱</x:v>
+        <x:v>救了雪山神女，满山珍宝任我取</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E26" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F26" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>种田囤货 / 战神异能</x:v>
       </x:c>
       <x:c r="G26" s="10" t="str">
-        <x:v>小狐狸剧场</x:v>
+        <x:v>潮汐互娱-爽剧社</x:v>
       </x:c>
       <x:c r="H26" s="11" t="str"/>
       <x:c r="I26" s="10" t="str"/>
       <x:c r="J26" s="10" t="str">
-        <x:v>阮朝歌与裴寂夜自幼相互扶持。婚后她扶他坐上裴氏掌权人之位，代行总裁权力，守住裴胤的继承权。后来，裴寂夜的心渐渐远了。阮朝歌表面纵容，实则早在那场手术里留下无法逆转的伏笔。宋玲儿回国后，表面替她不平，暗中却靠近裴寂夜，伤害她。宋玲儿有孕，裴家动摇。阮朝歌明知那不是裴寂夜的血脉，交权离婚，远走海外。</x:v>
+        <x:v>萧大根被贪婪的大哥萧大山推下雪山悬崖，大难不死，意外救下重伤的雪山神女，获赠山神之力。他回到村子当众揭穿大哥阴谋并分家，采得极品山货赚得第一桶金，狠狠打脸嫌贫爱富的前未婚妻林乃湘。能力出众的大根结识镇上泼辣妩媚的山货女商人柳芸，大根多次深入险地，采得极品山货，更在山中收服巨型白虎。最终大根用山神之力克服重重困难，带领兄弟们发家致富，并与心爱之人修成正果。</x:v>
       </x:c>
       <x:c r="K26" s="10" t="str">
-        <x:v>发布账号「小狐狸剧场」稳定产出（上榜11次/出过5部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；60集，主力长度；女频受众</x:v>
+        <x:v>发布账号「潮汐互娱-爽剧社」稳定产出（上榜8次/出过5部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；97集，主力长度</x:v>
       </x:c>
       <x:c r="L26" s="11" t="n">
         <x:v>11</x:v>
@@ -18707,33 +19484,33 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B27" s="11" t="str">
-        <x:v>09-17 06:00</x:v>
+        <x:v>09-17 06:10</x:v>
       </x:c>
       <x:c r="C27" s="10" t="str">
-        <x:v>救了雪山神女，满山珍宝任我取</x:v>
+        <x:v>回乡赶海：海底宝贝一眼看清</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E27" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F27" s="10" t="str">
-        <x:v>种田囤货 / 战神异能</x:v>
+        <x:v>种田囤货</x:v>
       </x:c>
       <x:c r="G27" s="10" t="str">
-        <x:v>潮汐互娱-爽剧社</x:v>
+        <x:v>星漫动漫剧场</x:v>
       </x:c>
       <x:c r="H27" s="11" t="str"/>
       <x:c r="I27" s="10" t="str"/>
       <x:c r="J27" s="10" t="str">
-        <x:v>萧大根被贪婪的大哥萧大山推下雪山悬崖，大难不死，意外救下重伤的雪山神女，获赠山神之力。他回到村子当众揭穿大哥阴谋并分家，采得极品山货赚得第一桶金，狠狠打脸嫌贫爱富的前未婚妻林乃湘。能力出众的大根结识镇上泼辣妩媚的山货女商人柳芸，大根多次深入险地，采得极品山货，更在山中收服巨型白虎。最终大根用山神之力克服重重困难，带领兄弟们发家致富，并与心爱之人修成正果。</x:v>
+        <x:v>叶廷遭上司陷害离职，回乡激活海洋系统。凭借海神之眼，他在碎石滩捕获珍稀海产，狠狠打脸嘲讽他的村民与亲戚。随后他发掘明代沉船获国家表彰，取得岛屿自治权。面对暗网高额悬赏，叶廷聘请特种兵教官，誓要守护宝藏并反击跨国势力。</x:v>
       </x:c>
       <x:c r="K27" s="10" t="str">
-        <x:v>发布账号「潮汐互娱-爽剧社」稳定产出（上榜8次/出过5部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；97集，主力长度</x:v>
+        <x:v>发布账号「星漫动漫剧场」稳定产出（上榜25次/出过5部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；152集，长度需关注</x:v>
       </x:c>
       <x:c r="L27" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -19824,8 +20601,12 @@
       <x:c r="G59" s="10" t="str">
         <x:v>盐系少女社</x:v>
       </x:c>
-      <x:c r="H59" s="11" t="str"/>
-      <x:c r="I59" s="10" t="str"/>
+      <x:c r="H59" s="11" t="str">
+        <x:v>已上榜</x:v>
+      </x:c>
+      <x:c r="I59" s="10" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
       <x:c r="J59" s="10" t="str">
         <x:v>相恋七年的姜栀子，凌晨去机场接出差归来的男友沈闻舟，却发现车内自己送的平安符，被换成实习生林暖手工做的拼豆挂件。面对男友的谎言与恼羞成怒的指责，姜栀子清醒识破背叛，抢先将试图把自己丢在郊外的沈闻舟赶下车。回到家中，林暖找上门，姜栀子直接将二人赶出属于自己的房子。经过一系列的矛盾之后，姜栀子彻底斩断过往，专注事业奔赴属于自己的人生。</x:v>
       </x:c>
@@ -23324,7 +24105,7 @@
         <x:v>已上榜</x:v>
       </x:c>
       <x:c r="I160" s="10" t="str">
-        <x:v>2026-09-09、2026-09-10、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-15</x:v>
       </x:c>
       <x:c r="J160" s="10" t="str">
         <x:v>工地老工友孟庆福深夜胃疾发作，求热一份食堂将要倒掉的剩饭，却遭相熟二十五年的食堂老板周大海拒绝，宁可倒进泔水桶也不通融。钢筋班班长陈守山目睹后不再做班组挂账，四十多名工人不再光顾。周大海为抢市场降价挤压对手，打压新入局者罗建军。罗建军从零摸索完善供餐制度，周大海恶性竞争选用低价货源，最终在食品安全检查中失去工地经营资格。二十五年工友情再也回不到当初，但彼此可以体面相见。</x:v>
@@ -29691,10 +30472,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>925</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>52.7%</x:v>
+        <x:v>53.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -29702,10 +30483,10 @@
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>479</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>27.3%</x:v>
+        <x:v>27.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -29713,10 +30494,10 @@
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>352</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>20.0%</x:v>
+        <x:v>19.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
@@ -29740,10 +30521,10 @@
         <x:v>30-49集</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>181</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>11.2%</x:v>
+        <x:v>11.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -29751,10 +30532,10 @@
         <x:v>50-79集</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>690</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>42.8%</x:v>
+        <x:v>42.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -29762,10 +30543,10 @@
         <x:v>80-99集</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>12.5%</x:v>
+        <x:v>12.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -29773,10 +30554,10 @@
         <x:v>100集以上</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>538</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>33.4%</x:v>
+        <x:v>33.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
@@ -29800,10 +30581,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>772</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>44.0%</x:v>
+        <x:v>44.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -29814,7 +30595,7 @@
         <x:v>315</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>17.9%</x:v>
+        <x:v>17.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -29822,7 +30603,7 @@
         <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
         <x:v>9.1%</x:v>
@@ -29830,10 +30611,10 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="10" t="str">
-        <x:v>年代怀旧/种田囤货</x:v>
+        <x:v>家庭伦理/萌宝</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>152</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
         <x:v>8.7%</x:v>
@@ -29841,10 +30622,10 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="10" t="str">
-        <x:v>家庭伦理/萌宝</x:v>
+        <x:v>年代怀旧/种田囤货</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>151</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
         <x:v>8.6%</x:v>
@@ -29855,10 +30636,10 @@
         <x:v>战神/异能/爽文</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>8.4%</x:v>
+        <x:v>8.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -29866,7 +30647,7 @@
         <x:v>现实反转/人性</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
         <x:v>6.3%</x:v>
@@ -29888,10 +30669,10 @@
         <x:v>逆袭/打脸</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>4.8%</x:v>
+        <x:v>4.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -29899,7 +30680,7 @@
         <x:v>都市职场</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
         <x:v>4.2%</x:v>
@@ -30025,10 +30806,10 @@
         <x:v>上榜19次</x:v>
       </x:c>
       <x:c r="B38" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C38" s="11" t="str">
-        <x:v>0.1%</x:v>
+        <x:v>0.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -30036,7 +30817,7 @@
         <x:v>上榜18次</x:v>
       </x:c>
       <x:c r="B39" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C39" s="11" t="str">
         <x:v>0.2%</x:v>
@@ -30138,7 +30919,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C48" s="11" t="str">
-        <x:v>1.7%</x:v>
+        <x:v>1.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -30149,7 +30930,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C49" s="11" t="str">
-        <x:v>3.0%</x:v>
+        <x:v>2.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -30171,7 +30952,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="C51" s="11" t="str">
-        <x:v>3.5%</x:v>
+        <x:v>3.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -30179,10 +30960,10 @@
         <x:v>上榜5次</x:v>
       </x:c>
       <x:c r="B52" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C52" s="11" t="str">
-        <x:v>4.0%</x:v>
+        <x:v>4.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -30190,10 +30971,10 @@
         <x:v>上榜4次</x:v>
       </x:c>
       <x:c r="B53" s="11" t="n">
-        <x:v>109</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C53" s="11" t="str">
-        <x:v>6.2%</x:v>
+        <x:v>6.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -30204,7 +30985,7 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="C54" s="11" t="str">
-        <x:v>11.6%</x:v>
+        <x:v>11.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -30215,7 +30996,7 @@
         <x:v>315</x:v>
       </x:c>
       <x:c r="C55" s="11" t="str">
-        <x:v>17.9%</x:v>
+        <x:v>17.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -30223,10 +31004,10 @@
         <x:v>上榜1次</x:v>
       </x:c>
       <x:c r="B56" s="11" t="n">
-        <x:v>774</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="C56" s="11" t="str">
-        <x:v>44.1%</x:v>
+        <x:v>44.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="22" customHeight="1">
@@ -30250,10 +31031,10 @@
         <x:v>CP自营</x:v>
       </x:c>
       <x:c r="B60" s="11" t="n">
-        <x:v>1158</x:v>
+        <x:v>1165</x:v>
       </x:c>
       <x:c r="C60" s="11" t="str">
-        <x:v>65.9%</x:v>
+        <x:v>65.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -30261,10 +31042,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B61" s="11" t="n">
-        <x:v>587</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="C61" s="11" t="str">
-        <x:v>33.4%</x:v>
+        <x:v>33.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -30439,7 +31220,7 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>腿毛漫漫</x:v>
       </x:c>
       <x:c r="B79" s="11" t="n">
         <x:v>28</x:v>
@@ -30450,10 +31231,10 @@
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="10" t="str">
-        <x:v>壹琚-娜娜看剧</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="B80" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C80" s="11" t="str">
         <x:v>0.5%</x:v>
@@ -30461,7 +31242,7 @@
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="10" t="str">
-        <x:v>一张不够花</x:v>
+        <x:v>壹琚-娜娜看剧</x:v>
       </x:c>
       <x:c r="B81" s="11" t="n">
         <x:v>27</x:v>
@@ -30587,7 +31368,7 @@
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>腿毛漫漫</x:v>
       </x:c>
       <x:c r="B94" s="11" t="n">
         <x:v>6</x:v>
@@ -30598,7 +31379,7 @@
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="10" t="str">
-        <x:v>至尊爽剧社</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="B95" s="11" t="n">
         <x:v>6</x:v>
@@ -30609,10 +31390,10 @@
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="10" t="str">
-        <x:v>星漫动漫剧场</x:v>
+        <x:v>至尊爽剧社</x:v>
       </x:c>
       <x:c r="B96" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C96" s="11" t="str">
         <x:v>0.3%</x:v>
@@ -30620,7 +31401,7 @@
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="10" t="str">
-        <x:v>腿毛漫漫</x:v>
+        <x:v>星漫动漫剧场</x:v>
       </x:c>
       <x:c r="B97" s="11" t="n">
         <x:v>5</x:v>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R825a0079333b4210"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="Raa713705da4f45c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="Ra69eb369d573474e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="R475d4140fae34ccf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP20剧重点跟踪" sheetId="5" r:id="R94c85084a583430f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="6" r:id="Ra3b5305435554c77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="7" r:id="R034980d438584d29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="8" r:id="R910e10a1c8354d21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="9" r:id="R4afdf7ad9328418f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R15d0368836e048c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="Re0c5e268ef6b4415"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="R44e750db178b4114"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="R386edf451e7a45f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP20剧重点跟踪" sheetId="5" r:id="R3d19cdb7b5664506"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="6" r:id="R6eb5f83d072c4c5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="7" r:id="Ra5a71fec216d412c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="8" r:id="R83de17c4143d403f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="9" r:id="R95618ba5823e405b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1202,7 +1202,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
         <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
@@ -1239,13 +1239,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
-        <x:v>攻略失败后我不装了</x:v>
+        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>09-15 15:00</x:v>
+        <x:v>09-15 08:30</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str"/>
       <x:c r="F4" s="11" t="str"/>
@@ -1256,19 +1256,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I4" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J4" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K4" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L4" s="11" t="str">
-        <x:v>喵喵说漫</x:v>
+        <x:v>琥珀漫剧</x:v>
       </x:c>
       <x:c r="M4" s="10" t="str">
-        <x:v>陆瑶做了百年攻略任务，反倒被系统判定为史上最废宿主，嘲讽她连宗门看门大黄都攻略不了，直接解绑。重获自由的她解开封印，觉醒万年难遇的天生道体。她撕碎弟子玉牌，决绝离开凌云峰，手握海量资源专心经商修炼。从前被她百般讨好的师尊师兄尽数落魄、满心悔意。她看淡情爱纠葛，收服大黄相伴，一路开挂逆袭，潇洒飞升开启全新仙生。</x:v>
+        <x:v>海鲜市场老手陈放，因一个两块钱的冰袋被十二年合伙人当众算旧账，心寒清账，净身出户。他没有抱怨，也没有以牙还牙，而是加入冷清档口“梅姐水产”，从零开始。他坚持明码标价、沥水称重、死活分卖、批次可查，宁可少接单，也不混货、不凑数、不赚亏心钱。面对低价抢客、恶意破坏、临时缺货等风波，他与叶梅靠诚信、规矩和彼此信任，一步步赢得客户与连锁企业的认可。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1276,13 +1276,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
-        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
+        <x:v>四个崽崽瞒不住了</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>09-15 08:30</x:v>
+        <x:v>09-15 00:08</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str"/>
       <x:c r="F5" s="11" t="str"/>
@@ -1293,19 +1293,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I5" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="J5" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K5" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L5" s="11" t="str">
-        <x:v>琥珀漫剧</x:v>
+        <x:v>桃子动漫剧场</x:v>
       </x:c>
       <x:c r="M5" s="10" t="str">
-        <x:v>海鲜市场老手陈放，因一个两块钱的冰袋被十二年合伙人当众算旧账，心寒清账，净身出户。他没有抱怨，也没有以牙还牙，而是加入冷清档口“梅姐水产”，从零开始。他坚持明码标价、沥水称重、死活分卖、批次可查，宁可少接单，也不混货、不凑数、不赚亏心钱。面对低价抢客、恶意破坏、临时缺货等风波，他与叶梅靠诚信、规矩和彼此信任，一步步赢得客户与连锁企业的认可。</x:v>
+        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1316,10 +1316,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
+        <x:v>攻略失败后我不装了</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>09-15 00:08</x:v>
+        <x:v>09-15 15:00</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str"/>
       <x:c r="F6" s="11" t="str"/>
@@ -1330,19 +1330,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I6" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="J6" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K6" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="L6" s="11" t="str">
-        <x:v>桃子动漫剧场</x:v>
+        <x:v>喵喵说漫</x:v>
       </x:c>
       <x:c r="M6" s="10" t="str">
-        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
+        <x:v>陆瑶做了百年攻略任务，反倒被系统判定为史上最废宿主，嘲讽她连宗门看门大黄都攻略不了，直接解绑。重获自由的她解开封印，觉醒万年难遇的天生道体。她撕碎弟子玉牌，决绝离开凌云峰，手握海量资源专心经商修炼。从前被她百般讨好的师尊师兄尽数落魄、满心悔意。她看淡情爱纠葛，收服大黄相伴，一路开挂逆袭，潇洒飞升开启全新仙生。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1350,7 +1350,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
         <x:v>一盒印泥引发的全局封锁</x:v>
@@ -1381,13 +1381,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
-        <x:v>我在工地卖盒饭带火一座城</x:v>
+        <x:v>我都元婴期了，你跟我说开学</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>09-14 14:52</x:v>
+        <x:v>09-16 00:10</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str"/>
       <x:c r="F8" s="11" t="str"/>
@@ -1398,19 +1398,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
-        <x:v>144</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="J8" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K8" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L8" s="11" t="str">
-        <x:v>左手良画</x:v>
+        <x:v>梦启剧场</x:v>
       </x:c>
       <x:c r="M8" s="10" t="str">
-        <x:v>小伙白叶遭遇老板跑路，半年工资付诸东流，意外被铁炒勺砸中觉醒超级餐饮系统。大雪封路堵车途中完成首份任务，靠着系统加持的厨艺，路边卖盒饭赚到第一桶金。回乡钻研秘制酱肉，赶集摆摊火爆出圈，还临危接手大型寿宴惊艳众人。过完新年，他怀揣梦想奔赴外地，准备开启属于自己的餐饮创业之路。</x:v>
+        <x:v>修士宁尘遭遇偷袭，身负重伤从修真界回到现代。时间只流逝一个暑假，他被迫入读青州大学，借居在乔姨家中，与傲娇少女许舒颜同住。一边伪装普通学生，一边寻找修复元神伤势的资源，接连化解校园、市井与古武圈子的各类风波，开启充满反差的现代生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1418,13 +1418,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
-        <x:v>我都元婴期了，你跟我说开学</x:v>
+        <x:v>我在工地卖盒饭带火一座城</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>09-16 00:10</x:v>
+        <x:v>09-14 14:52</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str"/>
       <x:c r="F9" s="11" t="str"/>
@@ -1435,19 +1435,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I9" s="11" t="n">
-        <x:v>475</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="J9" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K9" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="L9" s="11" t="str">
-        <x:v>梦启剧场</x:v>
+        <x:v>左手良画</x:v>
       </x:c>
       <x:c r="M9" s="10" t="str">
-        <x:v>修士宁尘遭遇偷袭，身负重伤从修真界回到现代。时间只流逝一个暑假，他被迫入读青州大学，借居在乔姨家中，与傲娇少女许舒颜同住。一边伪装普通学生，一边寻找修复元神伤势的资源，接连化解校园、市井与古武圈子的各类风波，开启充满反差的现代生活。</x:v>
+        <x:v>小伙白叶遭遇老板跑路，半年工资付诸东流，意外被铁炒勺砸中觉醒超级餐饮系统。大雪封路堵车途中完成首份任务，靠着系统加持的厨艺，路边卖盒饭赚到第一桶金。回乡钻研秘制酱肉，赶集摆摊火爆出圈，还临危接手大型寿宴惊艳众人。过完新年，他怀揣梦想奔赴外地，准备开启属于自己的餐饮创业之路。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1455,13 +1455,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
-        <x:v>被身高掩盖的谎言</x:v>
+        <x:v>高考刚结束父母就不装了</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>09-15 08:18</x:v>
+        <x:v>09-15 07:00</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str"/>
       <x:c r="F10" s="11" t="str"/>
@@ -1472,19 +1472,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I10" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="J10" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K10" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="L10" s="11" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>千慕剧场</x:v>
       </x:c>
       <x:c r="M10" s="10" t="str">
-        <x:v>女孩林知晚回到命运转折的关键节点。她凭借智慧与勇气，敏锐察觉家中隐患，冷静引导家人、寻求帮助，用爱守护姐姐与全家。在共同努力下危机化解、正义伸张，一家人愈发珍视彼此，并且帮助到了更多有同样遭遇的人，最后迎来温暖安宁的幸福生活。</x:v>
+        <x:v>高考结束那天，林寻在考场外被亲生父母认回原来十八年的普通生活，是父母为磨砺他而设的一场成长课。重回豪门，他没有迷失，反而在桥上遇见了那个让他心动的姑娘，南大冰山学姐苏清诗。从青涩的初次相遇，到演唱会上的合唱，再到大学校园里的朝夕相处，两个真诚的人慢慢靠近。曾经的求而不得终将释怀，双向奔赴的喜欢才最珍贵。褪去普通学生的身份，林寻只想以真心换真心。十八岁的夏天，最好的相遇，最甜的恋爱，才刚刚开始。</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1492,13 +1492,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C11" s="10" t="str">
-        <x:v>高考刚结束父母就不装了</x:v>
+        <x:v>被身高掩盖的谎言</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>09-15 07:00</x:v>
+        <x:v>09-15 08:18</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str"/>
       <x:c r="F11" s="11" t="str"/>
@@ -1509,19 +1509,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I11" s="11" t="n">
-        <x:v>173</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J11" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K11" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="L11" s="11" t="str">
-        <x:v>千慕剧场</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="M11" s="10" t="str">
-        <x:v>高考结束那天，林寻在考场外被亲生父母认回原来十八年的普通生活，是父母为磨砺他而设的一场成长课。重回豪门，他没有迷失，反而在桥上遇见了那个让他心动的姑娘，南大冰山学姐苏清诗。从青涩的初次相遇，到演唱会上的合唱，再到大学校园里的朝夕相处，两个真诚的人慢慢靠近。曾经的求而不得终将释怀，双向奔赴的喜欢才最珍贵。褪去普通学生的身份，林寻只想以真心换真心。十八岁的夏天，最好的相遇，最甜的恋爱，才刚刚开始。</x:v>
+        <x:v>女孩林知晚回到命运转折的关键节点。她凭借智慧与勇气，敏锐察觉家中隐患，冷静引导家人、寻求帮助，用爱守护姐姐与全家。在共同努力下危机化解、正义伸张，一家人愈发珍视彼此，并且帮助到了更多有同样遭遇的人，最后迎来温暖安宁的幸福生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1529,7 +1529,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>99</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
         <x:v>急诊摸鱼王2</x:v>
@@ -1566,7 +1566,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B13" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
         <x:v>傅少你夫人又在扮猪吃虎了</x:v>
@@ -1577,10 +1577,10 @@
       <x:c r="E13" s="11" t="str"/>
       <x:c r="F13" s="11" t="str"/>
       <x:c r="G13" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H13" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I13" s="11" t="str"/>
       <x:c r="J13" s="10" t="str">
@@ -1594,50 +1594,56 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="str">
-        <x:v>持续在榜</x:v>
+        <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B14" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
-        <x:v>患难门前见亲疏</x:v>
+        <x:v>重回雪崩泥石流，我不再犹豫</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>2026-09-16</x:v>
-      </x:c>
-      <x:c r="E14" s="11" t="str"/>
-      <x:c r="F14" s="11" t="str"/>
-      <x:c r="G14" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H14" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="I14" s="11" t="str"/>
+        <x:v>09-16 01:02</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="str">
+        <x:v>↑34位</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="str"/>
+      <x:c r="H14" s="11" t="str"/>
+      <x:c r="I14" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
       <x:c r="J14" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K14" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L14" s="11" t="str"/>
-      <x:c r="M14" s="10" t="str"/>
+        <x:v>年代怀旧</x:v>
+      </x:c>
+      <x:c r="L14" s="11" t="str">
+        <x:v>姜缘</x:v>
+      </x:c>
+      <x:c r="M14" s="10" t="str">
+        <x:v>前世，周清雨因犹豫错失逃生时机，眼睁睁看着全家被雪崩泥石流吞没。重生回灾难前三天，她当机立断卖掉五十头牦牛，囤积物资，带家人撤往高处。面对全村嘲讽和阻拦，她不再苦劝。直到雪山崩塌、洪流封村，昔日笑她疯癫的人纷纷求上门。这一次，她只救值得救的人！</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B15" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
-        <x:v>被身高掩盖的谎言</x:v>
+        <x:v>被诬陷诊出喜脉，重活一世我逆转前尘</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
-        <x:v>09-15 08:18</x:v>
+        <x:v>09-16 07:58</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F15" s="11" t="str">
         <x:v>↑32位</x:v>
@@ -1645,19 +1651,19 @@
       <x:c r="G15" s="11" t="str"/>
       <x:c r="H15" s="11" t="str"/>
       <x:c r="I15" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J15" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K15" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L15" s="11" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="M15" s="10" t="str">
-        <x:v>女孩林知晚回到命运转折的关键节点。她凭借智慧与勇气，敏锐察觉家中隐患，冷静引导家人、寻求帮助，用爱守护姐姐与全家。在共同努力下危机化解、正义伸张，一家人愈发珍视彼此，并且帮助到了更多有同样遭遇的人，最后迎来温暖安宁的幸福生活。</x:v>
+        <x:v>沈清瑶重生回到被“神医”姜辞诬陷喜脉那天。前世她因此身败名裂，被迫嫁给竹马萧景渊，后来才知这是两人为替姜辞上位设的局。这一世，她不再任人宰割，巧妙将诊脉丝线系在谢老夫人腕上，当众揭穿姜辞。萧景渊谎称“孩子是我的”，却被她揭发与姜辞的私情，两人丑态毕露。谢家震怒，姜辞被强嫁萧景渊，沈清瑶嫁入侯府。婚后她冷静布局，让萧景渊与姜辞内斗升级。最终姜辞伏法，沈清瑶挣脱前世枷锁。可重生真能让她彻底自由吗？</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1665,38 +1671,44 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C16" s="10" t="str">
-        <x:v>一盒印泥引发的全局封锁</x:v>
+        <x:v>我都元婴期了，你跟我说开学</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>09-16 00:10</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F16" s="11" t="str">
-        <x:v>↑25位</x:v>
+        <x:v>↑29位</x:v>
       </x:c>
       <x:c r="G16" s="11" t="str"/>
       <x:c r="H16" s="11" t="str"/>
-      <x:c r="I16" s="11" t="str"/>
+      <x:c r="I16" s="11" t="n">
+        <x:v>475</x:v>
+      </x:c>
       <x:c r="J16" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K16" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L16" s="11" t="str"/>
-      <x:c r="M16" s="10" t="str"/>
+      <x:c r="L16" s="11" t="str">
+        <x:v>梦启剧场</x:v>
+      </x:c>
+      <x:c r="M16" s="10" t="str">
+        <x:v>修士宁尘遭遇偷袭，身负重伤从修真界回到现代。时间只流逝一个暑假，他被迫入读青州大学，借居在乔姨家中，与傲娇少女许舒颜同住。一边伪装普通学生，一边寻找修复元神伤势的资源，接连化解校园、市井与古武圈子的各类风波，开启充满反差的现代生活。</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C17" s="10" t="str">
         <x:v>高考刚结束父母就不装了</x:v>
@@ -1705,10 +1717,10 @@
         <x:v>09-15 07:00</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F17" s="11" t="str">
-        <x:v>↑14位</x:v>
+        <x:v>↑22位</x:v>
       </x:c>
       <x:c r="G17" s="11" t="str"/>
       <x:c r="H17" s="11" t="str"/>
@@ -1733,36 +1745,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C18" s="10" t="str">
-        <x:v>我都元婴期了，你跟我说开学</x:v>
+        <x:v>我在工地卖盒饭带火一座城</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>09-16 00:10</x:v>
+        <x:v>09-14 14:52</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F18" s="11" t="str">
-        <x:v>↑13位</x:v>
+        <x:v>↑20位</x:v>
       </x:c>
       <x:c r="G18" s="11" t="str"/>
       <x:c r="H18" s="11" t="str"/>
       <x:c r="I18" s="11" t="n">
-        <x:v>475</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="J18" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K18" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="L18" s="11" t="str">
-        <x:v>梦启剧场</x:v>
+        <x:v>左手良画</x:v>
       </x:c>
       <x:c r="M18" s="10" t="str">
-        <x:v>修士宁尘遭遇偷袭，身负重伤从修真界回到现代。时间只流逝一个暑假，他被迫入读青州大学，借居在乔姨家中，与傲娇少女许舒颜同住。一边伪装普通学生，一边寻找修复元神伤势的资源，接连化解校园、市井与古武圈子的各类风波，开启充满反差的现代生活。</x:v>
+        <x:v>小伙白叶遭遇老板跑路，半年工资付诸东流，意外被铁炒勺砸中觉醒超级餐饮系统。大雪封路堵车途中完成首份任务，靠着系统加持的厨艺，路边卖盒饭赚到第一桶金。回乡钻研秘制酱肉，赶集摆摊火爆出圈，还临危接手大型寿宴惊艳众人。过完新年，他怀揣梦想奔赴外地，准备开启属于自己的餐饮创业之路。</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1770,36 +1782,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C19" s="10" t="str">
-        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
+        <x:v>被身高掩盖的谎言</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
-        <x:v>09-15 08:30</x:v>
+        <x:v>09-15 08:18</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
-        <x:v>34</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F19" s="11" t="str">
-        <x:v>↑9位</x:v>
+        <x:v>↑15位</x:v>
       </x:c>
       <x:c r="G19" s="11" t="str"/>
       <x:c r="H19" s="11" t="str"/>
       <x:c r="I19" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J19" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K19" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="L19" s="11" t="str">
-        <x:v>琥珀漫剧</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="M19" s="10" t="str">
-        <x:v>海鲜市场老手陈放，因一个两块钱的冰袋被十二年合伙人当众算旧账，心寒清账，净身出户。他没有抱怨，也没有以牙还牙，而是加入冷清档口“梅姐水产”，从零开始。他坚持明码标价、沥水称重、死活分卖、批次可查，宁可少接单，也不混货、不凑数、不赚亏心钱。面对低价抢客、恶意破坏、临时缺货等风波，他与叶梅靠诚信、规矩和彼此信任，一步步赢得客户与连锁企业的认可。</x:v>
+        <x:v>女孩林知晚回到命运转折的关键节点。她凭借智慧与勇气，敏锐察觉家中隐患，冷静引导家人、寻求帮助，用爱守护姐姐与全家。在共同努力下危机化解、正义伸张，一家人愈发珍视彼此，并且帮助到了更多有同样遭遇的人，最后迎来温暖安宁的幸福生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1807,36 +1819,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C20" s="10" t="str">
-        <x:v>我在工地卖盒饭带火一座城</x:v>
+        <x:v>嫡姐日日闹换夫，圣旨赐下后她悔疯了</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>09-14 14:52</x:v>
+        <x:v>09-16 08:00</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F20" s="11" t="str">
-        <x:v>↑6位</x:v>
+        <x:v>↑9位</x:v>
       </x:c>
       <x:c r="G20" s="11" t="str"/>
       <x:c r="H20" s="11" t="str"/>
       <x:c r="I20" s="11" t="n">
-        <x:v>144</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J20" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K20" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>婚姻情感 / 现实反转</x:v>
       </x:c>
       <x:c r="L20" s="11" t="str">
-        <x:v>左手良画</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="M20" s="10" t="str">
-        <x:v>小伙白叶遭遇老板跑路，半年工资付诸东流，意外被铁炒勺砸中觉醒超级餐饮系统。大雪封路堵车途中完成首份任务，靠着系统加持的厨艺，路边卖盒饭赚到第一桶金。回乡钻研秘制酱肉，赶集摆摊火爆出圈，还临危接手大型寿宴惊艳众人。过完新年，他怀揣梦想奔赴外地，准备开启属于自己的餐饮创业之路。</x:v>
+        <x:v>沈家庶女沈照蘅自幼被嫡姐沈令仪欺压。嫡姐与状元顾砚舟定亲，争吵便扬言抢她未婚夫谢长晏。嫡姐竟跪求御前换婚，圣旨互换。状元当庭抗旨，全家逼她退让，她一句“臣女不敢抗旨”拒绝牺牲。嫡姐掌掴她、嫡母夺嫁妆、状元逼签屈辱契约被她焚毁，沈家灌哑药逼她自毁，皇后女官相救亮出生母嫁妆凭证。宫宴上嫡姐撒泼名声尽毁，皇后请旨暂缓赐婚，沈照蘅入宫担任伴读女官。从庶女到御前女官，她的命自己写。</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1844,36 +1856,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C21" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
+        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
-        <x:v>09-15 00:08</x:v>
+        <x:v>09-15 08:30</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
-        <x:v>31</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F21" s="11" t="str">
-        <x:v>↑5位</x:v>
+        <x:v>↑8位</x:v>
       </x:c>
       <x:c r="G21" s="11" t="str"/>
       <x:c r="H21" s="11" t="str"/>
       <x:c r="I21" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J21" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K21" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L21" s="11" t="str">
-        <x:v>桃子动漫剧场</x:v>
+        <x:v>琥珀漫剧</x:v>
       </x:c>
       <x:c r="M21" s="10" t="str">
-        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
+        <x:v>海鲜市场老手陈放，因一个两块钱的冰袋被十二年合伙人当众算旧账，心寒清账，净身出户。他没有抱怨，也没有以牙还牙，而是加入冷清档口“梅姐水产”，从零开始。他坚持明码标价、沥水称重、死活分卖、批次可查，宁可少接单，也不混货、不凑数、不赚亏心钱。面对低价抢客、恶意破坏、临时缺货等风波，他与叶梅靠诚信、规矩和彼此信任，一步步赢得客户与连锁企业的认可。</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1881,24 +1893,24 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C22" s="10" t="str">
-        <x:v>晚棠知归，七年终见你</x:v>
+        <x:v>急诊摸鱼王2</x:v>
       </x:c>
       <x:c r="D22" s="11" t="str">
-        <x:v>09-14 11:26</x:v>
+        <x:v>09-15 20:00</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F22" s="11" t="str">
-        <x:v>↑2位</x:v>
+        <x:v>↑8位</x:v>
       </x:c>
       <x:c r="G22" s="11" t="str"/>
       <x:c r="H22" s="11" t="str"/>
       <x:c r="I22" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="J22" s="10" t="str">
         <x:v>其他</x:v>
@@ -1907,10 +1919,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L22" s="11" t="str">
-        <x:v>喵琪琪追剧</x:v>
+        <x:v>阿部漫剧</x:v>
       </x:c>
       <x:c r="M22" s="10" t="str">
-        <x:v>七年前，夏晚棠为救深爱的陆知珩，付出了一切，却被误会成背叛，独自带着女儿生活。多年后，两人再次相遇，陆知珩才发现当年的真相，也终于明白她承受了怎样的苦难。面对迟来的爱与亏欠，夏晚棠没有停留在过去，而是重新找回自己，用专业和坚强开启新的人生。最终，两人在女儿的陪伴下解开心结，携手迎来属于他们的幸福。</x:v>
+        <x:v>大佬贺知舟伪装咸鱼住院医，在急诊科继续摸鱼。院内急救考核到来，贺知舟笔试满分，实操手法惊艳一众同事。普外、麻醉科主任从特殊手术技巧，怀疑他就是消失的国际传奇DrZ。宿敌沈长风的势力不断逼近，旧身份危机迫在眉睫，贺知舟一边抢救危重病患，一边隐藏自己的过往。</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1918,19 +1930,19 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C23" s="10" t="str">
-        <x:v>傅少你夫人又在扮猪吃虎了</x:v>
+        <x:v>一盒印泥引发的全局封锁</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F23" s="11" t="str">
-        <x:v>↑2位</x:v>
+        <x:v>↑7位</x:v>
       </x:c>
       <x:c r="G23" s="11" t="str"/>
       <x:c r="H23" s="11" t="str"/>
@@ -1939,7 +1951,7 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="K23" s="10" t="str">
-        <x:v>婚姻情感 / 美食治愈</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L23" s="11" t="str"/>
       <x:c r="M23" s="10" t="str"/>
@@ -1949,34 +1961,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C24" s="10" t="str">
-        <x:v>被诬陷诊出喜脉，重活一世我逆转前尘</x:v>
+        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
       </x:c>
       <x:c r="D24" s="11" t="str">
-        <x:v>09-16 07:58</x:v>
-      </x:c>
-      <x:c r="E24" s="11" t="str"/>
+        <x:v>09-15 08:00</x:v>
+      </x:c>
+      <x:c r="E24" s="11" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="F24" s="11" t="str">
-        <x:v>新上榜</x:v>
+        <x:v>↑5位</x:v>
       </x:c>
       <x:c r="G24" s="11" t="str"/>
       <x:c r="H24" s="11" t="str"/>
       <x:c r="I24" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J24" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K24" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="L24" s="11" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="M24" s="10" t="str">
-        <x:v>沈清瑶重生回到被“神医”姜辞诬陷喜脉那天。前世她因此身败名裂，被迫嫁给竹马萧景渊，后来才知这是两人为替姜辞上位设的局。这一世，她不再任人宰割，巧妙将诊脉丝线系在谢老夫人腕上，当众揭穿姜辞。萧景渊谎称“孩子是我的”，却被她揭发与姜辞的私情，两人丑态毕露。谢家震怒，姜辞被强嫁萧景渊，沈清瑶嫁入侯府。婚后她冷静布局，让萧景渊与姜辞内斗升级。最终姜辞伏法，沈清瑶挣脱前世枷锁。可重生真能让她彻底自由吗？</x:v>
+        <x:v>沈清韵嫁入靖王府三年，王爷冷落，侧妃得宠。王爷当众许诺，谁先诞下儿子，便请封世子。苏氏先怀孕，沈清韵却发现自己怀的是龙凤胎，她隐瞒消息，买通太医推迟产期，忍痛让苏氏先产子。王爷果然请封庶长子为世子，折子递入宗人府。受理之后，沈清韵才发动，生下龙凤胎。太后与皇上视为祥瑞，下旨赐嫡子承恩为靖王世子、嫡女承华为安乐郡主。王爷措手不及，苏氏地位一落千丈。而沈清韵知道，这只是第一步。</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1984,34 +1998,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C25" s="10" t="str">
-        <x:v>嫡姐日日闹换夫，圣旨赐下后她悔疯了</x:v>
+        <x:v>四个崽崽瞒不住了</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
-        <x:v>09-16 08:00</x:v>
-      </x:c>
-      <x:c r="E25" s="11" t="str"/>
+        <x:v>09-15 00:08</x:v>
+      </x:c>
+      <x:c r="E25" s="11" t="n">
+        <x:v>26</x:v>
+      </x:c>
       <x:c r="F25" s="11" t="str">
-        <x:v>新上榜</x:v>
+        <x:v>↑3位</x:v>
       </x:c>
       <x:c r="G25" s="11" t="str"/>
       <x:c r="H25" s="11" t="str"/>
       <x:c r="I25" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="J25" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K25" s="10" t="str">
-        <x:v>婚姻情感 / 现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L25" s="11" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>桃子动漫剧场</x:v>
       </x:c>
       <x:c r="M25" s="10" t="str">
-        <x:v>沈家庶女沈照蘅自幼被嫡姐沈令仪欺压。嫡姐与状元顾砚舟定亲，争吵便扬言抢她未婚夫谢长晏。嫡姐竟跪求御前换婚，圣旨互换。状元当庭抗旨，全家逼她退让，她一句“臣女不敢抗旨”拒绝牺牲。嫡姐掌掴她、嫡母夺嫁妆、状元逼签屈辱契约被她焚毁，沈家灌哑药逼她自毁，皇后女官相救亮出生母嫁妆凭证。宫宴上嫡姐撒泼名声尽毁，皇后请旨暂缓赐婚，沈照蘅入宫担任伴读女官。从庶女到御前女官，她的命自己写。</x:v>
+        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -2019,13 +2035,13 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B26" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C26" s="10" t="str">
-        <x:v>悍妻大房不好惹</x:v>
+        <x:v>说好九十天就回来，我不等了</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>09-16 06:00</x:v>
       </x:c>
       <x:c r="E26" s="11" t="str"/>
       <x:c r="F26" s="11" t="str">
@@ -2033,28 +2049,34 @@
       </x:c>
       <x:c r="G26" s="11" t="str"/>
       <x:c r="H26" s="11" t="str"/>
-      <x:c r="I26" s="11" t="str"/>
+      <x:c r="I26" s="11" t="n">
+        <x:v>66</x:v>
+      </x:c>
       <x:c r="J26" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K26" s="10" t="str">
-        <x:v>婚姻情感</x:v>
-      </x:c>
-      <x:c r="L26" s="11" t="str"/>
-      <x:c r="M26" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L26" s="11" t="str">
+        <x:v>小宁漫漫</x:v>
+      </x:c>
+      <x:c r="M26" s="10" t="str">
+        <x:v>周衡挣脱错位的旧感情，坚守原则，专注医疗事业，打磨救死扶伤的星桥心泵。他与叶宁彼此尊重，感情建立在坦诚与边界之上，不盲目牺牲自我，平等相伴走向未来。林夏历经挫折后幡然醒悟，承担自己犯下的过错，放下执念踏实努力，靠双手重新经营人生。故事告诉人不必困在原地等候错的人，真心不该沦为候补，每个人都可以告别过往，奔赴属于自己的前路</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B27" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C27" s="10" t="str">
-        <x:v>重回雪崩泥石流，我不再犹豫</x:v>
+        <x:v>养娃记：八零四合院生活日常</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
-        <x:v>09-16 01:02</x:v>
+        <x:v>09-15 01:11</x:v>
       </x:c>
       <x:c r="E27" s="11" t="str"/>
       <x:c r="F27" s="11" t="str">
@@ -2063,19 +2085,54 @@
       <x:c r="G27" s="11" t="str"/>
       <x:c r="H27" s="11" t="str"/>
       <x:c r="I27" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="J27" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K27" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>年代怀旧 / 萌宝治愈</x:v>
       </x:c>
       <x:c r="L27" s="11" t="str">
-        <x:v>姜缘</x:v>
+        <x:v>香菜薯片</x:v>
       </x:c>
       <x:c r="M27" s="10" t="str">
-        <x:v>前世，周清雨因犹豫错失逃生时机，眼睁睁看着全家被雪崩泥石流吞没。重生回灾难前三天，她当机立断卖掉五十头牦牛，囤积物资，带家人撤往高处。面对全村嘲讽和阻拦，她不再苦劝。直到雪山崩塌、洪流封村，昔日笑她疯癫的人纷纷求上门。这一次，她只救值得救的人！</x:v>
+        <x:v>儿女已经成家立业，送走公公婆婆后，正准备全国游的六十多岁老太太赵锦舒重生了。重回到刚进城几个月时，那时什么都不懂，乡下来的年轻小媳妇脸皮薄，抹不开面子，也自卑，哪怕男人能挣钱，面对有权有势的婆家人，也自觉低人一头，更怕出错，给男人丢脸，很长一段时间都不敢多说一句话，明里暗里娘三个受了不少委屈。回到年轻时，赵锦舒老黄瓜刷绿漆，不管外表如何，内里都是老姜疙瘩，装不来腼腆小媳妇。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B28" s="11" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C28" s="10" t="str">
+        <x:v>重生极品婆婆，带全家发家致富！</x:v>
+      </x:c>
+      <x:c r="D28" s="11" t="str">
+        <x:v>09-14 20:29</x:v>
+      </x:c>
+      <x:c r="E28" s="11" t="str"/>
+      <x:c r="F28" s="11" t="str">
+        <x:v>新上榜</x:v>
+      </x:c>
+      <x:c r="G28" s="11" t="str"/>
+      <x:c r="H28" s="11" t="str"/>
+      <x:c r="I28" s="11" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="J28" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K28" s="10" t="str">
+        <x:v>家庭伦理 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="L28" s="11" t="str">
+        <x:v>懒少爱我</x:v>
+      </x:c>
+      <x:c r="M28" s="10" t="str">
+        <x:v>寡妇傅兰秀前世一生吝啬守财，刻薄对待儿女儿媳，到头来钱财被贼人掠夺，落得个凄惨离世的下场。一朝重生，她回到悲剧尚未发生之时。痛定思痛，她彻底改掉抠门的性子，学着善待家里的晚辈。可日子并不太平，爱占便宜的亲戚总上门搅扰，家中两个儿媳也矛盾不断，家务是非接连找上门。傅兰秀靠着清醒的头脑，一边化解各类家庭纷争，一边寻找营生门路，努力扭转命运，拼尽全力守护一家人的安稳生活。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2121,7 +2178,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
         <x:v>傅少你夫人又在扮猪吃虎了</x:v>
@@ -2138,196 +2195,181 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>两不相欠</x:v>
+        <x:v>被诬陷诊出喜脉，重活一世我逆转前尘</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>当日新上榜</x:v>
+        <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>05-25 08:00</x:v>
+        <x:v>09-16 07:58</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F3" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="G3" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G3" s="10" t="str">
+        <x:v>芙浚动漫短剧</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>被诬陷诊出喜脉，重活一世我逆转前尘</x:v>
+        <x:v>我都元婴期了，你跟我说开学</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>09-16 07:58</x:v>
+        <x:v>09-16 00:10</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="F4" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G4" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>梦启剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>46</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>扮猪吃老虎村霸被我一锅端</x:v>
+        <x:v>嫡姐日日闹换夫，圣旨赐下后她悔疯了</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>当日新上榜</x:v>
+        <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>08-30 12:00</x:v>
+        <x:v>09-16 08:00</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F5" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G5" s="10" t="str">
-        <x:v>漫界剧场</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>我都元婴期了，你跟我说开学</x:v>
+        <x:v>重回雪崩泥石流，我不再犹豫</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>09-16 00:10</x:v>
+        <x:v>09-16 01:02</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
-        <x:v>475</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F6" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G6" s="10" t="str">
-        <x:v>梦启剧场</x:v>
+        <x:v>姜缘</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>嫡姐日日闹换夫，圣旨赐下后她悔疯了</x:v>
+        <x:v>悍妻大房不好惹</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>今日发布</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="str">
-        <x:v>09-16 08:00</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="n">
-        <x:v>65</x:v>
-      </x:c>
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="str"/>
+      <x:c r="E7" s="11" t="str"/>
       <x:c r="F7" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G7" s="10" t="str">
-        <x:v>心动漫剧场</x:v>
-      </x:c>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>重生小渔村：海边捡个俏媳妇儿</x:v>
+        <x:v>扮猪吃老虎村霸被我一锅端</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>当日新上榜</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>08-29 17:00</x:v>
+        <x:v>08-30 12:00</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
-        <x:v>149</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F8" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="G8" s="10" t="str">
-        <x:v>恰饭动画</x:v>
+        <x:v>漫界剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>悍妻大房不好惹</x:v>
+        <x:v>说好九十天就回来，我不等了</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>当日新上榜</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="str"/>
-      <x:c r="E9" s="11" t="str"/>
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="str">
+        <x:v>09-16 06:00</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="n">
+        <x:v>66</x:v>
+      </x:c>
       <x:c r="F9" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="G9" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G9" s="10" t="str">
+        <x:v>小宁漫漫</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>重回雪崩泥石流，我不再犹豫</x:v>
+        <x:v>重生小渔村：海边捡个俏媳妇儿</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>今日发布</x:v>
+        <x:v>当日新上榜</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>09-16 01:02</x:v>
+        <x:v>08-29 17:00</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="F10" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G10" s="10" t="str">
-        <x:v>姜缘</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="11" t="n">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="B11" s="10" t="str">
-        <x:v>患难门前见亲疏</x:v>
-      </x:c>
-      <x:c r="C11" s="11" t="str">
-        <x:v>当日新上榜</x:v>
-      </x:c>
-      <x:c r="D11" s="11" t="str"/>
-      <x:c r="E11" s="11" t="str"/>
-      <x:c r="F11" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="G11" s="10" t="str"/>
+        <x:v>恰饭动画</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2396,16 +2438,16 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
-        <x:v>穿书后我带萌宝上门认爹</x:v>
+        <x:v>征地我秒签跑路，全村笑我半年</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>09-07 19:18</x:v>
+        <x:v>09-10 11:30</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
         <x:v>7</x:v>
@@ -2414,10 +2456,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G2" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H2" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I2" s="10" t="str">
         <x:v>其他</x:v>
@@ -2425,21 +2467,21 @@
       <x:c r="J2" s="11" t="str"/>
       <x:c r="K2" s="11" t="str"/>
       <x:c r="L2" s="10" t="str">
-        <x:v>虾仁不自在</x:v>
+        <x:v>小六动漫</x:v>
       </x:c>
       <x:c r="M2" s="10" t="str">
-        <x:v>许知棠重生穿进书中，当即带着五岁儿子许小舟登门，将孩子送到亲生父亲——傅氏集团总裁傅临川面前，只想抽身退出剧情。幼儿园里儿子遭同学诬陷、老师偏心，她强势护崽，硬刚蛮横家长与失职老师。亲子鉴定尘埃落定，萌娃黏妈不黏爹，反倒让清冷总裁渐渐上心。</x:v>
+        <x:v>赵家湾迎来高速征地，村民受村长赵德厚鼓动抱团拒签，妄想抬价拿到四百五十万补偿。林远察觉当地岩溶地质暗藏线路改线风险，不顾全村嘲讽，果断签下312万补偿款，带父母搬离老家。后续高速果真改线，全村一分补偿落空。曾经嘲笑林远的村民陷入债务困境，赵德厚登门求助，林远守住底线，一家人握紧安稳生活，告诫众人抉择要靠自己。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>征地我秒签跑路，全村笑我半年</x:v>
+        <x:v>大坝边寻回的真千金</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>09-10 11:30</x:v>
+        <x:v>09-10 11:26</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
         <x:v>6</x:v>
@@ -2451,10 +2493,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G3" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H3" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
         <x:v>其他</x:v>
@@ -2462,24 +2504,24 @@
       <x:c r="J3" s="11" t="str"/>
       <x:c r="K3" s="11" t="str"/>
       <x:c r="L3" s="10" t="str">
-        <x:v>小六动漫</x:v>
+        <x:v>喵琪琪追剧</x:v>
       </x:c>
       <x:c r="M3" s="10" t="str">
-        <x:v>赵家湾迎来高速征地，村民受村长赵德厚鼓动抱团拒签，妄想抬价拿到四百五十万补偿。林远察觉当地岩溶地质暗藏线路改线风险，不顾全村嘲讽，果断签下312万补偿款，带父母搬离老家。后续高速果真改线，全村一分补偿落空。曾经嘲笑林远的村民陷入债务困境，赵德厚登门求助，林远守住底线，一家人握紧安稳生活，告诫众人抉择要靠自己。</x:v>
+        <x:v>大坝突发险情，农村女孩夏晚禾凭借熟悉的环境和过人的勇气，不顾危险救下被困的沈长洲。一次意外的救援，让两个陌生人的命运重新交织。随着调查深入，沈长洲发现这个善良坚韧的女孩，竟是自己失散二十年的亲生女儿。面对迟来的亲情和真假千金的风波，夏晚禾没有依靠身份改变人生，而是用智慧、担当和努力证明自己的价值。陆言川也在一次次并肩相处中，被她的真诚与坚强打动，陪她找回亲情，走向新的未来。</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>惊絮无声：傻女的绝杀</x:v>
+        <x:v>穿书后我带萌宝上门认爹</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>09-06 10:00</x:v>
+        <x:v>09-07 19:18</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
         <x:v>7</x:v>
@@ -2488,10 +2530,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G4" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H4" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="I4" s="10" t="str">
         <x:v>其他</x:v>
@@ -2499,24 +2541,24 @@
       <x:c r="J4" s="11" t="str"/>
       <x:c r="K4" s="11" t="str"/>
       <x:c r="L4" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>虾仁不自在</x:v>
       </x:c>
       <x:c r="M4" s="10" t="str">
-        <x:v>沈家人人都是天才，唯独小女儿沈惊絮是公认的傻子。没人知道，她不仅装傻多年，还带着前世金牌律师的记忆重生而来。本想闭嘴躺平一生，谁料内鬼勾结资本做空沈氏，一纸合同就要让全家净身出户、背上百亿债务。父亲落笔前，她终于按住协议“这字不能签！”绝地反杀的沈惊絮，一步步挫败了对沈家的围剿，也让全家人重新认识了自己。沈家也迎来了新生。</x:v>
+        <x:v>许知棠重生穿进书中，当即带着五岁儿子许小舟登门，将孩子送到亲生父亲——傅氏集团总裁傅临川面前，只想抽身退出剧情。幼儿园里儿子遭同学诬陷、老师偏心，她强势护崽，硬刚蛮横家长与失职老师。亲子鉴定尘埃落定，萌娃黏妈不黏爹，反倒让清冷总裁渐渐上心。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>大坝边寻回的真千金</x:v>
+        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>09-10 11:26</x:v>
+        <x:v>09-08 17:58</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
         <x:v>7</x:v>
@@ -2525,10 +2567,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G5" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H5" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="I5" s="10" t="str">
         <x:v>其他</x:v>
@@ -2536,24 +2578,24 @@
       <x:c r="J5" s="11" t="str"/>
       <x:c r="K5" s="11" t="str"/>
       <x:c r="L5" s="10" t="str">
-        <x:v>喵琪琪追剧</x:v>
+        <x:v>禾苗动画</x:v>
       </x:c>
       <x:c r="M5" s="10" t="str">
-        <x:v>大坝突发险情，农村女孩夏晚禾凭借熟悉的环境和过人的勇气，不顾危险救下被困的沈长洲。一次意外的救援，让两个陌生人的命运重新交织。随着调查深入，沈长洲发现这个善良坚韧的女孩，竟是自己失散二十年的亲生女儿。面对迟来的亲情和真假千金的风波，夏晚禾没有依靠身份改变人生，而是用智慧、担当和努力证明自己的价值。陆言川也在一次次并肩相处中，被她的真诚与坚强打动，陪她找回亲情，走向新的未来。</x:v>
+        <x:v>末世异能者沐小暖意外穿书，成为七个反派继子的恶毒后娘。原主辛劳养娃却遭流言中伤，最终含恨而终。沐小暖决心扭转命运，恩威并施管教孩子，凭末世身手进山打猎采药、种地赶集改善家计，更以百年老参为礼，为长子求得名儒霍政谚收为关门弟子。她护佑家人躲过恶人算计与亲戚夺产，建起新宅。七个孩子从怨恨抗拒到真心信赖，争着喊她娘，一家人携手改写命运，收获温暖亲情。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
+        <x:v>惊絮无声：傻女的绝杀</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>09-08 17:58</x:v>
+        <x:v>09-06 10:00</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
         <x:v>7</x:v>
@@ -2562,10 +2604,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G6" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H6" s="11" t="n">
-        <x:v>111</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
         <x:v>其他</x:v>
@@ -2573,15 +2615,15 @@
       <x:c r="J6" s="11" t="str"/>
       <x:c r="K6" s="11" t="str"/>
       <x:c r="L6" s="10" t="str">
-        <x:v>禾苗动画</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="M6" s="10" t="str">
-        <x:v>末世异能者沐小暖意外穿书，成为七个反派继子的恶毒后娘。原主辛劳养娃却遭流言中伤，最终含恨而终。沐小暖决心扭转命运，恩威并施管教孩子，凭末世身手进山打猎采药、种地赶集改善家计，更以百年老参为礼，为长子求得名儒霍政谚收为关门弟子。她护佑家人躲过恶人算计与亲戚夺产，建起新宅。七个孩子从怨恨抗拒到真心信赖，争着喊她娘，一家人携手改写命运，收获温暖亲情。</x:v>
+        <x:v>沈家人人都是天才，唯独小女儿沈惊絮是公认的傻子。没人知道，她不仅装傻多年，还带着前世金牌律师的记忆重生而来。本想闭嘴躺平一生，谁料内鬼勾结资本做空沈氏，一纸合同就要让全家净身出户、背上百亿债务。父亲落笔前，她终于按住协议“这字不能签！”绝地反杀的沈惊絮，一步步挫败了对沈家的围剿，也让全家人重新认识了自己。沈家也迎来了新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
         <x:v>抢个新娘来当后娘第一季</x:v>
@@ -2618,16 +2660,16 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>重生三天前，我用水泥封死地下室</x:v>
+        <x:v>一墙之隔，皆是人心</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>09-09 09:28</x:v>
+        <x:v>09-06 15:48</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
         <x:v>7</x:v>
@@ -2639,7 +2681,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H8" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
         <x:v>其他</x:v>
@@ -2647,21 +2689,21 @@
       <x:c r="J8" s="11" t="str"/>
       <x:c r="K8" s="11" t="str"/>
       <x:c r="L8" s="10" t="str">
-        <x:v>忘忧剧场</x:v>
+        <x:v>在下长生</x:v>
       </x:c>
       <x:c r="M8" s="10" t="str">
-        <x:v>阮清重生回被保姆王妈一家害死的三天前，前世她因心善引狼入室，保姆全家蜗居别墅地下室偷窃投毒，最终惨遭勒死。重生后她假装不知，趁王妈外出时用水泥将地下室彻底封死。警方破墙后，五具尸体令真相大白，王妈因盗窃、投毒被判十五年。阮清与父母团聚，恶人终得恶报，她重获新生。</x:v>
+        <x:v>妻子临产被车堵住出口，叶瑾抱着羊水破裂的她跑了三公里才到医院，母子平安。面对无理的车主，他没有以暴制暴，而是选择依法行事——在自家院内合法砌墙、种下高价值树苗，全程录像留证。车主回来后暴力砸墙、碾压树苗，最终被依法追究责任。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>离家十年，回来女儿被换了</x:v>
+        <x:v>重生三天前，我用水泥封死地下室</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>09-09 00:04</x:v>
+        <x:v>09-09 09:28</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
         <x:v>7</x:v>
@@ -2676,7 +2718,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H9" s="11" t="n">
-        <x:v>155</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str">
         <x:v>其他</x:v>
@@ -2684,24 +2726,24 @@
       <x:c r="J9" s="11" t="str"/>
       <x:c r="K9" s="11" t="str"/>
       <x:c r="L9" s="10" t="str">
-        <x:v>魔方影视（上剧版</x:v>
+        <x:v>忘忧剧场</x:v>
       </x:c>
       <x:c r="M9" s="10" t="str">
-        <x:v>程砚宁完成长期绝密任务归来，满心想要弥补亲情，却发现家中早已物是人非。身边亲近之人被私欲蒙蔽，制造重重骗局，试图侵占她的事业与财富。面对接连而来的算计与危机，她凭借过人的魄力与智慧步步拆解阴谋，联合正义力量搜集证据，厘清全部是非纠葛。在守护自身事业的同时，她放下过往伤痛，投身公益，完成自我和解，迎来属于自己的全新人生。</x:v>
+        <x:v>阮清重生回被保姆王妈一家害死的三天前，前世她因心善引狼入室，保姆全家蜗居别墅地下室偷窃投毒，最终惨遭勒死。重生后她假装不知，趁王妈外出时用水泥将地下室彻底封死。警方破墙后，五具尸体令真相大白，王妈因盗窃、投毒被判十五年。阮清与父母团聚，恶人终得恶报，她重获新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>一墙之隔，皆是人心</x:v>
+        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>09-06 15:48</x:v>
+        <x:v>09-08 11:00</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
         <x:v>7</x:v>
@@ -2713,7 +2755,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H10" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="I10" s="10" t="str">
         <x:v>其他</x:v>
@@ -2721,15 +2763,15 @@
       <x:c r="J10" s="11" t="str"/>
       <x:c r="K10" s="11" t="str"/>
       <x:c r="L10" s="10" t="str">
-        <x:v>在下长生</x:v>
+        <x:v>白桃剧场</x:v>
       </x:c>
       <x:c r="M10" s="10" t="str">
-        <x:v>妻子临产被车堵住出口，叶瑾抱着羊水破裂的她跑了三公里才到医院，母子平安。面对无理的车主，他没有以暴制暴，而是选择依法行事——在自家院内合法砌墙、种下高价值树苗，全程录像留证。车主回来后暴力砸墙、碾压树苗，最终被依法追究责任。</x:v>
+        <x:v>阿梨一觉睡了三百年，养大的五只小兽尽数离去。她带着五只旧饭碗、十二枚铜钱与一把锈柴刀下山寻兽。昔日的小家伙已成威震四方的妖祖，历经重重相遇与揭秘，阿梨知晓三百年封印的真相，携手五只妖祖，一同对抗祸世灭灵兽神。</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
         <x:v>不靠谱爸妈很靠谱</x:v>
@@ -2766,16 +2808,16 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
+        <x:v>离家十年，回来女儿被换了</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>09-08 11:00</x:v>
+        <x:v>09-09 00:04</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
         <x:v>7</x:v>
@@ -2787,7 +2829,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H12" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str">
         <x:v>其他</x:v>
@@ -2795,24 +2837,24 @@
       <x:c r="J12" s="11" t="str"/>
       <x:c r="K12" s="11" t="str"/>
       <x:c r="L12" s="10" t="str">
-        <x:v>白桃剧场</x:v>
+        <x:v>魔方影视（上剧版</x:v>
       </x:c>
       <x:c r="M12" s="10" t="str">
-        <x:v>阿梨一觉睡了三百年，养大的五只小兽尽数离去。她带着五只旧饭碗、十二枚铜钱与一把锈柴刀下山寻兽。昔日的小家伙已成威震四方的妖祖，历经重重相遇与揭秘，阿梨知晓三百年封印的真相，携手五只妖祖，一同对抗祸世灭灵兽神。</x:v>
+        <x:v>程砚宁完成长期绝密任务归来，满心想要弥补亲情，却发现家中早已物是人非。身边亲近之人被私欲蒙蔽，制造重重骗局，试图侵占她的事业与财富。面对接连而来的算计与危机，她凭借过人的魄力与智慧步步拆解阴谋，联合正义力量搜集证据，厘清全部是非纠葛。在守护自身事业的同时，她放下过往伤痛，投身公益，完成自我和解，迎来属于自己的全新人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>美颜系统开挂，大佬全跪下</x:v>
+        <x:v>重启人生，拒绝校花？</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>09-09 00:10</x:v>
+        <x:v>09-08 08:30</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
         <x:v>7</x:v>
@@ -2824,7 +2866,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H13" s="11" t="n">
-        <x:v>172</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="I13" s="10" t="str">
         <x:v>其他</x:v>
@@ -2832,21 +2874,21 @@
       <x:c r="J13" s="11" t="str"/>
       <x:c r="K13" s="11" t="str"/>
       <x:c r="L13" s="10" t="str">
-        <x:v>御儿</x:v>
+        <x:v>肆漫简</x:v>
       </x:c>
       <x:c r="M13" s="10" t="str">
-        <x:v>曾因外形饱受非议的米珂华丽转身，蜕变得耀眼又夺目。从前对她嗤之以鼻的蒋少开始频频在意，素来冷眼毒舌的陆总不知不觉深陷其中，连一向克己的商界大佬也为她打破原则。米珂凭智商与手腕周旋于众人之间，上演一场势均力敌的情感博弈。没有俗套的救赎，只有双向的拉扯。看一众高高在上的精英暗自较劲、步步沉沦，心甘情愿为她卸下防备。</x:v>
+        <x:v>白陌重生回到2004年高考夜，果断避开前世陷害自己的宾馆陷阱，救下被下药的校花江洛菡，彻底扭转人生走向。他不再执着于过往的情感执念，跳出卑微追爱的困局，转而关心恩师健康、规划学业与创业方向，结识志同道合的伙伴。凭借重生阅历清醒选择前路，把握青春重启人生，用行动改写原本遗憾的命运，活出全新成长轨迹。</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>迟来深情皆是刃</x:v>
+        <x:v>美颜系统开挂，大佬全跪下</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>09-09 10:00</x:v>
+        <x:v>09-09 00:10</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
         <x:v>7</x:v>
@@ -2858,10 +2900,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G14" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H14" s="11" t="n">
-        <x:v>184</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="I14" s="10" t="str">
         <x:v>其他</x:v>
@@ -2869,36 +2911,36 @@
       <x:c r="J14" s="11" t="str"/>
       <x:c r="K14" s="11" t="str"/>
       <x:c r="L14" s="10" t="str">
-        <x:v>展瓦-佩云看剧</x:v>
+        <x:v>御儿</x:v>
       </x:c>
       <x:c r="M14" s="10" t="str">
-        <x:v>天才芯片科研人姜莱，隐去光芒，在婚姻里默默付出四年，却遭遇丈夫沈荀的背叛与冷待。看清现实的她挣脱窒息的婚姻，撕下普通家庭主妇的伪装，重拾科研理想。面对丈夫、情敌的百般算计，她冷静反击。在自研芯重大项目竞标舞台上，姜莱展露真实实力，完成华丽逆袭，实现自我价值。过往伤痛化作成长力量，她告别糟糕的旧生活，向着事业与崭新的人生大步奔赴，迎来属于自己的光明未来。</x:v>
+        <x:v>曾因外形饱受非议的米珂华丽转身，蜕变得耀眼又夺目。从前对她嗤之以鼻的蒋少开始频频在意，素来冷眼毒舌的陆总不知不觉深陷其中，连一向克己的商界大佬也为她打破原则。米珂凭智商与手腕周旋于众人之间，上演一场势均力敌的情感博弈。没有俗套的救赎，只有双向的拉扯。看一众高高在上的精英暗自较劲、步步沉沦，心甘情愿为她卸下防备。</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>穿越60我有空间不愁吃喝</x:v>
+        <x:v>重生后我守住全村</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
-        <x:v>09-07 00:04</x:v>
+        <x:v>09-10 08:08</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F15" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G15" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H15" s="11" t="n">
-        <x:v>1000</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="I15" s="10" t="str">
         <x:v>其他</x:v>
@@ -2906,24 +2948,24 @@
       <x:c r="J15" s="11" t="str"/>
       <x:c r="K15" s="11" t="str"/>
       <x:c r="L15" s="10" t="str">
-        <x:v>夜珠AI剧场</x:v>
+        <x:v>金果漫剧</x:v>
       </x:c>
       <x:c r="M15" s="10" t="str">
-        <x:v>现代青年刘大壮意外穿越到60年代，成了同名同姓的16岁穷小子。原主因相亲被拒、家徒四壁，下河摸鱼时溺亡。大壮醒来后发现脑中多了一座九层宝塔空间——内有灵药田与灵泉潭水，作物两小时成熟、产量翻五倍。饥荒年代，别人啃树皮喝稀粥，他靠空间种出满仓土豆粮食，黑市换粮票钞票，让饿肚子的父母姐姐们吃上饱饭。从人人嘲笑的穷小子，到带着全家逆袭翻盘，且看他手握宝塔空间，在艰苦年代闯出一条吃喝不愁的逆袭</x:v>
+        <x:v>70年代冬，赵满仓在父亲离世后重回鼠灾前八天。面对家中骤变，他选择先护住亲人，带着前世经验迁入碾坊，储粮备药，筑墙防鼠，设点防疫。灾情来临时，他联合李杏儿，刘石头和乡亲稳住村庄，并用账册与规矩澄清父亲名誉。风雪过后，黎家沟建起防鼠坊，猫舍和净粮地窖，众人也在互助中迎来新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>三分钱的取舍</x:v>
+        <x:v>穿越60我有空间不愁吃喝</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>09-10 17:29</x:v>
+        <x:v>09-07 00:04</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
         <x:v>6</x:v>
@@ -2932,10 +2974,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G16" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H16" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str">
         <x:v>其他</x:v>
@@ -2943,15 +2985,15 @@
       <x:c r="J16" s="11" t="str"/>
       <x:c r="K16" s="11" t="str"/>
       <x:c r="L16" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>夜珠AI剧场</x:v>
       </x:c>
       <x:c r="M16" s="10" t="str">
-        <x:v>青石沟果农为省下代办三分钱，甩开中间商周成岳，直接对接收购商方洪生收桃。可脱离周成岳统筹调度后，摘桃、排单、装车乱象丛生，桃子积压损耗。周成岳转身接手偏远的十里湾桃园，凭口碑站稳脚跟。经历一季波折，青石沟众人幡然醒悟，重新读懂代办的价值。</x:v>
+        <x:v>现代青年刘大壮意外穿越到60年代，成了同名同姓的16岁穷小子。原主因相亲被拒、家徒四壁，下河摸鱼时溺亡。大壮醒来后发现脑中多了一座九层宝塔空间——内有灵药田与灵泉潭水，作物两小时成熟、产量翻五倍。饥荒年代，别人啃树皮喝稀粥，他靠空间种出满仓土豆粮食，黑市换粮票钞票，让饿肚子的父母姐姐们吃上饱饭。从人人嘲笑的穷小子，到带着全家逆袭翻盘，且看他手握宝塔空间，在艰苦年代闯出一条吃喝不愁的逆袭</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
         <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
@@ -2988,13 +3030,13 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>重生一世，我不再痴恋竹马</x:v>
+        <x:v>三分钱的取舍</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>09-10 10:00</x:v>
+        <x:v>09-10 17:29</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
         <x:v>6</x:v>
@@ -3006,10 +3048,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G18" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H18" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I18" s="10" t="str">
         <x:v>其他</x:v>
@@ -3017,36 +3059,36 @@
       <x:c r="J18" s="11" t="str"/>
       <x:c r="K18" s="11" t="str"/>
       <x:c r="L18" s="10" t="str">
-        <x:v>锦书映年华</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="M18" s="10" t="str">
-        <x:v>承平公主前世错恋齐远安，受尽磋磨含恨落幕。一朝重生，恰逢圣旨赐婚，齐远安却当众恳请解除婚约，求取太后义孙女傅明珠。她坦然放手，主动成全二人，看着他们得偿所愿。宁国侯夫人动用旧物强求赐婚，她巧妙改换婚事，选择边关归来、品性刚正的齐远舟。婚后她聪慧通透，看清傅明珠与齐远安的本性，冷眼旁观二人矛盾丛生。历经风波，她与齐远舟彼此扶持，挣脱过往伤痛，收获属于自己安稳坦荡的人生。</x:v>
+        <x:v>青石沟果农为省下代办三分钱，甩开中间商周成岳，直接对接收购商方洪生收桃。可脱离周成岳统筹调度后，摘桃、排单、装车乱象丛生，桃子积压损耗。周成岳转身接手偏远的十里湾桃园，凭口碑站稳脚跟。经历一季波折，青石沟众人幡然醒悟，重新读懂代办的价值。</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>七套房产，换来一纸调令</x:v>
+        <x:v>重生一世，我不再痴恋竹马</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>09-12 08:18</x:v>
+        <x:v>09-10 10:00</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G19" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H19" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str">
         <x:v>其他</x:v>
@@ -3054,96 +3096,83 @@
       <x:c r="J19" s="11" t="str"/>
       <x:c r="K19" s="11" t="str"/>
       <x:c r="L19" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>锦书映年华</x:v>
       </x:c>
       <x:c r="M19" s="10" t="str">
-        <x:v>公婆将七套房产全数赠予小叔子，长子陈峰看似顺从鼓掌，实则暗中申请援疆调令。面对父母偏心和弟媳挑衅，陈峰携妻林晚隐忍筹备。最终在家庭会议上，他出示双人调令宣告远赴新疆，打破原生家庭剥削链条。经历异地磨砺与除夕和解，一家人终在理解中重建亲情边界，实现各自独立与成长。</x:v>
+        <x:v>承平公主前世错恋齐远安，受尽磋磨含恨落幕。一朝重生，恰逢圣旨赐婚，齐远安却当众恳请解除婚约，求取太后义孙女傅明珠。她坦然放手，主动成全二人，看着他们得偿所愿。宁国侯夫人动用旧物强求赐婚，她巧妙改换婚事，选择边关归来、品性刚正的齐远舟。婚后她聪慧通透，看清傅明珠与齐远安的本性，冷眼旁观二人矛盾丛生。历经风波，她与齐远舟彼此扶持，挣脱过往伤痛，收获属于自己安稳坦荡的人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="n">
-        <x:v>29</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>今天开始做裴总</x:v>
+        <x:v>一张废票毁了她</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>09-12 19:48</x:v>
+        <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F20" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G20" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H20" s="11" t="n">
-        <x:v>100</x:v>
-      </x:c>
+      <x:c r="H20" s="11" t="str"/>
       <x:c r="I20" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J20" s="11" t="str"/>
       <x:c r="K20" s="11" t="str"/>
-      <x:c r="L20" s="10" t="str">
-        <x:v>严墨墨</x:v>
-      </x:c>
-      <x:c r="M20" s="10" t="str">
-        <x:v>裴野低调蛰伏三年，甘愿扮作普通员工，在公司默默沉淀，面对职场非议、旁人轻视从未辩解。年会之上，他惨遭当众开除，相伴多年的婚姻也走向终点，跌入人生低谷。褪去伪装，他不再刻意隐忍，解锁真实身份，告别敷衍度日的过往。一路轻松逆袭，打破所有人的偏见，凭自身实力惊艳全场，开启属于自己的全新人生。</x:v>
-      </x:c>
+      <x:c r="L20" s="10" t="str"/>
+      <x:c r="M20" s="10" t="str"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>青牛引泉来</x:v>
+        <x:v>回到零四年进军彩铃界</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>09-11 15:20</x:v>
+        <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G21" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H21" s="11" t="n">
-        <x:v>79</x:v>
-      </x:c>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="H21" s="11" t="str"/>
       <x:c r="I21" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J21" s="11" t="str"/>
       <x:c r="K21" s="11" t="str"/>
-      <x:c r="L21" s="10" t="str">
-        <x:v>车仔漫</x:v>
-      </x:c>
-      <x:c r="M21" s="10" t="str">
-        <x:v>大旱之年，贫苦庄稼汉石满仓为宽慰盼他成家的母亲，扎了个稻草媳妇，谁料草人竟化作姑娘阿禾。原来阿禾是有灵性的青牛，十年前大旱濒死时被石满仓用豆秸和水救下，此番借稻草人身躯前来报恩。
-阿禾感知到村井即将枯竭，带领众人找到被封堵的牛眠岭古泉。靠卖自家井水牟利的马有财因利益受损，百般阻挠，甚至污染泉水、堵塞闸口。</x:v>
-      </x:c>
+      <x:c r="L21" s="10" t="str"/>
+      <x:c r="M21" s="10" t="str"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="n">
-        <x:v>44</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>锦书迟</x:v>
+        <x:v>七套房产，换来一纸调令</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>09-12 07:30</x:v>
+        <x:v>09-12 08:18</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
         <x:v>4</x:v>
@@ -3155,10 +3184,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G22" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H22" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str">
         <x:v>其他</x:v>
@@ -3166,24 +3195,24 @@
       <x:c r="J22" s="11" t="str"/>
       <x:c r="K22" s="11" t="str"/>
       <x:c r="L22" s="10" t="str">
-        <x:v>咩咩漫文</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="M22" s="10" t="str">
-        <x:v>三年前，沈昭昭嫁与永宁侯谢凛，新婚燕尔他便远赴边关。她苦等家书，却不知双向书信早被人暗中截留。她终于心冷离开侯府。三年后，她带着孩子在市井支摊卖画立足，他却循着蛛丝马迹寻来，真相层层揭开，原来他从未负她。</x:v>
+        <x:v>公婆将七套房产全数赠予小叔子，长子陈峰看似顺从鼓掌，实则暗中申请援疆调令。面对父母偏心和弟媳挑衅，陈峰携妻林晚隐忍筹备。最终在家庭会议上，他出示双人调令宣告远赴新疆，打破原生家庭剥削链条。经历异地磨砺与除夕和解，一家人终在理解中重建亲情边界，实现各自独立与成长。</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>装傻下山</x:v>
+        <x:v>青牛引泉来</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>2026-09-12</x:v>
+        <x:v>09-11 15:20</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
         <x:v>5</x:v>
@@ -3192,26 +3221,33 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G23" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H23" s="11" t="str"/>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H23" s="11" t="n">
+        <x:v>79</x:v>
+      </x:c>
       <x:c r="I23" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J23" s="11" t="str"/>
       <x:c r="K23" s="11" t="str"/>
-      <x:c r="L23" s="10" t="str"/>
-      <x:c r="M23" s="10" t="str"/>
+      <x:c r="L23" s="10" t="str">
+        <x:v>车仔漫</x:v>
+      </x:c>
+      <x:c r="M23" s="10" t="str">
+        <x:v>大旱之年，贫苦庄稼汉石满仓为宽慰盼他成家的母亲，扎了个稻草媳妇，谁料草人竟化作姑娘阿禾。原来阿禾是有灵性的青牛，十年前大旱濒死时被石满仓用豆秸和水救下，此番借稻草人身躯前来报恩。
+阿禾感知到村井即将枯竭，带领众人找到被封堵的牛眠岭古泉。靠卖自家井水牟利的马有财因利益受损，百般阻挠，甚至污染泉水、堵塞闸口。</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>泰城错嫁</x:v>
+        <x:v>锦书迟</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>09-12 21:10</x:v>
+        <x:v>09-12 07:30</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
         <x:v>4</x:v>
@@ -3223,10 +3259,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G24" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H24" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I24" s="10" t="str">
         <x:v>其他</x:v>
@@ -3234,21 +3270,21 @@
       <x:c r="J24" s="11" t="str"/>
       <x:c r="K24" s="11" t="str"/>
       <x:c r="L24" s="10" t="str">
-        <x:v>夜草剧场</x:v>
+        <x:v>咩咩漫文</x:v>
       </x:c>
       <x:c r="M24" s="10" t="str">
-        <x:v>二十世纪三十年代泰国，两姐妹姐妹同日嫁人，丑妹珠珠嫁帅气宋帕，美姐南佩却配憨汉啊光。迎亲途中大象突然发情，两对新人错上婚车、错入洞房。泼辣珠珠遇上憨厚啊光，闹洞房、斗婆婆，从互殴到相守；温柔南佩遇上冷脸宋帕，假装吵架赶走宾客，从陌生到动心。两对夫妻先后离婚，珠珠与啊光携手生子，南佩闯荡成舞台名角，与宋帕久别重逢。错的人成了对的人，两对冤家，各得圆满。</x:v>
+        <x:v>三年前，沈昭昭嫁与永宁侯谢凛，新婚燕尔他便远赴边关。她苦等家书，却不知双向书信早被人暗中截留。她终于心冷离开侯府。三年后，她带着孩子在市井支摊卖画立足，他却循着蛛丝马迹寻来，真相层层揭开，原来他从未负她。</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>重生山火前，我舍祖宅护全家</x:v>
+        <x:v>泰城错嫁</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>09-12 16:06</x:v>
+        <x:v>09-12 21:10</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
         <x:v>4</x:v>
@@ -3260,10 +3296,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G25" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H25" s="11" t="n">
-        <x:v>89</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str">
         <x:v>其他</x:v>
@@ -3271,21 +3307,21 @@
       <x:c r="J25" s="11" t="str"/>
       <x:c r="K25" s="11" t="str"/>
       <x:c r="L25" s="10" t="str">
-        <x:v>千鹤动漫</x:v>
+        <x:v>夜草剧场</x:v>
       </x:c>
       <x:c r="M25" s="10" t="str">
-        <x:v>顾长河带着前世山火中痛失全家的记忆重生归来，得知三日后西岭大火将再次席卷村庄，他不顾众人质疑，卖掉祖宅，带着妻子母亲和儿子搬上白石坡，储水备粮清出防火带，只为改写一家人的命运，当烈火真正逼近，所有人终于明白，他舍掉的只是房子，拼命守住的才是真正的家。</x:v>
+        <x:v>二十世纪三十年代泰国，两姐妹姐妹同日嫁人，丑妹珠珠嫁帅气宋帕，美姐南佩却配憨汉啊光。迎亲途中大象突然发情，两对新人错上婚车、错入洞房。泼辣珠珠遇上憨厚啊光，闹洞房、斗婆婆，从互殴到相守；温柔南佩遇上冷脸宋帕，假装吵架赶走宾客，从陌生到动心。两对夫妻先后离婚，珠珠与啊光携手生子，南佩闯荡成舞台名角，与宋帕久别重逢。错的人成了对的人，两对冤家，各得圆满。</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>我送弟弟上青云</x:v>
+        <x:v>重生山火前，我舍祖宅护全家</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
-        <x:v>09-12 09:52</x:v>
+        <x:v>09-12 16:06</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
         <x:v>4</x:v>
@@ -3297,10 +3333,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G26" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H26" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="I26" s="10" t="str">
         <x:v>其他</x:v>
@@ -3308,24 +3344,24 @@
       <x:c r="J26" s="11" t="str"/>
       <x:c r="K26" s="11" t="str"/>
       <x:c r="L26" s="10" t="str">
-        <x:v>落云</x:v>
+        <x:v>千鹤动漫</x:v>
       </x:c>
       <x:c r="M26" s="10" t="str">
-        <x:v>宋远回乡发现弟弟宋临被父亲剥夺上学权利，只能干农活。他毅然带走弟弟，用微薄工资供他读书。宋临考上名校建筑系，毕业后成为身价过亿的设计师。他用第一桶金给哥哥买房，报答当年恩情。面对迟来求和的父亲，宋临完成了心灵的真正和解。这是一个关于“长兄如父、手足情深”的故事，诠释了扶助与感恩的力量。</x:v>
+        <x:v>顾长河带着前世山火中痛失全家的记忆重生归来，得知三日后西岭大火将再次席卷村庄，他不顾众人质疑，卖掉祖宅，带着妻子母亲和儿子搬上白石坡，储水备粮清出防火带，只为改写一家人的命运，当烈火真正逼近，所有人终于明白，他舍掉的只是房子，拼命守住的才是真正的家。</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>重生1985年，赶海我有系统</x:v>
+        <x:v>我送弟弟上青云</x:v>
       </x:c>
       <x:c r="C27" s="11" t="str">
-        <x:v>09-11 07:00</x:v>
+        <x:v>09-12 09:52</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
         <x:v>5</x:v>
@@ -3334,10 +3370,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G27" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H27" s="11" t="n">
-        <x:v>132</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I27" s="10" t="str">
         <x:v>其他</x:v>
@@ -3345,24 +3381,24 @@
       <x:c r="J27" s="11" t="str"/>
       <x:c r="K27" s="11" t="str"/>
       <x:c r="L27" s="10" t="str">
-        <x:v>依语动漫</x:v>
+        <x:v>落云</x:v>
       </x:c>
       <x:c r="M27" s="10" t="str">
-        <x:v>八十年代小渔村，林舟出钱出力帮家里盖起红砖新房，落成之日却遭到父母兄长算计，新房被夺走，自己只分得被搬空的破旧老屋。带着前世被家人压榨到老的遗憾，重活一世的林舟不再愚孝，请来村长当众分家切割亲缘。绝境之中，他意外激活渔业情报系统，可以接收大海给出的渔获线索。他借得工具赶海，捞获珍贵大石斑鱼赚取第一笔启动资金，又约上好友李二狗大雾天冒险出海，依靠系统指引追逐鱼群。</x:v>
+        <x:v>宋远回乡发现弟弟宋临被父亲剥夺上学权利，只能干农活。他毅然带走弟弟，用微薄工资供他读书。宋临考上名校建筑系，毕业后成为身价过亿的设计师。他用第一桶金给哥哥买房，报答当年恩情。面对迟来求和的父亲，宋临完成了心灵的真正和解。这是一个关于“长兄如父、手足情深”的故事，诠释了扶助与感恩的力量。</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="11" t="n">
-        <x:v>86</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>敢抢我的车位</x:v>
+        <x:v>今天开始做裴总</x:v>
       </x:c>
       <x:c r="C28" s="11" t="str">
-        <x:v>09-11 18:00</x:v>
+        <x:v>09-12 19:48</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
         <x:v>5</x:v>
@@ -3371,10 +3407,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G28" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H28" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I28" s="10" t="str">
         <x:v>其他</x:v>
@@ -3382,24 +3418,24 @@
       <x:c r="J28" s="11" t="str"/>
       <x:c r="K28" s="11" t="str"/>
       <x:c r="L28" s="10" t="str">
-        <x:v>石爷剧场</x:v>
+        <x:v>严墨墨</x:v>
       </x:c>
       <x:c r="M28" s="10" t="str">
-        <x:v>蒋依依低调返乡履行婚约，却在王氏集团门口因停车问题，与柳如烟和未婚夫王霸产生误会。随着双方接触加深，婚约背后的分歧也逐渐显现。面对王霸前后不同的态度，蒋依依选择坚持自己的原则，果断结束这段并不合适的关系。与此同时，一场意外车辆纠纷也进入正式处理程序。原本普通的一次停车风波，让几个人重新认识彼此，也让蒋依依更加坚定了自己的选择。</x:v>
+        <x:v>裴野低调蛰伏三年，甘愿扮作普通员工，在公司默默沉淀，面对职场非议、旁人轻视从未辩解。年会之上，他惨遭当众开除，相伴多年的婚姻也走向终点，跌入人生低谷。褪去伪装，他不再刻意隐忍，解锁真实身份，告别敷衍度日的过往。一路轻松逆袭，打破所有人的偏见，凭自身实力惊艳全场，开启属于自己的全新人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="11" t="n">
-        <x:v>87</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>退婚从抢我车位开始</x:v>
+        <x:v>敢抢我的车位</x:v>
       </x:c>
       <x:c r="C29" s="11" t="str">
-        <x:v>2026-09-12</x:v>
+        <x:v>09-11 18:00</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
         <x:v>5</x:v>
@@ -3408,52 +3444,89 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G29" s="11" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H29" s="11" t="str"/>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H29" s="11" t="n">
+        <x:v>48</x:v>
+      </x:c>
       <x:c r="I29" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J29" s="11" t="str"/>
       <x:c r="K29" s="11" t="str"/>
-      <x:c r="L29" s="10" t="str"/>
-      <x:c r="M29" s="10" t="str"/>
+      <x:c r="L29" s="10" t="str">
+        <x:v>石爷剧场</x:v>
+      </x:c>
+      <x:c r="M29" s="10" t="str">
+        <x:v>蒋依依低调返乡履行婚约，却在王氏集团门口因停车问题，与柳如烟和未婚夫王霸产生误会。随着双方接触加深，婚约背后的分歧也逐渐显现。面对王霸前后不同的态度，蒋依依选择坚持自己的原则，果断结束这段并不合适的关系。与此同时，一场意外车辆纠纷也进入正式处理程序。原本普通的一次停车风波，让几个人重新认识彼此，也让蒋依依更加坚定了自己的选择。</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="11" t="n">
-        <x:v>98</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>我月薪八千，但公司是我的</x:v>
+        <x:v>退婚从抢我车位开始</x:v>
       </x:c>
       <x:c r="C30" s="11" t="str">
-        <x:v>09-09 20:47</x:v>
+        <x:v>2026-09-12</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E30" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F30" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G30" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E30" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F30" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G30" s="11" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="H30" s="11" t="n">
-        <x:v>97</x:v>
-      </x:c>
+      <x:c r="H30" s="11" t="str"/>
       <x:c r="I30" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J30" s="11" t="str"/>
       <x:c r="K30" s="11" t="str"/>
-      <x:c r="L30" s="10" t="str">
-        <x:v>阿宝剧场</x:v>
-      </x:c>
-      <x:c r="M30" s="10" t="str">
-        <x:v>北辰科技创始人陆景川为人低调，相亲时只坦言月薪八千，当即被相亲对象乔思雨嫌弃离场，还被对方在朋友圈造谣成“蹭咖啡捞男”。后续乔思雨应聘北辰科技、出席投资饭局，接连撞见陆景川，场面屡屡社死。陆景川却在常去的咖啡厅，因店员沈安然的仗义执言，窥见了比金钱更动人的真心。</x:v>
+      <x:c r="L30" s="10" t="str"/>
+      <x:c r="M30" s="10" t="str"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="11" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B31" s="10" t="str">
+        <x:v>重生1985年，赶海我有系统</x:v>
+      </x:c>
+      <x:c r="C31" s="11" t="str">
+        <x:v>09-11 07:00</x:v>
+      </x:c>
+      <x:c r="D31" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E31" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F31" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G31" s="11" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H31" s="11" t="n">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="I31" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="J31" s="11" t="str"/>
+      <x:c r="K31" s="11" t="str"/>
+      <x:c r="L31" s="10" t="str">
+        <x:v>依语动漫</x:v>
+      </x:c>
+      <x:c r="M31" s="10" t="str">
+        <x:v>八十年代小渔村，林舟出钱出力帮家里盖起红砖新房，落成之日却遭到父母兄长算计，新房被夺走，自己只分得被搬空的破旧老屋。带着前世被家人压榨到老的遗憾，重活一世的林舟不再愚孝，请来村长当众分家切割亲缘。绝境之中，他意外激活渔业情报系统，可以接收大海给出的渔获线索。他借得工具赶海，捞获珍贵大石斑鱼赚取第一笔启动资金，又约上好友李二狗大雾天冒险出海，依靠系统指引追逐鱼群。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3514,10 +3587,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F2" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3531,16 +3604,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
-        <x:v>5.7</x:v>
+        <x:v>6.2</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F3" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -3554,16 +3627,16 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>10.3</x:v>
+        <x:v>10.5</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F4" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3577,16 +3650,16 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>5.5</x:v>
+        <x:v>6.2</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F5" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>2026-09-15 23-11</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -3594,22 +3667,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>重生三天前，我用水泥封死地下室</x:v>
+        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
       </x:c>
       <x:c r="C6" s="11" t="n">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>7.3</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F6" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>2026-09-15 23-11</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3617,22 +3690,22 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
+        <x:v>搬进江景房，老公每晚对着鱼缸坐两小时</x:v>
       </x:c>
       <x:c r="C7" s="11" t="n">
         <x:v>24</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>7.2</x:v>
+        <x:v>6.7</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F7" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -3640,22 +3713,22 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
+        <x:v>重生三天前，我用水泥封死地下室</x:v>
       </x:c>
       <x:c r="C8" s="11" t="n">
         <x:v>24</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>12.7</x:v>
+        <x:v>12.2</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-15 23-11</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3663,22 +3736,22 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>搬进江景房，老公每晚对着鱼缸坐两小时</x:v>
+        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
       </x:c>
       <x:c r="C9" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>6.8</x:v>
+        <x:v>12.8</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -3686,22 +3759,22 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
+        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
       </x:c>
       <x:c r="C10" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>11.1</x:v>
+        <x:v>5.1</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F10" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>2026-09-15 21-11</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -3709,22 +3782,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
+        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
       </x:c>
       <x:c r="C11" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>5.2</x:v>
+        <x:v>11.3</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-15 21-11</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -3758,7 +3831,7 @@
         <x:v>15年青春苦守，未婚夫装穷归来</x:v>
       </x:c>
       <x:c r="C13" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
         <x:v>1.9</x:v>
@@ -3770,7 +3843,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G13" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -3778,22 +3851,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>破库房的秘密</x:v>
+        <x:v>重回82：我成山君契约万兽打猎宠妻</x:v>
       </x:c>
       <x:c r="C14" s="11" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>15.4</x:v>
+        <x:v>6.2</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G14" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -3801,22 +3874,22 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>重回82：我成山君契约万兽打猎宠妻</x:v>
+        <x:v>新厂旧账</x:v>
       </x:c>
       <x:c r="C15" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>6.2</x:v>
+        <x:v>8.9</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F15" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G15" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -3824,22 +3897,22 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>新厂旧账</x:v>
+        <x:v>破库房的秘密</x:v>
       </x:c>
       <x:c r="C16" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>8.8</x:v>
+        <x:v>15.6</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G16" s="11" t="str">
-        <x:v>2026-09-16 00-11</x:v>
+        <x:v>2026-09-16 02-11</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -3847,22 +3920,22 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>三分钱的取舍</x:v>
+        <x:v>穿书后我带萌宝上门认爹</x:v>
       </x:c>
       <x:c r="C17" s="11" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D17" s="11" t="n">
+        <x:v>14.9</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D17" s="11" t="n">
-        <x:v>13.9</x:v>
-      </x:c>
-      <x:c r="E17" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F17" s="11" t="n">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="G17" s="11" t="str">
-        <x:v>2026-09-15 18-11</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -3870,22 +3943,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>一墙之隔，皆是人心</x:v>
+        <x:v>三分钱的取舍</x:v>
       </x:c>
       <x:c r="C18" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>13.8</x:v>
+        <x:v>14.2</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G18" s="11" t="str">
-        <x:v>2026-09-15 20-11</x:v>
+        <x:v>2026-09-15 18-11</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -3893,22 +3966,22 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>穿书后我带萌宝上门认爹</x:v>
+        <x:v>一墙之隔，皆是人心</x:v>
       </x:c>
       <x:c r="C19" s="11" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>15.2</x:v>
+        <x:v>13.9</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G19" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-15 20-11</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -3939,22 +4012,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>离家十年，回来女儿被换了</x:v>
+        <x:v>晚棠知归，七年终见你</x:v>
       </x:c>
       <x:c r="C21" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>11.2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G21" s="11" t="str">
-        <x:v>2026-09-15 22-11</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -3962,22 +4035,22 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>晚棠知归，七年终见你</x:v>
+        <x:v>离家十年，回来女儿被换了</x:v>
       </x:c>
       <x:c r="C22" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>5.2</x:v>
+        <x:v>11.2</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G22" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-15 22-11</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -4008,22 +4081,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>泰城错嫁</x:v>
+        <x:v>我在工地卖盒饭带火一座城</x:v>
       </x:c>
       <x:c r="C24" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>14.6</x:v>
+        <x:v>12.9</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G24" s="11" t="str">
-        <x:v>2026-09-15 09-53</x:v>
+        <x:v>2026-09-15 21-11</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -4034,10 +4107,10 @@
         <x:v>不靠谱爸妈很靠谱</x:v>
       </x:c>
       <x:c r="C25" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>15.2</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
         <x:v>11</x:v>
@@ -4054,22 +4127,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>我在工地卖盒饭带火一座城</x:v>
+        <x:v>四个崽崽瞒不住了</x:v>
       </x:c>
       <x:c r="C26" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>12.9</x:v>
+        <x:v>16.1</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G26" s="11" t="str">
-        <x:v>2026-09-15 21-11</x:v>
+        <x:v>2026-09-15 10-11</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -4077,22 +4150,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
+        <x:v>泰城错嫁</x:v>
       </x:c>
       <x:c r="C27" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>16.1</x:v>
+        <x:v>15.9</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str">
-        <x:v>2026-09-15 10-11</x:v>
+        <x:v>2026-09-15 09-53</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -4123,22 +4196,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>退婚后我在七零赚钱养家致富</x:v>
+        <x:v>因为大黄遇见你</x:v>
       </x:c>
       <x:c r="C29" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>17.5</x:v>
+        <x:v>14.7</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str">
-        <x:v>2026-09-15 10-11</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -4146,22 +4219,22 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>今天开始做裴总</x:v>
+        <x:v>退婚后我在七零赚钱养家致富</x:v>
       </x:c>
       <x:c r="C30" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>9.6</x:v>
+        <x:v>17.5</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G30" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-15 10-11</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -4192,22 +4265,22 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="10" t="str">
-        <x:v>闪婚老公有点野</x:v>
+        <x:v>大坝边寻回的真千金</x:v>
       </x:c>
       <x:c r="C32" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D32" s="11" t="n">
-        <x:v>14.6</x:v>
+        <x:v>12.8</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G32" s="11" t="str">
-        <x:v>2026-09-15 06-54</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -4215,22 +4288,22 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="10" t="str">
-        <x:v>因为大黄遇见你</x:v>
+        <x:v>今天开始做裴总</x:v>
       </x:c>
       <x:c r="C33" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D33" s="11" t="n">
-        <x:v>13.8</x:v>
+        <x:v>7.5</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F33" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="G33" s="11" t="str">
-        <x:v>2026-09-15 23-11</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -4261,22 +4334,22 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="10" t="str">
-        <x:v>锦书迟</x:v>
+        <x:v>闪婚老公有点野</x:v>
       </x:c>
       <x:c r="C35" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D35" s="11" t="n">
-        <x:v>13.8</x:v>
+        <x:v>14.2</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F35" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G35" s="11" t="str">
-        <x:v>2026-09-15 02-44</x:v>
+        <x:v>2026-09-15 06-54</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -4284,22 +4357,22 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="10" t="str">
-        <x:v>大坝边寻回的真千金</x:v>
+        <x:v>穿越60我有空间不愁吃喝</x:v>
       </x:c>
       <x:c r="C36" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
-        <x:v>14.2</x:v>
+        <x:v>16.5</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G36" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -4307,22 +4380,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="10" t="str">
-        <x:v>辣媳进门，我给公婆撑腰</x:v>
+        <x:v>一针绣出自己的路</x:v>
       </x:c>
       <x:c r="C37" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D37" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G37" s="11" t="str">
-        <x:v>2026-09-15 06-08</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -4330,22 +4403,22 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="10" t="str">
-        <x:v>我的游戏好友现实里全是大佬</x:v>
+        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
       </x:c>
       <x:c r="C38" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D38" s="11" t="n">
-        <x:v>4.7</x:v>
+        <x:v>17.8</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F38" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G38" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -4353,22 +4426,22 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="10" t="str">
-        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
+        <x:v>辣媳进门，我给公婆撑腰</x:v>
       </x:c>
       <x:c r="C39" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D39" s="11" t="n">
-        <x:v>8.7</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G39" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-15 06-08</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -4376,22 +4449,22 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="10" t="str">
-        <x:v>攻略失败后我不装了</x:v>
+        <x:v>我的游戏好友现实里全是大佬</x:v>
       </x:c>
       <x:c r="C40" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D40" s="11" t="n">
-        <x:v>9.3</x:v>
+        <x:v>4.7</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G40" s="11" t="str">
-        <x:v>2026-09-16 01-11</x:v>
+        <x:v>2026-09-16 02-11</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -4399,22 +4472,22 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="10" t="str">
-        <x:v>红烛错缘，另寻良人</x:v>
+        <x:v>攻略失败后我不装了</x:v>
       </x:c>
       <x:c r="C41" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D41" s="11" t="n">
-        <x:v>10.7</x:v>
+        <x:v>9.3</x:v>
       </x:c>
       <x:c r="E41" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F41" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G41" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-16 01-11</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -4422,22 +4495,22 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B42" s="10" t="str">
-        <x:v>拂衣震九州</x:v>
+        <x:v>傅少你夫人又在扮猪吃虎了</x:v>
       </x:c>
       <x:c r="C42" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D42" s="11" t="n">
-        <x:v>10.3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E42" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F42" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G42" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -4445,22 +4518,22 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" s="10" t="str">
-        <x:v>山下是绝路，山上是生门</x:v>
+        <x:v>红烛错缘，另寻良人</x:v>
       </x:c>
       <x:c r="C43" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D43" s="11" t="n">
-        <x:v>14.3</x:v>
+        <x:v>10.7</x:v>
       </x:c>
       <x:c r="E43" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F43" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G43" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-16 02-11</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -4468,22 +4541,22 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="10" t="str">
-        <x:v>一针绣出自己的路</x:v>
+        <x:v>拂衣震九州</x:v>
       </x:c>
       <x:c r="C44" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D44" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>10.3</x:v>
       </x:c>
       <x:c r="E44" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F44" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G44" s="11" t="str">
-        <x:v>2026-09-15 21-11</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -4491,22 +4564,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="10" t="str">
-        <x:v>穿越60我有空间不愁吃喝</x:v>
+        <x:v>锦书迟</x:v>
       </x:c>
       <x:c r="C45" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D45" s="11" t="n">
+        <x:v>13.3</x:v>
+      </x:c>
+      <x:c r="E45" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F45" s="11" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="E45" s="11" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F45" s="11" t="n">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="G45" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-15 02-44</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -4514,22 +4587,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B46" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
+        <x:v>山下是绝路，山上是生门</x:v>
       </x:c>
       <x:c r="C46" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D46" s="11" t="n">
-        <x:v>17.7</x:v>
+        <x:v>14.3</x:v>
       </x:c>
       <x:c r="E46" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F46" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G46" s="11" t="str">
-        <x:v>2026-09-15 06-08</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -4537,22 +4610,22 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B47" s="10" t="str">
-        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
+        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
       </x:c>
       <x:c r="C47" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D47" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>17.7</x:v>
       </x:c>
       <x:c r="E47" s="11" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F47" s="11" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F47" s="11" t="n">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="G47" s="11" t="str">
-        <x:v>2026-09-15 20-11</x:v>
+        <x:v>2026-09-15 06-08</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -4560,19 +4633,19 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B48" s="10" t="str">
-        <x:v>我SSS级狂龙，出世即无敌</x:v>
+        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
       </x:c>
       <x:c r="C48" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D48" s="11" t="n">
-        <x:v>5.5</x:v>
+        <x:v>11.5</x:v>
       </x:c>
       <x:c r="E48" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F48" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G48" s="11" t="str">
         <x:v>2026-09-15 01-59</x:v>
@@ -4583,22 +4656,22 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B49" s="10" t="str">
-        <x:v>傅少你夫人又在扮猪吃虎了</x:v>
+        <x:v>我SSS级狂龙，出世即无敌</x:v>
       </x:c>
       <x:c r="C49" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D49" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>5.5</x:v>
       </x:c>
       <x:c r="E49" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F49" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G49" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-15 01-59</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -30681,10 +30754,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>975</x:v>
+        <x:v>978</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>53.8%</x:v>
+        <x:v>53.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -30741,7 +30814,7 @@
         <x:v>50-79集</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>711</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
         <x:v>42.9%</x:v>
@@ -30763,7 +30836,7 @@
         <x:v>100集以上</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>550</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
         <x:v>33.2%</x:v>
@@ -30790,7 +30863,7 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>803</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
         <x:v>44.3%</x:v>
@@ -30801,7 +30874,7 @@
         <x:v>婚姻/情感</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>321</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
         <x:v>17.7%</x:v>
@@ -30823,10 +30896,10 @@
         <x:v>年代怀旧/种田囤货</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>8.7%</x:v>
+        <x:v>8.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -30834,7 +30907,7 @@
         <x:v>家庭伦理/萌宝</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
         <x:v>8.7%</x:v>
@@ -31048,10 +31121,10 @@
         <x:v>上榜16次</x:v>
       </x:c>
       <x:c r="B41" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C41" s="11" t="str">
-        <x:v>0.2%</x:v>
+        <x:v>0.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -31070,10 +31143,10 @@
         <x:v>上榜14次</x:v>
       </x:c>
       <x:c r="B43" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C43" s="11" t="str">
-        <x:v>0.8%</x:v>
+        <x:v>0.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -31081,7 +31154,7 @@
         <x:v>上榜13次</x:v>
       </x:c>
       <x:c r="B44" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C44" s="11" t="str">
         <x:v>0.7%</x:v>
@@ -31092,10 +31165,10 @@
         <x:v>上榜12次</x:v>
       </x:c>
       <x:c r="B45" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C45" s="11" t="str">
-        <x:v>0.8%</x:v>
+        <x:v>0.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -31125,10 +31198,10 @@
         <x:v>上榜9次</x:v>
       </x:c>
       <x:c r="B48" s="11" t="n">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C48" s="11" t="str">
-        <x:v>1.6%</x:v>
+        <x:v>1.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -31136,10 +31209,10 @@
         <x:v>上榜8次</x:v>
       </x:c>
       <x:c r="B49" s="11" t="n">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C49" s="11" t="str">
-        <x:v>2.7%</x:v>
+        <x:v>2.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -31158,10 +31231,10 @@
         <x:v>上榜6次</x:v>
       </x:c>
       <x:c r="B51" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C51" s="11" t="str">
-        <x:v>3.3%</x:v>
+        <x:v>3.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -31169,10 +31242,10 @@
         <x:v>上榜5次</x:v>
       </x:c>
       <x:c r="B52" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C52" s="11" t="str">
-        <x:v>4.6%</x:v>
+        <x:v>4.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -31202,10 +31275,10 @@
         <x:v>上榜2次</x:v>
       </x:c>
       <x:c r="B55" s="11" t="n">
-        <x:v>334</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="C55" s="11" t="str">
-        <x:v>18.4%</x:v>
+        <x:v>18.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -31213,7 +31286,7 @@
         <x:v>上榜1次</x:v>
       </x:c>
       <x:c r="B56" s="11" t="n">
-        <x:v>800</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="C56" s="11" t="str">
         <x:v>44.2%</x:v>
@@ -31243,7 +31316,7 @@
         <x:v>1169</x:v>
       </x:c>
       <x:c r="C60" s="11" t="str">
-        <x:v>64.5%</x:v>
+        <x:v>64.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -31251,10 +31324,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B61" s="11" t="n">
-        <x:v>630</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="C61" s="11" t="str">
-        <x:v>34.8%</x:v>
+        <x:v>34.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="62">

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R15d0368836e048c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="Re0c5e268ef6b4415"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="R44e750db178b4114"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="R386edf451e7a45f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP20剧重点跟踪" sheetId="5" r:id="R3d19cdb7b5664506"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="6" r:id="R6eb5f83d072c4c5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="7" r:id="Ra5a71fec216d412c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="8" r:id="R83de17c4143d403f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="9" r:id="R95618ba5823e405b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R9a59b25b47b442a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="Re643a316e6d3408e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="R8a7b9ab87fe24a6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="R8c87b68f00d14185"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP20剧重点跟踪" sheetId="5" r:id="R2f3c9630b9a646f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="6" r:id="Rb2cd9e5f4031475d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="7" r:id="R8203d6050ced4693"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="8" r:id="R85f28c0a0d114bec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="9" r:id="Rf2d64ccacb2f48c0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -590,7 +590,7 @@
         <x:v>08-21 17:00</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E9" s="10" t="n">
         <x:v>50</x:v>
@@ -604,7 +604,7 @@
       <x:c r="H9" s="11" t="str"/>
       <x:c r="I9" s="11" t="str"/>
       <x:c r="J9" s="10" t="str">
-        <x:v>2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15</x:v>
+        <x:v>2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15、2026-09-16</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -644,27 +644,31 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>我将恩人一家捡回村</x:v>
+        <x:v>全世界都吃不下，只有我吃到服务器瘫痪</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>08-13 10:00</x:v>
+        <x:v>08-11 00:26</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E11" s="10" t="n">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F11" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G11" s="10" t="str">
-        <x:v>家庭伦理</x:v>
-      </x:c>
-      <x:c r="H11" s="11" t="str"/>
-      <x:c r="I11" s="11" t="str"/>
+        <x:v>美食治愈</x:v>
+      </x:c>
+      <x:c r="H11" s="11" t="n">
+        <x:v>883</x:v>
+      </x:c>
+      <x:c r="I11" s="11" t="str">
+        <x:v>0.95</x:v>
+      </x:c>
       <x:c r="J11" s="10" t="str">
-        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-03、2026-09-04、2026-09-05、2026-09-07、2026-09-08、2026-09-09、2026-09-11、2026-09-12、2026-09-13</x:v>
+        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-19、2026-08-20、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28、2026-09-03、2026-09-05、2026-09-06、2026-09-07、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-16</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -672,27 +676,27 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>我年终奖80w降到1w9，领导却慌了</x:v>
+        <x:v>我将恩人一家捡回村</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>08-24 08:00</x:v>
+        <x:v>08-13 10:00</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E12" s="10" t="n">
-        <x:v>77</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F12" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="G12" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="H12" s="11" t="str"/>
       <x:c r="I12" s="11" t="str"/>
       <x:c r="J12" s="10" t="str">
-        <x:v>2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-03、2026-09-04、2026-09-05、2026-09-07、2026-09-08、2026-09-09、2026-09-11、2026-09-12、2026-09-13</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -700,31 +704,27 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>全世界都吃不下，只有我吃到服务器瘫痪</x:v>
+        <x:v>我年终奖80w降到1w9，领导却慌了</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>08-11 00:26</x:v>
+        <x:v>08-24 08:00</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E13" s="10" t="n">
-        <x:v>50</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F13" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G13" s="10" t="str">
-        <x:v>美食治愈</x:v>
-      </x:c>
-      <x:c r="H13" s="11" t="n">
-        <x:v>883</x:v>
-      </x:c>
-      <x:c r="I13" s="11" t="str">
-        <x:v>0.95</x:v>
-      </x:c>
+        <x:v>都市职场</x:v>
+      </x:c>
+      <x:c r="H13" s="11" t="str"/>
+      <x:c r="I13" s="11" t="str"/>
       <x:c r="J13" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-19、2026-08-20、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28、2026-09-03、2026-09-05、2026-09-06、2026-09-07、2026-09-11、2026-09-12、2026-09-13、2026-09-14</x:v>
+        <x:v>2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -788,31 +788,27 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>重回八零，赶山狩猎养妻女</x:v>
+        <x:v>姜猎娶妻之知青良缘</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>07-17 18:30</x:v>
+        <x:v>08-17 09:38</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="E16" s="10" t="n">
-        <x:v>108</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F16" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G16" s="10" t="str">
-        <x:v>年代怀旧 / 种田囤货 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="H16" s="11" t="n">
-        <x:v>1708</x:v>
-      </x:c>
-      <x:c r="I16" s="11" t="str">
-        <x:v>0.96</x:v>
-      </x:c>
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="H16" s="11" t="str"/>
+      <x:c r="I16" s="11" t="str"/>
       <x:c r="J16" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-22、2026-08-23、2026-08-24、2026-08-29、2026-09-05、2026-09-06、2026-09-07、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-09、2026-09-11、2026-09-12、2026-09-13、2026-09-15、2026-09-16</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -820,27 +816,31 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>冷宫开席：陛下又来蹭饭了</x:v>
+        <x:v>重回八零，赶山狩猎养妻女</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>08-02 14:08</x:v>
+        <x:v>07-17 18:30</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E17" s="10" t="n">
-        <x:v>122</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F17" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="G17" s="10" t="str">
-        <x:v>古装宫廷 / 美食治愈</x:v>
-      </x:c>
-      <x:c r="H17" s="11" t="str"/>
-      <x:c r="I17" s="11" t="str"/>
+        <x:v>年代怀旧 / 种田囤货 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="H17" s="11" t="n">
+        <x:v>1708</x:v>
+      </x:c>
+      <x:c r="I17" s="11" t="str">
+        <x:v>0.96</x:v>
+      </x:c>
       <x:c r="J17" s="10" t="str">
-        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-22、2026-08-23、2026-08-24、2026-08-29、2026-09-05、2026-09-06、2026-09-07、2026-09-11、2026-09-12</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -848,27 +848,27 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>姜猎娶妻之知青良缘</x:v>
+        <x:v>冷宫开席：陛下又来蹭饭了</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>08-17 09:38</x:v>
+        <x:v>08-02 14:08</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="E18" s="10" t="n">
-        <x:v>62</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="F18" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G18" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷 / 美食治愈</x:v>
       </x:c>
       <x:c r="H18" s="11" t="str"/>
       <x:c r="I18" s="11" t="str"/>
       <x:c r="J18" s="10" t="str">
-        <x:v>2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-09、2026-09-11、2026-09-12、2026-09-13、2026-09-15</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1239,7 +1239,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
         <x:v>一块冰袋，冻凉十二年合伙情</x:v>
@@ -1276,13 +1276,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
+        <x:v>我都元婴期了，你跟我说开学</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>09-15 00:08</x:v>
+        <x:v>09-16 00:10</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str"/>
       <x:c r="F5" s="11" t="str"/>
@@ -1293,7 +1293,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I5" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="J5" s="10" t="str">
         <x:v>其他</x:v>
@@ -1302,10 +1302,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L5" s="11" t="str">
-        <x:v>桃子动漫剧场</x:v>
+        <x:v>梦启剧场</x:v>
       </x:c>
       <x:c r="M5" s="10" t="str">
-        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
+        <x:v>修士宁尘遭遇偷袭，身负重伤从修真界回到现代。时间只流逝一个暑假，他被迫入读青州大学，借居在乔姨家中，与傲娇少女许舒颜同住。一边伪装普通学生，一边寻找修复元神伤势的资源，接连化解校园、市井与古武圈子的各类风波，开启充满反差的现代生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1313,13 +1313,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>攻略失败后我不装了</x:v>
+        <x:v>我在工地卖盒饭带火一座城</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>09-15 15:00</x:v>
+        <x:v>09-14 14:52</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str"/>
       <x:c r="F6" s="11" t="str"/>
@@ -1330,19 +1330,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I6" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="J6" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K6" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="L6" s="11" t="str">
-        <x:v>喵喵说漫</x:v>
+        <x:v>左手良画</x:v>
       </x:c>
       <x:c r="M6" s="10" t="str">
-        <x:v>陆瑶做了百年攻略任务，反倒被系统判定为史上最废宿主，嘲讽她连宗门看门大黄都攻略不了，直接解绑。重获自由的她解开封印，觉醒万年难遇的天生道体。她撕碎弟子玉牌，决绝离开凌云峰，手握海量资源专心经商修炼。从前被她百般讨好的师尊师兄尽数落魄、满心悔意。她看淡情爱纠葛，收服大黄相伴，一路开挂逆袭，潇洒飞升开启全新仙生。</x:v>
+        <x:v>小伙白叶遭遇老板跑路，半年工资付诸东流，意外被铁炒勺砸中觉醒超级餐饮系统。大雪封路堵车途中完成首份任务，靠着系统加持的厨艺，路边卖盒饭赚到第一桶金。回乡钻研秘制酱肉，赶集摆摊火爆出圈，还临危接手大型寿宴惊艳众人。过完新年，他怀揣梦想奔赴外地，准备开启属于自己的餐饮创业之路。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1350,7 +1350,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
         <x:v>一盒印泥引发的全局封锁</x:v>
@@ -1381,13 +1381,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
-        <x:v>我都元婴期了，你跟我说开学</x:v>
+        <x:v>四个崽崽瞒不住了</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>09-16 00:10</x:v>
+        <x:v>09-15 00:08</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str"/>
       <x:c r="F8" s="11" t="str"/>
@@ -1398,7 +1398,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
-        <x:v>475</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="J8" s="10" t="str">
         <x:v>其他</x:v>
@@ -1407,10 +1407,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L8" s="11" t="str">
-        <x:v>梦启剧场</x:v>
+        <x:v>桃子动漫剧场</x:v>
       </x:c>
       <x:c r="M8" s="10" t="str">
-        <x:v>修士宁尘遭遇偷袭，身负重伤从修真界回到现代。时间只流逝一个暑假，他被迫入读青州大学，借居在乔姨家中，与傲娇少女许舒颜同住。一边伪装普通学生，一边寻找修复元神伤势的资源，接连化解校园、市井与古武圈子的各类风波，开启充满反差的现代生活。</x:v>
+        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1418,13 +1418,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>34</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
-        <x:v>我在工地卖盒饭带火一座城</x:v>
+        <x:v>攻略失败后我不装了</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>09-14 14:52</x:v>
+        <x:v>09-15 15:00</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str"/>
       <x:c r="F9" s="11" t="str"/>
@@ -1435,19 +1435,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I9" s="11" t="n">
-        <x:v>144</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="J9" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K9" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="L9" s="11" t="str">
-        <x:v>左手良画</x:v>
+        <x:v>喵喵说漫</x:v>
       </x:c>
       <x:c r="M9" s="10" t="str">
-        <x:v>小伙白叶遭遇老板跑路，半年工资付诸东流，意外被铁炒勺砸中觉醒超级餐饮系统。大雪封路堵车途中完成首份任务，靠着系统加持的厨艺，路边卖盒饭赚到第一桶金。回乡钻研秘制酱肉，赶集摆摊火爆出圈，还临危接手大型寿宴惊艳众人。过完新年，他怀揣梦想奔赴外地，准备开启属于自己的餐饮创业之路。</x:v>
+        <x:v>陆瑶做了百年攻略任务，反倒被系统判定为史上最废宿主，嘲讽她连宗门看门大黄都攻略不了，直接解绑。重获自由的她解开封印，觉醒万年难遇的天生道体。她撕碎弟子玉牌，决绝离开凌云峰，手握海量资源专心经商修炼。从前被她百般讨好的师尊师兄尽数落魄、满心悔意。她看淡情爱纠葛，收服大黄相伴，一路开挂逆袭，潇洒飞升开启全新仙生。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1455,7 +1455,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
         <x:v>高考刚结束父母就不装了</x:v>
@@ -1492,7 +1492,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C11" s="10" t="str">
         <x:v>被身高掩盖的谎言</x:v>
@@ -1529,7 +1529,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
         <x:v>急诊摸鱼王2</x:v>
@@ -1566,7 +1566,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B13" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
         <x:v>傅少你夫人又在扮猪吃虎了</x:v>
@@ -1577,10 +1577,10 @@
       <x:c r="E13" s="11" t="str"/>
       <x:c r="F13" s="11" t="str"/>
       <x:c r="G13" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H13" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I13" s="11" t="str"/>
       <x:c r="J13" s="10" t="str">
@@ -1594,47 +1594,47 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B14" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
-        <x:v>重回雪崩泥石流，我不再犹豫</x:v>
+        <x:v>三十年退让，摒弃无底线的迁就</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>09-16 01:02</x:v>
-      </x:c>
-      <x:c r="E14" s="11" t="n">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="F14" s="11" t="str">
-        <x:v>↑34位</x:v>
-      </x:c>
-      <x:c r="G14" s="11" t="str"/>
-      <x:c r="H14" s="11" t="str"/>
+        <x:v>09-15 15:00</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="str"/>
+      <x:c r="F14" s="11" t="str"/>
+      <x:c r="G14" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="I14" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J14" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K14" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="L14" s="11" t="str">
-        <x:v>姜缘</x:v>
+        <x:v>浮光漫影</x:v>
       </x:c>
       <x:c r="M14" s="10" t="str">
-        <x:v>前世，周清雨因犹豫错失逃生时机，眼睁睁看着全家被雪崩泥石流吞没。重生回灾难前三天，她当机立断卖掉五十头牦牛，囤积物资，带家人撤往高处。面对全村嘲讽和阻拦，她不再苦劝。直到雪山崩塌、洪流封村，昔日笑她疯癫的人纷纷求上门。这一次，她只救值得救的人！</x:v>
+        <x:v>陈远辛苦规划全家自驾游，在高速服务区上厕所时，被家人为腾出位置搭载二叔一家直接抛下。过往他一直习惯为家里出钱出力，这次他不再一味妥协。经历一路波折后，陈远回归江城，分清家庭边界。后续弟弟学着独立承担生活，父母也慢慢反思过往。陈远守住自我，坦然面对亲情，过好属于自己的生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B15" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
         <x:v>被诬陷诊出喜脉，重活一世我逆转前尘</x:v>
@@ -1642,14 +1642,14 @@
       <x:c r="D15" s="11" t="str">
         <x:v>09-16 07:58</x:v>
       </x:c>
-      <x:c r="E15" s="11" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F15" s="11" t="str">
-        <x:v>↑32位</x:v>
-      </x:c>
-      <x:c r="G15" s="11" t="str"/>
-      <x:c r="H15" s="11" t="str"/>
+      <x:c r="E15" s="11" t="str"/>
+      <x:c r="F15" s="11" t="str"/>
+      <x:c r="G15" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H15" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="I15" s="11" t="n">
         <x:v>50</x:v>
       </x:c>
@@ -1668,150 +1668,144 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C16" s="10" t="str">
-        <x:v>我都元婴期了，你跟我说开学</x:v>
+        <x:v>重回雪崩泥石流，我不再犹豫</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
-        <x:v>09-16 00:10</x:v>
-      </x:c>
-      <x:c r="E16" s="11" t="n">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F16" s="11" t="str">
-        <x:v>↑29位</x:v>
-      </x:c>
-      <x:c r="G16" s="11" t="str"/>
-      <x:c r="H16" s="11" t="str"/>
+        <x:v>09-16 01:02</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="str"/>
+      <x:c r="F16" s="11" t="str"/>
+      <x:c r="G16" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H16" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="I16" s="11" t="n">
-        <x:v>475</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J16" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K16" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="L16" s="11" t="str">
-        <x:v>梦启剧场</x:v>
+        <x:v>姜缘</x:v>
       </x:c>
       <x:c r="M16" s="10" t="str">
-        <x:v>修士宁尘遭遇偷袭，身负重伤从修真界回到现代。时间只流逝一个暑假，他被迫入读青州大学，借居在乔姨家中，与傲娇少女许舒颜同住。一边伪装普通学生，一边寻找修复元神伤势的资源，接连化解校园、市井与古武圈子的各类风波，开启充满反差的现代生活。</x:v>
+        <x:v>前世，周清雨因犹豫错失逃生时机，眼睁睁看着全家被雪崩泥石流吞没。重生回灾难前三天，她当机立断卖掉五十头牦牛，囤积物资，带家人撤往高处。面对全村嘲讽和阻拦，她不再苦劝。直到雪山崩塌、洪流封村，昔日笑她疯癫的人纷纷求上门。这一次，她只救值得救的人！</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C17" s="10" t="str">
-        <x:v>高考刚结束父母就不装了</x:v>
+        <x:v>嫡姐日日闹换夫，圣旨赐下后她悔疯了</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
-        <x:v>09-15 07:00</x:v>
-      </x:c>
-      <x:c r="E17" s="11" t="n">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F17" s="11" t="str">
-        <x:v>↑22位</x:v>
-      </x:c>
-      <x:c r="G17" s="11" t="str"/>
-      <x:c r="H17" s="11" t="str"/>
+        <x:v>09-16 08:00</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="str"/>
+      <x:c r="F17" s="11" t="str"/>
+      <x:c r="G17" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H17" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="I17" s="11" t="n">
-        <x:v>173</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J17" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K17" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>婚姻情感 / 现实反转</x:v>
       </x:c>
       <x:c r="L17" s="11" t="str">
-        <x:v>千慕剧场</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="M17" s="10" t="str">
-        <x:v>高考结束那天，林寻在考场外被亲生父母认回原来十八年的普通生活，是父母为磨砺他而设的一场成长课。重回豪门，他没有迷失，反而在桥上遇见了那个让他心动的姑娘，南大冰山学姐苏清诗。从青涩的初次相遇，到演唱会上的合唱，再到大学校园里的朝夕相处，两个真诚的人慢慢靠近。曾经的求而不得终将释怀，双向奔赴的喜欢才最珍贵。褪去普通学生的身份，林寻只想以真心换真心。十八岁的夏天，最好的相遇，最甜的恋爱，才刚刚开始。</x:v>
+        <x:v>沈家庶女沈照蘅自幼被嫡姐沈令仪欺压。嫡姐与状元顾砚舟定亲，争吵便扬言抢她未婚夫谢长晏。嫡姐竟跪求御前换婚，圣旨互换。状元当庭抗旨，全家逼她退让，她一句“臣女不敢抗旨”拒绝牺牲。嫡姐掌掴她、嫡母夺嫁妆、状元逼签屈辱契约被她焚毁，沈家灌哑药逼她自毁，皇后女官相救亮出生母嫁妆凭证。宫宴上嫡姐撒泼名声尽毁，皇后请旨暂缓赐婚，沈照蘅入宫担任伴读女官。从庶女到御前女官，她的命自己写。</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>34</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C18" s="10" t="str">
-        <x:v>我在工地卖盒饭带火一座城</x:v>
+        <x:v>悍妻大房不好惹</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>09-14 14:52</x:v>
-      </x:c>
-      <x:c r="E18" s="11" t="n">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F18" s="11" t="str">
-        <x:v>↑20位</x:v>
-      </x:c>
-      <x:c r="G18" s="11" t="str"/>
-      <x:c r="H18" s="11" t="str"/>
-      <x:c r="I18" s="11" t="n">
-        <x:v>144</x:v>
-      </x:c>
+        <x:v>2026-09-16</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="str"/>
+      <x:c r="F18" s="11" t="str"/>
+      <x:c r="G18" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H18" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I18" s="11" t="str"/>
       <x:c r="J18" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K18" s="10" t="str">
-        <x:v>美食治愈</x:v>
-      </x:c>
-      <x:c r="L18" s="11" t="str">
-        <x:v>左手良画</x:v>
-      </x:c>
-      <x:c r="M18" s="10" t="str">
-        <x:v>小伙白叶遭遇老板跑路，半年工资付诸东流，意外被铁炒勺砸中觉醒超级餐饮系统。大雪封路堵车途中完成首份任务，靠着系统加持的厨艺，路边卖盒饭赚到第一桶金。回乡钻研秘制酱肉，赶集摆摊火爆出圈，还临危接手大型寿宴惊艳众人。过完新年，他怀揣梦想奔赴外地，准备开启属于自己的餐饮创业之路。</x:v>
-      </x:c>
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="L18" s="11" t="str"/>
+      <x:c r="M18" s="10" t="str"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C19" s="10" t="str">
-        <x:v>被身高掩盖的谎言</x:v>
+        <x:v>刺耳的邻里情</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
-        <x:v>09-15 08:18</x:v>
-      </x:c>
-      <x:c r="E19" s="11" t="n">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F19" s="11" t="str">
-        <x:v>↑15位</x:v>
-      </x:c>
-      <x:c r="G19" s="11" t="str"/>
-      <x:c r="H19" s="11" t="str"/>
+        <x:v>09-15 11:00</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="str"/>
+      <x:c r="F19" s="11" t="str"/>
+      <x:c r="G19" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H19" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="I19" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J19" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K19" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L19" s="11" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>酒写一首诗</x:v>
       </x:c>
       <x:c r="M19" s="10" t="str">
-        <x:v>女孩林知晚回到命运转折的关键节点。她凭借智慧与勇气，敏锐察觉家中隐患，冷静引导家人、寻求帮助，用爱守护姐姐与全家。在共同努力下危机化解、正义伸张，一家人愈发珍视彼此，并且帮助到了更多有同样遭遇的人，最后迎来温暖安宁的幸福生活。</x:v>
+        <x:v>邻居大强夫妇痴迷比赛，深夜制造噪音打扰四邻，甚至潜入邻院破坏，终因违规致使墙倒器毁、面临赔偿。青年陈默没有以怨报怨，只凭合农机与科学常识理性应对。大强夫妇在赔偿检讨中受教，重新学会遵守规则、尊重邻里；陈默则凭宽容智慧用赔款修筑村广场，走出一条和谐讲理的乡村新路。</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1819,36 +1813,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C20" s="10" t="str">
-        <x:v>嫡姐日日闹换夫，圣旨赐下后她悔疯了</x:v>
+        <x:v>说好九十天就回来，我不等了</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>09-16 08:00</x:v>
+        <x:v>09-16 06:00</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F20" s="11" t="str">
-        <x:v>↑9位</x:v>
+        <x:v>↑26位</x:v>
       </x:c>
       <x:c r="G20" s="11" t="str"/>
       <x:c r="H20" s="11" t="str"/>
       <x:c r="I20" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J20" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K20" s="10" t="str">
-        <x:v>婚姻情感 / 现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L20" s="11" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>小宁漫漫</x:v>
       </x:c>
       <x:c r="M20" s="10" t="str">
-        <x:v>沈家庶女沈照蘅自幼被嫡姐沈令仪欺压。嫡姐与状元顾砚舟定亲，争吵便扬言抢她未婚夫谢长晏。嫡姐竟跪求御前换婚，圣旨互换。状元当庭抗旨，全家逼她退让，她一句“臣女不敢抗旨”拒绝牺牲。嫡姐掌掴她、嫡母夺嫁妆、状元逼签屈辱契约被她焚毁，沈家灌哑药逼她自毁，皇后女官相救亮出生母嫁妆凭证。宫宴上嫡姐撒泼名声尽毁，皇后请旨暂缓赐婚，沈照蘅入宫担任伴读女官。从庶女到御前女官，她的命自己写。</x:v>
+        <x:v>周衡挣脱错位的旧感情，坚守原则，专注医疗事业，打磨救死扶伤的星桥心泵。他与叶宁彼此尊重，感情建立在坦诚与边界之上，不盲目牺牲自我，平等相伴走向未来。林夏历经挫折后幡然醒悟，承担自己犯下的过错，放下执念踏实努力，靠双手重新经营人生。故事告诉人不必困在原地等候错的人，真心不该沦为候补，每个人都可以告别过往，奔赴属于自己的前路</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1856,36 +1850,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C21" s="10" t="str">
-        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
+        <x:v>重回雪崩泥石流，我不再犹豫</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
-        <x:v>09-15 08:30</x:v>
+        <x:v>09-16 01:02</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F21" s="11" t="str">
-        <x:v>↑8位</x:v>
+        <x:v>↑14位</x:v>
       </x:c>
       <x:c r="G21" s="11" t="str"/>
       <x:c r="H21" s="11" t="str"/>
       <x:c r="I21" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J21" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K21" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="L21" s="11" t="str">
-        <x:v>琥珀漫剧</x:v>
+        <x:v>姜缘</x:v>
       </x:c>
       <x:c r="M21" s="10" t="str">
-        <x:v>海鲜市场老手陈放，因一个两块钱的冰袋被十二年合伙人当众算旧账，心寒清账，净身出户。他没有抱怨，也没有以牙还牙，而是加入冷清档口“梅姐水产”，从零开始。他坚持明码标价、沥水称重、死活分卖、批次可查，宁可少接单，也不混货、不凑数、不赚亏心钱。面对低价抢客、恶意破坏、临时缺货等风波，他与叶梅靠诚信、规矩和彼此信任，一步步赢得客户与连锁企业的认可。</x:v>
+        <x:v>前世，周清雨因犹豫错失逃生时机，眼睁睁看着全家被雪崩泥石流吞没。重生回灾难前三天，她当机立断卖掉五十头牦牛，囤积物资，带家人撤往高处。面对全村嘲讽和阻拦，她不再苦劝。直到雪山崩塌、洪流封村，昔日笑她疯癫的人纷纷求上门。这一次，她只救值得救的人！</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1893,24 +1887,24 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C22" s="10" t="str">
-        <x:v>急诊摸鱼王2</x:v>
+        <x:v>被诬陷诊出喜脉，重活一世我逆转前尘</x:v>
       </x:c>
       <x:c r="D22" s="11" t="str">
-        <x:v>09-15 20:00</x:v>
+        <x:v>09-16 07:58</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
-        <x:v>99</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F22" s="11" t="str">
-        <x:v>↑8位</x:v>
+        <x:v>↑10位</x:v>
       </x:c>
       <x:c r="G22" s="11" t="str"/>
       <x:c r="H22" s="11" t="str"/>
       <x:c r="I22" s="11" t="n">
-        <x:v>114</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J22" s="10" t="str">
         <x:v>其他</x:v>
@@ -1919,10 +1913,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L22" s="11" t="str">
-        <x:v>阿部漫剧</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="M22" s="10" t="str">
-        <x:v>大佬贺知舟伪装咸鱼住院医，在急诊科继续摸鱼。院内急救考核到来，贺知舟笔试满分，实操手法惊艳一众同事。普外、麻醉科主任从特殊手术技巧，怀疑他就是消失的国际传奇DrZ。宿敌沈长风的势力不断逼近，旧身份危机迫在眉睫，贺知舟一边抢救危重病患，一边隐藏自己的过往。</x:v>
+        <x:v>沈清瑶重生回到被“神医”姜辞诬陷喜脉那天。前世她因此身败名裂，被迫嫁给竹马萧景渊，后来才知这是两人为替姜辞上位设的局。这一世，她不再任人宰割，巧妙将诊脉丝线系在谢老夫人腕上，当众揭穿姜辞。萧景渊谎称“孩子是我的”，却被她揭发与姜辞的私情，两人丑态毕露。谢家震怒，姜辞被强嫁萧景渊，沈清瑶嫁入侯府。婚后她冷静布局，让萧景渊与姜辞内斗升级。最终姜辞伏法，沈清瑶挣脱前世枷锁。可重生真能让她彻底自由吗？</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1930,47 +1924,53 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>31</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C23" s="10" t="str">
-        <x:v>一盒印泥引发的全局封锁</x:v>
+        <x:v>我都元婴期了，你跟我说开学</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>09-16 00:10</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F23" s="11" t="str">
-        <x:v>↑7位</x:v>
+        <x:v>↑10位</x:v>
       </x:c>
       <x:c r="G23" s="11" t="str"/>
       <x:c r="H23" s="11" t="str"/>
-      <x:c r="I23" s="11" t="str"/>
+      <x:c r="I23" s="11" t="n">
+        <x:v>475</x:v>
+      </x:c>
       <x:c r="J23" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K23" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L23" s="11" t="str"/>
-      <x:c r="M23" s="10" t="str"/>
+      <x:c r="L23" s="11" t="str">
+        <x:v>梦启剧场</x:v>
+      </x:c>
+      <x:c r="M23" s="10" t="str">
+        <x:v>修士宁尘遭遇偷袭，身负重伤从修真界回到现代。时间只流逝一个暑假，他被迫入读青州大学，借居在乔姨家中，与傲娇少女许舒颜同住。一边伪装普通学生，一边寻找修复元神伤势的资源，接连化解校园、市井与古武圈子的各类风波，开启充满反差的现代生活。</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C24" s="10" t="str">
-        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
+        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
       </x:c>
       <x:c r="D24" s="11" t="str">
-        <x:v>09-15 08:00</x:v>
+        <x:v>09-15 08:30</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F24" s="11" t="str">
         <x:v>↑5位</x:v>
@@ -1978,19 +1978,19 @@
       <x:c r="G24" s="11" t="str"/>
       <x:c r="H24" s="11" t="str"/>
       <x:c r="I24" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J24" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K24" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L24" s="11" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>琥珀漫剧</x:v>
       </x:c>
       <x:c r="M24" s="10" t="str">
-        <x:v>沈清韵嫁入靖王府三年，王爷冷落，侧妃得宠。王爷当众许诺，谁先诞下儿子，便请封世子。苏氏先怀孕，沈清韵却发现自己怀的是龙凤胎，她隐瞒消息，买通太医推迟产期，忍痛让苏氏先产子。王爷果然请封庶长子为世子，折子递入宗人府。受理之后，沈清韵才发动，生下龙凤胎。太后与皇上视为祥瑞，下旨赐嫡子承恩为靖王世子、嫡女承华为安乐郡主。王爷措手不及，苏氏地位一落千丈。而沈清韵知道，这只是第一步。</x:v>
+        <x:v>海鲜市场老手陈放，因一个两块钱的冰袋被十二年合伙人当众算旧账，心寒清账，净身出户。他没有抱怨，也没有以牙还牙，而是加入冷清档口“梅姐水产”，从零开始。他坚持明码标价、沥水称重、死活分卖、批次可查，宁可少接单，也不混货、不凑数、不赚亏心钱。面对低价抢客、恶意破坏、临时缺货等风波，他与叶梅靠诚信、规矩和彼此信任，一步步赢得客户与连锁企业的认可。</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1998,36 +1998,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C25" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
+        <x:v>我在工地卖盒饭带火一座城</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
-        <x:v>09-15 00:08</x:v>
+        <x:v>09-14 14:52</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F25" s="11" t="str">
-        <x:v>↑3位</x:v>
+        <x:v>↑4位</x:v>
       </x:c>
       <x:c r="G25" s="11" t="str"/>
       <x:c r="H25" s="11" t="str"/>
       <x:c r="I25" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="J25" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K25" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="L25" s="11" t="str">
-        <x:v>桃子动漫剧场</x:v>
+        <x:v>左手良画</x:v>
       </x:c>
       <x:c r="M25" s="10" t="str">
-        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
+        <x:v>小伙白叶遭遇老板跑路，半年工资付诸东流，意外被铁炒勺砸中觉醒超级餐饮系统。大雪封路堵车途中完成首份任务，靠着系统加持的厨艺，路边卖盒饭赚到第一桶金。回乡钻研秘制酱肉，赶集摆摊火爆出圈，还临危接手大型寿宴惊艳众人。过完新年，他怀揣梦想奔赴外地，准备开启属于自己的餐饮创业之路。</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -2035,34 +2035,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B26" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C26" s="10" t="str">
-        <x:v>说好九十天就回来，我不等了</x:v>
+        <x:v>嫡姐日日闹换夫，圣旨赐下后她悔疯了</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
-        <x:v>09-16 06:00</x:v>
-      </x:c>
-      <x:c r="E26" s="11" t="str"/>
+        <x:v>09-16 08:00</x:v>
+      </x:c>
+      <x:c r="E26" s="11" t="n">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="F26" s="11" t="str">
-        <x:v>新上榜</x:v>
+        <x:v>↑3位</x:v>
       </x:c>
       <x:c r="G26" s="11" t="str"/>
       <x:c r="H26" s="11" t="str"/>
       <x:c r="I26" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J26" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K26" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感 / 现实反转</x:v>
       </x:c>
       <x:c r="L26" s="11" t="str">
-        <x:v>小宁漫漫</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="M26" s="10" t="str">
-        <x:v>周衡挣脱错位的旧感情，坚守原则，专注医疗事业，打磨救死扶伤的星桥心泵。他与叶宁彼此尊重，感情建立在坦诚与边界之上，不盲目牺牲自我，平等相伴走向未来。林夏历经挫折后幡然醒悟，承担自己犯下的过错，放下执念踏实努力，靠双手重新经营人生。故事告诉人不必困在原地等候错的人，真心不该沦为候补，每个人都可以告别过往，奔赴属于自己的前路</x:v>
+        <x:v>沈家庶女沈照蘅自幼被嫡姐沈令仪欺压。嫡姐与状元顾砚舟定亲，争吵便扬言抢她未婚夫谢长晏。嫡姐竟跪求御前换婚，圣旨互换。状元当庭抗旨，全家逼她退让，她一句“臣女不敢抗旨”拒绝牺牲。嫡姐掌掴她、嫡母夺嫁妆、状元逼签屈辱契约被她焚毁，沈家灌哑药逼她自毁，皇后女官相救亮出生母嫁妆凭证。宫宴上嫡姐撒泼名声尽毁，皇后请旨暂缓赐婚，沈照蘅入宫担任伴读女官。从庶女到御前女官，她的命自己写。</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -2073,31 +2075,33 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="C27" s="10" t="str">
-        <x:v>养娃记：八零四合院生活日常</x:v>
+        <x:v>重生极品婆婆，带全家发家致富！</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
-        <x:v>09-15 01:11</x:v>
-      </x:c>
-      <x:c r="E27" s="11" t="str"/>
+        <x:v>09-14 20:29</x:v>
+      </x:c>
+      <x:c r="E27" s="11" t="n">
+        <x:v>100</x:v>
+      </x:c>
       <x:c r="F27" s="11" t="str">
-        <x:v>新上榜</x:v>
+        <x:v>↑2位</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str"/>
       <x:c r="H27" s="11" t="str"/>
       <x:c r="I27" s="11" t="n">
-        <x:v>191</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="J27" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K27" s="10" t="str">
-        <x:v>年代怀旧 / 萌宝治愈</x:v>
+        <x:v>家庭伦理 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="L27" s="11" t="str">
-        <x:v>香菜薯片</x:v>
+        <x:v>懒少爱我</x:v>
       </x:c>
       <x:c r="M27" s="10" t="str">
-        <x:v>儿女已经成家立业，送走公公婆婆后，正准备全国游的六十多岁老太太赵锦舒重生了。重回到刚进城几个月时，那时什么都不懂，乡下来的年轻小媳妇脸皮薄，抹不开面子，也自卑，哪怕男人能挣钱，面对有权有势的婆家人，也自觉低人一头，更怕出错，给男人丢脸，很长一段时间都不敢多说一句话，明里暗里娘三个受了不少委屈。回到年轻时，赵锦舒老黄瓜刷绿漆，不管外表如何，内里都是老姜疙瘩，装不来腼腆小媳妇。</x:v>
+        <x:v>寡妇傅兰秀前世一生吝啬守财，刻薄对待儿女儿媳，到头来钱财被贼人掠夺，落得个凄惨离世的下场。一朝重生，她回到悲剧尚未发生之时。痛定思痛，她彻底改掉抠门的性子，学着善待家里的晚辈。可日子并不太平，爱占便宜的亲戚总上门搅扰，家中两个儿媳也矛盾不断，家务是非接连找上门。傅兰秀靠着清醒的头脑，一边化解各类家庭纷争，一边寻找营生门路，努力扭转命运，拼尽全力守护一家人的安稳生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -2105,13 +2109,13 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B28" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C28" s="10" t="str">
-        <x:v>重生极品婆婆，带全家发家致富！</x:v>
+        <x:v>我能看见每个人的剩余寿命</x:v>
       </x:c>
       <x:c r="D28" s="11" t="str">
-        <x:v>09-14 20:29</x:v>
+        <x:v>09-15 00:04</x:v>
       </x:c>
       <x:c r="E28" s="11" t="str"/>
       <x:c r="F28" s="11" t="str">
@@ -2120,19 +2124,89 @@
       <x:c r="G28" s="11" t="str"/>
       <x:c r="H28" s="11" t="str"/>
       <x:c r="I28" s="11" t="n">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="J28" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K28" s="10" t="str">
-        <x:v>家庭伦理 / 逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L28" s="11" t="str">
-        <x:v>懒少爱我</x:v>
+        <x:v>酒森漫剧</x:v>
       </x:c>
       <x:c r="M28" s="10" t="str">
-        <x:v>寡妇傅兰秀前世一生吝啬守财，刻薄对待儿女儿媳，到头来钱财被贼人掠夺，落得个凄惨离世的下场。一朝重生，她回到悲剧尚未发生之时。痛定思痛，她彻底改掉抠门的性子，学着善待家里的晚辈。可日子并不太平，爱占便宜的亲戚总上门搅扰，家中两个儿媳也矛盾不断，家务是非接连找上门。傅兰秀靠着清醒的头脑，一边化解各类家庭纷争，一边寻找营生门路，努力扭转命运，拼尽全力守护一家人的安稳生活。</x:v>
+        <x:v>青山村少女沈海棠觉醒异能，能看见每个人头顶的剩余寿命。全村人寿命骤剩七天，唯有猎户萧野一家存活时间更长，海棠为护住幼妹小满，想方设法嫁入萧家。不久丧尸灾变爆发，她靠着寿命预知，提前囤积粮草兵器，带领萧家与部部分村民艰难求生。在残酷的末世之中，聪慧厚脸皮的海棠与外冷内热武力高强的萧野从契约夫妻走向彼此倾心。众人一边对抗变异丧尸、应对自私村民的算计，一边开荒筑防拼命改写死亡倒计时，可寿命数字仍在跳动。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B29" s="11" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C29" s="10" t="str">
+        <x:v>我堂堂元婴老祖，让我给大小姐当保镖</x:v>
+      </x:c>
+      <x:c r="D29" s="11" t="str">
+        <x:v>09-15 23:57</x:v>
+      </x:c>
+      <x:c r="E29" s="11" t="str"/>
+      <x:c r="F29" s="11" t="str">
+        <x:v>新上榜</x:v>
+      </x:c>
+      <x:c r="G29" s="11" t="str"/>
+      <x:c r="H29" s="11" t="str"/>
+      <x:c r="I29" s="11" t="n">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="J29" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K29" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L29" s="11" t="str">
+        <x:v>扶摇精品剧场</x:v>
+      </x:c>
+      <x:c r="M29" s="10" t="str">
+        <x:v>宁尘穿越到修仙界两千年，居然只过了一个暑假！什么？你说我堂堂元婴老祖，不但被亲妈逼着去上大学，还要和校花大小姐同居？很快，同学们惊呆了随手扔铅球破世界纪录，你说这是大一新生？古武界集体怀疑人生修炼了几十年的武道老家伙，被一个年轻人当球踢？校花大小姐气得跺脚想接我电话的人能绕青州一圈，你居然嫌我吵？宁尘我，元婴老祖，真的只想做个普通人，既然你们非要逼我，那我只能一路横推，专治各种不服！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B30" s="11" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C30" s="10" t="str">
+        <x:v>我的系统不对劲，行善积德反着来</x:v>
+      </x:c>
+      <x:c r="D30" s="11" t="str">
+        <x:v>09-15 10:00</x:v>
+      </x:c>
+      <x:c r="E30" s="11" t="str"/>
+      <x:c r="F30" s="11" t="str">
+        <x:v>新上榜</x:v>
+      </x:c>
+      <x:c r="G30" s="11" t="str"/>
+      <x:c r="H30" s="11" t="str"/>
+      <x:c r="I30" s="11" t="n">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="J30" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K30" s="10" t="str">
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="L30" s="11" t="str">
+        <x:v>掌读微剧</x:v>
+      </x:c>
+      <x:c r="M30" s="10" t="str">
+        <x:v>贵为玄天宗第一天骄，苏云峰惨遭师尊沈傲雪背叛，被夺去至尊骨后含恨而亡！再度睁眼，他意外获得另类的行善积德系统。在系统的帮助下，昔日温顺弟子彻底觉醒，不再任人宰割，苏云峰的命运轨迹被彻底改写，走出一条截然不同的修行路！</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2178,198 +2252,152 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
-        <x:v>傅少你夫人又在扮猪吃虎了</x:v>
+        <x:v>被诬陷诊出喜脉，重活一世我逆转前尘</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>当日新上榜</x:v>
-      </x:c>
-      <x:c r="D2" s="11" t="str"/>
-      <x:c r="E2" s="11" t="str"/>
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D2" s="11" t="str">
+        <x:v>09-16 07:58</x:v>
+      </x:c>
+      <x:c r="E2" s="11" t="n">
+        <x:v>50</x:v>
+      </x:c>
       <x:c r="F2" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="G2" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G2" s="10" t="str">
+        <x:v>芙浚动漫短剧</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>被诬陷诊出喜脉，重活一世我逆转前尘</x:v>
+        <x:v>我都元婴期了，你跟我说开学</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>09-16 07:58</x:v>
+        <x:v>09-16 00:10</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="F3" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G3" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>梦启剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>我都元婴期了，你跟我说开学</x:v>
+        <x:v>傅少你夫人又在扮猪吃虎了</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>今日发布</x:v>
-      </x:c>
-      <x:c r="D4" s="11" t="str">
-        <x:v>09-16 00:10</x:v>
-      </x:c>
-      <x:c r="E4" s="11" t="n">
-        <x:v>475</x:v>
-      </x:c>
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D4" s="11" t="str"/>
+      <x:c r="E4" s="11" t="str"/>
       <x:c r="F4" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G4" s="10" t="str">
-        <x:v>梦启剧场</x:v>
-      </x:c>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="G4" s="10" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>嫡姐日日闹换夫，圣旨赐下后她悔疯了</x:v>
+        <x:v>重回雪崩泥石流，我不再犹豫</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>09-16 08:00</x:v>
+        <x:v>09-16 01:02</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F5" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G5" s="10" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>姜缘</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>重回雪崩泥石流，我不再犹豫</x:v>
+        <x:v>嫡姐日日闹换夫，圣旨赐下后她悔疯了</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>09-16 01:02</x:v>
+        <x:v>09-16 08:00</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F6" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G6" s="10" t="str">
-        <x:v>姜缘</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>77</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>悍妻大房不好惹</x:v>
+        <x:v>说好九十天就回来，我不等了</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>当日新上榜</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="str"/>
-      <x:c r="E7" s="11" t="str"/>
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="str">
+        <x:v>09-16 06:00</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="n">
+        <x:v>66</x:v>
+      </x:c>
       <x:c r="F7" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="G7" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="str">
+        <x:v>小宁漫漫</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="n">
-        <x:v>86</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>扮猪吃老虎村霸被我一锅端</x:v>
+        <x:v>悍妻大房不好惹</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>当日新上榜</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="str">
-        <x:v>08-30 12:00</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="n">
-        <x:v>81</x:v>
-      </x:c>
+      <x:c r="D8" s="11" t="str"/>
+      <x:c r="E8" s="11" t="str"/>
       <x:c r="F8" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="G8" s="10" t="str">
-        <x:v>漫界剧场</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="11" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="B9" s="10" t="str">
-        <x:v>说好九十天就回来，我不等了</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="str">
-        <x:v>今日发布</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="str">
-        <x:v>09-16 06:00</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="n">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F9" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G9" s="10" t="str">
-        <x:v>小宁漫漫</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="11" t="n">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="B10" s="10" t="str">
-        <x:v>重生小渔村：海边捡个俏媳妇儿</x:v>
-      </x:c>
-      <x:c r="C10" s="11" t="str">
-        <x:v>当日新上榜</x:v>
-      </x:c>
-      <x:c r="D10" s="11" t="str">
-        <x:v>08-29 17:00</x:v>
-      </x:c>
-      <x:c r="E10" s="11" t="n">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="F10" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="G10" s="10" t="str">
-        <x:v>恰饭动画</x:v>
-      </x:c>
+      <x:c r="G8" s="10" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2438,7 +2466,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
         <x:v>征地我秒签跑路，全村笑我半年</x:v>
@@ -2475,16 +2503,16 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>大坝边寻回的真千金</x:v>
+        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>09-10 11:26</x:v>
+        <x:v>09-08 17:58</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
         <x:v>7</x:v>
@@ -2493,10 +2521,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G3" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H3" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
         <x:v>其他</x:v>
@@ -2504,24 +2532,24 @@
       <x:c r="J3" s="11" t="str"/>
       <x:c r="K3" s="11" t="str"/>
       <x:c r="L3" s="10" t="str">
-        <x:v>喵琪琪追剧</x:v>
+        <x:v>禾苗动画</x:v>
       </x:c>
       <x:c r="M3" s="10" t="str">
-        <x:v>大坝突发险情，农村女孩夏晚禾凭借熟悉的环境和过人的勇气，不顾危险救下被困的沈长洲。一次意外的救援，让两个陌生人的命运重新交织。随着调查深入，沈长洲发现这个善良坚韧的女孩，竟是自己失散二十年的亲生女儿。面对迟来的亲情和真假千金的风波，夏晚禾没有依靠身份改变人生，而是用智慧、担当和努力证明自己的价值。陆言川也在一次次并肩相处中，被她的真诚与坚强打动，陪她找回亲情，走向新的未来。</x:v>
+        <x:v>末世异能者沐小暖意外穿书，成为七个反派继子的恶毒后娘。原主辛劳养娃却遭流言中伤，最终含恨而终。沐小暖决心扭转命运，恩威并施管教孩子，凭末世身手进山打猎采药、种地赶集改善家计，更以百年老参为礼，为长子求得名儒霍政谚收为关门弟子。她护佑家人躲过恶人算计与亲戚夺产，建起新宅。七个孩子从怨恨抗拒到真心信赖，争着喊她娘，一家人携手改写命运，收获温暖亲情。</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>穿书后我带萌宝上门认爹</x:v>
+        <x:v>大坝边寻回的真千金</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>09-07 19:18</x:v>
+        <x:v>09-10 11:26</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
         <x:v>7</x:v>
@@ -2530,10 +2558,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G4" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H4" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I4" s="10" t="str">
         <x:v>其他</x:v>
@@ -2541,24 +2569,24 @@
       <x:c r="J4" s="11" t="str"/>
       <x:c r="K4" s="11" t="str"/>
       <x:c r="L4" s="10" t="str">
-        <x:v>虾仁不自在</x:v>
+        <x:v>喵琪琪追剧</x:v>
       </x:c>
       <x:c r="M4" s="10" t="str">
-        <x:v>许知棠重生穿进书中，当即带着五岁儿子许小舟登门，将孩子送到亲生父亲——傅氏集团总裁傅临川面前，只想抽身退出剧情。幼儿园里儿子遭同学诬陷、老师偏心，她强势护崽，硬刚蛮横家长与失职老师。亲子鉴定尘埃落定，萌娃黏妈不黏爹，反倒让清冷总裁渐渐上心。</x:v>
+        <x:v>大坝突发险情，农村女孩夏晚禾凭借熟悉的环境和过人的勇气，不顾危险救下被困的沈长洲。一次意外的救援，让两个陌生人的命运重新交织。随着调查深入，沈长洲发现这个善良坚韧的女孩，竟是自己失散二十年的亲生女儿。面对迟来的亲情和真假千金的风波，夏晚禾没有依靠身份改变人生，而是用智慧、担当和努力证明自己的价值。陆言川也在一次次并肩相处中，被她的真诚与坚强打动，陪她找回亲情，走向新的未来。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
+        <x:v>穿书后我带萌宝上门认爹</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>09-08 17:58</x:v>
+        <x:v>09-07 19:18</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
         <x:v>7</x:v>
@@ -2567,10 +2595,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G5" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H5" s="11" t="n">
-        <x:v>111</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="I5" s="10" t="str">
         <x:v>其他</x:v>
@@ -2578,21 +2606,21 @@
       <x:c r="J5" s="11" t="str"/>
       <x:c r="K5" s="11" t="str"/>
       <x:c r="L5" s="10" t="str">
-        <x:v>禾苗动画</x:v>
+        <x:v>虾仁不自在</x:v>
       </x:c>
       <x:c r="M5" s="10" t="str">
-        <x:v>末世异能者沐小暖意外穿书，成为七个反派继子的恶毒后娘。原主辛劳养娃却遭流言中伤，最终含恨而终。沐小暖决心扭转命运，恩威并施管教孩子，凭末世身手进山打猎采药、种地赶集改善家计，更以百年老参为礼，为长子求得名儒霍政谚收为关门弟子。她护佑家人躲过恶人算计与亲戚夺产，建起新宅。七个孩子从怨恨抗拒到真心信赖，争着喊她娘，一家人携手改写命运，收获温暖亲情。</x:v>
+        <x:v>许知棠重生穿进书中，当即带着五岁儿子许小舟登门，将孩子送到亲生父亲——傅氏集团总裁傅临川面前，只想抽身退出剧情。幼儿园里儿子遭同学诬陷、老师偏心，她强势护崽，硬刚蛮横家长与失职老师。亲子鉴定尘埃落定，萌娃黏妈不黏爹，反倒让清冷总裁渐渐上心。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>惊絮无声：傻女的绝杀</x:v>
+        <x:v>一墙之隔，皆是人心</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>09-06 10:00</x:v>
+        <x:v>09-06 15:48</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
         <x:v>10</x:v>
@@ -2604,10 +2632,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G6" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
         <x:v>其他</x:v>
@@ -2615,24 +2643,24 @@
       <x:c r="J6" s="11" t="str"/>
       <x:c r="K6" s="11" t="str"/>
       <x:c r="L6" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>在下长生</x:v>
       </x:c>
       <x:c r="M6" s="10" t="str">
-        <x:v>沈家人人都是天才，唯独小女儿沈惊絮是公认的傻子。没人知道，她不仅装傻多年，还带着前世金牌律师的记忆重生而来。本想闭嘴躺平一生，谁料内鬼勾结资本做空沈氏，一纸合同就要让全家净身出户、背上百亿债务。父亲落笔前，她终于按住协议“这字不能签！”绝地反杀的沈惊絮，一步步挫败了对沈家的围剿，也让全家人重新认识了自己。沈家也迎来了新生。</x:v>
+        <x:v>妻子临产被车堵住出口，叶瑾抱着羊水破裂的她跑了三公里才到医院，母子平安。面对无理的车主，他没有以暴制暴，而是选择依法行事——在自家院内合法砌墙、种下高价值树苗，全程录像留证。车主回来后暴力砸墙、碾压树苗，最终被依法追究责任。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>抢个新娘来当后娘第一季</x:v>
+        <x:v>惊絮无声：傻女的绝杀</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>09-08 15:10</x:v>
+        <x:v>09-06 10:00</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
         <x:v>7</x:v>
@@ -2641,10 +2669,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G7" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H7" s="11" t="n">
-        <x:v>177</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I7" s="10" t="str">
         <x:v>其他</x:v>
@@ -2652,10 +2680,10 @@
       <x:c r="J7" s="11" t="str"/>
       <x:c r="K7" s="11" t="str"/>
       <x:c r="L7" s="10" t="str">
-        <x:v>麻辣公主</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="M7" s="10" t="str">
-        <x:v>带着十里红妆出嫁那日，我才得知新郎早已另娶，这门亲事不过是盯上了我李家的家产。换作旁人或许忍气吞声，我偏不。我当众拒入侯府，主动上书朝廷，愿以嫁妆资援南方水患，只求解除婚约、护我父母周全。这份胆识赢得安王敬重，他以正妃之礼娶我入门。我立誓此生不做妾、不与人共侍一夫，终得一份彼此尊重的姻缘。</x:v>
+        <x:v>沈家人人都是天才，唯独小女儿沈惊絮是公认的傻子。没人知道，她不仅装傻多年，还带着前世金牌律师的记忆重生而来。本想闭嘴躺平一生，谁料内鬼勾结资本做空沈氏，一纸合同就要让全家净身出户、背上百亿债务。父亲落笔前，她终于按住协议“这字不能签！”绝地反杀的沈惊絮，一步步挫败了对沈家的围剿，也让全家人重新认识了自己。沈家也迎来了新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2663,13 +2691,13 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>一墙之隔，皆是人心</x:v>
+        <x:v>重生三天前，我用水泥封死地下室</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>09-06 15:48</x:v>
+        <x:v>09-09 09:28</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
         <x:v>7</x:v>
@@ -2681,7 +2709,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H8" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
         <x:v>其他</x:v>
@@ -2689,24 +2717,24 @@
       <x:c r="J8" s="11" t="str"/>
       <x:c r="K8" s="11" t="str"/>
       <x:c r="L8" s="10" t="str">
-        <x:v>在下长生</x:v>
+        <x:v>忘忧剧场</x:v>
       </x:c>
       <x:c r="M8" s="10" t="str">
-        <x:v>妻子临产被车堵住出口，叶瑾抱着羊水破裂的她跑了三公里才到医院，母子平安。面对无理的车主，他没有以暴制暴，而是选择依法行事——在自家院内合法砌墙、种下高价值树苗，全程录像留证。车主回来后暴力砸墙、碾压树苗，最终被依法追究责任。</x:v>
+        <x:v>阮清重生回被保姆王妈一家害死的三天前，前世她因心善引狼入室，保姆全家蜗居别墅地下室偷窃投毒，最终惨遭勒死。重生后她假装不知，趁王妈外出时用水泥将地下室彻底封死。警方破墙后，五具尸体令真相大白，王妈因盗窃、投毒被判十五年。阮清与父母团聚，恶人终得恶报，她重获新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>重生三天前，我用水泥封死地下室</x:v>
+        <x:v>抢个新娘来当后娘第一季</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>09-09 09:28</x:v>
+        <x:v>09-08 15:10</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
         <x:v>7</x:v>
@@ -2715,10 +2743,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G9" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H9" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str">
         <x:v>其他</x:v>
@@ -2726,15 +2754,15 @@
       <x:c r="J9" s="11" t="str"/>
       <x:c r="K9" s="11" t="str"/>
       <x:c r="L9" s="10" t="str">
-        <x:v>忘忧剧场</x:v>
+        <x:v>麻辣公主</x:v>
       </x:c>
       <x:c r="M9" s="10" t="str">
-        <x:v>阮清重生回被保姆王妈一家害死的三天前，前世她因心善引狼入室，保姆全家蜗居别墅地下室偷窃投毒，最终惨遭勒死。重生后她假装不知，趁王妈外出时用水泥将地下室彻底封死。警方破墙后，五具尸体令真相大白，王妈因盗窃、投毒被判十五年。阮清与父母团聚，恶人终得恶报，她重获新生。</x:v>
+        <x:v>带着十里红妆出嫁那日，我才得知新郎早已另娶，这门亲事不过是盯上了我李家的家产。换作旁人或许忍气吞声，我偏不。我当众拒入侯府，主动上书朝廷，愿以嫁妆资援南方水患，只求解除婚约、护我父母周全。这份胆识赢得安王敬重，他以正妃之礼娶我入门。我立誓此生不做妾、不与人共侍一夫，终得一份彼此尊重的姻缘。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
         <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
@@ -2771,7 +2799,7 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
         <x:v>不靠谱爸妈很靠谱</x:v>
@@ -2808,7 +2836,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
         <x:v>离家十年，回来女儿被换了</x:v>
@@ -2845,7 +2873,7 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
         <x:v>重启人生，拒绝校花？</x:v>
@@ -2882,7 +2910,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
         <x:v>美颜系统开挂，大佬全跪下</x:v>
@@ -2919,7 +2947,7 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
         <x:v>重生后我守住全村</x:v>
@@ -2956,28 +2984,28 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>穿越60我有空间不愁吃喝</x:v>
+        <x:v>全家施压：我反手签了过户合同</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>09-07 00:04</x:v>
+        <x:v>09-08 16:58</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G16" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H16" s="11" t="n">
-        <x:v>1000</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str">
         <x:v>其他</x:v>
@@ -2985,24 +3013,24 @@
       <x:c r="J16" s="11" t="str"/>
       <x:c r="K16" s="11" t="str"/>
       <x:c r="L16" s="10" t="str">
-        <x:v>夜珠AI剧场</x:v>
+        <x:v>灵川剧场</x:v>
       </x:c>
       <x:c r="M16" s="10" t="str">
-        <x:v>现代青年刘大壮意外穿越到60年代，成了同名同姓的16岁穷小子。原主因相亲被拒、家徒四壁，下河摸鱼时溺亡。大壮醒来后发现脑中多了一座九层宝塔空间——内有灵药田与灵泉潭水，作物两小时成熟、产量翻五倍。饥荒年代，别人啃树皮喝稀粥，他靠空间种出满仓土豆粮食，黑市换粮票钞票，让饿肚子的父母姐姐们吃上饱饭。从人人嘲笑的穷小子，到带着全家逆袭翻盘，且看他手握宝塔空间，在艰苦年代闯出一条吃喝不愁的逆袭</x:v>
+        <x:v>儿子儿媳多次提议我搬回乡下养老，将城里的宽敞住房腾出来给女方父母长期居住。我笑着点头应下，转头便将这套三室朝南的江景房产挂牌出售，最终成交二百八十万元。我随即购置了一套一室一厅的小户型，更换门锁后独自入住。他们上门索要钥匙，我没有开门。名下房产我自有主张，谁也别想插手安排。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
+        <x:v>穿越60我有空间不愁吃喝</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>09-11 09:00</x:v>
+        <x:v>09-07 00:04</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
         <x:v>6</x:v>
@@ -3011,10 +3039,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G17" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H17" s="11" t="n">
-        <x:v>133</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="I17" s="10" t="str">
         <x:v>其他</x:v>
@@ -3022,15 +3050,15 @@
       <x:c r="J17" s="11" t="str"/>
       <x:c r="K17" s="11" t="str"/>
       <x:c r="L17" s="10" t="str">
-        <x:v>阳阳动画</x:v>
+        <x:v>夜珠AI剧场</x:v>
       </x:c>
       <x:c r="M17" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
+        <x:v>现代青年刘大壮意外穿越到60年代，成了同名同姓的16岁穷小子。原主因相亲被拒、家徒四壁，下河摸鱼时溺亡。大壮醒来后发现脑中多了一座九层宝塔空间——内有灵药田与灵泉潭水，作物两小时成熟、产量翻五倍。饥荒年代，别人啃树皮喝稀粥，他靠空间种出满仓土豆粮食，黑市换粮票钞票，让饿肚子的父母姐姐们吃上饱饭。从人人嘲笑的穷小子，到带着全家逆袭翻盘，且看他手握宝塔空间，在艰苦年代闯出一条吃喝不愁的逆袭</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
         <x:v>三分钱的取舍</x:v>
@@ -3067,16 +3095,16 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>重生一世，我不再痴恋竹马</x:v>
+        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>09-10 10:00</x:v>
+        <x:v>09-11 09:00</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
         <x:v>6</x:v>
@@ -3085,10 +3113,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G19" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H19" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str">
         <x:v>其他</x:v>
@@ -3096,15 +3124,15 @@
       <x:c r="J19" s="11" t="str"/>
       <x:c r="K19" s="11" t="str"/>
       <x:c r="L19" s="10" t="str">
-        <x:v>锦书映年华</x:v>
+        <x:v>阳阳动画</x:v>
       </x:c>
       <x:c r="M19" s="10" t="str">
-        <x:v>承平公主前世错恋齐远安，受尽磋磨含恨落幕。一朝重生，恰逢圣旨赐婚，齐远安却当众恳请解除婚约，求取太后义孙女傅明珠。她坦然放手，主动成全二人，看着他们得偿所愿。宁国侯夫人动用旧物强求赐婚，她巧妙改换婚事，选择边关归来、品性刚正的齐远舟。婚后她聪慧通透，看清傅明珠与齐远安的本性，冷眼旁观二人矛盾丛生。历经风波，她与齐远舟彼此扶持，挣脱过往伤痛，收获属于自己安稳坦荡的人生。</x:v>
+        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="n">
-        <x:v>89</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
         <x:v>一张废票毁了她</x:v>
@@ -3135,16 +3163,16 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="n">
-        <x:v>93</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>回到零四年进军彩铃界</x:v>
+        <x:v>重生一世，我不再痴恋竹马</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>2026-09-11</x:v>
+        <x:v>09-10 10:00</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
         <x:v>6</x:v>
@@ -3153,66 +3181,66 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G21" s="11" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H21" s="11" t="str"/>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H21" s="11" t="n">
+        <x:v>65</x:v>
+      </x:c>
       <x:c r="I21" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J21" s="11" t="str"/>
       <x:c r="K21" s="11" t="str"/>
-      <x:c r="L21" s="10" t="str"/>
-      <x:c r="M21" s="10" t="str"/>
+      <x:c r="L21" s="10" t="str">
+        <x:v>锦书映年华</x:v>
+      </x:c>
+      <x:c r="M21" s="10" t="str">
+        <x:v>承平公主前世错恋齐远安，受尽磋磨含恨落幕。一朝重生，恰逢圣旨赐婚，齐远安却当众恳请解除婚约，求取太后义孙女傅明珠。她坦然放手，主动成全二人，看着他们得偿所愿。宁国侯夫人动用旧物强求赐婚，她巧妙改换婚事，选择边关归来、品性刚正的齐远舟。婚后她聪慧通透，看清傅明珠与齐远安的本性，冷眼旁观二人矛盾丛生。历经风波，她与齐远舟彼此扶持，挣脱过往伤痛，收获属于自己安稳坦荡的人生。</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>七套房产，换来一纸调令</x:v>
+        <x:v>回到零四年进军彩铃界</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>09-12 08:18</x:v>
+        <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G22" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H22" s="11" t="n">
-        <x:v>60</x:v>
-      </x:c>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="H22" s="11" t="str"/>
       <x:c r="I22" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J22" s="11" t="str"/>
       <x:c r="K22" s="11" t="str"/>
-      <x:c r="L22" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
-      </x:c>
-      <x:c r="M22" s="10" t="str">
-        <x:v>公婆将七套房产全数赠予小叔子，长子陈峰看似顺从鼓掌，实则暗中申请援疆调令。面对父母偏心和弟媳挑衅，陈峰携妻林晚隐忍筹备。最终在家庭会议上，他出示双人调令宣告远赴新疆，打破原生家庭剥削链条。经历异地磨砺与除夕和解，一家人终在理解中重建亲情边界，实现各自独立与成长。</x:v>
-      </x:c>
+      <x:c r="L22" s="10" t="str"/>
+      <x:c r="M22" s="10" t="str"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>青牛引泉来</x:v>
+        <x:v>泰城错嫁</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>09-11 15:20</x:v>
+        <x:v>09-12 21:10</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
         <x:v>5</x:v>
@@ -3221,10 +3249,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G23" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H23" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
         <x:v>其他</x:v>
@@ -3232,25 +3260,24 @@
       <x:c r="J23" s="11" t="str"/>
       <x:c r="K23" s="11" t="str"/>
       <x:c r="L23" s="10" t="str">
-        <x:v>车仔漫</x:v>
+        <x:v>夜草剧场</x:v>
       </x:c>
       <x:c r="M23" s="10" t="str">
-        <x:v>大旱之年，贫苦庄稼汉石满仓为宽慰盼他成家的母亲，扎了个稻草媳妇，谁料草人竟化作姑娘阿禾。原来阿禾是有灵性的青牛，十年前大旱濒死时被石满仓用豆秸和水救下，此番借稻草人身躯前来报恩。
-阿禾感知到村井即将枯竭，带领众人找到被封堵的牛眠岭古泉。靠卖自家井水牟利的马有财因利益受损，百般阻挠，甚至污染泉水、堵塞闸口。</x:v>
+        <x:v>二十世纪三十年代泰国，两姐妹姐妹同日嫁人，丑妹珠珠嫁帅气宋帕，美姐南佩却配憨汉啊光。迎亲途中大象突然发情，两对新人错上婚车、错入洞房。泼辣珠珠遇上憨厚啊光，闹洞房、斗婆婆，从互殴到相守；温柔南佩遇上冷脸宋帕，假装吵架赶走宾客，从陌生到动心。两对夫妻先后离婚，珠珠与啊光携手生子，南佩闯荡成舞台名角，与宋帕久别重逢。错的人成了对的人，两对冤家，各得圆满。</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="n">
-        <x:v>29</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>锦书迟</x:v>
+        <x:v>青牛引泉来</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>09-12 07:30</x:v>
+        <x:v>09-11 15:20</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
         <x:v>5</x:v>
@@ -3259,10 +3286,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G24" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H24" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="I24" s="10" t="str">
         <x:v>其他</x:v>
@@ -3270,21 +3297,22 @@
       <x:c r="J24" s="11" t="str"/>
       <x:c r="K24" s="11" t="str"/>
       <x:c r="L24" s="10" t="str">
-        <x:v>咩咩漫文</x:v>
+        <x:v>车仔漫</x:v>
       </x:c>
       <x:c r="M24" s="10" t="str">
-        <x:v>三年前，沈昭昭嫁与永宁侯谢凛，新婚燕尔他便远赴边关。她苦等家书，却不知双向书信早被人暗中截留。她终于心冷离开侯府。三年后，她带着孩子在市井支摊卖画立足，他却循着蛛丝马迹寻来，真相层层揭开，原来他从未负她。</x:v>
+        <x:v>大旱之年，贫苦庄稼汉石满仓为宽慰盼他成家的母亲，扎了个稻草媳妇，谁料草人竟化作姑娘阿禾。原来阿禾是有灵性的青牛，十年前大旱濒死时被石满仓用豆秸和水救下，此番借稻草人身躯前来报恩。
+阿禾感知到村井即将枯竭，带领众人找到被封堵的牛眠岭古泉。靠卖自家井水牟利的马有财因利益受损，百般阻挠，甚至污染泉水、堵塞闸口。</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="n">
-        <x:v>43</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>泰城错嫁</x:v>
+        <x:v>七套房产，换来一纸调令</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>09-12 21:10</x:v>
+        <x:v>09-12 08:18</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
         <x:v>4</x:v>
@@ -3296,10 +3324,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G25" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H25" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str">
         <x:v>其他</x:v>
@@ -3307,21 +3335,21 @@
       <x:c r="J25" s="11" t="str"/>
       <x:c r="K25" s="11" t="str"/>
       <x:c r="L25" s="10" t="str">
-        <x:v>夜草剧场</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="M25" s="10" t="str">
-        <x:v>二十世纪三十年代泰国，两姐妹姐妹同日嫁人，丑妹珠珠嫁帅气宋帕，美姐南佩却配憨汉啊光。迎亲途中大象突然发情，两对新人错上婚车、错入洞房。泼辣珠珠遇上憨厚啊光，闹洞房、斗婆婆，从互殴到相守；温柔南佩遇上冷脸宋帕，假装吵架赶走宾客，从陌生到动心。两对夫妻先后离婚，珠珠与啊光携手生子，南佩闯荡成舞台名角，与宋帕久别重逢。错的人成了对的人，两对冤家，各得圆满。</x:v>
+        <x:v>公婆将七套房产全数赠予小叔子，长子陈峰看似顺从鼓掌，实则暗中申请援疆调令。面对父母偏心和弟媳挑衅，陈峰携妻林晚隐忍筹备。最终在家庭会议上，他出示双人调令宣告远赴新疆，打破原生家庭剥削链条。经历异地磨砺与除夕和解，一家人终在理解中重建亲情边界，实现各自独立与成长。</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="n">
-        <x:v>44</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>重生山火前，我舍祖宅护全家</x:v>
+        <x:v>锦书迟</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
-        <x:v>09-12 16:06</x:v>
+        <x:v>09-12 07:30</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
         <x:v>4</x:v>
@@ -3333,10 +3361,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G26" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H26" s="11" t="n">
-        <x:v>89</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I26" s="10" t="str">
         <x:v>其他</x:v>
@@ -3344,21 +3372,21 @@
       <x:c r="J26" s="11" t="str"/>
       <x:c r="K26" s="11" t="str"/>
       <x:c r="L26" s="10" t="str">
-        <x:v>千鹤动漫</x:v>
+        <x:v>咩咩漫文</x:v>
       </x:c>
       <x:c r="M26" s="10" t="str">
-        <x:v>顾长河带着前世山火中痛失全家的记忆重生归来，得知三日后西岭大火将再次席卷村庄，他不顾众人质疑，卖掉祖宅，带着妻子母亲和儿子搬上白石坡，储水备粮清出防火带，只为改写一家人的命运，当烈火真正逼近，所有人终于明白，他舍掉的只是房子，拼命守住的才是真正的家。</x:v>
+        <x:v>三年前，沈昭昭嫁与永宁侯谢凛，新婚燕尔他便远赴边关。她苦等家书，却不知双向书信早被人暗中截留。她终于心冷离开侯府。三年后，她带着孩子在市井支摊卖画立足，他却循着蛛丝马迹寻来，真相层层揭开，原来他从未负她。</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="11" t="n">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>我送弟弟上青云</x:v>
+        <x:v>重生山火前，我舍祖宅护全家</x:v>
       </x:c>
       <x:c r="C27" s="11" t="str">
-        <x:v>09-12 09:52</x:v>
+        <x:v>09-12 16:06</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
         <x:v>4</x:v>
@@ -3370,10 +3398,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G27" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H27" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="I27" s="10" t="str">
         <x:v>其他</x:v>
@@ -3381,21 +3409,21 @@
       <x:c r="J27" s="11" t="str"/>
       <x:c r="K27" s="11" t="str"/>
       <x:c r="L27" s="10" t="str">
-        <x:v>落云</x:v>
+        <x:v>千鹤动漫</x:v>
       </x:c>
       <x:c r="M27" s="10" t="str">
-        <x:v>宋远回乡发现弟弟宋临被父亲剥夺上学权利，只能干农活。他毅然带走弟弟，用微薄工资供他读书。宋临考上名校建筑系，毕业后成为身价过亿的设计师。他用第一桶金给哥哥买房，报答当年恩情。面对迟来求和的父亲，宋临完成了心灵的真正和解。这是一个关于“长兄如父、手足情深”的故事，诠释了扶助与感恩的力量。</x:v>
+        <x:v>顾长河带着前世山火中痛失全家的记忆重生归来，得知三日后西岭大火将再次席卷村庄，他不顾众人质疑，卖掉祖宅，带着妻子母亲和儿子搬上白石坡，储水备粮清出防火带，只为改写一家人的命运，当烈火真正逼近，所有人终于明白，他舍掉的只是房子，拼命守住的才是真正的家。</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>今天开始做裴总</x:v>
+        <x:v>我送弟弟上青云</x:v>
       </x:c>
       <x:c r="C28" s="11" t="str">
-        <x:v>09-12 19:48</x:v>
+        <x:v>09-12 09:52</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
         <x:v>4</x:v>
@@ -3407,10 +3435,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G28" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H28" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I28" s="10" t="str">
         <x:v>其他</x:v>
@@ -3418,15 +3446,15 @@
       <x:c r="J28" s="11" t="str"/>
       <x:c r="K28" s="11" t="str"/>
       <x:c r="L28" s="10" t="str">
-        <x:v>严墨墨</x:v>
+        <x:v>落云</x:v>
       </x:c>
       <x:c r="M28" s="10" t="str">
-        <x:v>裴野低调蛰伏三年，甘愿扮作普通员工，在公司默默沉淀，面对职场非议、旁人轻视从未辩解。年会之上，他惨遭当众开除，相伴多年的婚姻也走向终点，跌入人生低谷。褪去伪装，他不再刻意隐忍，解锁真实身份，告别敷衍度日的过往。一路轻松逆袭，打破所有人的偏见，凭自身实力惊艳全场，开启属于自己的全新人生。</x:v>
+        <x:v>宋远回乡发现弟弟宋临被父亲剥夺上学权利，只能干农活。他毅然带走弟弟，用微薄工资供他读书。宋临考上名校建筑系，毕业后成为身价过亿的设计师。他用第一桶金给哥哥买房，报答当年恩情。面对迟来求和的父亲，宋临完成了心灵的真正和解。这是一个关于“长兄如父、手足情深”的故事，诠释了扶助与感恩的力量。</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
         <x:v>敢抢我的车位</x:v>
@@ -3463,7 +3491,7 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
         <x:v>退婚从抢我车位开始</x:v>
@@ -3494,16 +3522,16 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>重生1985年，赶海我有系统</x:v>
+        <x:v>今天开始做裴总</x:v>
       </x:c>
       <x:c r="C31" s="11" t="str">
-        <x:v>09-11 07:00</x:v>
+        <x:v>09-12 19:48</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
         <x:v>5</x:v>
@@ -3512,10 +3540,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G31" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H31" s="11" t="n">
-        <x:v>132</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I31" s="10" t="str">
         <x:v>其他</x:v>
@@ -3523,10 +3551,10 @@
       <x:c r="J31" s="11" t="str"/>
       <x:c r="K31" s="11" t="str"/>
       <x:c r="L31" s="10" t="str">
-        <x:v>依语动漫</x:v>
+        <x:v>严墨墨</x:v>
       </x:c>
       <x:c r="M31" s="10" t="str">
-        <x:v>八十年代小渔村，林舟出钱出力帮家里盖起红砖新房，落成之日却遭到父母兄长算计，新房被夺走，自己只分得被搬空的破旧老屋。带着前世被家人压榨到老的遗憾，重活一世的林舟不再愚孝，请来村长当众分家切割亲缘。绝境之中，他意外激活渔业情报系统，可以接收大海给出的渔获线索。他借得工具赶海，捞获珍贵大石斑鱼赚取第一笔启动资金，又约上好友李二狗大雾天冒险出海，依靠系统指引追逐鱼群。</x:v>
+        <x:v>裴野低调蛰伏三年，甘愿扮作普通员工，在公司默默沉淀，面对职场非议、旁人轻视从未辩解。年会之上，他惨遭当众开除，相伴多年的婚姻也走向终点，跌入人生低谷。褪去伪装，他不再刻意隐忍，解锁真实身份，告别敷衍度日的过往。一路轻松逆袭，打破所有人的偏见，凭自身实力惊艳全场，开启属于自己的全新人生。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3581,16 +3609,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
-        <x:v>4.9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F2" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>2026-09-16 03-11</x:v>
+        <x:v>2026-09-16 04-21</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3604,16 +3632,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
-        <x:v>6.2</x:v>
+        <x:v>6.7</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F3" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>2026-09-16 03-11</x:v>
+        <x:v>2026-09-16 04-21</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -3627,16 +3655,16 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>10.5</x:v>
+        <x:v>10.8</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F4" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>2026-09-16 03-11</x:v>
+        <x:v>2026-09-16 04-21</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3650,16 +3678,16 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>6.2</x:v>
+        <x:v>6.8</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F5" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>2026-09-16 03-11</x:v>
+        <x:v>2026-09-16 04-21</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -3670,7 +3698,7 @@
         <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
       </x:c>
       <x:c r="C6" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
         <x:v>7.3</x:v>
@@ -3682,7 +3710,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>2026-09-16 03-11</x:v>
+        <x:v>2026-09-16 04-21</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3693,7 +3721,7 @@
         <x:v>搬进江景房，老公每晚对着鱼缸坐两小时</x:v>
       </x:c>
       <x:c r="C7" s="11" t="n">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
         <x:v>6.7</x:v>
@@ -3702,10 +3730,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="F7" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>2026-09-16 03-11</x:v>
+        <x:v>2026-09-16 04-21</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -3713,22 +3741,22 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>重生三天前，我用水泥封死地下室</x:v>
+        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
       </x:c>
       <x:c r="C8" s="11" t="n">
         <x:v>24</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>12.2</x:v>
+        <x:v>12.9</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>2026-09-15 23-11</x:v>
+        <x:v>2026-09-16 04-21</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3736,22 +3764,22 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
+        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
       </x:c>
       <x:c r="C9" s="11" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>12.8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>2026-09-16 03-11</x:v>
+        <x:v>2026-09-16 04-21</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -3759,22 +3787,22 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
+        <x:v>重生三天前，我用水泥封死地下室</x:v>
       </x:c>
       <x:c r="C10" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>5.1</x:v>
+        <x:v>12.6</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F10" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>2026-09-16 03-11</x:v>
+        <x:v>2026-09-15 23-11</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -3782,22 +3810,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
+        <x:v>青牛引泉来</x:v>
       </x:c>
       <x:c r="C11" s="11" t="n">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>11.3</x:v>
+        <x:v>12.4</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
-        <x:v>2026-09-15 21-11</x:v>
+        <x:v>2026-09-16 04-21</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -3805,22 +3833,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>青牛引泉来</x:v>
+        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
       </x:c>
       <x:c r="C12" s="11" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>12.2</x:v>
+        <x:v>11.2</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G12" s="11" t="str">
-        <x:v>2026-09-15 23-11</x:v>
+        <x:v>2026-09-15 21-11</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -3831,7 +3859,7 @@
         <x:v>15年青春苦守，未婚夫装穷归来</x:v>
       </x:c>
       <x:c r="C13" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
         <x:v>1.9</x:v>
@@ -3843,7 +3871,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G13" s="11" t="str">
-        <x:v>2026-09-16 03-11</x:v>
+        <x:v>2026-09-16 04-21</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -3854,7 +3882,7 @@
         <x:v>重回82：我成山君契约万兽打猎宠妻</x:v>
       </x:c>
       <x:c r="C14" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
         <x:v>6.2</x:v>
@@ -3863,10 +3891,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G14" s="11" t="str">
-        <x:v>2026-09-16 03-11</x:v>
+        <x:v>2026-09-16 04-21</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -3877,7 +3905,7 @@
         <x:v>新厂旧账</x:v>
       </x:c>
       <x:c r="C15" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
         <x:v>8.9</x:v>
@@ -3886,10 +3914,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="F15" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G15" s="11" t="str">
-        <x:v>2026-09-16 03-11</x:v>
+        <x:v>2026-09-16 04-21</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -3900,10 +3928,10 @@
         <x:v>破库房的秘密</x:v>
       </x:c>
       <x:c r="C16" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>15.6</x:v>
+        <x:v>15.4</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
         <x:v>9</x:v>
@@ -3920,22 +3948,22 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>穿书后我带萌宝上门认爹</x:v>
+        <x:v>晚棠知归，七年终见你</x:v>
       </x:c>
       <x:c r="C17" s="11" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>14.9</x:v>
+        <x:v>4.8</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F17" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G17" s="11" t="str">
-        <x:v>2026-09-16 03-11</x:v>
+        <x:v>2026-09-16 04-21</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -3943,22 +3971,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>三分钱的取舍</x:v>
+        <x:v>重生80，救下神雕后我带村民走出大山</x:v>
       </x:c>
       <x:c r="C18" s="11" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>14.2</x:v>
+        <x:v>17.3</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G18" s="11" t="str">
-        <x:v>2026-09-15 18-11</x:v>
+        <x:v>2026-09-15 22-11</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -3966,22 +3994,22 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>一墙之隔，皆是人心</x:v>
+        <x:v>穿书后我带萌宝上门认爹</x:v>
       </x:c>
       <x:c r="C19" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>13.9</x:v>
+        <x:v>15.1</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G19" s="11" t="str">
-        <x:v>2026-09-15 20-11</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -3989,22 +4017,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>重生80，救下神雕后我带村民走出大山</x:v>
+        <x:v>三分钱的取舍</x:v>
       </x:c>
       <x:c r="C20" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>17.3</x:v>
+        <x:v>14.5</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G20" s="11" t="str">
-        <x:v>2026-09-15 22-11</x:v>
+        <x:v>2026-09-15 18-11</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -4012,22 +4040,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>晚棠知归，七年终见你</x:v>
+        <x:v>一墙之隔，皆是人心</x:v>
       </x:c>
       <x:c r="C21" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>13.5</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G21" s="11" t="str">
-        <x:v>2026-09-16 03-11</x:v>
+        <x:v>2026-09-15 20-11</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -4104,22 +4132,22 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>不靠谱爸妈很靠谱</x:v>
+        <x:v>因为大黄遇见你</x:v>
       </x:c>
       <x:c r="C25" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>14.4</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G25" s="11" t="str">
-        <x:v>2026-09-15 11-11</x:v>
+        <x:v>2026-09-16 04-21</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -4127,22 +4155,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
+        <x:v>不靠谱爸妈很靠谱</x:v>
       </x:c>
       <x:c r="C26" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>16.1</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G26" s="11" t="str">
-        <x:v>2026-09-15 10-11</x:v>
+        <x:v>2026-09-15 11-11</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -4150,22 +4178,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>泰城错嫁</x:v>
+        <x:v>四个崽崽瞒不住了</x:v>
       </x:c>
       <x:c r="C27" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>15.9</x:v>
+        <x:v>16.1</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str">
-        <x:v>2026-09-15 09-53</x:v>
+        <x:v>2026-09-15 10-11</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -4173,22 +4201,22 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>一盒印泥引发的全局封锁</x:v>
+        <x:v>泰城错嫁</x:v>
       </x:c>
       <x:c r="C28" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
-        <x:v>16.4</x:v>
+        <x:v>15.6</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F28" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G28" s="11" t="str">
-        <x:v>2026-09-15 21-11</x:v>
+        <x:v>2026-09-16 04-21</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -4196,22 +4224,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>因为大黄遇见你</x:v>
+        <x:v>一盒印泥引发的全局封锁</x:v>
       </x:c>
       <x:c r="C29" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>14.7</x:v>
+        <x:v>16.4</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str">
-        <x:v>2026-09-16 03-11</x:v>
+        <x:v>2026-09-15 21-11</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -4219,22 +4247,22 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>退婚后我在七零赚钱养家致富</x:v>
+        <x:v>八零悍妇：女汉子逆袭记</x:v>
       </x:c>
       <x:c r="C30" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>17.5</x:v>
+        <x:v>10.8</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G30" s="11" t="str">
-        <x:v>2026-09-15 10-11</x:v>
+        <x:v>2026-09-15 15-11</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -4242,22 +4270,22 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>八零悍妇：女汉子逆袭记</x:v>
+        <x:v>大坝边寻回的真千金</x:v>
       </x:c>
       <x:c r="C31" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
-        <x:v>10.8</x:v>
+        <x:v>12.8</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G31" s="11" t="str">
-        <x:v>2026-09-15 15-11</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -4265,22 +4293,22 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="10" t="str">
-        <x:v>大坝边寻回的真千金</x:v>
+        <x:v>穿越60我有空间不愁吃喝</x:v>
       </x:c>
       <x:c r="C32" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D32" s="11" t="n">
-        <x:v>12.8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G32" s="11" t="str">
-        <x:v>2026-09-16 03-11</x:v>
+        <x:v>2026-09-16 04-21</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -4288,22 +4316,22 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="10" t="str">
-        <x:v>今天开始做裴总</x:v>
+        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
       </x:c>
       <x:c r="C33" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D33" s="11" t="n">
-        <x:v>7.5</x:v>
+        <x:v>16.6</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F33" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="G33" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-16 04-21</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -4311,22 +4339,22 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="10" t="str">
-        <x:v>离婚那天我多了个痞帅老爹</x:v>
+        <x:v>退婚后我在七零赚钱养家致富</x:v>
       </x:c>
       <x:c r="C34" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D34" s="11" t="n">
-        <x:v>11.2</x:v>
+        <x:v>17.2</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F34" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G34" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-15 10-11</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -4334,22 +4362,22 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="10" t="str">
-        <x:v>闪婚老公有点野</x:v>
+        <x:v>今天开始做裴总</x:v>
       </x:c>
       <x:c r="C35" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D35" s="11" t="n">
-        <x:v>14.2</x:v>
+        <x:v>7.5</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F35" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G35" s="11" t="str">
-        <x:v>2026-09-15 06-54</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -4357,22 +4385,22 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="10" t="str">
-        <x:v>穿越60我有空间不愁吃喝</x:v>
+        <x:v>离婚那天我多了个痞帅老爹</x:v>
       </x:c>
       <x:c r="C36" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
-        <x:v>16.5</x:v>
+        <x:v>11.2</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G36" s="11" t="str">
-        <x:v>2026-09-16 03-11</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -4403,22 +4431,22 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="10" t="str">
-        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
+        <x:v>辣媳进门，我给公婆撑腰</x:v>
       </x:c>
       <x:c r="C38" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D38" s="11" t="n">
-        <x:v>17.8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F38" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G38" s="11" t="str">
-        <x:v>2026-09-16 03-11</x:v>
+        <x:v>2026-09-15 06-08</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -4426,22 +4454,22 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="10" t="str">
-        <x:v>辣媳进门，我给公婆撑腰</x:v>
+        <x:v>我的游戏好友现实里全是大佬</x:v>
       </x:c>
       <x:c r="C39" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D39" s="11" t="n">
+        <x:v>4.7</x:v>
+      </x:c>
+      <x:c r="E39" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F39" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E39" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F39" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="G39" s="11" t="str">
-        <x:v>2026-09-15 06-08</x:v>
+        <x:v>2026-09-16 02-11</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -4449,22 +4477,22 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="10" t="str">
-        <x:v>我的游戏好友现实里全是大佬</x:v>
+        <x:v>攻略失败后我不装了</x:v>
       </x:c>
       <x:c r="C40" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D40" s="11" t="n">
-        <x:v>4.7</x:v>
+        <x:v>9.3</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G40" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-16 01-11</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -4472,22 +4500,22 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="10" t="str">
-        <x:v>攻略失败后我不装了</x:v>
+        <x:v>傅少你夫人又在扮猪吃虎了</x:v>
       </x:c>
       <x:c r="C41" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D41" s="11" t="n">
-        <x:v>9.3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E41" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F41" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G41" s="11" t="str">
-        <x:v>2026-09-16 01-11</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -4495,22 +4523,22 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B42" s="10" t="str">
-        <x:v>傅少你夫人又在扮猪吃虎了</x:v>
+        <x:v>红烛错缘，另寻良人</x:v>
       </x:c>
       <x:c r="C42" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D42" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>10.7</x:v>
       </x:c>
       <x:c r="E42" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F42" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="G42" s="11" t="str">
-        <x:v>2026-09-16 03-11</x:v>
+        <x:v>2026-09-16 02-11</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -4518,22 +4546,22 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" s="10" t="str">
-        <x:v>红烛错缘，另寻良人</x:v>
+        <x:v>拂衣震九州</x:v>
       </x:c>
       <x:c r="C43" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D43" s="11" t="n">
-        <x:v>10.7</x:v>
+        <x:v>10.3</x:v>
       </x:c>
       <x:c r="E43" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F43" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G43" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -4541,22 +4569,22 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="10" t="str">
-        <x:v>拂衣震九州</x:v>
+        <x:v>闪婚老公有点野</x:v>
       </x:c>
       <x:c r="C44" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D44" s="11" t="n">
-        <x:v>10.3</x:v>
+        <x:v>16.3</x:v>
       </x:c>
       <x:c r="E44" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F44" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G44" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-15 06-54</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -4564,22 +4592,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="10" t="str">
-        <x:v>锦书迟</x:v>
+        <x:v>山下是绝路，山上是生门</x:v>
       </x:c>
       <x:c r="C45" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D45" s="11" t="n">
-        <x:v>13.3</x:v>
+        <x:v>14.3</x:v>
       </x:c>
       <x:c r="E45" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F45" s="11" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="G45" s="11" t="str">
-        <x:v>2026-09-15 02-44</x:v>
+        <x:v>2026-09-15 03-38</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -4587,22 +4615,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B46" s="10" t="str">
-        <x:v>山下是绝路，山上是生门</x:v>
+        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
       </x:c>
       <x:c r="C46" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D46" s="11" t="n">
-        <x:v>14.3</x:v>
+        <x:v>17.7</x:v>
       </x:c>
       <x:c r="E46" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F46" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G46" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-15 06-08</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -4610,22 +4638,22 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B47" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
+        <x:v>被诬陷诊出喜脉，重活一世我逆转前尘</x:v>
       </x:c>
       <x:c r="C47" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D47" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E47" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D47" s="11" t="n">
-        <x:v>17.7</x:v>
-      </x:c>
-      <x:c r="E47" s="11" t="n">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="F47" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G47" s="11" t="str">
-        <x:v>2026-09-15 06-08</x:v>
+        <x:v>2026-09-16 04-21</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -4633,22 +4661,22 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B48" s="10" t="str">
-        <x:v>重回千禧年，赶海捡出万贯家财</x:v>
+        <x:v>小福星驾到，通通闪开第一季</x:v>
       </x:c>
       <x:c r="C48" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D48" s="11" t="n">
-        <x:v>11.5</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="E48" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F48" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G48" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-16 01-11</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -4656,22 +4684,22 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B49" s="10" t="str">
-        <x:v>我SSS级狂龙，出世即无敌</x:v>
+        <x:v>家有新章</x:v>
       </x:c>
       <x:c r="C49" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D49" s="11" t="n">
-        <x:v>5.5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E49" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F49" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G49" s="11" t="str">
-        <x:v>2026-09-15 01-59</x:v>
+        <x:v>2026-09-15 23-11</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -4679,22 +4707,22 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B50" s="10" t="str">
-        <x:v>小福星驾到，通通闪开第一季</x:v>
+        <x:v>假老板娘遇上真董事长</x:v>
       </x:c>
       <x:c r="C50" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D50" s="11" t="n">
-        <x:v>8.5</x:v>
+        <x:v>12.5</x:v>
       </x:c>
       <x:c r="E50" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="F50" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G50" s="11" t="str">
-        <x:v>2026-09-16 01-11</x:v>
+        <x:v>2026-09-15 02-44</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -4702,22 +4730,22 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B51" s="10" t="str">
-        <x:v>家有新章</x:v>
+        <x:v>被女神抛弃：我却在荒岛吃香喝辣</x:v>
       </x:c>
       <x:c r="C51" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D51" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E51" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F51" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G51" s="11" t="str">
-        <x:v>2026-09-15 23-11</x:v>
+        <x:v>2026-09-15 12-43</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -18631,7 +18659,7 @@
         <x:v>一次针孔摄像头的意外发现，撬开了一场长达三年半的骗局。副院长手握年轻医生的排班、名额、前程，把“帮忙”变成了拿捏；一个母亲用一场“演出”护着儿子的秘密；一个新人医生，认错了恩人整整三年半。当所有人都以为真相已经水落石出，一句“谁说没证据”，才是这场博弈真正的开始。</x:v>
       </x:c>
       <x:c r="K8" s="10" t="str">
-        <x:v>发布账号「星漫动漫剧场」稳定产出（上榜25次/出过5部），账号基础分；题材契合爆款主线×2（剧名/分类/简介三路识别）；70集，主力长度</x:v>
+        <x:v>发布账号「星漫动漫剧场」稳定产出（上榜26次/出过5部），账号基础分；题材契合爆款主线×2（剧名/分类/简介三路识别）；70集，主力长度</x:v>
       </x:c>
       <x:c r="L8" s="11" t="n">
         <x:v>9</x:v>
@@ -19069,7 +19097,7 @@
         <x:v>林海洋为救女向家人求助遭拒，绝望中溺亡并重生回1991年。激活赶海系统后，他利用每日高价值海货指引，誓要改变命运。面对母亲和弟弟的无理索取，林海洋坚决断亲止损，专心呵护孕妻。凭借系统助力与敏锐眼光，他在海边捕获珍稀海产，逐步积累财富，守护小家幸福。</x:v>
       </x:c>
       <x:c r="K21" s="10" t="str">
-        <x:v>发布账号「星漫动漫剧场」稳定产出（上榜25次/出过5部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；100集，主力长度；剧名钩子×1</x:v>
+        <x:v>发布账号「星漫动漫剧场」稳定产出（上榜26次/出过5部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；100集，主力长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="L21" s="11" t="n">
         <x:v>13</x:v>
@@ -19171,7 +19199,7 @@
         <x:v>叶廷车祸意外获得透视异能，在古玩店低价购入藏有珍稀古币的残破佛像，转手获利百万。随后他转战原石街，凭借异能识破废料表象，接连赌出高价值翡翠，与商界女强人林雅茹达成合作。面对反派韩泽宇的挑衅与巨额赌局，叶廷从容应对，最终切出极品红翡，彻底击败对手，实现财富与地位的双重逆袭。</x:v>
       </x:c>
       <x:c r="K24" s="10" t="str">
-        <x:v>发布账号「星漫动漫剧场」稳定产出（上榜25次/出过5部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；171集，长度需关注；剧名钩子×1</x:v>
+        <x:v>发布账号「星漫动漫剧场」稳定产出（上榜26次/出过5部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；171集，长度需关注；剧名钩子×1</x:v>
       </x:c>
       <x:c r="L24" s="11" t="n">
         <x:v>10</x:v>
@@ -19205,7 +19233,7 @@
         <x:v>大柳村青年叶晨生带回洋女友阿米拉，遭村民与前女友嘲讽。他表面是普通业务员，实则身怀绝技。阿米拉看似天真，实为沙特公主。随着县领导登门拜访及中东代表团将至，叶晨生隐藏的身份与阿米拉的皇室背景逐渐浮出水面，两人携手应对各方势力挑战。</x:v>
       </x:c>
       <x:c r="K25" s="10" t="str">
-        <x:v>发布账号「星漫动漫剧场」稳定产出（上榜25次/出过5部），账号基础分；题材契合爆款主线×2（剧名/分类/简介三路识别）；81集，主力长度；通用受众</x:v>
+        <x:v>发布账号「星漫动漫剧场」稳定产出（上榜26次/出过5部），账号基础分；题材契合爆款主线×2（剧名/分类/简介三路识别）；81集，主力长度；通用受众</x:v>
       </x:c>
       <x:c r="L25" s="11" t="n">
         <x:v>9.5</x:v>
@@ -19239,7 +19267,7 @@
         <x:v>1997年，钳工陈景明为争口气，挪用买冰箱的九百元买入被嘲笑的“垃圾股”。随后他遗忘密码与交割单，以为资产归零。十余年后，证券商通知销户，陈景明意外发现股票经重组已价值百万。面对昔日仇人的陷害与高利贷威胁，他凭借法律手段追回清白，并以德报怨化解恩怨，最终实现人生逆袭。</x:v>
       </x:c>
       <x:c r="K26" s="10" t="str">
-        <x:v>发布账号「星漫动漫剧场」稳定产出（上榜25次/出过5部），账号基础分；题材契合爆款主线×1（剧名/分类/简介三路识别）；简介爽点词×1；100集，主力长度</x:v>
+        <x:v>发布账号「星漫动漫剧场」稳定产出（上榜26次/出过5部），账号基础分；题材契合爆款主线×1（剧名/分类/简介三路识别）；简介爽点词×1；100集，主力长度</x:v>
       </x:c>
       <x:c r="L26" s="11" t="n">
         <x:v>9</x:v>
@@ -19273,7 +19301,7 @@
         <x:v>网络安全工程师陈东明因抵御黑客攻击累倒，醒来却遭副总监孙振邦以旷工为由处罚。陈东明未作争辩，而是依据员工手册对孙振邦的管理行为进行合规审查。他通过调取日志与单据，揭露对方虚报加班及违规操作导致安全漏洞的事实，最终借助审计力量使真相大白，维护了职场公平与正义。</x:v>
       </x:c>
       <x:c r="K27" s="10" t="str">
-        <x:v>发布账号「星漫动漫剧场」稳定产出（上榜25次/出过5部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；54集，次优长度</x:v>
+        <x:v>发布账号「星漫动漫剧场」稳定产出（上榜26次/出过5部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；54集，次优长度</x:v>
       </x:c>
       <x:c r="L27" s="11" t="n">
         <x:v>9</x:v>
@@ -19341,7 +19369,7 @@
         <x:v>陈江河在分红大会上遭姐夫赵洪涛羞辱，愤而退出赵氏水产。他接手贾金福的废弃虾塘，凭借精湛技术扭转局面，推出高品质清水虾。面对赵洪涛的恶意竞争与官方收编诱惑，陈江河坚守初心，带领村民成立互助社，实现共同富裕，最终收获事业与爱情。</x:v>
       </x:c>
       <x:c r="K29" s="10" t="str">
-        <x:v>发布账号「星漫动漫剧场」稳定产出（上榜25次/出过5部），账号基础分；题材契合爆款主线×2（剧名/分类/简介三路识别）；124集，次优长度；剧名钩子×1</x:v>
+        <x:v>发布账号「星漫动漫剧场」稳定产出（上榜26次/出过5部），账号基础分；题材契合爆款主线×2（剧名/分类/简介三路识别）；124集，次优长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="L29" s="11" t="n">
         <x:v>9</x:v>
@@ -19375,7 +19403,7 @@
         <x:v>澜城妇产医院唯一男产科医生钟叙白，因护工邢奎恶意剪辑视频造谣，被院方停职。面对不公，他未做无谓争辩，而是冷静收集证据。随着患者与网友协助澄清真相，监控录屏证实清白。最终钟叙白拒绝原单位挽留，选择离职前往新医院，以专业能力赢得尊重，实现自我价值。</x:v>
       </x:c>
       <x:c r="K30" s="10" t="str">
-        <x:v>发布账号「星漫动漫剧场」稳定产出（上榜25次/出过5部），账号基础分；题材契合爆款主线×2（剧名/分类/简介三路识别）；81集，主力长度</x:v>
+        <x:v>发布账号「星漫动漫剧场」稳定产出（上榜26次/出过5部），账号基础分；题材契合爆款主线×2（剧名/分类/简介三路识别）；81集，主力长度</x:v>
       </x:c>
       <x:c r="L30" s="11" t="n">
         <x:v>9</x:v>
@@ -30754,10 +30782,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>978</x:v>
+        <x:v>981</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>53.9%</x:v>
+        <x:v>54.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -30768,7 +30796,7 @@
         <x:v>482</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>26.6%</x:v>
+        <x:v>26.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -30779,7 +30807,7 @@
         <x:v>355</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>19.6%</x:v>
+        <x:v>19.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
@@ -30814,10 +30842,10 @@
         <x:v>50-79集</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>712</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>42.9%</x:v>
+        <x:v>42.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -30836,10 +30864,10 @@
         <x:v>100集以上</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>552</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>33.2%</x:v>
+        <x:v>33.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
@@ -30863,10 +30891,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>804</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>44.3%</x:v>
+        <x:v>44.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -30899,7 +30927,7 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>8.8%</x:v>
+        <x:v>8.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -31022,15 +31050,15 @@
         <x:v>上榜26次</x:v>
       </x:c>
       <x:c r="B32" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C32" s="11" t="str">
-        <x:v>0.1%</x:v>
+        <x:v>0.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="10" t="str">
-        <x:v>上榜25次</x:v>
+        <x:v>上榜23次</x:v>
       </x:c>
       <x:c r="B33" s="11" t="n">
         <x:v>1</x:v>
@@ -31041,21 +31069,21 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="10" t="str">
-        <x:v>上榜23次</x:v>
+        <x:v>上榜22次</x:v>
       </x:c>
       <x:c r="B34" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C34" s="11" t="str">
-        <x:v>0.1%</x:v>
+        <x:v>0.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="10" t="str">
-        <x:v>上榜22次</x:v>
+        <x:v>上榜21次</x:v>
       </x:c>
       <x:c r="B35" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C35" s="11" t="str">
         <x:v>0.1%</x:v>
@@ -31063,84 +31091,84 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="10" t="str">
-        <x:v>上榜21次</x:v>
+        <x:v>上榜20次</x:v>
       </x:c>
       <x:c r="B36" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C36" s="11" t="str">
-        <x:v>0.1%</x:v>
+        <x:v>0.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="10" t="str">
-        <x:v>上榜20次</x:v>
+        <x:v>上榜19次</x:v>
       </x:c>
       <x:c r="B37" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C37" s="11" t="str">
-        <x:v>0.1%</x:v>
+        <x:v>0.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="10" t="str">
-        <x:v>上榜19次</x:v>
+        <x:v>上榜18次</x:v>
       </x:c>
       <x:c r="B38" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C38" s="11" t="str">
-        <x:v>0.2%</x:v>
+        <x:v>0.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="10" t="str">
-        <x:v>上榜18次</x:v>
+        <x:v>上榜17次</x:v>
       </x:c>
       <x:c r="B39" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C39" s="11" t="str">
-        <x:v>0.1%</x:v>
+        <x:v>0.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="10" t="str">
-        <x:v>上榜17次</x:v>
+        <x:v>上榜16次</x:v>
       </x:c>
       <x:c r="B40" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C40" s="11" t="str">
-        <x:v>0.2%</x:v>
+        <x:v>0.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="10" t="str">
-        <x:v>上榜16次</x:v>
+        <x:v>上榜15次</x:v>
       </x:c>
       <x:c r="B41" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C41" s="11" t="str">
-        <x:v>0.3%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="10" t="str">
-        <x:v>上榜15次</x:v>
+        <x:v>上榜14次</x:v>
       </x:c>
       <x:c r="B42" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C42" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="10" t="str">
-        <x:v>上榜14次</x:v>
+        <x:v>上榜13次</x:v>
       </x:c>
       <x:c r="B43" s="11" t="n">
         <x:v>13</x:v>
@@ -31151,7 +31179,7 @@
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="10" t="str">
-        <x:v>上榜13次</x:v>
+        <x:v>上榜12次</x:v>
       </x:c>
       <x:c r="B44" s="11" t="n">
         <x:v>13</x:v>
@@ -31162,248 +31190,248 @@
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="10" t="str">
-        <x:v>上榜12次</x:v>
+        <x:v>上榜11次</x:v>
       </x:c>
       <x:c r="B45" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C45" s="11" t="str">
-        <x:v>0.7%</x:v>
+        <x:v>0.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="10" t="str">
-        <x:v>上榜11次</x:v>
+        <x:v>上榜10次</x:v>
       </x:c>
       <x:c r="B46" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C46" s="11" t="str">
-        <x:v>0.8%</x:v>
+        <x:v>1.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="10" t="str">
-        <x:v>上榜10次</x:v>
+        <x:v>上榜9次</x:v>
       </x:c>
       <x:c r="B47" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C47" s="11" t="str">
-        <x:v>1.3%</x:v>
+        <x:v>1.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="10" t="str">
-        <x:v>上榜9次</x:v>
+        <x:v>上榜8次</x:v>
       </x:c>
       <x:c r="B48" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C48" s="11" t="str">
-        <x:v>1.7%</x:v>
+        <x:v>2.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="10" t="str">
-        <x:v>上榜8次</x:v>
+        <x:v>上榜7次</x:v>
       </x:c>
       <x:c r="B49" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C49" s="11" t="str">
-        <x:v>2.6%</x:v>
+        <x:v>2.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="10" t="str">
-        <x:v>上榜7次</x:v>
+        <x:v>上榜6次</x:v>
       </x:c>
       <x:c r="B50" s="11" t="n">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C50" s="11" t="str">
-        <x:v>2.0%</x:v>
+        <x:v>3.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="10" t="str">
-        <x:v>上榜6次</x:v>
+        <x:v>上榜5次</x:v>
       </x:c>
       <x:c r="B51" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C51" s="11" t="str">
-        <x:v>3.4%</x:v>
+        <x:v>4.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="10" t="str">
-        <x:v>上榜5次</x:v>
+        <x:v>上榜4次</x:v>
       </x:c>
       <x:c r="B52" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C52" s="11" t="str">
-        <x:v>4.5%</x:v>
+        <x:v>5.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="10" t="str">
-        <x:v>上榜4次</x:v>
+        <x:v>上榜3次</x:v>
       </x:c>
       <x:c r="B53" s="11" t="n">
-        <x:v>105</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C53" s="11" t="str">
-        <x:v>5.8%</x:v>
+        <x:v>11.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="10" t="str">
-        <x:v>上榜3次</x:v>
+        <x:v>上榜2次</x:v>
       </x:c>
       <x:c r="B54" s="11" t="n">
-        <x:v>200</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C54" s="11" t="str">
-        <x:v>11.0%</x:v>
+        <x:v>18.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="10" t="str">
-        <x:v>上榜2次</x:v>
+        <x:v>上榜1次</x:v>
       </x:c>
       <x:c r="B55" s="11" t="n">
-        <x:v>335</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="C55" s="11" t="str">
-        <x:v>18.5%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56">
-      <x:c r="A56" s="10" t="str">
-        <x:v>上榜1次</x:v>
-      </x:c>
-      <x:c r="B56" s="11" t="n">
-        <x:v>802</x:v>
-      </x:c>
-      <x:c r="C56" s="11" t="str">
         <x:v>44.2%</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="22" customHeight="1">
-      <x:c r="A58" s="14" t="str">
+    <x:row r="57" ht="22" customHeight="1">
+      <x:c r="A57" s="14" t="str">
         <x:v>版权类型分布</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" ht="24" customHeight="1">
-      <x:c r="A59" s="5" t="str">
+    <x:row r="58" ht="24" customHeight="1">
+      <x:c r="A58" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B59" t="str">
+      <x:c r="B58" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C59" t="str">
+      <x:c r="C58" t="str">
         <x:v>占比</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="10" t="str">
+        <x:v>CP自营</x:v>
+      </x:c>
+      <x:c r="B59" s="11" t="n">
+        <x:v>1169</x:v>
+      </x:c>
+      <x:c r="C59" s="11" t="str">
+        <x:v>64.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="10" t="str">
-        <x:v>CP自营</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="B60" s="11" t="n">
-        <x:v>1169</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="C60" s="11" t="str">
-        <x:v>64.4%</x:v>
+        <x:v>35.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>CP托管</x:v>
       </x:c>
       <x:c r="B61" s="11" t="n">
-        <x:v>633</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C61" s="11" t="str">
-        <x:v>34.9%</x:v>
+        <x:v>0.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="10" t="str">
-        <x:v>CP托管</x:v>
+        <x:v>番茄原创</x:v>
       </x:c>
       <x:c r="B62" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C62" s="11" t="str">
-        <x:v>0.6%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63">
-      <x:c r="A63" s="10" t="str">
-        <x:v>番茄原创</x:v>
-      </x:c>
-      <x:c r="B63" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C63" s="11" t="str">
         <x:v>0.1%</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" ht="22" customHeight="1">
-      <x:c r="A65" s="14" t="str">
+    <x:row r="64" ht="22" customHeight="1">
+      <x:c r="A64" s="14" t="str">
         <x:v>发布抖音号TOP15·上榜次数</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" ht="24" customHeight="1">
-      <x:c r="A66" s="5" t="str">
+    <x:row r="65" ht="24" customHeight="1">
+      <x:c r="A65" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B66" t="str">
+      <x:c r="B65" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C66" t="str">
+      <x:c r="C65" t="str">
         <x:v>占比</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="10" t="str">
+        <x:v>孤灵剧场</x:v>
+      </x:c>
+      <x:c r="B66" s="11" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C66" s="11" t="str">
+        <x:v>1.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
+        <x:v>番荔枝剧场</x:v>
       </x:c>
       <x:c r="B67" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C67" s="11" t="str">
-        <x:v>1.1%</x:v>
+        <x:v>1%</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="10" t="str">
-        <x:v>番荔枝剧场</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="B68" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C68" s="11" t="str">
-        <x:v>1%</x:v>
+        <x:v>0.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="B69" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C69" s="11" t="str">
-        <x:v>0.9%</x:v>
+        <x:v>0.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="10" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="B70" s="11" t="n">
         <x:v>45</x:v>
@@ -31414,10 +31442,10 @@
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>渲渲动画</x:v>
       </x:c>
       <x:c r="B71" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C71" s="11" t="str">
         <x:v>0.8%</x:v>
@@ -31425,18 +31453,18 @@
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="10" t="str">
-        <x:v>渲渲动画</x:v>
+        <x:v>左手良画</x:v>
       </x:c>
       <x:c r="B72" s="11" t="n">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C72" s="11" t="str">
-        <x:v>0.8%</x:v>
+        <x:v>0.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="10" t="str">
-        <x:v>左手良画</x:v>
+        <x:v>阅友动漫</x:v>
       </x:c>
       <x:c r="B73" s="11" t="n">
         <x:v>36</x:v>
@@ -31447,10 +31475,10 @@
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="10" t="str">
-        <x:v>阅友动漫</x:v>
+        <x:v>东山啊</x:v>
       </x:c>
       <x:c r="B74" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C74" s="11" t="str">
         <x:v>0.6%</x:v>
@@ -31458,21 +31486,21 @@
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="10" t="str">
-        <x:v>东山啊</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="B75" s="11" t="n">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C75" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="B76" s="11" t="n">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C76" s="11" t="str">
         <x:v>0.5%</x:v>
@@ -31480,10 +31508,10 @@
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>茉冉漫影</x:v>
       </x:c>
       <x:c r="B77" s="11" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C77" s="11" t="str">
         <x:v>0.5%</x:v>
@@ -31491,7 +31519,7 @@
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="10" t="str">
-        <x:v>茉冉漫影</x:v>
+        <x:v>在下轻北</x:v>
       </x:c>
       <x:c r="B78" s="11" t="n">
         <x:v>28</x:v>
@@ -31502,7 +31530,7 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="10" t="str">
-        <x:v>在下轻北</x:v>
+        <x:v>腿毛漫漫</x:v>
       </x:c>
       <x:c r="B79" s="11" t="n">
         <x:v>28</x:v>
@@ -31513,67 +31541,67 @@
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="10" t="str">
-        <x:v>腿毛漫漫</x:v>
+        <x:v>壹琚-娜娜看剧</x:v>
       </x:c>
       <x:c r="B80" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C80" s="11" t="str">
         <x:v>0.5%</x:v>
       </x:c>
     </x:row>
-    <x:row r="81">
-      <x:c r="A81" s="10" t="str">
-        <x:v>壹琚-娜娜看剧</x:v>
-      </x:c>
-      <x:c r="B81" s="11" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C81" s="11" t="str">
-        <x:v>0.5%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83" ht="22" customHeight="1">
-      <x:c r="A83" s="14" t="str">
+    <x:row r="82" ht="22" customHeight="1">
+      <x:c r="A82" s="14" t="str">
         <x:v>发布抖音号TOP15·上榜剧数</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="24" customHeight="1">
-      <x:c r="A84" s="5" t="str">
+    <x:row r="83" ht="24" customHeight="1">
+      <x:c r="A83" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B84" t="str">
+      <x:c r="B83" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C84" t="str">
+      <x:c r="C83" t="str">
         <x:v>占比</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="B84" s="11" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C84" s="11" t="str">
+        <x:v>1.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="B85" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C85" s="11" t="str">
-        <x:v>1.1%</x:v>
+        <x:v>0.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="B86" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C86" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="B87" s="11" t="n">
         <x:v>9</x:v>
@@ -31584,21 +31612,21 @@
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="10" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>星漫世界</x:v>
       </x:c>
       <x:c r="B88" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C88" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="10" t="str">
-        <x:v>星漫世界</x:v>
+        <x:v>番荔枝剧场</x:v>
       </x:c>
       <x:c r="B89" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C89" s="11" t="str">
         <x:v>0.4%</x:v>
@@ -31606,18 +31634,18 @@
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="10" t="str">
-        <x:v>番荔枝剧场</x:v>
+        <x:v>渲渲动画</x:v>
       </x:c>
       <x:c r="B90" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C90" s="11" t="str">
-        <x:v>0.4%</x:v>
+        <x:v>0.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="10" t="str">
-        <x:v>渲渲动画</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="B91" s="11" t="n">
         <x:v>6</x:v>
@@ -31628,7 +31656,7 @@
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>阅友动漫</x:v>
       </x:c>
       <x:c r="B92" s="11" t="n">
         <x:v>6</x:v>
@@ -31639,7 +31667,7 @@
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="10" t="str">
-        <x:v>阅友动漫</x:v>
+        <x:v>腿毛漫漫</x:v>
       </x:c>
       <x:c r="B93" s="11" t="n">
         <x:v>6</x:v>
@@ -31650,7 +31678,7 @@
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="10" t="str">
-        <x:v>腿毛漫漫</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="B94" s="11" t="n">
         <x:v>6</x:v>
@@ -31661,7 +31689,7 @@
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>至尊爽剧社</x:v>
       </x:c>
       <x:c r="B95" s="11" t="n">
         <x:v>6</x:v>
@@ -31672,7 +31700,7 @@
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="10" t="str">
-        <x:v>至尊爽剧社</x:v>
+        <x:v>潮汐互娱-爽剧社</x:v>
       </x:c>
       <x:c r="B96" s="11" t="n">
         <x:v>6</x:v>
@@ -31683,10 +31711,10 @@
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="10" t="str">
-        <x:v>潮汐互娱-爽剧社</x:v>
+        <x:v>星漫动漫剧场</x:v>
       </x:c>
       <x:c r="B97" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C97" s="11" t="str">
         <x:v>0.3%</x:v>
@@ -31694,7 +31722,7 @@
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="10" t="str">
-        <x:v>星漫动漫剧场</x:v>
+        <x:v>忆梦剧场</x:v>
       </x:c>
       <x:c r="B98" s="11" t="n">
         <x:v>5</x:v>
@@ -31703,91 +31731,91 @@
         <x:v>0.3%</x:v>
       </x:c>
     </x:row>
-    <x:row r="99">
-      <x:c r="A99" s="10" t="str">
-        <x:v>忆梦剧场</x:v>
-      </x:c>
-      <x:c r="B99" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C99" s="11" t="str">
-        <x:v>0.3%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101" ht="22" customHeight="1">
-      <x:c r="A101" s="14" t="str">
+    <x:row r="100" ht="22" customHeight="1">
+      <x:c r="A100" s="14" t="str">
         <x:v>付费榜主题分布</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" ht="24" customHeight="1">
-      <x:c r="A102" s="5" t="str">
+    <x:row r="101" ht="24" customHeight="1">
+      <x:c r="A101" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B102" t="str">
+      <x:c r="B101" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C102" t="str">
+      <x:c r="C101" t="str">
         <x:v>占比</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="10" t="str">
+        <x:v>婚姻/情感</x:v>
+      </x:c>
+      <x:c r="B102" s="11" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C102" s="11" t="str">
+        <x:v>19.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="10" t="str">
-        <x:v>婚姻/情感</x:v>
+        <x:v>家庭伦理/萌宝</x:v>
       </x:c>
       <x:c r="B103" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C103" s="11" t="str">
-        <x:v>19.0%</x:v>
+        <x:v>15.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="10" t="str">
-        <x:v>家庭伦理/萌宝</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="B104" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C104" s="11" t="str">
-        <x:v>15.0%</x:v>
+        <x:v>10.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="B105" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C105" s="11" t="str">
-        <x:v>10.0%</x:v>
+        <x:v>9.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>年代怀旧/种田</x:v>
       </x:c>
       <x:c r="B106" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C106" s="11" t="str">
-        <x:v>9.0%</x:v>
+        <x:v>7.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="10" t="str">
-        <x:v>年代怀旧/种田</x:v>
+        <x:v>现实反转/人性</x:v>
       </x:c>
       <x:c r="B107" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C107" s="11" t="str">
-        <x:v>7.0%</x:v>
+        <x:v>6.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="10" t="str">
-        <x:v>现实反转/人性</x:v>
+        <x:v>战神/异能</x:v>
       </x:c>
       <x:c r="B108" s="11" t="n">
         <x:v>6</x:v>
@@ -31798,23 +31826,12 @@
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="10" t="str">
-        <x:v>战神/异能</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="B109" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C109" s="11" t="str">
-        <x:v>6.0%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110">
-      <x:c r="A110" s="10" t="str">
-        <x:v>美食治愈</x:v>
-      </x:c>
-      <x:c r="B110" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C110" s="11" t="str">
         <x:v>5.0%</x:v>
       </x:c>
     </x:row>
@@ -31824,10 +31841,10 @@
     <x:mergeCell ref="A7:C7"/>
     <x:mergeCell ref="A14:C14"/>
     <x:mergeCell ref="A27:C27"/>
-    <x:mergeCell ref="A58:C58"/>
-    <x:mergeCell ref="A65:C65"/>
-    <x:mergeCell ref="A83:C83"/>
-    <x:mergeCell ref="A101:C101"/>
+    <x:mergeCell ref="A57:C57"/>
+    <x:mergeCell ref="A64:C64"/>
+    <x:mergeCell ref="A82:C82"/>
+    <x:mergeCell ref="A100:C100"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R9a59b25b47b442a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="Re643a316e6d3408e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="R8a7b9ab87fe24a6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="R8c87b68f00d14185"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP20剧重点跟踪" sheetId="5" r:id="R2f3c9630b9a646f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="6" r:id="Rb2cd9e5f4031475d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="7" r:id="R8203d6050ced4693"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="8" r:id="R85f28c0a0d114bec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="9" r:id="Rf2d64ccacb2f48c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="Re61c893443094aa9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="R341e8561f630474f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="Rb6bb9b81676947b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="R70e71fcc4158474d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP20剧重点跟踪" sheetId="5" r:id="Rc6f65eb3019b4217"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="6" r:id="R835319459af94cd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="7" r:id="Rb0bd4fcb70e74f73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="8" r:id="R2914aa5c2e354d8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="9" r:id="R322319c40efd40b9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -366,7 +366,7 @@
         <x:v>08-11 16:40</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E2" s="10" t="n">
         <x:v>82</x:v>
@@ -384,7 +384,7 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="J2" s="10" t="str">
-        <x:v>2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15</x:v>
+        <x:v>2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15、2026-09-16</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -424,31 +424,31 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>1977山猎重生，我以余生偿前错</x:v>
+        <x:v>县令哭穷五年，李世民进城懵了</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>08-10 20:00</x:v>
+        <x:v>06-29 17:30</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E4" s="10" t="n">
-        <x:v>375</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F4" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="G4" s="10" t="str">
-        <x:v>年代怀旧 / 种田囤货</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="H4" s="11" t="n">
-        <x:v>10183</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="I4" s="11" t="str">
-        <x:v>1.07</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="J4" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-13、2026-09-15</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15、2026-09-16</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -456,31 +456,31 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>县令哭穷五年，李世民进城懵了</x:v>
+        <x:v>1977山猎重生，我以余生偿前错</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>06-29 17:30</x:v>
+        <x:v>08-10 20:00</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E5" s="10" t="n">
-        <x:v>67</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="F5" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G5" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧 / 种田囤货</x:v>
       </x:c>
       <x:c r="H5" s="11" t="n">
-        <x:v>86</x:v>
+        <x:v>10183</x:v>
       </x:c>
       <x:c r="I5" s="11" t="str">
-        <x:v>0.78</x:v>
+        <x:v>1.07</x:v>
       </x:c>
       <x:c r="J5" s="10" t="str">
-        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15</x:v>
+        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-13、2026-09-15</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -988,27 +988,27 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>38元炒鸡风波</x:v>
+        <x:v>铺子空了，房东慌了</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>06-03 09:01</x:v>
+        <x:v>08-29 16:49</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E23" s="10" t="n">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F23" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G23" s="10" t="str">
-        <x:v>美食治愈 / 现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="H23" s="11" t="str"/>
       <x:c r="I23" s="11" t="str"/>
       <x:c r="J23" s="10" t="str">
-        <x:v>2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-09-03、2026-09-04、2026-09-05、2026-09-07、2026-09-09、2026-09-10、2026-09-11、2026-09-12</x:v>
+        <x:v>2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15、2026-09-16</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1016,27 +1016,27 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>精通婴语满朝权贵求我带娃</x:v>
+        <x:v>38元炒鸡风波</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>08-03 11:51</x:v>
+        <x:v>06-03 09:01</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E24" s="10" t="n">
-        <x:v>116</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F24" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="G24" s="10" t="str">
-        <x:v>萌宝治愈</x:v>
+        <x:v>美食治愈 / 现实反转</x:v>
       </x:c>
       <x:c r="H24" s="11" t="str"/>
       <x:c r="I24" s="11" t="str"/>
       <x:c r="J24" s="10" t="str">
-        <x:v>2026-08-20、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15</x:v>
+        <x:v>2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-09-03、2026-09-04、2026-09-05、2026-09-07、2026-09-09、2026-09-10、2026-09-11、2026-09-12</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1044,27 +1044,27 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>贪念散尽卤香</x:v>
+        <x:v>一瓶水，让我看清亲生女儿</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>08-24 08:26</x:v>
+        <x:v>08-23 10:00</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E25" s="10" t="n">
-        <x:v>41</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F25" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="G25" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="H25" s="11" t="str"/>
       <x:c r="I25" s="11" t="str"/>
       <x:c r="J25" s="10" t="str">
-        <x:v>2026-08-23、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-09、2026-09-12、2026-09-15</x:v>
+        <x:v>2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-15、2026-09-16</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1072,27 +1072,27 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>铺子空了，房东慌了</x:v>
+        <x:v>精通婴语满朝权贵求我带娃</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
-        <x:v>08-29 16:49</x:v>
+        <x:v>08-03 11:51</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E26" s="10" t="n">
-        <x:v>55</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F26" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="G26" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>萌宝治愈</x:v>
       </x:c>
       <x:c r="H26" s="11" t="str"/>
       <x:c r="I26" s="11" t="str"/>
       <x:c r="J26" s="10" t="str">
-        <x:v>2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15</x:v>
+        <x:v>2026-08-20、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1202,13 +1202,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
-        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
+        <x:v>被诬陷诊出喜脉，重活一世我逆转前尘</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>09-15 08:00</x:v>
+        <x:v>09-16 07:58</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str"/>
       <x:c r="F3" s="11" t="str"/>
@@ -1219,19 +1219,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I3" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K3" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L3" s="11" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="M3" s="10" t="str">
-        <x:v>沈清韵嫁入靖王府三年，王爷冷落，侧妃得宠。王爷当众许诺，谁先诞下儿子，便请封世子。苏氏先怀孕，沈清韵却发现自己怀的是龙凤胎，她隐瞒消息，买通太医推迟产期，忍痛让苏氏先产子。王爷果然请封庶长子为世子，折子递入宗人府。受理之后，沈清韵才发动，生下龙凤胎。太后与皇上视为祥瑞，下旨赐嫡子承恩为靖王世子、嫡女承华为安乐郡主。王爷措手不及，苏氏地位一落千丈。而沈清韵知道，这只是第一步。</x:v>
+        <x:v>沈清瑶重生回到被“神医”姜辞诬陷喜脉那天。前世她因此身败名裂，被迫嫁给竹马萧景渊，后来才知这是两人为替姜辞上位设的局。这一世，她不再任人宰割，巧妙将诊脉丝线系在谢老夫人腕上，当众揭穿姜辞。萧景渊谎称“孩子是我的”，却被她揭发与姜辞的私情，两人丑态毕露。谢家震怒，姜辞被强嫁萧景渊，沈清瑶嫁入侯府。婚后她冷静布局，让萧景渊与姜辞内斗升级。最终姜辞伏法，沈清瑶挣脱前世枷锁。可重生真能让她彻底自由吗？</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1239,13 +1239,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
-        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
+        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>09-15 08:30</x:v>
+        <x:v>09-15 08:00</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str"/>
       <x:c r="F4" s="11" t="str"/>
@@ -1256,19 +1256,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I4" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J4" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K4" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="L4" s="11" t="str">
-        <x:v>琥珀漫剧</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="M4" s="10" t="str">
-        <x:v>海鲜市场老手陈放，因一个两块钱的冰袋被十二年合伙人当众算旧账，心寒清账，净身出户。他没有抱怨，也没有以牙还牙，而是加入冷清档口“梅姐水产”，从零开始。他坚持明码标价、沥水称重、死活分卖、批次可查，宁可少接单，也不混货、不凑数、不赚亏心钱。面对低价抢客、恶意破坏、临时缺货等风波，他与叶梅靠诚信、规矩和彼此信任，一步步赢得客户与连锁企业的认可。</x:v>
+        <x:v>沈清韵嫁入靖王府三年，王爷冷落，侧妃得宠。王爷当众许诺，谁先诞下儿子，便请封世子。苏氏先怀孕，沈清韵却发现自己怀的是龙凤胎，她隐瞒消息，买通太医推迟产期，忍痛让苏氏先产子。王爷果然请封庶长子为世子，折子递入宗人府。受理之后，沈清韵才发动，生下龙凤胎。太后与皇上视为祥瑞，下旨赐嫡子承恩为靖王世子、嫡女承华为安乐郡主。王爷措手不及，苏氏地位一落千丈。而沈清韵知道，这只是第一步。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1276,7 +1276,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
         <x:v>我都元婴期了，你跟我说开学</x:v>
@@ -1313,13 +1313,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>我在工地卖盒饭带火一座城</x:v>
+        <x:v>重回雪崩泥石流，我不再犹豫</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>09-14 14:52</x:v>
+        <x:v>09-16 01:02</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str"/>
       <x:c r="F6" s="11" t="str"/>
@@ -1330,19 +1330,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I6" s="11" t="n">
-        <x:v>144</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J6" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K6" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="L6" s="11" t="str">
-        <x:v>左手良画</x:v>
+        <x:v>姜缘</x:v>
       </x:c>
       <x:c r="M6" s="10" t="str">
-        <x:v>小伙白叶遭遇老板跑路，半年工资付诸东流，意外被铁炒勺砸中觉醒超级餐饮系统。大雪封路堵车途中完成首份任务，靠着系统加持的厨艺，路边卖盒饭赚到第一桶金。回乡钻研秘制酱肉，赶集摆摊火爆出圈，还临危接手大型寿宴惊艳众人。过完新年，他怀揣梦想奔赴外地，准备开启属于自己的餐饮创业之路。</x:v>
+        <x:v>前世，周清雨因犹豫错失逃生时机，眼睁睁看着全家被雪崩泥石流吞没。重生回灾难前三天，她当机立断卖掉五十头牦牛，囤积物资，带家人撤往高处。面对全村嘲讽和阻拦，她不再苦劝。直到雪山崩塌、洪流封村，昔日笑她疯癫的人纷纷求上门。这一次，她只救值得救的人！</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1350,13 +1350,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
-        <x:v>一盒印泥引发的全局封锁</x:v>
+        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>09-15 08:30</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str"/>
       <x:c r="F7" s="11" t="str"/>
@@ -1366,28 +1366,34 @@
       <x:c r="H7" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="str"/>
+      <x:c r="I7" s="11" t="n">
+        <x:v>70</x:v>
+      </x:c>
       <x:c r="J7" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K7" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L7" s="11" t="str"/>
-      <x:c r="M7" s="10" t="str"/>
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="L7" s="11" t="str">
+        <x:v>琥珀漫剧</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="str">
+        <x:v>海鲜市场老手陈放，因一个两块钱的冰袋被十二年合伙人当众算旧账，心寒清账，净身出户。他没有抱怨，也没有以牙还牙，而是加入冷清档口“梅姐水产”，从零开始。他坚持明码标价、沥水称重、死活分卖、批次可查，宁可少接单，也不混货、不凑数、不赚亏心钱。面对低价抢客、恶意破坏、临时缺货等风波，他与叶梅靠诚信、规矩和彼此信任，一步步赢得客户与连锁企业的认可。</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
+        <x:v>我在工地卖盒饭带火一座城</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>09-15 00:08</x:v>
+        <x:v>09-14 14:52</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str"/>
       <x:c r="F8" s="11" t="str"/>
@@ -1398,19 +1404,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="J8" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K8" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="L8" s="11" t="str">
-        <x:v>桃子动漫剧场</x:v>
+        <x:v>左手良画</x:v>
       </x:c>
       <x:c r="M8" s="10" t="str">
-        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
+        <x:v>小伙白叶遭遇老板跑路，半年工资付诸东流，意外被铁炒勺砸中觉醒超级餐饮系统。大雪封路堵车途中完成首份任务，靠着系统加持的厨艺，路边卖盒饭赚到第一桶金。回乡钻研秘制酱肉，赶集摆摊火爆出圈，还临危接手大型寿宴惊艳众人。过完新年，他怀揣梦想奔赴外地，准备开启属于自己的餐饮创业之路。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1418,13 +1424,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
-        <x:v>攻略失败后我不装了</x:v>
+        <x:v>一盒印泥引发的全局封锁</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>09-15 15:00</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str"/>
       <x:c r="F9" s="11" t="str"/>
@@ -1434,34 +1440,28 @@
       <x:c r="H9" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I9" s="11" t="n">
-        <x:v>69</x:v>
-      </x:c>
+      <x:c r="I9" s="11" t="str"/>
       <x:c r="J9" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K9" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
-      </x:c>
-      <x:c r="L9" s="11" t="str">
-        <x:v>喵喵说漫</x:v>
-      </x:c>
-      <x:c r="M9" s="10" t="str">
-        <x:v>陆瑶做了百年攻略任务，反倒被系统判定为史上最废宿主，嘲讽她连宗门看门大黄都攻略不了，直接解绑。重获自由的她解开封印，觉醒万年难遇的天生道体。她撕碎弟子玉牌，决绝离开凌云峰，手握海量资源专心经商修炼。从前被她百般讨好的师尊师兄尽数落魄、满心悔意。她看淡情爱纠葛，收服大黄相伴，一路开挂逆袭，潇洒飞升开启全新仙生。</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L9" s="11" t="str"/>
+      <x:c r="M9" s="10" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
-        <x:v>高考刚结束父母就不装了</x:v>
+        <x:v>被身高掩盖的谎言</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>09-15 07:00</x:v>
+        <x:v>09-15 08:18</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str"/>
       <x:c r="F10" s="11" t="str"/>
@@ -1472,19 +1472,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I10" s="11" t="n">
-        <x:v>173</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J10" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K10" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="L10" s="11" t="str">
-        <x:v>千慕剧场</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="M10" s="10" t="str">
-        <x:v>高考结束那天，林寻在考场外被亲生父母认回原来十八年的普通生活，是父母为磨砺他而设的一场成长课。重回豪门，他没有迷失，反而在桥上遇见了那个让他心动的姑娘，南大冰山学姐苏清诗。从青涩的初次相遇，到演唱会上的合唱，再到大学校园里的朝夕相处，两个真诚的人慢慢靠近。曾经的求而不得终将释怀，双向奔赴的喜欢才最珍贵。褪去普通学生的身份，林寻只想以真心换真心。十八岁的夏天，最好的相遇，最甜的恋爱，才刚刚开始。</x:v>
+        <x:v>女孩林知晚回到命运转折的关键节点。她凭借智慧与勇气，敏锐察觉家中隐患，冷静引导家人、寻求帮助，用爱守护姐姐与全家。在共同努力下危机化解、正义伸张，一家人愈发珍视彼此，并且帮助到了更多有同样遭遇的人，最后迎来温暖安宁的幸福生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1492,13 +1492,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C11" s="10" t="str">
-        <x:v>被身高掩盖的谎言</x:v>
+        <x:v>重生极品婆婆，带全家发家致富！</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>09-15 08:18</x:v>
+        <x:v>09-14 20:29</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str"/>
       <x:c r="F11" s="11" t="str"/>
@@ -1509,19 +1509,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I11" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="J11" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K11" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>家庭伦理 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="L11" s="11" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>懒少爱我</x:v>
       </x:c>
       <x:c r="M11" s="10" t="str">
-        <x:v>女孩林知晚回到命运转折的关键节点。她凭借智慧与勇气，敏锐察觉家中隐患，冷静引导家人、寻求帮助，用爱守护姐姐与全家。在共同努力下危机化解、正义伸张，一家人愈发珍视彼此，并且帮助到了更多有同样遭遇的人，最后迎来温暖安宁的幸福生活。</x:v>
+        <x:v>寡妇傅兰秀前世一生吝啬守财，刻薄对待儿女儿媳，到头来钱财被贼人掠夺，落得个凄惨离世的下场。一朝重生，她回到悲剧尚未发生之时。痛定思痛，她彻底改掉抠门的性子，学着善待家里的晚辈。可日子并不太平，爱占便宜的亲戚总上门搅扰，家中两个儿媳也矛盾不断，家务是非接连找上门。傅兰秀靠着清醒的头脑，一边化解各类家庭纷争，一边寻找营生门路，努力扭转命运，拼尽全力守护一家人的安稳生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1529,13 +1529,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>99</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
-        <x:v>急诊摸鱼王2</x:v>
+        <x:v>高考刚结束父母就不装了</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>09-15 20:00</x:v>
+        <x:v>09-15 07:00</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str"/>
       <x:c r="F12" s="11" t="str"/>
@@ -1546,19 +1546,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I12" s="11" t="n">
-        <x:v>114</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="J12" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K12" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="L12" s="11" t="str">
-        <x:v>阿部漫剧</x:v>
+        <x:v>千慕剧场</x:v>
       </x:c>
       <x:c r="M12" s="10" t="str">
-        <x:v>大佬贺知舟伪装咸鱼住院医，在急诊科继续摸鱼。院内急救考核到来，贺知舟笔试满分，实操手法惊艳一众同事。普外、麻醉科主任从特殊手术技巧，怀疑他就是消失的国际传奇DrZ。宿敌沈长风的势力不断逼近，旧身份危机迫在眉睫，贺知舟一边抢救危重病患，一边隐藏自己的过往。</x:v>
+        <x:v>高考结束那天，林寻在考场外被亲生父母认回原来十八年的普通生活，是父母为磨砺他而设的一场成长课。重回豪门，他没有迷失，反而在桥上遇见了那个让他心动的姑娘，南大冰山学姐苏清诗。从青涩的初次相遇，到演唱会上的合唱，再到大学校园里的朝夕相处，两个真诚的人慢慢靠近。曾经的求而不得终将释怀，双向奔赴的喜欢才最珍贵。褪去普通学生的身份，林寻只想以真心换真心。十八岁的夏天，最好的相遇，最甜的恋爱，才刚刚开始。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1566,67 +1566,73 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B13" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
-        <x:v>傅少你夫人又在扮猪吃虎了</x:v>
+        <x:v>嫡姐日日闹换夫，圣旨赐下后她悔疯了</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>09-16 08:00</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str"/>
       <x:c r="F13" s="11" t="str"/>
       <x:c r="G13" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H13" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I13" s="11" t="str"/>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I13" s="11" t="n">
+        <x:v>65</x:v>
+      </x:c>
       <x:c r="J13" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K13" s="10" t="str">
-        <x:v>婚姻情感 / 美食治愈</x:v>
-      </x:c>
-      <x:c r="L13" s="11" t="str"/>
-      <x:c r="M13" s="10" t="str"/>
+        <x:v>婚姻情感 / 现实反转</x:v>
+      </x:c>
+      <x:c r="L13" s="11" t="str">
+        <x:v>心动漫剧场</x:v>
+      </x:c>
+      <x:c r="M13" s="10" t="str">
+        <x:v>沈家庶女沈照蘅自幼被嫡姐沈令仪欺压。嫡姐与状元顾砚舟定亲，争吵便扬言抢她未婚夫谢长晏。嫡姐竟跪求御前换婚，圣旨互换。状元当庭抗旨，全家逼她退让，她一句“臣女不敢抗旨”拒绝牺牲。嫡姐掌掴她、嫡母夺嫁妆、状元逼签屈辱契约被她焚毁，沈家灌哑药逼她自毁，皇后女官相救亮出生母嫁妆凭证。宫宴上嫡姐撒泼名声尽毁，皇后请旨暂缓赐婚，沈照蘅入宫担任伴读女官。从庶女到御前女官，她的命自己写。</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B14" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
-        <x:v>三十年退让，摒弃无底线的迁就</x:v>
+        <x:v>说好九十天就回来，我不等了</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>09-15 15:00</x:v>
+        <x:v>09-16 06:00</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str"/>
       <x:c r="F14" s="11" t="str"/>
       <x:c r="G14" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H14" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I14" s="11" t="n">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J14" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K14" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L14" s="11" t="str">
-        <x:v>浮光漫影</x:v>
+        <x:v>小宁漫漫</x:v>
       </x:c>
       <x:c r="M14" s="10" t="str">
-        <x:v>陈远辛苦规划全家自驾游，在高速服务区上厕所时，被家人为腾出位置搭载二叔一家直接抛下。过往他一直习惯为家里出钱出力，这次他不再一味妥协。经历一路波折后，陈远回归江城，分清家庭边界。后续弟弟学着独立承担生活，父母也慢慢反思过往。陈远守住自我，坦然面对亲情，过好属于自己的生活。</x:v>
+        <x:v>周衡挣脱错位的旧感情，坚守原则，专注医疗事业，打磨救死扶伤的星桥心泵。他与叶宁彼此尊重，感情建立在坦诚与边界之上，不盲目牺牲自我，平等相伴走向未来。林夏历经挫折后幡然醒悟，承担自己犯下的过错，放下执念踏实努力，靠双手重新经营人生。故事告诉人不必困在原地等候错的人，真心不该沦为候补，每个人都可以告别过往，奔赴属于自己的前路</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1634,24 +1640,24 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B15" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
-        <x:v>被诬陷诊出喜脉，重活一世我逆转前尘</x:v>
+        <x:v>四个崽崽瞒不住了</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
-        <x:v>09-16 07:58</x:v>
+        <x:v>09-15 00:08</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str"/>
       <x:c r="F15" s="11" t="str"/>
       <x:c r="G15" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H15" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I15" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="J15" s="10" t="str">
         <x:v>其他</x:v>
@@ -1660,10 +1666,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L15" s="11" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>桃子动漫剧场</x:v>
       </x:c>
       <x:c r="M15" s="10" t="str">
-        <x:v>沈清瑶重生回到被“神医”姜辞诬陷喜脉那天。前世她因此身败名裂，被迫嫁给竹马萧景渊，后来才知这是两人为替姜辞上位设的局。这一世，她不再任人宰割，巧妙将诊脉丝线系在谢老夫人腕上，当众揭穿姜辞。萧景渊谎称“孩子是我的”，却被她揭发与姜辞的私情，两人丑态毕露。谢家震怒，姜辞被强嫁萧景渊，沈清瑶嫁入侯府。婚后她冷静布局，让萧景渊与姜辞内斗升级。最终姜辞伏法，沈清瑶挣脱前世枷锁。可重生真能让她彻底自由吗？</x:v>
+        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1671,73 +1677,67 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C16" s="10" t="str">
-        <x:v>重回雪崩泥石流，我不再犹豫</x:v>
+        <x:v>傅少你夫人又在扮猪吃虎了</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
-        <x:v>09-16 01:02</x:v>
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str"/>
       <x:c r="F16" s="11" t="str"/>
       <x:c r="G16" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H16" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="I16" s="11" t="n">
-        <x:v>60</x:v>
-      </x:c>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I16" s="11" t="str"/>
       <x:c r="J16" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K16" s="10" t="str">
-        <x:v>年代怀旧</x:v>
-      </x:c>
-      <x:c r="L16" s="11" t="str">
-        <x:v>姜缘</x:v>
-      </x:c>
-      <x:c r="M16" s="10" t="str">
-        <x:v>前世，周清雨因犹豫错失逃生时机，眼睁睁看着全家被雪崩泥石流吞没。重生回灾难前三天，她当机立断卖掉五十头牦牛，囤积物资，带家人撤往高处。面对全村嘲讽和阻拦，她不再苦劝。直到雪山崩塌、洪流封村，昔日笑她疯癫的人纷纷求上门。这一次，她只救值得救的人！</x:v>
-      </x:c>
+        <x:v>婚姻情感 / 美食治愈</x:v>
+      </x:c>
+      <x:c r="L16" s="11" t="str"/>
+      <x:c r="M16" s="10" t="str"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C17" s="10" t="str">
-        <x:v>嫡姐日日闹换夫，圣旨赐下后她悔疯了</x:v>
+        <x:v>攻略失败后我不装了</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
-        <x:v>09-16 08:00</x:v>
+        <x:v>09-15 15:00</x:v>
       </x:c>
       <x:c r="E17" s="11" t="str"/>
       <x:c r="F17" s="11" t="str"/>
       <x:c r="G17" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H17" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I17" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="J17" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K17" s="10" t="str">
-        <x:v>婚姻情感 / 现实反转</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="L17" s="11" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>喵喵说漫</x:v>
       </x:c>
       <x:c r="M17" s="10" t="str">
-        <x:v>沈家庶女沈照蘅自幼被嫡姐沈令仪欺压。嫡姐与状元顾砚舟定亲，争吵便扬言抢她未婚夫谢长晏。嫡姐竟跪求御前换婚，圣旨互换。状元当庭抗旨，全家逼她退让，她一句“臣女不敢抗旨”拒绝牺牲。嫡姐掌掴她、嫡母夺嫁妆、状元逼签屈辱契约被她焚毁，沈家灌哑药逼她自毁，皇后女官相救亮出生母嫁妆凭证。宫宴上嫡姐撒泼名声尽毁，皇后请旨暂缓赐婚，沈照蘅入宫担任伴读女官。从庶女到御前女官，她的命自己写。</x:v>
+        <x:v>陆瑶做了百年攻略任务，反倒被系统判定为史上最废宿主，嘲讽她连宗门看门大黄都攻略不了，直接解绑。重获自由的她解开封印，觉醒万年难遇的天生道体。她撕碎弟子玉牌，决绝离开凌云峰，手握海量资源专心经商修炼。从前被她百般讨好的师尊师兄尽数落魄、满心悔意。她看淡情爱纠葛，收服大黄相伴，一路开挂逆袭，潇洒飞升开启全新仙生。</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1745,92 +1745,98 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C18" s="10" t="str">
-        <x:v>悍妻大房不好惹</x:v>
+        <x:v>我堂堂元婴老祖，让我给大小姐当保镖</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>09-15 23:57</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str"/>
       <x:c r="F18" s="11" t="str"/>
       <x:c r="G18" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H18" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="I18" s="11" t="str"/>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I18" s="11" t="n">
+        <x:v>217</x:v>
+      </x:c>
       <x:c r="J18" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K18" s="10" t="str">
-        <x:v>婚姻情感</x:v>
-      </x:c>
-      <x:c r="L18" s="11" t="str"/>
-      <x:c r="M18" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L18" s="11" t="str">
+        <x:v>扶摇精品剧场</x:v>
+      </x:c>
+      <x:c r="M18" s="10" t="str">
+        <x:v>宁尘穿越到修仙界两千年，居然只过了一个暑假！什么？你说我堂堂元婴老祖，不但被亲妈逼着去上大学，还要和校花大小姐同居？很快，同学们惊呆了随手扔铅球破世界纪录，你说这是大一新生？古武界集体怀疑人生修炼了几十年的武道老家伙，被一个年轻人当球踢？校花大小姐气得跺脚想接我电话的人能绕青州一圈，你居然嫌我吵？宁尘我，元婴老祖，真的只想做个普通人，既然你们非要逼我，那我只能一路横推，专治各种不服！</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C19" s="10" t="str">
-        <x:v>刺耳的邻里情</x:v>
+        <x:v>有米偏要讨三场雨</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
-        <x:v>09-15 11:00</x:v>
+        <x:v>09-16 08:18</x:v>
       </x:c>
       <x:c r="E19" s="11" t="str"/>
       <x:c r="F19" s="11" t="str"/>
       <x:c r="G19" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H19" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I19" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="J19" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K19" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L19" s="11" t="str">
-        <x:v>酒写一首诗</x:v>
+        <x:v>剧有米</x:v>
       </x:c>
       <x:c r="M19" s="10" t="str">
-        <x:v>邻居大强夫妇痴迷比赛，深夜制造噪音打扰四邻，甚至潜入邻院破坏，终因违规致使墙倒器毁、面临赔偿。青年陈默没有以怨报怨，只凭合农机与科学常识理性应对。大强夫妇在赔偿检讨中受教，重新学会遵守规则、尊重邻里；陈默则凭宽容智慧用赔款修筑村广场，走出一条和谐讲理的乡村新路。</x:v>
+        <x:v>青石村大旱三月，全村跪求龙王赐雨，四岁的有米却爬上供桌，张口就说龙王敖澜欠她三场雨。为了讨债，她扣雨牌、锁水门、放掉偷接的水、挖通公沟，还把只认天规的敖澜一次次拖进人间麻烦。暴风、山火和争水接连袭来，有米也在一次次选择中让周守财和全村学会先顾人、再顾利。三场雨终于还清，青石村重新秋种，山外却传来石狮异响，新的怪事又找上了她。</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C20" s="10" t="str">
-        <x:v>说好九十天就回来，我不等了</x:v>
+        <x:v>霁月安遥之以余生为诺护你岁岁无忧第一季</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>09-16 06:00</x:v>
-      </x:c>
-      <x:c r="E20" s="11" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="F20" s="11" t="str">
-        <x:v>↑26位</x:v>
-      </x:c>
-      <x:c r="G20" s="11" t="str"/>
-      <x:c r="H20" s="11" t="str"/>
+        <x:v>09-16 06:06</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="str"/>
+      <x:c r="F20" s="11" t="str"/>
+      <x:c r="G20" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H20" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="I20" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="J20" s="10" t="str">
         <x:v>其他</x:v>
@@ -1839,84 +1845,78 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L20" s="11" t="str">
-        <x:v>小宁漫漫</x:v>
+        <x:v>花花说漫</x:v>
       </x:c>
       <x:c r="M20" s="10" t="str">
-        <x:v>周衡挣脱错位的旧感情，坚守原则，专注医疗事业，打磨救死扶伤的星桥心泵。他与叶宁彼此尊重，感情建立在坦诚与边界之上，不盲目牺牲自我，平等相伴走向未来。林夏历经挫折后幡然醒悟，承担自己犯下的过错，放下执念踏实努力，靠双手重新经营人生。故事告诉人不必困在原地等候错的人，真心不该沦为候补，每个人都可以告别过往，奔赴属于自己的前路</x:v>
+        <x:v>22岁的医大学生辛知遥意外与大学教授周霁结缘，步入婚姻。初时二人的结合源于一场意外，彼此尚有距离。婚后辛知遥一边完成繁重的学业，一边适应全新的家庭生活。她挣脱原生家庭带来的压抑与束缚，学着正视内心、勇敢表达自我。周霁沉稳体贴，给予她尊重、陪伴与满满的安全感。二人在朝夕相处中慢慢卸下防备，从责任走向真心，携手面对生活里的重重风波，互相扶持，奔赴温暖安稳的幸福生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C21" s="10" t="str">
-        <x:v>重回雪崩泥石流，我不再犹豫</x:v>
+        <x:v>弄权大玄：我有购物系统</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
-        <x:v>09-16 01:02</x:v>
-      </x:c>
-      <x:c r="E21" s="11" t="n">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F21" s="11" t="str">
-        <x:v>↑14位</x:v>
-      </x:c>
-      <x:c r="G21" s="11" t="str"/>
-      <x:c r="H21" s="11" t="str"/>
-      <x:c r="I21" s="11" t="n">
-        <x:v>60</x:v>
-      </x:c>
+        <x:v>2026-09-16</x:v>
+      </x:c>
+      <x:c r="E21" s="11" t="str"/>
+      <x:c r="F21" s="11" t="str"/>
+      <x:c r="G21" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H21" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I21" s="11" t="str"/>
       <x:c r="J21" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K21" s="10" t="str">
-        <x:v>年代怀旧</x:v>
-      </x:c>
-      <x:c r="L21" s="11" t="str">
-        <x:v>姜缘</x:v>
-      </x:c>
-      <x:c r="M21" s="10" t="str">
-        <x:v>前世，周清雨因犹豫错失逃生时机，眼睁睁看着全家被雪崩泥石流吞没。重生回灾难前三天，她当机立断卖掉五十头牦牛，囤积物资，带家人撤往高处。面对全村嘲讽和阻拦，她不再苦劝。直到雪山崩塌、洪流封村，昔日笑她疯癫的人纷纷求上门。这一次，她只救值得救的人！</x:v>
-      </x:c>
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="L21" s="11" t="str"/>
+      <x:c r="M21" s="10" t="str"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C22" s="10" t="str">
+        <x:v>刺耳的邻里情</x:v>
+      </x:c>
+      <x:c r="D22" s="11" t="str">
+        <x:v>09-15 11:00</x:v>
+      </x:c>
+      <x:c r="E22" s="11" t="str"/>
+      <x:c r="F22" s="11" t="str"/>
+      <x:c r="G22" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C22" s="10" t="str">
-        <x:v>被诬陷诊出喜脉，重活一世我逆转前尘</x:v>
-      </x:c>
-      <x:c r="D22" s="11" t="str">
-        <x:v>09-16 07:58</x:v>
-      </x:c>
-      <x:c r="E22" s="11" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F22" s="11" t="str">
-        <x:v>↑10位</x:v>
-      </x:c>
-      <x:c r="G22" s="11" t="str"/>
-      <x:c r="H22" s="11" t="str"/>
+      <x:c r="H22" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="I22" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J22" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K22" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L22" s="11" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>酒写一首诗</x:v>
       </x:c>
       <x:c r="M22" s="10" t="str">
-        <x:v>沈清瑶重生回到被“神医”姜辞诬陷喜脉那天。前世她因此身败名裂，被迫嫁给竹马萧景渊，后来才知这是两人为替姜辞上位设的局。这一世，她不再任人宰割，巧妙将诊脉丝线系在谢老夫人腕上，当众揭穿姜辞。萧景渊谎称“孩子是我的”，却被她揭发与姜辞的私情，两人丑态毕露。谢家震怒，姜辞被强嫁萧景渊，沈清瑶嫁入侯府。婚后她冷静布局，让萧景渊与姜辞内斗升级。最终姜辞伏法，沈清瑶挣脱前世枷锁。可重生真能让她彻底自由吗？</x:v>
+        <x:v>邻居大强夫妇痴迷比赛，深夜制造噪音打扰四邻，甚至潜入邻院破坏，终因违规致使墙倒器毁、面临赔偿。青年陈默没有以怨报怨，只凭合农机与科学常识理性应对。大强夫妇在赔偿检讨中受教，重新学会遵守规则、尊重邻里；陈默则凭宽容智慧用赔款修筑村广场，走出一条和谐讲理的乡村新路。</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1924,24 +1924,24 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C23" s="10" t="str">
-        <x:v>我都元婴期了，你跟我说开学</x:v>
+        <x:v>八媳妇只想买包，一不小心拯救了全家</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
-        <x:v>09-16 00:10</x:v>
+        <x:v>09-16 10:00</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F23" s="11" t="str">
-        <x:v>↑10位</x:v>
+        <x:v>↑26位</x:v>
       </x:c>
       <x:c r="G23" s="11" t="str"/>
       <x:c r="H23" s="11" t="str"/>
       <x:c r="I23" s="11" t="n">
-        <x:v>475</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J23" s="10" t="str">
         <x:v>其他</x:v>
@@ -1950,10 +1950,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L23" s="11" t="str">
-        <x:v>梦启剧场</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="M23" s="10" t="str">
-        <x:v>修士宁尘遭遇偷袭，身负重伤从修真界回到现代。时间只流逝一个暑假，他被迫入读青州大学，借居在乔姨家中，与傲娇少女许舒颜同住。一边伪装普通学生，一边寻找修复元神伤势的资源，接连化解校园、市井与古武圈子的各类风波，开启充满反差的现代生活。</x:v>
+        <x:v>顾家八位儿媳皆各有所长。大嫂秦蕴章深耕华尔街并购领域，二嫂林疏桐是风投行业的杰出从业者。晏姝岚平日生活低调随性，外界便对她产生片面认知，认为她只注重物质消费。实际上，晏姝岚来自底蕴更为深厚的大家族。当顾氏集团遭遇多家境外企业联合围堵，经营陷入巨大危机。顾家公公心力交瘁，能力出众的嫂嫂们多方调动资源，依旧难以摸清对手的真实布局。在对手步步施压的危急时刻，晏姝岚挺身而出，守护顾家渡过这场商业危机。</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1961,36 +1961,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C24" s="10" t="str">
-        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
+        <x:v>重生第七节车厢</x:v>
       </x:c>
       <x:c r="D24" s="11" t="str">
-        <x:v>09-15 08:30</x:v>
+        <x:v>09-16 11:39</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F24" s="11" t="str">
-        <x:v>↑5位</x:v>
+        <x:v>↑20位</x:v>
       </x:c>
       <x:c r="G24" s="11" t="str"/>
       <x:c r="H24" s="11" t="str"/>
       <x:c r="I24" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J24" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K24" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L24" s="11" t="str">
-        <x:v>琥珀漫剧</x:v>
+        <x:v>千一剧场</x:v>
       </x:c>
       <x:c r="M24" s="10" t="str">
-        <x:v>海鲜市场老手陈放，因一个两块钱的冰袋被十二年合伙人当众算旧账，心寒清账，净身出户。他没有抱怨，也没有以牙还牙，而是加入冷清档口“梅姐水产”，从零开始。他坚持明码标价、沥水称重、死活分卖、批次可查，宁可少接单，也不混货、不凑数、不赚亏心钱。面对低价抢客、恶意破坏、临时缺货等风波，他与叶梅靠诚信、规矩和彼此信任，一步步赢得客户与连锁企业的认可。</x:v>
+        <x:v>高铁列车长林铮死过一次。上一世，四名大学生私带危险实验样品登车，一句“毒倒整节车厢”的戏言被他放行，最终隧道内毒气泄漏，全车罹难，他成了千夫所指的责任人。重回发车前最后一分钟，他顶住求情、质疑与全网非议，硬封第七节车厢，叫停整趟列车。层层戳破瞒报的谎言，这一次，他死守安全红线，要让车上一千零八十六人，全都平安抵达终点。</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1998,36 +1998,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C25" s="10" t="str">
-        <x:v>我在工地卖盒饭带火一座城</x:v>
+        <x:v>错婚觉醒</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
-        <x:v>09-14 14:52</x:v>
+        <x:v>09-14 18:03</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:v>34</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F25" s="11" t="str">
-        <x:v>↑4位</x:v>
+        <x:v>↑20位</x:v>
       </x:c>
       <x:c r="G25" s="11" t="str"/>
       <x:c r="H25" s="11" t="str"/>
       <x:c r="I25" s="11" t="n">
-        <x:v>144</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="J25" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K25" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>婚姻情感 / 战神异能</x:v>
       </x:c>
       <x:c r="L25" s="11" t="str">
-        <x:v>左手良画</x:v>
+        <x:v>小7AI漫剧</x:v>
       </x:c>
       <x:c r="M25" s="10" t="str">
-        <x:v>小伙白叶遭遇老板跑路，半年工资付诸东流，意外被铁炒勺砸中觉醒超级餐饮系统。大雪封路堵车途中完成首份任务，靠着系统加持的厨艺，路边卖盒饭赚到第一桶金。回乡钻研秘制酱肉，赶集摆摊火爆出圈，还临危接手大型寿宴惊艳众人。过完新年，他怀揣梦想奔赴外地，准备开启属于自己的餐饮创业之路。</x:v>
+        <x:v>新婚当夜那天，姜云笙重生回到了被陆家算计的那天。面对虚伪丈夫陆卫民、苟且的小姑陆红梅与贪婪婆婆，她决定不再愚善隐忍。而是步步设局撕开陆家真面目，夺回被窃取的前途与财物，奋力挣脱不幸婚姻，为自己讨回公道。</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -2035,36 +2035,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B26" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C26" s="10" t="str">
-        <x:v>嫡姐日日闹换夫，圣旨赐下后她悔疯了</x:v>
+        <x:v>有米偏要讨三场雨</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
-        <x:v>09-16 08:00</x:v>
+        <x:v>09-16 08:18</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F26" s="11" t="str">
-        <x:v>↑3位</x:v>
+        <x:v>↑17位</x:v>
       </x:c>
       <x:c r="G26" s="11" t="str"/>
       <x:c r="H26" s="11" t="str"/>
       <x:c r="I26" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="J26" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K26" s="10" t="str">
-        <x:v>婚姻情感 / 现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L26" s="11" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>剧有米</x:v>
       </x:c>
       <x:c r="M26" s="10" t="str">
-        <x:v>沈家庶女沈照蘅自幼被嫡姐沈令仪欺压。嫡姐与状元顾砚舟定亲，争吵便扬言抢她未婚夫谢长晏。嫡姐竟跪求御前换婚，圣旨互换。状元当庭抗旨，全家逼她退让，她一句“臣女不敢抗旨”拒绝牺牲。嫡姐掌掴她、嫡母夺嫁妆、状元逼签屈辱契约被她焚毁，沈家灌哑药逼她自毁，皇后女官相救亮出生母嫁妆凭证。宫宴上嫡姐撒泼名声尽毁，皇后请旨暂缓赐婚，沈照蘅入宫担任伴读女官。从庶女到御前女官，她的命自己写。</x:v>
+        <x:v>青石村大旱三月，全村跪求龙王赐雨，四岁的有米却爬上供桌，张口就说龙王敖澜欠她三场雨。为了讨债，她扣雨牌、锁水门、放掉偷接的水、挖通公沟，还把只认天规的敖澜一次次拖进人间麻烦。暴风、山火和争水接连袭来，有米也在一次次选择中让周守财和全村学会先顾人、再顾利。三场雨终于还清，青石村重新秋种，山外却传来石狮异响，新的怪事又找上了她。</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -2072,36 +2072,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B27" s="11" t="n">
-        <x:v>98</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C27" s="10" t="str">
-        <x:v>重生极品婆婆，带全家发家致富！</x:v>
+        <x:v>霁月安遥之以余生为诺护你岁岁无忧第一季</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
-        <x:v>09-14 20:29</x:v>
+        <x:v>09-16 06:06</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F27" s="11" t="str">
-        <x:v>↑2位</x:v>
+        <x:v>↑8位</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str"/>
       <x:c r="H27" s="11" t="str"/>
       <x:c r="I27" s="11" t="n">
-        <x:v>126</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="J27" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K27" s="10" t="str">
-        <x:v>家庭伦理 / 逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L27" s="11" t="str">
-        <x:v>懒少爱我</x:v>
+        <x:v>花花说漫</x:v>
       </x:c>
       <x:c r="M27" s="10" t="str">
-        <x:v>寡妇傅兰秀前世一生吝啬守财，刻薄对待儿女儿媳，到头来钱财被贼人掠夺，落得个凄惨离世的下场。一朝重生，她回到悲剧尚未发生之时。痛定思痛，她彻底改掉抠门的性子，学着善待家里的晚辈。可日子并不太平，爱占便宜的亲戚总上门搅扰，家中两个儿媳也矛盾不断，家务是非接连找上门。傅兰秀靠着清醒的头脑，一边化解各类家庭纷争，一边寻找营生门路，努力扭转命运，拼尽全力守护一家人的安稳生活。</x:v>
+        <x:v>22岁的医大学生辛知遥意外与大学教授周霁结缘，步入婚姻。初时二人的结合源于一场意外，彼此尚有距离。婚后辛知遥一边完成繁重的学业，一边适应全新的家庭生活。她挣脱原生家庭带来的压抑与束缚，学着正视内心、勇敢表达自我。周霁沉稳体贴，给予她尊重、陪伴与满满的安全感。二人在朝夕相处中慢慢卸下防备，从责任走向真心，携手面对生活里的重重风波，互相扶持，奔赴温暖安稳的幸福生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -2109,34 +2109,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B28" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C28" s="10" t="str">
-        <x:v>我能看见每个人的剩余寿命</x:v>
+        <x:v>重回雪崩泥石流，我不再犹豫</x:v>
       </x:c>
       <x:c r="D28" s="11" t="str">
-        <x:v>09-15 00:04</x:v>
-      </x:c>
-      <x:c r="E28" s="11" t="str"/>
+        <x:v>09-16 01:02</x:v>
+      </x:c>
+      <x:c r="E28" s="11" t="n">
+        <x:v>26</x:v>
+      </x:c>
       <x:c r="F28" s="11" t="str">
-        <x:v>新上榜</x:v>
+        <x:v>↑4位</x:v>
       </x:c>
       <x:c r="G28" s="11" t="str"/>
       <x:c r="H28" s="11" t="str"/>
       <x:c r="I28" s="11" t="n">
-        <x:v>123</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J28" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K28" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="L28" s="11" t="str">
-        <x:v>酒森漫剧</x:v>
+        <x:v>姜缘</x:v>
       </x:c>
       <x:c r="M28" s="10" t="str">
-        <x:v>青山村少女沈海棠觉醒异能，能看见每个人头顶的剩余寿命。全村人寿命骤剩七天，唯有猎户萧野一家存活时间更长，海棠为护住幼妹小满，想方设法嫁入萧家。不久丧尸灾变爆发，她靠着寿命预知，提前囤积粮草兵器，带领萧家与部部分村民艰难求生。在残酷的末世之中，聪慧厚脸皮的海棠与外冷内热武力高强的萧野从契约夫妻走向彼此倾心。众人一边对抗变异丧尸、应对自私村民的算计，一边开荒筑防拼命改写死亡倒计时，可寿命数字仍在跳动。</x:v>
+        <x:v>前世，周清雨因犹豫错失逃生时机，眼睁睁看着全家被雪崩泥石流吞没。重生回灾难前三天，她当机立断卖掉五十头牦牛，囤积物资，带家人撤往高处。面对全村嘲讽和阻拦，她不再苦劝。直到雪山崩塌、洪流封村，昔日笑她疯癫的人纷纷求上门。这一次，她只救值得救的人！</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -2144,48 +2146,44 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B29" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C29" s="10" t="str">
-        <x:v>我堂堂元婴老祖，让我给大小姐当保镖</x:v>
+        <x:v>弄权大玄：我有购物系统</x:v>
       </x:c>
       <x:c r="D29" s="11" t="str">
-        <x:v>09-15 23:57</x:v>
-      </x:c>
-      <x:c r="E29" s="11" t="str"/>
+        <x:v>2026-09-16</x:v>
+      </x:c>
+      <x:c r="E29" s="11" t="n">
+        <x:v>75</x:v>
+      </x:c>
       <x:c r="F29" s="11" t="str">
-        <x:v>新上榜</x:v>
+        <x:v>↑4位</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str"/>
       <x:c r="H29" s="11" t="str"/>
-      <x:c r="I29" s="11" t="n">
-        <x:v>217</x:v>
-      </x:c>
+      <x:c r="I29" s="11" t="str"/>
       <x:c r="J29" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K29" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L29" s="11" t="str">
-        <x:v>扶摇精品剧场</x:v>
-      </x:c>
-      <x:c r="M29" s="10" t="str">
-        <x:v>宁尘穿越到修仙界两千年，居然只过了一个暑假！什么？你说我堂堂元婴老祖，不但被亲妈逼着去上大学，还要和校花大小姐同居？很快，同学们惊呆了随手扔铅球破世界纪录，你说这是大一新生？古武界集体怀疑人生修炼了几十年的武道老家伙，被一个年轻人当球踢？校花大小姐气得跺脚想接我电话的人能绕青州一圈，你居然嫌我吵？宁尘我，元婴老祖，真的只想做个普通人，既然你们非要逼我，那我只能一路横推，专治各种不服！</x:v>
-      </x:c>
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="L29" s="11" t="str"/>
+      <x:c r="M29" s="10" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B30" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C30" s="10" t="str">
-        <x:v>我的系统不对劲，行善积德反着来</x:v>
+        <x:v>敢泼我馄饨，整条街都别要了</x:v>
       </x:c>
       <x:c r="D30" s="11" t="str">
-        <x:v>09-15 10:00</x:v>
+        <x:v>09-16 10:00</x:v>
       </x:c>
       <x:c r="E30" s="11" t="str"/>
       <x:c r="F30" s="11" t="str">
@@ -2194,19 +2192,54 @@
       <x:c r="G30" s="11" t="str"/>
       <x:c r="H30" s="11" t="str"/>
       <x:c r="I30" s="11" t="n">
-        <x:v>122</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J30" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K30" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L30" s="11" t="str">
-        <x:v>掌读微剧</x:v>
+        <x:v>治愈 AI 恋</x:v>
       </x:c>
       <x:c r="M30" s="10" t="str">
-        <x:v>贵为玄天宗第一天骄，苏云峰惨遭师尊沈傲雪背叛，被夺去至尊骨后含恨而亡！再度睁眼，他意外获得另类的行善积德系统。在系统的帮助下，昔日温顺弟子彻底觉醒，不再任人宰割，苏云峰的命运轨迹被彻底改写，走出一条截然不同的修行路！</x:v>
+        <x:v>南桥旧街投资人许总多年悉心扶持一众商户，给予租金减免与基建投入，可赵川等人却贪念作祟，撕毁协议，还刻意编造谎言煽动网络暴力。面对恩将仇报的局面，许总没有冲动行事，而是恪守契约精神，凭借完备证据通过合法途径理性维权。随着真相公之于众，造谣闹事者自食恶果，承担起违约带来的相应代价。旧街完成焕新升级，充分彰显出法律与规则守护公平正义的强大力量。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B31" s="11" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C31" s="10" t="str">
+        <x:v>工地前的一碗盒饭</x:v>
+      </x:c>
+      <x:c r="D31" s="11" t="str">
+        <x:v>09-15 11:00</x:v>
+      </x:c>
+      <x:c r="E31" s="11" t="str"/>
+      <x:c r="F31" s="11" t="str">
+        <x:v>新上榜</x:v>
+      </x:c>
+      <x:c r="G31" s="11" t="str"/>
+      <x:c r="H31" s="11" t="str"/>
+      <x:c r="I31" s="11" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="J31" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K31" s="10" t="str">
+        <x:v>美食治愈</x:v>
+      </x:c>
+      <x:c r="L31" s="11" t="str">
+        <x:v>小羊说漫</x:v>
+      </x:c>
+      <x:c r="M31" s="10" t="str">
+        <x:v>热火朝天的建筑工地旁，盒饭摊主老陈始终不为暴利所动，坚持猛火现炒和选用新鲜优质的好肉，默默守护工人们的食品安全。最终，在一场危机后，贪婪者受到了严惩，工人们也彻底醒悟。赞美了老陈纯粹的工匠精神，传递了坚守底线、正义必胜的温暖价值观。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2275,7 +2308,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
         <x:v>我都元婴期了，你跟我说开学</x:v>
@@ -2298,24 +2331,30 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>傅少你夫人又在扮猪吃虎了</x:v>
+        <x:v>有米偏要讨三场雨</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>当日新上榜</x:v>
-      </x:c>
-      <x:c r="D4" s="11" t="str"/>
-      <x:c r="E4" s="11" t="str"/>
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D4" s="11" t="str">
+        <x:v>09-16 08:18</x:v>
+      </x:c>
+      <x:c r="E4" s="11" t="n">
+        <x:v>98</x:v>
+      </x:c>
       <x:c r="F4" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="G4" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G4" s="10" t="str">
+        <x:v>剧有米</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
         <x:v>重回雪崩泥石流，我不再犹豫</x:v>
@@ -2338,66 +2377,175 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>嫡姐日日闹换夫，圣旨赐下后她悔疯了</x:v>
+        <x:v>霁月安遥之以余生为诺护你岁岁无忧第一季</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>09-16 08:00</x:v>
+        <x:v>09-16 06:06</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F6" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G6" s="10" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>花花说漫</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>说好九十天就回来，我不等了</x:v>
+        <x:v>重生第七节车厢</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>09-16 06:00</x:v>
+        <x:v>09-16 11:39</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F7" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G7" s="10" t="str">
-        <x:v>小宁漫漫</x:v>
+        <x:v>千一剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B8" s="10" t="str">
+        <x:v>敢泼我馄饨，整条街都别要了</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="str">
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="str">
+        <x:v>09-16 10:00</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F8" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G8" s="10" t="str">
+        <x:v>治愈 AI 恋</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="11" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B9" s="10" t="str">
+        <x:v>八媳妇只想买包，一不小心拯救了全家</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="str">
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="str">
+        <x:v>09-16 10:00</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F9" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G9" s="10" t="str">
+        <x:v>闪闪动漫社</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="11" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B10" s="10" t="str">
+        <x:v>嫡姐日日闹换夫，圣旨赐下后她悔疯了</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="str">
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D10" s="11" t="str">
+        <x:v>09-16 08:00</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F10" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G10" s="10" t="str">
+        <x:v>心动漫剧场</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="11" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B11" s="10" t="str">
+        <x:v>弄权大玄：我有购物系统</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="str">
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="str"/>
+      <x:c r="E11" s="11" t="str"/>
+      <x:c r="F11" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="G11" s="10" t="str"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="11" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B12" s="10" t="str">
+        <x:v>说好九十天就回来，我不等了</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="str">
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D12" s="11" t="str">
+        <x:v>09-16 06:00</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F12" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G12" s="10" t="str">
+        <x:v>小宁漫漫</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="11" t="n">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="B8" s="10" t="str">
-        <x:v>悍妻大房不好惹</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="str">
+      <x:c r="B13" s="10" t="str">
+        <x:v>傅少你夫人又在扮猪吃虎了</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="str">
         <x:v>当日新上榜</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="str"/>
-      <x:c r="E8" s="11" t="str"/>
-      <x:c r="F8" s="10" t="str">
+      <x:c r="D13" s="11" t="str"/>
+      <x:c r="E13" s="11" t="str"/>
+      <x:c r="F13" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="G8" s="10" t="str"/>
+      <x:c r="G13" s="10" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2466,7 +2614,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
         <x:v>征地我秒签跑路，全村笑我半年</x:v>
@@ -2503,16 +2651,16 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
-        <x:v>24</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
+        <x:v>穿书后我带萌宝上门认爹</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>09-08 17:58</x:v>
+        <x:v>09-07 19:18</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
         <x:v>7</x:v>
@@ -2521,10 +2669,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G3" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H3" s="11" t="n">
-        <x:v>111</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
         <x:v>其他</x:v>
@@ -2532,24 +2680,24 @@
       <x:c r="J3" s="11" t="str"/>
       <x:c r="K3" s="11" t="str"/>
       <x:c r="L3" s="10" t="str">
-        <x:v>禾苗动画</x:v>
+        <x:v>虾仁不自在</x:v>
       </x:c>
       <x:c r="M3" s="10" t="str">
-        <x:v>末世异能者沐小暖意外穿书，成为七个反派继子的恶毒后娘。原主辛劳养娃却遭流言中伤，最终含恨而终。沐小暖决心扭转命运，恩威并施管教孩子，凭末世身手进山打猎采药、种地赶集改善家计，更以百年老参为礼，为长子求得名儒霍政谚收为关门弟子。她护佑家人躲过恶人算计与亲戚夺产，建起新宅。七个孩子从怨恨抗拒到真心信赖，争着喊她娘，一家人携手改写命运，收获温暖亲情。</x:v>
+        <x:v>许知棠重生穿进书中，当即带着五岁儿子许小舟登门，将孩子送到亲生父亲——傅氏集团总裁傅临川面前，只想抽身退出剧情。幼儿园里儿子遭同学诬陷、老师偏心，她强势护崽，硬刚蛮横家长与失职老师。亲子鉴定尘埃落定，萌娃黏妈不黏爹，反倒让清冷总裁渐渐上心。</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>大坝边寻回的真千金</x:v>
+        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>09-10 11:26</x:v>
+        <x:v>09-08 17:58</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
         <x:v>7</x:v>
@@ -2558,10 +2706,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G4" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H4" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="I4" s="10" t="str">
         <x:v>其他</x:v>
@@ -2569,24 +2717,24 @@
       <x:c r="J4" s="11" t="str"/>
       <x:c r="K4" s="11" t="str"/>
       <x:c r="L4" s="10" t="str">
-        <x:v>喵琪琪追剧</x:v>
+        <x:v>禾苗动画</x:v>
       </x:c>
       <x:c r="M4" s="10" t="str">
-        <x:v>大坝突发险情，农村女孩夏晚禾凭借熟悉的环境和过人的勇气，不顾危险救下被困的沈长洲。一次意外的救援，让两个陌生人的命运重新交织。随着调查深入，沈长洲发现这个善良坚韧的女孩，竟是自己失散二十年的亲生女儿。面对迟来的亲情和真假千金的风波，夏晚禾没有依靠身份改变人生，而是用智慧、担当和努力证明自己的价值。陆言川也在一次次并肩相处中，被她的真诚与坚强打动，陪她找回亲情，走向新的未来。</x:v>
+        <x:v>末世异能者沐小暖意外穿书，成为七个反派继子的恶毒后娘。原主辛劳养娃却遭流言中伤，最终含恨而终。沐小暖决心扭转命运，恩威并施管教孩子，凭末世身手进山打猎采药、种地赶集改善家计，更以百年老参为礼，为长子求得名儒霍政谚收为关门弟子。她护佑家人躲过恶人算计与亲戚夺产，建起新宅。七个孩子从怨恨抗拒到真心信赖，争着喊她娘，一家人携手改写命运，收获温暖亲情。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>穿书后我带萌宝上门认爹</x:v>
+        <x:v>抢个新娘来当后娘第一季</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>09-07 19:18</x:v>
+        <x:v>09-08 15:10</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
         <x:v>7</x:v>
@@ -2595,10 +2743,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G5" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H5" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="I5" s="10" t="str">
         <x:v>其他</x:v>
@@ -2606,24 +2754,24 @@
       <x:c r="J5" s="11" t="str"/>
       <x:c r="K5" s="11" t="str"/>
       <x:c r="L5" s="10" t="str">
-        <x:v>虾仁不自在</x:v>
+        <x:v>麻辣公主</x:v>
       </x:c>
       <x:c r="M5" s="10" t="str">
-        <x:v>许知棠重生穿进书中，当即带着五岁儿子许小舟登门，将孩子送到亲生父亲——傅氏集团总裁傅临川面前，只想抽身退出剧情。幼儿园里儿子遭同学诬陷、老师偏心，她强势护崽，硬刚蛮横家长与失职老师。亲子鉴定尘埃落定，萌娃黏妈不黏爹，反倒让清冷总裁渐渐上心。</x:v>
+        <x:v>带着十里红妆出嫁那日，我才得知新郎早已另娶，这门亲事不过是盯上了我李家的家产。换作旁人或许忍气吞声，我偏不。我当众拒入侯府，主动上书朝廷，愿以嫁妆资援南方水患，只求解除婚约、护我父母周全。这份胆识赢得安王敬重，他以正妃之礼娶我入门。我立誓此生不做妾、不与人共侍一夫，终得一份彼此尊重的姻缘。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>一墙之隔，皆是人心</x:v>
+        <x:v>重生三天前，我用水泥封死地下室</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>09-06 15:48</x:v>
+        <x:v>09-09 09:28</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
         <x:v>7</x:v>
@@ -2635,7 +2783,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
         <x:v>其他</x:v>
@@ -2643,21 +2791,21 @@
       <x:c r="J6" s="11" t="str"/>
       <x:c r="K6" s="11" t="str"/>
       <x:c r="L6" s="10" t="str">
-        <x:v>在下长生</x:v>
+        <x:v>忘忧剧场</x:v>
       </x:c>
       <x:c r="M6" s="10" t="str">
-        <x:v>妻子临产被车堵住出口，叶瑾抱着羊水破裂的她跑了三公里才到医院，母子平安。面对无理的车主，他没有以暴制暴，而是选择依法行事——在自家院内合法砌墙、种下高价值树苗，全程录像留证。车主回来后暴力砸墙、碾压树苗，最终被依法追究责任。</x:v>
+        <x:v>阮清重生回被保姆王妈一家害死的三天前，前世她因心善引狼入室，保姆全家蜗居别墅地下室偷窃投毒，最终惨遭勒死。重生后她假装不知，趁王妈外出时用水泥将地下室彻底封死。警方破墙后，五具尸体令真相大白，王妈因盗窃、投毒被判十五年。阮清与父母团聚，恶人终得恶报，她重获新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>惊絮无声：傻女的绝杀</x:v>
+        <x:v>一墙之隔，皆是人心</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>09-06 10:00</x:v>
+        <x:v>09-06 15:48</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
         <x:v>10</x:v>
@@ -2669,10 +2817,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G7" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H7" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="I7" s="10" t="str">
         <x:v>其他</x:v>
@@ -2680,10 +2828,10 @@
       <x:c r="J7" s="11" t="str"/>
       <x:c r="K7" s="11" t="str"/>
       <x:c r="L7" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>在下长生</x:v>
       </x:c>
       <x:c r="M7" s="10" t="str">
-        <x:v>沈家人人都是天才，唯独小女儿沈惊絮是公认的傻子。没人知道，她不仅装傻多年，还带着前世金牌律师的记忆重生而来。本想闭嘴躺平一生，谁料内鬼勾结资本做空沈氏，一纸合同就要让全家净身出户、背上百亿债务。父亲落笔前，她终于按住协议“这字不能签！”绝地反杀的沈惊絮，一步步挫败了对沈家的围剿，也让全家人重新认识了自己。沈家也迎来了新生。</x:v>
+        <x:v>妻子临产被车堵住出口，叶瑾抱着羊水破裂的她跑了三公里才到医院，母子平安。面对无理的车主，他没有以暴制暴，而是选择依法行事——在自家院内合法砌墙、种下高价值树苗，全程录像留证。车主回来后暴力砸墙、碾压树苗，最终被依法追究责任。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2691,13 +2839,13 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>重生三天前，我用水泥封死地下室</x:v>
+        <x:v>黑蛋孵出山海神兽后我无敌了</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>09-09 09:28</x:v>
+        <x:v>09-06 18:00</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
         <x:v>7</x:v>
@@ -2706,10 +2854,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G8" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H8" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
         <x:v>其他</x:v>
@@ -2717,24 +2865,24 @@
       <x:c r="J8" s="11" t="str"/>
       <x:c r="K8" s="11" t="str"/>
       <x:c r="L8" s="10" t="str">
-        <x:v>忘忧剧场</x:v>
+        <x:v>抱月剧场</x:v>
       </x:c>
       <x:c r="M8" s="10" t="str">
-        <x:v>阮清重生回被保姆王妈一家害死的三天前，前世她因心善引狼入室，保姆全家蜗居别墅地下室偷窃投毒，最终惨遭勒死。重生后她假装不知，趁王妈外出时用水泥将地下室彻底封死。警方破墙后，五具尸体令真相大白，王妈因盗窃、投毒被判十五年。阮清与父母团聚，恶人终得恶报，她重获新生。</x:v>
+        <x:v>寒门少年李初七攒了三年银子，仍买不起最低等的兽蛋。一次意外，他在后山捡到一枚黑蛋，孵出的煤球又小又馋，偏偏爱啃铜钱。可每吞下一缕兽息，它便能复现对手的能力。县学测灵那日，测灵石骤然亮起黑光，群兽伏地。所有人都以为他只是走了好运，只有陆远山想起古籍中的禁忌——黑光现，万兽伏。煤球究竟是什么？</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>抢个新娘来当后娘第一季</x:v>
+        <x:v>不靠谱爸妈很靠谱</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>09-08 15:10</x:v>
+        <x:v>09-09 11:08</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
         <x:v>7</x:v>
@@ -2743,10 +2891,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G9" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H9" s="11" t="n">
-        <x:v>177</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str">
         <x:v>其他</x:v>
@@ -2754,24 +2902,24 @@
       <x:c r="J9" s="11" t="str"/>
       <x:c r="K9" s="11" t="str"/>
       <x:c r="L9" s="10" t="str">
-        <x:v>麻辣公主</x:v>
+        <x:v>灵妹儿</x:v>
       </x:c>
       <x:c r="M9" s="10" t="str">
-        <x:v>带着十里红妆出嫁那日，我才得知新郎早已另娶，这门亲事不过是盯上了我李家的家产。换作旁人或许忍气吞声，我偏不。我当众拒入侯府，主动上书朝廷，愿以嫁妆资援南方水患，只求解除婚约、护我父母周全。这份胆识赢得安王敬重，他以正妃之礼娶我入门。我立誓此生不做妾、不与人共侍一夫，终得一份彼此尊重的姻缘。</x:v>
+        <x:v>外表张扬的年轻夫妻在冬夜救下女婴林小小，用十七年的辛勤劳动和无条件陪伴，为她撑起温暖的家。曾经成绩落后的林小小，在父母的鼓励下重新学习，一步步成长为优秀学生。面对亲生家庭带来的资源与人生选择，她也开始重新理解血缘、养育与责任。当外界的误解影响到父母的生活，林小小决定勇敢站出来，用事实守护家人，也用努力证明真正的爱，是尊重、陪伴和彼此成就。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="n">
-        <x:v>44</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
+        <x:v>惊絮无声：傻女的绝杀</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>09-08 11:00</x:v>
+        <x:v>09-06 10:00</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
         <x:v>7</x:v>
@@ -2780,10 +2928,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G10" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H10" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I10" s="10" t="str">
         <x:v>其他</x:v>
@@ -2791,21 +2939,21 @@
       <x:c r="J10" s="11" t="str"/>
       <x:c r="K10" s="11" t="str"/>
       <x:c r="L10" s="10" t="str">
-        <x:v>白桃剧场</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="M10" s="10" t="str">
-        <x:v>阿梨一觉睡了三百年，养大的五只小兽尽数离去。她带着五只旧饭碗、十二枚铜钱与一把锈柴刀下山寻兽。昔日的小家伙已成威震四方的妖祖，历经重重相遇与揭秘，阿梨知晓三百年封印的真相，携手五只妖祖，一同对抗祸世灭灵兽神。</x:v>
+        <x:v>沈家人人都是天才，唯独小女儿沈惊絮是公认的傻子。没人知道，她不仅装傻多年，还带着前世金牌律师的记忆重生而来。本想闭嘴躺平一生，谁料内鬼勾结资本做空沈氏，一纸合同就要让全家净身出户、背上百亿债务。父亲落笔前，她终于按住协议“这字不能签！”绝地反杀的沈惊絮，一步步挫败了对沈家的围剿，也让全家人重新认识了自己。沈家也迎来了新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>不靠谱爸妈很靠谱</x:v>
+        <x:v>离家十年，回来女儿被换了</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>09-09 11:08</x:v>
+        <x:v>09-09 00:04</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
         <x:v>7</x:v>
@@ -2817,10 +2965,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G11" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H11" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="I11" s="10" t="str">
         <x:v>其他</x:v>
@@ -2828,24 +2976,24 @@
       <x:c r="J11" s="11" t="str"/>
       <x:c r="K11" s="11" t="str"/>
       <x:c r="L11" s="10" t="str">
-        <x:v>灵妹儿</x:v>
+        <x:v>魔方影视（上剧版</x:v>
       </x:c>
       <x:c r="M11" s="10" t="str">
-        <x:v>外表张扬的年轻夫妻在冬夜救下女婴林小小，用十七年的辛勤劳动和无条件陪伴，为她撑起温暖的家。曾经成绩落后的林小小，在父母的鼓励下重新学习，一步步成长为优秀学生。面对亲生家庭带来的资源与人生选择，她也开始重新理解血缘、养育与责任。当外界的误解影响到父母的生活，林小小决定勇敢站出来，用事实守护家人，也用努力证明真正的爱，是尊重、陪伴和彼此成就。</x:v>
+        <x:v>程砚宁完成长期绝密任务归来，满心想要弥补亲情，却发现家中早已物是人非。身边亲近之人被私欲蒙蔽，制造重重骗局，试图侵占她的事业与财富。面对接连而来的算计与危机，她凭借过人的魄力与智慧步步拆解阴谋，联合正义力量搜集证据，厘清全部是非纠葛。在守护自身事业的同时，她放下过往伤痛，投身公益，完成自我和解，迎来属于自己的全新人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="n">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>离家十年，回来女儿被换了</x:v>
+        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>09-09 00:04</x:v>
+        <x:v>09-08 11:00</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
         <x:v>7</x:v>
@@ -2857,7 +3005,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H12" s="11" t="n">
-        <x:v>155</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str">
         <x:v>其他</x:v>
@@ -2865,24 +3013,24 @@
       <x:c r="J12" s="11" t="str"/>
       <x:c r="K12" s="11" t="str"/>
       <x:c r="L12" s="10" t="str">
-        <x:v>魔方影视（上剧版</x:v>
+        <x:v>白桃剧场</x:v>
       </x:c>
       <x:c r="M12" s="10" t="str">
-        <x:v>程砚宁完成长期绝密任务归来，满心想要弥补亲情，却发现家中早已物是人非。身边亲近之人被私欲蒙蔽，制造重重骗局，试图侵占她的事业与财富。面对接连而来的算计与危机，她凭借过人的魄力与智慧步步拆解阴谋，联合正义力量搜集证据，厘清全部是非纠葛。在守护自身事业的同时，她放下过往伤痛，投身公益，完成自我和解，迎来属于自己的全新人生。</x:v>
+        <x:v>阿梨一觉睡了三百年，养大的五只小兽尽数离去。她带着五只旧饭碗、十二枚铜钱与一把锈柴刀下山寻兽。昔日的小家伙已成威震四方的妖祖，历经重重相遇与揭秘，阿梨知晓三百年封印的真相，携手五只妖祖，一同对抗祸世灭灵兽神。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="n">
-        <x:v>76</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>重启人生，拒绝校花？</x:v>
+        <x:v>大坝边寻回的真千金</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>09-08 08:30</x:v>
+        <x:v>09-10 11:26</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
         <x:v>7</x:v>
@@ -2891,10 +3039,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G13" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H13" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I13" s="10" t="str">
         <x:v>其他</x:v>
@@ -2902,36 +3050,36 @@
       <x:c r="J13" s="11" t="str"/>
       <x:c r="K13" s="11" t="str"/>
       <x:c r="L13" s="10" t="str">
-        <x:v>肆漫简</x:v>
+        <x:v>喵琪琪追剧</x:v>
       </x:c>
       <x:c r="M13" s="10" t="str">
-        <x:v>白陌重生回到2004年高考夜，果断避开前世陷害自己的宾馆陷阱，救下被下药的校花江洛菡，彻底扭转人生走向。他不再执着于过往的情感执念，跳出卑微追爱的困局，转而关心恩师健康、规划学业与创业方向，结识志同道合的伙伴。凭借重生阅历清醒选择前路，把握青春重启人生，用行动改写原本遗憾的命运，活出全新成长轨迹。</x:v>
+        <x:v>大坝突发险情，农村女孩夏晚禾凭借熟悉的环境和过人的勇气，不顾危险救下被困的沈长洲。一次意外的救援，让两个陌生人的命运重新交织。随着调查深入，沈长洲发现这个善良坚韧的女孩，竟是自己失散二十年的亲生女儿。面对迟来的亲情和真假千金的风波，夏晚禾没有依靠身份改变人生，而是用智慧、担当和努力证明自己的价值。陆言川也在一次次并肩相处中，被她的真诚与坚强打动，陪她找回亲情，走向新的未来。</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="n">
-        <x:v>86</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>美颜系统开挂，大佬全跪下</x:v>
+        <x:v>穿越60我有空间不愁吃喝</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>09-09 00:10</x:v>
+        <x:v>09-07 00:04</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G14" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H14" s="11" t="n">
-        <x:v>172</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="I14" s="10" t="str">
         <x:v>其他</x:v>
@@ -2939,36 +3087,36 @@
       <x:c r="J14" s="11" t="str"/>
       <x:c r="K14" s="11" t="str"/>
       <x:c r="L14" s="10" t="str">
-        <x:v>御儿</x:v>
+        <x:v>夜珠AI剧场</x:v>
       </x:c>
       <x:c r="M14" s="10" t="str">
-        <x:v>曾因外形饱受非议的米珂华丽转身，蜕变得耀眼又夺目。从前对她嗤之以鼻的蒋少开始频频在意，素来冷眼毒舌的陆总不知不觉深陷其中，连一向克己的商界大佬也为她打破原则。米珂凭智商与手腕周旋于众人之间，上演一场势均力敌的情感博弈。没有俗套的救赎，只有双向的拉扯。看一众高高在上的精英暗自较劲、步步沉沦，心甘情愿为她卸下防备。</x:v>
+        <x:v>现代青年刘大壮意外穿越到60年代，成了同名同姓的16岁穷小子。原主因相亲被拒、家徒四壁，下河摸鱼时溺亡。大壮醒来后发现脑中多了一座九层宝塔空间——内有灵药田与灵泉潭水，作物两小时成熟、产量翻五倍。饥荒年代，别人啃树皮喝稀粥，他靠空间种出满仓土豆粮食，黑市换粮票钞票，让饿肚子的父母姐姐们吃上饱饭。从人人嘲笑的穷小子，到带着全家逆袭翻盘，且看他手握宝塔空间，在艰苦年代闯出一条吃喝不愁的逆袭</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>重生后我守住全村</x:v>
+        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
-        <x:v>09-10 08:08</x:v>
+        <x:v>09-11 09:00</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E15" s="11" t="n">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="F15" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G15" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H15" s="11" t="n">
-        <x:v>129</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="I15" s="10" t="str">
         <x:v>其他</x:v>
@@ -2976,36 +3124,36 @@
       <x:c r="J15" s="11" t="str"/>
       <x:c r="K15" s="11" t="str"/>
       <x:c r="L15" s="10" t="str">
-        <x:v>金果漫剧</x:v>
+        <x:v>阳阳动画</x:v>
       </x:c>
       <x:c r="M15" s="10" t="str">
-        <x:v>70年代冬，赵满仓在父亲离世后重回鼠灾前八天。面对家中骤变，他选择先护住亲人，带着前世经验迁入碾坊，储粮备药，筑墙防鼠，设点防疫。灾情来临时，他联合李杏儿，刘石头和乡亲稳住村庄，并用账册与规矩澄清父亲名誉。风雪过后，黎家沟建起防鼠坊，猫舍和净粮地窖，众人也在互助中迎来新生。</x:v>
+        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="n">
-        <x:v>93</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>全家施压：我反手签了过户合同</x:v>
+        <x:v>三分钱的取舍</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>09-08 16:58</x:v>
+        <x:v>09-10 17:29</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G16" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H16" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str">
         <x:v>其他</x:v>
@@ -3013,24 +3161,24 @@
       <x:c r="J16" s="11" t="str"/>
       <x:c r="K16" s="11" t="str"/>
       <x:c r="L16" s="10" t="str">
-        <x:v>灵川剧场</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="M16" s="10" t="str">
-        <x:v>儿子儿媳多次提议我搬回乡下养老，将城里的宽敞住房腾出来给女方父母长期居住。我笑着点头应下，转头便将这套三室朝南的江景房产挂牌出售，最终成交二百八十万元。我随即购置了一套一室一厅的小户型，更换门锁后独自入住。他们上门索要钥匙，我没有开门。名下房产我自有主张，谁也别想插手安排。</x:v>
+        <x:v>青石沟果农为省下代办三分钱，甩开中间商周成岳，直接对接收购商方洪生收桃。可脱离周成岳统筹调度后，摘桃、排单、装车乱象丛生，桃子积压损耗。周成岳转身接手偏远的十里湾桃园，凭口碑站稳脚跟。经历一季波折，青石沟众人幡然醒悟，重新读懂代办的价值。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>穿越60我有空间不愁吃喝</x:v>
+        <x:v>回到零四年进军彩铃界</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>09-07 00:04</x:v>
+        <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
         <x:v>6</x:v>
@@ -3039,47 +3187,41 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G17" s="11" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H17" s="11" t="n">
-        <x:v>1000</x:v>
-      </x:c>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="H17" s="11" t="str"/>
       <x:c r="I17" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J17" s="11" t="str"/>
       <x:c r="K17" s="11" t="str"/>
-      <x:c r="L17" s="10" t="str">
-        <x:v>夜珠AI剧场</x:v>
-      </x:c>
-      <x:c r="M17" s="10" t="str">
-        <x:v>现代青年刘大壮意外穿越到60年代，成了同名同姓的16岁穷小子。原主因相亲被拒、家徒四壁，下河摸鱼时溺亡。大壮醒来后发现脑中多了一座九层宝塔空间——内有灵药田与灵泉潭水，作物两小时成熟、产量翻五倍。饥荒年代，别人啃树皮喝稀粥，他靠空间种出满仓土豆粮食，黑市换粮票钞票，让饿肚子的父母姐姐们吃上饱饭。从人人嘲笑的穷小子，到带着全家逆袭翻盘，且看他手握宝塔空间，在艰苦年代闯出一条吃喝不愁的逆袭</x:v>
-      </x:c>
+      <x:c r="L17" s="10" t="str"/>
+      <x:c r="M17" s="10" t="str"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="n">
-        <x:v>29</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>三分钱的取舍</x:v>
+        <x:v>青牛引泉来</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>09-10 17:29</x:v>
+        <x:v>09-11 15:20</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G18" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H18" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="I18" s="10" t="str">
         <x:v>其他</x:v>
@@ -3087,36 +3229,37 @@
       <x:c r="J18" s="11" t="str"/>
       <x:c r="K18" s="11" t="str"/>
       <x:c r="L18" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>车仔漫</x:v>
       </x:c>
       <x:c r="M18" s="10" t="str">
-        <x:v>青石沟果农为省下代办三分钱，甩开中间商周成岳，直接对接收购商方洪生收桃。可脱离周成岳统筹调度后，摘桃、排单、装车乱象丛生，桃子积压损耗。周成岳转身接手偏远的十里湾桃园，凭口碑站稳脚跟。经历一季波折，青石沟众人幡然醒悟，重新读懂代办的价值。</x:v>
+        <x:v>大旱之年，贫苦庄稼汉石满仓为宽慰盼他成家的母亲，扎了个稻草媳妇，谁料草人竟化作姑娘阿禾。原来阿禾是有灵性的青牛，十年前大旱濒死时被石满仓用豆秸和水救下，此番借稻草人身躯前来报恩。
+阿禾感知到村井即将枯竭，带领众人找到被封堵的牛眠岭古泉。靠卖自家井水牟利的马有财因利益受损，百般阻挠，甚至污染泉水、堵塞闸口。</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
+        <x:v>七套房产，换来一纸调令</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>09-11 09:00</x:v>
+        <x:v>09-12 08:18</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E19" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="F19" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G19" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H19" s="11" t="n">
-        <x:v>133</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str">
         <x:v>其他</x:v>
@@ -3124,67 +3267,73 @@
       <x:c r="J19" s="11" t="str"/>
       <x:c r="K19" s="11" t="str"/>
       <x:c r="L19" s="10" t="str">
-        <x:v>阳阳动画</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="M19" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
+        <x:v>公婆将七套房产全数赠予小叔子，长子陈峰看似顺从鼓掌，实则暗中申请援疆调令。面对父母偏心和弟媳挑衅，陈峰携妻林晚隐忍筹备。最终在家庭会议上，他出示双人调令宣告远赴新疆，打破原生家庭剥削链条。经历异地磨砺与除夕和解，一家人终在理解中重建亲情边界，实现各自独立与成长。</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>一张废票毁了她</x:v>
+        <x:v>泰城错嫁</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>2026-09-11</x:v>
+        <x:v>09-12 21:10</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E20" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="F20" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G20" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H20" s="11" t="str"/>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H20" s="11" t="n">
+        <x:v>50</x:v>
+      </x:c>
       <x:c r="I20" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J20" s="11" t="str"/>
       <x:c r="K20" s="11" t="str"/>
-      <x:c r="L20" s="10" t="str"/>
-      <x:c r="M20" s="10" t="str"/>
+      <x:c r="L20" s="10" t="str">
+        <x:v>夜草剧场</x:v>
+      </x:c>
+      <x:c r="M20" s="10" t="str">
+        <x:v>二十世纪三十年代泰国，两姐妹姐妹同日嫁人，丑妹珠珠嫁帅气宋帕，美姐南佩却配憨汉啊光。迎亲途中大象突然发情，两对新人错上婚车、错入洞房。泼辣珠珠遇上憨厚啊光，闹洞房、斗婆婆，从互殴到相守；温柔南佩遇上冷脸宋帕，假装吵架赶走宾客，从陌生到动心。两对夫妻先后离婚，珠珠与啊光携手生子，南佩闯荡成舞台名角，与宋帕久别重逢。错的人成了对的人，两对冤家，各得圆满。</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>重生一世，我不再痴恋竹马</x:v>
+        <x:v>敢抢我的车位</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>09-10 10:00</x:v>
+        <x:v>09-11 18:00</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G21" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H21" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I21" s="10" t="str">
         <x:v>其他</x:v>
@@ -3192,52 +3341,58 @@
       <x:c r="J21" s="11" t="str"/>
       <x:c r="K21" s="11" t="str"/>
       <x:c r="L21" s="10" t="str">
-        <x:v>锦书映年华</x:v>
+        <x:v>石爷剧场</x:v>
       </x:c>
       <x:c r="M21" s="10" t="str">
-        <x:v>承平公主前世错恋齐远安，受尽磋磨含恨落幕。一朝重生，恰逢圣旨赐婚，齐远安却当众恳请解除婚约，求取太后义孙女傅明珠。她坦然放手，主动成全二人，看着他们得偿所愿。宁国侯夫人动用旧物强求赐婚，她巧妙改换婚事，选择边关归来、品性刚正的齐远舟。婚后她聪慧通透，看清傅明珠与齐远安的本性，冷眼旁观二人矛盾丛生。历经风波，她与齐远舟彼此扶持，挣脱过往伤痛，收获属于自己安稳坦荡的人生。</x:v>
+        <x:v>蒋依依低调返乡履行婚约，却在王氏集团门口因停车问题，与柳如烟和未婚夫王霸产生误会。随着双方接触加深，婚约背后的分歧也逐渐显现。面对王霸前后不同的态度，蒋依依选择坚持自己的原则，果断结束这段并不合适的关系。与此同时，一场意外车辆纠纷也进入正式处理程序。原本普通的一次停车风波，让几个人重新认识彼此，也让蒋依依更加坚定了自己的选择。</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="n">
-        <x:v>89</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>回到零四年进军彩铃界</x:v>
+        <x:v>锦书迟</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>2026-09-11</x:v>
+        <x:v>09-12 07:30</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E22" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E22" s="11" t="n">
+      <x:c r="F22" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G22" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F22" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G22" s="11" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H22" s="11" t="str"/>
+      <x:c r="H22" s="11" t="n">
+        <x:v>58</x:v>
+      </x:c>
       <x:c r="I22" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J22" s="11" t="str"/>
       <x:c r="K22" s="11" t="str"/>
-      <x:c r="L22" s="10" t="str"/>
-      <x:c r="M22" s="10" t="str"/>
+      <x:c r="L22" s="10" t="str">
+        <x:v>咩咩漫文</x:v>
+      </x:c>
+      <x:c r="M22" s="10" t="str">
+        <x:v>三年前，沈昭昭嫁与永宁侯谢凛，新婚燕尔他便远赴边关。她苦等家书，却不知双向书信早被人暗中截留。她终于心冷离开侯府。三年后，她带着孩子在市井支摊卖画立足，他却循着蛛丝马迹寻来，真相层层揭开，原来他从未负她。</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>泰城错嫁</x:v>
+        <x:v>我送弟弟上青云</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>09-12 21:10</x:v>
+        <x:v>09-12 09:52</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
         <x:v>4</x:v>
@@ -3249,10 +3404,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G23" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H23" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
         <x:v>其他</x:v>
@@ -3260,24 +3415,24 @@
       <x:c r="J23" s="11" t="str"/>
       <x:c r="K23" s="11" t="str"/>
       <x:c r="L23" s="10" t="str">
-        <x:v>夜草剧场</x:v>
+        <x:v>落云</x:v>
       </x:c>
       <x:c r="M23" s="10" t="str">
-        <x:v>二十世纪三十年代泰国，两姐妹姐妹同日嫁人，丑妹珠珠嫁帅气宋帕，美姐南佩却配憨汉啊光。迎亲途中大象突然发情，两对新人错上婚车、错入洞房。泼辣珠珠遇上憨厚啊光，闹洞房、斗婆婆，从互殴到相守；温柔南佩遇上冷脸宋帕，假装吵架赶走宾客，从陌生到动心。两对夫妻先后离婚，珠珠与啊光携手生子，南佩闯荡成舞台名角，与宋帕久别重逢。错的人成了对的人，两对冤家，各得圆满。</x:v>
+        <x:v>宋远回乡发现弟弟宋临被父亲剥夺上学权利，只能干农活。他毅然带走弟弟，用微薄工资供他读书。宋临考上名校建筑系，毕业后成为身价过亿的设计师。他用第一桶金给哥哥买房，报答当年恩情。面对迟来求和的父亲，宋临完成了心灵的真正和解。这是一个关于“长兄如父、手足情深”的故事，诠释了扶助与感恩的力量。</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>青牛引泉来</x:v>
+        <x:v>重生山火前，我舍祖宅护全家</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>09-11 15:20</x:v>
+        <x:v>09-12 16:06</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
         <x:v>5</x:v>
@@ -3286,10 +3441,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G24" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H24" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="I24" s="10" t="str">
         <x:v>其他</x:v>
@@ -3297,25 +3452,24 @@
       <x:c r="J24" s="11" t="str"/>
       <x:c r="K24" s="11" t="str"/>
       <x:c r="L24" s="10" t="str">
-        <x:v>车仔漫</x:v>
+        <x:v>千鹤动漫</x:v>
       </x:c>
       <x:c r="M24" s="10" t="str">
-        <x:v>大旱之年，贫苦庄稼汉石满仓为宽慰盼他成家的母亲，扎了个稻草媳妇，谁料草人竟化作姑娘阿禾。原来阿禾是有灵性的青牛，十年前大旱濒死时被石满仓用豆秸和水救下，此番借稻草人身躯前来报恩。
-阿禾感知到村井即将枯竭，带领众人找到被封堵的牛眠岭古泉。靠卖自家井水牟利的马有财因利益受损，百般阻挠，甚至污染泉水、堵塞闸口。</x:v>
+        <x:v>顾长河带着前世山火中痛失全家的记忆重生归来，得知三日后西岭大火将再次席卷村庄，他不顾众人质疑，卖掉祖宅，带着妻子母亲和儿子搬上白石坡，储水备粮清出防火带，只为改写一家人的命运，当烈火真正逼近，所有人终于明白，他舍掉的只是房子，拼命守住的才是真正的家。</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>七套房产，换来一纸调令</x:v>
+        <x:v>我的师兄全是修仙界大佬</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>09-12 08:18</x:v>
+        <x:v>09-11 18:16</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
         <x:v>5</x:v>
@@ -3324,10 +3478,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G25" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H25" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str">
         <x:v>其他</x:v>
@@ -3335,21 +3489,21 @@
       <x:c r="J25" s="11" t="str"/>
       <x:c r="K25" s="11" t="str"/>
       <x:c r="L25" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>大公鸡剧场</x:v>
       </x:c>
       <x:c r="M25" s="10" t="str">
-        <x:v>公婆将七套房产全数赠予小叔子，长子陈峰看似顺从鼓掌，实则暗中申请援疆调令。面对父母偏心和弟媳挑衅，陈峰携妻林晚隐忍筹备。最终在家庭会议上，他出示双人调令宣告远赴新疆，打破原生家庭剥削链条。经历异地磨砺与除夕和解，一家人终在理解中重建亲情边界，实现各自独立与成长。</x:v>
+        <x:v>六岁的女主奉师父顾青崖之命下山历练，寻找五位失散数百年的师兄。她天生神力，把九品丹药当糖豆吃，背着重剑闯修仙界。本以为师兄们在外落魄难归，却发现大师兄是正道第一人九天仙尊，二师兄是统御九幽的幽冥帝君，余下三位也皆是绝世大佬。小奶娃一路闯荡，把隐世多年的师兄们挨个喊回了家。</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>锦书迟</x:v>
+        <x:v>双姝逢旧岸，一怒扫尘奸</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
-        <x:v>09-12 07:30</x:v>
+        <x:v>09-12 11:00</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
         <x:v>4</x:v>
@@ -3361,10 +3515,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G26" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H26" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I26" s="10" t="str">
         <x:v>其他</x:v>
@@ -3372,21 +3526,21 @@
       <x:c r="J26" s="11" t="str"/>
       <x:c r="K26" s="11" t="str"/>
       <x:c r="L26" s="10" t="str">
-        <x:v>咩咩漫文</x:v>
+        <x:v>情深剧场</x:v>
       </x:c>
       <x:c r="M26" s="10" t="str">
-        <x:v>三年前，沈昭昭嫁与永宁侯谢凛，新婚燕尔他便远赴边关。她苦等家书，却不知双向书信早被人暗中截留。她终于心冷离开侯府。三年后，她带着孩子在市井支摊卖画立足，他却循着蛛丝马迹寻来，真相层层揭开，原来他从未负她。</x:v>
+        <x:v>毒人谷圣女荼蘼，收到失散孪生妹妹、当朝义女公主沈青芜的求助。妹妹身中剧毒命不久矣，恳求容貌一致的她顶替自己进入公主府，守护一双饱受欺凌的儿女。荼蘼踏入危机四伏的公主府，手撕虚伪驸马、跋扈老夫人与心机妾室，为受磋磨的嫡女灵犀、桀骜少年沈琢玉撑腰。她以蛊术为妹妹解毒，在寿宴揭穿敌人诬陷邪祟的阴谋，亮出本命黑蟒，助妹妹夺回一切。历经风波，姐妹二人携手，守护孩子，收获难得的人间温情。</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>重生山火前，我舍祖宅护全家</x:v>
+        <x:v>退婚从抢我车位开始</x:v>
       </x:c>
       <x:c r="C27" s="11" t="str">
-        <x:v>09-12 16:06</x:v>
+        <x:v>2026-09-12</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
         <x:v>4</x:v>
@@ -3398,32 +3552,26 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G27" s="11" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H27" s="11" t="n">
-        <x:v>89</x:v>
-      </x:c>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H27" s="11" t="str"/>
       <x:c r="I27" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J27" s="11" t="str"/>
       <x:c r="K27" s="11" t="str"/>
-      <x:c r="L27" s="10" t="str">
-        <x:v>千鹤动漫</x:v>
-      </x:c>
-      <x:c r="M27" s="10" t="str">
-        <x:v>顾长河带着前世山火中痛失全家的记忆重生归来，得知三日后西岭大火将再次席卷村庄，他不顾众人质疑，卖掉祖宅，带着妻子母亲和儿子搬上白石坡，储水备粮清出防火带，只为改写一家人的命运，当烈火真正逼近，所有人终于明白，他舍掉的只是房子，拼命守住的才是真正的家。</x:v>
-      </x:c>
+      <x:c r="L27" s="10" t="str"/>
+      <x:c r="M27" s="10" t="str"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="11" t="n">
-        <x:v>43</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>我送弟弟上青云</x:v>
+        <x:v>提分手那天，我的任职令刚下来</x:v>
       </x:c>
       <x:c r="C28" s="11" t="str">
-        <x:v>09-12 09:52</x:v>
+        <x:v>09-12 07:40</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
         <x:v>4</x:v>
@@ -3435,10 +3583,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G28" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H28" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="I28" s="10" t="str">
         <x:v>其他</x:v>
@@ -3446,21 +3594,21 @@
       <x:c r="J28" s="11" t="str"/>
       <x:c r="K28" s="11" t="str"/>
       <x:c r="L28" s="10" t="str">
-        <x:v>落云</x:v>
+        <x:v>星漫世界</x:v>
       </x:c>
       <x:c r="M28" s="10" t="str">
-        <x:v>宋远回乡发现弟弟宋临被父亲剥夺上学权利，只能干农活。他毅然带走弟弟，用微薄工资供他读书。宋临考上名校建筑系，毕业后成为身价过亿的设计师。他用第一桶金给哥哥买房，报答当年恩情。面对迟来求和的父亲，宋临完成了心灵的真正和解。这是一个关于“长兄如父、手足情深”的故事，诠释了扶助与感恩的力量。</x:v>
+        <x:v>澜江市，刚结束七年恋情的江晓棠如愿上岸，决然转身离去。没曾想，前男友贺铭以转业安置身份，空降进入同一应急管理局。旧爱狭路相逢，尴尬拉扯还未落幕，滨南快速路突发危化品连环车祸。报到首日的贺铭无视现场命令，冲破警戒线冲入火场，拼尽全力营救被困女童。就在撤离瞬间轿车爆炸，火光席卷全场，他纵身将怀中女孩与赶来的女医生向澜舒一并护在身下。</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>敢抢我的车位</x:v>
+        <x:v>重生1985年，赶海我有系统</x:v>
       </x:c>
       <x:c r="C29" s="11" t="str">
-        <x:v>09-11 18:00</x:v>
+        <x:v>09-11 07:00</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
         <x:v>5</x:v>
@@ -3472,10 +3620,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G29" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H29" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="I29" s="10" t="str">
         <x:v>其他</x:v>
@@ -3483,33 +3631,33 @@
       <x:c r="J29" s="11" t="str"/>
       <x:c r="K29" s="11" t="str"/>
       <x:c r="L29" s="10" t="str">
-        <x:v>石爷剧场</x:v>
+        <x:v>依语动漫</x:v>
       </x:c>
       <x:c r="M29" s="10" t="str">
-        <x:v>蒋依依低调返乡履行婚约，却在王氏集团门口因停车问题，与柳如烟和未婚夫王霸产生误会。随着双方接触加深，婚约背后的分歧也逐渐显现。面对王霸前后不同的态度，蒋依依选择坚持自己的原则，果断结束这段并不合适的关系。与此同时，一场意外车辆纠纷也进入正式处理程序。原本普通的一次停车风波，让几个人重新认识彼此，也让蒋依依更加坚定了自己的选择。</x:v>
+        <x:v>八十年代小渔村，林舟出钱出力帮家里盖起红砖新房，落成之日却遭到父母兄长算计，新房被夺走，自己只分得被搬空的破旧老屋。带着前世被家人压榨到老的遗憾，重活一世的林舟不再愚孝，请来村长当众分家切割亲缘。绝境之中，他意外激活渔业情报系统，可以接收大海给出的渔获线索。他借得工具赶海，捞获珍贵大石斑鱼赚取第一笔启动资金，又约上好友李二狗大雾天冒险出海，依靠系统指引追逐鱼群。</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>退婚从抢我车位开始</x:v>
+        <x:v>穿成恋爱脑女配，我把将军府带偏了呀</x:v>
       </x:c>
       <x:c r="C30" s="11" t="str">
-        <x:v>2026-09-12</x:v>
+        <x:v>2026-09-06</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G30" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H30" s="11" t="str"/>
       <x:c r="I30" s="10" t="str">
@@ -3522,28 +3670,28 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>今天开始做裴总</x:v>
+        <x:v>我月薪八千，但公司是我的</x:v>
       </x:c>
       <x:c r="C31" s="11" t="str">
-        <x:v>09-12 19:48</x:v>
+        <x:v>09-09 20:47</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G31" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H31" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I31" s="10" t="str">
         <x:v>其他</x:v>
@@ -3551,10 +3699,10 @@
       <x:c r="J31" s="11" t="str"/>
       <x:c r="K31" s="11" t="str"/>
       <x:c r="L31" s="10" t="str">
-        <x:v>严墨墨</x:v>
+        <x:v>阿宝剧场</x:v>
       </x:c>
       <x:c r="M31" s="10" t="str">
-        <x:v>裴野低调蛰伏三年，甘愿扮作普通员工，在公司默默沉淀，面对职场非议、旁人轻视从未辩解。年会之上，他惨遭当众开除，相伴多年的婚姻也走向终点，跌入人生低谷。褪去伪装，他不再刻意隐忍，解锁真实身份，告别敷衍度日的过往。一路轻松逆袭，打破所有人的偏见，凭自身实力惊艳全场，开启属于自己的全新人生。</x:v>
+        <x:v>北辰科技创始人陆景川为人低调，相亲时只坦言月薪八千，当即被相亲对象乔思雨嫌弃离场，还被对方在朋友圈造谣成“蹭咖啡捞男”。后续乔思雨应聘北辰科技、出席投资饭局，接连撞见陆景川，场面屡屡社死。陆景川却在常去的咖啡厅，因店员沈安然的仗义执言，窥见了比金钱更动人的真心。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3609,16 +3757,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>5.2</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F2" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>2026-09-16 04-21</x:v>
+        <x:v>2026-09-16 08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3626,22 +3774,22 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>听水小锦鲤</x:v>
+        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
       </x:c>
       <x:c r="C3" s="11" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
-        <x:v>6.7</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F3" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>2026-09-16 04-21</x:v>
+        <x:v>2026-09-16 08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -3649,22 +3797,22 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>七套房产，换来一纸调令</x:v>
+        <x:v>听水小锦鲤</x:v>
       </x:c>
       <x:c r="C4" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>10.8</x:v>
+        <x:v>8.3</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F4" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>2026-09-16 04-21</x:v>
+        <x:v>2026-09-16 08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3672,22 +3820,22 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>今晚查寝，别开门</x:v>
+        <x:v>搬进江景房，老公每晚对着鱼缸坐两小时</x:v>
       </x:c>
       <x:c r="C5" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>6.8</x:v>
+        <x:v>6.9</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F5" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>2026-09-16 04-21</x:v>
+        <x:v>2026-09-16 08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -3695,22 +3843,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
+        <x:v>今晚查寝，别开门</x:v>
       </x:c>
       <x:c r="C6" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>7.3</x:v>
+        <x:v>7.7</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F6" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>2026-09-16 04-21</x:v>
+        <x:v>2026-09-16 08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3718,22 +3866,22 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>搬进江景房，老公每晚对着鱼缸坐两小时</x:v>
+        <x:v>七套房产，换来一纸调令</x:v>
       </x:c>
       <x:c r="C7" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>6.7</x:v>
+        <x:v>12.1</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F7" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>2026-09-16 04-21</x:v>
+        <x:v>2026-09-16 06-44</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -3741,22 +3889,22 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
+        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
       </x:c>
       <x:c r="C8" s="11" t="n">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>12.9</x:v>
+        <x:v>4.6</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>2026-09-16 04-21</x:v>
+        <x:v>2026-09-16 08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3764,22 +3912,22 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
+        <x:v>15年青春苦守，未婚夫装穷归来</x:v>
       </x:c>
       <x:c r="C9" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>1.7</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>2026-09-16 04-21</x:v>
+        <x:v>2026-09-16 08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -3787,22 +3935,22 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>重生三天前，我用水泥封死地下室</x:v>
+        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
       </x:c>
       <x:c r="C10" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>12.6</x:v>
+        <x:v>12.9</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="F10" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>2026-09-15 23-11</x:v>
+        <x:v>2026-09-16 08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -3813,19 +3961,19 @@
         <x:v>青牛引泉来</x:v>
       </x:c>
       <x:c r="C11" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>12.4</x:v>
+        <x:v>12.5</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
-        <x:v>2026-09-16 04-21</x:v>
+        <x:v>2026-09-16 08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -3833,22 +3981,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
+        <x:v>重回82：我成山君契约万兽打猎宠妻</x:v>
       </x:c>
       <x:c r="C12" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>11.2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G12" s="11" t="str">
-        <x:v>2026-09-15 21-11</x:v>
+        <x:v>2026-09-16 08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -3856,22 +4004,22 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>15年青春苦守，未婚夫装穷归来</x:v>
+        <x:v>新厂旧账</x:v>
       </x:c>
       <x:c r="C13" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>1.9</x:v>
+        <x:v>8.7</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G13" s="11" t="str">
-        <x:v>2026-09-16 04-21</x:v>
+        <x:v>2026-09-16 08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -3879,22 +4027,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>重回82：我成山君契约万兽打猎宠妻</x:v>
+        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
       </x:c>
       <x:c r="C14" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>6.2</x:v>
+        <x:v>11.4</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G14" s="11" t="str">
-        <x:v>2026-09-16 04-21</x:v>
+        <x:v>2026-09-16 08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -3902,22 +4050,22 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>新厂旧账</x:v>
+        <x:v>重生三天前，我用水泥封死地下室</x:v>
       </x:c>
       <x:c r="C15" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>8.9</x:v>
+        <x:v>12.7</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F15" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G15" s="11" t="str">
-        <x:v>2026-09-16 04-21</x:v>
+        <x:v>2026-09-16 08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -3925,22 +4073,22 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>破库房的秘密</x:v>
+        <x:v>晚棠知归，七年终见你</x:v>
       </x:c>
       <x:c r="C16" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>15.4</x:v>
+        <x:v>4.2</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G16" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-16 08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -3948,22 +4096,22 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>晚棠知归，七年终见你</x:v>
+        <x:v>穿书后我带萌宝上门认爹</x:v>
       </x:c>
       <x:c r="C17" s="11" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>4.8</x:v>
+        <x:v>14.9</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F17" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G17" s="11" t="str">
-        <x:v>2026-09-16 04-21</x:v>
+        <x:v>2026-09-16 08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -3994,22 +4142,22 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>穿书后我带萌宝上门认爹</x:v>
+        <x:v>一墙之隔，皆是人心</x:v>
       </x:c>
       <x:c r="C19" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>15.1</x:v>
+        <x:v>13.1</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G19" s="11" t="str">
-        <x:v>2026-09-16 03-11</x:v>
+        <x:v>2026-09-15 20-11</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -4017,22 +4165,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>三分钱的取舍</x:v>
+        <x:v>破库房的秘密</x:v>
       </x:c>
       <x:c r="C20" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>14.5</x:v>
+        <x:v>15.8</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G20" s="11" t="str">
-        <x:v>2026-09-15 18-11</x:v>
+        <x:v>2026-09-16 02-11</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -4040,22 +4188,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>一墙之隔，皆是人心</x:v>
+        <x:v>因为大黄遇见你</x:v>
       </x:c>
       <x:c r="C21" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>13.5</x:v>
+        <x:v>14.7</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G21" s="11" t="str">
-        <x:v>2026-09-15 20-11</x:v>
+        <x:v>2026-09-16 06-44</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -4063,22 +4211,22 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>离家十年，回来女儿被换了</x:v>
+        <x:v>穿越60我有空间不愁吃喝</x:v>
       </x:c>
       <x:c r="C22" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D22" s="11" t="n">
+        <x:v>16.8</x:v>
+      </x:c>
+      <x:c r="E22" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D22" s="11" t="n">
-        <x:v>11.2</x:v>
-      </x:c>
-      <x:c r="E22" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="F22" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G22" s="11" t="str">
-        <x:v>2026-09-15 22-11</x:v>
+        <x:v>2026-09-16 08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -4086,22 +4234,22 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>惊絮无声：傻女的绝杀</x:v>
+        <x:v>三分钱的取舍</x:v>
       </x:c>
       <x:c r="C23" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>12.8</x:v>
+        <x:v>16.6</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G23" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-15 18-11</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -4109,22 +4257,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>我在工地卖盒饭带火一座城</x:v>
+        <x:v>离家十年，回来女儿被换了</x:v>
       </x:c>
       <x:c r="C24" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>12.9</x:v>
+        <x:v>14.9</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G24" s="11" t="str">
-        <x:v>2026-09-15 21-11</x:v>
+        <x:v>2026-09-15 22-11</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -4132,22 +4280,22 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>因为大黄遇见你</x:v>
+        <x:v>一针绣出自己的路</x:v>
       </x:c>
       <x:c r="C25" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>14.4</x:v>
+        <x:v>16.9</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G25" s="11" t="str">
-        <x:v>2026-09-16 04-21</x:v>
+        <x:v>2026-09-16 08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -4155,22 +4303,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>不靠谱爸妈很靠谱</x:v>
+        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
       </x:c>
       <x:c r="C26" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>16.1</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G26" s="11" t="str">
-        <x:v>2026-09-15 11-11</x:v>
+        <x:v>2026-09-16 06-44</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -4178,22 +4326,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
+        <x:v>我在工地卖盒饭带火一座城</x:v>
       </x:c>
       <x:c r="C27" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>16.1</x:v>
+        <x:v>12.9</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str">
-        <x:v>2026-09-15 10-11</x:v>
+        <x:v>2026-09-15 21-11</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -4201,22 +4349,22 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>泰城错嫁</x:v>
+        <x:v>不靠谱爸妈很靠谱</x:v>
       </x:c>
       <x:c r="C28" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
-        <x:v>15.6</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F28" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G28" s="11" t="str">
-        <x:v>2026-09-16 04-21</x:v>
+        <x:v>2026-09-15 11-11</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -4224,22 +4372,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>一盒印泥引发的全局封锁</x:v>
+        <x:v>四个崽崽瞒不住了</x:v>
       </x:c>
       <x:c r="C29" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>16.4</x:v>
+        <x:v>16.1</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str">
-        <x:v>2026-09-15 21-11</x:v>
+        <x:v>2026-09-15 10-11</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -4247,22 +4395,22 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>八零悍妇：女汉子逆袭记</x:v>
+        <x:v>泰城错嫁</x:v>
       </x:c>
       <x:c r="C30" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>10.8</x:v>
+        <x:v>15.6</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G30" s="11" t="str">
-        <x:v>2026-09-15 15-11</x:v>
+        <x:v>2026-09-16 04-21</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -4270,22 +4418,22 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>大坝边寻回的真千金</x:v>
+        <x:v>一盒印泥引发的全局封锁</x:v>
       </x:c>
       <x:c r="C31" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
-        <x:v>12.8</x:v>
+        <x:v>16.4</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G31" s="11" t="str">
-        <x:v>2026-09-16 03-11</x:v>
+        <x:v>2026-09-15 21-11</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -4293,22 +4441,22 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="10" t="str">
-        <x:v>穿越60我有空间不愁吃喝</x:v>
+        <x:v>被诬陷诊出喜脉，重活一世我逆转前尘</x:v>
       </x:c>
       <x:c r="C32" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D32" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>4.7</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G32" s="11" t="str">
-        <x:v>2026-09-16 04-21</x:v>
+        <x:v>2026-09-16 08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -4316,22 +4464,22 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="10" t="str">
-        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
+        <x:v>八零悍妇：女汉子逆袭记</x:v>
       </x:c>
       <x:c r="C33" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D33" s="11" t="n">
-        <x:v>16.6</x:v>
+        <x:v>10.8</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F33" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G33" s="11" t="str">
-        <x:v>2026-09-16 04-21</x:v>
+        <x:v>2026-09-15 15-11</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -4339,22 +4487,22 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="10" t="str">
-        <x:v>退婚后我在七零赚钱养家致富</x:v>
+        <x:v>惊絮无声：傻女的绝杀</x:v>
       </x:c>
       <x:c r="C34" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D34" s="11" t="n">
-        <x:v>17.2</x:v>
+        <x:v>14.2</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F34" s="11" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="F34" s="11" t="n">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="G34" s="11" t="str">
-        <x:v>2026-09-15 10-11</x:v>
+        <x:v>2026-09-16 02-11</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -4362,22 +4510,22 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="10" t="str">
-        <x:v>今天开始做裴总</x:v>
+        <x:v>退婚后我在七零赚钱养家致富</x:v>
       </x:c>
       <x:c r="C35" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D35" s="11" t="n">
-        <x:v>7.5</x:v>
+        <x:v>17.2</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F35" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G35" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-15 10-11</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -4385,22 +4533,22 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="10" t="str">
-        <x:v>离婚那天我多了个痞帅老爹</x:v>
+        <x:v>我都元婴期了，你跟我说开学</x:v>
       </x:c>
       <x:c r="C36" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
-        <x:v>11.2</x:v>
+        <x:v>12.8</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G36" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-16 08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -4408,22 +4556,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="10" t="str">
-        <x:v>一针绣出自己的路</x:v>
+        <x:v>辣媳进门，我给公婆撑腰</x:v>
       </x:c>
       <x:c r="C37" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D37" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G37" s="11" t="str">
-        <x:v>2026-09-16 03-11</x:v>
+        <x:v>2026-09-15 06-08</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -4431,22 +4579,22 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="10" t="str">
-        <x:v>辣媳进门，我给公婆撑腰</x:v>
+        <x:v>我的游戏好友现实里全是大佬</x:v>
       </x:c>
       <x:c r="C38" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D38" s="11" t="n">
+        <x:v>4.7</x:v>
+      </x:c>
+      <x:c r="E38" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F38" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E38" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F38" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="G38" s="11" t="str">
-        <x:v>2026-09-15 06-08</x:v>
+        <x:v>2026-09-16 02-11</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -4454,22 +4602,22 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="10" t="str">
-        <x:v>我的游戏好友现实里全是大佬</x:v>
+        <x:v>攻略失败后我不装了</x:v>
       </x:c>
       <x:c r="C39" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D39" s="11" t="n">
-        <x:v>4.7</x:v>
+        <x:v>9.3</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G39" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-16 01-11</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -4477,22 +4625,22 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="10" t="str">
-        <x:v>攻略失败后我不装了</x:v>
+        <x:v>傅少你夫人又在扮猪吃虎了</x:v>
       </x:c>
       <x:c r="C40" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D40" s="11" t="n">
-        <x:v>9.3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G40" s="11" t="str">
-        <x:v>2026-09-16 01-11</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -4500,22 +4648,22 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="10" t="str">
-        <x:v>傅少你夫人又在扮猪吃虎了</x:v>
+        <x:v>红烛错缘，另寻良人</x:v>
       </x:c>
       <x:c r="C41" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D41" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>10.7</x:v>
       </x:c>
       <x:c r="E41" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F41" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="G41" s="11" t="str">
-        <x:v>2026-09-16 03-11</x:v>
+        <x:v>2026-09-16 02-11</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -4523,22 +4671,22 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B42" s="10" t="str">
-        <x:v>红烛错缘，另寻良人</x:v>
+        <x:v>抢个新娘来当后娘第一季</x:v>
       </x:c>
       <x:c r="C42" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D42" s="11" t="n">
-        <x:v>10.7</x:v>
+        <x:v>18.7</x:v>
       </x:c>
       <x:c r="E42" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F42" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G42" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-16 08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -4546,22 +4694,22 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" s="10" t="str">
-        <x:v>拂衣震九州</x:v>
+        <x:v>小福星驾到，通通闪开第一季</x:v>
       </x:c>
       <x:c r="C43" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D43" s="11" t="n">
-        <x:v>10.3</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="E43" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F43" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G43" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-16 01-11</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -4569,22 +4717,22 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="10" t="str">
-        <x:v>闪婚老公有点野</x:v>
+        <x:v>家有新章</x:v>
       </x:c>
       <x:c r="C44" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D44" s="11" t="n">
-        <x:v>16.3</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E44" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F44" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G44" s="11" t="str">
-        <x:v>2026-09-15 06-54</x:v>
+        <x:v>2026-09-15 23-11</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -4592,22 +4740,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="10" t="str">
-        <x:v>山下是绝路，山上是生门</x:v>
+        <x:v>大坝边寻回的真千金</x:v>
       </x:c>
       <x:c r="C45" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D45" s="11" t="n">
-        <x:v>14.3</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E45" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F45" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G45" s="11" t="str">
-        <x:v>2026-09-15 03-38</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -4615,22 +4763,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B46" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
+        <x:v>被女神抛弃：我却在荒岛吃香喝辣</x:v>
       </x:c>
       <x:c r="C46" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D46" s="11" t="n">
-        <x:v>17.7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E46" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F46" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G46" s="11" t="str">
-        <x:v>2026-09-15 06-08</x:v>
+        <x:v>2026-09-15 12-43</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -4638,22 +4786,22 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B47" s="10" t="str">
-        <x:v>被诬陷诊出喜脉，重活一世我逆转前尘</x:v>
+        <x:v>一纸离书赴南港</x:v>
       </x:c>
       <x:c r="C47" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D47" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E47" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F47" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G47" s="11" t="str">
-        <x:v>2026-09-16 04-21</x:v>
+        <x:v>2026-09-15 12-43</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -4661,22 +4809,22 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B48" s="10" t="str">
-        <x:v>小福星驾到，通通闪开第一季</x:v>
+        <x:v>前妻让我净身出户，我撤资离场</x:v>
       </x:c>
       <x:c r="C48" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D48" s="11" t="n">
-        <x:v>8.5</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E48" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F48" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G48" s="11" t="str">
-        <x:v>2026-09-16 01-11</x:v>
+        <x:v>2026-09-16 05-11</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -4684,22 +4832,22 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B49" s="10" t="str">
-        <x:v>家有新章</x:v>
+        <x:v>七年，抵不过她男闺蜜一张机票</x:v>
       </x:c>
       <x:c r="C49" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D49" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E49" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F49" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G49" s="11" t="str">
-        <x:v>2026-09-15 23-11</x:v>
+        <x:v>2026-09-15 14-11</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -4707,22 +4855,22 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B50" s="10" t="str">
-        <x:v>假老板娘遇上真董事长</x:v>
+        <x:v>300块报销单，作没了一家千万公司</x:v>
       </x:c>
       <x:c r="C50" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D50" s="11" t="n">
-        <x:v>12.5</x:v>
+        <x:v>13.5</x:v>
       </x:c>
       <x:c r="E50" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F50" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G50" s="11" t="str">
-        <x:v>2026-09-15 02-44</x:v>
+        <x:v>2026-09-15 12-43</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -4730,22 +4878,22 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B51" s="10" t="str">
-        <x:v>被女神抛弃：我却在荒岛吃香喝辣</x:v>
+        <x:v>一碗剩饭，看清二十五年工友情</x:v>
       </x:c>
       <x:c r="C51" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D51" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E51" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F51" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G51" s="11" t="str">
-        <x:v>2026-09-15 12-43</x:v>
+        <x:v>2026-09-15 14-11</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -22499,7 +22647,7 @@
         <x:v>已上榜</x:v>
       </x:c>
       <x:c r="I120" s="10" t="str">
-        <x:v>2026-09-12、2026-09-13、2026-09-14、2026-09-15</x:v>
+        <x:v>2026-09-12、2026-09-13、2026-09-14、2026-09-15、2026-09-16</x:v>
       </x:c>
       <x:c r="J120" s="10" t="str">
         <x:v>澜江市，刚结束七年恋情的江晓棠如愿上岸，决然转身离去。没曾想，前男友贺铭以转业安置身份，空降进入同一应急管理局。旧爱狭路相逢，尴尬拉扯还未落幕，滨南快速路突发危化品连环车祸。报到首日的贺铭无视现场命令，冲破警戒线冲入火场，拼尽全力营救被困女童。就在撤离瞬间轿车爆炸，火光席卷全场，他纵身将怀中女孩与赶来的女医生向澜舒一并护在身下。</x:v>
@@ -30782,10 +30930,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>981</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>54.0%</x:v>
+        <x:v>54.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -30796,7 +30944,7 @@
         <x:v>482</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>26.5%</x:v>
+        <x:v>26.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -30804,7 +30952,7 @@
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>355</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
         <x:v>19.5%</x:v>
@@ -30834,7 +30982,7 @@
         <x:v>189</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>11.4%</x:v>
+        <x:v>11.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -30842,7 +30990,7 @@
         <x:v>50-79集</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>713</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
         <x:v>42.8%</x:v>
@@ -30853,10 +31001,10 @@
         <x:v>80-99集</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>206</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>12.4%</x:v>
+        <x:v>12.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -30864,7 +31012,7 @@
         <x:v>100集以上</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>554</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
         <x:v>33.3%</x:v>
@@ -30891,7 +31039,7 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>807</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
         <x:v>44.4%</x:v>
@@ -30902,7 +31050,7 @@
         <x:v>婚姻/情感</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>322</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
         <x:v>17.7%</x:v>
@@ -30916,7 +31064,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>8.9%</x:v>
+        <x:v>8.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -30924,10 +31072,10 @@
         <x:v>年代怀旧/种田囤货</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>8.7%</x:v>
+        <x:v>8.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -30938,7 +31086,7 @@
         <x:v>158</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>8.7%</x:v>
+        <x:v>8.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -30946,7 +31094,7 @@
         <x:v>战神/异能/爽文</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>150</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
         <x:v>8.3%</x:v>
@@ -30960,7 +31108,7 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>6.3%</x:v>
+        <x:v>6.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -30968,7 +31116,7 @@
         <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
         <x:v>5.7%</x:v>
@@ -30990,7 +31138,7 @@
         <x:v>都市职场</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
         <x:v>4.2%</x:v>
@@ -31014,7 +31162,7 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="10" t="str">
-        <x:v>上榜32次</x:v>
+        <x:v>上榜33次</x:v>
       </x:c>
       <x:c r="B29" s="11" t="n">
         <x:v>1</x:v>
@@ -31036,73 +31184,73 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="10" t="str">
-        <x:v>上榜28次</x:v>
+        <x:v>上榜29次</x:v>
       </x:c>
       <x:c r="B31" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C31" s="11" t="str">
-        <x:v>0.2%</x:v>
+        <x:v>0.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="10" t="str">
-        <x:v>上榜26次</x:v>
+        <x:v>上榜28次</x:v>
       </x:c>
       <x:c r="B32" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C32" s="11" t="str">
-        <x:v>0.2%</x:v>
+        <x:v>0.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="10" t="str">
-        <x:v>上榜23次</x:v>
+        <x:v>上榜26次</x:v>
       </x:c>
       <x:c r="B33" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C33" s="11" t="str">
-        <x:v>0.1%</x:v>
+        <x:v>0.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="10" t="str">
-        <x:v>上榜22次</x:v>
+        <x:v>上榜23次</x:v>
       </x:c>
       <x:c r="B34" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C34" s="11" t="str">
-        <x:v>0.2%</x:v>
+        <x:v>0.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="10" t="str">
-        <x:v>上榜21次</x:v>
+        <x:v>上榜22次</x:v>
       </x:c>
       <x:c r="B35" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C35" s="11" t="str">
-        <x:v>0.1%</x:v>
+        <x:v>0.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="10" t="str">
-        <x:v>上榜20次</x:v>
+        <x:v>上榜21次</x:v>
       </x:c>
       <x:c r="B36" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C36" s="11" t="str">
-        <x:v>0.2%</x:v>
+        <x:v>0.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="10" t="str">
-        <x:v>上榜19次</x:v>
+        <x:v>上榜20次</x:v>
       </x:c>
       <x:c r="B37" s="11" t="n">
         <x:v>3</x:v>
@@ -31113,21 +31261,21 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="10" t="str">
-        <x:v>上榜18次</x:v>
+        <x:v>上榜19次</x:v>
       </x:c>
       <x:c r="B38" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C38" s="11" t="str">
-        <x:v>0.1%</x:v>
+        <x:v>0.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="10" t="str">
-        <x:v>上榜17次</x:v>
+        <x:v>上榜18次</x:v>
       </x:c>
       <x:c r="B39" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C39" s="11" t="str">
         <x:v>0.2%</x:v>
@@ -31135,43 +31283,43 @@
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="10" t="str">
-        <x:v>上榜16次</x:v>
+        <x:v>上榜17次</x:v>
       </x:c>
       <x:c r="B40" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C40" s="11" t="str">
-        <x:v>0.3%</x:v>
+        <x:v>0.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="10" t="str">
-        <x:v>上榜15次</x:v>
+        <x:v>上榜16次</x:v>
       </x:c>
       <x:c r="B41" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C41" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="10" t="str">
-        <x:v>上榜14次</x:v>
+        <x:v>上榜15次</x:v>
       </x:c>
       <x:c r="B42" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C42" s="11" t="str">
-        <x:v>0.7%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="10" t="str">
-        <x:v>上榜13次</x:v>
+        <x:v>上榜14次</x:v>
       </x:c>
       <x:c r="B43" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C43" s="11" t="str">
         <x:v>0.7%</x:v>
@@ -31179,7 +31327,7 @@
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="10" t="str">
-        <x:v>上榜12次</x:v>
+        <x:v>上榜13次</x:v>
       </x:c>
       <x:c r="B44" s="11" t="n">
         <x:v>13</x:v>
@@ -31190,248 +31338,248 @@
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="10" t="str">
-        <x:v>上榜11次</x:v>
+        <x:v>上榜12次</x:v>
       </x:c>
       <x:c r="B45" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C45" s="11" t="str">
-        <x:v>0.8%</x:v>
+        <x:v>0.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="10" t="str">
-        <x:v>上榜10次</x:v>
+        <x:v>上榜11次</x:v>
       </x:c>
       <x:c r="B46" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C46" s="11" t="str">
-        <x:v>1.3%</x:v>
+        <x:v>0.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="10" t="str">
-        <x:v>上榜9次</x:v>
+        <x:v>上榜10次</x:v>
       </x:c>
       <x:c r="B47" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C47" s="11" t="str">
-        <x:v>1.7%</x:v>
+        <x:v>1.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="10" t="str">
-        <x:v>上榜8次</x:v>
+        <x:v>上榜9次</x:v>
       </x:c>
       <x:c r="B48" s="11" t="n">
-        <x:v>49</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C48" s="11" t="str">
-        <x:v>2.7%</x:v>
+        <x:v>1.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="10" t="str">
-        <x:v>上榜7次</x:v>
+        <x:v>上榜8次</x:v>
       </x:c>
       <x:c r="B49" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C49" s="11" t="str">
-        <x:v>2.0%</x:v>
+        <x:v>2.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="10" t="str">
-        <x:v>上榜6次</x:v>
+        <x:v>上榜7次</x:v>
       </x:c>
       <x:c r="B50" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C50" s="11" t="str">
-        <x:v>3.4%</x:v>
+        <x:v>1.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="10" t="str">
-        <x:v>上榜5次</x:v>
+        <x:v>上榜6次</x:v>
       </x:c>
       <x:c r="B51" s="11" t="n">
-        <x:v>82</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C51" s="11" t="str">
-        <x:v>4.5%</x:v>
+        <x:v>3.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="10" t="str">
-        <x:v>上榜4次</x:v>
+        <x:v>上榜5次</x:v>
       </x:c>
       <x:c r="B52" s="11" t="n">
-        <x:v>104</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C52" s="11" t="str">
-        <x:v>5.7%</x:v>
+        <x:v>4.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="10" t="str">
-        <x:v>上榜3次</x:v>
+        <x:v>上榜4次</x:v>
       </x:c>
       <x:c r="B53" s="11" t="n">
-        <x:v>200</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C53" s="11" t="str">
-        <x:v>11.0%</x:v>
+        <x:v>5.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="10" t="str">
-        <x:v>上榜2次</x:v>
+        <x:v>上榜3次</x:v>
       </x:c>
       <x:c r="B54" s="11" t="n">
-        <x:v>336</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C54" s="11" t="str">
-        <x:v>18.5%</x:v>
+        <x:v>10.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="10" t="str">
+        <x:v>上榜2次</x:v>
+      </x:c>
+      <x:c r="B55" s="11" t="n">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="C55" s="11" t="str">
+        <x:v>18.6%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="10" t="str">
         <x:v>上榜1次</x:v>
       </x:c>
-      <x:c r="B55" s="11" t="n">
-        <x:v>804</x:v>
-      </x:c>
-      <x:c r="C55" s="11" t="str">
-        <x:v>44.2%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" ht="22" customHeight="1">
-      <x:c r="A57" s="14" t="str">
+      <x:c r="B56" s="11" t="n">
+        <x:v>809</x:v>
+      </x:c>
+      <x:c r="C56" s="11" t="str">
+        <x:v>44.3%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="22" customHeight="1">
+      <x:c r="A58" s="14" t="str">
         <x:v>版权类型分布</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="24" customHeight="1">
-      <x:c r="A58" s="5" t="str">
+    <x:row r="59" ht="24" customHeight="1">
+      <x:c r="A59" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B58" t="str">
+      <x:c r="B59" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C58" t="str">
+      <x:c r="C59" t="str">
         <x:v>占比</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59">
-      <x:c r="A59" s="10" t="str">
-        <x:v>CP自营</x:v>
-      </x:c>
-      <x:c r="B59" s="11" t="n">
-        <x:v>1169</x:v>
-      </x:c>
-      <x:c r="C59" s="11" t="str">
-        <x:v>64.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>CP自营</x:v>
       </x:c>
       <x:c r="B60" s="11" t="n">
-        <x:v>636</x:v>
+        <x:v>1170</x:v>
       </x:c>
       <x:c r="C60" s="11" t="str">
-        <x:v>35.0%</x:v>
+        <x:v>64.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="10" t="str">
-        <x:v>CP托管</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="B61" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="C61" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>35.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="10" t="str">
+        <x:v>CP托管</x:v>
+      </x:c>
+      <x:c r="B62" s="11" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C62" s="11" t="str">
+        <x:v>0.6%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="10" t="str">
         <x:v>番茄原创</x:v>
       </x:c>
-      <x:c r="B62" s="11" t="n">
+      <x:c r="B63" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C62" s="11" t="str">
+      <x:c r="C63" s="11" t="str">
         <x:v>0.1%</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" ht="22" customHeight="1">
-      <x:c r="A64" s="14" t="str">
+    <x:row r="65" ht="22" customHeight="1">
+      <x:c r="A65" s="14" t="str">
         <x:v>发布抖音号TOP15·上榜次数</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" ht="24" customHeight="1">
-      <x:c r="A65" s="5" t="str">
+    <x:row r="66" ht="24" customHeight="1">
+      <x:c r="A66" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B65" t="str">
+      <x:c r="B66" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C65" t="str">
+      <x:c r="C66" t="str">
         <x:v>占比</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66">
-      <x:c r="A66" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
-      </x:c>
-      <x:c r="B66" s="11" t="n">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C66" s="11" t="str">
-        <x:v>1.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="10" t="str">
-        <x:v>番荔枝剧场</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="B67" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C67" s="11" t="str">
-        <x:v>1%</x:v>
+        <x:v>1.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>番荔枝剧场</x:v>
       </x:c>
       <x:c r="B68" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C68" s="11" t="str">
-        <x:v>0.9%</x:v>
+        <x:v>1%</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="10" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="B69" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C69" s="11" t="str">
-        <x:v>0.8%</x:v>
+        <x:v>0.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="B70" s="11" t="n">
         <x:v>45</x:v>
@@ -31442,10 +31590,10 @@
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="10" t="str">
-        <x:v>渲渲动画</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="B71" s="11" t="n">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C71" s="11" t="str">
         <x:v>0.8%</x:v>
@@ -31453,21 +31601,21 @@
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="10" t="str">
-        <x:v>左手良画</x:v>
+        <x:v>渲渲动画</x:v>
       </x:c>
       <x:c r="B72" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C72" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>0.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="10" t="str">
-        <x:v>阅友动漫</x:v>
+        <x:v>左手良画</x:v>
       </x:c>
       <x:c r="B73" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C73" s="11" t="str">
         <x:v>0.6%</x:v>
@@ -31475,10 +31623,10 @@
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="10" t="str">
-        <x:v>东山啊</x:v>
+        <x:v>阅友动漫</x:v>
       </x:c>
       <x:c r="B74" s="11" t="n">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C74" s="11" t="str">
         <x:v>0.6%</x:v>
@@ -31486,21 +31634,21 @@
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>东山啊</x:v>
       </x:c>
       <x:c r="B75" s="11" t="n">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C75" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="B76" s="11" t="n">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C76" s="11" t="str">
         <x:v>0.5%</x:v>
@@ -31508,10 +31656,10 @@
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="10" t="str">
-        <x:v>茉冉漫影</x:v>
+        <x:v>在下轻北</x:v>
       </x:c>
       <x:c r="B77" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C77" s="11" t="str">
         <x:v>0.5%</x:v>
@@ -31519,10 +31667,10 @@
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="10" t="str">
-        <x:v>在下轻北</x:v>
+        <x:v>腿毛漫漫</x:v>
       </x:c>
       <x:c r="B78" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C78" s="11" t="str">
         <x:v>0.5%</x:v>
@@ -31530,10 +31678,10 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="10" t="str">
-        <x:v>腿毛漫漫</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="B79" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C79" s="11" t="str">
         <x:v>0.5%</x:v>
@@ -31541,59 +31689,59 @@
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="10" t="str">
-        <x:v>壹琚-娜娜看剧</x:v>
+        <x:v>茉冉漫影</x:v>
       </x:c>
       <x:c r="B80" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C80" s="11" t="str">
         <x:v>0.5%</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" ht="22" customHeight="1">
-      <x:c r="A82" s="14" t="str">
+    <x:row r="81">
+      <x:c r="A81" s="10" t="str">
+        <x:v>壹琚-娜娜看剧</x:v>
+      </x:c>
+      <x:c r="B81" s="11" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C81" s="11" t="str">
+        <x:v>0.5%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="22" customHeight="1">
+      <x:c r="A83" s="14" t="str">
         <x:v>发布抖音号TOP15·上榜剧数</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" ht="24" customHeight="1">
-      <x:c r="A83" s="5" t="str">
+    <x:row r="84" ht="24" customHeight="1">
+      <x:c r="A84" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B83" t="str">
+      <x:c r="B84" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C83" t="str">
+      <x:c r="C84" t="str">
         <x:v>占比</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84">
-      <x:c r="A84" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
-      </x:c>
-      <x:c r="B84" s="11" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C84" s="11" t="str">
-        <x:v>1.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="B85" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C85" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>1.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="B86" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C86" s="11" t="str">
         <x:v>0.5%</x:v>
@@ -31601,7 +31749,7 @@
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="10" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="B87" s="11" t="n">
         <x:v>9</x:v>
@@ -31612,21 +31760,21 @@
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="10" t="str">
-        <x:v>星漫世界</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="B88" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C88" s="11" t="str">
-        <x:v>0.4%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="10" t="str">
-        <x:v>番荔枝剧场</x:v>
+        <x:v>星漫世界</x:v>
       </x:c>
       <x:c r="B89" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C89" s="11" t="str">
         <x:v>0.4%</x:v>
@@ -31634,29 +31782,29 @@
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="10" t="str">
-        <x:v>渲渲动画</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="B90" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C90" s="11" t="str">
-        <x:v>0.3%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>番荔枝剧场</x:v>
       </x:c>
       <x:c r="B91" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C91" s="11" t="str">
-        <x:v>0.3%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="10" t="str">
-        <x:v>阅友动漫</x:v>
+        <x:v>渲渲动画</x:v>
       </x:c>
       <x:c r="B92" s="11" t="n">
         <x:v>6</x:v>
@@ -31667,7 +31815,7 @@
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="10" t="str">
-        <x:v>腿毛漫漫</x:v>
+        <x:v>阅友动漫</x:v>
       </x:c>
       <x:c r="B93" s="11" t="n">
         <x:v>6</x:v>
@@ -31678,7 +31826,7 @@
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>腿毛漫漫</x:v>
       </x:c>
       <x:c r="B94" s="11" t="n">
         <x:v>6</x:v>
@@ -31689,7 +31837,7 @@
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="10" t="str">
-        <x:v>至尊爽剧社</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="B95" s="11" t="n">
         <x:v>6</x:v>
@@ -31700,7 +31848,7 @@
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="10" t="str">
-        <x:v>潮汐互娱-爽剧社</x:v>
+        <x:v>至尊爽剧社</x:v>
       </x:c>
       <x:c r="B96" s="11" t="n">
         <x:v>6</x:v>
@@ -31711,10 +31859,10 @@
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="10" t="str">
-        <x:v>星漫动漫剧场</x:v>
+        <x:v>潮汐互娱-爽剧社</x:v>
       </x:c>
       <x:c r="B97" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C97" s="11" t="str">
         <x:v>0.3%</x:v>
@@ -31722,7 +31870,7 @@
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="10" t="str">
-        <x:v>忆梦剧场</x:v>
+        <x:v>星漫动漫剧场</x:v>
       </x:c>
       <x:c r="B98" s="11" t="n">
         <x:v>5</x:v>
@@ -31731,91 +31879,91 @@
         <x:v>0.3%</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" ht="22" customHeight="1">
-      <x:c r="A100" s="14" t="str">
+    <x:row r="99">
+      <x:c r="A99" s="10" t="str">
+        <x:v>忆梦剧场</x:v>
+      </x:c>
+      <x:c r="B99" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C99" s="11" t="str">
+        <x:v>0.3%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="22" customHeight="1">
+      <x:c r="A101" s="14" t="str">
         <x:v>付费榜主题分布</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" ht="24" customHeight="1">
-      <x:c r="A101" s="5" t="str">
+    <x:row r="102" ht="24" customHeight="1">
+      <x:c r="A102" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B101" t="str">
+      <x:c r="B102" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C101" t="str">
+      <x:c r="C102" t="str">
         <x:v>占比</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102">
-      <x:c r="A102" s="10" t="str">
-        <x:v>婚姻/情感</x:v>
-      </x:c>
-      <x:c r="B102" s="11" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C102" s="11" t="str">
-        <x:v>19.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="10" t="str">
-        <x:v>家庭伦理/萌宝</x:v>
+        <x:v>婚姻/情感</x:v>
       </x:c>
       <x:c r="B103" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C103" s="11" t="str">
-        <x:v>15.0%</x:v>
+        <x:v>19.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>家庭伦理/萌宝</x:v>
       </x:c>
       <x:c r="B104" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C104" s="11" t="str">
-        <x:v>10.0%</x:v>
+        <x:v>15.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="B105" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C105" s="11" t="str">
-        <x:v>9.0%</x:v>
+        <x:v>10.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="10" t="str">
-        <x:v>年代怀旧/种田</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="B106" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C106" s="11" t="str">
-        <x:v>7.0%</x:v>
+        <x:v>9.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="10" t="str">
-        <x:v>现实反转/人性</x:v>
+        <x:v>年代怀旧/种田</x:v>
       </x:c>
       <x:c r="B107" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C107" s="11" t="str">
-        <x:v>6.0%</x:v>
+        <x:v>7.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="10" t="str">
-        <x:v>战神/异能</x:v>
+        <x:v>现实反转/人性</x:v>
       </x:c>
       <x:c r="B108" s="11" t="n">
         <x:v>6</x:v>
@@ -31826,12 +31974,23 @@
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="10" t="str">
+        <x:v>战神/异能</x:v>
+      </x:c>
+      <x:c r="B109" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C109" s="11" t="str">
+        <x:v>6.0%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="10" t="str">
         <x:v>美食治愈</x:v>
       </x:c>
-      <x:c r="B109" s="11" t="n">
+      <x:c r="B110" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C109" s="11" t="str">
+      <x:c r="C110" s="11" t="str">
         <x:v>5.0%</x:v>
       </x:c>
     </x:row>
@@ -31841,10 +32000,10 @@
     <x:mergeCell ref="A7:C7"/>
     <x:mergeCell ref="A14:C14"/>
     <x:mergeCell ref="A27:C27"/>
-    <x:mergeCell ref="A57:C57"/>
-    <x:mergeCell ref="A64:C64"/>
-    <x:mergeCell ref="A82:C82"/>
-    <x:mergeCell ref="A100:C100"/>
+    <x:mergeCell ref="A58:C58"/>
+    <x:mergeCell ref="A65:C65"/>
+    <x:mergeCell ref="A83:C83"/>
+    <x:mergeCell ref="A101:C101"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="Re61c893443094aa9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="R341e8561f630474f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="Rb6bb9b81676947b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="R70e71fcc4158474d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP20剧重点跟踪" sheetId="5" r:id="Rc6f65eb3019b4217"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="6" r:id="R835319459af94cd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="7" r:id="Rb0bd4fcb70e74f73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="8" r:id="R2914aa5c2e354d8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="9" r:id="R322319c40efd40b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R1dd784602bab4da6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="R096de5411c6f4888"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="R8be9af86456542a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="R72f35dcc51dc4e05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP20剧重点跟踪" sheetId="5" r:id="R61ba3b1a2bed47fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="6" r:id="R9dfef16576884758"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径A(上榜剧数)" sheetId="7" r:id="Ra1fd92c07593447e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重50%)" sheetId="8" r:id="R8aab25fcc7cf4366"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="9" r:id="Rb26d01155b5c4a74"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1202,7 +1202,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
         <x:v>被诬陷诊出喜脉，重活一世我逆转前尘</x:v>
@@ -1239,7 +1239,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
         <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
@@ -1276,7 +1276,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
         <x:v>我都元婴期了，你跟我说开学</x:v>
@@ -1313,7 +1313,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
         <x:v>重回雪崩泥石流，我不再犹豫</x:v>
@@ -1350,13 +1350,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>29</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
-        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
+        <x:v>我在工地卖盒饭带火一座城</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>09-15 08:30</x:v>
+        <x:v>09-14 14:52</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str"/>
       <x:c r="F7" s="11" t="str"/>
@@ -1367,19 +1367,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I7" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="J7" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K7" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="L7" s="11" t="str">
-        <x:v>琥珀漫剧</x:v>
+        <x:v>左手良画</x:v>
       </x:c>
       <x:c r="M7" s="10" t="str">
-        <x:v>海鲜市场老手陈放，因一个两块钱的冰袋被十二年合伙人当众算旧账，心寒清账，净身出户。他没有抱怨，也没有以牙还牙，而是加入冷清档口“梅姐水产”，从零开始。他坚持明码标价、沥水称重、死活分卖、批次可查，宁可少接单，也不混货、不凑数、不赚亏心钱。面对低价抢客、恶意破坏、临时缺货等风波，他与叶梅靠诚信、规矩和彼此信任，一步步赢得客户与连锁企业的认可。</x:v>
+        <x:v>小伙白叶遭遇老板跑路，半年工资付诸东流，意外被铁炒勺砸中觉醒超级餐饮系统。大雪封路堵车途中完成首份任务，靠着系统加持的厨艺，路边卖盒饭赚到第一桶金。回乡钻研秘制酱肉，赶集摆摊火爆出圈，还临危接手大型寿宴惊艳众人。过完新年，他怀揣梦想奔赴外地，准备开启属于自己的餐饮创业之路。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1387,13 +1387,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
-        <x:v>我在工地卖盒饭带火一座城</x:v>
+        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>09-14 14:52</x:v>
+        <x:v>09-15 08:30</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str"/>
       <x:c r="F8" s="11" t="str"/>
@@ -1404,19 +1404,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
-        <x:v>144</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J8" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K8" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L8" s="11" t="str">
-        <x:v>左手良画</x:v>
+        <x:v>琥珀漫剧</x:v>
       </x:c>
       <x:c r="M8" s="10" t="str">
-        <x:v>小伙白叶遭遇老板跑路，半年工资付诸东流，意外被铁炒勺砸中觉醒超级餐饮系统。大雪封路堵车途中完成首份任务，靠着系统加持的厨艺，路边卖盒饭赚到第一桶金。回乡钻研秘制酱肉，赶集摆摊火爆出圈，还临危接手大型寿宴惊艳众人。过完新年，他怀揣梦想奔赴外地，准备开启属于自己的餐饮创业之路。</x:v>
+        <x:v>海鲜市场老手陈放，因一个两块钱的冰袋被十二年合伙人当众算旧账，心寒清账，净身出户。他没有抱怨，也没有以牙还牙，而是加入冷清档口“梅姐水产”，从零开始。他坚持明码标价、沥水称重、死活分卖、批次可查，宁可少接单，也不混货、不凑数、不赚亏心钱。面对低价抢客、恶意破坏、临时缺货等风波，他与叶梅靠诚信、规矩和彼此信任，一步步赢得客户与连锁企业的认可。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1424,7 +1424,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
         <x:v>一盒印泥引发的全局封锁</x:v>
@@ -1455,13 +1455,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
-        <x:v>被身高掩盖的谎言</x:v>
+        <x:v>高考刚结束父母就不装了</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>09-15 08:18</x:v>
+        <x:v>09-15 07:00</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str"/>
       <x:c r="F10" s="11" t="str"/>
@@ -1472,19 +1472,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I10" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="J10" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K10" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="L10" s="11" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>千慕剧场</x:v>
       </x:c>
       <x:c r="M10" s="10" t="str">
-        <x:v>女孩林知晚回到命运转折的关键节点。她凭借智慧与勇气，敏锐察觉家中隐患，冷静引导家人、寻求帮助，用爱守护姐姐与全家。在共同努力下危机化解、正义伸张，一家人愈发珍视彼此，并且帮助到了更多有同样遭遇的人，最后迎来温暖安宁的幸福生活。</x:v>
+        <x:v>高考结束那天，林寻在考场外被亲生父母认回原来十八年的普通生活，是父母为磨砺他而设的一场成长课。重回豪门，他没有迷失，反而在桥上遇见了那个让他心动的姑娘，南大冰山学姐苏清诗。从青涩的初次相遇，到演唱会上的合唱，再到大学校园里的朝夕相处，两个真诚的人慢慢靠近。曾经的求而不得终将释怀，双向奔赴的喜欢才最珍贵。褪去普通学生的身份，林寻只想以真心换真心。十八岁的夏天，最好的相遇，最甜的恋爱，才刚刚开始。</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1492,13 +1492,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C11" s="10" t="str">
-        <x:v>重生极品婆婆，带全家发家致富！</x:v>
+        <x:v>被身高掩盖的谎言</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>09-14 20:29</x:v>
+        <x:v>09-15 08:18</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str"/>
       <x:c r="F11" s="11" t="str"/>
@@ -1509,19 +1509,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I11" s="11" t="n">
-        <x:v>126</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J11" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K11" s="10" t="str">
-        <x:v>家庭伦理 / 逆袭打脸</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="L11" s="11" t="str">
-        <x:v>懒少爱我</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="M11" s="10" t="str">
-        <x:v>寡妇傅兰秀前世一生吝啬守财，刻薄对待儿女儿媳，到头来钱财被贼人掠夺，落得个凄惨离世的下场。一朝重生，她回到悲剧尚未发生之时。痛定思痛，她彻底改掉抠门的性子，学着善待家里的晚辈。可日子并不太平，爱占便宜的亲戚总上门搅扰，家中两个儿媳也矛盾不断，家务是非接连找上门。傅兰秀靠着清醒的头脑，一边化解各类家庭纷争，一边寻找营生门路，努力扭转命运，拼尽全力守护一家人的安稳生活。</x:v>
+        <x:v>女孩林知晚回到命运转折的关键节点。她凭借智慧与勇气，敏锐察觉家中隐患，冷静引导家人、寻求帮助，用爱守护姐姐与全家。在共同努力下危机化解、正义伸张，一家人愈发珍视彼此，并且帮助到了更多有同样遭遇的人，最后迎来温暖安宁的幸福生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1529,13 +1529,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
-        <x:v>高考刚结束父母就不装了</x:v>
+        <x:v>重生极品婆婆，带全家发家致富！</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>09-15 07:00</x:v>
+        <x:v>09-14 20:29</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str"/>
       <x:c r="F12" s="11" t="str"/>
@@ -1546,19 +1546,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I12" s="11" t="n">
-        <x:v>173</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="J12" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K12" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>家庭伦理 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="L12" s="11" t="str">
-        <x:v>千慕剧场</x:v>
+        <x:v>懒少爱我</x:v>
       </x:c>
       <x:c r="M12" s="10" t="str">
-        <x:v>高考结束那天，林寻在考场外被亲生父母认回原来十八年的普通生活，是父母为磨砺他而设的一场成长课。重回豪门，他没有迷失，反而在桥上遇见了那个让他心动的姑娘，南大冰山学姐苏清诗。从青涩的初次相遇，到演唱会上的合唱，再到大学校园里的朝夕相处，两个真诚的人慢慢靠近。曾经的求而不得终将释怀，双向奔赴的喜欢才最珍贵。褪去普通学生的身份，林寻只想以真心换真心。十八岁的夏天，最好的相遇，最甜的恋爱，才刚刚开始。</x:v>
+        <x:v>寡妇傅兰秀前世一生吝啬守财，刻薄对待儿女儿媳，到头来钱财被贼人掠夺，落得个凄惨离世的下场。一朝重生，她回到悲剧尚未发生之时。痛定思痛，她彻底改掉抠门的性子，学着善待家里的晚辈。可日子并不太平，爱占便宜的亲戚总上门搅扰，家中两个儿媳也矛盾不断，家务是非接连找上门。傅兰秀靠着清醒的头脑，一边化解各类家庭纷争，一边寻找营生门路，努力扭转命运，拼尽全力守护一家人的安稳生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1566,7 +1566,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B13" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
         <x:v>嫡姐日日闹换夫，圣旨赐下后她悔疯了</x:v>
@@ -1603,13 +1603,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B14" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
-        <x:v>说好九十天就回来，我不等了</x:v>
+        <x:v>四个崽崽瞒不住了</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>09-16 06:00</x:v>
+        <x:v>09-15 00:08</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str"/>
       <x:c r="F14" s="11" t="str"/>
@@ -1620,7 +1620,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I14" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="J14" s="10" t="str">
         <x:v>其他</x:v>
@@ -1629,10 +1629,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L14" s="11" t="str">
-        <x:v>小宁漫漫</x:v>
+        <x:v>桃子动漫剧场</x:v>
       </x:c>
       <x:c r="M14" s="10" t="str">
-        <x:v>周衡挣脱错位的旧感情，坚守原则，专注医疗事业，打磨救死扶伤的星桥心泵。他与叶宁彼此尊重，感情建立在坦诚与边界之上，不盲目牺牲自我，平等相伴走向未来。林夏历经挫折后幡然醒悟，承担自己犯下的过错，放下执念踏实努力，靠双手重新经营人生。故事告诉人不必困在原地等候错的人，真心不该沦为候补，每个人都可以告别过往，奔赴属于自己的前路</x:v>
+        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1640,13 +1640,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B15" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
+        <x:v>说好九十天就回来，我不等了</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
-        <x:v>09-15 00:08</x:v>
+        <x:v>09-16 06:00</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str"/>
       <x:c r="F15" s="11" t="str"/>
@@ -1657,7 +1657,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I15" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J15" s="10" t="str">
         <x:v>其他</x:v>
@@ -1666,10 +1666,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L15" s="11" t="str">
-        <x:v>桃子动漫剧场</x:v>
+        <x:v>小宁漫漫</x:v>
       </x:c>
       <x:c r="M15" s="10" t="str">
-        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
+        <x:v>周衡挣脱错位的旧感情，坚守原则，专注医疗事业，打磨救死扶伤的星桥心泵。他与叶宁彼此尊重，感情建立在坦诚与边界之上，不盲目牺牲自我，平等相伴走向未来。林夏历经挫折后幡然醒悟，承担自己犯下的过错，放下执念踏实努力，靠双手重新经营人生。故事告诉人不必困在原地等候错的人，真心不该沦为候补，每个人都可以告别过往，奔赴属于自己的前路</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1677,13 +1677,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C16" s="10" t="str">
-        <x:v>傅少你夫人又在扮猪吃虎了</x:v>
+        <x:v>我堂堂元婴老祖，让我给大小姐当保镖</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>09-15 23:57</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str"/>
       <x:c r="F16" s="11" t="str"/>
@@ -1693,22 +1693,28 @@
       <x:c r="H16" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I16" s="11" t="str"/>
+      <x:c r="I16" s="11" t="n">
+        <x:v>217</x:v>
+      </x:c>
       <x:c r="J16" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K16" s="10" t="str">
-        <x:v>婚姻情感 / 美食治愈</x:v>
-      </x:c>
-      <x:c r="L16" s="11" t="str"/>
-      <x:c r="M16" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L16" s="11" t="str">
+        <x:v>扶摇精品剧场</x:v>
+      </x:c>
+      <x:c r="M16" s="10" t="str">
+        <x:v>宁尘穿越到修仙界两千年，居然只过了一个暑假！什么？你说我堂堂元婴老祖，不但被亲妈逼着去上大学，还要和校花大小姐同居？很快，同学们惊呆了随手扔铅球破世界纪录，你说这是大一新生？古武界集体怀疑人生修炼了几十年的武道老家伙，被一个年轻人当球踢？校花大小姐气得跺脚想接我电话的人能绕青州一圈，你居然嫌我吵？宁尘我，元婴老祖，真的只想做个普通人，既然你们非要逼我，那我只能一路横推，专治各种不服！</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C17" s="10" t="str">
         <x:v>攻略失败后我不装了</x:v>
@@ -1745,13 +1751,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C18" s="10" t="str">
-        <x:v>我堂堂元婴老祖，让我给大小姐当保镖</x:v>
+        <x:v>有米偏要讨三场雨</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>09-15 23:57</x:v>
+        <x:v>09-16 08:18</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str"/>
       <x:c r="F18" s="11" t="str"/>
@@ -1762,7 +1768,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I18" s="11" t="n">
-        <x:v>217</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="J18" s="10" t="str">
         <x:v>其他</x:v>
@@ -1771,10 +1777,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L18" s="11" t="str">
-        <x:v>扶摇精品剧场</x:v>
+        <x:v>剧有米</x:v>
       </x:c>
       <x:c r="M18" s="10" t="str">
-        <x:v>宁尘穿越到修仙界两千年，居然只过了一个暑假！什么？你说我堂堂元婴老祖，不但被亲妈逼着去上大学，还要和校花大小姐同居？很快，同学们惊呆了随手扔铅球破世界纪录，你说这是大一新生？古武界集体怀疑人生修炼了几十年的武道老家伙，被一个年轻人当球踢？校花大小姐气得跺脚想接我电话的人能绕青州一圈，你居然嫌我吵？宁尘我，元婴老祖，真的只想做个普通人，既然你们非要逼我，那我只能一路横推，专治各种不服！</x:v>
+        <x:v>青石村大旱三月，全村跪求龙王赐雨，四岁的有米却爬上供桌，张口就说龙王敖澜欠她三场雨。为了讨债，她扣雨牌、锁水门、放掉偷接的水、挖通公沟，还把只认天规的敖澜一次次拖进人间麻烦。暴风、山火和争水接连袭来，有米也在一次次选择中让周守财和全村学会先顾人、再顾利。三场雨终于还清，青石村重新秋种，山外却传来石狮异响，新的怪事又找上了她。</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1782,24 +1788,24 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C19" s="10" t="str">
-        <x:v>有米偏要讨三场雨</x:v>
+        <x:v>霁月安遥之以余生为诺护你岁岁无忧第一季</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
-        <x:v>09-16 08:18</x:v>
+        <x:v>09-16 06:06</x:v>
       </x:c>
       <x:c r="E19" s="11" t="str"/>
       <x:c r="F19" s="11" t="str"/>
       <x:c r="G19" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H19" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I19" s="11" t="n">
-        <x:v>98</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="J19" s="10" t="str">
         <x:v>其他</x:v>
@@ -1808,10 +1814,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L19" s="11" t="str">
-        <x:v>剧有米</x:v>
+        <x:v>花花说漫</x:v>
       </x:c>
       <x:c r="M19" s="10" t="str">
-        <x:v>青石村大旱三月，全村跪求龙王赐雨，四岁的有米却爬上供桌，张口就说龙王敖澜欠她三场雨。为了讨债，她扣雨牌、锁水门、放掉偷接的水、挖通公沟，还把只认天规的敖澜一次次拖进人间麻烦。暴风、山火和争水接连袭来，有米也在一次次选择中让周守财和全村学会先顾人、再顾利。三场雨终于还清，青石村重新秋种，山外却传来石狮异响，新的怪事又找上了她。</x:v>
+        <x:v>22岁的医大学生辛知遥意外与大学教授周霁结缘，步入婚姻。初时二人的结合源于一场意外，彼此尚有距离。婚后辛知遥一边完成繁重的学业，一边适应全新的家庭生活。她挣脱原生家庭带来的压抑与束缚，学着正视内心、勇敢表达自我。周霁沉稳体贴，给予她尊重、陪伴与满满的安全感。二人在朝夕相处中慢慢卸下防备，从责任走向真心，携手面对生活里的重重风波，互相扶持，奔赴温暖安稳的幸福生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1819,13 +1825,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>31</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C20" s="10" t="str">
-        <x:v>霁月安遥之以余生为诺护你岁岁无忧第一季</x:v>
+        <x:v>弄权大玄：我有购物系统</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>09-16 06:06</x:v>
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="E20" s="11" t="str"/>
       <x:c r="F20" s="11" t="str"/>
@@ -1835,34 +1841,28 @@
       <x:c r="H20" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I20" s="11" t="n">
-        <x:v>144</x:v>
-      </x:c>
+      <x:c r="I20" s="11" t="str"/>
       <x:c r="J20" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K20" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L20" s="11" t="str">
-        <x:v>花花说漫</x:v>
-      </x:c>
-      <x:c r="M20" s="10" t="str">
-        <x:v>22岁的医大学生辛知遥意外与大学教授周霁结缘，步入婚姻。初时二人的结合源于一场意外，彼此尚有距离。婚后辛知遥一边完成繁重的学业，一边适应全新的家庭生活。她挣脱原生家庭带来的压抑与束缚，学着正视内心、勇敢表达自我。周霁沉稳体贴，给予她尊重、陪伴与满满的安全感。二人在朝夕相处中慢慢卸下防备，从责任走向真心，携手面对生活里的重重风波，互相扶持，奔赴温暖安稳的幸福生活。</x:v>
-      </x:c>
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="L20" s="11" t="str"/>
+      <x:c r="M20" s="10" t="str"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C21" s="10" t="str">
-        <x:v>弄权大玄：我有购物系统</x:v>
+        <x:v>重生第七节车厢</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>09-16 11:39</x:v>
       </x:c>
       <x:c r="E21" s="11" t="str"/>
       <x:c r="F21" s="11" t="str"/>
@@ -1872,28 +1872,34 @@
       <x:c r="H21" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I21" s="11" t="str"/>
+      <x:c r="I21" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
       <x:c r="J21" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K21" s="10" t="str">
-        <x:v>战神异能</x:v>
-      </x:c>
-      <x:c r="L21" s="11" t="str"/>
-      <x:c r="M21" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L21" s="11" t="str">
+        <x:v>千一剧场</x:v>
+      </x:c>
+      <x:c r="M21" s="10" t="str">
+        <x:v>高铁列车长林铮死过一次。上一世，四名大学生私带危险实验样品登车，一句“毒倒整节车厢”的戏言被他放行，最终隧道内毒气泄漏，全车罹难，他成了千夫所指的责任人。重回发车前最后一分钟，他顶住求情、质疑与全网非议，硬封第七节车厢，叫停整趟列车。层层戳破瞒报的谎言，这一次，他死守安全红线，要让车上一千零八十六人，全都平安抵达终点。</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C22" s="10" t="str">
-        <x:v>刺耳的邻里情</x:v>
+        <x:v>八媳妇只想买包，一不小心拯救了全家</x:v>
       </x:c>
       <x:c r="D22" s="11" t="str">
-        <x:v>09-15 11:00</x:v>
+        <x:v>09-16 10:00</x:v>
       </x:c>
       <x:c r="E22" s="11" t="str"/>
       <x:c r="F22" s="11" t="str"/>
@@ -1901,59 +1907,59 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H22" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I22" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J22" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K22" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L22" s="11" t="str">
-        <x:v>酒写一首诗</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="M22" s="10" t="str">
-        <x:v>邻居大强夫妇痴迷比赛，深夜制造噪音打扰四邻，甚至潜入邻院破坏，终因违规致使墙倒器毁、面临赔偿。青年陈默没有以怨报怨，只凭合农机与科学常识理性应对。大强夫妇在赔偿检讨中受教，重新学会遵守规则、尊重邻里；陈默则凭宽容智慧用赔款修筑村广场，走出一条和谐讲理的乡村新路。</x:v>
+        <x:v>顾家八位儿媳皆各有所长。大嫂秦蕴章深耕华尔街并购领域，二嫂林疏桐是风投行业的杰出从业者。晏姝岚平日生活低调随性，外界便对她产生片面认知，认为她只注重物质消费。实际上，晏姝岚来自底蕴更为深厚的大家族。当顾氏集团遭遇多家境外企业联合围堵，经营陷入巨大危机。顾家公公心力交瘁，能力出众的嫂嫂们多方调动资源，依旧难以摸清对手的真实布局。在对手步步施压的危急时刻，晏姝岚挺身而出，守护顾家渡过这场商业危机。</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>46</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C23" s="10" t="str">
-        <x:v>八媳妇只想买包，一不小心拯救了全家</x:v>
+        <x:v>错婚觉醒</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
-        <x:v>09-16 10:00</x:v>
-      </x:c>
-      <x:c r="E23" s="11" t="n">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="F23" s="11" t="str">
-        <x:v>↑26位</x:v>
-      </x:c>
-      <x:c r="G23" s="11" t="str"/>
-      <x:c r="H23" s="11" t="str"/>
+        <x:v>09-14 18:03</x:v>
+      </x:c>
+      <x:c r="E23" s="11" t="str"/>
+      <x:c r="F23" s="11" t="str"/>
+      <x:c r="G23" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H23" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="I23" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="J23" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K23" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感 / 战神异能</x:v>
       </x:c>
       <x:c r="L23" s="11" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>小7AI漫剧</x:v>
       </x:c>
       <x:c r="M23" s="10" t="str">
-        <x:v>顾家八位儿媳皆各有所长。大嫂秦蕴章深耕华尔街并购领域，二嫂林疏桐是风投行业的杰出从业者。晏姝岚平日生活低调随性，外界便对她产生片面认知，认为她只注重物质消费。实际上，晏姝岚来自底蕴更为深厚的大家族。当顾氏集团遭遇多家境外企业联合围堵，经营陷入巨大危机。顾家公公心力交瘁，能力出众的嫂嫂们多方调动资源，依旧难以摸清对手的真实布局。在对手步步施压的危急时刻，晏姝岚挺身而出，守护顾家渡过这场商业危机。</x:v>
+        <x:v>新婚当夜那天，姜云笙重生回到了被陆家算计的那天。面对虚伪丈夫陆卫民、苟且的小姑陆红梅与贪婪婆婆，她决定不再愚善隐忍。而是步步设局撕开陆家真面目，夺回被窃取的前途与财物，奋力挣脱不幸婚姻，为自己讨回公道。</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1961,24 +1967,24 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C24" s="10" t="str">
-        <x:v>重生第七节车厢</x:v>
+        <x:v>敢泼我馄饨，整条街都别要了</x:v>
       </x:c>
       <x:c r="D24" s="11" t="str">
-        <x:v>09-16 11:39</x:v>
+        <x:v>09-16 10:00</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F24" s="11" t="str">
-        <x:v>↑20位</x:v>
+        <x:v>↑30位</x:v>
       </x:c>
       <x:c r="G24" s="11" t="str"/>
       <x:c r="H24" s="11" t="str"/>
       <x:c r="I24" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J24" s="10" t="str">
         <x:v>其他</x:v>
@@ -1987,10 +1993,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L24" s="11" t="str">
-        <x:v>千一剧场</x:v>
+        <x:v>治愈 AI 恋</x:v>
       </x:c>
       <x:c r="M24" s="10" t="str">
-        <x:v>高铁列车长林铮死过一次。上一世，四名大学生私带危险实验样品登车，一句“毒倒整节车厢”的戏言被他放行，最终隧道内毒气泄漏，全车罹难，他成了千夫所指的责任人。重回发车前最后一分钟，他顶住求情、质疑与全网非议，硬封第七节车厢，叫停整趟列车。层层戳破瞒报的谎言，这一次，他死守安全红线，要让车上一千零八十六人，全都平安抵达终点。</x:v>
+        <x:v>南桥旧街投资人许总多年悉心扶持一众商户，给予租金减免与基建投入，可赵川等人却贪念作祟，撕毁协议，还刻意编造谎言煽动网络暴力。面对恩将仇报的局面，许总没有冲动行事，而是恪守契约精神，凭借完备证据通过合法途径理性维权。随着真相公之于众，造谣闹事者自食恶果，承担起违约带来的相应代价。旧街完成焕新升级，充分彰显出法律与规则守护公平正义的强大力量。</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1998,36 +2004,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C25" s="10" t="str">
-        <x:v>错婚觉醒</x:v>
+        <x:v>工地前的一碗盒饭</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
-        <x:v>09-14 18:03</x:v>
+        <x:v>09-15 11:00</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F25" s="11" t="str">
-        <x:v>↑20位</x:v>
+        <x:v>↑22位</x:v>
       </x:c>
       <x:c r="G25" s="11" t="str"/>
       <x:c r="H25" s="11" t="str"/>
       <x:c r="I25" s="11" t="n">
-        <x:v>113</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="J25" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K25" s="10" t="str">
-        <x:v>婚姻情感 / 战神异能</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="L25" s="11" t="str">
-        <x:v>小7AI漫剧</x:v>
+        <x:v>小羊说漫</x:v>
       </x:c>
       <x:c r="M25" s="10" t="str">
-        <x:v>新婚当夜那天，姜云笙重生回到了被陆家算计的那天。面对虚伪丈夫陆卫民、苟且的小姑陆红梅与贪婪婆婆，她决定不再愚善隐忍。而是步步设局撕开陆家真面目，夺回被窃取的前途与财物，奋力挣脱不幸婚姻，为自己讨回公道。</x:v>
+        <x:v>热火朝天的建筑工地旁，盒饭摊主老陈始终不为暴利所动，坚持猛火现炒和选用新鲜优质的好肉，默默守护工人们的食品安全。最终，在一场危机后，贪婪者受到了严惩，工人们也彻底醒悟。赞美了老陈纯粹的工匠精神，传递了坚守底线、正义必胜的温暖价值观。</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -2035,24 +2041,24 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B26" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C26" s="10" t="str">
-        <x:v>有米偏要讨三场雨</x:v>
+        <x:v>我堂堂元婴老祖，让我给大小姐当保镖</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
-        <x:v>09-16 08:18</x:v>
+        <x:v>09-15 23:57</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F26" s="11" t="str">
-        <x:v>↑17位</x:v>
+        <x:v>↑10位</x:v>
       </x:c>
       <x:c r="G26" s="11" t="str"/>
       <x:c r="H26" s="11" t="str"/>
       <x:c r="I26" s="11" t="n">
-        <x:v>98</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="J26" s="10" t="str">
         <x:v>其他</x:v>
@@ -2061,10 +2067,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L26" s="11" t="str">
-        <x:v>剧有米</x:v>
+        <x:v>扶摇精品剧场</x:v>
       </x:c>
       <x:c r="M26" s="10" t="str">
-        <x:v>青石村大旱三月，全村跪求龙王赐雨，四岁的有米却爬上供桌，张口就说龙王敖澜欠她三场雨。为了讨债，她扣雨牌、锁水门、放掉偷接的水、挖通公沟，还把只认天规的敖澜一次次拖进人间麻烦。暴风、山火和争水接连袭来，有米也在一次次选择中让周守财和全村学会先顾人、再顾利。三场雨终于还清，青石村重新秋种，山外却传来石狮异响，新的怪事又找上了她。</x:v>
+        <x:v>宁尘穿越到修仙界两千年，居然只过了一个暑假！什么？你说我堂堂元婴老祖，不但被亲妈逼着去上大学，还要和校花大小姐同居？很快，同学们惊呆了随手扔铅球破世界纪录，你说这是大一新生？古武界集体怀疑人生修炼了几十年的武道老家伙，被一个年轻人当球踢？校花大小姐气得跺脚想接我电话的人能绕青州一圈，你居然嫌我吵？宁尘我，元婴老祖，真的只想做个普通人，既然你们非要逼我，那我只能一路横推，专治各种不服！</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -2072,36 +2078,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B27" s="11" t="n">
-        <x:v>31</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C27" s="10" t="str">
-        <x:v>霁月安遥之以余生为诺护你岁岁无忧第一季</x:v>
+        <x:v>高考刚结束父母就不装了</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
-        <x:v>09-16 06:06</x:v>
+        <x:v>09-15 07:00</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F27" s="11" t="str">
-        <x:v>↑8位</x:v>
+        <x:v>↑5位</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str"/>
       <x:c r="H27" s="11" t="str"/>
       <x:c r="I27" s="11" t="n">
-        <x:v>144</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="J27" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K27" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="L27" s="11" t="str">
-        <x:v>花花说漫</x:v>
+        <x:v>千慕剧场</x:v>
       </x:c>
       <x:c r="M27" s="10" t="str">
-        <x:v>22岁的医大学生辛知遥意外与大学教授周霁结缘，步入婚姻。初时二人的结合源于一场意外，彼此尚有距离。婚后辛知遥一边完成繁重的学业，一边适应全新的家庭生活。她挣脱原生家庭带来的压抑与束缚，学着正视内心、勇敢表达自我。周霁沉稳体贴，给予她尊重、陪伴与满满的安全感。二人在朝夕相处中慢慢卸下防备，从责任走向真心，携手面对生活里的重重风波，互相扶持，奔赴温暖安稳的幸福生活。</x:v>
+        <x:v>高考结束那天，林寻在考场外被亲生父母认回原来十八年的普通生活，是父母为磨砺他而设的一场成长课。重回豪门，他没有迷失，反而在桥上遇见了那个让他心动的姑娘，南大冰山学姐苏清诗。从青涩的初次相遇，到演唱会上的合唱，再到大学校园里的朝夕相处，两个真诚的人慢慢靠近。曾经的求而不得终将释怀，双向奔赴的喜欢才最珍贵。褪去普通学生的身份，林寻只想以真心换真心。十八岁的夏天，最好的相遇，最甜的恋爱，才刚刚开始。</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -2109,90 +2115,92 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B28" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C28" s="10" t="str">
-        <x:v>重回雪崩泥石流，我不再犹豫</x:v>
+        <x:v>弄权大玄：我有购物系统</x:v>
       </x:c>
       <x:c r="D28" s="11" t="str">
-        <x:v>09-16 01:02</x:v>
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F28" s="11" t="str">
-        <x:v>↑4位</x:v>
+        <x:v>↑5位</x:v>
       </x:c>
       <x:c r="G28" s="11" t="str"/>
       <x:c r="H28" s="11" t="str"/>
-      <x:c r="I28" s="11" t="n">
-        <x:v>60</x:v>
-      </x:c>
+      <x:c r="I28" s="11" t="str"/>
       <x:c r="J28" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K28" s="10" t="str">
-        <x:v>年代怀旧</x:v>
-      </x:c>
-      <x:c r="L28" s="11" t="str">
-        <x:v>姜缘</x:v>
-      </x:c>
-      <x:c r="M28" s="10" t="str">
-        <x:v>前世，周清雨因犹豫错失逃生时机，眼睁睁看着全家被雪崩泥石流吞没。重生回灾难前三天，她当机立断卖掉五十头牦牛，囤积物资，带家人撤往高处。面对全村嘲讽和阻拦，她不再苦劝。直到雪山崩塌、洪流封村，昔日笑她疯癫的人纷纷求上门。这一次，她只救值得救的人！</x:v>
-      </x:c>
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="L28" s="11" t="str"/>
+      <x:c r="M28" s="10" t="str"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B29" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C29" s="10" t="str">
-        <x:v>弄权大玄：我有购物系统</x:v>
+        <x:v>四个崽崽瞒不住了</x:v>
       </x:c>
       <x:c r="D29" s="11" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>09-15 00:08</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F29" s="11" t="str">
-        <x:v>↑4位</x:v>
+        <x:v>↑5位</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str"/>
       <x:c r="H29" s="11" t="str"/>
-      <x:c r="I29" s="11" t="str"/>
+      <x:c r="I29" s="11" t="n">
+        <x:v>124</x:v>
+      </x:c>
       <x:c r="J29" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K29" s="10" t="str">
-        <x:v>战神异能</x:v>
-      </x:c>
-      <x:c r="L29" s="11" t="str"/>
-      <x:c r="M29" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L29" s="11" t="str">
+        <x:v>桃子动漫剧场</x:v>
+      </x:c>
+      <x:c r="M29" s="10" t="str">
+        <x:v>温茉意外穿书，成为霸总文中声名狼藉的炮灰捞女，原主靠网恋诈骗捞钱挥霍一空，只留给她四个面黄肌瘦、嗷嗷待哺的萌宝烂摊子。本就处境艰难，其中一个孩子还意外走失，转头却直接认回顶级大佬亲爹。全网众人皆坐等她翻车入狱、含泪踩缝纫机，谁知剧情彻底跑偏。高冷封心锁爱的裴少深陷温柔乡，甘愿推掉所有应酬，居家带娃宠妻，彻底化身黏人恋爱脑。</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B30" s="11" t="n">
-        <x:v>44</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C30" s="10" t="str">
-        <x:v>敢泼我馄饨，整条街都别要了</x:v>
+        <x:v>重生第七节车厢</x:v>
       </x:c>
       <x:c r="D30" s="11" t="str">
-        <x:v>09-16 10:00</x:v>
-      </x:c>
-      <x:c r="E30" s="11" t="str"/>
+        <x:v>09-16 11:39</x:v>
+      </x:c>
+      <x:c r="E30" s="11" t="n">
+        <x:v>33</x:v>
+      </x:c>
       <x:c r="F30" s="11" t="str">
-        <x:v>新上榜</x:v>
+        <x:v>↑4位</x:v>
       </x:c>
       <x:c r="G30" s="11" t="str"/>
       <x:c r="H30" s="11" t="str"/>
       <x:c r="I30" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J30" s="10" t="str">
         <x:v>其他</x:v>
@@ -2201,10 +2209,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L30" s="11" t="str">
-        <x:v>治愈 AI 恋</x:v>
+        <x:v>千一剧场</x:v>
       </x:c>
       <x:c r="M30" s="10" t="str">
-        <x:v>南桥旧街投资人许总多年悉心扶持一众商户，给予租金减免与基建投入，可赵川等人却贪念作祟，撕毁协议，还刻意编造谎言煽动网络暴力。面对恩将仇报的局面，许总没有冲动行事，而是恪守契约精神，凭借完备证据通过合法途径理性维权。随着真相公之于众，造谣闹事者自食恶果，承担起违约带来的相应代价。旧街完成焕新升级，充分彰显出法律与规则守护公平正义的强大力量。</x:v>
+        <x:v>高铁列车长林铮死过一次。上一世，四名大学生私带危险实验样品登车，一句“毒倒整节车厢”的戏言被他放行，最终隧道内毒气泄漏，全车罹难，他成了千夫所指的责任人。重回发车前最后一分钟，他顶住求情、质疑与全网非议，硬封第七节车厢，叫停整趟列车。层层戳破瞒报的谎言，这一次，他死守安全红线，要让车上一千零八十六人，全都平安抵达终点。</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -2212,35 +2220,165 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B31" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C31" s="10" t="str">
-        <x:v>工地前的一碗盒饭</x:v>
+        <x:v>有米偏要讨三场雨</x:v>
       </x:c>
       <x:c r="D31" s="11" t="str">
-        <x:v>09-15 11:00</x:v>
-      </x:c>
-      <x:c r="E31" s="11" t="str"/>
+        <x:v>09-16 08:18</x:v>
+      </x:c>
+      <x:c r="E31" s="11" t="n">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="F31" s="11" t="str">
-        <x:v>新上榜</x:v>
+        <x:v>↑2位</x:v>
       </x:c>
       <x:c r="G31" s="11" t="str"/>
       <x:c r="H31" s="11" t="str"/>
       <x:c r="I31" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="J31" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K31" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L31" s="11" t="str">
-        <x:v>小羊说漫</x:v>
+        <x:v>剧有米</x:v>
       </x:c>
       <x:c r="M31" s="10" t="str">
-        <x:v>热火朝天的建筑工地旁，盒饭摊主老陈始终不为暴利所动，坚持猛火现炒和选用新鲜优质的好肉，默默守护工人们的食品安全。最终，在一场危机后，贪婪者受到了严惩，工人们也彻底醒悟。赞美了老陈纯粹的工匠精神，传递了坚守底线、正义必胜的温暖价值观。</x:v>
-      </x:c>
+        <x:v>青石村大旱三月，全村跪求龙王赐雨，四岁的有米却爬上供桌，张口就说龙王敖澜欠她三场雨。为了讨债，她扣雨牌、锁水门、放掉偷接的水、挖通公沟，还把只认天规的敖澜一次次拖进人间麻烦。暴风、山火和争水接连袭来，有米也在一次次选择中让周守财和全村学会先顾人、再顾利。三场雨终于还清，青石村重新秋种，山外却传来石狮异响，新的怪事又找上了她。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B32" s="11" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C32" s="10" t="str">
+        <x:v>瘦身归来，前男友悔不当初</x:v>
+      </x:c>
+      <x:c r="D32" s="11" t="str">
+        <x:v>2026-09-16</x:v>
+      </x:c>
+      <x:c r="E32" s="11" t="str"/>
+      <x:c r="F32" s="11" t="str">
+        <x:v>新上榜</x:v>
+      </x:c>
+      <x:c r="G32" s="11" t="str"/>
+      <x:c r="H32" s="11" t="str"/>
+      <x:c r="I32" s="11" t="str"/>
+      <x:c r="J32" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="K32" s="10" t="str">
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="L32" s="11" t="str"/>
+      <x:c r="M32" s="10" t="str"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B33" s="11" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C33" s="10" t="str">
+        <x:v>冰海沉旧爱</x:v>
+      </x:c>
+      <x:c r="D33" s="11" t="str">
+        <x:v>09-16 10:00</x:v>
+      </x:c>
+      <x:c r="E33" s="11" t="str"/>
+      <x:c r="F33" s="11" t="str">
+        <x:v>新上榜</x:v>
+      </x:c>
+      <x:c r="G33" s="11" t="str"/>
+      <x:c r="H33" s="11" t="str"/>
+      <x:c r="I33" s="11" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="J33" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K33" s="10" t="str">
+        <x:v>年代怀旧 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="L33" s="11" t="str">
+        <x:v>反转超上头</x:v>
+      </x:c>
+      <x:c r="M33" s="10" t="str">
+        <x:v>沈青山曾为一份旧日温情隐去锋芒，默默守护宋妍多年，却在一场变故中看清了人心冷暖。面对误解、背叛与伤害，他不再一味隐忍，而是选择拿回属于自己的一切。随着真实身份浮出水面，昔日被轻视的他重新站上巅峰，也让所有真相随之揭开。宋妍在失去中看见自己的傲慢与短视，终于明白真心从不是理所当然。有人在风雨后重获新生，有人在悔恨中学会担当。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B34" s="11" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C34" s="10" t="str">
+        <x:v>暴雨末世：我绑定缩小千倍系统</x:v>
+      </x:c>
+      <x:c r="D34" s="11" t="str">
+        <x:v>09-16 10:00</x:v>
+      </x:c>
+      <x:c r="E34" s="11" t="str"/>
+      <x:c r="F34" s="11" t="str">
+        <x:v>新上榜</x:v>
+      </x:c>
+      <x:c r="G34" s="11" t="str"/>
+      <x:c r="H34" s="11" t="str"/>
+      <x:c r="I34" s="11" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="J34" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K34" s="10" t="str">
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="L34" s="11" t="str">
+        <x:v>丹丹动漫</x:v>
+      </x:c>
+      <x:c r="M34" s="10" t="str">
+        <x:v>姐妹双重生回到暴雨末世前夜，妹妹王涵抢走“放大千倍”系统争当救世圣母，反手将扶持她十二年的姐姐王澜推入洪水害死。重生归来，王澜绑定被妹妹嫌弃的“缩小千倍”系统，套现百万卷走海量物资，躲进天花板通风管道打造微观要塞，杀巨虫、垦良田，携手硬核工程师陆沉舟建起机械生态伊甸园。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B35" s="11" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C35" s="10" t="str">
+        <x:v>结婚八年，我娶的原来是仇人的女儿</x:v>
+      </x:c>
+      <x:c r="D35" s="11" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="E35" s="11" t="str"/>
+      <x:c r="F35" s="11" t="str">
+        <x:v>新上榜</x:v>
+      </x:c>
+      <x:c r="G35" s="11" t="str"/>
+      <x:c r="H35" s="11" t="str"/>
+      <x:c r="I35" s="11" t="str"/>
+      <x:c r="J35" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="K35" s="10" t="str">
+        <x:v>家庭伦理 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="L35" s="11" t="str"/>
+      <x:c r="M35" s="10" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2285,7 +2423,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
         <x:v>被诬陷诊出喜脉，重活一世我逆转前尘</x:v>
@@ -2308,7 +2446,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
         <x:v>我都元婴期了，你跟我说开学</x:v>
@@ -2331,76 +2469,76 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>有米偏要讨三场雨</x:v>
+        <x:v>敢泼我馄饨，整条街都别要了</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>09-16 08:18</x:v>
+        <x:v>09-16 10:00</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
-        <x:v>98</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F4" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G4" s="10" t="str">
-        <x:v>剧有米</x:v>
+        <x:v>治愈 AI 恋</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>重回雪崩泥石流，我不再犹豫</x:v>
+        <x:v>有米偏要讨三场雨</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>09-16 01:02</x:v>
+        <x:v>09-16 08:18</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F5" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G5" s="10" t="str">
-        <x:v>姜缘</x:v>
+        <x:v>剧有米</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>霁月安遥之以余生为诺护你岁岁无忧第一季</x:v>
+        <x:v>重回雪崩泥石流，我不再犹豫</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>09-16 06:06</x:v>
+        <x:v>09-16 01:02</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
-        <x:v>144</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F6" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G6" s="10" t="str">
-        <x:v>花花说漫</x:v>
+        <x:v>姜缘</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
         <x:v>重生第七节车厢</x:v>
@@ -2423,76 +2561,70 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="n">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>敢泼我馄饨，整条街都别要了</x:v>
+        <x:v>霁月安遥之以余生为诺护你岁岁无忧第一季</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>09-16 10:00</x:v>
+        <x:v>09-16 06:06</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F8" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G8" s="10" t="str">
-        <x:v>治愈 AI 恋</x:v>
+        <x:v>花花说漫</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="n">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>八媳妇只想买包，一不小心拯救了全家</x:v>
+        <x:v>瘦身归来，前男友悔不当初</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>今日发布</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="str">
-        <x:v>09-16 10:00</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="n">
-        <x:v>80</x:v>
-      </x:c>
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="str"/>
+      <x:c r="E9" s="11" t="str"/>
       <x:c r="F9" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G9" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
-      </x:c>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="G9" s="10" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>嫡姐日日闹换夫，圣旨赐下后她悔疯了</x:v>
+        <x:v>八媳妇只想买包，一不小心拯救了全家</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>09-16 08:00</x:v>
+        <x:v>09-16 10:00</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F10" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G10" s="10" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
         <x:v>弄权大玄：我有购物系统</x:v>
@@ -2509,43 +2641,95 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>说好九十天就回来，我不等了</x:v>
+        <x:v>嫡姐日日闹换夫，圣旨赐下后她悔疯了</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
         <x:v>今日发布</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>09-16 06:00</x:v>
+        <x:v>09-16 08:00</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F12" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G12" s="10" t="str">
-        <x:v>小宁漫漫</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>傅少你夫人又在扮猪吃虎了</x:v>
+        <x:v>说好九十天就回来，我不等了</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>当日新上榜</x:v>
-      </x:c>
-      <x:c r="D13" s="11" t="str"/>
-      <x:c r="E13" s="11" t="str"/>
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D13" s="11" t="str">
+        <x:v>09-16 06:00</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="n">
+        <x:v>66</x:v>
+      </x:c>
       <x:c r="F13" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="G13" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G13" s="10" t="str">
+        <x:v>小宁漫漫</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="11" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B14" s="10" t="str">
+        <x:v>冰海沉旧爱</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="str">
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="str">
+        <x:v>09-16 10:00</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F14" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G14" s="10" t="str">
+        <x:v>反转超上头</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="11" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B15" s="10" t="str">
+        <x:v>暴雨末世：我绑定缩小千倍系统</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="str">
+        <x:v>今日发布</x:v>
+      </x:c>
+      <x:c r="D15" s="11" t="str">
+        <x:v>09-16 10:00</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="F15" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G15" s="10" t="str">
+        <x:v>丹丹动漫</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2614,7 +2798,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
         <x:v>征地我秒签跑路，全村笑我半年</x:v>
@@ -2688,7 +2872,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
         <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
@@ -2725,16 +2909,16 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>抢个新娘来当后娘第一季</x:v>
+        <x:v>重生三天前，我用水泥封死地下室</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>09-08 15:10</x:v>
+        <x:v>09-09 09:28</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
         <x:v>7</x:v>
@@ -2743,10 +2927,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G5" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H5" s="11" t="n">
-        <x:v>177</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I5" s="10" t="str">
         <x:v>其他</x:v>
@@ -2754,24 +2938,24 @@
       <x:c r="J5" s="11" t="str"/>
       <x:c r="K5" s="11" t="str"/>
       <x:c r="L5" s="10" t="str">
-        <x:v>麻辣公主</x:v>
+        <x:v>忘忧剧场</x:v>
       </x:c>
       <x:c r="M5" s="10" t="str">
-        <x:v>带着十里红妆出嫁那日，我才得知新郎早已另娶，这门亲事不过是盯上了我李家的家产。换作旁人或许忍气吞声，我偏不。我当众拒入侯府，主动上书朝廷，愿以嫁妆资援南方水患，只求解除婚约、护我父母周全。这份胆识赢得安王敬重，他以正妃之礼娶我入门。我立誓此生不做妾、不与人共侍一夫，终得一份彼此尊重的姻缘。</x:v>
+        <x:v>阮清重生回被保姆王妈一家害死的三天前，前世她因心善引狼入室，保姆全家蜗居别墅地下室偷窃投毒，最终惨遭勒死。重生后她假装不知，趁王妈外出时用水泥将地下室彻底封死。警方破墙后，五具尸体令真相大白，王妈因盗窃、投毒被判十五年。阮清与父母团聚，恶人终得恶报，她重获新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>重生三天前，我用水泥封死地下室</x:v>
+        <x:v>抢个新娘来当后娘第一季</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>09-09 09:28</x:v>
+        <x:v>09-08 15:10</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
         <x:v>7</x:v>
@@ -2780,10 +2964,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G6" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H6" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
         <x:v>其他</x:v>
@@ -2791,15 +2975,15 @@
       <x:c r="J6" s="11" t="str"/>
       <x:c r="K6" s="11" t="str"/>
       <x:c r="L6" s="10" t="str">
-        <x:v>忘忧剧场</x:v>
+        <x:v>麻辣公主</x:v>
       </x:c>
       <x:c r="M6" s="10" t="str">
-        <x:v>阮清重生回被保姆王妈一家害死的三天前，前世她因心善引狼入室，保姆全家蜗居别墅地下室偷窃投毒，最终惨遭勒死。重生后她假装不知，趁王妈外出时用水泥将地下室彻底封死。警方破墙后，五具尸体令真相大白，王妈因盗窃、投毒被判十五年。阮清与父母团聚，恶人终得恶报，她重获新生。</x:v>
+        <x:v>带着十里红妆出嫁那日，我才得知新郎早已另娶，这门亲事不过是盯上了我李家的家产。换作旁人或许忍气吞声，我偏不。我当众拒入侯府，主动上书朝廷，愿以嫁妆资援南方水患，只求解除婚约、护我父母周全。这份胆识赢得安王敬重，他以正妃之礼娶我入门。我立誓此生不做妾、不与人共侍一夫，终得一份彼此尊重的姻缘。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
         <x:v>一墙之隔，皆是人心</x:v>
@@ -2836,16 +3020,16 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>黑蛋孵出山海神兽后我无敌了</x:v>
+        <x:v>不靠谱爸妈很靠谱</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>09-06 18:00</x:v>
+        <x:v>09-09 11:08</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
         <x:v>7</x:v>
@@ -2854,10 +3038,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G8" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H8" s="11" t="n">
-        <x:v>154</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
         <x:v>其他</x:v>
@@ -2865,24 +3049,24 @@
       <x:c r="J8" s="11" t="str"/>
       <x:c r="K8" s="11" t="str"/>
       <x:c r="L8" s="10" t="str">
-        <x:v>抱月剧场</x:v>
+        <x:v>灵妹儿</x:v>
       </x:c>
       <x:c r="M8" s="10" t="str">
-        <x:v>寒门少年李初七攒了三年银子，仍买不起最低等的兽蛋。一次意外，他在后山捡到一枚黑蛋，孵出的煤球又小又馋，偏偏爱啃铜钱。可每吞下一缕兽息，它便能复现对手的能力。县学测灵那日，测灵石骤然亮起黑光，群兽伏地。所有人都以为他只是走了好运，只有陆远山想起古籍中的禁忌——黑光现，万兽伏。煤球究竟是什么？</x:v>
+        <x:v>外表张扬的年轻夫妻在冬夜救下女婴林小小，用十七年的辛勤劳动和无条件陪伴，为她撑起温暖的家。曾经成绩落后的林小小，在父母的鼓励下重新学习，一步步成长为优秀学生。面对亲生家庭带来的资源与人生选择，她也开始重新理解血缘、养育与责任。当外界的误解影响到父母的生活，林小小决定勇敢站出来，用事实守护家人，也用努力证明真正的爱，是尊重、陪伴和彼此成就。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>不靠谱爸妈很靠谱</x:v>
+        <x:v>黑蛋孵出山海神兽后我无敌了</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>09-09 11:08</x:v>
+        <x:v>09-06 18:00</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
         <x:v>7</x:v>
@@ -2891,10 +3075,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G9" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H9" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str">
         <x:v>其他</x:v>
@@ -2902,24 +3086,24 @@
       <x:c r="J9" s="11" t="str"/>
       <x:c r="K9" s="11" t="str"/>
       <x:c r="L9" s="10" t="str">
-        <x:v>灵妹儿</x:v>
+        <x:v>抱月剧场</x:v>
       </x:c>
       <x:c r="M9" s="10" t="str">
-        <x:v>外表张扬的年轻夫妻在冬夜救下女婴林小小，用十七年的辛勤劳动和无条件陪伴，为她撑起温暖的家。曾经成绩落后的林小小，在父母的鼓励下重新学习，一步步成长为优秀学生。面对亲生家庭带来的资源与人生选择，她也开始重新理解血缘、养育与责任。当外界的误解影响到父母的生活，林小小决定勇敢站出来，用事实守护家人，也用努力证明真正的爱，是尊重、陪伴和彼此成就。</x:v>
+        <x:v>寒门少年李初七攒了三年银子，仍买不起最低等的兽蛋。一次意外，他在后山捡到一枚黑蛋，孵出的煤球又小又馋，偏偏爱啃铜钱。可每吞下一缕兽息，它便能复现对手的能力。县学测灵那日，测灵石骤然亮起黑光，群兽伏地。所有人都以为他只是走了好运，只有陆远山想起古籍中的禁忌——黑光现，万兽伏。煤球究竟是什么？</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>惊絮无声：傻女的绝杀</x:v>
+        <x:v>离家十年，回来女儿被换了</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>09-06 10:00</x:v>
+        <x:v>09-09 00:04</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
         <x:v>7</x:v>
@@ -2928,10 +3112,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G10" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H10" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="I10" s="10" t="str">
         <x:v>其他</x:v>
@@ -2939,24 +3123,24 @@
       <x:c r="J10" s="11" t="str"/>
       <x:c r="K10" s="11" t="str"/>
       <x:c r="L10" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>魔方影视（上剧版</x:v>
       </x:c>
       <x:c r="M10" s="10" t="str">
-        <x:v>沈家人人都是天才，唯独小女儿沈惊絮是公认的傻子。没人知道，她不仅装傻多年，还带着前世金牌律师的记忆重生而来。本想闭嘴躺平一生，谁料内鬼勾结资本做空沈氏，一纸合同就要让全家净身出户、背上百亿债务。父亲落笔前，她终于按住协议“这字不能签！”绝地反杀的沈惊絮，一步步挫败了对沈家的围剿，也让全家人重新认识了自己。沈家也迎来了新生。</x:v>
+        <x:v>程砚宁完成长期绝密任务归来，满心想要弥补亲情，却发现家中早已物是人非。身边亲近之人被私欲蒙蔽，制造重重骗局，试图侵占她的事业与财富。面对接连而来的算计与危机，她凭借过人的魄力与智慧步步拆解阴谋，联合正义力量搜集证据，厘清全部是非纠葛。在守护自身事业的同时，她放下过往伤痛，投身公益，完成自我和解，迎来属于自己的全新人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>离家十年，回来女儿被换了</x:v>
+        <x:v>惊絮无声：傻女的绝杀</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>09-09 00:04</x:v>
+        <x:v>09-06 10:00</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
         <x:v>7</x:v>
@@ -2965,10 +3149,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G11" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H11" s="11" t="n">
-        <x:v>155</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I11" s="10" t="str">
         <x:v>其他</x:v>
@@ -2976,24 +3160,24 @@
       <x:c r="J11" s="11" t="str"/>
       <x:c r="K11" s="11" t="str"/>
       <x:c r="L11" s="10" t="str">
-        <x:v>魔方影视（上剧版</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="M11" s="10" t="str">
-        <x:v>程砚宁完成长期绝密任务归来，满心想要弥补亲情，却发现家中早已物是人非。身边亲近之人被私欲蒙蔽，制造重重骗局，试图侵占她的事业与财富。面对接连而来的算计与危机，她凭借过人的魄力与智慧步步拆解阴谋，联合正义力量搜集证据，厘清全部是非纠葛。在守护自身事业的同时，她放下过往伤痛，投身公益，完成自我和解，迎来属于自己的全新人生。</x:v>
+        <x:v>沈家人人都是天才，唯独小女儿沈惊絮是公认的傻子。没人知道，她不仅装傻多年，还带着前世金牌律师的记忆重生而来。本想闭嘴躺平一生，谁料内鬼勾结资本做空沈氏，一纸合同就要让全家净身出户、背上百亿债务。父亲落笔前，她终于按住协议“这字不能签！”绝地反杀的沈惊絮，一步步挫败了对沈家的围剿，也让全家人重新认识了自己。沈家也迎来了新生。</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
+        <x:v>大坝边寻回的真千金</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>09-08 11:00</x:v>
+        <x:v>09-10 11:26</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
         <x:v>7</x:v>
@@ -3002,10 +3186,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G12" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H12" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str">
         <x:v>其他</x:v>
@@ -3013,24 +3197,24 @@
       <x:c r="J12" s="11" t="str"/>
       <x:c r="K12" s="11" t="str"/>
       <x:c r="L12" s="10" t="str">
-        <x:v>白桃剧场</x:v>
+        <x:v>喵琪琪追剧</x:v>
       </x:c>
       <x:c r="M12" s="10" t="str">
-        <x:v>阿梨一觉睡了三百年，养大的五只小兽尽数离去。她带着五只旧饭碗、十二枚铜钱与一把锈柴刀下山寻兽。昔日的小家伙已成威震四方的妖祖，历经重重相遇与揭秘，阿梨知晓三百年封印的真相，携手五只妖祖，一同对抗祸世灭灵兽神。</x:v>
+        <x:v>大坝突发险情，农村女孩夏晚禾凭借熟悉的环境和过人的勇气，不顾危险救下被困的沈长洲。一次意外的救援，让两个陌生人的命运重新交织。随着调查深入，沈长洲发现这个善良坚韧的女孩，竟是自己失散二十年的亲生女儿。面对迟来的亲情和真假千金的风波，夏晚禾没有依靠身份改变人生，而是用智慧、担当和努力证明自己的价值。陆言川也在一次次并肩相处中，被她的真诚与坚强打动，陪她找回亲情，走向新的未来。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>大坝边寻回的真千金</x:v>
+        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>09-10 11:26</x:v>
+        <x:v>09-08 11:00</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
         <x:v>7</x:v>
@@ -3039,10 +3223,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G13" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H13" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="I13" s="10" t="str">
         <x:v>其他</x:v>
@@ -3050,61 +3234,55 @@
       <x:c r="J13" s="11" t="str"/>
       <x:c r="K13" s="11" t="str"/>
       <x:c r="L13" s="10" t="str">
-        <x:v>喵琪琪追剧</x:v>
+        <x:v>白桃剧场</x:v>
       </x:c>
       <x:c r="M13" s="10" t="str">
-        <x:v>大坝突发险情，农村女孩夏晚禾凭借熟悉的环境和过人的勇气，不顾危险救下被困的沈长洲。一次意外的救援，让两个陌生人的命运重新交织。随着调查深入，沈长洲发现这个善良坚韧的女孩，竟是自己失散二十年的亲生女儿。面对迟来的亲情和真假千金的风波，夏晚禾没有依靠身份改变人生，而是用智慧、担当和努力证明自己的价值。陆言川也在一次次并肩相处中，被她的真诚与坚强打动，陪她找回亲情，走向新的未来。</x:v>
+        <x:v>阿梨一觉睡了三百年，养大的五只小兽尽数离去。她带着五只旧饭碗、十二枚铜钱与一把锈柴刀下山寻兽。昔日的小家伙已成威震四方的妖祖，历经重重相遇与揭秘，阿梨知晓三百年封印的真相，携手五只妖祖，一同对抗祸世灭灵兽神。</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>穿越60我有空间不愁吃喝</x:v>
+        <x:v>凤阙承安</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>09-07 00:04</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G14" s="11" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H14" s="11" t="n">
-        <x:v>1000</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="str"/>
       <x:c r="I14" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J14" s="11" t="str"/>
       <x:c r="K14" s="11" t="str"/>
-      <x:c r="L14" s="10" t="str">
-        <x:v>夜珠AI剧场</x:v>
-      </x:c>
-      <x:c r="M14" s="10" t="str">
-        <x:v>现代青年刘大壮意外穿越到60年代，成了同名同姓的16岁穷小子。原主因相亲被拒、家徒四壁，下河摸鱼时溺亡。大壮醒来后发现脑中多了一座九层宝塔空间——内有灵药田与灵泉潭水，作物两小时成熟、产量翻五倍。饥荒年代，别人啃树皮喝稀粥，他靠空间种出满仓土豆粮食，黑市换粮票钞票，让饿肚子的父母姐姐们吃上饱饭。从人人嘲笑的穷小子，到带着全家逆袭翻盘，且看他手握宝塔空间，在艰苦年代闯出一条吃喝不愁的逆袭</x:v>
-      </x:c>
+      <x:c r="L14" s="10" t="str"/>
+      <x:c r="M14" s="10" t="str"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
+        <x:v>穿越60我有空间不愁吃喝</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
-        <x:v>09-11 09:00</x:v>
+        <x:v>09-07 00:04</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
         <x:v>6</x:v>
@@ -3113,10 +3291,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G15" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H15" s="11" t="n">
-        <x:v>133</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="I15" s="10" t="str">
         <x:v>其他</x:v>
@@ -3124,24 +3302,24 @@
       <x:c r="J15" s="11" t="str"/>
       <x:c r="K15" s="11" t="str"/>
       <x:c r="L15" s="10" t="str">
-        <x:v>阳阳动画</x:v>
+        <x:v>夜珠AI剧场</x:v>
       </x:c>
       <x:c r="M15" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
+        <x:v>现代青年刘大壮意外穿越到60年代，成了同名同姓的16岁穷小子。原主因相亲被拒、家徒四壁，下河摸鱼时溺亡。大壮醒来后发现脑中多了一座九层宝塔空间——内有灵药田与灵泉潭水，作物两小时成熟、产量翻五倍。饥荒年代，别人啃树皮喝稀粥，他靠空间种出满仓土豆粮食，黑市换粮票钞票，让饿肚子的父母姐姐们吃上饱饭。从人人嘲笑的穷小子，到带着全家逆袭翻盘，且看他手握宝塔空间，在艰苦年代闯出一条吃喝不愁的逆袭</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>三分钱的取舍</x:v>
+        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>09-10 17:29</x:v>
+        <x:v>09-11 09:00</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
         <x:v>6</x:v>
@@ -3150,10 +3328,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G16" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H16" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str">
         <x:v>其他</x:v>
@@ -3161,24 +3339,24 @@
       <x:c r="J16" s="11" t="str"/>
       <x:c r="K16" s="11" t="str"/>
       <x:c r="L16" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>阳阳动画</x:v>
       </x:c>
       <x:c r="M16" s="10" t="str">
-        <x:v>青石沟果农为省下代办三分钱，甩开中间商周成岳，直接对接收购商方洪生收桃。可脱离周成岳统筹调度后，摘桃、排单、装车乱象丛生，桃子积压损耗。周成岳转身接手偏远的十里湾桃园，凭口碑站稳脚跟。经历一季波折，青石沟众人幡然醒悟，重新读懂代办的价值。</x:v>
+        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="n">
-        <x:v>84</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>回到零四年进军彩铃界</x:v>
+        <x:v>三分钱的取舍</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>2026-09-11</x:v>
+        <x:v>09-10 17:29</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
         <x:v>6</x:v>
@@ -3187,20 +3365,26 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G17" s="11" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H17" s="11" t="str"/>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H17" s="11" t="n">
+        <x:v>58</x:v>
+      </x:c>
       <x:c r="I17" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J17" s="11" t="str"/>
       <x:c r="K17" s="11" t="str"/>
-      <x:c r="L17" s="10" t="str"/>
-      <x:c r="M17" s="10" t="str"/>
+      <x:c r="L17" s="10" t="str">
+        <x:v>马克动漫</x:v>
+      </x:c>
+      <x:c r="M17" s="10" t="str">
+        <x:v>青石沟果农为省下代办三分钱，甩开中间商周成岳，直接对接收购商方洪生收桃。可脱离周成岳统筹调度后，摘桃、排单、装车乱象丛生，桃子积压损耗。周成岳转身接手偏远的十里湾桃园，凭口碑站稳脚跟。经历一季波折，青石沟众人幡然醒悟，重新读懂代办的价值。</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
         <x:v>青牛引泉来</x:v>
@@ -3238,7 +3422,7 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
         <x:v>七套房产，换来一纸调令</x:v>
@@ -3275,7 +3459,7 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="n">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
         <x:v>泰城错嫁</x:v>
@@ -3312,7 +3496,7 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
         <x:v>敢抢我的车位</x:v>
@@ -3349,13 +3533,13 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="n">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>锦书迟</x:v>
+        <x:v>重生山火前，我舍祖宅护全家</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>09-12 07:30</x:v>
+        <x:v>09-12 16:06</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
         <x:v>4</x:v>
@@ -3367,10 +3551,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G22" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H22" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str">
         <x:v>其他</x:v>
@@ -3378,21 +3562,21 @@
       <x:c r="J22" s="11" t="str"/>
       <x:c r="K22" s="11" t="str"/>
       <x:c r="L22" s="10" t="str">
-        <x:v>咩咩漫文</x:v>
+        <x:v>千鹤动漫</x:v>
       </x:c>
       <x:c r="M22" s="10" t="str">
-        <x:v>三年前，沈昭昭嫁与永宁侯谢凛，新婚燕尔他便远赴边关。她苦等家书，却不知双向书信早被人暗中截留。她终于心冷离开侯府。三年后，她带着孩子在市井支摊卖画立足，他却循着蛛丝马迹寻来，真相层层揭开，原来他从未负她。</x:v>
+        <x:v>顾长河带着前世山火中痛失全家的记忆重生归来，得知三日后西岭大火将再次席卷村庄，他不顾众人质疑，卖掉祖宅，带着妻子母亲和儿子搬上白石坡，储水备粮清出防火带，只为改写一家人的命运，当烈火真正逼近，所有人终于明白，他舍掉的只是房子，拼命守住的才是真正的家。</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>我送弟弟上青云</x:v>
+        <x:v>锦书迟</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>09-12 09:52</x:v>
+        <x:v>09-12 07:30</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
         <x:v>4</x:v>
@@ -3404,10 +3588,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G23" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H23" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
         <x:v>其他</x:v>
@@ -3415,21 +3599,21 @@
       <x:c r="J23" s="11" t="str"/>
       <x:c r="K23" s="11" t="str"/>
       <x:c r="L23" s="10" t="str">
-        <x:v>落云</x:v>
+        <x:v>咩咩漫文</x:v>
       </x:c>
       <x:c r="M23" s="10" t="str">
-        <x:v>宋远回乡发现弟弟宋临被父亲剥夺上学权利，只能干农活。他毅然带走弟弟，用微薄工资供他读书。宋临考上名校建筑系，毕业后成为身价过亿的设计师。他用第一桶金给哥哥买房，报答当年恩情。面对迟来求和的父亲，宋临完成了心灵的真正和解。这是一个关于“长兄如父、手足情深”的故事，诠释了扶助与感恩的力量。</x:v>
+        <x:v>三年前，沈昭昭嫁与永宁侯谢凛，新婚燕尔他便远赴边关。她苦等家书，却不知双向书信早被人暗中截留。她终于心冷离开侯府。三年后，她带着孩子在市井支摊卖画立足，他却循着蛛丝马迹寻来，真相层层揭开，原来他从未负她。</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>重生山火前，我舍祖宅护全家</x:v>
+        <x:v>我送弟弟上青云</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>09-12 16:06</x:v>
+        <x:v>09-12 09:52</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
         <x:v>4</x:v>
@@ -3441,10 +3625,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G24" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H24" s="11" t="n">
-        <x:v>89</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I24" s="10" t="str">
         <x:v>其他</x:v>
@@ -3452,15 +3636,15 @@
       <x:c r="J24" s="11" t="str"/>
       <x:c r="K24" s="11" t="str"/>
       <x:c r="L24" s="10" t="str">
-        <x:v>千鹤动漫</x:v>
+        <x:v>落云</x:v>
       </x:c>
       <x:c r="M24" s="10" t="str">
-        <x:v>顾长河带着前世山火中痛失全家的记忆重生归来，得知三日后西岭大火将再次席卷村庄，他不顾众人质疑，卖掉祖宅，带着妻子母亲和儿子搬上白石坡，储水备粮清出防火带，只为改写一家人的命运，当烈火真正逼近，所有人终于明白，他舍掉的只是房子，拼命守住的才是真正的家。</x:v>
+        <x:v>宋远回乡发现弟弟宋临被父亲剥夺上学权利，只能干农活。他毅然带走弟弟，用微薄工资供他读书。宋临考上名校建筑系，毕业后成为身价过亿的设计师。他用第一桶金给哥哥买房，报答当年恩情。面对迟来求和的父亲，宋临完成了心灵的真正和解。这是一个关于“长兄如父、手足情深”的故事，诠释了扶助与感恩的力量。</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
         <x:v>我的师兄全是修仙界大佬</x:v>
@@ -3497,7 +3681,7 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
         <x:v>双姝逢旧岸，一怒扫尘奸</x:v>
@@ -3537,13 +3721,13 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>退婚从抢我车位开始</x:v>
+        <x:v>重生1985年，赶海我有系统</x:v>
       </x:c>
       <x:c r="C27" s="11" t="str">
-        <x:v>2026-09-12</x:v>
+        <x:v>09-11 07:00</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
         <x:v>5</x:v>
@@ -3552,26 +3736,32 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G27" s="11" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H27" s="11" t="str"/>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H27" s="11" t="n">
+        <x:v>132</x:v>
+      </x:c>
       <x:c r="I27" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J27" s="11" t="str"/>
       <x:c r="K27" s="11" t="str"/>
-      <x:c r="L27" s="10" t="str"/>
-      <x:c r="M27" s="10" t="str"/>
+      <x:c r="L27" s="10" t="str">
+        <x:v>依语动漫</x:v>
+      </x:c>
+      <x:c r="M27" s="10" t="str">
+        <x:v>八十年代小渔村，林舟出钱出力帮家里盖起红砖新房，落成之日却遭到父母兄长算计，新房被夺走，自己只分得被搬空的破旧老屋。带着前世被家人压榨到老的遗憾，重活一世的林舟不再愚孝，请来村长当众分家切割亲缘。绝境之中，他意外激活渔业情报系统，可以接收大海给出的渔获线索。他借得工具赶海，捞获珍贵大石斑鱼赚取第一笔启动资金，又约上好友李二狗大雾天冒险出海，依靠系统指引追逐鱼群。</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="11" t="n">
-        <x:v>89</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>提分手那天，我的任职令刚下来</x:v>
+        <x:v>退婚从抢我车位开始</x:v>
       </x:c>
       <x:c r="C28" s="11" t="str">
-        <x:v>09-12 07:40</x:v>
+        <x:v>2026-09-12</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
         <x:v>4</x:v>
@@ -3583,115 +3773,109 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G28" s="11" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H28" s="11" t="n">
-        <x:v>64</x:v>
-      </x:c>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H28" s="11" t="str"/>
       <x:c r="I28" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J28" s="11" t="str"/>
       <x:c r="K28" s="11" t="str"/>
-      <x:c r="L28" s="10" t="str">
-        <x:v>星漫世界</x:v>
-      </x:c>
-      <x:c r="M28" s="10" t="str">
-        <x:v>澜江市，刚结束七年恋情的江晓棠如愿上岸，决然转身离去。没曾想，前男友贺铭以转业安置身份，空降进入同一应急管理局。旧爱狭路相逢，尴尬拉扯还未落幕，滨南快速路突发危化品连环车祸。报到首日的贺铭无视现场命令，冲破警戒线冲入火场，拼尽全力营救被困女童。就在撤离瞬间轿车爆炸，火光席卷全场，他纵身将怀中女孩与赶来的女医生向澜舒一并护在身下。</x:v>
-      </x:c>
+      <x:c r="L28" s="10" t="str"/>
+      <x:c r="M28" s="10" t="str"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>重生1985年，赶海我有系统</x:v>
+        <x:v>穿成恋爱脑女配，我把将军府带偏了呀</x:v>
       </x:c>
       <x:c r="C29" s="11" t="str">
-        <x:v>09-11 07:00</x:v>
+        <x:v>2026-09-06</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G29" s="11" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H29" s="11" t="n">
-        <x:v>132</x:v>
-      </x:c>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H29" s="11" t="str"/>
       <x:c r="I29" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J29" s="11" t="str"/>
       <x:c r="K29" s="11" t="str"/>
-      <x:c r="L29" s="10" t="str">
-        <x:v>依语动漫</x:v>
-      </x:c>
-      <x:c r="M29" s="10" t="str">
-        <x:v>八十年代小渔村，林舟出钱出力帮家里盖起红砖新房，落成之日却遭到父母兄长算计，新房被夺走，自己只分得被搬空的破旧老屋。带着前世被家人压榨到老的遗憾，重活一世的林舟不再愚孝，请来村长当众分家切割亲缘。绝境之中，他意外激活渔业情报系统，可以接收大海给出的渔获线索。他借得工具赶海，捞获珍贵大石斑鱼赚取第一笔启动资金，又约上好友李二狗大雾天冒险出海，依靠系统指引追逐鱼群。</x:v>
-      </x:c>
+      <x:c r="L29" s="10" t="str"/>
+      <x:c r="M29" s="10" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>穿成恋爱脑女配，我把将军府带偏了呀</x:v>
+        <x:v>我月薪八千，但公司是我的</x:v>
       </x:c>
       <x:c r="C30" s="11" t="str">
-        <x:v>2026-09-06</x:v>
+        <x:v>09-09 20:47</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G30" s="11" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H30" s="11" t="str"/>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H30" s="11" t="n">
+        <x:v>97</x:v>
+      </x:c>
       <x:c r="I30" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J30" s="11" t="str"/>
       <x:c r="K30" s="11" t="str"/>
-      <x:c r="L30" s="10" t="str"/>
-      <x:c r="M30" s="10" t="str"/>
+      <x:c r="L30" s="10" t="str">
+        <x:v>阿宝剧场</x:v>
+      </x:c>
+      <x:c r="M30" s="10" t="str">
+        <x:v>北辰科技创始人陆景川为人低调，相亲时只坦言月薪八千，当即被相亲对象乔思雨嫌弃离场，还被对方在朋友圈造谣成“蹭咖啡捞男”。后续乔思雨应聘北辰科技、出席投资饭局，接连撞见陆景川，场面屡屡社死。陆景川却在常去的咖啡厅，因店员沈安然的仗义执言，窥见了比金钱更动人的真心。</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="11" t="n">
-        <x:v>77</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>我月薪八千，但公司是我的</x:v>
+        <x:v>南乔渡夜寒</x:v>
       </x:c>
       <x:c r="C31" s="11" t="str">
-        <x:v>09-09 20:47</x:v>
+        <x:v>09-09 09:28</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G31" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H31" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="I31" s="10" t="str">
         <x:v>其他</x:v>
@@ -3699,10 +3883,10 @@
       <x:c r="J31" s="11" t="str"/>
       <x:c r="K31" s="11" t="str"/>
       <x:c r="L31" s="10" t="str">
-        <x:v>阿宝剧场</x:v>
+        <x:v>馨动剧场</x:v>
       </x:c>
       <x:c r="M31" s="10" t="str">
-        <x:v>北辰科技创始人陆景川为人低调，相亲时只坦言月薪八千，当即被相亲对象乔思雨嫌弃离场，还被对方在朋友圈造谣成“蹭咖啡捞男”。后续乔思雨应聘北辰科技、出席投资饭局，接连撞见陆景川，场面屡屡社死。陆景川却在常去的咖啡厅，因店员沈安然的仗义执言，窥见了比金钱更动人的真心。</x:v>
+        <x:v>沈南乔斩断屈辱错婚，与摄政王萧夜寒结盟彼此救赎。她凭精湛医术压制寒毒、整肃药局、为母昭雪沉冤，救下受陷害的宫妃；他以权势相护，予她全然信任与底气。二人并肩撕破东宫与相府的层层阴谋，拔除朝堂蛀虫，女主从深闺弃女逆袭成掌兵王妃，两人从交易羁绊走向情深意笃，共守家国安稳</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3757,16 +3941,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
-        <x:v>5.2</x:v>
+        <x:v>5.4</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F2" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>2026-09-16 08-11</x:v>
+        <x:v>2026-09-16 09-11</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3780,16 +3964,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
-        <x:v>7.2</x:v>
+        <x:v>7.4</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F3" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>2026-09-16 08-11</x:v>
+        <x:v>2026-09-16 09-11</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -3803,16 +3987,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>8.3</x:v>
+        <x:v>8.7</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F4" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>2026-09-16 08-11</x:v>
+        <x:v>2026-09-16 09-11</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3826,16 +4010,16 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>6.9</x:v>
+        <x:v>6.8</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F5" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>2026-09-16 08-11</x:v>
+        <x:v>2026-09-16 09-11</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -3849,16 +4033,16 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>7.7</x:v>
+        <x:v>7.9</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F6" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>2026-09-16 08-11</x:v>
+        <x:v>2026-09-16 09-11</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3866,22 +4050,22 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>七套房产，换来一纸调令</x:v>
+        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
       </x:c>
       <x:c r="C7" s="11" t="n">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>12.1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F7" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>2026-09-16 06-44</x:v>
+        <x:v>2026-09-16 09-11</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -3889,22 +4073,22 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>满宫都以为我是摆设，直到父皇为我废了东宫</x:v>
+        <x:v>15年青春苦守，未婚夫装穷归来</x:v>
       </x:c>
       <x:c r="C8" s="11" t="n">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>4.6</x:v>
+        <x:v>1.7</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>2026-09-16 08-11</x:v>
+        <x:v>2026-09-16 09-11</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3912,22 +4096,22 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>15年青春苦守，未婚夫装穷归来</x:v>
+        <x:v>七套房产，换来一纸调令</x:v>
       </x:c>
       <x:c r="C9" s="11" t="n">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>1.7</x:v>
+        <x:v>12.3</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>2026-09-16 08-11</x:v>
+        <x:v>2026-09-16 06-44</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -3941,16 +4125,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>12.9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="F10" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>2026-09-16 08-11</x:v>
+        <x:v>2026-09-16 09-11</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -3958,22 +4142,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>青牛引泉来</x:v>
+        <x:v>重回82：我成山君契约万兽打猎宠妻</x:v>
       </x:c>
       <x:c r="C11" s="11" t="n">
         <x:v>23</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>12.5</x:v>
+        <x:v>5.9</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
-        <x:v>2026-09-16 08-11</x:v>
+        <x:v>2026-09-16 09-11</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -3981,22 +4165,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>重回82：我成山君契约万兽打猎宠妻</x:v>
+        <x:v>新厂旧账</x:v>
       </x:c>
       <x:c r="C12" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G12" s="11" t="str">
-        <x:v>2026-09-16 08-11</x:v>
+        <x:v>2026-09-16 09-11</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -4004,19 +4188,19 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>新厂旧账</x:v>
+        <x:v>青牛引泉来</x:v>
       </x:c>
       <x:c r="C13" s="11" t="n">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>8.7</x:v>
+        <x:v>12.8</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G13" s="11" t="str">
         <x:v>2026-09-16 08-11</x:v>
@@ -4030,10 +4214,10 @@
         <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
       </x:c>
       <x:c r="C14" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>11.4</x:v>
+        <x:v>11.6</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
         <x:v>6</x:v>
@@ -4050,22 +4234,22 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>重生三天前，我用水泥封死地下室</x:v>
+        <x:v>晚棠知归，七年终见你</x:v>
       </x:c>
       <x:c r="C15" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>12.7</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F15" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G15" s="11" t="str">
-        <x:v>2026-09-16 08-11</x:v>
+        <x:v>2026-09-16 09-11</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -4073,19 +4257,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>晚棠知归，七年终见你</x:v>
+        <x:v>重生三天前，我用水泥封死地下室</x:v>
       </x:c>
       <x:c r="C16" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>4.2</x:v>
+        <x:v>12.8</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G16" s="11" t="str">
         <x:v>2026-09-16 08-11</x:v>
@@ -4102,7 +4286,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>14.9</x:v>
+        <x:v>14.4</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
         <x:v>4</x:v>
@@ -4111,7 +4295,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="G17" s="11" t="str">
-        <x:v>2026-09-16 08-11</x:v>
+        <x:v>2026-09-16 09-11</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -4142,22 +4326,22 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>一墙之隔，皆是人心</x:v>
+        <x:v>破库房的秘密</x:v>
       </x:c>
       <x:c r="C19" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>13.1</x:v>
+        <x:v>15.8</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G19" s="11" t="str">
-        <x:v>2026-09-15 20-11</x:v>
+        <x:v>2026-09-16 02-11</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -4165,22 +4349,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>破库房的秘密</x:v>
+        <x:v>一墙之隔，皆是人心</x:v>
       </x:c>
       <x:c r="C20" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>15.8</x:v>
+        <x:v>13.3</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G20" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-15 20-11</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -4188,22 +4372,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>因为大黄遇见你</x:v>
+        <x:v>穿越60我有空间不愁吃喝</x:v>
       </x:c>
       <x:c r="C21" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>14.7</x:v>
+        <x:v>17.1</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G21" s="11" t="str">
-        <x:v>2026-09-16 06-44</x:v>
+        <x:v>2026-09-16 09-11</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -4211,22 +4395,22 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>穿越60我有空间不愁吃喝</x:v>
+        <x:v>因为大黄遇见你</x:v>
       </x:c>
       <x:c r="C22" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>16.8</x:v>
+        <x:v>14.7</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G22" s="11" t="str">
-        <x:v>2026-09-16 08-11</x:v>
+        <x:v>2026-09-16 06-44</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -4237,10 +4421,10 @@
         <x:v>三分钱的取舍</x:v>
       </x:c>
       <x:c r="C23" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>16.6</x:v>
+        <x:v>16.2</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
         <x:v>13</x:v>
@@ -4257,22 +4441,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>离家十年，回来女儿被换了</x:v>
+        <x:v>一针绣出自己的路</x:v>
       </x:c>
       <x:c r="C24" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>14.9</x:v>
+        <x:v>16.9</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G24" s="11" t="str">
-        <x:v>2026-09-15 22-11</x:v>
+        <x:v>2026-09-16 08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -4280,22 +4464,22 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>一针绣出自己的路</x:v>
+        <x:v>被诬陷诊出喜脉，重活一世我逆转前尘</x:v>
       </x:c>
       <x:c r="C25" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>16.9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G25" s="11" t="str">
-        <x:v>2026-09-16 08-11</x:v>
+        <x:v>2026-09-16 09-11</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -4303,22 +4487,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
+        <x:v>离家十年，回来女儿被换了</x:v>
       </x:c>
       <x:c r="C26" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>16.1</x:v>
+        <x:v>15.3</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G26" s="11" t="str">
-        <x:v>2026-09-16 06-44</x:v>
+        <x:v>2026-09-15 22-11</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -4326,22 +4510,22 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>我在工地卖盒饭带火一座城</x:v>
+        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
       </x:c>
       <x:c r="C27" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>12.9</x:v>
+        <x:v>16.1</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str">
-        <x:v>2026-09-15 21-11</x:v>
+        <x:v>2026-09-16 06-44</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -4349,13 +4533,13 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>不靠谱爸妈很靠谱</x:v>
+        <x:v>我在工地卖盒饭带火一座城</x:v>
       </x:c>
       <x:c r="C28" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>12.9</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
         <x:v>11</x:v>
@@ -4364,7 +4548,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="G28" s="11" t="str">
-        <x:v>2026-09-15 11-11</x:v>
+        <x:v>2026-09-15 21-11</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -4372,22 +4556,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>四个崽崽瞒不住了</x:v>
+        <x:v>一盒印泥引发的全局封锁</x:v>
       </x:c>
       <x:c r="C29" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>16.1</x:v>
+        <x:v>16.4</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str">
-        <x:v>2026-09-15 10-11</x:v>
+        <x:v>2026-09-15 21-11</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -4395,22 +4579,22 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>泰城错嫁</x:v>
+        <x:v>不靠谱爸妈很靠谱</x:v>
       </x:c>
       <x:c r="C30" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>15.6</x:v>
+        <x:v>14.2</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G30" s="11" t="str">
-        <x:v>2026-09-16 04-21</x:v>
+        <x:v>2026-09-15 11-11</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -4418,22 +4602,22 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>一盒印泥引发的全局封锁</x:v>
+        <x:v>四个崽崽瞒不住了</x:v>
       </x:c>
       <x:c r="C31" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
-        <x:v>16.4</x:v>
+        <x:v>16.5</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G31" s="11" t="str">
-        <x:v>2026-09-15 21-11</x:v>
+        <x:v>2026-09-15 10-11</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -4441,22 +4625,22 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="10" t="str">
-        <x:v>被诬陷诊出喜脉，重活一世我逆转前尘</x:v>
+        <x:v>泰城错嫁</x:v>
       </x:c>
       <x:c r="C32" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D32" s="11" t="n">
-        <x:v>4.7</x:v>
+        <x:v>15.3</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G32" s="11" t="str">
-        <x:v>2026-09-16 08-11</x:v>
+        <x:v>2026-09-16 04-21</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -4487,22 +4671,22 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="10" t="str">
-        <x:v>惊絮无声：傻女的绝杀</x:v>
+        <x:v>我都元婴期了，你跟我说开学</x:v>
       </x:c>
       <x:c r="C34" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D34" s="11" t="n">
-        <x:v>14.2</x:v>
+        <x:v>12.8</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F34" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G34" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-16 09-11</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -4533,22 +4717,22 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="10" t="str">
-        <x:v>我都元婴期了，你跟我说开学</x:v>
+        <x:v>惊絮无声：傻女的绝杀</x:v>
       </x:c>
       <x:c r="C36" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
-        <x:v>12.8</x:v>
+        <x:v>13.2</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G36" s="11" t="str">
-        <x:v>2026-09-16 08-11</x:v>
+        <x:v>2026-09-16 02-11</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -4556,22 +4740,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="10" t="str">
-        <x:v>辣媳进门，我给公婆撑腰</x:v>
+        <x:v>我的游戏好友现实里全是大佬</x:v>
       </x:c>
       <x:c r="C37" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D37" s="11" t="n">
+        <x:v>4.7</x:v>
+      </x:c>
+      <x:c r="E37" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F37" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E37" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F37" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="G37" s="11" t="str">
-        <x:v>2026-09-15 06-08</x:v>
+        <x:v>2026-09-16 02-11</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -4579,22 +4763,22 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="10" t="str">
-        <x:v>我的游戏好友现实里全是大佬</x:v>
+        <x:v>攻略失败后我不装了</x:v>
       </x:c>
       <x:c r="C38" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D38" s="11" t="n">
-        <x:v>4.7</x:v>
+        <x:v>9.3</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F38" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G38" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-16 01-11</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -4602,22 +4786,22 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="10" t="str">
-        <x:v>攻略失败后我不装了</x:v>
+        <x:v>傅少你夫人又在扮猪吃虎了</x:v>
       </x:c>
       <x:c r="C39" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D39" s="11" t="n">
-        <x:v>9.3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G39" s="11" t="str">
-        <x:v>2026-09-16 01-11</x:v>
+        <x:v>2026-09-16 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -4625,22 +4809,22 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="10" t="str">
-        <x:v>傅少你夫人又在扮猪吃虎了</x:v>
+        <x:v>红烛错缘，另寻良人</x:v>
       </x:c>
       <x:c r="C40" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D40" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>10.7</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="G40" s="11" t="str">
-        <x:v>2026-09-16 03-11</x:v>
+        <x:v>2026-09-16 02-11</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -4648,22 +4832,22 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="10" t="str">
-        <x:v>红烛错缘，另寻良人</x:v>
+        <x:v>抢个新娘来当后娘第一季</x:v>
       </x:c>
       <x:c r="C41" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D41" s="11" t="n">
-        <x:v>10.7</x:v>
+        <x:v>18.7</x:v>
       </x:c>
       <x:c r="E41" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F41" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G41" s="11" t="str">
-        <x:v>2026-09-16 02-11</x:v>
+        <x:v>2026-09-16 08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -4671,22 +4855,22 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B42" s="10" t="str">
-        <x:v>抢个新娘来当后娘第一季</x:v>
+        <x:v>辣媳进门，我给公婆撑腰</x:v>
       </x:c>
       <x:c r="C42" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D42" s="11" t="n">
-        <x:v>18.7</x:v>
+        <x:v>9.5</x:v>
       </x:c>
       <x:c r="E42" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F42" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G42" s="11" t="str">
-        <x:v>2026-09-16 08-11</x:v>
+        <x:v>2026-09-15 06-08</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -30930,7 +31114,7 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>990</x:v>
+        <x:v>993</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
         <x:v>54.2%</x:v>
@@ -30944,7 +31128,7 @@
         <x:v>482</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>26.4%</x:v>
+        <x:v>26.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -30955,7 +31139,7 @@
         <x:v>356</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>19.5%</x:v>
+        <x:v>19.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
@@ -30990,7 +31174,7 @@
         <x:v>50-79集</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>715</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
         <x:v>42.8%</x:v>
@@ -31004,7 +31188,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>12.6%</x:v>
+        <x:v>12.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -31012,7 +31196,7 @@
         <x:v>100集以上</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>556</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
         <x:v>33.3%</x:v>
@@ -31042,7 +31226,7 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>44.4%</x:v>
+        <x:v>44.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -31050,7 +31234,7 @@
         <x:v>婚姻/情感</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>324</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
         <x:v>17.7%</x:v>
@@ -31058,7 +31242,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>年代怀旧/种田囤货</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
         <x:v>161</x:v>
@@ -31069,10 +31253,10 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="10" t="str">
-        <x:v>年代怀旧/种田囤货</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
         <x:v>8.8%</x:v>
@@ -31094,10 +31278,10 @@
         <x:v>战神/异能/爽文</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>8.3%</x:v>
+        <x:v>8.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -31127,10 +31311,10 @@
         <x:v>逆袭/打脸</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>4.7%</x:v>
+        <x:v>4.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -31407,10 +31591,10 @@
         <x:v>上榜6次</x:v>
       </x:c>
       <x:c r="B51" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C51" s="11" t="str">
-        <x:v>3.4%</x:v>
+        <x:v>3.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -31440,10 +31624,10 @@
         <x:v>上榜3次</x:v>
       </x:c>
       <x:c r="B54" s="11" t="n">
-        <x:v>199</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C54" s="11" t="str">
-        <x:v>10.9%</x:v>
+        <x:v>10.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -31451,7 +31635,7 @@
         <x:v>上榜2次</x:v>
       </x:c>
       <x:c r="B55" s="11" t="n">
-        <x:v>340</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="C55" s="11" t="str">
         <x:v>18.6%</x:v>
@@ -31462,7 +31646,7 @@
         <x:v>上榜1次</x:v>
       </x:c>
       <x:c r="B56" s="11" t="n">
-        <x:v>809</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="C56" s="11" t="str">
         <x:v>44.3%</x:v>
@@ -31492,7 +31676,7 @@
         <x:v>1170</x:v>
       </x:c>
       <x:c r="C60" s="11" t="str">
-        <x:v>64.0%</x:v>
+        <x:v>63.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -31500,10 +31684,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B61" s="11" t="n">
-        <x:v>645</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="C61" s="11" t="str">
-        <x:v>35.3%</x:v>
+        <x:v>35.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="62">

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R565f4f8b1e424b4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="R1b50337e3e65456d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="R3553388d84884d4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="R8e85e24173b743fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP20剧重点跟踪" sheetId="5" r:id="R64f796d66e1441f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="6" r:id="R0bf7efb4e1314a27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="选剧规则说明" sheetId="7" r:id="Rd424ba1d02434f6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重型)" sheetId="8" r:id="Rbb30bdbc96b84215"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径C(账号层级优先)" sheetId="9" r:id="R6fecdcd73a35418c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="10" r:id="R3daa474987fc4f38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="Rf4ef05d0295c42c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="R3c116118284349bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="R1602c83d4c4a44d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="Rbb0a926ad26d4483"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP20剧重点跟踪" sheetId="5" r:id="Rc3670fea583d404e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="6" r:id="R77f294dec0664883"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="选剧规则说明" sheetId="7" r:id="R697dd976820143df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重型)" sheetId="8" r:id="R35399f54581a4d55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径C(账号层级优先)" sheetId="9" r:id="R834d1790cd7f45c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="10" r:id="R1d25ff51a6c64dc2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1131,7 +1131,7 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>1038</x:v>
+        <x:v>1042</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
         <x:v>55.0%</x:v>
@@ -1145,7 +1145,7 @@
         <x:v>487</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>25.8%</x:v>
+        <x:v>25.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1153,7 +1153,7 @@
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>363</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
         <x:v>19.2%</x:v>
@@ -1180,7 +1180,7 @@
         <x:v>30-49集</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
         <x:v>11.1%</x:v>
@@ -1191,7 +1191,7 @@
         <x:v>50-79集</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>740</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
         <x:v>42.9%</x:v>
@@ -1202,10 +1202,10 @@
         <x:v>80-99集</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>216</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>12.5%</x:v>
+        <x:v>12.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1213,10 +1213,10 @@
         <x:v>100集以上</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>575</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>33.4%</x:v>
+        <x:v>33.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
@@ -1240,10 +1240,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>835</x:v>
+        <x:v>838</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>44.2%</x:v>
+        <x:v>44.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1251,7 +1251,7 @@
         <x:v>婚姻/情感</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>341</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
         <x:v>18.1%</x:v>
@@ -1262,7 +1262,7 @@
         <x:v>年代怀旧/种田囤货</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
         <x:v>8.9%</x:v>
@@ -1317,10 +1317,10 @@
         <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>5.6%</x:v>
+        <x:v>5.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1575,10 +1575,10 @@
         <x:v>上榜10次</x:v>
       </x:c>
       <x:c r="B48" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C48" s="11" t="str">
-        <x:v>1.2%</x:v>
+        <x:v>1.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -1586,10 +1586,10 @@
         <x:v>上榜9次</x:v>
       </x:c>
       <x:c r="B49" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C49" s="11" t="str">
-        <x:v>1.7%</x:v>
+        <x:v>1.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -1608,7 +1608,7 @@
         <x:v>上榜7次</x:v>
       </x:c>
       <x:c r="B51" s="11" t="n">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C51" s="11" t="str">
         <x:v>2.0%</x:v>
@@ -1630,10 +1630,10 @@
         <x:v>上榜5次</x:v>
       </x:c>
       <x:c r="B53" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C53" s="11" t="str">
-        <x:v>4.2%</x:v>
+        <x:v>4.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -1641,7 +1641,7 @@
         <x:v>上榜4次</x:v>
       </x:c>
       <x:c r="B54" s="11" t="n">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C54" s="11" t="str">
         <x:v>5.7%</x:v>
@@ -1652,10 +1652,10 @@
         <x:v>上榜3次</x:v>
       </x:c>
       <x:c r="B55" s="11" t="n">
-        <x:v>211</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C55" s="11" t="str">
-        <x:v>11.2%</x:v>
+        <x:v>11.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -1674,10 +1674,10 @@
         <x:v>上榜1次</x:v>
       </x:c>
       <x:c r="B57" s="11" t="n">
-        <x:v>827</x:v>
+        <x:v>832</x:v>
       </x:c>
       <x:c r="C57" s="11" t="str">
-        <x:v>43.8%</x:v>
+        <x:v>44.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="22" customHeight="1">
@@ -1701,10 +1701,10 @@
         <x:v>CP自营</x:v>
       </x:c>
       <x:c r="B61" s="11" t="n">
-        <x:v>1185</x:v>
+        <x:v>1186</x:v>
       </x:c>
       <x:c r="C61" s="11" t="str">
-        <x:v>62.8%</x:v>
+        <x:v>62.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -1712,10 +1712,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B62" s="11" t="n">
-        <x:v>690</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="C62" s="11" t="str">
-        <x:v>36.5%</x:v>
+        <x:v>36.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -2286,7 +2286,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B2" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
         <x:v>被诬陷诊出喜脉，重活一世我逆转前尘</x:v>
@@ -2323,7 +2323,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
         <x:v>糯糯下山，师兄们都慌了第三季</x:v>
@@ -2360,13 +2360,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
-        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
+        <x:v>敢泼我馄饨，整条街都别要了</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>09-15 08:30</x:v>
+        <x:v>09-16 10:00</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str"/>
       <x:c r="F4" s="11" t="str"/>
@@ -2377,19 +2377,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I4" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J4" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K4" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L4" s="11" t="str">
-        <x:v>琥珀漫剧</x:v>
+        <x:v>治愈 AI 恋</x:v>
       </x:c>
       <x:c r="M4" s="10" t="str">
-        <x:v>海鲜市场老手陈放，因一个两块钱的冰袋被十二年合伙人当众算旧账，心寒清账，净身出户。他没有抱怨，也没有以牙还牙，而是加入冷清档口“梅姐水产”，从零开始。他坚持明码标价、沥水称重、死活分卖、批次可查，宁可少接单，也不混货、不凑数、不赚亏心钱。面对低价抢客、恶意破坏、临时缺货等风波，他与叶梅靠诚信、规矩和彼此信任，一步步赢得客户与连锁企业的认可。</x:v>
+        <x:v>南桥旧街投资人许总多年悉心扶持一众商户，给予租金减免与基建投入，可赵川等人却贪念作祟，撕毁协议，还刻意编造谎言煽动网络暴力。面对恩将仇报的局面，许总没有冲动行事，而是恪守契约精神，凭借完备证据通过合法途径理性维权。随着真相公之于众，造谣闹事者自食恶果，承担起违约带来的相应代价。旧街完成焕新升级，充分彰显出法律与规则守护公平正义的强大力量。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2397,13 +2397,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
-        <x:v>敢泼我馄饨，整条街都别要了</x:v>
+        <x:v>霁月安遥之以余生为诺护你岁岁无忧第一季</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>09-16 10:00</x:v>
+        <x:v>09-16 06:06</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str"/>
       <x:c r="F5" s="11" t="str"/>
@@ -2414,7 +2414,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I5" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="J5" s="10" t="str">
         <x:v>其他</x:v>
@@ -2423,10 +2423,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L5" s="11" t="str">
-        <x:v>治愈 AI 恋</x:v>
+        <x:v>花花说漫</x:v>
       </x:c>
       <x:c r="M5" s="10" t="str">
-        <x:v>南桥旧街投资人许总多年悉心扶持一众商户，给予租金减免与基建投入，可赵川等人却贪念作祟，撕毁协议，还刻意编造谎言煽动网络暴力。面对恩将仇报的局面，许总没有冲动行事，而是恪守契约精神，凭借完备证据通过合法途径理性维权。随着真相公之于众，造谣闹事者自食恶果，承担起违约带来的相应代价。旧街完成焕新升级，充分彰显出法律与规则守护公平正义的强大力量。</x:v>
+        <x:v>22岁的医大学生辛知遥意外与大学教授周霁结缘，步入婚姻。初时二人的结合源于一场意外，彼此尚有距离。婚后辛知遥一边完成繁重的学业，一边适应全新的家庭生活。她挣脱原生家庭带来的压抑与束缚，学着正视内心、勇敢表达自我。周霁沉稳体贴，给予她尊重、陪伴与满满的安全感。二人在朝夕相处中慢慢卸下防备，从责任走向真心，携手面对生活里的重重风波，互相扶持，奔赴温暖安稳的幸福生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2434,13 +2434,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>霁月安遥之以余生为诺护你岁岁无忧第一季</x:v>
+        <x:v>老板砍薪，我买下酒楼</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>09-16 06:06</x:v>
+        <x:v>09-15 18:11</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str"/>
       <x:c r="F6" s="11" t="str"/>
@@ -2451,19 +2451,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I6" s="11" t="n">
-        <x:v>144</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="J6" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K6" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="L6" s="11" t="str">
-        <x:v>花花说漫</x:v>
+        <x:v>逸漫</x:v>
       </x:c>
       <x:c r="M6" s="10" t="str">
-        <x:v>22岁的医大学生辛知遥意外与大学教授周霁结缘，步入婚姻。初时二人的结合源于一场意外，彼此尚有距离。婚后辛知遥一边完成繁重的学业，一边适应全新的家庭生活。她挣脱原生家庭带来的压抑与束缚，学着正视内心、勇敢表达自我。周霁沉稳体贴，给予她尊重、陪伴与满满的安全感。二人在朝夕相处中慢慢卸下防备，从责任走向真心，携手面对生活里的重重风波，互相扶持，奔赴温暖安稳的幸福生活。</x:v>
+        <x:v>在美娟大酒楼掌勺十五年的林桂芬，因待遇调整选择离开。面对场地偏远和客户观望，她从老粮库重新起步，凭过硬手艺与真诚待客赢回乡亲认可。从十二桌寿宴到四十桌婚宴，生意越做越红火。后来，她再次走进昔日酒楼，这一次，不是回来打工，而是带着自己的招牌开启新生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2471,13 +2471,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
-        <x:v>老板砍薪，我买下酒楼</x:v>
+        <x:v>重回雪崩泥石流，我不再犹豫</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>09-15 18:11</x:v>
+        <x:v>09-16 01:02</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str"/>
       <x:c r="F7" s="11" t="str"/>
@@ -2488,19 +2488,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I7" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J7" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K7" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="L7" s="11" t="str">
-        <x:v>逸漫</x:v>
+        <x:v>姜缘</x:v>
       </x:c>
       <x:c r="M7" s="10" t="str">
-        <x:v>在美娟大酒楼掌勺十五年的林桂芬，因待遇调整选择离开。面对场地偏远和客户观望，她从老粮库重新起步，凭过硬手艺与真诚待客赢回乡亲认可。从十二桌寿宴到四十桌婚宴，生意越做越红火。后来，她再次走进昔日酒楼，这一次，不是回来打工，而是带着自己的招牌开启新生活。</x:v>
+        <x:v>前世，周清雨因犹豫错失逃生时机，眼睁睁看着全家被雪崩泥石流吞没。重生回灾难前三天，她当机立断卖掉五十头牦牛，囤积物资，带家人撤往高处。面对全村嘲讽和阻拦，她不再苦劝。直到雪山崩塌、洪流封村，昔日笑她疯癫的人纷纷求上门。这一次，她只救值得救的人！</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2545,13 +2545,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
-        <x:v>有米偏要讨三场雨</x:v>
+        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>09-16 08:18</x:v>
+        <x:v>09-15 08:30</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str"/>
       <x:c r="F9" s="11" t="str"/>
@@ -2562,19 +2562,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I9" s="11" t="n">
-        <x:v>98</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J9" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K9" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L9" s="11" t="str">
-        <x:v>剧有米</x:v>
+        <x:v>琥珀漫剧</x:v>
       </x:c>
       <x:c r="M9" s="10" t="str">
-        <x:v>青石村大旱三月，全村跪求龙王赐雨，四岁的有米却爬上供桌，张口就说龙王敖澜欠她三场雨。为了讨债，她扣雨牌、锁水门、放掉偷接的水、挖通公沟，还把只认天规的敖澜一次次拖进人间麻烦。暴风、山火和争水接连袭来，有米也在一次次选择中让周守财和全村学会先顾人、再顾利。三场雨终于还清，青石村重新秋种，山外却传来石狮异响，新的怪事又找上了她。</x:v>
+        <x:v>海鲜市场老手陈放，因一个两块钱的冰袋被十二年合伙人当众算旧账，心寒清账，净身出户。他没有抱怨，也没有以牙还牙，而是加入冷清档口“梅姐水产”，从零开始。他坚持明码标价、沥水称重、死活分卖、批次可查，宁可少接单，也不混货、不凑数、不赚亏心钱。面对低价抢客、恶意破坏、临时缺货等风波，他与叶梅靠诚信、规矩和彼此信任，一步步赢得客户与连锁企业的认可。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -2582,13 +2582,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
-        <x:v>一墙隔冷暖，五年借暖终归零</x:v>
+        <x:v>情深错付</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>09-15 15:27</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str"/>
       <x:c r="F10" s="11" t="str"/>
@@ -2598,28 +2598,34 @@
       <x:c r="H10" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I10" s="11" t="str"/>
+      <x:c r="I10" s="11" t="n">
+        <x:v>79</x:v>
+      </x:c>
       <x:c r="J10" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K10" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L10" s="11" t="str"/>
-      <x:c r="M10" s="10" t="str"/>
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="L10" s="11" t="str">
+        <x:v>沐光剧场</x:v>
+      </x:c>
+      <x:c r="M10" s="10" t="str">
+        <x:v>苏橙橙倒追陆深两年，却始终没等来一句承认。一次争执后，她被当众羞辱，车祸重伤时更亲眼看见陆深先救走白月光李芸。彻底清醒后，她拉黑、离职、离城，重新开始。等陆深终于看清真心、拼命追回时，她早已放下。三年后重逢，他以为她已结婚生子，最终带着遗憾彻底错过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C11" s="10" t="str">
-        <x:v>说好九十天就回来，我不等了</x:v>
+        <x:v>我都元婴期了，你跟我说开学</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>09-16 06:00</x:v>
+        <x:v>09-16 00:10</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str"/>
       <x:c r="F11" s="11" t="str"/>
@@ -2630,7 +2636,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I11" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="J11" s="10" t="str">
         <x:v>其他</x:v>
@@ -2639,10 +2645,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L11" s="11" t="str">
-        <x:v>小宁漫漫</x:v>
+        <x:v>梦启剧场</x:v>
       </x:c>
       <x:c r="M11" s="10" t="str">
-        <x:v>周衡挣脱错位的旧感情，坚守原则，专注医疗事业，打磨救死扶伤的星桥心泵。他与叶宁彼此尊重，感情建立在坦诚与边界之上，不盲目牺牲自我，平等相伴走向未来。林夏历经挫折后幡然醒悟，承担自己犯下的过错，放下执念踏实努力，靠双手重新经营人生。故事告诉人不必困在原地等候错的人，真心不该沦为候补，每个人都可以告别过往，奔赴属于自己的前路</x:v>
+        <x:v>修士宁尘遭遇偷袭，身负重伤从修真界回到现代。时间只流逝一个暑假，他被迫入读青州大学，借居在乔姨家中，与傲娇少女许舒颜同住。一边伪装普通学生，一边寻找修复元神伤势的资源，接连化解校园、市井与古武圈子的各类风波，开启充满反差的现代生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -2650,13 +2656,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
-        <x:v>我都元婴期了，你跟我说开学</x:v>
+        <x:v>瘦身归来，前男友悔不当初</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>09-16 00:10</x:v>
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str"/>
       <x:c r="F12" s="11" t="str"/>
@@ -2666,34 +2672,28 @@
       <x:c r="H12" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I12" s="11" t="n">
-        <x:v>475</x:v>
-      </x:c>
+      <x:c r="I12" s="11" t="str"/>
       <x:c r="J12" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K12" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L12" s="11" t="str">
-        <x:v>梦启剧场</x:v>
-      </x:c>
-      <x:c r="M12" s="10" t="str">
-        <x:v>修士宁尘遭遇偷袭，身负重伤从修真界回到现代。时间只流逝一个暑假，他被迫入读青州大学，借居在乔姨家中，与傲娇少女许舒颜同住。一边伪装普通学生，一边寻找修复元神伤势的资源，接连化解校园、市井与古武圈子的各类风波，开启充满反差的现代生活。</x:v>
-      </x:c>
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="L12" s="11" t="str"/>
+      <x:c r="M12" s="10" t="str"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B13" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
-        <x:v>情深错付</x:v>
+        <x:v>一墙隔冷暖，五年借暖终归零</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
-        <x:v>09-15 15:27</x:v>
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str"/>
       <x:c r="F13" s="11" t="str"/>
@@ -2703,21 +2703,15 @@
       <x:c r="H13" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I13" s="11" t="n">
-        <x:v>79</x:v>
-      </x:c>
+      <x:c r="I13" s="11" t="str"/>
       <x:c r="J13" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K13" s="10" t="str">
-        <x:v>婚姻情感</x:v>
-      </x:c>
-      <x:c r="L13" s="11" t="str">
-        <x:v>沐光剧场</x:v>
-      </x:c>
-      <x:c r="M13" s="10" t="str">
-        <x:v>苏橙橙倒追陆深两年，却始终没等来一句承认。一次争执后，她被当众羞辱，车祸重伤时更亲眼看见陆深先救走白月光李芸。彻底清醒后，她拉黑、离职、离城，重新开始。等陆深终于看清真心、拼命追回时，她早已放下。三年后重逢，他以为她已结婚生子，最终带着遗憾彻底错过。</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L13" s="11" t="str"/>
+      <x:c r="M13" s="10" t="str"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="str">
@@ -2727,10 +2721,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
-        <x:v>瘦身归来，前男友悔不当初</x:v>
+        <x:v>我把真心留给真心的人</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>09-16 11:20</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str"/>
       <x:c r="F14" s="11" t="str"/>
@@ -2740,28 +2734,34 @@
       <x:c r="H14" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I14" s="11" t="str"/>
+      <x:c r="I14" s="11" t="n">
+        <x:v>72</x:v>
+      </x:c>
       <x:c r="J14" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K14" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
-      </x:c>
-      <x:c r="L14" s="11" t="str"/>
-      <x:c r="M14" s="10" t="str"/>
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="L14" s="11" t="str">
+        <x:v>逆命漫剧场</x:v>
+      </x:c>
+      <x:c r="M14" s="10" t="str">
+        <x:v>失散二十年的方小树意外归家，却被大哥二姐当成乞丐嫌弃，唯有三姐方秀兰护着他。一次受伤让他恢复记忆，为看清人心，他选择继续装傻。面对亲人的贪婪算计、骗钱逼婚与恶意陷害，小树一次次反击，也因救命之恩得到顾家、沈家相助，并与沈清月渐生真情。最终，他揭开被拐真相，惩治恶人，守住亲情与爱情，迎来人生逆袭。</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B15" s="11" t="n">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
-        <x:v>重回雪崩泥石流，我不再犹豫</x:v>
+        <x:v>萌娃兽语满级，动物园天天爆红</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
-        <x:v>09-16 01:02</x:v>
+        <x:v>09-16 10:00</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str"/>
       <x:c r="F15" s="11" t="str"/>
@@ -2772,19 +2772,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I15" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="J15" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K15" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>萌宝治愈 / 战神异能</x:v>
       </x:c>
       <x:c r="L15" s="11" t="str">
-        <x:v>姜缘</x:v>
+        <x:v>一口漫剧</x:v>
       </x:c>
       <x:c r="M15" s="10" t="str">
-        <x:v>前世，周清雨因犹豫错失逃生时机，眼睁睁看着全家被雪崩泥石流吞没。重生回灾难前三天，她当机立断卖掉五十头牦牛，囤积物资，带家人撤往高处。面对全村嘲讽和阻拦，她不再苦劝。直到雪山崩塌、洪流封村，昔日笑她疯癫的人纷纷求上门。这一次，她只救值得救的人！</x:v>
+        <x:v>八岁女孩汤圆拥有听懂动物语言的特殊能力，助力濒临倒闭的自家动物园破局重生。她读懂动物的内心诉求，化解人与动物之间的认知误解，坚守科学救助理念，拒绝猎奇表演。动物园成为科普教育阵地，传递尊重生命、人与自然和谐共生的理念，以孩童的善意守护生灵，诠释新时代少年的社会担当。</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2792,13 +2792,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C16" s="10" t="str">
-        <x:v>我把真心留给真心的人</x:v>
+        <x:v>有米偏要讨三场雨</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
-        <x:v>09-16 11:20</x:v>
+        <x:v>09-16 08:18</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str"/>
       <x:c r="F16" s="11" t="str"/>
@@ -2809,19 +2809,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I16" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="J16" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K16" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L16" s="11" t="str">
-        <x:v>逆命漫剧场</x:v>
+        <x:v>剧有米</x:v>
       </x:c>
       <x:c r="M16" s="10" t="str">
-        <x:v>失散二十年的方小树意外归家，却被大哥二姐当成乞丐嫌弃，唯有三姐方秀兰护着他。一次受伤让他恢复记忆，为看清人心，他选择继续装傻。面对亲人的贪婪算计、骗钱逼婚与恶意陷害，小树一次次反击，也因救命之恩得到顾家、沈家相助，并与沈清月渐生真情。最终，他揭开被拐真相，惩治恶人，守住亲情与爱情，迎来人生逆袭。</x:v>
+        <x:v>青石村大旱三月，全村跪求龙王赐雨，四岁的有米却爬上供桌，张口就说龙王敖澜欠她三场雨。为了讨债，她扣雨牌、锁水门、放掉偷接的水、挖通公沟，还把只认天规的敖澜一次次拖进人间麻烦。暴风、山火和争水接连袭来，有米也在一次次选择中让周守财和全村学会先顾人、再顾利。三场雨终于还清，青石村重新秋种，山外却传来石狮异响，新的怪事又找上了她。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -2829,13 +2829,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C17" s="10" t="str">
-        <x:v>八媳妇只想买包，一不小心拯救了全家</x:v>
+        <x:v>七零：穿成锦鲤文里的炮灰女配</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
-        <x:v>09-16 10:00</x:v>
+        <x:v>09-16 17:00</x:v>
       </x:c>
       <x:c r="E17" s="11" t="str"/>
       <x:c r="F17" s="11" t="str"/>
@@ -2846,19 +2846,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I17" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="J17" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K17" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧 / 战神异能</x:v>
       </x:c>
       <x:c r="L17" s="11" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>小树动漫剧场</x:v>
       </x:c>
       <x:c r="M17" s="10" t="str">
-        <x:v>顾家八位儿媳皆各有所长。大嫂秦蕴章深耕华尔街并购领域，二嫂林疏桐是风投行业的杰出从业者。晏姝岚平日生活低调随性，外界便对她产生片面认知，认为她只注重物质消费。实际上，晏姝岚来自底蕴更为深厚的大家族。当顾氏集团遭遇多家境外企业联合围堵，经营陷入巨大危机。顾家公公心力交瘁，能力出众的嫂嫂们多方调动资源，依旧难以摸清对手的真实布局。在对手步步施压的危急时刻，晏姝岚挺身而出，守护顾家渡过这场商业危机。</x:v>
+        <x:v>现代女孩温梨穿越到七十年代小说，成为结局悲惨的炮灰女配，她抢先激活沉香木牌中的灵泉空间，凭借敏锐察觉化解列车上的重大隐患，得到官方表彰，为下乡做好铺垫；来到红星公社后，温梨依靠灵泉水强化体质，不再被白眼狼郭彩霞道德绑架，还截胡了本该属于女主姜月儿的机缘，她一边下地挣工分，一边利用空间物资在黑市与顾淮合作，面对姜月儿、江辰等人的屡次算计构陷，温梨从容反击，结识神秘知青陆泽川，改写自己注定悲剧的命运。</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -2866,10 +2866,10 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C18" s="10" t="str">
-        <x:v>萌娃兽语满级，动物园天天爆红</x:v>
+        <x:v>八媳妇只想买包，一不小心拯救了全家</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
         <x:v>09-16 10:00</x:v>
@@ -2883,19 +2883,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I18" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J18" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K18" s="10" t="str">
-        <x:v>萌宝治愈 / 战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L18" s="11" t="str">
-        <x:v>一口漫剧</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="M18" s="10" t="str">
-        <x:v>八岁女孩汤圆拥有听懂动物语言的特殊能力，助力濒临倒闭的自家动物园破局重生。她读懂动物的内心诉求，化解人与动物之间的认知误解，坚守科学救助理念，拒绝猎奇表演。动物园成为科普教育阵地，传递尊重生命、人与自然和谐共生的理念，以孩童的善意守护生灵，诠释新时代少年的社会担当。</x:v>
+        <x:v>顾家八位儿媳皆各有所长。大嫂秦蕴章深耕华尔街并购领域，二嫂林疏桐是风投行业的杰出从业者。晏姝岚平日生活低调随性，外界便对她产生片面认知，认为她只注重物质消费。实际上，晏姝岚来自底蕴更为深厚的大家族。当顾氏集团遭遇多家境外企业联合围堵，经营陷入巨大危机。顾家公公心力交瘁，能力出众的嫂嫂们多方调动资源，依旧难以摸清对手的真实布局。在对手步步施压的危急时刻，晏姝岚挺身而出，守护顾家渡过这场商业危机。</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -2903,13 +2903,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>77</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C19" s="10" t="str">
-        <x:v>重生第七节车厢</x:v>
+        <x:v>说好九十天就回来，我不等了</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
-        <x:v>09-16 11:39</x:v>
+        <x:v>09-16 06:00</x:v>
       </x:c>
       <x:c r="E19" s="11" t="str"/>
       <x:c r="F19" s="11" t="str"/>
@@ -2920,7 +2920,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I19" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J19" s="10" t="str">
         <x:v>其他</x:v>
@@ -2929,10 +2929,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L19" s="11" t="str">
-        <x:v>千一剧场</x:v>
+        <x:v>小宁漫漫</x:v>
       </x:c>
       <x:c r="M19" s="10" t="str">
-        <x:v>高铁列车长林铮死过一次。上一世，四名大学生私带危险实验样品登车，一句“毒倒整节车厢”的戏言被他放行，最终隧道内毒气泄漏，全车罹难，他成了千夫所指的责任人。重回发车前最后一分钟，他顶住求情、质疑与全网非议，硬封第七节车厢，叫停整趟列车。层层戳破瞒报的谎言，这一次，他死守安全红线，要让车上一千零八十六人，全都平安抵达终点。</x:v>
+        <x:v>周衡挣脱错位的旧感情，坚守原则，专注医疗事业，打磨救死扶伤的星桥心泵。他与叶宁彼此尊重，感情建立在坦诚与边界之上，不盲目牺牲自我，平等相伴走向未来。林夏历经挫折后幡然醒悟，承担自己犯下的过错，放下执念踏实努力，靠双手重新经营人生。故事告诉人不必困在原地等候错的人，真心不该沦为候补，每个人都可以告别过往，奔赴属于自己的前路</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -2940,13 +2940,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C20" s="10" t="str">
-        <x:v>七零：穿成锦鲤文里的炮灰女配</x:v>
+        <x:v>重生第七节车厢</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>09-16 17:00</x:v>
+        <x:v>09-16 11:39</x:v>
       </x:c>
       <x:c r="E20" s="11" t="str"/>
       <x:c r="F20" s="11" t="str"/>
@@ -2957,19 +2957,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I20" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J20" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K20" s="10" t="str">
-        <x:v>年代怀旧 / 战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L20" s="11" t="str">
-        <x:v>小树动漫剧场</x:v>
+        <x:v>千一剧场</x:v>
       </x:c>
       <x:c r="M20" s="10" t="str">
-        <x:v>现代女孩温梨穿越到七十年代小说，成为结局悲惨的炮灰女配，她抢先激活沉香木牌中的灵泉空间，凭借敏锐察觉化解列车上的重大隐患，得到官方表彰，为下乡做好铺垫；来到红星公社后，温梨依靠灵泉水强化体质，不再被白眼狼郭彩霞道德绑架，还截胡了本该属于女主姜月儿的机缘，她一边下地挣工分，一边利用空间物资在黑市与顾淮合作，面对姜月儿、江辰等人的屡次算计构陷，温梨从容反击，结识神秘知青陆泽川，改写自己注定悲剧的命运。</x:v>
+        <x:v>高铁列车长林铮死过一次。上一世，四名大学生私带危险实验样品登车，一句“毒倒整节车厢”的戏言被他放行，最终隧道内毒气泄漏，全车罹难，他成了千夫所指的责任人。重回发车前最后一分钟，他顶住求情、质疑与全网非议，硬封第七节车厢，叫停整趟列车。层层戳破瞒报的谎言，这一次，他死守安全红线，要让车上一千零八十六人，全都平安抵达终点。</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -2977,10 +2977,10 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C21" s="10" t="str">
-        <x:v>鱼缸之眼</x:v>
+        <x:v>重生归来，只为守护她</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
         <x:v>2026-09-16</x:v>
@@ -2991,14 +2991,14 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H21" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I21" s="11" t="str"/>
       <x:c r="J21" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="K21" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="L21" s="11" t="str"/>
       <x:c r="M21" s="10" t="str"/>
@@ -3008,10 +3008,10 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C22" s="10" t="str">
-        <x:v>重生归来，只为守护她</x:v>
+        <x:v>鱼缸之眼</x:v>
       </x:c>
       <x:c r="D22" s="11" t="str">
         <x:v>2026-09-16</x:v>
@@ -3019,7 +3019,7 @@
       <x:c r="E22" s="11" t="str"/>
       <x:c r="F22" s="11" t="str"/>
       <x:c r="G22" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H22" s="11" t="n">
         <x:v>4</x:v>
@@ -3029,7 +3029,7 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="K22" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L22" s="11" t="str"/>
       <x:c r="M22" s="10" t="str"/>
@@ -3039,13 +3039,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C23" s="10" t="str">
-        <x:v>浮世红痕</x:v>
+        <x:v>养娃记：八零四合院生活日常</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
-        <x:v>09-16 07:58</x:v>
+        <x:v>09-15 01:11</x:v>
       </x:c>
       <x:c r="E23" s="11" t="str"/>
       <x:c r="F23" s="11" t="str"/>
@@ -3053,22 +3053,22 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H23" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I23" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="J23" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K23" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧 / 萌宝治愈</x:v>
       </x:c>
       <x:c r="L23" s="11" t="str">
-        <x:v>久久漫剧</x:v>
+        <x:v>香菜薯片</x:v>
       </x:c>
       <x:c r="M23" s="10" t="str">
-        <x:v>乔舒天生拥有一项特殊能力——能看见连接亲密男女的隐秘红线。她以此选定了看似专一的未婚夫陆宥泽，却在婚礼前夜，赫然发现他与自己闺蜜许澜之间缠上了红线。婚礼现场她当众揭露真相，果断终止婚约。此后她凭借异能开设“红线鉴渣工作室”，帮深陷情感疑云的人勘破真心，而更多意想不到的考验与纠葛也随之而来。</x:v>
+        <x:v>儿女已经成家立业，送走公公婆婆后，正准备全国游的六十多岁老太太赵锦舒重生了。重回到刚进城几个月时，那时什么都不懂，乡下来的年轻小媳妇脸皮薄，抹不开面子，也自卑，哪怕男人能挣钱，面对有权有势的婆家人，也自觉低人一头，更怕出错，给男人丢脸，很长一段时间都不敢多说一句话，明里暗里娘三个受了不少委屈。回到年轻时，赵锦舒老黄瓜刷绿漆，不管外表如何，内里都是老姜疙瘩，装不来腼腆小媳妇。</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -3076,13 +3076,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C24" s="10" t="str">
-        <x:v>高考刚结束父母就不装了</x:v>
+        <x:v>晚来的圆满</x:v>
       </x:c>
       <x:c r="D24" s="11" t="str">
-        <x:v>09-15 07:00</x:v>
+        <x:v>09-15 13:14</x:v>
       </x:c>
       <x:c r="E24" s="11" t="str"/>
       <x:c r="F24" s="11" t="str"/>
@@ -3090,22 +3090,22 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H24" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I24" s="11" t="n">
-        <x:v>173</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="J24" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K24" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L24" s="11" t="str">
-        <x:v>千慕剧场</x:v>
+        <x:v>杭鹿二姐爱看剧</x:v>
       </x:c>
       <x:c r="M24" s="10" t="str">
-        <x:v>高考结束那天，林寻在考场外被亲生父母认回原来十八年的普通生活，是父母为磨砺他而设的一场成长课。重回豪门，他没有迷失，反而在桥上遇见了那个让他心动的姑娘，南大冰山学姐苏清诗。从青涩的初次相遇，到演唱会上的合唱，再到大学校园里的朝夕相处，两个真诚的人慢慢靠近。曾经的求而不得终将释怀，双向奔赴的喜欢才最珍贵。褪去普通学生的身份，林寻只想以真心换真心。十八岁的夏天，最好的相遇，最甜的恋爱，才刚刚开始。</x:v>
+        <x:v>白手起家的女企业家沈玉珍，将独子陆衍视作家族企业的唯一继承人。谁知陆衍结识顾念后性情大变，不仅执意拒绝生育、与母亲渐行渐远，还任由顾念家人插手公司事务。眼看毕生心血面临失控，沈玉珍挺身而出，以沉稳手腕化解层层危机。最终真相水落石出，顾念的图谋落空，陆衍迷途知返担起责任，沈玉珍守护住了家业，也让家庭重归温暖圆满。</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -3113,36 +3113,36 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C25" s="10" t="str">
-        <x:v>晚来的圆满</x:v>
+        <x:v>高考落榜，从听彩票心声开始逆袭</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
-        <x:v>09-15 13:14</x:v>
+        <x:v>09-15 10:00</x:v>
       </x:c>
       <x:c r="E25" s="11" t="str"/>
       <x:c r="F25" s="11" t="str"/>
       <x:c r="G25" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H25" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I25" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J25" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K25" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="L25" s="11" t="str">
-        <x:v>杭鹿二姐爱看剧</x:v>
+        <x:v>糖糖动漫剧场</x:v>
       </x:c>
       <x:c r="M25" s="10" t="str">
-        <x:v>白手起家的女企业家沈玉珍，将独子陆衍视作家族企业的唯一继承人。谁知陆衍结识顾念后性情大变，不仅执意拒绝生育、与母亲渐行渐远，还任由顾念家人插手公司事务。眼看毕生心血面临失控，沈玉珍挺身而出，以沉稳手腕化解层层危机。最终真相水落石出，顾念的图谋落空，陆衍迷途知返担起责任，沈玉珍守护住了家业，也让家庭重归温暖圆满。</x:v>
+        <x:v>高考落榜的陈阳意外觉醒聆听万物心声的特殊能力。面对世俗偏见与亲友的冷眼，他没有沉沦，坚守本心脚踏实地，凭借能力识破骗局、守护家人。抓住机遇创业致富，反哺故土，助力乡村建设，伸张社会正义，用实干证明人生不止高考一条出路，诠释新时代青年的责任与担当。</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -3150,36 +3150,36 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B26" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C26" s="10" t="str">
-        <x:v>养娃记：八零四合院生活日常</x:v>
+        <x:v>浮世红痕</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
-        <x:v>09-15 01:11</x:v>
+        <x:v>09-16 07:58</x:v>
       </x:c>
       <x:c r="E26" s="11" t="str"/>
       <x:c r="F26" s="11" t="str"/>
       <x:c r="G26" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H26" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="I26" s="11" t="n">
-        <x:v>191</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J26" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K26" s="10" t="str">
-        <x:v>年代怀旧 / 萌宝治愈</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L26" s="11" t="str">
-        <x:v>香菜薯片</x:v>
+        <x:v>久久漫剧</x:v>
       </x:c>
       <x:c r="M26" s="10" t="str">
-        <x:v>儿女已经成家立业，送走公公婆婆后，正准备全国游的六十多岁老太太赵锦舒重生了。重回到刚进城几个月时，那时什么都不懂，乡下来的年轻小媳妇脸皮薄，抹不开面子，也自卑，哪怕男人能挣钱，面对有权有势的婆家人，也自觉低人一头，更怕出错，给男人丢脸，很长一段时间都不敢多说一句话，明里暗里娘三个受了不少委屈。回到年轻时，赵锦舒老黄瓜刷绿漆，不管外表如何，内里都是老姜疙瘩，装不来腼腆小媳妇。</x:v>
+        <x:v>乔舒天生拥有一项特殊能力——能看见连接亲密男女的隐秘红线。她以此选定了看似专一的未婚夫陆宥泽，却在婚礼前夜，赫然发现他与自己闺蜜许澜之间缠上了红线。婚礼现场她当众揭露真相，果断终止婚约。此后她凭借异能开设“红线鉴渣工作室”，帮深陷情感疑云的人勘破真心，而更多意想不到的考验与纠葛也随之而来。</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -3187,36 +3187,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B27" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C27" s="10" t="str">
-        <x:v>有米偏要讨三场雨</x:v>
+        <x:v>萌娃兽语满级，动物园天天爆红</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
-        <x:v>09-16 08:18</x:v>
+        <x:v>09-16 10:00</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F27" s="11" t="str">
-        <x:v>↑49位</x:v>
+        <x:v>↑24位</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str"/>
       <x:c r="H27" s="11" t="str"/>
       <x:c r="I27" s="11" t="n">
-        <x:v>98</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="J27" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K27" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>萌宝治愈 / 战神异能</x:v>
       </x:c>
       <x:c r="L27" s="11" t="str">
-        <x:v>剧有米</x:v>
+        <x:v>一口漫剧</x:v>
       </x:c>
       <x:c r="M27" s="10" t="str">
-        <x:v>青石村大旱三月，全村跪求龙王赐雨，四岁的有米却爬上供桌，张口就说龙王敖澜欠她三场雨。为了讨债，她扣雨牌、锁水门、放掉偷接的水、挖通公沟，还把只认天规的敖澜一次次拖进人间麻烦。暴风、山火和争水接连袭来，有米也在一次次选择中让周守财和全村学会先顾人、再顾利。三场雨终于还清，青石村重新秋种，山外却传来石狮异响，新的怪事又找上了她。</x:v>
+        <x:v>八岁女孩汤圆拥有听懂动物语言的特殊能力，助力濒临倒闭的自家动物园破局重生。她读懂动物的内心诉求，化解人与动物之间的认知误解，坚守科学救助理念，拒绝猎奇表演。动物园成为科普教育阵地，传递尊重生命、人与自然和谐共生的理念，以孩童的善意守护生灵，诠释新时代少年的社会担当。</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -3224,36 +3224,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B28" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C28" s="10" t="str">
-        <x:v>浮世红痕</x:v>
+        <x:v>重回雪崩泥石流，我不再犹豫</x:v>
       </x:c>
       <x:c r="D28" s="11" t="str">
-        <x:v>09-16 07:58</x:v>
+        <x:v>09-16 01:02</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F28" s="11" t="str">
-        <x:v>↑45位</x:v>
+        <x:v>↑23位</x:v>
       </x:c>
       <x:c r="G28" s="11" t="str"/>
       <x:c r="H28" s="11" t="str"/>
       <x:c r="I28" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J28" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K28" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="L28" s="11" t="str">
-        <x:v>久久漫剧</x:v>
+        <x:v>姜缘</x:v>
       </x:c>
       <x:c r="M28" s="10" t="str">
-        <x:v>乔舒天生拥有一项特殊能力——能看见连接亲密男女的隐秘红线。她以此选定了看似专一的未婚夫陆宥泽，却在婚礼前夜，赫然发现他与自己闺蜜许澜之间缠上了红线。婚礼现场她当众揭露真相，果断终止婚约。此后她凭借异能开设“红线鉴渣工作室”，帮深陷情感疑云的人勘破真心，而更多意想不到的考验与纠葛也随之而来。</x:v>
+        <x:v>前世，周清雨因犹豫错失逃生时机，眼睁睁看着全家被雪崩泥石流吞没。重生回灾难前三天，她当机立断卖掉五十头牦牛，囤积物资，带家人撤往高处。面对全村嘲讽和阻拦，她不再苦劝。直到雪山崩塌、洪流封村，昔日笑她疯癫的人纷纷求上门。这一次，她只救值得救的人！</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -3261,7 +3261,7 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B29" s="11" t="n">
-        <x:v>46</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C29" s="10" t="str">
         <x:v>剑道：贴地武夫，谁教他练剑起飞的</x:v>
@@ -3270,10 +3270,10 @@
         <x:v>09-16 17:23</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F29" s="11" t="str">
-        <x:v>↑26位</x:v>
+        <x:v>↑21位</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str"/>
       <x:c r="H29" s="11" t="str"/>
@@ -3298,73 +3298,67 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B30" s="11" t="n">
-        <x:v>24</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C30" s="10" t="str">
-        <x:v>重回失事当晚，我扣下整条跑道</x:v>
+        <x:v>重生归来，只为守护她</x:v>
       </x:c>
       <x:c r="D30" s="11" t="str">
-        <x:v>09-17 06:08</x:v>
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>43</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F30" s="11" t="str">
-        <x:v>↑19位</x:v>
+        <x:v>↑20位</x:v>
       </x:c>
       <x:c r="G30" s="11" t="str"/>
       <x:c r="H30" s="11" t="str"/>
-      <x:c r="I30" s="11" t="n">
-        <x:v>61</x:v>
-      </x:c>
+      <x:c r="I30" s="11" t="str"/>
       <x:c r="J30" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K30" s="10" t="str">
-        <x:v>年代怀旧</x:v>
-      </x:c>
-      <x:c r="L30" s="11" t="str">
-        <x:v>星漫剧院</x:v>
-      </x:c>
-      <x:c r="M30" s="10" t="str">
-        <x:v>上一世，一场诡异空难，塔台管制员谢昀含冤惨死。重生回到悲剧前夜，十五架学生无人机尽数落地，领导、师生、全网都逼她签字开放跑道。所有人都认定危险已经解除，可她笃定空域还藏着未知黑影。顶着限时命令与铺天盖地非议死扛复核。那看不见的第十六架，究竟是谁布下的致命陷阱？</x:v>
-      </x:c>
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="L30" s="11" t="str"/>
+      <x:c r="M30" s="10" t="str"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B31" s="11" t="n">
-        <x:v>43</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C31" s="10" t="str">
-        <x:v>重回雪崩泥石流，我不再犹豫</x:v>
+        <x:v>高考刚结束父母就不装了</x:v>
       </x:c>
       <x:c r="D31" s="11" t="str">
-        <x:v>09-16 01:02</x:v>
+        <x:v>09-15 07:00</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F31" s="11" t="str">
-        <x:v>↑17位</x:v>
+        <x:v>↑19位</x:v>
       </x:c>
       <x:c r="G31" s="11" t="str"/>
       <x:c r="H31" s="11" t="str"/>
       <x:c r="I31" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="J31" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K31" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="L31" s="11" t="str">
-        <x:v>姜缘</x:v>
+        <x:v>千慕剧场</x:v>
       </x:c>
       <x:c r="M31" s="10" t="str">
-        <x:v>前世，周清雨因犹豫错失逃生时机，眼睁睁看着全家被雪崩泥石流吞没。重生回灾难前三天，她当机立断卖掉五十头牦牛，囤积物资，带家人撤往高处。面对全村嘲讽和阻拦，她不再苦劝。直到雪山崩塌、洪流封村，昔日笑她疯癫的人纷纷求上门。这一次，她只救值得救的人！</x:v>
+        <x:v>高考结束那天，林寻在考场外被亲生父母认回原来十八年的普通生活，是父母为磨砺他而设的一场成长课。重回豪门，他没有迷失，反而在桥上遇见了那个让他心动的姑娘，南大冰山学姐苏清诗。从青涩的初次相遇，到演唱会上的合唱，再到大学校园里的朝夕相处，两个真诚的人慢慢靠近。曾经的求而不得终将释怀，双向奔赴的喜欢才最珍贵。褪去普通学生的身份，林寻只想以真心换真心。十八岁的夏天，最好的相遇，最甜的恋爱，才刚刚开始。</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -3372,16 +3366,16 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B32" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C32" s="10" t="str">
-        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
+        <x:v>我把真心留给真心的人</x:v>
       </x:c>
       <x:c r="D32" s="11" t="str">
-        <x:v>09-15 08:30</x:v>
+        <x:v>09-16 11:20</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F32" s="11" t="str">
         <x:v>↑12位</x:v>
@@ -3389,7 +3383,7 @@
       <x:c r="G32" s="11" t="str"/>
       <x:c r="H32" s="11" t="str"/>
       <x:c r="I32" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J32" s="10" t="str">
         <x:v>其他</x:v>
@@ -3398,10 +3392,10 @@
         <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L32" s="11" t="str">
-        <x:v>琥珀漫剧</x:v>
+        <x:v>逆命漫剧场</x:v>
       </x:c>
       <x:c r="M32" s="10" t="str">
-        <x:v>海鲜市场老手陈放，因一个两块钱的冰袋被十二年合伙人当众算旧账，心寒清账，净身出户。他没有抱怨，也没有以牙还牙，而是加入冷清档口“梅姐水产”，从零开始。他坚持明码标价、沥水称重、死活分卖、批次可查，宁可少接单，也不混货、不凑数、不赚亏心钱。面对低价抢客、恶意破坏、临时缺货等风波，他与叶梅靠诚信、规矩和彼此信任，一步步赢得客户与连锁企业的认可。</x:v>
+        <x:v>失散二十年的方小树意外归家，却被大哥二姐当成乞丐嫌弃，唯有三姐方秀兰护着他。一次受伤让他恢复记忆，为看清人心，他选择继续装傻。面对亲人的贪婪算计、骗钱逼婚与恶意陷害，小树一次次反击，也因救命之恩得到顾家、沈家相助，并与沈清月渐生真情。最终，他揭开被拐真相，惩治恶人，守住亲情与爱情，迎来人生逆袭。</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -3409,16 +3403,16 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B33" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C33" s="10" t="str">
-        <x:v>我把真心留给真心的人</x:v>
+        <x:v>守成包子铺</x:v>
       </x:c>
       <x:c r="D33" s="11" t="str">
-        <x:v>09-16 11:20</x:v>
+        <x:v>09-15 16:00</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F33" s="11" t="str">
         <x:v>↑11位</x:v>
@@ -3426,19 +3420,19 @@
       <x:c r="G33" s="11" t="str"/>
       <x:c r="H33" s="11" t="str"/>
       <x:c r="I33" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J33" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K33" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="L33" s="11" t="str">
-        <x:v>逆命漫剧场</x:v>
+        <x:v>空白漫</x:v>
       </x:c>
       <x:c r="M33" s="10" t="str">
-        <x:v>失散二十年的方小树意外归家，却被大哥二姐当成乞丐嫌弃，唯有三姐方秀兰护着他。一次受伤让他恢复记忆，为看清人心，他选择继续装傻。面对亲人的贪婪算计、骗钱逼婚与恶意陷害，小树一次次反击，也因救命之恩得到顾家、沈家相助，并与沈清月渐生真情。最终，他揭开被拐真相，惩治恶人，守住亲情与爱情，迎来人生逆袭。</x:v>
+        <x:v>周守成经营八年的早餐铺被迫搬走，熟客流失、徒弟离开，新店第一天一百多个包子无人问津。面对低价竞争和经营困境，他没有偷工减料，而是从菜贩、司机、工地和学生家长的真实需求出发，重新摸索预订与配送。靠一笼笼热包子和一次次准时守信，他终于让偏僻小店重新有了烟火气。守住一门小生意，靠的从来不是门脸，而是手艺、诚信和顾客愿意再来的信任。</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -3446,36 +3440,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B34" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C34" s="10" t="str">
-        <x:v>晚来的圆满</x:v>
+        <x:v>被身高掩盖的谎言</x:v>
       </x:c>
       <x:c r="D34" s="11" t="str">
-        <x:v>09-15 13:14</x:v>
+        <x:v>09-15 08:18</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F34" s="11" t="str">
-        <x:v>↑10位</x:v>
+        <x:v>↑9位</x:v>
       </x:c>
       <x:c r="G34" s="11" t="str"/>
       <x:c r="H34" s="11" t="str"/>
       <x:c r="I34" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J34" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K34" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="L34" s="11" t="str">
-        <x:v>杭鹿二姐爱看剧</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="M34" s="10" t="str">
-        <x:v>白手起家的女企业家沈玉珍，将独子陆衍视作家族企业的唯一继承人。谁知陆衍结识顾念后性情大变，不仅执意拒绝生育、与母亲渐行渐远，还任由顾念家人插手公司事务。眼看毕生心血面临失控，沈玉珍挺身而出，以沉稳手腕化解层层危机。最终真相水落石出，顾念的图谋落空，陆衍迷途知返担起责任，沈玉珍守护住了家业，也让家庭重归温暖圆满。</x:v>
+        <x:v>女孩林知晚回到命运转折的关键节点。她凭借智慧与勇气，敏锐察觉家中隐患，冷静引导家人、寻求帮助，用爱守护姐姐与全家。在共同努力下危机化解、正义伸张，一家人愈发珍视彼此，并且帮助到了更多有同样遭遇的人，最后迎来温暖安宁的幸福生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -3483,67 +3477,73 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B35" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C35" s="10" t="str">
-        <x:v>瘦身归来，前男友悔不当初</x:v>
+        <x:v>重回失事当晚，我扣下整条跑道</x:v>
       </x:c>
       <x:c r="D35" s="11" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>09-17 06:08</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F35" s="11" t="str">
-        <x:v>↑10位</x:v>
+        <x:v>↑6位</x:v>
       </x:c>
       <x:c r="G35" s="11" t="str"/>
       <x:c r="H35" s="11" t="str"/>
-      <x:c r="I35" s="11" t="str"/>
+      <x:c r="I35" s="11" t="n">
+        <x:v>61</x:v>
+      </x:c>
       <x:c r="J35" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K35" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
-      </x:c>
-      <x:c r="L35" s="11" t="str"/>
-      <x:c r="M35" s="10" t="str"/>
+        <x:v>年代怀旧</x:v>
+      </x:c>
+      <x:c r="L35" s="11" t="str">
+        <x:v>星漫剧院</x:v>
+      </x:c>
+      <x:c r="M35" s="10" t="str">
+        <x:v>上一世，一场诡异空难，塔台管制员谢昀含冤惨死。重生回到悲剧前夜，十五架学生无人机尽数落地，领导、师生、全网都逼她签字开放跑道。所有人都认定危险已经解除，可她笃定空域还藏着未知黑影。顶着限时命令与铺天盖地非议死扛复核。那看不见的第十六架，究竟是谁布下的致命陷阱？</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B36" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C36" s="10" t="str">
-        <x:v>萌娃兽语满级，动物园天天爆红</x:v>
+        <x:v>浮世红痕</x:v>
       </x:c>
       <x:c r="D36" s="11" t="str">
-        <x:v>09-16 10:00</x:v>
+        <x:v>09-16 07:58</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
-        <x:v>76</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F36" s="11" t="str">
-        <x:v>↑10位</x:v>
+        <x:v>↑6位</x:v>
       </x:c>
       <x:c r="G36" s="11" t="str"/>
       <x:c r="H36" s="11" t="str"/>
       <x:c r="I36" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J36" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K36" s="10" t="str">
-        <x:v>萌宝治愈 / 战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L36" s="11" t="str">
-        <x:v>一口漫剧</x:v>
+        <x:v>久久漫剧</x:v>
       </x:c>
       <x:c r="M36" s="10" t="str">
-        <x:v>八岁女孩汤圆拥有听懂动物语言的特殊能力，助力濒临倒闭的自家动物园破局重生。她读懂动物的内心诉求，化解人与动物之间的认知误解，坚守科学救助理念，拒绝猎奇表演。动物园成为科普教育阵地，传递尊重生命、人与自然和谐共生的理念，以孩童的善意守护生灵，诠释新时代少年的社会担当。</x:v>
+        <x:v>乔舒天生拥有一项特殊能力——能看见连接亲密男女的隐秘红线。她以此选定了看似专一的未婚夫陆宥泽，却在婚礼前夜，赫然发现他与自己闺蜜许澜之间缠上了红线。婚礼现场她当众揭露真相，果断终止婚约。此后她凭借异能开设“红线鉴渣工作室”，帮深陷情感疑云的人勘破真心，而更多意想不到的考验与纠葛也随之而来。</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -3551,36 +3551,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B37" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C37" s="10" t="str">
-        <x:v>养娃记：八零四合院生活日常</x:v>
+        <x:v>敢泼我馄饨，整条街都别要了</x:v>
       </x:c>
       <x:c r="D37" s="11" t="str">
-        <x:v>09-15 01:11</x:v>
+        <x:v>09-16 10:00</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F37" s="11" t="str">
-        <x:v>↑8位</x:v>
+        <x:v>↑4位</x:v>
       </x:c>
       <x:c r="G37" s="11" t="str"/>
       <x:c r="H37" s="11" t="str"/>
       <x:c r="I37" s="11" t="n">
-        <x:v>191</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J37" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K37" s="10" t="str">
-        <x:v>年代怀旧 / 萌宝治愈</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L37" s="11" t="str">
-        <x:v>香菜薯片</x:v>
+        <x:v>治愈 AI 恋</x:v>
       </x:c>
       <x:c r="M37" s="10" t="str">
-        <x:v>儿女已经成家立业，送走公公婆婆后，正准备全国游的六十多岁老太太赵锦舒重生了。重回到刚进城几个月时，那时什么都不懂，乡下来的年轻小媳妇脸皮薄，抹不开面子，也自卑，哪怕男人能挣钱，面对有权有势的婆家人，也自觉低人一头，更怕出错，给男人丢脸，很长一段时间都不敢多说一句话，明里暗里娘三个受了不少委屈。回到年轻时，赵锦舒老黄瓜刷绿漆，不管外表如何，内里都是老姜疙瘩，装不来腼腆小媳妇。</x:v>
+        <x:v>南桥旧街投资人许总多年悉心扶持一众商户，给予租金减免与基建投入，可赵川等人却贪念作祟，撕毁协议，还刻意编造谎言煽动网络暴力。面对恩将仇报的局面，许总没有冲动行事，而是恪守契约精神，凭借完备证据通过合法途径理性维权。随着真相公之于众，造谣闹事者自食恶果，承担起违约带来的相应代价。旧街完成焕新升级，充分彰显出法律与规则守护公平正义的强大力量。</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -3588,36 +3588,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B38" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C38" s="10" t="str">
-        <x:v>老板砍薪，我买下酒楼</x:v>
+        <x:v>养娃记：八零四合院生活日常</x:v>
       </x:c>
       <x:c r="D38" s="11" t="str">
-        <x:v>09-15 18:11</x:v>
+        <x:v>09-15 01:11</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F38" s="11" t="str">
-        <x:v>↑5位</x:v>
+        <x:v>↑4位</x:v>
       </x:c>
       <x:c r="G38" s="11" t="str"/>
       <x:c r="H38" s="11" t="str"/>
       <x:c r="I38" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="J38" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K38" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>年代怀旧 / 萌宝治愈</x:v>
       </x:c>
       <x:c r="L38" s="11" t="str">
-        <x:v>逸漫</x:v>
+        <x:v>香菜薯片</x:v>
       </x:c>
       <x:c r="M38" s="10" t="str">
-        <x:v>在美娟大酒楼掌勺十五年的林桂芬，因待遇调整选择离开。面对场地偏远和客户观望，她从老粮库重新起步，凭过硬手艺与真诚待客赢回乡亲认可。从十二桌寿宴到四十桌婚宴，生意越做越红火。后来，她再次走进昔日酒楼，这一次，不是回来打工，而是带着自己的招牌开启新生活。</x:v>
+        <x:v>儿女已经成家立业，送走公公婆婆后，正准备全国游的六十多岁老太太赵锦舒重生了。重回到刚进城几个月时，那时什么都不懂，乡下来的年轻小媳妇脸皮薄，抹不开面子，也自卑，哪怕男人能挣钱，面对有权有势的婆家人，也自觉低人一头，更怕出错，给男人丢脸，很长一段时间都不敢多说一句话，明里暗里娘三个受了不少委屈。回到年轻时，赵锦舒老黄瓜刷绿漆，不管外表如何，内里都是老姜疙瘩，装不来腼腆小媳妇。</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -3625,36 +3625,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B39" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C39" s="10" t="str">
-        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
+        <x:v>被诬陷诊出喜脉，重活一世我逆转前尘</x:v>
       </x:c>
       <x:c r="D39" s="11" t="str">
-        <x:v>09-15 08:00</x:v>
+        <x:v>09-16 07:58</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F39" s="11" t="str">
-        <x:v>↑5位</x:v>
+        <x:v>↑3位</x:v>
       </x:c>
       <x:c r="G39" s="11" t="str"/>
       <x:c r="H39" s="11" t="str"/>
       <x:c r="I39" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J39" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K39" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L39" s="11" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="M39" s="10" t="str">
-        <x:v>沈清韵嫁入靖王府三年，王爷冷落，侧妃得宠。王爷当众许诺，谁先诞下儿子，便请封世子。苏氏先怀孕，沈清韵却发现自己怀的是龙凤胎，她隐瞒消息，买通太医推迟产期，忍痛让苏氏先产子。王爷果然请封庶长子为世子，折子递入宗人府。受理之后，沈清韵才发动，生下龙凤胎。太后与皇上视为祥瑞，下旨赐嫡子承恩为靖王世子、嫡女承华为安乐郡主。王爷措手不及，苏氏地位一落千丈。而沈清韵知道，这只是第一步。</x:v>
+        <x:v>沈清瑶重生回到被“神医”姜辞诬陷喜脉那天。前世她因此身败名裂，被迫嫁给竹马萧景渊，后来才知这是两人为替姜辞上位设的局。这一世，她不再任人宰割，巧妙将诊脉丝线系在谢老夫人腕上，当众揭穿姜辞。萧景渊谎称“孩子是我的”，却被她揭发与姜辞的私情，两人丑态毕露。谢家震怒，姜辞被强嫁萧景渊，沈清瑶嫁入侯府。婚后她冷静布局，让萧景渊与姜辞内斗升级。最终姜辞伏法，沈清瑶挣脱前世枷锁。可重生真能让她彻底自由吗？</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -3662,24 +3662,24 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B40" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C40" s="10" t="str">
-        <x:v>我都元婴期了，你跟我说开学</x:v>
+        <x:v>糯糯下山，师兄们都慌了第三季</x:v>
       </x:c>
       <x:c r="D40" s="11" t="str">
-        <x:v>09-16 00:10</x:v>
+        <x:v>09-17 00:06</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F40" s="11" t="str">
-        <x:v>↑5位</x:v>
+        <x:v>↑3位</x:v>
       </x:c>
       <x:c r="G40" s="11" t="str"/>
       <x:c r="H40" s="11" t="str"/>
       <x:c r="I40" s="11" t="n">
-        <x:v>475</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="J40" s="10" t="str">
         <x:v>其他</x:v>
@@ -3688,10 +3688,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L40" s="11" t="str">
-        <x:v>梦启剧场</x:v>
+        <x:v>青椒剪辑</x:v>
       </x:c>
       <x:c r="M40" s="10" t="str">
-        <x:v>修士宁尘遭遇偷袭，身负重伤从修真界回到现代。时间只流逝一个暑假，他被迫入读青州大学，借居在乔姨家中，与傲娇少女许舒颜同住。一边伪装普通学生，一边寻找修复元神伤势的资源，接连化解校园、市井与古武圈子的各类风波，开启充满反差的现代生活。</x:v>
+        <x:v>六岁那年，云糯糯被师父派下山历练，顺便寻找失散多年的五位师兄。她本以为师兄们只是普通修士，生活过得不太好。可随着她一路寻找，才发现大师兄竟是镇压天下的九天仙尊，二师兄是统御九幽的魔界帝君，三师兄是丹道圣人。小奶娃背着一柄破旧黑铁巨剑，带着上古异兽，一路闯荡修仙界，顺手把五位绝世大佬师兄全部喊回了家。</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -3699,69 +3699,139 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B41" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C41" s="10" t="str">
-        <x:v>落魄老公别黑化，恶毒前妻来贴贴</x:v>
+        <x:v>瘦身归来，前男友悔不当初</x:v>
       </x:c>
       <x:c r="D41" s="11" t="str">
-        <x:v>09-17 00:06</x:v>
-      </x:c>
-      <x:c r="E41" s="11" t="str"/>
+        <x:v>2026-09-16</x:v>
+      </x:c>
+      <x:c r="E41" s="11" t="n">
+        <x:v>41</x:v>
+      </x:c>
       <x:c r="F41" s="11" t="str">
-        <x:v>新上榜</x:v>
+        <x:v>↑3位</x:v>
       </x:c>
       <x:c r="G41" s="11" t="str"/>
       <x:c r="H41" s="11" t="str"/>
-      <x:c r="I41" s="11" t="n">
-        <x:v>100</x:v>
-      </x:c>
+      <x:c r="I41" s="11" t="str"/>
       <x:c r="J41" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K41" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="L41" s="11" t="str">
-        <x:v>漫剧工厂</x:v>
-      </x:c>
-      <x:c r="M41" s="10" t="str">
-        <x:v>江城章家破产负债，昔日千金章月被父亲安排嫁给曾受章家资助、如今落魄的江远辞。相亲时章月出言羞辱，遇债主围堵被江远辞救下，躲进简陋出租屋。章月意外觉醒金手指，靠近江远辞一米内，便能看见原著弹幕，得知对方未来会成为江城首富，自己却是凄惨的恶毒前妻。为改写命运，她主动提出领证绑定彼此。二人从互相试探的契约夫妻，摆摊谋生共渡难关，对抗外界冷眼，彼此治愈内心伤痕，从各取所需慢慢走向双向救赎真心相守。</x:v>
-      </x:c>
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="L41" s="11" t="str"/>
+      <x:c r="M41" s="10" t="str"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B42" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C42" s="10" t="str">
-        <x:v>守成包子铺</x:v>
+        <x:v>情深错付</x:v>
       </x:c>
       <x:c r="D42" s="11" t="str">
-        <x:v>09-15 16:00</x:v>
-      </x:c>
-      <x:c r="E42" s="11" t="str"/>
+        <x:v>09-15 15:27</x:v>
+      </x:c>
+      <x:c r="E42" s="11" t="n">
+        <x:v>36</x:v>
+      </x:c>
       <x:c r="F42" s="11" t="str">
-        <x:v>新上榜</x:v>
+        <x:v>↑1位</x:v>
       </x:c>
       <x:c r="G42" s="11" t="str"/>
       <x:c r="H42" s="11" t="str"/>
       <x:c r="I42" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="J42" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K42" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L42" s="11" t="str">
-        <x:v>空白漫</x:v>
+        <x:v>沐光剧场</x:v>
       </x:c>
       <x:c r="M42" s="10" t="str">
-        <x:v>周守成经营八年的早餐铺被迫搬走，熟客流失、徒弟离开，新店第一天一百多个包子无人问津。面对低价竞争和经营困境，他没有偷工减料，而是从菜贩、司机、工地和学生家长的真实需求出发，重新摸索预订与配送。靠一笼笼热包子和一次次准时守信，他终于让偏僻小店重新有了烟火气。守住一门小生意，靠的从来不是门脸，而是手艺、诚信和顾客愿意再来的信任。</x:v>
+        <x:v>苏橙橙倒追陆深两年，却始终没等来一句承认。一次争执后，她被当众羞辱，车祸重伤时更亲眼看见陆深先救走白月光李芸。彻底清醒后，她拉黑、离职、离城，重新开始。等陆深终于看清真心、拼命追回时，她早已放下。三年后重逢，他以为她已结婚生子，最终带着遗憾彻底错过。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B43" s="11" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C43" s="10" t="str">
+        <x:v>七零：穿成锦鲤文里的炮灰女配</x:v>
+      </x:c>
+      <x:c r="D43" s="11" t="str">
+        <x:v>09-16 17:00</x:v>
+      </x:c>
+      <x:c r="E43" s="11" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F43" s="11" t="str">
+        <x:v>↑1位</x:v>
+      </x:c>
+      <x:c r="G43" s="11" t="str"/>
+      <x:c r="H43" s="11" t="str"/>
+      <x:c r="I43" s="11" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="J43" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K43" s="10" t="str">
+        <x:v>年代怀旧 / 战神异能</x:v>
+      </x:c>
+      <x:c r="L43" s="11" t="str">
+        <x:v>小树动漫剧场</x:v>
+      </x:c>
+      <x:c r="M43" s="10" t="str">
+        <x:v>现代女孩温梨穿越到七十年代小说，成为结局悲惨的炮灰女配，她抢先激活沉香木牌中的灵泉空间，凭借敏锐察觉化解列车上的重大隐患，得到官方表彰，为下乡做好铺垫；来到红星公社后，温梨依靠灵泉水强化体质，不再被白眼狼郭彩霞道德绑架，还截胡了本该属于女主姜月儿的机缘，她一边下地挣工分，一边利用空间物资在黑市与顾淮合作，面对姜月儿、江辰等人的屡次算计构陷，温梨从容反击，结识神秘知青陆泽川，改写自己注定悲剧的命运。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="11" t="str">
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B44" s="11" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C44" s="10" t="str">
+        <x:v>狭路遇清婉</x:v>
+      </x:c>
+      <x:c r="D44" s="11" t="str">
+        <x:v>09-15 23:30</x:v>
+      </x:c>
+      <x:c r="E44" s="11" t="str"/>
+      <x:c r="F44" s="11" t="str">
+        <x:v>新上榜</x:v>
+      </x:c>
+      <x:c r="G44" s="11" t="str"/>
+      <x:c r="H44" s="11" t="str"/>
+      <x:c r="I44" s="11" t="n">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="J44" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K44" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L44" s="11" t="str">
+        <x:v>莫忘糯糯</x:v>
+      </x:c>
+      <x:c r="M44" s="10" t="str">
+        <x:v>白辰被家里安排去俞清婉身边当助理。二人一拍即合闪婚领证，本是一场各取所需的契约婚姻。婚后朝夕相处，暧昧不断，可俞清婉的青梅竹马韩泰锡突然归国，过往纠葛接踵而至。白辰选择远走海外，俞清婉放下国内事业奔赴千里追夫。历经误会与考验，两人解开所有心结，契约情愫落地成真，携手直面风雨，收获双向奔赴的圆满爱情。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3807,7 +3877,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
         <x:v>糯糯下山，师兄们都慌了第三季</x:v>
@@ -3830,7 +3900,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
-        <x:v>24</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
         <x:v>重回失事当晚，我扣下整条跑道</x:v>
@@ -3853,7 +3923,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
         <x:v>落魄老公别黑化，恶毒前妻来贴贴</x:v>
@@ -3872,6 +3942,29 @@
       </x:c>
       <x:c r="G4" s="10" t="str">
         <x:v>漫剧工厂</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="11" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B5" s="10" t="str">
+        <x:v>灯火阑珊故人归</x:v>
+      </x:c>
+      <x:c r="C5" s="11" t="str">
+        <x:v>当日新上榜</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>08-02 17:27</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F5" s="10" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="G5" s="10" t="str">
+        <x:v>爆量短剧</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3941,7 +4034,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
         <x:v>征地我秒签跑路，全村笑我半年</x:v>
@@ -3978,7 +4071,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
         <x:v>抢个新娘来当后娘第一季</x:v>
@@ -4015,7 +4108,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
         <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
@@ -4052,16 +4145,16 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>离家十年，回来女儿被换了</x:v>
+        <x:v>穿越60我有空间不愁吃喝</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>09-09 00:04</x:v>
+        <x:v>09-07 00:04</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
         <x:v>7</x:v>
@@ -4070,10 +4163,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G5" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H5" s="11" t="n">
-        <x:v>155</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="I5" s="10" t="str">
         <x:v>其他</x:v>
@@ -4081,24 +4174,24 @@
       <x:c r="J5" s="11" t="str"/>
       <x:c r="K5" s="11" t="str"/>
       <x:c r="L5" s="10" t="str">
-        <x:v>魔方影视（上剧版</x:v>
+        <x:v>夜珠AI剧场</x:v>
       </x:c>
       <x:c r="M5" s="10" t="str">
-        <x:v>程砚宁完成长期绝密任务归来，满心想要弥补亲情，却发现家中早已物是人非。身边亲近之人被私欲蒙蔽，制造重重骗局，试图侵占她的事业与财富。面对接连而来的算计与危机，她凭借过人的魄力与智慧步步拆解阴谋，联合正义力量搜集证据，厘清全部是非纠葛。在守护自身事业的同时，她放下过往伤痛，投身公益，完成自我和解，迎来属于自己的全新人生。</x:v>
+        <x:v>现代青年刘大壮意外穿越到60年代，成了同名同姓的16岁穷小子。原主因相亲被拒、家徒四壁，下河摸鱼时溺亡。大壮醒来后发现脑中多了一座九层宝塔空间——内有灵药田与灵泉潭水，作物两小时成熟、产量翻五倍。饥荒年代，别人啃树皮喝稀粥，他靠空间种出满仓土豆粮食，黑市换粮票钞票，让饿肚子的父母姐姐们吃上饱饭。从人人嘲笑的穷小子，到带着全家逆袭翻盘，且看他手握宝塔空间，在艰苦年代闯出一条吃喝不愁的逆袭</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>穿越60我有空间不愁吃喝</x:v>
+        <x:v>离家十年，回来女儿被换了</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>09-07 00:04</x:v>
+        <x:v>09-09 00:04</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
         <x:v>7</x:v>
@@ -4107,10 +4200,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G6" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="11" t="n">
-        <x:v>1000</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
         <x:v>其他</x:v>
@@ -4118,15 +4211,15 @@
       <x:c r="J6" s="11" t="str"/>
       <x:c r="K6" s="11" t="str"/>
       <x:c r="L6" s="10" t="str">
-        <x:v>夜珠AI剧场</x:v>
+        <x:v>魔方影视（上剧版</x:v>
       </x:c>
       <x:c r="M6" s="10" t="str">
-        <x:v>现代青年刘大壮意外穿越到60年代，成了同名同姓的16岁穷小子。原主因相亲被拒、家徒四壁，下河摸鱼时溺亡。大壮醒来后发现脑中多了一座九层宝塔空间——内有灵药田与灵泉潭水，作物两小时成熟、产量翻五倍。饥荒年代，别人啃树皮喝稀粥，他靠空间种出满仓土豆粮食，黑市换粮票钞票，让饿肚子的父母姐姐们吃上饱饭。从人人嘲笑的穷小子，到带着全家逆袭翻盘，且看他手握宝塔空间，在艰苦年代闯出一条吃喝不愁的逆袭</x:v>
+        <x:v>程砚宁完成长期绝密任务归来，满心想要弥补亲情，却发现家中早已物是人非。身边亲近之人被私欲蒙蔽，制造重重骗局，试图侵占她的事业与财富。面对接连而来的算计与危机，她凭借过人的魄力与智慧步步拆解阴谋，联合正义力量搜集证据，厘清全部是非纠葛。在守护自身事业的同时，她放下过往伤痛，投身公益，完成自我和解，迎来属于自己的全新人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
         <x:v>重生三天前，我用水泥封死地下室</x:v>
@@ -4163,16 +4256,16 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="n">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>穿书后我带萌宝上门认爹</x:v>
+        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>09-07 19:18</x:v>
+        <x:v>09-11 09:00</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
         <x:v>7</x:v>
@@ -4181,10 +4274,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G8" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H8" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
         <x:v>其他</x:v>
@@ -4192,24 +4285,24 @@
       <x:c r="J8" s="11" t="str"/>
       <x:c r="K8" s="11" t="str"/>
       <x:c r="L8" s="10" t="str">
-        <x:v>虾仁不自在</x:v>
+        <x:v>阳阳动画</x:v>
       </x:c>
       <x:c r="M8" s="10" t="str">
-        <x:v>许知棠重生穿进书中，当即带着五岁儿子许小舟登门，将孩子送到亲生父亲——傅氏集团总裁傅临川面前，只想抽身退出剧情。幼儿园里儿子遭同学诬陷、老师偏心，她强势护崽，硬刚蛮横家长与失职老师。亲子鉴定尘埃落定，萌娃黏妈不黏爹，反倒让清冷总裁渐渐上心。</x:v>
+        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>末世来临，我靠囤货种田丰衣足食</x:v>
+        <x:v>穿书后我带萌宝上门认爹</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>09-09 15:30</x:v>
+        <x:v>09-07 19:18</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
         <x:v>7</x:v>
@@ -4221,7 +4314,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H9" s="11" t="n">
-        <x:v>344</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str">
         <x:v>其他</x:v>
@@ -4229,15 +4322,15 @@
       <x:c r="J9" s="11" t="str"/>
       <x:c r="K9" s="11" t="str"/>
       <x:c r="L9" s="10" t="str">
-        <x:v>渲渲动画</x:v>
+        <x:v>虾仁不自在</x:v>
       </x:c>
       <x:c r="M9" s="10" t="str">
-        <x:v>吴真真带着末世惨死的记忆重生，抢下秘宝空间，囤积海量物资，提前规避天灾人祸。她意外发现家人同样重生，一家人携手为末日做足准备。灾变如期而至，病毒、台风、极寒轮番降临。她机缘结识实力强悍的谢穆辰，二人从互相试探到并肩而立。面对凶悍恶徒与重重危机，吴真真依靠空间与智慧守护至亲，谢穆辰以自身力量与之守望相助，在满目疮痍的末世里，拼尽全力守住生存希望，奔赴属于他们的新生。</x:v>
+        <x:v>许知棠重生穿进书中，当即带着五岁儿子许小舟登门，将孩子送到亲生父亲——傅氏集团总裁傅临川面前，只想抽身退出剧情。幼儿园里儿子遭同学诬陷、老师偏心，她强势护崽，硬刚蛮横家长与失职老师。亲子鉴定尘埃落定，萌娃黏妈不黏爹，反倒让清冷总裁渐渐上心。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
         <x:v>不靠谱爸妈很靠谱</x:v>
@@ -4274,16 +4367,16 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，老公又红温啦</x:v>
+        <x:v>凤阙承安</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>09-11 09:00</x:v>
+        <x:v>2026-09-07</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
         <x:v>7</x:v>
@@ -4292,35 +4385,29 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G11" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H11" s="11" t="n">
-        <x:v>133</x:v>
-      </x:c>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H11" s="11" t="str"/>
       <x:c r="I11" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="J11" s="11" t="str"/>
       <x:c r="K11" s="11" t="str"/>
-      <x:c r="L11" s="10" t="str">
-        <x:v>阳阳动画</x:v>
-      </x:c>
-      <x:c r="M11" s="10" t="str">
-        <x:v>唐瑾穿到八零家属院，成了大院里人人避之不及的麻烦人物。原主骄纵胡闹，把日子过得一团糟，婚姻岌岌可危。开局手握烂牌，她不愿接受离婚结局，一边花式撩拨，一边努力搞事业谋生。本打算靠自己闯出一片天地，谁知冷淡的老公彻底动了心，态度急剧反转，死死纠缠不肯放手。</x:v>
-      </x:c>
+      <x:c r="L11" s="10" t="str"/>
+      <x:c r="M11" s="10" t="str"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>凤阙承安</x:v>
+        <x:v>末世来临，我靠囤货种田丰衣足食</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>09-09 15:30</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
         <x:v>7</x:v>
@@ -4329,41 +4416,47 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G12" s="11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H12" s="11" t="str"/>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H12" s="11" t="n">
+        <x:v>344</x:v>
+      </x:c>
       <x:c r="I12" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J12" s="11" t="str"/>
       <x:c r="K12" s="11" t="str"/>
-      <x:c r="L12" s="10" t="str"/>
-      <x:c r="M12" s="10" t="str"/>
+      <x:c r="L12" s="10" t="str">
+        <x:v>渲渲动画</x:v>
+      </x:c>
+      <x:c r="M12" s="10" t="str">
+        <x:v>吴真真带着末世惨死的记忆重生，抢下秘宝空间，囤积海量物资，提前规避天灾人祸。她意外发现家人同样重生，一家人携手为末日做足准备。灾变如期而至，病毒、台风、极寒轮番降临。她机缘结识实力强悍的谢穆辰，二人从互相试探到并肩而立。面对凶悍恶徒与重重危机，吴真真依靠空间与智慧守护至亲，谢穆辰以自身力量与之守望相助，在满目疮痍的末世里，拼尽全力守住生存希望，奔赴属于他们的新生。</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>重生山火前，我舍祖宅护全家</x:v>
+        <x:v>睡醒三百年，养的五只小兽全成妖祖啦</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>09-12 16:06</x:v>
+        <x:v>09-08 11:00</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G13" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H13" s="11" t="n">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="I13" s="10" t="str">
         <x:v>其他</x:v>
@@ -4371,21 +4464,21 @@
       <x:c r="J13" s="11" t="str"/>
       <x:c r="K13" s="11" t="str"/>
       <x:c r="L13" s="10" t="str">
-        <x:v>千鹤动漫</x:v>
+        <x:v>白桃剧场</x:v>
       </x:c>
       <x:c r="M13" s="10" t="str">
-        <x:v>顾长河带着前世山火中痛失全家的记忆重生归来，得知三日后西岭大火将再次席卷村庄，他不顾众人质疑，卖掉祖宅，带着妻子母亲和儿子搬上白石坡，储水备粮清出防火带，只为改写一家人的命运，当烈火真正逼近，所有人终于明白，他舍掉的只是房子，拼命守住的才是真正的家。</x:v>
+        <x:v>阿梨一觉睡了三百年，养大的五只小兽尽数离去。她带着五只旧饭碗、十二枚铜钱与一把锈柴刀下山寻兽。昔日的小家伙已成威震四方的妖祖，历经重重相遇与揭秘，阿梨知晓三百年封印的真相，携手五只妖祖，一同对抗祸世灭灵兽神。</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>今天开始做裴总</x:v>
+        <x:v>重生山火前，我舍祖宅护全家</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>09-12 19:48</x:v>
+        <x:v>09-12 16:06</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
         <x:v>5</x:v>
@@ -4397,10 +4490,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G14" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H14" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="I14" s="10" t="str">
         <x:v>其他</x:v>
@@ -4408,24 +4501,24 @@
       <x:c r="J14" s="11" t="str"/>
       <x:c r="K14" s="11" t="str"/>
       <x:c r="L14" s="10" t="str">
-        <x:v>严墨墨</x:v>
+        <x:v>千鹤动漫</x:v>
       </x:c>
       <x:c r="M14" s="10" t="str">
-        <x:v>裴野低调蛰伏三年，甘愿扮作普通员工，在公司默默沉淀，面对职场非议、旁人轻视从未辩解。年会之上，他惨遭当众开除，相伴多年的婚姻也走向终点，跌入人生低谷。褪去伪装，他不再刻意隐忍，解锁真实身份，告别敷衍度日的过往。一路轻松逆袭，打破所有人的偏见，凭自身实力惊艳全场，开启属于自己的全新人生。</x:v>
+        <x:v>顾长河带着前世山火中痛失全家的记忆重生归来，得知三日后西岭大火将再次席卷村庄，他不顾众人质疑，卖掉祖宅，带着妻子母亲和儿子搬上白石坡，储水备粮清出防火带，只为改写一家人的命运，当烈火真正逼近，所有人终于明白，他舍掉的只是房子，拼命守住的才是真正的家。</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>深海之王：我体内有个海</x:v>
+        <x:v>今天开始做裴总</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
-        <x:v>09-11 10:00</x:v>
+        <x:v>09-12 19:48</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
         <x:v>6</x:v>
@@ -4434,10 +4527,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G15" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H15" s="11" t="n">
-        <x:v>215</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I15" s="10" t="str">
         <x:v>其他</x:v>
@@ -4445,24 +4538,24 @@
       <x:c r="J15" s="11" t="str"/>
       <x:c r="K15" s="11" t="str"/>
       <x:c r="L15" s="10" t="str">
-        <x:v>阅友动漫</x:v>
+        <x:v>严墨墨</x:v>
       </x:c>
       <x:c r="M15" s="10" t="str">
-        <x:v>沈泽凯衣锦还乡想要报恩，却得知当年为供他读书卖掉家中唯一土地的小舅早已病故。悲痛之际，他在海边捡到金色珍珠，意外重返少年，觉醒小世界沙盘，可洞悉整片海域动向。重活一世，小舅依旧为他倾尽所有。前世已是县城首富的沈泽凯，打算利用暑假借助沙盘帮小舅赚钱娶妻。赶海寻宝、乘风破浪，他屡次邂逅深海智慧生灵，逐步揭开海王宝藏的秘密。这一世，他守护至亲，驰骋碧海，活出别样人生。</x:v>
+        <x:v>裴野低调蛰伏三年，甘愿扮作普通员工，在公司默默沉淀，面对职场非议、旁人轻视从未辩解。年会之上，他惨遭当众开除，相伴多年的婚姻也走向终点，跌入人生低谷。褪去伪装，他不再刻意隐忍，解锁真实身份，告别敷衍度日的过往。一路轻松逆袭，打破所有人的偏见，凭自身实力惊艳全场，开启属于自己的全新人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>锦书迟</x:v>
+        <x:v>深海之王：我体内有个海</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>09-12 07:30</x:v>
+        <x:v>09-11 10:00</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
         <x:v>6</x:v>
@@ -4471,10 +4564,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G16" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H16" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str">
         <x:v>其他</x:v>
@@ -4482,21 +4575,21 @@
       <x:c r="J16" s="11" t="str"/>
       <x:c r="K16" s="11" t="str"/>
       <x:c r="L16" s="10" t="str">
-        <x:v>咩咩漫文</x:v>
+        <x:v>阅友动漫</x:v>
       </x:c>
       <x:c r="M16" s="10" t="str">
-        <x:v>三年前，沈昭昭嫁与永宁侯谢凛，新婚燕尔他便远赴边关。她苦等家书，却不知双向书信早被人暗中截留。她终于心冷离开侯府。三年后，她带着孩子在市井支摊卖画立足，他却循着蛛丝马迹寻来，真相层层揭开，原来他从未负她。</x:v>
+        <x:v>沈泽凯衣锦还乡想要报恩，却得知当年为供他读书卖掉家中唯一土地的小舅早已病故。悲痛之际，他在海边捡到金色珍珠，意外重返少年，觉醒小世界沙盘，可洞悉整片海域动向。重活一世，小舅依旧为他倾尽所有。前世已是县城首富的沈泽凯，打算利用暑假借助沙盘帮小舅赚钱娶妻。赶海寻宝、乘风破浪，他屡次邂逅深海智慧生灵，逐步揭开海王宝藏的秘密。这一世，他守护至亲，驰骋碧海，活出别样人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>我送弟弟上青云</x:v>
+        <x:v>锦书迟</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>09-12 09:52</x:v>
+        <x:v>09-12 07:30</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
         <x:v>5</x:v>
@@ -4508,10 +4601,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G17" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H17" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I17" s="10" t="str">
         <x:v>其他</x:v>
@@ -4519,15 +4612,15 @@
       <x:c r="J17" s="11" t="str"/>
       <x:c r="K17" s="11" t="str"/>
       <x:c r="L17" s="10" t="str">
-        <x:v>落云</x:v>
+        <x:v>咩咩漫文</x:v>
       </x:c>
       <x:c r="M17" s="10" t="str">
-        <x:v>宋远回乡发现弟弟宋临被父亲剥夺上学权利，只能干农活。他毅然带走弟弟，用微薄工资供他读书。宋临考上名校建筑系，毕业后成为身价过亿的设计师。他用第一桶金给哥哥买房，报答当年恩情。面对迟来求和的父亲，宋临完成了心灵的真正和解。这是一个关于“长兄如父、手足情深”的故事，诠释了扶助与感恩的力量。</x:v>
+        <x:v>三年前，沈昭昭嫁与永宁侯谢凛，新婚燕尔他便远赴边关。她苦等家书，却不知双向书信早被人暗中截留。她终于心冷离开侯府。三年后，她带着孩子在市井支摊卖画立足，他却循着蛛丝马迹寻来，真相层层揭开，原来他从未负她。</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
         <x:v>双姝逢旧岸，一怒扫尘奸</x:v>
@@ -4564,13 +4657,13 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>泰城错嫁</x:v>
+        <x:v>我送弟弟上青云</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>09-12 21:10</x:v>
+        <x:v>09-12 09:52</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
         <x:v>5</x:v>
@@ -4582,10 +4675,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G19" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H19" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str">
         <x:v>其他</x:v>
@@ -4593,21 +4686,21 @@
       <x:c r="J19" s="11" t="str"/>
       <x:c r="K19" s="11" t="str"/>
       <x:c r="L19" s="10" t="str">
-        <x:v>夜草剧场</x:v>
+        <x:v>落云</x:v>
       </x:c>
       <x:c r="M19" s="10" t="str">
-        <x:v>二十世纪三十年代泰国，两姐妹姐妹同日嫁人，丑妹珠珠嫁帅气宋帕，美姐南佩却配憨汉啊光。迎亲途中大象突然发情，两对新人错上婚车、错入洞房。泼辣珠珠遇上憨厚啊光，闹洞房、斗婆婆，从互殴到相守；温柔南佩遇上冷脸宋帕，假装吵架赶走宾客，从陌生到动心。两对夫妻先后离婚，珠珠与啊光携手生子，南佩闯荡成舞台名角，与宋帕久别重逢。错的人成了对的人，两对冤家，各得圆满。</x:v>
+        <x:v>宋远回乡发现弟弟宋临被父亲剥夺上学权利，只能干农活。他毅然带走弟弟，用微薄工资供他读书。宋临考上名校建筑系，毕业后成为身价过亿的设计师。他用第一桶金给哥哥买房，报答当年恩情。面对迟来求和的父亲，宋临完成了心灵的真正和解。这是一个关于“长兄如父、手足情深”的故事，诠释了扶助与感恩的力量。</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="n">
-        <x:v>86</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>七套房产，换来一纸调令</x:v>
+        <x:v>泰城错嫁</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>09-12 08:18</x:v>
+        <x:v>09-12 21:10</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
         <x:v>5</x:v>
@@ -4619,10 +4712,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G20" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H20" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I20" s="10" t="str">
         <x:v>其他</x:v>
@@ -4630,21 +4723,21 @@
       <x:c r="J20" s="11" t="str"/>
       <x:c r="K20" s="11" t="str"/>
       <x:c r="L20" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>夜草剧场</x:v>
       </x:c>
       <x:c r="M20" s="10" t="str">
-        <x:v>公婆将七套房产全数赠予小叔子，长子陈峰看似顺从鼓掌，实则暗中申请援疆调令。面对父母偏心和弟媳挑衅，陈峰携妻林晚隐忍筹备。最终在家庭会议上，他出示双人调令宣告远赴新疆，打破原生家庭剥削链条。经历异地磨砺与除夕和解，一家人终在理解中重建亲情边界，实现各自独立与成长。</x:v>
+        <x:v>二十世纪三十年代泰国，两姐妹姐妹同日嫁人，丑妹珠珠嫁帅气宋帕，美姐南佩却配憨汉啊光。迎亲途中大象突然发情，两对新人错上婚车、错入洞房。泼辣珠珠遇上憨厚啊光，闹洞房、斗婆婆，从互殴到相守；温柔南佩遇上冷脸宋帕，假装吵架赶走宾客，从陌生到动心。两对夫妻先后离婚，珠珠与啊光携手生子，南佩闯荡成舞台名角，与宋帕久别重逢。错的人成了对的人，两对冤家，各得圆满。</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="n">
-        <x:v>94</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>重生1985年，赶海我有系统</x:v>
+        <x:v>青牛引泉来</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>09-11 07:00</x:v>
+        <x:v>09-11 15:20</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
         <x:v>6</x:v>
@@ -4656,10 +4749,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G21" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H21" s="11" t="n">
-        <x:v>132</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="I21" s="10" t="str">
         <x:v>其他</x:v>
@@ -4667,24 +4760,25 @@
       <x:c r="J21" s="11" t="str"/>
       <x:c r="K21" s="11" t="str"/>
       <x:c r="L21" s="10" t="str">
-        <x:v>依语动漫</x:v>
+        <x:v>车仔漫</x:v>
       </x:c>
       <x:c r="M21" s="10" t="str">
-        <x:v>八十年代小渔村，林舟出钱出力帮家里盖起红砖新房，落成之日却遭到父母兄长算计，新房被夺走，自己只分得被搬空的破旧老屋。带着前世被家人压榨到老的遗憾，重活一世的林舟不再愚孝，请来村长当众分家切割亲缘。绝境之中，他意外激活渔业情报系统，可以接收大海给出的渔获线索。他借得工具赶海，捞获珍贵大石斑鱼赚取第一笔启动资金，又约上好友李二狗大雾天冒险出海，依靠系统指引追逐鱼群。</x:v>
+        <x:v>大旱之年，贫苦庄稼汉石满仓为宽慰盼他成家的母亲，扎了个稻草媳妇，谁料草人竟化作姑娘阿禾。原来阿禾是有灵性的青牛，十年前大旱濒死时被石满仓用豆秸和水救下，此番借稻草人身躯前来报恩。
+阿禾感知到村井即将枯竭，带领众人找到被封堵的牛眠岭古泉。靠卖自家井水牟利的马有财因利益受损，百般阻挠，甚至污染泉水、堵塞闸口。</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>穿越七零:月季花开</x:v>
+        <x:v>七套房产，换来一纸调令</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>09-11 22:25</x:v>
+        <x:v>09-12 08:18</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
         <x:v>6</x:v>
@@ -4693,10 +4787,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G22" s="11" t="n">
-        <x:v>29</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H22" s="11" t="n">
-        <x:v>219</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str">
         <x:v>其他</x:v>
@@ -4704,21 +4798,21 @@
       <x:c r="J22" s="11" t="str"/>
       <x:c r="K22" s="11" t="str"/>
       <x:c r="L22" s="10" t="str">
-        <x:v>维维动画</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="M22" s="10" t="str">
-        <x:v>女知青白月季意外穿进书中，原主本打算上山打掉腹中孩子。清醒过来的她选择接受命运，不再执念过往的情缘，决定和周野好好过日子。周野看似粗犷，实则重情重义，满心珍视白月季。二人携手扎根乡村，对抗邻里闲言碎语，努力耕耘生活。白月季凭借文笔投稿赚取稿费，周野踏实打拼养家，还迎来双胞胎。在柴米烟火里互相扶持，跨过重重风波，把平凡的农家日子过得滚烫又幸福。</x:v>
+        <x:v>公婆将七套房产全数赠予小叔子，长子陈峰看似顺从鼓掌，实则暗中申请援疆调令。面对父母偏心和弟媳挑衅，陈峰携妻林晚隐忍筹备。最终在家庭会议上，他出示双人调令宣告远赴新疆，打破原生家庭剥削链条。经历异地磨砺与除夕和解，一家人终在理解中重建亲情边界，实现各自独立与成长。</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>青牛引泉来</x:v>
+        <x:v>重生1985年，赶海我有系统</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>09-11 15:20</x:v>
+        <x:v>09-11 07:00</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
         <x:v>6</x:v>
@@ -4730,10 +4824,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="G23" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H23" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
         <x:v>其他</x:v>
@@ -4741,11 +4835,10 @@
       <x:c r="J23" s="11" t="str"/>
       <x:c r="K23" s="11" t="str"/>
       <x:c r="L23" s="10" t="str">
-        <x:v>车仔漫</x:v>
+        <x:v>依语动漫</x:v>
       </x:c>
       <x:c r="M23" s="10" t="str">
-        <x:v>大旱之年，贫苦庄稼汉石满仓为宽慰盼他成家的母亲，扎了个稻草媳妇，谁料草人竟化作姑娘阿禾。原来阿禾是有灵性的青牛，十年前大旱濒死时被石满仓用豆秸和水救下，此番借稻草人身躯前来报恩。
-阿禾感知到村井即将枯竭，带领众人找到被封堵的牛眠岭古泉。靠卖自家井水牟利的马有财因利益受损，百般阻挠，甚至污染泉水、堵塞闸口。</x:v>
+        <x:v>八十年代小渔村，林舟出钱出力帮家里盖起红砖新房，落成之日却遭到父母兄长算计，新房被夺走，自己只分得被搬空的破旧老屋。带着前世被家人压榨到老的遗憾，重活一世的林舟不再愚孝，请来村长当众分家切割亲缘。绝境之中，他意外激活渔业情报系统，可以接收大海给出的渔获线索。他借得工具赶海，捞获珍贵大石斑鱼赚取第一笔启动资金，又约上好友李二狗大雾天冒险出海，依靠系统指引追逐鱼群。</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -4787,7 +4880,7 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
         <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
@@ -4824,7 +4917,7 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
         <x:v>返乡种田，我看透了人性</x:v>
@@ -4861,7 +4954,7 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="11" t="n">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
         <x:v>听水小锦鲤</x:v>
@@ -4898,7 +4991,7 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
         <x:v>今晚查寝，别开门</x:v>
@@ -4935,13 +5028,13 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>家有新章</x:v>
+        <x:v>除夕夜，我被直升机接回前夫家</x:v>
       </x:c>
       <x:c r="C29" s="11" t="str">
-        <x:v>09-10 09:00</x:v>
+        <x:v>09-10 08:00</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
         <x:v>7</x:v>
@@ -4953,10 +5046,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G29" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H29" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="I29" s="10" t="str">
         <x:v>其他</x:v>
@@ -4964,9 +5057,46 @@
       <x:c r="J29" s="11" t="str"/>
       <x:c r="K29" s="11" t="str"/>
       <x:c r="L29" s="10" t="str">
+        <x:v>小狐狸剧场</x:v>
+      </x:c>
+      <x:c r="M29" s="10" t="str">
+        <x:v>除夕夜，一架直升机将顾晚棠从苏州小院接回豪门。十九年前，她背负罪名被傅家扫地出门，与幼子傅知衍骨肉分离。如今化名林棠的她，已是高端苏绣“棠记”的主理人，归来只为讨一个公道。宴会上，面对伪善的沈若薇与家族胁迫，她亮出证据步步为营。真相浮出水面，儿子终知愧疚。然而傅老夫人觊觎棠记，设局破坏。顾晚棠能否守住心血，彻底挣脱过往枷锁？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="11" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B30" s="10" t="str">
+        <x:v>家有新章</x:v>
+      </x:c>
+      <x:c r="C30" s="11" t="str">
+        <x:v>09-10 09:00</x:v>
+      </x:c>
+      <x:c r="D30" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E30" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F30" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G30" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H30" s="11" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="I30" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="J30" s="11" t="str"/>
+      <x:c r="K30" s="11" t="str"/>
+      <x:c r="L30" s="10" t="str">
         <x:v>尔尔剧场</x:v>
       </x:c>
-      <x:c r="M29" s="10" t="str">
+      <x:c r="M30" s="10" t="str">
         <x:v>新婚回门日，新媳妇秦麦穗因拒被大伯母郭凤英拿捏、不让丈夫无偿干活，彻底得罪大房一家。郭凤英处处刁难，断其公公杀猪活路麦穗逆势创业，靠卤味、腊肠做起小作坊，安稳养家。反观眼高手低的堂哥梁大勇，贪快钱误入骗局欠债，辛苦还债幡然醒悟。最终两家境遇悬殊，踏实肯干的秦家岁岁安稳、日子红火。</x:v>
       </x:c>
     </x:row>
@@ -5028,10 +5158,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F2" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>2026-09-17 02-11</x:v>
+        <x:v>2026-09-17 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -5051,10 +5181,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F3" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>2026-09-17 02-11</x:v>
+        <x:v>2026-09-17 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -5077,7 +5207,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>2026-09-17 02-11</x:v>
+        <x:v>2026-09-17 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -5097,10 +5227,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F5" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>2026-09-17 02-11</x:v>
+        <x:v>2026-09-17 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -5108,22 +5238,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>重回82：我成山君契约万兽打猎宠妻</x:v>
+        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
       </x:c>
       <x:c r="C6" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>11.1</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F6" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>2026-09-17 00-11</x:v>
+        <x:v>2026-09-17 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -5137,7 +5267,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>11.2</x:v>
+        <x:v>11.5</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
         <x:v>4</x:v>
@@ -5146,7 +5276,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>2026-09-17 02-11</x:v>
+        <x:v>2026-09-17 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -5154,22 +5284,22 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>我的游戏好友全是大佬2：姐妹出场</x:v>
+        <x:v>重回82：我成山君契约万兽打猎宠妻</x:v>
       </x:c>
       <x:c r="C8" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>11.2</x:v>
+        <x:v>6.1</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>2026-09-17 02-11</x:v>
+        <x:v>2026-09-17 00-11</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -5180,19 +5310,19 @@
         <x:v>被诬陷诊出喜脉，重活一世我逆转前尘</x:v>
       </x:c>
       <x:c r="C9" s="11" t="n">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>5.9</x:v>
+        <x:v>5.8</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>2026-09-17 02-11</x:v>
+        <x:v>2026-09-17 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -5200,22 +5330,22 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>今晚查寝，别开门</x:v>
+        <x:v>新厂旧账</x:v>
       </x:c>
       <x:c r="C10" s="11" t="n">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>8.8</x:v>
+        <x:v>11.9</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F10" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>2026-09-16 21-13</x:v>
+        <x:v>2026-09-17 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -5223,22 +5353,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>听水小锦鲤</x:v>
+        <x:v>今晚查寝，别开门</x:v>
       </x:c>
       <x:c r="C11" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>12.8</x:v>
+        <x:v>8.9</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
-        <x:v>2026-09-17 00-11</x:v>
+        <x:v>2026-09-16 21-13</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -5246,19 +5376,19 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>新厂旧账</x:v>
+        <x:v>听水小锦鲤</x:v>
       </x:c>
       <x:c r="C12" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>11.6</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G12" s="11" t="str">
         <x:v>2026-09-17 00-11</x:v>
@@ -5272,10 +5402,10 @@
         <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
       </x:c>
       <x:c r="C13" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>9.5</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
         <x:v>6</x:v>
@@ -5295,19 +5425,19 @@
         <x:v>敢泼我馄饨，整条街都别要了</x:v>
       </x:c>
       <x:c r="C14" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>13.2</x:v>
+        <x:v>13.1</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G14" s="11" t="str">
-        <x:v>2026-09-17 02-11</x:v>
+        <x:v>2026-09-17 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -5384,22 +5514,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>青牛引泉来</x:v>
+        <x:v>重生山火前，我舍祖宅护全家</x:v>
       </x:c>
       <x:c r="C18" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>16.8</x:v>
+        <x:v>10.6</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G18" s="11" t="str">
-        <x:v>2026-09-16 14-11</x:v>
+        <x:v>2026-09-17 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -5407,22 +5537,22 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>重生山火前，我舍祖宅护全家</x:v>
+        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
       </x:c>
       <x:c r="C19" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>13.4</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G19" s="11" t="str">
-        <x:v>2026-09-17 02-11</x:v>
+        <x:v>2026-09-17 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -5430,22 +5560,22 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>穿成恶毒后娘，七个反派争着喊娘</x:v>
+        <x:v>青牛引泉来</x:v>
       </x:c>
       <x:c r="C20" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>13.6</x:v>
+        <x:v>16.7</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="G20" s="11" t="str">
-        <x:v>2026-09-17 02-11</x:v>
+        <x:v>2026-09-16 14-11</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -5453,22 +5583,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>一张煎饼，扯出满纸谎言</x:v>
+        <x:v>糯糯下山，师兄们都慌了第三季</x:v>
       </x:c>
       <x:c r="C21" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>6.8</x:v>
+        <x:v>7.7</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G21" s="11" t="str">
-        <x:v>2026-09-16 17-11</x:v>
+        <x:v>2026-09-17 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -5476,22 +5606,22 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>糯糯下山，师兄们都慌了第三季</x:v>
+        <x:v>一张煎饼，扯出满纸谎言</x:v>
       </x:c>
       <x:c r="C22" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6.8</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G22" s="11" t="str">
-        <x:v>2026-09-17 02-11</x:v>
+        <x:v>2026-09-16 17-11</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -5522,22 +5652,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>重生三天前，我用水泥封死地下室</x:v>
+        <x:v>霁月安遥之以余生为诺护你岁岁无忧第一季</x:v>
       </x:c>
       <x:c r="C24" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>13.6</x:v>
+        <x:v>13.2</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G24" s="11" t="str">
-        <x:v>2026-09-16 21-13</x:v>
+        <x:v>2026-09-17 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -5545,22 +5675,22 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>破库房的秘密</x:v>
+        <x:v>重生三天前，我用水泥封死地下室</x:v>
       </x:c>
       <x:c r="C25" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>18.3</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G25" s="11" t="str">
-        <x:v>2026-09-16 20-11</x:v>
+        <x:v>2026-09-16 21-13</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -5568,22 +5698,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>因为大黄遇见你</x:v>
+        <x:v>破库房的秘密</x:v>
       </x:c>
       <x:c r="C26" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>14.2</x:v>
+        <x:v>18.2</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G26" s="11" t="str">
-        <x:v>2026-09-16 14-11</x:v>
+        <x:v>2026-09-16 20-11</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -5614,22 +5744,22 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>霁月安遥之以余生为诺护你岁岁无忧第一季</x:v>
+        <x:v>老板砍薪，我买下酒楼</x:v>
       </x:c>
       <x:c r="C28" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>16.9</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F28" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G28" s="11" t="str">
-        <x:v>2026-09-17 02-11</x:v>
+        <x:v>2026-09-17 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -5637,22 +5767,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>一针绣出自己的路</x:v>
+        <x:v>因为大黄遇见你</x:v>
       </x:c>
       <x:c r="C29" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>14.7</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str">
-        <x:v>2026-09-16 17-11</x:v>
+        <x:v>2026-09-16 14-11</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -5660,22 +5790,22 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>老板砍薪，我买下酒楼</x:v>
+        <x:v>一针绣出自己的路</x:v>
       </x:c>
       <x:c r="C30" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>16.8</x:v>
+        <x:v>18.8</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G30" s="11" t="str">
-        <x:v>2026-09-17 02-11</x:v>
+        <x:v>2026-09-16 17-11</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -5683,22 +5813,22 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>我在工地卖盒饭带火一座城</x:v>
+        <x:v>萌娃兽语满级，动物园天天爆红</x:v>
       </x:c>
       <x:c r="C31" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
-        <x:v>16.2</x:v>
+        <x:v>10.8</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G31" s="11" t="str">
-        <x:v>2026-09-16 17-11</x:v>
+        <x:v>2026-09-16 20-11</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -5706,22 +5836,22 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="10" t="str">
-        <x:v>萌娃兽语满级，动物园天天爆红</x:v>
+        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
       </x:c>
       <x:c r="C32" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D32" s="11" t="n">
-        <x:v>10.8</x:v>
+        <x:v>13.6</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G32" s="11" t="str">
-        <x:v>2026-09-16 20-11</x:v>
+        <x:v>2026-09-17 02-11</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -5729,13 +5859,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="10" t="str">
-        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
+        <x:v>抢个新娘来当后娘第一季</x:v>
       </x:c>
       <x:c r="C33" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D33" s="11" t="n">
-        <x:v>13.6</x:v>
+        <x:v>14.8</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
         <x:v>9</x:v>
@@ -5744,7 +5874,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="G33" s="11" t="str">
-        <x:v>2026-09-17 02-11</x:v>
+        <x:v>2026-09-17 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -5752,22 +5882,22 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="10" t="str">
-        <x:v>家有新章</x:v>
+        <x:v>我在工地卖盒饭带火一座城</x:v>
       </x:c>
       <x:c r="C34" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D34" s="11" t="n">
-        <x:v>13.5</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F34" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G34" s="11" t="str">
-        <x:v>2026-09-17 02-11</x:v>
+        <x:v>2026-09-16 17-11</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -5775,22 +5905,22 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="10" t="str">
-        <x:v>高考刚结束父母就不装了</x:v>
+        <x:v>今天开始做裴总</x:v>
       </x:c>
       <x:c r="C35" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D35" s="11" t="n">
-        <x:v>12.8</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F35" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G35" s="11" t="str">
-        <x:v>2026-09-16 14-11</x:v>
+        <x:v>2026-09-17 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -5798,19 +5928,19 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="10" t="str">
-        <x:v>抢个新娘来当后娘第一季</x:v>
+        <x:v>家有新章</x:v>
       </x:c>
       <x:c r="C36" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
-        <x:v>16.2</x:v>
+        <x:v>13.5</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G36" s="11" t="str">
         <x:v>2026-09-17 02-11</x:v>
@@ -5821,22 +5951,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="10" t="str">
-        <x:v>今天开始做裴总</x:v>
+        <x:v>高考刚结束父母就不装了</x:v>
       </x:c>
       <x:c r="C37" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D37" s="11" t="n">
-        <x:v>3.3</x:v>
+        <x:v>12.8</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G37" s="11" t="str">
-        <x:v>2026-09-17 02-11</x:v>
+        <x:v>2026-09-16 14-11</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -6074,22 +6204,22 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B48" s="10" t="str">
-        <x:v>离家十年，回来女儿被换了</x:v>
+        <x:v>一墙之隔，皆是人心</x:v>
       </x:c>
       <x:c r="C48" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D48" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>17.3</x:v>
       </x:c>
       <x:c r="E48" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F48" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G48" s="11" t="str">
-        <x:v>2026-09-16 11-11</x:v>
+        <x:v>2026-09-17 03-11</x:v>
       </x:c>
     </x:row>
     <x:row r="49">

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="Rf4ef05d0295c42c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="R3c116118284349bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="R1602c83d4c4a44d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="Rbb0a926ad26d4483"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP20剧重点跟踪" sheetId="5" r:id="Rc3670fea583d404e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="6" r:id="R77f294dec0664883"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="选剧规则说明" sheetId="7" r:id="R697dd976820143df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重型)" sheetId="8" r:id="R35399f54581a4d55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径C(账号层级优先)" sheetId="9" r:id="R834d1790cd7f45c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="10" r:id="R1d25ff51a6c64dc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R5aea275645ff450a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="Rd0dc8daed95a4f96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日新剧上榜单" sheetId="3" r:id="R6a84c7c0c4c24e5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="长跑新剧榜" sheetId="4" r:id="Rffe3a3d33a42432c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOP20剧重点跟踪" sheetId="5" r:id="Rca29f70432bd44f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="6" r:id="R3eeac7a62f254371"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="选剧规则说明" sheetId="7" r:id="R8edc50349fa74326"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径B(账号权重型)" sheetId="8" r:id="Rd22accd7e6804c20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·口径C(账号层级优先)" sheetId="9" r:id="R114ecfd3ecaf4468"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="10" r:id="R5780f5e4c84d4311"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -553,31 +553,27 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>占院风波</x:v>
+        <x:v>菌香深处见人心</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>08-08 17:00</x:v>
+        <x:v>08-21 17:00</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E8" s="10" t="n">
-        <x:v>66</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F8" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G8" s="10" t="str">
         <x:v>现实反转</x:v>
       </x:c>
-      <x:c r="H8" s="11" t="n">
-        <x:v>976</x:v>
-      </x:c>
-      <x:c r="I8" s="11" t="str">
-        <x:v>1.03</x:v>
-      </x:c>
+      <x:c r="H8" s="11" t="str"/>
+      <x:c r="I8" s="11" t="str"/>
       <x:c r="J8" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-30、2026-08-31、2026-09-02、2026-09-03、2026-09-09、2026-09-12、2026-09-13、2026-09-14、2026-09-15</x:v>
+        <x:v>2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15、2026-09-16、2026-09-17</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -585,27 +581,31 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>菌香深处见人心</x:v>
+        <x:v>占院风波</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>08-21 17:00</x:v>
+        <x:v>08-08 17:00</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E9" s="10" t="n">
-        <x:v>50</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F9" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G9" s="10" t="str">
         <x:v>现实反转</x:v>
       </x:c>
-      <x:c r="H9" s="11" t="str"/>
-      <x:c r="I9" s="11" t="str"/>
+      <x:c r="H9" s="11" t="n">
+        <x:v>976</x:v>
+      </x:c>
+      <x:c r="I9" s="11" t="str">
+        <x:v>1.03</x:v>
+      </x:c>
       <x:c r="J9" s="10" t="str">
-        <x:v>2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15、2026-09-16</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-30、2026-08-31、2026-09-02、2026-09-03、2026-09-09、2026-09-12、2026-09-13、2026-09-14、2026-09-15</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -905,27 +905,27 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>重生六七：赶山狩猎养全家</x:v>
+        <x:v>精通婴语满朝权贵求我带娃</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>08-25 18:00</x:v>
+        <x:v>08-03 11:51</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="E20" s="10" t="n">
-        <x:v>108</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F20" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="G20" s="10" t="str">
-        <x:v>种田囤货</x:v>
+        <x:v>萌宝治愈</x:v>
       </x:c>
       <x:c r="H20" s="11" t="str"/>
       <x:c r="I20" s="11" t="str"/>
       <x:c r="J20" s="10" t="str">
-        <x:v>2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
+        <x:v>2026-08-20、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15、2026-09-16、2026-09-17</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -933,27 +933,27 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>山下是绝路，山上是生门</x:v>
+        <x:v>重生六七：赶山狩猎养全家</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>08-27 07:03</x:v>
+        <x:v>08-25 18:00</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E21" s="10" t="n">
-        <x:v>99</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F21" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G21" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>种田囤货</x:v>
       </x:c>
       <x:c r="H21" s="11" t="str"/>
       <x:c r="I21" s="11" t="str"/>
       <x:c r="J21" s="10" t="str">
-        <x:v>2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-15</x:v>
+        <x:v>2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -961,27 +961,27 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>精通婴语满朝权贵求我带娃</x:v>
+        <x:v>铺子空了，房东慌了</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>08-03 11:51</x:v>
+        <x:v>08-29 16:49</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E22" s="10" t="n">
-        <x:v>116</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F22" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="G22" s="10" t="str">
-        <x:v>萌宝治愈</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="H22" s="11" t="str"/>
       <x:c r="I22" s="11" t="str"/>
       <x:c r="J22" s="10" t="str">
-        <x:v>2026-08-20、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15、2026-09-16</x:v>
+        <x:v>2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15、2026-09-16、2026-09-17</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -989,27 +989,27 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>重生之从迎娶大小姐开始逆袭</x:v>
+        <x:v>山下是绝路，山上是生门</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>08-23 11:00</x:v>
+        <x:v>08-27 07:03</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="E23" s="10" t="n">
-        <x:v>145</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F23" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G23" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="H23" s="11" t="str"/>
       <x:c r="I23" s="11" t="str"/>
       <x:c r="J23" s="10" t="str">
-        <x:v>2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-09、2026-09-11、2026-09-12、2026-09-13、2026-09-14</x:v>
+        <x:v>2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-15</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1017,27 +1017,27 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>铺子空了，房东慌了</x:v>
+        <x:v>重生之从迎娶大小姐开始逆袭</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>08-29 16:49</x:v>
+        <x:v>08-23 11:00</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="E24" s="10" t="n">
-        <x:v>55</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="F24" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="G24" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="H24" s="11" t="str"/>
       <x:c r="I24" s="11" t="str"/>
       <x:c r="J24" s="10" t="str">
-        <x:v>2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-05、2026-09-06、2026-09-07、2026-09-08、2026-09-09、2026-09-10、2026-09-11、2026-09-12、2026-09-13、2026-09-14、2026-09-15、2026-09-16</x:v>
+        <x:v>2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03、2026-09-04、2026-09-09、2026-09-11、2026-09-12、2026-09-13、2026-09-14</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1131,10 +1131,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>1042</x:v>
+        <x:v>1047</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>55.0%</x:v>
+        <x:v>55.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1180,7 +1180,7 @@
         <x:v>30-49集</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
         <x:v>11.1%</x:v>
@@ -1191,10 +1191,10 @@
         <x:v>50-79集</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>742</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>42.9%</x:v>
+        <x:v>42.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1202,7 +1202,7 @@
         <x:v>80-99集</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>217</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
         <x:v>12.6%</x:v>
@@ -1213,7 +1213,7 @@
         <x:v>100集以上</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>576</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
         <x:v>33.3%</x:v>
@@ -1240,7 +1240,7 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>838</x:v>
+        <x:v>841</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
         <x:v>44.3%</x:v>
@@ -1251,7 +1251,7 @@
         <x:v>婚姻/情感</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>343</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
         <x:v>18.1%</x:v>
@@ -1273,7 +1273,7 @@
         <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
         <x:v>8.6%</x:v>
@@ -1287,7 +1287,7 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>8.5%</x:v>
+        <x:v>8.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1320,7 +1320,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>5.7%</x:v>
+        <x:v>5.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1331,7 +1331,7 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>4.8%</x:v>
+        <x:v>4.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1418,10 +1418,10 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="10" t="str">
-        <x:v>上榜26次</x:v>
+        <x:v>上榜27次</x:v>
       </x:c>
       <x:c r="B34" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C34" s="11" t="str">
         <x:v>0.1%</x:v>
@@ -1429,7 +1429,7 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="10" t="str">
-        <x:v>上榜23次</x:v>
+        <x:v>上榜26次</x:v>
       </x:c>
       <x:c r="B35" s="11" t="n">
         <x:v>1</x:v>
@@ -1440,29 +1440,29 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="10" t="str">
-        <x:v>上榜22次</x:v>
+        <x:v>上榜23次</x:v>
       </x:c>
       <x:c r="B36" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C36" s="11" t="str">
-        <x:v>0.2%</x:v>
+        <x:v>0.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="10" t="str">
-        <x:v>上榜21次</x:v>
+        <x:v>上榜22次</x:v>
       </x:c>
       <x:c r="B37" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C37" s="11" t="str">
-        <x:v>0.1%</x:v>
+        <x:v>0.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="10" t="str">
-        <x:v>上榜20次</x:v>
+        <x:v>上榜21次</x:v>
       </x:c>
       <x:c r="B38" s="11" t="n">
         <x:v>2</x:v>
@@ -1473,43 +1473,43 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="10" t="str">
-        <x:v>上榜19次</x:v>
+        <x:v>上榜20次</x:v>
       </x:c>
       <x:c r="B39" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C39" s="11" t="str">
-        <x:v>0.2%</x:v>
+        <x:v>0.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="10" t="str">
-        <x:v>上榜18次</x:v>
+        <x:v>上榜19次</x:v>
       </x:c>
       <x:c r="B40" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C40" s="11" t="str">
-        <x:v>0.2%</x:v>
+        <x:v>0.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="10" t="str">
-        <x:v>上榜17次</x:v>
+        <x:v>上榜18次</x:v>
       </x:c>
       <x:c r="B41" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C41" s="11" t="str">
-        <x:v>0.3%</x:v>
+        <x:v>0.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="10" t="str">
-        <x:v>上榜16次</x:v>
+        <x:v>上榜17次</x:v>
       </x:c>
       <x:c r="B42" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C42" s="11" t="str">
         <x:v>0.3%</x:v>
@@ -1517,7 +1517,7 @@
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="10" t="str">
-        <x:v>上榜15次</x:v>
+        <x:v>上榜16次</x:v>
       </x:c>
       <x:c r="B43" s="11" t="n">
         <x:v>6</x:v>
@@ -1528,276 +1528,276 @@
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="10" t="str">
-        <x:v>上榜14次</x:v>
+        <x:v>上榜15次</x:v>
       </x:c>
       <x:c r="B44" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C44" s="11" t="str">
-        <x:v>0.8%</x:v>
+        <x:v>0.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="10" t="str">
-        <x:v>上榜13次</x:v>
+        <x:v>上榜14次</x:v>
       </x:c>
       <x:c r="B45" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C45" s="11" t="str">
-        <x:v>0.7%</x:v>
+        <x:v>0.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="10" t="str">
-        <x:v>上榜12次</x:v>
+        <x:v>上榜13次</x:v>
       </x:c>
       <x:c r="B46" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C46" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>0.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="10" t="str">
-        <x:v>上榜11次</x:v>
+        <x:v>上榜12次</x:v>
       </x:c>
       <x:c r="B47" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C47" s="11" t="str">
-        <x:v>0.8%</x:v>
+        <x:v>0.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="10" t="str">
-        <x:v>上榜10次</x:v>
+        <x:v>上榜11次</x:v>
       </x:c>
       <x:c r="B48" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C48" s="11" t="str">
-        <x:v>1.3%</x:v>
+        <x:v>0.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="10" t="str">
-        <x:v>上榜9次</x:v>
+        <x:v>上榜10次</x:v>
       </x:c>
       <x:c r="B49" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C49" s="11" t="str">
-        <x:v>1.6%</x:v>
+        <x:v>1.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="10" t="str">
-        <x:v>上榜8次</x:v>
+        <x:v>上榜9次</x:v>
       </x:c>
       <x:c r="B50" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C50" s="11" t="str">
-        <x:v>2.5%</x:v>
+        <x:v>1.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="10" t="str">
-        <x:v>上榜7次</x:v>
+        <x:v>上榜8次</x:v>
       </x:c>
       <x:c r="B51" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C51" s="11" t="str">
-        <x:v>2.0%</x:v>
+        <x:v>2.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="10" t="str">
-        <x:v>上榜6次</x:v>
+        <x:v>上榜7次</x:v>
       </x:c>
       <x:c r="B52" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C52" s="11" t="str">
-        <x:v>3.8%</x:v>
+        <x:v>2.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="10" t="str">
-        <x:v>上榜5次</x:v>
+        <x:v>上榜6次</x:v>
       </x:c>
       <x:c r="B53" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C53" s="11" t="str">
-        <x:v>4.1%</x:v>
+        <x:v>3.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="10" t="str">
-        <x:v>上榜4次</x:v>
+        <x:v>上榜5次</x:v>
       </x:c>
       <x:c r="B54" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C54" s="11" t="str">
-        <x:v>5.7%</x:v>
+        <x:v>4.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="10" t="str">
-        <x:v>上榜3次</x:v>
+        <x:v>上榜4次</x:v>
       </x:c>
       <x:c r="B55" s="11" t="n">
-        <x:v>210</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C55" s="11" t="str">
-        <x:v>11.1%</x:v>
+        <x:v>5.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="10" t="str">
-        <x:v>上榜2次</x:v>
+        <x:v>上榜3次</x:v>
       </x:c>
       <x:c r="B56" s="11" t="n">
-        <x:v>357</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C56" s="11" t="str">
-        <x:v>18.9%</x:v>
+        <x:v>11.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="10" t="str">
+        <x:v>上榜2次</x:v>
+      </x:c>
+      <x:c r="B57" s="11" t="n">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="C57" s="11" t="str">
+        <x:v>18.9%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="10" t="str">
         <x:v>上榜1次</x:v>
       </x:c>
-      <x:c r="B57" s="11" t="n">
-        <x:v>832</x:v>
-      </x:c>
-      <x:c r="C57" s="11" t="str">
-        <x:v>44.0%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" ht="22" customHeight="1">
-      <x:c r="A59" s="14" t="str">
+      <x:c r="B58" s="11" t="n">
+        <x:v>834</x:v>
+      </x:c>
+      <x:c r="C58" s="11" t="str">
+        <x:v>43.9%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="22" customHeight="1">
+      <x:c r="A60" s="14" t="str">
         <x:v>版权类型分布</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" ht="24" customHeight="1">
-      <x:c r="A60" s="5" t="str">
+    <x:row r="61" ht="24" customHeight="1">
+      <x:c r="A61" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B60" t="str">
+      <x:c r="B61" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C60" t="str">
+      <x:c r="C61" t="str">
         <x:v>占比</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61">
-      <x:c r="A61" s="10" t="str">
-        <x:v>CP自营</x:v>
-      </x:c>
-      <x:c r="B61" s="11" t="n">
-        <x:v>1186</x:v>
-      </x:c>
-      <x:c r="C61" s="11" t="str">
-        <x:v>62.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>CP自营</x:v>
       </x:c>
       <x:c r="B62" s="11" t="n">
-        <x:v>694</x:v>
+        <x:v>1186</x:v>
       </x:c>
       <x:c r="C62" s="11" t="str">
-        <x:v>36.7%</x:v>
+        <x:v>62.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="10" t="str">
-        <x:v>CP托管</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="B63" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="C63" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>36.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="10" t="str">
+        <x:v>CP托管</x:v>
+      </x:c>
+      <x:c r="B64" s="11" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C64" s="11" t="str">
+        <x:v>0.6%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="10" t="str">
         <x:v>番茄原创</x:v>
       </x:c>
-      <x:c r="B64" s="11" t="n">
+      <x:c r="B65" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C64" s="11" t="str">
+      <x:c r="C65" s="11" t="str">
         <x:v>0.1%</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" ht="22" customHeight="1">
-      <x:c r="A66" s="14" t="str">
+    <x:row r="67" ht="22" customHeight="1">
+      <x:c r="A67" s="14" t="str">
         <x:v>发布抖音号TOP15·上榜次数</x:v>
       </x:c>
     </x:row>
-    <x:row r="67" ht="24" customHeight="1">
-      <x:c r="A67" s="5" t="str">
+    <x:row r="68" ht="24" customHeight="1">
+      <x:c r="A68" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B67" t="str">
+      <x:c r="B68" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C67" t="str">
+      <x:c r="C68" t="str">
         <x:v>占比</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68">
-      <x:c r="A68" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
-      </x:c>
-      <x:c r="B68" s="11" t="n">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C68" s="11" t="str">
-        <x:v>1.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="10" t="str">
-        <x:v>番荔枝剧场</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="B69" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C69" s="11" t="str">
-        <x:v>1%</x:v>
+        <x:v>1.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>番荔枝剧场</x:v>
       </x:c>
       <x:c r="B70" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C70" s="11" t="str">
-        <x:v>0.9%</x:v>
+        <x:v>1%</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="10" t="str">
-        <x:v>渲渲动画</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="B71" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C71" s="11" t="str">
-        <x:v>0.8%</x:v>
+        <x:v>0.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -1805,7 +1805,7 @@
         <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="B72" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C72" s="11" t="str">
         <x:v>0.8%</x:v>
@@ -1813,7 +1813,7 @@
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>渲渲动画</x:v>
       </x:c>
       <x:c r="B73" s="11" t="n">
         <x:v>47</x:v>
@@ -1824,21 +1824,21 @@
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="10" t="str">
-        <x:v>阅友动漫</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="B74" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C74" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>0.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="10" t="str">
-        <x:v>左手良画</x:v>
+        <x:v>阅友动漫</x:v>
       </x:c>
       <x:c r="B75" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C75" s="11" t="str">
         <x:v>0.6%</x:v>
@@ -1846,10 +1846,10 @@
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="10" t="str">
-        <x:v>东山啊</x:v>
+        <x:v>左手良画</x:v>
       </x:c>
       <x:c r="B76" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C76" s="11" t="str">
         <x:v>0.6%</x:v>
@@ -1857,10 +1857,10 @@
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>东山啊</x:v>
       </x:c>
       <x:c r="B77" s="11" t="n">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C77" s="11" t="str">
         <x:v>0.6%</x:v>
@@ -1868,18 +1868,18 @@
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="10" t="str">
-        <x:v>在下轻北</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="B78" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C78" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>在下轻北</x:v>
       </x:c>
       <x:c r="B79" s="11" t="n">
         <x:v>30</x:v>
@@ -1890,10 +1890,10 @@
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="10" t="str">
-        <x:v>壹琚-娜娜看剧</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="B80" s="11" t="n">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C80" s="11" t="str">
         <x:v>0.5%</x:v>
@@ -1901,7 +1901,7 @@
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="10" t="str">
-        <x:v>腿毛漫漫</x:v>
+        <x:v>壹琚-娜娜看剧</x:v>
       </x:c>
       <x:c r="B81" s="11" t="n">
         <x:v>29</x:v>
@@ -1912,67 +1912,67 @@
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="10" t="str">
-        <x:v>茉冉漫影</x:v>
+        <x:v>腿毛漫漫</x:v>
       </x:c>
       <x:c r="B82" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C82" s="11" t="str">
         <x:v>0.5%</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="22" customHeight="1">
-      <x:c r="A84" s="14" t="str">
+    <x:row r="83">
+      <x:c r="A83" s="10" t="str">
+        <x:v>茉冉漫影</x:v>
+      </x:c>
+      <x:c r="B83" s="11" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C83" s="11" t="str">
+        <x:v>0.5%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="22" customHeight="1">
+      <x:c r="A85" s="14" t="str">
         <x:v>发布抖音号TOP15·上榜剧数</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" ht="24" customHeight="1">
-      <x:c r="A85" s="5" t="str">
+    <x:row r="86" ht="24" customHeight="1">
+      <x:c r="A86" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B85" t="str">
+      <x:c r="B86" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C85" t="str">
+      <x:c r="C86" t="str">
         <x:v>占比</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86">
-      <x:c r="A86" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
-      </x:c>
-      <x:c r="B86" s="11" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C86" s="11" t="str">
-        <x:v>1.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="B87" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C87" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>1.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="B88" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C88" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="10" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="B89" s="11" t="n">
         <x:v>9</x:v>
@@ -1983,7 +1983,7 @@
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="10" t="str">
-        <x:v>星漫世界</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="B90" s="11" t="n">
         <x:v>9</x:v>
@@ -1994,18 +1994,18 @@
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>星漫世界</x:v>
       </x:c>
       <x:c r="B91" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C91" s="11" t="str">
-        <x:v>0.4%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="10" t="str">
-        <x:v>番荔枝剧场</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="B92" s="11" t="n">
         <x:v>7</x:v>
@@ -2016,7 +2016,7 @@
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="10" t="str">
-        <x:v>糖糖动漫剧场</x:v>
+        <x:v>番荔枝剧场</x:v>
       </x:c>
       <x:c r="B93" s="11" t="n">
         <x:v>7</x:v>
@@ -2027,7 +2027,7 @@
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="10" t="str">
-        <x:v>潮汐互娱-爽剧社</x:v>
+        <x:v>糖糖动漫剧场</x:v>
       </x:c>
       <x:c r="B94" s="11" t="n">
         <x:v>7</x:v>
@@ -2038,18 +2038,18 @@
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="10" t="str">
-        <x:v>渲渲动画</x:v>
+        <x:v>潮汐互娱-爽剧社</x:v>
       </x:c>
       <x:c r="B95" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C95" s="11" t="str">
-        <x:v>0.3%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="10" t="str">
-        <x:v>星漫动漫剧场</x:v>
+        <x:v>渲渲动画</x:v>
       </x:c>
       <x:c r="B96" s="11" t="n">
         <x:v>6</x:v>
@@ -2060,7 +2060,7 @@
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="10" t="str">
-        <x:v>阅友动漫</x:v>
+        <x:v>星漫动漫剧场</x:v>
       </x:c>
       <x:c r="B97" s="11" t="n">
         <x:v>6</x:v>
@@ -2071,7 +2071,7 @@
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="10" t="str">
-        <x:v>腿毛漫漫</x:v>
+        <x:v>阅友动漫</x:v>
       </x:c>
       <x:c r="B98" s="11" t="n">
         <x:v>6</x:v>
@@ -2082,7 +2082,7 @@
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>腿毛漫漫</x:v>
       </x:c>
       <x:c r="B99" s="11" t="n">
         <x:v>6</x:v>
@@ -2093,7 +2093,7 @@
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="10" t="str">
-        <x:v>云间漫剧-玉川</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="B100" s="11" t="n">
         <x:v>6</x:v>
@@ -2102,91 +2102,91 @@
         <x:v>0.3%</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" ht="22" customHeight="1">
-      <x:c r="A102" s="14" t="str">
+    <x:row r="101">
+      <x:c r="A101" s="10" t="str">
+        <x:v>云间漫剧-玉川</x:v>
+      </x:c>
+      <x:c r="B101" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C101" s="11" t="str">
+        <x:v>0.3%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="22" customHeight="1">
+      <x:c r="A103" s="14" t="str">
         <x:v>付费榜主题分布</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" ht="24" customHeight="1">
-      <x:c r="A103" s="5" t="str">
+    <x:row r="104" ht="24" customHeight="1">
+      <x:c r="A104" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B103" t="str">
+      <x:c r="B104" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C103" t="str">
+      <x:c r="C104" t="str">
         <x:v>占比</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="104">
-      <x:c r="A104" s="10" t="str">
-        <x:v>婚姻/情感</x:v>
-      </x:c>
-      <x:c r="B104" s="11" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C104" s="11" t="str">
-        <x:v>19.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="10" t="str">
-        <x:v>家庭伦理/萌宝</x:v>
+        <x:v>婚姻/情感</x:v>
       </x:c>
       <x:c r="B105" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C105" s="11" t="str">
-        <x:v>15.0%</x:v>
+        <x:v>19.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>家庭伦理/萌宝</x:v>
       </x:c>
       <x:c r="B106" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C106" s="11" t="str">
-        <x:v>10.0%</x:v>
+        <x:v>15.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="B107" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C107" s="11" t="str">
-        <x:v>9.0%</x:v>
+        <x:v>10.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="10" t="str">
-        <x:v>年代怀旧/种田</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="B108" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C108" s="11" t="str">
-        <x:v>7.0%</x:v>
+        <x:v>9.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="10" t="str">
-        <x:v>现实反转/人性</x:v>
+        <x:v>年代怀旧/种田</x:v>
       </x:c>
       <x:c r="B109" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C109" s="11" t="str">
-        <x:v>6.0%</x:v>
+        <x:v>7.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="10" t="str">
-        <x:v>战神/异能</x:v>
+        <x:v>现实反转/人性</x:v>
       </x:c>
       <x:c r="B110" s="11" t="n">
         <x:v>6</x:v>
@@ -2197,12 +2197,23 @@
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="10" t="str">
+        <x:v>战神/异能</x:v>
+      </x:c>
+      <x:c r="B111" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C111" s="11" t="str">
+        <x:v>6.0%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="10" t="str">
         <x:v>美食治愈</x:v>
       </x:c>
-      <x:c r="B111" s="11" t="n">
+      <x:c r="B112" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C111" s="11" t="str">
+      <x:c r="C112" s="11" t="str">
         <x:v>5.0%</x:v>
       </x:c>
     </x:row>
@@ -2212,10 +2223,10 @@
     <x:mergeCell ref="A7:C7"/>
     <x:mergeCell ref="A14:C14"/>
     <x:mergeCell ref="A27:C27"/>
-    <x:mergeCell ref="A59:C59"/>
-    <x:mergeCell ref="A66:C66"/>
-    <x:mergeCell ref="A84:C84"/>
-    <x:mergeCell ref="A102:C102"/>
+    <x:mergeCell ref="A60:C60"/>
+    <x:mergeCell ref="A67:C67"/>
+    <x:mergeCell ref="A85:C85"/>
+    <x:mergeCell ref="A103:C103"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2323,13 +2334,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
-        <x:v>糯糯下山，师兄们都慌了第三季</x:v>
+        <x:v>敢泼我馄饨，整条街都别要了</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>09-17 00:06</x:v>
+        <x:v>09-16 10:00</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str"/>
       <x:c r="F3" s="11" t="str"/>
@@ -2340,7 +2351,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I3" s="11" t="n">
-        <x:v>152</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str">
         <x:v>其他</x:v>
@@ -2349,10 +2360,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L3" s="11" t="str">
-        <x:v>青椒剪辑</x:v>
+        <x:v>治愈 AI 恋</x:v>
       </x:c>
       <x:c r="M3" s="10" t="str">
-        <x:v>六岁那年，云糯糯被师父派下山历练，顺便寻找失散多年的五位师兄。她本以为师兄们只是普通修士，生活过得不太好。可随着她一路寻找，才发现大师兄竟是镇压天下的九天仙尊，二师兄是统御九幽的魔界帝君，三师兄是丹道圣人。小奶娃背着一柄破旧黑铁巨剑，带着上古异兽，一路闯荡修仙界，顺手把五位绝世大佬师兄全部喊回了家。</x:v>
+        <x:v>南桥旧街投资人许总多年悉心扶持一众商户，给予租金减免与基建投入，可赵川等人却贪念作祟，撕毁协议，还刻意编造谎言煽动网络暴力。面对恩将仇报的局面，许总没有冲动行事，而是恪守契约精神，凭借完备证据通过合法途径理性维权。随着真相公之于众，造谣闹事者自食恶果，承担起违约带来的相应代价。旧街完成焕新升级，充分彰显出法律与规则守护公平正义的强大力量。</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2360,13 +2371,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
-        <x:v>敢泼我馄饨，整条街都别要了</x:v>
+        <x:v>糯糯下山，师兄们都慌了第三季</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>09-16 10:00</x:v>
+        <x:v>09-17 00:06</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str"/>
       <x:c r="F4" s="11" t="str"/>
@@ -2377,7 +2388,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I4" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="J4" s="10" t="str">
         <x:v>其他</x:v>
@@ -2386,10 +2397,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L4" s="11" t="str">
-        <x:v>治愈 AI 恋</x:v>
+        <x:v>青椒剪辑</x:v>
       </x:c>
       <x:c r="M4" s="10" t="str">
-        <x:v>南桥旧街投资人许总多年悉心扶持一众商户，给予租金减免与基建投入，可赵川等人却贪念作祟，撕毁协议，还刻意编造谎言煽动网络暴力。面对恩将仇报的局面，许总没有冲动行事，而是恪守契约精神，凭借完备证据通过合法途径理性维权。随着真相公之于众，造谣闹事者自食恶果，承担起违约带来的相应代价。旧街完成焕新升级，充分彰显出法律与规则守护公平正义的强大力量。</x:v>
+        <x:v>六岁那年，云糯糯被师父派下山历练，顺便寻找失散多年的五位师兄。她本以为师兄们只是普通修士，生活过得不太好。可随着她一路寻找，才发现大师兄竟是镇压天下的九天仙尊，二师兄是统御九幽的魔界帝君，三师兄是丹道圣人。小奶娃背着一柄破旧黑铁巨剑，带着上古异兽，一路闯荡修仙界，顺手把五位绝世大佬师兄全部喊回了家。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2397,13 +2408,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
-        <x:v>霁月安遥之以余生为诺护你岁岁无忧第一季</x:v>
+        <x:v>老板砍薪，我买下酒楼</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>09-16 06:06</x:v>
+        <x:v>09-15 18:11</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str"/>
       <x:c r="F5" s="11" t="str"/>
@@ -2414,19 +2425,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I5" s="11" t="n">
-        <x:v>144</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="J5" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K5" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="L5" s="11" t="str">
-        <x:v>花花说漫</x:v>
+        <x:v>逸漫</x:v>
       </x:c>
       <x:c r="M5" s="10" t="str">
-        <x:v>22岁的医大学生辛知遥意外与大学教授周霁结缘，步入婚姻。初时二人的结合源于一场意外，彼此尚有距离。婚后辛知遥一边完成繁重的学业，一边适应全新的家庭生活。她挣脱原生家庭带来的压抑与束缚，学着正视内心、勇敢表达自我。周霁沉稳体贴，给予她尊重、陪伴与满满的安全感。二人在朝夕相处中慢慢卸下防备，从责任走向真心，携手面对生活里的重重风波，互相扶持，奔赴温暖安稳的幸福生活。</x:v>
+        <x:v>在美娟大酒楼掌勺十五年的林桂芬，因待遇调整选择离开。面对场地偏远和客户观望，她从老粮库重新起步，凭过硬手艺与真诚待客赢回乡亲认可。从十二桌寿宴到四十桌婚宴，生意越做越红火。后来，她再次走进昔日酒楼，这一次，不是回来打工，而是带着自己的招牌开启新生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2434,13 +2445,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>老板砍薪，我买下酒楼</x:v>
+        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>09-15 18:11</x:v>
+        <x:v>09-15 08:00</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str"/>
       <x:c r="F6" s="11" t="str"/>
@@ -2451,19 +2462,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I6" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J6" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K6" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="L6" s="11" t="str">
-        <x:v>逸漫</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="M6" s="10" t="str">
-        <x:v>在美娟大酒楼掌勺十五年的林桂芬，因待遇调整选择离开。面对场地偏远和客户观望，她从老粮库重新起步，凭过硬手艺与真诚待客赢回乡亲认可。从十二桌寿宴到四十桌婚宴，生意越做越红火。后来，她再次走进昔日酒楼，这一次，不是回来打工，而是带着自己的招牌开启新生活。</x:v>
+        <x:v>沈清韵嫁入靖王府三年，王爷冷落，侧妃得宠。王爷当众许诺，谁先诞下儿子，便请封世子。苏氏先怀孕，沈清韵却发现自己怀的是龙凤胎，她隐瞒消息，买通太医推迟产期，忍痛让苏氏先产子。王爷果然请封庶长子为世子，折子递入宗人府。受理之后，沈清韵才发动，生下龙凤胎。太后与皇上视为祥瑞，下旨赐嫡子承恩为靖王世子、嫡女承华为安乐郡主。王爷措手不及，苏氏地位一落千丈。而沈清韵知道，这只是第一步。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2471,7 +2482,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
         <x:v>重回雪崩泥石流，我不再犹豫</x:v>
@@ -2508,13 +2519,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
-        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
+        <x:v>萌娃兽语满级，动物园天天爆红</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>09-15 08:00</x:v>
+        <x:v>09-16 10:00</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str"/>
       <x:c r="F8" s="11" t="str"/>
@@ -2525,19 +2536,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="J8" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K8" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>萌宝治愈 / 战神异能</x:v>
       </x:c>
       <x:c r="L8" s="11" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>一口漫剧</x:v>
       </x:c>
       <x:c r="M8" s="10" t="str">
-        <x:v>沈清韵嫁入靖王府三年，王爷冷落，侧妃得宠。王爷当众许诺，谁先诞下儿子，便请封世子。苏氏先怀孕，沈清韵却发现自己怀的是龙凤胎，她隐瞒消息，买通太医推迟产期，忍痛让苏氏先产子。王爷果然请封庶长子为世子，折子递入宗人府。受理之后，沈清韵才发动，生下龙凤胎。太后与皇上视为祥瑞，下旨赐嫡子承恩为靖王世子、嫡女承华为安乐郡主。王爷措手不及，苏氏地位一落千丈。而沈清韵知道，这只是第一步。</x:v>
+        <x:v>八岁女孩汤圆拥有听懂动物语言的特殊能力，助力濒临倒闭的自家动物园破局重生。她读懂动物的内心诉求，化解人与动物之间的认知误解，坚守科学救助理念，拒绝猎奇表演。动物园成为科普教育阵地，传递尊重生命、人与自然和谐共生的理念，以孩童的善意守护生灵，诠释新时代少年的社会担当。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -2545,13 +2556,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
-        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
+        <x:v>我把真心留给真心的人</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>09-15 08:30</x:v>
+        <x:v>09-16 11:20</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str"/>
       <x:c r="F9" s="11" t="str"/>
@@ -2562,7 +2573,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I9" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J9" s="10" t="str">
         <x:v>其他</x:v>
@@ -2571,10 +2582,10 @@
         <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L9" s="11" t="str">
-        <x:v>琥珀漫剧</x:v>
+        <x:v>逆命漫剧场</x:v>
       </x:c>
       <x:c r="M9" s="10" t="str">
-        <x:v>海鲜市场老手陈放，因一个两块钱的冰袋被十二年合伙人当众算旧账，心寒清账，净身出户。他没有抱怨，也没有以牙还牙，而是加入冷清档口“梅姐水产”，从零开始。他坚持明码标价、沥水称重、死活分卖、批次可查，宁可少接单，也不混货、不凑数、不赚亏心钱。面对低价抢客、恶意破坏、临时缺货等风波，他与叶梅靠诚信、规矩和彼此信任，一步步赢得客户与连锁企业的认可。</x:v>
+        <x:v>失散二十年的方小树意外归家，却被大哥二姐当成乞丐嫌弃，唯有三姐方秀兰护着他。一次受伤让他恢复记忆，为看清人心，他选择继续装傻。面对亲人的贪婪算计、骗钱逼婚与恶意陷害，小树一次次反击，也因救命之恩得到顾家、沈家相助，并与沈清月渐生真情。最终，他揭开被拐真相，惩治恶人，守住亲情与爱情，迎来人生逆袭。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -2582,13 +2593,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>35</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
-        <x:v>情深错付</x:v>
+        <x:v>霁月安遥之以余生为诺护你岁岁无忧第一季</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>09-15 15:27</x:v>
+        <x:v>09-16 06:06</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str"/>
       <x:c r="F10" s="11" t="str"/>
@@ -2599,19 +2610,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I10" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="J10" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K10" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L10" s="11" t="str">
-        <x:v>沐光剧场</x:v>
+        <x:v>花花说漫</x:v>
       </x:c>
       <x:c r="M10" s="10" t="str">
-        <x:v>苏橙橙倒追陆深两年，却始终没等来一句承认。一次争执后，她被当众羞辱，车祸重伤时更亲眼看见陆深先救走白月光李芸。彻底清醒后，她拉黑、离职、离城，重新开始。等陆深终于看清真心、拼命追回时，她早已放下。三年后重逢，他以为她已结婚生子，最终带着遗憾彻底错过。</x:v>
+        <x:v>22岁的医大学生辛知遥意外与大学教授周霁结缘，步入婚姻。初时二人的结合源于一场意外，彼此尚有距离。婚后辛知遥一边完成繁重的学业，一边适应全新的家庭生活。她挣脱原生家庭带来的压抑与束缚，学着正视内心、勇敢表达自我。周霁沉稳体贴，给予她尊重、陪伴与满满的安全感。二人在朝夕相处中慢慢卸下防备，从责任走向真心，携手面对生活里的重重风波，互相扶持，奔赴温暖安稳的幸福生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -2619,7 +2630,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="10" t="str">
         <x:v>我都元婴期了，你跟我说开学</x:v>
@@ -2656,10 +2667,10 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
-        <x:v>瘦身归来，前男友悔不当初</x:v>
+        <x:v>一墙隔冷暖，五年借暖终归零</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
         <x:v>2026-09-16</x:v>
@@ -2677,7 +2688,7 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="K12" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L12" s="11" t="str"/>
       <x:c r="M12" s="10" t="str"/>
@@ -2687,13 +2698,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B13" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
-        <x:v>一墙隔冷暖，五年借暖终归零</x:v>
+        <x:v>一块冰袋，冻凉十二年合伙情</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>09-15 08:30</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str"/>
       <x:c r="F13" s="11" t="str"/>
@@ -2703,28 +2714,34 @@
       <x:c r="H13" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I13" s="11" t="str"/>
+      <x:c r="I13" s="11" t="n">
+        <x:v>70</x:v>
+      </x:c>
       <x:c r="J13" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K13" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L13" s="11" t="str"/>
-      <x:c r="M13" s="10" t="str"/>
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="L13" s="11" t="str">
+        <x:v>琥珀漫剧</x:v>
+      </x:c>
+      <x:c r="M13" s="10" t="str">
+        <x:v>海鲜市场老手陈放，因一个两块钱的冰袋被十二年合伙人当众算旧账，心寒清账，净身出户。他没有抱怨，也没有以牙还牙，而是加入冷清档口“梅姐水产”，从零开始。他坚持明码标价、沥水称重、死活分卖、批次可查，宁可少接单，也不混货、不凑数、不赚亏心钱。面对低价抢客、恶意破坏、临时缺货等风波，他与叶梅靠诚信、规矩和彼此信任，一步步赢得客户与连锁企业的认可。</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B14" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
-        <x:v>我把真心留给真心的人</x:v>
+        <x:v>重生归来，只为守护她</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>09-16 11:20</x:v>
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str"/>
       <x:c r="F14" s="11" t="str"/>
@@ -2734,34 +2751,28 @@
       <x:c r="H14" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I14" s="11" t="n">
-        <x:v>72</x:v>
-      </x:c>
+      <x:c r="I14" s="11" t="str"/>
       <x:c r="J14" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K14" s="10" t="str">
-        <x:v>婚姻情感</x:v>
-      </x:c>
-      <x:c r="L14" s="11" t="str">
-        <x:v>逆命漫剧场</x:v>
-      </x:c>
-      <x:c r="M14" s="10" t="str">
-        <x:v>失散二十年的方小树意外归家，却被大哥二姐当成乞丐嫌弃，唯有三姐方秀兰护着他。一次受伤让他恢复记忆，为看清人心，他选择继续装傻。面对亲人的贪婪算计、骗钱逼婚与恶意陷害，小树一次次反击，也因救命之恩得到顾家、沈家相助，并与沈清月渐生真情。最终，他揭开被拐真相，惩治恶人，守住亲情与爱情，迎来人生逆袭。</x:v>
-      </x:c>
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="L14" s="11" t="str"/>
+      <x:c r="M14" s="10" t="str"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B15" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
-        <x:v>萌娃兽语满级，动物园天天爆红</x:v>
+        <x:v>重生第七节车厢</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
-        <x:v>09-16 10:00</x:v>
+        <x:v>09-16 11:39</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str"/>
       <x:c r="F15" s="11" t="str"/>
@@ -2772,19 +2783,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I15" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J15" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K15" s="10" t="str">
-        <x:v>萌宝治愈 / 战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L15" s="11" t="str">
-        <x:v>一口漫剧</x:v>
+        <x:v>千一剧场</x:v>
       </x:c>
       <x:c r="M15" s="10" t="str">
-        <x:v>八岁女孩汤圆拥有听懂动物语言的特殊能力，助力濒临倒闭的自家动物园破局重生。她读懂动物的内心诉求，化解人与动物之间的认知误解，坚守科学救助理念，拒绝猎奇表演。动物园成为科普教育阵地，传递尊重生命、人与自然和谐共生的理念，以孩童的善意守护生灵，诠释新时代少年的社会担当。</x:v>
+        <x:v>高铁列车长林铮死过一次。上一世，四名大学生私带危险实验样品登车，一句“毒倒整节车厢”的戏言被他放行，最终隧道内毒气泄漏，全车罹难，他成了千夫所指的责任人。重回发车前最后一分钟，他顶住求情、质疑与全网非议，硬封第七节车厢，叫停整趟列车。层层戳破瞒报的谎言，这一次，他死守安全红线，要让车上一千零八十六人，全都平安抵达终点。</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2792,13 +2803,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>44</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C16" s="10" t="str">
-        <x:v>有米偏要讨三场雨</x:v>
+        <x:v>养娃记：八零四合院生活日常</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
-        <x:v>09-16 08:18</x:v>
+        <x:v>09-15 01:11</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str"/>
       <x:c r="F16" s="11" t="str"/>
@@ -2809,19 +2820,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I16" s="11" t="n">
-        <x:v>98</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="J16" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K16" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧 / 萌宝治愈</x:v>
       </x:c>
       <x:c r="L16" s="11" t="str">
-        <x:v>剧有米</x:v>
+        <x:v>香菜薯片</x:v>
       </x:c>
       <x:c r="M16" s="10" t="str">
-        <x:v>青石村大旱三月，全村跪求龙王赐雨，四岁的有米却爬上供桌，张口就说龙王敖澜欠她三场雨。为了讨债，她扣雨牌、锁水门、放掉偷接的水、挖通公沟，还把只认天规的敖澜一次次拖进人间麻烦。暴风、山火和争水接连袭来，有米也在一次次选择中让周守财和全村学会先顾人、再顾利。三场雨终于还清，青石村重新秋种，山外却传来石狮异响，新的怪事又找上了她。</x:v>
+        <x:v>儿女已经成家立业，送走公公婆婆后，正准备全国游的六十多岁老太太赵锦舒重生了。重回到刚进城几个月时，那时什么都不懂，乡下来的年轻小媳妇脸皮薄，抹不开面子，也自卑，哪怕男人能挣钱，面对有权有势的婆家人，也自觉低人一头，更怕出错，给男人丢脸，很长一段时间都不敢多说一句话，明里暗里娘三个受了不少委屈。回到年轻时，赵锦舒老黄瓜刷绿漆，不管外表如何，内里都是老姜疙瘩，装不来腼腆小媳妇。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -2829,13 +2840,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C17" s="10" t="str">
-        <x:v>七零：穿成锦鲤文里的炮灰女配</x:v>
+        <x:v>情深错付</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
-        <x:v>09-16 17:00</x:v>
+        <x:v>09-15 15:27</x:v>
       </x:c>
       <x:c r="E17" s="11" t="str"/>
       <x:c r="F17" s="11" t="str"/>
@@ -2846,19 +2857,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I17" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="J17" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K17" s="10" t="str">
-        <x:v>年代怀旧 / 战神异能</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L17" s="11" t="str">
-        <x:v>小树动漫剧场</x:v>
+        <x:v>沐光剧场</x:v>
       </x:c>
       <x:c r="M17" s="10" t="str">
-        <x:v>现代女孩温梨穿越到七十年代小说，成为结局悲惨的炮灰女配，她抢先激活沉香木牌中的灵泉空间，凭借敏锐察觉化解列车上的重大隐患，得到官方表彰，为下乡做好铺垫；来到红星公社后，温梨依靠灵泉水强化体质，不再被白眼狼郭彩霞道德绑架，还截胡了本该属于女主姜月儿的机缘，她一边下地挣工分，一边利用空间物资在黑市与顾淮合作，面对姜月儿、江辰等人的屡次算计构陷，温梨从容反击，结识神秘知青陆泽川，改写自己注定悲剧的命运。</x:v>
+        <x:v>苏橙橙倒追陆深两年，却始终没等来一句承认。一次争执后，她被当众羞辱，车祸重伤时更亲眼看见陆深先救走白月光李芸。彻底清醒后，她拉黑、离职、离城，重新开始。等陆深终于看清真心、拼命追回时，她早已放下。三年后重逢，他以为她已结婚生子，最终带着遗憾彻底错过。</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -2866,13 +2877,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>82</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C18" s="10" t="str">
-        <x:v>八媳妇只想买包，一不小心拯救了全家</x:v>
+        <x:v>七零：穿成锦鲤文里的炮灰女配</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>09-16 10:00</x:v>
+        <x:v>09-16 17:00</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str"/>
       <x:c r="F18" s="11" t="str"/>
@@ -2883,19 +2894,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I18" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="J18" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K18" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧 / 战神异能</x:v>
       </x:c>
       <x:c r="L18" s="11" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>小树动漫剧场</x:v>
       </x:c>
       <x:c r="M18" s="10" t="str">
-        <x:v>顾家八位儿媳皆各有所长。大嫂秦蕴章深耕华尔街并购领域，二嫂林疏桐是风投行业的杰出从业者。晏姝岚平日生活低调随性，外界便对她产生片面认知，认为她只注重物质消费。实际上，晏姝岚来自底蕴更为深厚的大家族。当顾氏集团遭遇多家境外企业联合围堵，经营陷入巨大危机。顾家公公心力交瘁，能力出众的嫂嫂们多方调动资源，依旧难以摸清对手的真实布局。在对手步步施压的危急时刻，晏姝岚挺身而出，守护顾家渡过这场商业危机。</x:v>
+        <x:v>现代女孩温梨穿越到七十年代小说，成为结局悲惨的炮灰女配，她抢先激活沉香木牌中的灵泉空间，凭借敏锐察觉化解列车上的重大隐患，得到官方表彰，为下乡做好铺垫；来到红星公社后，温梨依靠灵泉水强化体质，不再被白眼狼郭彩霞道德绑架，还截胡了本该属于女主姜月儿的机缘，她一边下地挣工分，一边利用空间物资在黑市与顾淮合作，面对姜月儿、江辰等人的屡次算计构陷，温梨从容反击，结识神秘知青陆泽川，改写自己注定悲剧的命运。</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -2903,7 +2914,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>84</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C19" s="10" t="str">
         <x:v>说好九十天就回来，我不等了</x:v>
@@ -2940,13 +2951,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>89</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C20" s="10" t="str">
-        <x:v>重生第七节车厢</x:v>
+        <x:v>有米偏要讨三场雨</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>09-16 11:39</x:v>
+        <x:v>09-16 08:18</x:v>
       </x:c>
       <x:c r="E20" s="11" t="str"/>
       <x:c r="F20" s="11" t="str"/>
@@ -2957,7 +2968,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I20" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="J20" s="10" t="str">
         <x:v>其他</x:v>
@@ -2966,10 +2977,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L20" s="11" t="str">
-        <x:v>千一剧场</x:v>
+        <x:v>剧有米</x:v>
       </x:c>
       <x:c r="M20" s="10" t="str">
-        <x:v>高铁列车长林铮死过一次。上一世，四名大学生私带危险实验样品登车，一句“毒倒整节车厢”的戏言被他放行，最终隧道内毒气泄漏，全车罹难，他成了千夫所指的责任人。重回发车前最后一分钟，他顶住求情、质疑与全网非议，硬封第七节车厢，叫停整趟列车。层层戳破瞒报的谎言，这一次，他死守安全红线，要让车上一千零八十六人，全都平安抵达终点。</x:v>
+        <x:v>青石村大旱三月，全村跪求龙王赐雨，四岁的有米却爬上供桌，张口就说龙王敖澜欠她三场雨。为了讨债，她扣雨牌、锁水门、放掉偷接的水、挖通公沟，还把只认天规的敖澜一次次拖进人间麻烦。暴风、山火和争水接连袭来，有米也在一次次选择中让周守财和全村学会先顾人、再顾利。三场雨终于还清，青石村重新秋种，山外却传来石狮异响，新的怪事又找上了她。</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -2977,13 +2988,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C21" s="10" t="str">
-        <x:v>重生归来，只为守护她</x:v>
+        <x:v>重回失事当晚，我扣下整条跑道</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>09-17 06:08</x:v>
       </x:c>
       <x:c r="E21" s="11" t="str"/>
       <x:c r="F21" s="11" t="str"/>
@@ -2993,28 +3004,34 @@
       <x:c r="H21" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I21" s="11" t="str"/>
+      <x:c r="I21" s="11" t="n">
+        <x:v>61</x:v>
+      </x:c>
       <x:c r="J21" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K21" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
-      </x:c>
-      <x:c r="L21" s="11" t="str"/>
-      <x:c r="M21" s="10" t="str"/>
+        <x:v>年代怀旧</x:v>
+      </x:c>
+      <x:c r="L21" s="11" t="str">
+        <x:v>星漫剧院</x:v>
+      </x:c>
+      <x:c r="M21" s="10" t="str">
+        <x:v>上一世，一场诡异空难，塔台管制员谢昀含冤惨死。重生回到悲剧前夜，十五架学生无人机尽数落地，领导、师生、全网都逼她签字开放跑道。所有人都认定危险已经解除，可她笃定空域还藏着未知黑影。顶着限时命令与铺天盖地非议死扛复核。那看不见的第十六架，究竟是谁布下的致命陷阱？</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>77</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C22" s="10" t="str">
-        <x:v>鱼缸之眼</x:v>
+        <x:v>剑道：贴地武夫，谁教他练剑起飞的</x:v>
       </x:c>
       <x:c r="D22" s="11" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>09-16 17:23</x:v>
       </x:c>
       <x:c r="E22" s="11" t="str"/>
       <x:c r="F22" s="11" t="str"/>
@@ -3022,53 +3039,59 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H22" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="I22" s="11" t="str"/>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I22" s="11" t="n">
+        <x:v>140</x:v>
+      </x:c>
       <x:c r="J22" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K22" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L22" s="11" t="str"/>
-      <x:c r="M22" s="10" t="str"/>
+        <x:v>古装宫廷 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="L22" s="11" t="str">
+        <x:v>繁星剧场</x:v>
+      </x:c>
+      <x:c r="M22" s="10" t="str">
+        <x:v>八境武夫秦关遵师命下山履约，遭逢嫌弃退婚，最终娶了替嫁的病危大小姐南柔。世人皆笑他是个没丹田的废物，殊不知他乃肉身无敌的满级大佬，更暗中觉醒混沌体，剑武双修！他反手治好娇妻，助其觉醒太阴圣体。面对豪门天骄的挑衅、灵剑学院的追杀、中州刀圣的降临，乃至龙云帝国的皇权威逼，秦关皆以一双铁拳强势轰爆！管你剑皇刀圣还是九五之尊，敢惹我老婆，通通骨灰扬了！且看无敌武夫如何带着傲娇黑塔与腹黑神犬，一路护妻狂飙</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="str">
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C23" s="10" t="str">
-        <x:v>养娃记：八零四合院生活日常</x:v>
+        <x:v>浮世红痕</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
-        <x:v>09-15 01:11</x:v>
+        <x:v>09-16 07:58</x:v>
       </x:c>
       <x:c r="E23" s="11" t="str"/>
       <x:c r="F23" s="11" t="str"/>
       <x:c r="G23" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H23" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I23" s="11" t="n">
-        <x:v>191</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J23" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K23" s="10" t="str">
-        <x:v>年代怀旧 / 萌宝治愈</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L23" s="11" t="str">
-        <x:v>香菜薯片</x:v>
+        <x:v>久久漫剧</x:v>
       </x:c>
       <x:c r="M23" s="10" t="str">
-        <x:v>儿女已经成家立业，送走公公婆婆后，正准备全国游的六十多岁老太太赵锦舒重生了。重回到刚进城几个月时，那时什么都不懂，乡下来的年轻小媳妇脸皮薄，抹不开面子，也自卑，哪怕男人能挣钱，面对有权有势的婆家人，也自觉低人一头，更怕出错，给男人丢脸，很长一段时间都不敢多说一句话，明里暗里娘三个受了不少委屈。回到年轻时，赵锦舒老黄瓜刷绿漆，不管外表如何，内里都是老姜疙瘩，装不来腼腆小媳妇。</x:v>
+        <x:v>乔舒天生拥有一项特殊能力——能看见连接亲密男女的隐秘红线。她以此选定了看似专一的未婚夫陆宥泽，却在婚礼前夜，赫然发现他与自己闺蜜许澜之间缠上了红线。婚礼现场她当众揭露真相，果断终止婚约。此后她凭借异能开设“红线鉴渣工作室”，帮深陷情感疑云的人勘破真心，而更多意想不到的考验与纠葛也随之而来。</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -3076,13 +3099,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C24" s="10" t="str">
-        <x:v>晚来的圆满</x:v>
+        <x:v>守成包子铺</x:v>
       </x:c>
       <x:c r="D24" s="11" t="str">
-        <x:v>09-15 13:14</x:v>
+        <x:v>09-15 16:00</x:v>
       </x:c>
       <x:c r="E24" s="11" t="str"/>
       <x:c r="F24" s="11" t="str"/>
@@ -3093,19 +3116,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I24" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J24" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K24" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="L24" s="11" t="str">
-        <x:v>杭鹿二姐爱看剧</x:v>
+        <x:v>空白漫</x:v>
       </x:c>
       <x:c r="M24" s="10" t="str">
-        <x:v>白手起家的女企业家沈玉珍，将独子陆衍视作家族企业的唯一继承人。谁知陆衍结识顾念后性情大变，不仅执意拒绝生育、与母亲渐行渐远，还任由顾念家人插手公司事务。眼看毕生心血面临失控，沈玉珍挺身而出，以沉稳手腕化解层层危机。最终真相水落石出，顾念的图谋落空，陆衍迷途知返担起责任，沈玉珍守护住了家业，也让家庭重归温暖圆满。</x:v>
+        <x:v>周守成经营八年的早餐铺被迫搬走，熟客流失、徒弟离开，新店第一天一百多个包子无人问津。面对低价竞争和经营困境，他没有偷工减料，而是从菜贩、司机、工地和学生家长的真实需求出发，重新摸索预订与配送。靠一笼笼热包子和一次次准时守信，他终于让偏僻小店重新有了烟火气。守住一门小生意，靠的从来不是门脸，而是手艺、诚信和顾客愿意再来的信任。</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -3113,13 +3136,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C25" s="10" t="str">
-        <x:v>高考落榜，从听彩票心声开始逆袭</x:v>
+        <x:v>落魄老公别黑化，恶毒前妻来贴贴</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
-        <x:v>09-15 10:00</x:v>
+        <x:v>09-17 00:06</x:v>
       </x:c>
       <x:c r="E25" s="11" t="str"/>
       <x:c r="F25" s="11" t="str"/>
@@ -3130,19 +3153,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I25" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J25" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K25" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>家庭伦理 / 婚姻情感</x:v>
       </x:c>
       <x:c r="L25" s="11" t="str">
-        <x:v>糖糖动漫剧场</x:v>
+        <x:v>漫剧工厂</x:v>
       </x:c>
       <x:c r="M25" s="10" t="str">
-        <x:v>高考落榜的陈阳意外觉醒聆听万物心声的特殊能力。面对世俗偏见与亲友的冷眼，他没有沉沦，坚守本心脚踏实地，凭借能力识破骗局、守护家人。抓住机遇创业致富，反哺故土，助力乡村建设，伸张社会正义，用实干证明人生不止高考一条出路，诠释新时代青年的责任与担当。</x:v>
+        <x:v>江城章家破产负债，昔日千金章月被父亲安排嫁给曾受章家资助、如今落魄的江远辞。相亲时章月出言羞辱，遇债主围堵被江远辞救下，躲进简陋出租屋。章月意外觉醒金手指，靠近江远辞一米内，便能看见原著弹幕，得知对方未来会成为江城首富，自己却是凄惨的恶毒前妻。为改写命运，她主动提出领证绑定彼此。二人从互相试探的契约夫妻，摆摊谋生共渡难关，对抗外界冷眼，彼此治愈内心伤痕，从各取所需慢慢走向双向救赎真心相守。</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -3150,13 +3173,13 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B26" s="11" t="n">
-        <x:v>46</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C26" s="10" t="str">
-        <x:v>浮世红痕</x:v>
+        <x:v>被身高掩盖的谎言</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
-        <x:v>09-16 07:58</x:v>
+        <x:v>09-15 08:18</x:v>
       </x:c>
       <x:c r="E26" s="11" t="str"/>
       <x:c r="F26" s="11" t="str"/>
@@ -3164,22 +3187,22 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H26" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I26" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J26" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K26" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="L26" s="11" t="str">
-        <x:v>久久漫剧</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="M26" s="10" t="str">
-        <x:v>乔舒天生拥有一项特殊能力——能看见连接亲密男女的隐秘红线。她以此选定了看似专一的未婚夫陆宥泽，却在婚礼前夜，赫然发现他与自己闺蜜许澜之间缠上了红线。婚礼现场她当众揭露真相，果断终止婚约。此后她凭借异能开设“红线鉴渣工作室”，帮深陷情感疑云的人勘破真心，而更多意想不到的考验与纠葛也随之而来。</x:v>
+        <x:v>女孩林知晚回到命运转折的关键节点。她凭借智慧与勇气，敏锐察觉家中隐患，冷静引导家人、寻求帮助，用爱守护姐姐与全家。在共同努力下危机化解、正义伸张，一家人愈发珍视彼此，并且帮助到了更多有同样遭遇的人，最后迎来温暖安宁的幸福生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -3187,36 +3210,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B27" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C27" s="10" t="str">
-        <x:v>萌娃兽语满级，动物园天天爆红</x:v>
+        <x:v>重生第七节车厢</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
-        <x:v>09-16 10:00</x:v>
+        <x:v>09-16 11:39</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F27" s="11" t="str">
-        <x:v>↑24位</x:v>
+        <x:v>↑41位</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str"/>
       <x:c r="H27" s="11" t="str"/>
       <x:c r="I27" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J27" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K27" s="10" t="str">
-        <x:v>萌宝治愈 / 战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L27" s="11" t="str">
-        <x:v>一口漫剧</x:v>
+        <x:v>千一剧场</x:v>
       </x:c>
       <x:c r="M27" s="10" t="str">
-        <x:v>八岁女孩汤圆拥有听懂动物语言的特殊能力，助力濒临倒闭的自家动物园破局重生。她读懂动物的内心诉求，化解人与动物之间的认知误解，坚守科学救助理念，拒绝猎奇表演。动物园成为科普教育阵地，传递尊重生命、人与自然和谐共生的理念，以孩童的善意守护生灵，诠释新时代少年的社会担当。</x:v>
+        <x:v>高铁列车长林铮死过一次。上一世，四名大学生私带危险实验样品登车，一句“毒倒整节车厢”的戏言被他放行，最终隧道内毒气泄漏，全车罹难，他成了千夫所指的责任人。重回发车前最后一分钟，他顶住求情、质疑与全网非议，硬封第七节车厢，叫停整趟列车。层层戳破瞒报的谎言，这一次，他死守安全红线，要让车上一千零八十六人，全都平安抵达终点。</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -3224,36 +3247,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B28" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C28" s="10" t="str">
-        <x:v>重回雪崩泥石流，我不再犹豫</x:v>
+        <x:v>浮世红痕</x:v>
       </x:c>
       <x:c r="D28" s="11" t="str">
-        <x:v>09-16 01:02</x:v>
+        <x:v>09-16 07:58</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F28" s="11" t="str">
-        <x:v>↑23位</x:v>
+        <x:v>↑20位</x:v>
       </x:c>
       <x:c r="G28" s="11" t="str"/>
       <x:c r="H28" s="11" t="str"/>
       <x:c r="I28" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J28" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K28" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L28" s="11" t="str">
-        <x:v>姜缘</x:v>
+        <x:v>久久漫剧</x:v>
       </x:c>
       <x:c r="M28" s="10" t="str">
-        <x:v>前世，周清雨因犹豫错失逃生时机，眼睁睁看着全家被雪崩泥石流吞没。重生回灾难前三天，她当机立断卖掉五十头牦牛，囤积物资，带家人撤往高处。面对全村嘲讽和阻拦，她不再苦劝。直到雪山崩塌、洪流封村，昔日笑她疯癫的人纷纷求上门。这一次，她只救值得救的人！</x:v>
+        <x:v>乔舒天生拥有一项特殊能力——能看见连接亲密男女的隐秘红线。她以此选定了看似专一的未婚夫陆宥泽，却在婚礼前夜，赫然发现他与自己闺蜜许澜之间缠上了红线。婚礼现场她当众揭露真相，果断终止婚约。此后她凭借异能开设“红线鉴渣工作室”，帮深陷情感疑云的人勘破真心，而更多意想不到的考验与纠葛也随之而来。</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -3261,36 +3284,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B29" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C29" s="10" t="str">
-        <x:v>剑道：贴地武夫，谁教他练剑起飞的</x:v>
+        <x:v>守成包子铺</x:v>
       </x:c>
       <x:c r="D29" s="11" t="str">
-        <x:v>09-16 17:23</x:v>
+        <x:v>09-15 16:00</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>46</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F29" s="11" t="str">
-        <x:v>↑21位</x:v>
+        <x:v>↑16位</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str"/>
       <x:c r="H29" s="11" t="str"/>
       <x:c r="I29" s="11" t="n">
-        <x:v>140</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J29" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K29" s="10" t="str">
-        <x:v>古装宫廷 / 婚姻情感</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="L29" s="11" t="str">
-        <x:v>繁星剧场</x:v>
+        <x:v>空白漫</x:v>
       </x:c>
       <x:c r="M29" s="10" t="str">
-        <x:v>八境武夫秦关遵师命下山履约，遭逢嫌弃退婚，最终娶了替嫁的病危大小姐南柔。世人皆笑他是个没丹田的废物，殊不知他乃肉身无敌的满级大佬，更暗中觉醒混沌体，剑武双修！他反手治好娇妻，助其觉醒太阴圣体。面对豪门天骄的挑衅、灵剑学院的追杀、中州刀圣的降临，乃至龙云帝国的皇权威逼，秦关皆以一双铁拳强势轰爆！管你剑皇刀圣还是九五之尊，敢惹我老婆，通通骨灰扬了！且看无敌武夫如何带着傲娇黑塔与腹黑神犬，一路护妻狂飙</x:v>
+        <x:v>周守成经营八年的早餐铺被迫搬走，熟客流失、徒弟离开，新店第一天一百多个包子无人问津。面对低价竞争和经营困境，他没有偷工减料，而是从菜贩、司机、工地和学生家长的真实需求出发，重新摸索预订与配送。靠一笼笼热包子和一次次准时守信，他终于让偏僻小店重新有了烟火气。守住一门小生意，靠的从来不是门脸，而是手艺、诚信和顾客愿意再来的信任。</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -3298,67 +3321,73 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B30" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C30" s="10" t="str">
-        <x:v>重生归来，只为守护她</x:v>
+        <x:v>重生回到坠崖日，我松开了他的背包</x:v>
       </x:c>
       <x:c r="D30" s="11" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>09-17 06:35</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F30" s="11" t="str">
-        <x:v>↑20位</x:v>
+        <x:v>↑16位</x:v>
       </x:c>
       <x:c r="G30" s="11" t="str"/>
       <x:c r="H30" s="11" t="str"/>
-      <x:c r="I30" s="11" t="str"/>
+      <x:c r="I30" s="11" t="n">
+        <x:v>61</x:v>
+      </x:c>
       <x:c r="J30" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K30" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
-      </x:c>
-      <x:c r="L30" s="11" t="str"/>
-      <x:c r="M30" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L30" s="11" t="str">
+        <x:v>魔力动漫剧场</x:v>
+      </x:c>
+      <x:c r="M30" s="10" t="str">
+        <x:v>前世，丈夫陆成宇的小青梅柳婉宁意外坠崖，她拼命拉住欲冒险救人的丈夫，自己善良忍让，却反被诬陷，最终含冤离世。重生回到意外发生那天，沈知夏不再委曲求全，她选择先护住自己。此后她凭家传手艺开面馆自力更生，面对陆家的屡次刁难和误解，她不卑不亢、冷静应对，用智慧和证据化解一次次危机，最终赢得尊重，活成自己人生的主人。</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B31" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C31" s="10" t="str">
-        <x:v>高考刚结束父母就不装了</x:v>
+        <x:v>残像守桑田</x:v>
       </x:c>
       <x:c r="D31" s="11" t="str">
-        <x:v>09-15 07:00</x:v>
+        <x:v>09-16 06:10</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F31" s="11" t="str">
-        <x:v>↑19位</x:v>
+        <x:v>↑13位</x:v>
       </x:c>
       <x:c r="G31" s="11" t="str"/>
       <x:c r="H31" s="11" t="str"/>
       <x:c r="I31" s="11" t="n">
-        <x:v>173</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J31" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K31" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L31" s="11" t="str">
-        <x:v>千慕剧场</x:v>
+        <x:v>香菜动漫</x:v>
       </x:c>
       <x:c r="M31" s="10" t="str">
-        <x:v>高考结束那天，林寻在考场外被亲生父母认回原来十八年的普通生活，是父母为磨砺他而设的一场成长课。重回豪门，他没有迷失，反而在桥上遇见了那个让他心动的姑娘，南大冰山学姐苏清诗。从青涩的初次相遇，到演唱会上的合唱，再到大学校园里的朝夕相处，两个真诚的人慢慢靠近。曾经的求而不得终将释怀，双向奔赴的喜欢才最珍贵。褪去普通学生的身份，林寻只想以真心换真心。十八岁的夏天，最好的相遇，最甜的恋爱，才刚刚开始。</x:v>
+        <x:v>清河村的沈青禾，捡回被乡绅钱大年弃置损毁的土地神像。得神指点，她以神土盘活家中盐碱死地，凭勤恳耕作换来温饱。大旱骤至，贪念作祟的钱大年巧取资源，肆意挥霍地力。当山洪汹汹迫近，沈青禾忍痛舍弃心血田地，保全三村百姓。土地无言，终究厚待懂得索取亦懂得回馈的耕者。</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -3366,36 +3395,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B32" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C32" s="10" t="str">
-        <x:v>我把真心留给真心的人</x:v>
+        <x:v>重回失事当晚，我扣下整条跑道</x:v>
       </x:c>
       <x:c r="D32" s="11" t="str">
-        <x:v>09-16 11:20</x:v>
+        <x:v>09-17 06:08</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F32" s="11" t="str">
-        <x:v>↑12位</x:v>
+        <x:v>↑10位</x:v>
       </x:c>
       <x:c r="G32" s="11" t="str"/>
       <x:c r="H32" s="11" t="str"/>
       <x:c r="I32" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J32" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K32" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="L32" s="11" t="str">
-        <x:v>逆命漫剧场</x:v>
+        <x:v>星漫剧院</x:v>
       </x:c>
       <x:c r="M32" s="10" t="str">
-        <x:v>失散二十年的方小树意外归家，却被大哥二姐当成乞丐嫌弃，唯有三姐方秀兰护着他。一次受伤让他恢复记忆，为看清人心，他选择继续装傻。面对亲人的贪婪算计、骗钱逼婚与恶意陷害，小树一次次反击，也因救命之恩得到顾家、沈家相助，并与沈清月渐生真情。最终，他揭开被拐真相，惩治恶人，守住亲情与爱情，迎来人生逆袭。</x:v>
+        <x:v>上一世，一场诡异空难，塔台管制员谢昀含冤惨死。重生回到悲剧前夜，十五架学生无人机尽数落地，领导、师生、全网都逼她签字开放跑道。所有人都认定危险已经解除，可她笃定空域还藏着未知黑影。顶着限时命令与铺天盖地非议死扛复核。那看不见的第十六架，究竟是谁布下的致命陷阱？</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -3403,36 +3432,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B33" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C33" s="10" t="str">
-        <x:v>守成包子铺</x:v>
+        <x:v>七零：穿成锦鲤文里的炮灰女配</x:v>
       </x:c>
       <x:c r="D33" s="11" t="str">
-        <x:v>09-15 16:00</x:v>
+        <x:v>09-16 17:00</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F33" s="11" t="str">
-        <x:v>↑11位</x:v>
+        <x:v>↑7位</x:v>
       </x:c>
       <x:c r="G33" s="11" t="str"/>
       <x:c r="H33" s="11" t="str"/>
       <x:c r="I33" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="J33" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K33" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>年代怀旧 / 战神异能</x:v>
       </x:c>
       <x:c r="L33" s="11" t="str">
-        <x:v>空白漫</x:v>
+        <x:v>小树动漫剧场</x:v>
       </x:c>
       <x:c r="M33" s="10" t="str">
-        <x:v>周守成经营八年的早餐铺被迫搬走，熟客流失、徒弟离开，新店第一天一百多个包子无人问津。面对低价竞争和经营困境，他没有偷工减料，而是从菜贩、司机、工地和学生家长的真实需求出发，重新摸索预订与配送。靠一笼笼热包子和一次次准时守信，他终于让偏僻小店重新有了烟火气。守住一门小生意，靠的从来不是门脸，而是手艺、诚信和顾客愿意再来的信任。</x:v>
+        <x:v>现代女孩温梨穿越到七十年代小说，成为结局悲惨的炮灰女配，她抢先激活沉香木牌中的灵泉空间，凭借敏锐察觉化解列车上的重大隐患，得到官方表彰，为下乡做好铺垫；来到红星公社后，温梨依靠灵泉水强化体质，不再被白眼狼郭彩霞道德绑架，还截胡了本该属于女主姜月儿的机缘，她一边下地挣工分，一边利用空间物资在黑市与顾淮合作，面对姜月儿、江辰等人的屡次算计构陷，温梨从容反击，结识神秘知青陆泽川，改写自己注定悲剧的命运。</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -3440,36 +3469,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B34" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C34" s="10" t="str">
-        <x:v>被身高掩盖的谎言</x:v>
+        <x:v>王爷请封庶子为世子，我生下嫡子后他慌了</x:v>
       </x:c>
       <x:c r="D34" s="11" t="str">
-        <x:v>09-15 08:18</x:v>
+        <x:v>09-15 08:00</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F34" s="11" t="str">
-        <x:v>↑9位</x:v>
+        <x:v>↑6位</x:v>
       </x:c>
       <x:c r="G34" s="11" t="str"/>
       <x:c r="H34" s="11" t="str"/>
       <x:c r="I34" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J34" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K34" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="L34" s="11" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="M34" s="10" t="str">
-        <x:v>女孩林知晚回到命运转折的关键节点。她凭借智慧与勇气，敏锐察觉家中隐患，冷静引导家人、寻求帮助，用爱守护姐姐与全家。在共同努力下危机化解、正义伸张，一家人愈发珍视彼此，并且帮助到了更多有同样遭遇的人，最后迎来温暖安宁的幸福生活。</x:v>
+        <x:v>沈清韵嫁入靖王府三年，王爷冷落，侧妃得宠。王爷当众许诺，谁先诞下儿子，便请封世子。苏氏先怀孕，沈清韵却发现自己怀的是龙凤胎，她隐瞒消息，买通太医推迟产期，忍痛让苏氏先产子。王爷果然请封庶长子为世子，折子递入宗人府。受理之后，沈清韵才发动，生下龙凤胎。太后与皇上视为祥瑞，下旨赐嫡子承恩为靖王世子、嫡女承华为安乐郡主。王爷措手不及，苏氏地位一落千丈。而沈清韵知道，这只是第一步。</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -3477,16 +3506,16 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B35" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C35" s="10" t="str">
-        <x:v>重回失事当晚，我扣下整条跑道</x:v>
+        <x:v>我把真心留给真心的人</x:v>
       </x:c>
       <x:c r="D35" s="11" t="str">
-        <x:v>09-17 06:08</x:v>
+        <x:v>09-16 11:20</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F35" s="11" t="str">
         <x:v>↑6位</x:v>
@@ -3494,19 +3523,19 @@
       <x:c r="G35" s="11" t="str"/>
       <x:c r="H35" s="11" t="str"/>
       <x:c r="I35" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J35" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K35" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L35" s="11" t="str">
-        <x:v>星漫剧院</x:v>
+        <x:v>逆命漫剧场</x:v>
       </x:c>
       <x:c r="M35" s="10" t="str">
-        <x:v>上一世，一场诡异空难，塔台管制员谢昀含冤惨死。重生回到悲剧前夜，十五架学生无人机尽数落地，领导、师生、全网都逼她签字开放跑道。所有人都认定危险已经解除，可她笃定空域还藏着未知黑影。顶着限时命令与铺天盖地非议死扛复核。那看不见的第十六架，究竟是谁布下的致命陷阱？</x:v>
+        <x:v>失散二十年的方小树意外归家，却被大哥二姐当成乞丐嫌弃，唯有三姐方秀兰护着他。一次受伤让他恢复记忆，为看清人心，他选择继续装傻。面对亲人的贪婪算计、骗钱逼婚与恶意陷害，小树一次次反击，也因救命之恩得到顾家、沈家相助，并与沈清月渐生真情。最终，他揭开被拐真相，惩治恶人，守住亲情与爱情，迎来人生逆袭。</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -3514,53 +3543,47 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B36" s="11" t="n">
-        <x:v>46</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C36" s="10" t="str">
-        <x:v>浮世红痕</x:v>
+        <x:v>一墙隔冷暖，五年借暖终归零</x:v>
       </x:c>
       <x:c r="D36" s="11" t="str">
-        <x:v>09-16 07:58</x:v>
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F36" s="11" t="str">
-        <x:v>↑6位</x:v>
+        <x:v>↑5位</x:v>
       </x:c>
       <x:c r="G36" s="11" t="str"/>
       <x:c r="H36" s="11" t="str"/>
-      <x:c r="I36" s="11" t="n">
-        <x:v>52</x:v>
-      </x:c>
+      <x:c r="I36" s="11" t="str"/>
       <x:c r="J36" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K36" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L36" s="11" t="str">
-        <x:v>久久漫剧</x:v>
-      </x:c>
-      <x:c r="M36" s="10" t="str">
-        <x:v>乔舒天生拥有一项特殊能力——能看见连接亲密男女的隐秘红线。她以此选定了看似专一的未婚夫陆宥泽，却在婚礼前夜，赫然发现他与自己闺蜜许澜之间缠上了红线。婚礼现场她当众揭露真相，果断终止婚约。此后她凭借异能开设“红线鉴渣工作室”，帮深陷情感疑云的人勘破真心，而更多意想不到的考验与纠葛也随之而来。</x:v>
-      </x:c>
+      <x:c r="L36" s="11" t="str"/>
+      <x:c r="M36" s="10" t="str"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B37" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C37" s="10" t="str">
-        <x:v>敢泼我馄饨，整条街都别要了</x:v>
+        <x:v>说好九十天就回来，我不等了</x:v>
       </x:c>
       <x:c r="D37" s="11" t="str">
-        <x:v>09-16 10:00</x:v>
+        <x:v>09-16 06:00</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F37" s="11" t="str">
         <x:v>↑4位</x:v>
@@ -3568,7 +3591,7 @@
       <x:c r="G37" s="11" t="str"/>
       <x:c r="H37" s="11" t="str"/>
       <x:c r="I37" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J37" s="10" t="str">
         <x:v>其他</x:v>
@@ -3577,10 +3600,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L37" s="11" t="str">
-        <x:v>治愈 AI 恋</x:v>
+        <x:v>小宁漫漫</x:v>
       </x:c>
       <x:c r="M37" s="10" t="str">
-        <x:v>南桥旧街投资人许总多年悉心扶持一众商户，给予租金减免与基建投入，可赵川等人却贪念作祟，撕毁协议，还刻意编造谎言煽动网络暴力。面对恩将仇报的局面，许总没有冲动行事，而是恪守契约精神，凭借完备证据通过合法途径理性维权。随着真相公之于众，造谣闹事者自食恶果，承担起违约带来的相应代价。旧街完成焕新升级，充分彰显出法律与规则守护公平正义的强大力量。</x:v>
+        <x:v>周衡挣脱错位的旧感情，坚守原则，专注医疗事业，打磨救死扶伤的星桥心泵。他与叶宁彼此尊重，感情建立在坦诚与边界之上，不盲目牺牲自我，平等相伴走向未来。林夏历经挫折后幡然醒悟，承担自己犯下的过错，放下执念踏实努力，靠双手重新经营人生。故事告诉人不必困在原地等候错的人，真心不该沦为候补，每个人都可以告别过往，奔赴属于自己的前路</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -3588,36 +3611,36 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B38" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C38" s="10" t="str">
-        <x:v>养娃记：八零四合院生活日常</x:v>
+        <x:v>老板砍薪，我买下酒楼</x:v>
       </x:c>
       <x:c r="D38" s="11" t="str">
-        <x:v>09-15 01:11</x:v>
+        <x:v>09-15 18:11</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F38" s="11" t="str">
-        <x:v>↑4位</x:v>
+        <x:v>↑3位</x:v>
       </x:c>
       <x:c r="G38" s="11" t="str"/>
       <x:c r="H38" s="11" t="str"/>
       <x:c r="I38" s="11" t="n">
-        <x:v>191</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="J38" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K38" s="10" t="str">
-        <x:v>年代怀旧 / 萌宝治愈</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="L38" s="11" t="str">
-        <x:v>香菜薯片</x:v>
+        <x:v>逸漫</x:v>
       </x:c>
       <x:c r="M38" s="10" t="str">
-        <x:v>儿女已经成家立业，送走公公婆婆后，正准备全国游的六十多岁老太太赵锦舒重生了。重回到刚进城几个月时，那时什么都不懂，乡下来的年轻小媳妇脸皮薄，抹不开面子，也自卑，哪怕男人能挣钱，面对有权有势的婆家人，也自觉低人一头，更怕出错，给男人丢脸，很长一段时间都不敢多说一句话，明里暗里娘三个受了不少委屈。回到年轻时，赵锦舒老黄瓜刷绿漆，不管外表如何，内里都是老姜疙瘩，装不来腼腆小媳妇。</x:v>
+        <x:v>在美娟大酒楼掌勺十五年的林桂芬，因待遇调整选择离开。面对场地偏远和客户观望，她从老粮库重新起步，凭过硬手艺与真诚待客赢回乡亲认可。从十二桌寿宴到四十桌婚宴，生意越做越红火。后来，她再次走进昔日酒楼，这一次，不是回来打工，而是带着自己的招牌开启新生活。</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -3625,16 +3648,16 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B39" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C39" s="10" t="str">
-        <x:v>被诬陷诊出喜脉，重活一世我逆转前尘</x:v>
+        <x:v>萌娃兽语满级，动物园天天爆红</x:v>
       </x:c>
       <x:c r="D39" s="11" t="str">
-        <x:v>09-16 07:58</x:v>
+        <x:v>09-16 10:00</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F39" s="11" t="str">
         <x:v>↑3位</x:v>
@@ -3642,19 +3665,19 @@
       <x:c r="G39" s="11" t="str"/>
       <x:c r="H39" s="11" t="str"/>
       <x:c r="I39" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="J39" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K39" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>萌宝治愈 / 战神异能</x:v>
       </x:c>
       <x:c r="L39" s="11" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>一口漫剧</x:v>
       </x:c>
       <x:c r="M39" s="10" t="str">
-        <x:v>沈清瑶重生回到被“神医”姜辞诬陷喜脉那天。前世她因此身败名裂，被迫嫁给竹马萧景渊，后来才知这是两人为替姜辞上位设的局。这一世，她不再任人宰割，巧妙将诊脉丝线系在谢老夫人腕上，当众揭穿姜辞。萧景渊谎称“孩子是我的”，却被她揭发与姜辞的私情，两人丑态毕露。谢家震怒，姜辞被强嫁萧景渊，沈清瑶嫁入侯府。婚后她冷静布局，让萧景渊与姜辞内斗升级。最终姜辞伏法，沈清瑶挣脱前世枷锁。可重生真能让她彻底自由吗？</x:v>
+        <x:v>八岁女孩汤圆拥有听懂动物语言的特殊能力，助力濒临倒闭的自家动物园破局重生。她读懂动物的内心诉求，化解人与动物之间的认知误解，坚守科学救助理念，拒绝猎奇表演。动物园成为科普教育阵地，传递尊重生命、人与自然和谐共生的理念，以孩童的善意守护生灵，诠释新时代少年的社会担当。</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -3662,84 +3685,84 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B40" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C40" s="10" t="str">
-        <x:v>糯糯下山，师兄们都慌了第三季</x:v>
+        <x:v>穿越后我带全家吃肉</x:v>
       </x:c>
       <x:c r="D40" s="11" t="str">
-        <x:v>09-17 00:06</x:v>
+        <x:v>2026-09-16</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F40" s="11" t="str">
         <x:v>↑3位</x:v>
       </x:c>
       <x:c r="G40" s="11" t="str"/>
       <x:c r="H40" s="11" t="str"/>
-      <x:c r="I40" s="11" t="n">
-        <x:v>152</x:v>
-      </x:c>
+      <x:c r="I40" s="11" t="str"/>
       <x:c r="J40" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K40" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L40" s="11" t="str">
-        <x:v>青椒剪辑</x:v>
-      </x:c>
-      <x:c r="M40" s="10" t="str">
-        <x:v>六岁那年，云糯糯被师父派下山历练，顺便寻找失散多年的五位师兄。她本以为师兄们只是普通修士，生活过得不太好。可随着她一路寻找，才发现大师兄竟是镇压天下的九天仙尊，二师兄是统御九幽的魔界帝君，三师兄是丹道圣人。小奶娃背着一柄破旧黑铁巨剑，带着上古异兽，一路闯荡修仙界，顺手把五位绝世大佬师兄全部喊回了家。</x:v>
-      </x:c>
+        <x:v>美食治愈</x:v>
+      </x:c>
+      <x:c r="L40" s="11" t="str"/>
+      <x:c r="M40" s="10" t="str"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B41" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C41" s="10" t="str">
-        <x:v>瘦身归来，前男友悔不当初</x:v>
+        <x:v>敢泼我馄饨，整条街都别要了</x:v>
       </x:c>
       <x:c r="D41" s="11" t="str">
-        <x:v>2026-09-16</x:v>
+        <x:v>09-16 10:00</x:v>
       </x:c>
       <x:c r="E41" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F41" s="11" t="str">
-        <x:v>↑3位</x:v>
+        <x:v>↑2位</x:v>
       </x:c>
       <x:c r="G41" s="11" t="str"/>
       <x:c r="H41" s="11" t="str"/>
-      <x:c r="I41" s="11" t="str"/>
+      <x:c r="I41" s="11" t="n">
+        <x:v>71</x:v>
+      </x:c>
       <x:c r="J41" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K41" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
-      </x:c>
-      <x:c r="L41" s="11" t="str"/>
-      <x:c r="M41" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L41" s="11" t="str">
+        <x:v>治愈 AI 恋</x:v>
+      </x:c>
+      <x:c r="M41" s="10" t="str">
+        <x:v>南桥旧街投资人许总多年悉心扶持一众商户，给予租金减免与基建投入，可赵川等人却贪念作祟，撕毁协议，还刻意编造谎言煽动网络暴力。面对恩将仇报的局面，许总没有冲动行事，而是恪守契约精神，凭借完备证据通过合法途径理性维权。随着真相公之于众，造谣闹事者自食恶果，承担起违约带来的相应代价。旧街完成焕新升级，充分彰显出法律与规则守护公平正义的强大力量。</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B42" s="11" t="n">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C42" s="10" t="str">
-        <x:v>情深错付</x:v>
+        <x:v>剑道：贴地武夫，谁教他练剑起飞的</x:v>
       </x:c>
       <x:c r="D42" s="11" t="str">
-        <x:v>09-15 15:27</x:v>
+        <x:v>09-16 17:23</x:v>
       </x:c>
       <x:c r="E42" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F42" s="11" t="str">
         <x:v>↑1位</x:v>
@@ -3747,19 +3770,19 @@
       <x:c r="G42" s="11" t="str"/>
       <x:c r="H42" s="11" t="str"/>
       <x:c r="I42" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J42" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K42" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷 / 婚姻情感</x:v>
       </x:c>
       <x:c r="L42" s="11" t="str">
-        <x:v>沐光剧场</x:v>
+        <x:v>繁星剧场</x:v>
       </x:c>
       <x:c r="M42" s="10" t="str">
-        <x:v>苏橙橙倒追陆深两年，却始终没等来一句承认。一次争执后，她被当众羞辱，车祸重伤时更亲眼看见陆深先救走白月光李芸。彻底清醒后，她拉黑、离职、离城，重新开始。等陆深终于看清真心、拼命追回时，她早已放下。三年后重逢，他以为她已结婚生子，最终带着遗憾彻底错过。</x:v>
+        <x:v>八境武夫秦关遵师命下山履约，遭逢嫌弃退婚，最终娶了替嫁的病危大小姐南柔。世人皆笑他是个没丹田的废物，殊不知他乃肉身无敌的满级大佬，更暗中觉醒混沌体，剑武双修！他反手治好娇妻，助其觉醒太阴圣体。面对豪门天骄的挑衅、灵剑学院的追杀、中州刀圣的降临，乃至龙云帝国的皇权威逼，秦关皆以一双铁拳强势轰爆！管你剑皇刀圣还是九五之尊，敢惹我老婆，通通骨灰扬了！且看无敌武夫如何带着傲娇黑塔与腹黑神犬，一路护妻狂飙</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -3767,16 +3790,16 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B43" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C43" s="10" t="str">
-        <x:v>七零：穿成锦鲤文里的炮灰女配</x:v>
+        <x:v>我都元婴期了，你跟我说开学</x:v>
       </x:c>
       <x:c r="D43" s="11" t="str">
-        <x:v>09-16 17:00</x:v>
+        <x:v>09-16 00:10</x:v>
       </x:c>
       <x:c r="E43" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F43" s="11" t="str">
         <x:v>↑1位</x:v>
@@ -3784,19 +3807,19 @@
       <x:c r="G43" s="11" t="str"/>
       <x:c r="H43" s="11" t="str"/>
       <x:c r="I43" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="J43" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K43" s="10"